--- a/Copa del Mundo-2026 trabajo.xlsx
+++ b/Copa del Mundo-2026 trabajo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_corporativa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{4B119FBF-818B-466F-B1F3-AB97609A7929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BEA33BE-94C5-4ADD-BB47-3B501F65E901}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{4B119FBF-818B-466F-B1F3-AB97609A7929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{073A29A9-3FE6-425F-96CB-066F72E934CD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1664,6 +1664,180 @@
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="9" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="9" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
@@ -1679,196 +1853,14 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="9" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="9" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1880,12 +1872,28 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1896,20 +1904,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2524,17 +2524,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
       <c r="J1" s="43">
         <v>1</v>
       </c>
@@ -2656,9 +2656,9 @@
       <c r="F2" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="101"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="145"/>
+      <c r="I2" s="146"/>
       <c r="J2" s="45" t="s">
         <v>153</v>
       </c>
@@ -2790,160 +2790,160 @@
       <c r="F3" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="102" t="s">
+      <c r="G3" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="H3" s="102"/>
+      <c r="H3" s="147"/>
       <c r="I3" s="60" t="s">
         <v>8</v>
       </c>
       <c r="J3" s="67">
         <f>SUM(J4+J5)-SUM(J6+J7)</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K3" s="68">
         <f>SUM(K4+K5)-SUM(K6+K7)</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L3" s="68">
         <f>SUM(L4+L5)-SUM(L6+L7)</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M3" s="68">
         <f>SUM(M4+M5)-SUM(M6+M7)</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N3" s="68">
         <f>SUM(N4+N5)-SUM(N6+N7)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O3" s="68">
         <f>SUM(O4+O5)-SUM(O6+O7)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P3" s="68">
         <f>SUM(P4+P5)-SUM(P6+P7)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Q3" s="68">
         <f>SUM(Q4+Q5)-SUM(Q6+Q7)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R3" s="68">
         <f>SUM(R4+R5)-SUM(R6+R7)</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="S3" s="68">
         <f>SUM(S4+S5)-SUM(S6+S7)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T3" s="68">
         <f>SUM(T4+T5)-SUM(T6+T7)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="U3" s="68">
         <f>SUM(U4+U5)-SUM(U6+U7)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V3" s="68">
         <f>SUM(V4+V5)-SUM(V6+V7)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W3" s="68">
         <f>SUM(W4+W5)-SUM(W6+W7)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="X3" s="68">
         <f>SUM(X4+X5)-SUM(X6+X7)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y3" s="68">
         <f>SUM(Y4+Y5)-SUM(Y6+Y7)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="68">
         <f>SUM(Z4+Z5)-SUM(Z6+Z7)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AA3" s="68">
         <f>SUM(AA4+AA5)-SUM(AA6+AA7)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AB3" s="68">
         <f>SUM(AB4+AB5)-SUM(AB6+AB7)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AC3" s="68">
         <f>SUM(AC4+AC5)-SUM(AC6+AC7)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AD3" s="68">
         <f>SUM(AD4+AD5)-SUM(AD6+AD7)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE3" s="68">
         <f>SUM(AE4+AE5)-SUM(AE6+AE7)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AF3" s="68">
         <f>SUM(AF4+AF5)-SUM(AF6+AF7)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AG3" s="68">
         <f>SUM(AG4+AG5)-SUM(AG6+AG7)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH3" s="68">
         <f>SUM(AH4+AH5)-SUM(AH6+AH7)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI3" s="68">
         <f>SUM(AI4+AI5)-SUM(AI6+AI7)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AJ3" s="68">
         <f>SUM(AJ4+AJ5)-SUM(AJ6+AJ7)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AK3" s="68">
         <f>SUM(AK4+AK5)-SUM(AK6+AK7)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AL3" s="68">
         <f>SUM(AL4+AL5)-SUM(AL6+AL7)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AM3" s="68">
         <f>SUM(AM4+AM5)-SUM(AM6+AM7)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AN3" s="68">
         <f>SUM(AN4+AN5)-SUM(AN6+AN7)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AO3" s="68">
         <f>SUM(AO4+AO5)-SUM(AO6+AO7)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AP3" s="68">
         <f>SUM(AP4+AP5)-SUM(AP6+AP7)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AQ3" s="68">
         <f>SUM(AQ4+AQ5)-SUM(AQ6+AQ7)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AR3" s="68">
         <f>SUM(AR4+AR5)-SUM(AR6+AR7)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AS3" s="68">
         <f>SUM(AS4+AS5)-SUM(AS6+AS7)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AT3" s="69">
         <f>SUM(AT4+AT5)-SUM(AT6+AT7)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:54" ht="14.4" x14ac:dyDescent="0.3">
@@ -2959,187 +2959,187 @@
       <c r="J4" s="72">
         <f>SUM(IF(J8=$I$8,3,0)+IF(J9=$G8+$H8,1,0)+IF(J10=$I$10,3,0)+IF(J11=$G10+$H10,1,0)+IF(J12=$I$12,3,0)+IF(J13=$G12+$H12,1,0)+IF(J14=$I$14,3,0)+IF(J15=$G14+$H14,1,0)
 +IF(J16=$I$16,3,0)+IF(J17=$G16+$H16,1,0)+IF(J18=$I$18,3,0)+IF(J19=$G18+$H18,1,0)+IF(J20=$I$20,3,0)+IF(J21=$G20+$H20,1,0)+IF(J22=$I$22,3,0)+IF(J23=$G22+$H22,1,0)+IF(J24=$I$24,3,0)+IF(J25=$G24+$H24,1,0)+IF(J26=$I$26,3,0)+IF(J27=$G26+$H26,1,0)+IF(J28=$I$28,3,0)+IF(J29=$G28+$H28,1,0)+IF(J30=$I$30,3,0)+IF(J31=$G30+$H30,1,0)+IF(J32=$I$32,3,0)+IF(J33=$G32+$H32,1,0)+IF(J34=$I$34,3,0)+IF(J35=$G34+$H34,1,0)+IF(J36=$I$36,3,0)+IF(J37=$G36+$H36,1,0)+IF(J38=$I$38,3,0)+IF(J39=$G38+$H38,1,0)+IF(J40=$I$40,3,0)+IF(J41=$G40+$H40,1,0)+IF(J42=$I$42,3,0)+IF(J43=$G42+$H42,1,0)+IF(J44=$I$44,3,0)+IF(J45=$G44+$H44,1,0)+IF(J46=$I$46,3,0)+IF(J47=$G46+$H46,1,0)+IF(J48=$I$48,3,0)+IF(J49=$G48+$H48,1,0)+IF(J50=$I$50,3,0)+IF(J51=$G50+$H50,1,0)+IF(J52=$I$52,3,0)+IF(J53=$G52+$H52,1,0)+IF(J54=$I$54,3,0)+IF(J55=$G54+$H54,1,0)+IF(J56=$I$56,3,0)+IF(J57=$G56+$H56,1,0)+IF(J58=$I$58,3,0)+IF(J59=$G58+$H58,1,0)+IF(J60=$I$60,3,0)+IF(J61=$G60+$H60,1,0)+IF(J62=$I$62,3,0)+IF(J63=$G62+$H62,1,0)+IF(J64=$I$64,3,0)+IF(J65=$G64+$H64,1,0)+IF(J66=$I$66,3,0)+IF(J67=$G66+$H66,1,0)+IF(J68=$I$68,3,0)+IF(J69=$G68+$H68,1,0)+IF(J70=$I$70,3,0)+IF(J71=$G70+$H70,1,0)+IF(J72=$I$72,3,0)+IF(J73=$G72+$H72,1,0)+IF(J74=$I$74,3,0)+IF(J75=$G74+$H74,1,0)+IF(J76=$I$76,3,0)+IF(J77=$G76+$H76,1,0)+IF(J78=$I$78,3,0)+IF(J79=$G78+$H78,1,0))</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K4" s="73">
         <f>SUM(IF(K8=$I$8,3,0)+IF(K9=$G8+$H8,1,0)+IF(K10=$I$10,3,0)+IF(K11=$G10+$H10,1,0)+IF(K12=$I$12,3,0)+IF(K13=$G12+$H12,1,0)+IF(K14=$I$14,3,0)+IF(K15=$G14+$H14,1,0)
 +IF(K16=$I$16,3,0)+IF(K17=$G16+$H16,1,0)+IF(K18=$I$18,3,0)+IF(K19=$G18+$H18,1,0)+IF(K20=$I$20,3,0)+IF(K21=$G20+$H20,1,0)+IF(K22=$I$22,3,0)+IF(K23=$G22+$H22,1,0)+IF(K24=$I$24,3,0)+IF(K25=$G24+$H24,1,0)+IF(K26=$I$26,3,0)+IF(K27=$G26+$H26,1,0)+IF(K28=$I$28,3,0)+IF(K29=$G28+$H28,1,0)+IF(K30=$I$30,3,0)+IF(K31=$G30+$H30,1,0)+IF(K32=$I$32,3,0)+IF(K33=$G32+$H32,1,0)+IF(K34=$I$34,3,0)+IF(K35=$G34+$H34,1,0)+IF(K36=$I$36,3,0)+IF(K37=$G36+$H36,1,0)+IF(K38=$I$38,3,0)+IF(K39=$G38+$H38,1,0)+IF(K40=$I$40,3,0)+IF(K41=$G40+$H40,1,0)+IF(K42=$I$42,3,0)+IF(K43=$G42+$H42,1,0)+IF(K44=$I$44,3,0)+IF(K45=$G44+$H44,1,0)+IF(K46=$I$46,3,0)+IF(K47=$G46+$H46,1,0)+IF(K48=$I$48,3,0)+IF(K49=$G48+$H48,1,0)+IF(K50=$I$50,3,0)+IF(K51=$G50+$H50,1,0)+IF(K52=$I$52,3,0)+IF(K53=$G52+$H52,1,0)+IF(K54=$I$54,3,0)+IF(K55=$G54+$H54,1,0)+IF(K56=$I$56,3,0)+IF(K57=$G56+$H56,1,0)+IF(K58=$I$58,3,0)+IF(K59=$G58+$H58,1,0)+IF(K60=$I$60,3,0)+IF(K61=$G60+$H60,1,0)+IF(K62=$I$62,3,0)+IF(K63=$G62+$H62,1,0)+IF(K64=$I$64,3,0)+IF(K65=$G64+$H64,1,0)+IF(K66=$I$66,3,0)+IF(K67=$G66+$H66,1,0)+IF(K68=$I$68,3,0)+IF(K69=$G68+$H68,1,0)+IF(K70=$I$70,3,0)+IF(K71=$G70+$H70,1,0)+IF(K72=$I$72,3,0)+IF(K73=$G72+$H72,1,0)+IF(K74=$I$74,3,0)+IF(K75=$G74+$H74,1,0)+IF(K76=$I$76,3,0)+IF(K77=$G76+$H76,1,0)+IF(K78=$I$78,3,0)+IF(K79=$G78+$H78,1,0))</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L4" s="73">
         <f>SUM(IF(L8=$I$8,3,0)+IF(L9=$G8+$H8,1,0)+IF(L10=$I$10,3,0)+IF(L11=$G10+$H10,1,0)+IF(L12=$I$12,3,0)+IF(L13=$G12+$H12,1,0)+IF(L14=$I$14,3,0)+IF(L15=$G14+$H14,1,0)
 +IF(L16=$I$16,3,0)+IF(L17=$G16+$H16,1,0)+IF(L18=$I$18,3,0)+IF(L19=$G18+$H18,1,0)+IF(L20=$I$20,3,0)+IF(L21=$G20+$H20,1,0)+IF(L22=$I$22,3,0)+IF(L23=$G22+$H22,1,0)+IF(L24=$I$24,3,0)+IF(L25=$G24+$H24,1,0)+IF(L26=$I$26,3,0)+IF(L27=$G26+$H26,1,0)+IF(L28=$I$28,3,0)+IF(L29=$G28+$H28,1,0)+IF(L30=$I$30,3,0)+IF(L31=$G30+$H30,1,0)+IF(L32=$I$32,3,0)+IF(L33=$G32+$H32,1,0)+IF(L34=$I$34,3,0)+IF(L35=$G34+$H34,1,0)+IF(L36=$I$36,3,0)+IF(L37=$G36+$H36,1,0)+IF(L38=$I$38,3,0)+IF(L39=$G38+$H38,1,0)+IF(L40=$I$40,3,0)+IF(L41=$G40+$H40,1,0)+IF(L42=$I$42,3,0)+IF(L43=$G42+$H42,1,0)+IF(L44=$I$44,3,0)+IF(L45=$G44+$H44,1,0)+IF(L46=$I$46,3,0)+IF(L47=$G46+$H46,1,0)+IF(L48=$I$48,3,0)+IF(L49=$G48+$H48,1,0)+IF(L50=$I$50,3,0)+IF(L51=$G50+$H50,1,0)+IF(L52=$I$52,3,0)+IF(L53=$G52+$H52,1,0)+IF(L54=$I$54,3,0)+IF(L55=$G54+$H54,1,0)+IF(L56=$I$56,3,0)+IF(L57=$G56+$H56,1,0)+IF(L58=$I$58,3,0)+IF(L59=$G58+$H58,1,0)+IF(L60=$I$60,3,0)+IF(L61=$G60+$H60,1,0)+IF(L62=$I$62,3,0)+IF(L63=$G62+$H62,1,0)+IF(L64=$I$64,3,0)+IF(L65=$G64+$H64,1,0)+IF(L66=$I$66,3,0)+IF(L67=$G66+$H66,1,0)+IF(L68=$I$68,3,0)+IF(L69=$G68+$H68,1,0)+IF(L70=$I$70,3,0)+IF(L71=$G70+$H70,1,0)+IF(L72=$I$72,3,0)+IF(L73=$G72+$H72,1,0)+IF(L74=$I$74,3,0)+IF(L75=$G74+$H74,1,0)+IF(L76=$I$76,3,0)+IF(L77=$G76+$H76,1,0)+IF(L78=$I$78,3,0)+IF(L79=$G78+$H78,1,0))</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M4" s="73">
         <f>SUM(IF(M8=$I$8,3,0)+IF(M9=$G8+$H8,1,0)+IF(M10=$I$10,3,0)+IF(M11=$G10+$H10,1,0)+IF(M12=$I$12,3,0)+IF(M13=$G12+$H12,1,0)+IF(M14=$I$14,3,0)+IF(M15=$G14+$H14,1,0)
 +IF(M16=$I$16,3,0)+IF(M17=$G16+$H16,1,0)+IF(M18=$I$18,3,0)+IF(M19=$G18+$H18,1,0)+IF(M20=$I$20,3,0)+IF(M21=$G20+$H20,1,0)+IF(M22=$I$22,3,0)+IF(M23=$G22+$H22,1,0)+IF(M24=$I$24,3,0)+IF(M25=$G24+$H24,1,0)+IF(M26=$I$26,3,0)+IF(M27=$G26+$H26,1,0)+IF(M28=$I$28,3,0)+IF(M29=$G28+$H28,1,0)+IF(M30=$I$30,3,0)+IF(M31=$G30+$H30,1,0)+IF(M32=$I$32,3,0)+IF(M33=$G32+$H32,1,0)+IF(M34=$I$34,3,0)+IF(M35=$G34+$H34,1,0)+IF(M36=$I$36,3,0)+IF(M37=$G36+$H36,1,0)+IF(M38=$I$38,3,0)+IF(M39=$G38+$H38,1,0)+IF(M40=$I$40,3,0)+IF(M41=$G40+$H40,1,0)+IF(M42=$I$42,3,0)+IF(M43=$G42+$H42,1,0)+IF(M44=$I$44,3,0)+IF(M45=$G44+$H44,1,0)+IF(M46=$I$46,3,0)+IF(M47=$G46+$H46,1,0)+IF(M48=$I$48,3,0)+IF(M49=$G48+$H48,1,0)+IF(M50=$I$50,3,0)+IF(M51=$G50+$H50,1,0)+IF(M52=$I$52,3,0)+IF(M53=$G52+$H52,1,0)+IF(M54=$I$54,3,0)+IF(M55=$G54+$H54,1,0)+IF(M56=$I$56,3,0)+IF(M57=$G56+$H56,1,0)+IF(M58=$I$58,3,0)+IF(M59=$G58+$H58,1,0)+IF(M60=$I$60,3,0)+IF(M61=$G60+$H60,1,0)+IF(M62=$I$62,3,0)+IF(M63=$G62+$H62,1,0)+IF(M64=$I$64,3,0)+IF(M65=$G64+$H64,1,0)+IF(M66=$I$66,3,0)+IF(M67=$G66+$H66,1,0)+IF(M68=$I$68,3,0)+IF(M69=$G68+$H68,1,0)+IF(M70=$I$70,3,0)+IF(M71=$G70+$H70,1,0)+IF(M72=$I$72,3,0)+IF(M73=$G72+$H72,1,0)+IF(M74=$I$74,3,0)+IF(M75=$G74+$H74,1,0)+IF(M76=$I$76,3,0)+IF(M77=$G76+$H76,1,0)+IF(M78=$I$78,3,0)+IF(M79=$G78+$H78,1,0))</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N4" s="73">
         <f>SUM(IF(N8=$I$8,3,0)+IF(N9=$G8+$H8,1,0)+IF(N10=$I$10,3,0)+IF(N11=$G10+$H10,1,0)+IF(N12=$I$12,3,0)+IF(N13=$G12+$H12,1,0)+IF(N14=$I$14,3,0)+IF(N15=$G14+$H14,1,0)
 +IF(N16=$I$16,3,0)+IF(N17=$G16+$H16,1,0)+IF(N18=$I$18,3,0)+IF(N19=$G18+$H18,1,0)+IF(N20=$I$20,3,0)+IF(N21=$G20+$H20,1,0)+IF(N22=$I$22,3,0)+IF(N23=$G22+$H22,1,0)+IF(N24=$I$24,3,0)+IF(N25=$G24+$H24,1,0)+IF(N26=$I$26,3,0)+IF(N27=$G26+$H26,1,0)+IF(N28=$I$28,3,0)+IF(N29=$G28+$H28,1,0)+IF(N30=$I$30,3,0)+IF(N31=$G30+$H30,1,0)+IF(N32=$I$32,3,0)+IF(N33=$G32+$H32,1,0)+IF(N34=$I$34,3,0)+IF(N35=$G34+$H34,1,0)+IF(N36=$I$36,3,0)+IF(N37=$G36+$H36,1,0)+IF(N38=$I$38,3,0)+IF(N39=$G38+$H38,1,0)+IF(N40=$I$40,3,0)+IF(N41=$G40+$H40,1,0)+IF(N42=$I$42,3,0)+IF(N43=$G42+$H42,1,0)+IF(N44=$I$44,3,0)+IF(N45=$G44+$H44,1,0)+IF(N46=$I$46,3,0)+IF(N47=$G46+$H46,1,0)+IF(N48=$I$48,3,0)+IF(N49=$G48+$H48,1,0)+IF(N50=$I$50,3,0)+IF(N51=$G50+$H50,1,0)+IF(N52=$I$52,3,0)+IF(N53=$G52+$H52,1,0)+IF(N54=$I$54,3,0)+IF(N55=$G54+$H54,1,0)+IF(N56=$I$56,3,0)+IF(N57=$G56+$H56,1,0)+IF(N58=$I$58,3,0)+IF(N59=$G58+$H58,1,0)+IF(N60=$I$60,3,0)+IF(N61=$G60+$H60,1,0)+IF(N62=$I$62,3,0)+IF(N63=$G62+$H62,1,0)+IF(N64=$I$64,3,0)+IF(N65=$G64+$H64,1,0)+IF(N66=$I$66,3,0)+IF(N67=$G66+$H66,1,0)+IF(N68=$I$68,3,0)+IF(N69=$G68+$H68,1,0)+IF(N70=$I$70,3,0)+IF(N71=$G70+$H70,1,0)+IF(N72=$I$72,3,0)+IF(N73=$G72+$H72,1,0)+IF(N74=$I$74,3,0)+IF(N75=$G74+$H74,1,0)+IF(N76=$I$76,3,0)+IF(N77=$G76+$H76,1,0)+IF(N78=$I$78,3,0)+IF(N79=$G78+$H78,1,0))</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O4" s="73">
         <f>SUM(IF(O8=$I$8,3,0)+IF(O9=$G8+$H8,1,0)+IF(O10=$I$10,3,0)+IF(O11=$G10+$H10,1,0)+IF(O12=$I$12,3,0)+IF(O13=$G12+$H12,1,0)+IF(O14=$I$14,3,0)+IF(O15=$G14+$H14,1,0)
 +IF(O16=$I$16,3,0)+IF(O17=$G16+$H16,1,0)+IF(O18=$I$18,3,0)+IF(O19=$G18+$H18,1,0)+IF(O20=$I$20,3,0)+IF(O21=$G20+$H20,1,0)+IF(O22=$I$22,3,0)+IF(O23=$G22+$H22,1,0)+IF(O24=$I$24,3,0)+IF(O25=$G24+$H24,1,0)+IF(O26=$I$26,3,0)+IF(O27=$G26+$H26,1,0)+IF(O28=$I$28,3,0)+IF(O29=$G28+$H28,1,0)+IF(O30=$I$30,3,0)+IF(O31=$G30+$H30,1,0)+IF(O32=$I$32,3,0)+IF(O33=$G32+$H32,1,0)+IF(O34=$I$34,3,0)+IF(O35=$G34+$H34,1,0)+IF(O36=$I$36,3,0)+IF(O37=$G36+$H36,1,0)+IF(O38=$I$38,3,0)+IF(O39=$G38+$H38,1,0)+IF(O40=$I$40,3,0)+IF(O41=$G40+$H40,1,0)+IF(O42=$I$42,3,0)+IF(O43=$G42+$H42,1,0)+IF(O44=$I$44,3,0)+IF(O45=$G44+$H44,1,0)+IF(O46=$I$46,3,0)+IF(O47=$G46+$H46,1,0)+IF(O48=$I$48,3,0)+IF(O49=$G48+$H48,1,0)+IF(O50=$I$50,3,0)+IF(O51=$G50+$H50,1,0)+IF(O52=$I$52,3,0)+IF(O53=$G52+$H52,1,0)+IF(O54=$I$54,3,0)+IF(O55=$G54+$H54,1,0)+IF(O56=$I$56,3,0)+IF(O57=$G56+$H56,1,0)+IF(O58=$I$58,3,0)+IF(O59=$G58+$H58,1,0)+IF(O60=$I$60,3,0)+IF(O61=$G60+$H60,1,0)+IF(O62=$I$62,3,0)+IF(O63=$G62+$H62,1,0)+IF(O64=$I$64,3,0)+IF(O65=$G64+$H64,1,0)+IF(O66=$I$66,3,0)+IF(O67=$G66+$H66,1,0)+IF(O68=$I$68,3,0)+IF(O69=$G68+$H68,1,0)+IF(O70=$I$70,3,0)+IF(O71=$G70+$H70,1,0)+IF(O72=$I$72,3,0)+IF(O73=$G72+$H72,1,0)+IF(O74=$I$74,3,0)+IF(O75=$G74+$H74,1,0)+IF(O76=$I$76,3,0)+IF(O77=$G76+$H76,1,0)+IF(O78=$I$78,3,0)+IF(O79=$G78+$H78,1,0))</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P4" s="73">
         <f>SUM(IF(P8=$I$8,3,0)+IF(P9=$G8+$H8,1,0)+IF(P10=$I$10,3,0)+IF(P11=$G10+$H10,1,0)+IF(P12=$I$12,3,0)+IF(P13=$G12+$H12,1,0)+IF(P14=$I$14,3,0)+IF(P15=$G14+$H14,1,0)
 +IF(P16=$I$16,3,0)+IF(P17=$G16+$H16,1,0)+IF(P18=$I$18,3,0)+IF(P19=$G18+$H18,1,0)+IF(P20=$I$20,3,0)+IF(P21=$G20+$H20,1,0)+IF(P22=$I$22,3,0)+IF(P23=$G22+$H22,1,0)+IF(P24=$I$24,3,0)+IF(P25=$G24+$H24,1,0)+IF(P26=$I$26,3,0)+IF(P27=$G26+$H26,1,0)+IF(P28=$I$28,3,0)+IF(P29=$G28+$H28,1,0)+IF(P30=$I$30,3,0)+IF(P31=$G30+$H30,1,0)+IF(P32=$I$32,3,0)+IF(P33=$G32+$H32,1,0)+IF(P34=$I$34,3,0)+IF(P35=$G34+$H34,1,0)+IF(P36=$I$36,3,0)+IF(P37=$G36+$H36,1,0)+IF(P38=$I$38,3,0)+IF(P39=$G38+$H38,1,0)+IF(P40=$I$40,3,0)+IF(P41=$G40+$H40,1,0)+IF(P42=$I$42,3,0)+IF(P43=$G42+$H42,1,0)+IF(P44=$I$44,3,0)+IF(P45=$G44+$H44,1,0)+IF(P46=$I$46,3,0)+IF(P47=$G46+$H46,1,0)+IF(P48=$I$48,3,0)+IF(P49=$G48+$H48,1,0)+IF(P50=$I$50,3,0)+IF(P51=$G50+$H50,1,0)+IF(P52=$I$52,3,0)+IF(P53=$G52+$H52,1,0)+IF(P54=$I$54,3,0)+IF(P55=$G54+$H54,1,0)+IF(P56=$I$56,3,0)+IF(P57=$G56+$H56,1,0)+IF(P58=$I$58,3,0)+IF(P59=$G58+$H58,1,0)+IF(P60=$I$60,3,0)+IF(P61=$G60+$H60,1,0)+IF(P62=$I$62,3,0)+IF(P63=$G62+$H62,1,0)+IF(P64=$I$64,3,0)+IF(P65=$G64+$H64,1,0)+IF(P66=$I$66,3,0)+IF(P67=$G66+$H66,1,0)+IF(P68=$I$68,3,0)+IF(P69=$G68+$H68,1,0)+IF(P70=$I$70,3,0)+IF(P71=$G70+$H70,1,0)+IF(P72=$I$72,3,0)+IF(P73=$G72+$H72,1,0)+IF(P74=$I$74,3,0)+IF(P75=$G74+$H74,1,0)+IF(P76=$I$76,3,0)+IF(P77=$G76+$H76,1,0)+IF(P78=$I$78,3,0)+IF(P79=$G78+$H78,1,0))</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Q4" s="73">
         <f>SUM(IF(Q8=$I$8,3,0)+IF(Q9=$G8+$H8,1,0)+IF(Q10=$I$10,3,0)+IF(Q11=$G10+$H10,1,0)+IF(Q12=$I$12,3,0)+IF(Q13=$G12+$H12,1,0)+IF(Q14=$I$14,3,0)+IF(Q15=$G14+$H14,1,0)
 +IF(Q16=$I$16,3,0)+IF(Q17=$G16+$H16,1,0)+IF(Q18=$I$18,3,0)+IF(Q19=$G18+$H18,1,0)+IF(Q20=$I$20,3,0)+IF(Q21=$G20+$H20,1,0)+IF(Q22=$I$22,3,0)+IF(Q23=$G22+$H22,1,0)+IF(Q24=$I$24,3,0)+IF(Q25=$G24+$H24,1,0)+IF(Q26=$I$26,3,0)+IF(Q27=$G26+$H26,1,0)+IF(Q28=$I$28,3,0)+IF(Q29=$G28+$H28,1,0)+IF(Q30=$I$30,3,0)+IF(Q31=$G30+$H30,1,0)+IF(Q32=$I$32,3,0)+IF(Q33=$G32+$H32,1,0)+IF(Q34=$I$34,3,0)+IF(Q35=$G34+$H34,1,0)+IF(Q36=$I$36,3,0)+IF(Q37=$G36+$H36,1,0)+IF(Q38=$I$38,3,0)+IF(Q39=$G38+$H38,1,0)+IF(Q40=$I$40,3,0)+IF(Q41=$G40+$H40,1,0)+IF(Q42=$I$42,3,0)+IF(Q43=$G42+$H42,1,0)+IF(Q44=$I$44,3,0)+IF(Q45=$G44+$H44,1,0)+IF(Q46=$I$46,3,0)+IF(Q47=$G46+$H46,1,0)+IF(Q48=$I$48,3,0)+IF(Q49=$G48+$H48,1,0)+IF(Q50=$I$50,3,0)+IF(Q51=$G50+$H50,1,0)+IF(Q52=$I$52,3,0)+IF(Q53=$G52+$H52,1,0)+IF(Q54=$I$54,3,0)+IF(Q55=$G54+$H54,1,0)+IF(Q56=$I$56,3,0)+IF(Q57=$G56+$H56,1,0)+IF(Q58=$I$58,3,0)+IF(Q59=$G58+$H58,1,0)+IF(Q60=$I$60,3,0)+IF(Q61=$G60+$H60,1,0)+IF(Q62=$I$62,3,0)+IF(Q63=$G62+$H62,1,0)+IF(Q64=$I$64,3,0)+IF(Q65=$G64+$H64,1,0)+IF(Q66=$I$66,3,0)+IF(Q67=$G66+$H66,1,0)+IF(Q68=$I$68,3,0)+IF(Q69=$G68+$H68,1,0)+IF(Q70=$I$70,3,0)+IF(Q71=$G70+$H70,1,0)+IF(Q72=$I$72,3,0)+IF(Q73=$G72+$H72,1,0)+IF(Q74=$I$74,3,0)+IF(Q75=$G74+$H74,1,0)+IF(Q76=$I$76,3,0)+IF(Q77=$G76+$H76,1,0)+IF(Q78=$I$78,3,0)+IF(Q79=$G78+$H78,1,0))</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R4" s="73">
         <f>SUM(IF(R8=$I$8,3,0)+IF(R9=$G8+$H8,1,0)+IF(R10=$I$10,3,0)+IF(R11=$G10+$H10,1,0)+IF(R12=$I$12,3,0)+IF(R13=$G12+$H12,1,0)+IF(R14=$I$14,3,0)+IF(R15=$G14+$H14,1,0)
 +IF(R16=$I$16,3,0)+IF(R17=$G16+$H16,1,0)+IF(R18=$I$18,3,0)+IF(R19=$G18+$H18,1,0)+IF(R20=$I$20,3,0)+IF(R21=$G20+$H20,1,0)+IF(R22=$I$22,3,0)+IF(R23=$G22+$H22,1,0)+IF(R24=$I$24,3,0)+IF(R25=$G24+$H24,1,0)+IF(R26=$I$26,3,0)+IF(R27=$G26+$H26,1,0)+IF(R28=$I$28,3,0)+IF(R29=$G28+$H28,1,0)+IF(R30=$I$30,3,0)+IF(R31=$G30+$H30,1,0)+IF(R32=$I$32,3,0)+IF(R33=$G32+$H32,1,0)+IF(R34=$I$34,3,0)+IF(R35=$G34+$H34,1,0)+IF(R36=$I$36,3,0)+IF(R37=$G36+$H36,1,0)+IF(R38=$I$38,3,0)+IF(R39=$G38+$H38,1,0)+IF(R40=$I$40,3,0)+IF(R41=$G40+$H40,1,0)+IF(R42=$I$42,3,0)+IF(R43=$G42+$H42,1,0)+IF(R44=$I$44,3,0)+IF(R45=$G44+$H44,1,0)+IF(R46=$I$46,3,0)+IF(R47=$G46+$H46,1,0)+IF(R48=$I$48,3,0)+IF(R49=$G48+$H48,1,0)+IF(R50=$I$50,3,0)+IF(R51=$G50+$H50,1,0)+IF(R52=$I$52,3,0)+IF(R53=$G52+$H52,1,0)+IF(R54=$I$54,3,0)+IF(R55=$G54+$H54,1,0)+IF(R56=$I$56,3,0)+IF(R57=$G56+$H56,1,0)+IF(R58=$I$58,3,0)+IF(R59=$G58+$H58,1,0)+IF(R60=$I$60,3,0)+IF(R61=$G60+$H60,1,0)+IF(R62=$I$62,3,0)+IF(R63=$G62+$H62,1,0)+IF(R64=$I$64,3,0)+IF(R65=$G64+$H64,1,0)+IF(R66=$I$66,3,0)+IF(R67=$G66+$H66,1,0)+IF(R68=$I$68,3,0)+IF(R69=$G68+$H68,1,0)+IF(R70=$I$70,3,0)+IF(R71=$G70+$H70,1,0)+IF(R72=$I$72,3,0)+IF(R73=$G72+$H72,1,0)+IF(R74=$I$74,3,0)+IF(R75=$G74+$H74,1,0)+IF(R76=$I$76,3,0)+IF(R77=$G76+$H76,1,0)+IF(R78=$I$78,3,0)+IF(R79=$G78+$H78,1,0))</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="S4" s="73">
         <f>SUM(IF(S8=$I$8,3,0)+IF(S9=$G8+$H8,1,0)+IF(S10=$I$10,3,0)+IF(S11=$G10+$H10,1,0)+IF(S12=$I$12,3,0)+IF(S13=$G12+$H12,1,0)+IF(S14=$I$14,3,0)+IF(S15=$G14+$H14,1,0)
 +IF(S16=$I$16,3,0)+IF(S17=$G16+$H16,1,0)+IF(S18=$I$18,3,0)+IF(S19=$G18+$H18,1,0)+IF(S20=$I$20,3,0)+IF(S21=$G20+$H20,1,0)+IF(S22=$I$22,3,0)+IF(S23=$G22+$H22,1,0)+IF(S24=$I$24,3,0)+IF(S25=$G24+$H24,1,0)+IF(S26=$I$26,3,0)+IF(S27=$G26+$H26,1,0)+IF(S28=$I$28,3,0)+IF(S29=$G28+$H28,1,0)+IF(S30=$I$30,3,0)+IF(S31=$G30+$H30,1,0)+IF(S32=$I$32,3,0)+IF(S33=$G32+$H32,1,0)+IF(S34=$I$34,3,0)+IF(S35=$G34+$H34,1,0)+IF(S36=$I$36,3,0)+IF(S37=$G36+$H36,1,0)+IF(S38=$I$38,3,0)+IF(S39=$G38+$H38,1,0)+IF(S40=$I$40,3,0)+IF(S41=$G40+$H40,1,0)+IF(S42=$I$42,3,0)+IF(S43=$G42+$H42,1,0)+IF(S44=$I$44,3,0)+IF(S45=$G44+$H44,1,0)+IF(S46=$I$46,3,0)+IF(S47=$G46+$H46,1,0)+IF(S48=$I$48,3,0)+IF(S49=$G48+$H48,1,0)+IF(S50=$I$50,3,0)+IF(S51=$G50+$H50,1,0)+IF(S52=$I$52,3,0)+IF(S53=$G52+$H52,1,0)+IF(S54=$I$54,3,0)+IF(S55=$G54+$H54,1,0)+IF(S56=$I$56,3,0)+IF(S57=$G56+$H56,1,0)+IF(S58=$I$58,3,0)+IF(S59=$G58+$H58,1,0)+IF(S60=$I$60,3,0)+IF(S61=$G60+$H60,1,0)+IF(S62=$I$62,3,0)+IF(S63=$G62+$H62,1,0)+IF(S64=$I$64,3,0)+IF(S65=$G64+$H64,1,0)+IF(S66=$I$66,3,0)+IF(S67=$G66+$H66,1,0)+IF(S68=$I$68,3,0)+IF(S69=$G68+$H68,1,0)+IF(S70=$I$70,3,0)+IF(S71=$G70+$H70,1,0)+IF(S72=$I$72,3,0)+IF(S73=$G72+$H72,1,0)+IF(S74=$I$74,3,0)+IF(S75=$G74+$H74,1,0)+IF(S76=$I$76,3,0)+IF(S77=$G76+$H76,1,0)+IF(S78=$I$78,3,0)+IF(S79=$G78+$H78,1,0))</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T4" s="73">
         <f>SUM(IF(T8=$I$8,3,0)+IF(T9=$G8+$H8,1,0)+IF(T10=$I$10,3,0)+IF(T11=$G10+$H10,1,0)+IF(T12=$I$12,3,0)+IF(T13=$G12+$H12,1,0)+IF(T14=$I$14,3,0)+IF(T15=$G14+$H14,1,0)
 +IF(T16=$I$16,3,0)+IF(T17=$G16+$H16,1,0)+IF(T18=$I$18,3,0)+IF(T19=$G18+$H18,1,0)+IF(T20=$I$20,3,0)+IF(T21=$G20+$H20,1,0)+IF(T22=$I$22,3,0)+IF(T23=$G22+$H22,1,0)+IF(T24=$I$24,3,0)+IF(T25=$G24+$H24,1,0)+IF(T26=$I$26,3,0)+IF(T27=$G26+$H26,1,0)+IF(T28=$I$28,3,0)+IF(T29=$G28+$H28,1,0)+IF(T30=$I$30,3,0)+IF(T31=$G30+$H30,1,0)+IF(T32=$I$32,3,0)+IF(T33=$G32+$H32,1,0)+IF(T34=$I$34,3,0)+IF(T35=$G34+$H34,1,0)+IF(T36=$I$36,3,0)+IF(T37=$G36+$H36,1,0)+IF(T38=$I$38,3,0)+IF(T39=$G38+$H38,1,0)+IF(T40=$I$40,3,0)+IF(T41=$G40+$H40,1,0)+IF(T42=$I$42,3,0)+IF(T43=$G42+$H42,1,0)+IF(T44=$I$44,3,0)+IF(T45=$G44+$H44,1,0)+IF(T46=$I$46,3,0)+IF(T47=$G46+$H46,1,0)+IF(T48=$I$48,3,0)+IF(T49=$G48+$H48,1,0)+IF(T50=$I$50,3,0)+IF(T51=$G50+$H50,1,0)+IF(T52=$I$52,3,0)+IF(T53=$G52+$H52,1,0)+IF(T54=$I$54,3,0)+IF(T55=$G54+$H54,1,0)+IF(T56=$I$56,3,0)+IF(T57=$G56+$H56,1,0)+IF(T58=$I$58,3,0)+IF(T59=$G58+$H58,1,0)+IF(T60=$I$60,3,0)+IF(T61=$G60+$H60,1,0)+IF(T62=$I$62,3,0)+IF(T63=$G62+$H62,1,0)+IF(T64=$I$64,3,0)+IF(T65=$G64+$H64,1,0)+IF(T66=$I$66,3,0)+IF(T67=$G66+$H66,1,0)+IF(T68=$I$68,3,0)+IF(T69=$G68+$H68,1,0)+IF(T70=$I$70,3,0)+IF(T71=$G70+$H70,1,0)+IF(T72=$I$72,3,0)+IF(T73=$G72+$H72,1,0)+IF(T74=$I$74,3,0)+IF(T75=$G74+$H74,1,0)+IF(T76=$I$76,3,0)+IF(T77=$G76+$H76,1,0)+IF(T78=$I$78,3,0)+IF(T79=$G78+$H78,1,0))</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U4" s="73">
         <f>SUM(IF(U8=$I$8,3,0)+IF(U9=$G8+$H8,1,0)+IF(U10=$I$10,3,0)+IF(U11=$G10+$H10,1,0)+IF(U12=$I$12,3,0)+IF(U13=$G12+$H12,1,0)+IF(U14=$I$14,3,0)+IF(U15=$G14+$H14,1,0)
 +IF(U16=$I$16,3,0)+IF(U17=$G16+$H16,1,0)+IF(U18=$I$18,3,0)+IF(U19=$G18+$H18,1,0)+IF(U20=$I$20,3,0)+IF(U21=$G20+$H20,1,0)+IF(U22=$I$22,3,0)+IF(U23=$G22+$H22,1,0)+IF(U24=$I$24,3,0)+IF(U25=$G24+$H24,1,0)+IF(U26=$I$26,3,0)+IF(U27=$G26+$H26,1,0)+IF(U28=$I$28,3,0)+IF(U29=$G28+$H28,1,0)+IF(U30=$I$30,3,0)+IF(U31=$G30+$H30,1,0)+IF(U32=$I$32,3,0)+IF(U33=$G32+$H32,1,0)+IF(U34=$I$34,3,0)+IF(U35=$G34+$H34,1,0)+IF(U36=$I$36,3,0)+IF(U37=$G36+$H36,1,0)+IF(U38=$I$38,3,0)+IF(U39=$G38+$H38,1,0)+IF(U40=$I$40,3,0)+IF(U41=$G40+$H40,1,0)+IF(U42=$I$42,3,0)+IF(U43=$G42+$H42,1,0)+IF(U44=$I$44,3,0)+IF(U45=$G44+$H44,1,0)+IF(U46=$I$46,3,0)+IF(U47=$G46+$H46,1,0)+IF(U48=$I$48,3,0)+IF(U49=$G48+$H48,1,0)+IF(U50=$I$50,3,0)+IF(U51=$G50+$H50,1,0)+IF(U52=$I$52,3,0)+IF(U53=$G52+$H52,1,0)+IF(U54=$I$54,3,0)+IF(U55=$G54+$H54,1,0)+IF(U56=$I$56,3,0)+IF(U57=$G56+$H56,1,0)+IF(U58=$I$58,3,0)+IF(U59=$G58+$H58,1,0)+IF(U60=$I$60,3,0)+IF(U61=$G60+$H60,1,0)+IF(U62=$I$62,3,0)+IF(U63=$G62+$H62,1,0)+IF(U64=$I$64,3,0)+IF(U65=$G64+$H64,1,0)+IF(U66=$I$66,3,0)+IF(U67=$G66+$H66,1,0)+IF(U68=$I$68,3,0)+IF(U69=$G68+$H68,1,0)+IF(U70=$I$70,3,0)+IF(U71=$G70+$H70,1,0)+IF(U72=$I$72,3,0)+IF(U73=$G72+$H72,1,0)+IF(U74=$I$74,3,0)+IF(U75=$G74+$H74,1,0)+IF(U76=$I$76,3,0)+IF(U77=$G76+$H76,1,0)+IF(U78=$I$78,3,0)+IF(U79=$G78+$H78,1,0))</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V4" s="73">
         <f>SUM(IF(V8=$I$8,3,0)+IF(V9=$G8+$H8,1,0)+IF(V10=$I$10,3,0)+IF(V11=$G10+$H10,1,0)+IF(V12=$I$12,3,0)+IF(V13=$G12+$H12,1,0)+IF(V14=$I$14,3,0)+IF(V15=$G14+$H14,1,0)
 +IF(V16=$I$16,3,0)+IF(V17=$G16+$H16,1,0)+IF(V18=$I$18,3,0)+IF(V19=$G18+$H18,1,0)+IF(V20=$I$20,3,0)+IF(V21=$G20+$H20,1,0)+IF(V22=$I$22,3,0)+IF(V23=$G22+$H22,1,0)+IF(V24=$I$24,3,0)+IF(V25=$G24+$H24,1,0)+IF(V26=$I$26,3,0)+IF(V27=$G26+$H26,1,0)+IF(V28=$I$28,3,0)+IF(V29=$G28+$H28,1,0)+IF(V30=$I$30,3,0)+IF(V31=$G30+$H30,1,0)+IF(V32=$I$32,3,0)+IF(V33=$G32+$H32,1,0)+IF(V34=$I$34,3,0)+IF(V35=$G34+$H34,1,0)+IF(V36=$I$36,3,0)+IF(V37=$G36+$H36,1,0)+IF(V38=$I$38,3,0)+IF(V39=$G38+$H38,1,0)+IF(V40=$I$40,3,0)+IF(V41=$G40+$H40,1,0)+IF(V42=$I$42,3,0)+IF(V43=$G42+$H42,1,0)+IF(V44=$I$44,3,0)+IF(V45=$G44+$H44,1,0)+IF(V46=$I$46,3,0)+IF(V47=$G46+$H46,1,0)+IF(V48=$I$48,3,0)+IF(V49=$G48+$H48,1,0)+IF(V50=$I$50,3,0)+IF(V51=$G50+$H50,1,0)+IF(V52=$I$52,3,0)+IF(V53=$G52+$H52,1,0)+IF(V54=$I$54,3,0)+IF(V55=$G54+$H54,1,0)+IF(V56=$I$56,3,0)+IF(V57=$G56+$H56,1,0)+IF(V58=$I$58,3,0)+IF(V59=$G58+$H58,1,0)+IF(V60=$I$60,3,0)+IF(V61=$G60+$H60,1,0)+IF(V62=$I$62,3,0)+IF(V63=$G62+$H62,1,0)+IF(V64=$I$64,3,0)+IF(V65=$G64+$H64,1,0)+IF(V66=$I$66,3,0)+IF(V67=$G66+$H66,1,0)+IF(V68=$I$68,3,0)+IF(V69=$G68+$H68,1,0)+IF(V70=$I$70,3,0)+IF(V71=$G70+$H70,1,0)+IF(V72=$I$72,3,0)+IF(V73=$G72+$H72,1,0)+IF(V74=$I$74,3,0)+IF(V75=$G74+$H74,1,0)+IF(V76=$I$76,3,0)+IF(V77=$G76+$H76,1,0)+IF(V78=$I$78,3,0)+IF(V79=$G78+$H78,1,0))</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W4" s="73">
         <f>SUM(IF(W8=$I$8,3,0)+IF(W9=$G8+$H8,1,0)+IF(W10=$I$10,3,0)+IF(W11=$G10+$H10,1,0)+IF(W12=$I$12,3,0)+IF(W13=$G12+$H12,1,0)+IF(W14=$I$14,3,0)+IF(W15=$G14+$H14,1,0)
 +IF(W16=$I$16,3,0)+IF(W17=$G16+$H16,1,0)+IF(W18=$I$18,3,0)+IF(W19=$G18+$H18,1,0)+IF(W20=$I$20,3,0)+IF(W21=$G20+$H20,1,0)+IF(W22=$I$22,3,0)+IF(W23=$G22+$H22,1,0)+IF(W24=$I$24,3,0)+IF(W25=$G24+$H24,1,0)+IF(W26=$I$26,3,0)+IF(W27=$G26+$H26,1,0)+IF(W28=$I$28,3,0)+IF(W29=$G28+$H28,1,0)+IF(W30=$I$30,3,0)+IF(W31=$G30+$H30,1,0)+IF(W32=$I$32,3,0)+IF(W33=$G32+$H32,1,0)+IF(W34=$I$34,3,0)+IF(W35=$G34+$H34,1,0)+IF(W36=$I$36,3,0)+IF(W37=$G36+$H36,1,0)+IF(W38=$I$38,3,0)+IF(W39=$G38+$H38,1,0)+IF(W40=$I$40,3,0)+IF(W41=$G40+$H40,1,0)+IF(W42=$I$42,3,0)+IF(W43=$G42+$H42,1,0)+IF(W44=$I$44,3,0)+IF(W45=$G44+$H44,1,0)+IF(W46=$I$46,3,0)+IF(W47=$G46+$H46,1,0)+IF(W48=$I$48,3,0)+IF(W49=$G48+$H48,1,0)+IF(W50=$I$50,3,0)+IF(W51=$G50+$H50,1,0)+IF(W52=$I$52,3,0)+IF(W53=$G52+$H52,1,0)+IF(W54=$I$54,3,0)+IF(W55=$G54+$H54,1,0)+IF(W56=$I$56,3,0)+IF(W57=$G56+$H56,1,0)+IF(W58=$I$58,3,0)+IF(W59=$G58+$H58,1,0)+IF(W60=$I$60,3,0)+IF(W61=$G60+$H60,1,0)+IF(W62=$I$62,3,0)+IF(W63=$G62+$H62,1,0)+IF(W64=$I$64,3,0)+IF(W65=$G64+$H64,1,0)+IF(W66=$I$66,3,0)+IF(W67=$G66+$H66,1,0)+IF(W68=$I$68,3,0)+IF(W69=$G68+$H68,1,0)+IF(W70=$I$70,3,0)+IF(W71=$G70+$H70,1,0)+IF(W72=$I$72,3,0)+IF(W73=$G72+$H72,1,0)+IF(W74=$I$74,3,0)+IF(W75=$G74+$H74,1,0)+IF(W76=$I$76,3,0)+IF(W77=$G76+$H76,1,0)+IF(W78=$I$78,3,0)+IF(W79=$G78+$H78,1,0))</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="X4" s="73">
         <f>SUM(IF(X8=$I$8,3,0)+IF(X9=$G8+$H8,1,0)+IF(X10=$I$10,3,0)+IF(X11=$G10+$H10,1,0)+IF(X12=$I$12,3,0)+IF(X13=$G12+$H12,1,0)+IF(X14=$I$14,3,0)+IF(X15=$G14+$H14,1,0)
 +IF(X16=$I$16,3,0)+IF(X17=$G16+$H16,1,0)+IF(X18=$I$18,3,0)+IF(X19=$G18+$H18,1,0)+IF(X20=$I$20,3,0)+IF(X21=$G20+$H20,1,0)+IF(X22=$I$22,3,0)+IF(X23=$G22+$H22,1,0)+IF(X24=$I$24,3,0)+IF(X25=$G24+$H24,1,0)+IF(X26=$I$26,3,0)+IF(X27=$G26+$H26,1,0)+IF(X28=$I$28,3,0)+IF(X29=$G28+$H28,1,0)+IF(X30=$I$30,3,0)+IF(X31=$G30+$H30,1,0)+IF(X32=$I$32,3,0)+IF(X33=$G32+$H32,1,0)+IF(X34=$I$34,3,0)+IF(X35=$G34+$H34,1,0)+IF(X36=$I$36,3,0)+IF(X37=$G36+$H36,1,0)+IF(X38=$I$38,3,0)+IF(X39=$G38+$H38,1,0)+IF(X40=$I$40,3,0)+IF(X41=$G40+$H40,1,0)+IF(X42=$I$42,3,0)+IF(X43=$G42+$H42,1,0)+IF(X44=$I$44,3,0)+IF(X45=$G44+$H44,1,0)+IF(X46=$I$46,3,0)+IF(X47=$G46+$H46,1,0)+IF(X48=$I$48,3,0)+IF(X49=$G48+$H48,1,0)+IF(X50=$I$50,3,0)+IF(X51=$G50+$H50,1,0)+IF(X52=$I$52,3,0)+IF(X53=$G52+$H52,1,0)+IF(X54=$I$54,3,0)+IF(X55=$G54+$H54,1,0)+IF(X56=$I$56,3,0)+IF(X57=$G56+$H56,1,0)+IF(X58=$I$58,3,0)+IF(X59=$G58+$H58,1,0)+IF(X60=$I$60,3,0)+IF(X61=$G60+$H60,1,0)+IF(X62=$I$62,3,0)+IF(X63=$G62+$H62,1,0)+IF(X64=$I$64,3,0)+IF(X65=$G64+$H64,1,0)+IF(X66=$I$66,3,0)+IF(X67=$G66+$H66,1,0)+IF(X68=$I$68,3,0)+IF(X69=$G68+$H68,1,0)+IF(X70=$I$70,3,0)+IF(X71=$G70+$H70,1,0)+IF(X72=$I$72,3,0)+IF(X73=$G72+$H72,1,0)+IF(X74=$I$74,3,0)+IF(X75=$G74+$H74,1,0)+IF(X76=$I$76,3,0)+IF(X77=$G76+$H76,1,0)+IF(X78=$I$78,3,0)+IF(X79=$G78+$H78,1,0))</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y4" s="73">
         <f>SUM(IF(Y8=$I$8,3,0)+IF(Y9=$G8+$H8,1,0)+IF(Y10=$I$10,3,0)+IF(Y11=$G10+$H10,1,0)+IF(Y12=$I$12,3,0)+IF(Y13=$G12+$H12,1,0)+IF(Y14=$I$14,3,0)+IF(Y15=$G14+$H14,1,0)
 +IF(Y16=$I$16,3,0)+IF(Y17=$G16+$H16,1,0)+IF(Y18=$I$18,3,0)+IF(Y19=$G18+$H18,1,0)+IF(Y20=$I$20,3,0)+IF(Y21=$G20+$H20,1,0)+IF(Y22=$I$22,3,0)+IF(Y23=$G22+$H22,1,0)+IF(Y24=$I$24,3,0)+IF(Y25=$G24+$H24,1,0)+IF(Y26=$I$26,3,0)+IF(Y27=$G26+$H26,1,0)+IF(Y28=$I$28,3,0)+IF(Y29=$G28+$H28,1,0)+IF(Y30=$I$30,3,0)+IF(Y31=$G30+$H30,1,0)+IF(Y32=$I$32,3,0)+IF(Y33=$G32+$H32,1,0)+IF(Y34=$I$34,3,0)+IF(Y35=$G34+$H34,1,0)+IF(Y36=$I$36,3,0)+IF(Y37=$G36+$H36,1,0)+IF(Y38=$I$38,3,0)+IF(Y39=$G38+$H38,1,0)+IF(Y40=$I$40,3,0)+IF(Y41=$G40+$H40,1,0)+IF(Y42=$I$42,3,0)+IF(Y43=$G42+$H42,1,0)+IF(Y44=$I$44,3,0)+IF(Y45=$G44+$H44,1,0)+IF(Y46=$I$46,3,0)+IF(Y47=$G46+$H46,1,0)+IF(Y48=$I$48,3,0)+IF(Y49=$G48+$H48,1,0)+IF(Y50=$I$50,3,0)+IF(Y51=$G50+$H50,1,0)+IF(Y52=$I$52,3,0)+IF(Y53=$G52+$H52,1,0)+IF(Y54=$I$54,3,0)+IF(Y55=$G54+$H54,1,0)+IF(Y56=$I$56,3,0)+IF(Y57=$G56+$H56,1,0)+IF(Y58=$I$58,3,0)+IF(Y59=$G58+$H58,1,0)+IF(Y60=$I$60,3,0)+IF(Y61=$G60+$H60,1,0)+IF(Y62=$I$62,3,0)+IF(Y63=$G62+$H62,1,0)+IF(Y64=$I$64,3,0)+IF(Y65=$G64+$H64,1,0)+IF(Y66=$I$66,3,0)+IF(Y67=$G66+$H66,1,0)+IF(Y68=$I$68,3,0)+IF(Y69=$G68+$H68,1,0)+IF(Y70=$I$70,3,0)+IF(Y71=$G70+$H70,1,0)+IF(Y72=$I$72,3,0)+IF(Y73=$G72+$H72,1,0)+IF(Y74=$I$74,3,0)+IF(Y75=$G74+$H74,1,0)+IF(Y76=$I$76,3,0)+IF(Y77=$G76+$H76,1,0)+IF(Y78=$I$78,3,0)+IF(Y79=$G78+$H78,1,0))</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z4" s="73">
         <f>SUM(IF(Z8=$I$8,3,0)+IF(Z9=$G8+$H8,1,0)+IF(Z10=$I$10,3,0)+IF(Z11=$G10+$H10,1,0)+IF(Z12=$I$12,3,0)+IF(Z13=$G12+$H12,1,0)+IF(Z14=$I$14,3,0)+IF(Z15=$G14+$H14,1,0)
 +IF(Z16=$I$16,3,0)+IF(Z17=$G16+$H16,1,0)+IF(Z18=$I$18,3,0)+IF(Z19=$G18+$H18,1,0)+IF(Z20=$I$20,3,0)+IF(Z21=$G20+$H20,1,0)+IF(Z22=$I$22,3,0)+IF(Z23=$G22+$H22,1,0)+IF(Z24=$I$24,3,0)+IF(Z25=$G24+$H24,1,0)+IF(Z26=$I$26,3,0)+IF(Z27=$G26+$H26,1,0)+IF(Z28=$I$28,3,0)+IF(Z29=$G28+$H28,1,0)+IF(Z30=$I$30,3,0)+IF(Z31=$G30+$H30,1,0)+IF(Z32=$I$32,3,0)+IF(Z33=$G32+$H32,1,0)+IF(Z34=$I$34,3,0)+IF(Z35=$G34+$H34,1,0)+IF(Z36=$I$36,3,0)+IF(Z37=$G36+$H36,1,0)+IF(Z38=$I$38,3,0)+IF(Z39=$G38+$H38,1,0)+IF(Z40=$I$40,3,0)+IF(Z41=$G40+$H40,1,0)+IF(Z42=$I$42,3,0)+IF(Z43=$G42+$H42,1,0)+IF(Z44=$I$44,3,0)+IF(Z45=$G44+$H44,1,0)+IF(Z46=$I$46,3,0)+IF(Z47=$G46+$H46,1,0)+IF(Z48=$I$48,3,0)+IF(Z49=$G48+$H48,1,0)+IF(Z50=$I$50,3,0)+IF(Z51=$G50+$H50,1,0)+IF(Z52=$I$52,3,0)+IF(Z53=$G52+$H52,1,0)+IF(Z54=$I$54,3,0)+IF(Z55=$G54+$H54,1,0)+IF(Z56=$I$56,3,0)+IF(Z57=$G56+$H56,1,0)+IF(Z58=$I$58,3,0)+IF(Z59=$G58+$H58,1,0)+IF(Z60=$I$60,3,0)+IF(Z61=$G60+$H60,1,0)+IF(Z62=$I$62,3,0)+IF(Z63=$G62+$H62,1,0)+IF(Z64=$I$64,3,0)+IF(Z65=$G64+$H64,1,0)+IF(Z66=$I$66,3,0)+IF(Z67=$G66+$H66,1,0)+IF(Z68=$I$68,3,0)+IF(Z69=$G68+$H68,1,0)+IF(Z70=$I$70,3,0)+IF(Z71=$G70+$H70,1,0)+IF(Z72=$I$72,3,0)+IF(Z73=$G72+$H72,1,0)+IF(Z74=$I$74,3,0)+IF(Z75=$G74+$H74,1,0)+IF(Z76=$I$76,3,0)+IF(Z77=$G76+$H76,1,0)+IF(Z78=$I$78,3,0)+IF(Z79=$G78+$H78,1,0))</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AA4" s="73">
         <f>SUM(IF(AA8=$I$8,3,0)+IF(AA9=$G8+$H8,1,0)+IF(AA10=$I$10,3,0)+IF(AA11=$G10+$H10,1,0)+IF(AA12=$I$12,3,0)+IF(AA13=$G12+$H12,1,0)+IF(AA14=$I$14,3,0)+IF(AA15=$G14+$H14,1,0)
 +IF(AA16=$I$16,3,0)+IF(AA17=$G16+$H16,1,0)+IF(AA18=$I$18,3,0)+IF(AA19=$G18+$H18,1,0)+IF(AA20=$I$20,3,0)+IF(AA21=$G20+$H20,1,0)+IF(AA22=$I$22,3,0)+IF(AA23=$G22+$H22,1,0)+IF(AA24=$I$24,3,0)+IF(AA25=$G24+$H24,1,0)+IF(AA26=$I$26,3,0)+IF(AA27=$G26+$H26,1,0)+IF(AA28=$I$28,3,0)+IF(AA29=$G28+$H28,1,0)+IF(AA30=$I$30,3,0)+IF(AA31=$G30+$H30,1,0)+IF(AA32=$I$32,3,0)+IF(AA33=$G32+$H32,1,0)+IF(AA34=$I$34,3,0)+IF(AA35=$G34+$H34,1,0)+IF(AA36=$I$36,3,0)+IF(AA37=$G36+$H36,1,0)+IF(AA38=$I$38,3,0)+IF(AA39=$G38+$H38,1,0)+IF(AA40=$I$40,3,0)+IF(AA41=$G40+$H40,1,0)+IF(AA42=$I$42,3,0)+IF(AA43=$G42+$H42,1,0)+IF(AA44=$I$44,3,0)+IF(AA45=$G44+$H44,1,0)+IF(AA46=$I$46,3,0)+IF(AA47=$G46+$H46,1,0)+IF(AA48=$I$48,3,0)+IF(AA49=$G48+$H48,1,0)+IF(AA50=$I$50,3,0)+IF(AA51=$G50+$H50,1,0)+IF(AA52=$I$52,3,0)+IF(AA53=$G52+$H52,1,0)+IF(AA54=$I$54,3,0)+IF(AA55=$G54+$H54,1,0)+IF(AA56=$I$56,3,0)+IF(AA57=$G56+$H56,1,0)+IF(AA58=$I$58,3,0)+IF(AA59=$G58+$H58,1,0)+IF(AA60=$I$60,3,0)+IF(AA61=$G60+$H60,1,0)+IF(AA62=$I$62,3,0)+IF(AA63=$G62+$H62,1,0)+IF(AA64=$I$64,3,0)+IF(AA65=$G64+$H64,1,0)+IF(AA66=$I$66,3,0)+IF(AA67=$G66+$H66,1,0)+IF(AA68=$I$68,3,0)+IF(AA69=$G68+$H68,1,0)+IF(AA70=$I$70,3,0)+IF(AA71=$G70+$H70,1,0)+IF(AA72=$I$72,3,0)+IF(AA73=$G72+$H72,1,0)+IF(AA74=$I$74,3,0)+IF(AA75=$G74+$H74,1,0)+IF(AA76=$I$76,3,0)+IF(AA77=$G76+$H76,1,0)+IF(AA78=$I$78,3,0)+IF(AA79=$G78+$H78,1,0))</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AB4" s="73">
         <f>SUM(IF(AB8=$I$8,3,0)+IF(AB9=$G8+$H8,1,0)+IF(AB10=$I$10,3,0)+IF(AB11=$G10+$H10,1,0)+IF(AB12=$I$12,3,0)+IF(AB13=$G12+$H12,1,0)+IF(AB14=$I$14,3,0)+IF(AB15=$G14+$H14,1,0)
 +IF(AB16=$I$16,3,0)+IF(AB17=$G16+$H16,1,0)+IF(AB18=$I$18,3,0)+IF(AB19=$G18+$H18,1,0)+IF(AB20=$I$20,3,0)+IF(AB21=$G20+$H20,1,0)+IF(AB22=$I$22,3,0)+IF(AB23=$G22+$H22,1,0)+IF(AB24=$I$24,3,0)+IF(AB25=$G24+$H24,1,0)+IF(AB26=$I$26,3,0)+IF(AB27=$G26+$H26,1,0)+IF(AB28=$I$28,3,0)+IF(AB29=$G28+$H28,1,0)+IF(AB30=$I$30,3,0)+IF(AB31=$G30+$H30,1,0)+IF(AB32=$I$32,3,0)+IF(AB33=$G32+$H32,1,0)+IF(AB34=$I$34,3,0)+IF(AB35=$G34+$H34,1,0)+IF(AB36=$I$36,3,0)+IF(AB37=$G36+$H36,1,0)+IF(AB38=$I$38,3,0)+IF(AB39=$G38+$H38,1,0)+IF(AB40=$I$40,3,0)+IF(AB41=$G40+$H40,1,0)+IF(AB42=$I$42,3,0)+IF(AB43=$G42+$H42,1,0)+IF(AB44=$I$44,3,0)+IF(AB45=$G44+$H44,1,0)+IF(AB46=$I$46,3,0)+IF(AB47=$G46+$H46,1,0)+IF(AB48=$I$48,3,0)+IF(AB49=$G48+$H48,1,0)+IF(AB50=$I$50,3,0)+IF(AB51=$G50+$H50,1,0)+IF(AB52=$I$52,3,0)+IF(AB53=$G52+$H52,1,0)+IF(AB54=$I$54,3,0)+IF(AB55=$G54+$H54,1,0)+IF(AB56=$I$56,3,0)+IF(AB57=$G56+$H56,1,0)+IF(AB58=$I$58,3,0)+IF(AB59=$G58+$H58,1,0)+IF(AB60=$I$60,3,0)+IF(AB61=$G60+$H60,1,0)+IF(AB62=$I$62,3,0)+IF(AB63=$G62+$H62,1,0)+IF(AB64=$I$64,3,0)+IF(AB65=$G64+$H64,1,0)+IF(AB66=$I$66,3,0)+IF(AB67=$G66+$H66,1,0)+IF(AB68=$I$68,3,0)+IF(AB69=$G68+$H68,1,0)+IF(AB70=$I$70,3,0)+IF(AB71=$G70+$H70,1,0)+IF(AB72=$I$72,3,0)+IF(AB73=$G72+$H72,1,0)+IF(AB74=$I$74,3,0)+IF(AB75=$G74+$H74,1,0)+IF(AB76=$I$76,3,0)+IF(AB77=$G76+$H76,1,0)+IF(AB78=$I$78,3,0)+IF(AB79=$G78+$H78,1,0))</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AC4" s="73">
         <f>SUM(IF(AC8=$I$8,3,0)+IF(AC9=$G8+$H8,1,0)+IF(AC10=$I$10,3,0)+IF(AC11=$G10+$H10,1,0)+IF(AC12=$I$12,3,0)+IF(AC13=$G12+$H12,1,0)+IF(AC14=$I$14,3,0)+IF(AC15=$G14+$H14,1,0)
 +IF(AC16=$I$16,3,0)+IF(AC17=$G16+$H16,1,0)+IF(AC18=$I$18,3,0)+IF(AC19=$G18+$H18,1,0)+IF(AC20=$I$20,3,0)+IF(AC21=$G20+$H20,1,0)+IF(AC22=$I$22,3,0)+IF(AC23=$G22+$H22,1,0)+IF(AC24=$I$24,3,0)+IF(AC25=$G24+$H24,1,0)+IF(AC26=$I$26,3,0)+IF(AC27=$G26+$H26,1,0)+IF(AC28=$I$28,3,0)+IF(AC29=$G28+$H28,1,0)+IF(AC30=$I$30,3,0)+IF(AC31=$G30+$H30,1,0)+IF(AC32=$I$32,3,0)+IF(AC33=$G32+$H32,1,0)+IF(AC34=$I$34,3,0)+IF(AC35=$G34+$H34,1,0)+IF(AC36=$I$36,3,0)+IF(AC37=$G36+$H36,1,0)+IF(AC38=$I$38,3,0)+IF(AC39=$G38+$H38,1,0)+IF(AC40=$I$40,3,0)+IF(AC41=$G40+$H40,1,0)+IF(AC42=$I$42,3,0)+IF(AC43=$G42+$H42,1,0)+IF(AC44=$I$44,3,0)+IF(AC45=$G44+$H44,1,0)+IF(AC46=$I$46,3,0)+IF(AC47=$G46+$H46,1,0)+IF(AC48=$I$48,3,0)+IF(AC49=$G48+$H48,1,0)+IF(AC50=$I$50,3,0)+IF(AC51=$G50+$H50,1,0)+IF(AC52=$I$52,3,0)+IF(AC53=$G52+$H52,1,0)+IF(AC54=$I$54,3,0)+IF(AC55=$G54+$H54,1,0)+IF(AC56=$I$56,3,0)+IF(AC57=$G56+$H56,1,0)+IF(AC58=$I$58,3,0)+IF(AC59=$G58+$H58,1,0)+IF(AC60=$I$60,3,0)+IF(AC61=$G60+$H60,1,0)+IF(AC62=$I$62,3,0)+IF(AC63=$G62+$H62,1,0)+IF(AC64=$I$64,3,0)+IF(AC65=$G64+$H64,1,0)+IF(AC66=$I$66,3,0)+IF(AC67=$G66+$H66,1,0)+IF(AC68=$I$68,3,0)+IF(AC69=$G68+$H68,1,0)+IF(AC70=$I$70,3,0)+IF(AC71=$G70+$H70,1,0)+IF(AC72=$I$72,3,0)+IF(AC73=$G72+$H72,1,0)+IF(AC74=$I$74,3,0)+IF(AC75=$G74+$H74,1,0)+IF(AC76=$I$76,3,0)+IF(AC77=$G76+$H76,1,0)+IF(AC78=$I$78,3,0)+IF(AC79=$G78+$H78,1,0))</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AD4" s="73">
         <f>SUM(IF(AD8=$I$8,3,0)+IF(AD9=$G8+$H8,1,0)+IF(AD10=$I$10,3,0)+IF(AD11=$G10+$H10,1,0)+IF(AD12=$I$12,3,0)+IF(AD13=$G12+$H12,1,0)+IF(AD14=$I$14,3,0)+IF(AD15=$G14+$H14,1,0)
 +IF(AD16=$I$16,3,0)+IF(AD17=$G16+$H16,1,0)+IF(AD18=$I$18,3,0)+IF(AD19=$G18+$H18,1,0)+IF(AD20=$I$20,3,0)+IF(AD21=$G20+$H20,1,0)+IF(AD22=$I$22,3,0)+IF(AD23=$G22+$H22,1,0)+IF(AD24=$I$24,3,0)+IF(AD25=$G24+$H24,1,0)+IF(AD26=$I$26,3,0)+IF(AD27=$G26+$H26,1,0)+IF(AD28=$I$28,3,0)+IF(AD29=$G28+$H28,1,0)+IF(AD30=$I$30,3,0)+IF(AD31=$G30+$H30,1,0)+IF(AD32=$I$32,3,0)+IF(AD33=$G32+$H32,1,0)+IF(AD34=$I$34,3,0)+IF(AD35=$G34+$H34,1,0)+IF(AD36=$I$36,3,0)+IF(AD37=$G36+$H36,1,0)+IF(AD38=$I$38,3,0)+IF(AD39=$G38+$H38,1,0)+IF(AD40=$I$40,3,0)+IF(AD41=$G40+$H40,1,0)+IF(AD42=$I$42,3,0)+IF(AD43=$G42+$H42,1,0)+IF(AD44=$I$44,3,0)+IF(AD45=$G44+$H44,1,0)+IF(AD46=$I$46,3,0)+IF(AD47=$G46+$H46,1,0)+IF(AD48=$I$48,3,0)+IF(AD49=$G48+$H48,1,0)+IF(AD50=$I$50,3,0)+IF(AD51=$G50+$H50,1,0)+IF(AD52=$I$52,3,0)+IF(AD53=$G52+$H52,1,0)+IF(AD54=$I$54,3,0)+IF(AD55=$G54+$H54,1,0)+IF(AD56=$I$56,3,0)+IF(AD57=$G56+$H56,1,0)+IF(AD58=$I$58,3,0)+IF(AD59=$G58+$H58,1,0)+IF(AD60=$I$60,3,0)+IF(AD61=$G60+$H60,1,0)+IF(AD62=$I$62,3,0)+IF(AD63=$G62+$H62,1,0)+IF(AD64=$I$64,3,0)+IF(AD65=$G64+$H64,1,0)+IF(AD66=$I$66,3,0)+IF(AD67=$G66+$H66,1,0)+IF(AD68=$I$68,3,0)+IF(AD69=$G68+$H68,1,0)+IF(AD70=$I$70,3,0)+IF(AD71=$G70+$H70,1,0)+IF(AD72=$I$72,3,0)+IF(AD73=$G72+$H72,1,0)+IF(AD74=$I$74,3,0)+IF(AD75=$G74+$H74,1,0)+IF(AD76=$I$76,3,0)+IF(AD77=$G76+$H76,1,0)+IF(AD78=$I$78,3,0)+IF(AD79=$G78+$H78,1,0))</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AE4" s="73">
         <f>SUM(IF(AE8=$I$8,3,0)+IF(AE9=$G8+$H8,1,0)+IF(AE10=$I$10,3,0)+IF(AE11=$G10+$H10,1,0)+IF(AE12=$I$12,3,0)+IF(AE13=$G12+$H12,1,0)+IF(AE14=$I$14,3,0)+IF(AE15=$G14+$H14,1,0)
 +IF(AE16=$I$16,3,0)+IF(AE17=$G16+$H16,1,0)+IF(AE18=$I$18,3,0)+IF(AE19=$G18+$H18,1,0)+IF(AE20=$I$20,3,0)+IF(AE21=$G20+$H20,1,0)+IF(AE22=$I$22,3,0)+IF(AE23=$G22+$H22,1,0)+IF(AE24=$I$24,3,0)+IF(AE25=$G24+$H24,1,0)+IF(AE26=$I$26,3,0)+IF(AE27=$G26+$H26,1,0)+IF(AE28=$I$28,3,0)+IF(AE29=$G28+$H28,1,0)+IF(AE30=$I$30,3,0)+IF(AE31=$G30+$H30,1,0)+IF(AE32=$I$32,3,0)+IF(AE33=$G32+$H32,1,0)+IF(AE34=$I$34,3,0)+IF(AE35=$G34+$H34,1,0)+IF(AE36=$I$36,3,0)+IF(AE37=$G36+$H36,1,0)+IF(AE38=$I$38,3,0)+IF(AE39=$G38+$H38,1,0)+IF(AE40=$I$40,3,0)+IF(AE41=$G40+$H40,1,0)+IF(AE42=$I$42,3,0)+IF(AE43=$G42+$H42,1,0)+IF(AE44=$I$44,3,0)+IF(AE45=$G44+$H44,1,0)+IF(AE46=$I$46,3,0)+IF(AE47=$G46+$H46,1,0)+IF(AE48=$I$48,3,0)+IF(AE49=$G48+$H48,1,0)+IF(AE50=$I$50,3,0)+IF(AE51=$G50+$H50,1,0)+IF(AE52=$I$52,3,0)+IF(AE53=$G52+$H52,1,0)+IF(AE54=$I$54,3,0)+IF(AE55=$G54+$H54,1,0)+IF(AE56=$I$56,3,0)+IF(AE57=$G56+$H56,1,0)+IF(AE58=$I$58,3,0)+IF(AE59=$G58+$H58,1,0)+IF(AE60=$I$60,3,0)+IF(AE61=$G60+$H60,1,0)+IF(AE62=$I$62,3,0)+IF(AE63=$G62+$H62,1,0)+IF(AE64=$I$64,3,0)+IF(AE65=$G64+$H64,1,0)+IF(AE66=$I$66,3,0)+IF(AE67=$G66+$H66,1,0)+IF(AE68=$I$68,3,0)+IF(AE69=$G68+$H68,1,0)+IF(AE70=$I$70,3,0)+IF(AE71=$G70+$H70,1,0)+IF(AE72=$I$72,3,0)+IF(AE73=$G72+$H72,1,0)+IF(AE74=$I$74,3,0)+IF(AE75=$G74+$H74,1,0)+IF(AE76=$I$76,3,0)+IF(AE77=$G76+$H76,1,0)+IF(AE78=$I$78,3,0)+IF(AE79=$G78+$H78,1,0))</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AF4" s="73">
         <f>SUM(IF(AF8=$I$8,3,0)+IF(AF9=$G8+$H8,1,0)+IF(AF10=$I$10,3,0)+IF(AF11=$G10+$H10,1,0)+IF(AF12=$I$12,3,0)+IF(AF13=$G12+$H12,1,0)+IF(AF14=$I$14,3,0)+IF(AF15=$G14+$H14,1,0)
 +IF(AF16=$I$16,3,0)+IF(AF17=$G16+$H16,1,0)+IF(AF18=$I$18,3,0)+IF(AF19=$G18+$H18,1,0)+IF(AF20=$I$20,3,0)+IF(AF21=$G20+$H20,1,0)+IF(AF22=$I$22,3,0)+IF(AF23=$G22+$H22,1,0)+IF(AF24=$I$24,3,0)+IF(AF25=$G24+$H24,1,0)+IF(AF26=$I$26,3,0)+IF(AF27=$G26+$H26,1,0)+IF(AF28=$I$28,3,0)+IF(AF29=$G28+$H28,1,0)+IF(AF30=$I$30,3,0)+IF(AF31=$G30+$H30,1,0)+IF(AF32=$I$32,3,0)+IF(AF33=$G32+$H32,1,0)+IF(AF34=$I$34,3,0)+IF(AF35=$G34+$H34,1,0)+IF(AF36=$I$36,3,0)+IF(AF37=$G36+$H36,1,0)+IF(AF38=$I$38,3,0)+IF(AF39=$G38+$H38,1,0)+IF(AF40=$I$40,3,0)+IF(AF41=$G40+$H40,1,0)+IF(AF42=$I$42,3,0)+IF(AF43=$G42+$H42,1,0)+IF(AF44=$I$44,3,0)+IF(AF45=$G44+$H44,1,0)+IF(AF46=$I$46,3,0)+IF(AF47=$G46+$H46,1,0)+IF(AF48=$I$48,3,0)+IF(AF49=$G48+$H48,1,0)+IF(AF50=$I$50,3,0)+IF(AF51=$G50+$H50,1,0)+IF(AF52=$I$52,3,0)+IF(AF53=$G52+$H52,1,0)+IF(AF54=$I$54,3,0)+IF(AF55=$G54+$H54,1,0)+IF(AF56=$I$56,3,0)+IF(AF57=$G56+$H56,1,0)+IF(AF58=$I$58,3,0)+IF(AF59=$G58+$H58,1,0)+IF(AF60=$I$60,3,0)+IF(AF61=$G60+$H60,1,0)+IF(AF62=$I$62,3,0)+IF(AF63=$G62+$H62,1,0)+IF(AF64=$I$64,3,0)+IF(AF65=$G64+$H64,1,0)+IF(AF66=$I$66,3,0)+IF(AF67=$G66+$H66,1,0)+IF(AF68=$I$68,3,0)+IF(AF69=$G68+$H68,1,0)+IF(AF70=$I$70,3,0)+IF(AF71=$G70+$H70,1,0)+IF(AF72=$I$72,3,0)+IF(AF73=$G72+$H72,1,0)+IF(AF74=$I$74,3,0)+IF(AF75=$G74+$H74,1,0)+IF(AF76=$I$76,3,0)+IF(AF77=$G76+$H76,1,0)+IF(AF78=$I$78,3,0)+IF(AF79=$G78+$H78,1,0))</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AG4" s="73">
         <f>SUM(IF(AG8=$I$8,3,0)+IF(AG9=$G8+$H8,1,0)+IF(AG10=$I$10,3,0)+IF(AG11=$G10+$H10,1,0)+IF(AG12=$I$12,3,0)+IF(AG13=$G12+$H12,1,0)+IF(AG14=$I$14,3,0)+IF(AG15=$G14+$H14,1,0)
 +IF(AG16=$I$16,3,0)+IF(AG17=$G16+$H16,1,0)+IF(AG18=$I$18,3,0)+IF(AG19=$G18+$H18,1,0)+IF(AG20=$I$20,3,0)+IF(AG21=$G20+$H20,1,0)+IF(AG22=$I$22,3,0)+IF(AG23=$G22+$H22,1,0)+IF(AG24=$I$24,3,0)+IF(AG25=$G24+$H24,1,0)+IF(AG26=$I$26,3,0)+IF(AG27=$G26+$H26,1,0)+IF(AG28=$I$28,3,0)+IF(AG29=$G28+$H28,1,0)+IF(AG30=$I$30,3,0)+IF(AG31=$G30+$H30,1,0)+IF(AG32=$I$32,3,0)+IF(AG33=$G32+$H32,1,0)+IF(AG34=$I$34,3,0)+IF(AG35=$G34+$H34,1,0)+IF(AG36=$I$36,3,0)+IF(AG37=$G36+$H36,1,0)+IF(AG38=$I$38,3,0)+IF(AG39=$G38+$H38,1,0)+IF(AG40=$I$40,3,0)+IF(AG41=$G40+$H40,1,0)+IF(AG42=$I$42,3,0)+IF(AG43=$G42+$H42,1,0)+IF(AG44=$I$44,3,0)+IF(AG45=$G44+$H44,1,0)+IF(AG46=$I$46,3,0)+IF(AG47=$G46+$H46,1,0)+IF(AG48=$I$48,3,0)+IF(AG49=$G48+$H48,1,0)+IF(AG50=$I$50,3,0)+IF(AG51=$G50+$H50,1,0)+IF(AG52=$I$52,3,0)+IF(AG53=$G52+$H52,1,0)+IF(AG54=$I$54,3,0)+IF(AG55=$G54+$H54,1,0)+IF(AG56=$I$56,3,0)+IF(AG57=$G56+$H56,1,0)+IF(AG58=$I$58,3,0)+IF(AG59=$G58+$H58,1,0)+IF(AG60=$I$60,3,0)+IF(AG61=$G60+$H60,1,0)+IF(AG62=$I$62,3,0)+IF(AG63=$G62+$H62,1,0)+IF(AG64=$I$64,3,0)+IF(AG65=$G64+$H64,1,0)+IF(AG66=$I$66,3,0)+IF(AG67=$G66+$H66,1,0)+IF(AG68=$I$68,3,0)+IF(AG69=$G68+$H68,1,0)+IF(AG70=$I$70,3,0)+IF(AG71=$G70+$H70,1,0)+IF(AG72=$I$72,3,0)+IF(AG73=$G72+$H72,1,0)+IF(AG74=$I$74,3,0)+IF(AG75=$G74+$H74,1,0)+IF(AG76=$I$76,3,0)+IF(AG77=$G76+$H76,1,0)+IF(AG78=$I$78,3,0)+IF(AG79=$G78+$H78,1,0))</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH4" s="73">
         <f>SUM(IF(AH8=$I$8,3,0)+IF(AH9=$G8+$H8,1,0)+IF(AH10=$I$10,3,0)+IF(AH11=$G10+$H10,1,0)+IF(AH12=$I$12,3,0)+IF(AH13=$G12+$H12,1,0)+IF(AH14=$I$14,3,0)+IF(AH15=$G14+$H14,1,0)
 +IF(AH16=$I$16,3,0)+IF(AH17=$G16+$H16,1,0)+IF(AH18=$I$18,3,0)+IF(AH19=$G18+$H18,1,0)+IF(AH20=$I$20,3,0)+IF(AH21=$G20+$H20,1,0)+IF(AH22=$I$22,3,0)+IF(AH23=$G22+$H22,1,0)+IF(AH24=$I$24,3,0)+IF(AH25=$G24+$H24,1,0)+IF(AH26=$I$26,3,0)+IF(AH27=$G26+$H26,1,0)+IF(AH28=$I$28,3,0)+IF(AH29=$G28+$H28,1,0)+IF(AH30=$I$30,3,0)+IF(AH31=$G30+$H30,1,0)+IF(AH32=$I$32,3,0)+IF(AH33=$G32+$H32,1,0)+IF(AH34=$I$34,3,0)+IF(AH35=$G34+$H34,1,0)+IF(AH36=$I$36,3,0)+IF(AH37=$G36+$H36,1,0)+IF(AH38=$I$38,3,0)+IF(AH39=$G38+$H38,1,0)+IF(AH40=$I$40,3,0)+IF(AH41=$G40+$H40,1,0)+IF(AH42=$I$42,3,0)+IF(AH43=$G42+$H42,1,0)+IF(AH44=$I$44,3,0)+IF(AH45=$G44+$H44,1,0)+IF(AH46=$I$46,3,0)+IF(AH47=$G46+$H46,1,0)+IF(AH48=$I$48,3,0)+IF(AH49=$G48+$H48,1,0)+IF(AH50=$I$50,3,0)+IF(AH51=$G50+$H50,1,0)+IF(AH52=$I$52,3,0)+IF(AH53=$G52+$H52,1,0)+IF(AH54=$I$54,3,0)+IF(AH55=$G54+$H54,1,0)+IF(AH56=$I$56,3,0)+IF(AH57=$G56+$H56,1,0)+IF(AH58=$I$58,3,0)+IF(AH59=$G58+$H58,1,0)+IF(AH60=$I$60,3,0)+IF(AH61=$G60+$H60,1,0)+IF(AH62=$I$62,3,0)+IF(AH63=$G62+$H62,1,0)+IF(AH64=$I$64,3,0)+IF(AH65=$G64+$H64,1,0)+IF(AH66=$I$66,3,0)+IF(AH67=$G66+$H66,1,0)+IF(AH68=$I$68,3,0)+IF(AH69=$G68+$H68,1,0)+IF(AH70=$I$70,3,0)+IF(AH71=$G70+$H70,1,0)+IF(AH72=$I$72,3,0)+IF(AH73=$G72+$H72,1,0)+IF(AH74=$I$74,3,0)+IF(AH75=$G74+$H74,1,0)+IF(AH76=$I$76,3,0)+IF(AH77=$G76+$H76,1,0)+IF(AH78=$I$78,3,0)+IF(AH79=$G78+$H78,1,0))</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AI4" s="73">
         <f>SUM(IF(AI8=$I$8,3,0)+IF(AI9=$G8+$H8,1,0)+IF(AI10=$I$10,3,0)+IF(AI11=$G10+$H10,1,0)+IF(AI12=$I$12,3,0)+IF(AI13=$G12+$H12,1,0)+IF(AI14=$I$14,3,0)+IF(AI15=$G14+$H14,1,0)
 +IF(AI16=$I$16,3,0)+IF(AI17=$G16+$H16,1,0)+IF(AI18=$I$18,3,0)+IF(AI19=$G18+$H18,1,0)+IF(AI20=$I$20,3,0)+IF(AI21=$G20+$H20,1,0)+IF(AI22=$I$22,3,0)+IF(AI23=$G22+$H22,1,0)+IF(AI24=$I$24,3,0)+IF(AI25=$G24+$H24,1,0)+IF(AI26=$I$26,3,0)+IF(AI27=$G26+$H26,1,0)+IF(AI28=$I$28,3,0)+IF(AI29=$G28+$H28,1,0)+IF(AI30=$I$30,3,0)+IF(AI31=$G30+$H30,1,0)+IF(AI32=$I$32,3,0)+IF(AI33=$G32+$H32,1,0)+IF(AI34=$I$34,3,0)+IF(AI35=$G34+$H34,1,0)+IF(AI36=$I$36,3,0)+IF(AI37=$G36+$H36,1,0)+IF(AI38=$I$38,3,0)+IF(AI39=$G38+$H38,1,0)+IF(AI40=$I$40,3,0)+IF(AI41=$G40+$H40,1,0)+IF(AI42=$I$42,3,0)+IF(AI43=$G42+$H42,1,0)+IF(AI44=$I$44,3,0)+IF(AI45=$G44+$H44,1,0)+IF(AI46=$I$46,3,0)+IF(AI47=$G46+$H46,1,0)+IF(AI48=$I$48,3,0)+IF(AI49=$G48+$H48,1,0)+IF(AI50=$I$50,3,0)+IF(AI51=$G50+$H50,1,0)+IF(AI52=$I$52,3,0)+IF(AI53=$G52+$H52,1,0)+IF(AI54=$I$54,3,0)+IF(AI55=$G54+$H54,1,0)+IF(AI56=$I$56,3,0)+IF(AI57=$G56+$H56,1,0)+IF(AI58=$I$58,3,0)+IF(AI59=$G58+$H58,1,0)+IF(AI60=$I$60,3,0)+IF(AI61=$G60+$H60,1,0)+IF(AI62=$I$62,3,0)+IF(AI63=$G62+$H62,1,0)+IF(AI64=$I$64,3,0)+IF(AI65=$G64+$H64,1,0)+IF(AI66=$I$66,3,0)+IF(AI67=$G66+$H66,1,0)+IF(AI68=$I$68,3,0)+IF(AI69=$G68+$H68,1,0)+IF(AI70=$I$70,3,0)+IF(AI71=$G70+$H70,1,0)+IF(AI72=$I$72,3,0)+IF(AI73=$G72+$H72,1,0)+IF(AI74=$I$74,3,0)+IF(AI75=$G74+$H74,1,0)+IF(AI76=$I$76,3,0)+IF(AI77=$G76+$H76,1,0)+IF(AI78=$I$78,3,0)+IF(AI79=$G78+$H78,1,0))</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AJ4" s="73">
         <f>SUM(IF(AJ8=$I$8,3,0)+IF(AJ9=$G8+$H8,1,0)+IF(AJ10=$I$10,3,0)+IF(AJ11=$G10+$H10,1,0)+IF(AJ12=$I$12,3,0)+IF(AJ13=$G12+$H12,1,0)+IF(AJ14=$I$14,3,0)+IF(AJ15=$G14+$H14,1,0)
 +IF(AJ16=$I$16,3,0)+IF(AJ17=$G16+$H16,1,0)+IF(AJ18=$I$18,3,0)+IF(AJ19=$G18+$H18,1,0)+IF(AJ20=$I$20,3,0)+IF(AJ21=$G20+$H20,1,0)+IF(AJ22=$I$22,3,0)+IF(AJ23=$G22+$H22,1,0)+IF(AJ24=$I$24,3,0)+IF(AJ25=$G24+$H24,1,0)+IF(AJ26=$I$26,3,0)+IF(AJ27=$G26+$H26,1,0)+IF(AJ28=$I$28,3,0)+IF(AJ29=$G28+$H28,1,0)+IF(AJ30=$I$30,3,0)+IF(AJ31=$G30+$H30,1,0)+IF(AJ32=$I$32,3,0)+IF(AJ33=$G32+$H32,1,0)+IF(AJ34=$I$34,3,0)+IF(AJ35=$G34+$H34,1,0)+IF(AJ36=$I$36,3,0)+IF(AJ37=$G36+$H36,1,0)+IF(AJ38=$I$38,3,0)+IF(AJ39=$G38+$H38,1,0)+IF(AJ40=$I$40,3,0)+IF(AJ41=$G40+$H40,1,0)+IF(AJ42=$I$42,3,0)+IF(AJ43=$G42+$H42,1,0)+IF(AJ44=$I$44,3,0)+IF(AJ45=$G44+$H44,1,0)+IF(AJ46=$I$46,3,0)+IF(AJ47=$G46+$H46,1,0)+IF(AJ48=$I$48,3,0)+IF(AJ49=$G48+$H48,1,0)+IF(AJ50=$I$50,3,0)+IF(AJ51=$G50+$H50,1,0)+IF(AJ52=$I$52,3,0)+IF(AJ53=$G52+$H52,1,0)+IF(AJ54=$I$54,3,0)+IF(AJ55=$G54+$H54,1,0)+IF(AJ56=$I$56,3,0)+IF(AJ57=$G56+$H56,1,0)+IF(AJ58=$I$58,3,0)+IF(AJ59=$G58+$H58,1,0)+IF(AJ60=$I$60,3,0)+IF(AJ61=$G60+$H60,1,0)+IF(AJ62=$I$62,3,0)+IF(AJ63=$G62+$H62,1,0)+IF(AJ64=$I$64,3,0)+IF(AJ65=$G64+$H64,1,0)+IF(AJ66=$I$66,3,0)+IF(AJ67=$G66+$H66,1,0)+IF(AJ68=$I$68,3,0)+IF(AJ69=$G68+$H68,1,0)+IF(AJ70=$I$70,3,0)+IF(AJ71=$G70+$H70,1,0)+IF(AJ72=$I$72,3,0)+IF(AJ73=$G72+$H72,1,0)+IF(AJ74=$I$74,3,0)+IF(AJ75=$G74+$H74,1,0)+IF(AJ76=$I$76,3,0)+IF(AJ77=$G76+$H76,1,0)+IF(AJ78=$I$78,3,0)+IF(AJ79=$G78+$H78,1,0))</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AK4" s="73">
         <f>SUM(IF(AK8=$I$8,3,0)+IF(AK9=$G8+$H8,1,0)+IF(AK10=$I$10,3,0)+IF(AK11=$G10+$H10,1,0)+IF(AK12=$I$12,3,0)+IF(AK13=$G12+$H12,1,0)+IF(AK14=$I$14,3,0)+IF(AK15=$G14+$H14,1,0)
 +IF(AK16=$I$16,3,0)+IF(AK17=$G16+$H16,1,0)+IF(AK18=$I$18,3,0)+IF(AK19=$G18+$H18,1,0)+IF(AK20=$I$20,3,0)+IF(AK21=$G20+$H20,1,0)+IF(AK22=$I$22,3,0)+IF(AK23=$G22+$H22,1,0)+IF(AK24=$I$24,3,0)+IF(AK25=$G24+$H24,1,0)+IF(AK26=$I$26,3,0)+IF(AK27=$G26+$H26,1,0)+IF(AK28=$I$28,3,0)+IF(AK29=$G28+$H28,1,0)+IF(AK30=$I$30,3,0)+IF(AK31=$G30+$H30,1,0)+IF(AK32=$I$32,3,0)+IF(AK33=$G32+$H32,1,0)+IF(AK34=$I$34,3,0)+IF(AK35=$G34+$H34,1,0)+IF(AK36=$I$36,3,0)+IF(AK37=$G36+$H36,1,0)+IF(AK38=$I$38,3,0)+IF(AK39=$G38+$H38,1,0)+IF(AK40=$I$40,3,0)+IF(AK41=$G40+$H40,1,0)+IF(AK42=$I$42,3,0)+IF(AK43=$G42+$H42,1,0)+IF(AK44=$I$44,3,0)+IF(AK45=$G44+$H44,1,0)+IF(AK46=$I$46,3,0)+IF(AK47=$G46+$H46,1,0)+IF(AK48=$I$48,3,0)+IF(AK49=$G48+$H48,1,0)+IF(AK50=$I$50,3,0)+IF(AK51=$G50+$H50,1,0)+IF(AK52=$I$52,3,0)+IF(AK53=$G52+$H52,1,0)+IF(AK54=$I$54,3,0)+IF(AK55=$G54+$H54,1,0)+IF(AK56=$I$56,3,0)+IF(AK57=$G56+$H56,1,0)+IF(AK58=$I$58,3,0)+IF(AK59=$G58+$H58,1,0)+IF(AK60=$I$60,3,0)+IF(AK61=$G60+$H60,1,0)+IF(AK62=$I$62,3,0)+IF(AK63=$G62+$H62,1,0)+IF(AK64=$I$64,3,0)+IF(AK65=$G64+$H64,1,0)+IF(AK66=$I$66,3,0)+IF(AK67=$G66+$H66,1,0)+IF(AK68=$I$68,3,0)+IF(AK69=$G68+$H68,1,0)+IF(AK70=$I$70,3,0)+IF(AK71=$G70+$H70,1,0)+IF(AK72=$I$72,3,0)+IF(AK73=$G72+$H72,1,0)+IF(AK74=$I$74,3,0)+IF(AK75=$G74+$H74,1,0)+IF(AK76=$I$76,3,0)+IF(AK77=$G76+$H76,1,0)+IF(AK78=$I$78,3,0)+IF(AK79=$G78+$H78,1,0))</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AL4" s="73">
         <f>SUM(IF(AL8=$I$8,3,0)+IF(AL9=$G8+$H8,1,0)+IF(AL10=$I$10,3,0)+IF(AL11=$G10+$H10,1,0)+IF(AL12=$I$12,3,0)+IF(AL13=$G12+$H12,1,0)+IF(AL14=$I$14,3,0)+IF(AL15=$G14+$H14,1,0)
 +IF(AL16=$I$16,3,0)+IF(AL17=$G16+$H16,1,0)+IF(AL18=$I$18,3,0)+IF(AL19=$G18+$H18,1,0)+IF(AL20=$I$20,3,0)+IF(AL21=$G20+$H20,1,0)+IF(AL22=$I$22,3,0)+IF(AL23=$G22+$H22,1,0)+IF(AL24=$I$24,3,0)+IF(AL25=$G24+$H24,1,0)+IF(AL26=$I$26,3,0)+IF(AL27=$G26+$H26,1,0)+IF(AL28=$I$28,3,0)+IF(AL29=$G28+$H28,1,0)+IF(AL30=$I$30,3,0)+IF(AL31=$G30+$H30,1,0)+IF(AL32=$I$32,3,0)+IF(AL33=$G32+$H32,1,0)+IF(AL34=$I$34,3,0)+IF(AL35=$G34+$H34,1,0)+IF(AL36=$I$36,3,0)+IF(AL37=$G36+$H36,1,0)+IF(AL38=$I$38,3,0)+IF(AL39=$G38+$H38,1,0)+IF(AL40=$I$40,3,0)+IF(AL41=$G40+$H40,1,0)+IF(AL42=$I$42,3,0)+IF(AL43=$G42+$H42,1,0)+IF(AL44=$I$44,3,0)+IF(AL45=$G44+$H44,1,0)+IF(AL46=$I$46,3,0)+IF(AL47=$G46+$H46,1,0)+IF(AL48=$I$48,3,0)+IF(AL49=$G48+$H48,1,0)+IF(AL50=$I$50,3,0)+IF(AL51=$G50+$H50,1,0)+IF(AL52=$I$52,3,0)+IF(AL53=$G52+$H52,1,0)+IF(AL54=$I$54,3,0)+IF(AL55=$G54+$H54,1,0)+IF(AL56=$I$56,3,0)+IF(AL57=$G56+$H56,1,0)+IF(AL58=$I$58,3,0)+IF(AL59=$G58+$H58,1,0)+IF(AL60=$I$60,3,0)+IF(AL61=$G60+$H60,1,0)+IF(AL62=$I$62,3,0)+IF(AL63=$G62+$H62,1,0)+IF(AL64=$I$64,3,0)+IF(AL65=$G64+$H64,1,0)+IF(AL66=$I$66,3,0)+IF(AL67=$G66+$H66,1,0)+IF(AL68=$I$68,3,0)+IF(AL69=$G68+$H68,1,0)+IF(AL70=$I$70,3,0)+IF(AL71=$G70+$H70,1,0)+IF(AL72=$I$72,3,0)+IF(AL73=$G72+$H72,1,0)+IF(AL74=$I$74,3,0)+IF(AL75=$G74+$H74,1,0)+IF(AL76=$I$76,3,0)+IF(AL77=$G76+$H76,1,0)+IF(AL78=$I$78,3,0)+IF(AL79=$G78+$H78,1,0))</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AM4" s="73">
         <f>SUM(IF(AM8=$I$8,3,0)+IF(AM9=$G8+$H8,1,0)+IF(AM10=$I$10,3,0)+IF(AM11=$G10+$H10,1,0)+IF(AM12=$I$12,3,0)+IF(AM13=$G12+$H12,1,0)+IF(AM14=$I$14,3,0)+IF(AM15=$G14+$H14,1,0)
 +IF(AM16=$I$16,3,0)+IF(AM17=$G16+$H16,1,0)+IF(AM18=$I$18,3,0)+IF(AM19=$G18+$H18,1,0)+IF(AM20=$I$20,3,0)+IF(AM21=$G20+$H20,1,0)+IF(AM22=$I$22,3,0)+IF(AM23=$G22+$H22,1,0)+IF(AM24=$I$24,3,0)+IF(AM25=$G24+$H24,1,0)+IF(AM26=$I$26,3,0)+IF(AM27=$G26+$H26,1,0)+IF(AM28=$I$28,3,0)+IF(AM29=$G28+$H28,1,0)+IF(AM30=$I$30,3,0)+IF(AM31=$G30+$H30,1,0)+IF(AM32=$I$32,3,0)+IF(AM33=$G32+$H32,1,0)+IF(AM34=$I$34,3,0)+IF(AM35=$G34+$H34,1,0)+IF(AM36=$I$36,3,0)+IF(AM37=$G36+$H36,1,0)+IF(AM38=$I$38,3,0)+IF(AM39=$G38+$H38,1,0)+IF(AM40=$I$40,3,0)+IF(AM41=$G40+$H40,1,0)+IF(AM42=$I$42,3,0)+IF(AM43=$G42+$H42,1,0)+IF(AM44=$I$44,3,0)+IF(AM45=$G44+$H44,1,0)+IF(AM46=$I$46,3,0)+IF(AM47=$G46+$H46,1,0)+IF(AM48=$I$48,3,0)+IF(AM49=$G48+$H48,1,0)+IF(AM50=$I$50,3,0)+IF(AM51=$G50+$H50,1,0)+IF(AM52=$I$52,3,0)+IF(AM53=$G52+$H52,1,0)+IF(AM54=$I$54,3,0)+IF(AM55=$G54+$H54,1,0)+IF(AM56=$I$56,3,0)+IF(AM57=$G56+$H56,1,0)+IF(AM58=$I$58,3,0)+IF(AM59=$G58+$H58,1,0)+IF(AM60=$I$60,3,0)+IF(AM61=$G60+$H60,1,0)+IF(AM62=$I$62,3,0)+IF(AM63=$G62+$H62,1,0)+IF(AM64=$I$64,3,0)+IF(AM65=$G64+$H64,1,0)+IF(AM66=$I$66,3,0)+IF(AM67=$G66+$H66,1,0)+IF(AM68=$I$68,3,0)+IF(AM69=$G68+$H68,1,0)+IF(AM70=$I$70,3,0)+IF(AM71=$G70+$H70,1,0)+IF(AM72=$I$72,3,0)+IF(AM73=$G72+$H72,1,0)+IF(AM74=$I$74,3,0)+IF(AM75=$G74+$H74,1,0)+IF(AM76=$I$76,3,0)+IF(AM77=$G76+$H76,1,0)+IF(AM78=$I$78,3,0)+IF(AM79=$G78+$H78,1,0))</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AN4" s="73">
         <f>SUM(IF(AN8=$I$8,3,0)+IF(AN9=$G8+$H8,1,0)+IF(AN10=$I$10,3,0)+IF(AN11=$G10+$H10,1,0)+IF(AN12=$I$12,3,0)+IF(AN13=$G12+$H12,1,0)+IF(AN14=$I$14,3,0)+IF(AN15=$G14+$H14,1,0)
 +IF(AN16=$I$16,3,0)+IF(AN17=$G16+$H16,1,0)+IF(AN18=$I$18,3,0)+IF(AN19=$G18+$H18,1,0)+IF(AN20=$I$20,3,0)+IF(AN21=$G20+$H20,1,0)+IF(AN22=$I$22,3,0)+IF(AN23=$G22+$H22,1,0)+IF(AN24=$I$24,3,0)+IF(AN25=$G24+$H24,1,0)+IF(AN26=$I$26,3,0)+IF(AN27=$G26+$H26,1,0)+IF(AN28=$I$28,3,0)+IF(AN29=$G28+$H28,1,0)+IF(AN30=$I$30,3,0)+IF(AN31=$G30+$H30,1,0)+IF(AN32=$I$32,3,0)+IF(AN33=$G32+$H32,1,0)+IF(AN34=$I$34,3,0)+IF(AN35=$G34+$H34,1,0)+IF(AN36=$I$36,3,0)+IF(AN37=$G36+$H36,1,0)+IF(AN38=$I$38,3,0)+IF(AN39=$G38+$H38,1,0)+IF(AN40=$I$40,3,0)+IF(AN41=$G40+$H40,1,0)+IF(AN42=$I$42,3,0)+IF(AN43=$G42+$H42,1,0)+IF(AN44=$I$44,3,0)+IF(AN45=$G44+$H44,1,0)+IF(AN46=$I$46,3,0)+IF(AN47=$G46+$H46,1,0)+IF(AN48=$I$48,3,0)+IF(AN49=$G48+$H48,1,0)+IF(AN50=$I$50,3,0)+IF(AN51=$G50+$H50,1,0)+IF(AN52=$I$52,3,0)+IF(AN53=$G52+$H52,1,0)+IF(AN54=$I$54,3,0)+IF(AN55=$G54+$H54,1,0)+IF(AN56=$I$56,3,0)+IF(AN57=$G56+$H56,1,0)+IF(AN58=$I$58,3,0)+IF(AN59=$G58+$H58,1,0)+IF(AN60=$I$60,3,0)+IF(AN61=$G60+$H60,1,0)+IF(AN62=$I$62,3,0)+IF(AN63=$G62+$H62,1,0)+IF(AN64=$I$64,3,0)+IF(AN65=$G64+$H64,1,0)+IF(AN66=$I$66,3,0)+IF(AN67=$G66+$H66,1,0)+IF(AN68=$I$68,3,0)+IF(AN69=$G68+$H68,1,0)+IF(AN70=$I$70,3,0)+IF(AN71=$G70+$H70,1,0)+IF(AN72=$I$72,3,0)+IF(AN73=$G72+$H72,1,0)+IF(AN74=$I$74,3,0)+IF(AN75=$G74+$H74,1,0)+IF(AN76=$I$76,3,0)+IF(AN77=$G76+$H76,1,0)+IF(AN78=$I$78,3,0)+IF(AN79=$G78+$H78,1,0))</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AO4" s="73">
         <f>SUM(IF(AO8=$I$8,3,0)+IF(AO9=$G8+$H8,1,0)+IF(AO10=$I$10,3,0)+IF(AO11=$G10+$H10,1,0)+IF(AO12=$I$12,3,0)+IF(AO13=$G12+$H12,1,0)+IF(AO14=$I$14,3,0)+IF(AO15=$G14+$H14,1,0)
 +IF(AO16=$I$16,3,0)+IF(AO17=$G16+$H16,1,0)+IF(AO18=$I$18,3,0)+IF(AO19=$G18+$H18,1,0)+IF(AO20=$I$20,3,0)+IF(AO21=$G20+$H20,1,0)+IF(AO22=$I$22,3,0)+IF(AO23=$G22+$H22,1,0)+IF(AO24=$I$24,3,0)+IF(AO25=$G24+$H24,1,0)+IF(AO26=$I$26,3,0)+IF(AO27=$G26+$H26,1,0)+IF(AO28=$I$28,3,0)+IF(AO29=$G28+$H28,1,0)+IF(AO30=$I$30,3,0)+IF(AO31=$G30+$H30,1,0)+IF(AO32=$I$32,3,0)+IF(AO33=$G32+$H32,1,0)+IF(AO34=$I$34,3,0)+IF(AO35=$G34+$H34,1,0)+IF(AO36=$I$36,3,0)+IF(AO37=$G36+$H36,1,0)+IF(AO38=$I$38,3,0)+IF(AO39=$G38+$H38,1,0)+IF(AO40=$I$40,3,0)+IF(AO41=$G40+$H40,1,0)+IF(AO42=$I$42,3,0)+IF(AO43=$G42+$H42,1,0)+IF(AO44=$I$44,3,0)+IF(AO45=$G44+$H44,1,0)+IF(AO46=$I$46,3,0)+IF(AO47=$G46+$H46,1,0)+IF(AO48=$I$48,3,0)+IF(AO49=$G48+$H48,1,0)+IF(AO50=$I$50,3,0)+IF(AO51=$G50+$H50,1,0)+IF(AO52=$I$52,3,0)+IF(AO53=$G52+$H52,1,0)+IF(AO54=$I$54,3,0)+IF(AO55=$G54+$H54,1,0)+IF(AO56=$I$56,3,0)+IF(AO57=$G56+$H56,1,0)+IF(AO58=$I$58,3,0)+IF(AO59=$G58+$H58,1,0)+IF(AO60=$I$60,3,0)+IF(AO61=$G60+$H60,1,0)+IF(AO62=$I$62,3,0)+IF(AO63=$G62+$H62,1,0)+IF(AO64=$I$64,3,0)+IF(AO65=$G64+$H64,1,0)+IF(AO66=$I$66,3,0)+IF(AO67=$G66+$H66,1,0)+IF(AO68=$I$68,3,0)+IF(AO69=$G68+$H68,1,0)+IF(AO70=$I$70,3,0)+IF(AO71=$G70+$H70,1,0)+IF(AO72=$I$72,3,0)+IF(AO73=$G72+$H72,1,0)+IF(AO74=$I$74,3,0)+IF(AO75=$G74+$H74,1,0)+IF(AO76=$I$76,3,0)+IF(AO77=$G76+$H76,1,0)+IF(AO78=$I$78,3,0)+IF(AO79=$G78+$H78,1,0))</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AP4" s="73">
         <f>SUM(IF(AP8=$I$8,3,0)+IF(AP9=$G8+$H8,1,0)+IF(AP10=$I$10,3,0)+IF(AP11=$G10+$H10,1,0)+IF(AP12=$I$12,3,0)+IF(AP13=$G12+$H12,1,0)+IF(AP14=$I$14,3,0)+IF(AP15=$G14+$H14,1,0)
 +IF(AP16=$I$16,3,0)+IF(AP17=$G16+$H16,1,0)+IF(AP18=$I$18,3,0)+IF(AP19=$G18+$H18,1,0)+IF(AP20=$I$20,3,0)+IF(AP21=$G20+$H20,1,0)+IF(AP22=$I$22,3,0)+IF(AP23=$G22+$H22,1,0)+IF(AP24=$I$24,3,0)+IF(AP25=$G24+$H24,1,0)+IF(AP26=$I$26,3,0)+IF(AP27=$G26+$H26,1,0)+IF(AP28=$I$28,3,0)+IF(AP29=$G28+$H28,1,0)+IF(AP30=$I$30,3,0)+IF(AP31=$G30+$H30,1,0)+IF(AP32=$I$32,3,0)+IF(AP33=$G32+$H32,1,0)+IF(AP34=$I$34,3,0)+IF(AP35=$G34+$H34,1,0)+IF(AP36=$I$36,3,0)+IF(AP37=$G36+$H36,1,0)+IF(AP38=$I$38,3,0)+IF(AP39=$G38+$H38,1,0)+IF(AP40=$I$40,3,0)+IF(AP41=$G40+$H40,1,0)+IF(AP42=$I$42,3,0)+IF(AP43=$G42+$H42,1,0)+IF(AP44=$I$44,3,0)+IF(AP45=$G44+$H44,1,0)+IF(AP46=$I$46,3,0)+IF(AP47=$G46+$H46,1,0)+IF(AP48=$I$48,3,0)+IF(AP49=$G48+$H48,1,0)+IF(AP50=$I$50,3,0)+IF(AP51=$G50+$H50,1,0)+IF(AP52=$I$52,3,0)+IF(AP53=$G52+$H52,1,0)+IF(AP54=$I$54,3,0)+IF(AP55=$G54+$H54,1,0)+IF(AP56=$I$56,3,0)+IF(AP57=$G56+$H56,1,0)+IF(AP58=$I$58,3,0)+IF(AP59=$G58+$H58,1,0)+IF(AP60=$I$60,3,0)+IF(AP61=$G60+$H60,1,0)+IF(AP62=$I$62,3,0)+IF(AP63=$G62+$H62,1,0)+IF(AP64=$I$64,3,0)+IF(AP65=$G64+$H64,1,0)+IF(AP66=$I$66,3,0)+IF(AP67=$G66+$H66,1,0)+IF(AP68=$I$68,3,0)+IF(AP69=$G68+$H68,1,0)+IF(AP70=$I$70,3,0)+IF(AP71=$G70+$H70,1,0)+IF(AP72=$I$72,3,0)+IF(AP73=$G72+$H72,1,0)+IF(AP74=$I$74,3,0)+IF(AP75=$G74+$H74,1,0)+IF(AP76=$I$76,3,0)+IF(AP77=$G76+$H76,1,0)+IF(AP78=$I$78,3,0)+IF(AP79=$G78+$H78,1,0))</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AQ4" s="73">
         <f>SUM(IF(AQ8=$I$8,3,0)+IF(AQ9=$G8+$H8,1,0)+IF(AQ10=$I$10,3,0)+IF(AQ11=$G10+$H10,1,0)+IF(AQ12=$I$12,3,0)+IF(AQ13=$G12+$H12,1,0)+IF(AQ14=$I$14,3,0)+IF(AQ15=$G14+$H14,1,0)
 +IF(AQ16=$I$16,3,0)+IF(AQ17=$G16+$H16,1,0)+IF(AQ18=$I$18,3,0)+IF(AQ19=$G18+$H18,1,0)+IF(AQ20=$I$20,3,0)+IF(AQ21=$G20+$H20,1,0)+IF(AQ22=$I$22,3,0)+IF(AQ23=$G22+$H22,1,0)+IF(AQ24=$I$24,3,0)+IF(AQ25=$G24+$H24,1,0)+IF(AQ26=$I$26,3,0)+IF(AQ27=$G26+$H26,1,0)+IF(AQ28=$I$28,3,0)+IF(AQ29=$G28+$H28,1,0)+IF(AQ30=$I$30,3,0)+IF(AQ31=$G30+$H30,1,0)+IF(AQ32=$I$32,3,0)+IF(AQ33=$G32+$H32,1,0)+IF(AQ34=$I$34,3,0)+IF(AQ35=$G34+$H34,1,0)+IF(AQ36=$I$36,3,0)+IF(AQ37=$G36+$H36,1,0)+IF(AQ38=$I$38,3,0)+IF(AQ39=$G38+$H38,1,0)+IF(AQ40=$I$40,3,0)+IF(AQ41=$G40+$H40,1,0)+IF(AQ42=$I$42,3,0)+IF(AQ43=$G42+$H42,1,0)+IF(AQ44=$I$44,3,0)+IF(AQ45=$G44+$H44,1,0)+IF(AQ46=$I$46,3,0)+IF(AQ47=$G46+$H46,1,0)+IF(AQ48=$I$48,3,0)+IF(AQ49=$G48+$H48,1,0)+IF(AQ50=$I$50,3,0)+IF(AQ51=$G50+$H50,1,0)+IF(AQ52=$I$52,3,0)+IF(AQ53=$G52+$H52,1,0)+IF(AQ54=$I$54,3,0)+IF(AQ55=$G54+$H54,1,0)+IF(AQ56=$I$56,3,0)+IF(AQ57=$G56+$H56,1,0)+IF(AQ58=$I$58,3,0)+IF(AQ59=$G58+$H58,1,0)+IF(AQ60=$I$60,3,0)+IF(AQ61=$G60+$H60,1,0)+IF(AQ62=$I$62,3,0)+IF(AQ63=$G62+$H62,1,0)+IF(AQ64=$I$64,3,0)+IF(AQ65=$G64+$H64,1,0)+IF(AQ66=$I$66,3,0)+IF(AQ67=$G66+$H66,1,0)+IF(AQ68=$I$68,3,0)+IF(AQ69=$G68+$H68,1,0)+IF(AQ70=$I$70,3,0)+IF(AQ71=$G70+$H70,1,0)+IF(AQ72=$I$72,3,0)+IF(AQ73=$G72+$H72,1,0)+IF(AQ74=$I$74,3,0)+IF(AQ75=$G74+$H74,1,0)+IF(AQ76=$I$76,3,0)+IF(AQ77=$G76+$H76,1,0)+IF(AQ78=$I$78,3,0)+IF(AQ79=$G78+$H78,1,0))</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AR4" s="73">
         <f>SUM(IF(AR8=$I$8,3,0)+IF(AR9=$G8+$H8,1,0)+IF(AR10=$I$10,3,0)+IF(AR11=$G10+$H10,1,0)+IF(AR12=$I$12,3,0)+IF(AR13=$G12+$H12,1,0)+IF(AR14=$I$14,3,0)+IF(AR15=$G14+$H14,1,0)
 +IF(AR16=$I$16,3,0)+IF(AR17=$G16+$H16,1,0)+IF(AR18=$I$18,3,0)+IF(AR19=$G18+$H18,1,0)+IF(AR20=$I$20,3,0)+IF(AR21=$G20+$H20,1,0)+IF(AR22=$I$22,3,0)+IF(AR23=$G22+$H22,1,0)+IF(AR24=$I$24,3,0)+IF(AR25=$G24+$H24,1,0)+IF(AR26=$I$26,3,0)+IF(AR27=$G26+$H26,1,0)+IF(AR28=$I$28,3,0)+IF(AR29=$G28+$H28,1,0)+IF(AR30=$I$30,3,0)+IF(AR31=$G30+$H30,1,0)+IF(AR32=$I$32,3,0)+IF(AR33=$G32+$H32,1,0)+IF(AR34=$I$34,3,0)+IF(AR35=$G34+$H34,1,0)+IF(AR36=$I$36,3,0)+IF(AR37=$G36+$H36,1,0)+IF(AR38=$I$38,3,0)+IF(AR39=$G38+$H38,1,0)+IF(AR40=$I$40,3,0)+IF(AR41=$G40+$H40,1,0)+IF(AR42=$I$42,3,0)+IF(AR43=$G42+$H42,1,0)+IF(AR44=$I$44,3,0)+IF(AR45=$G44+$H44,1,0)+IF(AR46=$I$46,3,0)+IF(AR47=$G46+$H46,1,0)+IF(AR48=$I$48,3,0)+IF(AR49=$G48+$H48,1,0)+IF(AR50=$I$50,3,0)+IF(AR51=$G50+$H50,1,0)+IF(AR52=$I$52,3,0)+IF(AR53=$G52+$H52,1,0)+IF(AR54=$I$54,3,0)+IF(AR55=$G54+$H54,1,0)+IF(AR56=$I$56,3,0)+IF(AR57=$G56+$H56,1,0)+IF(AR58=$I$58,3,0)+IF(AR59=$G58+$H58,1,0)+IF(AR60=$I$60,3,0)+IF(AR61=$G60+$H60,1,0)+IF(AR62=$I$62,3,0)+IF(AR63=$G62+$H62,1,0)+IF(AR64=$I$64,3,0)+IF(AR65=$G64+$H64,1,0)+IF(AR66=$I$66,3,0)+IF(AR67=$G66+$H66,1,0)+IF(AR68=$I$68,3,0)+IF(AR69=$G68+$H68,1,0)+IF(AR70=$I$70,3,0)+IF(AR71=$G70+$H70,1,0)+IF(AR72=$I$72,3,0)+IF(AR73=$G72+$H72,1,0)+IF(AR74=$I$74,3,0)+IF(AR75=$G74+$H74,1,0)+IF(AR76=$I$76,3,0)+IF(AR77=$G76+$H76,1,0)+IF(AR78=$I$78,3,0)+IF(AR79=$G78+$H78,1,0))</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AS4" s="73">
         <f>SUM(IF(AS8=$I$8,3,0)+IF(AS9=$G8+$H8,1,0)+IF(AS10=$I$10,3,0)+IF(AS11=$G10+$H10,1,0)+IF(AS12=$I$12,3,0)+IF(AS13=$G12+$H12,1,0)+IF(AS14=$I$14,3,0)+IF(AS15=$G14+$H14,1,0)
 +IF(AS16=$I$16,3,0)+IF(AS17=$G16+$H16,1,0)+IF(AS18=$I$18,3,0)+IF(AS19=$G18+$H18,1,0)+IF(AS20=$I$20,3,0)+IF(AS21=$G20+$H20,1,0)+IF(AS22=$I$22,3,0)+IF(AS23=$G22+$H22,1,0)+IF(AS24=$I$24,3,0)+IF(AS25=$G24+$H24,1,0)+IF(AS26=$I$26,3,0)+IF(AS27=$G26+$H26,1,0)+IF(AS28=$I$28,3,0)+IF(AS29=$G28+$H28,1,0)+IF(AS30=$I$30,3,0)+IF(AS31=$G30+$H30,1,0)+IF(AS32=$I$32,3,0)+IF(AS33=$G32+$H32,1,0)+IF(AS34=$I$34,3,0)+IF(AS35=$G34+$H34,1,0)+IF(AS36=$I$36,3,0)+IF(AS37=$G36+$H36,1,0)+IF(AS38=$I$38,3,0)+IF(AS39=$G38+$H38,1,0)+IF(AS40=$I$40,3,0)+IF(AS41=$G40+$H40,1,0)+IF(AS42=$I$42,3,0)+IF(AS43=$G42+$H42,1,0)+IF(AS44=$I$44,3,0)+IF(AS45=$G44+$H44,1,0)+IF(AS46=$I$46,3,0)+IF(AS47=$G46+$H46,1,0)+IF(AS48=$I$48,3,0)+IF(AS49=$G48+$H48,1,0)+IF(AS50=$I$50,3,0)+IF(AS51=$G50+$H50,1,0)+IF(AS52=$I$52,3,0)+IF(AS53=$G52+$H52,1,0)+IF(AS54=$I$54,3,0)+IF(AS55=$G54+$H54,1,0)+IF(AS56=$I$56,3,0)+IF(AS57=$G56+$H56,1,0)+IF(AS58=$I$58,3,0)+IF(AS59=$G58+$H58,1,0)+IF(AS60=$I$60,3,0)+IF(AS61=$G60+$H60,1,0)+IF(AS62=$I$62,3,0)+IF(AS63=$G62+$H62,1,0)+IF(AS64=$I$64,3,0)+IF(AS65=$G64+$H64,1,0)+IF(AS66=$I$66,3,0)+IF(AS67=$G66+$H66,1,0)+IF(AS68=$I$68,3,0)+IF(AS69=$G68+$H68,1,0)+IF(AS70=$I$70,3,0)+IF(AS71=$G70+$H70,1,0)+IF(AS72=$I$72,3,0)+IF(AS73=$G72+$H72,1,0)+IF(AS74=$I$74,3,0)+IF(AS75=$G74+$H74,1,0)+IF(AS76=$I$76,3,0)+IF(AS77=$G76+$H76,1,0)+IF(AS78=$I$78,3,0)+IF(AS79=$G78+$H78,1,0))</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AT4" s="78">
         <f>SUM(IF(AT8=$I$8,3,0)+IF(AT9=$G8+$H8,1,0)+IF(AT10=$I$10,3,0)+IF(AT11=$G10+$H10,1,0)+IF(AT12=$I$12,3,0)+IF(AT13=$G12+$H12,1,0)+IF(AT14=$I$14,3,0)+IF(AT15=$G14+$H14,1,0)
 +IF(AT16=$I$16,3,0)+IF(AT17=$G16+$H16,1,0)+IF(AT18=$I$18,3,0)+IF(AT19=$G18+$H18,1,0)+IF(AT20=$I$20,3,0)+IF(AT21=$G20+$H20,1,0)+IF(AT22=$I$22,3,0)+IF(AT23=$G22+$H22,1,0)+IF(AT24=$I$24,3,0)+IF(AT25=$G24+$H24,1,0)+IF(AT26=$I$26,3,0)+IF(AT27=$G26+$H26,1,0)+IF(AT28=$I$28,3,0)+IF(AT29=$G28+$H28,1,0)+IF(AT30=$I$30,3,0)+IF(AT31=$G30+$H30,1,0)+IF(AT32=$I$32,3,0)+IF(AT33=$G32+$H32,1,0)+IF(AT34=$I$34,3,0)+IF(AT35=$G34+$H34,1,0)+IF(AT36=$I$36,3,0)+IF(AT37=$G36+$H36,1,0)+IF(AT38=$I$38,3,0)+IF(AT39=$G38+$H38,1,0)+IF(AT40=$I$40,3,0)+IF(AT41=$G40+$H40,1,0)+IF(AT42=$I$42,3,0)+IF(AT43=$G42+$H42,1,0)+IF(AT44=$I$44,3,0)+IF(AT45=$G44+$H44,1,0)+IF(AT46=$I$46,3,0)+IF(AT47=$G46+$H46,1,0)+IF(AT48=$I$48,3,0)+IF(AT49=$G48+$H48,1,0)+IF(AT50=$I$50,3,0)+IF(AT51=$G50+$H50,1,0)+IF(AT52=$I$52,3,0)+IF(AT53=$G52+$H52,1,0)+IF(AT54=$I$54,3,0)+IF(AT55=$G54+$H54,1,0)+IF(AT56=$I$56,3,0)+IF(AT57=$G56+$H56,1,0)+IF(AT58=$I$58,3,0)+IF(AT59=$G58+$H58,1,0)+IF(AT60=$I$60,3,0)+IF(AT61=$G60+$H60,1,0)+IF(AT62=$I$62,3,0)+IF(AT63=$G62+$H62,1,0)+IF(AT64=$I$64,3,0)+IF(AT65=$G64+$H64,1,0)+IF(AT66=$I$66,3,0)+IF(AT67=$G66+$H66,1,0)+IF(AT68=$I$68,3,0)+IF(AT69=$G68+$H68,1,0)+IF(AT70=$I$70,3,0)+IF(AT71=$G70+$H70,1,0)+IF(AT72=$I$72,3,0)+IF(AT73=$G72+$H72,1,0)+IF(AT74=$I$74,3,0)+IF(AT75=$G74+$H74,1,0)+IF(AT76=$I$76,3,0)+IF(AT77=$G76+$H76,1,0)+IF(AT78=$I$78,3,0)+IF(AT79=$G78+$H78,1,0))</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:54" ht="14.4" x14ac:dyDescent="0.3">
@@ -3620,31 +3620,31 @@
       </c>
     </row>
     <row r="8" spans="1:54" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="103" t="s">
+      <c r="A8" s="123" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="141">
+      <c r="B8" s="120">
         <v>46184</v>
       </c>
-      <c r="C8" s="142">
+      <c r="C8" s="117">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D8" s="146" t="s">
+      <c r="D8" s="111" t="s">
         <v>89</v>
       </c>
-      <c r="E8" s="105" t="s">
+      <c r="E8" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="105" t="s">
+      <c r="F8" s="148" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="107">
-        <v>2</v>
-      </c>
-      <c r="H8" s="107">
-        <v>0</v>
-      </c>
-      <c r="I8" s="109" t="str">
+      <c r="G8" s="149">
+        <v>2</v>
+      </c>
+      <c r="H8" s="149">
+        <v>0</v>
+      </c>
+      <c r="I8" s="150" t="str">
         <f>IF(G8="","-",IF(G8&gt;H8,"L",IF(G8=H8,"E",IF(G8&lt;H8,"V"))))</f>
         <v>L</v>
       </c>
@@ -3761,15 +3761,15 @@
       </c>
     </row>
     <row r="9" spans="1:54" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="103"/>
-      <c r="B9" s="133"/>
-      <c r="C9" s="133"/>
-      <c r="D9" s="106"/>
-      <c r="E9" s="106"/>
-      <c r="F9" s="106"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="110"/>
+      <c r="A9" s="123"/>
+      <c r="B9" s="108"/>
+      <c r="C9" s="108"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="131"/>
+      <c r="I9" s="137"/>
       <c r="J9" s="23">
         <v>3</v>
       </c>
@@ -3889,29 +3889,29 @@
       </c>
     </row>
     <row r="10" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="103"/>
-      <c r="B10" s="132">
+      <c r="A10" s="123"/>
+      <c r="B10" s="119">
         <v>46184</v>
       </c>
-      <c r="C10" s="143">
+      <c r="C10" s="107">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D10" s="137" t="s">
+      <c r="D10" s="99" t="s">
         <v>137</v>
       </c>
-      <c r="E10" s="111" t="s">
+      <c r="E10" s="132" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="111" t="s">
+      <c r="F10" s="132" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="113">
-        <v>2</v>
-      </c>
-      <c r="H10" s="113">
+      <c r="G10" s="130">
+        <v>2</v>
+      </c>
+      <c r="H10" s="130">
         <v>1</v>
       </c>
-      <c r="I10" s="112" t="str">
+      <c r="I10" s="136" t="str">
         <f t="shared" ref="I10:I54" si="0">IF(G10="","-",IF(G10&gt;H10,"L",IF(G10=H10,"E",IF(G10&lt;H10,"V"))))</f>
         <v>L</v>
       </c>
@@ -4034,15 +4034,15 @@
       </c>
     </row>
     <row r="11" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="103"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="133"/>
-      <c r="D11" s="106"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="110"/>
+      <c r="A11" s="123"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="131"/>
+      <c r="H11" s="131"/>
+      <c r="I11" s="137"/>
       <c r="J11" s="26">
         <v>3</v>
       </c>
@@ -4162,25 +4162,25 @@
       </c>
     </row>
     <row r="12" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="103"/>
-      <c r="B12" s="132">
+      <c r="A12" s="123"/>
+      <c r="B12" s="119">
         <v>46191</v>
       </c>
-      <c r="C12" s="143">
+      <c r="C12" s="107">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D12" s="137" t="s">
+      <c r="D12" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="111" t="s">
+      <c r="E12" s="132" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="111" t="s">
+      <c r="F12" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="113"/>
-      <c r="H12" s="113"/>
-      <c r="I12" s="112" t="str">
+      <c r="G12" s="130"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="136" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -4301,15 +4301,15 @@
       </c>
     </row>
     <row r="13" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="103"/>
-      <c r="B13" s="133"/>
-      <c r="C13" s="133"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="108"/>
-      <c r="I13" s="110"/>
+      <c r="A13" s="123"/>
+      <c r="B13" s="108"/>
+      <c r="C13" s="108"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="131"/>
+      <c r="H13" s="131"/>
+      <c r="I13" s="137"/>
       <c r="J13" s="23">
         <v>4</v>
       </c>
@@ -4427,25 +4427,25 @@
       </c>
     </row>
     <row r="14" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="103"/>
-      <c r="B14" s="132">
+      <c r="A14" s="123"/>
+      <c r="B14" s="119">
         <v>46191</v>
       </c>
-      <c r="C14" s="143">
+      <c r="C14" s="107">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D14" s="137" t="s">
+      <c r="D14" s="99" t="s">
         <v>137</v>
       </c>
-      <c r="E14" s="111" t="s">
+      <c r="E14" s="132" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="111" t="s">
+      <c r="F14" s="132" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="113"/>
-      <c r="H14" s="113"/>
-      <c r="I14" s="112" t="str">
+      <c r="G14" s="130"/>
+      <c r="H14" s="130"/>
+      <c r="I14" s="136" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -4566,15 +4566,15 @@
       </c>
     </row>
     <row r="15" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="103"/>
-      <c r="B15" s="133"/>
-      <c r="C15" s="133"/>
-      <c r="D15" s="106"/>
-      <c r="E15" s="106"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="108"/>
-      <c r="H15" s="108"/>
-      <c r="I15" s="110"/>
+      <c r="A15" s="123"/>
+      <c r="B15" s="108"/>
+      <c r="C15" s="108"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="100"/>
+      <c r="F15" s="100"/>
+      <c r="G15" s="131"/>
+      <c r="H15" s="131"/>
+      <c r="I15" s="137"/>
       <c r="J15" s="26">
         <v>2</v>
       </c>
@@ -4692,25 +4692,25 @@
       </c>
     </row>
     <row r="16" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="103"/>
-      <c r="B16" s="132">
+      <c r="A16" s="123"/>
+      <c r="B16" s="119">
         <v>46197</v>
       </c>
-      <c r="C16" s="143">
+      <c r="C16" s="107">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D16" s="137" t="s">
+      <c r="D16" s="99" t="s">
         <v>89</v>
       </c>
-      <c r="E16" s="111" t="s">
+      <c r="E16" s="132" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="111" t="s">
+      <c r="F16" s="132" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="113"/>
-      <c r="H16" s="113"/>
-      <c r="I16" s="112" t="str">
+      <c r="G16" s="130"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="136" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -4831,15 +4831,15 @@
       </c>
     </row>
     <row r="17" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="103"/>
-      <c r="B17" s="133"/>
-      <c r="C17" s="133"/>
-      <c r="D17" s="106"/>
-      <c r="E17" s="106"/>
-      <c r="F17" s="106"/>
-      <c r="G17" s="108"/>
-      <c r="H17" s="108"/>
-      <c r="I17" s="110"/>
+      <c r="A17" s="123"/>
+      <c r="B17" s="108"/>
+      <c r="C17" s="108"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="131"/>
+      <c r="H17" s="131"/>
+      <c r="I17" s="137"/>
       <c r="J17" s="23">
         <v>3</v>
       </c>
@@ -4957,25 +4957,25 @@
       </c>
     </row>
     <row r="18" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="103"/>
-      <c r="B18" s="132">
+      <c r="A18" s="123"/>
+      <c r="B18" s="119">
         <v>46197</v>
       </c>
-      <c r="C18" s="143">
+      <c r="C18" s="107">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D18" s="137" t="s">
+      <c r="D18" s="99" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="111" t="s">
+      <c r="E18" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="111" t="s">
+      <c r="F18" s="132" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="113"/>
-      <c r="H18" s="113"/>
-      <c r="I18" s="112" t="str">
+      <c r="G18" s="130"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="136" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -5096,15 +5096,15 @@
       </c>
     </row>
     <row r="19" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="104"/>
-      <c r="B19" s="133"/>
-      <c r="C19" s="133"/>
-      <c r="D19" s="106"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="108"/>
-      <c r="I19" s="110"/>
+      <c r="A19" s="124"/>
+      <c r="B19" s="108"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="131"/>
+      <c r="H19" s="131"/>
+      <c r="I19" s="137"/>
       <c r="J19" s="26">
         <v>3</v>
       </c>
@@ -5222,31 +5222,31 @@
       </c>
     </row>
     <row r="20" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="114" t="s">
-        <v>2</v>
-      </c>
-      <c r="B20" s="130">
+      <c r="A20" s="133" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="118">
         <v>46185</v>
       </c>
-      <c r="C20" s="138">
+      <c r="C20" s="109">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D20" s="147" t="s">
+      <c r="D20" s="101" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="117" t="s">
+      <c r="E20" s="127" t="s">
         <v>35</v>
       </c>
-      <c r="F20" s="117" t="s">
+      <c r="F20" s="127" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="119">
+      <c r="G20" s="128">
         <v>1</v>
       </c>
-      <c r="H20" s="119">
+      <c r="H20" s="128">
         <v>1</v>
       </c>
-      <c r="I20" s="121" t="str">
+      <c r="I20" s="125" t="str">
         <f t="shared" si="0"/>
         <v>E</v>
       </c>
@@ -5367,15 +5367,15 @@
       </c>
     </row>
     <row r="21" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="115"/>
-      <c r="B21" s="131"/>
-      <c r="C21" s="131"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="118"/>
-      <c r="F21" s="118"/>
-      <c r="G21" s="120"/>
-      <c r="H21" s="120"/>
-      <c r="I21" s="122"/>
+      <c r="A21" s="134"/>
+      <c r="B21" s="110"/>
+      <c r="C21" s="110"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="102"/>
+      <c r="F21" s="102"/>
+      <c r="G21" s="129"/>
+      <c r="H21" s="129"/>
+      <c r="I21" s="126"/>
       <c r="J21" s="27">
         <v>2</v>
       </c>
@@ -5493,29 +5493,29 @@
       </c>
     </row>
     <row r="22" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="115"/>
-      <c r="B22" s="130">
+      <c r="A22" s="134"/>
+      <c r="B22" s="118">
         <v>46186</v>
       </c>
-      <c r="C22" s="130" t="s">
+      <c r="C22" s="118" t="s">
         <v>136</v>
       </c>
-      <c r="D22" s="148" t="s">
+      <c r="D22" s="112" t="s">
         <v>85</v>
       </c>
-      <c r="E22" s="117" t="s">
+      <c r="E22" s="127" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="117" t="s">
+      <c r="F22" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="119">
+      <c r="G22" s="128">
         <v>1</v>
       </c>
-      <c r="H22" s="119">
+      <c r="H22" s="128">
         <v>1</v>
       </c>
-      <c r="I22" s="121" t="str">
+      <c r="I22" s="125" t="str">
         <f t="shared" si="0"/>
         <v>E</v>
       </c>
@@ -5636,15 +5636,15 @@
       </c>
     </row>
     <row r="23" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="115"/>
-      <c r="B23" s="131"/>
-      <c r="C23" s="131"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="118"/>
-      <c r="G23" s="120"/>
-      <c r="H23" s="120"/>
-      <c r="I23" s="122"/>
+      <c r="A23" s="134"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="102"/>
+      <c r="E23" s="102"/>
+      <c r="F23" s="102"/>
+      <c r="G23" s="129"/>
+      <c r="H23" s="129"/>
+      <c r="I23" s="126"/>
       <c r="J23" s="26">
         <v>2</v>
       </c>
@@ -5762,25 +5762,25 @@
       </c>
     </row>
     <row r="24" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="115"/>
-      <c r="B24" s="130">
+      <c r="A24" s="134"/>
+      <c r="B24" s="118">
         <v>46191</v>
       </c>
-      <c r="C24" s="138">
+      <c r="C24" s="109">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D24" s="147" t="s">
+      <c r="D24" s="101" t="s">
         <v>82</v>
       </c>
-      <c r="E24" s="117" t="s">
+      <c r="E24" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="F24" s="117" t="s">
+      <c r="F24" s="127" t="s">
         <v>37</v>
       </c>
-      <c r="G24" s="119"/>
-      <c r="H24" s="119"/>
-      <c r="I24" s="121" t="str">
+      <c r="G24" s="128"/>
+      <c r="H24" s="128"/>
+      <c r="I24" s="125" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -5901,15 +5901,15 @@
       </c>
     </row>
     <row r="25" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="115"/>
-      <c r="B25" s="131"/>
-      <c r="C25" s="131"/>
-      <c r="D25" s="118"/>
-      <c r="E25" s="118"/>
-      <c r="F25" s="118"/>
-      <c r="G25" s="120"/>
-      <c r="H25" s="120"/>
-      <c r="I25" s="122"/>
+      <c r="A25" s="134"/>
+      <c r="B25" s="110"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="102"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="102"/>
+      <c r="G25" s="129"/>
+      <c r="H25" s="129"/>
+      <c r="I25" s="126"/>
       <c r="J25" s="27">
         <v>3</v>
       </c>
@@ -6027,25 +6027,25 @@
       </c>
     </row>
     <row r="26" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="115"/>
-      <c r="B26" s="130">
+      <c r="A26" s="134"/>
+      <c r="B26" s="118">
         <v>46191</v>
       </c>
-      <c r="C26" s="138">
+      <c r="C26" s="109">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D26" s="147" t="s">
+      <c r="D26" s="101" t="s">
         <v>92</v>
       </c>
-      <c r="E26" s="117" t="s">
+      <c r="E26" s="127" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="117" t="s">
+      <c r="F26" s="127" t="s">
         <v>36</v>
       </c>
-      <c r="G26" s="119"/>
-      <c r="H26" s="119"/>
-      <c r="I26" s="121" t="str">
+      <c r="G26" s="128"/>
+      <c r="H26" s="128"/>
+      <c r="I26" s="125" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -6166,15 +6166,15 @@
       </c>
     </row>
     <row r="27" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="115"/>
-      <c r="B27" s="131"/>
-      <c r="C27" s="131"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="118"/>
-      <c r="F27" s="118"/>
-      <c r="G27" s="120"/>
-      <c r="H27" s="120"/>
-      <c r="I27" s="122"/>
+      <c r="A27" s="134"/>
+      <c r="B27" s="110"/>
+      <c r="C27" s="110"/>
+      <c r="D27" s="102"/>
+      <c r="E27" s="102"/>
+      <c r="F27" s="102"/>
+      <c r="G27" s="129"/>
+      <c r="H27" s="129"/>
+      <c r="I27" s="126"/>
       <c r="J27" s="26">
         <v>3</v>
       </c>
@@ -6292,25 +6292,25 @@
       </c>
     </row>
     <row r="28" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="115"/>
-      <c r="B28" s="130">
+      <c r="A28" s="134"/>
+      <c r="B28" s="118">
         <v>46197</v>
       </c>
-      <c r="C28" s="138">
+      <c r="C28" s="109">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D28" s="147" t="s">
+      <c r="D28" s="101" t="s">
         <v>92</v>
       </c>
-      <c r="E28" s="117" t="s">
+      <c r="E28" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="F28" s="117" t="s">
+      <c r="F28" s="127" t="s">
         <v>35</v>
       </c>
-      <c r="G28" s="119"/>
-      <c r="H28" s="119"/>
-      <c r="I28" s="121" t="str">
+      <c r="G28" s="128"/>
+      <c r="H28" s="128"/>
+      <c r="I28" s="125" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -6431,15 +6431,15 @@
       </c>
     </row>
     <row r="29" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="115"/>
-      <c r="B29" s="131"/>
-      <c r="C29" s="131"/>
-      <c r="D29" s="118"/>
-      <c r="E29" s="118"/>
-      <c r="F29" s="118"/>
-      <c r="G29" s="120"/>
-      <c r="H29" s="120"/>
-      <c r="I29" s="122"/>
+      <c r="A29" s="134"/>
+      <c r="B29" s="110"/>
+      <c r="C29" s="110"/>
+      <c r="D29" s="102"/>
+      <c r="E29" s="102"/>
+      <c r="F29" s="102"/>
+      <c r="G29" s="129"/>
+      <c r="H29" s="129"/>
+      <c r="I29" s="126"/>
       <c r="J29" s="27">
         <v>1</v>
       </c>
@@ -6557,25 +6557,25 @@
       </c>
     </row>
     <row r="30" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="115"/>
-      <c r="B30" s="130">
+      <c r="A30" s="134"/>
+      <c r="B30" s="118">
         <v>46197</v>
       </c>
-      <c r="C30" s="138">
+      <c r="C30" s="109">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D30" s="147" t="s">
+      <c r="D30" s="101" t="s">
         <v>86</v>
       </c>
-      <c r="E30" s="117" t="s">
+      <c r="E30" s="127" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="117" t="s">
+      <c r="F30" s="127" t="s">
         <v>36</v>
       </c>
-      <c r="G30" s="119"/>
-      <c r="H30" s="119"/>
-      <c r="I30" s="121" t="str">
+      <c r="G30" s="128"/>
+      <c r="H30" s="128"/>
+      <c r="I30" s="125" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -6696,15 +6696,15 @@
       </c>
     </row>
     <row r="31" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="116"/>
-      <c r="B31" s="131"/>
-      <c r="C31" s="131"/>
-      <c r="D31" s="118"/>
-      <c r="E31" s="118"/>
-      <c r="F31" s="118"/>
-      <c r="G31" s="120"/>
-      <c r="H31" s="120"/>
-      <c r="I31" s="122"/>
+      <c r="A31" s="135"/>
+      <c r="B31" s="110"/>
+      <c r="C31" s="110"/>
+      <c r="D31" s="102"/>
+      <c r="E31" s="102"/>
+      <c r="F31" s="102"/>
+      <c r="G31" s="129"/>
+      <c r="H31" s="129"/>
+      <c r="I31" s="126"/>
       <c r="J31" s="26">
         <v>0</v>
       </c>
@@ -6818,31 +6818,31 @@
       </c>
     </row>
     <row r="32" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="125" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" s="132">
+      <c r="A32" s="122" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="119">
         <v>46186</v>
       </c>
-      <c r="C32" s="143">
+      <c r="C32" s="107">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D32" s="137" t="s">
+      <c r="D32" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="111" t="s">
+      <c r="E32" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="F32" s="123" t="s">
+      <c r="F32" s="142" t="s">
         <v>40</v>
       </c>
-      <c r="G32" s="113">
+      <c r="G32" s="130">
         <v>1</v>
       </c>
-      <c r="H32" s="113">
+      <c r="H32" s="130">
         <v>1</v>
       </c>
-      <c r="I32" s="112" t="str">
+      <c r="I32" s="136" t="str">
         <f t="shared" si="0"/>
         <v>E</v>
       </c>
@@ -6959,15 +6959,15 @@
       </c>
     </row>
     <row r="33" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="103"/>
-      <c r="B33" s="133"/>
-      <c r="C33" s="133"/>
-      <c r="D33" s="106"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="124"/>
-      <c r="G33" s="108"/>
-      <c r="H33" s="108"/>
-      <c r="I33" s="110"/>
+      <c r="A33" s="123"/>
+      <c r="B33" s="108"/>
+      <c r="C33" s="108"/>
+      <c r="D33" s="100"/>
+      <c r="E33" s="100"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="131"/>
+      <c r="H33" s="131"/>
+      <c r="I33" s="137"/>
       <c r="J33" s="23">
         <v>4</v>
       </c>
@@ -7081,29 +7081,29 @@
       </c>
     </row>
     <row r="34" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="103"/>
-      <c r="B34" s="132">
+      <c r="A34" s="123"/>
+      <c r="B34" s="119">
         <v>46186</v>
       </c>
-      <c r="C34" s="143">
+      <c r="C34" s="107">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D34" s="137" t="s">
+      <c r="D34" s="99" t="s">
         <v>80</v>
       </c>
-      <c r="E34" s="111" t="s">
+      <c r="E34" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="F34" s="111" t="s">
+      <c r="F34" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="G34" s="113">
-        <v>0</v>
-      </c>
-      <c r="H34" s="113">
+      <c r="G34" s="130">
+        <v>0</v>
+      </c>
+      <c r="H34" s="130">
         <v>1</v>
       </c>
-      <c r="I34" s="112" t="str">
+      <c r="I34" s="136" t="str">
         <f t="shared" si="0"/>
         <v>V</v>
       </c>
@@ -7220,15 +7220,15 @@
       </c>
     </row>
     <row r="35" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="103"/>
-      <c r="B35" s="133"/>
-      <c r="C35" s="133"/>
-      <c r="D35" s="106"/>
-      <c r="E35" s="106"/>
-      <c r="F35" s="106"/>
-      <c r="G35" s="108"/>
-      <c r="H35" s="108"/>
-      <c r="I35" s="110"/>
+      <c r="A35" s="123"/>
+      <c r="B35" s="108"/>
+      <c r="C35" s="108"/>
+      <c r="D35" s="100"/>
+      <c r="E35" s="100"/>
+      <c r="F35" s="100"/>
+      <c r="G35" s="131"/>
+      <c r="H35" s="131"/>
+      <c r="I35" s="137"/>
       <c r="J35" s="26">
         <v>3</v>
       </c>
@@ -7342,25 +7342,25 @@
       </c>
     </row>
     <row r="36" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="103"/>
-      <c r="B36" s="132">
+      <c r="A36" s="123"/>
+      <c r="B36" s="119">
         <v>46192</v>
       </c>
-      <c r="C36" s="143">
+      <c r="C36" s="107">
         <v>0.77083333333333337</v>
       </c>
-      <c r="D36" s="137" t="s">
+      <c r="D36" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="E36" s="111" t="s">
+      <c r="E36" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="F36" s="123" t="s">
+      <c r="F36" s="142" t="s">
         <v>39</v>
       </c>
-      <c r="G36" s="113"/>
-      <c r="H36" s="113"/>
-      <c r="I36" s="112" t="str">
+      <c r="G36" s="130"/>
+      <c r="H36" s="130"/>
+      <c r="I36" s="136" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -7477,15 +7477,15 @@
       </c>
     </row>
     <row r="37" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="103"/>
-      <c r="B37" s="133"/>
-      <c r="C37" s="133"/>
-      <c r="D37" s="106"/>
-      <c r="E37" s="106"/>
-      <c r="F37" s="124"/>
-      <c r="G37" s="108"/>
-      <c r="H37" s="108"/>
-      <c r="I37" s="110"/>
+      <c r="A37" s="123"/>
+      <c r="B37" s="108"/>
+      <c r="C37" s="108"/>
+      <c r="D37" s="100"/>
+      <c r="E37" s="100"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="131"/>
+      <c r="H37" s="131"/>
+      <c r="I37" s="137"/>
       <c r="J37" s="23">
         <v>4</v>
       </c>
@@ -7599,25 +7599,25 @@
       </c>
     </row>
     <row r="38" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="103"/>
-      <c r="B38" s="132">
+      <c r="A38" s="123"/>
+      <c r="B38" s="119">
         <v>46192</v>
       </c>
-      <c r="C38" s="143">
+      <c r="C38" s="107">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D38" s="137" t="s">
+      <c r="D38" s="99" t="s">
         <v>80</v>
       </c>
-      <c r="E38" s="111" t="s">
+      <c r="E38" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="F38" s="111" t="s">
+      <c r="F38" s="132" t="s">
         <v>40</v>
       </c>
-      <c r="G38" s="113"/>
-      <c r="H38" s="113"/>
-      <c r="I38" s="112" t="str">
+      <c r="G38" s="130"/>
+      <c r="H38" s="130"/>
+      <c r="I38" s="136" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -7734,15 +7734,15 @@
       </c>
     </row>
     <row r="39" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="103"/>
-      <c r="B39" s="133"/>
-      <c r="C39" s="133"/>
-      <c r="D39" s="106"/>
-      <c r="E39" s="106"/>
-      <c r="F39" s="106"/>
-      <c r="G39" s="108"/>
-      <c r="H39" s="108"/>
-      <c r="I39" s="110"/>
+      <c r="A39" s="123"/>
+      <c r="B39" s="108"/>
+      <c r="C39" s="108"/>
+      <c r="D39" s="100"/>
+      <c r="E39" s="100"/>
+      <c r="F39" s="100"/>
+      <c r="G39" s="131"/>
+      <c r="H39" s="131"/>
+      <c r="I39" s="137"/>
       <c r="J39" s="26">
         <v>3</v>
       </c>
@@ -7856,25 +7856,25 @@
       </c>
     </row>
     <row r="40" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="103"/>
-      <c r="B40" s="139">
+      <c r="A40" s="123"/>
+      <c r="B40" s="121">
         <v>46197</v>
       </c>
-      <c r="C40" s="144">
+      <c r="C40" s="115">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D40" s="149" t="s">
+      <c r="D40" s="103" t="s">
         <v>91</v>
       </c>
-      <c r="E40" s="123" t="s">
+      <c r="E40" s="142" t="s">
         <v>27</v>
       </c>
-      <c r="F40" s="111" t="s">
+      <c r="F40" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="G40" s="113"/>
-      <c r="H40" s="113"/>
-      <c r="I40" s="112" t="str">
+      <c r="G40" s="130"/>
+      <c r="H40" s="130"/>
+      <c r="I40" s="136" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -7991,15 +7991,15 @@
       </c>
     </row>
     <row r="41" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="103"/>
-      <c r="B41" s="140"/>
-      <c r="C41" s="140"/>
-      <c r="D41" s="124"/>
-      <c r="E41" s="124"/>
-      <c r="F41" s="106"/>
-      <c r="G41" s="108"/>
-      <c r="H41" s="108"/>
-      <c r="I41" s="110"/>
+      <c r="A41" s="123"/>
+      <c r="B41" s="116"/>
+      <c r="C41" s="116"/>
+      <c r="D41" s="104"/>
+      <c r="E41" s="104"/>
+      <c r="F41" s="100"/>
+      <c r="G41" s="131"/>
+      <c r="H41" s="131"/>
+      <c r="I41" s="137"/>
       <c r="J41" s="23">
         <v>2</v>
       </c>
@@ -8113,25 +8113,25 @@
       </c>
     </row>
     <row r="42" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="103"/>
-      <c r="B42" s="132">
+      <c r="A42" s="123"/>
+      <c r="B42" s="119">
         <v>46197</v>
       </c>
-      <c r="C42" s="143">
+      <c r="C42" s="107">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D42" s="137" t="s">
+      <c r="D42" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="E42" s="111" t="s">
+      <c r="E42" s="132" t="s">
         <v>40</v>
       </c>
-      <c r="F42" s="111" t="s">
+      <c r="F42" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="G42" s="113"/>
-      <c r="H42" s="113"/>
-      <c r="I42" s="112" t="str">
+      <c r="G42" s="130"/>
+      <c r="H42" s="130"/>
+      <c r="I42" s="136" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -8248,15 +8248,15 @@
       </c>
     </row>
     <row r="43" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="104"/>
-      <c r="B43" s="133"/>
-      <c r="C43" s="133"/>
-      <c r="D43" s="106"/>
-      <c r="E43" s="106"/>
-      <c r="F43" s="106"/>
-      <c r="G43" s="108"/>
-      <c r="H43" s="108"/>
-      <c r="I43" s="110"/>
+      <c r="A43" s="124"/>
+      <c r="B43" s="108"/>
+      <c r="C43" s="108"/>
+      <c r="D43" s="100"/>
+      <c r="E43" s="100"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="131"/>
+      <c r="H43" s="131"/>
+      <c r="I43" s="137"/>
       <c r="J43" s="26">
         <v>5</v>
       </c>
@@ -8370,31 +8370,31 @@
       </c>
     </row>
     <row r="44" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="114" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" s="130">
+      <c r="A44" s="133" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="118">
         <v>46185</v>
       </c>
-      <c r="C44" s="138">
+      <c r="C44" s="109">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D44" s="147" t="s">
+      <c r="D44" s="101" t="s">
         <v>82</v>
       </c>
-      <c r="E44" s="117" t="s">
+      <c r="E44" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="F44" s="117" t="s">
+      <c r="F44" s="127" t="s">
         <v>43</v>
       </c>
-      <c r="G44" s="119">
-        <v>4</v>
-      </c>
-      <c r="H44" s="119">
+      <c r="G44" s="128">
+        <v>4</v>
+      </c>
+      <c r="H44" s="128">
         <v>1</v>
       </c>
-      <c r="I44" s="121" t="str">
+      <c r="I44" s="125" t="str">
         <f t="shared" si="0"/>
         <v>L</v>
       </c>
@@ -8511,15 +8511,15 @@
       </c>
     </row>
     <row r="45" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="115"/>
-      <c r="B45" s="131"/>
-      <c r="C45" s="131"/>
-      <c r="D45" s="118"/>
-      <c r="E45" s="118"/>
-      <c r="F45" s="118"/>
-      <c r="G45" s="120"/>
-      <c r="H45" s="120"/>
-      <c r="I45" s="122"/>
+      <c r="A45" s="134"/>
+      <c r="B45" s="110"/>
+      <c r="C45" s="110"/>
+      <c r="D45" s="102"/>
+      <c r="E45" s="102"/>
+      <c r="F45" s="102"/>
+      <c r="G45" s="129"/>
+      <c r="H45" s="129"/>
+      <c r="I45" s="126"/>
       <c r="J45" s="27">
         <v>1</v>
       </c>
@@ -8633,29 +8633,29 @@
       </c>
     </row>
     <row r="46" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="115"/>
-      <c r="B46" s="130">
+      <c r="A46" s="134"/>
+      <c r="B46" s="118">
         <v>46186</v>
       </c>
-      <c r="C46" s="138">
+      <c r="C46" s="109">
         <v>0.91666666666666663</v>
       </c>
-      <c r="D46" s="147" t="s">
+      <c r="D46" s="101" t="s">
         <v>92</v>
       </c>
-      <c r="E46" s="117" t="s">
+      <c r="E46" s="127" t="s">
         <v>42</v>
       </c>
-      <c r="F46" s="126" t="s">
+      <c r="F46" s="141" t="s">
         <v>30</v>
       </c>
-      <c r="G46" s="119">
-        <v>0</v>
-      </c>
-      <c r="H46" s="119">
-        <v>2</v>
-      </c>
-      <c r="I46" s="121" t="str">
+      <c r="G46" s="128">
+        <v>0</v>
+      </c>
+      <c r="H46" s="128">
+        <v>2</v>
+      </c>
+      <c r="I46" s="125" t="str">
         <f t="shared" si="0"/>
         <v>V</v>
       </c>
@@ -8772,15 +8772,15 @@
       </c>
     </row>
     <row r="47" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="115"/>
-      <c r="B47" s="131"/>
-      <c r="C47" s="131"/>
-      <c r="D47" s="118"/>
-      <c r="E47" s="118"/>
-      <c r="F47" s="127"/>
-      <c r="G47" s="120"/>
-      <c r="H47" s="120"/>
-      <c r="I47" s="122"/>
+      <c r="A47" s="134"/>
+      <c r="B47" s="110"/>
+      <c r="C47" s="110"/>
+      <c r="D47" s="102"/>
+      <c r="E47" s="102"/>
+      <c r="F47" s="106"/>
+      <c r="G47" s="129"/>
+      <c r="H47" s="129"/>
+      <c r="I47" s="126"/>
       <c r="J47" s="26">
         <v>2</v>
       </c>
@@ -8894,25 +8894,25 @@
       </c>
     </row>
     <row r="48" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="115"/>
-      <c r="B48" s="130">
+      <c r="A48" s="134"/>
+      <c r="B48" s="118">
         <v>46192</v>
       </c>
-      <c r="C48" s="138">
+      <c r="C48" s="109">
         <v>0.875</v>
       </c>
-      <c r="D48" s="147" t="s">
+      <c r="D48" s="101" t="s">
         <v>85</v>
       </c>
-      <c r="E48" s="117" t="s">
+      <c r="E48" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="F48" s="126" t="s">
+      <c r="F48" s="141" t="s">
         <v>44</v>
       </c>
-      <c r="G48" s="119"/>
-      <c r="H48" s="119"/>
-      <c r="I48" s="121" t="str">
+      <c r="G48" s="128"/>
+      <c r="H48" s="128"/>
+      <c r="I48" s="125" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -9029,15 +9029,15 @@
       </c>
     </row>
     <row r="49" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="115"/>
-      <c r="B49" s="131"/>
-      <c r="C49" s="131"/>
-      <c r="D49" s="118"/>
-      <c r="E49" s="118"/>
-      <c r="F49" s="127"/>
-      <c r="G49" s="120"/>
-      <c r="H49" s="120"/>
-      <c r="I49" s="122"/>
+      <c r="A49" s="134"/>
+      <c r="B49" s="110"/>
+      <c r="C49" s="110"/>
+      <c r="D49" s="102"/>
+      <c r="E49" s="102"/>
+      <c r="F49" s="106"/>
+      <c r="G49" s="129"/>
+      <c r="H49" s="129"/>
+      <c r="I49" s="126"/>
       <c r="J49" s="27">
         <v>2</v>
       </c>
@@ -9151,25 +9151,25 @@
       </c>
     </row>
     <row r="50" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="115"/>
-      <c r="B50" s="130">
+      <c r="A50" s="134"/>
+      <c r="B50" s="118">
         <v>46192</v>
       </c>
-      <c r="C50" s="138">
+      <c r="C50" s="109">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D50" s="147" t="s">
+      <c r="D50" s="101" t="s">
         <v>86</v>
       </c>
-      <c r="E50" s="117" t="s">
+      <c r="E50" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="F50" s="117" t="s">
+      <c r="F50" s="127" t="s">
         <v>42</v>
       </c>
-      <c r="G50" s="119"/>
-      <c r="H50" s="119"/>
-      <c r="I50" s="121" t="str">
+      <c r="G50" s="128"/>
+      <c r="H50" s="128"/>
+      <c r="I50" s="125" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -9286,15 +9286,15 @@
       </c>
     </row>
     <row r="51" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="115"/>
-      <c r="B51" s="131"/>
-      <c r="C51" s="131"/>
-      <c r="D51" s="118"/>
-      <c r="E51" s="118"/>
-      <c r="F51" s="118"/>
-      <c r="G51" s="120"/>
-      <c r="H51" s="120"/>
-      <c r="I51" s="122"/>
+      <c r="A51" s="134"/>
+      <c r="B51" s="110"/>
+      <c r="C51" s="110"/>
+      <c r="D51" s="102"/>
+      <c r="E51" s="102"/>
+      <c r="F51" s="102"/>
+      <c r="G51" s="129"/>
+      <c r="H51" s="129"/>
+      <c r="I51" s="126"/>
       <c r="J51" s="26">
         <v>3</v>
       </c>
@@ -9408,25 +9408,25 @@
       </c>
     </row>
     <row r="52" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="115"/>
-      <c r="B52" s="130">
+      <c r="A52" s="134"/>
+      <c r="B52" s="118">
         <v>46198</v>
       </c>
-      <c r="C52" s="138">
+      <c r="C52" s="109">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D52" s="147" t="s">
+      <c r="D52" s="101" t="s">
         <v>82</v>
       </c>
-      <c r="E52" s="117" t="s">
+      <c r="E52" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="F52" s="117" t="s">
+      <c r="F52" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="G52" s="119"/>
-      <c r="H52" s="119"/>
-      <c r="I52" s="121" t="str">
+      <c r="G52" s="128"/>
+      <c r="H52" s="128"/>
+      <c r="I52" s="125" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -9543,15 +9543,15 @@
       </c>
     </row>
     <row r="53" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="115"/>
-      <c r="B53" s="131"/>
-      <c r="C53" s="131"/>
-      <c r="D53" s="118"/>
-      <c r="E53" s="118"/>
-      <c r="F53" s="118"/>
-      <c r="G53" s="120"/>
-      <c r="H53" s="120"/>
-      <c r="I53" s="122"/>
+      <c r="A53" s="134"/>
+      <c r="B53" s="110"/>
+      <c r="C53" s="110"/>
+      <c r="D53" s="102"/>
+      <c r="E53" s="102"/>
+      <c r="F53" s="102"/>
+      <c r="G53" s="129"/>
+      <c r="H53" s="129"/>
+      <c r="I53" s="126"/>
       <c r="J53" s="27">
         <v>4</v>
       </c>
@@ -9665,25 +9665,25 @@
       </c>
     </row>
     <row r="54" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="115"/>
-      <c r="B54" s="128">
+      <c r="A54" s="134"/>
+      <c r="B54" s="143">
         <v>46198</v>
       </c>
-      <c r="C54" s="145">
+      <c r="C54" s="113">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D54" s="150" t="s">
+      <c r="D54" s="105" t="s">
         <v>85</v>
       </c>
-      <c r="E54" s="126" t="s">
+      <c r="E54" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="F54" s="117" t="s">
+      <c r="F54" s="127" t="s">
         <v>42</v>
       </c>
-      <c r="G54" s="119"/>
-      <c r="H54" s="119"/>
-      <c r="I54" s="121" t="str">
+      <c r="G54" s="128"/>
+      <c r="H54" s="128"/>
+      <c r="I54" s="125" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -9800,15 +9800,15 @@
       </c>
     </row>
     <row r="55" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="116"/>
-      <c r="B55" s="129"/>
-      <c r="C55" s="129"/>
-      <c r="D55" s="127"/>
-      <c r="E55" s="127"/>
-      <c r="F55" s="118"/>
-      <c r="G55" s="120"/>
-      <c r="H55" s="120"/>
-      <c r="I55" s="122"/>
+      <c r="A55" s="135"/>
+      <c r="B55" s="114"/>
+      <c r="C55" s="114"/>
+      <c r="D55" s="106"/>
+      <c r="E55" s="106"/>
+      <c r="F55" s="102"/>
+      <c r="G55" s="129"/>
+      <c r="H55" s="129"/>
+      <c r="I55" s="126"/>
       <c r="J55" s="26">
         <v>1</v>
       </c>
@@ -9922,29 +9922,33 @@
       </c>
     </row>
     <row r="56" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="125" t="s">
-        <v>16</v>
-      </c>
-      <c r="B56" s="132">
+      <c r="A56" s="122" t="s">
+        <v>16</v>
+      </c>
+      <c r="B56" s="119">
         <v>46187</v>
       </c>
-      <c r="C56" s="143">
+      <c r="C56" s="107">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D56" s="137" t="s">
+      <c r="D56" s="99" t="s">
         <v>87</v>
       </c>
-      <c r="E56" s="111" t="s">
+      <c r="E56" s="132" t="s">
         <v>23</v>
       </c>
-      <c r="F56" s="111" t="s">
+      <c r="F56" s="132" t="s">
         <v>47</v>
       </c>
-      <c r="G56" s="113"/>
-      <c r="H56" s="113"/>
-      <c r="I56" s="112" t="str">
+      <c r="G56" s="130">
+        <v>7</v>
+      </c>
+      <c r="H56" s="130">
+        <v>1</v>
+      </c>
+      <c r="I56" s="136" t="str">
         <f>IF(G56="","-",IF(G56&gt;H56,"L",IF(G56=H56,"E",IF(G56&lt;H56,"V"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="J56" s="23" t="s">
         <v>7</v>
@@ -10059,15 +10063,15 @@
       </c>
     </row>
     <row r="57" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="103"/>
-      <c r="B57" s="133"/>
-      <c r="C57" s="133"/>
-      <c r="D57" s="106"/>
-      <c r="E57" s="106"/>
-      <c r="F57" s="106"/>
-      <c r="G57" s="108"/>
-      <c r="H57" s="108"/>
-      <c r="I57" s="110"/>
+      <c r="A57" s="123"/>
+      <c r="B57" s="108"/>
+      <c r="C57" s="108"/>
+      <c r="D57" s="100"/>
+      <c r="E57" s="100"/>
+      <c r="F57" s="100"/>
+      <c r="G57" s="131"/>
+      <c r="H57" s="131"/>
+      <c r="I57" s="137"/>
       <c r="J57" s="23">
         <v>3</v>
       </c>
@@ -10181,25 +10185,25 @@
       </c>
     </row>
     <row r="58" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="103"/>
-      <c r="B58" s="132">
+      <c r="A58" s="123"/>
+      <c r="B58" s="119">
         <v>46187</v>
       </c>
-      <c r="C58" s="143">
+      <c r="C58" s="107">
         <v>0.70833333333333337</v>
       </c>
-      <c r="D58" s="137" t="s">
+      <c r="D58" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="E58" s="111" t="s">
+      <c r="E58" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="F58" s="111" t="s">
+      <c r="F58" s="132" t="s">
         <v>46</v>
       </c>
-      <c r="G58" s="113"/>
-      <c r="H58" s="113"/>
-      <c r="I58" s="112" t="str">
+      <c r="G58" s="130"/>
+      <c r="H58" s="130"/>
+      <c r="I58" s="136" t="str">
         <f t="shared" ref="I58" si="1">IF(G58="","-",IF(G58&gt;H58,"L",IF(G58=H58,"E",IF(G58&lt;H58,"V"))))</f>
         <v>-</v>
       </c>
@@ -10316,15 +10320,15 @@
       </c>
     </row>
     <row r="59" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="103"/>
-      <c r="B59" s="133"/>
-      <c r="C59" s="133"/>
-      <c r="D59" s="106"/>
-      <c r="E59" s="106"/>
-      <c r="F59" s="106"/>
-      <c r="G59" s="108"/>
-      <c r="H59" s="108"/>
-      <c r="I59" s="110"/>
+      <c r="A59" s="123"/>
+      <c r="B59" s="108"/>
+      <c r="C59" s="108"/>
+      <c r="D59" s="100"/>
+      <c r="E59" s="100"/>
+      <c r="F59" s="100"/>
+      <c r="G59" s="131"/>
+      <c r="H59" s="131"/>
+      <c r="I59" s="137"/>
       <c r="J59" s="26">
         <v>3</v>
       </c>
@@ -10438,25 +10442,25 @@
       </c>
     </row>
     <row r="60" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="103"/>
-      <c r="B60" s="132">
+      <c r="A60" s="123"/>
+      <c r="B60" s="119">
         <v>46193</v>
       </c>
-      <c r="C60" s="143">
+      <c r="C60" s="107">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D60" s="137" t="s">
+      <c r="D60" s="99" t="s">
         <v>84</v>
       </c>
-      <c r="E60" s="111" t="s">
+      <c r="E60" s="132" t="s">
         <v>23</v>
       </c>
-      <c r="F60" s="111" t="s">
+      <c r="F60" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="112" t="str">
+      <c r="G60" s="130"/>
+      <c r="H60" s="130"/>
+      <c r="I60" s="136" t="str">
         <f t="shared" ref="I60" si="2">IF(G60="","-",IF(G60&gt;H60,"L",IF(G60=H60,"E",IF(G60&lt;H60,"V"))))</f>
         <v>-</v>
       </c>
@@ -10573,15 +10577,15 @@
       </c>
     </row>
     <row r="61" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="103"/>
-      <c r="B61" s="133"/>
-      <c r="C61" s="133"/>
-      <c r="D61" s="106"/>
-      <c r="E61" s="106"/>
-      <c r="F61" s="106"/>
-      <c r="G61" s="108"/>
-      <c r="H61" s="108"/>
-      <c r="I61" s="110"/>
+      <c r="A61" s="123"/>
+      <c r="B61" s="108"/>
+      <c r="C61" s="108"/>
+      <c r="D61" s="100"/>
+      <c r="E61" s="100"/>
+      <c r="F61" s="100"/>
+      <c r="G61" s="131"/>
+      <c r="H61" s="131"/>
+      <c r="I61" s="137"/>
       <c r="J61" s="23">
         <v>3</v>
       </c>
@@ -10695,25 +10699,25 @@
       </c>
     </row>
     <row r="62" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="103"/>
-      <c r="B62" s="132">
+      <c r="A62" s="123"/>
+      <c r="B62" s="119">
         <v>46193</v>
       </c>
-      <c r="C62" s="143">
+      <c r="C62" s="107">
         <v>0.75</v>
       </c>
-      <c r="D62" s="137" t="s">
+      <c r="D62" s="99" t="s">
         <v>93</v>
       </c>
-      <c r="E62" s="111" t="s">
+      <c r="E62" s="132" t="s">
         <v>46</v>
       </c>
-      <c r="F62" s="111" t="s">
+      <c r="F62" s="132" t="s">
         <v>47</v>
       </c>
-      <c r="G62" s="113"/>
-      <c r="H62" s="113"/>
-      <c r="I62" s="112" t="str">
+      <c r="G62" s="130"/>
+      <c r="H62" s="130"/>
+      <c r="I62" s="136" t="str">
         <f t="shared" ref="I62" si="3">IF(G62="","-",IF(G62&gt;H62,"L",IF(G62=H62,"E",IF(G62&lt;H62,"V"))))</f>
         <v>-</v>
       </c>
@@ -10830,15 +10834,15 @@
       </c>
     </row>
     <row r="63" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="103"/>
-      <c r="B63" s="133"/>
-      <c r="C63" s="133"/>
-      <c r="D63" s="106"/>
-      <c r="E63" s="106"/>
-      <c r="F63" s="106"/>
-      <c r="G63" s="108"/>
-      <c r="H63" s="108"/>
-      <c r="I63" s="110"/>
+      <c r="A63" s="123"/>
+      <c r="B63" s="108"/>
+      <c r="C63" s="108"/>
+      <c r="D63" s="100"/>
+      <c r="E63" s="100"/>
+      <c r="F63" s="100"/>
+      <c r="G63" s="131"/>
+      <c r="H63" s="131"/>
+      <c r="I63" s="137"/>
       <c r="J63" s="26">
         <v>1</v>
       </c>
@@ -10952,25 +10956,25 @@
       </c>
     </row>
     <row r="64" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="103"/>
-      <c r="B64" s="132">
+      <c r="A64" s="123"/>
+      <c r="B64" s="119">
         <v>46198</v>
       </c>
-      <c r="C64" s="143">
+      <c r="C64" s="107">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D64" s="137" t="s">
+      <c r="D64" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="E64" s="111" t="s">
+      <c r="E64" s="132" t="s">
         <v>46</v>
       </c>
-      <c r="F64" s="111" t="s">
+      <c r="F64" s="132" t="s">
         <v>23</v>
       </c>
-      <c r="G64" s="113"/>
-      <c r="H64" s="113"/>
-      <c r="I64" s="112" t="str">
+      <c r="G64" s="130"/>
+      <c r="H64" s="130"/>
+      <c r="I64" s="136" t="str">
         <f t="shared" ref="I64" si="4">IF(G64="","-",IF(G64&gt;H64,"L",IF(G64=H64,"E",IF(G64&lt;H64,"V"))))</f>
         <v>-</v>
       </c>
@@ -11087,15 +11091,15 @@
       </c>
     </row>
     <row r="65" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="103"/>
-      <c r="B65" s="133"/>
-      <c r="C65" s="133"/>
-      <c r="D65" s="106"/>
-      <c r="E65" s="106"/>
-      <c r="F65" s="106"/>
-      <c r="G65" s="108"/>
-      <c r="H65" s="108"/>
-      <c r="I65" s="110"/>
+      <c r="A65" s="123"/>
+      <c r="B65" s="108"/>
+      <c r="C65" s="108"/>
+      <c r="D65" s="100"/>
+      <c r="E65" s="100"/>
+      <c r="F65" s="100"/>
+      <c r="G65" s="131"/>
+      <c r="H65" s="131"/>
+      <c r="I65" s="137"/>
       <c r="J65" s="23">
         <v>2</v>
       </c>
@@ -11209,25 +11213,25 @@
       </c>
     </row>
     <row r="66" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="103"/>
-      <c r="B66" s="132">
+      <c r="A66" s="123"/>
+      <c r="B66" s="119">
         <v>46198</v>
       </c>
-      <c r="C66" s="143">
+      <c r="C66" s="107">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D66" s="137" t="s">
+      <c r="D66" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="E66" s="111" t="s">
+      <c r="E66" s="132" t="s">
         <v>47</v>
       </c>
-      <c r="F66" s="111" t="s">
+      <c r="F66" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="G66" s="113"/>
-      <c r="H66" s="113"/>
-      <c r="I66" s="112" t="str">
+      <c r="G66" s="130"/>
+      <c r="H66" s="130"/>
+      <c r="I66" s="136" t="str">
         <f t="shared" ref="I66" si="5">IF(G66="","-",IF(G66&gt;H66,"L",IF(G66=H66,"E",IF(G66&lt;H66,"V"))))</f>
         <v>-</v>
       </c>
@@ -11344,15 +11348,15 @@
       </c>
     </row>
     <row r="67" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="104"/>
-      <c r="B67" s="133"/>
-      <c r="C67" s="133"/>
-      <c r="D67" s="106"/>
-      <c r="E67" s="106"/>
-      <c r="F67" s="106"/>
-      <c r="G67" s="108"/>
-      <c r="H67" s="108"/>
-      <c r="I67" s="110"/>
+      <c r="A67" s="124"/>
+      <c r="B67" s="108"/>
+      <c r="C67" s="108"/>
+      <c r="D67" s="100"/>
+      <c r="E67" s="100"/>
+      <c r="F67" s="100"/>
+      <c r="G67" s="131"/>
+      <c r="H67" s="131"/>
+      <c r="I67" s="137"/>
       <c r="J67" s="26">
         <v>0</v>
       </c>
@@ -11466,27 +11470,27 @@
       </c>
     </row>
     <row r="68" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="114" t="s">
+      <c r="A68" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="B68" s="130">
+      <c r="B68" s="118">
         <v>46187</v>
       </c>
-      <c r="C68" s="138">
+      <c r="C68" s="109">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D68" s="147" t="s">
+      <c r="D68" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="E68" s="117" t="s">
+      <c r="E68" s="127" t="s">
         <v>53</v>
       </c>
-      <c r="F68" s="117" t="s">
+      <c r="F68" s="127" t="s">
         <v>56</v>
       </c>
-      <c r="G68" s="119"/>
-      <c r="H68" s="119"/>
-      <c r="I68" s="121" t="str">
+      <c r="G68" s="128"/>
+      <c r="H68" s="128"/>
+      <c r="I68" s="125" t="str">
         <f t="shared" ref="I68" si="6">IF(G68="","-",IF(G68&gt;H68,"L",IF(G68=H68,"E",IF(G68&lt;H68,"V"))))</f>
         <v>-</v>
       </c>
@@ -11603,15 +11607,15 @@
       </c>
     </row>
     <row r="69" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="115"/>
-      <c r="B69" s="131"/>
-      <c r="C69" s="131"/>
-      <c r="D69" s="118"/>
-      <c r="E69" s="118"/>
-      <c r="F69" s="118"/>
-      <c r="G69" s="120"/>
-      <c r="H69" s="120"/>
-      <c r="I69" s="122"/>
+      <c r="A69" s="134"/>
+      <c r="B69" s="110"/>
+      <c r="C69" s="110"/>
+      <c r="D69" s="102"/>
+      <c r="E69" s="102"/>
+      <c r="F69" s="102"/>
+      <c r="G69" s="129"/>
+      <c r="H69" s="129"/>
+      <c r="I69" s="126"/>
       <c r="J69" s="27">
         <v>2</v>
       </c>
@@ -11725,25 +11729,25 @@
       </c>
     </row>
     <row r="70" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="115"/>
-      <c r="B70" s="130">
+      <c r="A70" s="134"/>
+      <c r="B70" s="118">
         <v>46187</v>
       </c>
-      <c r="C70" s="138">
+      <c r="C70" s="109">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D70" s="147" t="s">
+      <c r="D70" s="101" t="s">
         <v>83</v>
       </c>
-      <c r="E70" s="117" t="s">
+      <c r="E70" s="127" t="s">
         <v>54</v>
       </c>
-      <c r="F70" s="117" t="s">
+      <c r="F70" s="127" t="s">
         <v>55</v>
       </c>
-      <c r="G70" s="119"/>
-      <c r="H70" s="119"/>
-      <c r="I70" s="121" t="str">
+      <c r="G70" s="128"/>
+      <c r="H70" s="128"/>
+      <c r="I70" s="125" t="str">
         <f t="shared" ref="I70" si="7">IF(G70="","-",IF(G70&gt;H70,"L",IF(G70=H70,"E",IF(G70&lt;H70,"V"))))</f>
         <v>-</v>
       </c>
@@ -11860,15 +11864,15 @@
       </c>
     </row>
     <row r="71" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="115"/>
-      <c r="B71" s="131"/>
-      <c r="C71" s="131"/>
-      <c r="D71" s="118"/>
-      <c r="E71" s="118"/>
-      <c r="F71" s="118"/>
-      <c r="G71" s="120"/>
-      <c r="H71" s="120"/>
-      <c r="I71" s="122"/>
+      <c r="A71" s="134"/>
+      <c r="B71" s="110"/>
+      <c r="C71" s="110"/>
+      <c r="D71" s="102"/>
+      <c r="E71" s="102"/>
+      <c r="F71" s="102"/>
+      <c r="G71" s="129"/>
+      <c r="H71" s="129"/>
+      <c r="I71" s="126"/>
       <c r="J71" s="26">
         <v>3</v>
       </c>
@@ -11982,25 +11986,25 @@
       </c>
     </row>
     <row r="72" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="115"/>
-      <c r="B72" s="130">
+      <c r="A72" s="134"/>
+      <c r="B72" s="118">
         <v>46193</v>
       </c>
-      <c r="C72" s="138">
+      <c r="C72" s="109">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D72" s="147" t="s">
+      <c r="D72" s="101" t="s">
         <v>87</v>
       </c>
-      <c r="E72" s="117" t="s">
+      <c r="E72" s="127" t="s">
         <v>53</v>
       </c>
-      <c r="F72" s="117" t="s">
+      <c r="F72" s="127" t="s">
         <v>54</v>
       </c>
-      <c r="G72" s="119"/>
-      <c r="H72" s="119"/>
-      <c r="I72" s="121" t="str">
+      <c r="G72" s="128"/>
+      <c r="H72" s="128"/>
+      <c r="I72" s="125" t="str">
         <f t="shared" ref="I72" si="8">IF(G72="","-",IF(G72&gt;H72,"L",IF(G72=H72,"E",IF(G72&lt;H72,"V"))))</f>
         <v>-</v>
       </c>
@@ -12117,15 +12121,15 @@
       </c>
     </row>
     <row r="73" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="115"/>
-      <c r="B73" s="131"/>
-      <c r="C73" s="131"/>
-      <c r="D73" s="118"/>
-      <c r="E73" s="118"/>
-      <c r="F73" s="118"/>
-      <c r="G73" s="120"/>
-      <c r="H73" s="120"/>
-      <c r="I73" s="122"/>
+      <c r="A73" s="134"/>
+      <c r="B73" s="110"/>
+      <c r="C73" s="110"/>
+      <c r="D73" s="102"/>
+      <c r="E73" s="102"/>
+      <c r="F73" s="102"/>
+      <c r="G73" s="129"/>
+      <c r="H73" s="129"/>
+      <c r="I73" s="126"/>
       <c r="J73" s="27">
         <v>4</v>
       </c>
@@ -12239,25 +12243,25 @@
       </c>
     </row>
     <row r="74" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="115"/>
-      <c r="B74" s="130">
+      <c r="A74" s="134"/>
+      <c r="B74" s="118">
         <v>46193</v>
       </c>
-      <c r="C74" s="138">
+      <c r="C74" s="109">
         <v>0.91666666666666663</v>
       </c>
-      <c r="D74" s="147" t="s">
+      <c r="D74" s="101" t="s">
         <v>83</v>
       </c>
-      <c r="E74" s="117" t="s">
+      <c r="E74" s="127" t="s">
         <v>55</v>
       </c>
-      <c r="F74" s="117" t="s">
+      <c r="F74" s="127" t="s">
         <v>56</v>
       </c>
-      <c r="G74" s="119"/>
-      <c r="H74" s="119"/>
-      <c r="I74" s="121" t="str">
+      <c r="G74" s="128"/>
+      <c r="H74" s="128"/>
+      <c r="I74" s="125" t="str">
         <f t="shared" ref="I74" si="9">IF(G74="","-",IF(G74&gt;H74,"L",IF(G74=H74,"E",IF(G74&lt;H74,"V"))))</f>
         <v>-</v>
       </c>
@@ -12374,15 +12378,15 @@
       </c>
     </row>
     <row r="75" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="115"/>
-      <c r="B75" s="131"/>
-      <c r="C75" s="131"/>
-      <c r="D75" s="118"/>
-      <c r="E75" s="118"/>
-      <c r="F75" s="118"/>
-      <c r="G75" s="120"/>
-      <c r="H75" s="120"/>
-      <c r="I75" s="122"/>
+      <c r="A75" s="134"/>
+      <c r="B75" s="110"/>
+      <c r="C75" s="110"/>
+      <c r="D75" s="102"/>
+      <c r="E75" s="102"/>
+      <c r="F75" s="102"/>
+      <c r="G75" s="129"/>
+      <c r="H75" s="129"/>
+      <c r="I75" s="126"/>
       <c r="J75" s="26">
         <v>3</v>
       </c>
@@ -12496,25 +12500,25 @@
       </c>
     </row>
     <row r="76" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="115"/>
-      <c r="B76" s="130">
+      <c r="A76" s="134"/>
+      <c r="B76" s="118">
         <v>46198</v>
       </c>
-      <c r="C76" s="138">
+      <c r="C76" s="109">
         <v>0.70833333333333337</v>
       </c>
-      <c r="D76" s="147" t="s">
+      <c r="D76" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="E76" s="117" t="s">
+      <c r="E76" s="127" t="s">
         <v>56</v>
       </c>
-      <c r="F76" s="117" t="s">
+      <c r="F76" s="127" t="s">
         <v>54</v>
       </c>
-      <c r="G76" s="119"/>
-      <c r="H76" s="119"/>
-      <c r="I76" s="121" t="str">
+      <c r="G76" s="128"/>
+      <c r="H76" s="128"/>
+      <c r="I76" s="125" t="str">
         <f t="shared" ref="I76" si="10">IF(G76="","-",IF(G76&gt;H76,"L",IF(G76=H76,"E",IF(G76&lt;H76,"V"))))</f>
         <v>-</v>
       </c>
@@ -12631,15 +12635,15 @@
       </c>
     </row>
     <row r="77" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="115"/>
-      <c r="B77" s="131"/>
-      <c r="C77" s="131"/>
-      <c r="D77" s="118"/>
-      <c r="E77" s="118"/>
-      <c r="F77" s="118"/>
-      <c r="G77" s="120"/>
-      <c r="H77" s="120"/>
-      <c r="I77" s="122"/>
+      <c r="A77" s="134"/>
+      <c r="B77" s="110"/>
+      <c r="C77" s="110"/>
+      <c r="D77" s="102"/>
+      <c r="E77" s="102"/>
+      <c r="F77" s="102"/>
+      <c r="G77" s="129"/>
+      <c r="H77" s="129"/>
+      <c r="I77" s="126"/>
       <c r="J77" s="27">
         <v>1</v>
       </c>
@@ -12753,25 +12757,25 @@
       </c>
     </row>
     <row r="78" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="115"/>
-      <c r="B78" s="130">
+      <c r="A78" s="134"/>
+      <c r="B78" s="118">
         <v>46198</v>
       </c>
-      <c r="C78" s="138">
+      <c r="C78" s="109">
         <v>0.70833333333333337</v>
       </c>
-      <c r="D78" s="147" t="s">
+      <c r="D78" s="101" t="s">
         <v>93</v>
       </c>
-      <c r="E78" s="117" t="s">
+      <c r="E78" s="127" t="s">
         <v>55</v>
       </c>
-      <c r="F78" s="117" t="s">
+      <c r="F78" s="127" t="s">
         <v>53</v>
       </c>
-      <c r="G78" s="119"/>
-      <c r="H78" s="119"/>
-      <c r="I78" s="121" t="str">
+      <c r="G78" s="128"/>
+      <c r="H78" s="128"/>
+      <c r="I78" s="125" t="str">
         <f t="shared" ref="I78" si="11">IF(G78="","-",IF(G78&gt;H78,"L",IF(G78=H78,"E",IF(G78&lt;H78,"V"))))</f>
         <v>-</v>
       </c>
@@ -12888,15 +12892,15 @@
       </c>
     </row>
     <row r="79" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="116"/>
-      <c r="B79" s="131"/>
-      <c r="C79" s="131"/>
-      <c r="D79" s="118"/>
-      <c r="E79" s="118"/>
-      <c r="F79" s="118"/>
-      <c r="G79" s="120"/>
-      <c r="H79" s="120"/>
-      <c r="I79" s="122"/>
+      <c r="A79" s="135"/>
+      <c r="B79" s="110"/>
+      <c r="C79" s="110"/>
+      <c r="D79" s="102"/>
+      <c r="E79" s="102"/>
+      <c r="F79" s="102"/>
+      <c r="G79" s="129"/>
+      <c r="H79" s="129"/>
+      <c r="I79" s="126"/>
       <c r="J79" s="93">
         <v>3</v>
       </c>
@@ -13010,27 +13014,27 @@
       </c>
     </row>
     <row r="80" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="125" t="s">
+      <c r="A80" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="B80" s="132">
+      <c r="B80" s="119">
         <v>46188</v>
       </c>
-      <c r="C80" s="143">
+      <c r="C80" s="107">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D80" s="137" t="s">
+      <c r="D80" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="E80" s="111" t="s">
+      <c r="E80" s="132" t="s">
         <v>57</v>
       </c>
-      <c r="F80" s="111" t="s">
+      <c r="F80" s="132" t="s">
         <v>58</v>
       </c>
-      <c r="G80" s="113"/>
-      <c r="H80" s="113"/>
-      <c r="I80" s="112" t="str">
+      <c r="G80" s="130"/>
+      <c r="H80" s="130"/>
+      <c r="I80" s="136" t="str">
         <f>IF(G80="","-",IF(G80&gt;H80,"L",IF(G80=H80,"E",IF(G80&lt;H80,"V"))))</f>
         <v>-</v>
       </c>
@@ -13147,15 +13151,15 @@
       </c>
     </row>
     <row r="81" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="103"/>
-      <c r="B81" s="133"/>
-      <c r="C81" s="133"/>
-      <c r="D81" s="106"/>
-      <c r="E81" s="106"/>
-      <c r="F81" s="106"/>
-      <c r="G81" s="108"/>
-      <c r="H81" s="108"/>
-      <c r="I81" s="110"/>
+      <c r="A81" s="123"/>
+      <c r="B81" s="108"/>
+      <c r="C81" s="108"/>
+      <c r="D81" s="100"/>
+      <c r="E81" s="100"/>
+      <c r="F81" s="100"/>
+      <c r="G81" s="131"/>
+      <c r="H81" s="131"/>
+      <c r="I81" s="137"/>
       <c r="J81" s="23">
         <v>2</v>
       </c>
@@ -13269,25 +13273,25 @@
       </c>
     </row>
     <row r="82" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="103"/>
-      <c r="B82" s="132">
+      <c r="A82" s="123"/>
+      <c r="B82" s="119">
         <v>46188</v>
       </c>
-      <c r="C82" s="143">
+      <c r="C82" s="107">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D82" s="137" t="s">
+      <c r="D82" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="E82" s="111" t="s">
+      <c r="E82" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="F82" s="111" t="s">
+      <c r="F82" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="G82" s="113"/>
-      <c r="H82" s="113"/>
-      <c r="I82" s="112" t="str">
+      <c r="G82" s="130"/>
+      <c r="H82" s="130"/>
+      <c r="I82" s="136" t="str">
         <f t="shared" ref="I82" si="12">IF(G82="","-",IF(G82&gt;H82,"L",IF(G82=H82,"E",IF(G82&lt;H82,"V"))))</f>
         <v>-</v>
       </c>
@@ -13404,15 +13408,15 @@
       </c>
     </row>
     <row r="83" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="103"/>
-      <c r="B83" s="133"/>
-      <c r="C83" s="133"/>
-      <c r="D83" s="106"/>
-      <c r="E83" s="106"/>
-      <c r="F83" s="106"/>
-      <c r="G83" s="108"/>
-      <c r="H83" s="108"/>
-      <c r="I83" s="110"/>
+      <c r="A83" s="123"/>
+      <c r="B83" s="108"/>
+      <c r="C83" s="108"/>
+      <c r="D83" s="100"/>
+      <c r="E83" s="100"/>
+      <c r="F83" s="100"/>
+      <c r="G83" s="131"/>
+      <c r="H83" s="131"/>
+      <c r="I83" s="137"/>
       <c r="J83" s="26">
         <v>3</v>
       </c>
@@ -13526,25 +13530,25 @@
       </c>
     </row>
     <row r="84" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="103"/>
-      <c r="B84" s="132">
+      <c r="A84" s="123"/>
+      <c r="B84" s="119">
         <v>46194</v>
       </c>
-      <c r="C84" s="143">
+      <c r="C84" s="107">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D84" s="137" t="s">
+      <c r="D84" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="E84" s="111" t="s">
+      <c r="E84" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="F84" s="111" t="s">
+      <c r="F84" s="132" t="s">
         <v>57</v>
       </c>
-      <c r="G84" s="113"/>
-      <c r="H84" s="113"/>
-      <c r="I84" s="112" t="str">
+      <c r="G84" s="130"/>
+      <c r="H84" s="130"/>
+      <c r="I84" s="136" t="str">
         <f t="shared" ref="I84" si="13">IF(G84="","-",IF(G84&gt;H84,"L",IF(G84=H84,"E",IF(G84&lt;H84,"V"))))</f>
         <v>-</v>
       </c>
@@ -13661,15 +13665,15 @@
       </c>
     </row>
     <row r="85" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="103"/>
-      <c r="B85" s="133"/>
-      <c r="C85" s="133"/>
-      <c r="D85" s="106"/>
-      <c r="E85" s="106"/>
-      <c r="F85" s="106"/>
-      <c r="G85" s="108"/>
-      <c r="H85" s="108"/>
-      <c r="I85" s="110"/>
+      <c r="A85" s="123"/>
+      <c r="B85" s="108"/>
+      <c r="C85" s="108"/>
+      <c r="D85" s="100"/>
+      <c r="E85" s="100"/>
+      <c r="F85" s="100"/>
+      <c r="G85" s="131"/>
+      <c r="H85" s="131"/>
+      <c r="I85" s="137"/>
       <c r="J85" s="23">
         <v>2</v>
       </c>
@@ -13783,25 +13787,25 @@
       </c>
     </row>
     <row r="86" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="103"/>
-      <c r="B86" s="132">
+      <c r="A86" s="123"/>
+      <c r="B86" s="119">
         <v>46194</v>
       </c>
-      <c r="C86" s="143">
+      <c r="C86" s="107">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D86" s="137" t="s">
+      <c r="D86" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="E86" s="111" t="s">
+      <c r="E86" s="132" t="s">
         <v>58</v>
       </c>
-      <c r="F86" s="111" t="s">
+      <c r="F86" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="G86" s="113"/>
-      <c r="H86" s="113"/>
-      <c r="I86" s="112" t="str">
+      <c r="G86" s="130"/>
+      <c r="H86" s="130"/>
+      <c r="I86" s="136" t="str">
         <f t="shared" ref="I86" si="14">IF(G86="","-",IF(G86&gt;H86,"L",IF(G86=H86,"E",IF(G86&lt;H86,"V"))))</f>
         <v>-</v>
       </c>
@@ -13918,15 +13922,15 @@
       </c>
     </row>
     <row r="87" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="103"/>
-      <c r="B87" s="133"/>
-      <c r="C87" s="133"/>
-      <c r="D87" s="106"/>
-      <c r="E87" s="106"/>
-      <c r="F87" s="106"/>
-      <c r="G87" s="108"/>
-      <c r="H87" s="108"/>
-      <c r="I87" s="110"/>
+      <c r="A87" s="123"/>
+      <c r="B87" s="108"/>
+      <c r="C87" s="108"/>
+      <c r="D87" s="100"/>
+      <c r="E87" s="100"/>
+      <c r="F87" s="100"/>
+      <c r="G87" s="131"/>
+      <c r="H87" s="131"/>
+      <c r="I87" s="137"/>
       <c r="J87" s="26">
         <v>1</v>
       </c>
@@ -14040,25 +14044,25 @@
       </c>
     </row>
     <row r="88" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="103"/>
-      <c r="B88" s="132">
+      <c r="A88" s="123"/>
+      <c r="B88" s="119">
         <v>46199</v>
       </c>
-      <c r="C88" s="143">
+      <c r="C88" s="107">
         <v>0.875</v>
       </c>
-      <c r="D88" s="137" t="s">
+      <c r="D88" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="E88" s="111" t="s">
+      <c r="E88" s="132" t="s">
         <v>58</v>
       </c>
-      <c r="F88" s="111" t="s">
+      <c r="F88" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="G88" s="113"/>
-      <c r="H88" s="113"/>
-      <c r="I88" s="112" t="str">
+      <c r="G88" s="130"/>
+      <c r="H88" s="130"/>
+      <c r="I88" s="136" t="str">
         <f t="shared" ref="I88" si="15">IF(G88="","-",IF(G88&gt;H88,"L",IF(G88=H88,"E",IF(G88&lt;H88,"V"))))</f>
         <v>-</v>
       </c>
@@ -14175,15 +14179,15 @@
       </c>
     </row>
     <row r="89" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="103"/>
-      <c r="B89" s="133"/>
-      <c r="C89" s="133"/>
-      <c r="D89" s="106"/>
-      <c r="E89" s="106"/>
-      <c r="F89" s="106"/>
-      <c r="G89" s="108"/>
-      <c r="H89" s="108"/>
-      <c r="I89" s="110"/>
+      <c r="A89" s="123"/>
+      <c r="B89" s="108"/>
+      <c r="C89" s="108"/>
+      <c r="D89" s="100"/>
+      <c r="E89" s="100"/>
+      <c r="F89" s="100"/>
+      <c r="G89" s="131"/>
+      <c r="H89" s="131"/>
+      <c r="I89" s="137"/>
       <c r="J89" s="23">
         <v>2</v>
       </c>
@@ -14297,25 +14301,25 @@
       </c>
     </row>
     <row r="90" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="103"/>
-      <c r="B90" s="132">
+      <c r="A90" s="123"/>
+      <c r="B90" s="119">
         <v>46199</v>
       </c>
-      <c r="C90" s="143">
+      <c r="C90" s="107">
         <v>0.875</v>
       </c>
-      <c r="D90" s="137" t="s">
+      <c r="D90" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="E90" s="111" t="s">
+      <c r="E90" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="F90" s="111" t="s">
+      <c r="F90" s="132" t="s">
         <v>57</v>
       </c>
-      <c r="G90" s="113"/>
-      <c r="H90" s="113"/>
-      <c r="I90" s="112" t="str">
+      <c r="G90" s="130"/>
+      <c r="H90" s="130"/>
+      <c r="I90" s="136" t="str">
         <f t="shared" ref="I90" si="16">IF(G90="","-",IF(G90&gt;H90,"L",IF(G90=H90,"E",IF(G90&lt;H90,"V"))))</f>
         <v>-</v>
       </c>
@@ -14432,15 +14436,15 @@
       </c>
     </row>
     <row r="91" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="104"/>
-      <c r="B91" s="133"/>
-      <c r="C91" s="133"/>
-      <c r="D91" s="106"/>
-      <c r="E91" s="106"/>
-      <c r="F91" s="106"/>
-      <c r="G91" s="108"/>
-      <c r="H91" s="108"/>
-      <c r="I91" s="110"/>
+      <c r="A91" s="124"/>
+      <c r="B91" s="108"/>
+      <c r="C91" s="108"/>
+      <c r="D91" s="100"/>
+      <c r="E91" s="100"/>
+      <c r="F91" s="100"/>
+      <c r="G91" s="131"/>
+      <c r="H91" s="131"/>
+      <c r="I91" s="137"/>
       <c r="J91" s="26">
         <v>0</v>
       </c>
@@ -14554,27 +14558,27 @@
       </c>
     </row>
     <row r="92" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="114" t="s">
+      <c r="A92" s="133" t="s">
         <v>49</v>
       </c>
-      <c r="B92" s="130">
+      <c r="B92" s="118">
         <v>46188</v>
       </c>
-      <c r="C92" s="138">
+      <c r="C92" s="109">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D92" s="147" t="s">
+      <c r="D92" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="E92" s="117" t="s">
+      <c r="E92" s="127" t="s">
         <v>18</v>
       </c>
-      <c r="F92" s="117" t="s">
+      <c r="F92" s="127" t="s">
         <v>62</v>
       </c>
-      <c r="G92" s="119"/>
-      <c r="H92" s="119"/>
-      <c r="I92" s="121" t="str">
+      <c r="G92" s="128"/>
+      <c r="H92" s="128"/>
+      <c r="I92" s="125" t="str">
         <f t="shared" ref="I92" si="17">IF(G92="","-",IF(G92&gt;H92,"L",IF(G92=H92,"E",IF(G92&lt;H92,"V"))))</f>
         <v>-</v>
       </c>
@@ -14691,15 +14695,15 @@
       </c>
     </row>
     <row r="93" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="115"/>
-      <c r="B93" s="131"/>
-      <c r="C93" s="131"/>
-      <c r="D93" s="118"/>
-      <c r="E93" s="118"/>
-      <c r="F93" s="118"/>
-      <c r="G93" s="120"/>
-      <c r="H93" s="120"/>
-      <c r="I93" s="122"/>
+      <c r="A93" s="134"/>
+      <c r="B93" s="110"/>
+      <c r="C93" s="110"/>
+      <c r="D93" s="102"/>
+      <c r="E93" s="102"/>
+      <c r="F93" s="102"/>
+      <c r="G93" s="129"/>
+      <c r="H93" s="129"/>
+      <c r="I93" s="126"/>
       <c r="J93" s="27">
         <v>3</v>
       </c>
@@ -14813,25 +14817,25 @@
       </c>
     </row>
     <row r="94" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="115"/>
-      <c r="B94" s="130">
+      <c r="A94" s="134"/>
+      <c r="B94" s="118">
         <v>46188</v>
       </c>
-      <c r="C94" s="138">
+      <c r="C94" s="109">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D94" s="147" t="s">
+      <c r="D94" s="101" t="s">
         <v>91</v>
       </c>
-      <c r="E94" s="117" t="s">
+      <c r="E94" s="127" t="s">
         <v>60</v>
       </c>
-      <c r="F94" s="117" t="s">
+      <c r="F94" s="127" t="s">
         <v>61</v>
       </c>
-      <c r="G94" s="119"/>
-      <c r="H94" s="119"/>
-      <c r="I94" s="121" t="str">
+      <c r="G94" s="128"/>
+      <c r="H94" s="128"/>
+      <c r="I94" s="125" t="str">
         <f t="shared" ref="I94" si="18">IF(G94="","-",IF(G94&gt;H94,"L",IF(G94=H94,"E",IF(G94&lt;H94,"V"))))</f>
         <v>-</v>
       </c>
@@ -14948,15 +14952,15 @@
       </c>
     </row>
     <row r="95" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="115"/>
-      <c r="B95" s="131"/>
-      <c r="C95" s="131"/>
-      <c r="D95" s="118"/>
-      <c r="E95" s="118"/>
-      <c r="F95" s="118"/>
-      <c r="G95" s="120"/>
-      <c r="H95" s="120"/>
-      <c r="I95" s="122"/>
+      <c r="A95" s="134"/>
+      <c r="B95" s="110"/>
+      <c r="C95" s="110"/>
+      <c r="D95" s="102"/>
+      <c r="E95" s="102"/>
+      <c r="F95" s="102"/>
+      <c r="G95" s="129"/>
+      <c r="H95" s="129"/>
+      <c r="I95" s="126"/>
       <c r="J95" s="26">
         <v>2</v>
       </c>
@@ -15070,25 +15074,25 @@
       </c>
     </row>
     <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="115"/>
-      <c r="B96" s="130">
+      <c r="A96" s="134"/>
+      <c r="B96" s="118">
         <v>46194</v>
       </c>
-      <c r="C96" s="138">
+      <c r="C96" s="109">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D96" s="147" t="s">
+      <c r="D96" s="101" t="s">
         <v>90</v>
       </c>
-      <c r="E96" s="117" t="s">
+      <c r="E96" s="127" t="s">
         <v>18</v>
       </c>
-      <c r="F96" s="117" t="s">
+      <c r="F96" s="127" t="s">
         <v>60</v>
       </c>
-      <c r="G96" s="119"/>
-      <c r="H96" s="119"/>
-      <c r="I96" s="121" t="str">
+      <c r="G96" s="128"/>
+      <c r="H96" s="128"/>
+      <c r="I96" s="125" t="str">
         <f t="shared" ref="I96" si="19">IF(G96="","-",IF(G96&gt;H96,"L",IF(G96=H96,"E",IF(G96&lt;H96,"V"))))</f>
         <v>-</v>
       </c>
@@ -15205,15 +15209,15 @@
       </c>
     </row>
     <row r="97" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="115"/>
-      <c r="B97" s="131"/>
-      <c r="C97" s="131"/>
-      <c r="D97" s="118"/>
-      <c r="E97" s="118"/>
-      <c r="F97" s="118"/>
-      <c r="G97" s="120"/>
-      <c r="H97" s="120"/>
-      <c r="I97" s="122"/>
+      <c r="A97" s="134"/>
+      <c r="B97" s="110"/>
+      <c r="C97" s="110"/>
+      <c r="D97" s="102"/>
+      <c r="E97" s="102"/>
+      <c r="F97" s="102"/>
+      <c r="G97" s="129"/>
+      <c r="H97" s="129"/>
+      <c r="I97" s="126"/>
       <c r="J97" s="27">
         <v>2</v>
       </c>
@@ -15327,25 +15331,25 @@
       </c>
     </row>
     <row r="98" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="115"/>
-      <c r="B98" s="130">
+      <c r="A98" s="134"/>
+      <c r="B98" s="118">
         <v>46194</v>
       </c>
-      <c r="C98" s="138">
+      <c r="C98" s="109">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D98" s="147" t="s">
+      <c r="D98" s="101" t="s">
         <v>91</v>
       </c>
-      <c r="E98" s="117" t="s">
+      <c r="E98" s="127" t="s">
         <v>61</v>
       </c>
-      <c r="F98" s="117" t="s">
+      <c r="F98" s="127" t="s">
         <v>62</v>
       </c>
-      <c r="G98" s="119"/>
-      <c r="H98" s="119"/>
-      <c r="I98" s="121" t="str">
+      <c r="G98" s="128"/>
+      <c r="H98" s="128"/>
+      <c r="I98" s="125" t="str">
         <f t="shared" ref="I98" si="20">IF(G98="","-",IF(G98&gt;H98,"L",IF(G98=H98,"E",IF(G98&lt;H98,"V"))))</f>
         <v>-</v>
       </c>
@@ -15462,15 +15466,15 @@
       </c>
     </row>
     <row r="99" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="115"/>
-      <c r="B99" s="131"/>
-      <c r="C99" s="131"/>
-      <c r="D99" s="118"/>
-      <c r="E99" s="118"/>
-      <c r="F99" s="118"/>
-      <c r="G99" s="120"/>
-      <c r="H99" s="120"/>
-      <c r="I99" s="122"/>
+      <c r="A99" s="134"/>
+      <c r="B99" s="110"/>
+      <c r="C99" s="110"/>
+      <c r="D99" s="102"/>
+      <c r="E99" s="102"/>
+      <c r="F99" s="102"/>
+      <c r="G99" s="129"/>
+      <c r="H99" s="129"/>
+      <c r="I99" s="126"/>
       <c r="J99" s="26">
         <v>2</v>
       </c>
@@ -15584,25 +15588,25 @@
       </c>
     </row>
     <row r="100" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="115"/>
-      <c r="B100" s="130">
+      <c r="A100" s="134"/>
+      <c r="B100" s="118">
         <v>46199</v>
       </c>
-      <c r="C100" s="138">
+      <c r="C100" s="109">
         <v>0.75</v>
       </c>
-      <c r="D100" s="147" t="s">
+      <c r="D100" s="101" t="s">
         <v>137</v>
       </c>
-      <c r="E100" s="117" t="s">
+      <c r="E100" s="127" t="s">
         <v>61</v>
       </c>
-      <c r="F100" s="117" t="s">
+      <c r="F100" s="127" t="s">
         <v>18</v>
       </c>
-      <c r="G100" s="119"/>
-      <c r="H100" s="119"/>
-      <c r="I100" s="121" t="str">
+      <c r="G100" s="128"/>
+      <c r="H100" s="128"/>
+      <c r="I100" s="125" t="str">
         <f t="shared" ref="I100" si="21">IF(G100="","-",IF(G100&gt;H100,"L",IF(G100=H100,"E",IF(G100&lt;H100,"V"))))</f>
         <v>-</v>
       </c>
@@ -15719,15 +15723,15 @@
       </c>
     </row>
     <row r="101" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="115"/>
-      <c r="B101" s="131"/>
-      <c r="C101" s="131"/>
-      <c r="D101" s="118"/>
-      <c r="E101" s="118"/>
-      <c r="F101" s="118"/>
-      <c r="G101" s="120"/>
-      <c r="H101" s="120"/>
-      <c r="I101" s="122"/>
+      <c r="A101" s="134"/>
+      <c r="B101" s="110"/>
+      <c r="C101" s="110"/>
+      <c r="D101" s="102"/>
+      <c r="E101" s="102"/>
+      <c r="F101" s="102"/>
+      <c r="G101" s="129"/>
+      <c r="H101" s="129"/>
+      <c r="I101" s="126"/>
       <c r="J101" s="27">
         <v>4</v>
       </c>
@@ -15841,25 +15845,25 @@
       </c>
     </row>
     <row r="102" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="115"/>
-      <c r="B102" s="130">
+      <c r="A102" s="134"/>
+      <c r="B102" s="118">
         <v>46199</v>
       </c>
-      <c r="C102" s="138">
+      <c r="C102" s="109">
         <v>0.75</v>
       </c>
-      <c r="D102" s="147" t="s">
+      <c r="D102" s="101" t="s">
         <v>87</v>
       </c>
-      <c r="E102" s="117" t="s">
+      <c r="E102" s="127" t="s">
         <v>62</v>
       </c>
-      <c r="F102" s="117" t="s">
+      <c r="F102" s="127" t="s">
         <v>60</v>
       </c>
-      <c r="G102" s="119"/>
-      <c r="H102" s="119"/>
-      <c r="I102" s="121" t="str">
+      <c r="G102" s="128"/>
+      <c r="H102" s="128"/>
+      <c r="I102" s="125" t="str">
         <f t="shared" ref="I102" si="22">IF(G102="","-",IF(G102&gt;H102,"L",IF(G102=H102,"E",IF(G102&lt;H102,"V"))))</f>
         <v>-</v>
       </c>
@@ -15976,15 +15980,15 @@
       </c>
     </row>
     <row r="103" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="116"/>
-      <c r="B103" s="131"/>
-      <c r="C103" s="131"/>
-      <c r="D103" s="118"/>
-      <c r="E103" s="118"/>
-      <c r="F103" s="118"/>
-      <c r="G103" s="120"/>
-      <c r="H103" s="120"/>
-      <c r="I103" s="122"/>
+      <c r="A103" s="135"/>
+      <c r="B103" s="110"/>
+      <c r="C103" s="110"/>
+      <c r="D103" s="102"/>
+      <c r="E103" s="102"/>
+      <c r="F103" s="102"/>
+      <c r="G103" s="129"/>
+      <c r="H103" s="129"/>
+      <c r="I103" s="126"/>
       <c r="J103" s="93">
         <v>2</v>
       </c>
@@ -16098,27 +16102,27 @@
       </c>
     </row>
     <row r="104" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="125" t="s">
+      <c r="A104" s="122" t="s">
         <v>50</v>
       </c>
-      <c r="B104" s="132">
+      <c r="B104" s="119">
         <v>46189</v>
       </c>
-      <c r="C104" s="143">
+      <c r="C104" s="107">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D104" s="137" t="s">
+      <c r="D104" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="E104" s="111" t="s">
+      <c r="E104" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="F104" s="111" t="s">
+      <c r="F104" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="G104" s="113"/>
-      <c r="H104" s="113"/>
-      <c r="I104" s="112" t="str">
+      <c r="G104" s="130"/>
+      <c r="H104" s="130"/>
+      <c r="I104" s="136" t="str">
         <f>IF(G104="","-",IF(G104&gt;H104,"L",IF(G104=H104,"E",IF(G104&lt;H104,"V"))))</f>
         <v>-</v>
       </c>
@@ -16235,15 +16239,15 @@
       </c>
     </row>
     <row r="105" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="103"/>
-      <c r="B105" s="133"/>
-      <c r="C105" s="133"/>
-      <c r="D105" s="106"/>
-      <c r="E105" s="106"/>
-      <c r="F105" s="106"/>
-      <c r="G105" s="108"/>
-      <c r="H105" s="108"/>
-      <c r="I105" s="110"/>
+      <c r="A105" s="123"/>
+      <c r="B105" s="108"/>
+      <c r="C105" s="108"/>
+      <c r="D105" s="100"/>
+      <c r="E105" s="100"/>
+      <c r="F105" s="100"/>
+      <c r="G105" s="131"/>
+      <c r="H105" s="131"/>
+      <c r="I105" s="137"/>
       <c r="J105" s="23">
         <v>3</v>
       </c>
@@ -16357,25 +16361,25 @@
       </c>
     </row>
     <row r="106" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="103"/>
-      <c r="B106" s="132">
+      <c r="A106" s="123"/>
+      <c r="B106" s="119">
         <v>46189</v>
       </c>
-      <c r="C106" s="143">
+      <c r="C106" s="107">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D106" s="137" t="s">
+      <c r="D106" s="99" t="s">
         <v>80</v>
       </c>
-      <c r="E106" s="111" t="s">
+      <c r="E106" s="132" t="s">
         <v>63</v>
       </c>
-      <c r="F106" s="111" t="s">
+      <c r="F106" s="132" t="s">
         <v>64</v>
       </c>
-      <c r="G106" s="113"/>
-      <c r="H106" s="113"/>
-      <c r="I106" s="112" t="str">
+      <c r="G106" s="130"/>
+      <c r="H106" s="130"/>
+      <c r="I106" s="136" t="str">
         <f t="shared" ref="I106" si="23">IF(G106="","-",IF(G106&gt;H106,"L",IF(G106=H106,"E",IF(G106&lt;H106,"V"))))</f>
         <v>-</v>
       </c>
@@ -16492,15 +16496,15 @@
       </c>
     </row>
     <row r="107" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="103"/>
-      <c r="B107" s="133"/>
-      <c r="C107" s="133"/>
-      <c r="D107" s="106"/>
-      <c r="E107" s="106"/>
-      <c r="F107" s="106"/>
-      <c r="G107" s="108"/>
-      <c r="H107" s="108"/>
-      <c r="I107" s="110"/>
+      <c r="A107" s="123"/>
+      <c r="B107" s="108"/>
+      <c r="C107" s="108"/>
+      <c r="D107" s="100"/>
+      <c r="E107" s="100"/>
+      <c r="F107" s="100"/>
+      <c r="G107" s="131"/>
+      <c r="H107" s="131"/>
+      <c r="I107" s="137"/>
       <c r="J107" s="26">
         <v>2</v>
       </c>
@@ -16614,25 +16618,25 @@
       </c>
     </row>
     <row r="108" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="103"/>
-      <c r="B108" s="132">
+      <c r="A108" s="123"/>
+      <c r="B108" s="119">
         <v>46195</v>
       </c>
-      <c r="C108" s="143">
+      <c r="C108" s="107">
         <v>0.625</v>
       </c>
-      <c r="D108" s="137" t="s">
+      <c r="D108" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="E108" s="111" t="s">
+      <c r="E108" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="F108" s="111" t="s">
+      <c r="F108" s="132" t="s">
         <v>63</v>
       </c>
-      <c r="G108" s="113"/>
-      <c r="H108" s="113"/>
-      <c r="I108" s="112" t="str">
+      <c r="G108" s="130"/>
+      <c r="H108" s="130"/>
+      <c r="I108" s="136" t="str">
         <f t="shared" ref="I108" si="24">IF(G108="","-",IF(G108&gt;H108,"L",IF(G108=H108,"E",IF(G108&lt;H108,"V"))))</f>
         <v>-</v>
       </c>
@@ -16749,15 +16753,15 @@
       </c>
     </row>
     <row r="109" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="103"/>
-      <c r="B109" s="133"/>
-      <c r="C109" s="133"/>
-      <c r="D109" s="106"/>
-      <c r="E109" s="106"/>
-      <c r="F109" s="106"/>
-      <c r="G109" s="108"/>
-      <c r="H109" s="108"/>
-      <c r="I109" s="110"/>
+      <c r="A109" s="123"/>
+      <c r="B109" s="108"/>
+      <c r="C109" s="108"/>
+      <c r="D109" s="100"/>
+      <c r="E109" s="100"/>
+      <c r="F109" s="100"/>
+      <c r="G109" s="131"/>
+      <c r="H109" s="131"/>
+      <c r="I109" s="137"/>
       <c r="J109" s="23">
         <v>3</v>
       </c>
@@ -16871,25 +16875,25 @@
       </c>
     </row>
     <row r="110" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="103"/>
-      <c r="B110" s="132">
+      <c r="A110" s="123"/>
+      <c r="B110" s="119">
         <v>46195</v>
       </c>
-      <c r="C110" s="143">
+      <c r="C110" s="107">
         <v>0.75</v>
       </c>
-      <c r="D110" s="137" t="s">
+      <c r="D110" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="E110" s="111" t="s">
+      <c r="E110" s="132" t="s">
         <v>64</v>
       </c>
-      <c r="F110" s="111" t="s">
+      <c r="F110" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="G110" s="113"/>
-      <c r="H110" s="113"/>
-      <c r="I110" s="112" t="str">
+      <c r="G110" s="130"/>
+      <c r="H110" s="130"/>
+      <c r="I110" s="136" t="str">
         <f t="shared" ref="I110" si="25">IF(G110="","-",IF(G110&gt;H110,"L",IF(G110=H110,"E",IF(G110&lt;H110,"V"))))</f>
         <v>-</v>
       </c>
@@ -17006,15 +17010,15 @@
       </c>
     </row>
     <row r="111" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="103"/>
-      <c r="B111" s="133"/>
-      <c r="C111" s="133"/>
-      <c r="D111" s="106"/>
-      <c r="E111" s="106"/>
-      <c r="F111" s="106"/>
-      <c r="G111" s="108"/>
-      <c r="H111" s="108"/>
-      <c r="I111" s="110"/>
+      <c r="A111" s="123"/>
+      <c r="B111" s="108"/>
+      <c r="C111" s="108"/>
+      <c r="D111" s="100"/>
+      <c r="E111" s="100"/>
+      <c r="F111" s="100"/>
+      <c r="G111" s="131"/>
+      <c r="H111" s="131"/>
+      <c r="I111" s="137"/>
       <c r="J111" s="26">
         <v>2</v>
       </c>
@@ -17128,25 +17132,25 @@
       </c>
     </row>
     <row r="112" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="103"/>
-      <c r="B112" s="132">
+      <c r="A112" s="123"/>
+      <c r="B112" s="119">
         <v>46199</v>
       </c>
-      <c r="C112" s="143">
+      <c r="C112" s="107">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D112" s="137" t="s">
+      <c r="D112" s="99" t="s">
         <v>80</v>
       </c>
-      <c r="E112" s="111" t="s">
+      <c r="E112" s="132" t="s">
         <v>64</v>
       </c>
-      <c r="F112" s="111" t="s">
+      <c r="F112" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="G112" s="113"/>
-      <c r="H112" s="113"/>
-      <c r="I112" s="112" t="str">
+      <c r="G112" s="130"/>
+      <c r="H112" s="130"/>
+      <c r="I112" s="136" t="str">
         <f t="shared" ref="I112" si="26">IF(G112="","-",IF(G112&gt;H112,"L",IF(G112=H112,"E",IF(G112&lt;H112,"V"))))</f>
         <v>-</v>
       </c>
@@ -17263,15 +17267,15 @@
       </c>
     </row>
     <row r="113" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="103"/>
-      <c r="B113" s="133"/>
-      <c r="C113" s="133"/>
-      <c r="D113" s="106"/>
-      <c r="E113" s="106"/>
-      <c r="F113" s="106"/>
-      <c r="G113" s="108"/>
-      <c r="H113" s="108"/>
-      <c r="I113" s="110"/>
+      <c r="A113" s="123"/>
+      <c r="B113" s="108"/>
+      <c r="C113" s="108"/>
+      <c r="D113" s="100"/>
+      <c r="E113" s="100"/>
+      <c r="F113" s="100"/>
+      <c r="G113" s="131"/>
+      <c r="H113" s="131"/>
+      <c r="I113" s="137"/>
       <c r="J113" s="23">
         <v>4</v>
       </c>
@@ -17385,25 +17389,25 @@
       </c>
     </row>
     <row r="114" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="103"/>
-      <c r="B114" s="132">
+      <c r="A114" s="123"/>
+      <c r="B114" s="119">
         <v>46199</v>
       </c>
-      <c r="C114" s="143">
+      <c r="C114" s="107">
         <v>0.54166666666666663</v>
       </c>
-      <c r="D114" s="137" t="s">
+      <c r="D114" s="99" t="s">
         <v>84</v>
       </c>
-      <c r="E114" s="111" t="s">
+      <c r="E114" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="F114" s="111" t="s">
+      <c r="F114" s="132" t="s">
         <v>63</v>
       </c>
-      <c r="G114" s="113"/>
-      <c r="H114" s="113"/>
-      <c r="I114" s="112" t="str">
+      <c r="G114" s="130"/>
+      <c r="H114" s="130"/>
+      <c r="I114" s="136" t="str">
         <f t="shared" ref="I114" si="27">IF(G114="","-",IF(G114&gt;H114,"L",IF(G114=H114,"E",IF(G114&lt;H114,"V"))))</f>
         <v>-</v>
       </c>
@@ -17520,15 +17524,15 @@
       </c>
     </row>
     <row r="115" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="104"/>
-      <c r="B115" s="133"/>
-      <c r="C115" s="133"/>
-      <c r="D115" s="106"/>
-      <c r="E115" s="106"/>
-      <c r="F115" s="106"/>
-      <c r="G115" s="108"/>
-      <c r="H115" s="108"/>
-      <c r="I115" s="110"/>
+      <c r="A115" s="124"/>
+      <c r="B115" s="108"/>
+      <c r="C115" s="108"/>
+      <c r="D115" s="100"/>
+      <c r="E115" s="100"/>
+      <c r="F115" s="100"/>
+      <c r="G115" s="131"/>
+      <c r="H115" s="131"/>
+      <c r="I115" s="137"/>
       <c r="J115" s="26">
         <v>2</v>
       </c>
@@ -17642,27 +17646,27 @@
       </c>
     </row>
     <row r="116" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="114" t="s">
+      <c r="A116" s="133" t="s">
         <v>51</v>
       </c>
-      <c r="B116" s="130">
+      <c r="B116" s="118">
         <v>46189</v>
       </c>
-      <c r="C116" s="138">
+      <c r="C116" s="109">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D116" s="147" t="s">
+      <c r="D116" s="101" t="s">
         <v>93</v>
       </c>
-      <c r="E116" s="117" t="s">
+      <c r="E116" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="F116" s="117" t="s">
+      <c r="F116" s="127" t="s">
         <v>68</v>
       </c>
-      <c r="G116" s="119"/>
-      <c r="H116" s="119"/>
-      <c r="I116" s="121" t="str">
+      <c r="G116" s="128"/>
+      <c r="H116" s="128"/>
+      <c r="I116" s="125" t="str">
         <f t="shared" ref="I116" si="28">IF(G116="","-",IF(G116&gt;H116,"L",IF(G116=H116,"E",IF(G116&lt;H116,"V"))))</f>
         <v>-</v>
       </c>
@@ -17779,15 +17783,15 @@
       </c>
     </row>
     <row r="117" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="115"/>
-      <c r="B117" s="131"/>
-      <c r="C117" s="131"/>
-      <c r="D117" s="118"/>
-      <c r="E117" s="118"/>
-      <c r="F117" s="118"/>
-      <c r="G117" s="120"/>
-      <c r="H117" s="120"/>
-      <c r="I117" s="122"/>
+      <c r="A117" s="134"/>
+      <c r="B117" s="110"/>
+      <c r="C117" s="110"/>
+      <c r="D117" s="102"/>
+      <c r="E117" s="102"/>
+      <c r="F117" s="102"/>
+      <c r="G117" s="129"/>
+      <c r="H117" s="129"/>
+      <c r="I117" s="126"/>
       <c r="J117" s="27">
         <v>1</v>
       </c>
@@ -17901,25 +17905,25 @@
       </c>
     </row>
     <row r="118" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="115"/>
-      <c r="B118" s="130">
+      <c r="A118" s="134"/>
+      <c r="B118" s="118">
         <v>46189</v>
       </c>
-      <c r="C118" s="138">
+      <c r="C118" s="109">
         <v>0.91666666666666663</v>
       </c>
-      <c r="D118" s="147" t="s">
+      <c r="D118" s="101" t="s">
         <v>85</v>
       </c>
-      <c r="E118" s="117" t="s">
+      <c r="E118" s="127" t="s">
         <v>26</v>
       </c>
-      <c r="F118" s="117" t="s">
+      <c r="F118" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="G118" s="119"/>
-      <c r="H118" s="119"/>
-      <c r="I118" s="121" t="str">
+      <c r="G118" s="128"/>
+      <c r="H118" s="128"/>
+      <c r="I118" s="125" t="str">
         <f t="shared" ref="I118" si="29">IF(G118="","-",IF(G118&gt;H118,"L",IF(G118=H118,"E",IF(G118&lt;H118,"V"))))</f>
         <v>-</v>
       </c>
@@ -18036,15 +18040,15 @@
       </c>
     </row>
     <row r="119" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="115"/>
-      <c r="B119" s="131"/>
-      <c r="C119" s="131"/>
-      <c r="D119" s="118"/>
-      <c r="E119" s="118"/>
-      <c r="F119" s="118"/>
-      <c r="G119" s="120"/>
-      <c r="H119" s="120"/>
-      <c r="I119" s="122"/>
+      <c r="A119" s="134"/>
+      <c r="B119" s="110"/>
+      <c r="C119" s="110"/>
+      <c r="D119" s="102"/>
+      <c r="E119" s="102"/>
+      <c r="F119" s="102"/>
+      <c r="G119" s="129"/>
+      <c r="H119" s="129"/>
+      <c r="I119" s="126"/>
       <c r="J119" s="26">
         <v>2</v>
       </c>
@@ -18158,25 +18162,25 @@
       </c>
     </row>
     <row r="120" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="115"/>
-      <c r="B120" s="130">
+      <c r="A120" s="134"/>
+      <c r="B120" s="118">
         <v>46195</v>
       </c>
-      <c r="C120" s="138">
+      <c r="C120" s="109">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D120" s="147" t="s">
+      <c r="D120" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="E120" s="117" t="s">
+      <c r="E120" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="F120" s="117" t="s">
+      <c r="F120" s="127" t="s">
         <v>26</v>
       </c>
-      <c r="G120" s="119"/>
-      <c r="H120" s="119"/>
-      <c r="I120" s="121" t="str">
+      <c r="G120" s="128"/>
+      <c r="H120" s="128"/>
+      <c r="I120" s="125" t="str">
         <f t="shared" ref="I120" si="30">IF(G120="","-",IF(G120&gt;H120,"L",IF(G120=H120,"E",IF(G120&lt;H120,"V"))))</f>
         <v>-</v>
       </c>
@@ -18293,15 +18297,15 @@
       </c>
     </row>
     <row r="121" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="115"/>
-      <c r="B121" s="131"/>
-      <c r="C121" s="131"/>
-      <c r="D121" s="118"/>
-      <c r="E121" s="118"/>
-      <c r="F121" s="118"/>
-      <c r="G121" s="120"/>
-      <c r="H121" s="120"/>
-      <c r="I121" s="122"/>
+      <c r="A121" s="134"/>
+      <c r="B121" s="110"/>
+      <c r="C121" s="110"/>
+      <c r="D121" s="102"/>
+      <c r="E121" s="102"/>
+      <c r="F121" s="102"/>
+      <c r="G121" s="129"/>
+      <c r="H121" s="129"/>
+      <c r="I121" s="126"/>
       <c r="J121" s="27">
         <v>3</v>
       </c>
@@ -18415,25 +18419,25 @@
       </c>
     </row>
     <row r="122" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="115"/>
-      <c r="B122" s="130">
+      <c r="A122" s="134"/>
+      <c r="B122" s="118">
         <v>46195</v>
       </c>
-      <c r="C122" s="138">
+      <c r="C122" s="109">
         <v>0.875</v>
       </c>
-      <c r="D122" s="147" t="s">
+      <c r="D122" s="101" t="s">
         <v>85</v>
       </c>
-      <c r="E122" s="117" t="s">
+      <c r="E122" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="F122" s="117" t="s">
+      <c r="F122" s="127" t="s">
         <v>68</v>
       </c>
-      <c r="G122" s="119"/>
-      <c r="H122" s="119"/>
-      <c r="I122" s="121" t="str">
+      <c r="G122" s="128"/>
+      <c r="H122" s="128"/>
+      <c r="I122" s="125" t="str">
         <f t="shared" ref="I122" si="31">IF(G122="","-",IF(G122&gt;H122,"L",IF(G122=H122,"E",IF(G122&lt;H122,"V"))))</f>
         <v>-</v>
       </c>
@@ -18550,15 +18554,15 @@
       </c>
     </row>
     <row r="123" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="115"/>
-      <c r="B123" s="131"/>
-      <c r="C123" s="131"/>
-      <c r="D123" s="118"/>
-      <c r="E123" s="118"/>
-      <c r="F123" s="118"/>
-      <c r="G123" s="120"/>
-      <c r="H123" s="120"/>
-      <c r="I123" s="122"/>
+      <c r="A123" s="134"/>
+      <c r="B123" s="110"/>
+      <c r="C123" s="110"/>
+      <c r="D123" s="102"/>
+      <c r="E123" s="102"/>
+      <c r="F123" s="102"/>
+      <c r="G123" s="129"/>
+      <c r="H123" s="129"/>
+      <c r="I123" s="126"/>
       <c r="J123" s="26">
         <v>4</v>
       </c>
@@ -18672,25 +18676,25 @@
       </c>
     </row>
     <row r="124" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="115"/>
-      <c r="B124" s="130">
+      <c r="A124" s="134"/>
+      <c r="B124" s="118">
         <v>46200</v>
       </c>
-      <c r="C124" s="138">
+      <c r="C124" s="109">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D124" s="147" t="s">
+      <c r="D124" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="E124" s="117" t="s">
+      <c r="E124" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="F124" s="117" t="s">
+      <c r="F124" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="G124" s="119"/>
-      <c r="H124" s="119"/>
-      <c r="I124" s="121" t="str">
+      <c r="G124" s="128"/>
+      <c r="H124" s="128"/>
+      <c r="I124" s="125" t="str">
         <f t="shared" ref="I124" si="32">IF(G124="","-",IF(G124&gt;H124,"L",IF(G124=H124,"E",IF(G124&lt;H124,"V"))))</f>
         <v>-</v>
       </c>
@@ -18807,15 +18811,15 @@
       </c>
     </row>
     <row r="125" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="115"/>
-      <c r="B125" s="131"/>
-      <c r="C125" s="131"/>
-      <c r="D125" s="118"/>
-      <c r="E125" s="118"/>
-      <c r="F125" s="118"/>
-      <c r="G125" s="120"/>
-      <c r="H125" s="120"/>
-      <c r="I125" s="122"/>
+      <c r="A125" s="134"/>
+      <c r="B125" s="110"/>
+      <c r="C125" s="110"/>
+      <c r="D125" s="102"/>
+      <c r="E125" s="102"/>
+      <c r="F125" s="102"/>
+      <c r="G125" s="129"/>
+      <c r="H125" s="129"/>
+      <c r="I125" s="126"/>
       <c r="J125" s="27">
         <v>4</v>
       </c>
@@ -18929,25 +18933,25 @@
       </c>
     </row>
     <row r="126" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="115"/>
-      <c r="B126" s="130">
+      <c r="A126" s="134"/>
+      <c r="B126" s="118">
         <v>46200</v>
       </c>
-      <c r="C126" s="138">
+      <c r="C126" s="109">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D126" s="147" t="s">
+      <c r="D126" s="101" t="s">
         <v>93</v>
       </c>
-      <c r="E126" s="117" t="s">
+      <c r="E126" s="127" t="s">
         <v>68</v>
       </c>
-      <c r="F126" s="117" t="s">
+      <c r="F126" s="127" t="s">
         <v>26</v>
       </c>
-      <c r="G126" s="119"/>
-      <c r="H126" s="119"/>
-      <c r="I126" s="121" t="str">
+      <c r="G126" s="128"/>
+      <c r="H126" s="128"/>
+      <c r="I126" s="125" t="str">
         <f t="shared" ref="I126" si="33">IF(G126="","-",IF(G126&gt;H126,"L",IF(G126=H126,"E",IF(G126&lt;H126,"V"))))</f>
         <v>-</v>
       </c>
@@ -19064,15 +19068,15 @@
       </c>
     </row>
     <row r="127" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="116"/>
-      <c r="B127" s="131"/>
-      <c r="C127" s="131"/>
-      <c r="D127" s="118"/>
-      <c r="E127" s="118"/>
-      <c r="F127" s="118"/>
-      <c r="G127" s="120"/>
-      <c r="H127" s="120"/>
-      <c r="I127" s="122"/>
+      <c r="A127" s="135"/>
+      <c r="B127" s="110"/>
+      <c r="C127" s="110"/>
+      <c r="D127" s="102"/>
+      <c r="E127" s="102"/>
+      <c r="F127" s="102"/>
+      <c r="G127" s="129"/>
+      <c r="H127" s="129"/>
+      <c r="I127" s="126"/>
       <c r="J127" s="93">
         <v>2</v>
       </c>
@@ -19186,27 +19190,27 @@
       </c>
     </row>
     <row r="128" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="125" t="s">
+      <c r="A128" s="122" t="s">
         <v>52</v>
       </c>
-      <c r="B128" s="132">
+      <c r="B128" s="119">
         <v>46190</v>
       </c>
-      <c r="C128" s="143">
+      <c r="C128" s="107">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D128" s="137" t="s">
+      <c r="D128" s="99" t="s">
         <v>87</v>
       </c>
-      <c r="E128" s="111" t="s">
+      <c r="E128" s="132" t="s">
         <v>17</v>
       </c>
-      <c r="F128" s="111" t="s">
+      <c r="F128" s="132" t="s">
         <v>71</v>
       </c>
-      <c r="G128" s="113"/>
-      <c r="H128" s="113"/>
-      <c r="I128" s="112" t="str">
+      <c r="G128" s="130"/>
+      <c r="H128" s="130"/>
+      <c r="I128" s="136" t="str">
         <f>IF(G128="","-",IF(G128&gt;H128,"L",IF(G128=H128,"E",IF(G128&lt;H128,"V"))))</f>
         <v>-</v>
       </c>
@@ -19323,15 +19327,15 @@
       </c>
     </row>
     <row r="129" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="103"/>
-      <c r="B129" s="133"/>
-      <c r="C129" s="133"/>
-      <c r="D129" s="106"/>
-      <c r="E129" s="106"/>
-      <c r="F129" s="106"/>
-      <c r="G129" s="108"/>
-      <c r="H129" s="108"/>
-      <c r="I129" s="110"/>
+      <c r="A129" s="123"/>
+      <c r="B129" s="108"/>
+      <c r="C129" s="108"/>
+      <c r="D129" s="100"/>
+      <c r="E129" s="100"/>
+      <c r="F129" s="100"/>
+      <c r="G129" s="131"/>
+      <c r="H129" s="131"/>
+      <c r="I129" s="137"/>
       <c r="J129" s="23">
         <v>2</v>
       </c>
@@ -19445,25 +19449,25 @@
       </c>
     </row>
     <row r="130" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="103"/>
-      <c r="B130" s="132">
+      <c r="A130" s="123"/>
+      <c r="B130" s="119">
         <v>46190</v>
       </c>
-      <c r="C130" s="143">
+      <c r="C130" s="107">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D130" s="137" t="s">
+      <c r="D130" s="99" t="s">
         <v>89</v>
       </c>
-      <c r="E130" s="111" t="s">
+      <c r="E130" s="132" t="s">
         <v>69</v>
       </c>
-      <c r="F130" s="111" t="s">
+      <c r="F130" s="132" t="s">
         <v>70</v>
       </c>
-      <c r="G130" s="113"/>
-      <c r="H130" s="113"/>
-      <c r="I130" s="112" t="str">
+      <c r="G130" s="130"/>
+      <c r="H130" s="130"/>
+      <c r="I130" s="136" t="str">
         <f t="shared" ref="I130" si="34">IF(G130="","-",IF(G130&gt;H130,"L",IF(G130=H130,"E",IF(G130&lt;H130,"V"))))</f>
         <v>-</v>
       </c>
@@ -19580,15 +19584,15 @@
       </c>
     </row>
     <row r="131" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="103"/>
-      <c r="B131" s="133"/>
-      <c r="C131" s="133"/>
-      <c r="D131" s="106"/>
-      <c r="E131" s="106"/>
-      <c r="F131" s="106"/>
-      <c r="G131" s="108"/>
-      <c r="H131" s="108"/>
-      <c r="I131" s="110"/>
+      <c r="A131" s="123"/>
+      <c r="B131" s="108"/>
+      <c r="C131" s="108"/>
+      <c r="D131" s="100"/>
+      <c r="E131" s="100"/>
+      <c r="F131" s="100"/>
+      <c r="G131" s="131"/>
+      <c r="H131" s="131"/>
+      <c r="I131" s="137"/>
       <c r="J131" s="26">
         <v>1</v>
       </c>
@@ -19702,25 +19706,25 @@
       </c>
     </row>
     <row r="132" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="103"/>
-      <c r="B132" s="132">
+      <c r="A132" s="123"/>
+      <c r="B132" s="119">
         <v>46196</v>
       </c>
-      <c r="C132" s="143">
+      <c r="C132" s="107">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D132" s="137" t="s">
+      <c r="D132" s="99" t="s">
         <v>87</v>
       </c>
-      <c r="E132" s="111" t="s">
+      <c r="E132" s="132" t="s">
         <v>17</v>
       </c>
-      <c r="F132" s="111" t="s">
+      <c r="F132" s="132" t="s">
         <v>69</v>
       </c>
-      <c r="G132" s="113"/>
-      <c r="H132" s="113"/>
-      <c r="I132" s="112" t="str">
+      <c r="G132" s="130"/>
+      <c r="H132" s="130"/>
+      <c r="I132" s="136" t="str">
         <f t="shared" ref="I132" si="35">IF(G132="","-",IF(G132&gt;H132,"L",IF(G132=H132,"E",IF(G132&lt;H132,"V"))))</f>
         <v>-</v>
       </c>
@@ -19837,15 +19841,15 @@
       </c>
     </row>
     <row r="133" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="103"/>
-      <c r="B133" s="133"/>
-      <c r="C133" s="133"/>
-      <c r="D133" s="106"/>
-      <c r="E133" s="106"/>
-      <c r="F133" s="106"/>
-      <c r="G133" s="108"/>
-      <c r="H133" s="108"/>
-      <c r="I133" s="110"/>
+      <c r="A133" s="123"/>
+      <c r="B133" s="108"/>
+      <c r="C133" s="108"/>
+      <c r="D133" s="100"/>
+      <c r="E133" s="100"/>
+      <c r="F133" s="100"/>
+      <c r="G133" s="131"/>
+      <c r="H133" s="131"/>
+      <c r="I133" s="137"/>
       <c r="J133" s="23">
         <v>4</v>
       </c>
@@ -19959,25 +19963,25 @@
       </c>
     </row>
     <row r="134" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="103"/>
-      <c r="B134" s="132">
+      <c r="A134" s="123"/>
+      <c r="B134" s="119">
         <v>46196</v>
       </c>
-      <c r="C134" s="143">
+      <c r="C134" s="107">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D134" s="137" t="s">
+      <c r="D134" s="99" t="s">
         <v>137</v>
       </c>
-      <c r="E134" s="111" t="s">
+      <c r="E134" s="132" t="s">
         <v>70</v>
       </c>
-      <c r="F134" s="111" t="s">
+      <c r="F134" s="132" t="s">
         <v>71</v>
       </c>
-      <c r="G134" s="113"/>
-      <c r="H134" s="113"/>
-      <c r="I134" s="112" t="str">
+      <c r="G134" s="130"/>
+      <c r="H134" s="130"/>
+      <c r="I134" s="136" t="str">
         <f t="shared" ref="I134" si="36">IF(G134="","-",IF(G134&gt;H134,"L",IF(G134=H134,"E",IF(G134&lt;H134,"V"))))</f>
         <v>-</v>
       </c>
@@ -20094,15 +20098,15 @@
       </c>
     </row>
     <row r="135" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="103"/>
-      <c r="B135" s="133"/>
-      <c r="C135" s="133"/>
-      <c r="D135" s="106"/>
-      <c r="E135" s="106"/>
-      <c r="F135" s="106"/>
-      <c r="G135" s="108"/>
-      <c r="H135" s="108"/>
-      <c r="I135" s="110"/>
+      <c r="A135" s="123"/>
+      <c r="B135" s="108"/>
+      <c r="C135" s="108"/>
+      <c r="D135" s="100"/>
+      <c r="E135" s="100"/>
+      <c r="F135" s="100"/>
+      <c r="G135" s="131"/>
+      <c r="H135" s="131"/>
+      <c r="I135" s="137"/>
       <c r="J135" s="26">
         <v>0</v>
       </c>
@@ -20216,25 +20220,25 @@
       </c>
     </row>
     <row r="136" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="103"/>
-      <c r="B136" s="132">
+      <c r="A136" s="123"/>
+      <c r="B136" s="119">
         <v>46200</v>
       </c>
-      <c r="C136" s="143">
+      <c r="C136" s="107">
         <v>0.72916666666666663</v>
       </c>
-      <c r="D136" s="137" t="s">
+      <c r="D136" s="99" t="s">
         <v>91</v>
       </c>
-      <c r="E136" s="111" t="s">
+      <c r="E136" s="132" t="s">
         <v>70</v>
       </c>
-      <c r="F136" s="111" t="s">
+      <c r="F136" s="132" t="s">
         <v>17</v>
       </c>
-      <c r="G136" s="113"/>
-      <c r="H136" s="113"/>
-      <c r="I136" s="112" t="str">
+      <c r="G136" s="130"/>
+      <c r="H136" s="130"/>
+      <c r="I136" s="136" t="str">
         <f t="shared" ref="I136" si="37">IF(G136="","-",IF(G136&gt;H136,"L",IF(G136=H136,"E",IF(G136&lt;H136,"V"))))</f>
         <v>-</v>
       </c>
@@ -20351,15 +20355,15 @@
       </c>
     </row>
     <row r="137" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="103"/>
-      <c r="B137" s="133"/>
-      <c r="C137" s="133"/>
-      <c r="D137" s="106"/>
-      <c r="E137" s="106"/>
-      <c r="F137" s="106"/>
-      <c r="G137" s="108"/>
-      <c r="H137" s="108"/>
-      <c r="I137" s="110"/>
+      <c r="A137" s="123"/>
+      <c r="B137" s="108"/>
+      <c r="C137" s="108"/>
+      <c r="D137" s="100"/>
+      <c r="E137" s="100"/>
+      <c r="F137" s="100"/>
+      <c r="G137" s="131"/>
+      <c r="H137" s="131"/>
+      <c r="I137" s="137"/>
       <c r="J137" s="23">
         <v>3</v>
       </c>
@@ -20473,25 +20477,25 @@
       </c>
     </row>
     <row r="138" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="103"/>
-      <c r="B138" s="132">
+      <c r="A138" s="123"/>
+      <c r="B138" s="119">
         <v>46200</v>
       </c>
-      <c r="C138" s="143">
+      <c r="C138" s="107">
         <v>0.72916666666666663</v>
       </c>
-      <c r="D138" s="137" t="s">
+      <c r="D138" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="E138" s="111" t="s">
+      <c r="E138" s="132" t="s">
         <v>71</v>
       </c>
-      <c r="F138" s="111" t="s">
+      <c r="F138" s="132" t="s">
         <v>69</v>
       </c>
-      <c r="G138" s="113"/>
-      <c r="H138" s="113"/>
-      <c r="I138" s="112" t="str">
+      <c r="G138" s="130"/>
+      <c r="H138" s="130"/>
+      <c r="I138" s="136" t="str">
         <f t="shared" ref="I138" si="38">IF(G138="","-",IF(G138&gt;H138,"L",IF(G138=H138,"E",IF(G138&lt;H138,"V"))))</f>
         <v>-</v>
       </c>
@@ -20608,15 +20612,15 @@
       </c>
     </row>
     <row r="139" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="104"/>
-      <c r="B139" s="133"/>
-      <c r="C139" s="133"/>
-      <c r="D139" s="106"/>
-      <c r="E139" s="106"/>
-      <c r="F139" s="106"/>
-      <c r="G139" s="108"/>
-      <c r="H139" s="108"/>
-      <c r="I139" s="110"/>
+      <c r="A139" s="124"/>
+      <c r="B139" s="108"/>
+      <c r="C139" s="108"/>
+      <c r="D139" s="100"/>
+      <c r="E139" s="100"/>
+      <c r="F139" s="100"/>
+      <c r="G139" s="131"/>
+      <c r="H139" s="131"/>
+      <c r="I139" s="137"/>
       <c r="J139" s="26">
         <v>1</v>
       </c>
@@ -20730,27 +20734,27 @@
       </c>
     </row>
     <row r="140" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="114" t="s">
-        <v>7</v>
-      </c>
-      <c r="B140" s="130">
+      <c r="A140" s="133" t="s">
+        <v>7</v>
+      </c>
+      <c r="B140" s="118">
         <v>46190</v>
       </c>
-      <c r="C140" s="138">
+      <c r="C140" s="109">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D140" s="147" t="s">
+      <c r="D140" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="E140" s="117" t="s">
+      <c r="E140" s="127" t="s">
         <v>24</v>
       </c>
-      <c r="F140" s="117" t="s">
+      <c r="F140" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="G140" s="119"/>
-      <c r="H140" s="119"/>
-      <c r="I140" s="121" t="str">
+      <c r="G140" s="128"/>
+      <c r="H140" s="128"/>
+      <c r="I140" s="125" t="str">
         <f t="shared" ref="I140" si="39">IF(G140="","-",IF(G140&gt;H140,"L",IF(G140=H140,"E",IF(G140&lt;H140,"V"))))</f>
         <v>-</v>
       </c>
@@ -20867,15 +20871,15 @@
       </c>
     </row>
     <row r="141" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="115"/>
-      <c r="B141" s="131"/>
-      <c r="C141" s="131"/>
-      <c r="D141" s="118"/>
-      <c r="E141" s="118"/>
-      <c r="F141" s="118"/>
-      <c r="G141" s="120"/>
-      <c r="H141" s="120"/>
-      <c r="I141" s="122"/>
+      <c r="A141" s="134"/>
+      <c r="B141" s="110"/>
+      <c r="C141" s="110"/>
+      <c r="D141" s="102"/>
+      <c r="E141" s="102"/>
+      <c r="F141" s="102"/>
+      <c r="G141" s="129"/>
+      <c r="H141" s="129"/>
+      <c r="I141" s="126"/>
       <c r="J141" s="27">
         <v>2</v>
       </c>
@@ -20989,25 +20993,25 @@
       </c>
     </row>
     <row r="142" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="115"/>
-      <c r="B142" s="130">
+      <c r="A142" s="134"/>
+      <c r="B142" s="118">
         <v>46190</v>
       </c>
-      <c r="C142" s="138">
+      <c r="C142" s="109">
         <v>0.70833333333333337</v>
       </c>
-      <c r="D142" s="147" t="s">
+      <c r="D142" s="101" t="s">
         <v>84</v>
       </c>
-      <c r="E142" s="117" t="s">
+      <c r="E142" s="127" t="s">
         <v>72</v>
       </c>
-      <c r="F142" s="117" t="s">
+      <c r="F142" s="127" t="s">
         <v>73</v>
       </c>
-      <c r="G142" s="119"/>
-      <c r="H142" s="119"/>
-      <c r="I142" s="121" t="str">
+      <c r="G142" s="128"/>
+      <c r="H142" s="128"/>
+      <c r="I142" s="125" t="str">
         <f t="shared" ref="I142" si="40">IF(G142="","-",IF(G142&gt;H142,"L",IF(G142=H142,"E",IF(G142&lt;H142,"V"))))</f>
         <v>-</v>
       </c>
@@ -21124,15 +21128,15 @@
       </c>
     </row>
     <row r="143" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="115"/>
-      <c r="B143" s="131"/>
-      <c r="C143" s="131"/>
-      <c r="D143" s="118"/>
-      <c r="E143" s="118"/>
-      <c r="F143" s="118"/>
-      <c r="G143" s="120"/>
-      <c r="H143" s="120"/>
-      <c r="I143" s="122"/>
+      <c r="A143" s="134"/>
+      <c r="B143" s="110"/>
+      <c r="C143" s="110"/>
+      <c r="D143" s="102"/>
+      <c r="E143" s="102"/>
+      <c r="F143" s="102"/>
+      <c r="G143" s="129"/>
+      <c r="H143" s="129"/>
+      <c r="I143" s="126"/>
       <c r="J143" s="26">
         <v>2</v>
       </c>
@@ -21246,25 +21250,25 @@
       </c>
     </row>
     <row r="144" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="115"/>
-      <c r="B144" s="130">
+      <c r="A144" s="134"/>
+      <c r="B144" s="118">
         <v>46196</v>
       </c>
-      <c r="C144" s="138">
+      <c r="C144" s="109">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D144" s="147" t="s">
+      <c r="D144" s="101" t="s">
         <v>80</v>
       </c>
-      <c r="E144" s="117" t="s">
+      <c r="E144" s="127" t="s">
         <v>24</v>
       </c>
-      <c r="F144" s="117" t="s">
+      <c r="F144" s="127" t="s">
         <v>72</v>
       </c>
-      <c r="G144" s="119"/>
-      <c r="H144" s="119"/>
-      <c r="I144" s="121" t="str">
+      <c r="G144" s="128"/>
+      <c r="H144" s="128"/>
+      <c r="I144" s="125" t="str">
         <f t="shared" ref="I144" si="41">IF(G144="","-",IF(G144&gt;H144,"L",IF(G144=H144,"E",IF(G144&lt;H144,"V"))))</f>
         <v>-</v>
       </c>
@@ -21381,15 +21385,15 @@
       </c>
     </row>
     <row r="145" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="115"/>
-      <c r="B145" s="131"/>
-      <c r="C145" s="131"/>
-      <c r="D145" s="118"/>
-      <c r="E145" s="118"/>
-      <c r="F145" s="118"/>
-      <c r="G145" s="120"/>
-      <c r="H145" s="120"/>
-      <c r="I145" s="122"/>
+      <c r="A145" s="134"/>
+      <c r="B145" s="110"/>
+      <c r="C145" s="110"/>
+      <c r="D145" s="102"/>
+      <c r="E145" s="102"/>
+      <c r="F145" s="102"/>
+      <c r="G145" s="129"/>
+      <c r="H145" s="129"/>
+      <c r="I145" s="126"/>
       <c r="J145" s="27">
         <v>3</v>
       </c>
@@ -21503,25 +21507,25 @@
       </c>
     </row>
     <row r="146" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="115"/>
-      <c r="B146" s="130">
+      <c r="A146" s="134"/>
+      <c r="B146" s="118">
         <v>46196</v>
       </c>
-      <c r="C146" s="138">
+      <c r="C146" s="109">
         <v>0.70833333333333337</v>
       </c>
-      <c r="D146" s="147" t="s">
+      <c r="D146" s="101" t="s">
         <v>84</v>
       </c>
-      <c r="E146" s="117" t="s">
+      <c r="E146" s="127" t="s">
         <v>73</v>
       </c>
-      <c r="F146" s="117" t="s">
+      <c r="F146" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="G146" s="119"/>
-      <c r="H146" s="119"/>
-      <c r="I146" s="121" t="str">
+      <c r="G146" s="128"/>
+      <c r="H146" s="128"/>
+      <c r="I146" s="125" t="str">
         <f t="shared" ref="I146" si="42">IF(G146="","-",IF(G146&gt;H146,"L",IF(G146=H146,"E",IF(G146&lt;H146,"V"))))</f>
         <v>-</v>
       </c>
@@ -21638,15 +21642,15 @@
       </c>
     </row>
     <row r="147" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="115"/>
-      <c r="B147" s="131"/>
-      <c r="C147" s="131"/>
-      <c r="D147" s="118"/>
-      <c r="E147" s="118"/>
-      <c r="F147" s="118"/>
-      <c r="G147" s="120"/>
-      <c r="H147" s="120"/>
-      <c r="I147" s="122"/>
+      <c r="A147" s="134"/>
+      <c r="B147" s="110"/>
+      <c r="C147" s="110"/>
+      <c r="D147" s="102"/>
+      <c r="E147" s="102"/>
+      <c r="F147" s="102"/>
+      <c r="G147" s="129"/>
+      <c r="H147" s="129"/>
+      <c r="I147" s="126"/>
       <c r="J147" s="26">
         <v>2</v>
       </c>
@@ -21760,25 +21764,25 @@
       </c>
     </row>
     <row r="148" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="115"/>
-      <c r="B148" s="130">
+      <c r="A148" s="134"/>
+      <c r="B148" s="118">
         <v>46200</v>
       </c>
-      <c r="C148" s="138">
+      <c r="C148" s="109">
         <v>0.625</v>
       </c>
-      <c r="D148" s="147" t="s">
+      <c r="D148" s="101" t="s">
         <v>81</v>
       </c>
-      <c r="E148" s="117" t="s">
+      <c r="E148" s="127" t="s">
         <v>73</v>
       </c>
-      <c r="F148" s="117" t="s">
+      <c r="F148" s="127" t="s">
         <v>24</v>
       </c>
-      <c r="G148" s="119"/>
-      <c r="H148" s="119"/>
-      <c r="I148" s="121" t="str">
+      <c r="G148" s="128"/>
+      <c r="H148" s="128"/>
+      <c r="I148" s="125" t="str">
         <f t="shared" ref="I148" si="43">IF(G148="","-",IF(G148&gt;H148,"L",IF(G148=H148,"E",IF(G148&lt;H148,"V"))))</f>
         <v>-</v>
       </c>
@@ -21895,15 +21899,15 @@
       </c>
     </row>
     <row r="149" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="115"/>
-      <c r="B149" s="131"/>
-      <c r="C149" s="131"/>
-      <c r="D149" s="118"/>
-      <c r="E149" s="118"/>
-      <c r="F149" s="118"/>
-      <c r="G149" s="120"/>
-      <c r="H149" s="120"/>
-      <c r="I149" s="122"/>
+      <c r="A149" s="134"/>
+      <c r="B149" s="110"/>
+      <c r="C149" s="110"/>
+      <c r="D149" s="102"/>
+      <c r="E149" s="102"/>
+      <c r="F149" s="102"/>
+      <c r="G149" s="129"/>
+      <c r="H149" s="129"/>
+      <c r="I149" s="126"/>
       <c r="J149" s="27">
         <v>4</v>
       </c>
@@ -22017,25 +22021,25 @@
       </c>
     </row>
     <row r="150" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="115"/>
-      <c r="B150" s="130">
+      <c r="A150" s="134"/>
+      <c r="B150" s="118">
         <v>46200</v>
       </c>
-      <c r="C150" s="138">
+      <c r="C150" s="109">
         <v>0.625</v>
       </c>
-      <c r="D150" s="147" t="s">
+      <c r="D150" s="101" t="s">
         <v>94</v>
       </c>
-      <c r="E150" s="117" t="s">
+      <c r="E150" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="F150" s="117" t="s">
+      <c r="F150" s="127" t="s">
         <v>72</v>
       </c>
-      <c r="G150" s="119"/>
-      <c r="H150" s="119"/>
-      <c r="I150" s="121" t="str">
+      <c r="G150" s="128"/>
+      <c r="H150" s="128"/>
+      <c r="I150" s="125" t="str">
         <f t="shared" ref="I150" si="44">IF(G150="","-",IF(G150&gt;H150,"L",IF(G150=H150,"E",IF(G150&lt;H150,"V"))))</f>
         <v>-</v>
       </c>
@@ -22152,15 +22156,15 @@
       </c>
     </row>
     <row r="151" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="116"/>
-      <c r="B151" s="131"/>
-      <c r="C151" s="131"/>
-      <c r="D151" s="118"/>
-      <c r="E151" s="118"/>
-      <c r="F151" s="118"/>
-      <c r="G151" s="120"/>
-      <c r="H151" s="120"/>
-      <c r="I151" s="122"/>
+      <c r="A151" s="135"/>
+      <c r="B151" s="110"/>
+      <c r="C151" s="110"/>
+      <c r="D151" s="102"/>
+      <c r="E151" s="102"/>
+      <c r="F151" s="102"/>
+      <c r="G151" s="129"/>
+      <c r="H151" s="129"/>
+      <c r="I151" s="126"/>
       <c r="J151" s="93">
         <v>3</v>
       </c>
@@ -22274,14 +22278,14 @@
       </c>
     </row>
     <row r="152" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F152" s="134" t="s">
+      <c r="F152" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="G152" s="134"/>
-      <c r="H152" s="134"/>
+      <c r="G152" s="138"/>
+      <c r="H152" s="138"/>
       <c r="I152" s="5">
         <f>SUM(G8:H79)</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J152" s="51">
         <f>SUM(J79,J77,J75,J73,J71,J69,J67,J65,J63,J61,J59,J57,J55,J53,J51,J49,J47,J45,J43,J41,J39,J37,J35,J33,J31,J29,J27,J25,J23,J21,J19,J17,J15,J13,J11,J9,J81,J83,J85,J87,J89,J91,J93,J95,J97,J99,J101,J103,J105,J107,J109,J111,J113,J115,J117,J119,J121,J123,J125,J127,J129,J131,J133,J135,J137,J139,J141,J143,J145,J147,J149,J151)</f>
@@ -22433,12 +22437,12 @@
       </c>
     </row>
     <row r="153" spans="1:46" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F153" s="135" t="s">
+      <c r="F153" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="G153" s="135"/>
-      <c r="H153" s="135"/>
-      <c r="I153" s="135"/>
+      <c r="G153" s="139"/>
+      <c r="H153" s="139"/>
+      <c r="I153" s="139"/>
       <c r="J153" s="31">
         <f>SUM(J154:J157)</f>
         <v>0</v>
@@ -23205,24 +23209,24 @@
       </c>
     </row>
     <row r="158" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E158" s="136"/>
-      <c r="F158" s="136"/>
-      <c r="G158" s="136"/>
-      <c r="H158" s="136"/>
+      <c r="E158" s="140"/>
+      <c r="F158" s="140"/>
+      <c r="G158" s="140"/>
+      <c r="H158" s="140"/>
       <c r="I158" s="3"/>
     </row>
     <row r="159" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E159" s="136"/>
-      <c r="F159" s="136"/>
-      <c r="G159" s="136"/>
-      <c r="H159" s="136"/>
+      <c r="E159" s="140"/>
+      <c r="F159" s="140"/>
+      <c r="G159" s="140"/>
+      <c r="H159" s="140"/>
       <c r="I159" s="3"/>
     </row>
     <row r="160" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E160" s="136"/>
-      <c r="F160" s="136"/>
-      <c r="G160" s="136"/>
-      <c r="H160" s="136"/>
+      <c r="E160" s="140"/>
+      <c r="F160" s="140"/>
+      <c r="G160" s="140"/>
+      <c r="H160" s="140"/>
       <c r="I160" s="3"/>
     </row>
     <row r="181" spans="10:10" x14ac:dyDescent="0.3">
@@ -23236,60 +23240,524 @@
     <sortCondition descending="1" ref="J153:AT153"/>
   </sortState>
   <mergeCells count="596">
-    <mergeCell ref="D134:D135"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="D140:D141"/>
-    <mergeCell ref="D142:D143"/>
-    <mergeCell ref="D144:D145"/>
-    <mergeCell ref="D146:D147"/>
-    <mergeCell ref="D148:D149"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="D116:D117"/>
-    <mergeCell ref="D118:D119"/>
-    <mergeCell ref="D120:D121"/>
-    <mergeCell ref="D122:D123"/>
-    <mergeCell ref="D124:D125"/>
-    <mergeCell ref="D126:D127"/>
-    <mergeCell ref="D128:D129"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="D132:D133"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="D98:D99"/>
-    <mergeCell ref="D100:D101"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="D110:D111"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="D86:D87"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A8:A19"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A20:A31"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="A44:A55"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="A32:A43"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="I48:I49"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="I56:I57"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="I62:I63"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="F64:F65"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="H64:H65"/>
+    <mergeCell ref="I64:I65"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="I60:I61"/>
+    <mergeCell ref="A68:A79"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="F68:F69"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="H68:H69"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="H62:H63"/>
+    <mergeCell ref="A56:A67"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="F78:F79"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="H78:H79"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="F66:F67"/>
+    <mergeCell ref="G66:G67"/>
+    <mergeCell ref="H66:H67"/>
+    <mergeCell ref="I66:I67"/>
+    <mergeCell ref="I72:I73"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="F74:F75"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="H74:H75"/>
+    <mergeCell ref="I74:I75"/>
+    <mergeCell ref="E76:E77"/>
+    <mergeCell ref="F76:F77"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="H76:H77"/>
+    <mergeCell ref="I76:I77"/>
+    <mergeCell ref="I78:I79"/>
+    <mergeCell ref="F152:H152"/>
+    <mergeCell ref="F153:I153"/>
+    <mergeCell ref="E158:H158"/>
+    <mergeCell ref="E159:H159"/>
+    <mergeCell ref="E160:H160"/>
+    <mergeCell ref="H88:H89"/>
+    <mergeCell ref="I88:I89"/>
+    <mergeCell ref="E90:E91"/>
+    <mergeCell ref="F90:F91"/>
+    <mergeCell ref="G90:G91"/>
+    <mergeCell ref="H90:H91"/>
+    <mergeCell ref="I90:I91"/>
+    <mergeCell ref="E100:E101"/>
+    <mergeCell ref="F100:F101"/>
+    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="H108:H109"/>
+    <mergeCell ref="I108:I109"/>
+    <mergeCell ref="E110:E111"/>
+    <mergeCell ref="H110:H111"/>
+    <mergeCell ref="I110:I111"/>
+    <mergeCell ref="H100:H101"/>
+    <mergeCell ref="I100:I101"/>
+    <mergeCell ref="E102:E103"/>
+    <mergeCell ref="A80:A91"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:F81"/>
+    <mergeCell ref="G80:G81"/>
+    <mergeCell ref="H80:H81"/>
+    <mergeCell ref="I80:I81"/>
+    <mergeCell ref="E82:E83"/>
+    <mergeCell ref="F82:F83"/>
+    <mergeCell ref="G82:G83"/>
+    <mergeCell ref="H82:H83"/>
+    <mergeCell ref="I82:I83"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:F85"/>
+    <mergeCell ref="G84:G85"/>
+    <mergeCell ref="H84:H85"/>
+    <mergeCell ref="I84:I85"/>
+    <mergeCell ref="E86:E87"/>
+    <mergeCell ref="F86:F87"/>
+    <mergeCell ref="G86:G87"/>
+    <mergeCell ref="H86:H87"/>
+    <mergeCell ref="I86:I87"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="F88:F89"/>
+    <mergeCell ref="G88:G89"/>
+    <mergeCell ref="A92:A103"/>
+    <mergeCell ref="E92:E93"/>
+    <mergeCell ref="F92:F93"/>
+    <mergeCell ref="G92:G93"/>
+    <mergeCell ref="H92:H93"/>
+    <mergeCell ref="I92:I93"/>
+    <mergeCell ref="E94:E95"/>
+    <mergeCell ref="F94:F95"/>
+    <mergeCell ref="G94:G95"/>
+    <mergeCell ref="H94:H95"/>
+    <mergeCell ref="I94:I95"/>
+    <mergeCell ref="E96:E97"/>
+    <mergeCell ref="F96:F97"/>
+    <mergeCell ref="G96:G97"/>
+    <mergeCell ref="H96:H97"/>
+    <mergeCell ref="I96:I97"/>
+    <mergeCell ref="E98:E99"/>
+    <mergeCell ref="F98:F99"/>
+    <mergeCell ref="G98:G99"/>
+    <mergeCell ref="H98:H99"/>
+    <mergeCell ref="I98:I99"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="F102:F103"/>
+    <mergeCell ref="G102:G103"/>
+    <mergeCell ref="H102:H103"/>
+    <mergeCell ref="I102:I103"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="F104:F105"/>
+    <mergeCell ref="G104:G105"/>
+    <mergeCell ref="H104:H105"/>
+    <mergeCell ref="I104:I105"/>
+    <mergeCell ref="A104:A115"/>
+    <mergeCell ref="E108:E109"/>
+    <mergeCell ref="F108:F109"/>
+    <mergeCell ref="G108:G109"/>
+    <mergeCell ref="E112:E113"/>
+    <mergeCell ref="F112:F113"/>
+    <mergeCell ref="G112:G113"/>
+    <mergeCell ref="H112:H113"/>
+    <mergeCell ref="I112:I113"/>
+    <mergeCell ref="E106:E107"/>
+    <mergeCell ref="F106:F107"/>
+    <mergeCell ref="G106:G107"/>
+    <mergeCell ref="H106:H107"/>
+    <mergeCell ref="I106:I107"/>
+    <mergeCell ref="E114:E115"/>
+    <mergeCell ref="F114:F115"/>
+    <mergeCell ref="G114:G115"/>
+    <mergeCell ref="H114:H115"/>
+    <mergeCell ref="F110:F111"/>
+    <mergeCell ref="G110:G111"/>
+    <mergeCell ref="D112:D113"/>
+    <mergeCell ref="D114:D115"/>
+    <mergeCell ref="A116:A127"/>
+    <mergeCell ref="E116:E117"/>
+    <mergeCell ref="F116:F117"/>
+    <mergeCell ref="G116:G117"/>
+    <mergeCell ref="H116:H117"/>
+    <mergeCell ref="I116:I117"/>
+    <mergeCell ref="E118:E119"/>
+    <mergeCell ref="F118:F119"/>
+    <mergeCell ref="G118:G119"/>
+    <mergeCell ref="H118:H119"/>
+    <mergeCell ref="I118:I119"/>
+    <mergeCell ref="E120:E121"/>
+    <mergeCell ref="F120:F121"/>
+    <mergeCell ref="G120:G121"/>
+    <mergeCell ref="H120:H121"/>
+    <mergeCell ref="I120:I121"/>
+    <mergeCell ref="E122:E123"/>
+    <mergeCell ref="F122:F123"/>
+    <mergeCell ref="G122:G123"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="I128:I129"/>
+    <mergeCell ref="E130:E131"/>
+    <mergeCell ref="F130:F131"/>
+    <mergeCell ref="G130:G131"/>
+    <mergeCell ref="H130:H131"/>
+    <mergeCell ref="I130:I131"/>
+    <mergeCell ref="E132:E133"/>
+    <mergeCell ref="F132:F133"/>
+    <mergeCell ref="I114:I115"/>
+    <mergeCell ref="H122:H123"/>
+    <mergeCell ref="I122:I123"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="F124:F125"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="I124:I125"/>
+    <mergeCell ref="E126:E127"/>
+    <mergeCell ref="F126:F127"/>
+    <mergeCell ref="G126:G127"/>
+    <mergeCell ref="H126:H127"/>
+    <mergeCell ref="I126:I127"/>
+    <mergeCell ref="G132:G133"/>
+    <mergeCell ref="H132:H133"/>
+    <mergeCell ref="I132:I133"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="F138:F139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="H138:H139"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="I134:I135"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="F136:F137"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="A140:A151"/>
+    <mergeCell ref="E140:E141"/>
+    <mergeCell ref="F140:F141"/>
+    <mergeCell ref="G140:G141"/>
+    <mergeCell ref="H140:H141"/>
+    <mergeCell ref="I140:I141"/>
+    <mergeCell ref="E142:E143"/>
+    <mergeCell ref="F142:F143"/>
+    <mergeCell ref="G142:G143"/>
+    <mergeCell ref="H142:H143"/>
+    <mergeCell ref="I142:I143"/>
+    <mergeCell ref="E144:E145"/>
+    <mergeCell ref="F144:F145"/>
+    <mergeCell ref="G144:G145"/>
+    <mergeCell ref="H144:H145"/>
+    <mergeCell ref="I144:I145"/>
+    <mergeCell ref="E146:E147"/>
+    <mergeCell ref="A128:A139"/>
+    <mergeCell ref="I150:I151"/>
+    <mergeCell ref="F146:F147"/>
+    <mergeCell ref="G146:G147"/>
+    <mergeCell ref="H146:H147"/>
+    <mergeCell ref="I146:I147"/>
+    <mergeCell ref="E148:E149"/>
+    <mergeCell ref="F148:F149"/>
+    <mergeCell ref="G148:G149"/>
+    <mergeCell ref="H148:H149"/>
+    <mergeCell ref="I148:I149"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="F150:F151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="H150:H151"/>
+    <mergeCell ref="H136:H137"/>
+    <mergeCell ref="E128:E129"/>
+    <mergeCell ref="F128:F129"/>
+    <mergeCell ref="G128:G129"/>
+    <mergeCell ref="H128:H129"/>
+    <mergeCell ref="E134:E135"/>
+    <mergeCell ref="F134:F135"/>
+    <mergeCell ref="G134:G135"/>
+    <mergeCell ref="H134:H135"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="B132:B133"/>
+    <mergeCell ref="B134:B135"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="C112:C113"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="C134:C135"/>
     <mergeCell ref="C136:C137"/>
     <mergeCell ref="C138:C139"/>
     <mergeCell ref="C140:C141"/>
@@ -23314,524 +23782,60 @@
     <mergeCell ref="D34:D35"/>
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="D38:D39"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="C110:C111"/>
-    <mergeCell ref="C112:C113"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="B132:B133"/>
-    <mergeCell ref="B134:B135"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="A128:A139"/>
-    <mergeCell ref="I150:I151"/>
-    <mergeCell ref="F146:F147"/>
-    <mergeCell ref="G146:G147"/>
-    <mergeCell ref="H146:H147"/>
-    <mergeCell ref="I146:I147"/>
-    <mergeCell ref="E148:E149"/>
-    <mergeCell ref="F148:F149"/>
-    <mergeCell ref="G148:G149"/>
-    <mergeCell ref="H148:H149"/>
-    <mergeCell ref="I148:I149"/>
-    <mergeCell ref="E150:E151"/>
-    <mergeCell ref="F150:F151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="H150:H151"/>
-    <mergeCell ref="H136:H137"/>
-    <mergeCell ref="E128:E129"/>
-    <mergeCell ref="F128:F129"/>
-    <mergeCell ref="G128:G129"/>
-    <mergeCell ref="H128:H129"/>
-    <mergeCell ref="E134:E135"/>
-    <mergeCell ref="F134:F135"/>
-    <mergeCell ref="G134:G135"/>
-    <mergeCell ref="H134:H135"/>
-    <mergeCell ref="A140:A151"/>
-    <mergeCell ref="E140:E141"/>
-    <mergeCell ref="F140:F141"/>
-    <mergeCell ref="G140:G141"/>
-    <mergeCell ref="H140:H141"/>
-    <mergeCell ref="I140:I141"/>
-    <mergeCell ref="E142:E143"/>
-    <mergeCell ref="F142:F143"/>
-    <mergeCell ref="G142:G143"/>
-    <mergeCell ref="H142:H143"/>
-    <mergeCell ref="I142:I143"/>
-    <mergeCell ref="E144:E145"/>
-    <mergeCell ref="F144:F145"/>
-    <mergeCell ref="G144:G145"/>
-    <mergeCell ref="H144:H145"/>
-    <mergeCell ref="I144:I145"/>
-    <mergeCell ref="E146:E147"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="F138:F139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="H138:H139"/>
-    <mergeCell ref="I138:I139"/>
-    <mergeCell ref="I134:I135"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="F136:F137"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="I128:I129"/>
-    <mergeCell ref="E130:E131"/>
-    <mergeCell ref="F130:F131"/>
-    <mergeCell ref="G130:G131"/>
-    <mergeCell ref="H130:H131"/>
-    <mergeCell ref="I130:I131"/>
-    <mergeCell ref="E132:E133"/>
-    <mergeCell ref="F132:F133"/>
-    <mergeCell ref="I114:I115"/>
-    <mergeCell ref="H122:H123"/>
-    <mergeCell ref="I122:I123"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="F124:F125"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="H124:H125"/>
-    <mergeCell ref="I124:I125"/>
-    <mergeCell ref="E126:E127"/>
-    <mergeCell ref="F126:F127"/>
-    <mergeCell ref="G126:G127"/>
-    <mergeCell ref="H126:H127"/>
-    <mergeCell ref="I126:I127"/>
-    <mergeCell ref="G132:G133"/>
-    <mergeCell ref="H132:H133"/>
-    <mergeCell ref="I132:I133"/>
-    <mergeCell ref="A116:A127"/>
-    <mergeCell ref="E116:E117"/>
-    <mergeCell ref="F116:F117"/>
-    <mergeCell ref="G116:G117"/>
-    <mergeCell ref="H116:H117"/>
-    <mergeCell ref="I116:I117"/>
-    <mergeCell ref="E118:E119"/>
-    <mergeCell ref="F118:F119"/>
-    <mergeCell ref="G118:G119"/>
-    <mergeCell ref="H118:H119"/>
-    <mergeCell ref="I118:I119"/>
-    <mergeCell ref="E120:E121"/>
-    <mergeCell ref="F120:F121"/>
-    <mergeCell ref="G120:G121"/>
-    <mergeCell ref="H120:H121"/>
-    <mergeCell ref="I120:I121"/>
-    <mergeCell ref="E122:E123"/>
-    <mergeCell ref="F122:F123"/>
-    <mergeCell ref="G122:G123"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="A104:A115"/>
-    <mergeCell ref="E108:E109"/>
-    <mergeCell ref="F108:F109"/>
-    <mergeCell ref="G108:G109"/>
-    <mergeCell ref="E112:E113"/>
-    <mergeCell ref="F112:F113"/>
-    <mergeCell ref="G112:G113"/>
-    <mergeCell ref="H112:H113"/>
-    <mergeCell ref="I112:I113"/>
-    <mergeCell ref="E106:E107"/>
-    <mergeCell ref="F106:F107"/>
-    <mergeCell ref="G106:G107"/>
-    <mergeCell ref="H106:H107"/>
-    <mergeCell ref="I106:I107"/>
-    <mergeCell ref="E114:E115"/>
-    <mergeCell ref="F114:F115"/>
-    <mergeCell ref="G114:G115"/>
-    <mergeCell ref="H114:H115"/>
-    <mergeCell ref="F110:F111"/>
-    <mergeCell ref="G110:G111"/>
-    <mergeCell ref="D112:D113"/>
-    <mergeCell ref="D114:D115"/>
-    <mergeCell ref="F102:F103"/>
-    <mergeCell ref="G102:G103"/>
-    <mergeCell ref="H102:H103"/>
-    <mergeCell ref="I102:I103"/>
-    <mergeCell ref="E104:E105"/>
-    <mergeCell ref="F104:F105"/>
-    <mergeCell ref="G104:G105"/>
-    <mergeCell ref="H104:H105"/>
-    <mergeCell ref="I104:I105"/>
-    <mergeCell ref="A92:A103"/>
-    <mergeCell ref="E92:E93"/>
-    <mergeCell ref="F92:F93"/>
-    <mergeCell ref="G92:G93"/>
-    <mergeCell ref="H92:H93"/>
-    <mergeCell ref="I92:I93"/>
-    <mergeCell ref="E94:E95"/>
-    <mergeCell ref="F94:F95"/>
-    <mergeCell ref="G94:G95"/>
-    <mergeCell ref="H94:H95"/>
-    <mergeCell ref="I94:I95"/>
-    <mergeCell ref="E96:E97"/>
-    <mergeCell ref="F96:F97"/>
-    <mergeCell ref="G96:G97"/>
-    <mergeCell ref="H96:H97"/>
-    <mergeCell ref="I96:I97"/>
-    <mergeCell ref="E98:E99"/>
-    <mergeCell ref="F98:F99"/>
-    <mergeCell ref="G98:G99"/>
-    <mergeCell ref="H98:H99"/>
-    <mergeCell ref="I98:I99"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="A80:A91"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:F81"/>
-    <mergeCell ref="G80:G81"/>
-    <mergeCell ref="H80:H81"/>
-    <mergeCell ref="I80:I81"/>
-    <mergeCell ref="E82:E83"/>
-    <mergeCell ref="F82:F83"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="H82:H83"/>
-    <mergeCell ref="I82:I83"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:F85"/>
-    <mergeCell ref="G84:G85"/>
-    <mergeCell ref="H84:H85"/>
-    <mergeCell ref="I84:I85"/>
-    <mergeCell ref="E86:E87"/>
-    <mergeCell ref="F86:F87"/>
-    <mergeCell ref="G86:G87"/>
-    <mergeCell ref="H86:H87"/>
-    <mergeCell ref="I86:I87"/>
-    <mergeCell ref="E88:E89"/>
-    <mergeCell ref="F88:F89"/>
-    <mergeCell ref="G88:G89"/>
-    <mergeCell ref="I78:I79"/>
-    <mergeCell ref="F152:H152"/>
-    <mergeCell ref="F153:I153"/>
-    <mergeCell ref="E158:H158"/>
-    <mergeCell ref="E159:H159"/>
-    <mergeCell ref="E160:H160"/>
-    <mergeCell ref="H88:H89"/>
-    <mergeCell ref="I88:I89"/>
-    <mergeCell ref="E90:E91"/>
-    <mergeCell ref="F90:F91"/>
-    <mergeCell ref="G90:G91"/>
-    <mergeCell ref="H90:H91"/>
-    <mergeCell ref="I90:I91"/>
-    <mergeCell ref="E100:E101"/>
-    <mergeCell ref="F100:F101"/>
-    <mergeCell ref="G100:G101"/>
-    <mergeCell ref="H108:H109"/>
-    <mergeCell ref="I108:I109"/>
-    <mergeCell ref="E110:E111"/>
-    <mergeCell ref="H110:H111"/>
-    <mergeCell ref="I110:I111"/>
-    <mergeCell ref="H100:H101"/>
-    <mergeCell ref="I100:I101"/>
-    <mergeCell ref="E102:E103"/>
-    <mergeCell ref="I72:I73"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="F74:F75"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="H74:H75"/>
-    <mergeCell ref="I74:I75"/>
-    <mergeCell ref="E76:E77"/>
-    <mergeCell ref="F76:F77"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="H76:H77"/>
-    <mergeCell ref="I76:I77"/>
-    <mergeCell ref="I68:I69"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="F70:F71"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="H70:H71"/>
-    <mergeCell ref="I70:I71"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="F66:F67"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="H66:H67"/>
-    <mergeCell ref="I66:I67"/>
-    <mergeCell ref="A68:A79"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="F68:F69"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="H68:H69"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="F62:F63"/>
-    <mergeCell ref="G62:G63"/>
-    <mergeCell ref="H62:H63"/>
-    <mergeCell ref="A56:A67"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="F56:F57"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="F78:F79"/>
-    <mergeCell ref="G78:G79"/>
-    <mergeCell ref="H78:H79"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="I62:I63"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="F64:F65"/>
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="H64:H65"/>
-    <mergeCell ref="I64:I65"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="I60:I61"/>
-    <mergeCell ref="I48:I49"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="I56:I57"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="H52:H53"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="I54:I55"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="I42:I43"/>
-    <mergeCell ref="A44:A55"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="A32:A43"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I34:I35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="A20:A31"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A8:A19"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="D98:D99"/>
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="D110:D111"/>
+    <mergeCell ref="D116:D117"/>
+    <mergeCell ref="D118:D119"/>
+    <mergeCell ref="D120:D121"/>
+    <mergeCell ref="D122:D123"/>
+    <mergeCell ref="D124:D125"/>
+    <mergeCell ref="D126:D127"/>
+    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="D132:D133"/>
+    <mergeCell ref="D134:D135"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="D140:D141"/>
+    <mergeCell ref="D142:D143"/>
+    <mergeCell ref="D144:D145"/>
+    <mergeCell ref="D146:D147"/>
+    <mergeCell ref="D148:D149"/>
+    <mergeCell ref="D150:D151"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J8:P8 R148:AT148 R8:AT8 R10:AT10 R12:AT12 R14:AT14 R150:AT150 R128:AT128 R130:AT130 R132:AT132 R134:AT134 R136:AT136 R138:AT138 R140:AT140 R142:AT142 R144:AT144 R146:AT146 R124:AT124 R126:AT126 R104:AT104 R106:AT106 R108:AT108 R110:AT110 R112:AT112 R114:AT114 R116:AT116 R118:AT118 R120:AT120 R122:AT122 R100:AT100 R102:AT102 R80:AT80 R82:AT82 R84:AT84 R86:AT86 R88:AT88 R90:AT90 R92:AT92 R94:AT94 R96:AT96 R98:AT98 R76:AT76 R78:AT78 R16:AT16 R18:AT18 R20:AT20 R22:AT22 R24:AT24 R26:AT26 R28:AT28 R30:AT30 R32:AT32 R34:AT34 R36:AT36 R38:AT38 R40:AT40 R42:AT42 R44:AT44 R46:AT46 R48:AT48 R50:AT50 R52:AT52 R54:AT54 R56:AT56 R58:AT58 R60:AT60 R62:AT62 R64:AT64 R66:AT66 R68:AT68 R70:AT70 R72:AT72 R74:AT74 J10:P10 J12:P12 J14:P14 J150:P150 J128:P128 J130:P130 J132:P132 J134:P134 J136:P136 J138:P138 J140:P140 J142:P142 J144:P144 J146:P146 J124:P124 J126:P126 J104:P104 J106:P106 J108:P108 J110:P110 J112:P112 J114:P114 J116:P116 J118:P118 J120:P120 J122:P122 J100:P100 J102:P102 J80:P80 J82:P82 J84:P84 J86:P86 J88:P88 J90:P90 J92:P92 J94:P94 J96:P96 J98:P98 J76:P76 J78:P78 J16:P16 J18:P18 J20:P20 J22:P22 J24:P24 J26:P26 J28:P28 J30:P30 J32:P32 J34:P34 J36:P36 J38:P38 J40:P40 J42:P42 J44:P44 J46:P46 J48:P48 J50:P50 J52:P52 J54:P54 J56:P56 J58:P58 J60:P60 J62:P62 J64:P64 J66:P66 J68:P68 J70:P70 J72:P72 J74:P74 J148:P148" xr:uid="{5B7EC075-BC45-41B2-9DB1-1D8DBC4AE17C}">
@@ -25853,16 +25857,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
       <c r="I1" s="44">
         <v>1</v>
       </c>
@@ -25918,9 +25922,9 @@
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
       <c r="E2" s="41"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="101"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="146"/>
       <c r="I2" s="45"/>
       <c r="J2" s="35"/>
       <c r="K2" s="36"/>
@@ -25954,10 +25958,10 @@
       <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="162" t="s">
+      <c r="F3" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="G3" s="162"/>
+      <c r="G3" s="153"/>
       <c r="H3" s="16" t="s">
         <v>8</v>
       </c>
@@ -26030,24 +26034,24 @@
       </c>
     </row>
     <row r="4" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="125" t="s">
+      <c r="A4" s="122" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="132">
+      <c r="B4" s="119">
         <v>46202</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="151" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="153" t="s">
+      <c r="D4" s="151" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="153" t="s">
+      <c r="E4" s="151" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="112" t="str">
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="136" t="str">
         <f>IF(F4="","-",IF(F4&gt;G4,"L",IF(F4=G4,"E",IF(F4&lt;G4,"V"))))</f>
         <v>-</v>
       </c>
@@ -26069,14 +26073,14 @@
       <c r="X4" s="22"/>
     </row>
     <row r="5" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="103"/>
-      <c r="B5" s="133"/>
-      <c r="C5" s="154"/>
-      <c r="D5" s="154"/>
-      <c r="E5" s="154"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="110"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="152"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="137"/>
       <c r="I5" s="23" t="s">
         <v>9</v>
       </c>
@@ -26133,22 +26137,22 @@
       </c>
     </row>
     <row r="6" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="103"/>
-      <c r="B6" s="132">
+      <c r="A6" s="123"/>
+      <c r="B6" s="119">
         <v>46203</v>
       </c>
-      <c r="C6" s="153" t="s">
+      <c r="C6" s="151" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="153" t="s">
+      <c r="D6" s="151" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="153" t="s">
+      <c r="E6" s="151" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="112" t="str">
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="136" t="str">
         <f t="shared" ref="H6:H34" si="1">IF(F6="","-",IF(F6&gt;G6,"L",IF(F6=G6,"E",IF(F6&lt;G6,"V"))))</f>
         <v>-</v>
       </c>
@@ -26176,14 +26180,14 @@
       </c>
     </row>
     <row r="7" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="103"/>
-      <c r="B7" s="133"/>
-      <c r="C7" s="154"/>
-      <c r="D7" s="154"/>
-      <c r="E7" s="154"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="110"/>
+      <c r="A7" s="123"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="152"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="137"/>
       <c r="I7" s="26" t="s">
         <v>9</v>
       </c>
@@ -26240,22 +26244,22 @@
       </c>
     </row>
     <row r="8" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="103"/>
-      <c r="B8" s="132">
+      <c r="A8" s="123"/>
+      <c r="B8" s="119">
         <v>46201</v>
       </c>
-      <c r="C8" s="153" t="s">
+      <c r="C8" s="151" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="153" t="s">
+      <c r="D8" s="151" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="153" t="s">
+      <c r="E8" s="151" t="s">
         <v>100</v>
       </c>
-      <c r="F8" s="111"/>
-      <c r="G8" s="111"/>
-      <c r="H8" s="112" t="str">
+      <c r="F8" s="132"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="136" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -26281,14 +26285,14 @@
       </c>
     </row>
     <row r="9" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="103"/>
-      <c r="B9" s="133"/>
-      <c r="C9" s="154"/>
-      <c r="D9" s="154"/>
-      <c r="E9" s="154"/>
-      <c r="F9" s="106"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="110"/>
+      <c r="A9" s="123"/>
+      <c r="B9" s="108"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="152"/>
+      <c r="E9" s="152"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="137"/>
       <c r="I9" s="23" t="s">
         <v>9</v>
       </c>
@@ -26343,22 +26347,22 @@
       </c>
     </row>
     <row r="10" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="103"/>
-      <c r="B10" s="132">
+      <c r="A10" s="123"/>
+      <c r="B10" s="119">
         <v>46202</v>
       </c>
-      <c r="C10" s="153" t="s">
+      <c r="C10" s="151" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="153" t="s">
+      <c r="D10" s="151" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="153" t="s">
+      <c r="E10" s="151" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="111"/>
-      <c r="G10" s="111"/>
-      <c r="H10" s="112" t="str">
+      <c r="F10" s="132"/>
+      <c r="G10" s="132"/>
+      <c r="H10" s="136" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -26384,14 +26388,14 @@
       </c>
     </row>
     <row r="11" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="103"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="154"/>
-      <c r="D11" s="154"/>
-      <c r="E11" s="154"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="110"/>
+      <c r="A11" s="123"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="152"/>
+      <c r="E11" s="152"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="100"/>
+      <c r="H11" s="137"/>
       <c r="I11" s="26" t="s">
         <v>9</v>
       </c>
@@ -26446,22 +26450,22 @@
       </c>
     </row>
     <row r="12" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="103"/>
-      <c r="B12" s="130">
+      <c r="A12" s="123"/>
+      <c r="B12" s="118">
         <v>46205</v>
       </c>
-      <c r="C12" s="155" t="s">
+      <c r="C12" s="156" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="155" t="s">
+      <c r="D12" s="156" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="155" t="s">
+      <c r="E12" s="156" t="s">
         <v>104</v>
       </c>
-      <c r="F12" s="117"/>
-      <c r="G12" s="117"/>
-      <c r="H12" s="121" t="str">
+      <c r="F12" s="127"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="125" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -26487,14 +26491,14 @@
       </c>
     </row>
     <row r="13" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="103"/>
-      <c r="B13" s="131"/>
-      <c r="C13" s="156"/>
-      <c r="D13" s="156"/>
-      <c r="E13" s="156"/>
-      <c r="F13" s="118"/>
-      <c r="G13" s="118"/>
-      <c r="H13" s="122"/>
+      <c r="A13" s="123"/>
+      <c r="B13" s="110"/>
+      <c r="C13" s="155"/>
+      <c r="D13" s="155"/>
+      <c r="E13" s="155"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="126"/>
       <c r="I13" s="27" t="s">
         <v>9</v>
       </c>
@@ -26549,22 +26553,22 @@
       </c>
     </row>
     <row r="14" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="103"/>
-      <c r="B14" s="130">
+      <c r="A14" s="123"/>
+      <c r="B14" s="118">
         <v>46205</v>
       </c>
-      <c r="C14" s="155" t="s">
+      <c r="C14" s="156" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="161" t="s">
+      <c r="D14" s="154" t="s">
         <v>105</v>
       </c>
-      <c r="E14" s="155" t="s">
+      <c r="E14" s="156" t="s">
         <v>106</v>
       </c>
-      <c r="F14" s="117"/>
-      <c r="G14" s="117"/>
-      <c r="H14" s="121" t="str">
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="125" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -26590,14 +26594,14 @@
       </c>
     </row>
     <row r="15" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="103"/>
-      <c r="B15" s="131"/>
-      <c r="C15" s="156"/>
-      <c r="D15" s="156"/>
-      <c r="E15" s="156"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="122"/>
+      <c r="A15" s="123"/>
+      <c r="B15" s="110"/>
+      <c r="C15" s="155"/>
+      <c r="D15" s="155"/>
+      <c r="E15" s="155"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="126"/>
       <c r="I15" s="26" t="s">
         <v>9</v>
       </c>
@@ -26652,22 +26656,22 @@
       </c>
     </row>
     <row r="16" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="103"/>
-      <c r="B16" s="130">
+      <c r="A16" s="123"/>
+      <c r="B16" s="118">
         <v>46204</v>
       </c>
-      <c r="C16" s="155" t="s">
+      <c r="C16" s="156" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="155" t="s">
+      <c r="D16" s="156" t="s">
         <v>107</v>
       </c>
-      <c r="E16" s="155" t="s">
+      <c r="E16" s="156" t="s">
         <v>108</v>
       </c>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="121" t="str">
+      <c r="F16" s="127"/>
+      <c r="G16" s="127"/>
+      <c r="H16" s="125" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -26693,14 +26697,14 @@
       </c>
     </row>
     <row r="17" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="103"/>
-      <c r="B17" s="131"/>
-      <c r="C17" s="156"/>
-      <c r="D17" s="156"/>
-      <c r="E17" s="156"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="122"/>
+      <c r="A17" s="123"/>
+      <c r="B17" s="110"/>
+      <c r="C17" s="155"/>
+      <c r="D17" s="155"/>
+      <c r="E17" s="155"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="102"/>
+      <c r="H17" s="126"/>
       <c r="I17" s="27" t="s">
         <v>9</v>
       </c>
@@ -26755,22 +26759,22 @@
       </c>
     </row>
     <row r="18" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="103"/>
-      <c r="B18" s="130">
+      <c r="A18" s="123"/>
+      <c r="B18" s="118">
         <v>46204</v>
       </c>
-      <c r="C18" s="155" t="s">
+      <c r="C18" s="156" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="155" t="s">
+      <c r="D18" s="156" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="155" t="s">
+      <c r="E18" s="156" t="s">
         <v>110</v>
       </c>
-      <c r="F18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="121" t="str">
+      <c r="F18" s="127"/>
+      <c r="G18" s="127"/>
+      <c r="H18" s="125" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -26796,14 +26800,14 @@
       </c>
     </row>
     <row r="19" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="103"/>
-      <c r="B19" s="131"/>
-      <c r="C19" s="156"/>
-      <c r="D19" s="156"/>
-      <c r="E19" s="156"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="118"/>
-      <c r="H19" s="122"/>
+      <c r="A19" s="123"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="155"/>
+      <c r="D19" s="155"/>
+      <c r="E19" s="155"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="126"/>
       <c r="I19" s="26" t="s">
         <v>9</v>
       </c>
@@ -26858,24 +26862,24 @@
       </c>
     </row>
     <row r="20" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="125" t="s">
+      <c r="A20" s="122" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="132">
+      <c r="B20" s="119">
         <v>46202</v>
       </c>
-      <c r="C20" s="153" t="s">
+      <c r="C20" s="151" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="153" t="s">
+      <c r="D20" s="151" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="159" t="s">
+      <c r="E20" s="157" t="s">
         <v>112</v>
       </c>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="112" t="str">
+      <c r="F20" s="132"/>
+      <c r="G20" s="132"/>
+      <c r="H20" s="136" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -26897,14 +26901,14 @@
       <c r="X20" s="24"/>
     </row>
     <row r="21" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="103"/>
-      <c r="B21" s="133"/>
-      <c r="C21" s="154"/>
-      <c r="D21" s="154"/>
-      <c r="E21" s="160"/>
-      <c r="F21" s="106"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="110"/>
+      <c r="A21" s="123"/>
+      <c r="B21" s="108"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="158"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="100"/>
+      <c r="H21" s="137"/>
       <c r="I21" s="23" t="s">
         <v>9</v>
       </c>
@@ -26955,22 +26959,22 @@
       </c>
     </row>
     <row r="22" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="103"/>
-      <c r="B22" s="132">
+      <c r="A22" s="123"/>
+      <c r="B22" s="119">
         <v>46203</v>
       </c>
-      <c r="C22" s="153" t="s">
+      <c r="C22" s="151" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="153" t="s">
+      <c r="D22" s="151" t="s">
         <v>113</v>
       </c>
-      <c r="E22" s="153" t="s">
+      <c r="E22" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="F22" s="111"/>
-      <c r="G22" s="111"/>
-      <c r="H22" s="112" t="str">
+      <c r="F22" s="132"/>
+      <c r="G22" s="132"/>
+      <c r="H22" s="136" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -26992,14 +26996,14 @@
       <c r="X22" s="25"/>
     </row>
     <row r="23" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="103"/>
-      <c r="B23" s="133"/>
-      <c r="C23" s="154"/>
-      <c r="D23" s="154"/>
-      <c r="E23" s="154"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="110"/>
+      <c r="A23" s="123"/>
+      <c r="B23" s="108"/>
+      <c r="C23" s="152"/>
+      <c r="D23" s="152"/>
+      <c r="E23" s="152"/>
+      <c r="F23" s="100"/>
+      <c r="G23" s="100"/>
+      <c r="H23" s="137"/>
       <c r="I23" s="26" t="s">
         <v>9</v>
       </c>
@@ -27050,22 +27054,22 @@
       </c>
     </row>
     <row r="24" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="103"/>
-      <c r="B24" s="132">
+      <c r="A24" s="123"/>
+      <c r="B24" s="119">
         <v>46203</v>
       </c>
-      <c r="C24" s="153" t="s">
+      <c r="C24" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="D24" s="153" t="s">
+      <c r="D24" s="151" t="s">
         <v>115</v>
       </c>
-      <c r="E24" s="159" t="s">
+      <c r="E24" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="F24" s="111"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="112" t="str">
+      <c r="F24" s="132"/>
+      <c r="G24" s="132"/>
+      <c r="H24" s="136" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -27087,14 +27091,14 @@
       <c r="X24" s="24"/>
     </row>
     <row r="25" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="103"/>
-      <c r="B25" s="133"/>
-      <c r="C25" s="154"/>
-      <c r="D25" s="154"/>
-      <c r="E25" s="160"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="110"/>
+      <c r="A25" s="123"/>
+      <c r="B25" s="108"/>
+      <c r="C25" s="152"/>
+      <c r="D25" s="152"/>
+      <c r="E25" s="158"/>
+      <c r="F25" s="100"/>
+      <c r="G25" s="100"/>
+      <c r="H25" s="137"/>
       <c r="I25" s="23" t="s">
         <v>9</v>
       </c>
@@ -27145,22 +27149,22 @@
       </c>
     </row>
     <row r="26" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="103"/>
-      <c r="B26" s="132">
+      <c r="A26" s="123"/>
+      <c r="B26" s="119">
         <v>46204</v>
       </c>
-      <c r="C26" s="153" t="s">
+      <c r="C26" s="151" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="153" t="s">
+      <c r="D26" s="151" t="s">
         <v>117</v>
       </c>
-      <c r="E26" s="153" t="s">
+      <c r="E26" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="F26" s="111"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="112" t="str">
+      <c r="F26" s="132"/>
+      <c r="G26" s="132"/>
+      <c r="H26" s="136" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -27182,14 +27186,14 @@
       <c r="X26" s="25"/>
     </row>
     <row r="27" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="103"/>
-      <c r="B27" s="133"/>
-      <c r="C27" s="154"/>
-      <c r="D27" s="154"/>
-      <c r="E27" s="154"/>
-      <c r="F27" s="106"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="110"/>
+      <c r="A27" s="123"/>
+      <c r="B27" s="108"/>
+      <c r="C27" s="152"/>
+      <c r="D27" s="152"/>
+      <c r="E27" s="152"/>
+      <c r="F27" s="100"/>
+      <c r="G27" s="100"/>
+      <c r="H27" s="137"/>
       <c r="I27" s="26" t="s">
         <v>9</v>
       </c>
@@ -27240,22 +27244,22 @@
       </c>
     </row>
     <row r="28" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="103"/>
-      <c r="B28" s="130">
+      <c r="A28" s="123"/>
+      <c r="B28" s="118">
         <v>46206</v>
       </c>
-      <c r="C28" s="155" t="s">
+      <c r="C28" s="156" t="s">
         <v>91</v>
       </c>
-      <c r="D28" s="155" t="s">
+      <c r="D28" s="156" t="s">
         <v>119</v>
       </c>
-      <c r="E28" s="155" t="s">
+      <c r="E28" s="156" t="s">
         <v>120</v>
       </c>
-      <c r="F28" s="117"/>
-      <c r="G28" s="117"/>
-      <c r="H28" s="121" t="str">
+      <c r="F28" s="127"/>
+      <c r="G28" s="127"/>
+      <c r="H28" s="125" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -27277,14 +27281,14 @@
       <c r="X28" s="28"/>
     </row>
     <row r="29" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="103"/>
-      <c r="B29" s="131"/>
-      <c r="C29" s="156"/>
-      <c r="D29" s="156"/>
-      <c r="E29" s="156"/>
-      <c r="F29" s="118"/>
-      <c r="G29" s="118"/>
-      <c r="H29" s="122"/>
+      <c r="A29" s="123"/>
+      <c r="B29" s="110"/>
+      <c r="C29" s="155"/>
+      <c r="D29" s="155"/>
+      <c r="E29" s="155"/>
+      <c r="F29" s="102"/>
+      <c r="G29" s="102"/>
+      <c r="H29" s="126"/>
       <c r="I29" s="27" t="s">
         <v>9</v>
       </c>
@@ -27335,22 +27339,22 @@
       </c>
     </row>
     <row r="30" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="103"/>
-      <c r="B30" s="130">
+      <c r="A30" s="123"/>
+      <c r="B30" s="118">
         <v>46206</v>
       </c>
-      <c r="C30" s="155" t="s">
+      <c r="C30" s="156" t="s">
         <v>88</v>
       </c>
-      <c r="D30" s="155" t="s">
+      <c r="D30" s="156" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="157" t="s">
+      <c r="E30" s="159" t="s">
         <v>122</v>
       </c>
-      <c r="F30" s="117"/>
-      <c r="G30" s="117"/>
-      <c r="H30" s="121" t="str">
+      <c r="F30" s="127"/>
+      <c r="G30" s="127"/>
+      <c r="H30" s="125" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -27372,14 +27376,14 @@
       <c r="X30" s="25"/>
     </row>
     <row r="31" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="103"/>
-      <c r="B31" s="131"/>
-      <c r="C31" s="156"/>
-      <c r="D31" s="156"/>
-      <c r="E31" s="158"/>
-      <c r="F31" s="118"/>
-      <c r="G31" s="118"/>
-      <c r="H31" s="122"/>
+      <c r="A31" s="123"/>
+      <c r="B31" s="110"/>
+      <c r="C31" s="155"/>
+      <c r="D31" s="155"/>
+      <c r="E31" s="160"/>
+      <c r="F31" s="102"/>
+      <c r="G31" s="102"/>
+      <c r="H31" s="126"/>
       <c r="I31" s="26" t="s">
         <v>9</v>
       </c>
@@ -27430,22 +27434,22 @@
       </c>
     </row>
     <row r="32" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="103"/>
-      <c r="B32" s="130">
+      <c r="A32" s="123"/>
+      <c r="B32" s="118">
         <v>46205</v>
       </c>
-      <c r="C32" s="155" t="s">
+      <c r="C32" s="156" t="s">
         <v>92</v>
       </c>
-      <c r="D32" s="155" t="s">
+      <c r="D32" s="156" t="s">
         <v>123</v>
       </c>
-      <c r="E32" s="157" t="s">
+      <c r="E32" s="159" t="s">
         <v>124</v>
       </c>
-      <c r="F32" s="117"/>
-      <c r="G32" s="117"/>
-      <c r="H32" s="121" t="str">
+      <c r="F32" s="127"/>
+      <c r="G32" s="127"/>
+      <c r="H32" s="125" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -27467,14 +27471,14 @@
       <c r="X32" s="28"/>
     </row>
     <row r="33" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="103"/>
-      <c r="B33" s="131"/>
-      <c r="C33" s="156"/>
-      <c r="D33" s="156"/>
-      <c r="E33" s="158"/>
-      <c r="F33" s="118"/>
-      <c r="G33" s="118"/>
-      <c r="H33" s="122"/>
+      <c r="A33" s="123"/>
+      <c r="B33" s="110"/>
+      <c r="C33" s="155"/>
+      <c r="D33" s="155"/>
+      <c r="E33" s="160"/>
+      <c r="F33" s="102"/>
+      <c r="G33" s="102"/>
+      <c r="H33" s="126"/>
       <c r="I33" s="27" t="s">
         <v>9</v>
       </c>
@@ -27525,22 +27529,22 @@
       </c>
     </row>
     <row r="34" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="103"/>
-      <c r="B34" s="130">
+      <c r="A34" s="123"/>
+      <c r="B34" s="118">
         <v>46206</v>
       </c>
-      <c r="C34" s="155" t="s">
+      <c r="C34" s="156" t="s">
         <v>93</v>
       </c>
-      <c r="D34" s="155" t="s">
+      <c r="D34" s="156" t="s">
         <v>125</v>
       </c>
-      <c r="E34" s="155" t="s">
+      <c r="E34" s="156" t="s">
         <v>126</v>
       </c>
-      <c r="F34" s="117"/>
-      <c r="G34" s="117"/>
-      <c r="H34" s="121" t="str">
+      <c r="F34" s="127"/>
+      <c r="G34" s="127"/>
+      <c r="H34" s="125" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -27562,14 +27566,14 @@
       <c r="X34" s="25"/>
     </row>
     <row r="35" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="104"/>
-      <c r="B35" s="131"/>
-      <c r="C35" s="156"/>
-      <c r="D35" s="156"/>
-      <c r="E35" s="156"/>
-      <c r="F35" s="118"/>
-      <c r="G35" s="118"/>
-      <c r="H35" s="122"/>
+      <c r="A35" s="124"/>
+      <c r="B35" s="110"/>
+      <c r="C35" s="155"/>
+      <c r="D35" s="155"/>
+      <c r="E35" s="155"/>
+      <c r="F35" s="102"/>
+      <c r="G35" s="102"/>
+      <c r="H35" s="126"/>
       <c r="I35" s="26" t="s">
         <v>9</v>
       </c>
@@ -27620,11 +27624,11 @@
       </c>
     </row>
     <row r="36" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E36" s="151" t="s">
+      <c r="E36" s="161" t="s">
         <v>10</v>
       </c>
-      <c r="F36" s="151"/>
-      <c r="G36" s="151"/>
+      <c r="F36" s="161"/>
+      <c r="G36" s="161"/>
       <c r="H36" s="5">
         <f>SUM(F4:G35)</f>
         <v>0</v>
@@ -27695,12 +27699,12 @@
       </c>
     </row>
     <row r="37" spans="1:24" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E37" s="135" t="s">
+      <c r="E37" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="F37" s="135"/>
-      <c r="G37" s="135"/>
-      <c r="H37" s="135"/>
+      <c r="F37" s="139"/>
+      <c r="G37" s="139"/>
+      <c r="H37" s="139"/>
       <c r="I37" s="31">
         <f t="shared" ref="I37:X37" si="3">SUM(I38:I41)</f>
         <v>100</v>
@@ -28031,22 +28035,22 @@
       </c>
     </row>
     <row r="42" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="152"/>
-      <c r="E42" s="152"/>
-      <c r="F42" s="152"/>
-      <c r="G42" s="152"/>
+      <c r="D42" s="162"/>
+      <c r="E42" s="162"/>
+      <c r="F42" s="162"/>
+      <c r="G42" s="162"/>
     </row>
     <row r="43" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D43" s="152"/>
-      <c r="E43" s="152"/>
-      <c r="F43" s="152"/>
-      <c r="G43" s="152"/>
+      <c r="D43" s="162"/>
+      <c r="E43" s="162"/>
+      <c r="F43" s="162"/>
+      <c r="G43" s="162"/>
     </row>
     <row r="44" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D44" s="152"/>
-      <c r="E44" s="152"/>
-      <c r="F44" s="152"/>
-      <c r="G44" s="152"/>
+      <c r="D44" s="162"/>
+      <c r="E44" s="162"/>
+      <c r="F44" s="162"/>
+      <c r="G44" s="162"/>
     </row>
     <row r="65" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I65" s="3">
@@ -28056,104 +28060,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="g9mYDjDnmTBP3swZeU2s76OH9tuO/a4+BUMDIUn1ivyJ0jYZvhcsp/rKVKq9ZNZoEIYDc9hBW+5pWujIk6K9qg==" saltValue="kOCvHQt7CCHPcHDEC7jJBg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="122">
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C28:C29"/>
     <mergeCell ref="E36:G36"/>
     <mergeCell ref="E37:H37"/>
     <mergeCell ref="D42:G42"/>
@@ -28178,6 +28084,104 @@
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="D30:D31"/>
     <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:X5 I7:X7 I9:X9 I35:X35 I33:X33 I31:X31 I29:X29 I27:X27 I25:X25 I23:X23 I21:X21 I19:X19 I17:X17 I15:X15 I13:X13 I11:X11" xr:uid="{15935602-46AC-4392-BF7C-7DDF6FAA9E44}">
@@ -28214,16 +28218,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
       <c r="I1" s="44">
         <v>1</v>
       </c>
@@ -28258,9 +28262,9 @@
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
       <c r="E2" s="41"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="101"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="146"/>
       <c r="I2" s="45"/>
       <c r="J2" s="35"/>
       <c r="K2" s="36"/>
@@ -28287,10 +28291,10 @@
       <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="162" t="s">
+      <c r="F3" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="G3" s="162"/>
+      <c r="G3" s="153"/>
       <c r="H3" s="16" t="s">
         <v>8</v>
       </c>
@@ -28341,24 +28345,24 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="125" t="s">
+      <c r="A4" s="122" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="132">
+      <c r="B4" s="119">
         <v>46207</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="151" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="153" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="153" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="112" t="str">
+      <c r="D4" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="136" t="str">
         <f>IF(F4="","-",IF(F4&gt;G4,"L",IF(F4=G4,"E",IF(F4&lt;G4,"V"))))</f>
         <v>-</v>
       </c>
@@ -28373,14 +28377,14 @@
       <c r="Q4" s="22"/>
     </row>
     <row r="5" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="103"/>
-      <c r="B5" s="133"/>
-      <c r="C5" s="154"/>
-      <c r="D5" s="154"/>
-      <c r="E5" s="154"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="110"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="152"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="137"/>
       <c r="I5" s="23" t="s">
         <v>9</v>
       </c>
@@ -28416,22 +28420,22 @@
       </c>
     </row>
     <row r="6" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="103"/>
-      <c r="B6" s="132">
+      <c r="A6" s="123"/>
+      <c r="B6" s="119">
         <v>46207</v>
       </c>
-      <c r="C6" s="153" t="s">
+      <c r="C6" s="151" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="153" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="153" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="112" t="str">
+      <c r="D6" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="136" t="str">
         <f t="shared" ref="H6:H18" si="0">IF(F6="","-",IF(F6&gt;G6,"L",IF(F6=G6,"E",IF(F6&lt;G6,"V"))))</f>
         <v>-</v>
       </c>
@@ -28452,14 +28456,14 @@
       </c>
     </row>
     <row r="7" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="103"/>
-      <c r="B7" s="133"/>
-      <c r="C7" s="154"/>
-      <c r="D7" s="154"/>
-      <c r="E7" s="154"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="110"/>
+      <c r="A7" s="123"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="152"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="137"/>
       <c r="I7" s="26" t="s">
         <v>9</v>
       </c>
@@ -28495,22 +28499,22 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="103"/>
-      <c r="B8" s="132">
+      <c r="A8" s="123"/>
+      <c r="B8" s="119">
         <v>46209</v>
       </c>
-      <c r="C8" s="153" t="s">
+      <c r="C8" s="151" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="153" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="153" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="111"/>
-      <c r="G8" s="111"/>
-      <c r="H8" s="112" t="str">
+      <c r="D8" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="132"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="136" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -28529,14 +28533,14 @@
       </c>
     </row>
     <row r="9" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="103"/>
-      <c r="B9" s="133"/>
-      <c r="C9" s="154"/>
-      <c r="D9" s="154"/>
-      <c r="E9" s="154"/>
-      <c r="F9" s="106"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="110"/>
+      <c r="A9" s="123"/>
+      <c r="B9" s="108"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="152"/>
+      <c r="E9" s="152"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="137"/>
       <c r="I9" s="23" t="s">
         <v>9</v>
       </c>
@@ -28570,22 +28574,22 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="103"/>
-      <c r="B10" s="132">
+      <c r="A10" s="123"/>
+      <c r="B10" s="119">
         <v>46209</v>
       </c>
-      <c r="C10" s="153" t="s">
+      <c r="C10" s="151" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="153" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="153" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="111"/>
-      <c r="G10" s="111"/>
-      <c r="H10" s="112" t="str">
+      <c r="D10" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="132"/>
+      <c r="G10" s="132"/>
+      <c r="H10" s="136" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -28604,14 +28608,14 @@
       </c>
     </row>
     <row r="11" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="103"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="154"/>
-      <c r="D11" s="154"/>
-      <c r="E11" s="154"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="110"/>
+      <c r="A11" s="123"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="152"/>
+      <c r="E11" s="152"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="100"/>
+      <c r="H11" s="137"/>
       <c r="I11" s="26" t="s">
         <v>9</v>
       </c>
@@ -28645,24 +28649,24 @@
       </c>
     </row>
     <row r="12" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="125" t="s">
+      <c r="A12" s="122" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="130">
+      <c r="B12" s="118">
         <v>46208</v>
       </c>
-      <c r="C12" s="155" t="s">
+      <c r="C12" s="156" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="155" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="155" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="117"/>
-      <c r="G12" s="117"/>
-      <c r="H12" s="121" t="str">
+      <c r="D12" s="156" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="156" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="127"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="125" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -28677,14 +28681,14 @@
       <c r="Q12" s="28"/>
     </row>
     <row r="13" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="103"/>
-      <c r="B13" s="131"/>
-      <c r="C13" s="156"/>
-      <c r="D13" s="156"/>
-      <c r="E13" s="156"/>
-      <c r="F13" s="118"/>
-      <c r="G13" s="118"/>
-      <c r="H13" s="122"/>
+      <c r="A13" s="123"/>
+      <c r="B13" s="110"/>
+      <c r="C13" s="155"/>
+      <c r="D13" s="155"/>
+      <c r="E13" s="155"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="126"/>
       <c r="I13" s="27" t="s">
         <v>9</v>
       </c>
@@ -28714,22 +28718,22 @@
       </c>
     </row>
     <row r="14" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="103"/>
-      <c r="B14" s="130">
+      <c r="A14" s="123"/>
+      <c r="B14" s="118">
         <v>46208</v>
       </c>
-      <c r="C14" s="155" t="s">
+      <c r="C14" s="156" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="155" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="157" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="117"/>
-      <c r="G14" s="117"/>
-      <c r="H14" s="121" t="str">
+      <c r="D14" s="156" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="159" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="125" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -28744,14 +28748,14 @@
       <c r="Q14" s="25"/>
     </row>
     <row r="15" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="103"/>
-      <c r="B15" s="131"/>
-      <c r="C15" s="156"/>
-      <c r="D15" s="156"/>
-      <c r="E15" s="158"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="122"/>
+      <c r="A15" s="123"/>
+      <c r="B15" s="110"/>
+      <c r="C15" s="155"/>
+      <c r="D15" s="155"/>
+      <c r="E15" s="160"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="126"/>
       <c r="I15" s="26" t="s">
         <v>9</v>
       </c>
@@ -28781,22 +28785,22 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="103"/>
-      <c r="B16" s="130">
+      <c r="A16" s="123"/>
+      <c r="B16" s="118">
         <v>46210</v>
       </c>
-      <c r="C16" s="155" t="s">
+      <c r="C16" s="156" t="s">
         <v>90</v>
       </c>
-      <c r="D16" s="155" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="157" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="121" t="str">
+      <c r="D16" s="156" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="159" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="127"/>
+      <c r="G16" s="127"/>
+      <c r="H16" s="125" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -28811,14 +28815,14 @@
       <c r="Q16" s="28"/>
     </row>
     <row r="17" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="103"/>
-      <c r="B17" s="131"/>
-      <c r="C17" s="156"/>
-      <c r="D17" s="156"/>
-      <c r="E17" s="158"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="122"/>
+      <c r="A17" s="123"/>
+      <c r="B17" s="110"/>
+      <c r="C17" s="155"/>
+      <c r="D17" s="155"/>
+      <c r="E17" s="160"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="102"/>
+      <c r="H17" s="126"/>
       <c r="I17" s="27" t="s">
         <v>9</v>
       </c>
@@ -28848,22 +28852,22 @@
       </c>
     </row>
     <row r="18" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="103"/>
-      <c r="B18" s="130">
+      <c r="A18" s="123"/>
+      <c r="B18" s="118">
         <v>46210</v>
       </c>
-      <c r="C18" s="155" t="s">
+      <c r="C18" s="156" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="155" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="155" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="121" t="str">
+      <c r="D18" s="156" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="156" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="127"/>
+      <c r="G18" s="127"/>
+      <c r="H18" s="125" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
@@ -28878,14 +28882,14 @@
       <c r="Q18" s="25"/>
     </row>
     <row r="19" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="104"/>
-      <c r="B19" s="131"/>
-      <c r="C19" s="156"/>
-      <c r="D19" s="156"/>
-      <c r="E19" s="156"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="118"/>
-      <c r="H19" s="122"/>
+      <c r="A19" s="124"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="155"/>
+      <c r="D19" s="155"/>
+      <c r="E19" s="155"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="126"/>
       <c r="I19" s="26" t="s">
         <v>9</v>
       </c>
@@ -28915,11 +28919,11 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E20" s="151" t="s">
+      <c r="E20" s="161" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="151"/>
-      <c r="G20" s="151"/>
+      <c r="F20" s="161"/>
+      <c r="G20" s="161"/>
       <c r="H20" s="5">
         <f>SUM(F4:G19)</f>
         <v>0</v>
@@ -28962,12 +28966,12 @@
       </c>
     </row>
     <row r="21" spans="1:17" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E21" s="135" t="s">
+      <c r="E21" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="135"/>
-      <c r="G21" s="135"/>
-      <c r="H21" s="135"/>
+      <c r="F21" s="139"/>
+      <c r="G21" s="139"/>
+      <c r="H21" s="139"/>
       <c r="I21" s="31" t="e">
         <f t="shared" ref="I21:Q21" si="1">SUM(I22:I25)</f>
         <v>#REF!</v>
@@ -29158,22 +29162,22 @@
       </c>
     </row>
     <row r="26" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D26" s="152"/>
-      <c r="E26" s="152"/>
-      <c r="F26" s="152"/>
-      <c r="G26" s="152"/>
+      <c r="D26" s="162"/>
+      <c r="E26" s="162"/>
+      <c r="F26" s="162"/>
+      <c r="G26" s="162"/>
     </row>
     <row r="27" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D27" s="152"/>
-      <c r="E27" s="152"/>
-      <c r="F27" s="152"/>
-      <c r="G27" s="152"/>
+      <c r="D27" s="162"/>
+      <c r="E27" s="162"/>
+      <c r="F27" s="162"/>
+      <c r="G27" s="162"/>
     </row>
     <row r="28" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D28" s="152"/>
-      <c r="E28" s="152"/>
-      <c r="F28" s="152"/>
-      <c r="G28" s="152"/>
+      <c r="D28" s="162"/>
+      <c r="E28" s="162"/>
+      <c r="F28" s="162"/>
+      <c r="G28" s="162"/>
     </row>
     <row r="49" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I49" s="3">
@@ -29183,6 +29187,56 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="sl3hmfUsP/0AEGdKnHzML/fRKVmeGjpDx1lfIugg/uB+UULGPZmfjV4NtTq5UJrqjztYnMlJzv/6FsEOA+H16g==" saltValue="0vDxLtjmVc4hjWW1RQJDzw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="66">
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A12:A19"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="F3:G3"/>
@@ -29199,56 +29253,6 @@
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A12:A19"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="D28:G28"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I6:Q6 I8:Q8 I10:Q10 I12:Q12 I14:Q14 I16:Q16 I18:Q18 I4:Q4" xr:uid="{794EB591-2727-4BCF-9E9E-A16E63499017}">
@@ -29285,16 +29289,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
       <c r="I1" s="44">
         <v>1</v>
       </c>
@@ -29320,9 +29324,9 @@
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
       <c r="E2" s="41"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="101"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="146"/>
       <c r="I2" s="45"/>
       <c r="J2" s="35"/>
       <c r="K2" s="36"/>
@@ -29346,10 +29350,10 @@
       <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="162" t="s">
+      <c r="F3" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="G3" s="162"/>
+      <c r="G3" s="153"/>
       <c r="H3" s="16" t="s">
         <v>8</v>
       </c>
@@ -29379,24 +29383,24 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="125" t="s">
+      <c r="A4" s="122" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="132">
+      <c r="B4" s="119">
         <v>46212</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="151" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="153" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="153" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="112" t="str">
+      <c r="D4" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="136" t="str">
         <f>IF(F4="","-",IF(F4&gt;G4,"L",IF(F4=G4,"E",IF(F4&lt;G4,"V"))))</f>
         <v>-</v>
       </c>
@@ -29408,14 +29412,14 @@
       <c r="N4" s="22"/>
     </row>
     <row r="5" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="103"/>
-      <c r="B5" s="133"/>
-      <c r="C5" s="154"/>
-      <c r="D5" s="154"/>
-      <c r="E5" s="154"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="110"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="152"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="137"/>
       <c r="I5" s="23" t="s">
         <v>9</v>
       </c>
@@ -29442,22 +29446,22 @@
       </c>
     </row>
     <row r="6" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="103"/>
-      <c r="B6" s="132">
+      <c r="A6" s="123"/>
+      <c r="B6" s="119">
         <v>46213</v>
       </c>
-      <c r="C6" s="153" t="s">
+      <c r="C6" s="151" t="s">
         <v>82</v>
       </c>
-      <c r="D6" s="153" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="153" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="112" t="str">
+      <c r="D6" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="136" t="str">
         <f t="shared" ref="H6:H10" si="1">IF(F6="","-",IF(F6&gt;G6,"L",IF(F6=G6,"E",IF(F6&lt;G6,"V"))))</f>
         <v>-</v>
       </c>
@@ -29475,14 +29479,14 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="103"/>
-      <c r="B7" s="133"/>
-      <c r="C7" s="154"/>
-      <c r="D7" s="154"/>
-      <c r="E7" s="154"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="110"/>
+      <c r="A7" s="123"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="152"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="137"/>
       <c r="I7" s="26" t="s">
         <v>9</v>
       </c>
@@ -29509,24 +29513,24 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="125" t="s">
+      <c r="A8" s="122" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="130">
+      <c r="B8" s="118">
         <v>46214</v>
       </c>
-      <c r="C8" s="155" t="s">
+      <c r="C8" s="156" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="155" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="155" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="117"/>
-      <c r="G8" s="117"/>
-      <c r="H8" s="121" t="str">
+      <c r="D8" s="156" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="156" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="127"/>
+      <c r="G8" s="127"/>
+      <c r="H8" s="125" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -29538,14 +29542,14 @@
       <c r="N8" s="28"/>
     </row>
     <row r="9" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="103"/>
-      <c r="B9" s="131"/>
-      <c r="C9" s="156"/>
-      <c r="D9" s="156"/>
-      <c r="E9" s="156"/>
-      <c r="F9" s="118"/>
-      <c r="G9" s="118"/>
-      <c r="H9" s="122"/>
+      <c r="A9" s="123"/>
+      <c r="B9" s="110"/>
+      <c r="C9" s="155"/>
+      <c r="D9" s="155"/>
+      <c r="E9" s="155"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="102"/>
+      <c r="H9" s="126"/>
       <c r="I9" s="27" t="s">
         <v>9</v>
       </c>
@@ -29566,22 +29570,22 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="103"/>
-      <c r="B10" s="130">
+      <c r="A10" s="123"/>
+      <c r="B10" s="118">
         <v>46214</v>
       </c>
-      <c r="C10" s="155" t="s">
+      <c r="C10" s="156" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="155" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="157" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="117"/>
-      <c r="G10" s="117"/>
-      <c r="H10" s="121" t="str">
+      <c r="D10" s="156" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="159" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="127"/>
+      <c r="G10" s="127"/>
+      <c r="H10" s="125" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -29593,14 +29597,14 @@
       <c r="N10" s="25"/>
     </row>
     <row r="11" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="104"/>
-      <c r="B11" s="131"/>
-      <c r="C11" s="156"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="158"/>
-      <c r="F11" s="118"/>
-      <c r="G11" s="118"/>
-      <c r="H11" s="122"/>
+      <c r="A11" s="124"/>
+      <c r="B11" s="110"/>
+      <c r="C11" s="155"/>
+      <c r="D11" s="155"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="126"/>
       <c r="I11" s="26" t="s">
         <v>9</v>
       </c>
@@ -29621,11 +29625,11 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E12" s="151" t="s">
+      <c r="E12" s="161" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="151"/>
-      <c r="G12" s="151"/>
+      <c r="F12" s="161"/>
+      <c r="G12" s="161"/>
       <c r="H12" s="5">
         <f>SUM(F4:G11)</f>
         <v>0</v>
@@ -29656,12 +29660,12 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E13" s="135" t="s">
+      <c r="E13" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="135"/>
-      <c r="G13" s="135"/>
-      <c r="H13" s="135"/>
+      <c r="F13" s="139"/>
+      <c r="G13" s="139"/>
+      <c r="H13" s="139"/>
       <c r="I13" s="31">
         <f t="shared" ref="I13:N13" si="3">SUM(I14:I17)</f>
         <v>100</v>
@@ -29792,22 +29796,22 @@
       </c>
     </row>
     <row r="18" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D18" s="152"/>
-      <c r="E18" s="152"/>
-      <c r="F18" s="152"/>
-      <c r="G18" s="152"/>
+      <c r="D18" s="162"/>
+      <c r="E18" s="162"/>
+      <c r="F18" s="162"/>
+      <c r="G18" s="162"/>
     </row>
     <row r="19" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D19" s="152"/>
-      <c r="E19" s="152"/>
-      <c r="F19" s="152"/>
-      <c r="G19" s="152"/>
+      <c r="D19" s="162"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="162"/>
+      <c r="G19" s="162"/>
     </row>
     <row r="20" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D20" s="152"/>
-      <c r="E20" s="152"/>
-      <c r="F20" s="152"/>
-      <c r="G20" s="152"/>
+      <c r="D20" s="162"/>
+      <c r="E20" s="162"/>
+      <c r="F20" s="162"/>
+      <c r="G20" s="162"/>
     </row>
     <row r="41" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I41" s="3">
@@ -29817,6 +29821,28 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="jDy+TaaBus/YLoP0DGJXAnoaRJcFT+Oo6OOpILcNCb6W3EZSLBOg/eSnJOd8WYIYjy08krdRsxEJosK80+KEiw==" saltValue="Mo2geWJ/Nb+toLk/aMnOlQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="38">
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="F3:G3"/>
@@ -29833,28 +29859,6 @@
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D19:G19"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:N5 I11:N11 I7:N7 I9:N9" xr:uid="{94B81B5B-5F71-4D3E-9072-59EC7004E880}">
@@ -29891,16 +29895,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
       <c r="I1" s="44">
         <v>1</v>
       </c>
@@ -29920,9 +29924,9 @@
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
       <c r="E2" s="41"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="101"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="146"/>
       <c r="I2" s="45"/>
       <c r="J2" s="42"/>
       <c r="K2" s="38"/>
@@ -29944,10 +29948,10 @@
       <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="162" t="s">
+      <c r="F3" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="G3" s="162"/>
+      <c r="G3" s="153"/>
       <c r="H3" s="16" t="s">
         <v>8</v>
       </c>
@@ -29969,24 +29973,24 @@
       </c>
     </row>
     <row r="4" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="125" t="s">
+      <c r="A4" s="122" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="132">
+      <c r="B4" s="119">
         <v>46217</v>
       </c>
-      <c r="C4" s="153" t="s">
+      <c r="C4" s="151" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="153" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="153" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="112" t="str">
+      <c r="D4" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="136" t="str">
         <f>IF(F4="","-",IF(F4&gt;G4,"L",IF(F4=G4,"E",IF(F4&lt;G4,"V"))))</f>
         <v>-</v>
       </c>
@@ -29996,14 +30000,14 @@
       <c r="L4" s="22"/>
     </row>
     <row r="5" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="103"/>
-      <c r="B5" s="133"/>
-      <c r="C5" s="154"/>
-      <c r="D5" s="154"/>
-      <c r="E5" s="154"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="110"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="152"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="137"/>
       <c r="I5" s="23" t="s">
         <v>9</v>
       </c>
@@ -30024,22 +30028,22 @@
       </c>
     </row>
     <row r="6" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="103"/>
-      <c r="B6" s="132">
+      <c r="A6" s="123"/>
+      <c r="B6" s="119">
         <v>46218</v>
       </c>
-      <c r="C6" s="153" t="s">
+      <c r="C6" s="151" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="153" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="153" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="112" t="str">
+      <c r="D6" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="136" t="str">
         <f t="shared" ref="H6:H10" si="1">IF(F6="","-",IF(F6&gt;G6,"L",IF(F6=G6,"E",IF(F6&lt;G6,"V"))))</f>
         <v>-</v>
       </c>
@@ -30055,14 +30059,14 @@
       </c>
     </row>
     <row r="7" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="103"/>
-      <c r="B7" s="133"/>
-      <c r="C7" s="154"/>
-      <c r="D7" s="154"/>
-      <c r="E7" s="154"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="110"/>
+      <c r="A7" s="123"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="152"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="137"/>
       <c r="I7" s="26" t="s">
         <v>9</v>
       </c>
@@ -30086,21 +30090,21 @@
       <c r="A8" s="163" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="130">
+      <c r="B8" s="118">
         <v>46221</v>
       </c>
-      <c r="C8" s="155" t="s">
+      <c r="C8" s="156" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="155" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="155" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="117"/>
-      <c r="G8" s="117"/>
-      <c r="H8" s="121" t="str">
+      <c r="D8" s="156" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="156" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="127"/>
+      <c r="G8" s="127"/>
+      <c r="H8" s="125" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -30111,13 +30115,13 @@
     </row>
     <row r="9" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="163"/>
-      <c r="B9" s="131"/>
-      <c r="C9" s="156"/>
-      <c r="D9" s="156"/>
-      <c r="E9" s="156"/>
-      <c r="F9" s="118"/>
-      <c r="G9" s="118"/>
-      <c r="H9" s="122"/>
+      <c r="B9" s="110"/>
+      <c r="C9" s="155"/>
+      <c r="D9" s="155"/>
+      <c r="E9" s="155"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="102"/>
+      <c r="H9" s="126"/>
       <c r="I9" s="27" t="s">
         <v>9</v>
       </c>
@@ -30135,21 +30139,21 @@
       <c r="A10" s="163" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="130">
+      <c r="B10" s="118">
         <v>46222</v>
       </c>
-      <c r="C10" s="155" t="s">
+      <c r="C10" s="156" t="s">
         <v>81</v>
       </c>
-      <c r="D10" s="155" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="157" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="117"/>
-      <c r="G10" s="117"/>
-      <c r="H10" s="121" t="str">
+      <c r="D10" s="156" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="159" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="127"/>
+      <c r="G10" s="127"/>
+      <c r="H10" s="125" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
@@ -30160,13 +30164,13 @@
     </row>
     <row r="11" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="163"/>
-      <c r="B11" s="131"/>
-      <c r="C11" s="156"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="158"/>
-      <c r="F11" s="118"/>
-      <c r="G11" s="118"/>
-      <c r="H11" s="122"/>
+      <c r="B11" s="110"/>
+      <c r="C11" s="155"/>
+      <c r="D11" s="155"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="126"/>
       <c r="I11" s="26" t="s">
         <v>9</v>
       </c>
@@ -30181,11 +30185,11 @@
       </c>
     </row>
     <row r="12" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E12" s="151" t="s">
+      <c r="E12" s="161" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="151"/>
-      <c r="G12" s="151"/>
+      <c r="F12" s="161"/>
+      <c r="G12" s="161"/>
       <c r="H12" s="5">
         <f>SUM(F4:G11)</f>
         <v>0</v>
@@ -30208,12 +30212,12 @@
       </c>
     </row>
     <row r="13" spans="1:20" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E13" s="135" t="s">
+      <c r="E13" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="135"/>
-      <c r="G13" s="135"/>
-      <c r="H13" s="135"/>
+      <c r="F13" s="139"/>
+      <c r="G13" s="139"/>
+      <c r="H13" s="139"/>
       <c r="I13" s="31">
         <f t="shared" ref="I13:L13" si="3">SUM(I14:I17)</f>
         <v>100</v>
@@ -30304,22 +30308,22 @@
       </c>
     </row>
     <row r="18" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D18" s="152"/>
-      <c r="E18" s="152"/>
-      <c r="F18" s="152"/>
-      <c r="G18" s="152"/>
+      <c r="D18" s="162"/>
+      <c r="E18" s="162"/>
+      <c r="F18" s="162"/>
+      <c r="G18" s="162"/>
     </row>
     <row r="19" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D19" s="152"/>
-      <c r="E19" s="152"/>
-      <c r="F19" s="152"/>
-      <c r="G19" s="152"/>
+      <c r="D19" s="162"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="162"/>
+      <c r="G19" s="162"/>
     </row>
     <row r="20" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D20" s="152"/>
-      <c r="E20" s="152"/>
-      <c r="F20" s="152"/>
-      <c r="G20" s="152"/>
+      <c r="D20" s="162"/>
+      <c r="E20" s="162"/>
+      <c r="F20" s="162"/>
+      <c r="G20" s="162"/>
     </row>
     <row r="41" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I41" s="3">
@@ -30329,6 +30333,29 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="/MtXfXly9R3REBvntxKIZCD91y4iUcT9D4ILujy83mCENsUO31lAw/oxWtxDAESQFa94XZmCo+1hXgm3XCxfag==" saltValue="RySVb+JvM8dpz69XIc5rYQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="39">
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="F3:G3"/>
@@ -30345,29 +30372,6 @@
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="D18:G18"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:L4 I6:L6 I8:L8 I10:L10" xr:uid="{D1202CE7-020E-413B-9703-A70D7B5DC815}">

--- a/Copa del Mundo-2026 trabajo.xlsx
+++ b/Copa del Mundo-2026 trabajo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_corporativa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{4B119FBF-818B-466F-B1F3-AB97609A7929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{230577A8-1D12-4C70-8D16-0D71A4B600D2}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{4B119FBF-818B-466F-B1F3-AB97609A7929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2555CCC-C352-404C-B424-69368D489B17}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA 2026" sheetId="3" r:id="rId1"/>
@@ -2485,45 +2485,45 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:BB181"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="20.6640625" style="56" customWidth="1"/>
-    <col min="7" max="8" width="6.109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.44140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="4.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="7.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.33203125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.33203125" style="2" customWidth="1"/>
-    <col min="25" max="27" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.33203125" style="2" customWidth="1"/>
-    <col min="29" max="31" width="4.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="5.33203125" style="2" customWidth="1"/>
-    <col min="35" max="35" width="4.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="5.33203125" style="2" customWidth="1"/>
-    <col min="39" max="40" width="4.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="4.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="4.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="47" max="52" width="11.44140625" style="2"/>
-    <col min="53" max="54" width="11.44140625" style="2" customWidth="1"/>
-    <col min="55" max="16384" width="11.44140625" style="2"/>
+    <col min="1" max="1" width="8.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" style="56" customWidth="1"/>
+    <col min="7" max="8" width="6.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.28515625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.28515625" style="2" customWidth="1"/>
+    <col min="25" max="27" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.28515625" style="2" customWidth="1"/>
+    <col min="29" max="31" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="5.28515625" style="2" customWidth="1"/>
+    <col min="35" max="35" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="5.28515625" style="2" customWidth="1"/>
+    <col min="39" max="40" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="47" max="52" width="11.42578125" style="2"/>
+    <col min="53" max="54" width="11.42578125" style="2" customWidth="1"/>
+    <col min="55" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:54" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="99" t="s">
         <v>28</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:54" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -2771,7 +2771,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:54" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
         <v>0</v>
       </c>
@@ -2798,155 +2798,155 @@
         <v>8</v>
       </c>
       <c r="J3" s="67">
-        <f>SUM(J4+J5)-SUM(J6+J7)</f>
+        <f t="shared" ref="J3:AT3" si="0">SUM(J4+J5)-SUM(J6+J7)</f>
         <v>37</v>
       </c>
       <c r="K3" s="68">
-        <f>SUM(K4+K5)-SUM(K6+K7)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="L3" s="68">
-        <f>SUM(L4+L5)-SUM(L6+L7)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="M3" s="68">
-        <f>SUM(M4+M5)-SUM(M6+M7)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="N3" s="68">
-        <f>SUM(N4+N5)-SUM(N6+N7)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="O3" s="68">
-        <f>SUM(O4+O5)-SUM(O6+O7)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="P3" s="68">
-        <f>SUM(P4+P5)-SUM(P6+P7)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="Q3" s="68">
-        <f>SUM(Q4+Q5)-SUM(Q6+Q7)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="R3" s="68">
-        <f>SUM(R4+R5)-SUM(R6+R7)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="S3" s="68">
-        <f>SUM(S4+S5)-SUM(S6+S7)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="T3" s="68">
-        <f>SUM(T4+T5)-SUM(T6+T7)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="U3" s="68">
-        <f>SUM(U4+U5)-SUM(U6+U7)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="V3" s="68">
-        <f>SUM(V4+V5)-SUM(V6+V7)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="W3" s="68">
-        <f>SUM(W4+W5)-SUM(W6+W7)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="X3" s="68">
-        <f>SUM(X4+X5)-SUM(X6+X7)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="Y3" s="68">
-        <f>SUM(Y4+Y5)-SUM(Y6+Y7)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="Z3" s="68">
-        <f>SUM(Z4+Z5)-SUM(Z6+Z7)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="AA3" s="68">
-        <f>SUM(AA4+AA5)-SUM(AA6+AA7)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="AB3" s="68">
-        <f>SUM(AB4+AB5)-SUM(AB6+AB7)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="AC3" s="68">
-        <f>SUM(AC4+AC5)-SUM(AC6+AC7)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="AD3" s="68">
-        <f>SUM(AD4+AD5)-SUM(AD6+AD7)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="AE3" s="68">
-        <f>SUM(AE4+AE5)-SUM(AE6+AE7)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="AF3" s="68">
-        <f>SUM(AF4+AF5)-SUM(AF6+AF7)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="AG3" s="68">
-        <f>SUM(AG4+AG5)-SUM(AG6+AG7)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="AH3" s="68">
-        <f>SUM(AH4+AH5)-SUM(AH6+AH7)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="AI3" s="68">
-        <f>SUM(AI4+AI5)-SUM(AI6+AI7)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="AJ3" s="68">
-        <f>SUM(AJ4+AJ5)-SUM(AJ6+AJ7)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="AK3" s="68">
-        <f>SUM(AK4+AK5)-SUM(AK6+AK7)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="AL3" s="68">
-        <f>SUM(AL4+AL5)-SUM(AL6+AL7)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="AM3" s="68">
-        <f>SUM(AM4+AM5)-SUM(AM6+AM7)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="AN3" s="68">
-        <f>SUM(AN4+AN5)-SUM(AN6+AN7)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="AO3" s="68">
-        <f>SUM(AO4+AO5)-SUM(AO6+AO7)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="AP3" s="68">
-        <f>SUM(AP4+AP5)-SUM(AP6+AP7)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="AQ3" s="68">
-        <f>SUM(AQ4+AQ5)-SUM(AQ6+AQ7)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="AR3" s="68">
-        <f>SUM(AR4+AR5)-SUM(AR6+AR7)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="AS3" s="68">
-        <f>SUM(AS4+AS5)-SUM(AS6+AS7)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="AT3" s="69">
-        <f>SUM(AT4+AT5)-SUM(AT6+AT7)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:54" ht="14.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:54" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="61"/>
       <c r="B4" s="61"/>
       <c r="C4" s="61"/>
@@ -2957,192 +2957,156 @@
       <c r="H4" s="62"/>
       <c r="I4" s="63"/>
       <c r="J4" s="72">
-        <f>SUM(IF(J8=$I$8,3,0)+IF(J9=$G8+$H8,1,0)+IF(J10=$I$10,3,0)+IF(J11=$G10+$H10,1,0)+IF(J12=$I$12,3,0)+IF(J13=$G12+$H12,1,0)+IF(J14=$I$14,3,0)+IF(J15=$G14+$H14,1,0)
+        <f t="shared" ref="J4:AT4" si="1">SUM(IF(J8=$I$8,3,0)+IF(J9=$G8+$H8,1,0)+IF(J10=$I$10,3,0)+IF(J11=$G10+$H10,1,0)+IF(J12=$I$12,3,0)+IF(J13=$G12+$H12,1,0)+IF(J14=$I$14,3,0)+IF(J15=$G14+$H14,1,0)
 +IF(J16=$I$16,3,0)+IF(J17=$G16+$H16,1,0)+IF(J18=$I$18,3,0)+IF(J19=$G18+$H18,1,0)+IF(J20=$I$20,3,0)+IF(J21=$G20+$H20,1,0)+IF(J22=$I$22,3,0)+IF(J23=$G22+$H22,1,0)+IF(J24=$I$24,3,0)+IF(J25=$G24+$H24,1,0)+IF(J26=$I$26,3,0)+IF(J27=$G26+$H26,1,0)+IF(J28=$I$28,3,0)+IF(J29=$G28+$H28,1,0)+IF(J30=$I$30,3,0)+IF(J31=$G30+$H30,1,0)+IF(J32=$I$32,3,0)+IF(J33=$G32+$H32,1,0)+IF(J34=$I$34,3,0)+IF(J35=$G34+$H34,1,0)+IF(J36=$I$36,3,0)+IF(J37=$G36+$H36,1,0)+IF(J38=$I$38,3,0)+IF(J39=$G38+$H38,1,0)+IF(J40=$I$40,3,0)+IF(J41=$G40+$H40,1,0)+IF(J42=$I$42,3,0)+IF(J43=$G42+$H42,1,0)+IF(J44=$I$44,3,0)+IF(J45=$G44+$H44,1,0)+IF(J46=$I$46,3,0)+IF(J47=$G46+$H46,1,0)+IF(J48=$I$48,3,0)+IF(J49=$G48+$H48,1,0)+IF(J50=$I$50,3,0)+IF(J51=$G50+$H50,1,0)+IF(J52=$I$52,3,0)+IF(J53=$G52+$H52,1,0)+IF(J54=$I$54,3,0)+IF(J55=$G54+$H54,1,0)+IF(J56=$I$56,3,0)+IF(J57=$G56+$H56,1,0)+IF(J58=$I$58,3,0)+IF(J59=$G58+$H58,1,0)+IF(J60=$I$60,3,0)+IF(J61=$G60+$H60,1,0)+IF(J62=$I$62,3,0)+IF(J63=$G62+$H62,1,0)+IF(J64=$I$64,3,0)+IF(J65=$G64+$H64,1,0)+IF(J66=$I$66,3,0)+IF(J67=$G66+$H66,1,0)+IF(J68=$I$68,3,0)+IF(J69=$G68+$H68,1,0)+IF(J70=$I$70,3,0)+IF(J71=$G70+$H70,1,0)+IF(J72=$I$72,3,0)+IF(J73=$G72+$H72,1,0)+IF(J74=$I$74,3,0)+IF(J75=$G74+$H74,1,0)+IF(J76=$I$76,3,0)+IF(J77=$G76+$H76,1,0)+IF(J78=$I$78,3,0)+IF(J79=$G78+$H78,1,0))</f>
         <v>39</v>
       </c>
       <c r="K4" s="73">
-        <f>SUM(IF(K8=$I$8,3,0)+IF(K9=$G8+$H8,1,0)+IF(K10=$I$10,3,0)+IF(K11=$G10+$H10,1,0)+IF(K12=$I$12,3,0)+IF(K13=$G12+$H12,1,0)+IF(K14=$I$14,3,0)+IF(K15=$G14+$H14,1,0)
-+IF(K16=$I$16,3,0)+IF(K17=$G16+$H16,1,0)+IF(K18=$I$18,3,0)+IF(K19=$G18+$H18,1,0)+IF(K20=$I$20,3,0)+IF(K21=$G20+$H20,1,0)+IF(K22=$I$22,3,0)+IF(K23=$G22+$H22,1,0)+IF(K24=$I$24,3,0)+IF(K25=$G24+$H24,1,0)+IF(K26=$I$26,3,0)+IF(K27=$G26+$H26,1,0)+IF(K28=$I$28,3,0)+IF(K29=$G28+$H28,1,0)+IF(K30=$I$30,3,0)+IF(K31=$G30+$H30,1,0)+IF(K32=$I$32,3,0)+IF(K33=$G32+$H32,1,0)+IF(K34=$I$34,3,0)+IF(K35=$G34+$H34,1,0)+IF(K36=$I$36,3,0)+IF(K37=$G36+$H36,1,0)+IF(K38=$I$38,3,0)+IF(K39=$G38+$H38,1,0)+IF(K40=$I$40,3,0)+IF(K41=$G40+$H40,1,0)+IF(K42=$I$42,3,0)+IF(K43=$G42+$H42,1,0)+IF(K44=$I$44,3,0)+IF(K45=$G44+$H44,1,0)+IF(K46=$I$46,3,0)+IF(K47=$G46+$H46,1,0)+IF(K48=$I$48,3,0)+IF(K49=$G48+$H48,1,0)+IF(K50=$I$50,3,0)+IF(K51=$G50+$H50,1,0)+IF(K52=$I$52,3,0)+IF(K53=$G52+$H52,1,0)+IF(K54=$I$54,3,0)+IF(K55=$G54+$H54,1,0)+IF(K56=$I$56,3,0)+IF(K57=$G56+$H56,1,0)+IF(K58=$I$58,3,0)+IF(K59=$G58+$H58,1,0)+IF(K60=$I$60,3,0)+IF(K61=$G60+$H60,1,0)+IF(K62=$I$62,3,0)+IF(K63=$G62+$H62,1,0)+IF(K64=$I$64,3,0)+IF(K65=$G64+$H64,1,0)+IF(K66=$I$66,3,0)+IF(K67=$G66+$H66,1,0)+IF(K68=$I$68,3,0)+IF(K69=$G68+$H68,1,0)+IF(K70=$I$70,3,0)+IF(K71=$G70+$H70,1,0)+IF(K72=$I$72,3,0)+IF(K73=$G72+$H72,1,0)+IF(K74=$I$74,3,0)+IF(K75=$G74+$H74,1,0)+IF(K76=$I$76,3,0)+IF(K77=$G76+$H76,1,0)+IF(K78=$I$78,3,0)+IF(K79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="L4" s="73">
-        <f>SUM(IF(L8=$I$8,3,0)+IF(L9=$G8+$H8,1,0)+IF(L10=$I$10,3,0)+IF(L11=$G10+$H10,1,0)+IF(L12=$I$12,3,0)+IF(L13=$G12+$H12,1,0)+IF(L14=$I$14,3,0)+IF(L15=$G14+$H14,1,0)
-+IF(L16=$I$16,3,0)+IF(L17=$G16+$H16,1,0)+IF(L18=$I$18,3,0)+IF(L19=$G18+$H18,1,0)+IF(L20=$I$20,3,0)+IF(L21=$G20+$H20,1,0)+IF(L22=$I$22,3,0)+IF(L23=$G22+$H22,1,0)+IF(L24=$I$24,3,0)+IF(L25=$G24+$H24,1,0)+IF(L26=$I$26,3,0)+IF(L27=$G26+$H26,1,0)+IF(L28=$I$28,3,0)+IF(L29=$G28+$H28,1,0)+IF(L30=$I$30,3,0)+IF(L31=$G30+$H30,1,0)+IF(L32=$I$32,3,0)+IF(L33=$G32+$H32,1,0)+IF(L34=$I$34,3,0)+IF(L35=$G34+$H34,1,0)+IF(L36=$I$36,3,0)+IF(L37=$G36+$H36,1,0)+IF(L38=$I$38,3,0)+IF(L39=$G38+$H38,1,0)+IF(L40=$I$40,3,0)+IF(L41=$G40+$H40,1,0)+IF(L42=$I$42,3,0)+IF(L43=$G42+$H42,1,0)+IF(L44=$I$44,3,0)+IF(L45=$G44+$H44,1,0)+IF(L46=$I$46,3,0)+IF(L47=$G46+$H46,1,0)+IF(L48=$I$48,3,0)+IF(L49=$G48+$H48,1,0)+IF(L50=$I$50,3,0)+IF(L51=$G50+$H50,1,0)+IF(L52=$I$52,3,0)+IF(L53=$G52+$H52,1,0)+IF(L54=$I$54,3,0)+IF(L55=$G54+$H54,1,0)+IF(L56=$I$56,3,0)+IF(L57=$G56+$H56,1,0)+IF(L58=$I$58,3,0)+IF(L59=$G58+$H58,1,0)+IF(L60=$I$60,3,0)+IF(L61=$G60+$H60,1,0)+IF(L62=$I$62,3,0)+IF(L63=$G62+$H62,1,0)+IF(L64=$I$64,3,0)+IF(L65=$G64+$H64,1,0)+IF(L66=$I$66,3,0)+IF(L67=$G66+$H66,1,0)+IF(L68=$I$68,3,0)+IF(L69=$G68+$H68,1,0)+IF(L70=$I$70,3,0)+IF(L71=$G70+$H70,1,0)+IF(L72=$I$72,3,0)+IF(L73=$G72+$H72,1,0)+IF(L74=$I$74,3,0)+IF(L75=$G74+$H74,1,0)+IF(L76=$I$76,3,0)+IF(L77=$G76+$H76,1,0)+IF(L78=$I$78,3,0)+IF(L79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="M4" s="73">
-        <f>SUM(IF(M8=$I$8,3,0)+IF(M9=$G8+$H8,1,0)+IF(M10=$I$10,3,0)+IF(M11=$G10+$H10,1,0)+IF(M12=$I$12,3,0)+IF(M13=$G12+$H12,1,0)+IF(M14=$I$14,3,0)+IF(M15=$G14+$H14,1,0)
-+IF(M16=$I$16,3,0)+IF(M17=$G16+$H16,1,0)+IF(M18=$I$18,3,0)+IF(M19=$G18+$H18,1,0)+IF(M20=$I$20,3,0)+IF(M21=$G20+$H20,1,0)+IF(M22=$I$22,3,0)+IF(M23=$G22+$H22,1,0)+IF(M24=$I$24,3,0)+IF(M25=$G24+$H24,1,0)+IF(M26=$I$26,3,0)+IF(M27=$G26+$H26,1,0)+IF(M28=$I$28,3,0)+IF(M29=$G28+$H28,1,0)+IF(M30=$I$30,3,0)+IF(M31=$G30+$H30,1,0)+IF(M32=$I$32,3,0)+IF(M33=$G32+$H32,1,0)+IF(M34=$I$34,3,0)+IF(M35=$G34+$H34,1,0)+IF(M36=$I$36,3,0)+IF(M37=$G36+$H36,1,0)+IF(M38=$I$38,3,0)+IF(M39=$G38+$H38,1,0)+IF(M40=$I$40,3,0)+IF(M41=$G40+$H40,1,0)+IF(M42=$I$42,3,0)+IF(M43=$G42+$H42,1,0)+IF(M44=$I$44,3,0)+IF(M45=$G44+$H44,1,0)+IF(M46=$I$46,3,0)+IF(M47=$G46+$H46,1,0)+IF(M48=$I$48,3,0)+IF(M49=$G48+$H48,1,0)+IF(M50=$I$50,3,0)+IF(M51=$G50+$H50,1,0)+IF(M52=$I$52,3,0)+IF(M53=$G52+$H52,1,0)+IF(M54=$I$54,3,0)+IF(M55=$G54+$H54,1,0)+IF(M56=$I$56,3,0)+IF(M57=$G56+$H56,1,0)+IF(M58=$I$58,3,0)+IF(M59=$G58+$H58,1,0)+IF(M60=$I$60,3,0)+IF(M61=$G60+$H60,1,0)+IF(M62=$I$62,3,0)+IF(M63=$G62+$H62,1,0)+IF(M64=$I$64,3,0)+IF(M65=$G64+$H64,1,0)+IF(M66=$I$66,3,0)+IF(M67=$G66+$H66,1,0)+IF(M68=$I$68,3,0)+IF(M69=$G68+$H68,1,0)+IF(M70=$I$70,3,0)+IF(M71=$G70+$H70,1,0)+IF(M72=$I$72,3,0)+IF(M73=$G72+$H72,1,0)+IF(M74=$I$74,3,0)+IF(M75=$G74+$H74,1,0)+IF(M76=$I$76,3,0)+IF(M77=$G76+$H76,1,0)+IF(M78=$I$78,3,0)+IF(M79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="N4" s="73">
-        <f>SUM(IF(N8=$I$8,3,0)+IF(N9=$G8+$H8,1,0)+IF(N10=$I$10,3,0)+IF(N11=$G10+$H10,1,0)+IF(N12=$I$12,3,0)+IF(N13=$G12+$H12,1,0)+IF(N14=$I$14,3,0)+IF(N15=$G14+$H14,1,0)
-+IF(N16=$I$16,3,0)+IF(N17=$G16+$H16,1,0)+IF(N18=$I$18,3,0)+IF(N19=$G18+$H18,1,0)+IF(N20=$I$20,3,0)+IF(N21=$G20+$H20,1,0)+IF(N22=$I$22,3,0)+IF(N23=$G22+$H22,1,0)+IF(N24=$I$24,3,0)+IF(N25=$G24+$H24,1,0)+IF(N26=$I$26,3,0)+IF(N27=$G26+$H26,1,0)+IF(N28=$I$28,3,0)+IF(N29=$G28+$H28,1,0)+IF(N30=$I$30,3,0)+IF(N31=$G30+$H30,1,0)+IF(N32=$I$32,3,0)+IF(N33=$G32+$H32,1,0)+IF(N34=$I$34,3,0)+IF(N35=$G34+$H34,1,0)+IF(N36=$I$36,3,0)+IF(N37=$G36+$H36,1,0)+IF(N38=$I$38,3,0)+IF(N39=$G38+$H38,1,0)+IF(N40=$I$40,3,0)+IF(N41=$G40+$H40,1,0)+IF(N42=$I$42,3,0)+IF(N43=$G42+$H42,1,0)+IF(N44=$I$44,3,0)+IF(N45=$G44+$H44,1,0)+IF(N46=$I$46,3,0)+IF(N47=$G46+$H46,1,0)+IF(N48=$I$48,3,0)+IF(N49=$G48+$H48,1,0)+IF(N50=$I$50,3,0)+IF(N51=$G50+$H50,1,0)+IF(N52=$I$52,3,0)+IF(N53=$G52+$H52,1,0)+IF(N54=$I$54,3,0)+IF(N55=$G54+$H54,1,0)+IF(N56=$I$56,3,0)+IF(N57=$G56+$H56,1,0)+IF(N58=$I$58,3,0)+IF(N59=$G58+$H58,1,0)+IF(N60=$I$60,3,0)+IF(N61=$G60+$H60,1,0)+IF(N62=$I$62,3,0)+IF(N63=$G62+$H62,1,0)+IF(N64=$I$64,3,0)+IF(N65=$G64+$H64,1,0)+IF(N66=$I$66,3,0)+IF(N67=$G66+$H66,1,0)+IF(N68=$I$68,3,0)+IF(N69=$G68+$H68,1,0)+IF(N70=$I$70,3,0)+IF(N71=$G70+$H70,1,0)+IF(N72=$I$72,3,0)+IF(N73=$G72+$H72,1,0)+IF(N74=$I$74,3,0)+IF(N75=$G74+$H74,1,0)+IF(N76=$I$76,3,0)+IF(N77=$G76+$H76,1,0)+IF(N78=$I$78,3,0)+IF(N79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="O4" s="73">
-        <f>SUM(IF(O8=$I$8,3,0)+IF(O9=$G8+$H8,1,0)+IF(O10=$I$10,3,0)+IF(O11=$G10+$H10,1,0)+IF(O12=$I$12,3,0)+IF(O13=$G12+$H12,1,0)+IF(O14=$I$14,3,0)+IF(O15=$G14+$H14,1,0)
-+IF(O16=$I$16,3,0)+IF(O17=$G16+$H16,1,0)+IF(O18=$I$18,3,0)+IF(O19=$G18+$H18,1,0)+IF(O20=$I$20,3,0)+IF(O21=$G20+$H20,1,0)+IF(O22=$I$22,3,0)+IF(O23=$G22+$H22,1,0)+IF(O24=$I$24,3,0)+IF(O25=$G24+$H24,1,0)+IF(O26=$I$26,3,0)+IF(O27=$G26+$H26,1,0)+IF(O28=$I$28,3,0)+IF(O29=$G28+$H28,1,0)+IF(O30=$I$30,3,0)+IF(O31=$G30+$H30,1,0)+IF(O32=$I$32,3,0)+IF(O33=$G32+$H32,1,0)+IF(O34=$I$34,3,0)+IF(O35=$G34+$H34,1,0)+IF(O36=$I$36,3,0)+IF(O37=$G36+$H36,1,0)+IF(O38=$I$38,3,0)+IF(O39=$G38+$H38,1,0)+IF(O40=$I$40,3,0)+IF(O41=$G40+$H40,1,0)+IF(O42=$I$42,3,0)+IF(O43=$G42+$H42,1,0)+IF(O44=$I$44,3,0)+IF(O45=$G44+$H44,1,0)+IF(O46=$I$46,3,0)+IF(O47=$G46+$H46,1,0)+IF(O48=$I$48,3,0)+IF(O49=$G48+$H48,1,0)+IF(O50=$I$50,3,0)+IF(O51=$G50+$H50,1,0)+IF(O52=$I$52,3,0)+IF(O53=$G52+$H52,1,0)+IF(O54=$I$54,3,0)+IF(O55=$G54+$H54,1,0)+IF(O56=$I$56,3,0)+IF(O57=$G56+$H56,1,0)+IF(O58=$I$58,3,0)+IF(O59=$G58+$H58,1,0)+IF(O60=$I$60,3,0)+IF(O61=$G60+$H60,1,0)+IF(O62=$I$62,3,0)+IF(O63=$G62+$H62,1,0)+IF(O64=$I$64,3,0)+IF(O65=$G64+$H64,1,0)+IF(O66=$I$66,3,0)+IF(O67=$G66+$H66,1,0)+IF(O68=$I$68,3,0)+IF(O69=$G68+$H68,1,0)+IF(O70=$I$70,3,0)+IF(O71=$G70+$H70,1,0)+IF(O72=$I$72,3,0)+IF(O73=$G72+$H72,1,0)+IF(O74=$I$74,3,0)+IF(O75=$G74+$H74,1,0)+IF(O76=$I$76,3,0)+IF(O77=$G76+$H76,1,0)+IF(O78=$I$78,3,0)+IF(O79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="P4" s="73">
-        <f>SUM(IF(P8=$I$8,3,0)+IF(P9=$G8+$H8,1,0)+IF(P10=$I$10,3,0)+IF(P11=$G10+$H10,1,0)+IF(P12=$I$12,3,0)+IF(P13=$G12+$H12,1,0)+IF(P14=$I$14,3,0)+IF(P15=$G14+$H14,1,0)
-+IF(P16=$I$16,3,0)+IF(P17=$G16+$H16,1,0)+IF(P18=$I$18,3,0)+IF(P19=$G18+$H18,1,0)+IF(P20=$I$20,3,0)+IF(P21=$G20+$H20,1,0)+IF(P22=$I$22,3,0)+IF(P23=$G22+$H22,1,0)+IF(P24=$I$24,3,0)+IF(P25=$G24+$H24,1,0)+IF(P26=$I$26,3,0)+IF(P27=$G26+$H26,1,0)+IF(P28=$I$28,3,0)+IF(P29=$G28+$H28,1,0)+IF(P30=$I$30,3,0)+IF(P31=$G30+$H30,1,0)+IF(P32=$I$32,3,0)+IF(P33=$G32+$H32,1,0)+IF(P34=$I$34,3,0)+IF(P35=$G34+$H34,1,0)+IF(P36=$I$36,3,0)+IF(P37=$G36+$H36,1,0)+IF(P38=$I$38,3,0)+IF(P39=$G38+$H38,1,0)+IF(P40=$I$40,3,0)+IF(P41=$G40+$H40,1,0)+IF(P42=$I$42,3,0)+IF(P43=$G42+$H42,1,0)+IF(P44=$I$44,3,0)+IF(P45=$G44+$H44,1,0)+IF(P46=$I$46,3,0)+IF(P47=$G46+$H46,1,0)+IF(P48=$I$48,3,0)+IF(P49=$G48+$H48,1,0)+IF(P50=$I$50,3,0)+IF(P51=$G50+$H50,1,0)+IF(P52=$I$52,3,0)+IF(P53=$G52+$H52,1,0)+IF(P54=$I$54,3,0)+IF(P55=$G54+$H54,1,0)+IF(P56=$I$56,3,0)+IF(P57=$G56+$H56,1,0)+IF(P58=$I$58,3,0)+IF(P59=$G58+$H58,1,0)+IF(P60=$I$60,3,0)+IF(P61=$G60+$H60,1,0)+IF(P62=$I$62,3,0)+IF(P63=$G62+$H62,1,0)+IF(P64=$I$64,3,0)+IF(P65=$G64+$H64,1,0)+IF(P66=$I$66,3,0)+IF(P67=$G66+$H66,1,0)+IF(P68=$I$68,3,0)+IF(P69=$G68+$H68,1,0)+IF(P70=$I$70,3,0)+IF(P71=$G70+$H70,1,0)+IF(P72=$I$72,3,0)+IF(P73=$G72+$H72,1,0)+IF(P74=$I$74,3,0)+IF(P75=$G74+$H74,1,0)+IF(P76=$I$76,3,0)+IF(P77=$G76+$H76,1,0)+IF(P78=$I$78,3,0)+IF(P79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="Q4" s="73">
-        <f>SUM(IF(Q8=$I$8,3,0)+IF(Q9=$G8+$H8,1,0)+IF(Q10=$I$10,3,0)+IF(Q11=$G10+$H10,1,0)+IF(Q12=$I$12,3,0)+IF(Q13=$G12+$H12,1,0)+IF(Q14=$I$14,3,0)+IF(Q15=$G14+$H14,1,0)
-+IF(Q16=$I$16,3,0)+IF(Q17=$G16+$H16,1,0)+IF(Q18=$I$18,3,0)+IF(Q19=$G18+$H18,1,0)+IF(Q20=$I$20,3,0)+IF(Q21=$G20+$H20,1,0)+IF(Q22=$I$22,3,0)+IF(Q23=$G22+$H22,1,0)+IF(Q24=$I$24,3,0)+IF(Q25=$G24+$H24,1,0)+IF(Q26=$I$26,3,0)+IF(Q27=$G26+$H26,1,0)+IF(Q28=$I$28,3,0)+IF(Q29=$G28+$H28,1,0)+IF(Q30=$I$30,3,0)+IF(Q31=$G30+$H30,1,0)+IF(Q32=$I$32,3,0)+IF(Q33=$G32+$H32,1,0)+IF(Q34=$I$34,3,0)+IF(Q35=$G34+$H34,1,0)+IF(Q36=$I$36,3,0)+IF(Q37=$G36+$H36,1,0)+IF(Q38=$I$38,3,0)+IF(Q39=$G38+$H38,1,0)+IF(Q40=$I$40,3,0)+IF(Q41=$G40+$H40,1,0)+IF(Q42=$I$42,3,0)+IF(Q43=$G42+$H42,1,0)+IF(Q44=$I$44,3,0)+IF(Q45=$G44+$H44,1,0)+IF(Q46=$I$46,3,0)+IF(Q47=$G46+$H46,1,0)+IF(Q48=$I$48,3,0)+IF(Q49=$G48+$H48,1,0)+IF(Q50=$I$50,3,0)+IF(Q51=$G50+$H50,1,0)+IF(Q52=$I$52,3,0)+IF(Q53=$G52+$H52,1,0)+IF(Q54=$I$54,3,0)+IF(Q55=$G54+$H54,1,0)+IF(Q56=$I$56,3,0)+IF(Q57=$G56+$H56,1,0)+IF(Q58=$I$58,3,0)+IF(Q59=$G58+$H58,1,0)+IF(Q60=$I$60,3,0)+IF(Q61=$G60+$H60,1,0)+IF(Q62=$I$62,3,0)+IF(Q63=$G62+$H62,1,0)+IF(Q64=$I$64,3,0)+IF(Q65=$G64+$H64,1,0)+IF(Q66=$I$66,3,0)+IF(Q67=$G66+$H66,1,0)+IF(Q68=$I$68,3,0)+IF(Q69=$G68+$H68,1,0)+IF(Q70=$I$70,3,0)+IF(Q71=$G70+$H70,1,0)+IF(Q72=$I$72,3,0)+IF(Q73=$G72+$H72,1,0)+IF(Q74=$I$74,3,0)+IF(Q75=$G74+$H74,1,0)+IF(Q76=$I$76,3,0)+IF(Q77=$G76+$H76,1,0)+IF(Q78=$I$78,3,0)+IF(Q79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="R4" s="73">
-        <f>SUM(IF(R8=$I$8,3,0)+IF(R9=$G8+$H8,1,0)+IF(R10=$I$10,3,0)+IF(R11=$G10+$H10,1,0)+IF(R12=$I$12,3,0)+IF(R13=$G12+$H12,1,0)+IF(R14=$I$14,3,0)+IF(R15=$G14+$H14,1,0)
-+IF(R16=$I$16,3,0)+IF(R17=$G16+$H16,1,0)+IF(R18=$I$18,3,0)+IF(R19=$G18+$H18,1,0)+IF(R20=$I$20,3,0)+IF(R21=$G20+$H20,1,0)+IF(R22=$I$22,3,0)+IF(R23=$G22+$H22,1,0)+IF(R24=$I$24,3,0)+IF(R25=$G24+$H24,1,0)+IF(R26=$I$26,3,0)+IF(R27=$G26+$H26,1,0)+IF(R28=$I$28,3,0)+IF(R29=$G28+$H28,1,0)+IF(R30=$I$30,3,0)+IF(R31=$G30+$H30,1,0)+IF(R32=$I$32,3,0)+IF(R33=$G32+$H32,1,0)+IF(R34=$I$34,3,0)+IF(R35=$G34+$H34,1,0)+IF(R36=$I$36,3,0)+IF(R37=$G36+$H36,1,0)+IF(R38=$I$38,3,0)+IF(R39=$G38+$H38,1,0)+IF(R40=$I$40,3,0)+IF(R41=$G40+$H40,1,0)+IF(R42=$I$42,3,0)+IF(R43=$G42+$H42,1,0)+IF(R44=$I$44,3,0)+IF(R45=$G44+$H44,1,0)+IF(R46=$I$46,3,0)+IF(R47=$G46+$H46,1,0)+IF(R48=$I$48,3,0)+IF(R49=$G48+$H48,1,0)+IF(R50=$I$50,3,0)+IF(R51=$G50+$H50,1,0)+IF(R52=$I$52,3,0)+IF(R53=$G52+$H52,1,0)+IF(R54=$I$54,3,0)+IF(R55=$G54+$H54,1,0)+IF(R56=$I$56,3,0)+IF(R57=$G56+$H56,1,0)+IF(R58=$I$58,3,0)+IF(R59=$G58+$H58,1,0)+IF(R60=$I$60,3,0)+IF(R61=$G60+$H60,1,0)+IF(R62=$I$62,3,0)+IF(R63=$G62+$H62,1,0)+IF(R64=$I$64,3,0)+IF(R65=$G64+$H64,1,0)+IF(R66=$I$66,3,0)+IF(R67=$G66+$H66,1,0)+IF(R68=$I$68,3,0)+IF(R69=$G68+$H68,1,0)+IF(R70=$I$70,3,0)+IF(R71=$G70+$H70,1,0)+IF(R72=$I$72,3,0)+IF(R73=$G72+$H72,1,0)+IF(R74=$I$74,3,0)+IF(R75=$G74+$H74,1,0)+IF(R76=$I$76,3,0)+IF(R77=$G76+$H76,1,0)+IF(R78=$I$78,3,0)+IF(R79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="S4" s="73">
-        <f>SUM(IF(S8=$I$8,3,0)+IF(S9=$G8+$H8,1,0)+IF(S10=$I$10,3,0)+IF(S11=$G10+$H10,1,0)+IF(S12=$I$12,3,0)+IF(S13=$G12+$H12,1,0)+IF(S14=$I$14,3,0)+IF(S15=$G14+$H14,1,0)
-+IF(S16=$I$16,3,0)+IF(S17=$G16+$H16,1,0)+IF(S18=$I$18,3,0)+IF(S19=$G18+$H18,1,0)+IF(S20=$I$20,3,0)+IF(S21=$G20+$H20,1,0)+IF(S22=$I$22,3,0)+IF(S23=$G22+$H22,1,0)+IF(S24=$I$24,3,0)+IF(S25=$G24+$H24,1,0)+IF(S26=$I$26,3,0)+IF(S27=$G26+$H26,1,0)+IF(S28=$I$28,3,0)+IF(S29=$G28+$H28,1,0)+IF(S30=$I$30,3,0)+IF(S31=$G30+$H30,1,0)+IF(S32=$I$32,3,0)+IF(S33=$G32+$H32,1,0)+IF(S34=$I$34,3,0)+IF(S35=$G34+$H34,1,0)+IF(S36=$I$36,3,0)+IF(S37=$G36+$H36,1,0)+IF(S38=$I$38,3,0)+IF(S39=$G38+$H38,1,0)+IF(S40=$I$40,3,0)+IF(S41=$G40+$H40,1,0)+IF(S42=$I$42,3,0)+IF(S43=$G42+$H42,1,0)+IF(S44=$I$44,3,0)+IF(S45=$G44+$H44,1,0)+IF(S46=$I$46,3,0)+IF(S47=$G46+$H46,1,0)+IF(S48=$I$48,3,0)+IF(S49=$G48+$H48,1,0)+IF(S50=$I$50,3,0)+IF(S51=$G50+$H50,1,0)+IF(S52=$I$52,3,0)+IF(S53=$G52+$H52,1,0)+IF(S54=$I$54,3,0)+IF(S55=$G54+$H54,1,0)+IF(S56=$I$56,3,0)+IF(S57=$G56+$H56,1,0)+IF(S58=$I$58,3,0)+IF(S59=$G58+$H58,1,0)+IF(S60=$I$60,3,0)+IF(S61=$G60+$H60,1,0)+IF(S62=$I$62,3,0)+IF(S63=$G62+$H62,1,0)+IF(S64=$I$64,3,0)+IF(S65=$G64+$H64,1,0)+IF(S66=$I$66,3,0)+IF(S67=$G66+$H66,1,0)+IF(S68=$I$68,3,0)+IF(S69=$G68+$H68,1,0)+IF(S70=$I$70,3,0)+IF(S71=$G70+$H70,1,0)+IF(S72=$I$72,3,0)+IF(S73=$G72+$H72,1,0)+IF(S74=$I$74,3,0)+IF(S75=$G74+$H74,1,0)+IF(S76=$I$76,3,0)+IF(S77=$G76+$H76,1,0)+IF(S78=$I$78,3,0)+IF(S79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="T4" s="73">
-        <f>SUM(IF(T8=$I$8,3,0)+IF(T9=$G8+$H8,1,0)+IF(T10=$I$10,3,0)+IF(T11=$G10+$H10,1,0)+IF(T12=$I$12,3,0)+IF(T13=$G12+$H12,1,0)+IF(T14=$I$14,3,0)+IF(T15=$G14+$H14,1,0)
-+IF(T16=$I$16,3,0)+IF(T17=$G16+$H16,1,0)+IF(T18=$I$18,3,0)+IF(T19=$G18+$H18,1,0)+IF(T20=$I$20,3,0)+IF(T21=$G20+$H20,1,0)+IF(T22=$I$22,3,0)+IF(T23=$G22+$H22,1,0)+IF(T24=$I$24,3,0)+IF(T25=$G24+$H24,1,0)+IF(T26=$I$26,3,0)+IF(T27=$G26+$H26,1,0)+IF(T28=$I$28,3,0)+IF(T29=$G28+$H28,1,0)+IF(T30=$I$30,3,0)+IF(T31=$G30+$H30,1,0)+IF(T32=$I$32,3,0)+IF(T33=$G32+$H32,1,0)+IF(T34=$I$34,3,0)+IF(T35=$G34+$H34,1,0)+IF(T36=$I$36,3,0)+IF(T37=$G36+$H36,1,0)+IF(T38=$I$38,3,0)+IF(T39=$G38+$H38,1,0)+IF(T40=$I$40,3,0)+IF(T41=$G40+$H40,1,0)+IF(T42=$I$42,3,0)+IF(T43=$G42+$H42,1,0)+IF(T44=$I$44,3,0)+IF(T45=$G44+$H44,1,0)+IF(T46=$I$46,3,0)+IF(T47=$G46+$H46,1,0)+IF(T48=$I$48,3,0)+IF(T49=$G48+$H48,1,0)+IF(T50=$I$50,3,0)+IF(T51=$G50+$H50,1,0)+IF(T52=$I$52,3,0)+IF(T53=$G52+$H52,1,0)+IF(T54=$I$54,3,0)+IF(T55=$G54+$H54,1,0)+IF(T56=$I$56,3,0)+IF(T57=$G56+$H56,1,0)+IF(T58=$I$58,3,0)+IF(T59=$G58+$H58,1,0)+IF(T60=$I$60,3,0)+IF(T61=$G60+$H60,1,0)+IF(T62=$I$62,3,0)+IF(T63=$G62+$H62,1,0)+IF(T64=$I$64,3,0)+IF(T65=$G64+$H64,1,0)+IF(T66=$I$66,3,0)+IF(T67=$G66+$H66,1,0)+IF(T68=$I$68,3,0)+IF(T69=$G68+$H68,1,0)+IF(T70=$I$70,3,0)+IF(T71=$G70+$H70,1,0)+IF(T72=$I$72,3,0)+IF(T73=$G72+$H72,1,0)+IF(T74=$I$74,3,0)+IF(T75=$G74+$H74,1,0)+IF(T76=$I$76,3,0)+IF(T77=$G76+$H76,1,0)+IF(T78=$I$78,3,0)+IF(T79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="U4" s="73">
-        <f>SUM(IF(U8=$I$8,3,0)+IF(U9=$G8+$H8,1,0)+IF(U10=$I$10,3,0)+IF(U11=$G10+$H10,1,0)+IF(U12=$I$12,3,0)+IF(U13=$G12+$H12,1,0)+IF(U14=$I$14,3,0)+IF(U15=$G14+$H14,1,0)
-+IF(U16=$I$16,3,0)+IF(U17=$G16+$H16,1,0)+IF(U18=$I$18,3,0)+IF(U19=$G18+$H18,1,0)+IF(U20=$I$20,3,0)+IF(U21=$G20+$H20,1,0)+IF(U22=$I$22,3,0)+IF(U23=$G22+$H22,1,0)+IF(U24=$I$24,3,0)+IF(U25=$G24+$H24,1,0)+IF(U26=$I$26,3,0)+IF(U27=$G26+$H26,1,0)+IF(U28=$I$28,3,0)+IF(U29=$G28+$H28,1,0)+IF(U30=$I$30,3,0)+IF(U31=$G30+$H30,1,0)+IF(U32=$I$32,3,0)+IF(U33=$G32+$H32,1,0)+IF(U34=$I$34,3,0)+IF(U35=$G34+$H34,1,0)+IF(U36=$I$36,3,0)+IF(U37=$G36+$H36,1,0)+IF(U38=$I$38,3,0)+IF(U39=$G38+$H38,1,0)+IF(U40=$I$40,3,0)+IF(U41=$G40+$H40,1,0)+IF(U42=$I$42,3,0)+IF(U43=$G42+$H42,1,0)+IF(U44=$I$44,3,0)+IF(U45=$G44+$H44,1,0)+IF(U46=$I$46,3,0)+IF(U47=$G46+$H46,1,0)+IF(U48=$I$48,3,0)+IF(U49=$G48+$H48,1,0)+IF(U50=$I$50,3,0)+IF(U51=$G50+$H50,1,0)+IF(U52=$I$52,3,0)+IF(U53=$G52+$H52,1,0)+IF(U54=$I$54,3,0)+IF(U55=$G54+$H54,1,0)+IF(U56=$I$56,3,0)+IF(U57=$G56+$H56,1,0)+IF(U58=$I$58,3,0)+IF(U59=$G58+$H58,1,0)+IF(U60=$I$60,3,0)+IF(U61=$G60+$H60,1,0)+IF(U62=$I$62,3,0)+IF(U63=$G62+$H62,1,0)+IF(U64=$I$64,3,0)+IF(U65=$G64+$H64,1,0)+IF(U66=$I$66,3,0)+IF(U67=$G66+$H66,1,0)+IF(U68=$I$68,3,0)+IF(U69=$G68+$H68,1,0)+IF(U70=$I$70,3,0)+IF(U71=$G70+$H70,1,0)+IF(U72=$I$72,3,0)+IF(U73=$G72+$H72,1,0)+IF(U74=$I$74,3,0)+IF(U75=$G74+$H74,1,0)+IF(U76=$I$76,3,0)+IF(U77=$G76+$H76,1,0)+IF(U78=$I$78,3,0)+IF(U79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="V4" s="73">
-        <f>SUM(IF(V8=$I$8,3,0)+IF(V9=$G8+$H8,1,0)+IF(V10=$I$10,3,0)+IF(V11=$G10+$H10,1,0)+IF(V12=$I$12,3,0)+IF(V13=$G12+$H12,1,0)+IF(V14=$I$14,3,0)+IF(V15=$G14+$H14,1,0)
-+IF(V16=$I$16,3,0)+IF(V17=$G16+$H16,1,0)+IF(V18=$I$18,3,0)+IF(V19=$G18+$H18,1,0)+IF(V20=$I$20,3,0)+IF(V21=$G20+$H20,1,0)+IF(V22=$I$22,3,0)+IF(V23=$G22+$H22,1,0)+IF(V24=$I$24,3,0)+IF(V25=$G24+$H24,1,0)+IF(V26=$I$26,3,0)+IF(V27=$G26+$H26,1,0)+IF(V28=$I$28,3,0)+IF(V29=$G28+$H28,1,0)+IF(V30=$I$30,3,0)+IF(V31=$G30+$H30,1,0)+IF(V32=$I$32,3,0)+IF(V33=$G32+$H32,1,0)+IF(V34=$I$34,3,0)+IF(V35=$G34+$H34,1,0)+IF(V36=$I$36,3,0)+IF(V37=$G36+$H36,1,0)+IF(V38=$I$38,3,0)+IF(V39=$G38+$H38,1,0)+IF(V40=$I$40,3,0)+IF(V41=$G40+$H40,1,0)+IF(V42=$I$42,3,0)+IF(V43=$G42+$H42,1,0)+IF(V44=$I$44,3,0)+IF(V45=$G44+$H44,1,0)+IF(V46=$I$46,3,0)+IF(V47=$G46+$H46,1,0)+IF(V48=$I$48,3,0)+IF(V49=$G48+$H48,1,0)+IF(V50=$I$50,3,0)+IF(V51=$G50+$H50,1,0)+IF(V52=$I$52,3,0)+IF(V53=$G52+$H52,1,0)+IF(V54=$I$54,3,0)+IF(V55=$G54+$H54,1,0)+IF(V56=$I$56,3,0)+IF(V57=$G56+$H56,1,0)+IF(V58=$I$58,3,0)+IF(V59=$G58+$H58,1,0)+IF(V60=$I$60,3,0)+IF(V61=$G60+$H60,1,0)+IF(V62=$I$62,3,0)+IF(V63=$G62+$H62,1,0)+IF(V64=$I$64,3,0)+IF(V65=$G64+$H64,1,0)+IF(V66=$I$66,3,0)+IF(V67=$G66+$H66,1,0)+IF(V68=$I$68,3,0)+IF(V69=$G68+$H68,1,0)+IF(V70=$I$70,3,0)+IF(V71=$G70+$H70,1,0)+IF(V72=$I$72,3,0)+IF(V73=$G72+$H72,1,0)+IF(V74=$I$74,3,0)+IF(V75=$G74+$H74,1,0)+IF(V76=$I$76,3,0)+IF(V77=$G76+$H76,1,0)+IF(V78=$I$78,3,0)+IF(V79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="W4" s="73">
-        <f>SUM(IF(W8=$I$8,3,0)+IF(W9=$G8+$H8,1,0)+IF(W10=$I$10,3,0)+IF(W11=$G10+$H10,1,0)+IF(W12=$I$12,3,0)+IF(W13=$G12+$H12,1,0)+IF(W14=$I$14,3,0)+IF(W15=$G14+$H14,1,0)
-+IF(W16=$I$16,3,0)+IF(W17=$G16+$H16,1,0)+IF(W18=$I$18,3,0)+IF(W19=$G18+$H18,1,0)+IF(W20=$I$20,3,0)+IF(W21=$G20+$H20,1,0)+IF(W22=$I$22,3,0)+IF(W23=$G22+$H22,1,0)+IF(W24=$I$24,3,0)+IF(W25=$G24+$H24,1,0)+IF(W26=$I$26,3,0)+IF(W27=$G26+$H26,1,0)+IF(W28=$I$28,3,0)+IF(W29=$G28+$H28,1,0)+IF(W30=$I$30,3,0)+IF(W31=$G30+$H30,1,0)+IF(W32=$I$32,3,0)+IF(W33=$G32+$H32,1,0)+IF(W34=$I$34,3,0)+IF(W35=$G34+$H34,1,0)+IF(W36=$I$36,3,0)+IF(W37=$G36+$H36,1,0)+IF(W38=$I$38,3,0)+IF(W39=$G38+$H38,1,0)+IF(W40=$I$40,3,0)+IF(W41=$G40+$H40,1,0)+IF(W42=$I$42,3,0)+IF(W43=$G42+$H42,1,0)+IF(W44=$I$44,3,0)+IF(W45=$G44+$H44,1,0)+IF(W46=$I$46,3,0)+IF(W47=$G46+$H46,1,0)+IF(W48=$I$48,3,0)+IF(W49=$G48+$H48,1,0)+IF(W50=$I$50,3,0)+IF(W51=$G50+$H50,1,0)+IF(W52=$I$52,3,0)+IF(W53=$G52+$H52,1,0)+IF(W54=$I$54,3,0)+IF(W55=$G54+$H54,1,0)+IF(W56=$I$56,3,0)+IF(W57=$G56+$H56,1,0)+IF(W58=$I$58,3,0)+IF(W59=$G58+$H58,1,0)+IF(W60=$I$60,3,0)+IF(W61=$G60+$H60,1,0)+IF(W62=$I$62,3,0)+IF(W63=$G62+$H62,1,0)+IF(W64=$I$64,3,0)+IF(W65=$G64+$H64,1,0)+IF(W66=$I$66,3,0)+IF(W67=$G66+$H66,1,0)+IF(W68=$I$68,3,0)+IF(W69=$G68+$H68,1,0)+IF(W70=$I$70,3,0)+IF(W71=$G70+$H70,1,0)+IF(W72=$I$72,3,0)+IF(W73=$G72+$H72,1,0)+IF(W74=$I$74,3,0)+IF(W75=$G74+$H74,1,0)+IF(W76=$I$76,3,0)+IF(W77=$G76+$H76,1,0)+IF(W78=$I$78,3,0)+IF(W79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="X4" s="73">
-        <f>SUM(IF(X8=$I$8,3,0)+IF(X9=$G8+$H8,1,0)+IF(X10=$I$10,3,0)+IF(X11=$G10+$H10,1,0)+IF(X12=$I$12,3,0)+IF(X13=$G12+$H12,1,0)+IF(X14=$I$14,3,0)+IF(X15=$G14+$H14,1,0)
-+IF(X16=$I$16,3,0)+IF(X17=$G16+$H16,1,0)+IF(X18=$I$18,3,0)+IF(X19=$G18+$H18,1,0)+IF(X20=$I$20,3,0)+IF(X21=$G20+$H20,1,0)+IF(X22=$I$22,3,0)+IF(X23=$G22+$H22,1,0)+IF(X24=$I$24,3,0)+IF(X25=$G24+$H24,1,0)+IF(X26=$I$26,3,0)+IF(X27=$G26+$H26,1,0)+IF(X28=$I$28,3,0)+IF(X29=$G28+$H28,1,0)+IF(X30=$I$30,3,0)+IF(X31=$G30+$H30,1,0)+IF(X32=$I$32,3,0)+IF(X33=$G32+$H32,1,0)+IF(X34=$I$34,3,0)+IF(X35=$G34+$H34,1,0)+IF(X36=$I$36,3,0)+IF(X37=$G36+$H36,1,0)+IF(X38=$I$38,3,0)+IF(X39=$G38+$H38,1,0)+IF(X40=$I$40,3,0)+IF(X41=$G40+$H40,1,0)+IF(X42=$I$42,3,0)+IF(X43=$G42+$H42,1,0)+IF(X44=$I$44,3,0)+IF(X45=$G44+$H44,1,0)+IF(X46=$I$46,3,0)+IF(X47=$G46+$H46,1,0)+IF(X48=$I$48,3,0)+IF(X49=$G48+$H48,1,0)+IF(X50=$I$50,3,0)+IF(X51=$G50+$H50,1,0)+IF(X52=$I$52,3,0)+IF(X53=$G52+$H52,1,0)+IF(X54=$I$54,3,0)+IF(X55=$G54+$H54,1,0)+IF(X56=$I$56,3,0)+IF(X57=$G56+$H56,1,0)+IF(X58=$I$58,3,0)+IF(X59=$G58+$H58,1,0)+IF(X60=$I$60,3,0)+IF(X61=$G60+$H60,1,0)+IF(X62=$I$62,3,0)+IF(X63=$G62+$H62,1,0)+IF(X64=$I$64,3,0)+IF(X65=$G64+$H64,1,0)+IF(X66=$I$66,3,0)+IF(X67=$G66+$H66,1,0)+IF(X68=$I$68,3,0)+IF(X69=$G68+$H68,1,0)+IF(X70=$I$70,3,0)+IF(X71=$G70+$H70,1,0)+IF(X72=$I$72,3,0)+IF(X73=$G72+$H72,1,0)+IF(X74=$I$74,3,0)+IF(X75=$G74+$H74,1,0)+IF(X76=$I$76,3,0)+IF(X77=$G76+$H76,1,0)+IF(X78=$I$78,3,0)+IF(X79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="Y4" s="73">
-        <f>SUM(IF(Y8=$I$8,3,0)+IF(Y9=$G8+$H8,1,0)+IF(Y10=$I$10,3,0)+IF(Y11=$G10+$H10,1,0)+IF(Y12=$I$12,3,0)+IF(Y13=$G12+$H12,1,0)+IF(Y14=$I$14,3,0)+IF(Y15=$G14+$H14,1,0)
-+IF(Y16=$I$16,3,0)+IF(Y17=$G16+$H16,1,0)+IF(Y18=$I$18,3,0)+IF(Y19=$G18+$H18,1,0)+IF(Y20=$I$20,3,0)+IF(Y21=$G20+$H20,1,0)+IF(Y22=$I$22,3,0)+IF(Y23=$G22+$H22,1,0)+IF(Y24=$I$24,3,0)+IF(Y25=$G24+$H24,1,0)+IF(Y26=$I$26,3,0)+IF(Y27=$G26+$H26,1,0)+IF(Y28=$I$28,3,0)+IF(Y29=$G28+$H28,1,0)+IF(Y30=$I$30,3,0)+IF(Y31=$G30+$H30,1,0)+IF(Y32=$I$32,3,0)+IF(Y33=$G32+$H32,1,0)+IF(Y34=$I$34,3,0)+IF(Y35=$G34+$H34,1,0)+IF(Y36=$I$36,3,0)+IF(Y37=$G36+$H36,1,0)+IF(Y38=$I$38,3,0)+IF(Y39=$G38+$H38,1,0)+IF(Y40=$I$40,3,0)+IF(Y41=$G40+$H40,1,0)+IF(Y42=$I$42,3,0)+IF(Y43=$G42+$H42,1,0)+IF(Y44=$I$44,3,0)+IF(Y45=$G44+$H44,1,0)+IF(Y46=$I$46,3,0)+IF(Y47=$G46+$H46,1,0)+IF(Y48=$I$48,3,0)+IF(Y49=$G48+$H48,1,0)+IF(Y50=$I$50,3,0)+IF(Y51=$G50+$H50,1,0)+IF(Y52=$I$52,3,0)+IF(Y53=$G52+$H52,1,0)+IF(Y54=$I$54,3,0)+IF(Y55=$G54+$H54,1,0)+IF(Y56=$I$56,3,0)+IF(Y57=$G56+$H56,1,0)+IF(Y58=$I$58,3,0)+IF(Y59=$G58+$H58,1,0)+IF(Y60=$I$60,3,0)+IF(Y61=$G60+$H60,1,0)+IF(Y62=$I$62,3,0)+IF(Y63=$G62+$H62,1,0)+IF(Y64=$I$64,3,0)+IF(Y65=$G64+$H64,1,0)+IF(Y66=$I$66,3,0)+IF(Y67=$G66+$H66,1,0)+IF(Y68=$I$68,3,0)+IF(Y69=$G68+$H68,1,0)+IF(Y70=$I$70,3,0)+IF(Y71=$G70+$H70,1,0)+IF(Y72=$I$72,3,0)+IF(Y73=$G72+$H72,1,0)+IF(Y74=$I$74,3,0)+IF(Y75=$G74+$H74,1,0)+IF(Y76=$I$76,3,0)+IF(Y77=$G76+$H76,1,0)+IF(Y78=$I$78,3,0)+IF(Y79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="Z4" s="73">
-        <f>SUM(IF(Z8=$I$8,3,0)+IF(Z9=$G8+$H8,1,0)+IF(Z10=$I$10,3,0)+IF(Z11=$G10+$H10,1,0)+IF(Z12=$I$12,3,0)+IF(Z13=$G12+$H12,1,0)+IF(Z14=$I$14,3,0)+IF(Z15=$G14+$H14,1,0)
-+IF(Z16=$I$16,3,0)+IF(Z17=$G16+$H16,1,0)+IF(Z18=$I$18,3,0)+IF(Z19=$G18+$H18,1,0)+IF(Z20=$I$20,3,0)+IF(Z21=$G20+$H20,1,0)+IF(Z22=$I$22,3,0)+IF(Z23=$G22+$H22,1,0)+IF(Z24=$I$24,3,0)+IF(Z25=$G24+$H24,1,0)+IF(Z26=$I$26,3,0)+IF(Z27=$G26+$H26,1,0)+IF(Z28=$I$28,3,0)+IF(Z29=$G28+$H28,1,0)+IF(Z30=$I$30,3,0)+IF(Z31=$G30+$H30,1,0)+IF(Z32=$I$32,3,0)+IF(Z33=$G32+$H32,1,0)+IF(Z34=$I$34,3,0)+IF(Z35=$G34+$H34,1,0)+IF(Z36=$I$36,3,0)+IF(Z37=$G36+$H36,1,0)+IF(Z38=$I$38,3,0)+IF(Z39=$G38+$H38,1,0)+IF(Z40=$I$40,3,0)+IF(Z41=$G40+$H40,1,0)+IF(Z42=$I$42,3,0)+IF(Z43=$G42+$H42,1,0)+IF(Z44=$I$44,3,0)+IF(Z45=$G44+$H44,1,0)+IF(Z46=$I$46,3,0)+IF(Z47=$G46+$H46,1,0)+IF(Z48=$I$48,3,0)+IF(Z49=$G48+$H48,1,0)+IF(Z50=$I$50,3,0)+IF(Z51=$G50+$H50,1,0)+IF(Z52=$I$52,3,0)+IF(Z53=$G52+$H52,1,0)+IF(Z54=$I$54,3,0)+IF(Z55=$G54+$H54,1,0)+IF(Z56=$I$56,3,0)+IF(Z57=$G56+$H56,1,0)+IF(Z58=$I$58,3,0)+IF(Z59=$G58+$H58,1,0)+IF(Z60=$I$60,3,0)+IF(Z61=$G60+$H60,1,0)+IF(Z62=$I$62,3,0)+IF(Z63=$G62+$H62,1,0)+IF(Z64=$I$64,3,0)+IF(Z65=$G64+$H64,1,0)+IF(Z66=$I$66,3,0)+IF(Z67=$G66+$H66,1,0)+IF(Z68=$I$68,3,0)+IF(Z69=$G68+$H68,1,0)+IF(Z70=$I$70,3,0)+IF(Z71=$G70+$H70,1,0)+IF(Z72=$I$72,3,0)+IF(Z73=$G72+$H72,1,0)+IF(Z74=$I$74,3,0)+IF(Z75=$G74+$H74,1,0)+IF(Z76=$I$76,3,0)+IF(Z77=$G76+$H76,1,0)+IF(Z78=$I$78,3,0)+IF(Z79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="AA4" s="73">
-        <f>SUM(IF(AA8=$I$8,3,0)+IF(AA9=$G8+$H8,1,0)+IF(AA10=$I$10,3,0)+IF(AA11=$G10+$H10,1,0)+IF(AA12=$I$12,3,0)+IF(AA13=$G12+$H12,1,0)+IF(AA14=$I$14,3,0)+IF(AA15=$G14+$H14,1,0)
-+IF(AA16=$I$16,3,0)+IF(AA17=$G16+$H16,1,0)+IF(AA18=$I$18,3,0)+IF(AA19=$G18+$H18,1,0)+IF(AA20=$I$20,3,0)+IF(AA21=$G20+$H20,1,0)+IF(AA22=$I$22,3,0)+IF(AA23=$G22+$H22,1,0)+IF(AA24=$I$24,3,0)+IF(AA25=$G24+$H24,1,0)+IF(AA26=$I$26,3,0)+IF(AA27=$G26+$H26,1,0)+IF(AA28=$I$28,3,0)+IF(AA29=$G28+$H28,1,0)+IF(AA30=$I$30,3,0)+IF(AA31=$G30+$H30,1,0)+IF(AA32=$I$32,3,0)+IF(AA33=$G32+$H32,1,0)+IF(AA34=$I$34,3,0)+IF(AA35=$G34+$H34,1,0)+IF(AA36=$I$36,3,0)+IF(AA37=$G36+$H36,1,0)+IF(AA38=$I$38,3,0)+IF(AA39=$G38+$H38,1,0)+IF(AA40=$I$40,3,0)+IF(AA41=$G40+$H40,1,0)+IF(AA42=$I$42,3,0)+IF(AA43=$G42+$H42,1,0)+IF(AA44=$I$44,3,0)+IF(AA45=$G44+$H44,1,0)+IF(AA46=$I$46,3,0)+IF(AA47=$G46+$H46,1,0)+IF(AA48=$I$48,3,0)+IF(AA49=$G48+$H48,1,0)+IF(AA50=$I$50,3,0)+IF(AA51=$G50+$H50,1,0)+IF(AA52=$I$52,3,0)+IF(AA53=$G52+$H52,1,0)+IF(AA54=$I$54,3,0)+IF(AA55=$G54+$H54,1,0)+IF(AA56=$I$56,3,0)+IF(AA57=$G56+$H56,1,0)+IF(AA58=$I$58,3,0)+IF(AA59=$G58+$H58,1,0)+IF(AA60=$I$60,3,0)+IF(AA61=$G60+$H60,1,0)+IF(AA62=$I$62,3,0)+IF(AA63=$G62+$H62,1,0)+IF(AA64=$I$64,3,0)+IF(AA65=$G64+$H64,1,0)+IF(AA66=$I$66,3,0)+IF(AA67=$G66+$H66,1,0)+IF(AA68=$I$68,3,0)+IF(AA69=$G68+$H68,1,0)+IF(AA70=$I$70,3,0)+IF(AA71=$G70+$H70,1,0)+IF(AA72=$I$72,3,0)+IF(AA73=$G72+$H72,1,0)+IF(AA74=$I$74,3,0)+IF(AA75=$G74+$H74,1,0)+IF(AA76=$I$76,3,0)+IF(AA77=$G76+$H76,1,0)+IF(AA78=$I$78,3,0)+IF(AA79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="AB4" s="73">
-        <f>SUM(IF(AB8=$I$8,3,0)+IF(AB9=$G8+$H8,1,0)+IF(AB10=$I$10,3,0)+IF(AB11=$G10+$H10,1,0)+IF(AB12=$I$12,3,0)+IF(AB13=$G12+$H12,1,0)+IF(AB14=$I$14,3,0)+IF(AB15=$G14+$H14,1,0)
-+IF(AB16=$I$16,3,0)+IF(AB17=$G16+$H16,1,0)+IF(AB18=$I$18,3,0)+IF(AB19=$G18+$H18,1,0)+IF(AB20=$I$20,3,0)+IF(AB21=$G20+$H20,1,0)+IF(AB22=$I$22,3,0)+IF(AB23=$G22+$H22,1,0)+IF(AB24=$I$24,3,0)+IF(AB25=$G24+$H24,1,0)+IF(AB26=$I$26,3,0)+IF(AB27=$G26+$H26,1,0)+IF(AB28=$I$28,3,0)+IF(AB29=$G28+$H28,1,0)+IF(AB30=$I$30,3,0)+IF(AB31=$G30+$H30,1,0)+IF(AB32=$I$32,3,0)+IF(AB33=$G32+$H32,1,0)+IF(AB34=$I$34,3,0)+IF(AB35=$G34+$H34,1,0)+IF(AB36=$I$36,3,0)+IF(AB37=$G36+$H36,1,0)+IF(AB38=$I$38,3,0)+IF(AB39=$G38+$H38,1,0)+IF(AB40=$I$40,3,0)+IF(AB41=$G40+$H40,1,0)+IF(AB42=$I$42,3,0)+IF(AB43=$G42+$H42,1,0)+IF(AB44=$I$44,3,0)+IF(AB45=$G44+$H44,1,0)+IF(AB46=$I$46,3,0)+IF(AB47=$G46+$H46,1,0)+IF(AB48=$I$48,3,0)+IF(AB49=$G48+$H48,1,0)+IF(AB50=$I$50,3,0)+IF(AB51=$G50+$H50,1,0)+IF(AB52=$I$52,3,0)+IF(AB53=$G52+$H52,1,0)+IF(AB54=$I$54,3,0)+IF(AB55=$G54+$H54,1,0)+IF(AB56=$I$56,3,0)+IF(AB57=$G56+$H56,1,0)+IF(AB58=$I$58,3,0)+IF(AB59=$G58+$H58,1,0)+IF(AB60=$I$60,3,0)+IF(AB61=$G60+$H60,1,0)+IF(AB62=$I$62,3,0)+IF(AB63=$G62+$H62,1,0)+IF(AB64=$I$64,3,0)+IF(AB65=$G64+$H64,1,0)+IF(AB66=$I$66,3,0)+IF(AB67=$G66+$H66,1,0)+IF(AB68=$I$68,3,0)+IF(AB69=$G68+$H68,1,0)+IF(AB70=$I$70,3,0)+IF(AB71=$G70+$H70,1,0)+IF(AB72=$I$72,3,0)+IF(AB73=$G72+$H72,1,0)+IF(AB74=$I$74,3,0)+IF(AB75=$G74+$H74,1,0)+IF(AB76=$I$76,3,0)+IF(AB77=$G76+$H76,1,0)+IF(AB78=$I$78,3,0)+IF(AB79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="AC4" s="73">
-        <f>SUM(IF(AC8=$I$8,3,0)+IF(AC9=$G8+$H8,1,0)+IF(AC10=$I$10,3,0)+IF(AC11=$G10+$H10,1,0)+IF(AC12=$I$12,3,0)+IF(AC13=$G12+$H12,1,0)+IF(AC14=$I$14,3,0)+IF(AC15=$G14+$H14,1,0)
-+IF(AC16=$I$16,3,0)+IF(AC17=$G16+$H16,1,0)+IF(AC18=$I$18,3,0)+IF(AC19=$G18+$H18,1,0)+IF(AC20=$I$20,3,0)+IF(AC21=$G20+$H20,1,0)+IF(AC22=$I$22,3,0)+IF(AC23=$G22+$H22,1,0)+IF(AC24=$I$24,3,0)+IF(AC25=$G24+$H24,1,0)+IF(AC26=$I$26,3,0)+IF(AC27=$G26+$H26,1,0)+IF(AC28=$I$28,3,0)+IF(AC29=$G28+$H28,1,0)+IF(AC30=$I$30,3,0)+IF(AC31=$G30+$H30,1,0)+IF(AC32=$I$32,3,0)+IF(AC33=$G32+$H32,1,0)+IF(AC34=$I$34,3,0)+IF(AC35=$G34+$H34,1,0)+IF(AC36=$I$36,3,0)+IF(AC37=$G36+$H36,1,0)+IF(AC38=$I$38,3,0)+IF(AC39=$G38+$H38,1,0)+IF(AC40=$I$40,3,0)+IF(AC41=$G40+$H40,1,0)+IF(AC42=$I$42,3,0)+IF(AC43=$G42+$H42,1,0)+IF(AC44=$I$44,3,0)+IF(AC45=$G44+$H44,1,0)+IF(AC46=$I$46,3,0)+IF(AC47=$G46+$H46,1,0)+IF(AC48=$I$48,3,0)+IF(AC49=$G48+$H48,1,0)+IF(AC50=$I$50,3,0)+IF(AC51=$G50+$H50,1,0)+IF(AC52=$I$52,3,0)+IF(AC53=$G52+$H52,1,0)+IF(AC54=$I$54,3,0)+IF(AC55=$G54+$H54,1,0)+IF(AC56=$I$56,3,0)+IF(AC57=$G56+$H56,1,0)+IF(AC58=$I$58,3,0)+IF(AC59=$G58+$H58,1,0)+IF(AC60=$I$60,3,0)+IF(AC61=$G60+$H60,1,0)+IF(AC62=$I$62,3,0)+IF(AC63=$G62+$H62,1,0)+IF(AC64=$I$64,3,0)+IF(AC65=$G64+$H64,1,0)+IF(AC66=$I$66,3,0)+IF(AC67=$G66+$H66,1,0)+IF(AC68=$I$68,3,0)+IF(AC69=$G68+$H68,1,0)+IF(AC70=$I$70,3,0)+IF(AC71=$G70+$H70,1,0)+IF(AC72=$I$72,3,0)+IF(AC73=$G72+$H72,1,0)+IF(AC74=$I$74,3,0)+IF(AC75=$G74+$H74,1,0)+IF(AC76=$I$76,3,0)+IF(AC77=$G76+$H76,1,0)+IF(AC78=$I$78,3,0)+IF(AC79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="AD4" s="73">
-        <f>SUM(IF(AD8=$I$8,3,0)+IF(AD9=$G8+$H8,1,0)+IF(AD10=$I$10,3,0)+IF(AD11=$G10+$H10,1,0)+IF(AD12=$I$12,3,0)+IF(AD13=$G12+$H12,1,0)+IF(AD14=$I$14,3,0)+IF(AD15=$G14+$H14,1,0)
-+IF(AD16=$I$16,3,0)+IF(AD17=$G16+$H16,1,0)+IF(AD18=$I$18,3,0)+IF(AD19=$G18+$H18,1,0)+IF(AD20=$I$20,3,0)+IF(AD21=$G20+$H20,1,0)+IF(AD22=$I$22,3,0)+IF(AD23=$G22+$H22,1,0)+IF(AD24=$I$24,3,0)+IF(AD25=$G24+$H24,1,0)+IF(AD26=$I$26,3,0)+IF(AD27=$G26+$H26,1,0)+IF(AD28=$I$28,3,0)+IF(AD29=$G28+$H28,1,0)+IF(AD30=$I$30,3,0)+IF(AD31=$G30+$H30,1,0)+IF(AD32=$I$32,3,0)+IF(AD33=$G32+$H32,1,0)+IF(AD34=$I$34,3,0)+IF(AD35=$G34+$H34,1,0)+IF(AD36=$I$36,3,0)+IF(AD37=$G36+$H36,1,0)+IF(AD38=$I$38,3,0)+IF(AD39=$G38+$H38,1,0)+IF(AD40=$I$40,3,0)+IF(AD41=$G40+$H40,1,0)+IF(AD42=$I$42,3,0)+IF(AD43=$G42+$H42,1,0)+IF(AD44=$I$44,3,0)+IF(AD45=$G44+$H44,1,0)+IF(AD46=$I$46,3,0)+IF(AD47=$G46+$H46,1,0)+IF(AD48=$I$48,3,0)+IF(AD49=$G48+$H48,1,0)+IF(AD50=$I$50,3,0)+IF(AD51=$G50+$H50,1,0)+IF(AD52=$I$52,3,0)+IF(AD53=$G52+$H52,1,0)+IF(AD54=$I$54,3,0)+IF(AD55=$G54+$H54,1,0)+IF(AD56=$I$56,3,0)+IF(AD57=$G56+$H56,1,0)+IF(AD58=$I$58,3,0)+IF(AD59=$G58+$H58,1,0)+IF(AD60=$I$60,3,0)+IF(AD61=$G60+$H60,1,0)+IF(AD62=$I$62,3,0)+IF(AD63=$G62+$H62,1,0)+IF(AD64=$I$64,3,0)+IF(AD65=$G64+$H64,1,0)+IF(AD66=$I$66,3,0)+IF(AD67=$G66+$H66,1,0)+IF(AD68=$I$68,3,0)+IF(AD69=$G68+$H68,1,0)+IF(AD70=$I$70,3,0)+IF(AD71=$G70+$H70,1,0)+IF(AD72=$I$72,3,0)+IF(AD73=$G72+$H72,1,0)+IF(AD74=$I$74,3,0)+IF(AD75=$G74+$H74,1,0)+IF(AD76=$I$76,3,0)+IF(AD77=$G76+$H76,1,0)+IF(AD78=$I$78,3,0)+IF(AD79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="AE4" s="73">
-        <f>SUM(IF(AE8=$I$8,3,0)+IF(AE9=$G8+$H8,1,0)+IF(AE10=$I$10,3,0)+IF(AE11=$G10+$H10,1,0)+IF(AE12=$I$12,3,0)+IF(AE13=$G12+$H12,1,0)+IF(AE14=$I$14,3,0)+IF(AE15=$G14+$H14,1,0)
-+IF(AE16=$I$16,3,0)+IF(AE17=$G16+$H16,1,0)+IF(AE18=$I$18,3,0)+IF(AE19=$G18+$H18,1,0)+IF(AE20=$I$20,3,0)+IF(AE21=$G20+$H20,1,0)+IF(AE22=$I$22,3,0)+IF(AE23=$G22+$H22,1,0)+IF(AE24=$I$24,3,0)+IF(AE25=$G24+$H24,1,0)+IF(AE26=$I$26,3,0)+IF(AE27=$G26+$H26,1,0)+IF(AE28=$I$28,3,0)+IF(AE29=$G28+$H28,1,0)+IF(AE30=$I$30,3,0)+IF(AE31=$G30+$H30,1,0)+IF(AE32=$I$32,3,0)+IF(AE33=$G32+$H32,1,0)+IF(AE34=$I$34,3,0)+IF(AE35=$G34+$H34,1,0)+IF(AE36=$I$36,3,0)+IF(AE37=$G36+$H36,1,0)+IF(AE38=$I$38,3,0)+IF(AE39=$G38+$H38,1,0)+IF(AE40=$I$40,3,0)+IF(AE41=$G40+$H40,1,0)+IF(AE42=$I$42,3,0)+IF(AE43=$G42+$H42,1,0)+IF(AE44=$I$44,3,0)+IF(AE45=$G44+$H44,1,0)+IF(AE46=$I$46,3,0)+IF(AE47=$G46+$H46,1,0)+IF(AE48=$I$48,3,0)+IF(AE49=$G48+$H48,1,0)+IF(AE50=$I$50,3,0)+IF(AE51=$G50+$H50,1,0)+IF(AE52=$I$52,3,0)+IF(AE53=$G52+$H52,1,0)+IF(AE54=$I$54,3,0)+IF(AE55=$G54+$H54,1,0)+IF(AE56=$I$56,3,0)+IF(AE57=$G56+$H56,1,0)+IF(AE58=$I$58,3,0)+IF(AE59=$G58+$H58,1,0)+IF(AE60=$I$60,3,0)+IF(AE61=$G60+$H60,1,0)+IF(AE62=$I$62,3,0)+IF(AE63=$G62+$H62,1,0)+IF(AE64=$I$64,3,0)+IF(AE65=$G64+$H64,1,0)+IF(AE66=$I$66,3,0)+IF(AE67=$G66+$H66,1,0)+IF(AE68=$I$68,3,0)+IF(AE69=$G68+$H68,1,0)+IF(AE70=$I$70,3,0)+IF(AE71=$G70+$H70,1,0)+IF(AE72=$I$72,3,0)+IF(AE73=$G72+$H72,1,0)+IF(AE74=$I$74,3,0)+IF(AE75=$G74+$H74,1,0)+IF(AE76=$I$76,3,0)+IF(AE77=$G76+$H76,1,0)+IF(AE78=$I$78,3,0)+IF(AE79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="AF4" s="73">
-        <f>SUM(IF(AF8=$I$8,3,0)+IF(AF9=$G8+$H8,1,0)+IF(AF10=$I$10,3,0)+IF(AF11=$G10+$H10,1,0)+IF(AF12=$I$12,3,0)+IF(AF13=$G12+$H12,1,0)+IF(AF14=$I$14,3,0)+IF(AF15=$G14+$H14,1,0)
-+IF(AF16=$I$16,3,0)+IF(AF17=$G16+$H16,1,0)+IF(AF18=$I$18,3,0)+IF(AF19=$G18+$H18,1,0)+IF(AF20=$I$20,3,0)+IF(AF21=$G20+$H20,1,0)+IF(AF22=$I$22,3,0)+IF(AF23=$G22+$H22,1,0)+IF(AF24=$I$24,3,0)+IF(AF25=$G24+$H24,1,0)+IF(AF26=$I$26,3,0)+IF(AF27=$G26+$H26,1,0)+IF(AF28=$I$28,3,0)+IF(AF29=$G28+$H28,1,0)+IF(AF30=$I$30,3,0)+IF(AF31=$G30+$H30,1,0)+IF(AF32=$I$32,3,0)+IF(AF33=$G32+$H32,1,0)+IF(AF34=$I$34,3,0)+IF(AF35=$G34+$H34,1,0)+IF(AF36=$I$36,3,0)+IF(AF37=$G36+$H36,1,0)+IF(AF38=$I$38,3,0)+IF(AF39=$G38+$H38,1,0)+IF(AF40=$I$40,3,0)+IF(AF41=$G40+$H40,1,0)+IF(AF42=$I$42,3,0)+IF(AF43=$G42+$H42,1,0)+IF(AF44=$I$44,3,0)+IF(AF45=$G44+$H44,1,0)+IF(AF46=$I$46,3,0)+IF(AF47=$G46+$H46,1,0)+IF(AF48=$I$48,3,0)+IF(AF49=$G48+$H48,1,0)+IF(AF50=$I$50,3,0)+IF(AF51=$G50+$H50,1,0)+IF(AF52=$I$52,3,0)+IF(AF53=$G52+$H52,1,0)+IF(AF54=$I$54,3,0)+IF(AF55=$G54+$H54,1,0)+IF(AF56=$I$56,3,0)+IF(AF57=$G56+$H56,1,0)+IF(AF58=$I$58,3,0)+IF(AF59=$G58+$H58,1,0)+IF(AF60=$I$60,3,0)+IF(AF61=$G60+$H60,1,0)+IF(AF62=$I$62,3,0)+IF(AF63=$G62+$H62,1,0)+IF(AF64=$I$64,3,0)+IF(AF65=$G64+$H64,1,0)+IF(AF66=$I$66,3,0)+IF(AF67=$G66+$H66,1,0)+IF(AF68=$I$68,3,0)+IF(AF69=$G68+$H68,1,0)+IF(AF70=$I$70,3,0)+IF(AF71=$G70+$H70,1,0)+IF(AF72=$I$72,3,0)+IF(AF73=$G72+$H72,1,0)+IF(AF74=$I$74,3,0)+IF(AF75=$G74+$H74,1,0)+IF(AF76=$I$76,3,0)+IF(AF77=$G76+$H76,1,0)+IF(AF78=$I$78,3,0)+IF(AF79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="AG4" s="73">
-        <f>SUM(IF(AG8=$I$8,3,0)+IF(AG9=$G8+$H8,1,0)+IF(AG10=$I$10,3,0)+IF(AG11=$G10+$H10,1,0)+IF(AG12=$I$12,3,0)+IF(AG13=$G12+$H12,1,0)+IF(AG14=$I$14,3,0)+IF(AG15=$G14+$H14,1,0)
-+IF(AG16=$I$16,3,0)+IF(AG17=$G16+$H16,1,0)+IF(AG18=$I$18,3,0)+IF(AG19=$G18+$H18,1,0)+IF(AG20=$I$20,3,0)+IF(AG21=$G20+$H20,1,0)+IF(AG22=$I$22,3,0)+IF(AG23=$G22+$H22,1,0)+IF(AG24=$I$24,3,0)+IF(AG25=$G24+$H24,1,0)+IF(AG26=$I$26,3,0)+IF(AG27=$G26+$H26,1,0)+IF(AG28=$I$28,3,0)+IF(AG29=$G28+$H28,1,0)+IF(AG30=$I$30,3,0)+IF(AG31=$G30+$H30,1,0)+IF(AG32=$I$32,3,0)+IF(AG33=$G32+$H32,1,0)+IF(AG34=$I$34,3,0)+IF(AG35=$G34+$H34,1,0)+IF(AG36=$I$36,3,0)+IF(AG37=$G36+$H36,1,0)+IF(AG38=$I$38,3,0)+IF(AG39=$G38+$H38,1,0)+IF(AG40=$I$40,3,0)+IF(AG41=$G40+$H40,1,0)+IF(AG42=$I$42,3,0)+IF(AG43=$G42+$H42,1,0)+IF(AG44=$I$44,3,0)+IF(AG45=$G44+$H44,1,0)+IF(AG46=$I$46,3,0)+IF(AG47=$G46+$H46,1,0)+IF(AG48=$I$48,3,0)+IF(AG49=$G48+$H48,1,0)+IF(AG50=$I$50,3,0)+IF(AG51=$G50+$H50,1,0)+IF(AG52=$I$52,3,0)+IF(AG53=$G52+$H52,1,0)+IF(AG54=$I$54,3,0)+IF(AG55=$G54+$H54,1,0)+IF(AG56=$I$56,3,0)+IF(AG57=$G56+$H56,1,0)+IF(AG58=$I$58,3,0)+IF(AG59=$G58+$H58,1,0)+IF(AG60=$I$60,3,0)+IF(AG61=$G60+$H60,1,0)+IF(AG62=$I$62,3,0)+IF(AG63=$G62+$H62,1,0)+IF(AG64=$I$64,3,0)+IF(AG65=$G64+$H64,1,0)+IF(AG66=$I$66,3,0)+IF(AG67=$G66+$H66,1,0)+IF(AG68=$I$68,3,0)+IF(AG69=$G68+$H68,1,0)+IF(AG70=$I$70,3,0)+IF(AG71=$G70+$H70,1,0)+IF(AG72=$I$72,3,0)+IF(AG73=$G72+$H72,1,0)+IF(AG74=$I$74,3,0)+IF(AG75=$G74+$H74,1,0)+IF(AG76=$I$76,3,0)+IF(AG77=$G76+$H76,1,0)+IF(AG78=$I$78,3,0)+IF(AG79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="AH4" s="73">
-        <f>SUM(IF(AH8=$I$8,3,0)+IF(AH9=$G8+$H8,1,0)+IF(AH10=$I$10,3,0)+IF(AH11=$G10+$H10,1,0)+IF(AH12=$I$12,3,0)+IF(AH13=$G12+$H12,1,0)+IF(AH14=$I$14,3,0)+IF(AH15=$G14+$H14,1,0)
-+IF(AH16=$I$16,3,0)+IF(AH17=$G16+$H16,1,0)+IF(AH18=$I$18,3,0)+IF(AH19=$G18+$H18,1,0)+IF(AH20=$I$20,3,0)+IF(AH21=$G20+$H20,1,0)+IF(AH22=$I$22,3,0)+IF(AH23=$G22+$H22,1,0)+IF(AH24=$I$24,3,0)+IF(AH25=$G24+$H24,1,0)+IF(AH26=$I$26,3,0)+IF(AH27=$G26+$H26,1,0)+IF(AH28=$I$28,3,0)+IF(AH29=$G28+$H28,1,0)+IF(AH30=$I$30,3,0)+IF(AH31=$G30+$H30,1,0)+IF(AH32=$I$32,3,0)+IF(AH33=$G32+$H32,1,0)+IF(AH34=$I$34,3,0)+IF(AH35=$G34+$H34,1,0)+IF(AH36=$I$36,3,0)+IF(AH37=$G36+$H36,1,0)+IF(AH38=$I$38,3,0)+IF(AH39=$G38+$H38,1,0)+IF(AH40=$I$40,3,0)+IF(AH41=$G40+$H40,1,0)+IF(AH42=$I$42,3,0)+IF(AH43=$G42+$H42,1,0)+IF(AH44=$I$44,3,0)+IF(AH45=$G44+$H44,1,0)+IF(AH46=$I$46,3,0)+IF(AH47=$G46+$H46,1,0)+IF(AH48=$I$48,3,0)+IF(AH49=$G48+$H48,1,0)+IF(AH50=$I$50,3,0)+IF(AH51=$G50+$H50,1,0)+IF(AH52=$I$52,3,0)+IF(AH53=$G52+$H52,1,0)+IF(AH54=$I$54,3,0)+IF(AH55=$G54+$H54,1,0)+IF(AH56=$I$56,3,0)+IF(AH57=$G56+$H56,1,0)+IF(AH58=$I$58,3,0)+IF(AH59=$G58+$H58,1,0)+IF(AH60=$I$60,3,0)+IF(AH61=$G60+$H60,1,0)+IF(AH62=$I$62,3,0)+IF(AH63=$G62+$H62,1,0)+IF(AH64=$I$64,3,0)+IF(AH65=$G64+$H64,1,0)+IF(AH66=$I$66,3,0)+IF(AH67=$G66+$H66,1,0)+IF(AH68=$I$68,3,0)+IF(AH69=$G68+$H68,1,0)+IF(AH70=$I$70,3,0)+IF(AH71=$G70+$H70,1,0)+IF(AH72=$I$72,3,0)+IF(AH73=$G72+$H72,1,0)+IF(AH74=$I$74,3,0)+IF(AH75=$G74+$H74,1,0)+IF(AH76=$I$76,3,0)+IF(AH77=$G76+$H76,1,0)+IF(AH78=$I$78,3,0)+IF(AH79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="AI4" s="73">
-        <f>SUM(IF(AI8=$I$8,3,0)+IF(AI9=$G8+$H8,1,0)+IF(AI10=$I$10,3,0)+IF(AI11=$G10+$H10,1,0)+IF(AI12=$I$12,3,0)+IF(AI13=$G12+$H12,1,0)+IF(AI14=$I$14,3,0)+IF(AI15=$G14+$H14,1,0)
-+IF(AI16=$I$16,3,0)+IF(AI17=$G16+$H16,1,0)+IF(AI18=$I$18,3,0)+IF(AI19=$G18+$H18,1,0)+IF(AI20=$I$20,3,0)+IF(AI21=$G20+$H20,1,0)+IF(AI22=$I$22,3,0)+IF(AI23=$G22+$H22,1,0)+IF(AI24=$I$24,3,0)+IF(AI25=$G24+$H24,1,0)+IF(AI26=$I$26,3,0)+IF(AI27=$G26+$H26,1,0)+IF(AI28=$I$28,3,0)+IF(AI29=$G28+$H28,1,0)+IF(AI30=$I$30,3,0)+IF(AI31=$G30+$H30,1,0)+IF(AI32=$I$32,3,0)+IF(AI33=$G32+$H32,1,0)+IF(AI34=$I$34,3,0)+IF(AI35=$G34+$H34,1,0)+IF(AI36=$I$36,3,0)+IF(AI37=$G36+$H36,1,0)+IF(AI38=$I$38,3,0)+IF(AI39=$G38+$H38,1,0)+IF(AI40=$I$40,3,0)+IF(AI41=$G40+$H40,1,0)+IF(AI42=$I$42,3,0)+IF(AI43=$G42+$H42,1,0)+IF(AI44=$I$44,3,0)+IF(AI45=$G44+$H44,1,0)+IF(AI46=$I$46,3,0)+IF(AI47=$G46+$H46,1,0)+IF(AI48=$I$48,3,0)+IF(AI49=$G48+$H48,1,0)+IF(AI50=$I$50,3,0)+IF(AI51=$G50+$H50,1,0)+IF(AI52=$I$52,3,0)+IF(AI53=$G52+$H52,1,0)+IF(AI54=$I$54,3,0)+IF(AI55=$G54+$H54,1,0)+IF(AI56=$I$56,3,0)+IF(AI57=$G56+$H56,1,0)+IF(AI58=$I$58,3,0)+IF(AI59=$G58+$H58,1,0)+IF(AI60=$I$60,3,0)+IF(AI61=$G60+$H60,1,0)+IF(AI62=$I$62,3,0)+IF(AI63=$G62+$H62,1,0)+IF(AI64=$I$64,3,0)+IF(AI65=$G64+$H64,1,0)+IF(AI66=$I$66,3,0)+IF(AI67=$G66+$H66,1,0)+IF(AI68=$I$68,3,0)+IF(AI69=$G68+$H68,1,0)+IF(AI70=$I$70,3,0)+IF(AI71=$G70+$H70,1,0)+IF(AI72=$I$72,3,0)+IF(AI73=$G72+$H72,1,0)+IF(AI74=$I$74,3,0)+IF(AI75=$G74+$H74,1,0)+IF(AI76=$I$76,3,0)+IF(AI77=$G76+$H76,1,0)+IF(AI78=$I$78,3,0)+IF(AI79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="AJ4" s="73">
-        <f>SUM(IF(AJ8=$I$8,3,0)+IF(AJ9=$G8+$H8,1,0)+IF(AJ10=$I$10,3,0)+IF(AJ11=$G10+$H10,1,0)+IF(AJ12=$I$12,3,0)+IF(AJ13=$G12+$H12,1,0)+IF(AJ14=$I$14,3,0)+IF(AJ15=$G14+$H14,1,0)
-+IF(AJ16=$I$16,3,0)+IF(AJ17=$G16+$H16,1,0)+IF(AJ18=$I$18,3,0)+IF(AJ19=$G18+$H18,1,0)+IF(AJ20=$I$20,3,0)+IF(AJ21=$G20+$H20,1,0)+IF(AJ22=$I$22,3,0)+IF(AJ23=$G22+$H22,1,0)+IF(AJ24=$I$24,3,0)+IF(AJ25=$G24+$H24,1,0)+IF(AJ26=$I$26,3,0)+IF(AJ27=$G26+$H26,1,0)+IF(AJ28=$I$28,3,0)+IF(AJ29=$G28+$H28,1,0)+IF(AJ30=$I$30,3,0)+IF(AJ31=$G30+$H30,1,0)+IF(AJ32=$I$32,3,0)+IF(AJ33=$G32+$H32,1,0)+IF(AJ34=$I$34,3,0)+IF(AJ35=$G34+$H34,1,0)+IF(AJ36=$I$36,3,0)+IF(AJ37=$G36+$H36,1,0)+IF(AJ38=$I$38,3,0)+IF(AJ39=$G38+$H38,1,0)+IF(AJ40=$I$40,3,0)+IF(AJ41=$G40+$H40,1,0)+IF(AJ42=$I$42,3,0)+IF(AJ43=$G42+$H42,1,0)+IF(AJ44=$I$44,3,0)+IF(AJ45=$G44+$H44,1,0)+IF(AJ46=$I$46,3,0)+IF(AJ47=$G46+$H46,1,0)+IF(AJ48=$I$48,3,0)+IF(AJ49=$G48+$H48,1,0)+IF(AJ50=$I$50,3,0)+IF(AJ51=$G50+$H50,1,0)+IF(AJ52=$I$52,3,0)+IF(AJ53=$G52+$H52,1,0)+IF(AJ54=$I$54,3,0)+IF(AJ55=$G54+$H54,1,0)+IF(AJ56=$I$56,3,0)+IF(AJ57=$G56+$H56,1,0)+IF(AJ58=$I$58,3,0)+IF(AJ59=$G58+$H58,1,0)+IF(AJ60=$I$60,3,0)+IF(AJ61=$G60+$H60,1,0)+IF(AJ62=$I$62,3,0)+IF(AJ63=$G62+$H62,1,0)+IF(AJ64=$I$64,3,0)+IF(AJ65=$G64+$H64,1,0)+IF(AJ66=$I$66,3,0)+IF(AJ67=$G66+$H66,1,0)+IF(AJ68=$I$68,3,0)+IF(AJ69=$G68+$H68,1,0)+IF(AJ70=$I$70,3,0)+IF(AJ71=$G70+$H70,1,0)+IF(AJ72=$I$72,3,0)+IF(AJ73=$G72+$H72,1,0)+IF(AJ74=$I$74,3,0)+IF(AJ75=$G74+$H74,1,0)+IF(AJ76=$I$76,3,0)+IF(AJ77=$G76+$H76,1,0)+IF(AJ78=$I$78,3,0)+IF(AJ79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="AK4" s="73">
-        <f>SUM(IF(AK8=$I$8,3,0)+IF(AK9=$G8+$H8,1,0)+IF(AK10=$I$10,3,0)+IF(AK11=$G10+$H10,1,0)+IF(AK12=$I$12,3,0)+IF(AK13=$G12+$H12,1,0)+IF(AK14=$I$14,3,0)+IF(AK15=$G14+$H14,1,0)
-+IF(AK16=$I$16,3,0)+IF(AK17=$G16+$H16,1,0)+IF(AK18=$I$18,3,0)+IF(AK19=$G18+$H18,1,0)+IF(AK20=$I$20,3,0)+IF(AK21=$G20+$H20,1,0)+IF(AK22=$I$22,3,0)+IF(AK23=$G22+$H22,1,0)+IF(AK24=$I$24,3,0)+IF(AK25=$G24+$H24,1,0)+IF(AK26=$I$26,3,0)+IF(AK27=$G26+$H26,1,0)+IF(AK28=$I$28,3,0)+IF(AK29=$G28+$H28,1,0)+IF(AK30=$I$30,3,0)+IF(AK31=$G30+$H30,1,0)+IF(AK32=$I$32,3,0)+IF(AK33=$G32+$H32,1,0)+IF(AK34=$I$34,3,0)+IF(AK35=$G34+$H34,1,0)+IF(AK36=$I$36,3,0)+IF(AK37=$G36+$H36,1,0)+IF(AK38=$I$38,3,0)+IF(AK39=$G38+$H38,1,0)+IF(AK40=$I$40,3,0)+IF(AK41=$G40+$H40,1,0)+IF(AK42=$I$42,3,0)+IF(AK43=$G42+$H42,1,0)+IF(AK44=$I$44,3,0)+IF(AK45=$G44+$H44,1,0)+IF(AK46=$I$46,3,0)+IF(AK47=$G46+$H46,1,0)+IF(AK48=$I$48,3,0)+IF(AK49=$G48+$H48,1,0)+IF(AK50=$I$50,3,0)+IF(AK51=$G50+$H50,1,0)+IF(AK52=$I$52,3,0)+IF(AK53=$G52+$H52,1,0)+IF(AK54=$I$54,3,0)+IF(AK55=$G54+$H54,1,0)+IF(AK56=$I$56,3,0)+IF(AK57=$G56+$H56,1,0)+IF(AK58=$I$58,3,0)+IF(AK59=$G58+$H58,1,0)+IF(AK60=$I$60,3,0)+IF(AK61=$G60+$H60,1,0)+IF(AK62=$I$62,3,0)+IF(AK63=$G62+$H62,1,0)+IF(AK64=$I$64,3,0)+IF(AK65=$G64+$H64,1,0)+IF(AK66=$I$66,3,0)+IF(AK67=$G66+$H66,1,0)+IF(AK68=$I$68,3,0)+IF(AK69=$G68+$H68,1,0)+IF(AK70=$I$70,3,0)+IF(AK71=$G70+$H70,1,0)+IF(AK72=$I$72,3,0)+IF(AK73=$G72+$H72,1,0)+IF(AK74=$I$74,3,0)+IF(AK75=$G74+$H74,1,0)+IF(AK76=$I$76,3,0)+IF(AK77=$G76+$H76,1,0)+IF(AK78=$I$78,3,0)+IF(AK79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="AL4" s="73">
-        <f>SUM(IF(AL8=$I$8,3,0)+IF(AL9=$G8+$H8,1,0)+IF(AL10=$I$10,3,0)+IF(AL11=$G10+$H10,1,0)+IF(AL12=$I$12,3,0)+IF(AL13=$G12+$H12,1,0)+IF(AL14=$I$14,3,0)+IF(AL15=$G14+$H14,1,0)
-+IF(AL16=$I$16,3,0)+IF(AL17=$G16+$H16,1,0)+IF(AL18=$I$18,3,0)+IF(AL19=$G18+$H18,1,0)+IF(AL20=$I$20,3,0)+IF(AL21=$G20+$H20,1,0)+IF(AL22=$I$22,3,0)+IF(AL23=$G22+$H22,1,0)+IF(AL24=$I$24,3,0)+IF(AL25=$G24+$H24,1,0)+IF(AL26=$I$26,3,0)+IF(AL27=$G26+$H26,1,0)+IF(AL28=$I$28,3,0)+IF(AL29=$G28+$H28,1,0)+IF(AL30=$I$30,3,0)+IF(AL31=$G30+$H30,1,0)+IF(AL32=$I$32,3,0)+IF(AL33=$G32+$H32,1,0)+IF(AL34=$I$34,3,0)+IF(AL35=$G34+$H34,1,0)+IF(AL36=$I$36,3,0)+IF(AL37=$G36+$H36,1,0)+IF(AL38=$I$38,3,0)+IF(AL39=$G38+$H38,1,0)+IF(AL40=$I$40,3,0)+IF(AL41=$G40+$H40,1,0)+IF(AL42=$I$42,3,0)+IF(AL43=$G42+$H42,1,0)+IF(AL44=$I$44,3,0)+IF(AL45=$G44+$H44,1,0)+IF(AL46=$I$46,3,0)+IF(AL47=$G46+$H46,1,0)+IF(AL48=$I$48,3,0)+IF(AL49=$G48+$H48,1,0)+IF(AL50=$I$50,3,0)+IF(AL51=$G50+$H50,1,0)+IF(AL52=$I$52,3,0)+IF(AL53=$G52+$H52,1,0)+IF(AL54=$I$54,3,0)+IF(AL55=$G54+$H54,1,0)+IF(AL56=$I$56,3,0)+IF(AL57=$G56+$H56,1,0)+IF(AL58=$I$58,3,0)+IF(AL59=$G58+$H58,1,0)+IF(AL60=$I$60,3,0)+IF(AL61=$G60+$H60,1,0)+IF(AL62=$I$62,3,0)+IF(AL63=$G62+$H62,1,0)+IF(AL64=$I$64,3,0)+IF(AL65=$G64+$H64,1,0)+IF(AL66=$I$66,3,0)+IF(AL67=$G66+$H66,1,0)+IF(AL68=$I$68,3,0)+IF(AL69=$G68+$H68,1,0)+IF(AL70=$I$70,3,0)+IF(AL71=$G70+$H70,1,0)+IF(AL72=$I$72,3,0)+IF(AL73=$G72+$H72,1,0)+IF(AL74=$I$74,3,0)+IF(AL75=$G74+$H74,1,0)+IF(AL76=$I$76,3,0)+IF(AL77=$G76+$H76,1,0)+IF(AL78=$I$78,3,0)+IF(AL79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="AM4" s="73">
-        <f>SUM(IF(AM8=$I$8,3,0)+IF(AM9=$G8+$H8,1,0)+IF(AM10=$I$10,3,0)+IF(AM11=$G10+$H10,1,0)+IF(AM12=$I$12,3,0)+IF(AM13=$G12+$H12,1,0)+IF(AM14=$I$14,3,0)+IF(AM15=$G14+$H14,1,0)
-+IF(AM16=$I$16,3,0)+IF(AM17=$G16+$H16,1,0)+IF(AM18=$I$18,3,0)+IF(AM19=$G18+$H18,1,0)+IF(AM20=$I$20,3,0)+IF(AM21=$G20+$H20,1,0)+IF(AM22=$I$22,3,0)+IF(AM23=$G22+$H22,1,0)+IF(AM24=$I$24,3,0)+IF(AM25=$G24+$H24,1,0)+IF(AM26=$I$26,3,0)+IF(AM27=$G26+$H26,1,0)+IF(AM28=$I$28,3,0)+IF(AM29=$G28+$H28,1,0)+IF(AM30=$I$30,3,0)+IF(AM31=$G30+$H30,1,0)+IF(AM32=$I$32,3,0)+IF(AM33=$G32+$H32,1,0)+IF(AM34=$I$34,3,0)+IF(AM35=$G34+$H34,1,0)+IF(AM36=$I$36,3,0)+IF(AM37=$G36+$H36,1,0)+IF(AM38=$I$38,3,0)+IF(AM39=$G38+$H38,1,0)+IF(AM40=$I$40,3,0)+IF(AM41=$G40+$H40,1,0)+IF(AM42=$I$42,3,0)+IF(AM43=$G42+$H42,1,0)+IF(AM44=$I$44,3,0)+IF(AM45=$G44+$H44,1,0)+IF(AM46=$I$46,3,0)+IF(AM47=$G46+$H46,1,0)+IF(AM48=$I$48,3,0)+IF(AM49=$G48+$H48,1,0)+IF(AM50=$I$50,3,0)+IF(AM51=$G50+$H50,1,0)+IF(AM52=$I$52,3,0)+IF(AM53=$G52+$H52,1,0)+IF(AM54=$I$54,3,0)+IF(AM55=$G54+$H54,1,0)+IF(AM56=$I$56,3,0)+IF(AM57=$G56+$H56,1,0)+IF(AM58=$I$58,3,0)+IF(AM59=$G58+$H58,1,0)+IF(AM60=$I$60,3,0)+IF(AM61=$G60+$H60,1,0)+IF(AM62=$I$62,3,0)+IF(AM63=$G62+$H62,1,0)+IF(AM64=$I$64,3,0)+IF(AM65=$G64+$H64,1,0)+IF(AM66=$I$66,3,0)+IF(AM67=$G66+$H66,1,0)+IF(AM68=$I$68,3,0)+IF(AM69=$G68+$H68,1,0)+IF(AM70=$I$70,3,0)+IF(AM71=$G70+$H70,1,0)+IF(AM72=$I$72,3,0)+IF(AM73=$G72+$H72,1,0)+IF(AM74=$I$74,3,0)+IF(AM75=$G74+$H74,1,0)+IF(AM76=$I$76,3,0)+IF(AM77=$G76+$H76,1,0)+IF(AM78=$I$78,3,0)+IF(AM79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="AN4" s="73">
-        <f>SUM(IF(AN8=$I$8,3,0)+IF(AN9=$G8+$H8,1,0)+IF(AN10=$I$10,3,0)+IF(AN11=$G10+$H10,1,0)+IF(AN12=$I$12,3,0)+IF(AN13=$G12+$H12,1,0)+IF(AN14=$I$14,3,0)+IF(AN15=$G14+$H14,1,0)
-+IF(AN16=$I$16,3,0)+IF(AN17=$G16+$H16,1,0)+IF(AN18=$I$18,3,0)+IF(AN19=$G18+$H18,1,0)+IF(AN20=$I$20,3,0)+IF(AN21=$G20+$H20,1,0)+IF(AN22=$I$22,3,0)+IF(AN23=$G22+$H22,1,0)+IF(AN24=$I$24,3,0)+IF(AN25=$G24+$H24,1,0)+IF(AN26=$I$26,3,0)+IF(AN27=$G26+$H26,1,0)+IF(AN28=$I$28,3,0)+IF(AN29=$G28+$H28,1,0)+IF(AN30=$I$30,3,0)+IF(AN31=$G30+$H30,1,0)+IF(AN32=$I$32,3,0)+IF(AN33=$G32+$H32,1,0)+IF(AN34=$I$34,3,0)+IF(AN35=$G34+$H34,1,0)+IF(AN36=$I$36,3,0)+IF(AN37=$G36+$H36,1,0)+IF(AN38=$I$38,3,0)+IF(AN39=$G38+$H38,1,0)+IF(AN40=$I$40,3,0)+IF(AN41=$G40+$H40,1,0)+IF(AN42=$I$42,3,0)+IF(AN43=$G42+$H42,1,0)+IF(AN44=$I$44,3,0)+IF(AN45=$G44+$H44,1,0)+IF(AN46=$I$46,3,0)+IF(AN47=$G46+$H46,1,0)+IF(AN48=$I$48,3,0)+IF(AN49=$G48+$H48,1,0)+IF(AN50=$I$50,3,0)+IF(AN51=$G50+$H50,1,0)+IF(AN52=$I$52,3,0)+IF(AN53=$G52+$H52,1,0)+IF(AN54=$I$54,3,0)+IF(AN55=$G54+$H54,1,0)+IF(AN56=$I$56,3,0)+IF(AN57=$G56+$H56,1,0)+IF(AN58=$I$58,3,0)+IF(AN59=$G58+$H58,1,0)+IF(AN60=$I$60,3,0)+IF(AN61=$G60+$H60,1,0)+IF(AN62=$I$62,3,0)+IF(AN63=$G62+$H62,1,0)+IF(AN64=$I$64,3,0)+IF(AN65=$G64+$H64,1,0)+IF(AN66=$I$66,3,0)+IF(AN67=$G66+$H66,1,0)+IF(AN68=$I$68,3,0)+IF(AN69=$G68+$H68,1,0)+IF(AN70=$I$70,3,0)+IF(AN71=$G70+$H70,1,0)+IF(AN72=$I$72,3,0)+IF(AN73=$G72+$H72,1,0)+IF(AN74=$I$74,3,0)+IF(AN75=$G74+$H74,1,0)+IF(AN76=$I$76,3,0)+IF(AN77=$G76+$H76,1,0)+IF(AN78=$I$78,3,0)+IF(AN79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="AO4" s="73">
-        <f>SUM(IF(AO8=$I$8,3,0)+IF(AO9=$G8+$H8,1,0)+IF(AO10=$I$10,3,0)+IF(AO11=$G10+$H10,1,0)+IF(AO12=$I$12,3,0)+IF(AO13=$G12+$H12,1,0)+IF(AO14=$I$14,3,0)+IF(AO15=$G14+$H14,1,0)
-+IF(AO16=$I$16,3,0)+IF(AO17=$G16+$H16,1,0)+IF(AO18=$I$18,3,0)+IF(AO19=$G18+$H18,1,0)+IF(AO20=$I$20,3,0)+IF(AO21=$G20+$H20,1,0)+IF(AO22=$I$22,3,0)+IF(AO23=$G22+$H22,1,0)+IF(AO24=$I$24,3,0)+IF(AO25=$G24+$H24,1,0)+IF(AO26=$I$26,3,0)+IF(AO27=$G26+$H26,1,0)+IF(AO28=$I$28,3,0)+IF(AO29=$G28+$H28,1,0)+IF(AO30=$I$30,3,0)+IF(AO31=$G30+$H30,1,0)+IF(AO32=$I$32,3,0)+IF(AO33=$G32+$H32,1,0)+IF(AO34=$I$34,3,0)+IF(AO35=$G34+$H34,1,0)+IF(AO36=$I$36,3,0)+IF(AO37=$G36+$H36,1,0)+IF(AO38=$I$38,3,0)+IF(AO39=$G38+$H38,1,0)+IF(AO40=$I$40,3,0)+IF(AO41=$G40+$H40,1,0)+IF(AO42=$I$42,3,0)+IF(AO43=$G42+$H42,1,0)+IF(AO44=$I$44,3,0)+IF(AO45=$G44+$H44,1,0)+IF(AO46=$I$46,3,0)+IF(AO47=$G46+$H46,1,0)+IF(AO48=$I$48,3,0)+IF(AO49=$G48+$H48,1,0)+IF(AO50=$I$50,3,0)+IF(AO51=$G50+$H50,1,0)+IF(AO52=$I$52,3,0)+IF(AO53=$G52+$H52,1,0)+IF(AO54=$I$54,3,0)+IF(AO55=$G54+$H54,1,0)+IF(AO56=$I$56,3,0)+IF(AO57=$G56+$H56,1,0)+IF(AO58=$I$58,3,0)+IF(AO59=$G58+$H58,1,0)+IF(AO60=$I$60,3,0)+IF(AO61=$G60+$H60,1,0)+IF(AO62=$I$62,3,0)+IF(AO63=$G62+$H62,1,0)+IF(AO64=$I$64,3,0)+IF(AO65=$G64+$H64,1,0)+IF(AO66=$I$66,3,0)+IF(AO67=$G66+$H66,1,0)+IF(AO68=$I$68,3,0)+IF(AO69=$G68+$H68,1,0)+IF(AO70=$I$70,3,0)+IF(AO71=$G70+$H70,1,0)+IF(AO72=$I$72,3,0)+IF(AO73=$G72+$H72,1,0)+IF(AO74=$I$74,3,0)+IF(AO75=$G74+$H74,1,0)+IF(AO76=$I$76,3,0)+IF(AO77=$G76+$H76,1,0)+IF(AO78=$I$78,3,0)+IF(AO79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="AP4" s="73">
-        <f>SUM(IF(AP8=$I$8,3,0)+IF(AP9=$G8+$H8,1,0)+IF(AP10=$I$10,3,0)+IF(AP11=$G10+$H10,1,0)+IF(AP12=$I$12,3,0)+IF(AP13=$G12+$H12,1,0)+IF(AP14=$I$14,3,0)+IF(AP15=$G14+$H14,1,0)
-+IF(AP16=$I$16,3,0)+IF(AP17=$G16+$H16,1,0)+IF(AP18=$I$18,3,0)+IF(AP19=$G18+$H18,1,0)+IF(AP20=$I$20,3,0)+IF(AP21=$G20+$H20,1,0)+IF(AP22=$I$22,3,0)+IF(AP23=$G22+$H22,1,0)+IF(AP24=$I$24,3,0)+IF(AP25=$G24+$H24,1,0)+IF(AP26=$I$26,3,0)+IF(AP27=$G26+$H26,1,0)+IF(AP28=$I$28,3,0)+IF(AP29=$G28+$H28,1,0)+IF(AP30=$I$30,3,0)+IF(AP31=$G30+$H30,1,0)+IF(AP32=$I$32,3,0)+IF(AP33=$G32+$H32,1,0)+IF(AP34=$I$34,3,0)+IF(AP35=$G34+$H34,1,0)+IF(AP36=$I$36,3,0)+IF(AP37=$G36+$H36,1,0)+IF(AP38=$I$38,3,0)+IF(AP39=$G38+$H38,1,0)+IF(AP40=$I$40,3,0)+IF(AP41=$G40+$H40,1,0)+IF(AP42=$I$42,3,0)+IF(AP43=$G42+$H42,1,0)+IF(AP44=$I$44,3,0)+IF(AP45=$G44+$H44,1,0)+IF(AP46=$I$46,3,0)+IF(AP47=$G46+$H46,1,0)+IF(AP48=$I$48,3,0)+IF(AP49=$G48+$H48,1,0)+IF(AP50=$I$50,3,0)+IF(AP51=$G50+$H50,1,0)+IF(AP52=$I$52,3,0)+IF(AP53=$G52+$H52,1,0)+IF(AP54=$I$54,3,0)+IF(AP55=$G54+$H54,1,0)+IF(AP56=$I$56,3,0)+IF(AP57=$G56+$H56,1,0)+IF(AP58=$I$58,3,0)+IF(AP59=$G58+$H58,1,0)+IF(AP60=$I$60,3,0)+IF(AP61=$G60+$H60,1,0)+IF(AP62=$I$62,3,0)+IF(AP63=$G62+$H62,1,0)+IF(AP64=$I$64,3,0)+IF(AP65=$G64+$H64,1,0)+IF(AP66=$I$66,3,0)+IF(AP67=$G66+$H66,1,0)+IF(AP68=$I$68,3,0)+IF(AP69=$G68+$H68,1,0)+IF(AP70=$I$70,3,0)+IF(AP71=$G70+$H70,1,0)+IF(AP72=$I$72,3,0)+IF(AP73=$G72+$H72,1,0)+IF(AP74=$I$74,3,0)+IF(AP75=$G74+$H74,1,0)+IF(AP76=$I$76,3,0)+IF(AP77=$G76+$H76,1,0)+IF(AP78=$I$78,3,0)+IF(AP79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="AQ4" s="73">
-        <f>SUM(IF(AQ8=$I$8,3,0)+IF(AQ9=$G8+$H8,1,0)+IF(AQ10=$I$10,3,0)+IF(AQ11=$G10+$H10,1,0)+IF(AQ12=$I$12,3,0)+IF(AQ13=$G12+$H12,1,0)+IF(AQ14=$I$14,3,0)+IF(AQ15=$G14+$H14,1,0)
-+IF(AQ16=$I$16,3,0)+IF(AQ17=$G16+$H16,1,0)+IF(AQ18=$I$18,3,0)+IF(AQ19=$G18+$H18,1,0)+IF(AQ20=$I$20,3,0)+IF(AQ21=$G20+$H20,1,0)+IF(AQ22=$I$22,3,0)+IF(AQ23=$G22+$H22,1,0)+IF(AQ24=$I$24,3,0)+IF(AQ25=$G24+$H24,1,0)+IF(AQ26=$I$26,3,0)+IF(AQ27=$G26+$H26,1,0)+IF(AQ28=$I$28,3,0)+IF(AQ29=$G28+$H28,1,0)+IF(AQ30=$I$30,3,0)+IF(AQ31=$G30+$H30,1,0)+IF(AQ32=$I$32,3,0)+IF(AQ33=$G32+$H32,1,0)+IF(AQ34=$I$34,3,0)+IF(AQ35=$G34+$H34,1,0)+IF(AQ36=$I$36,3,0)+IF(AQ37=$G36+$H36,1,0)+IF(AQ38=$I$38,3,0)+IF(AQ39=$G38+$H38,1,0)+IF(AQ40=$I$40,3,0)+IF(AQ41=$G40+$H40,1,0)+IF(AQ42=$I$42,3,0)+IF(AQ43=$G42+$H42,1,0)+IF(AQ44=$I$44,3,0)+IF(AQ45=$G44+$H44,1,0)+IF(AQ46=$I$46,3,0)+IF(AQ47=$G46+$H46,1,0)+IF(AQ48=$I$48,3,0)+IF(AQ49=$G48+$H48,1,0)+IF(AQ50=$I$50,3,0)+IF(AQ51=$G50+$H50,1,0)+IF(AQ52=$I$52,3,0)+IF(AQ53=$G52+$H52,1,0)+IF(AQ54=$I$54,3,0)+IF(AQ55=$G54+$H54,1,0)+IF(AQ56=$I$56,3,0)+IF(AQ57=$G56+$H56,1,0)+IF(AQ58=$I$58,3,0)+IF(AQ59=$G58+$H58,1,0)+IF(AQ60=$I$60,3,0)+IF(AQ61=$G60+$H60,1,0)+IF(AQ62=$I$62,3,0)+IF(AQ63=$G62+$H62,1,0)+IF(AQ64=$I$64,3,0)+IF(AQ65=$G64+$H64,1,0)+IF(AQ66=$I$66,3,0)+IF(AQ67=$G66+$H66,1,0)+IF(AQ68=$I$68,3,0)+IF(AQ69=$G68+$H68,1,0)+IF(AQ70=$I$70,3,0)+IF(AQ71=$G70+$H70,1,0)+IF(AQ72=$I$72,3,0)+IF(AQ73=$G72+$H72,1,0)+IF(AQ74=$I$74,3,0)+IF(AQ75=$G74+$H74,1,0)+IF(AQ76=$I$76,3,0)+IF(AQ77=$G76+$H76,1,0)+IF(AQ78=$I$78,3,0)+IF(AQ79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="AR4" s="73">
-        <f>SUM(IF(AR8=$I$8,3,0)+IF(AR9=$G8+$H8,1,0)+IF(AR10=$I$10,3,0)+IF(AR11=$G10+$H10,1,0)+IF(AR12=$I$12,3,0)+IF(AR13=$G12+$H12,1,0)+IF(AR14=$I$14,3,0)+IF(AR15=$G14+$H14,1,0)
-+IF(AR16=$I$16,3,0)+IF(AR17=$G16+$H16,1,0)+IF(AR18=$I$18,3,0)+IF(AR19=$G18+$H18,1,0)+IF(AR20=$I$20,3,0)+IF(AR21=$G20+$H20,1,0)+IF(AR22=$I$22,3,0)+IF(AR23=$G22+$H22,1,0)+IF(AR24=$I$24,3,0)+IF(AR25=$G24+$H24,1,0)+IF(AR26=$I$26,3,0)+IF(AR27=$G26+$H26,1,0)+IF(AR28=$I$28,3,0)+IF(AR29=$G28+$H28,1,0)+IF(AR30=$I$30,3,0)+IF(AR31=$G30+$H30,1,0)+IF(AR32=$I$32,3,0)+IF(AR33=$G32+$H32,1,0)+IF(AR34=$I$34,3,0)+IF(AR35=$G34+$H34,1,0)+IF(AR36=$I$36,3,0)+IF(AR37=$G36+$H36,1,0)+IF(AR38=$I$38,3,0)+IF(AR39=$G38+$H38,1,0)+IF(AR40=$I$40,3,0)+IF(AR41=$G40+$H40,1,0)+IF(AR42=$I$42,3,0)+IF(AR43=$G42+$H42,1,0)+IF(AR44=$I$44,3,0)+IF(AR45=$G44+$H44,1,0)+IF(AR46=$I$46,3,0)+IF(AR47=$G46+$H46,1,0)+IF(AR48=$I$48,3,0)+IF(AR49=$G48+$H48,1,0)+IF(AR50=$I$50,3,0)+IF(AR51=$G50+$H50,1,0)+IF(AR52=$I$52,3,0)+IF(AR53=$G52+$H52,1,0)+IF(AR54=$I$54,3,0)+IF(AR55=$G54+$H54,1,0)+IF(AR56=$I$56,3,0)+IF(AR57=$G56+$H56,1,0)+IF(AR58=$I$58,3,0)+IF(AR59=$G58+$H58,1,0)+IF(AR60=$I$60,3,0)+IF(AR61=$G60+$H60,1,0)+IF(AR62=$I$62,3,0)+IF(AR63=$G62+$H62,1,0)+IF(AR64=$I$64,3,0)+IF(AR65=$G64+$H64,1,0)+IF(AR66=$I$66,3,0)+IF(AR67=$G66+$H66,1,0)+IF(AR68=$I$68,3,0)+IF(AR69=$G68+$H68,1,0)+IF(AR70=$I$70,3,0)+IF(AR71=$G70+$H70,1,0)+IF(AR72=$I$72,3,0)+IF(AR73=$G72+$H72,1,0)+IF(AR74=$I$74,3,0)+IF(AR75=$G74+$H74,1,0)+IF(AR76=$I$76,3,0)+IF(AR77=$G76+$H76,1,0)+IF(AR78=$I$78,3,0)+IF(AR79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="AS4" s="73">
-        <f>SUM(IF(AS8=$I$8,3,0)+IF(AS9=$G8+$H8,1,0)+IF(AS10=$I$10,3,0)+IF(AS11=$G10+$H10,1,0)+IF(AS12=$I$12,3,0)+IF(AS13=$G12+$H12,1,0)+IF(AS14=$I$14,3,0)+IF(AS15=$G14+$H14,1,0)
-+IF(AS16=$I$16,3,0)+IF(AS17=$G16+$H16,1,0)+IF(AS18=$I$18,3,0)+IF(AS19=$G18+$H18,1,0)+IF(AS20=$I$20,3,0)+IF(AS21=$G20+$H20,1,0)+IF(AS22=$I$22,3,0)+IF(AS23=$G22+$H22,1,0)+IF(AS24=$I$24,3,0)+IF(AS25=$G24+$H24,1,0)+IF(AS26=$I$26,3,0)+IF(AS27=$G26+$H26,1,0)+IF(AS28=$I$28,3,0)+IF(AS29=$G28+$H28,1,0)+IF(AS30=$I$30,3,0)+IF(AS31=$G30+$H30,1,0)+IF(AS32=$I$32,3,0)+IF(AS33=$G32+$H32,1,0)+IF(AS34=$I$34,3,0)+IF(AS35=$G34+$H34,1,0)+IF(AS36=$I$36,3,0)+IF(AS37=$G36+$H36,1,0)+IF(AS38=$I$38,3,0)+IF(AS39=$G38+$H38,1,0)+IF(AS40=$I$40,3,0)+IF(AS41=$G40+$H40,1,0)+IF(AS42=$I$42,3,0)+IF(AS43=$G42+$H42,1,0)+IF(AS44=$I$44,3,0)+IF(AS45=$G44+$H44,1,0)+IF(AS46=$I$46,3,0)+IF(AS47=$G46+$H46,1,0)+IF(AS48=$I$48,3,0)+IF(AS49=$G48+$H48,1,0)+IF(AS50=$I$50,3,0)+IF(AS51=$G50+$H50,1,0)+IF(AS52=$I$52,3,0)+IF(AS53=$G52+$H52,1,0)+IF(AS54=$I$54,3,0)+IF(AS55=$G54+$H54,1,0)+IF(AS56=$I$56,3,0)+IF(AS57=$G56+$H56,1,0)+IF(AS58=$I$58,3,0)+IF(AS59=$G58+$H58,1,0)+IF(AS60=$I$60,3,0)+IF(AS61=$G60+$H60,1,0)+IF(AS62=$I$62,3,0)+IF(AS63=$G62+$H62,1,0)+IF(AS64=$I$64,3,0)+IF(AS65=$G64+$H64,1,0)+IF(AS66=$I$66,3,0)+IF(AS67=$G66+$H66,1,0)+IF(AS68=$I$68,3,0)+IF(AS69=$G68+$H68,1,0)+IF(AS70=$I$70,3,0)+IF(AS71=$G70+$H70,1,0)+IF(AS72=$I$72,3,0)+IF(AS73=$G72+$H72,1,0)+IF(AS74=$I$74,3,0)+IF(AS75=$G74+$H74,1,0)+IF(AS76=$I$76,3,0)+IF(AS77=$G76+$H76,1,0)+IF(AS78=$I$78,3,0)+IF(AS79=$G78+$H78,1,0))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="AT4" s="78">
-        <f>SUM(IF(AT8=$I$8,3,0)+IF(AT9=$G8+$H8,1,0)+IF(AT10=$I$10,3,0)+IF(AT11=$G10+$H10,1,0)+IF(AT12=$I$12,3,0)+IF(AT13=$G12+$H12,1,0)+IF(AT14=$I$14,3,0)+IF(AT15=$G14+$H14,1,0)
-+IF(AT16=$I$16,3,0)+IF(AT17=$G16+$H16,1,0)+IF(AT18=$I$18,3,0)+IF(AT19=$G18+$H18,1,0)+IF(AT20=$I$20,3,0)+IF(AT21=$G20+$H20,1,0)+IF(AT22=$I$22,3,0)+IF(AT23=$G22+$H22,1,0)+IF(AT24=$I$24,3,0)+IF(AT25=$G24+$H24,1,0)+IF(AT26=$I$26,3,0)+IF(AT27=$G26+$H26,1,0)+IF(AT28=$I$28,3,0)+IF(AT29=$G28+$H28,1,0)+IF(AT30=$I$30,3,0)+IF(AT31=$G30+$H30,1,0)+IF(AT32=$I$32,3,0)+IF(AT33=$G32+$H32,1,0)+IF(AT34=$I$34,3,0)+IF(AT35=$G34+$H34,1,0)+IF(AT36=$I$36,3,0)+IF(AT37=$G36+$H36,1,0)+IF(AT38=$I$38,3,0)+IF(AT39=$G38+$H38,1,0)+IF(AT40=$I$40,3,0)+IF(AT41=$G40+$H40,1,0)+IF(AT42=$I$42,3,0)+IF(AT43=$G42+$H42,1,0)+IF(AT44=$I$44,3,0)+IF(AT45=$G44+$H44,1,0)+IF(AT46=$I$46,3,0)+IF(AT47=$G46+$H46,1,0)+IF(AT48=$I$48,3,0)+IF(AT49=$G48+$H48,1,0)+IF(AT50=$I$50,3,0)+IF(AT51=$G50+$H50,1,0)+IF(AT52=$I$52,3,0)+IF(AT53=$G52+$H52,1,0)+IF(AT54=$I$54,3,0)+IF(AT55=$G54+$H54,1,0)+IF(AT56=$I$56,3,0)+IF(AT57=$G56+$H56,1,0)+IF(AT58=$I$58,3,0)+IF(AT59=$G58+$H58,1,0)+IF(AT60=$I$60,3,0)+IF(AT61=$G60+$H60,1,0)+IF(AT62=$I$62,3,0)+IF(AT63=$G62+$H62,1,0)+IF(AT64=$I$64,3,0)+IF(AT65=$G64+$H64,1,0)+IF(AT66=$I$66,3,0)+IF(AT67=$G66+$H66,1,0)+IF(AT68=$I$68,3,0)+IF(AT69=$G68+$H68,1,0)+IF(AT70=$I$70,3,0)+IF(AT71=$G70+$H70,1,0)+IF(AT72=$I$72,3,0)+IF(AT73=$G72+$H72,1,0)+IF(AT74=$I$74,3,0)+IF(AT75=$G74+$H74,1,0)+IF(AT76=$I$76,3,0)+IF(AT77=$G76+$H76,1,0)+IF(AT78=$I$78,3,0)+IF(AT79=$G78+$H78,1,0))</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:54" ht="14.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:54" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="64"/>
       <c r="B5" s="64"/>
       <c r="C5" s="64"/>
@@ -3153,155 +3117,155 @@
       <c r="H5" s="65"/>
       <c r="I5" s="66"/>
       <c r="J5" s="74">
-        <f>SUM(IF(J80=$I$80,3,0)+IF(J81=$G80+$H80,1,0)+IF(J82=$I$82,3,0)+IF(J83=$G82+$H82,1,0)+IF(J84=$I$84,3,0)+IF(J85=$G84+$H84,1,0)+IF(J86=$I$86,3,0)+IF(J87=$G86+$H86,1,0)+IF(J88=$I$88,3,0)+IF(J89=$G88+$H88,1,0)+IF(J90=$I$90,3,0)+IF(J91=$G90+$H90,1,0)+IF(J92=$I$92,3,0)+IF(J93=$G92+$H92,1,0)+IF(J94=$I$94,3,0)+IF(J95=$G94+$H94,1,0)+IF(J96=$I$96,3,0)+IF(J97=$G96+$H96,1,0)+IF(J98=$I$98,3,0)+IF(J99=$G98+$H98,1,0)+IF(J100=$I$100,3,0)+IF(J101=$G100+$H100,1,0)+IF(J102=$I$102,3,0)+IF(J103=$G102+$H102,1,0)+IF(J104=$I$104,3,0)+IF(J105=$G104+$H104,1,0)+IF(J106=$I$106,3,0)+IF(J107=$G106+$H106,1,0)+IF(J108=$I$108,3,0)+IF(J109=$G108+$H108,1,0)+IF(J110=$I$110,3,0)+IF(J111=$G110+$H110,1,0)+IF(J112=$I$112,3,0)+IF(J113=$G112+$H112,1,0)+IF(J114=$I$114,3,0)+IF(J115=$G114+$H114,1,0)+IF(J116=$I$116,3,0)+IF(J117=$G116+$H116,1,0)+IF(J118=$I$118,3,0)+IF(J119=$G118+$H118,1,0)+IF(J120=$I$120,3,0)+IF(J121=$G120+$H120,1,0)+IF(J122=$I$122,3,0)+IF(J123=$G122+$H122,1,0)+IF(J124=$I$124,3,0)+IF(J125=$G124+$H124,1,0)+IF(J126=$I$126,3,0)+IF(J127=$G126+$H126,1,0)+IF(J128=$I$128,3,0)+IF(J129=$G128+$H128,1,0)+IF(J130=$I$130,3,0)+IF(J131=$G130+$H130,1,0)+IF(J132=$I$132,3,0)+IF(J133=$G132+$H132,1,0)+IF(J134=$I$134,3,0)+IF(J135=$G134+$H134,1,0)+IF(J136=$I$136,3,0)+IF(J137=$G136+$H136,1,0)+IF(J138=$I$138,3,0)+IF(J139=$G138+$H138,1,0)+IF(J140=$I$140,3,0)+IF(J141=$G140+$H140,1,0)+IF(J142=$I$142,3,0)+IF(J143=$G142+$H142,1,0)+IF(J144=$I$144,3,0)+IF(J145=$G144+$H144,1,0)+IF(J146=$I$146,3,0)+IF(J147=$G146+$H146,1,0)+IF(J148=$I$148,3,0)+IF(J149=$G148+$H148,1,0)+IF(J150=$I$150,3,0)+IF(J151=$G150+$H150,1,0))</f>
+        <f t="shared" ref="J5:AT5" si="2">SUM(IF(J80=$I$80,3,0)+IF(J81=$G80+$H80,1,0)+IF(J82=$I$82,3,0)+IF(J83=$G82+$H82,1,0)+IF(J84=$I$84,3,0)+IF(J85=$G84+$H84,1,0)+IF(J86=$I$86,3,0)+IF(J87=$G86+$H86,1,0)+IF(J88=$I$88,3,0)+IF(J89=$G88+$H88,1,0)+IF(J90=$I$90,3,0)+IF(J91=$G90+$H90,1,0)+IF(J92=$I$92,3,0)+IF(J93=$G92+$H92,1,0)+IF(J94=$I$94,3,0)+IF(J95=$G94+$H94,1,0)+IF(J96=$I$96,3,0)+IF(J97=$G96+$H96,1,0)+IF(J98=$I$98,3,0)+IF(J99=$G98+$H98,1,0)+IF(J100=$I$100,3,0)+IF(J101=$G100+$H100,1,0)+IF(J102=$I$102,3,0)+IF(J103=$G102+$H102,1,0)+IF(J104=$I$104,3,0)+IF(J105=$G104+$H104,1,0)+IF(J106=$I$106,3,0)+IF(J107=$G106+$H106,1,0)+IF(J108=$I$108,3,0)+IF(J109=$G108+$H108,1,0)+IF(J110=$I$110,3,0)+IF(J111=$G110+$H110,1,0)+IF(J112=$I$112,3,0)+IF(J113=$G112+$H112,1,0)+IF(J114=$I$114,3,0)+IF(J115=$G114+$H114,1,0)+IF(J116=$I$116,3,0)+IF(J117=$G116+$H116,1,0)+IF(J118=$I$118,3,0)+IF(J119=$G118+$H118,1,0)+IF(J120=$I$120,3,0)+IF(J121=$G120+$H120,1,0)+IF(J122=$I$122,3,0)+IF(J123=$G122+$H122,1,0)+IF(J124=$I$124,3,0)+IF(J125=$G124+$H124,1,0)+IF(J126=$I$126,3,0)+IF(J127=$G126+$H126,1,0)+IF(J128=$I$128,3,0)+IF(J129=$G128+$H128,1,0)+IF(J130=$I$130,3,0)+IF(J131=$G130+$H130,1,0)+IF(J132=$I$132,3,0)+IF(J133=$G132+$H132,1,0)+IF(J134=$I$134,3,0)+IF(J135=$G134+$H134,1,0)+IF(J136=$I$136,3,0)+IF(J137=$G136+$H136,1,0)+IF(J138=$I$138,3,0)+IF(J139=$G138+$H138,1,0)+IF(J140=$I$140,3,0)+IF(J141=$G140+$H140,1,0)+IF(J142=$I$142,3,0)+IF(J143=$G142+$H142,1,0)+IF(J144=$I$144,3,0)+IF(J145=$G144+$H144,1,0)+IF(J146=$I$146,3,0)+IF(J147=$G146+$H146,1,0)+IF(J148=$I$148,3,0)+IF(J149=$G148+$H148,1,0)+IF(J150=$I$150,3,0)+IF(J151=$G150+$H150,1,0))</f>
         <v>2</v>
       </c>
       <c r="K5" s="75">
-        <f>SUM(IF(K80=$I$80,3,0)+IF(K81=$G80+$H80,1,0)+IF(K82=$I$82,3,0)+IF(K83=$G82+$H82,1,0)+IF(K84=$I$84,3,0)+IF(K85=$G84+$H84,1,0)+IF(K86=$I$86,3,0)+IF(K87=$G86+$H86,1,0)+IF(K88=$I$88,3,0)+IF(K89=$G88+$H88,1,0)+IF(K90=$I$90,3,0)+IF(K91=$G90+$H90,1,0)+IF(K92=$I$92,3,0)+IF(K93=$G92+$H92,1,0)+IF(K94=$I$94,3,0)+IF(K95=$G94+$H94,1,0)+IF(K96=$I$96,3,0)+IF(K97=$G96+$H96,1,0)+IF(K98=$I$98,3,0)+IF(K99=$G98+$H98,1,0)+IF(K100=$I$100,3,0)+IF(K101=$G100+$H100,1,0)+IF(K102=$I$102,3,0)+IF(K103=$G102+$H102,1,0)+IF(K104=$I$104,3,0)+IF(K105=$G104+$H104,1,0)+IF(K106=$I$106,3,0)+IF(K107=$G106+$H106,1,0)+IF(K108=$I$108,3,0)+IF(K109=$G108+$H108,1,0)+IF(K110=$I$110,3,0)+IF(K111=$G110+$H110,1,0)+IF(K112=$I$112,3,0)+IF(K113=$G112+$H112,1,0)+IF(K114=$I$114,3,0)+IF(K115=$G114+$H114,1,0)+IF(K116=$I$116,3,0)+IF(K117=$G116+$H116,1,0)+IF(K118=$I$118,3,0)+IF(K119=$G118+$H118,1,0)+IF(K120=$I$120,3,0)+IF(K121=$G120+$H120,1,0)+IF(K122=$I$122,3,0)+IF(K123=$G122+$H122,1,0)+IF(K124=$I$124,3,0)+IF(K125=$G124+$H124,1,0)+IF(K126=$I$126,3,0)+IF(K127=$G126+$H126,1,0)+IF(K128=$I$128,3,0)+IF(K129=$G128+$H128,1,0)+IF(K130=$I$130,3,0)+IF(K131=$G130+$H130,1,0)+IF(K132=$I$132,3,0)+IF(K133=$G132+$H132,1,0)+IF(K134=$I$134,3,0)+IF(K135=$G134+$H134,1,0)+IF(K136=$I$136,3,0)+IF(K137=$G136+$H136,1,0)+IF(K138=$I$138,3,0)+IF(K139=$G138+$H138,1,0)+IF(K140=$I$140,3,0)+IF(K141=$G140+$H140,1,0)+IF(K142=$I$142,3,0)+IF(K143=$G142+$H142,1,0)+IF(K144=$I$144,3,0)+IF(K145=$G144+$H144,1,0)+IF(K146=$I$146,3,0)+IF(K147=$G146+$H146,1,0)+IF(K148=$I$148,3,0)+IF(K149=$G148+$H148,1,0)+IF(K150=$I$150,3,0)+IF(K151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L5" s="75">
-        <f>SUM(IF(L80=$I$80,3,0)+IF(L81=$G80+$H80,1,0)+IF(L82=$I$82,3,0)+IF(L83=$G82+$H82,1,0)+IF(L84=$I$84,3,0)+IF(L85=$G84+$H84,1,0)+IF(L86=$I$86,3,0)+IF(L87=$G86+$H86,1,0)+IF(L88=$I$88,3,0)+IF(L89=$G88+$H88,1,0)+IF(L90=$I$90,3,0)+IF(L91=$G90+$H90,1,0)+IF(L92=$I$92,3,0)+IF(L93=$G92+$H92,1,0)+IF(L94=$I$94,3,0)+IF(L95=$G94+$H94,1,0)+IF(L96=$I$96,3,0)+IF(L97=$G96+$H96,1,0)+IF(L98=$I$98,3,0)+IF(L99=$G98+$H98,1,0)+IF(L100=$I$100,3,0)+IF(L101=$G100+$H100,1,0)+IF(L102=$I$102,3,0)+IF(L103=$G102+$H102,1,0)+IF(L104=$I$104,3,0)+IF(L105=$G104+$H104,1,0)+IF(L106=$I$106,3,0)+IF(L107=$G106+$H106,1,0)+IF(L108=$I$108,3,0)+IF(L109=$G108+$H108,1,0)+IF(L110=$I$110,3,0)+IF(L111=$G110+$H110,1,0)+IF(L112=$I$112,3,0)+IF(L113=$G112+$H112,1,0)+IF(L114=$I$114,3,0)+IF(L115=$G114+$H114,1,0)+IF(L116=$I$116,3,0)+IF(L117=$G116+$H116,1,0)+IF(L118=$I$118,3,0)+IF(L119=$G118+$H118,1,0)+IF(L120=$I$120,3,0)+IF(L121=$G120+$H120,1,0)+IF(L122=$I$122,3,0)+IF(L123=$G122+$H122,1,0)+IF(L124=$I$124,3,0)+IF(L125=$G124+$H124,1,0)+IF(L126=$I$126,3,0)+IF(L127=$G126+$H126,1,0)+IF(L128=$I$128,3,0)+IF(L129=$G128+$H128,1,0)+IF(L130=$I$130,3,0)+IF(L131=$G130+$H130,1,0)+IF(L132=$I$132,3,0)+IF(L133=$G132+$H132,1,0)+IF(L134=$I$134,3,0)+IF(L135=$G134+$H134,1,0)+IF(L136=$I$136,3,0)+IF(L137=$G136+$H136,1,0)+IF(L138=$I$138,3,0)+IF(L139=$G138+$H138,1,0)+IF(L140=$I$140,3,0)+IF(L141=$G140+$H140,1,0)+IF(L142=$I$142,3,0)+IF(L143=$G142+$H142,1,0)+IF(L144=$I$144,3,0)+IF(L145=$G144+$H144,1,0)+IF(L146=$I$146,3,0)+IF(L147=$G146+$H146,1,0)+IF(L148=$I$148,3,0)+IF(L149=$G148+$H148,1,0)+IF(L150=$I$150,3,0)+IF(L151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M5" s="75">
-        <f>SUM(IF(M80=$I$80,3,0)+IF(M81=$G80+$H80,1,0)+IF(M82=$I$82,3,0)+IF(M83=$G82+$H82,1,0)+IF(M84=$I$84,3,0)+IF(M85=$G84+$H84,1,0)+IF(M86=$I$86,3,0)+IF(M87=$G86+$H86,1,0)+IF(M88=$I$88,3,0)+IF(M89=$G88+$H88,1,0)+IF(M90=$I$90,3,0)+IF(M91=$G90+$H90,1,0)+IF(M92=$I$92,3,0)+IF(M93=$G92+$H92,1,0)+IF(M94=$I$94,3,0)+IF(M95=$G94+$H94,1,0)+IF(M96=$I$96,3,0)+IF(M97=$G96+$H96,1,0)+IF(M98=$I$98,3,0)+IF(M99=$G98+$H98,1,0)+IF(M100=$I$100,3,0)+IF(M101=$G100+$H100,1,0)+IF(M102=$I$102,3,0)+IF(M103=$G102+$H102,1,0)+IF(M104=$I$104,3,0)+IF(M105=$G104+$H104,1,0)+IF(M106=$I$106,3,0)+IF(M107=$G106+$H106,1,0)+IF(M108=$I$108,3,0)+IF(M109=$G108+$H108,1,0)+IF(M110=$I$110,3,0)+IF(M111=$G110+$H110,1,0)+IF(M112=$I$112,3,0)+IF(M113=$G112+$H112,1,0)+IF(M114=$I$114,3,0)+IF(M115=$G114+$H114,1,0)+IF(M116=$I$116,3,0)+IF(M117=$G116+$H116,1,0)+IF(M118=$I$118,3,0)+IF(M119=$G118+$H118,1,0)+IF(M120=$I$120,3,0)+IF(M121=$G120+$H120,1,0)+IF(M122=$I$122,3,0)+IF(M123=$G122+$H122,1,0)+IF(M124=$I$124,3,0)+IF(M125=$G124+$H124,1,0)+IF(M126=$I$126,3,0)+IF(M127=$G126+$H126,1,0)+IF(M128=$I$128,3,0)+IF(M129=$G128+$H128,1,0)+IF(M130=$I$130,3,0)+IF(M131=$G130+$H130,1,0)+IF(M132=$I$132,3,0)+IF(M133=$G132+$H132,1,0)+IF(M134=$I$134,3,0)+IF(M135=$G134+$H134,1,0)+IF(M136=$I$136,3,0)+IF(M137=$G136+$H136,1,0)+IF(M138=$I$138,3,0)+IF(M139=$G138+$H138,1,0)+IF(M140=$I$140,3,0)+IF(M141=$G140+$H140,1,0)+IF(M142=$I$142,3,0)+IF(M143=$G142+$H142,1,0)+IF(M144=$I$144,3,0)+IF(M145=$G144+$H144,1,0)+IF(M146=$I$146,3,0)+IF(M147=$G146+$H146,1,0)+IF(M148=$I$148,3,0)+IF(M149=$G148+$H148,1,0)+IF(M150=$I$150,3,0)+IF(M151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N5" s="75">
-        <f>SUM(IF(N80=$I$80,3,0)+IF(N81=$G80+$H80,1,0)+IF(N82=$I$82,3,0)+IF(N83=$G82+$H82,1,0)+IF(N84=$I$84,3,0)+IF(N85=$G84+$H84,1,0)+IF(N86=$I$86,3,0)+IF(N87=$G86+$H86,1,0)+IF(N88=$I$88,3,0)+IF(N89=$G88+$H88,1,0)+IF(N90=$I$90,3,0)+IF(N91=$G90+$H90,1,0)+IF(N92=$I$92,3,0)+IF(N93=$G92+$H92,1,0)+IF(N94=$I$94,3,0)+IF(N95=$G94+$H94,1,0)+IF(N96=$I$96,3,0)+IF(N97=$G96+$H96,1,0)+IF(N98=$I$98,3,0)+IF(N99=$G98+$H98,1,0)+IF(N100=$I$100,3,0)+IF(N101=$G100+$H100,1,0)+IF(N102=$I$102,3,0)+IF(N103=$G102+$H102,1,0)+IF(N104=$I$104,3,0)+IF(N105=$G104+$H104,1,0)+IF(N106=$I$106,3,0)+IF(N107=$G106+$H106,1,0)+IF(N108=$I$108,3,0)+IF(N109=$G108+$H108,1,0)+IF(N110=$I$110,3,0)+IF(N111=$G110+$H110,1,0)+IF(N112=$I$112,3,0)+IF(N113=$G112+$H112,1,0)+IF(N114=$I$114,3,0)+IF(N115=$G114+$H114,1,0)+IF(N116=$I$116,3,0)+IF(N117=$G116+$H116,1,0)+IF(N118=$I$118,3,0)+IF(N119=$G118+$H118,1,0)+IF(N120=$I$120,3,0)+IF(N121=$G120+$H120,1,0)+IF(N122=$I$122,3,0)+IF(N123=$G122+$H122,1,0)+IF(N124=$I$124,3,0)+IF(N125=$G124+$H124,1,0)+IF(N126=$I$126,3,0)+IF(N127=$G126+$H126,1,0)+IF(N128=$I$128,3,0)+IF(N129=$G128+$H128,1,0)+IF(N130=$I$130,3,0)+IF(N131=$G130+$H130,1,0)+IF(N132=$I$132,3,0)+IF(N133=$G132+$H132,1,0)+IF(N134=$I$134,3,0)+IF(N135=$G134+$H134,1,0)+IF(N136=$I$136,3,0)+IF(N137=$G136+$H136,1,0)+IF(N138=$I$138,3,0)+IF(N139=$G138+$H138,1,0)+IF(N140=$I$140,3,0)+IF(N141=$G140+$H140,1,0)+IF(N142=$I$142,3,0)+IF(N143=$G142+$H142,1,0)+IF(N144=$I$144,3,0)+IF(N145=$G144+$H144,1,0)+IF(N146=$I$146,3,0)+IF(N147=$G146+$H146,1,0)+IF(N148=$I$148,3,0)+IF(N149=$G148+$H148,1,0)+IF(N150=$I$150,3,0)+IF(N151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O5" s="75">
-        <f>SUM(IF(O80=$I$80,3,0)+IF(O81=$G80+$H80,1,0)+IF(O82=$I$82,3,0)+IF(O83=$G82+$H82,1,0)+IF(O84=$I$84,3,0)+IF(O85=$G84+$H84,1,0)+IF(O86=$I$86,3,0)+IF(O87=$G86+$H86,1,0)+IF(O88=$I$88,3,0)+IF(O89=$G88+$H88,1,0)+IF(O90=$I$90,3,0)+IF(O91=$G90+$H90,1,0)+IF(O92=$I$92,3,0)+IF(O93=$G92+$H92,1,0)+IF(O94=$I$94,3,0)+IF(O95=$G94+$H94,1,0)+IF(O96=$I$96,3,0)+IF(O97=$G96+$H96,1,0)+IF(O98=$I$98,3,0)+IF(O99=$G98+$H98,1,0)+IF(O100=$I$100,3,0)+IF(O101=$G100+$H100,1,0)+IF(O102=$I$102,3,0)+IF(O103=$G102+$H102,1,0)+IF(O104=$I$104,3,0)+IF(O105=$G104+$H104,1,0)+IF(O106=$I$106,3,0)+IF(O107=$G106+$H106,1,0)+IF(O108=$I$108,3,0)+IF(O109=$G108+$H108,1,0)+IF(O110=$I$110,3,0)+IF(O111=$G110+$H110,1,0)+IF(O112=$I$112,3,0)+IF(O113=$G112+$H112,1,0)+IF(O114=$I$114,3,0)+IF(O115=$G114+$H114,1,0)+IF(O116=$I$116,3,0)+IF(O117=$G116+$H116,1,0)+IF(O118=$I$118,3,0)+IF(O119=$G118+$H118,1,0)+IF(O120=$I$120,3,0)+IF(O121=$G120+$H120,1,0)+IF(O122=$I$122,3,0)+IF(O123=$G122+$H122,1,0)+IF(O124=$I$124,3,0)+IF(O125=$G124+$H124,1,0)+IF(O126=$I$126,3,0)+IF(O127=$G126+$H126,1,0)+IF(O128=$I$128,3,0)+IF(O129=$G128+$H128,1,0)+IF(O130=$I$130,3,0)+IF(O131=$G130+$H130,1,0)+IF(O132=$I$132,3,0)+IF(O133=$G132+$H132,1,0)+IF(O134=$I$134,3,0)+IF(O135=$G134+$H134,1,0)+IF(O136=$I$136,3,0)+IF(O137=$G136+$H136,1,0)+IF(O138=$I$138,3,0)+IF(O139=$G138+$H138,1,0)+IF(O140=$I$140,3,0)+IF(O141=$G140+$H140,1,0)+IF(O142=$I$142,3,0)+IF(O143=$G142+$H142,1,0)+IF(O144=$I$144,3,0)+IF(O145=$G144+$H144,1,0)+IF(O146=$I$146,3,0)+IF(O147=$G146+$H146,1,0)+IF(O148=$I$148,3,0)+IF(O149=$G148+$H148,1,0)+IF(O150=$I$150,3,0)+IF(O151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P5" s="75">
-        <f>SUM(IF(P80=$I$80,3,0)+IF(P81=$G80+$H80,1,0)+IF(P82=$I$82,3,0)+IF(P83=$G82+$H82,1,0)+IF(P84=$I$84,3,0)+IF(P85=$G84+$H84,1,0)+IF(P86=$I$86,3,0)+IF(P87=$G86+$H86,1,0)+IF(P88=$I$88,3,0)+IF(P89=$G88+$H88,1,0)+IF(P90=$I$90,3,0)+IF(P91=$G90+$H90,1,0)+IF(P92=$I$92,3,0)+IF(P93=$G92+$H92,1,0)+IF(P94=$I$94,3,0)+IF(P95=$G94+$H94,1,0)+IF(P96=$I$96,3,0)+IF(P97=$G96+$H96,1,0)+IF(P98=$I$98,3,0)+IF(P99=$G98+$H98,1,0)+IF(P100=$I$100,3,0)+IF(P101=$G100+$H100,1,0)+IF(P102=$I$102,3,0)+IF(P103=$G102+$H102,1,0)+IF(P104=$I$104,3,0)+IF(P105=$G104+$H104,1,0)+IF(P106=$I$106,3,0)+IF(P107=$G106+$H106,1,0)+IF(P108=$I$108,3,0)+IF(P109=$G108+$H108,1,0)+IF(P110=$I$110,3,0)+IF(P111=$G110+$H110,1,0)+IF(P112=$I$112,3,0)+IF(P113=$G112+$H112,1,0)+IF(P114=$I$114,3,0)+IF(P115=$G114+$H114,1,0)+IF(P116=$I$116,3,0)+IF(P117=$G116+$H116,1,0)+IF(P118=$I$118,3,0)+IF(P119=$G118+$H118,1,0)+IF(P120=$I$120,3,0)+IF(P121=$G120+$H120,1,0)+IF(P122=$I$122,3,0)+IF(P123=$G122+$H122,1,0)+IF(P124=$I$124,3,0)+IF(P125=$G124+$H124,1,0)+IF(P126=$I$126,3,0)+IF(P127=$G126+$H126,1,0)+IF(P128=$I$128,3,0)+IF(P129=$G128+$H128,1,0)+IF(P130=$I$130,3,0)+IF(P131=$G130+$H130,1,0)+IF(P132=$I$132,3,0)+IF(P133=$G132+$H132,1,0)+IF(P134=$I$134,3,0)+IF(P135=$G134+$H134,1,0)+IF(P136=$I$136,3,0)+IF(P137=$G136+$H136,1,0)+IF(P138=$I$138,3,0)+IF(P139=$G138+$H138,1,0)+IF(P140=$I$140,3,0)+IF(P141=$G140+$H140,1,0)+IF(P142=$I$142,3,0)+IF(P143=$G142+$H142,1,0)+IF(P144=$I$144,3,0)+IF(P145=$G144+$H144,1,0)+IF(P146=$I$146,3,0)+IF(P147=$G146+$H146,1,0)+IF(P148=$I$148,3,0)+IF(P149=$G148+$H148,1,0)+IF(P150=$I$150,3,0)+IF(P151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q5" s="75">
-        <f>SUM(IF(Q80=$I$80,3,0)+IF(Q81=$G80+$H80,1,0)+IF(Q82=$I$82,3,0)+IF(Q83=$G82+$H82,1,0)+IF(Q84=$I$84,3,0)+IF(Q85=$G84+$H84,1,0)+IF(Q86=$I$86,3,0)+IF(Q87=$G86+$H86,1,0)+IF(Q88=$I$88,3,0)+IF(Q89=$G88+$H88,1,0)+IF(Q90=$I$90,3,0)+IF(Q91=$G90+$H90,1,0)+IF(Q92=$I$92,3,0)+IF(Q93=$G92+$H92,1,0)+IF(Q94=$I$94,3,0)+IF(Q95=$G94+$H94,1,0)+IF(Q96=$I$96,3,0)+IF(Q97=$G96+$H96,1,0)+IF(Q98=$I$98,3,0)+IF(Q99=$G98+$H98,1,0)+IF(Q100=$I$100,3,0)+IF(Q101=$G100+$H100,1,0)+IF(Q102=$I$102,3,0)+IF(Q103=$G102+$H102,1,0)+IF(Q104=$I$104,3,0)+IF(Q105=$G104+$H104,1,0)+IF(Q106=$I$106,3,0)+IF(Q107=$G106+$H106,1,0)+IF(Q108=$I$108,3,0)+IF(Q109=$G108+$H108,1,0)+IF(Q110=$I$110,3,0)+IF(Q111=$G110+$H110,1,0)+IF(Q112=$I$112,3,0)+IF(Q113=$G112+$H112,1,0)+IF(Q114=$I$114,3,0)+IF(Q115=$G114+$H114,1,0)+IF(Q116=$I$116,3,0)+IF(Q117=$G116+$H116,1,0)+IF(Q118=$I$118,3,0)+IF(Q119=$G118+$H118,1,0)+IF(Q120=$I$120,3,0)+IF(Q121=$G120+$H120,1,0)+IF(Q122=$I$122,3,0)+IF(Q123=$G122+$H122,1,0)+IF(Q124=$I$124,3,0)+IF(Q125=$G124+$H124,1,0)+IF(Q126=$I$126,3,0)+IF(Q127=$G126+$H126,1,0)+IF(Q128=$I$128,3,0)+IF(Q129=$G128+$H128,1,0)+IF(Q130=$I$130,3,0)+IF(Q131=$G130+$H130,1,0)+IF(Q132=$I$132,3,0)+IF(Q133=$G132+$H132,1,0)+IF(Q134=$I$134,3,0)+IF(Q135=$G134+$H134,1,0)+IF(Q136=$I$136,3,0)+IF(Q137=$G136+$H136,1,0)+IF(Q138=$I$138,3,0)+IF(Q139=$G138+$H138,1,0)+IF(Q140=$I$140,3,0)+IF(Q141=$G140+$H140,1,0)+IF(Q142=$I$142,3,0)+IF(Q143=$G142+$H142,1,0)+IF(Q144=$I$144,3,0)+IF(Q145=$G144+$H144,1,0)+IF(Q146=$I$146,3,0)+IF(Q147=$G146+$H146,1,0)+IF(Q148=$I$148,3,0)+IF(Q149=$G148+$H148,1,0)+IF(Q150=$I$150,3,0)+IF(Q151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R5" s="75">
-        <f>SUM(IF(R80=$I$80,3,0)+IF(R81=$G80+$H80,1,0)+IF(R82=$I$82,3,0)+IF(R83=$G82+$H82,1,0)+IF(R84=$I$84,3,0)+IF(R85=$G84+$H84,1,0)+IF(R86=$I$86,3,0)+IF(R87=$G86+$H86,1,0)+IF(R88=$I$88,3,0)+IF(R89=$G88+$H88,1,0)+IF(R90=$I$90,3,0)+IF(R91=$G90+$H90,1,0)+IF(R92=$I$92,3,0)+IF(R93=$G92+$H92,1,0)+IF(R94=$I$94,3,0)+IF(R95=$G94+$H94,1,0)+IF(R96=$I$96,3,0)+IF(R97=$G96+$H96,1,0)+IF(R98=$I$98,3,0)+IF(R99=$G98+$H98,1,0)+IF(R100=$I$100,3,0)+IF(R101=$G100+$H100,1,0)+IF(R102=$I$102,3,0)+IF(R103=$G102+$H102,1,0)+IF(R104=$I$104,3,0)+IF(R105=$G104+$H104,1,0)+IF(R106=$I$106,3,0)+IF(R107=$G106+$H106,1,0)+IF(R108=$I$108,3,0)+IF(R109=$G108+$H108,1,0)+IF(R110=$I$110,3,0)+IF(R111=$G110+$H110,1,0)+IF(R112=$I$112,3,0)+IF(R113=$G112+$H112,1,0)+IF(R114=$I$114,3,0)+IF(R115=$G114+$H114,1,0)+IF(R116=$I$116,3,0)+IF(R117=$G116+$H116,1,0)+IF(R118=$I$118,3,0)+IF(R119=$G118+$H118,1,0)+IF(R120=$I$120,3,0)+IF(R121=$G120+$H120,1,0)+IF(R122=$I$122,3,0)+IF(R123=$G122+$H122,1,0)+IF(R124=$I$124,3,0)+IF(R125=$G124+$H124,1,0)+IF(R126=$I$126,3,0)+IF(R127=$G126+$H126,1,0)+IF(R128=$I$128,3,0)+IF(R129=$G128+$H128,1,0)+IF(R130=$I$130,3,0)+IF(R131=$G130+$H130,1,0)+IF(R132=$I$132,3,0)+IF(R133=$G132+$H132,1,0)+IF(R134=$I$134,3,0)+IF(R135=$G134+$H134,1,0)+IF(R136=$I$136,3,0)+IF(R137=$G136+$H136,1,0)+IF(R138=$I$138,3,0)+IF(R139=$G138+$H138,1,0)+IF(R140=$I$140,3,0)+IF(R141=$G140+$H140,1,0)+IF(R142=$I$142,3,0)+IF(R143=$G142+$H142,1,0)+IF(R144=$I$144,3,0)+IF(R145=$G144+$H144,1,0)+IF(R146=$I$146,3,0)+IF(R147=$G146+$H146,1,0)+IF(R148=$I$148,3,0)+IF(R149=$G148+$H148,1,0)+IF(R150=$I$150,3,0)+IF(R151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S5" s="75">
-        <f>SUM(IF(S80=$I$80,3,0)+IF(S81=$G80+$H80,1,0)+IF(S82=$I$82,3,0)+IF(S83=$G82+$H82,1,0)+IF(S84=$I$84,3,0)+IF(S85=$G84+$H84,1,0)+IF(S86=$I$86,3,0)+IF(S87=$G86+$H86,1,0)+IF(S88=$I$88,3,0)+IF(S89=$G88+$H88,1,0)+IF(S90=$I$90,3,0)+IF(S91=$G90+$H90,1,0)+IF(S92=$I$92,3,0)+IF(S93=$G92+$H92,1,0)+IF(S94=$I$94,3,0)+IF(S95=$G94+$H94,1,0)+IF(S96=$I$96,3,0)+IF(S97=$G96+$H96,1,0)+IF(S98=$I$98,3,0)+IF(S99=$G98+$H98,1,0)+IF(S100=$I$100,3,0)+IF(S101=$G100+$H100,1,0)+IF(S102=$I$102,3,0)+IF(S103=$G102+$H102,1,0)+IF(S104=$I$104,3,0)+IF(S105=$G104+$H104,1,0)+IF(S106=$I$106,3,0)+IF(S107=$G106+$H106,1,0)+IF(S108=$I$108,3,0)+IF(S109=$G108+$H108,1,0)+IF(S110=$I$110,3,0)+IF(S111=$G110+$H110,1,0)+IF(S112=$I$112,3,0)+IF(S113=$G112+$H112,1,0)+IF(S114=$I$114,3,0)+IF(S115=$G114+$H114,1,0)+IF(S116=$I$116,3,0)+IF(S117=$G116+$H116,1,0)+IF(S118=$I$118,3,0)+IF(S119=$G118+$H118,1,0)+IF(S120=$I$120,3,0)+IF(S121=$G120+$H120,1,0)+IF(S122=$I$122,3,0)+IF(S123=$G122+$H122,1,0)+IF(S124=$I$124,3,0)+IF(S125=$G124+$H124,1,0)+IF(S126=$I$126,3,0)+IF(S127=$G126+$H126,1,0)+IF(S128=$I$128,3,0)+IF(S129=$G128+$H128,1,0)+IF(S130=$I$130,3,0)+IF(S131=$G130+$H130,1,0)+IF(S132=$I$132,3,0)+IF(S133=$G132+$H132,1,0)+IF(S134=$I$134,3,0)+IF(S135=$G134+$H134,1,0)+IF(S136=$I$136,3,0)+IF(S137=$G136+$H136,1,0)+IF(S138=$I$138,3,0)+IF(S139=$G138+$H138,1,0)+IF(S140=$I$140,3,0)+IF(S141=$G140+$H140,1,0)+IF(S142=$I$142,3,0)+IF(S143=$G142+$H142,1,0)+IF(S144=$I$144,3,0)+IF(S145=$G144+$H144,1,0)+IF(S146=$I$146,3,0)+IF(S147=$G146+$H146,1,0)+IF(S148=$I$148,3,0)+IF(S149=$G148+$H148,1,0)+IF(S150=$I$150,3,0)+IF(S151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="T5" s="75">
-        <f>SUM(IF(T80=$I$80,3,0)+IF(T81=$G80+$H80,1,0)+IF(T82=$I$82,3,0)+IF(T83=$G82+$H82,1,0)+IF(T84=$I$84,3,0)+IF(T85=$G84+$H84,1,0)+IF(T86=$I$86,3,0)+IF(T87=$G86+$H86,1,0)+IF(T88=$I$88,3,0)+IF(T89=$G88+$H88,1,0)+IF(T90=$I$90,3,0)+IF(T91=$G90+$H90,1,0)+IF(T92=$I$92,3,0)+IF(T93=$G92+$H92,1,0)+IF(T94=$I$94,3,0)+IF(T95=$G94+$H94,1,0)+IF(T96=$I$96,3,0)+IF(T97=$G96+$H96,1,0)+IF(T98=$I$98,3,0)+IF(T99=$G98+$H98,1,0)+IF(T100=$I$100,3,0)+IF(T101=$G100+$H100,1,0)+IF(T102=$I$102,3,0)+IF(T103=$G102+$H102,1,0)+IF(T104=$I$104,3,0)+IF(T105=$G104+$H104,1,0)+IF(T106=$I$106,3,0)+IF(T107=$G106+$H106,1,0)+IF(T108=$I$108,3,0)+IF(T109=$G108+$H108,1,0)+IF(T110=$I$110,3,0)+IF(T111=$G110+$H110,1,0)+IF(T112=$I$112,3,0)+IF(T113=$G112+$H112,1,0)+IF(T114=$I$114,3,0)+IF(T115=$G114+$H114,1,0)+IF(T116=$I$116,3,0)+IF(T117=$G116+$H116,1,0)+IF(T118=$I$118,3,0)+IF(T119=$G118+$H118,1,0)+IF(T120=$I$120,3,0)+IF(T121=$G120+$H120,1,0)+IF(T122=$I$122,3,0)+IF(T123=$G122+$H122,1,0)+IF(T124=$I$124,3,0)+IF(T125=$G124+$H124,1,0)+IF(T126=$I$126,3,0)+IF(T127=$G126+$H126,1,0)+IF(T128=$I$128,3,0)+IF(T129=$G128+$H128,1,0)+IF(T130=$I$130,3,0)+IF(T131=$G130+$H130,1,0)+IF(T132=$I$132,3,0)+IF(T133=$G132+$H132,1,0)+IF(T134=$I$134,3,0)+IF(T135=$G134+$H134,1,0)+IF(T136=$I$136,3,0)+IF(T137=$G136+$H136,1,0)+IF(T138=$I$138,3,0)+IF(T139=$G138+$H138,1,0)+IF(T140=$I$140,3,0)+IF(T141=$G140+$H140,1,0)+IF(T142=$I$142,3,0)+IF(T143=$G142+$H142,1,0)+IF(T144=$I$144,3,0)+IF(T145=$G144+$H144,1,0)+IF(T146=$I$146,3,0)+IF(T147=$G146+$H146,1,0)+IF(T148=$I$148,3,0)+IF(T149=$G148+$H148,1,0)+IF(T150=$I$150,3,0)+IF(T151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U5" s="75">
-        <f>SUM(IF(U80=$I$80,3,0)+IF(U81=$G80+$H80,1,0)+IF(U82=$I$82,3,0)+IF(U83=$G82+$H82,1,0)+IF(U84=$I$84,3,0)+IF(U85=$G84+$H84,1,0)+IF(U86=$I$86,3,0)+IF(U87=$G86+$H86,1,0)+IF(U88=$I$88,3,0)+IF(U89=$G88+$H88,1,0)+IF(U90=$I$90,3,0)+IF(U91=$G90+$H90,1,0)+IF(U92=$I$92,3,0)+IF(U93=$G92+$H92,1,0)+IF(U94=$I$94,3,0)+IF(U95=$G94+$H94,1,0)+IF(U96=$I$96,3,0)+IF(U97=$G96+$H96,1,0)+IF(U98=$I$98,3,0)+IF(U99=$G98+$H98,1,0)+IF(U100=$I$100,3,0)+IF(U101=$G100+$H100,1,0)+IF(U102=$I$102,3,0)+IF(U103=$G102+$H102,1,0)+IF(U104=$I$104,3,0)+IF(U105=$G104+$H104,1,0)+IF(U106=$I$106,3,0)+IF(U107=$G106+$H106,1,0)+IF(U108=$I$108,3,0)+IF(U109=$G108+$H108,1,0)+IF(U110=$I$110,3,0)+IF(U111=$G110+$H110,1,0)+IF(U112=$I$112,3,0)+IF(U113=$G112+$H112,1,0)+IF(U114=$I$114,3,0)+IF(U115=$G114+$H114,1,0)+IF(U116=$I$116,3,0)+IF(U117=$G116+$H116,1,0)+IF(U118=$I$118,3,0)+IF(U119=$G118+$H118,1,0)+IF(U120=$I$120,3,0)+IF(U121=$G120+$H120,1,0)+IF(U122=$I$122,3,0)+IF(U123=$G122+$H122,1,0)+IF(U124=$I$124,3,0)+IF(U125=$G124+$H124,1,0)+IF(U126=$I$126,3,0)+IF(U127=$G126+$H126,1,0)+IF(U128=$I$128,3,0)+IF(U129=$G128+$H128,1,0)+IF(U130=$I$130,3,0)+IF(U131=$G130+$H130,1,0)+IF(U132=$I$132,3,0)+IF(U133=$G132+$H132,1,0)+IF(U134=$I$134,3,0)+IF(U135=$G134+$H134,1,0)+IF(U136=$I$136,3,0)+IF(U137=$G136+$H136,1,0)+IF(U138=$I$138,3,0)+IF(U139=$G138+$H138,1,0)+IF(U140=$I$140,3,0)+IF(U141=$G140+$H140,1,0)+IF(U142=$I$142,3,0)+IF(U143=$G142+$H142,1,0)+IF(U144=$I$144,3,0)+IF(U145=$G144+$H144,1,0)+IF(U146=$I$146,3,0)+IF(U147=$G146+$H146,1,0)+IF(U148=$I$148,3,0)+IF(U149=$G148+$H148,1,0)+IF(U150=$I$150,3,0)+IF(U151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V5" s="75">
-        <f>SUM(IF(V80=$I$80,3,0)+IF(V81=$G80+$H80,1,0)+IF(V82=$I$82,3,0)+IF(V83=$G82+$H82,1,0)+IF(V84=$I$84,3,0)+IF(V85=$G84+$H84,1,0)+IF(V86=$I$86,3,0)+IF(V87=$G86+$H86,1,0)+IF(V88=$I$88,3,0)+IF(V89=$G88+$H88,1,0)+IF(V90=$I$90,3,0)+IF(V91=$G90+$H90,1,0)+IF(V92=$I$92,3,0)+IF(V93=$G92+$H92,1,0)+IF(V94=$I$94,3,0)+IF(V95=$G94+$H94,1,0)+IF(V96=$I$96,3,0)+IF(V97=$G96+$H96,1,0)+IF(V98=$I$98,3,0)+IF(V99=$G98+$H98,1,0)+IF(V100=$I$100,3,0)+IF(V101=$G100+$H100,1,0)+IF(V102=$I$102,3,0)+IF(V103=$G102+$H102,1,0)+IF(V104=$I$104,3,0)+IF(V105=$G104+$H104,1,0)+IF(V106=$I$106,3,0)+IF(V107=$G106+$H106,1,0)+IF(V108=$I$108,3,0)+IF(V109=$G108+$H108,1,0)+IF(V110=$I$110,3,0)+IF(V111=$G110+$H110,1,0)+IF(V112=$I$112,3,0)+IF(V113=$G112+$H112,1,0)+IF(V114=$I$114,3,0)+IF(V115=$G114+$H114,1,0)+IF(V116=$I$116,3,0)+IF(V117=$G116+$H116,1,0)+IF(V118=$I$118,3,0)+IF(V119=$G118+$H118,1,0)+IF(V120=$I$120,3,0)+IF(V121=$G120+$H120,1,0)+IF(V122=$I$122,3,0)+IF(V123=$G122+$H122,1,0)+IF(V124=$I$124,3,0)+IF(V125=$G124+$H124,1,0)+IF(V126=$I$126,3,0)+IF(V127=$G126+$H126,1,0)+IF(V128=$I$128,3,0)+IF(V129=$G128+$H128,1,0)+IF(V130=$I$130,3,0)+IF(V131=$G130+$H130,1,0)+IF(V132=$I$132,3,0)+IF(V133=$G132+$H132,1,0)+IF(V134=$I$134,3,0)+IF(V135=$G134+$H134,1,0)+IF(V136=$I$136,3,0)+IF(V137=$G136+$H136,1,0)+IF(V138=$I$138,3,0)+IF(V139=$G138+$H138,1,0)+IF(V140=$I$140,3,0)+IF(V141=$G140+$H140,1,0)+IF(V142=$I$142,3,0)+IF(V143=$G142+$H142,1,0)+IF(V144=$I$144,3,0)+IF(V145=$G144+$H144,1,0)+IF(V146=$I$146,3,0)+IF(V147=$G146+$H146,1,0)+IF(V148=$I$148,3,0)+IF(V149=$G148+$H148,1,0)+IF(V150=$I$150,3,0)+IF(V151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W5" s="75">
-        <f>SUM(IF(W80=$I$80,3,0)+IF(W81=$G80+$H80,1,0)+IF(W82=$I$82,3,0)+IF(W83=$G82+$H82,1,0)+IF(W84=$I$84,3,0)+IF(W85=$G84+$H84,1,0)+IF(W86=$I$86,3,0)+IF(W87=$G86+$H86,1,0)+IF(W88=$I$88,3,0)+IF(W89=$G88+$H88,1,0)+IF(W90=$I$90,3,0)+IF(W91=$G90+$H90,1,0)+IF(W92=$I$92,3,0)+IF(W93=$G92+$H92,1,0)+IF(W94=$I$94,3,0)+IF(W95=$G94+$H94,1,0)+IF(W96=$I$96,3,0)+IF(W97=$G96+$H96,1,0)+IF(W98=$I$98,3,0)+IF(W99=$G98+$H98,1,0)+IF(W100=$I$100,3,0)+IF(W101=$G100+$H100,1,0)+IF(W102=$I$102,3,0)+IF(W103=$G102+$H102,1,0)+IF(W104=$I$104,3,0)+IF(W105=$G104+$H104,1,0)+IF(W106=$I$106,3,0)+IF(W107=$G106+$H106,1,0)+IF(W108=$I$108,3,0)+IF(W109=$G108+$H108,1,0)+IF(W110=$I$110,3,0)+IF(W111=$G110+$H110,1,0)+IF(W112=$I$112,3,0)+IF(W113=$G112+$H112,1,0)+IF(W114=$I$114,3,0)+IF(W115=$G114+$H114,1,0)+IF(W116=$I$116,3,0)+IF(W117=$G116+$H116,1,0)+IF(W118=$I$118,3,0)+IF(W119=$G118+$H118,1,0)+IF(W120=$I$120,3,0)+IF(W121=$G120+$H120,1,0)+IF(W122=$I$122,3,0)+IF(W123=$G122+$H122,1,0)+IF(W124=$I$124,3,0)+IF(W125=$G124+$H124,1,0)+IF(W126=$I$126,3,0)+IF(W127=$G126+$H126,1,0)+IF(W128=$I$128,3,0)+IF(W129=$G128+$H128,1,0)+IF(W130=$I$130,3,0)+IF(W131=$G130+$H130,1,0)+IF(W132=$I$132,3,0)+IF(W133=$G132+$H132,1,0)+IF(W134=$I$134,3,0)+IF(W135=$G134+$H134,1,0)+IF(W136=$I$136,3,0)+IF(W137=$G136+$H136,1,0)+IF(W138=$I$138,3,0)+IF(W139=$G138+$H138,1,0)+IF(W140=$I$140,3,0)+IF(W141=$G140+$H140,1,0)+IF(W142=$I$142,3,0)+IF(W143=$G142+$H142,1,0)+IF(W144=$I$144,3,0)+IF(W145=$G144+$H144,1,0)+IF(W146=$I$146,3,0)+IF(W147=$G146+$H146,1,0)+IF(W148=$I$148,3,0)+IF(W149=$G148+$H148,1,0)+IF(W150=$I$150,3,0)+IF(W151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="X5" s="75">
-        <f>SUM(IF(X80=$I$80,3,0)+IF(X81=$G80+$H80,1,0)+IF(X82=$I$82,3,0)+IF(X83=$G82+$H82,1,0)+IF(X84=$I$84,3,0)+IF(X85=$G84+$H84,1,0)+IF(X86=$I$86,3,0)+IF(X87=$G86+$H86,1,0)+IF(X88=$I$88,3,0)+IF(X89=$G88+$H88,1,0)+IF(X90=$I$90,3,0)+IF(X91=$G90+$H90,1,0)+IF(X92=$I$92,3,0)+IF(X93=$G92+$H92,1,0)+IF(X94=$I$94,3,0)+IF(X95=$G94+$H94,1,0)+IF(X96=$I$96,3,0)+IF(X97=$G96+$H96,1,0)+IF(X98=$I$98,3,0)+IF(X99=$G98+$H98,1,0)+IF(X100=$I$100,3,0)+IF(X101=$G100+$H100,1,0)+IF(X102=$I$102,3,0)+IF(X103=$G102+$H102,1,0)+IF(X104=$I$104,3,0)+IF(X105=$G104+$H104,1,0)+IF(X106=$I$106,3,0)+IF(X107=$G106+$H106,1,0)+IF(X108=$I$108,3,0)+IF(X109=$G108+$H108,1,0)+IF(X110=$I$110,3,0)+IF(X111=$G110+$H110,1,0)+IF(X112=$I$112,3,0)+IF(X113=$G112+$H112,1,0)+IF(X114=$I$114,3,0)+IF(X115=$G114+$H114,1,0)+IF(X116=$I$116,3,0)+IF(X117=$G116+$H116,1,0)+IF(X118=$I$118,3,0)+IF(X119=$G118+$H118,1,0)+IF(X120=$I$120,3,0)+IF(X121=$G120+$H120,1,0)+IF(X122=$I$122,3,0)+IF(X123=$G122+$H122,1,0)+IF(X124=$I$124,3,0)+IF(X125=$G124+$H124,1,0)+IF(X126=$I$126,3,0)+IF(X127=$G126+$H126,1,0)+IF(X128=$I$128,3,0)+IF(X129=$G128+$H128,1,0)+IF(X130=$I$130,3,0)+IF(X131=$G130+$H130,1,0)+IF(X132=$I$132,3,0)+IF(X133=$G132+$H132,1,0)+IF(X134=$I$134,3,0)+IF(X135=$G134+$H134,1,0)+IF(X136=$I$136,3,0)+IF(X137=$G136+$H136,1,0)+IF(X138=$I$138,3,0)+IF(X139=$G138+$H138,1,0)+IF(X140=$I$140,3,0)+IF(X141=$G140+$H140,1,0)+IF(X142=$I$142,3,0)+IF(X143=$G142+$H142,1,0)+IF(X144=$I$144,3,0)+IF(X145=$G144+$H144,1,0)+IF(X146=$I$146,3,0)+IF(X147=$G146+$H146,1,0)+IF(X148=$I$148,3,0)+IF(X149=$G148+$H148,1,0)+IF(X150=$I$150,3,0)+IF(X151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y5" s="75">
-        <f>SUM(IF(Y80=$I$80,3,0)+IF(Y81=$G80+$H80,1,0)+IF(Y82=$I$82,3,0)+IF(Y83=$G82+$H82,1,0)+IF(Y84=$I$84,3,0)+IF(Y85=$G84+$H84,1,0)+IF(Y86=$I$86,3,0)+IF(Y87=$G86+$H86,1,0)+IF(Y88=$I$88,3,0)+IF(Y89=$G88+$H88,1,0)+IF(Y90=$I$90,3,0)+IF(Y91=$G90+$H90,1,0)+IF(Y92=$I$92,3,0)+IF(Y93=$G92+$H92,1,0)+IF(Y94=$I$94,3,0)+IF(Y95=$G94+$H94,1,0)+IF(Y96=$I$96,3,0)+IF(Y97=$G96+$H96,1,0)+IF(Y98=$I$98,3,0)+IF(Y99=$G98+$H98,1,0)+IF(Y100=$I$100,3,0)+IF(Y101=$G100+$H100,1,0)+IF(Y102=$I$102,3,0)+IF(Y103=$G102+$H102,1,0)+IF(Y104=$I$104,3,0)+IF(Y105=$G104+$H104,1,0)+IF(Y106=$I$106,3,0)+IF(Y107=$G106+$H106,1,0)+IF(Y108=$I$108,3,0)+IF(Y109=$G108+$H108,1,0)+IF(Y110=$I$110,3,0)+IF(Y111=$G110+$H110,1,0)+IF(Y112=$I$112,3,0)+IF(Y113=$G112+$H112,1,0)+IF(Y114=$I$114,3,0)+IF(Y115=$G114+$H114,1,0)+IF(Y116=$I$116,3,0)+IF(Y117=$G116+$H116,1,0)+IF(Y118=$I$118,3,0)+IF(Y119=$G118+$H118,1,0)+IF(Y120=$I$120,3,0)+IF(Y121=$G120+$H120,1,0)+IF(Y122=$I$122,3,0)+IF(Y123=$G122+$H122,1,0)+IF(Y124=$I$124,3,0)+IF(Y125=$G124+$H124,1,0)+IF(Y126=$I$126,3,0)+IF(Y127=$G126+$H126,1,0)+IF(Y128=$I$128,3,0)+IF(Y129=$G128+$H128,1,0)+IF(Y130=$I$130,3,0)+IF(Y131=$G130+$H130,1,0)+IF(Y132=$I$132,3,0)+IF(Y133=$G132+$H132,1,0)+IF(Y134=$I$134,3,0)+IF(Y135=$G134+$H134,1,0)+IF(Y136=$I$136,3,0)+IF(Y137=$G136+$H136,1,0)+IF(Y138=$I$138,3,0)+IF(Y139=$G138+$H138,1,0)+IF(Y140=$I$140,3,0)+IF(Y141=$G140+$H140,1,0)+IF(Y142=$I$142,3,0)+IF(Y143=$G142+$H142,1,0)+IF(Y144=$I$144,3,0)+IF(Y145=$G144+$H144,1,0)+IF(Y146=$I$146,3,0)+IF(Y147=$G146+$H146,1,0)+IF(Y148=$I$148,3,0)+IF(Y149=$G148+$H148,1,0)+IF(Y150=$I$150,3,0)+IF(Y151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Z5" s="75">
-        <f>SUM(IF(Z80=$I$80,3,0)+IF(Z81=$G80+$H80,1,0)+IF(Z82=$I$82,3,0)+IF(Z83=$G82+$H82,1,0)+IF(Z84=$I$84,3,0)+IF(Z85=$G84+$H84,1,0)+IF(Z86=$I$86,3,0)+IF(Z87=$G86+$H86,1,0)+IF(Z88=$I$88,3,0)+IF(Z89=$G88+$H88,1,0)+IF(Z90=$I$90,3,0)+IF(Z91=$G90+$H90,1,0)+IF(Z92=$I$92,3,0)+IF(Z93=$G92+$H92,1,0)+IF(Z94=$I$94,3,0)+IF(Z95=$G94+$H94,1,0)+IF(Z96=$I$96,3,0)+IF(Z97=$G96+$H96,1,0)+IF(Z98=$I$98,3,0)+IF(Z99=$G98+$H98,1,0)+IF(Z100=$I$100,3,0)+IF(Z101=$G100+$H100,1,0)+IF(Z102=$I$102,3,0)+IF(Z103=$G102+$H102,1,0)+IF(Z104=$I$104,3,0)+IF(Z105=$G104+$H104,1,0)+IF(Z106=$I$106,3,0)+IF(Z107=$G106+$H106,1,0)+IF(Z108=$I$108,3,0)+IF(Z109=$G108+$H108,1,0)+IF(Z110=$I$110,3,0)+IF(Z111=$G110+$H110,1,0)+IF(Z112=$I$112,3,0)+IF(Z113=$G112+$H112,1,0)+IF(Z114=$I$114,3,0)+IF(Z115=$G114+$H114,1,0)+IF(Z116=$I$116,3,0)+IF(Z117=$G116+$H116,1,0)+IF(Z118=$I$118,3,0)+IF(Z119=$G118+$H118,1,0)+IF(Z120=$I$120,3,0)+IF(Z121=$G120+$H120,1,0)+IF(Z122=$I$122,3,0)+IF(Z123=$G122+$H122,1,0)+IF(Z124=$I$124,3,0)+IF(Z125=$G124+$H124,1,0)+IF(Z126=$I$126,3,0)+IF(Z127=$G126+$H126,1,0)+IF(Z128=$I$128,3,0)+IF(Z129=$G128+$H128,1,0)+IF(Z130=$I$130,3,0)+IF(Z131=$G130+$H130,1,0)+IF(Z132=$I$132,3,0)+IF(Z133=$G132+$H132,1,0)+IF(Z134=$I$134,3,0)+IF(Z135=$G134+$H134,1,0)+IF(Z136=$I$136,3,0)+IF(Z137=$G136+$H136,1,0)+IF(Z138=$I$138,3,0)+IF(Z139=$G138+$H138,1,0)+IF(Z140=$I$140,3,0)+IF(Z141=$G140+$H140,1,0)+IF(Z142=$I$142,3,0)+IF(Z143=$G142+$H142,1,0)+IF(Z144=$I$144,3,0)+IF(Z145=$G144+$H144,1,0)+IF(Z146=$I$146,3,0)+IF(Z147=$G146+$H146,1,0)+IF(Z148=$I$148,3,0)+IF(Z149=$G148+$H148,1,0)+IF(Z150=$I$150,3,0)+IF(Z151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AA5" s="75">
-        <f>SUM(IF(AA80=$I$80,3,0)+IF(AA81=$G80+$H80,1,0)+IF(AA82=$I$82,3,0)+IF(AA83=$G82+$H82,1,0)+IF(AA84=$I$84,3,0)+IF(AA85=$G84+$H84,1,0)+IF(AA86=$I$86,3,0)+IF(AA87=$G86+$H86,1,0)+IF(AA88=$I$88,3,0)+IF(AA89=$G88+$H88,1,0)+IF(AA90=$I$90,3,0)+IF(AA91=$G90+$H90,1,0)+IF(AA92=$I$92,3,0)+IF(AA93=$G92+$H92,1,0)+IF(AA94=$I$94,3,0)+IF(AA95=$G94+$H94,1,0)+IF(AA96=$I$96,3,0)+IF(AA97=$G96+$H96,1,0)+IF(AA98=$I$98,3,0)+IF(AA99=$G98+$H98,1,0)+IF(AA100=$I$100,3,0)+IF(AA101=$G100+$H100,1,0)+IF(AA102=$I$102,3,0)+IF(AA103=$G102+$H102,1,0)+IF(AA104=$I$104,3,0)+IF(AA105=$G104+$H104,1,0)+IF(AA106=$I$106,3,0)+IF(AA107=$G106+$H106,1,0)+IF(AA108=$I$108,3,0)+IF(AA109=$G108+$H108,1,0)+IF(AA110=$I$110,3,0)+IF(AA111=$G110+$H110,1,0)+IF(AA112=$I$112,3,0)+IF(AA113=$G112+$H112,1,0)+IF(AA114=$I$114,3,0)+IF(AA115=$G114+$H114,1,0)+IF(AA116=$I$116,3,0)+IF(AA117=$G116+$H116,1,0)+IF(AA118=$I$118,3,0)+IF(AA119=$G118+$H118,1,0)+IF(AA120=$I$120,3,0)+IF(AA121=$G120+$H120,1,0)+IF(AA122=$I$122,3,0)+IF(AA123=$G122+$H122,1,0)+IF(AA124=$I$124,3,0)+IF(AA125=$G124+$H124,1,0)+IF(AA126=$I$126,3,0)+IF(AA127=$G126+$H126,1,0)+IF(AA128=$I$128,3,0)+IF(AA129=$G128+$H128,1,0)+IF(AA130=$I$130,3,0)+IF(AA131=$G130+$H130,1,0)+IF(AA132=$I$132,3,0)+IF(AA133=$G132+$H132,1,0)+IF(AA134=$I$134,3,0)+IF(AA135=$G134+$H134,1,0)+IF(AA136=$I$136,3,0)+IF(AA137=$G136+$H136,1,0)+IF(AA138=$I$138,3,0)+IF(AA139=$G138+$H138,1,0)+IF(AA140=$I$140,3,0)+IF(AA141=$G140+$H140,1,0)+IF(AA142=$I$142,3,0)+IF(AA143=$G142+$H142,1,0)+IF(AA144=$I$144,3,0)+IF(AA145=$G144+$H144,1,0)+IF(AA146=$I$146,3,0)+IF(AA147=$G146+$H146,1,0)+IF(AA148=$I$148,3,0)+IF(AA149=$G148+$H148,1,0)+IF(AA150=$I$150,3,0)+IF(AA151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AB5" s="75">
-        <f>SUM(IF(AB80=$I$80,3,0)+IF(AB81=$G80+$H80,1,0)+IF(AB82=$I$82,3,0)+IF(AB83=$G82+$H82,1,0)+IF(AB84=$I$84,3,0)+IF(AB85=$G84+$H84,1,0)+IF(AB86=$I$86,3,0)+IF(AB87=$G86+$H86,1,0)+IF(AB88=$I$88,3,0)+IF(AB89=$G88+$H88,1,0)+IF(AB90=$I$90,3,0)+IF(AB91=$G90+$H90,1,0)+IF(AB92=$I$92,3,0)+IF(AB93=$G92+$H92,1,0)+IF(AB94=$I$94,3,0)+IF(AB95=$G94+$H94,1,0)+IF(AB96=$I$96,3,0)+IF(AB97=$G96+$H96,1,0)+IF(AB98=$I$98,3,0)+IF(AB99=$G98+$H98,1,0)+IF(AB100=$I$100,3,0)+IF(AB101=$G100+$H100,1,0)+IF(AB102=$I$102,3,0)+IF(AB103=$G102+$H102,1,0)+IF(AB104=$I$104,3,0)+IF(AB105=$G104+$H104,1,0)+IF(AB106=$I$106,3,0)+IF(AB107=$G106+$H106,1,0)+IF(AB108=$I$108,3,0)+IF(AB109=$G108+$H108,1,0)+IF(AB110=$I$110,3,0)+IF(AB111=$G110+$H110,1,0)+IF(AB112=$I$112,3,0)+IF(AB113=$G112+$H112,1,0)+IF(AB114=$I$114,3,0)+IF(AB115=$G114+$H114,1,0)+IF(AB116=$I$116,3,0)+IF(AB117=$G116+$H116,1,0)+IF(AB118=$I$118,3,0)+IF(AB119=$G118+$H118,1,0)+IF(AB120=$I$120,3,0)+IF(AB121=$G120+$H120,1,0)+IF(AB122=$I$122,3,0)+IF(AB123=$G122+$H122,1,0)+IF(AB124=$I$124,3,0)+IF(AB125=$G124+$H124,1,0)+IF(AB126=$I$126,3,0)+IF(AB127=$G126+$H126,1,0)+IF(AB128=$I$128,3,0)+IF(AB129=$G128+$H128,1,0)+IF(AB130=$I$130,3,0)+IF(AB131=$G130+$H130,1,0)+IF(AB132=$I$132,3,0)+IF(AB133=$G132+$H132,1,0)+IF(AB134=$I$134,3,0)+IF(AB135=$G134+$H134,1,0)+IF(AB136=$I$136,3,0)+IF(AB137=$G136+$H136,1,0)+IF(AB138=$I$138,3,0)+IF(AB139=$G138+$H138,1,0)+IF(AB140=$I$140,3,0)+IF(AB141=$G140+$H140,1,0)+IF(AB142=$I$142,3,0)+IF(AB143=$G142+$H142,1,0)+IF(AB144=$I$144,3,0)+IF(AB145=$G144+$H144,1,0)+IF(AB146=$I$146,3,0)+IF(AB147=$G146+$H146,1,0)+IF(AB148=$I$148,3,0)+IF(AB149=$G148+$H148,1,0)+IF(AB150=$I$150,3,0)+IF(AB151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AC5" s="75">
-        <f>SUM(IF(AC80=$I$80,3,0)+IF(AC81=$G80+$H80,1,0)+IF(AC82=$I$82,3,0)+IF(AC83=$G82+$H82,1,0)+IF(AC84=$I$84,3,0)+IF(AC85=$G84+$H84,1,0)+IF(AC86=$I$86,3,0)+IF(AC87=$G86+$H86,1,0)+IF(AC88=$I$88,3,0)+IF(AC89=$G88+$H88,1,0)+IF(AC90=$I$90,3,0)+IF(AC91=$G90+$H90,1,0)+IF(AC92=$I$92,3,0)+IF(AC93=$G92+$H92,1,0)+IF(AC94=$I$94,3,0)+IF(AC95=$G94+$H94,1,0)+IF(AC96=$I$96,3,0)+IF(AC97=$G96+$H96,1,0)+IF(AC98=$I$98,3,0)+IF(AC99=$G98+$H98,1,0)+IF(AC100=$I$100,3,0)+IF(AC101=$G100+$H100,1,0)+IF(AC102=$I$102,3,0)+IF(AC103=$G102+$H102,1,0)+IF(AC104=$I$104,3,0)+IF(AC105=$G104+$H104,1,0)+IF(AC106=$I$106,3,0)+IF(AC107=$G106+$H106,1,0)+IF(AC108=$I$108,3,0)+IF(AC109=$G108+$H108,1,0)+IF(AC110=$I$110,3,0)+IF(AC111=$G110+$H110,1,0)+IF(AC112=$I$112,3,0)+IF(AC113=$G112+$H112,1,0)+IF(AC114=$I$114,3,0)+IF(AC115=$G114+$H114,1,0)+IF(AC116=$I$116,3,0)+IF(AC117=$G116+$H116,1,0)+IF(AC118=$I$118,3,0)+IF(AC119=$G118+$H118,1,0)+IF(AC120=$I$120,3,0)+IF(AC121=$G120+$H120,1,0)+IF(AC122=$I$122,3,0)+IF(AC123=$G122+$H122,1,0)+IF(AC124=$I$124,3,0)+IF(AC125=$G124+$H124,1,0)+IF(AC126=$I$126,3,0)+IF(AC127=$G126+$H126,1,0)+IF(AC128=$I$128,3,0)+IF(AC129=$G128+$H128,1,0)+IF(AC130=$I$130,3,0)+IF(AC131=$G130+$H130,1,0)+IF(AC132=$I$132,3,0)+IF(AC133=$G132+$H132,1,0)+IF(AC134=$I$134,3,0)+IF(AC135=$G134+$H134,1,0)+IF(AC136=$I$136,3,0)+IF(AC137=$G136+$H136,1,0)+IF(AC138=$I$138,3,0)+IF(AC139=$G138+$H138,1,0)+IF(AC140=$I$140,3,0)+IF(AC141=$G140+$H140,1,0)+IF(AC142=$I$142,3,0)+IF(AC143=$G142+$H142,1,0)+IF(AC144=$I$144,3,0)+IF(AC145=$G144+$H144,1,0)+IF(AC146=$I$146,3,0)+IF(AC147=$G146+$H146,1,0)+IF(AC148=$I$148,3,0)+IF(AC149=$G148+$H148,1,0)+IF(AC150=$I$150,3,0)+IF(AC151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD5" s="75">
-        <f>SUM(IF(AD80=$I$80,3,0)+IF(AD81=$G80+$H80,1,0)+IF(AD82=$I$82,3,0)+IF(AD83=$G82+$H82,1,0)+IF(AD84=$I$84,3,0)+IF(AD85=$G84+$H84,1,0)+IF(AD86=$I$86,3,0)+IF(AD87=$G86+$H86,1,0)+IF(AD88=$I$88,3,0)+IF(AD89=$G88+$H88,1,0)+IF(AD90=$I$90,3,0)+IF(AD91=$G90+$H90,1,0)+IF(AD92=$I$92,3,0)+IF(AD93=$G92+$H92,1,0)+IF(AD94=$I$94,3,0)+IF(AD95=$G94+$H94,1,0)+IF(AD96=$I$96,3,0)+IF(AD97=$G96+$H96,1,0)+IF(AD98=$I$98,3,0)+IF(AD99=$G98+$H98,1,0)+IF(AD100=$I$100,3,0)+IF(AD101=$G100+$H100,1,0)+IF(AD102=$I$102,3,0)+IF(AD103=$G102+$H102,1,0)+IF(AD104=$I$104,3,0)+IF(AD105=$G104+$H104,1,0)+IF(AD106=$I$106,3,0)+IF(AD107=$G106+$H106,1,0)+IF(AD108=$I$108,3,0)+IF(AD109=$G108+$H108,1,0)+IF(AD110=$I$110,3,0)+IF(AD111=$G110+$H110,1,0)+IF(AD112=$I$112,3,0)+IF(AD113=$G112+$H112,1,0)+IF(AD114=$I$114,3,0)+IF(AD115=$G114+$H114,1,0)+IF(AD116=$I$116,3,0)+IF(AD117=$G116+$H116,1,0)+IF(AD118=$I$118,3,0)+IF(AD119=$G118+$H118,1,0)+IF(AD120=$I$120,3,0)+IF(AD121=$G120+$H120,1,0)+IF(AD122=$I$122,3,0)+IF(AD123=$G122+$H122,1,0)+IF(AD124=$I$124,3,0)+IF(AD125=$G124+$H124,1,0)+IF(AD126=$I$126,3,0)+IF(AD127=$G126+$H126,1,0)+IF(AD128=$I$128,3,0)+IF(AD129=$G128+$H128,1,0)+IF(AD130=$I$130,3,0)+IF(AD131=$G130+$H130,1,0)+IF(AD132=$I$132,3,0)+IF(AD133=$G132+$H132,1,0)+IF(AD134=$I$134,3,0)+IF(AD135=$G134+$H134,1,0)+IF(AD136=$I$136,3,0)+IF(AD137=$G136+$H136,1,0)+IF(AD138=$I$138,3,0)+IF(AD139=$G138+$H138,1,0)+IF(AD140=$I$140,3,0)+IF(AD141=$G140+$H140,1,0)+IF(AD142=$I$142,3,0)+IF(AD143=$G142+$H142,1,0)+IF(AD144=$I$144,3,0)+IF(AD145=$G144+$H144,1,0)+IF(AD146=$I$146,3,0)+IF(AD147=$G146+$H146,1,0)+IF(AD148=$I$148,3,0)+IF(AD149=$G148+$H148,1,0)+IF(AD150=$I$150,3,0)+IF(AD151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AE5" s="75">
-        <f>SUM(IF(AE80=$I$80,3,0)+IF(AE81=$G80+$H80,1,0)+IF(AE82=$I$82,3,0)+IF(AE83=$G82+$H82,1,0)+IF(AE84=$I$84,3,0)+IF(AE85=$G84+$H84,1,0)+IF(AE86=$I$86,3,0)+IF(AE87=$G86+$H86,1,0)+IF(AE88=$I$88,3,0)+IF(AE89=$G88+$H88,1,0)+IF(AE90=$I$90,3,0)+IF(AE91=$G90+$H90,1,0)+IF(AE92=$I$92,3,0)+IF(AE93=$G92+$H92,1,0)+IF(AE94=$I$94,3,0)+IF(AE95=$G94+$H94,1,0)+IF(AE96=$I$96,3,0)+IF(AE97=$G96+$H96,1,0)+IF(AE98=$I$98,3,0)+IF(AE99=$G98+$H98,1,0)+IF(AE100=$I$100,3,0)+IF(AE101=$G100+$H100,1,0)+IF(AE102=$I$102,3,0)+IF(AE103=$G102+$H102,1,0)+IF(AE104=$I$104,3,0)+IF(AE105=$G104+$H104,1,0)+IF(AE106=$I$106,3,0)+IF(AE107=$G106+$H106,1,0)+IF(AE108=$I$108,3,0)+IF(AE109=$G108+$H108,1,0)+IF(AE110=$I$110,3,0)+IF(AE111=$G110+$H110,1,0)+IF(AE112=$I$112,3,0)+IF(AE113=$G112+$H112,1,0)+IF(AE114=$I$114,3,0)+IF(AE115=$G114+$H114,1,0)+IF(AE116=$I$116,3,0)+IF(AE117=$G116+$H116,1,0)+IF(AE118=$I$118,3,0)+IF(AE119=$G118+$H118,1,0)+IF(AE120=$I$120,3,0)+IF(AE121=$G120+$H120,1,0)+IF(AE122=$I$122,3,0)+IF(AE123=$G122+$H122,1,0)+IF(AE124=$I$124,3,0)+IF(AE125=$G124+$H124,1,0)+IF(AE126=$I$126,3,0)+IF(AE127=$G126+$H126,1,0)+IF(AE128=$I$128,3,0)+IF(AE129=$G128+$H128,1,0)+IF(AE130=$I$130,3,0)+IF(AE131=$G130+$H130,1,0)+IF(AE132=$I$132,3,0)+IF(AE133=$G132+$H132,1,0)+IF(AE134=$I$134,3,0)+IF(AE135=$G134+$H134,1,0)+IF(AE136=$I$136,3,0)+IF(AE137=$G136+$H136,1,0)+IF(AE138=$I$138,3,0)+IF(AE139=$G138+$H138,1,0)+IF(AE140=$I$140,3,0)+IF(AE141=$G140+$H140,1,0)+IF(AE142=$I$142,3,0)+IF(AE143=$G142+$H142,1,0)+IF(AE144=$I$144,3,0)+IF(AE145=$G144+$H144,1,0)+IF(AE146=$I$146,3,0)+IF(AE147=$G146+$H146,1,0)+IF(AE148=$I$148,3,0)+IF(AE149=$G148+$H148,1,0)+IF(AE150=$I$150,3,0)+IF(AE151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AF5" s="75">
-        <f>SUM(IF(AF80=$I$80,3,0)+IF(AF81=$G80+$H80,1,0)+IF(AF82=$I$82,3,0)+IF(AF83=$G82+$H82,1,0)+IF(AF84=$I$84,3,0)+IF(AF85=$G84+$H84,1,0)+IF(AF86=$I$86,3,0)+IF(AF87=$G86+$H86,1,0)+IF(AF88=$I$88,3,0)+IF(AF89=$G88+$H88,1,0)+IF(AF90=$I$90,3,0)+IF(AF91=$G90+$H90,1,0)+IF(AF92=$I$92,3,0)+IF(AF93=$G92+$H92,1,0)+IF(AF94=$I$94,3,0)+IF(AF95=$G94+$H94,1,0)+IF(AF96=$I$96,3,0)+IF(AF97=$G96+$H96,1,0)+IF(AF98=$I$98,3,0)+IF(AF99=$G98+$H98,1,0)+IF(AF100=$I$100,3,0)+IF(AF101=$G100+$H100,1,0)+IF(AF102=$I$102,3,0)+IF(AF103=$G102+$H102,1,0)+IF(AF104=$I$104,3,0)+IF(AF105=$G104+$H104,1,0)+IF(AF106=$I$106,3,0)+IF(AF107=$G106+$H106,1,0)+IF(AF108=$I$108,3,0)+IF(AF109=$G108+$H108,1,0)+IF(AF110=$I$110,3,0)+IF(AF111=$G110+$H110,1,0)+IF(AF112=$I$112,3,0)+IF(AF113=$G112+$H112,1,0)+IF(AF114=$I$114,3,0)+IF(AF115=$G114+$H114,1,0)+IF(AF116=$I$116,3,0)+IF(AF117=$G116+$H116,1,0)+IF(AF118=$I$118,3,0)+IF(AF119=$G118+$H118,1,0)+IF(AF120=$I$120,3,0)+IF(AF121=$G120+$H120,1,0)+IF(AF122=$I$122,3,0)+IF(AF123=$G122+$H122,1,0)+IF(AF124=$I$124,3,0)+IF(AF125=$G124+$H124,1,0)+IF(AF126=$I$126,3,0)+IF(AF127=$G126+$H126,1,0)+IF(AF128=$I$128,3,0)+IF(AF129=$G128+$H128,1,0)+IF(AF130=$I$130,3,0)+IF(AF131=$G130+$H130,1,0)+IF(AF132=$I$132,3,0)+IF(AF133=$G132+$H132,1,0)+IF(AF134=$I$134,3,0)+IF(AF135=$G134+$H134,1,0)+IF(AF136=$I$136,3,0)+IF(AF137=$G136+$H136,1,0)+IF(AF138=$I$138,3,0)+IF(AF139=$G138+$H138,1,0)+IF(AF140=$I$140,3,0)+IF(AF141=$G140+$H140,1,0)+IF(AF142=$I$142,3,0)+IF(AF143=$G142+$H142,1,0)+IF(AF144=$I$144,3,0)+IF(AF145=$G144+$H144,1,0)+IF(AF146=$I$146,3,0)+IF(AF147=$G146+$H146,1,0)+IF(AF148=$I$148,3,0)+IF(AF149=$G148+$H148,1,0)+IF(AF150=$I$150,3,0)+IF(AF151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG5" s="75">
-        <f>SUM(IF(AG80=$I$80,3,0)+IF(AG81=$G80+$H80,1,0)+IF(AG82=$I$82,3,0)+IF(AG83=$G82+$H82,1,0)+IF(AG84=$I$84,3,0)+IF(AG85=$G84+$H84,1,0)+IF(AG86=$I$86,3,0)+IF(AG87=$G86+$H86,1,0)+IF(AG88=$I$88,3,0)+IF(AG89=$G88+$H88,1,0)+IF(AG90=$I$90,3,0)+IF(AG91=$G90+$H90,1,0)+IF(AG92=$I$92,3,0)+IF(AG93=$G92+$H92,1,0)+IF(AG94=$I$94,3,0)+IF(AG95=$G94+$H94,1,0)+IF(AG96=$I$96,3,0)+IF(AG97=$G96+$H96,1,0)+IF(AG98=$I$98,3,0)+IF(AG99=$G98+$H98,1,0)+IF(AG100=$I$100,3,0)+IF(AG101=$G100+$H100,1,0)+IF(AG102=$I$102,3,0)+IF(AG103=$G102+$H102,1,0)+IF(AG104=$I$104,3,0)+IF(AG105=$G104+$H104,1,0)+IF(AG106=$I$106,3,0)+IF(AG107=$G106+$H106,1,0)+IF(AG108=$I$108,3,0)+IF(AG109=$G108+$H108,1,0)+IF(AG110=$I$110,3,0)+IF(AG111=$G110+$H110,1,0)+IF(AG112=$I$112,3,0)+IF(AG113=$G112+$H112,1,0)+IF(AG114=$I$114,3,0)+IF(AG115=$G114+$H114,1,0)+IF(AG116=$I$116,3,0)+IF(AG117=$G116+$H116,1,0)+IF(AG118=$I$118,3,0)+IF(AG119=$G118+$H118,1,0)+IF(AG120=$I$120,3,0)+IF(AG121=$G120+$H120,1,0)+IF(AG122=$I$122,3,0)+IF(AG123=$G122+$H122,1,0)+IF(AG124=$I$124,3,0)+IF(AG125=$G124+$H124,1,0)+IF(AG126=$I$126,3,0)+IF(AG127=$G126+$H126,1,0)+IF(AG128=$I$128,3,0)+IF(AG129=$G128+$H128,1,0)+IF(AG130=$I$130,3,0)+IF(AG131=$G130+$H130,1,0)+IF(AG132=$I$132,3,0)+IF(AG133=$G132+$H132,1,0)+IF(AG134=$I$134,3,0)+IF(AG135=$G134+$H134,1,0)+IF(AG136=$I$136,3,0)+IF(AG137=$G136+$H136,1,0)+IF(AG138=$I$138,3,0)+IF(AG139=$G138+$H138,1,0)+IF(AG140=$I$140,3,0)+IF(AG141=$G140+$H140,1,0)+IF(AG142=$I$142,3,0)+IF(AG143=$G142+$H142,1,0)+IF(AG144=$I$144,3,0)+IF(AG145=$G144+$H144,1,0)+IF(AG146=$I$146,3,0)+IF(AG147=$G146+$H146,1,0)+IF(AG148=$I$148,3,0)+IF(AG149=$G148+$H148,1,0)+IF(AG150=$I$150,3,0)+IF(AG151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AH5" s="75">
-        <f>SUM(IF(AH80=$I$80,3,0)+IF(AH81=$G80+$H80,1,0)+IF(AH82=$I$82,3,0)+IF(AH83=$G82+$H82,1,0)+IF(AH84=$I$84,3,0)+IF(AH85=$G84+$H84,1,0)+IF(AH86=$I$86,3,0)+IF(AH87=$G86+$H86,1,0)+IF(AH88=$I$88,3,0)+IF(AH89=$G88+$H88,1,0)+IF(AH90=$I$90,3,0)+IF(AH91=$G90+$H90,1,0)+IF(AH92=$I$92,3,0)+IF(AH93=$G92+$H92,1,0)+IF(AH94=$I$94,3,0)+IF(AH95=$G94+$H94,1,0)+IF(AH96=$I$96,3,0)+IF(AH97=$G96+$H96,1,0)+IF(AH98=$I$98,3,0)+IF(AH99=$G98+$H98,1,0)+IF(AH100=$I$100,3,0)+IF(AH101=$G100+$H100,1,0)+IF(AH102=$I$102,3,0)+IF(AH103=$G102+$H102,1,0)+IF(AH104=$I$104,3,0)+IF(AH105=$G104+$H104,1,0)+IF(AH106=$I$106,3,0)+IF(AH107=$G106+$H106,1,0)+IF(AH108=$I$108,3,0)+IF(AH109=$G108+$H108,1,0)+IF(AH110=$I$110,3,0)+IF(AH111=$G110+$H110,1,0)+IF(AH112=$I$112,3,0)+IF(AH113=$G112+$H112,1,0)+IF(AH114=$I$114,3,0)+IF(AH115=$G114+$H114,1,0)+IF(AH116=$I$116,3,0)+IF(AH117=$G116+$H116,1,0)+IF(AH118=$I$118,3,0)+IF(AH119=$G118+$H118,1,0)+IF(AH120=$I$120,3,0)+IF(AH121=$G120+$H120,1,0)+IF(AH122=$I$122,3,0)+IF(AH123=$G122+$H122,1,0)+IF(AH124=$I$124,3,0)+IF(AH125=$G124+$H124,1,0)+IF(AH126=$I$126,3,0)+IF(AH127=$G126+$H126,1,0)+IF(AH128=$I$128,3,0)+IF(AH129=$G128+$H128,1,0)+IF(AH130=$I$130,3,0)+IF(AH131=$G130+$H130,1,0)+IF(AH132=$I$132,3,0)+IF(AH133=$G132+$H132,1,0)+IF(AH134=$I$134,3,0)+IF(AH135=$G134+$H134,1,0)+IF(AH136=$I$136,3,0)+IF(AH137=$G136+$H136,1,0)+IF(AH138=$I$138,3,0)+IF(AH139=$G138+$H138,1,0)+IF(AH140=$I$140,3,0)+IF(AH141=$G140+$H140,1,0)+IF(AH142=$I$142,3,0)+IF(AH143=$G142+$H142,1,0)+IF(AH144=$I$144,3,0)+IF(AH145=$G144+$H144,1,0)+IF(AH146=$I$146,3,0)+IF(AH147=$G146+$H146,1,0)+IF(AH148=$I$148,3,0)+IF(AH149=$G148+$H148,1,0)+IF(AH150=$I$150,3,0)+IF(AH151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AI5" s="75">
-        <f>SUM(IF(AI80=$I$80,3,0)+IF(AI81=$G80+$H80,1,0)+IF(AI82=$I$82,3,0)+IF(AI83=$G82+$H82,1,0)+IF(AI84=$I$84,3,0)+IF(AI85=$G84+$H84,1,0)+IF(AI86=$I$86,3,0)+IF(AI87=$G86+$H86,1,0)+IF(AI88=$I$88,3,0)+IF(AI89=$G88+$H88,1,0)+IF(AI90=$I$90,3,0)+IF(AI91=$G90+$H90,1,0)+IF(AI92=$I$92,3,0)+IF(AI93=$G92+$H92,1,0)+IF(AI94=$I$94,3,0)+IF(AI95=$G94+$H94,1,0)+IF(AI96=$I$96,3,0)+IF(AI97=$G96+$H96,1,0)+IF(AI98=$I$98,3,0)+IF(AI99=$G98+$H98,1,0)+IF(AI100=$I$100,3,0)+IF(AI101=$G100+$H100,1,0)+IF(AI102=$I$102,3,0)+IF(AI103=$G102+$H102,1,0)+IF(AI104=$I$104,3,0)+IF(AI105=$G104+$H104,1,0)+IF(AI106=$I$106,3,0)+IF(AI107=$G106+$H106,1,0)+IF(AI108=$I$108,3,0)+IF(AI109=$G108+$H108,1,0)+IF(AI110=$I$110,3,0)+IF(AI111=$G110+$H110,1,0)+IF(AI112=$I$112,3,0)+IF(AI113=$G112+$H112,1,0)+IF(AI114=$I$114,3,0)+IF(AI115=$G114+$H114,1,0)+IF(AI116=$I$116,3,0)+IF(AI117=$G116+$H116,1,0)+IF(AI118=$I$118,3,0)+IF(AI119=$G118+$H118,1,0)+IF(AI120=$I$120,3,0)+IF(AI121=$G120+$H120,1,0)+IF(AI122=$I$122,3,0)+IF(AI123=$G122+$H122,1,0)+IF(AI124=$I$124,3,0)+IF(AI125=$G124+$H124,1,0)+IF(AI126=$I$126,3,0)+IF(AI127=$G126+$H126,1,0)+IF(AI128=$I$128,3,0)+IF(AI129=$G128+$H128,1,0)+IF(AI130=$I$130,3,0)+IF(AI131=$G130+$H130,1,0)+IF(AI132=$I$132,3,0)+IF(AI133=$G132+$H132,1,0)+IF(AI134=$I$134,3,0)+IF(AI135=$G134+$H134,1,0)+IF(AI136=$I$136,3,0)+IF(AI137=$G136+$H136,1,0)+IF(AI138=$I$138,3,0)+IF(AI139=$G138+$H138,1,0)+IF(AI140=$I$140,3,0)+IF(AI141=$G140+$H140,1,0)+IF(AI142=$I$142,3,0)+IF(AI143=$G142+$H142,1,0)+IF(AI144=$I$144,3,0)+IF(AI145=$G144+$H144,1,0)+IF(AI146=$I$146,3,0)+IF(AI147=$G146+$H146,1,0)+IF(AI148=$I$148,3,0)+IF(AI149=$G148+$H148,1,0)+IF(AI150=$I$150,3,0)+IF(AI151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ5" s="75">
-        <f>SUM(IF(AJ80=$I$80,3,0)+IF(AJ81=$G80+$H80,1,0)+IF(AJ82=$I$82,3,0)+IF(AJ83=$G82+$H82,1,0)+IF(AJ84=$I$84,3,0)+IF(AJ85=$G84+$H84,1,0)+IF(AJ86=$I$86,3,0)+IF(AJ87=$G86+$H86,1,0)+IF(AJ88=$I$88,3,0)+IF(AJ89=$G88+$H88,1,0)+IF(AJ90=$I$90,3,0)+IF(AJ91=$G90+$H90,1,0)+IF(AJ92=$I$92,3,0)+IF(AJ93=$G92+$H92,1,0)+IF(AJ94=$I$94,3,0)+IF(AJ95=$G94+$H94,1,0)+IF(AJ96=$I$96,3,0)+IF(AJ97=$G96+$H96,1,0)+IF(AJ98=$I$98,3,0)+IF(AJ99=$G98+$H98,1,0)+IF(AJ100=$I$100,3,0)+IF(AJ101=$G100+$H100,1,0)+IF(AJ102=$I$102,3,0)+IF(AJ103=$G102+$H102,1,0)+IF(AJ104=$I$104,3,0)+IF(AJ105=$G104+$H104,1,0)+IF(AJ106=$I$106,3,0)+IF(AJ107=$G106+$H106,1,0)+IF(AJ108=$I$108,3,0)+IF(AJ109=$G108+$H108,1,0)+IF(AJ110=$I$110,3,0)+IF(AJ111=$G110+$H110,1,0)+IF(AJ112=$I$112,3,0)+IF(AJ113=$G112+$H112,1,0)+IF(AJ114=$I$114,3,0)+IF(AJ115=$G114+$H114,1,0)+IF(AJ116=$I$116,3,0)+IF(AJ117=$G116+$H116,1,0)+IF(AJ118=$I$118,3,0)+IF(AJ119=$G118+$H118,1,0)+IF(AJ120=$I$120,3,0)+IF(AJ121=$G120+$H120,1,0)+IF(AJ122=$I$122,3,0)+IF(AJ123=$G122+$H122,1,0)+IF(AJ124=$I$124,3,0)+IF(AJ125=$G124+$H124,1,0)+IF(AJ126=$I$126,3,0)+IF(AJ127=$G126+$H126,1,0)+IF(AJ128=$I$128,3,0)+IF(AJ129=$G128+$H128,1,0)+IF(AJ130=$I$130,3,0)+IF(AJ131=$G130+$H130,1,0)+IF(AJ132=$I$132,3,0)+IF(AJ133=$G132+$H132,1,0)+IF(AJ134=$I$134,3,0)+IF(AJ135=$G134+$H134,1,0)+IF(AJ136=$I$136,3,0)+IF(AJ137=$G136+$H136,1,0)+IF(AJ138=$I$138,3,0)+IF(AJ139=$G138+$H138,1,0)+IF(AJ140=$I$140,3,0)+IF(AJ141=$G140+$H140,1,0)+IF(AJ142=$I$142,3,0)+IF(AJ143=$G142+$H142,1,0)+IF(AJ144=$I$144,3,0)+IF(AJ145=$G144+$H144,1,0)+IF(AJ146=$I$146,3,0)+IF(AJ147=$G146+$H146,1,0)+IF(AJ148=$I$148,3,0)+IF(AJ149=$G148+$H148,1,0)+IF(AJ150=$I$150,3,0)+IF(AJ151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AK5" s="75">
-        <f>SUM(IF(AK80=$I$80,3,0)+IF(AK81=$G80+$H80,1,0)+IF(AK82=$I$82,3,0)+IF(AK83=$G82+$H82,1,0)+IF(AK84=$I$84,3,0)+IF(AK85=$G84+$H84,1,0)+IF(AK86=$I$86,3,0)+IF(AK87=$G86+$H86,1,0)+IF(AK88=$I$88,3,0)+IF(AK89=$G88+$H88,1,0)+IF(AK90=$I$90,3,0)+IF(AK91=$G90+$H90,1,0)+IF(AK92=$I$92,3,0)+IF(AK93=$G92+$H92,1,0)+IF(AK94=$I$94,3,0)+IF(AK95=$G94+$H94,1,0)+IF(AK96=$I$96,3,0)+IF(AK97=$G96+$H96,1,0)+IF(AK98=$I$98,3,0)+IF(AK99=$G98+$H98,1,0)+IF(AK100=$I$100,3,0)+IF(AK101=$G100+$H100,1,0)+IF(AK102=$I$102,3,0)+IF(AK103=$G102+$H102,1,0)+IF(AK104=$I$104,3,0)+IF(AK105=$G104+$H104,1,0)+IF(AK106=$I$106,3,0)+IF(AK107=$G106+$H106,1,0)+IF(AK108=$I$108,3,0)+IF(AK109=$G108+$H108,1,0)+IF(AK110=$I$110,3,0)+IF(AK111=$G110+$H110,1,0)+IF(AK112=$I$112,3,0)+IF(AK113=$G112+$H112,1,0)+IF(AK114=$I$114,3,0)+IF(AK115=$G114+$H114,1,0)+IF(AK116=$I$116,3,0)+IF(AK117=$G116+$H116,1,0)+IF(AK118=$I$118,3,0)+IF(AK119=$G118+$H118,1,0)+IF(AK120=$I$120,3,0)+IF(AK121=$G120+$H120,1,0)+IF(AK122=$I$122,3,0)+IF(AK123=$G122+$H122,1,0)+IF(AK124=$I$124,3,0)+IF(AK125=$G124+$H124,1,0)+IF(AK126=$I$126,3,0)+IF(AK127=$G126+$H126,1,0)+IF(AK128=$I$128,3,0)+IF(AK129=$G128+$H128,1,0)+IF(AK130=$I$130,3,0)+IF(AK131=$G130+$H130,1,0)+IF(AK132=$I$132,3,0)+IF(AK133=$G132+$H132,1,0)+IF(AK134=$I$134,3,0)+IF(AK135=$G134+$H134,1,0)+IF(AK136=$I$136,3,0)+IF(AK137=$G136+$H136,1,0)+IF(AK138=$I$138,3,0)+IF(AK139=$G138+$H138,1,0)+IF(AK140=$I$140,3,0)+IF(AK141=$G140+$H140,1,0)+IF(AK142=$I$142,3,0)+IF(AK143=$G142+$H142,1,0)+IF(AK144=$I$144,3,0)+IF(AK145=$G144+$H144,1,0)+IF(AK146=$I$146,3,0)+IF(AK147=$G146+$H146,1,0)+IF(AK148=$I$148,3,0)+IF(AK149=$G148+$H148,1,0)+IF(AK150=$I$150,3,0)+IF(AK151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL5" s="75">
-        <f>SUM(IF(AL80=$I$80,3,0)+IF(AL81=$G80+$H80,1,0)+IF(AL82=$I$82,3,0)+IF(AL83=$G82+$H82,1,0)+IF(AL84=$I$84,3,0)+IF(AL85=$G84+$H84,1,0)+IF(AL86=$I$86,3,0)+IF(AL87=$G86+$H86,1,0)+IF(AL88=$I$88,3,0)+IF(AL89=$G88+$H88,1,0)+IF(AL90=$I$90,3,0)+IF(AL91=$G90+$H90,1,0)+IF(AL92=$I$92,3,0)+IF(AL93=$G92+$H92,1,0)+IF(AL94=$I$94,3,0)+IF(AL95=$G94+$H94,1,0)+IF(AL96=$I$96,3,0)+IF(AL97=$G96+$H96,1,0)+IF(AL98=$I$98,3,0)+IF(AL99=$G98+$H98,1,0)+IF(AL100=$I$100,3,0)+IF(AL101=$G100+$H100,1,0)+IF(AL102=$I$102,3,0)+IF(AL103=$G102+$H102,1,0)+IF(AL104=$I$104,3,0)+IF(AL105=$G104+$H104,1,0)+IF(AL106=$I$106,3,0)+IF(AL107=$G106+$H106,1,0)+IF(AL108=$I$108,3,0)+IF(AL109=$G108+$H108,1,0)+IF(AL110=$I$110,3,0)+IF(AL111=$G110+$H110,1,0)+IF(AL112=$I$112,3,0)+IF(AL113=$G112+$H112,1,0)+IF(AL114=$I$114,3,0)+IF(AL115=$G114+$H114,1,0)+IF(AL116=$I$116,3,0)+IF(AL117=$G116+$H116,1,0)+IF(AL118=$I$118,3,0)+IF(AL119=$G118+$H118,1,0)+IF(AL120=$I$120,3,0)+IF(AL121=$G120+$H120,1,0)+IF(AL122=$I$122,3,0)+IF(AL123=$G122+$H122,1,0)+IF(AL124=$I$124,3,0)+IF(AL125=$G124+$H124,1,0)+IF(AL126=$I$126,3,0)+IF(AL127=$G126+$H126,1,0)+IF(AL128=$I$128,3,0)+IF(AL129=$G128+$H128,1,0)+IF(AL130=$I$130,3,0)+IF(AL131=$G130+$H130,1,0)+IF(AL132=$I$132,3,0)+IF(AL133=$G132+$H132,1,0)+IF(AL134=$I$134,3,0)+IF(AL135=$G134+$H134,1,0)+IF(AL136=$I$136,3,0)+IF(AL137=$G136+$H136,1,0)+IF(AL138=$I$138,3,0)+IF(AL139=$G138+$H138,1,0)+IF(AL140=$I$140,3,0)+IF(AL141=$G140+$H140,1,0)+IF(AL142=$I$142,3,0)+IF(AL143=$G142+$H142,1,0)+IF(AL144=$I$144,3,0)+IF(AL145=$G144+$H144,1,0)+IF(AL146=$I$146,3,0)+IF(AL147=$G146+$H146,1,0)+IF(AL148=$I$148,3,0)+IF(AL149=$G148+$H148,1,0)+IF(AL150=$I$150,3,0)+IF(AL151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AM5" s="75">
-        <f>SUM(IF(AM80=$I$80,3,0)+IF(AM81=$G80+$H80,1,0)+IF(AM82=$I$82,3,0)+IF(AM83=$G82+$H82,1,0)+IF(AM84=$I$84,3,0)+IF(AM85=$G84+$H84,1,0)+IF(AM86=$I$86,3,0)+IF(AM87=$G86+$H86,1,0)+IF(AM88=$I$88,3,0)+IF(AM89=$G88+$H88,1,0)+IF(AM90=$I$90,3,0)+IF(AM91=$G90+$H90,1,0)+IF(AM92=$I$92,3,0)+IF(AM93=$G92+$H92,1,0)+IF(AM94=$I$94,3,0)+IF(AM95=$G94+$H94,1,0)+IF(AM96=$I$96,3,0)+IF(AM97=$G96+$H96,1,0)+IF(AM98=$I$98,3,0)+IF(AM99=$G98+$H98,1,0)+IF(AM100=$I$100,3,0)+IF(AM101=$G100+$H100,1,0)+IF(AM102=$I$102,3,0)+IF(AM103=$G102+$H102,1,0)+IF(AM104=$I$104,3,0)+IF(AM105=$G104+$H104,1,0)+IF(AM106=$I$106,3,0)+IF(AM107=$G106+$H106,1,0)+IF(AM108=$I$108,3,0)+IF(AM109=$G108+$H108,1,0)+IF(AM110=$I$110,3,0)+IF(AM111=$G110+$H110,1,0)+IF(AM112=$I$112,3,0)+IF(AM113=$G112+$H112,1,0)+IF(AM114=$I$114,3,0)+IF(AM115=$G114+$H114,1,0)+IF(AM116=$I$116,3,0)+IF(AM117=$G116+$H116,1,0)+IF(AM118=$I$118,3,0)+IF(AM119=$G118+$H118,1,0)+IF(AM120=$I$120,3,0)+IF(AM121=$G120+$H120,1,0)+IF(AM122=$I$122,3,0)+IF(AM123=$G122+$H122,1,0)+IF(AM124=$I$124,3,0)+IF(AM125=$G124+$H124,1,0)+IF(AM126=$I$126,3,0)+IF(AM127=$G126+$H126,1,0)+IF(AM128=$I$128,3,0)+IF(AM129=$G128+$H128,1,0)+IF(AM130=$I$130,3,0)+IF(AM131=$G130+$H130,1,0)+IF(AM132=$I$132,3,0)+IF(AM133=$G132+$H132,1,0)+IF(AM134=$I$134,3,0)+IF(AM135=$G134+$H134,1,0)+IF(AM136=$I$136,3,0)+IF(AM137=$G136+$H136,1,0)+IF(AM138=$I$138,3,0)+IF(AM139=$G138+$H138,1,0)+IF(AM140=$I$140,3,0)+IF(AM141=$G140+$H140,1,0)+IF(AM142=$I$142,3,0)+IF(AM143=$G142+$H142,1,0)+IF(AM144=$I$144,3,0)+IF(AM145=$G144+$H144,1,0)+IF(AM146=$I$146,3,0)+IF(AM147=$G146+$H146,1,0)+IF(AM148=$I$148,3,0)+IF(AM149=$G148+$H148,1,0)+IF(AM150=$I$150,3,0)+IF(AM151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AN5" s="75">
-        <f>SUM(IF(AN80=$I$80,3,0)+IF(AN81=$G80+$H80,1,0)+IF(AN82=$I$82,3,0)+IF(AN83=$G82+$H82,1,0)+IF(AN84=$I$84,3,0)+IF(AN85=$G84+$H84,1,0)+IF(AN86=$I$86,3,0)+IF(AN87=$G86+$H86,1,0)+IF(AN88=$I$88,3,0)+IF(AN89=$G88+$H88,1,0)+IF(AN90=$I$90,3,0)+IF(AN91=$G90+$H90,1,0)+IF(AN92=$I$92,3,0)+IF(AN93=$G92+$H92,1,0)+IF(AN94=$I$94,3,0)+IF(AN95=$G94+$H94,1,0)+IF(AN96=$I$96,3,0)+IF(AN97=$G96+$H96,1,0)+IF(AN98=$I$98,3,0)+IF(AN99=$G98+$H98,1,0)+IF(AN100=$I$100,3,0)+IF(AN101=$G100+$H100,1,0)+IF(AN102=$I$102,3,0)+IF(AN103=$G102+$H102,1,0)+IF(AN104=$I$104,3,0)+IF(AN105=$G104+$H104,1,0)+IF(AN106=$I$106,3,0)+IF(AN107=$G106+$H106,1,0)+IF(AN108=$I$108,3,0)+IF(AN109=$G108+$H108,1,0)+IF(AN110=$I$110,3,0)+IF(AN111=$G110+$H110,1,0)+IF(AN112=$I$112,3,0)+IF(AN113=$G112+$H112,1,0)+IF(AN114=$I$114,3,0)+IF(AN115=$G114+$H114,1,0)+IF(AN116=$I$116,3,0)+IF(AN117=$G116+$H116,1,0)+IF(AN118=$I$118,3,0)+IF(AN119=$G118+$H118,1,0)+IF(AN120=$I$120,3,0)+IF(AN121=$G120+$H120,1,0)+IF(AN122=$I$122,3,0)+IF(AN123=$G122+$H122,1,0)+IF(AN124=$I$124,3,0)+IF(AN125=$G124+$H124,1,0)+IF(AN126=$I$126,3,0)+IF(AN127=$G126+$H126,1,0)+IF(AN128=$I$128,3,0)+IF(AN129=$G128+$H128,1,0)+IF(AN130=$I$130,3,0)+IF(AN131=$G130+$H130,1,0)+IF(AN132=$I$132,3,0)+IF(AN133=$G132+$H132,1,0)+IF(AN134=$I$134,3,0)+IF(AN135=$G134+$H134,1,0)+IF(AN136=$I$136,3,0)+IF(AN137=$G136+$H136,1,0)+IF(AN138=$I$138,3,0)+IF(AN139=$G138+$H138,1,0)+IF(AN140=$I$140,3,0)+IF(AN141=$G140+$H140,1,0)+IF(AN142=$I$142,3,0)+IF(AN143=$G142+$H142,1,0)+IF(AN144=$I$144,3,0)+IF(AN145=$G144+$H144,1,0)+IF(AN146=$I$146,3,0)+IF(AN147=$G146+$H146,1,0)+IF(AN148=$I$148,3,0)+IF(AN149=$G148+$H148,1,0)+IF(AN150=$I$150,3,0)+IF(AN151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AO5" s="75">
-        <f>SUM(IF(AO80=$I$80,3,0)+IF(AO81=$G80+$H80,1,0)+IF(AO82=$I$82,3,0)+IF(AO83=$G82+$H82,1,0)+IF(AO84=$I$84,3,0)+IF(AO85=$G84+$H84,1,0)+IF(AO86=$I$86,3,0)+IF(AO87=$G86+$H86,1,0)+IF(AO88=$I$88,3,0)+IF(AO89=$G88+$H88,1,0)+IF(AO90=$I$90,3,0)+IF(AO91=$G90+$H90,1,0)+IF(AO92=$I$92,3,0)+IF(AO93=$G92+$H92,1,0)+IF(AO94=$I$94,3,0)+IF(AO95=$G94+$H94,1,0)+IF(AO96=$I$96,3,0)+IF(AO97=$G96+$H96,1,0)+IF(AO98=$I$98,3,0)+IF(AO99=$G98+$H98,1,0)+IF(AO100=$I$100,3,0)+IF(AO101=$G100+$H100,1,0)+IF(AO102=$I$102,3,0)+IF(AO103=$G102+$H102,1,0)+IF(AO104=$I$104,3,0)+IF(AO105=$G104+$H104,1,0)+IF(AO106=$I$106,3,0)+IF(AO107=$G106+$H106,1,0)+IF(AO108=$I$108,3,0)+IF(AO109=$G108+$H108,1,0)+IF(AO110=$I$110,3,0)+IF(AO111=$G110+$H110,1,0)+IF(AO112=$I$112,3,0)+IF(AO113=$G112+$H112,1,0)+IF(AO114=$I$114,3,0)+IF(AO115=$G114+$H114,1,0)+IF(AO116=$I$116,3,0)+IF(AO117=$G116+$H116,1,0)+IF(AO118=$I$118,3,0)+IF(AO119=$G118+$H118,1,0)+IF(AO120=$I$120,3,0)+IF(AO121=$G120+$H120,1,0)+IF(AO122=$I$122,3,0)+IF(AO123=$G122+$H122,1,0)+IF(AO124=$I$124,3,0)+IF(AO125=$G124+$H124,1,0)+IF(AO126=$I$126,3,0)+IF(AO127=$G126+$H126,1,0)+IF(AO128=$I$128,3,0)+IF(AO129=$G128+$H128,1,0)+IF(AO130=$I$130,3,0)+IF(AO131=$G130+$H130,1,0)+IF(AO132=$I$132,3,0)+IF(AO133=$G132+$H132,1,0)+IF(AO134=$I$134,3,0)+IF(AO135=$G134+$H134,1,0)+IF(AO136=$I$136,3,0)+IF(AO137=$G136+$H136,1,0)+IF(AO138=$I$138,3,0)+IF(AO139=$G138+$H138,1,0)+IF(AO140=$I$140,3,0)+IF(AO141=$G140+$H140,1,0)+IF(AO142=$I$142,3,0)+IF(AO143=$G142+$H142,1,0)+IF(AO144=$I$144,3,0)+IF(AO145=$G144+$H144,1,0)+IF(AO146=$I$146,3,0)+IF(AO147=$G146+$H146,1,0)+IF(AO148=$I$148,3,0)+IF(AO149=$G148+$H148,1,0)+IF(AO150=$I$150,3,0)+IF(AO151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="AP5" s="75">
-        <f>SUM(IF(AP80=$I$80,3,0)+IF(AP81=$G80+$H80,1,0)+IF(AP82=$I$82,3,0)+IF(AP83=$G82+$H82,1,0)+IF(AP84=$I$84,3,0)+IF(AP85=$G84+$H84,1,0)+IF(AP86=$I$86,3,0)+IF(AP87=$G86+$H86,1,0)+IF(AP88=$I$88,3,0)+IF(AP89=$G88+$H88,1,0)+IF(AP90=$I$90,3,0)+IF(AP91=$G90+$H90,1,0)+IF(AP92=$I$92,3,0)+IF(AP93=$G92+$H92,1,0)+IF(AP94=$I$94,3,0)+IF(AP95=$G94+$H94,1,0)+IF(AP96=$I$96,3,0)+IF(AP97=$G96+$H96,1,0)+IF(AP98=$I$98,3,0)+IF(AP99=$G98+$H98,1,0)+IF(AP100=$I$100,3,0)+IF(AP101=$G100+$H100,1,0)+IF(AP102=$I$102,3,0)+IF(AP103=$G102+$H102,1,0)+IF(AP104=$I$104,3,0)+IF(AP105=$G104+$H104,1,0)+IF(AP106=$I$106,3,0)+IF(AP107=$G106+$H106,1,0)+IF(AP108=$I$108,3,0)+IF(AP109=$G108+$H108,1,0)+IF(AP110=$I$110,3,0)+IF(AP111=$G110+$H110,1,0)+IF(AP112=$I$112,3,0)+IF(AP113=$G112+$H112,1,0)+IF(AP114=$I$114,3,0)+IF(AP115=$G114+$H114,1,0)+IF(AP116=$I$116,3,0)+IF(AP117=$G116+$H116,1,0)+IF(AP118=$I$118,3,0)+IF(AP119=$G118+$H118,1,0)+IF(AP120=$I$120,3,0)+IF(AP121=$G120+$H120,1,0)+IF(AP122=$I$122,3,0)+IF(AP123=$G122+$H122,1,0)+IF(AP124=$I$124,3,0)+IF(AP125=$G124+$H124,1,0)+IF(AP126=$I$126,3,0)+IF(AP127=$G126+$H126,1,0)+IF(AP128=$I$128,3,0)+IF(AP129=$G128+$H128,1,0)+IF(AP130=$I$130,3,0)+IF(AP131=$G130+$H130,1,0)+IF(AP132=$I$132,3,0)+IF(AP133=$G132+$H132,1,0)+IF(AP134=$I$134,3,0)+IF(AP135=$G134+$H134,1,0)+IF(AP136=$I$136,3,0)+IF(AP137=$G136+$H136,1,0)+IF(AP138=$I$138,3,0)+IF(AP139=$G138+$H138,1,0)+IF(AP140=$I$140,3,0)+IF(AP141=$G140+$H140,1,0)+IF(AP142=$I$142,3,0)+IF(AP143=$G142+$H142,1,0)+IF(AP144=$I$144,3,0)+IF(AP145=$G144+$H144,1,0)+IF(AP146=$I$146,3,0)+IF(AP147=$G146+$H146,1,0)+IF(AP148=$I$148,3,0)+IF(AP149=$G148+$H148,1,0)+IF(AP150=$I$150,3,0)+IF(AP151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AQ5" s="75">
-        <f>SUM(IF(AQ80=$I$80,3,0)+IF(AQ81=$G80+$H80,1,0)+IF(AQ82=$I$82,3,0)+IF(AQ83=$G82+$H82,1,0)+IF(AQ84=$I$84,3,0)+IF(AQ85=$G84+$H84,1,0)+IF(AQ86=$I$86,3,0)+IF(AQ87=$G86+$H86,1,0)+IF(AQ88=$I$88,3,0)+IF(AQ89=$G88+$H88,1,0)+IF(AQ90=$I$90,3,0)+IF(AQ91=$G90+$H90,1,0)+IF(AQ92=$I$92,3,0)+IF(AQ93=$G92+$H92,1,0)+IF(AQ94=$I$94,3,0)+IF(AQ95=$G94+$H94,1,0)+IF(AQ96=$I$96,3,0)+IF(AQ97=$G96+$H96,1,0)+IF(AQ98=$I$98,3,0)+IF(AQ99=$G98+$H98,1,0)+IF(AQ100=$I$100,3,0)+IF(AQ101=$G100+$H100,1,0)+IF(AQ102=$I$102,3,0)+IF(AQ103=$G102+$H102,1,0)+IF(AQ104=$I$104,3,0)+IF(AQ105=$G104+$H104,1,0)+IF(AQ106=$I$106,3,0)+IF(AQ107=$G106+$H106,1,0)+IF(AQ108=$I$108,3,0)+IF(AQ109=$G108+$H108,1,0)+IF(AQ110=$I$110,3,0)+IF(AQ111=$G110+$H110,1,0)+IF(AQ112=$I$112,3,0)+IF(AQ113=$G112+$H112,1,0)+IF(AQ114=$I$114,3,0)+IF(AQ115=$G114+$H114,1,0)+IF(AQ116=$I$116,3,0)+IF(AQ117=$G116+$H116,1,0)+IF(AQ118=$I$118,3,0)+IF(AQ119=$G118+$H118,1,0)+IF(AQ120=$I$120,3,0)+IF(AQ121=$G120+$H120,1,0)+IF(AQ122=$I$122,3,0)+IF(AQ123=$G122+$H122,1,0)+IF(AQ124=$I$124,3,0)+IF(AQ125=$G124+$H124,1,0)+IF(AQ126=$I$126,3,0)+IF(AQ127=$G126+$H126,1,0)+IF(AQ128=$I$128,3,0)+IF(AQ129=$G128+$H128,1,0)+IF(AQ130=$I$130,3,0)+IF(AQ131=$G130+$H130,1,0)+IF(AQ132=$I$132,3,0)+IF(AQ133=$G132+$H132,1,0)+IF(AQ134=$I$134,3,0)+IF(AQ135=$G134+$H134,1,0)+IF(AQ136=$I$136,3,0)+IF(AQ137=$G136+$H136,1,0)+IF(AQ138=$I$138,3,0)+IF(AQ139=$G138+$H138,1,0)+IF(AQ140=$I$140,3,0)+IF(AQ141=$G140+$H140,1,0)+IF(AQ142=$I$142,3,0)+IF(AQ143=$G142+$H142,1,0)+IF(AQ144=$I$144,3,0)+IF(AQ145=$G144+$H144,1,0)+IF(AQ146=$I$146,3,0)+IF(AQ147=$G146+$H146,1,0)+IF(AQ148=$I$148,3,0)+IF(AQ149=$G148+$H148,1,0)+IF(AQ150=$I$150,3,0)+IF(AQ151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AR5" s="75">
-        <f>SUM(IF(AR80=$I$80,3,0)+IF(AR81=$G80+$H80,1,0)+IF(AR82=$I$82,3,0)+IF(AR83=$G82+$H82,1,0)+IF(AR84=$I$84,3,0)+IF(AR85=$G84+$H84,1,0)+IF(AR86=$I$86,3,0)+IF(AR87=$G86+$H86,1,0)+IF(AR88=$I$88,3,0)+IF(AR89=$G88+$H88,1,0)+IF(AR90=$I$90,3,0)+IF(AR91=$G90+$H90,1,0)+IF(AR92=$I$92,3,0)+IF(AR93=$G92+$H92,1,0)+IF(AR94=$I$94,3,0)+IF(AR95=$G94+$H94,1,0)+IF(AR96=$I$96,3,0)+IF(AR97=$G96+$H96,1,0)+IF(AR98=$I$98,3,0)+IF(AR99=$G98+$H98,1,0)+IF(AR100=$I$100,3,0)+IF(AR101=$G100+$H100,1,0)+IF(AR102=$I$102,3,0)+IF(AR103=$G102+$H102,1,0)+IF(AR104=$I$104,3,0)+IF(AR105=$G104+$H104,1,0)+IF(AR106=$I$106,3,0)+IF(AR107=$G106+$H106,1,0)+IF(AR108=$I$108,3,0)+IF(AR109=$G108+$H108,1,0)+IF(AR110=$I$110,3,0)+IF(AR111=$G110+$H110,1,0)+IF(AR112=$I$112,3,0)+IF(AR113=$G112+$H112,1,0)+IF(AR114=$I$114,3,0)+IF(AR115=$G114+$H114,1,0)+IF(AR116=$I$116,3,0)+IF(AR117=$G116+$H116,1,0)+IF(AR118=$I$118,3,0)+IF(AR119=$G118+$H118,1,0)+IF(AR120=$I$120,3,0)+IF(AR121=$G120+$H120,1,0)+IF(AR122=$I$122,3,0)+IF(AR123=$G122+$H122,1,0)+IF(AR124=$I$124,3,0)+IF(AR125=$G124+$H124,1,0)+IF(AR126=$I$126,3,0)+IF(AR127=$G126+$H126,1,0)+IF(AR128=$I$128,3,0)+IF(AR129=$G128+$H128,1,0)+IF(AR130=$I$130,3,0)+IF(AR131=$G130+$H130,1,0)+IF(AR132=$I$132,3,0)+IF(AR133=$G132+$H132,1,0)+IF(AR134=$I$134,3,0)+IF(AR135=$G134+$H134,1,0)+IF(AR136=$I$136,3,0)+IF(AR137=$G136+$H136,1,0)+IF(AR138=$I$138,3,0)+IF(AR139=$G138+$H138,1,0)+IF(AR140=$I$140,3,0)+IF(AR141=$G140+$H140,1,0)+IF(AR142=$I$142,3,0)+IF(AR143=$G142+$H142,1,0)+IF(AR144=$I$144,3,0)+IF(AR145=$G144+$H144,1,0)+IF(AR146=$I$146,3,0)+IF(AR147=$G146+$H146,1,0)+IF(AR148=$I$148,3,0)+IF(AR149=$G148+$H148,1,0)+IF(AR150=$I$150,3,0)+IF(AR151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AS5" s="75">
-        <f>SUM(IF(AS80=$I$80,3,0)+IF(AS81=$G80+$H80,1,0)+IF(AS82=$I$82,3,0)+IF(AS83=$G82+$H82,1,0)+IF(AS84=$I$84,3,0)+IF(AS85=$G84+$H84,1,0)+IF(AS86=$I$86,3,0)+IF(AS87=$G86+$H86,1,0)+IF(AS88=$I$88,3,0)+IF(AS89=$G88+$H88,1,0)+IF(AS90=$I$90,3,0)+IF(AS91=$G90+$H90,1,0)+IF(AS92=$I$92,3,0)+IF(AS93=$G92+$H92,1,0)+IF(AS94=$I$94,3,0)+IF(AS95=$G94+$H94,1,0)+IF(AS96=$I$96,3,0)+IF(AS97=$G96+$H96,1,0)+IF(AS98=$I$98,3,0)+IF(AS99=$G98+$H98,1,0)+IF(AS100=$I$100,3,0)+IF(AS101=$G100+$H100,1,0)+IF(AS102=$I$102,3,0)+IF(AS103=$G102+$H102,1,0)+IF(AS104=$I$104,3,0)+IF(AS105=$G104+$H104,1,0)+IF(AS106=$I$106,3,0)+IF(AS107=$G106+$H106,1,0)+IF(AS108=$I$108,3,0)+IF(AS109=$G108+$H108,1,0)+IF(AS110=$I$110,3,0)+IF(AS111=$G110+$H110,1,0)+IF(AS112=$I$112,3,0)+IF(AS113=$G112+$H112,1,0)+IF(AS114=$I$114,3,0)+IF(AS115=$G114+$H114,1,0)+IF(AS116=$I$116,3,0)+IF(AS117=$G116+$H116,1,0)+IF(AS118=$I$118,3,0)+IF(AS119=$G118+$H118,1,0)+IF(AS120=$I$120,3,0)+IF(AS121=$G120+$H120,1,0)+IF(AS122=$I$122,3,0)+IF(AS123=$G122+$H122,1,0)+IF(AS124=$I$124,3,0)+IF(AS125=$G124+$H124,1,0)+IF(AS126=$I$126,3,0)+IF(AS127=$G126+$H126,1,0)+IF(AS128=$I$128,3,0)+IF(AS129=$G128+$H128,1,0)+IF(AS130=$I$130,3,0)+IF(AS131=$G130+$H130,1,0)+IF(AS132=$I$132,3,0)+IF(AS133=$G132+$H132,1,0)+IF(AS134=$I$134,3,0)+IF(AS135=$G134+$H134,1,0)+IF(AS136=$I$136,3,0)+IF(AS137=$G136+$H136,1,0)+IF(AS138=$I$138,3,0)+IF(AS139=$G138+$H138,1,0)+IF(AS140=$I$140,3,0)+IF(AS141=$G140+$H140,1,0)+IF(AS142=$I$142,3,0)+IF(AS143=$G142+$H142,1,0)+IF(AS144=$I$144,3,0)+IF(AS145=$G144+$H144,1,0)+IF(AS146=$I$146,3,0)+IF(AS147=$G146+$H146,1,0)+IF(AS148=$I$148,3,0)+IF(AS149=$G148+$H148,1,0)+IF(AS150=$I$150,3,0)+IF(AS151=$G150+$H150,1,0))</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AT5" s="79">
-        <f>SUM(IF(AT80=$I$80,3,0)+IF(AT81=$G80+$H80,1,0)+IF(AT82=$I$82,3,0)+IF(AT83=$G82+$H82,1,0)+IF(AT84=$I$84,3,0)+IF(AT85=$G84+$H84,1,0)+IF(AT86=$I$86,3,0)+IF(AT87=$G86+$H86,1,0)+IF(AT88=$I$88,3,0)+IF(AT89=$G88+$H88,1,0)+IF(AT90=$I$90,3,0)+IF(AT91=$G90+$H90,1,0)+IF(AT92=$I$92,3,0)+IF(AT93=$G92+$H92,1,0)+IF(AT94=$I$94,3,0)+IF(AT95=$G94+$H94,1,0)+IF(AT96=$I$96,3,0)+IF(AT97=$G96+$H96,1,0)+IF(AT98=$I$98,3,0)+IF(AT99=$G98+$H98,1,0)+IF(AT100=$I$100,3,0)+IF(AT101=$G100+$H100,1,0)+IF(AT102=$I$102,3,0)+IF(AT103=$G102+$H102,1,0)+IF(AT104=$I$104,3,0)+IF(AT105=$G104+$H104,1,0)+IF(AT106=$I$106,3,0)+IF(AT107=$G106+$H106,1,0)+IF(AT108=$I$108,3,0)+IF(AT109=$G108+$H108,1,0)+IF(AT110=$I$110,3,0)+IF(AT111=$G110+$H110,1,0)+IF(AT112=$I$112,3,0)+IF(AT113=$G112+$H112,1,0)+IF(AT114=$I$114,3,0)+IF(AT115=$G114+$H114,1,0)+IF(AT116=$I$116,3,0)+IF(AT117=$G116+$H116,1,0)+IF(AT118=$I$118,3,0)+IF(AT119=$G118+$H118,1,0)+IF(AT120=$I$120,3,0)+IF(AT121=$G120+$H120,1,0)+IF(AT122=$I$122,3,0)+IF(AT123=$G122+$H122,1,0)+IF(AT124=$I$124,3,0)+IF(AT125=$G124+$H124,1,0)+IF(AT126=$I$126,3,0)+IF(AT127=$G126+$H126,1,0)+IF(AT128=$I$128,3,0)+IF(AT129=$G128+$H128,1,0)+IF(AT130=$I$130,3,0)+IF(AT131=$G130+$H130,1,0)+IF(AT132=$I$132,3,0)+IF(AT133=$G132+$H132,1,0)+IF(AT134=$I$134,3,0)+IF(AT135=$G134+$H134,1,0)+IF(AT136=$I$136,3,0)+IF(AT137=$G136+$H136,1,0)+IF(AT138=$I$138,3,0)+IF(AT139=$G138+$H138,1,0)+IF(AT140=$I$140,3,0)+IF(AT141=$G140+$H140,1,0)+IF(AT142=$I$142,3,0)+IF(AT143=$G142+$H142,1,0)+IF(AT144=$I$144,3,0)+IF(AT145=$G144+$H144,1,0)+IF(AT146=$I$146,3,0)+IF(AT147=$G146+$H146,1,0)+IF(AT148=$I$148,3,0)+IF(AT149=$G148+$H148,1,0)+IF(AT150=$I$150,3,0)+IF(AT151=$G150+$H150,1,0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:54" ht="14.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:54" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="61"/>
       <c r="B6" s="61"/>
       <c r="C6" s="61"/>
@@ -3312,155 +3276,155 @@
       <c r="H6" s="62"/>
       <c r="I6" s="63"/>
       <c r="J6" s="74">
-        <f>SUM(AND($G$8="",$H$8="",J9=0)+AND($G$10="",$H$10="",J11=0)+AND($G$12="",$H$12="",J13=0)+AND($G$14="",$H$14="",J15=0)+AND($G$16="",$H$16="",J17=0)+AND($G$18="",$H$18="",J19=0)+AND($G$20="",$H$20="",J21=0)+AND($G$22="",$H$22="",J23=0)+AND($G$24="",$H$24="",J25=0)+AND($G$26="",$H$26="",J27=0)+AND($G$28="",$H$28="",J29=0)+AND($G$30="",$H$30="",J31=0)+AND($G$32="",$H$32="",J33=0)+AND($G$34="",$H$34="",J35=0)+AND($G$36="",$H$36="",J37=0)+AND($G$38="",$H$38="",J39=0)+AND($G$40="",$H$40="",J41=0)+AND($G$42="",$H$42="",J43=0)+AND($G$44="",$H$44="",J45=0)+AND($G$46="",$H$46="",J47=0)+AND($G$48="",$H$48="",J49=0)+AND($G$50="",$H$50="",J51=0)+AND($G$52="",$H$52="",J53=0)+AND($G$54="",$H$54="",J55=0)+AND($G$56="",$H$56="",J57=0)+AND($G$58="",$H$58="",J59=0)+AND($G$60="",$H$60="",J61=0)+AND($G$62="",$H$62="",J63=0)+AND($G$64="",$H$64="",J65=0)+AND($G$66="",$H$66="",J67=0)+AND($G$68="",$H$68="",J69=0)+AND($G$70="",$H$70="",J71=0)+AND($G$72="",$H$72="",J73=0)+AND($G$74="",$H$74="",J75=0)+AND($G$76="",$H$76="",J77=0)+AND($G$78="",$H$78="",J79=0))</f>
+        <f t="shared" ref="J6:AT6" si="3">SUM(AND($G$8="",$H$8="",J9=0)+AND($G$10="",$H$10="",J11=0)+AND($G$12="",$H$12="",J13=0)+AND($G$14="",$H$14="",J15=0)+AND($G$16="",$H$16="",J17=0)+AND($G$18="",$H$18="",J19=0)+AND($G$20="",$H$20="",J21=0)+AND($G$22="",$H$22="",J23=0)+AND($G$24="",$H$24="",J25=0)+AND($G$26="",$H$26="",J27=0)+AND($G$28="",$H$28="",J29=0)+AND($G$30="",$H$30="",J31=0)+AND($G$32="",$H$32="",J33=0)+AND($G$34="",$H$34="",J35=0)+AND($G$36="",$H$36="",J37=0)+AND($G$38="",$H$38="",J39=0)+AND($G$40="",$H$40="",J41=0)+AND($G$42="",$H$42="",J43=0)+AND($G$44="",$H$44="",J45=0)+AND($G$46="",$H$46="",J47=0)+AND($G$48="",$H$48="",J49=0)+AND($G$50="",$H$50="",J51=0)+AND($G$52="",$H$52="",J53=0)+AND($G$54="",$H$54="",J55=0)+AND($G$56="",$H$56="",J57=0)+AND($G$58="",$H$58="",J59=0)+AND($G$60="",$H$60="",J61=0)+AND($G$62="",$H$62="",J63=0)+AND($G$64="",$H$64="",J65=0)+AND($G$66="",$H$66="",J67=0)+AND($G$68="",$H$68="",J69=0)+AND($G$70="",$H$70="",J71=0)+AND($G$72="",$H$72="",J73=0)+AND($G$74="",$H$74="",J75=0)+AND($G$76="",$H$76="",J77=0)+AND($G$78="",$H$78="",J79=0))</f>
         <v>2</v>
       </c>
       <c r="K6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",K9=0)+AND($G$10="",$H$10="",K11=0)+AND($G$12="",$H$12="",K13=0)+AND($G$14="",$H$14="",K15=0)+AND($G$16="",$H$16="",K17=0)+AND($G$18="",$H$18="",K19=0)+AND($G$20="",$H$20="",K21=0)+AND($G$22="",$H$22="",K23=0)+AND($G$24="",$H$24="",K25=0)+AND($G$26="",$H$26="",K27=0)+AND($G$28="",$H$28="",K29=0)+AND($G$30="",$H$30="",K31=0)+AND($G$32="",$H$32="",K33=0)+AND($G$34="",$H$34="",K35=0)+AND($G$36="",$H$36="",K37=0)+AND($G$38="",$H$38="",K39=0)+AND($G$40="",$H$40="",K41=0)+AND($G$42="",$H$42="",K43=0)+AND($G$44="",$H$44="",K45=0)+AND($G$46="",$H$46="",K47=0)+AND($G$48="",$H$48="",K49=0)+AND($G$50="",$H$50="",K51=0)+AND($G$52="",$H$52="",K53=0)+AND($G$54="",$H$54="",K55=0)+AND($G$56="",$H$56="",K57=0)+AND($G$58="",$H$58="",K59=0)+AND($G$60="",$H$60="",K61=0)+AND($G$62="",$H$62="",K63=0)+AND($G$64="",$H$64="",K65=0)+AND($G$66="",$H$66="",K67=0)+AND($G$68="",$H$68="",K69=0)+AND($G$70="",$H$70="",K71=0)+AND($G$72="",$H$72="",K73=0)+AND($G$74="",$H$74="",K75=0)+AND($G$76="",$H$76="",K77=0)+AND($G$78="",$H$78="",K79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",L9=0)+AND($G$10="",$H$10="",L11=0)+AND($G$12="",$H$12="",L13=0)+AND($G$14="",$H$14="",L15=0)+AND($G$16="",$H$16="",L17=0)+AND($G$18="",$H$18="",L19=0)+AND($G$20="",$H$20="",L21=0)+AND($G$22="",$H$22="",L23=0)+AND($G$24="",$H$24="",L25=0)+AND($G$26="",$H$26="",L27=0)+AND($G$28="",$H$28="",L29=0)+AND($G$30="",$H$30="",L31=0)+AND($G$32="",$H$32="",L33=0)+AND($G$34="",$H$34="",L35=0)+AND($G$36="",$H$36="",L37=0)+AND($G$38="",$H$38="",L39=0)+AND($G$40="",$H$40="",L41=0)+AND($G$42="",$H$42="",L43=0)+AND($G$44="",$H$44="",L45=0)+AND($G$46="",$H$46="",L47=0)+AND($G$48="",$H$48="",L49=0)+AND($G$50="",$H$50="",L51=0)+AND($G$52="",$H$52="",L53=0)+AND($G$54="",$H$54="",L55=0)+AND($G$56="",$H$56="",L57=0)+AND($G$58="",$H$58="",L59=0)+AND($G$60="",$H$60="",L61=0)+AND($G$62="",$H$62="",L63=0)+AND($G$64="",$H$64="",L65=0)+AND($G$66="",$H$66="",L67=0)+AND($G$68="",$H$68="",L69=0)+AND($G$70="",$H$70="",L71=0)+AND($G$72="",$H$72="",L73=0)+AND($G$74="",$H$74="",L75=0)+AND($G$76="",$H$76="",L77=0)+AND($G$78="",$H$78="",L79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",M9=0)+AND($G$10="",$H$10="",M11=0)+AND($G$12="",$H$12="",M13=0)+AND($G$14="",$H$14="",M15=0)+AND($G$16="",$H$16="",M17=0)+AND($G$18="",$H$18="",M19=0)+AND($G$20="",$H$20="",M21=0)+AND($G$22="",$H$22="",M23=0)+AND($G$24="",$H$24="",M25=0)+AND($G$26="",$H$26="",M27=0)+AND($G$28="",$H$28="",M29=0)+AND($G$30="",$H$30="",M31=0)+AND($G$32="",$H$32="",M33=0)+AND($G$34="",$H$34="",M35=0)+AND($G$36="",$H$36="",M37=0)+AND($G$38="",$H$38="",M39=0)+AND($G$40="",$H$40="",M41=0)+AND($G$42="",$H$42="",M43=0)+AND($G$44="",$H$44="",M45=0)+AND($G$46="",$H$46="",M47=0)+AND($G$48="",$H$48="",M49=0)+AND($G$50="",$H$50="",M51=0)+AND($G$52="",$H$52="",M53=0)+AND($G$54="",$H$54="",M55=0)+AND($G$56="",$H$56="",M57=0)+AND($G$58="",$H$58="",M59=0)+AND($G$60="",$H$60="",M61=0)+AND($G$62="",$H$62="",M63=0)+AND($G$64="",$H$64="",M65=0)+AND($G$66="",$H$66="",M67=0)+AND($G$68="",$H$68="",M69=0)+AND($G$70="",$H$70="",M71=0)+AND($G$72="",$H$72="",M73=0)+AND($G$74="",$H$74="",M75=0)+AND($G$76="",$H$76="",M77=0)+AND($G$78="",$H$78="",M79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",N9=0)+AND($G$10="",$H$10="",N11=0)+AND($G$12="",$H$12="",N13=0)+AND($G$14="",$H$14="",N15=0)+AND($G$16="",$H$16="",N17=0)+AND($G$18="",$H$18="",N19=0)+AND($G$20="",$H$20="",N21=0)+AND($G$22="",$H$22="",N23=0)+AND($G$24="",$H$24="",N25=0)+AND($G$26="",$H$26="",N27=0)+AND($G$28="",$H$28="",N29=0)+AND($G$30="",$H$30="",N31=0)+AND($G$32="",$H$32="",N33=0)+AND($G$34="",$H$34="",N35=0)+AND($G$36="",$H$36="",N37=0)+AND($G$38="",$H$38="",N39=0)+AND($G$40="",$H$40="",N41=0)+AND($G$42="",$H$42="",N43=0)+AND($G$44="",$H$44="",N45=0)+AND($G$46="",$H$46="",N47=0)+AND($G$48="",$H$48="",N49=0)+AND($G$50="",$H$50="",N51=0)+AND($G$52="",$H$52="",N53=0)+AND($G$54="",$H$54="",N55=0)+AND($G$56="",$H$56="",N57=0)+AND($G$58="",$H$58="",N59=0)+AND($G$60="",$H$60="",N61=0)+AND($G$62="",$H$62="",N63=0)+AND($G$64="",$H$64="",N65=0)+AND($G$66="",$H$66="",N67=0)+AND($G$68="",$H$68="",N69=0)+AND($G$70="",$H$70="",N71=0)+AND($G$72="",$H$72="",N73=0)+AND($G$74="",$H$74="",N75=0)+AND($G$76="",$H$76="",N77=0)+AND($G$78="",$H$78="",N79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",O9=0)+AND($G$10="",$H$10="",O11=0)+AND($G$12="",$H$12="",O13=0)+AND($G$14="",$H$14="",O15=0)+AND($G$16="",$H$16="",O17=0)+AND($G$18="",$H$18="",O19=0)+AND($G$20="",$H$20="",O21=0)+AND($G$22="",$H$22="",O23=0)+AND($G$24="",$H$24="",O25=0)+AND($G$26="",$H$26="",O27=0)+AND($G$28="",$H$28="",O29=0)+AND($G$30="",$H$30="",O31=0)+AND($G$32="",$H$32="",O33=0)+AND($G$34="",$H$34="",O35=0)+AND($G$36="",$H$36="",O37=0)+AND($G$38="",$H$38="",O39=0)+AND($G$40="",$H$40="",O41=0)+AND($G$42="",$H$42="",O43=0)+AND($G$44="",$H$44="",O45=0)+AND($G$46="",$H$46="",O47=0)+AND($G$48="",$H$48="",O49=0)+AND($G$50="",$H$50="",O51=0)+AND($G$52="",$H$52="",O53=0)+AND($G$54="",$H$54="",O55=0)+AND($G$56="",$H$56="",O57=0)+AND($G$58="",$H$58="",O59=0)+AND($G$60="",$H$60="",O61=0)+AND($G$62="",$H$62="",O63=0)+AND($G$64="",$H$64="",O65=0)+AND($G$66="",$H$66="",O67=0)+AND($G$68="",$H$68="",O69=0)+AND($G$70="",$H$70="",O71=0)+AND($G$72="",$H$72="",O73=0)+AND($G$74="",$H$74="",O75=0)+AND($G$76="",$H$76="",O77=0)+AND($G$78="",$H$78="",O79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",P9=0)+AND($G$10="",$H$10="",P11=0)+AND($G$12="",$H$12="",P13=0)+AND($G$14="",$H$14="",P15=0)+AND($G$16="",$H$16="",P17=0)+AND($G$18="",$H$18="",P19=0)+AND($G$20="",$H$20="",P21=0)+AND($G$22="",$H$22="",P23=0)+AND($G$24="",$H$24="",P25=0)+AND($G$26="",$H$26="",P27=0)+AND($G$28="",$H$28="",P29=0)+AND($G$30="",$H$30="",P31=0)+AND($G$32="",$H$32="",P33=0)+AND($G$34="",$H$34="",P35=0)+AND($G$36="",$H$36="",P37=0)+AND($G$38="",$H$38="",P39=0)+AND($G$40="",$H$40="",P41=0)+AND($G$42="",$H$42="",P43=0)+AND($G$44="",$H$44="",P45=0)+AND($G$46="",$H$46="",P47=0)+AND($G$48="",$H$48="",P49=0)+AND($G$50="",$H$50="",P51=0)+AND($G$52="",$H$52="",P53=0)+AND($G$54="",$H$54="",P55=0)+AND($G$56="",$H$56="",P57=0)+AND($G$58="",$H$58="",P59=0)+AND($G$60="",$H$60="",P61=0)+AND($G$62="",$H$62="",P63=0)+AND($G$64="",$H$64="",P65=0)+AND($G$66="",$H$66="",P67=0)+AND($G$68="",$H$68="",P69=0)+AND($G$70="",$H$70="",P71=0)+AND($G$72="",$H$72="",P73=0)+AND($G$74="",$H$74="",P75=0)+AND($G$76="",$H$76="",P77=0)+AND($G$78="",$H$78="",P79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",Q9=0)+AND($G$10="",$H$10="",Q11=0)+AND($G$12="",$H$12="",Q13=0)+AND($G$14="",$H$14="",Q15=0)+AND($G$16="",$H$16="",Q17=0)+AND($G$18="",$H$18="",Q19=0)+AND($G$20="",$H$20="",Q21=0)+AND($G$22="",$H$22="",Q23=0)+AND($G$24="",$H$24="",Q25=0)+AND($G$26="",$H$26="",Q27=0)+AND($G$28="",$H$28="",Q29=0)+AND($G$30="",$H$30="",Q31=0)+AND($G$32="",$H$32="",Q33=0)+AND($G$34="",$H$34="",Q35=0)+AND($G$36="",$H$36="",Q37=0)+AND($G$38="",$H$38="",Q39=0)+AND($G$40="",$H$40="",Q41=0)+AND($G$42="",$H$42="",Q43=0)+AND($G$44="",$H$44="",Q45=0)+AND($G$46="",$H$46="",Q47=0)+AND($G$48="",$H$48="",Q49=0)+AND($G$50="",$H$50="",Q51=0)+AND($G$52="",$H$52="",Q53=0)+AND($G$54="",$H$54="",Q55=0)+AND($G$56="",$H$56="",Q57=0)+AND($G$58="",$H$58="",Q59=0)+AND($G$60="",$H$60="",Q61=0)+AND($G$62="",$H$62="",Q63=0)+AND($G$64="",$H$64="",Q65=0)+AND($G$66="",$H$66="",Q67=0)+AND($G$68="",$H$68="",Q69=0)+AND($G$70="",$H$70="",Q71=0)+AND($G$72="",$H$72="",Q73=0)+AND($G$74="",$H$74="",Q75=0)+AND($G$76="",$H$76="",Q77=0)+AND($G$78="",$H$78="",Q79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",R9=0)+AND($G$10="",$H$10="",R11=0)+AND($G$12="",$H$12="",R13=0)+AND($G$14="",$H$14="",R15=0)+AND($G$16="",$H$16="",R17=0)+AND($G$18="",$H$18="",R19=0)+AND($G$20="",$H$20="",R21=0)+AND($G$22="",$H$22="",R23=0)+AND($G$24="",$H$24="",R25=0)+AND($G$26="",$H$26="",R27=0)+AND($G$28="",$H$28="",R29=0)+AND($G$30="",$H$30="",R31=0)+AND($G$32="",$H$32="",R33=0)+AND($G$34="",$H$34="",R35=0)+AND($G$36="",$H$36="",R37=0)+AND($G$38="",$H$38="",R39=0)+AND($G$40="",$H$40="",R41=0)+AND($G$42="",$H$42="",R43=0)+AND($G$44="",$H$44="",R45=0)+AND($G$46="",$H$46="",R47=0)+AND($G$48="",$H$48="",R49=0)+AND($G$50="",$H$50="",R51=0)+AND($G$52="",$H$52="",R53=0)+AND($G$54="",$H$54="",R55=0)+AND($G$56="",$H$56="",R57=0)+AND($G$58="",$H$58="",R59=0)+AND($G$60="",$H$60="",R61=0)+AND($G$62="",$H$62="",R63=0)+AND($G$64="",$H$64="",R65=0)+AND($G$66="",$H$66="",R67=0)+AND($G$68="",$H$68="",R69=0)+AND($G$70="",$H$70="",R71=0)+AND($G$72="",$H$72="",R73=0)+AND($G$74="",$H$74="",R75=0)+AND($G$76="",$H$76="",R77=0)+AND($G$78="",$H$78="",R79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",S9=0)+AND($G$10="",$H$10="",S11=0)+AND($G$12="",$H$12="",S13=0)+AND($G$14="",$H$14="",S15=0)+AND($G$16="",$H$16="",S17=0)+AND($G$18="",$H$18="",S19=0)+AND($G$20="",$H$20="",S21=0)+AND($G$22="",$H$22="",S23=0)+AND($G$24="",$H$24="",S25=0)+AND($G$26="",$H$26="",S27=0)+AND($G$28="",$H$28="",S29=0)+AND($G$30="",$H$30="",S31=0)+AND($G$32="",$H$32="",S33=0)+AND($G$34="",$H$34="",S35=0)+AND($G$36="",$H$36="",S37=0)+AND($G$38="",$H$38="",S39=0)+AND($G$40="",$H$40="",S41=0)+AND($G$42="",$H$42="",S43=0)+AND($G$44="",$H$44="",S45=0)+AND($G$46="",$H$46="",S47=0)+AND($G$48="",$H$48="",S49=0)+AND($G$50="",$H$50="",S51=0)+AND($G$52="",$H$52="",S53=0)+AND($G$54="",$H$54="",S55=0)+AND($G$56="",$H$56="",S57=0)+AND($G$58="",$H$58="",S59=0)+AND($G$60="",$H$60="",S61=0)+AND($G$62="",$H$62="",S63=0)+AND($G$64="",$H$64="",S65=0)+AND($G$66="",$H$66="",S67=0)+AND($G$68="",$H$68="",S69=0)+AND($G$70="",$H$70="",S71=0)+AND($G$72="",$H$72="",S73=0)+AND($G$74="",$H$74="",S75=0)+AND($G$76="",$H$76="",S77=0)+AND($G$78="",$H$78="",S79=0))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="T6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",T9=0)+AND($G$10="",$H$10="",T11=0)+AND($G$12="",$H$12="",T13=0)+AND($G$14="",$H$14="",T15=0)+AND($G$16="",$H$16="",T17=0)+AND($G$18="",$H$18="",T19=0)+AND($G$20="",$H$20="",T21=0)+AND($G$22="",$H$22="",T23=0)+AND($G$24="",$H$24="",T25=0)+AND($G$26="",$H$26="",T27=0)+AND($G$28="",$H$28="",T29=0)+AND($G$30="",$H$30="",T31=0)+AND($G$32="",$H$32="",T33=0)+AND($G$34="",$H$34="",T35=0)+AND($G$36="",$H$36="",T37=0)+AND($G$38="",$H$38="",T39=0)+AND($G$40="",$H$40="",T41=0)+AND($G$42="",$H$42="",T43=0)+AND($G$44="",$H$44="",T45=0)+AND($G$46="",$H$46="",T47=0)+AND($G$48="",$H$48="",T49=0)+AND($G$50="",$H$50="",T51=0)+AND($G$52="",$H$52="",T53=0)+AND($G$54="",$H$54="",T55=0)+AND($G$56="",$H$56="",T57=0)+AND($G$58="",$H$58="",T59=0)+AND($G$60="",$H$60="",T61=0)+AND($G$62="",$H$62="",T63=0)+AND($G$64="",$H$64="",T65=0)+AND($G$66="",$H$66="",T67=0)+AND($G$68="",$H$68="",T69=0)+AND($G$70="",$H$70="",T71=0)+AND($G$72="",$H$72="",T73=0)+AND($G$74="",$H$74="",T75=0)+AND($G$76="",$H$76="",T77=0)+AND($G$78="",$H$78="",T79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",U9=0)+AND($G$10="",$H$10="",U11=0)+AND($G$12="",$H$12="",U13=0)+AND($G$14="",$H$14="",U15=0)+AND($G$16="",$H$16="",U17=0)+AND($G$18="",$H$18="",U19=0)+AND($G$20="",$H$20="",U21=0)+AND($G$22="",$H$22="",U23=0)+AND($G$24="",$H$24="",U25=0)+AND($G$26="",$H$26="",U27=0)+AND($G$28="",$H$28="",U29=0)+AND($G$30="",$H$30="",U31=0)+AND($G$32="",$H$32="",U33=0)+AND($G$34="",$H$34="",U35=0)+AND($G$36="",$H$36="",U37=0)+AND($G$38="",$H$38="",U39=0)+AND($G$40="",$H$40="",U41=0)+AND($G$42="",$H$42="",U43=0)+AND($G$44="",$H$44="",U45=0)+AND($G$46="",$H$46="",U47=0)+AND($G$48="",$H$48="",U49=0)+AND($G$50="",$H$50="",U51=0)+AND($G$52="",$H$52="",U53=0)+AND($G$54="",$H$54="",U55=0)+AND($G$56="",$H$56="",U57=0)+AND($G$58="",$H$58="",U59=0)+AND($G$60="",$H$60="",U61=0)+AND($G$62="",$H$62="",U63=0)+AND($G$64="",$H$64="",U65=0)+AND($G$66="",$H$66="",U67=0)+AND($G$68="",$H$68="",U69=0)+AND($G$70="",$H$70="",U71=0)+AND($G$72="",$H$72="",U73=0)+AND($G$74="",$H$74="",U75=0)+AND($G$76="",$H$76="",U77=0)+AND($G$78="",$H$78="",U79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",V9=0)+AND($G$10="",$H$10="",V11=0)+AND($G$12="",$H$12="",V13=0)+AND($G$14="",$H$14="",V15=0)+AND($G$16="",$H$16="",V17=0)+AND($G$18="",$H$18="",V19=0)+AND($G$20="",$H$20="",V21=0)+AND($G$22="",$H$22="",V23=0)+AND($G$24="",$H$24="",V25=0)+AND($G$26="",$H$26="",V27=0)+AND($G$28="",$H$28="",V29=0)+AND($G$30="",$H$30="",V31=0)+AND($G$32="",$H$32="",V33=0)+AND($G$34="",$H$34="",V35=0)+AND($G$36="",$H$36="",V37=0)+AND($G$38="",$H$38="",V39=0)+AND($G$40="",$H$40="",V41=0)+AND($G$42="",$H$42="",V43=0)+AND($G$44="",$H$44="",V45=0)+AND($G$46="",$H$46="",V47=0)+AND($G$48="",$H$48="",V49=0)+AND($G$50="",$H$50="",V51=0)+AND($G$52="",$H$52="",V53=0)+AND($G$54="",$H$54="",V55=0)+AND($G$56="",$H$56="",V57=0)+AND($G$58="",$H$58="",V59=0)+AND($G$60="",$H$60="",V61=0)+AND($G$62="",$H$62="",V63=0)+AND($G$64="",$H$64="",V65=0)+AND($G$66="",$H$66="",V67=0)+AND($G$68="",$H$68="",V69=0)+AND($G$70="",$H$70="",V71=0)+AND($G$72="",$H$72="",V73=0)+AND($G$74="",$H$74="",V75=0)+AND($G$76="",$H$76="",V77=0)+AND($G$78="",$H$78="",V79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",W9=0)+AND($G$10="",$H$10="",W11=0)+AND($G$12="",$H$12="",W13=0)+AND($G$14="",$H$14="",W15=0)+AND($G$16="",$H$16="",W17=0)+AND($G$18="",$H$18="",W19=0)+AND($G$20="",$H$20="",W21=0)+AND($G$22="",$H$22="",W23=0)+AND($G$24="",$H$24="",W25=0)+AND($G$26="",$H$26="",W27=0)+AND($G$28="",$H$28="",W29=0)+AND($G$30="",$H$30="",W31=0)+AND($G$32="",$H$32="",W33=0)+AND($G$34="",$H$34="",W35=0)+AND($G$36="",$H$36="",W37=0)+AND($G$38="",$H$38="",W39=0)+AND($G$40="",$H$40="",W41=0)+AND($G$42="",$H$42="",W43=0)+AND($G$44="",$H$44="",W45=0)+AND($G$46="",$H$46="",W47=0)+AND($G$48="",$H$48="",W49=0)+AND($G$50="",$H$50="",W51=0)+AND($G$52="",$H$52="",W53=0)+AND($G$54="",$H$54="",W55=0)+AND($G$56="",$H$56="",W57=0)+AND($G$58="",$H$58="",W59=0)+AND($G$60="",$H$60="",W61=0)+AND($G$62="",$H$62="",W63=0)+AND($G$64="",$H$64="",W65=0)+AND($G$66="",$H$66="",W67=0)+AND($G$68="",$H$68="",W69=0)+AND($G$70="",$H$70="",W71=0)+AND($G$72="",$H$72="",W73=0)+AND($G$74="",$H$74="",W75=0)+AND($G$76="",$H$76="",W77=0)+AND($G$78="",$H$78="",W79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",X9=0)+AND($G$10="",$H$10="",X11=0)+AND($G$12="",$H$12="",X13=0)+AND($G$14="",$H$14="",X15=0)+AND($G$16="",$H$16="",X17=0)+AND($G$18="",$H$18="",X19=0)+AND($G$20="",$H$20="",X21=0)+AND($G$22="",$H$22="",X23=0)+AND($G$24="",$H$24="",X25=0)+AND($G$26="",$H$26="",X27=0)+AND($G$28="",$H$28="",X29=0)+AND($G$30="",$H$30="",X31=0)+AND($G$32="",$H$32="",X33=0)+AND($G$34="",$H$34="",X35=0)+AND($G$36="",$H$36="",X37=0)+AND($G$38="",$H$38="",X39=0)+AND($G$40="",$H$40="",X41=0)+AND($G$42="",$H$42="",X43=0)+AND($G$44="",$H$44="",X45=0)+AND($G$46="",$H$46="",X47=0)+AND($G$48="",$H$48="",X49=0)+AND($G$50="",$H$50="",X51=0)+AND($G$52="",$H$52="",X53=0)+AND($G$54="",$H$54="",X55=0)+AND($G$56="",$H$56="",X57=0)+AND($G$58="",$H$58="",X59=0)+AND($G$60="",$H$60="",X61=0)+AND($G$62="",$H$62="",X63=0)+AND($G$64="",$H$64="",X65=0)+AND($G$66="",$H$66="",X67=0)+AND($G$68="",$H$68="",X69=0)+AND($G$70="",$H$70="",X71=0)+AND($G$72="",$H$72="",X73=0)+AND($G$74="",$H$74="",X75=0)+AND($G$76="",$H$76="",X77=0)+AND($G$78="",$H$78="",X79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Y6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",Y9=0)+AND($G$10="",$H$10="",Y11=0)+AND($G$12="",$H$12="",Y13=0)+AND($G$14="",$H$14="",Y15=0)+AND($G$16="",$H$16="",Y17=0)+AND($G$18="",$H$18="",Y19=0)+AND($G$20="",$H$20="",Y21=0)+AND($G$22="",$H$22="",Y23=0)+AND($G$24="",$H$24="",Y25=0)+AND($G$26="",$H$26="",Y27=0)+AND($G$28="",$H$28="",Y29=0)+AND($G$30="",$H$30="",Y31=0)+AND($G$32="",$H$32="",Y33=0)+AND($G$34="",$H$34="",Y35=0)+AND($G$36="",$H$36="",Y37=0)+AND($G$38="",$H$38="",Y39=0)+AND($G$40="",$H$40="",Y41=0)+AND($G$42="",$H$42="",Y43=0)+AND($G$44="",$H$44="",Y45=0)+AND($G$46="",$H$46="",Y47=0)+AND($G$48="",$H$48="",Y49=0)+AND($G$50="",$H$50="",Y51=0)+AND($G$52="",$H$52="",Y53=0)+AND($G$54="",$H$54="",Y55=0)+AND($G$56="",$H$56="",Y57=0)+AND($G$58="",$H$58="",Y59=0)+AND($G$60="",$H$60="",Y61=0)+AND($G$62="",$H$62="",Y63=0)+AND($G$64="",$H$64="",Y65=0)+AND($G$66="",$H$66="",Y67=0)+AND($G$68="",$H$68="",Y69=0)+AND($G$70="",$H$70="",Y71=0)+AND($G$72="",$H$72="",Y73=0)+AND($G$74="",$H$74="",Y75=0)+AND($G$76="",$H$76="",Y77=0)+AND($G$78="",$H$78="",Y79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",Z9=0)+AND($G$10="",$H$10="",Z11=0)+AND($G$12="",$H$12="",Z13=0)+AND($G$14="",$H$14="",Z15=0)+AND($G$16="",$H$16="",Z17=0)+AND($G$18="",$H$18="",Z19=0)+AND($G$20="",$H$20="",Z21=0)+AND($G$22="",$H$22="",Z23=0)+AND($G$24="",$H$24="",Z25=0)+AND($G$26="",$H$26="",Z27=0)+AND($G$28="",$H$28="",Z29=0)+AND($G$30="",$H$30="",Z31=0)+AND($G$32="",$H$32="",Z33=0)+AND($G$34="",$H$34="",Z35=0)+AND($G$36="",$H$36="",Z37=0)+AND($G$38="",$H$38="",Z39=0)+AND($G$40="",$H$40="",Z41=0)+AND($G$42="",$H$42="",Z43=0)+AND($G$44="",$H$44="",Z45=0)+AND($G$46="",$H$46="",Z47=0)+AND($G$48="",$H$48="",Z49=0)+AND($G$50="",$H$50="",Z51=0)+AND($G$52="",$H$52="",Z53=0)+AND($G$54="",$H$54="",Z55=0)+AND($G$56="",$H$56="",Z57=0)+AND($G$58="",$H$58="",Z59=0)+AND($G$60="",$H$60="",Z61=0)+AND($G$62="",$H$62="",Z63=0)+AND($G$64="",$H$64="",Z65=0)+AND($G$66="",$H$66="",Z67=0)+AND($G$68="",$H$68="",Z69=0)+AND($G$70="",$H$70="",Z71=0)+AND($G$72="",$H$72="",Z73=0)+AND($G$74="",$H$74="",Z75=0)+AND($G$76="",$H$76="",Z77=0)+AND($G$78="",$H$78="",Z79=0))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AA6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AA9=0)+AND($G$10="",$H$10="",AA11=0)+AND($G$12="",$H$12="",AA13=0)+AND($G$14="",$H$14="",AA15=0)+AND($G$16="",$H$16="",AA17=0)+AND($G$18="",$H$18="",AA19=0)+AND($G$20="",$H$20="",AA21=0)+AND($G$22="",$H$22="",AA23=0)+AND($G$24="",$H$24="",AA25=0)+AND($G$26="",$H$26="",AA27=0)+AND($G$28="",$H$28="",AA29=0)+AND($G$30="",$H$30="",AA31=0)+AND($G$32="",$H$32="",AA33=0)+AND($G$34="",$H$34="",AA35=0)+AND($G$36="",$H$36="",AA37=0)+AND($G$38="",$H$38="",AA39=0)+AND($G$40="",$H$40="",AA41=0)+AND($G$42="",$H$42="",AA43=0)+AND($G$44="",$H$44="",AA45=0)+AND($G$46="",$H$46="",AA47=0)+AND($G$48="",$H$48="",AA49=0)+AND($G$50="",$H$50="",AA51=0)+AND($G$52="",$H$52="",AA53=0)+AND($G$54="",$H$54="",AA55=0)+AND($G$56="",$H$56="",AA57=0)+AND($G$58="",$H$58="",AA59=0)+AND($G$60="",$H$60="",AA61=0)+AND($G$62="",$H$62="",AA63=0)+AND($G$64="",$H$64="",AA65=0)+AND($G$66="",$H$66="",AA67=0)+AND($G$68="",$H$68="",AA69=0)+AND($G$70="",$H$70="",AA71=0)+AND($G$72="",$H$72="",AA73=0)+AND($G$74="",$H$74="",AA75=0)+AND($G$76="",$H$76="",AA77=0)+AND($G$78="",$H$78="",AA79=0))</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AB6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AB9=0)+AND($G$10="",$H$10="",AB11=0)+AND($G$12="",$H$12="",AB13=0)+AND($G$14="",$H$14="",AB15=0)+AND($G$16="",$H$16="",AB17=0)+AND($G$18="",$H$18="",AB19=0)+AND($G$20="",$H$20="",AB21=0)+AND($G$22="",$H$22="",AB23=0)+AND($G$24="",$H$24="",AB25=0)+AND($G$26="",$H$26="",AB27=0)+AND($G$28="",$H$28="",AB29=0)+AND($G$30="",$H$30="",AB31=0)+AND($G$32="",$H$32="",AB33=0)+AND($G$34="",$H$34="",AB35=0)+AND($G$36="",$H$36="",AB37=0)+AND($G$38="",$H$38="",AB39=0)+AND($G$40="",$H$40="",AB41=0)+AND($G$42="",$H$42="",AB43=0)+AND($G$44="",$H$44="",AB45=0)+AND($G$46="",$H$46="",AB47=0)+AND($G$48="",$H$48="",AB49=0)+AND($G$50="",$H$50="",AB51=0)+AND($G$52="",$H$52="",AB53=0)+AND($G$54="",$H$54="",AB55=0)+AND($G$56="",$H$56="",AB57=0)+AND($G$58="",$H$58="",AB59=0)+AND($G$60="",$H$60="",AB61=0)+AND($G$62="",$H$62="",AB63=0)+AND($G$64="",$H$64="",AB65=0)+AND($G$66="",$H$66="",AB67=0)+AND($G$68="",$H$68="",AB69=0)+AND($G$70="",$H$70="",AB71=0)+AND($G$72="",$H$72="",AB73=0)+AND($G$74="",$H$74="",AB75=0)+AND($G$76="",$H$76="",AB77=0)+AND($G$78="",$H$78="",AB79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AC9=0)+AND($G$10="",$H$10="",AC11=0)+AND($G$12="",$H$12="",AC13=0)+AND($G$14="",$H$14="",AC15=0)+AND($G$16="",$H$16="",AC17=0)+AND($G$18="",$H$18="",AC19=0)+AND($G$20="",$H$20="",AC21=0)+AND($G$22="",$H$22="",AC23=0)+AND($G$24="",$H$24="",AC25=0)+AND($G$26="",$H$26="",AC27=0)+AND($G$28="",$H$28="",AC29=0)+AND($G$30="",$H$30="",AC31=0)+AND($G$32="",$H$32="",AC33=0)+AND($G$34="",$H$34="",AC35=0)+AND($G$36="",$H$36="",AC37=0)+AND($G$38="",$H$38="",AC39=0)+AND($G$40="",$H$40="",AC41=0)+AND($G$42="",$H$42="",AC43=0)+AND($G$44="",$H$44="",AC45=0)+AND($G$46="",$H$46="",AC47=0)+AND($G$48="",$H$48="",AC49=0)+AND($G$50="",$H$50="",AC51=0)+AND($G$52="",$H$52="",AC53=0)+AND($G$54="",$H$54="",AC55=0)+AND($G$56="",$H$56="",AC57=0)+AND($G$58="",$H$58="",AC59=0)+AND($G$60="",$H$60="",AC61=0)+AND($G$62="",$H$62="",AC63=0)+AND($G$64="",$H$64="",AC65=0)+AND($G$66="",$H$66="",AC67=0)+AND($G$68="",$H$68="",AC69=0)+AND($G$70="",$H$70="",AC71=0)+AND($G$72="",$H$72="",AC73=0)+AND($G$74="",$H$74="",AC75=0)+AND($G$76="",$H$76="",AC77=0)+AND($G$78="",$H$78="",AC79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AD9=0)+AND($G$10="",$H$10="",AD11=0)+AND($G$12="",$H$12="",AD13=0)+AND($G$14="",$H$14="",AD15=0)+AND($G$16="",$H$16="",AD17=0)+AND($G$18="",$H$18="",AD19=0)+AND($G$20="",$H$20="",AD21=0)+AND($G$22="",$H$22="",AD23=0)+AND($G$24="",$H$24="",AD25=0)+AND($G$26="",$H$26="",AD27=0)+AND($G$28="",$H$28="",AD29=0)+AND($G$30="",$H$30="",AD31=0)+AND($G$32="",$H$32="",AD33=0)+AND($G$34="",$H$34="",AD35=0)+AND($G$36="",$H$36="",AD37=0)+AND($G$38="",$H$38="",AD39=0)+AND($G$40="",$H$40="",AD41=0)+AND($G$42="",$H$42="",AD43=0)+AND($G$44="",$H$44="",AD45=0)+AND($G$46="",$H$46="",AD47=0)+AND($G$48="",$H$48="",AD49=0)+AND($G$50="",$H$50="",AD51=0)+AND($G$52="",$H$52="",AD53=0)+AND($G$54="",$H$54="",AD55=0)+AND($G$56="",$H$56="",AD57=0)+AND($G$58="",$H$58="",AD59=0)+AND($G$60="",$H$60="",AD61=0)+AND($G$62="",$H$62="",AD63=0)+AND($G$64="",$H$64="",AD65=0)+AND($G$66="",$H$66="",AD67=0)+AND($G$68="",$H$68="",AD69=0)+AND($G$70="",$H$70="",AD71=0)+AND($G$72="",$H$72="",AD73=0)+AND($G$74="",$H$74="",AD75=0)+AND($G$76="",$H$76="",AD77=0)+AND($G$78="",$H$78="",AD79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AE9=0)+AND($G$10="",$H$10="",AE11=0)+AND($G$12="",$H$12="",AE13=0)+AND($G$14="",$H$14="",AE15=0)+AND($G$16="",$H$16="",AE17=0)+AND($G$18="",$H$18="",AE19=0)+AND($G$20="",$H$20="",AE21=0)+AND($G$22="",$H$22="",AE23=0)+AND($G$24="",$H$24="",AE25=0)+AND($G$26="",$H$26="",AE27=0)+AND($G$28="",$H$28="",AE29=0)+AND($G$30="",$H$30="",AE31=0)+AND($G$32="",$H$32="",AE33=0)+AND($G$34="",$H$34="",AE35=0)+AND($G$36="",$H$36="",AE37=0)+AND($G$38="",$H$38="",AE39=0)+AND($G$40="",$H$40="",AE41=0)+AND($G$42="",$H$42="",AE43=0)+AND($G$44="",$H$44="",AE45=0)+AND($G$46="",$H$46="",AE47=0)+AND($G$48="",$H$48="",AE49=0)+AND($G$50="",$H$50="",AE51=0)+AND($G$52="",$H$52="",AE53=0)+AND($G$54="",$H$54="",AE55=0)+AND($G$56="",$H$56="",AE57=0)+AND($G$58="",$H$58="",AE59=0)+AND($G$60="",$H$60="",AE61=0)+AND($G$62="",$H$62="",AE63=0)+AND($G$64="",$H$64="",AE65=0)+AND($G$66="",$H$66="",AE67=0)+AND($G$68="",$H$68="",AE69=0)+AND($G$70="",$H$70="",AE71=0)+AND($G$72="",$H$72="",AE73=0)+AND($G$74="",$H$74="",AE75=0)+AND($G$76="",$H$76="",AE77=0)+AND($G$78="",$H$78="",AE79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AF9=0)+AND($G$10="",$H$10="",AF11=0)+AND($G$12="",$H$12="",AF13=0)+AND($G$14="",$H$14="",AF15=0)+AND($G$16="",$H$16="",AF17=0)+AND($G$18="",$H$18="",AF19=0)+AND($G$20="",$H$20="",AF21=0)+AND($G$22="",$H$22="",AF23=0)+AND($G$24="",$H$24="",AF25=0)+AND($G$26="",$H$26="",AF27=0)+AND($G$28="",$H$28="",AF29=0)+AND($G$30="",$H$30="",AF31=0)+AND($G$32="",$H$32="",AF33=0)+AND($G$34="",$H$34="",AF35=0)+AND($G$36="",$H$36="",AF37=0)+AND($G$38="",$H$38="",AF39=0)+AND($G$40="",$H$40="",AF41=0)+AND($G$42="",$H$42="",AF43=0)+AND($G$44="",$H$44="",AF45=0)+AND($G$46="",$H$46="",AF47=0)+AND($G$48="",$H$48="",AF49=0)+AND($G$50="",$H$50="",AF51=0)+AND($G$52="",$H$52="",AF53=0)+AND($G$54="",$H$54="",AF55=0)+AND($G$56="",$H$56="",AF57=0)+AND($G$58="",$H$58="",AF59=0)+AND($G$60="",$H$60="",AF61=0)+AND($G$62="",$H$62="",AF63=0)+AND($G$64="",$H$64="",AF65=0)+AND($G$66="",$H$66="",AF67=0)+AND($G$68="",$H$68="",AF69=0)+AND($G$70="",$H$70="",AF71=0)+AND($G$72="",$H$72="",AF73=0)+AND($G$74="",$H$74="",AF75=0)+AND($G$76="",$H$76="",AF77=0)+AND($G$78="",$H$78="",AF79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AG9=0)+AND($G$10="",$H$10="",AG11=0)+AND($G$12="",$H$12="",AG13=0)+AND($G$14="",$H$14="",AG15=0)+AND($G$16="",$H$16="",AG17=0)+AND($G$18="",$H$18="",AG19=0)+AND($G$20="",$H$20="",AG21=0)+AND($G$22="",$H$22="",AG23=0)+AND($G$24="",$H$24="",AG25=0)+AND($G$26="",$H$26="",AG27=0)+AND($G$28="",$H$28="",AG29=0)+AND($G$30="",$H$30="",AG31=0)+AND($G$32="",$H$32="",AG33=0)+AND($G$34="",$H$34="",AG35=0)+AND($G$36="",$H$36="",AG37=0)+AND($G$38="",$H$38="",AG39=0)+AND($G$40="",$H$40="",AG41=0)+AND($G$42="",$H$42="",AG43=0)+AND($G$44="",$H$44="",AG45=0)+AND($G$46="",$H$46="",AG47=0)+AND($G$48="",$H$48="",AG49=0)+AND($G$50="",$H$50="",AG51=0)+AND($G$52="",$H$52="",AG53=0)+AND($G$54="",$H$54="",AG55=0)+AND($G$56="",$H$56="",AG57=0)+AND($G$58="",$H$58="",AG59=0)+AND($G$60="",$H$60="",AG61=0)+AND($G$62="",$H$62="",AG63=0)+AND($G$64="",$H$64="",AG65=0)+AND($G$66="",$H$66="",AG67=0)+AND($G$68="",$H$68="",AG69=0)+AND($G$70="",$H$70="",AG71=0)+AND($G$72="",$H$72="",AG73=0)+AND($G$74="",$H$74="",AG75=0)+AND($G$76="",$H$76="",AG77=0)+AND($G$78="",$H$78="",AG79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AH9=0)+AND($G$10="",$H$10="",AH11=0)+AND($G$12="",$H$12="",AH13=0)+AND($G$14="",$H$14="",AH15=0)+AND($G$16="",$H$16="",AH17=0)+AND($G$18="",$H$18="",AH19=0)+AND($G$20="",$H$20="",AH21=0)+AND($G$22="",$H$22="",AH23=0)+AND($G$24="",$H$24="",AH25=0)+AND($G$26="",$H$26="",AH27=0)+AND($G$28="",$H$28="",AH29=0)+AND($G$30="",$H$30="",AH31=0)+AND($G$32="",$H$32="",AH33=0)+AND($G$34="",$H$34="",AH35=0)+AND($G$36="",$H$36="",AH37=0)+AND($G$38="",$H$38="",AH39=0)+AND($G$40="",$H$40="",AH41=0)+AND($G$42="",$H$42="",AH43=0)+AND($G$44="",$H$44="",AH45=0)+AND($G$46="",$H$46="",AH47=0)+AND($G$48="",$H$48="",AH49=0)+AND($G$50="",$H$50="",AH51=0)+AND($G$52="",$H$52="",AH53=0)+AND($G$54="",$H$54="",AH55=0)+AND($G$56="",$H$56="",AH57=0)+AND($G$58="",$H$58="",AH59=0)+AND($G$60="",$H$60="",AH61=0)+AND($G$62="",$H$62="",AH63=0)+AND($G$64="",$H$64="",AH65=0)+AND($G$66="",$H$66="",AH67=0)+AND($G$68="",$H$68="",AH69=0)+AND($G$70="",$H$70="",AH71=0)+AND($G$72="",$H$72="",AH73=0)+AND($G$74="",$H$74="",AH75=0)+AND($G$76="",$H$76="",AH77=0)+AND($G$78="",$H$78="",AH79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AI9=0)+AND($G$10="",$H$10="",AI11=0)+AND($G$12="",$H$12="",AI13=0)+AND($G$14="",$H$14="",AI15=0)+AND($G$16="",$H$16="",AI17=0)+AND($G$18="",$H$18="",AI19=0)+AND($G$20="",$H$20="",AI21=0)+AND($G$22="",$H$22="",AI23=0)+AND($G$24="",$H$24="",AI25=0)+AND($G$26="",$H$26="",AI27=0)+AND($G$28="",$H$28="",AI29=0)+AND($G$30="",$H$30="",AI31=0)+AND($G$32="",$H$32="",AI33=0)+AND($G$34="",$H$34="",AI35=0)+AND($G$36="",$H$36="",AI37=0)+AND($G$38="",$H$38="",AI39=0)+AND($G$40="",$H$40="",AI41=0)+AND($G$42="",$H$42="",AI43=0)+AND($G$44="",$H$44="",AI45=0)+AND($G$46="",$H$46="",AI47=0)+AND($G$48="",$H$48="",AI49=0)+AND($G$50="",$H$50="",AI51=0)+AND($G$52="",$H$52="",AI53=0)+AND($G$54="",$H$54="",AI55=0)+AND($G$56="",$H$56="",AI57=0)+AND($G$58="",$H$58="",AI59=0)+AND($G$60="",$H$60="",AI61=0)+AND($G$62="",$H$62="",AI63=0)+AND($G$64="",$H$64="",AI65=0)+AND($G$66="",$H$66="",AI67=0)+AND($G$68="",$H$68="",AI69=0)+AND($G$70="",$H$70="",AI71=0)+AND($G$72="",$H$72="",AI73=0)+AND($G$74="",$H$74="",AI75=0)+AND($G$76="",$H$76="",AI77=0)+AND($G$78="",$H$78="",AI79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AJ6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AJ9=0)+AND($G$10="",$H$10="",AJ11=0)+AND($G$12="",$H$12="",AJ13=0)+AND($G$14="",$H$14="",AJ15=0)+AND($G$16="",$H$16="",AJ17=0)+AND($G$18="",$H$18="",AJ19=0)+AND($G$20="",$H$20="",AJ21=0)+AND($G$22="",$H$22="",AJ23=0)+AND($G$24="",$H$24="",AJ25=0)+AND($G$26="",$H$26="",AJ27=0)+AND($G$28="",$H$28="",AJ29=0)+AND($G$30="",$H$30="",AJ31=0)+AND($G$32="",$H$32="",AJ33=0)+AND($G$34="",$H$34="",AJ35=0)+AND($G$36="",$H$36="",AJ37=0)+AND($G$38="",$H$38="",AJ39=0)+AND($G$40="",$H$40="",AJ41=0)+AND($G$42="",$H$42="",AJ43=0)+AND($G$44="",$H$44="",AJ45=0)+AND($G$46="",$H$46="",AJ47=0)+AND($G$48="",$H$48="",AJ49=0)+AND($G$50="",$H$50="",AJ51=0)+AND($G$52="",$H$52="",AJ53=0)+AND($G$54="",$H$54="",AJ55=0)+AND($G$56="",$H$56="",AJ57=0)+AND($G$58="",$H$58="",AJ59=0)+AND($G$60="",$H$60="",AJ61=0)+AND($G$62="",$H$62="",AJ63=0)+AND($G$64="",$H$64="",AJ65=0)+AND($G$66="",$H$66="",AJ67=0)+AND($G$68="",$H$68="",AJ69=0)+AND($G$70="",$H$70="",AJ71=0)+AND($G$72="",$H$72="",AJ73=0)+AND($G$74="",$H$74="",AJ75=0)+AND($G$76="",$H$76="",AJ77=0)+AND($G$78="",$H$78="",AJ79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AK6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AK9=0)+AND($G$10="",$H$10="",AK11=0)+AND($G$12="",$H$12="",AK13=0)+AND($G$14="",$H$14="",AK15=0)+AND($G$16="",$H$16="",AK17=0)+AND($G$18="",$H$18="",AK19=0)+AND($G$20="",$H$20="",AK21=0)+AND($G$22="",$H$22="",AK23=0)+AND($G$24="",$H$24="",AK25=0)+AND($G$26="",$H$26="",AK27=0)+AND($G$28="",$H$28="",AK29=0)+AND($G$30="",$H$30="",AK31=0)+AND($G$32="",$H$32="",AK33=0)+AND($G$34="",$H$34="",AK35=0)+AND($G$36="",$H$36="",AK37=0)+AND($G$38="",$H$38="",AK39=0)+AND($G$40="",$H$40="",AK41=0)+AND($G$42="",$H$42="",AK43=0)+AND($G$44="",$H$44="",AK45=0)+AND($G$46="",$H$46="",AK47=0)+AND($G$48="",$H$48="",AK49=0)+AND($G$50="",$H$50="",AK51=0)+AND($G$52="",$H$52="",AK53=0)+AND($G$54="",$H$54="",AK55=0)+AND($G$56="",$H$56="",AK57=0)+AND($G$58="",$H$58="",AK59=0)+AND($G$60="",$H$60="",AK61=0)+AND($G$62="",$H$62="",AK63=0)+AND($G$64="",$H$64="",AK65=0)+AND($G$66="",$H$66="",AK67=0)+AND($G$68="",$H$68="",AK69=0)+AND($G$70="",$H$70="",AK71=0)+AND($G$72="",$H$72="",AK73=0)+AND($G$74="",$H$74="",AK75=0)+AND($G$76="",$H$76="",AK77=0)+AND($G$78="",$H$78="",AK79=0))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AL6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AL9=0)+AND($G$10="",$H$10="",AL11=0)+AND($G$12="",$H$12="",AL13=0)+AND($G$14="",$H$14="",AL15=0)+AND($G$16="",$H$16="",AL17=0)+AND($G$18="",$H$18="",AL19=0)+AND($G$20="",$H$20="",AL21=0)+AND($G$22="",$H$22="",AL23=0)+AND($G$24="",$H$24="",AL25=0)+AND($G$26="",$H$26="",AL27=0)+AND($G$28="",$H$28="",AL29=0)+AND($G$30="",$H$30="",AL31=0)+AND($G$32="",$H$32="",AL33=0)+AND($G$34="",$H$34="",AL35=0)+AND($G$36="",$H$36="",AL37=0)+AND($G$38="",$H$38="",AL39=0)+AND($G$40="",$H$40="",AL41=0)+AND($G$42="",$H$42="",AL43=0)+AND($G$44="",$H$44="",AL45=0)+AND($G$46="",$H$46="",AL47=0)+AND($G$48="",$H$48="",AL49=0)+AND($G$50="",$H$50="",AL51=0)+AND($G$52="",$H$52="",AL53=0)+AND($G$54="",$H$54="",AL55=0)+AND($G$56="",$H$56="",AL57=0)+AND($G$58="",$H$58="",AL59=0)+AND($G$60="",$H$60="",AL61=0)+AND($G$62="",$H$62="",AL63=0)+AND($G$64="",$H$64="",AL65=0)+AND($G$66="",$H$66="",AL67=0)+AND($G$68="",$H$68="",AL69=0)+AND($G$70="",$H$70="",AL71=0)+AND($G$72="",$H$72="",AL73=0)+AND($G$74="",$H$74="",AL75=0)+AND($G$76="",$H$76="",AL77=0)+AND($G$78="",$H$78="",AL79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AM6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AM9=0)+AND($G$10="",$H$10="",AM11=0)+AND($G$12="",$H$12="",AM13=0)+AND($G$14="",$H$14="",AM15=0)+AND($G$16="",$H$16="",AM17=0)+AND($G$18="",$H$18="",AM19=0)+AND($G$20="",$H$20="",AM21=0)+AND($G$22="",$H$22="",AM23=0)+AND($G$24="",$H$24="",AM25=0)+AND($G$26="",$H$26="",AM27=0)+AND($G$28="",$H$28="",AM29=0)+AND($G$30="",$H$30="",AM31=0)+AND($G$32="",$H$32="",AM33=0)+AND($G$34="",$H$34="",AM35=0)+AND($G$36="",$H$36="",AM37=0)+AND($G$38="",$H$38="",AM39=0)+AND($G$40="",$H$40="",AM41=0)+AND($G$42="",$H$42="",AM43=0)+AND($G$44="",$H$44="",AM45=0)+AND($G$46="",$H$46="",AM47=0)+AND($G$48="",$H$48="",AM49=0)+AND($G$50="",$H$50="",AM51=0)+AND($G$52="",$H$52="",AM53=0)+AND($G$54="",$H$54="",AM55=0)+AND($G$56="",$H$56="",AM57=0)+AND($G$58="",$H$58="",AM59=0)+AND($G$60="",$H$60="",AM61=0)+AND($G$62="",$H$62="",AM63=0)+AND($G$64="",$H$64="",AM65=0)+AND($G$66="",$H$66="",AM67=0)+AND($G$68="",$H$68="",AM69=0)+AND($G$70="",$H$70="",AM71=0)+AND($G$72="",$H$72="",AM73=0)+AND($G$74="",$H$74="",AM75=0)+AND($G$76="",$H$76="",AM77=0)+AND($G$78="",$H$78="",AM79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AN6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AN9=0)+AND($G$10="",$H$10="",AN11=0)+AND($G$12="",$H$12="",AN13=0)+AND($G$14="",$H$14="",AN15=0)+AND($G$16="",$H$16="",AN17=0)+AND($G$18="",$H$18="",AN19=0)+AND($G$20="",$H$20="",AN21=0)+AND($G$22="",$H$22="",AN23=0)+AND($G$24="",$H$24="",AN25=0)+AND($G$26="",$H$26="",AN27=0)+AND($G$28="",$H$28="",AN29=0)+AND($G$30="",$H$30="",AN31=0)+AND($G$32="",$H$32="",AN33=0)+AND($G$34="",$H$34="",AN35=0)+AND($G$36="",$H$36="",AN37=0)+AND($G$38="",$H$38="",AN39=0)+AND($G$40="",$H$40="",AN41=0)+AND($G$42="",$H$42="",AN43=0)+AND($G$44="",$H$44="",AN45=0)+AND($G$46="",$H$46="",AN47=0)+AND($G$48="",$H$48="",AN49=0)+AND($G$50="",$H$50="",AN51=0)+AND($G$52="",$H$52="",AN53=0)+AND($G$54="",$H$54="",AN55=0)+AND($G$56="",$H$56="",AN57=0)+AND($G$58="",$H$58="",AN59=0)+AND($G$60="",$H$60="",AN61=0)+AND($G$62="",$H$62="",AN63=0)+AND($G$64="",$H$64="",AN65=0)+AND($G$66="",$H$66="",AN67=0)+AND($G$68="",$H$68="",AN69=0)+AND($G$70="",$H$70="",AN71=0)+AND($G$72="",$H$72="",AN73=0)+AND($G$74="",$H$74="",AN75=0)+AND($G$76="",$H$76="",AN77=0)+AND($G$78="",$H$78="",AN79=0))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AO6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AO9=0)+AND($G$10="",$H$10="",AO11=0)+AND($G$12="",$H$12="",AO13=0)+AND($G$14="",$H$14="",AO15=0)+AND($G$16="",$H$16="",AO17=0)+AND($G$18="",$H$18="",AO19=0)+AND($G$20="",$H$20="",AO21=0)+AND($G$22="",$H$22="",AO23=0)+AND($G$24="",$H$24="",AO25=0)+AND($G$26="",$H$26="",AO27=0)+AND($G$28="",$H$28="",AO29=0)+AND($G$30="",$H$30="",AO31=0)+AND($G$32="",$H$32="",AO33=0)+AND($G$34="",$H$34="",AO35=0)+AND($G$36="",$H$36="",AO37=0)+AND($G$38="",$H$38="",AO39=0)+AND($G$40="",$H$40="",AO41=0)+AND($G$42="",$H$42="",AO43=0)+AND($G$44="",$H$44="",AO45=0)+AND($G$46="",$H$46="",AO47=0)+AND($G$48="",$H$48="",AO49=0)+AND($G$50="",$H$50="",AO51=0)+AND($G$52="",$H$52="",AO53=0)+AND($G$54="",$H$54="",AO55=0)+AND($G$56="",$H$56="",AO57=0)+AND($G$58="",$H$58="",AO59=0)+AND($G$60="",$H$60="",AO61=0)+AND($G$62="",$H$62="",AO63=0)+AND($G$64="",$H$64="",AO65=0)+AND($G$66="",$H$66="",AO67=0)+AND($G$68="",$H$68="",AO69=0)+AND($G$70="",$H$70="",AO71=0)+AND($G$72="",$H$72="",AO73=0)+AND($G$74="",$H$74="",AO75=0)+AND($G$76="",$H$76="",AO77=0)+AND($G$78="",$H$78="",AO79=0))</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AP6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AP9=0)+AND($G$10="",$H$10="",AP11=0)+AND($G$12="",$H$12="",AP13=0)+AND($G$14="",$H$14="",AP15=0)+AND($G$16="",$H$16="",AP17=0)+AND($G$18="",$H$18="",AP19=0)+AND($G$20="",$H$20="",AP21=0)+AND($G$22="",$H$22="",AP23=0)+AND($G$24="",$H$24="",AP25=0)+AND($G$26="",$H$26="",AP27=0)+AND($G$28="",$H$28="",AP29=0)+AND($G$30="",$H$30="",AP31=0)+AND($G$32="",$H$32="",AP33=0)+AND($G$34="",$H$34="",AP35=0)+AND($G$36="",$H$36="",AP37=0)+AND($G$38="",$H$38="",AP39=0)+AND($G$40="",$H$40="",AP41=0)+AND($G$42="",$H$42="",AP43=0)+AND($G$44="",$H$44="",AP45=0)+AND($G$46="",$H$46="",AP47=0)+AND($G$48="",$H$48="",AP49=0)+AND($G$50="",$H$50="",AP51=0)+AND($G$52="",$H$52="",AP53=0)+AND($G$54="",$H$54="",AP55=0)+AND($G$56="",$H$56="",AP57=0)+AND($G$58="",$H$58="",AP59=0)+AND($G$60="",$H$60="",AP61=0)+AND($G$62="",$H$62="",AP63=0)+AND($G$64="",$H$64="",AP65=0)+AND($G$66="",$H$66="",AP67=0)+AND($G$68="",$H$68="",AP69=0)+AND($G$70="",$H$70="",AP71=0)+AND($G$72="",$H$72="",AP73=0)+AND($G$74="",$H$74="",AP75=0)+AND($G$76="",$H$76="",AP77=0)+AND($G$78="",$H$78="",AP79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AQ6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AQ9=0)+AND($G$10="",$H$10="",AQ11=0)+AND($G$12="",$H$12="",AQ13=0)+AND($G$14="",$H$14="",AQ15=0)+AND($G$16="",$H$16="",AQ17=0)+AND($G$18="",$H$18="",AQ19=0)+AND($G$20="",$H$20="",AQ21=0)+AND($G$22="",$H$22="",AQ23=0)+AND($G$24="",$H$24="",AQ25=0)+AND($G$26="",$H$26="",AQ27=0)+AND($G$28="",$H$28="",AQ29=0)+AND($G$30="",$H$30="",AQ31=0)+AND($G$32="",$H$32="",AQ33=0)+AND($G$34="",$H$34="",AQ35=0)+AND($G$36="",$H$36="",AQ37=0)+AND($G$38="",$H$38="",AQ39=0)+AND($G$40="",$H$40="",AQ41=0)+AND($G$42="",$H$42="",AQ43=0)+AND($G$44="",$H$44="",AQ45=0)+AND($G$46="",$H$46="",AQ47=0)+AND($G$48="",$H$48="",AQ49=0)+AND($G$50="",$H$50="",AQ51=0)+AND($G$52="",$H$52="",AQ53=0)+AND($G$54="",$H$54="",AQ55=0)+AND($G$56="",$H$56="",AQ57=0)+AND($G$58="",$H$58="",AQ59=0)+AND($G$60="",$H$60="",AQ61=0)+AND($G$62="",$H$62="",AQ63=0)+AND($G$64="",$H$64="",AQ65=0)+AND($G$66="",$H$66="",AQ67=0)+AND($G$68="",$H$68="",AQ69=0)+AND($G$70="",$H$70="",AQ71=0)+AND($G$72="",$H$72="",AQ73=0)+AND($G$74="",$H$74="",AQ75=0)+AND($G$76="",$H$76="",AQ77=0)+AND($G$78="",$H$78="",AQ79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AR6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AR9=0)+AND($G$10="",$H$10="",AR11=0)+AND($G$12="",$H$12="",AR13=0)+AND($G$14="",$H$14="",AR15=0)+AND($G$16="",$H$16="",AR17=0)+AND($G$18="",$H$18="",AR19=0)+AND($G$20="",$H$20="",AR21=0)+AND($G$22="",$H$22="",AR23=0)+AND($G$24="",$H$24="",AR25=0)+AND($G$26="",$H$26="",AR27=0)+AND($G$28="",$H$28="",AR29=0)+AND($G$30="",$H$30="",AR31=0)+AND($G$32="",$H$32="",AR33=0)+AND($G$34="",$H$34="",AR35=0)+AND($G$36="",$H$36="",AR37=0)+AND($G$38="",$H$38="",AR39=0)+AND($G$40="",$H$40="",AR41=0)+AND($G$42="",$H$42="",AR43=0)+AND($G$44="",$H$44="",AR45=0)+AND($G$46="",$H$46="",AR47=0)+AND($G$48="",$H$48="",AR49=0)+AND($G$50="",$H$50="",AR51=0)+AND($G$52="",$H$52="",AR53=0)+AND($G$54="",$H$54="",AR55=0)+AND($G$56="",$H$56="",AR57=0)+AND($G$58="",$H$58="",AR59=0)+AND($G$60="",$H$60="",AR61=0)+AND($G$62="",$H$62="",AR63=0)+AND($G$64="",$H$64="",AR65=0)+AND($G$66="",$H$66="",AR67=0)+AND($G$68="",$H$68="",AR69=0)+AND($G$70="",$H$70="",AR71=0)+AND($G$72="",$H$72="",AR73=0)+AND($G$74="",$H$74="",AR75=0)+AND($G$76="",$H$76="",AR77=0)+AND($G$78="",$H$78="",AR79=0))</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AS6" s="75">
-        <f>SUM(AND($G$8="",$H$8="",AS9=0)+AND($G$10="",$H$10="",AS11=0)+AND($G$12="",$H$12="",AS13=0)+AND($G$14="",$H$14="",AS15=0)+AND($G$16="",$H$16="",AS17=0)+AND($G$18="",$H$18="",AS19=0)+AND($G$20="",$H$20="",AS21=0)+AND($G$22="",$H$22="",AS23=0)+AND($G$24="",$H$24="",AS25=0)+AND($G$26="",$H$26="",AS27=0)+AND($G$28="",$H$28="",AS29=0)+AND($G$30="",$H$30="",AS31=0)+AND($G$32="",$H$32="",AS33=0)+AND($G$34="",$H$34="",AS35=0)+AND($G$36="",$H$36="",AS37=0)+AND($G$38="",$H$38="",AS39=0)+AND($G$40="",$H$40="",AS41=0)+AND($G$42="",$H$42="",AS43=0)+AND($G$44="",$H$44="",AS45=0)+AND($G$46="",$H$46="",AS47=0)+AND($G$48="",$H$48="",AS49=0)+AND($G$50="",$H$50="",AS51=0)+AND($G$52="",$H$52="",AS53=0)+AND($G$54="",$H$54="",AS55=0)+AND($G$56="",$H$56="",AS57=0)+AND($G$58="",$H$58="",AS59=0)+AND($G$60="",$H$60="",AS61=0)+AND($G$62="",$H$62="",AS63=0)+AND($G$64="",$H$64="",AS65=0)+AND($G$66="",$H$66="",AS67=0)+AND($G$68="",$H$68="",AS69=0)+AND($G$70="",$H$70="",AS71=0)+AND($G$72="",$H$72="",AS73=0)+AND($G$74="",$H$74="",AS75=0)+AND($G$76="",$H$76="",AS77=0)+AND($G$78="",$H$78="",AS79=0))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AT6" s="79">
-        <f>SUM(AND($G$8="",$H$8="",AT9=0)+AND($G$10="",$H$10="",AT11=0)+AND($G$12="",$H$12="",AT13=0)+AND($G$14="",$H$14="",AT15=0)+AND($G$16="",$H$16="",AT17=0)+AND($G$18="",$H$18="",AT19=0)+AND($G$20="",$H$20="",AT21=0)+AND($G$22="",$H$22="",AT23=0)+AND($G$24="",$H$24="",AT25=0)+AND($G$26="",$H$26="",AT27=0)+AND($G$28="",$H$28="",AT29=0)+AND($G$30="",$H$30="",AT31=0)+AND($G$32="",$H$32="",AT33=0)+AND($G$34="",$H$34="",AT35=0)+AND($G$36="",$H$36="",AT37=0)+AND($G$38="",$H$38="",AT39=0)+AND($G$40="",$H$40="",AT41=0)+AND($G$42="",$H$42="",AT43=0)+AND($G$44="",$H$44="",AT45=0)+AND($G$46="",$H$46="",AT47=0)+AND($G$48="",$H$48="",AT49=0)+AND($G$50="",$H$50="",AT51=0)+AND($G$52="",$H$52="",AT53=0)+AND($G$54="",$H$54="",AT55=0)+AND($G$56="",$H$56="",AT57=0)+AND($G$58="",$H$58="",AT59=0)+AND($G$60="",$H$60="",AT61=0)+AND($G$62="",$H$62="",AT63=0)+AND($G$64="",$H$64="",AT65=0)+AND($G$66="",$H$66="",AT67=0)+AND($G$68="",$H$68="",AT69=0)+AND($G$70="",$H$70="",AT71=0)+AND($G$72="",$H$72="",AT73=0)+AND($G$74="",$H$74="",AT75=0)+AND($G$76="",$H$76="",AT77=0)+AND($G$78="",$H$78="",AT79=0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:54" ht="14.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:54" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="61"/>
@@ -3471,155 +3435,155 @@
       <c r="H7" s="62"/>
       <c r="I7" s="63"/>
       <c r="J7" s="76">
-        <f>SUM(AND($G$80="",$H$80="",J81=0)+AND($G$82="",$H$82="",J83=0)+AND($G$84="",$H$84="",J85=0)+AND($G$86="",$H$86="",J87=0)+AND($G$88="",$H$88="",J89=0)+AND($G$90="",$H$90="",J91=0)+AND($G$92="",$H$92="",J93=0)+AND($G$94="",$H$94="",J95=0)+AND($G$96="",$H$96="",J97=0)+AND($G$98="",$H$98="",J99=0)+AND($G$100="",$H$100="",J101=0)+AND($G$102="",$H$102="",J103=0)+AND($G$104="",$H$104="",J105=0)+AND($G$106="",$H$106="",J107=0)+AND($G$108="",$H$108="",J109=0)+AND($G$110="",$H$110="",J111=0)+AND($G$112="",$H$112="",J113=0)+AND($G$114="",$H$114="",J115=0)+AND($G$116="",$H$116="",J117=0)+AND($G$118="",$H$118="",J119=0)+AND($G$120="",$H$120="",J121=0)+AND($G$122="",$H$122="",J123=0)+AND($G$124="",$H$124="",J125=0)+AND($G$126="",$H$126="",J127=0)+AND($G$128="",$H$128="",J129=0)+AND($G$130="",$H$130="",J131=0)+AND($G$132="",$H$132="",J133=0)+AND($G$134="",$H$134="",J135=0)+AND($G$136="",$H$136="",J137=0)+AND($G$138="",$H$138="",J139=0)+AND($G$140="",$H$140="",J141=0)+AND($G$142="",$H$142="",J143=0)+AND($G$144="",$H$144="",J145=0)+AND($G$146="",$H$146="",J147=0)+AND($G$148="",$H$148="",J149=0)+AND($G$150="",$H$150="",J151=0))</f>
+        <f t="shared" ref="J7:AT7" si="4">SUM(AND($G$80="",$H$80="",J81=0)+AND($G$82="",$H$82="",J83=0)+AND($G$84="",$H$84="",J85=0)+AND($G$86="",$H$86="",J87=0)+AND($G$88="",$H$88="",J89=0)+AND($G$90="",$H$90="",J91=0)+AND($G$92="",$H$92="",J93=0)+AND($G$94="",$H$94="",J95=0)+AND($G$96="",$H$96="",J97=0)+AND($G$98="",$H$98="",J99=0)+AND($G$100="",$H$100="",J101=0)+AND($G$102="",$H$102="",J103=0)+AND($G$104="",$H$104="",J105=0)+AND($G$106="",$H$106="",J107=0)+AND($G$108="",$H$108="",J109=0)+AND($G$110="",$H$110="",J111=0)+AND($G$112="",$H$112="",J113=0)+AND($G$114="",$H$114="",J115=0)+AND($G$116="",$H$116="",J117=0)+AND($G$118="",$H$118="",J119=0)+AND($G$120="",$H$120="",J121=0)+AND($G$122="",$H$122="",J123=0)+AND($G$124="",$H$124="",J125=0)+AND($G$126="",$H$126="",J127=0)+AND($G$128="",$H$128="",J129=0)+AND($G$130="",$H$130="",J131=0)+AND($G$132="",$H$132="",J133=0)+AND($G$134="",$H$134="",J135=0)+AND($G$136="",$H$136="",J137=0)+AND($G$138="",$H$138="",J139=0)+AND($G$140="",$H$140="",J141=0)+AND($G$142="",$H$142="",J143=0)+AND($G$144="",$H$144="",J145=0)+AND($G$146="",$H$146="",J147=0)+AND($G$148="",$H$148="",J149=0)+AND($G$150="",$H$150="",J151=0))</f>
         <v>2</v>
       </c>
       <c r="K7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",K81=0)+AND($G$82="",$H$82="",K83=0)+AND($G$84="",$H$84="",K85=0)+AND($G$86="",$H$86="",K87=0)+AND($G$88="",$H$88="",K89=0)+AND($G$90="",$H$90="",K91=0)+AND($G$92="",$H$92="",K93=0)+AND($G$94="",$H$94="",K95=0)+AND($G$96="",$H$96="",K97=0)+AND($G$98="",$H$98="",K99=0)+AND($G$100="",$H$100="",K101=0)+AND($G$102="",$H$102="",K103=0)+AND($G$104="",$H$104="",K105=0)+AND($G$106="",$H$106="",K107=0)+AND($G$108="",$H$108="",K109=0)+AND($G$110="",$H$110="",K111=0)+AND($G$112="",$H$112="",K113=0)+AND($G$114="",$H$114="",K115=0)+AND($G$116="",$H$116="",K117=0)+AND($G$118="",$H$118="",K119=0)+AND($G$120="",$H$120="",K121=0)+AND($G$122="",$H$122="",K123=0)+AND($G$124="",$H$124="",K125=0)+AND($G$126="",$H$126="",K127=0)+AND($G$128="",$H$128="",K129=0)+AND($G$130="",$H$130="",K131=0)+AND($G$132="",$H$132="",K133=0)+AND($G$134="",$H$134="",K135=0)+AND($G$136="",$H$136="",K137=0)+AND($G$138="",$H$138="",K139=0)+AND($G$140="",$H$140="",K141=0)+AND($G$142="",$H$142="",K143=0)+AND($G$144="",$H$144="",K145=0)+AND($G$146="",$H$146="",K147=0)+AND($G$148="",$H$148="",K149=0)+AND($G$150="",$H$150="",K151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",L81=0)+AND($G$82="",$H$82="",L83=0)+AND($G$84="",$H$84="",L85=0)+AND($G$86="",$H$86="",L87=0)+AND($G$88="",$H$88="",L89=0)+AND($G$90="",$H$90="",L91=0)+AND($G$92="",$H$92="",L93=0)+AND($G$94="",$H$94="",L95=0)+AND($G$96="",$H$96="",L97=0)+AND($G$98="",$H$98="",L99=0)+AND($G$100="",$H$100="",L101=0)+AND($G$102="",$H$102="",L103=0)+AND($G$104="",$H$104="",L105=0)+AND($G$106="",$H$106="",L107=0)+AND($G$108="",$H$108="",L109=0)+AND($G$110="",$H$110="",L111=0)+AND($G$112="",$H$112="",L113=0)+AND($G$114="",$H$114="",L115=0)+AND($G$116="",$H$116="",L117=0)+AND($G$118="",$H$118="",L119=0)+AND($G$120="",$H$120="",L121=0)+AND($G$122="",$H$122="",L123=0)+AND($G$124="",$H$124="",L125=0)+AND($G$126="",$H$126="",L127=0)+AND($G$128="",$H$128="",L129=0)+AND($G$130="",$H$130="",L131=0)+AND($G$132="",$H$132="",L133=0)+AND($G$134="",$H$134="",L135=0)+AND($G$136="",$H$136="",L137=0)+AND($G$138="",$H$138="",L139=0)+AND($G$140="",$H$140="",L141=0)+AND($G$142="",$H$142="",L143=0)+AND($G$144="",$H$144="",L145=0)+AND($G$146="",$H$146="",L147=0)+AND($G$148="",$H$148="",L149=0)+AND($G$150="",$H$150="",L151=0))</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="M7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",M81=0)+AND($G$82="",$H$82="",M83=0)+AND($G$84="",$H$84="",M85=0)+AND($G$86="",$H$86="",M87=0)+AND($G$88="",$H$88="",M89=0)+AND($G$90="",$H$90="",M91=0)+AND($G$92="",$H$92="",M93=0)+AND($G$94="",$H$94="",M95=0)+AND($G$96="",$H$96="",M97=0)+AND($G$98="",$H$98="",M99=0)+AND($G$100="",$H$100="",M101=0)+AND($G$102="",$H$102="",M103=0)+AND($G$104="",$H$104="",M105=0)+AND($G$106="",$H$106="",M107=0)+AND($G$108="",$H$108="",M109=0)+AND($G$110="",$H$110="",M111=0)+AND($G$112="",$H$112="",M113=0)+AND($G$114="",$H$114="",M115=0)+AND($G$116="",$H$116="",M117=0)+AND($G$118="",$H$118="",M119=0)+AND($G$120="",$H$120="",M121=0)+AND($G$122="",$H$122="",M123=0)+AND($G$124="",$H$124="",M125=0)+AND($G$126="",$H$126="",M127=0)+AND($G$128="",$H$128="",M129=0)+AND($G$130="",$H$130="",M131=0)+AND($G$132="",$H$132="",M133=0)+AND($G$134="",$H$134="",M135=0)+AND($G$136="",$H$136="",M137=0)+AND($G$138="",$H$138="",M139=0)+AND($G$140="",$H$140="",M141=0)+AND($G$142="",$H$142="",M143=0)+AND($G$144="",$H$144="",M145=0)+AND($G$146="",$H$146="",M147=0)+AND($G$148="",$H$148="",M149=0)+AND($G$150="",$H$150="",M151=0))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="N7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",N81=0)+AND($G$82="",$H$82="",N83=0)+AND($G$84="",$H$84="",N85=0)+AND($G$86="",$H$86="",N87=0)+AND($G$88="",$H$88="",N89=0)+AND($G$90="",$H$90="",N91=0)+AND($G$92="",$H$92="",N93=0)+AND($G$94="",$H$94="",N95=0)+AND($G$96="",$H$96="",N97=0)+AND($G$98="",$H$98="",N99=0)+AND($G$100="",$H$100="",N101=0)+AND($G$102="",$H$102="",N103=0)+AND($G$104="",$H$104="",N105=0)+AND($G$106="",$H$106="",N107=0)+AND($G$108="",$H$108="",N109=0)+AND($G$110="",$H$110="",N111=0)+AND($G$112="",$H$112="",N113=0)+AND($G$114="",$H$114="",N115=0)+AND($G$116="",$H$116="",N117=0)+AND($G$118="",$H$118="",N119=0)+AND($G$120="",$H$120="",N121=0)+AND($G$122="",$H$122="",N123=0)+AND($G$124="",$H$124="",N125=0)+AND($G$126="",$H$126="",N127=0)+AND($G$128="",$H$128="",N129=0)+AND($G$130="",$H$130="",N131=0)+AND($G$132="",$H$132="",N133=0)+AND($G$134="",$H$134="",N135=0)+AND($G$136="",$H$136="",N137=0)+AND($G$138="",$H$138="",N139=0)+AND($G$140="",$H$140="",N141=0)+AND($G$142="",$H$142="",N143=0)+AND($G$144="",$H$144="",N145=0)+AND($G$146="",$H$146="",N147=0)+AND($G$148="",$H$148="",N149=0)+AND($G$150="",$H$150="",N151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",O81=0)+AND($G$82="",$H$82="",O83=0)+AND($G$84="",$H$84="",O85=0)+AND($G$86="",$H$86="",O87=0)+AND($G$88="",$H$88="",O89=0)+AND($G$90="",$H$90="",O91=0)+AND($G$92="",$H$92="",O93=0)+AND($G$94="",$H$94="",O95=0)+AND($G$96="",$H$96="",O97=0)+AND($G$98="",$H$98="",O99=0)+AND($G$100="",$H$100="",O101=0)+AND($G$102="",$H$102="",O103=0)+AND($G$104="",$H$104="",O105=0)+AND($G$106="",$H$106="",O107=0)+AND($G$108="",$H$108="",O109=0)+AND($G$110="",$H$110="",O111=0)+AND($G$112="",$H$112="",O113=0)+AND($G$114="",$H$114="",O115=0)+AND($G$116="",$H$116="",O117=0)+AND($G$118="",$H$118="",O119=0)+AND($G$120="",$H$120="",O121=0)+AND($G$122="",$H$122="",O123=0)+AND($G$124="",$H$124="",O125=0)+AND($G$126="",$H$126="",O127=0)+AND($G$128="",$H$128="",O129=0)+AND($G$130="",$H$130="",O131=0)+AND($G$132="",$H$132="",O133=0)+AND($G$134="",$H$134="",O135=0)+AND($G$136="",$H$136="",O137=0)+AND($G$138="",$H$138="",O139=0)+AND($G$140="",$H$140="",O141=0)+AND($G$142="",$H$142="",O143=0)+AND($G$144="",$H$144="",O145=0)+AND($G$146="",$H$146="",O147=0)+AND($G$148="",$H$148="",O149=0)+AND($G$150="",$H$150="",O151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",P81=0)+AND($G$82="",$H$82="",P83=0)+AND($G$84="",$H$84="",P85=0)+AND($G$86="",$H$86="",P87=0)+AND($G$88="",$H$88="",P89=0)+AND($G$90="",$H$90="",P91=0)+AND($G$92="",$H$92="",P93=0)+AND($G$94="",$H$94="",P95=0)+AND($G$96="",$H$96="",P97=0)+AND($G$98="",$H$98="",P99=0)+AND($G$100="",$H$100="",P101=0)+AND($G$102="",$H$102="",P103=0)+AND($G$104="",$H$104="",P105=0)+AND($G$106="",$H$106="",P107=0)+AND($G$108="",$H$108="",P109=0)+AND($G$110="",$H$110="",P111=0)+AND($G$112="",$H$112="",P113=0)+AND($G$114="",$H$114="",P115=0)+AND($G$116="",$H$116="",P117=0)+AND($G$118="",$H$118="",P119=0)+AND($G$120="",$H$120="",P121=0)+AND($G$122="",$H$122="",P123=0)+AND($G$124="",$H$124="",P125=0)+AND($G$126="",$H$126="",P127=0)+AND($G$128="",$H$128="",P129=0)+AND($G$130="",$H$130="",P131=0)+AND($G$132="",$H$132="",P133=0)+AND($G$134="",$H$134="",P135=0)+AND($G$136="",$H$136="",P137=0)+AND($G$138="",$H$138="",P139=0)+AND($G$140="",$H$140="",P141=0)+AND($G$142="",$H$142="",P143=0)+AND($G$144="",$H$144="",P145=0)+AND($G$146="",$H$146="",P147=0)+AND($G$148="",$H$148="",P149=0)+AND($G$150="",$H$150="",P151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",Q81=0)+AND($G$82="",$H$82="",Q83=0)+AND($G$84="",$H$84="",Q85=0)+AND($G$86="",$H$86="",Q87=0)+AND($G$88="",$H$88="",Q89=0)+AND($G$90="",$H$90="",Q91=0)+AND($G$92="",$H$92="",Q93=0)+AND($G$94="",$H$94="",Q95=0)+AND($G$96="",$H$96="",Q97=0)+AND($G$98="",$H$98="",Q99=0)+AND($G$100="",$H$100="",Q101=0)+AND($G$102="",$H$102="",Q103=0)+AND($G$104="",$H$104="",Q105=0)+AND($G$106="",$H$106="",Q107=0)+AND($G$108="",$H$108="",Q109=0)+AND($G$110="",$H$110="",Q111=0)+AND($G$112="",$H$112="",Q113=0)+AND($G$114="",$H$114="",Q115=0)+AND($G$116="",$H$116="",Q117=0)+AND($G$118="",$H$118="",Q119=0)+AND($G$120="",$H$120="",Q121=0)+AND($G$122="",$H$122="",Q123=0)+AND($G$124="",$H$124="",Q125=0)+AND($G$126="",$H$126="",Q127=0)+AND($G$128="",$H$128="",Q129=0)+AND($G$130="",$H$130="",Q131=0)+AND($G$132="",$H$132="",Q133=0)+AND($G$134="",$H$134="",Q135=0)+AND($G$136="",$H$136="",Q137=0)+AND($G$138="",$H$138="",Q139=0)+AND($G$140="",$H$140="",Q141=0)+AND($G$142="",$H$142="",Q143=0)+AND($G$144="",$H$144="",Q145=0)+AND($G$146="",$H$146="",Q147=0)+AND($G$148="",$H$148="",Q149=0)+AND($G$150="",$H$150="",Q151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",R81=0)+AND($G$82="",$H$82="",R83=0)+AND($G$84="",$H$84="",R85=0)+AND($G$86="",$H$86="",R87=0)+AND($G$88="",$H$88="",R89=0)+AND($G$90="",$H$90="",R91=0)+AND($G$92="",$H$92="",R93=0)+AND($G$94="",$H$94="",R95=0)+AND($G$96="",$H$96="",R97=0)+AND($G$98="",$H$98="",R99=0)+AND($G$100="",$H$100="",R101=0)+AND($G$102="",$H$102="",R103=0)+AND($G$104="",$H$104="",R105=0)+AND($G$106="",$H$106="",R107=0)+AND($G$108="",$H$108="",R109=0)+AND($G$110="",$H$110="",R111=0)+AND($G$112="",$H$112="",R113=0)+AND($G$114="",$H$114="",R115=0)+AND($G$116="",$H$116="",R117=0)+AND($G$118="",$H$118="",R119=0)+AND($G$120="",$H$120="",R121=0)+AND($G$122="",$H$122="",R123=0)+AND($G$124="",$H$124="",R125=0)+AND($G$126="",$H$126="",R127=0)+AND($G$128="",$H$128="",R129=0)+AND($G$130="",$H$130="",R131=0)+AND($G$132="",$H$132="",R133=0)+AND($G$134="",$H$134="",R135=0)+AND($G$136="",$H$136="",R137=0)+AND($G$138="",$H$138="",R139=0)+AND($G$140="",$H$140="",R141=0)+AND($G$142="",$H$142="",R143=0)+AND($G$144="",$H$144="",R145=0)+AND($G$146="",$H$146="",R147=0)+AND($G$148="",$H$148="",R149=0)+AND($G$150="",$H$150="",R151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",S81=0)+AND($G$82="",$H$82="",S83=0)+AND($G$84="",$H$84="",S85=0)+AND($G$86="",$H$86="",S87=0)+AND($G$88="",$H$88="",S89=0)+AND($G$90="",$H$90="",S91=0)+AND($G$92="",$H$92="",S93=0)+AND($G$94="",$H$94="",S95=0)+AND($G$96="",$H$96="",S97=0)+AND($G$98="",$H$98="",S99=0)+AND($G$100="",$H$100="",S101=0)+AND($G$102="",$H$102="",S103=0)+AND($G$104="",$H$104="",S105=0)+AND($G$106="",$H$106="",S107=0)+AND($G$108="",$H$108="",S109=0)+AND($G$110="",$H$110="",S111=0)+AND($G$112="",$H$112="",S113=0)+AND($G$114="",$H$114="",S115=0)+AND($G$116="",$H$116="",S117=0)+AND($G$118="",$H$118="",S119=0)+AND($G$120="",$H$120="",S121=0)+AND($G$122="",$H$122="",S123=0)+AND($G$124="",$H$124="",S125=0)+AND($G$126="",$H$126="",S127=0)+AND($G$128="",$H$128="",S129=0)+AND($G$130="",$H$130="",S131=0)+AND($G$132="",$H$132="",S133=0)+AND($G$134="",$H$134="",S135=0)+AND($G$136="",$H$136="",S137=0)+AND($G$138="",$H$138="",S139=0)+AND($G$140="",$H$140="",S141=0)+AND($G$142="",$H$142="",S143=0)+AND($G$144="",$H$144="",S145=0)+AND($G$146="",$H$146="",S147=0)+AND($G$148="",$H$148="",S149=0)+AND($G$150="",$H$150="",S151=0))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="T7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",T81=0)+AND($G$82="",$H$82="",T83=0)+AND($G$84="",$H$84="",T85=0)+AND($G$86="",$H$86="",T87=0)+AND($G$88="",$H$88="",T89=0)+AND($G$90="",$H$90="",T91=0)+AND($G$92="",$H$92="",T93=0)+AND($G$94="",$H$94="",T95=0)+AND($G$96="",$H$96="",T97=0)+AND($G$98="",$H$98="",T99=0)+AND($G$100="",$H$100="",T101=0)+AND($G$102="",$H$102="",T103=0)+AND($G$104="",$H$104="",T105=0)+AND($G$106="",$H$106="",T107=0)+AND($G$108="",$H$108="",T109=0)+AND($G$110="",$H$110="",T111=0)+AND($G$112="",$H$112="",T113=0)+AND($G$114="",$H$114="",T115=0)+AND($G$116="",$H$116="",T117=0)+AND($G$118="",$H$118="",T119=0)+AND($G$120="",$H$120="",T121=0)+AND($G$122="",$H$122="",T123=0)+AND($G$124="",$H$124="",T125=0)+AND($G$126="",$H$126="",T127=0)+AND($G$128="",$H$128="",T129=0)+AND($G$130="",$H$130="",T131=0)+AND($G$132="",$H$132="",T133=0)+AND($G$134="",$H$134="",T135=0)+AND($G$136="",$H$136="",T137=0)+AND($G$138="",$H$138="",T139=0)+AND($G$140="",$H$140="",T141=0)+AND($G$142="",$H$142="",T143=0)+AND($G$144="",$H$144="",T145=0)+AND($G$146="",$H$146="",T147=0)+AND($G$148="",$H$148="",T149=0)+AND($G$150="",$H$150="",T151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="U7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",U81=0)+AND($G$82="",$H$82="",U83=0)+AND($G$84="",$H$84="",U85=0)+AND($G$86="",$H$86="",U87=0)+AND($G$88="",$H$88="",U89=0)+AND($G$90="",$H$90="",U91=0)+AND($G$92="",$H$92="",U93=0)+AND($G$94="",$H$94="",U95=0)+AND($G$96="",$H$96="",U97=0)+AND($G$98="",$H$98="",U99=0)+AND($G$100="",$H$100="",U101=0)+AND($G$102="",$H$102="",U103=0)+AND($G$104="",$H$104="",U105=0)+AND($G$106="",$H$106="",U107=0)+AND($G$108="",$H$108="",U109=0)+AND($G$110="",$H$110="",U111=0)+AND($G$112="",$H$112="",U113=0)+AND($G$114="",$H$114="",U115=0)+AND($G$116="",$H$116="",U117=0)+AND($G$118="",$H$118="",U119=0)+AND($G$120="",$H$120="",U121=0)+AND($G$122="",$H$122="",U123=0)+AND($G$124="",$H$124="",U125=0)+AND($G$126="",$H$126="",U127=0)+AND($G$128="",$H$128="",U129=0)+AND($G$130="",$H$130="",U131=0)+AND($G$132="",$H$132="",U133=0)+AND($G$134="",$H$134="",U135=0)+AND($G$136="",$H$136="",U137=0)+AND($G$138="",$H$138="",U139=0)+AND($G$140="",$H$140="",U141=0)+AND($G$142="",$H$142="",U143=0)+AND($G$144="",$H$144="",U145=0)+AND($G$146="",$H$146="",U147=0)+AND($G$148="",$H$148="",U149=0)+AND($G$150="",$H$150="",U151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="V7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",V81=0)+AND($G$82="",$H$82="",V83=0)+AND($G$84="",$H$84="",V85=0)+AND($G$86="",$H$86="",V87=0)+AND($G$88="",$H$88="",V89=0)+AND($G$90="",$H$90="",V91=0)+AND($G$92="",$H$92="",V93=0)+AND($G$94="",$H$94="",V95=0)+AND($G$96="",$H$96="",V97=0)+AND($G$98="",$H$98="",V99=0)+AND($G$100="",$H$100="",V101=0)+AND($G$102="",$H$102="",V103=0)+AND($G$104="",$H$104="",V105=0)+AND($G$106="",$H$106="",V107=0)+AND($G$108="",$H$108="",V109=0)+AND($G$110="",$H$110="",V111=0)+AND($G$112="",$H$112="",V113=0)+AND($G$114="",$H$114="",V115=0)+AND($G$116="",$H$116="",V117=0)+AND($G$118="",$H$118="",V119=0)+AND($G$120="",$H$120="",V121=0)+AND($G$122="",$H$122="",V123=0)+AND($G$124="",$H$124="",V125=0)+AND($G$126="",$H$126="",V127=0)+AND($G$128="",$H$128="",V129=0)+AND($G$130="",$H$130="",V131=0)+AND($G$132="",$H$132="",V133=0)+AND($G$134="",$H$134="",V135=0)+AND($G$136="",$H$136="",V137=0)+AND($G$138="",$H$138="",V139=0)+AND($G$140="",$H$140="",V141=0)+AND($G$142="",$H$142="",V143=0)+AND($G$144="",$H$144="",V145=0)+AND($G$146="",$H$146="",V147=0)+AND($G$148="",$H$148="",V149=0)+AND($G$150="",$H$150="",V151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",W81=0)+AND($G$82="",$H$82="",W83=0)+AND($G$84="",$H$84="",W85=0)+AND($G$86="",$H$86="",W87=0)+AND($G$88="",$H$88="",W89=0)+AND($G$90="",$H$90="",W91=0)+AND($G$92="",$H$92="",W93=0)+AND($G$94="",$H$94="",W95=0)+AND($G$96="",$H$96="",W97=0)+AND($G$98="",$H$98="",W99=0)+AND($G$100="",$H$100="",W101=0)+AND($G$102="",$H$102="",W103=0)+AND($G$104="",$H$104="",W105=0)+AND($G$106="",$H$106="",W107=0)+AND($G$108="",$H$108="",W109=0)+AND($G$110="",$H$110="",W111=0)+AND($G$112="",$H$112="",W113=0)+AND($G$114="",$H$114="",W115=0)+AND($G$116="",$H$116="",W117=0)+AND($G$118="",$H$118="",W119=0)+AND($G$120="",$H$120="",W121=0)+AND($G$122="",$H$122="",W123=0)+AND($G$124="",$H$124="",W125=0)+AND($G$126="",$H$126="",W127=0)+AND($G$128="",$H$128="",W129=0)+AND($G$130="",$H$130="",W131=0)+AND($G$132="",$H$132="",W133=0)+AND($G$134="",$H$134="",W135=0)+AND($G$136="",$H$136="",W137=0)+AND($G$138="",$H$138="",W139=0)+AND($G$140="",$H$140="",W141=0)+AND($G$142="",$H$142="",W143=0)+AND($G$144="",$H$144="",W145=0)+AND($G$146="",$H$146="",W147=0)+AND($G$148="",$H$148="",W149=0)+AND($G$150="",$H$150="",W151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",X81=0)+AND($G$82="",$H$82="",X83=0)+AND($G$84="",$H$84="",X85=0)+AND($G$86="",$H$86="",X87=0)+AND($G$88="",$H$88="",X89=0)+AND($G$90="",$H$90="",X91=0)+AND($G$92="",$H$92="",X93=0)+AND($G$94="",$H$94="",X95=0)+AND($G$96="",$H$96="",X97=0)+AND($G$98="",$H$98="",X99=0)+AND($G$100="",$H$100="",X101=0)+AND($G$102="",$H$102="",X103=0)+AND($G$104="",$H$104="",X105=0)+AND($G$106="",$H$106="",X107=0)+AND($G$108="",$H$108="",X109=0)+AND($G$110="",$H$110="",X111=0)+AND($G$112="",$H$112="",X113=0)+AND($G$114="",$H$114="",X115=0)+AND($G$116="",$H$116="",X117=0)+AND($G$118="",$H$118="",X119=0)+AND($G$120="",$H$120="",X121=0)+AND($G$122="",$H$122="",X123=0)+AND($G$124="",$H$124="",X125=0)+AND($G$126="",$H$126="",X127=0)+AND($G$128="",$H$128="",X129=0)+AND($G$130="",$H$130="",X131=0)+AND($G$132="",$H$132="",X133=0)+AND($G$134="",$H$134="",X135=0)+AND($G$136="",$H$136="",X137=0)+AND($G$138="",$H$138="",X139=0)+AND($G$140="",$H$140="",X141=0)+AND($G$142="",$H$142="",X143=0)+AND($G$144="",$H$144="",X145=0)+AND($G$146="",$H$146="",X147=0)+AND($G$148="",$H$148="",X149=0)+AND($G$150="",$H$150="",X151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Y7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",Y81=0)+AND($G$82="",$H$82="",Y83=0)+AND($G$84="",$H$84="",Y85=0)+AND($G$86="",$H$86="",Y87=0)+AND($G$88="",$H$88="",Y89=0)+AND($G$90="",$H$90="",Y91=0)+AND($G$92="",$H$92="",Y93=0)+AND($G$94="",$H$94="",Y95=0)+AND($G$96="",$H$96="",Y97=0)+AND($G$98="",$H$98="",Y99=0)+AND($G$100="",$H$100="",Y101=0)+AND($G$102="",$H$102="",Y103=0)+AND($G$104="",$H$104="",Y105=0)+AND($G$106="",$H$106="",Y107=0)+AND($G$108="",$H$108="",Y109=0)+AND($G$110="",$H$110="",Y111=0)+AND($G$112="",$H$112="",Y113=0)+AND($G$114="",$H$114="",Y115=0)+AND($G$116="",$H$116="",Y117=0)+AND($G$118="",$H$118="",Y119=0)+AND($G$120="",$H$120="",Y121=0)+AND($G$122="",$H$122="",Y123=0)+AND($G$124="",$H$124="",Y125=0)+AND($G$126="",$H$126="",Y127=0)+AND($G$128="",$H$128="",Y129=0)+AND($G$130="",$H$130="",Y131=0)+AND($G$132="",$H$132="",Y133=0)+AND($G$134="",$H$134="",Y135=0)+AND($G$136="",$H$136="",Y137=0)+AND($G$138="",$H$138="",Y139=0)+AND($G$140="",$H$140="",Y141=0)+AND($G$142="",$H$142="",Y143=0)+AND($G$144="",$H$144="",Y145=0)+AND($G$146="",$H$146="",Y147=0)+AND($G$148="",$H$148="",Y149=0)+AND($G$150="",$H$150="",Y151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Z7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",Z81=0)+AND($G$82="",$H$82="",Z83=0)+AND($G$84="",$H$84="",Z85=0)+AND($G$86="",$H$86="",Z87=0)+AND($G$88="",$H$88="",Z89=0)+AND($G$90="",$H$90="",Z91=0)+AND($G$92="",$H$92="",Z93=0)+AND($G$94="",$H$94="",Z95=0)+AND($G$96="",$H$96="",Z97=0)+AND($G$98="",$H$98="",Z99=0)+AND($G$100="",$H$100="",Z101=0)+AND($G$102="",$H$102="",Z103=0)+AND($G$104="",$H$104="",Z105=0)+AND($G$106="",$H$106="",Z107=0)+AND($G$108="",$H$108="",Z109=0)+AND($G$110="",$H$110="",Z111=0)+AND($G$112="",$H$112="",Z113=0)+AND($G$114="",$H$114="",Z115=0)+AND($G$116="",$H$116="",Z117=0)+AND($G$118="",$H$118="",Z119=0)+AND($G$120="",$H$120="",Z121=0)+AND($G$122="",$H$122="",Z123=0)+AND($G$124="",$H$124="",Z125=0)+AND($G$126="",$H$126="",Z127=0)+AND($G$128="",$H$128="",Z129=0)+AND($G$130="",$H$130="",Z131=0)+AND($G$132="",$H$132="",Z133=0)+AND($G$134="",$H$134="",Z135=0)+AND($G$136="",$H$136="",Z137=0)+AND($G$138="",$H$138="",Z139=0)+AND($G$140="",$H$140="",Z141=0)+AND($G$142="",$H$142="",Z143=0)+AND($G$144="",$H$144="",Z145=0)+AND($G$146="",$H$146="",Z147=0)+AND($G$148="",$H$148="",Z149=0)+AND($G$150="",$H$150="",Z151=0))</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AA7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AA81=0)+AND($G$82="",$H$82="",AA83=0)+AND($G$84="",$H$84="",AA85=0)+AND($G$86="",$H$86="",AA87=0)+AND($G$88="",$H$88="",AA89=0)+AND($G$90="",$H$90="",AA91=0)+AND($G$92="",$H$92="",AA93=0)+AND($G$94="",$H$94="",AA95=0)+AND($G$96="",$H$96="",AA97=0)+AND($G$98="",$H$98="",AA99=0)+AND($G$100="",$H$100="",AA101=0)+AND($G$102="",$H$102="",AA103=0)+AND($G$104="",$H$104="",AA105=0)+AND($G$106="",$H$106="",AA107=0)+AND($G$108="",$H$108="",AA109=0)+AND($G$110="",$H$110="",AA111=0)+AND($G$112="",$H$112="",AA113=0)+AND($G$114="",$H$114="",AA115=0)+AND($G$116="",$H$116="",AA117=0)+AND($G$118="",$H$118="",AA119=0)+AND($G$120="",$H$120="",AA121=0)+AND($G$122="",$H$122="",AA123=0)+AND($G$124="",$H$124="",AA125=0)+AND($G$126="",$H$126="",AA127=0)+AND($G$128="",$H$128="",AA129=0)+AND($G$130="",$H$130="",AA131=0)+AND($G$132="",$H$132="",AA133=0)+AND($G$134="",$H$134="",AA135=0)+AND($G$136="",$H$136="",AA137=0)+AND($G$138="",$H$138="",AA139=0)+AND($G$140="",$H$140="",AA141=0)+AND($G$142="",$H$142="",AA143=0)+AND($G$144="",$H$144="",AA145=0)+AND($G$146="",$H$146="",AA147=0)+AND($G$148="",$H$148="",AA149=0)+AND($G$150="",$H$150="",AA151=0))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AB7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AB81=0)+AND($G$82="",$H$82="",AB83=0)+AND($G$84="",$H$84="",AB85=0)+AND($G$86="",$H$86="",AB87=0)+AND($G$88="",$H$88="",AB89=0)+AND($G$90="",$H$90="",AB91=0)+AND($G$92="",$H$92="",AB93=0)+AND($G$94="",$H$94="",AB95=0)+AND($G$96="",$H$96="",AB97=0)+AND($G$98="",$H$98="",AB99=0)+AND($G$100="",$H$100="",AB101=0)+AND($G$102="",$H$102="",AB103=0)+AND($G$104="",$H$104="",AB105=0)+AND($G$106="",$H$106="",AB107=0)+AND($G$108="",$H$108="",AB109=0)+AND($G$110="",$H$110="",AB111=0)+AND($G$112="",$H$112="",AB113=0)+AND($G$114="",$H$114="",AB115=0)+AND($G$116="",$H$116="",AB117=0)+AND($G$118="",$H$118="",AB119=0)+AND($G$120="",$H$120="",AB121=0)+AND($G$122="",$H$122="",AB123=0)+AND($G$124="",$H$124="",AB125=0)+AND($G$126="",$H$126="",AB127=0)+AND($G$128="",$H$128="",AB129=0)+AND($G$130="",$H$130="",AB131=0)+AND($G$132="",$H$132="",AB133=0)+AND($G$134="",$H$134="",AB135=0)+AND($G$136="",$H$136="",AB137=0)+AND($G$138="",$H$138="",AB139=0)+AND($G$140="",$H$140="",AB141=0)+AND($G$142="",$H$142="",AB143=0)+AND($G$144="",$H$144="",AB145=0)+AND($G$146="",$H$146="",AB147=0)+AND($G$148="",$H$148="",AB149=0)+AND($G$150="",$H$150="",AB151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AC7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AC81=0)+AND($G$82="",$H$82="",AC83=0)+AND($G$84="",$H$84="",AC85=0)+AND($G$86="",$H$86="",AC87=0)+AND($G$88="",$H$88="",AC89=0)+AND($G$90="",$H$90="",AC91=0)+AND($G$92="",$H$92="",AC93=0)+AND($G$94="",$H$94="",AC95=0)+AND($G$96="",$H$96="",AC97=0)+AND($G$98="",$H$98="",AC99=0)+AND($G$100="",$H$100="",AC101=0)+AND($G$102="",$H$102="",AC103=0)+AND($G$104="",$H$104="",AC105=0)+AND($G$106="",$H$106="",AC107=0)+AND($G$108="",$H$108="",AC109=0)+AND($G$110="",$H$110="",AC111=0)+AND($G$112="",$H$112="",AC113=0)+AND($G$114="",$H$114="",AC115=0)+AND($G$116="",$H$116="",AC117=0)+AND($G$118="",$H$118="",AC119=0)+AND($G$120="",$H$120="",AC121=0)+AND($G$122="",$H$122="",AC123=0)+AND($G$124="",$H$124="",AC125=0)+AND($G$126="",$H$126="",AC127=0)+AND($G$128="",$H$128="",AC129=0)+AND($G$130="",$H$130="",AC131=0)+AND($G$132="",$H$132="",AC133=0)+AND($G$134="",$H$134="",AC135=0)+AND($G$136="",$H$136="",AC137=0)+AND($G$138="",$H$138="",AC139=0)+AND($G$140="",$H$140="",AC141=0)+AND($G$142="",$H$142="",AC143=0)+AND($G$144="",$H$144="",AC145=0)+AND($G$146="",$H$146="",AC147=0)+AND($G$148="",$H$148="",AC149=0)+AND($G$150="",$H$150="",AC151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AD7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AD81=0)+AND($G$82="",$H$82="",AD83=0)+AND($G$84="",$H$84="",AD85=0)+AND($G$86="",$H$86="",AD87=0)+AND($G$88="",$H$88="",AD89=0)+AND($G$90="",$H$90="",AD91=0)+AND($G$92="",$H$92="",AD93=0)+AND($G$94="",$H$94="",AD95=0)+AND($G$96="",$H$96="",AD97=0)+AND($G$98="",$H$98="",AD99=0)+AND($G$100="",$H$100="",AD101=0)+AND($G$102="",$H$102="",AD103=0)+AND($G$104="",$H$104="",AD105=0)+AND($G$106="",$H$106="",AD107=0)+AND($G$108="",$H$108="",AD109=0)+AND($G$110="",$H$110="",AD111=0)+AND($G$112="",$H$112="",AD113=0)+AND($G$114="",$H$114="",AD115=0)+AND($G$116="",$H$116="",AD117=0)+AND($G$118="",$H$118="",AD119=0)+AND($G$120="",$H$120="",AD121=0)+AND($G$122="",$H$122="",AD123=0)+AND($G$124="",$H$124="",AD125=0)+AND($G$126="",$H$126="",AD127=0)+AND($G$128="",$H$128="",AD129=0)+AND($G$130="",$H$130="",AD131=0)+AND($G$132="",$H$132="",AD133=0)+AND($G$134="",$H$134="",AD135=0)+AND($G$136="",$H$136="",AD137=0)+AND($G$138="",$H$138="",AD139=0)+AND($G$140="",$H$140="",AD141=0)+AND($G$142="",$H$142="",AD143=0)+AND($G$144="",$H$144="",AD145=0)+AND($G$146="",$H$146="",AD147=0)+AND($G$148="",$H$148="",AD149=0)+AND($G$150="",$H$150="",AD151=0))</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AE7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AE81=0)+AND($G$82="",$H$82="",AE83=0)+AND($G$84="",$H$84="",AE85=0)+AND($G$86="",$H$86="",AE87=0)+AND($G$88="",$H$88="",AE89=0)+AND($G$90="",$H$90="",AE91=0)+AND($G$92="",$H$92="",AE93=0)+AND($G$94="",$H$94="",AE95=0)+AND($G$96="",$H$96="",AE97=0)+AND($G$98="",$H$98="",AE99=0)+AND($G$100="",$H$100="",AE101=0)+AND($G$102="",$H$102="",AE103=0)+AND($G$104="",$H$104="",AE105=0)+AND($G$106="",$H$106="",AE107=0)+AND($G$108="",$H$108="",AE109=0)+AND($G$110="",$H$110="",AE111=0)+AND($G$112="",$H$112="",AE113=0)+AND($G$114="",$H$114="",AE115=0)+AND($G$116="",$H$116="",AE117=0)+AND($G$118="",$H$118="",AE119=0)+AND($G$120="",$H$120="",AE121=0)+AND($G$122="",$H$122="",AE123=0)+AND($G$124="",$H$124="",AE125=0)+AND($G$126="",$H$126="",AE127=0)+AND($G$128="",$H$128="",AE129=0)+AND($G$130="",$H$130="",AE131=0)+AND($G$132="",$H$132="",AE133=0)+AND($G$134="",$H$134="",AE135=0)+AND($G$136="",$H$136="",AE137=0)+AND($G$138="",$H$138="",AE139=0)+AND($G$140="",$H$140="",AE141=0)+AND($G$142="",$H$142="",AE143=0)+AND($G$144="",$H$144="",AE145=0)+AND($G$146="",$H$146="",AE147=0)+AND($G$148="",$H$148="",AE149=0)+AND($G$150="",$H$150="",AE151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AF7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AF81=0)+AND($G$82="",$H$82="",AF83=0)+AND($G$84="",$H$84="",AF85=0)+AND($G$86="",$H$86="",AF87=0)+AND($G$88="",$H$88="",AF89=0)+AND($G$90="",$H$90="",AF91=0)+AND($G$92="",$H$92="",AF93=0)+AND($G$94="",$H$94="",AF95=0)+AND($G$96="",$H$96="",AF97=0)+AND($G$98="",$H$98="",AF99=0)+AND($G$100="",$H$100="",AF101=0)+AND($G$102="",$H$102="",AF103=0)+AND($G$104="",$H$104="",AF105=0)+AND($G$106="",$H$106="",AF107=0)+AND($G$108="",$H$108="",AF109=0)+AND($G$110="",$H$110="",AF111=0)+AND($G$112="",$H$112="",AF113=0)+AND($G$114="",$H$114="",AF115=0)+AND($G$116="",$H$116="",AF117=0)+AND($G$118="",$H$118="",AF119=0)+AND($G$120="",$H$120="",AF121=0)+AND($G$122="",$H$122="",AF123=0)+AND($G$124="",$H$124="",AF125=0)+AND($G$126="",$H$126="",AF127=0)+AND($G$128="",$H$128="",AF129=0)+AND($G$130="",$H$130="",AF131=0)+AND($G$132="",$H$132="",AF133=0)+AND($G$134="",$H$134="",AF135=0)+AND($G$136="",$H$136="",AF137=0)+AND($G$138="",$H$138="",AF139=0)+AND($G$140="",$H$140="",AF141=0)+AND($G$142="",$H$142="",AF143=0)+AND($G$144="",$H$144="",AF145=0)+AND($G$146="",$H$146="",AF147=0)+AND($G$148="",$H$148="",AF149=0)+AND($G$150="",$H$150="",AF151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AG7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AG81=0)+AND($G$82="",$H$82="",AG83=0)+AND($G$84="",$H$84="",AG85=0)+AND($G$86="",$H$86="",AG87=0)+AND($G$88="",$H$88="",AG89=0)+AND($G$90="",$H$90="",AG91=0)+AND($G$92="",$H$92="",AG93=0)+AND($G$94="",$H$94="",AG95=0)+AND($G$96="",$H$96="",AG97=0)+AND($G$98="",$H$98="",AG99=0)+AND($G$100="",$H$100="",AG101=0)+AND($G$102="",$H$102="",AG103=0)+AND($G$104="",$H$104="",AG105=0)+AND($G$106="",$H$106="",AG107=0)+AND($G$108="",$H$108="",AG109=0)+AND($G$110="",$H$110="",AG111=0)+AND($G$112="",$H$112="",AG113=0)+AND($G$114="",$H$114="",AG115=0)+AND($G$116="",$H$116="",AG117=0)+AND($G$118="",$H$118="",AG119=0)+AND($G$120="",$H$120="",AG121=0)+AND($G$122="",$H$122="",AG123=0)+AND($G$124="",$H$124="",AG125=0)+AND($G$126="",$H$126="",AG127=0)+AND($G$128="",$H$128="",AG129=0)+AND($G$130="",$H$130="",AG131=0)+AND($G$132="",$H$132="",AG133=0)+AND($G$134="",$H$134="",AG135=0)+AND($G$136="",$H$136="",AG137=0)+AND($G$138="",$H$138="",AG139=0)+AND($G$140="",$H$140="",AG141=0)+AND($G$142="",$H$142="",AG143=0)+AND($G$144="",$H$144="",AG145=0)+AND($G$146="",$H$146="",AG147=0)+AND($G$148="",$H$148="",AG149=0)+AND($G$150="",$H$150="",AG151=0))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AH7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AH81=0)+AND($G$82="",$H$82="",AH83=0)+AND($G$84="",$H$84="",AH85=0)+AND($G$86="",$H$86="",AH87=0)+AND($G$88="",$H$88="",AH89=0)+AND($G$90="",$H$90="",AH91=0)+AND($G$92="",$H$92="",AH93=0)+AND($G$94="",$H$94="",AH95=0)+AND($G$96="",$H$96="",AH97=0)+AND($G$98="",$H$98="",AH99=0)+AND($G$100="",$H$100="",AH101=0)+AND($G$102="",$H$102="",AH103=0)+AND($G$104="",$H$104="",AH105=0)+AND($G$106="",$H$106="",AH107=0)+AND($G$108="",$H$108="",AH109=0)+AND($G$110="",$H$110="",AH111=0)+AND($G$112="",$H$112="",AH113=0)+AND($G$114="",$H$114="",AH115=0)+AND($G$116="",$H$116="",AH117=0)+AND($G$118="",$H$118="",AH119=0)+AND($G$120="",$H$120="",AH121=0)+AND($G$122="",$H$122="",AH123=0)+AND($G$124="",$H$124="",AH125=0)+AND($G$126="",$H$126="",AH127=0)+AND($G$128="",$H$128="",AH129=0)+AND($G$130="",$H$130="",AH131=0)+AND($G$132="",$H$132="",AH133=0)+AND($G$134="",$H$134="",AH135=0)+AND($G$136="",$H$136="",AH137=0)+AND($G$138="",$H$138="",AH139=0)+AND($G$140="",$H$140="",AH141=0)+AND($G$142="",$H$142="",AH143=0)+AND($G$144="",$H$144="",AH145=0)+AND($G$146="",$H$146="",AH147=0)+AND($G$148="",$H$148="",AH149=0)+AND($G$150="",$H$150="",AH151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AI7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AI81=0)+AND($G$82="",$H$82="",AI83=0)+AND($G$84="",$H$84="",AI85=0)+AND($G$86="",$H$86="",AI87=0)+AND($G$88="",$H$88="",AI89=0)+AND($G$90="",$H$90="",AI91=0)+AND($G$92="",$H$92="",AI93=0)+AND($G$94="",$H$94="",AI95=0)+AND($G$96="",$H$96="",AI97=0)+AND($G$98="",$H$98="",AI99=0)+AND($G$100="",$H$100="",AI101=0)+AND($G$102="",$H$102="",AI103=0)+AND($G$104="",$H$104="",AI105=0)+AND($G$106="",$H$106="",AI107=0)+AND($G$108="",$H$108="",AI109=0)+AND($G$110="",$H$110="",AI111=0)+AND($G$112="",$H$112="",AI113=0)+AND($G$114="",$H$114="",AI115=0)+AND($G$116="",$H$116="",AI117=0)+AND($G$118="",$H$118="",AI119=0)+AND($G$120="",$H$120="",AI121=0)+AND($G$122="",$H$122="",AI123=0)+AND($G$124="",$H$124="",AI125=0)+AND($G$126="",$H$126="",AI127=0)+AND($G$128="",$H$128="",AI129=0)+AND($G$130="",$H$130="",AI131=0)+AND($G$132="",$H$132="",AI133=0)+AND($G$134="",$H$134="",AI135=0)+AND($G$136="",$H$136="",AI137=0)+AND($G$138="",$H$138="",AI139=0)+AND($G$140="",$H$140="",AI141=0)+AND($G$142="",$H$142="",AI143=0)+AND($G$144="",$H$144="",AI145=0)+AND($G$146="",$H$146="",AI147=0)+AND($G$148="",$H$148="",AI149=0)+AND($G$150="",$H$150="",AI151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AJ7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AJ81=0)+AND($G$82="",$H$82="",AJ83=0)+AND($G$84="",$H$84="",AJ85=0)+AND($G$86="",$H$86="",AJ87=0)+AND($G$88="",$H$88="",AJ89=0)+AND($G$90="",$H$90="",AJ91=0)+AND($G$92="",$H$92="",AJ93=0)+AND($G$94="",$H$94="",AJ95=0)+AND($G$96="",$H$96="",AJ97=0)+AND($G$98="",$H$98="",AJ99=0)+AND($G$100="",$H$100="",AJ101=0)+AND($G$102="",$H$102="",AJ103=0)+AND($G$104="",$H$104="",AJ105=0)+AND($G$106="",$H$106="",AJ107=0)+AND($G$108="",$H$108="",AJ109=0)+AND($G$110="",$H$110="",AJ111=0)+AND($G$112="",$H$112="",AJ113=0)+AND($G$114="",$H$114="",AJ115=0)+AND($G$116="",$H$116="",AJ117=0)+AND($G$118="",$H$118="",AJ119=0)+AND($G$120="",$H$120="",AJ121=0)+AND($G$122="",$H$122="",AJ123=0)+AND($G$124="",$H$124="",AJ125=0)+AND($G$126="",$H$126="",AJ127=0)+AND($G$128="",$H$128="",AJ129=0)+AND($G$130="",$H$130="",AJ131=0)+AND($G$132="",$H$132="",AJ133=0)+AND($G$134="",$H$134="",AJ135=0)+AND($G$136="",$H$136="",AJ137=0)+AND($G$138="",$H$138="",AJ139=0)+AND($G$140="",$H$140="",AJ141=0)+AND($G$142="",$H$142="",AJ143=0)+AND($G$144="",$H$144="",AJ145=0)+AND($G$146="",$H$146="",AJ147=0)+AND($G$148="",$H$148="",AJ149=0)+AND($G$150="",$H$150="",AJ151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AK7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AK81=0)+AND($G$82="",$H$82="",AK83=0)+AND($G$84="",$H$84="",AK85=0)+AND($G$86="",$H$86="",AK87=0)+AND($G$88="",$H$88="",AK89=0)+AND($G$90="",$H$90="",AK91=0)+AND($G$92="",$H$92="",AK93=0)+AND($G$94="",$H$94="",AK95=0)+AND($G$96="",$H$96="",AK97=0)+AND($G$98="",$H$98="",AK99=0)+AND($G$100="",$H$100="",AK101=0)+AND($G$102="",$H$102="",AK103=0)+AND($G$104="",$H$104="",AK105=0)+AND($G$106="",$H$106="",AK107=0)+AND($G$108="",$H$108="",AK109=0)+AND($G$110="",$H$110="",AK111=0)+AND($G$112="",$H$112="",AK113=0)+AND($G$114="",$H$114="",AK115=0)+AND($G$116="",$H$116="",AK117=0)+AND($G$118="",$H$118="",AK119=0)+AND($G$120="",$H$120="",AK121=0)+AND($G$122="",$H$122="",AK123=0)+AND($G$124="",$H$124="",AK125=0)+AND($G$126="",$H$126="",AK127=0)+AND($G$128="",$H$128="",AK129=0)+AND($G$130="",$H$130="",AK131=0)+AND($G$132="",$H$132="",AK133=0)+AND($G$134="",$H$134="",AK135=0)+AND($G$136="",$H$136="",AK137=0)+AND($G$138="",$H$138="",AK139=0)+AND($G$140="",$H$140="",AK141=0)+AND($G$142="",$H$142="",AK143=0)+AND($G$144="",$H$144="",AK145=0)+AND($G$146="",$H$146="",AK147=0)+AND($G$148="",$H$148="",AK149=0)+AND($G$150="",$H$150="",AK151=0))</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AL7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AL81=0)+AND($G$82="",$H$82="",AL83=0)+AND($G$84="",$H$84="",AL85=0)+AND($G$86="",$H$86="",AL87=0)+AND($G$88="",$H$88="",AL89=0)+AND($G$90="",$H$90="",AL91=0)+AND($G$92="",$H$92="",AL93=0)+AND($G$94="",$H$94="",AL95=0)+AND($G$96="",$H$96="",AL97=0)+AND($G$98="",$H$98="",AL99=0)+AND($G$100="",$H$100="",AL101=0)+AND($G$102="",$H$102="",AL103=0)+AND($G$104="",$H$104="",AL105=0)+AND($G$106="",$H$106="",AL107=0)+AND($G$108="",$H$108="",AL109=0)+AND($G$110="",$H$110="",AL111=0)+AND($G$112="",$H$112="",AL113=0)+AND($G$114="",$H$114="",AL115=0)+AND($G$116="",$H$116="",AL117=0)+AND($G$118="",$H$118="",AL119=0)+AND($G$120="",$H$120="",AL121=0)+AND($G$122="",$H$122="",AL123=0)+AND($G$124="",$H$124="",AL125=0)+AND($G$126="",$H$126="",AL127=0)+AND($G$128="",$H$128="",AL129=0)+AND($G$130="",$H$130="",AL131=0)+AND($G$132="",$H$132="",AL133=0)+AND($G$134="",$H$134="",AL135=0)+AND($G$136="",$H$136="",AL137=0)+AND($G$138="",$H$138="",AL139=0)+AND($G$140="",$H$140="",AL141=0)+AND($G$142="",$H$142="",AL143=0)+AND($G$144="",$H$144="",AL145=0)+AND($G$146="",$H$146="",AL147=0)+AND($G$148="",$H$148="",AL149=0)+AND($G$150="",$H$150="",AL151=0))</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AM7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AM81=0)+AND($G$82="",$H$82="",AM83=0)+AND($G$84="",$H$84="",AM85=0)+AND($G$86="",$H$86="",AM87=0)+AND($G$88="",$H$88="",AM89=0)+AND($G$90="",$H$90="",AM91=0)+AND($G$92="",$H$92="",AM93=0)+AND($G$94="",$H$94="",AM95=0)+AND($G$96="",$H$96="",AM97=0)+AND($G$98="",$H$98="",AM99=0)+AND($G$100="",$H$100="",AM101=0)+AND($G$102="",$H$102="",AM103=0)+AND($G$104="",$H$104="",AM105=0)+AND($G$106="",$H$106="",AM107=0)+AND($G$108="",$H$108="",AM109=0)+AND($G$110="",$H$110="",AM111=0)+AND($G$112="",$H$112="",AM113=0)+AND($G$114="",$H$114="",AM115=0)+AND($G$116="",$H$116="",AM117=0)+AND($G$118="",$H$118="",AM119=0)+AND($G$120="",$H$120="",AM121=0)+AND($G$122="",$H$122="",AM123=0)+AND($G$124="",$H$124="",AM125=0)+AND($G$126="",$H$126="",AM127=0)+AND($G$128="",$H$128="",AM129=0)+AND($G$130="",$H$130="",AM131=0)+AND($G$132="",$H$132="",AM133=0)+AND($G$134="",$H$134="",AM135=0)+AND($G$136="",$H$136="",AM137=0)+AND($G$138="",$H$138="",AM139=0)+AND($G$140="",$H$140="",AM141=0)+AND($G$142="",$H$142="",AM143=0)+AND($G$144="",$H$144="",AM145=0)+AND($G$146="",$H$146="",AM147=0)+AND($G$148="",$H$148="",AM149=0)+AND($G$150="",$H$150="",AM151=0))</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AN7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AN81=0)+AND($G$82="",$H$82="",AN83=0)+AND($G$84="",$H$84="",AN85=0)+AND($G$86="",$H$86="",AN87=0)+AND($G$88="",$H$88="",AN89=0)+AND($G$90="",$H$90="",AN91=0)+AND($G$92="",$H$92="",AN93=0)+AND($G$94="",$H$94="",AN95=0)+AND($G$96="",$H$96="",AN97=0)+AND($G$98="",$H$98="",AN99=0)+AND($G$100="",$H$100="",AN101=0)+AND($G$102="",$H$102="",AN103=0)+AND($G$104="",$H$104="",AN105=0)+AND($G$106="",$H$106="",AN107=0)+AND($G$108="",$H$108="",AN109=0)+AND($G$110="",$H$110="",AN111=0)+AND($G$112="",$H$112="",AN113=0)+AND($G$114="",$H$114="",AN115=0)+AND($G$116="",$H$116="",AN117=0)+AND($G$118="",$H$118="",AN119=0)+AND($G$120="",$H$120="",AN121=0)+AND($G$122="",$H$122="",AN123=0)+AND($G$124="",$H$124="",AN125=0)+AND($G$126="",$H$126="",AN127=0)+AND($G$128="",$H$128="",AN129=0)+AND($G$130="",$H$130="",AN131=0)+AND($G$132="",$H$132="",AN133=0)+AND($G$134="",$H$134="",AN135=0)+AND($G$136="",$H$136="",AN137=0)+AND($G$138="",$H$138="",AN139=0)+AND($G$140="",$H$140="",AN141=0)+AND($G$142="",$H$142="",AN143=0)+AND($G$144="",$H$144="",AN145=0)+AND($G$146="",$H$146="",AN147=0)+AND($G$148="",$H$148="",AN149=0)+AND($G$150="",$H$150="",AN151=0))</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AO7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AO81=0)+AND($G$82="",$H$82="",AO83=0)+AND($G$84="",$H$84="",AO85=0)+AND($G$86="",$H$86="",AO87=0)+AND($G$88="",$H$88="",AO89=0)+AND($G$90="",$H$90="",AO91=0)+AND($G$92="",$H$92="",AO93=0)+AND($G$94="",$H$94="",AO95=0)+AND($G$96="",$H$96="",AO97=0)+AND($G$98="",$H$98="",AO99=0)+AND($G$100="",$H$100="",AO101=0)+AND($G$102="",$H$102="",AO103=0)+AND($G$104="",$H$104="",AO105=0)+AND($G$106="",$H$106="",AO107=0)+AND($G$108="",$H$108="",AO109=0)+AND($G$110="",$H$110="",AO111=0)+AND($G$112="",$H$112="",AO113=0)+AND($G$114="",$H$114="",AO115=0)+AND($G$116="",$H$116="",AO117=0)+AND($G$118="",$H$118="",AO119=0)+AND($G$120="",$H$120="",AO121=0)+AND($G$122="",$H$122="",AO123=0)+AND($G$124="",$H$124="",AO125=0)+AND($G$126="",$H$126="",AO127=0)+AND($G$128="",$H$128="",AO129=0)+AND($G$130="",$H$130="",AO131=0)+AND($G$132="",$H$132="",AO133=0)+AND($G$134="",$H$134="",AO135=0)+AND($G$136="",$H$136="",AO137=0)+AND($G$138="",$H$138="",AO139=0)+AND($G$140="",$H$140="",AO141=0)+AND($G$142="",$H$142="",AO143=0)+AND($G$144="",$H$144="",AO145=0)+AND($G$146="",$H$146="",AO147=0)+AND($G$148="",$H$148="",AO149=0)+AND($G$150="",$H$150="",AO151=0))</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="AP7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AP81=0)+AND($G$82="",$H$82="",AP83=0)+AND($G$84="",$H$84="",AP85=0)+AND($G$86="",$H$86="",AP87=0)+AND($G$88="",$H$88="",AP89=0)+AND($G$90="",$H$90="",AP91=0)+AND($G$92="",$H$92="",AP93=0)+AND($G$94="",$H$94="",AP95=0)+AND($G$96="",$H$96="",AP97=0)+AND($G$98="",$H$98="",AP99=0)+AND($G$100="",$H$100="",AP101=0)+AND($G$102="",$H$102="",AP103=0)+AND($G$104="",$H$104="",AP105=0)+AND($G$106="",$H$106="",AP107=0)+AND($G$108="",$H$108="",AP109=0)+AND($G$110="",$H$110="",AP111=0)+AND($G$112="",$H$112="",AP113=0)+AND($G$114="",$H$114="",AP115=0)+AND($G$116="",$H$116="",AP117=0)+AND($G$118="",$H$118="",AP119=0)+AND($G$120="",$H$120="",AP121=0)+AND($G$122="",$H$122="",AP123=0)+AND($G$124="",$H$124="",AP125=0)+AND($G$126="",$H$126="",AP127=0)+AND($G$128="",$H$128="",AP129=0)+AND($G$130="",$H$130="",AP131=0)+AND($G$132="",$H$132="",AP133=0)+AND($G$134="",$H$134="",AP135=0)+AND($G$136="",$H$136="",AP137=0)+AND($G$138="",$H$138="",AP139=0)+AND($G$140="",$H$140="",AP141=0)+AND($G$142="",$H$142="",AP143=0)+AND($G$144="",$H$144="",AP145=0)+AND($G$146="",$H$146="",AP147=0)+AND($G$148="",$H$148="",AP149=0)+AND($G$150="",$H$150="",AP151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AQ7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AQ81=0)+AND($G$82="",$H$82="",AQ83=0)+AND($G$84="",$H$84="",AQ85=0)+AND($G$86="",$H$86="",AQ87=0)+AND($G$88="",$H$88="",AQ89=0)+AND($G$90="",$H$90="",AQ91=0)+AND($G$92="",$H$92="",AQ93=0)+AND($G$94="",$H$94="",AQ95=0)+AND($G$96="",$H$96="",AQ97=0)+AND($G$98="",$H$98="",AQ99=0)+AND($G$100="",$H$100="",AQ101=0)+AND($G$102="",$H$102="",AQ103=0)+AND($G$104="",$H$104="",AQ105=0)+AND($G$106="",$H$106="",AQ107=0)+AND($G$108="",$H$108="",AQ109=0)+AND($G$110="",$H$110="",AQ111=0)+AND($G$112="",$H$112="",AQ113=0)+AND($G$114="",$H$114="",AQ115=0)+AND($G$116="",$H$116="",AQ117=0)+AND($G$118="",$H$118="",AQ119=0)+AND($G$120="",$H$120="",AQ121=0)+AND($G$122="",$H$122="",AQ123=0)+AND($G$124="",$H$124="",AQ125=0)+AND($G$126="",$H$126="",AQ127=0)+AND($G$128="",$H$128="",AQ129=0)+AND($G$130="",$H$130="",AQ131=0)+AND($G$132="",$H$132="",AQ133=0)+AND($G$134="",$H$134="",AQ135=0)+AND($G$136="",$H$136="",AQ137=0)+AND($G$138="",$H$138="",AQ139=0)+AND($G$140="",$H$140="",AQ141=0)+AND($G$142="",$H$142="",AQ143=0)+AND($G$144="",$H$144="",AQ145=0)+AND($G$146="",$H$146="",AQ147=0)+AND($G$148="",$H$148="",AQ149=0)+AND($G$150="",$H$150="",AQ151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AR7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AR81=0)+AND($G$82="",$H$82="",AR83=0)+AND($G$84="",$H$84="",AR85=0)+AND($G$86="",$H$86="",AR87=0)+AND($G$88="",$H$88="",AR89=0)+AND($G$90="",$H$90="",AR91=0)+AND($G$92="",$H$92="",AR93=0)+AND($G$94="",$H$94="",AR95=0)+AND($G$96="",$H$96="",AR97=0)+AND($G$98="",$H$98="",AR99=0)+AND($G$100="",$H$100="",AR101=0)+AND($G$102="",$H$102="",AR103=0)+AND($G$104="",$H$104="",AR105=0)+AND($G$106="",$H$106="",AR107=0)+AND($G$108="",$H$108="",AR109=0)+AND($G$110="",$H$110="",AR111=0)+AND($G$112="",$H$112="",AR113=0)+AND($G$114="",$H$114="",AR115=0)+AND($G$116="",$H$116="",AR117=0)+AND($G$118="",$H$118="",AR119=0)+AND($G$120="",$H$120="",AR121=0)+AND($G$122="",$H$122="",AR123=0)+AND($G$124="",$H$124="",AR125=0)+AND($G$126="",$H$126="",AR127=0)+AND($G$128="",$H$128="",AR129=0)+AND($G$130="",$H$130="",AR131=0)+AND($G$132="",$H$132="",AR133=0)+AND($G$134="",$H$134="",AR135=0)+AND($G$136="",$H$136="",AR137=0)+AND($G$138="",$H$138="",AR139=0)+AND($G$140="",$H$140="",AR141=0)+AND($G$142="",$H$142="",AR143=0)+AND($G$144="",$H$144="",AR145=0)+AND($G$146="",$H$146="",AR147=0)+AND($G$148="",$H$148="",AR149=0)+AND($G$150="",$H$150="",AR151=0))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AS7" s="77">
-        <f>SUM(AND($G$80="",$H$80="",AS81=0)+AND($G$82="",$H$82="",AS83=0)+AND($G$84="",$H$84="",AS85=0)+AND($G$86="",$H$86="",AS87=0)+AND($G$88="",$H$88="",AS89=0)+AND($G$90="",$H$90="",AS91=0)+AND($G$92="",$H$92="",AS93=0)+AND($G$94="",$H$94="",AS95=0)+AND($G$96="",$H$96="",AS97=0)+AND($G$98="",$H$98="",AS99=0)+AND($G$100="",$H$100="",AS101=0)+AND($G$102="",$H$102="",AS103=0)+AND($G$104="",$H$104="",AS105=0)+AND($G$106="",$H$106="",AS107=0)+AND($G$108="",$H$108="",AS109=0)+AND($G$110="",$H$110="",AS111=0)+AND($G$112="",$H$112="",AS113=0)+AND($G$114="",$H$114="",AS115=0)+AND($G$116="",$H$116="",AS117=0)+AND($G$118="",$H$118="",AS119=0)+AND($G$120="",$H$120="",AS121=0)+AND($G$122="",$H$122="",AS123=0)+AND($G$124="",$H$124="",AS125=0)+AND($G$126="",$H$126="",AS127=0)+AND($G$128="",$H$128="",AS129=0)+AND($G$130="",$H$130="",AS131=0)+AND($G$132="",$H$132="",AS133=0)+AND($G$134="",$H$134="",AS135=0)+AND($G$136="",$H$136="",AS137=0)+AND($G$138="",$H$138="",AS139=0)+AND($G$140="",$H$140="",AS141=0)+AND($G$142="",$H$142="",AS143=0)+AND($G$144="",$H$144="",AS145=0)+AND($G$146="",$H$146="",AS147=0)+AND($G$148="",$H$148="",AS149=0)+AND($G$150="",$H$150="",AS151=0))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AT7" s="80">
-        <f>SUM(AND($G$80="",$H$80="",AT81=0)+AND($G$82="",$H$82="",AT83=0)+AND($G$84="",$H$84="",AT85=0)+AND($G$86="",$H$86="",AT87=0)+AND($G$88="",$H$88="",AT89=0)+AND($G$90="",$H$90="",AT91=0)+AND($G$92="",$H$92="",AT93=0)+AND($G$94="",$H$94="",AT95=0)+AND($G$96="",$H$96="",AT97=0)+AND($G$98="",$H$98="",AT99=0)+AND($G$100="",$H$100="",AT101=0)+AND($G$102="",$H$102="",AT103=0)+AND($G$104="",$H$104="",AT105=0)+AND($G$106="",$H$106="",AT107=0)+AND($G$108="",$H$108="",AT109=0)+AND($G$110="",$H$110="",AT111=0)+AND($G$112="",$H$112="",AT113=0)+AND($G$114="",$H$114="",AT115=0)+AND($G$116="",$H$116="",AT117=0)+AND($G$118="",$H$118="",AT119=0)+AND($G$120="",$H$120="",AT121=0)+AND($G$122="",$H$122="",AT123=0)+AND($G$124="",$H$124="",AT125=0)+AND($G$126="",$H$126="",AT127=0)+AND($G$128="",$H$128="",AT129=0)+AND($G$130="",$H$130="",AT131=0)+AND($G$132="",$H$132="",AT133=0)+AND($G$134="",$H$134="",AT135=0)+AND($G$136="",$H$136="",AT137=0)+AND($G$138="",$H$138="",AT139=0)+AND($G$140="",$H$140="",AT141=0)+AND($G$142="",$H$142="",AT143=0)+AND($G$144="",$H$144="",AT145=0)+AND($G$146="",$H$146="",AT147=0)+AND($G$148="",$H$148="",AT149=0)+AND($G$150="",$H$150="",AT151=0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:54" ht="14.4" x14ac:dyDescent="0.3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:54" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="103" t="s">
         <v>1</v>
       </c>
@@ -3760,7 +3724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:54" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="103"/>
       <c r="B9" s="133"/>
       <c r="C9" s="133"/>
@@ -3888,7 +3852,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="103"/>
       <c r="B10" s="132">
         <v>46184</v>
@@ -3912,7 +3876,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="112" t="str">
-        <f t="shared" ref="I10:I54" si="0">IF(G10="","-",IF(G10&gt;H10,"L",IF(G10=H10,"E",IF(G10&lt;H10,"V"))))</f>
+        <f t="shared" ref="I10:I54" si="5">IF(G10="","-",IF(G10&gt;H10,"L",IF(G10=H10,"E",IF(G10&lt;H10,"V"))))</f>
         <v>L</v>
       </c>
       <c r="J10" s="26" t="s">
@@ -4033,7 +3997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="103"/>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -4161,7 +4125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="103"/>
       <c r="B12" s="132">
         <v>46191</v>
@@ -4181,7 +4145,7 @@
       <c r="G12" s="113"/>
       <c r="H12" s="113"/>
       <c r="I12" s="112" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="J12" s="23" t="s">
@@ -4300,7 +4264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="103"/>
       <c r="B13" s="133"/>
       <c r="C13" s="133"/>
@@ -4426,7 +4390,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="103"/>
       <c r="B14" s="132">
         <v>46191</v>
@@ -4446,7 +4410,7 @@
       <c r="G14" s="113"/>
       <c r="H14" s="113"/>
       <c r="I14" s="112" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="J14" s="26" t="s">
@@ -4565,7 +4529,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="103"/>
       <c r="B15" s="133"/>
       <c r="C15" s="133"/>
@@ -4691,7 +4655,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="103"/>
       <c r="B16" s="132">
         <v>46197</v>
@@ -4711,7 +4675,7 @@
       <c r="G16" s="113"/>
       <c r="H16" s="113"/>
       <c r="I16" s="112" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="J16" s="23" t="s">
@@ -4830,7 +4794,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="103"/>
       <c r="B17" s="133"/>
       <c r="C17" s="133"/>
@@ -4956,7 +4920,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="103"/>
       <c r="B18" s="132">
         <v>46197</v>
@@ -4976,7 +4940,7 @@
       <c r="G18" s="113"/>
       <c r="H18" s="113"/>
       <c r="I18" s="112" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="J18" s="26" t="s">
@@ -5095,7 +5059,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="104"/>
       <c r="B19" s="133"/>
       <c r="C19" s="133"/>
@@ -5221,7 +5185,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="114" t="s">
         <v>2</v>
       </c>
@@ -5247,7 +5211,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="121" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>E</v>
       </c>
       <c r="J20" s="27" t="s">
@@ -5366,7 +5330,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="115"/>
       <c r="B21" s="131"/>
       <c r="C21" s="131"/>
@@ -5492,7 +5456,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="115"/>
       <c r="B22" s="130">
         <v>46186</v>
@@ -5516,7 +5480,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="121" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>E</v>
       </c>
       <c r="J22" s="26" t="s">
@@ -5635,7 +5599,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="115"/>
       <c r="B23" s="131"/>
       <c r="C23" s="131"/>
@@ -5761,7 +5725,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="115"/>
       <c r="B24" s="130">
         <v>46191</v>
@@ -5781,7 +5745,7 @@
       <c r="G24" s="119"/>
       <c r="H24" s="119"/>
       <c r="I24" s="121" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="J24" s="27" t="s">
@@ -5900,7 +5864,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="115"/>
       <c r="B25" s="131"/>
       <c r="C25" s="131"/>
@@ -6026,7 +5990,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="115"/>
       <c r="B26" s="130">
         <v>46191</v>
@@ -6046,7 +6010,7 @@
       <c r="G26" s="119"/>
       <c r="H26" s="119"/>
       <c r="I26" s="121" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="J26" s="26" t="s">
@@ -6165,7 +6129,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="115"/>
       <c r="B27" s="131"/>
       <c r="C27" s="131"/>
@@ -6291,7 +6255,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="115"/>
       <c r="B28" s="130">
         <v>46197</v>
@@ -6311,7 +6275,7 @@
       <c r="G28" s="119"/>
       <c r="H28" s="119"/>
       <c r="I28" s="121" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="J28" s="27" t="s">
@@ -6430,7 +6394,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="115"/>
       <c r="B29" s="131"/>
       <c r="C29" s="131"/>
@@ -6556,7 +6520,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="115"/>
       <c r="B30" s="130">
         <v>46197</v>
@@ -6576,7 +6540,7 @@
       <c r="G30" s="119"/>
       <c r="H30" s="119"/>
       <c r="I30" s="121" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="J30" s="26" t="s">
@@ -6695,7 +6659,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="116"/>
       <c r="B31" s="131"/>
       <c r="C31" s="131"/>
@@ -6817,7 +6781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="125" t="s">
         <v>3</v>
       </c>
@@ -6843,7 +6807,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="112" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>E</v>
       </c>
       <c r="J32" s="23" t="s">
@@ -6958,7 +6922,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="103"/>
       <c r="B33" s="133"/>
       <c r="C33" s="133"/>
@@ -7080,7 +7044,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="103"/>
       <c r="B34" s="132">
         <v>46186</v>
@@ -7104,7 +7068,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="112" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>V</v>
       </c>
       <c r="J34" s="26" t="s">
@@ -7219,7 +7183,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="103"/>
       <c r="B35" s="133"/>
       <c r="C35" s="133"/>
@@ -7341,7 +7305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="103"/>
       <c r="B36" s="132">
         <v>46192</v>
@@ -7361,7 +7325,7 @@
       <c r="G36" s="113"/>
       <c r="H36" s="113"/>
       <c r="I36" s="112" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="J36" s="23" t="s">
@@ -7476,7 +7440,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="103"/>
       <c r="B37" s="133"/>
       <c r="C37" s="133"/>
@@ -7598,7 +7562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="103"/>
       <c r="B38" s="132">
         <v>46192</v>
@@ -7618,7 +7582,7 @@
       <c r="G38" s="113"/>
       <c r="H38" s="113"/>
       <c r="I38" s="112" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="J38" s="26" t="s">
@@ -7733,7 +7697,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="103"/>
       <c r="B39" s="133"/>
       <c r="C39" s="133"/>
@@ -7855,7 +7819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="103"/>
       <c r="B40" s="139">
         <v>46197</v>
@@ -7875,7 +7839,7 @@
       <c r="G40" s="113"/>
       <c r="H40" s="113"/>
       <c r="I40" s="112" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="J40" s="23" t="s">
@@ -7990,7 +7954,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="103"/>
       <c r="B41" s="140"/>
       <c r="C41" s="140"/>
@@ -8112,7 +8076,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="103"/>
       <c r="B42" s="132">
         <v>46197</v>
@@ -8132,7 +8096,7 @@
       <c r="G42" s="113"/>
       <c r="H42" s="113"/>
       <c r="I42" s="112" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="J42" s="26" t="s">
@@ -8247,7 +8211,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="104"/>
       <c r="B43" s="133"/>
       <c r="C43" s="133"/>
@@ -8369,7 +8333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="114" t="s">
         <v>4</v>
       </c>
@@ -8395,7 +8359,7 @@
         <v>1</v>
       </c>
       <c r="I44" s="121" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>L</v>
       </c>
       <c r="J44" s="27" t="s">
@@ -8510,7 +8474,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="115"/>
       <c r="B45" s="131"/>
       <c r="C45" s="131"/>
@@ -8632,7 +8596,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="115"/>
       <c r="B46" s="130">
         <v>46186</v>
@@ -8656,7 +8620,7 @@
         <v>2</v>
       </c>
       <c r="I46" s="121" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>V</v>
       </c>
       <c r="J46" s="26" t="s">
@@ -8771,7 +8735,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="115"/>
       <c r="B47" s="131"/>
       <c r="C47" s="131"/>
@@ -8893,7 +8857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="115"/>
       <c r="B48" s="130">
         <v>46192</v>
@@ -8913,7 +8877,7 @@
       <c r="G48" s="119"/>
       <c r="H48" s="119"/>
       <c r="I48" s="121" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="J48" s="27" t="s">
@@ -9028,7 +8992,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="115"/>
       <c r="B49" s="131"/>
       <c r="C49" s="131"/>
@@ -9150,7 +9114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="115"/>
       <c r="B50" s="130">
         <v>46192</v>
@@ -9170,7 +9134,7 @@
       <c r="G50" s="119"/>
       <c r="H50" s="119"/>
       <c r="I50" s="121" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="J50" s="26" t="s">
@@ -9285,7 +9249,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="115"/>
       <c r="B51" s="131"/>
       <c r="C51" s="131"/>
@@ -9407,7 +9371,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="115"/>
       <c r="B52" s="130">
         <v>46198</v>
@@ -9427,7 +9391,7 @@
       <c r="G52" s="119"/>
       <c r="H52" s="119"/>
       <c r="I52" s="121" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="J52" s="27" t="s">
@@ -9542,7 +9506,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="115"/>
       <c r="B53" s="131"/>
       <c r="C53" s="131"/>
@@ -9664,7 +9628,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="115"/>
       <c r="B54" s="128">
         <v>46198</v>
@@ -9684,7 +9648,7 @@
       <c r="G54" s="119"/>
       <c r="H54" s="119"/>
       <c r="I54" s="121" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="J54" s="26" t="s">
@@ -9799,7 +9763,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="116"/>
       <c r="B55" s="129"/>
       <c r="C55" s="129"/>
@@ -9921,7 +9885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="125" t="s">
         <v>16</v>
       </c>
@@ -10062,7 +10026,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="103"/>
       <c r="B57" s="133"/>
       <c r="C57" s="133"/>
@@ -10184,7 +10148,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="103"/>
       <c r="B58" s="132">
         <v>46187</v>
@@ -10208,7 +10172,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="112" t="str">
-        <f t="shared" ref="I58" si="1">IF(G58="","-",IF(G58&gt;H58,"L",IF(G58=H58,"E",IF(G58&lt;H58,"V"))))</f>
+        <f t="shared" ref="I58" si="6">IF(G58="","-",IF(G58&gt;H58,"L",IF(G58=H58,"E",IF(G58&lt;H58,"V"))))</f>
         <v>L</v>
       </c>
       <c r="J58" s="26" t="s">
@@ -10323,7 +10287,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="103"/>
       <c r="B59" s="133"/>
       <c r="C59" s="133"/>
@@ -10445,7 +10409,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="103"/>
       <c r="B60" s="132">
         <v>46193</v>
@@ -10465,7 +10429,7 @@
       <c r="G60" s="113"/>
       <c r="H60" s="113"/>
       <c r="I60" s="112" t="str">
-        <f t="shared" ref="I60" si="2">IF(G60="","-",IF(G60&gt;H60,"L",IF(G60=H60,"E",IF(G60&lt;H60,"V"))))</f>
+        <f t="shared" ref="I60" si="7">IF(G60="","-",IF(G60&gt;H60,"L",IF(G60=H60,"E",IF(G60&lt;H60,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J60" s="23" t="s">
@@ -10580,7 +10544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="103"/>
       <c r="B61" s="133"/>
       <c r="C61" s="133"/>
@@ -10702,7 +10666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="103"/>
       <c r="B62" s="132">
         <v>46193</v>
@@ -10722,7 +10686,7 @@
       <c r="G62" s="113"/>
       <c r="H62" s="113"/>
       <c r="I62" s="112" t="str">
-        <f t="shared" ref="I62" si="3">IF(G62="","-",IF(G62&gt;H62,"L",IF(G62=H62,"E",IF(G62&lt;H62,"V"))))</f>
+        <f t="shared" ref="I62" si="8">IF(G62="","-",IF(G62&gt;H62,"L",IF(G62=H62,"E",IF(G62&lt;H62,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J62" s="26" t="s">
@@ -10837,7 +10801,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="103"/>
       <c r="B63" s="133"/>
       <c r="C63" s="133"/>
@@ -10959,7 +10923,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="103"/>
       <c r="B64" s="132">
         <v>46198</v>
@@ -10979,7 +10943,7 @@
       <c r="G64" s="113"/>
       <c r="H64" s="113"/>
       <c r="I64" s="112" t="str">
-        <f t="shared" ref="I64" si="4">IF(G64="","-",IF(G64&gt;H64,"L",IF(G64=H64,"E",IF(G64&lt;H64,"V"))))</f>
+        <f t="shared" ref="I64" si="9">IF(G64="","-",IF(G64&gt;H64,"L",IF(G64=H64,"E",IF(G64&lt;H64,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J64" s="23" t="s">
@@ -11094,7 +11058,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="103"/>
       <c r="B65" s="133"/>
       <c r="C65" s="133"/>
@@ -11216,7 +11180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="103"/>
       <c r="B66" s="132">
         <v>46198</v>
@@ -11236,7 +11200,7 @@
       <c r="G66" s="113"/>
       <c r="H66" s="113"/>
       <c r="I66" s="112" t="str">
-        <f t="shared" ref="I66" si="5">IF(G66="","-",IF(G66&gt;H66,"L",IF(G66=H66,"E",IF(G66&lt;H66,"V"))))</f>
+        <f t="shared" ref="I66" si="10">IF(G66="","-",IF(G66&gt;H66,"L",IF(G66=H66,"E",IF(G66&lt;H66,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J66" s="26" t="s">
@@ -11351,7 +11315,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="104"/>
       <c r="B67" s="133"/>
       <c r="C67" s="133"/>
@@ -11473,7 +11437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="114" t="s">
         <v>21</v>
       </c>
@@ -11499,7 +11463,7 @@
         <v>2</v>
       </c>
       <c r="I68" s="121" t="str">
-        <f t="shared" ref="I68" si="6">IF(G68="","-",IF(G68&gt;H68,"L",IF(G68=H68,"E",IF(G68&lt;H68,"V"))))</f>
+        <f t="shared" ref="I68" si="11">IF(G68="","-",IF(G68&gt;H68,"L",IF(G68=H68,"E",IF(G68&lt;H68,"V"))))</f>
         <v>E</v>
       </c>
       <c r="J68" s="27" t="s">
@@ -11614,7 +11578,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="115"/>
       <c r="B69" s="131"/>
       <c r="C69" s="131"/>
@@ -11736,7 +11700,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="115"/>
       <c r="B70" s="130">
         <v>46187</v>
@@ -11760,7 +11724,7 @@
         <v>1</v>
       </c>
       <c r="I70" s="121" t="str">
-        <f t="shared" ref="I70" si="7">IF(G70="","-",IF(G70&gt;H70,"L",IF(G70=H70,"E",IF(G70&lt;H70,"V"))))</f>
+        <f t="shared" ref="I70" si="12">IF(G70="","-",IF(G70&gt;H70,"L",IF(G70=H70,"E",IF(G70&lt;H70,"V"))))</f>
         <v>L</v>
       </c>
       <c r="J70" s="26" t="s">
@@ -11875,7 +11839,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="115"/>
       <c r="B71" s="131"/>
       <c r="C71" s="131"/>
@@ -11997,7 +11961,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="115"/>
       <c r="B72" s="130">
         <v>46193</v>
@@ -12017,7 +11981,7 @@
       <c r="G72" s="119"/>
       <c r="H72" s="119"/>
       <c r="I72" s="121" t="str">
-        <f t="shared" ref="I72" si="8">IF(G72="","-",IF(G72&gt;H72,"L",IF(G72=H72,"E",IF(G72&lt;H72,"V"))))</f>
+        <f t="shared" ref="I72" si="13">IF(G72="","-",IF(G72&gt;H72,"L",IF(G72=H72,"E",IF(G72&lt;H72,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J72" s="27" t="s">
@@ -12132,7 +12096,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="115"/>
       <c r="B73" s="131"/>
       <c r="C73" s="131"/>
@@ -12254,7 +12218,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="115"/>
       <c r="B74" s="130">
         <v>46193</v>
@@ -12274,7 +12238,7 @@
       <c r="G74" s="119"/>
       <c r="H74" s="119"/>
       <c r="I74" s="121" t="str">
-        <f t="shared" ref="I74" si="9">IF(G74="","-",IF(G74&gt;H74,"L",IF(G74=H74,"E",IF(G74&lt;H74,"V"))))</f>
+        <f t="shared" ref="I74" si="14">IF(G74="","-",IF(G74&gt;H74,"L",IF(G74=H74,"E",IF(G74&lt;H74,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J74" s="26" t="s">
@@ -12389,7 +12353,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="115"/>
       <c r="B75" s="131"/>
       <c r="C75" s="131"/>
@@ -12511,7 +12475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="115"/>
       <c r="B76" s="130">
         <v>46198</v>
@@ -12531,7 +12495,7 @@
       <c r="G76" s="119"/>
       <c r="H76" s="119"/>
       <c r="I76" s="121" t="str">
-        <f t="shared" ref="I76" si="10">IF(G76="","-",IF(G76&gt;H76,"L",IF(G76=H76,"E",IF(G76&lt;H76,"V"))))</f>
+        <f t="shared" ref="I76" si="15">IF(G76="","-",IF(G76&gt;H76,"L",IF(G76=H76,"E",IF(G76&lt;H76,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J76" s="27" t="s">
@@ -12646,7 +12610,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="115"/>
       <c r="B77" s="131"/>
       <c r="C77" s="131"/>
@@ -12768,7 +12732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="115"/>
       <c r="B78" s="130">
         <v>46198</v>
@@ -12788,7 +12752,7 @@
       <c r="G78" s="119"/>
       <c r="H78" s="119"/>
       <c r="I78" s="121" t="str">
-        <f t="shared" ref="I78" si="11">IF(G78="","-",IF(G78&gt;H78,"L",IF(G78=H78,"E",IF(G78&lt;H78,"V"))))</f>
+        <f t="shared" ref="I78" si="16">IF(G78="","-",IF(G78&gt;H78,"L",IF(G78=H78,"E",IF(G78&lt;H78,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J78" s="26" t="s">
@@ -12903,7 +12867,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="116"/>
       <c r="B79" s="131"/>
       <c r="C79" s="131"/>
@@ -13025,7 +12989,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="125" t="s">
         <v>48</v>
       </c>
@@ -13162,7 +13126,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="103"/>
       <c r="B81" s="133"/>
       <c r="C81" s="133"/>
@@ -13284,7 +13248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="103"/>
       <c r="B82" s="132">
         <v>46188</v>
@@ -13304,7 +13268,7 @@
       <c r="G82" s="113"/>
       <c r="H82" s="113"/>
       <c r="I82" s="112" t="str">
-        <f t="shared" ref="I82" si="12">IF(G82="","-",IF(G82&gt;H82,"L",IF(G82=H82,"E",IF(G82&lt;H82,"V"))))</f>
+        <f t="shared" ref="I82" si="17">IF(G82="","-",IF(G82&gt;H82,"L",IF(G82=H82,"E",IF(G82&lt;H82,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J82" s="26" t="s">
@@ -13419,7 +13383,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="103"/>
       <c r="B83" s="133"/>
       <c r="C83" s="133"/>
@@ -13541,7 +13505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="103"/>
       <c r="B84" s="132">
         <v>46194</v>
@@ -13561,7 +13525,7 @@
       <c r="G84" s="113"/>
       <c r="H84" s="113"/>
       <c r="I84" s="112" t="str">
-        <f t="shared" ref="I84" si="13">IF(G84="","-",IF(G84&gt;H84,"L",IF(G84=H84,"E",IF(G84&lt;H84,"V"))))</f>
+        <f t="shared" ref="I84" si="18">IF(G84="","-",IF(G84&gt;H84,"L",IF(G84=H84,"E",IF(G84&lt;H84,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J84" s="23" t="s">
@@ -13676,7 +13640,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="103"/>
       <c r="B85" s="133"/>
       <c r="C85" s="133"/>
@@ -13798,7 +13762,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="103"/>
       <c r="B86" s="132">
         <v>46194</v>
@@ -13818,7 +13782,7 @@
       <c r="G86" s="113"/>
       <c r="H86" s="113"/>
       <c r="I86" s="112" t="str">
-        <f t="shared" ref="I86" si="14">IF(G86="","-",IF(G86&gt;H86,"L",IF(G86=H86,"E",IF(G86&lt;H86,"V"))))</f>
+        <f t="shared" ref="I86" si="19">IF(G86="","-",IF(G86&gt;H86,"L",IF(G86=H86,"E",IF(G86&lt;H86,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J86" s="26" t="s">
@@ -13933,7 +13897,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="103"/>
       <c r="B87" s="133"/>
       <c r="C87" s="133"/>
@@ -14055,7 +14019,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="103"/>
       <c r="B88" s="132">
         <v>46199</v>
@@ -14075,7 +14039,7 @@
       <c r="G88" s="113"/>
       <c r="H88" s="113"/>
       <c r="I88" s="112" t="str">
-        <f t="shared" ref="I88" si="15">IF(G88="","-",IF(G88&gt;H88,"L",IF(G88=H88,"E",IF(G88&lt;H88,"V"))))</f>
+        <f t="shared" ref="I88" si="20">IF(G88="","-",IF(G88&gt;H88,"L",IF(G88=H88,"E",IF(G88&lt;H88,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J88" s="23" t="s">
@@ -14190,7 +14154,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="89" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="103"/>
       <c r="B89" s="133"/>
       <c r="C89" s="133"/>
@@ -14312,7 +14276,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="103"/>
       <c r="B90" s="132">
         <v>46199</v>
@@ -14332,7 +14296,7 @@
       <c r="G90" s="113"/>
       <c r="H90" s="113"/>
       <c r="I90" s="112" t="str">
-        <f t="shared" ref="I90" si="16">IF(G90="","-",IF(G90&gt;H90,"L",IF(G90=H90,"E",IF(G90&lt;H90,"V"))))</f>
+        <f t="shared" ref="I90" si="21">IF(G90="","-",IF(G90&gt;H90,"L",IF(G90=H90,"E",IF(G90&lt;H90,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J90" s="26" t="s">
@@ -14447,7 +14411,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="104"/>
       <c r="B91" s="133"/>
       <c r="C91" s="133"/>
@@ -14569,7 +14533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="114" t="s">
         <v>49</v>
       </c>
@@ -14588,11 +14552,15 @@
       <c r="F92" s="117" t="s">
         <v>62</v>
       </c>
-      <c r="G92" s="119"/>
-      <c r="H92" s="119"/>
+      <c r="G92" s="119">
+        <v>0</v>
+      </c>
+      <c r="H92" s="119">
+        <v>0</v>
+      </c>
       <c r="I92" s="121" t="str">
-        <f t="shared" ref="I92" si="17">IF(G92="","-",IF(G92&gt;H92,"L",IF(G92=H92,"E",IF(G92&lt;H92,"V"))))</f>
-        <v>-</v>
+        <f t="shared" ref="I92" si="22">IF(G92="","-",IF(G92&gt;H92,"L",IF(G92=H92,"E",IF(G92&lt;H92,"V"))))</f>
+        <v>E</v>
       </c>
       <c r="J92" s="27" t="s">
         <v>7</v>
@@ -14706,7 +14674,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="115"/>
       <c r="B93" s="131"/>
       <c r="C93" s="131"/>
@@ -14828,7 +14796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="115"/>
       <c r="B94" s="130">
         <v>46188</v>
@@ -14848,7 +14816,7 @@
       <c r="G94" s="119"/>
       <c r="H94" s="119"/>
       <c r="I94" s="121" t="str">
-        <f t="shared" ref="I94" si="18">IF(G94="","-",IF(G94&gt;H94,"L",IF(G94=H94,"E",IF(G94&lt;H94,"V"))))</f>
+        <f t="shared" ref="I94" si="23">IF(G94="","-",IF(G94&gt;H94,"L",IF(G94=H94,"E",IF(G94&lt;H94,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J94" s="26" t="s">
@@ -14963,7 +14931,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="115"/>
       <c r="B95" s="131"/>
       <c r="C95" s="131"/>
@@ -15085,7 +15053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="115"/>
       <c r="B96" s="130">
         <v>46194</v>
@@ -15105,7 +15073,7 @@
       <c r="G96" s="119"/>
       <c r="H96" s="119"/>
       <c r="I96" s="121" t="str">
-        <f t="shared" ref="I96" si="19">IF(G96="","-",IF(G96&gt;H96,"L",IF(G96=H96,"E",IF(G96&lt;H96,"V"))))</f>
+        <f t="shared" ref="I96" si="24">IF(G96="","-",IF(G96&gt;H96,"L",IF(G96=H96,"E",IF(G96&lt;H96,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J96" s="27" t="s">
@@ -15220,7 +15188,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="115"/>
       <c r="B97" s="131"/>
       <c r="C97" s="131"/>
@@ -15342,7 +15310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="115"/>
       <c r="B98" s="130">
         <v>46194</v>
@@ -15362,7 +15330,7 @@
       <c r="G98" s="119"/>
       <c r="H98" s="119"/>
       <c r="I98" s="121" t="str">
-        <f t="shared" ref="I98" si="20">IF(G98="","-",IF(G98&gt;H98,"L",IF(G98=H98,"E",IF(G98&lt;H98,"V"))))</f>
+        <f t="shared" ref="I98" si="25">IF(G98="","-",IF(G98&gt;H98,"L",IF(G98=H98,"E",IF(G98&lt;H98,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J98" s="26" t="s">
@@ -15477,7 +15445,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="115"/>
       <c r="B99" s="131"/>
       <c r="C99" s="131"/>
@@ -15599,7 +15567,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="115"/>
       <c r="B100" s="130">
         <v>46199</v>
@@ -15619,7 +15587,7 @@
       <c r="G100" s="119"/>
       <c r="H100" s="119"/>
       <c r="I100" s="121" t="str">
-        <f t="shared" ref="I100" si="21">IF(G100="","-",IF(G100&gt;H100,"L",IF(G100=H100,"E",IF(G100&lt;H100,"V"))))</f>
+        <f t="shared" ref="I100" si="26">IF(G100="","-",IF(G100&gt;H100,"L",IF(G100=H100,"E",IF(G100&lt;H100,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J100" s="27" t="s">
@@ -15734,7 +15702,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="115"/>
       <c r="B101" s="131"/>
       <c r="C101" s="131"/>
@@ -15856,7 +15824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="115"/>
       <c r="B102" s="130">
         <v>46199</v>
@@ -15876,7 +15844,7 @@
       <c r="G102" s="119"/>
       <c r="H102" s="119"/>
       <c r="I102" s="121" t="str">
-        <f t="shared" ref="I102" si="22">IF(G102="","-",IF(G102&gt;H102,"L",IF(G102=H102,"E",IF(G102&lt;H102,"V"))))</f>
+        <f t="shared" ref="I102" si="27">IF(G102="","-",IF(G102&gt;H102,"L",IF(G102=H102,"E",IF(G102&lt;H102,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J102" s="26" t="s">
@@ -15991,7 +15959,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="116"/>
       <c r="B103" s="131"/>
       <c r="C103" s="131"/>
@@ -16113,7 +16081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="125" t="s">
         <v>50</v>
       </c>
@@ -16250,7 +16218,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="103"/>
       <c r="B105" s="133"/>
       <c r="C105" s="133"/>
@@ -16372,7 +16340,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="103"/>
       <c r="B106" s="132">
         <v>46189</v>
@@ -16392,7 +16360,7 @@
       <c r="G106" s="113"/>
       <c r="H106" s="113"/>
       <c r="I106" s="112" t="str">
-        <f t="shared" ref="I106" si="23">IF(G106="","-",IF(G106&gt;H106,"L",IF(G106=H106,"E",IF(G106&lt;H106,"V"))))</f>
+        <f t="shared" ref="I106" si="28">IF(G106="","-",IF(G106&gt;H106,"L",IF(G106=H106,"E",IF(G106&lt;H106,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J106" s="26" t="s">
@@ -16507,7 +16475,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="103"/>
       <c r="B107" s="133"/>
       <c r="C107" s="133"/>
@@ -16629,7 +16597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="103"/>
       <c r="B108" s="132">
         <v>46195</v>
@@ -16649,7 +16617,7 @@
       <c r="G108" s="113"/>
       <c r="H108" s="113"/>
       <c r="I108" s="112" t="str">
-        <f t="shared" ref="I108" si="24">IF(G108="","-",IF(G108&gt;H108,"L",IF(G108=H108,"E",IF(G108&lt;H108,"V"))))</f>
+        <f t="shared" ref="I108" si="29">IF(G108="","-",IF(G108&gt;H108,"L",IF(G108=H108,"E",IF(G108&lt;H108,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J108" s="23" t="s">
@@ -16764,7 +16732,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="103"/>
       <c r="B109" s="133"/>
       <c r="C109" s="133"/>
@@ -16886,7 +16854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="103"/>
       <c r="B110" s="132">
         <v>46195</v>
@@ -16906,7 +16874,7 @@
       <c r="G110" s="113"/>
       <c r="H110" s="113"/>
       <c r="I110" s="112" t="str">
-        <f t="shared" ref="I110" si="25">IF(G110="","-",IF(G110&gt;H110,"L",IF(G110=H110,"E",IF(G110&lt;H110,"V"))))</f>
+        <f t="shared" ref="I110" si="30">IF(G110="","-",IF(G110&gt;H110,"L",IF(G110=H110,"E",IF(G110&lt;H110,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J110" s="26" t="s">
@@ -17021,7 +16989,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="103"/>
       <c r="B111" s="133"/>
       <c r="C111" s="133"/>
@@ -17143,7 +17111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="103"/>
       <c r="B112" s="132">
         <v>46199</v>
@@ -17163,7 +17131,7 @@
       <c r="G112" s="113"/>
       <c r="H112" s="113"/>
       <c r="I112" s="112" t="str">
-        <f t="shared" ref="I112" si="26">IF(G112="","-",IF(G112&gt;H112,"L",IF(G112=H112,"E",IF(G112&lt;H112,"V"))))</f>
+        <f t="shared" ref="I112" si="31">IF(G112="","-",IF(G112&gt;H112,"L",IF(G112=H112,"E",IF(G112&lt;H112,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J112" s="23" t="s">
@@ -17278,7 +17246,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="103"/>
       <c r="B113" s="133"/>
       <c r="C113" s="133"/>
@@ -17400,7 +17368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="103"/>
       <c r="B114" s="132">
         <v>46199</v>
@@ -17420,7 +17388,7 @@
       <c r="G114" s="113"/>
       <c r="H114" s="113"/>
       <c r="I114" s="112" t="str">
-        <f t="shared" ref="I114" si="27">IF(G114="","-",IF(G114&gt;H114,"L",IF(G114=H114,"E",IF(G114&lt;H114,"V"))))</f>
+        <f t="shared" ref="I114" si="32">IF(G114="","-",IF(G114&gt;H114,"L",IF(G114=H114,"E",IF(G114&lt;H114,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J114" s="26" t="s">
@@ -17535,7 +17503,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="104"/>
       <c r="B115" s="133"/>
       <c r="C115" s="133"/>
@@ -17657,7 +17625,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="114" t="s">
         <v>51</v>
       </c>
@@ -17679,7 +17647,7 @@
       <c r="G116" s="119"/>
       <c r="H116" s="119"/>
       <c r="I116" s="121" t="str">
-        <f t="shared" ref="I116" si="28">IF(G116="","-",IF(G116&gt;H116,"L",IF(G116=H116,"E",IF(G116&lt;H116,"V"))))</f>
+        <f t="shared" ref="I116" si="33">IF(G116="","-",IF(G116&gt;H116,"L",IF(G116=H116,"E",IF(G116&lt;H116,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J116" s="27" t="s">
@@ -17794,7 +17762,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="115"/>
       <c r="B117" s="131"/>
       <c r="C117" s="131"/>
@@ -17916,7 +17884,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="115"/>
       <c r="B118" s="130">
         <v>46189</v>
@@ -17936,7 +17904,7 @@
       <c r="G118" s="119"/>
       <c r="H118" s="119"/>
       <c r="I118" s="121" t="str">
-        <f t="shared" ref="I118" si="29">IF(G118="","-",IF(G118&gt;H118,"L",IF(G118=H118,"E",IF(G118&lt;H118,"V"))))</f>
+        <f t="shared" ref="I118" si="34">IF(G118="","-",IF(G118&gt;H118,"L",IF(G118=H118,"E",IF(G118&lt;H118,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J118" s="26" t="s">
@@ -18051,7 +18019,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="115"/>
       <c r="B119" s="131"/>
       <c r="C119" s="131"/>
@@ -18173,7 +18141,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="115"/>
       <c r="B120" s="130">
         <v>46195</v>
@@ -18193,7 +18161,7 @@
       <c r="G120" s="119"/>
       <c r="H120" s="119"/>
       <c r="I120" s="121" t="str">
-        <f t="shared" ref="I120" si="30">IF(G120="","-",IF(G120&gt;H120,"L",IF(G120=H120,"E",IF(G120&lt;H120,"V"))))</f>
+        <f t="shared" ref="I120" si="35">IF(G120="","-",IF(G120&gt;H120,"L",IF(G120=H120,"E",IF(G120&lt;H120,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J120" s="27" t="s">
@@ -18308,7 +18276,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="121" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="115"/>
       <c r="B121" s="131"/>
       <c r="C121" s="131"/>
@@ -18430,7 +18398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="115"/>
       <c r="B122" s="130">
         <v>46195</v>
@@ -18450,7 +18418,7 @@
       <c r="G122" s="119"/>
       <c r="H122" s="119"/>
       <c r="I122" s="121" t="str">
-        <f t="shared" ref="I122" si="31">IF(G122="","-",IF(G122&gt;H122,"L",IF(G122=H122,"E",IF(G122&lt;H122,"V"))))</f>
+        <f t="shared" ref="I122" si="36">IF(G122="","-",IF(G122&gt;H122,"L",IF(G122=H122,"E",IF(G122&lt;H122,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J122" s="26" t="s">
@@ -18565,7 +18533,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="115"/>
       <c r="B123" s="131"/>
       <c r="C123" s="131"/>
@@ -18687,7 +18655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="115"/>
       <c r="B124" s="130">
         <v>46200</v>
@@ -18707,7 +18675,7 @@
       <c r="G124" s="119"/>
       <c r="H124" s="119"/>
       <c r="I124" s="121" t="str">
-        <f t="shared" ref="I124" si="32">IF(G124="","-",IF(G124&gt;H124,"L",IF(G124=H124,"E",IF(G124&lt;H124,"V"))))</f>
+        <f t="shared" ref="I124" si="37">IF(G124="","-",IF(G124&gt;H124,"L",IF(G124=H124,"E",IF(G124&lt;H124,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J124" s="27" t="s">
@@ -18822,7 +18790,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="125" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="115"/>
       <c r="B125" s="131"/>
       <c r="C125" s="131"/>
@@ -18944,7 +18912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="115"/>
       <c r="B126" s="130">
         <v>46200</v>
@@ -18964,7 +18932,7 @@
       <c r="G126" s="119"/>
       <c r="H126" s="119"/>
       <c r="I126" s="121" t="str">
-        <f t="shared" ref="I126" si="33">IF(G126="","-",IF(G126&gt;H126,"L",IF(G126=H126,"E",IF(G126&lt;H126,"V"))))</f>
+        <f t="shared" ref="I126" si="38">IF(G126="","-",IF(G126&gt;H126,"L",IF(G126=H126,"E",IF(G126&lt;H126,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J126" s="26" t="s">
@@ -19079,7 +19047,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="116"/>
       <c r="B127" s="131"/>
       <c r="C127" s="131"/>
@@ -19201,7 +19169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="125" t="s">
         <v>52</v>
       </c>
@@ -19338,7 +19306,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="103"/>
       <c r="B129" s="133"/>
       <c r="C129" s="133"/>
@@ -19460,7 +19428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="103"/>
       <c r="B130" s="132">
         <v>46190</v>
@@ -19480,7 +19448,7 @@
       <c r="G130" s="113"/>
       <c r="H130" s="113"/>
       <c r="I130" s="112" t="str">
-        <f t="shared" ref="I130" si="34">IF(G130="","-",IF(G130&gt;H130,"L",IF(G130=H130,"E",IF(G130&lt;H130,"V"))))</f>
+        <f t="shared" ref="I130" si="39">IF(G130="","-",IF(G130&gt;H130,"L",IF(G130=H130,"E",IF(G130&lt;H130,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J130" s="26" t="s">
@@ -19595,7 +19563,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="103"/>
       <c r="B131" s="133"/>
       <c r="C131" s="133"/>
@@ -19717,7 +19685,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="103"/>
       <c r="B132" s="132">
         <v>46196</v>
@@ -19737,7 +19705,7 @@
       <c r="G132" s="113"/>
       <c r="H132" s="113"/>
       <c r="I132" s="112" t="str">
-        <f t="shared" ref="I132" si="35">IF(G132="","-",IF(G132&gt;H132,"L",IF(G132=H132,"E",IF(G132&lt;H132,"V"))))</f>
+        <f t="shared" ref="I132" si="40">IF(G132="","-",IF(G132&gt;H132,"L",IF(G132=H132,"E",IF(G132&lt;H132,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J132" s="23" t="s">
@@ -19852,7 +19820,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="133" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="103"/>
       <c r="B133" s="133"/>
       <c r="C133" s="133"/>
@@ -19974,7 +19942,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="103"/>
       <c r="B134" s="132">
         <v>46196</v>
@@ -19994,7 +19962,7 @@
       <c r="G134" s="113"/>
       <c r="H134" s="113"/>
       <c r="I134" s="112" t="str">
-        <f t="shared" ref="I134" si="36">IF(G134="","-",IF(G134&gt;H134,"L",IF(G134=H134,"E",IF(G134&lt;H134,"V"))))</f>
+        <f t="shared" ref="I134" si="41">IF(G134="","-",IF(G134&gt;H134,"L",IF(G134=H134,"E",IF(G134&lt;H134,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J134" s="26" t="s">
@@ -20109,7 +20077,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="135" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="103"/>
       <c r="B135" s="133"/>
       <c r="C135" s="133"/>
@@ -20231,7 +20199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="103"/>
       <c r="B136" s="132">
         <v>46200</v>
@@ -20251,7 +20219,7 @@
       <c r="G136" s="113"/>
       <c r="H136" s="113"/>
       <c r="I136" s="112" t="str">
-        <f t="shared" ref="I136" si="37">IF(G136="","-",IF(G136&gt;H136,"L",IF(G136=H136,"E",IF(G136&lt;H136,"V"))))</f>
+        <f t="shared" ref="I136" si="42">IF(G136="","-",IF(G136&gt;H136,"L",IF(G136=H136,"E",IF(G136&lt;H136,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J136" s="23" t="s">
@@ -20366,7 +20334,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="137" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="103"/>
       <c r="B137" s="133"/>
       <c r="C137" s="133"/>
@@ -20488,7 +20456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="103"/>
       <c r="B138" s="132">
         <v>46200</v>
@@ -20508,7 +20476,7 @@
       <c r="G138" s="113"/>
       <c r="H138" s="113"/>
       <c r="I138" s="112" t="str">
-        <f t="shared" ref="I138" si="38">IF(G138="","-",IF(G138&gt;H138,"L",IF(G138=H138,"E",IF(G138&lt;H138,"V"))))</f>
+        <f t="shared" ref="I138" si="43">IF(G138="","-",IF(G138&gt;H138,"L",IF(G138=H138,"E",IF(G138&lt;H138,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J138" s="26" t="s">
@@ -20623,7 +20591,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="104"/>
       <c r="B139" s="133"/>
       <c r="C139" s="133"/>
@@ -20745,7 +20713,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="114" t="s">
         <v>7</v>
       </c>
@@ -20767,7 +20735,7 @@
       <c r="G140" s="119"/>
       <c r="H140" s="119"/>
       <c r="I140" s="121" t="str">
-        <f t="shared" ref="I140" si="39">IF(G140="","-",IF(G140&gt;H140,"L",IF(G140=H140,"E",IF(G140&lt;H140,"V"))))</f>
+        <f t="shared" ref="I140" si="44">IF(G140="","-",IF(G140&gt;H140,"L",IF(G140=H140,"E",IF(G140&lt;H140,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J140" s="27" t="s">
@@ -20882,7 +20850,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="141" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="115"/>
       <c r="B141" s="131"/>
       <c r="C141" s="131"/>
@@ -21004,7 +20972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="115"/>
       <c r="B142" s="130">
         <v>46190</v>
@@ -21024,7 +20992,7 @@
       <c r="G142" s="119"/>
       <c r="H142" s="119"/>
       <c r="I142" s="121" t="str">
-        <f t="shared" ref="I142" si="40">IF(G142="","-",IF(G142&gt;H142,"L",IF(G142=H142,"E",IF(G142&lt;H142,"V"))))</f>
+        <f t="shared" ref="I142" si="45">IF(G142="","-",IF(G142&gt;H142,"L",IF(G142=H142,"E",IF(G142&lt;H142,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J142" s="26" t="s">
@@ -21139,7 +21107,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="143" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="115"/>
       <c r="B143" s="131"/>
       <c r="C143" s="131"/>
@@ -21261,7 +21229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="115"/>
       <c r="B144" s="130">
         <v>46196</v>
@@ -21281,7 +21249,7 @@
       <c r="G144" s="119"/>
       <c r="H144" s="119"/>
       <c r="I144" s="121" t="str">
-        <f t="shared" ref="I144" si="41">IF(G144="","-",IF(G144&gt;H144,"L",IF(G144=H144,"E",IF(G144&lt;H144,"V"))))</f>
+        <f t="shared" ref="I144" si="46">IF(G144="","-",IF(G144&gt;H144,"L",IF(G144=H144,"E",IF(G144&lt;H144,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J144" s="27" t="s">
@@ -21396,7 +21364,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="145" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="115"/>
       <c r="B145" s="131"/>
       <c r="C145" s="131"/>
@@ -21518,7 +21486,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="115"/>
       <c r="B146" s="130">
         <v>46196</v>
@@ -21538,7 +21506,7 @@
       <c r="G146" s="119"/>
       <c r="H146" s="119"/>
       <c r="I146" s="121" t="str">
-        <f t="shared" ref="I146" si="42">IF(G146="","-",IF(G146&gt;H146,"L",IF(G146=H146,"E",IF(G146&lt;H146,"V"))))</f>
+        <f t="shared" ref="I146" si="47">IF(G146="","-",IF(G146&gt;H146,"L",IF(G146=H146,"E",IF(G146&lt;H146,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J146" s="26" t="s">
@@ -21653,7 +21621,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="115"/>
       <c r="B147" s="131"/>
       <c r="C147" s="131"/>
@@ -21775,7 +21743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="115"/>
       <c r="B148" s="130">
         <v>46200</v>
@@ -21795,7 +21763,7 @@
       <c r="G148" s="119"/>
       <c r="H148" s="119"/>
       <c r="I148" s="121" t="str">
-        <f t="shared" ref="I148" si="43">IF(G148="","-",IF(G148&gt;H148,"L",IF(G148=H148,"E",IF(G148&lt;H148,"V"))))</f>
+        <f t="shared" ref="I148" si="48">IF(G148="","-",IF(G148&gt;H148,"L",IF(G148=H148,"E",IF(G148&lt;H148,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J148" s="27" t="s">
@@ -21910,7 +21878,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="149" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="115"/>
       <c r="B149" s="131"/>
       <c r="C149" s="131"/>
@@ -22032,7 +22000,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="115"/>
       <c r="B150" s="130">
         <v>46200</v>
@@ -22052,7 +22020,7 @@
       <c r="G150" s="119"/>
       <c r="H150" s="119"/>
       <c r="I150" s="121" t="str">
-        <f t="shared" ref="I150" si="44">IF(G150="","-",IF(G150&gt;H150,"L",IF(G150=H150,"E",IF(G150&lt;H150,"V"))))</f>
+        <f t="shared" ref="I150" si="49">IF(G150="","-",IF(G150&gt;H150,"L",IF(G150=H150,"E",IF(G150&lt;H150,"V"))))</f>
         <v>-</v>
       </c>
       <c r="J150" s="26" t="s">
@@ -22167,7 +22135,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="151" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="116"/>
       <c r="B151" s="131"/>
       <c r="C151" s="131"/>
@@ -22289,7 +22257,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F152" s="134" t="s">
         <v>10</v>
       </c>
@@ -22300,155 +22268,155 @@
         <v>38</v>
       </c>
       <c r="J152" s="51">
-        <f>SUM(J79,J77,J75,J73,J71,J69,J67,J65,J63,J61,J59,J57,J55,J53,J51,J49,J47,J45,J43,J41,J39,J37,J35,J33,J31,J29,J27,J25,J23,J21,J19,J17,J15,J13,J11,J9,J81,J83,J85,J87,J89,J91,J93,J95,J97,J99,J101,J103,J105,J107,J109,J111,J113,J115,J117,J119,J121,J123,J125,J127,J129,J131,J133,J135,J137,J139,J141,J143,J145,J147,J149,J151)</f>
+        <f t="shared" ref="J152:AT152" si="50">SUM(J79,J77,J75,J73,J71,J69,J67,J65,J63,J61,J59,J57,J55,J53,J51,J49,J47,J45,J43,J41,J39,J37,J35,J33,J31,J29,J27,J25,J23,J21,J19,J17,J15,J13,J11,J9,J81,J83,J85,J87,J89,J91,J93,J95,J97,J99,J101,J103,J105,J107,J109,J111,J113,J115,J117,J119,J121,J123,J125,J127,J129,J131,J133,J135,J137,J139,J141,J143,J145,J147,J149,J151)</f>
         <v>175</v>
       </c>
       <c r="K152" s="15">
-        <f>SUM(K79,K77,K75,K73,K71,K69,K67,K65,K63,K61,K59,K57,K55,K53,K51,K49,K47,K45,K43,K41,K39,K37,K35,K33,K31,K29,K27,K25,K23,K21,K19,K17,K15,K13,K11,K9,K81,K83,K85,K87,K89,K91,K93,K95,K97,K99,K101,K103,K105,K107,K109,K111,K113,K115,K117,K119,K121,K123,K125,K127,K129,K131,K133,K135,K137,K139,K141,K143,K145,K147,K149,K151)</f>
+        <f t="shared" si="50"/>
         <v>169</v>
       </c>
       <c r="L152" s="15">
-        <f>SUM(L79,L77,L75,L73,L71,L69,L67,L65,L63,L61,L59,L57,L55,L53,L51,L49,L47,L45,L43,L41,L39,L37,L35,L33,L31,L29,L27,L25,L23,L21,L19,L17,L15,L13,L11,L9,L81,L83,L85,L87,L89,L91,L93,L95,L97,L99,L101,L103,L105,L107,L109,L111,L113,L115,L117,L119,L121,L123,L125,L127,L129,L131,L133,L135,L137,L139,L141,L143,L145,L147,L149,L151)</f>
+        <f t="shared" si="50"/>
         <v>181</v>
       </c>
       <c r="M152" s="15">
-        <f>SUM(M79,M77,M75,M73,M71,M69,M67,M65,M63,M61,M59,M57,M55,M53,M51,M49,M47,M45,M43,M41,M39,M37,M35,M33,M31,M29,M27,M25,M23,M21,M19,M17,M15,M13,M11,M9,M81,M83,M85,M87,M89,M91,M93,M95,M97,M99,M101,M103,M105,M107,M109,M111,M113,M115,M117,M119,M121,M123,M125,M127,M129,M131,M133,M135,M137,M139,M141,M143,M145,M147,M149,M151)</f>
+        <f t="shared" si="50"/>
         <v>172</v>
       </c>
       <c r="N152" s="15">
-        <f>SUM(N79,N77,N75,N73,N71,N69,N67,N65,N63,N61,N59,N57,N55,N53,N51,N49,N47,N45,N43,N41,N39,N37,N35,N33,N31,N29,N27,N25,N23,N21,N19,N17,N15,N13,N11,N9,N81,N83,N85,N87,N89,N91,N93,N95,N97,N99,N101,N103,N105,N107,N109,N111,N113,N115,N117,N119,N121,N123,N125,N127,N129,N131,N133,N135,N137,N139,N141,N143,N145,N147,N149,N151)</f>
+        <f t="shared" si="50"/>
         <v>190</v>
       </c>
       <c r="O152" s="15">
-        <f>SUM(O79,O77,O75,O73,O71,O69,O67,O65,O63,O61,O59,O57,O55,O53,O51,O49,O47,O45,O43,O41,O39,O37,O35,O33,O31,O29,O27,O25,O23,O21,O19,O17,O15,O13,O11,O9,O81,O83,O85,O87,O89,O91,O93,O95,O97,O99,O101,O103,O105,O107,O109,O111,O113,O115,O117,O119,O121,O123,O125,O127,O129,O131,O133,O135,O137,O139,O141,O143,O145,O147,O149,O151)</f>
+        <f t="shared" si="50"/>
         <v>201</v>
       </c>
       <c r="P152" s="15">
-        <f>SUM(P79,P77,P75,P73,P71,P69,P67,P65,P63,P61,P59,P57,P55,P53,P51,P49,P47,P45,P43,P41,P39,P37,P35,P33,P31,P29,P27,P25,P23,P21,P19,P17,P15,P13,P11,P9,P81,P83,P85,P87,P89,P91,P93,P95,P97,P99,P101,P103,P105,P107,P109,P111,P113,P115,P117,P119,P121,P123,P125,P127,P129,P131,P133,P135,P137,P139,P141,P143,P145,P147,P149,P151)</f>
+        <f t="shared" si="50"/>
         <v>162</v>
       </c>
       <c r="Q152" s="15">
-        <f>SUM(Q79,Q77,Q75,Q73,Q71,Q69,Q67,Q65,Q63,Q61,Q59,Q57,Q55,Q53,Q51,Q49,Q47,Q45,Q43,Q41,Q39,Q37,Q35,Q33,Q31,Q29,Q27,Q25,Q23,Q21,Q19,Q17,Q15,Q13,Q11,Q9,Q81,Q83,Q85,Q87,Q89,Q91,Q93,Q95,Q97,Q99,Q101,Q103,Q105,Q107,Q109,Q111,Q113,Q115,Q117,Q119,Q121,Q123,Q125,Q127,Q129,Q131,Q133,Q135,Q137,Q139,Q141,Q143,Q145,Q147,Q149,Q151)</f>
+        <f t="shared" si="50"/>
         <v>186</v>
       </c>
       <c r="R152" s="15">
-        <f>SUM(R79,R77,R75,R73,R71,R69,R67,R65,R63,R61,R59,R57,R55,R53,R51,R49,R47,R45,R43,R41,R39,R37,R35,R33,R31,R29,R27,R25,R23,R21,R19,R17,R15,R13,R11,R9,R81,R83,R85,R87,R89,R91,R93,R95,R97,R99,R101,R103,R105,R107,R109,R111,R113,R115,R117,R119,R121,R123,R125,R127,R129,R131,R133,R135,R137,R139,R141,R143,R145,R147,R149,R151)</f>
+        <f t="shared" si="50"/>
         <v>183</v>
       </c>
       <c r="S152" s="15">
-        <f>SUM(S79,S77,S75,S73,S71,S69,S67,S65,S63,S61,S59,S57,S55,S53,S51,S49,S47,S45,S43,S41,S39,S37,S35,S33,S31,S29,S27,S25,S23,S21,S19,S17,S15,S13,S11,S9,S81,S83,S85,S87,S89,S91,S93,S95,S97,S99,S101,S103,S105,S107,S109,S111,S113,S115,S117,S119,S121,S123,S125,S127,S129,S131,S133,S135,S137,S139,S141,S143,S145,S147,S149,S151)</f>
+        <f t="shared" si="50"/>
         <v>186</v>
       </c>
       <c r="T152" s="15">
-        <f>SUM(T79,T77,T75,T73,T71,T69,T67,T65,T63,T61,T59,T57,T55,T53,T51,T49,T47,T45,T43,T41,T39,T37,T35,T33,T31,T29,T27,T25,T23,T21,T19,T17,T15,T13,T11,T9,T81,T83,T85,T87,T89,T91,T93,T95,T97,T99,T101,T103,T105,T107,T109,T111,T113,T115,T117,T119,T121,T123,T125,T127,T129,T131,T133,T135,T137,T139,T141,T143,T145,T147,T149,T151)</f>
+        <f t="shared" si="50"/>
         <v>233</v>
       </c>
       <c r="U152" s="15">
-        <f>SUM(U79,U77,U75,U73,U71,U69,U67,U65,U63,U61,U59,U57,U55,U53,U51,U49,U47,U45,U43,U41,U39,U37,U35,U33,U31,U29,U27,U25,U23,U21,U19,U17,U15,U13,U11,U9,U81,U83,U85,U87,U89,U91,U93,U95,U97,U99,U101,U103,U105,U107,U109,U111,U113,U115,U117,U119,U121,U123,U125,U127,U129,U131,U133,U135,U137,U139,U141,U143,U145,U147,U149,U151)</f>
+        <f t="shared" si="50"/>
         <v>185</v>
       </c>
       <c r="V152" s="15">
-        <f>SUM(V79,V77,V75,V73,V71,V69,V67,V65,V63,V61,V59,V57,V55,V53,V51,V49,V47,V45,V43,V41,V39,V37,V35,V33,V31,V29,V27,V25,V23,V21,V19,V17,V15,V13,V11,V9,V81,V83,V85,V87,V89,V91,V93,V95,V97,V99,V101,V103,V105,V107,V109,V111,V113,V115,V117,V119,V121,V123,V125,V127,V129,V131,V133,V135,V137,V139,V141,V143,V145,V147,V149,V151)</f>
+        <f t="shared" si="50"/>
         <v>177</v>
       </c>
       <c r="W152" s="15">
-        <f>SUM(W79,W77,W75,W73,W71,W69,W67,W65,W63,W61,W59,W57,W55,W53,W51,W49,W47,W45,W43,W41,W39,W37,W35,W33,W31,W29,W27,W25,W23,W21,W19,W17,W15,W13,W11,W9,W81,W83,W85,W87,W89,W91,W93,W95,W97,W99,W101,W103,W105,W107,W109,W111,W113,W115,W117,W119,W121,W123,W125,W127,W129,W131,W133,W135,W137,W139,W141,W143,W145,W147,W149,W151)</f>
+        <f t="shared" si="50"/>
         <v>195</v>
       </c>
       <c r="X152" s="15">
-        <f>SUM(X79,X77,X75,X73,X71,X69,X67,X65,X63,X61,X59,X57,X55,X53,X51,X49,X47,X45,X43,X41,X39,X37,X35,X33,X31,X29,X27,X25,X23,X21,X19,X17,X15,X13,X11,X9,X81,X83,X85,X87,X89,X91,X93,X95,X97,X99,X101,X103,X105,X107,X109,X111,X113,X115,X117,X119,X121,X123,X125,X127,X129,X131,X133,X135,X137,X139,X141,X143,X145,X147,X149,X151)</f>
+        <f t="shared" si="50"/>
         <v>179</v>
       </c>
       <c r="Y152" s="15">
-        <f>SUM(Y79,Y77,Y75,Y73,Y71,Y69,Y67,Y65,Y63,Y61,Y59,Y57,Y55,Y53,Y51,Y49,Y47,Y45,Y43,Y41,Y39,Y37,Y35,Y33,Y31,Y29,Y27,Y25,Y23,Y21,Y19,Y17,Y15,Y13,Y11,Y9,Y81,Y83,Y85,Y87,Y89,Y91,Y93,Y95,Y97,Y99,Y101,Y103,Y105,Y107,Y109,Y111,Y113,Y115,Y117,Y119,Y121,Y123,Y125,Y127,Y129,Y131,Y133,Y135,Y137,Y139,Y141,Y143,Y145,Y147,Y149,Y151)</f>
+        <f t="shared" si="50"/>
         <v>190</v>
       </c>
       <c r="Z152" s="15">
-        <f>SUM(Z79,Z77,Z75,Z73,Z71,Z69,Z67,Z65,Z63,Z61,Z59,Z57,Z55,Z53,Z51,Z49,Z47,Z45,Z43,Z41,Z39,Z37,Z35,Z33,Z31,Z29,Z27,Z25,Z23,Z21,Z19,Z17,Z15,Z13,Z11,Z9,Z81,Z83,Z85,Z87,Z89,Z91,Z93,Z95,Z97,Z99,Z101,Z103,Z105,Z107,Z109,Z111,Z113,Z115,Z117,Z119,Z121,Z123,Z125,Z127,Z129,Z131,Z133,Z135,Z137,Z139,Z141,Z143,Z145,Z147,Z149,Z151)</f>
+        <f t="shared" si="50"/>
         <v>187</v>
       </c>
       <c r="AA152" s="15">
-        <f>SUM(AA79,AA77,AA75,AA73,AA71,AA69,AA67,AA65,AA63,AA61,AA59,AA57,AA55,AA53,AA51,AA49,AA47,AA45,AA43,AA41,AA39,AA37,AA35,AA33,AA31,AA29,AA27,AA25,AA23,AA21,AA19,AA17,AA15,AA13,AA11,AA9,AA81,AA83,AA85,AA87,AA89,AA91,AA93,AA95,AA97,AA99,AA101,AA103,AA105,AA107,AA109,AA111,AA113,AA115,AA117,AA119,AA121,AA123,AA125,AA127,AA129,AA131,AA133,AA135,AA137,AA139,AA141,AA143,AA145,AA147,AA149,AA151)</f>
+        <f t="shared" si="50"/>
         <v>222</v>
       </c>
       <c r="AB152" s="15">
-        <f>SUM(AB79,AB77,AB75,AB73,AB71,AB69,AB67,AB65,AB63,AB61,AB59,AB57,AB55,AB53,AB51,AB49,AB47,AB45,AB43,AB41,AB39,AB37,AB35,AB33,AB31,AB29,AB27,AB25,AB23,AB21,AB19,AB17,AB15,AB13,AB11,AB9,AB81,AB83,AB85,AB87,AB89,AB91,AB93,AB95,AB97,AB99,AB101,AB103,AB105,AB107,AB109,AB111,AB113,AB115,AB117,AB119,AB121,AB123,AB125,AB127,AB129,AB131,AB133,AB135,AB137,AB139,AB141,AB143,AB145,AB147,AB149,AB151)</f>
+        <f t="shared" si="50"/>
         <v>183</v>
       </c>
       <c r="AC152" s="15">
-        <f>SUM(AC79,AC77,AC75,AC73,AC71,AC69,AC67,AC65,AC63,AC61,AC59,AC57,AC55,AC53,AC51,AC49,AC47,AC45,AC43,AC41,AC39,AC37,AC35,AC33,AC31,AC29,AC27,AC25,AC23,AC21,AC19,AC17,AC15,AC13,AC11,AC9,AC81,AC83,AC85,AC87,AC89,AC91,AC93,AC95,AC97,AC99,AC101,AC103,AC105,AC107,AC109,AC111,AC113,AC115,AC117,AC119,AC121,AC123,AC125,AC127,AC129,AC131,AC133,AC135,AC137,AC139,AC141,AC143,AC145,AC147,AC149,AC151)</f>
+        <f t="shared" si="50"/>
         <v>194</v>
       </c>
       <c r="AD152" s="15">
-        <f>SUM(AD79,AD77,AD75,AD73,AD71,AD69,AD67,AD65,AD63,AD61,AD59,AD57,AD55,AD53,AD51,AD49,AD47,AD45,AD43,AD41,AD39,AD37,AD35,AD33,AD31,AD29,AD27,AD25,AD23,AD21,AD19,AD17,AD15,AD13,AD11,AD9,AD81,AD83,AD85,AD87,AD89,AD91,AD93,AD95,AD97,AD99,AD101,AD103,AD105,AD107,AD109,AD111,AD113,AD115,AD117,AD119,AD121,AD123,AD125,AD127,AD129,AD131,AD133,AD135,AD137,AD139,AD141,AD143,AD145,AD147,AD149,AD151)</f>
+        <f t="shared" si="50"/>
         <v>169</v>
       </c>
       <c r="AE152" s="15">
-        <f>SUM(AE79,AE77,AE75,AE73,AE71,AE69,AE67,AE65,AE63,AE61,AE59,AE57,AE55,AE53,AE51,AE49,AE47,AE45,AE43,AE41,AE39,AE37,AE35,AE33,AE31,AE29,AE27,AE25,AE23,AE21,AE19,AE17,AE15,AE13,AE11,AE9,AE81,AE83,AE85,AE87,AE89,AE91,AE93,AE95,AE97,AE99,AE101,AE103,AE105,AE107,AE109,AE111,AE113,AE115,AE117,AE119,AE121,AE123,AE125,AE127,AE129,AE131,AE133,AE135,AE137,AE139,AE141,AE143,AE145,AE147,AE149,AE151)</f>
+        <f t="shared" si="50"/>
         <v>167</v>
       </c>
       <c r="AF152" s="15">
-        <f>SUM(AF79,AF77,AF75,AF73,AF71,AF69,AF67,AF65,AF63,AF61,AF59,AF57,AF55,AF53,AF51,AF49,AF47,AF45,AF43,AF41,AF39,AF37,AF35,AF33,AF31,AF29,AF27,AF25,AF23,AF21,AF19,AF17,AF15,AF13,AF11,AF9,AF81,AF83,AF85,AF87,AF89,AF91,AF93,AF95,AF97,AF99,AF101,AF103,AF105,AF107,AF109,AF111,AF113,AF115,AF117,AF119,AF121,AF123,AF125,AF127,AF129,AF131,AF133,AF135,AF137,AF139,AF141,AF143,AF145,AF147,AF149,AF151)</f>
+        <f t="shared" si="50"/>
         <v>204</v>
       </c>
       <c r="AG152" s="15">
-        <f>SUM(AG79,AG77,AG75,AG73,AG71,AG69,AG67,AG65,AG63,AG61,AG59,AG57,AG55,AG53,AG51,AG49,AG47,AG45,AG43,AG41,AG39,AG37,AG35,AG33,AG31,AG29,AG27,AG25,AG23,AG21,AG19,AG17,AG15,AG13,AG11,AG9,AG81,AG83,AG85,AG87,AG89,AG91,AG93,AG95,AG97,AG99,AG101,AG103,AG105,AG107,AG109,AG111,AG113,AG115,AG117,AG119,AG121,AG123,AG125,AG127,AG129,AG131,AG133,AG135,AG137,AG139,AG141,AG143,AG145,AG147,AG149,AG151)</f>
+        <f t="shared" si="50"/>
         <v>163</v>
       </c>
       <c r="AH152" s="95">
-        <f>SUM(AH79,AH77,AH75,AH73,AH71,AH69,AH67,AH65,AH63,AH61,AH59,AH57,AH55,AH53,AH51,AH49,AH47,AH45,AH43,AH41,AH39,AH37,AH35,AH33,AH31,AH29,AH27,AH25,AH23,AH21,AH19,AH17,AH15,AH13,AH11,AH9,AH81,AH83,AH85,AH87,AH89,AH91,AH93,AH95,AH97,AH99,AH101,AH103,AH105,AH107,AH109,AH111,AH113,AH115,AH117,AH119,AH121,AH123,AH125,AH127,AH129,AH131,AH133,AH135,AH137,AH139,AH141,AH143,AH145,AH147,AH149,AH151)</f>
+        <f t="shared" si="50"/>
         <v>171</v>
       </c>
       <c r="AI152" s="15">
-        <f>SUM(AI79,AI77,AI75,AI73,AI71,AI69,AI67,AI65,AI63,AI61,AI59,AI57,AI55,AI53,AI51,AI49,AI47,AI45,AI43,AI41,AI39,AI37,AI35,AI33,AI31,AI29,AI27,AI25,AI23,AI21,AI19,AI17,AI15,AI13,AI11,AI9,AI81,AI83,AI85,AI87,AI89,AI91,AI93,AI95,AI97,AI99,AI101,AI103,AI105,AI107,AI109,AI111,AI113,AI115,AI117,AI119,AI121,AI123,AI125,AI127,AI129,AI131,AI133,AI135,AI137,AI139,AI141,AI143,AI145,AI147,AI149,AI151)</f>
+        <f t="shared" si="50"/>
         <v>220</v>
       </c>
       <c r="AJ152" s="15">
-        <f>SUM(AJ79,AJ77,AJ75,AJ73,AJ71,AJ69,AJ67,AJ65,AJ63,AJ61,AJ59,AJ57,AJ55,AJ53,AJ51,AJ49,AJ47,AJ45,AJ43,AJ41,AJ39,AJ37,AJ35,AJ33,AJ31,AJ29,AJ27,AJ25,AJ23,AJ21,AJ19,AJ17,AJ15,AJ13,AJ11,AJ9,AJ81,AJ83,AJ85,AJ87,AJ89,AJ91,AJ93,AJ95,AJ97,AJ99,AJ101,AJ103,AJ105,AJ107,AJ109,AJ111,AJ113,AJ115,AJ117,AJ119,AJ121,AJ123,AJ125,AJ127,AJ129,AJ131,AJ133,AJ135,AJ137,AJ139,AJ141,AJ143,AJ145,AJ147,AJ149,AJ151)</f>
+        <f t="shared" si="50"/>
         <v>154</v>
       </c>
       <c r="AK152" s="15">
-        <f>SUM(AK79,AK77,AK75,AK73,AK71,AK69,AK67,AK65,AK63,AK61,AK59,AK57,AK55,AK53,AK51,AK49,AK47,AK45,AK43,AK41,AK39,AK37,AK35,AK33,AK31,AK29,AK27,AK25,AK23,AK21,AK19,AK17,AK15,AK13,AK11,AK9,AK81,AK83,AK85,AK87,AK89,AK91,AK93,AK95,AK97,AK99,AK101,AK103,AK105,AK107,AK109,AK111,AK113,AK115,AK117,AK119,AK121,AK123,AK125,AK127,AK129,AK131,AK133,AK135,AK137,AK139,AK141,AK143,AK145,AK147,AK149,AK151)</f>
+        <f t="shared" si="50"/>
         <v>190</v>
       </c>
       <c r="AL152" s="15">
-        <f>SUM(AL79,AL77,AL75,AL73,AL71,AL69,AL67,AL65,AL63,AL61,AL59,AL57,AL55,AL53,AL51,AL49,AL47,AL45,AL43,AL41,AL39,AL37,AL35,AL33,AL31,AL29,AL27,AL25,AL23,AL21,AL19,AL17,AL15,AL13,AL11,AL9,AL81,AL83,AL85,AL87,AL89,AL91,AL93,AL95,AL97,AL99,AL101,AL103,AL105,AL107,AL109,AL111,AL113,AL115,AL117,AL119,AL121,AL123,AL125,AL127,AL129,AL131,AL133,AL135,AL137,AL139,AL141,AL143,AL145,AL147,AL149,AL151)</f>
+        <f t="shared" si="50"/>
         <v>177</v>
       </c>
       <c r="AM152" s="15">
-        <f>SUM(AM79,AM77,AM75,AM73,AM71,AM69,AM67,AM65,AM63,AM61,AM59,AM57,AM55,AM53,AM51,AM49,AM47,AM45,AM43,AM41,AM39,AM37,AM35,AM33,AM31,AM29,AM27,AM25,AM23,AM21,AM19,AM17,AM15,AM13,AM11,AM9,AM81,AM83,AM85,AM87,AM89,AM91,AM93,AM95,AM97,AM99,AM101,AM103,AM105,AM107,AM109,AM111,AM113,AM115,AM117,AM119,AM121,AM123,AM125,AM127,AM129,AM131,AM133,AM135,AM137,AM139,AM141,AM143,AM145,AM147,AM149,AM151)</f>
+        <f t="shared" si="50"/>
         <v>159</v>
       </c>
       <c r="AN152" s="15">
-        <f>SUM(AN79,AN77,AN75,AN73,AN71,AN69,AN67,AN65,AN63,AN61,AN59,AN57,AN55,AN53,AN51,AN49,AN47,AN45,AN43,AN41,AN39,AN37,AN35,AN33,AN31,AN29,AN27,AN25,AN23,AN21,AN19,AN17,AN15,AN13,AN11,AN9,AN81,AN83,AN85,AN87,AN89,AN91,AN93,AN95,AN97,AN99,AN101,AN103,AN105,AN107,AN109,AN111,AN113,AN115,AN117,AN119,AN121,AN123,AN125,AN127,AN129,AN131,AN133,AN135,AN137,AN139,AN141,AN143,AN145,AN147,AN149,AN151)</f>
+        <f t="shared" si="50"/>
         <v>170</v>
       </c>
       <c r="AO152" s="15">
-        <f>SUM(AO79,AO77,AO75,AO73,AO71,AO69,AO67,AO65,AO63,AO61,AO59,AO57,AO55,AO53,AO51,AO49,AO47,AO45,AO43,AO41,AO39,AO37,AO35,AO33,AO31,AO29,AO27,AO25,AO23,AO21,AO19,AO17,AO15,AO13,AO11,AO9,AO81,AO83,AO85,AO87,AO89,AO91,AO93,AO95,AO97,AO99,AO101,AO103,AO105,AO107,AO109,AO111,AO113,AO115,AO117,AO119,AO121,AO123,AO125,AO127,AO129,AO131,AO133,AO135,AO137,AO139,AO141,AO143,AO145,AO147,AO149,AO151)</f>
+        <f t="shared" si="50"/>
         <v>169</v>
       </c>
       <c r="AP152" s="15">
-        <f>SUM(AP79,AP77,AP75,AP73,AP71,AP69,AP67,AP65,AP63,AP61,AP59,AP57,AP55,AP53,AP51,AP49,AP47,AP45,AP43,AP41,AP39,AP37,AP35,AP33,AP31,AP29,AP27,AP25,AP23,AP21,AP19,AP17,AP15,AP13,AP11,AP9,AP81,AP83,AP85,AP87,AP89,AP91,AP93,AP95,AP97,AP99,AP101,AP103,AP105,AP107,AP109,AP111,AP113,AP115,AP117,AP119,AP121,AP123,AP125,AP127,AP129,AP131,AP133,AP135,AP137,AP139,AP141,AP143,AP145,AP147,AP149,AP151)</f>
+        <f t="shared" si="50"/>
         <v>231</v>
       </c>
       <c r="AQ152" s="15">
-        <f>SUM(AQ79,AQ77,AQ75,AQ73,AQ71,AQ69,AQ67,AQ65,AQ63,AQ61,AQ59,AQ57,AQ55,AQ53,AQ51,AQ49,AQ47,AQ45,AQ43,AQ41,AQ39,AQ37,AQ35,AQ33,AQ31,AQ29,AQ27,AQ25,AQ23,AQ21,AQ19,AQ17,AQ15,AQ13,AQ11,AQ9,AQ81,AQ83,AQ85,AQ87,AQ89,AQ91,AQ93,AQ95,AQ97,AQ99,AQ101,AQ103,AQ105,AQ107,AQ109,AQ111,AQ113,AQ115,AQ117,AQ119,AQ121,AQ123,AQ125,AQ127,AQ129,AQ131,AQ133,AQ135,AQ137,AQ139,AQ141,AQ143,AQ145,AQ147,AQ149,AQ151)</f>
+        <f t="shared" si="50"/>
         <v>237</v>
       </c>
       <c r="AR152" s="15">
-        <f>SUM(AR79,AR77,AR75,AR73,AR71,AR69,AR67,AR65,AR63,AR61,AR59,AR57,AR55,AR53,AR51,AR49,AR47,AR45,AR43,AR41,AR39,AR37,AR35,AR33,AR31,AR29,AR27,AR25,AR23,AR21,AR19,AR17,AR15,AR13,AR11,AR9,AR81,AR83,AR85,AR87,AR89,AR91,AR93,AR95,AR97,AR99,AR101,AR103,AR105,AR107,AR109,AR111,AR113,AR115,AR117,AR119,AR121,AR123,AR125,AR127,AR129,AR131,AR133,AR135,AR137,AR139,AR141,AR143,AR145,AR147,AR149,AR151)</f>
+        <f t="shared" si="50"/>
         <v>167</v>
       </c>
       <c r="AS152" s="15">
-        <f>SUM(AS79,AS77,AS75,AS73,AS71,AS69,AS67,AS65,AS63,AS61,AS59,AS57,AS55,AS53,AS51,AS49,AS47,AS45,AS43,AS41,AS39,AS37,AS35,AS33,AS31,AS29,AS27,AS25,AS23,AS21,AS19,AS17,AS15,AS13,AS11,AS9,AS81,AS83,AS85,AS87,AS89,AS91,AS93,AS95,AS97,AS99,AS101,AS103,AS105,AS107,AS109,AS111,AS113,AS115,AS117,AS119,AS121,AS123,AS125,AS127,AS129,AS131,AS133,AS135,AS137,AS139,AS141,AS143,AS145,AS147,AS149,AS151)</f>
+        <f t="shared" si="50"/>
         <v>208</v>
       </c>
       <c r="AT152" s="30">
-        <f>SUM(AT79,AT77,AT75,AT73,AT71,AT69,AT67,AT65,AT63,AT61,AT59,AT57,AT55,AT53,AT51,AT49,AT47,AT45,AT43,AT41,AT39,AT37,AT35,AT33,AT31,AT29,AT27,AT25,AT23,AT21,AT19,AT17,AT15,AT13,AT11,AT9,AT81,AT83,AT85,AT87,AT89,AT91,AT93,AT95,AT97,AT99,AT101,AT103,AT105,AT107,AT109,AT111,AT113,AT115,AT117,AT119,AT121,AT123,AT125,AT127,AT129,AT131,AT133,AT135,AT137,AT139,AT141,AT143,AT145,AT147,AT149,AT151)</f>
+        <f t="shared" si="50"/>
         <v>227</v>
       </c>
     </row>
-    <row r="153" spans="1:46" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:46" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F153" s="135" t="s">
         <v>14</v>
       </c>
@@ -22456,155 +22424,155 @@
       <c r="H153" s="135"/>
       <c r="I153" s="135"/>
       <c r="J153" s="31">
-        <f>SUM(J154:J157)</f>
+        <f t="shared" ref="J153:AT153" si="51">SUM(J154:J157)</f>
         <v>0</v>
       </c>
       <c r="K153" s="32">
-        <f>SUM(K154:K157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="L153" s="32">
-        <f>SUM(L154:L157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M153" s="32">
-        <f>SUM(M154:M157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="N153" s="32">
-        <f>SUM(N154:N157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="O153" s="32">
-        <f>SUM(O154:O157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="P153" s="32">
-        <f>SUM(P154:P157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="Q153" s="32">
-        <f>SUM(Q154:Q157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="R153" s="32">
-        <f>SUM(R154:R157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="S153" s="32">
-        <f>SUM(S154:S157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="T153" s="32">
-        <f>SUM(T154:T157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="U153" s="32">
-        <f>SUM(U154:U157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="V153" s="32">
-        <f>SUM(V154:V157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="W153" s="32">
-        <f>SUM(W154:W157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="X153" s="32">
-        <f>SUM(X154:X157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="Y153" s="32">
-        <f>SUM(Y154:Y157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="Z153" s="32">
-        <f>SUM(Z154:Z157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AA153" s="32">
-        <f>SUM(AA154:AA157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AB153" s="32">
-        <f>SUM(AB154:AB157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AC153" s="32">
-        <f>SUM(AC154:AC157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AD153" s="32">
-        <f>SUM(AD154:AD157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AE153" s="32">
-        <f>SUM(AE154:AE157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AF153" s="32">
-        <f>SUM(AF154:AF157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AG153" s="32">
-        <f>SUM(AG154:AG157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AH153" s="32">
-        <f>SUM(AH154:AH157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AI153" s="32">
-        <f>SUM(AI154:AI157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AJ153" s="32">
-        <f>SUM(AJ154:AJ157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AK153" s="32">
-        <f>SUM(AK154:AK157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AL153" s="32">
-        <f>SUM(AL154:AL157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AM153" s="32">
-        <f>SUM(AM154:AM157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AN153" s="32">
-        <f>SUM(AN154:AN157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AO153" s="32">
-        <f>SUM(AO154:AO157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AP153" s="32">
-        <f>SUM(AP154:AP157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AQ153" s="32">
-        <f>SUM(AQ154:AQ157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AR153" s="32">
-        <f>SUM(AR154:AR157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AS153" s="32">
-        <f>SUM(AS154:AS157)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AT153" s="33">
-        <f>SUM(AT154:AT157)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:46" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:46" ht="19.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="F154" s="57"/>
       <c r="G154" s="3"/>
       <c r="H154" s="3"/>
@@ -22614,151 +22582,151 @@
         <v>0</v>
       </c>
       <c r="K154" s="4">
-        <f t="shared" ref="K154:AL154" si="45">IF(K152=$I$152,100,IF($I$152-K152=1,99,IF($I$152-K152=-1,99,IF($I$152-K152=2,98,IF($I$152-K152=-2,98,IF($I$152-K152=3,97,IF($I$152-K152=-3,97,IF($I$152-K152=4,96,IF($I$152-K152=-4,96,IF($I$152-K152=5,95,IF($I$152-K152=-5,95,IF($I$152-K152=6,94,IF($I$152-K152=-6,94,IF($I$152-K152=7,93,IF($I$152-K152=-7,93,IF($I$152-K152=8,92,IF($I$152-K152=-8,92,IF($I$152-K152=9,91,IF($I$152-K152=-9,91,IF($I$152-K152=10,90,IF($I$152-K152=-10,90,IF($I$152-K152=11,89,IF($I$152-K152=-11,89,IF($I$152-K152=12,88,IF($I$152-K152=-12,88,IF($I$152-K152=13,87,IF($I$152-K152=-13,87,IF($I$152-K152=14,86,IF($I$152-K152=-14,86,IF($I$152-K152=15,85,IF($I$152-K152=-15,85,IF($I$152-K152=16,84,IF($I$152-K152=-16,84,IF($I$152-K152=17,83,IF($I$152-K152=-17,83,IF($I$152-K152=18,82,IF($I$152-K152=-18,82,IF($I$152-K152=19,81,IF($I$152-K152=-19,81,IF($I$152-K152=20,80,IF($I$152-K152=-20,80,IF($I$152-K152=21,79,IF($I$152-K152=-21,79,IF($I$152-K152=22,78,IF($I$152-K152=-22,78,IF($I$152-K152=23,77,IF($I$152-K152=-23,77,IF($I$152-K152=24,76,IF($I$152-K152=-24,76,IF($I$152-K152=25,75,IF($I$152-K152=-25,75,IF($I$152-K152=26,74,IF($I$152-K152=-26,74,IF($I$152-K152=27,73,IF($I$152-K152=-27,73,IF($I$152-K152=28,72,IF($I$152-K152=-28,72,IF($I$152-K152=29,71,IF($I$152-K152=-29,71,IF($I$152-K152=30,70,IF($I$152-K152=-30,70,IF($I$152-K152=31,69,IF($I$152-K152=-31,69,IF($I$152-K152=32,68,IF($I$152-K152=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="K154:AL154" si="52">IF(K152=$I$152,100,IF($I$152-K152=1,99,IF($I$152-K152=-1,99,IF($I$152-K152=2,98,IF($I$152-K152=-2,98,IF($I$152-K152=3,97,IF($I$152-K152=-3,97,IF($I$152-K152=4,96,IF($I$152-K152=-4,96,IF($I$152-K152=5,95,IF($I$152-K152=-5,95,IF($I$152-K152=6,94,IF($I$152-K152=-6,94,IF($I$152-K152=7,93,IF($I$152-K152=-7,93,IF($I$152-K152=8,92,IF($I$152-K152=-8,92,IF($I$152-K152=9,91,IF($I$152-K152=-9,91,IF($I$152-K152=10,90,IF($I$152-K152=-10,90,IF($I$152-K152=11,89,IF($I$152-K152=-11,89,IF($I$152-K152=12,88,IF($I$152-K152=-12,88,IF($I$152-K152=13,87,IF($I$152-K152=-13,87,IF($I$152-K152=14,86,IF($I$152-K152=-14,86,IF($I$152-K152=15,85,IF($I$152-K152=-15,85,IF($I$152-K152=16,84,IF($I$152-K152=-16,84,IF($I$152-K152=17,83,IF($I$152-K152=-17,83,IF($I$152-K152=18,82,IF($I$152-K152=-18,82,IF($I$152-K152=19,81,IF($I$152-K152=-19,81,IF($I$152-K152=20,80,IF($I$152-K152=-20,80,IF($I$152-K152=21,79,IF($I$152-K152=-21,79,IF($I$152-K152=22,78,IF($I$152-K152=-22,78,IF($I$152-K152=23,77,IF($I$152-K152=-23,77,IF($I$152-K152=24,76,IF($I$152-K152=-24,76,IF($I$152-K152=25,75,IF($I$152-K152=-25,75,IF($I$152-K152=26,74,IF($I$152-K152=-26,74,IF($I$152-K152=27,73,IF($I$152-K152=-27,73,IF($I$152-K152=28,72,IF($I$152-K152=-28,72,IF($I$152-K152=29,71,IF($I$152-K152=-29,71,IF($I$152-K152=30,70,IF($I$152-K152=-30,70,IF($I$152-K152=31,69,IF($I$152-K152=-31,69,IF($I$152-K152=32,68,IF($I$152-K152=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="L154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="M154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="N154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="O154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="P154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="Q154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="R154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="S154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="T154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="U154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="V154" s="4">
-        <f t="shared" ref="V154:X154" si="46">IF(V152=$I$152,100,IF($I$152-V152=1,99,IF($I$152-V152=-1,99,IF($I$152-V152=2,98,IF($I$152-V152=-2,98,IF($I$152-V152=3,97,IF($I$152-V152=-3,97,IF($I$152-V152=4,96,IF($I$152-V152=-4,96,IF($I$152-V152=5,95,IF($I$152-V152=-5,95,IF($I$152-V152=6,94,IF($I$152-V152=-6,94,IF($I$152-V152=7,93,IF($I$152-V152=-7,93,IF($I$152-V152=8,92,IF($I$152-V152=-8,92,IF($I$152-V152=9,91,IF($I$152-V152=-9,91,IF($I$152-V152=10,90,IF($I$152-V152=-10,90,IF($I$152-V152=11,89,IF($I$152-V152=-11,89,IF($I$152-V152=12,88,IF($I$152-V152=-12,88,IF($I$152-V152=13,87,IF($I$152-V152=-13,87,IF($I$152-V152=14,86,IF($I$152-V152=-14,86,IF($I$152-V152=15,85,IF($I$152-V152=-15,85,IF($I$152-V152=16,84,IF($I$152-V152=-16,84,IF($I$152-V152=17,83,IF($I$152-V152=-17,83,IF($I$152-V152=18,82,IF($I$152-V152=-18,82,IF($I$152-V152=19,81,IF($I$152-V152=-19,81,IF($I$152-V152=20,80,IF($I$152-V152=-20,80,IF($I$152-V152=21,79,IF($I$152-V152=-21,79,IF($I$152-V152=22,78,IF($I$152-V152=-22,78,IF($I$152-V152=23,77,IF($I$152-V152=-23,77,IF($I$152-V152=24,76,IF($I$152-V152=-24,76,IF($I$152-V152=25,75,IF($I$152-V152=-25,75,IF($I$152-V152=26,74,IF($I$152-V152=-26,74,IF($I$152-V152=27,73,IF($I$152-V152=-27,73,IF($I$152-V152=28,72,IF($I$152-V152=-28,72,IF($I$152-V152=29,71,IF($I$152-V152=-29,71,IF($I$152-V152=30,70,IF($I$152-V152=-30,70,IF($I$152-V152=31,69,IF($I$152-V152=-31,69,IF($I$152-V152=32,68,IF($I$152-V152=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="V154:X154" si="53">IF(V152=$I$152,100,IF($I$152-V152=1,99,IF($I$152-V152=-1,99,IF($I$152-V152=2,98,IF($I$152-V152=-2,98,IF($I$152-V152=3,97,IF($I$152-V152=-3,97,IF($I$152-V152=4,96,IF($I$152-V152=-4,96,IF($I$152-V152=5,95,IF($I$152-V152=-5,95,IF($I$152-V152=6,94,IF($I$152-V152=-6,94,IF($I$152-V152=7,93,IF($I$152-V152=-7,93,IF($I$152-V152=8,92,IF($I$152-V152=-8,92,IF($I$152-V152=9,91,IF($I$152-V152=-9,91,IF($I$152-V152=10,90,IF($I$152-V152=-10,90,IF($I$152-V152=11,89,IF($I$152-V152=-11,89,IF($I$152-V152=12,88,IF($I$152-V152=-12,88,IF($I$152-V152=13,87,IF($I$152-V152=-13,87,IF($I$152-V152=14,86,IF($I$152-V152=-14,86,IF($I$152-V152=15,85,IF($I$152-V152=-15,85,IF($I$152-V152=16,84,IF($I$152-V152=-16,84,IF($I$152-V152=17,83,IF($I$152-V152=-17,83,IF($I$152-V152=18,82,IF($I$152-V152=-18,82,IF($I$152-V152=19,81,IF($I$152-V152=-19,81,IF($I$152-V152=20,80,IF($I$152-V152=-20,80,IF($I$152-V152=21,79,IF($I$152-V152=-21,79,IF($I$152-V152=22,78,IF($I$152-V152=-22,78,IF($I$152-V152=23,77,IF($I$152-V152=-23,77,IF($I$152-V152=24,76,IF($I$152-V152=-24,76,IF($I$152-V152=25,75,IF($I$152-V152=-25,75,IF($I$152-V152=26,74,IF($I$152-V152=-26,74,IF($I$152-V152=27,73,IF($I$152-V152=-27,73,IF($I$152-V152=28,72,IF($I$152-V152=-28,72,IF($I$152-V152=29,71,IF($I$152-V152=-29,71,IF($I$152-V152=30,70,IF($I$152-V152=-30,70,IF($I$152-V152=31,69,IF($I$152-V152=-31,69,IF($I$152-V152=32,68,IF($I$152-V152=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="W154" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="X154" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="Y154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="Z154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="AA154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="AB154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="AC154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="AD154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="AE154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="AF154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="AG154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="AH154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="AI154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="AJ154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="AK154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="AL154" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="AM154" s="4">
-        <f t="shared" ref="AM154:AP154" si="47">IF(AM152=$I$152,100,IF($I$152-AM152=1,99,IF($I$152-AM152=-1,99,IF($I$152-AM152=2,98,IF($I$152-AM152=-2,98,IF($I$152-AM152=3,97,IF($I$152-AM152=-3,97,IF($I$152-AM152=4,96,IF($I$152-AM152=-4,96,IF($I$152-AM152=5,95,IF($I$152-AM152=-5,95,IF($I$152-AM152=6,94,IF($I$152-AM152=-6,94,IF($I$152-AM152=7,93,IF($I$152-AM152=-7,93,IF($I$152-AM152=8,92,IF($I$152-AM152=-8,92,IF($I$152-AM152=9,91,IF($I$152-AM152=-9,91,IF($I$152-AM152=10,90,IF($I$152-AM152=-10,90,IF($I$152-AM152=11,89,IF($I$152-AM152=-11,89,IF($I$152-AM152=12,88,IF($I$152-AM152=-12,88,IF($I$152-AM152=13,87,IF($I$152-AM152=-13,87,IF($I$152-AM152=14,86,IF($I$152-AM152=-14,86,IF($I$152-AM152=15,85,IF($I$152-AM152=-15,85,IF($I$152-AM152=16,84,IF($I$152-AM152=-16,84,IF($I$152-AM152=17,83,IF($I$152-AM152=-17,83,IF($I$152-AM152=18,82,IF($I$152-AM152=-18,82,IF($I$152-AM152=19,81,IF($I$152-AM152=-19,81,IF($I$152-AM152=20,80,IF($I$152-AM152=-20,80,IF($I$152-AM152=21,79,IF($I$152-AM152=-21,79,IF($I$152-AM152=22,78,IF($I$152-AM152=-22,78,IF($I$152-AM152=23,77,IF($I$152-AM152=-23,77,IF($I$152-AM152=24,76,IF($I$152-AM152=-24,76,IF($I$152-AM152=25,75,IF($I$152-AM152=-25,75,IF($I$152-AM152=26,74,IF($I$152-AM152=-26,74,IF($I$152-AM152=27,73,IF($I$152-AM152=-27,73,IF($I$152-AM152=28,72,IF($I$152-AM152=-28,72,IF($I$152-AM152=29,71,IF($I$152-AM152=-29,71,IF($I$152-AM152=30,70,IF($I$152-AM152=-30,70,IF($I$152-AM152=31,69,IF($I$152-AM152=-31,69,IF($I$152-AM152=32,68,IF($I$152-AM152=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="AM154:AP154" si="54">IF(AM152=$I$152,100,IF($I$152-AM152=1,99,IF($I$152-AM152=-1,99,IF($I$152-AM152=2,98,IF($I$152-AM152=-2,98,IF($I$152-AM152=3,97,IF($I$152-AM152=-3,97,IF($I$152-AM152=4,96,IF($I$152-AM152=-4,96,IF($I$152-AM152=5,95,IF($I$152-AM152=-5,95,IF($I$152-AM152=6,94,IF($I$152-AM152=-6,94,IF($I$152-AM152=7,93,IF($I$152-AM152=-7,93,IF($I$152-AM152=8,92,IF($I$152-AM152=-8,92,IF($I$152-AM152=9,91,IF($I$152-AM152=-9,91,IF($I$152-AM152=10,90,IF($I$152-AM152=-10,90,IF($I$152-AM152=11,89,IF($I$152-AM152=-11,89,IF($I$152-AM152=12,88,IF($I$152-AM152=-12,88,IF($I$152-AM152=13,87,IF($I$152-AM152=-13,87,IF($I$152-AM152=14,86,IF($I$152-AM152=-14,86,IF($I$152-AM152=15,85,IF($I$152-AM152=-15,85,IF($I$152-AM152=16,84,IF($I$152-AM152=-16,84,IF($I$152-AM152=17,83,IF($I$152-AM152=-17,83,IF($I$152-AM152=18,82,IF($I$152-AM152=-18,82,IF($I$152-AM152=19,81,IF($I$152-AM152=-19,81,IF($I$152-AM152=20,80,IF($I$152-AM152=-20,80,IF($I$152-AM152=21,79,IF($I$152-AM152=-21,79,IF($I$152-AM152=22,78,IF($I$152-AM152=-22,78,IF($I$152-AM152=23,77,IF($I$152-AM152=-23,77,IF($I$152-AM152=24,76,IF($I$152-AM152=-24,76,IF($I$152-AM152=25,75,IF($I$152-AM152=-25,75,IF($I$152-AM152=26,74,IF($I$152-AM152=-26,74,IF($I$152-AM152=27,73,IF($I$152-AM152=-27,73,IF($I$152-AM152=28,72,IF($I$152-AM152=-28,72,IF($I$152-AM152=29,71,IF($I$152-AM152=-29,71,IF($I$152-AM152=30,70,IF($I$152-AM152=-30,70,IF($I$152-AM152=31,69,IF($I$152-AM152=-31,69,IF($I$152-AM152=32,68,IF($I$152-AM152=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="AN154" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AO154" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AP154" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AQ154" s="4">
-        <f t="shared" ref="AQ154:AT154" si="48">IF(AQ152=$I$152,100,IF($I$152-AQ152=1,99,IF($I$152-AQ152=-1,99,IF($I$152-AQ152=2,98,IF($I$152-AQ152=-2,98,IF($I$152-AQ152=3,97,IF($I$152-AQ152=-3,97,IF($I$152-AQ152=4,96,IF($I$152-AQ152=-4,96,IF($I$152-AQ152=5,95,IF($I$152-AQ152=-5,95,IF($I$152-AQ152=6,94,IF($I$152-AQ152=-6,94,IF($I$152-AQ152=7,93,IF($I$152-AQ152=-7,93,IF($I$152-AQ152=8,92,IF($I$152-AQ152=-8,92,IF($I$152-AQ152=9,91,IF($I$152-AQ152=-9,91,IF($I$152-AQ152=10,90,IF($I$152-AQ152=-10,90,IF($I$152-AQ152=11,89,IF($I$152-AQ152=-11,89,IF($I$152-AQ152=12,88,IF($I$152-AQ152=-12,88,IF($I$152-AQ152=13,87,IF($I$152-AQ152=-13,87,IF($I$152-AQ152=14,86,IF($I$152-AQ152=-14,86,IF($I$152-AQ152=15,85,IF($I$152-AQ152=-15,85,IF($I$152-AQ152=16,84,IF($I$152-AQ152=-16,84,IF($I$152-AQ152=17,83,IF($I$152-AQ152=-17,83,IF($I$152-AQ152=18,82,IF($I$152-AQ152=-18,82,IF($I$152-AQ152=19,81,IF($I$152-AQ152=-19,81,IF($I$152-AQ152=20,80,IF($I$152-AQ152=-20,80,IF($I$152-AQ152=21,79,IF($I$152-AQ152=-21,79,IF($I$152-AQ152=22,78,IF($I$152-AQ152=-22,78,IF($I$152-AQ152=23,77,IF($I$152-AQ152=-23,77,IF($I$152-AQ152=24,76,IF($I$152-AQ152=-24,76,IF($I$152-AQ152=25,75,IF($I$152-AQ152=-25,75,IF($I$152-AQ152=26,74,IF($I$152-AQ152=-26,74,IF($I$152-AQ152=27,73,IF($I$152-AQ152=-27,73,IF($I$152-AQ152=28,72,IF($I$152-AQ152=-28,72,IF($I$152-AQ152=29,71,IF($I$152-AQ152=-29,71,IF($I$152-AQ152=30,70,IF($I$152-AQ152=-30,70,IF($I$152-AQ152=31,69,IF($I$152-AQ152=-31,69,IF($I$152-AQ152=32,68,IF($I$152-AQ152=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="AQ154:AT154" si="55">IF(AQ152=$I$152,100,IF($I$152-AQ152=1,99,IF($I$152-AQ152=-1,99,IF($I$152-AQ152=2,98,IF($I$152-AQ152=-2,98,IF($I$152-AQ152=3,97,IF($I$152-AQ152=-3,97,IF($I$152-AQ152=4,96,IF($I$152-AQ152=-4,96,IF($I$152-AQ152=5,95,IF($I$152-AQ152=-5,95,IF($I$152-AQ152=6,94,IF($I$152-AQ152=-6,94,IF($I$152-AQ152=7,93,IF($I$152-AQ152=-7,93,IF($I$152-AQ152=8,92,IF($I$152-AQ152=-8,92,IF($I$152-AQ152=9,91,IF($I$152-AQ152=-9,91,IF($I$152-AQ152=10,90,IF($I$152-AQ152=-10,90,IF($I$152-AQ152=11,89,IF($I$152-AQ152=-11,89,IF($I$152-AQ152=12,88,IF($I$152-AQ152=-12,88,IF($I$152-AQ152=13,87,IF($I$152-AQ152=-13,87,IF($I$152-AQ152=14,86,IF($I$152-AQ152=-14,86,IF($I$152-AQ152=15,85,IF($I$152-AQ152=-15,85,IF($I$152-AQ152=16,84,IF($I$152-AQ152=-16,84,IF($I$152-AQ152=17,83,IF($I$152-AQ152=-17,83,IF($I$152-AQ152=18,82,IF($I$152-AQ152=-18,82,IF($I$152-AQ152=19,81,IF($I$152-AQ152=-19,81,IF($I$152-AQ152=20,80,IF($I$152-AQ152=-20,80,IF($I$152-AQ152=21,79,IF($I$152-AQ152=-21,79,IF($I$152-AQ152=22,78,IF($I$152-AQ152=-22,78,IF($I$152-AQ152=23,77,IF($I$152-AQ152=-23,77,IF($I$152-AQ152=24,76,IF($I$152-AQ152=-24,76,IF($I$152-AQ152=25,75,IF($I$152-AQ152=-25,75,IF($I$152-AQ152=26,74,IF($I$152-AQ152=-26,74,IF($I$152-AQ152=27,73,IF($I$152-AQ152=-27,73,IF($I$152-AQ152=28,72,IF($I$152-AQ152=-28,72,IF($I$152-AQ152=29,71,IF($I$152-AQ152=-29,71,IF($I$152-AQ152=30,70,IF($I$152-AQ152=-30,70,IF($I$152-AQ152=31,69,IF($I$152-AQ152=-31,69,IF($I$152-AQ152=32,68,IF($I$152-AQ152=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="AR154" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="AS154" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="AT154" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:46" x14ac:dyDescent="0.25">
       <c r="F155" s="57"/>
       <c r="G155" s="3"/>
       <c r="H155" s="3"/>
@@ -22768,151 +22736,151 @@
         <v>0</v>
       </c>
       <c r="K155" s="4">
-        <f t="shared" ref="K155:AL155" si="49">IF($I$152-K152=33,67,IF($I$152-K152=-33,67,IF($I$152-K152=34,66,IF($I$152-K152=-34,66,IF($I$152-K152=35,65,IF($I$152-K152=-35,65,IF($I$152-K152=36,64,IF($I$152-K152=-36,64,IF($I$152-K152=37,63,IF($I$152-K152=-37,63,IF($I$152-K152=38,62,IF($I$152-K152=-38,62,IF($I$152-K152=39,61,IF($I$152-K152=-39,61,IF($I$152-K152=40,60,IF($I$152-K152=-40,60,IF($I$152-K152=41,59,IF($I$152-K152=-41,59,IF($I$152-K152=42,58,IF($I$152-K152=-42,58,IF($I$152-K152=43,57,IF($I$152-K152=-43,57,IF($I$152-K152=44,56,IF($I$152-K152=-44,56,IF($I$152-K152=45,55,IF($I$152-K152=-45,55,IF($I$152-K152=46,54,IF($I$152-K152=-46,54,IF($I$152-K152=47,53,IF($I$152-K152=-47,53,IF($I$152-K152=48,52,IF($I$152-K152=-48,52,IF($I$152-K152=49,51,IF($I$152-K152=-49,51,IF($I$152-K152=50,50,IF($I$152-K152=-50,50,IF($I$152-K152=51,49,IF($I$152-K152=-51,49,IF($I$152-K152=52,48,IF($I$152-K152=-52,48,IF($I$152-K152=53,47,IF($I$152-K152=-53,47,IF($I$152-K152=54,46,IF($I$152-K152=-54,46,IF($I$152-K152=55,45,IF($I$152-K152=-55,45,IF($I$152-K152=56,44,IF($I$152-K152=-56,44,IF($I$152-K152=57,43,IF($I$152-K152=-57,43,IF($I$152-K152=58,42,IF($I$152-K152=-58,42,IF($I$152-K152=59,41,IF($I$152-K152=-59,41,IF($I$152-K152=60,40,IF($I$152-K152=-60,40,IF($I$152-K152=61,39,IF($I$152-K152=-61,39,IF($I$152-K152=62,38,IF($I$152-K152=-62,38,IF($I$152-K152=63,37,IF($I$152-K152=-63,37,IF($I$152-K152=64,36,IF($I$152-K152=-64,36,IF($I$152-K152=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="K155:AL155" si="56">IF($I$152-K152=33,67,IF($I$152-K152=-33,67,IF($I$152-K152=34,66,IF($I$152-K152=-34,66,IF($I$152-K152=35,65,IF($I$152-K152=-35,65,IF($I$152-K152=36,64,IF($I$152-K152=-36,64,IF($I$152-K152=37,63,IF($I$152-K152=-37,63,IF($I$152-K152=38,62,IF($I$152-K152=-38,62,IF($I$152-K152=39,61,IF($I$152-K152=-39,61,IF($I$152-K152=40,60,IF($I$152-K152=-40,60,IF($I$152-K152=41,59,IF($I$152-K152=-41,59,IF($I$152-K152=42,58,IF($I$152-K152=-42,58,IF($I$152-K152=43,57,IF($I$152-K152=-43,57,IF($I$152-K152=44,56,IF($I$152-K152=-44,56,IF($I$152-K152=45,55,IF($I$152-K152=-45,55,IF($I$152-K152=46,54,IF($I$152-K152=-46,54,IF($I$152-K152=47,53,IF($I$152-K152=-47,53,IF($I$152-K152=48,52,IF($I$152-K152=-48,52,IF($I$152-K152=49,51,IF($I$152-K152=-49,51,IF($I$152-K152=50,50,IF($I$152-K152=-50,50,IF($I$152-K152=51,49,IF($I$152-K152=-51,49,IF($I$152-K152=52,48,IF($I$152-K152=-52,48,IF($I$152-K152=53,47,IF($I$152-K152=-53,47,IF($I$152-K152=54,46,IF($I$152-K152=-54,46,IF($I$152-K152=55,45,IF($I$152-K152=-55,45,IF($I$152-K152=56,44,IF($I$152-K152=-56,44,IF($I$152-K152=57,43,IF($I$152-K152=-57,43,IF($I$152-K152=58,42,IF($I$152-K152=-58,42,IF($I$152-K152=59,41,IF($I$152-K152=-59,41,IF($I$152-K152=60,40,IF($I$152-K152=-60,40,IF($I$152-K152=61,39,IF($I$152-K152=-61,39,IF($I$152-K152=62,38,IF($I$152-K152=-62,38,IF($I$152-K152=63,37,IF($I$152-K152=-63,37,IF($I$152-K152=64,36,IF($I$152-K152=-64,36,IF($I$152-K152=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="L155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="M155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="N155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="O155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="P155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="Q155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="R155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="S155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="T155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="U155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="V155" s="4">
-        <f t="shared" ref="V155:X155" si="50">IF($I$152-V152=33,67,IF($I$152-V152=-33,67,IF($I$152-V152=34,66,IF($I$152-V152=-34,66,IF($I$152-V152=35,65,IF($I$152-V152=-35,65,IF($I$152-V152=36,64,IF($I$152-V152=-36,64,IF($I$152-V152=37,63,IF($I$152-V152=-37,63,IF($I$152-V152=38,62,IF($I$152-V152=-38,62,IF($I$152-V152=39,61,IF($I$152-V152=-39,61,IF($I$152-V152=40,60,IF($I$152-V152=-40,60,IF($I$152-V152=41,59,IF($I$152-V152=-41,59,IF($I$152-V152=42,58,IF($I$152-V152=-42,58,IF($I$152-V152=43,57,IF($I$152-V152=-43,57,IF($I$152-V152=44,56,IF($I$152-V152=-44,56,IF($I$152-V152=45,55,IF($I$152-V152=-45,55,IF($I$152-V152=46,54,IF($I$152-V152=-46,54,IF($I$152-V152=47,53,IF($I$152-V152=-47,53,IF($I$152-V152=48,52,IF($I$152-V152=-48,52,IF($I$152-V152=49,51,IF($I$152-V152=-49,51,IF($I$152-V152=50,50,IF($I$152-V152=-50,50,IF($I$152-V152=51,49,IF($I$152-V152=-51,49,IF($I$152-V152=52,48,IF($I$152-V152=-52,48,IF($I$152-V152=53,47,IF($I$152-V152=-53,47,IF($I$152-V152=54,46,IF($I$152-V152=-54,46,IF($I$152-V152=55,45,IF($I$152-V152=-55,45,IF($I$152-V152=56,44,IF($I$152-V152=-56,44,IF($I$152-V152=57,43,IF($I$152-V152=-57,43,IF($I$152-V152=58,42,IF($I$152-V152=-58,42,IF($I$152-V152=59,41,IF($I$152-V152=-59,41,IF($I$152-V152=60,40,IF($I$152-V152=-60,40,IF($I$152-V152=61,39,IF($I$152-V152=-61,39,IF($I$152-V152=62,38,IF($I$152-V152=-62,38,IF($I$152-V152=63,37,IF($I$152-V152=-63,37,IF($I$152-V152=64,36,IF($I$152-V152=-64,36,IF($I$152-V152=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="V155:X155" si="57">IF($I$152-V152=33,67,IF($I$152-V152=-33,67,IF($I$152-V152=34,66,IF($I$152-V152=-34,66,IF($I$152-V152=35,65,IF($I$152-V152=-35,65,IF($I$152-V152=36,64,IF($I$152-V152=-36,64,IF($I$152-V152=37,63,IF($I$152-V152=-37,63,IF($I$152-V152=38,62,IF($I$152-V152=-38,62,IF($I$152-V152=39,61,IF($I$152-V152=-39,61,IF($I$152-V152=40,60,IF($I$152-V152=-40,60,IF($I$152-V152=41,59,IF($I$152-V152=-41,59,IF($I$152-V152=42,58,IF($I$152-V152=-42,58,IF($I$152-V152=43,57,IF($I$152-V152=-43,57,IF($I$152-V152=44,56,IF($I$152-V152=-44,56,IF($I$152-V152=45,55,IF($I$152-V152=-45,55,IF($I$152-V152=46,54,IF($I$152-V152=-46,54,IF($I$152-V152=47,53,IF($I$152-V152=-47,53,IF($I$152-V152=48,52,IF($I$152-V152=-48,52,IF($I$152-V152=49,51,IF($I$152-V152=-49,51,IF($I$152-V152=50,50,IF($I$152-V152=-50,50,IF($I$152-V152=51,49,IF($I$152-V152=-51,49,IF($I$152-V152=52,48,IF($I$152-V152=-52,48,IF($I$152-V152=53,47,IF($I$152-V152=-53,47,IF($I$152-V152=54,46,IF($I$152-V152=-54,46,IF($I$152-V152=55,45,IF($I$152-V152=-55,45,IF($I$152-V152=56,44,IF($I$152-V152=-56,44,IF($I$152-V152=57,43,IF($I$152-V152=-57,43,IF($I$152-V152=58,42,IF($I$152-V152=-58,42,IF($I$152-V152=59,41,IF($I$152-V152=-59,41,IF($I$152-V152=60,40,IF($I$152-V152=-60,40,IF($I$152-V152=61,39,IF($I$152-V152=-61,39,IF($I$152-V152=62,38,IF($I$152-V152=-62,38,IF($I$152-V152=63,37,IF($I$152-V152=-63,37,IF($I$152-V152=64,36,IF($I$152-V152=-64,36,IF($I$152-V152=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="W155" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="X155" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="Y155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="Z155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AA155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AB155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AC155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AD155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AE155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AF155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AG155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AH155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AI155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AJ155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AK155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AL155" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AM155" s="4">
-        <f t="shared" ref="AM155:AP155" si="51">IF($I$152-AM152=33,67,IF($I$152-AM152=-33,67,IF($I$152-AM152=34,66,IF($I$152-AM152=-34,66,IF($I$152-AM152=35,65,IF($I$152-AM152=-35,65,IF($I$152-AM152=36,64,IF($I$152-AM152=-36,64,IF($I$152-AM152=37,63,IF($I$152-AM152=-37,63,IF($I$152-AM152=38,62,IF($I$152-AM152=-38,62,IF($I$152-AM152=39,61,IF($I$152-AM152=-39,61,IF($I$152-AM152=40,60,IF($I$152-AM152=-40,60,IF($I$152-AM152=41,59,IF($I$152-AM152=-41,59,IF($I$152-AM152=42,58,IF($I$152-AM152=-42,58,IF($I$152-AM152=43,57,IF($I$152-AM152=-43,57,IF($I$152-AM152=44,56,IF($I$152-AM152=-44,56,IF($I$152-AM152=45,55,IF($I$152-AM152=-45,55,IF($I$152-AM152=46,54,IF($I$152-AM152=-46,54,IF($I$152-AM152=47,53,IF($I$152-AM152=-47,53,IF($I$152-AM152=48,52,IF($I$152-AM152=-48,52,IF($I$152-AM152=49,51,IF($I$152-AM152=-49,51,IF($I$152-AM152=50,50,IF($I$152-AM152=-50,50,IF($I$152-AM152=51,49,IF($I$152-AM152=-51,49,IF($I$152-AM152=52,48,IF($I$152-AM152=-52,48,IF($I$152-AM152=53,47,IF($I$152-AM152=-53,47,IF($I$152-AM152=54,46,IF($I$152-AM152=-54,46,IF($I$152-AM152=55,45,IF($I$152-AM152=-55,45,IF($I$152-AM152=56,44,IF($I$152-AM152=-56,44,IF($I$152-AM152=57,43,IF($I$152-AM152=-57,43,IF($I$152-AM152=58,42,IF($I$152-AM152=-58,42,IF($I$152-AM152=59,41,IF($I$152-AM152=-59,41,IF($I$152-AM152=60,40,IF($I$152-AM152=-60,40,IF($I$152-AM152=61,39,IF($I$152-AM152=-61,39,IF($I$152-AM152=62,38,IF($I$152-AM152=-62,38,IF($I$152-AM152=63,37,IF($I$152-AM152=-63,37,IF($I$152-AM152=64,36,IF($I$152-AM152=-64,36,IF($I$152-AM152=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="AM155:AP155" si="58">IF($I$152-AM152=33,67,IF($I$152-AM152=-33,67,IF($I$152-AM152=34,66,IF($I$152-AM152=-34,66,IF($I$152-AM152=35,65,IF($I$152-AM152=-35,65,IF($I$152-AM152=36,64,IF($I$152-AM152=-36,64,IF($I$152-AM152=37,63,IF($I$152-AM152=-37,63,IF($I$152-AM152=38,62,IF($I$152-AM152=-38,62,IF($I$152-AM152=39,61,IF($I$152-AM152=-39,61,IF($I$152-AM152=40,60,IF($I$152-AM152=-40,60,IF($I$152-AM152=41,59,IF($I$152-AM152=-41,59,IF($I$152-AM152=42,58,IF($I$152-AM152=-42,58,IF($I$152-AM152=43,57,IF($I$152-AM152=-43,57,IF($I$152-AM152=44,56,IF($I$152-AM152=-44,56,IF($I$152-AM152=45,55,IF($I$152-AM152=-45,55,IF($I$152-AM152=46,54,IF($I$152-AM152=-46,54,IF($I$152-AM152=47,53,IF($I$152-AM152=-47,53,IF($I$152-AM152=48,52,IF($I$152-AM152=-48,52,IF($I$152-AM152=49,51,IF($I$152-AM152=-49,51,IF($I$152-AM152=50,50,IF($I$152-AM152=-50,50,IF($I$152-AM152=51,49,IF($I$152-AM152=-51,49,IF($I$152-AM152=52,48,IF($I$152-AM152=-52,48,IF($I$152-AM152=53,47,IF($I$152-AM152=-53,47,IF($I$152-AM152=54,46,IF($I$152-AM152=-54,46,IF($I$152-AM152=55,45,IF($I$152-AM152=-55,45,IF($I$152-AM152=56,44,IF($I$152-AM152=-56,44,IF($I$152-AM152=57,43,IF($I$152-AM152=-57,43,IF($I$152-AM152=58,42,IF($I$152-AM152=-58,42,IF($I$152-AM152=59,41,IF($I$152-AM152=-59,41,IF($I$152-AM152=60,40,IF($I$152-AM152=-60,40,IF($I$152-AM152=61,39,IF($I$152-AM152=-61,39,IF($I$152-AM152=62,38,IF($I$152-AM152=-62,38,IF($I$152-AM152=63,37,IF($I$152-AM152=-63,37,IF($I$152-AM152=64,36,IF($I$152-AM152=-64,36,IF($I$152-AM152=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="AN155" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AO155" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AP155" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AQ155" s="4">
-        <f t="shared" ref="AQ155:AT155" si="52">IF($I$152-AQ152=33,67,IF($I$152-AQ152=-33,67,IF($I$152-AQ152=34,66,IF($I$152-AQ152=-34,66,IF($I$152-AQ152=35,65,IF($I$152-AQ152=-35,65,IF($I$152-AQ152=36,64,IF($I$152-AQ152=-36,64,IF($I$152-AQ152=37,63,IF($I$152-AQ152=-37,63,IF($I$152-AQ152=38,62,IF($I$152-AQ152=-38,62,IF($I$152-AQ152=39,61,IF($I$152-AQ152=-39,61,IF($I$152-AQ152=40,60,IF($I$152-AQ152=-40,60,IF($I$152-AQ152=41,59,IF($I$152-AQ152=-41,59,IF($I$152-AQ152=42,58,IF($I$152-AQ152=-42,58,IF($I$152-AQ152=43,57,IF($I$152-AQ152=-43,57,IF($I$152-AQ152=44,56,IF($I$152-AQ152=-44,56,IF($I$152-AQ152=45,55,IF($I$152-AQ152=-45,55,IF($I$152-AQ152=46,54,IF($I$152-AQ152=-46,54,IF($I$152-AQ152=47,53,IF($I$152-AQ152=-47,53,IF($I$152-AQ152=48,52,IF($I$152-AQ152=-48,52,IF($I$152-AQ152=49,51,IF($I$152-AQ152=-49,51,IF($I$152-AQ152=50,50,IF($I$152-AQ152=-50,50,IF($I$152-AQ152=51,49,IF($I$152-AQ152=-51,49,IF($I$152-AQ152=52,48,IF($I$152-AQ152=-52,48,IF($I$152-AQ152=53,47,IF($I$152-AQ152=-53,47,IF($I$152-AQ152=54,46,IF($I$152-AQ152=-54,46,IF($I$152-AQ152=55,45,IF($I$152-AQ152=-55,45,IF($I$152-AQ152=56,44,IF($I$152-AQ152=-56,44,IF($I$152-AQ152=57,43,IF($I$152-AQ152=-57,43,IF($I$152-AQ152=58,42,IF($I$152-AQ152=-58,42,IF($I$152-AQ152=59,41,IF($I$152-AQ152=-59,41,IF($I$152-AQ152=60,40,IF($I$152-AQ152=-60,40,IF($I$152-AQ152=61,39,IF($I$152-AQ152=-61,39,IF($I$152-AQ152=62,38,IF($I$152-AQ152=-62,38,IF($I$152-AQ152=63,37,IF($I$152-AQ152=-63,37,IF($I$152-AQ152=64,36,IF($I$152-AQ152=-64,36,IF($I$152-AQ152=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="AQ155:AT155" si="59">IF($I$152-AQ152=33,67,IF($I$152-AQ152=-33,67,IF($I$152-AQ152=34,66,IF($I$152-AQ152=-34,66,IF($I$152-AQ152=35,65,IF($I$152-AQ152=-35,65,IF($I$152-AQ152=36,64,IF($I$152-AQ152=-36,64,IF($I$152-AQ152=37,63,IF($I$152-AQ152=-37,63,IF($I$152-AQ152=38,62,IF($I$152-AQ152=-38,62,IF($I$152-AQ152=39,61,IF($I$152-AQ152=-39,61,IF($I$152-AQ152=40,60,IF($I$152-AQ152=-40,60,IF($I$152-AQ152=41,59,IF($I$152-AQ152=-41,59,IF($I$152-AQ152=42,58,IF($I$152-AQ152=-42,58,IF($I$152-AQ152=43,57,IF($I$152-AQ152=-43,57,IF($I$152-AQ152=44,56,IF($I$152-AQ152=-44,56,IF($I$152-AQ152=45,55,IF($I$152-AQ152=-45,55,IF($I$152-AQ152=46,54,IF($I$152-AQ152=-46,54,IF($I$152-AQ152=47,53,IF($I$152-AQ152=-47,53,IF($I$152-AQ152=48,52,IF($I$152-AQ152=-48,52,IF($I$152-AQ152=49,51,IF($I$152-AQ152=-49,51,IF($I$152-AQ152=50,50,IF($I$152-AQ152=-50,50,IF($I$152-AQ152=51,49,IF($I$152-AQ152=-51,49,IF($I$152-AQ152=52,48,IF($I$152-AQ152=-52,48,IF($I$152-AQ152=53,47,IF($I$152-AQ152=-53,47,IF($I$152-AQ152=54,46,IF($I$152-AQ152=-54,46,IF($I$152-AQ152=55,45,IF($I$152-AQ152=-55,45,IF($I$152-AQ152=56,44,IF($I$152-AQ152=-56,44,IF($I$152-AQ152=57,43,IF($I$152-AQ152=-57,43,IF($I$152-AQ152=58,42,IF($I$152-AQ152=-58,42,IF($I$152-AQ152=59,41,IF($I$152-AQ152=-59,41,IF($I$152-AQ152=60,40,IF($I$152-AQ152=-60,40,IF($I$152-AQ152=61,39,IF($I$152-AQ152=-61,39,IF($I$152-AQ152=62,38,IF($I$152-AQ152=-62,38,IF($I$152-AQ152=63,37,IF($I$152-AQ152=-63,37,IF($I$152-AQ152=64,36,IF($I$152-AQ152=-64,36,IF($I$152-AQ152=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="AR155" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AS155" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AT155" s="4">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:46" x14ac:dyDescent="0.25">
       <c r="F156" s="57"/>
       <c r="G156" s="3"/>
       <c r="H156" s="3"/>
@@ -22922,151 +22890,151 @@
         <v>0</v>
       </c>
       <c r="K156" s="4">
-        <f t="shared" ref="K156:AL156" si="53">IF($I$152-K152=-65,35,IF($I$152-K152=66,34,IF($I$152-K152=-66,34,IF($I$152-K152=67,33,IF($I$152-K152=-67,33,IF($I$152-K152=68,32,IF($I$152-K152=-68,32,IF($I$152-K152=69,31,IF($I$152-K152=-69,31,IF($I$152-K152=70,30,IF($I$152-K152=-70,30,IF($I$152-K152=71,29,IF($I$152-K152=-71,29,IF($I$152-K152=72,28,IF($I$152-K152=-72,28,IF($I$152-K152=73,27,IF($I$152-K152=-73,27,IF($I$152-K152=74,26,IF($I$152-K152=-74,26,IF($I$152-K152=75,25,IF($I$152-K152=-75,25,IF($I$152-K152=76,24,IF($I$152-K152=-76,24,IF($I$152-K152=77,23,IF($I$152-K152=-77,23,IF($I$152-K152=78,22,IF($I$152-K152=-78,22,IF($I$152-K152=79,21,IF($I$152-K152=-79,21,IF($I$152-K152=80,20,IF($I$152-K152=-80,20,IF($I$152-K152=81,19,IF($I$152-K152=-81,19,IF($I$152-K152=82,18,IF($I$152-K152=-82,18,IF($I$152-K152=83,17,IF($I$152-K152=-83,17,IF($I$152-K152=84,16,IF($I$152-K152=-84,16,IF($I$152-K152=85,15,IF($I$152-K152=-85,15,IF($I$152-K152=86,14,IF($I$152-K152=-86,14,IF($I$152-K152=87,13,IF($I$152-K152=-87,13,IF($I$152-K152=88,12,IF($I$152-K152=-88,12,IF($I$152-K152=89,11,IF($I$152-K152=-89,11,IF($I$152-K152=90,10,IF($I$152-K152=-90,10,IF($I$152-K152=91,9,IF($I$152-K152=-91,9,IF($I$152-K152=92,8,IF($I$152-K152=-92,8,IF($I$152-K152=93,7,IF($I$152-K152=-93,7,IF($I$152-K152=94,6,IF($I$152-K152=-94,6,IF($I$152-K152=95,5,IF($I$152-K152=-95,5,IF($I$152-K152=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="K156:AL156" si="60">IF($I$152-K152=-65,35,IF($I$152-K152=66,34,IF($I$152-K152=-66,34,IF($I$152-K152=67,33,IF($I$152-K152=-67,33,IF($I$152-K152=68,32,IF($I$152-K152=-68,32,IF($I$152-K152=69,31,IF($I$152-K152=-69,31,IF($I$152-K152=70,30,IF($I$152-K152=-70,30,IF($I$152-K152=71,29,IF($I$152-K152=-71,29,IF($I$152-K152=72,28,IF($I$152-K152=-72,28,IF($I$152-K152=73,27,IF($I$152-K152=-73,27,IF($I$152-K152=74,26,IF($I$152-K152=-74,26,IF($I$152-K152=75,25,IF($I$152-K152=-75,25,IF($I$152-K152=76,24,IF($I$152-K152=-76,24,IF($I$152-K152=77,23,IF($I$152-K152=-77,23,IF($I$152-K152=78,22,IF($I$152-K152=-78,22,IF($I$152-K152=79,21,IF($I$152-K152=-79,21,IF($I$152-K152=80,20,IF($I$152-K152=-80,20,IF($I$152-K152=81,19,IF($I$152-K152=-81,19,IF($I$152-K152=82,18,IF($I$152-K152=-82,18,IF($I$152-K152=83,17,IF($I$152-K152=-83,17,IF($I$152-K152=84,16,IF($I$152-K152=-84,16,IF($I$152-K152=85,15,IF($I$152-K152=-85,15,IF($I$152-K152=86,14,IF($I$152-K152=-86,14,IF($I$152-K152=87,13,IF($I$152-K152=-87,13,IF($I$152-K152=88,12,IF($I$152-K152=-88,12,IF($I$152-K152=89,11,IF($I$152-K152=-89,11,IF($I$152-K152=90,10,IF($I$152-K152=-90,10,IF($I$152-K152=91,9,IF($I$152-K152=-91,9,IF($I$152-K152=92,8,IF($I$152-K152=-92,8,IF($I$152-K152=93,7,IF($I$152-K152=-93,7,IF($I$152-K152=94,6,IF($I$152-K152=-94,6,IF($I$152-K152=95,5,IF($I$152-K152=-95,5,IF($I$152-K152=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="L156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="M156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="N156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="O156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="P156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="Q156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="R156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="S156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="T156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="U156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="V156" s="4">
-        <f t="shared" ref="V156:X156" si="54">IF($I$152-V152=-65,35,IF($I$152-V152=66,34,IF($I$152-V152=-66,34,IF($I$152-V152=67,33,IF($I$152-V152=-67,33,IF($I$152-V152=68,32,IF($I$152-V152=-68,32,IF($I$152-V152=69,31,IF($I$152-V152=-69,31,IF($I$152-V152=70,30,IF($I$152-V152=-70,30,IF($I$152-V152=71,29,IF($I$152-V152=-71,29,IF($I$152-V152=72,28,IF($I$152-V152=-72,28,IF($I$152-V152=73,27,IF($I$152-V152=-73,27,IF($I$152-V152=74,26,IF($I$152-V152=-74,26,IF($I$152-V152=75,25,IF($I$152-V152=-75,25,IF($I$152-V152=76,24,IF($I$152-V152=-76,24,IF($I$152-V152=77,23,IF($I$152-V152=-77,23,IF($I$152-V152=78,22,IF($I$152-V152=-78,22,IF($I$152-V152=79,21,IF($I$152-V152=-79,21,IF($I$152-V152=80,20,IF($I$152-V152=-80,20,IF($I$152-V152=81,19,IF($I$152-V152=-81,19,IF($I$152-V152=82,18,IF($I$152-V152=-82,18,IF($I$152-V152=83,17,IF($I$152-V152=-83,17,IF($I$152-V152=84,16,IF($I$152-V152=-84,16,IF($I$152-V152=85,15,IF($I$152-V152=-85,15,IF($I$152-V152=86,14,IF($I$152-V152=-86,14,IF($I$152-V152=87,13,IF($I$152-V152=-87,13,IF($I$152-V152=88,12,IF($I$152-V152=-88,12,IF($I$152-V152=89,11,IF($I$152-V152=-89,11,IF($I$152-V152=90,10,IF($I$152-V152=-90,10,IF($I$152-V152=91,9,IF($I$152-V152=-91,9,IF($I$152-V152=92,8,IF($I$152-V152=-92,8,IF($I$152-V152=93,7,IF($I$152-V152=-93,7,IF($I$152-V152=94,6,IF($I$152-V152=-94,6,IF($I$152-V152=95,5,IF($I$152-V152=-95,5,IF($I$152-V152=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="V156:X156" si="61">IF($I$152-V152=-65,35,IF($I$152-V152=66,34,IF($I$152-V152=-66,34,IF($I$152-V152=67,33,IF($I$152-V152=-67,33,IF($I$152-V152=68,32,IF($I$152-V152=-68,32,IF($I$152-V152=69,31,IF($I$152-V152=-69,31,IF($I$152-V152=70,30,IF($I$152-V152=-70,30,IF($I$152-V152=71,29,IF($I$152-V152=-71,29,IF($I$152-V152=72,28,IF($I$152-V152=-72,28,IF($I$152-V152=73,27,IF($I$152-V152=-73,27,IF($I$152-V152=74,26,IF($I$152-V152=-74,26,IF($I$152-V152=75,25,IF($I$152-V152=-75,25,IF($I$152-V152=76,24,IF($I$152-V152=-76,24,IF($I$152-V152=77,23,IF($I$152-V152=-77,23,IF($I$152-V152=78,22,IF($I$152-V152=-78,22,IF($I$152-V152=79,21,IF($I$152-V152=-79,21,IF($I$152-V152=80,20,IF($I$152-V152=-80,20,IF($I$152-V152=81,19,IF($I$152-V152=-81,19,IF($I$152-V152=82,18,IF($I$152-V152=-82,18,IF($I$152-V152=83,17,IF($I$152-V152=-83,17,IF($I$152-V152=84,16,IF($I$152-V152=-84,16,IF($I$152-V152=85,15,IF($I$152-V152=-85,15,IF($I$152-V152=86,14,IF($I$152-V152=-86,14,IF($I$152-V152=87,13,IF($I$152-V152=-87,13,IF($I$152-V152=88,12,IF($I$152-V152=-88,12,IF($I$152-V152=89,11,IF($I$152-V152=-89,11,IF($I$152-V152=90,10,IF($I$152-V152=-90,10,IF($I$152-V152=91,9,IF($I$152-V152=-91,9,IF($I$152-V152=92,8,IF($I$152-V152=-92,8,IF($I$152-V152=93,7,IF($I$152-V152=-93,7,IF($I$152-V152=94,6,IF($I$152-V152=-94,6,IF($I$152-V152=95,5,IF($I$152-V152=-95,5,IF($I$152-V152=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="W156" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="X156" s="4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="Y156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="Z156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AA156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AB156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AC156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AD156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AE156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AF156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AG156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AH156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AI156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AJ156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AK156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AL156" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AM156" s="4">
-        <f t="shared" ref="AM156:AP156" si="55">IF($I$152-AM152=-65,35,IF($I$152-AM152=66,34,IF($I$152-AM152=-66,34,IF($I$152-AM152=67,33,IF($I$152-AM152=-67,33,IF($I$152-AM152=68,32,IF($I$152-AM152=-68,32,IF($I$152-AM152=69,31,IF($I$152-AM152=-69,31,IF($I$152-AM152=70,30,IF($I$152-AM152=-70,30,IF($I$152-AM152=71,29,IF($I$152-AM152=-71,29,IF($I$152-AM152=72,28,IF($I$152-AM152=-72,28,IF($I$152-AM152=73,27,IF($I$152-AM152=-73,27,IF($I$152-AM152=74,26,IF($I$152-AM152=-74,26,IF($I$152-AM152=75,25,IF($I$152-AM152=-75,25,IF($I$152-AM152=76,24,IF($I$152-AM152=-76,24,IF($I$152-AM152=77,23,IF($I$152-AM152=-77,23,IF($I$152-AM152=78,22,IF($I$152-AM152=-78,22,IF($I$152-AM152=79,21,IF($I$152-AM152=-79,21,IF($I$152-AM152=80,20,IF($I$152-AM152=-80,20,IF($I$152-AM152=81,19,IF($I$152-AM152=-81,19,IF($I$152-AM152=82,18,IF($I$152-AM152=-82,18,IF($I$152-AM152=83,17,IF($I$152-AM152=-83,17,IF($I$152-AM152=84,16,IF($I$152-AM152=-84,16,IF($I$152-AM152=85,15,IF($I$152-AM152=-85,15,IF($I$152-AM152=86,14,IF($I$152-AM152=-86,14,IF($I$152-AM152=87,13,IF($I$152-AM152=-87,13,IF($I$152-AM152=88,12,IF($I$152-AM152=-88,12,IF($I$152-AM152=89,11,IF($I$152-AM152=-89,11,IF($I$152-AM152=90,10,IF($I$152-AM152=-90,10,IF($I$152-AM152=91,9,IF($I$152-AM152=-91,9,IF($I$152-AM152=92,8,IF($I$152-AM152=-92,8,IF($I$152-AM152=93,7,IF($I$152-AM152=-93,7,IF($I$152-AM152=94,6,IF($I$152-AM152=-94,6,IF($I$152-AM152=95,5,IF($I$152-AM152=-95,5,IF($I$152-AM152=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="AM156:AP156" si="62">IF($I$152-AM152=-65,35,IF($I$152-AM152=66,34,IF($I$152-AM152=-66,34,IF($I$152-AM152=67,33,IF($I$152-AM152=-67,33,IF($I$152-AM152=68,32,IF($I$152-AM152=-68,32,IF($I$152-AM152=69,31,IF($I$152-AM152=-69,31,IF($I$152-AM152=70,30,IF($I$152-AM152=-70,30,IF($I$152-AM152=71,29,IF($I$152-AM152=-71,29,IF($I$152-AM152=72,28,IF($I$152-AM152=-72,28,IF($I$152-AM152=73,27,IF($I$152-AM152=-73,27,IF($I$152-AM152=74,26,IF($I$152-AM152=-74,26,IF($I$152-AM152=75,25,IF($I$152-AM152=-75,25,IF($I$152-AM152=76,24,IF($I$152-AM152=-76,24,IF($I$152-AM152=77,23,IF($I$152-AM152=-77,23,IF($I$152-AM152=78,22,IF($I$152-AM152=-78,22,IF($I$152-AM152=79,21,IF($I$152-AM152=-79,21,IF($I$152-AM152=80,20,IF($I$152-AM152=-80,20,IF($I$152-AM152=81,19,IF($I$152-AM152=-81,19,IF($I$152-AM152=82,18,IF($I$152-AM152=-82,18,IF($I$152-AM152=83,17,IF($I$152-AM152=-83,17,IF($I$152-AM152=84,16,IF($I$152-AM152=-84,16,IF($I$152-AM152=85,15,IF($I$152-AM152=-85,15,IF($I$152-AM152=86,14,IF($I$152-AM152=-86,14,IF($I$152-AM152=87,13,IF($I$152-AM152=-87,13,IF($I$152-AM152=88,12,IF($I$152-AM152=-88,12,IF($I$152-AM152=89,11,IF($I$152-AM152=-89,11,IF($I$152-AM152=90,10,IF($I$152-AM152=-90,10,IF($I$152-AM152=91,9,IF($I$152-AM152=-91,9,IF($I$152-AM152=92,8,IF($I$152-AM152=-92,8,IF($I$152-AM152=93,7,IF($I$152-AM152=-93,7,IF($I$152-AM152=94,6,IF($I$152-AM152=-94,6,IF($I$152-AM152=95,5,IF($I$152-AM152=-95,5,IF($I$152-AM152=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="AN156" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="AO156" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="AP156" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="AQ156" s="4">
-        <f t="shared" ref="AQ156:AT156" si="56">IF($I$152-AQ152=-65,35,IF($I$152-AQ152=66,34,IF($I$152-AQ152=-66,34,IF($I$152-AQ152=67,33,IF($I$152-AQ152=-67,33,IF($I$152-AQ152=68,32,IF($I$152-AQ152=-68,32,IF($I$152-AQ152=69,31,IF($I$152-AQ152=-69,31,IF($I$152-AQ152=70,30,IF($I$152-AQ152=-70,30,IF($I$152-AQ152=71,29,IF($I$152-AQ152=-71,29,IF($I$152-AQ152=72,28,IF($I$152-AQ152=-72,28,IF($I$152-AQ152=73,27,IF($I$152-AQ152=-73,27,IF($I$152-AQ152=74,26,IF($I$152-AQ152=-74,26,IF($I$152-AQ152=75,25,IF($I$152-AQ152=-75,25,IF($I$152-AQ152=76,24,IF($I$152-AQ152=-76,24,IF($I$152-AQ152=77,23,IF($I$152-AQ152=-77,23,IF($I$152-AQ152=78,22,IF($I$152-AQ152=-78,22,IF($I$152-AQ152=79,21,IF($I$152-AQ152=-79,21,IF($I$152-AQ152=80,20,IF($I$152-AQ152=-80,20,IF($I$152-AQ152=81,19,IF($I$152-AQ152=-81,19,IF($I$152-AQ152=82,18,IF($I$152-AQ152=-82,18,IF($I$152-AQ152=83,17,IF($I$152-AQ152=-83,17,IF($I$152-AQ152=84,16,IF($I$152-AQ152=-84,16,IF($I$152-AQ152=85,15,IF($I$152-AQ152=-85,15,IF($I$152-AQ152=86,14,IF($I$152-AQ152=-86,14,IF($I$152-AQ152=87,13,IF($I$152-AQ152=-87,13,IF($I$152-AQ152=88,12,IF($I$152-AQ152=-88,12,IF($I$152-AQ152=89,11,IF($I$152-AQ152=-89,11,IF($I$152-AQ152=90,10,IF($I$152-AQ152=-90,10,IF($I$152-AQ152=91,9,IF($I$152-AQ152=-91,9,IF($I$152-AQ152=92,8,IF($I$152-AQ152=-92,8,IF($I$152-AQ152=93,7,IF($I$152-AQ152=-93,7,IF($I$152-AQ152=94,6,IF($I$152-AQ152=-94,6,IF($I$152-AQ152=95,5,IF($I$152-AQ152=-95,5,IF($I$152-AQ152=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="AQ156:AT156" si="63">IF($I$152-AQ152=-65,35,IF($I$152-AQ152=66,34,IF($I$152-AQ152=-66,34,IF($I$152-AQ152=67,33,IF($I$152-AQ152=-67,33,IF($I$152-AQ152=68,32,IF($I$152-AQ152=-68,32,IF($I$152-AQ152=69,31,IF($I$152-AQ152=-69,31,IF($I$152-AQ152=70,30,IF($I$152-AQ152=-70,30,IF($I$152-AQ152=71,29,IF($I$152-AQ152=-71,29,IF($I$152-AQ152=72,28,IF($I$152-AQ152=-72,28,IF($I$152-AQ152=73,27,IF($I$152-AQ152=-73,27,IF($I$152-AQ152=74,26,IF($I$152-AQ152=-74,26,IF($I$152-AQ152=75,25,IF($I$152-AQ152=-75,25,IF($I$152-AQ152=76,24,IF($I$152-AQ152=-76,24,IF($I$152-AQ152=77,23,IF($I$152-AQ152=-77,23,IF($I$152-AQ152=78,22,IF($I$152-AQ152=-78,22,IF($I$152-AQ152=79,21,IF($I$152-AQ152=-79,21,IF($I$152-AQ152=80,20,IF($I$152-AQ152=-80,20,IF($I$152-AQ152=81,19,IF($I$152-AQ152=-81,19,IF($I$152-AQ152=82,18,IF($I$152-AQ152=-82,18,IF($I$152-AQ152=83,17,IF($I$152-AQ152=-83,17,IF($I$152-AQ152=84,16,IF($I$152-AQ152=-84,16,IF($I$152-AQ152=85,15,IF($I$152-AQ152=-85,15,IF($I$152-AQ152=86,14,IF($I$152-AQ152=-86,14,IF($I$152-AQ152=87,13,IF($I$152-AQ152=-87,13,IF($I$152-AQ152=88,12,IF($I$152-AQ152=-88,12,IF($I$152-AQ152=89,11,IF($I$152-AQ152=-89,11,IF($I$152-AQ152=90,10,IF($I$152-AQ152=-90,10,IF($I$152-AQ152=91,9,IF($I$152-AQ152=-91,9,IF($I$152-AQ152=92,8,IF($I$152-AQ152=-92,8,IF($I$152-AQ152=93,7,IF($I$152-AQ152=-93,7,IF($I$152-AQ152=94,6,IF($I$152-AQ152=-94,6,IF($I$152-AQ152=95,5,IF($I$152-AQ152=-95,5,IF($I$152-AQ152=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="AR156" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="AS156" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="AT156" s="4">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:46" x14ac:dyDescent="0.3">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:46" x14ac:dyDescent="0.25">
       <c r="F157" s="57"/>
       <c r="G157" s="3"/>
       <c r="H157" s="3"/>
@@ -23076,172 +23044,172 @@
         <v>0</v>
       </c>
       <c r="K157" s="4">
-        <f t="shared" ref="K157:AL157" si="57">IF($I$152-K152=-96,4,IF($I$152-K152=97,3,IF($I$152-K152=-97,3,IF($I$152-K152=98,2,IF($I$152-K152=-98,2,IF($I$152-K152=99,1,IF($I$152-K152=-99,1,IF($I$152-K152=100,0,IF($I$152-K152=-100,0,0)))))))))</f>
+        <f t="shared" ref="K157:AL157" si="64">IF($I$152-K152=-96,4,IF($I$152-K152=97,3,IF($I$152-K152=-97,3,IF($I$152-K152=98,2,IF($I$152-K152=-98,2,IF($I$152-K152=99,1,IF($I$152-K152=-99,1,IF($I$152-K152=100,0,IF($I$152-K152=-100,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="L157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="N157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="O157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="P157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="Q157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="R157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="S157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="T157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="U157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="V157" s="4">
-        <f t="shared" ref="V157:X157" si="58">IF($I$152-V152=-96,4,IF($I$152-V152=97,3,IF($I$152-V152=-97,3,IF($I$152-V152=98,2,IF($I$152-V152=-98,2,IF($I$152-V152=99,1,IF($I$152-V152=-99,1,IF($I$152-V152=100,0,IF($I$152-V152=-100,0,0)))))))))</f>
+        <f t="shared" ref="V157:X157" si="65">IF($I$152-V152=-96,4,IF($I$152-V152=97,3,IF($I$152-V152=-97,3,IF($I$152-V152=98,2,IF($I$152-V152=-98,2,IF($I$152-V152=99,1,IF($I$152-V152=-99,1,IF($I$152-V152=100,0,IF($I$152-V152=-100,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="W157" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="X157" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="Y157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="Z157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AA157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AB157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AC157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AD157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AE157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AF157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AG157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AH157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AI157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AJ157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AK157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AL157" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AM157" s="4">
-        <f t="shared" ref="AM157:AP157" si="59">IF($I$152-AM152=-96,4,IF($I$152-AM152=97,3,IF($I$152-AM152=-97,3,IF($I$152-AM152=98,2,IF($I$152-AM152=-98,2,IF($I$152-AM152=99,1,IF($I$152-AM152=-99,1,IF($I$152-AM152=100,0,IF($I$152-AM152=-100,0,0)))))))))</f>
+        <f t="shared" ref="AM157:AP157" si="66">IF($I$152-AM152=-96,4,IF($I$152-AM152=97,3,IF($I$152-AM152=-97,3,IF($I$152-AM152=98,2,IF($I$152-AM152=-98,2,IF($I$152-AM152=99,1,IF($I$152-AM152=-99,1,IF($I$152-AM152=100,0,IF($I$152-AM152=-100,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="AN157" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AO157" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AP157" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AQ157" s="4">
-        <f t="shared" ref="AQ157:AT157" si="60">IF($I$152-AQ152=-96,4,IF($I$152-AQ152=97,3,IF($I$152-AQ152=-97,3,IF($I$152-AQ152=98,2,IF($I$152-AQ152=-98,2,IF($I$152-AQ152=99,1,IF($I$152-AQ152=-99,1,IF($I$152-AQ152=100,0,IF($I$152-AQ152=-100,0,0)))))))))</f>
+        <f t="shared" ref="AQ157:AT157" si="67">IF($I$152-AQ152=-96,4,IF($I$152-AQ152=97,3,IF($I$152-AQ152=-97,3,IF($I$152-AQ152=98,2,IF($I$152-AQ152=-98,2,IF($I$152-AQ152=99,1,IF($I$152-AQ152=-99,1,IF($I$152-AQ152=100,0,IF($I$152-AQ152=-100,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="AR157" s="4">
-        <f t="shared" si="60"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AS157" s="4">
-        <f t="shared" si="60"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AT157" s="4">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E158" s="136"/>
       <c r="F158" s="136"/>
       <c r="G158" s="136"/>
       <c r="H158" s="136"/>
       <c r="I158" s="3"/>
     </row>
-    <row r="159" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E159" s="136"/>
       <c r="F159" s="136"/>
       <c r="G159" s="136"/>
       <c r="H159" s="136"/>
       <c r="I159" s="3"/>
     </row>
-    <row r="160" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E160" s="136"/>
       <c r="F160" s="136"/>
       <c r="G160" s="136"/>
       <c r="H160" s="136"/>
       <c r="I160" s="3"/>
     </row>
-    <row r="181" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="181" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J181" s="2">
         <v>1</v>
       </c>
@@ -23875,17 +23843,17 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A2:K76"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>8</v>
       </c>
@@ -23916,7 +23884,7 @@
         <v>SUMA(Y($G$8="",$H$8="",J9=0)+Y($G$10="",$H$10="",J11=0)+Y($G$12="",$H$12="",J13=0)+Y($G$14="",$H$14="",J15=0)+Y($G$16="",$H$16="",J17=0)+Y($G$18="",$H$18="",J19=0)+Y($G$20="",$H$20="",J21=0)+Y($G$22="",$H$22="",J23=0)+Y($G$24="",$H$24="",J25=0)+Y($G$26="",$H$26="",J27=0)+Y($G$28="",$H$28="",J29=0)+Y($G$30="",$H$30="",J31=0)+Y($G$32="",$H$32="",J33=0)+Y($G$34="",$H$34="",J35=0)+Y($G$36="",$H$36="",J37=0)+Y($G$38="",$H$38="",J39=0)+Y($G$40="",$H$40="",J41=0)+Y($G$42="",$H$42="",J43=0)+Y($G$44="",$H$44="",J45=0)+Y($G$46="",$H$46="",J47=0)+Y($G$48="",$H$48="",J49=0)+Y($G$50="",$H$50="",J51=0)+Y($G$52="",$H$52="",J53=0)+Y($G$54="",$H$54="",J55=0)+Y($G$56="",$H$56="",J57=0)+Y($G$58="",$H$58="",J59=0)+Y($G$60="",$H$60="",J61=0)+Y($G$62="",$H$62="",J63=0)+Y($G$64="",$H$64="",J65=0)+Y($G$66="",$H$66="",J67=0)+Y($G$68="",$H$68="",J69=0)+Y($G$70="",$H$70="",J71=0)+Y($G$72="",$H$72="",J73=0)+Y($G$74="",$H$74="",J75=0)+Y($G$76="",$H$76="",J77=0)+Y($G$78="",$H$78="",J79=0)+</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>10</v>
       </c>
@@ -23946,7 +23914,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>12</v>
       </c>
@@ -23973,7 +23941,7 @@
         <v>Y($G$12="",$H$12="",J13=0)+</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>14</v>
       </c>
@@ -24000,7 +23968,7 @@
         <v>Y($G$14="",$H$14="",J15=0)+</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>16</v>
       </c>
@@ -24027,7 +23995,7 @@
         <v>Y($G$16="",$H$16="",J17=0)+</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>18</v>
       </c>
@@ -24054,7 +24022,7 @@
         <v>Y($G$18="",$H$18="",J19=0)+</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>20</v>
       </c>
@@ -24081,7 +24049,7 @@
         <v>Y($G$20="",$H$20="",J21=0)+</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>22</v>
       </c>
@@ -24108,7 +24076,7 @@
         <v>Y($G$22="",$H$22="",J23=0)+</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>24</v>
       </c>
@@ -24135,7 +24103,7 @@
         <v>Y($G$24="",$H$24="",J25=0)+</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26</v>
       </c>
@@ -24162,7 +24130,7 @@
         <v>Y($G$26="",$H$26="",J27=0)+</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>28</v>
       </c>
@@ -24189,7 +24157,7 @@
         <v>Y($G$28="",$H$28="",J29=0)+</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>30</v>
       </c>
@@ -24216,7 +24184,7 @@
         <v>Y($G$30="",$H$30="",J31=0)+</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>32</v>
       </c>
@@ -24243,7 +24211,7 @@
         <v>Y($G$32="",$H$32="",J33=0)+</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>34</v>
       </c>
@@ -24270,7 +24238,7 @@
         <v>Y($G$34="",$H$34="",J35=0)+</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>36</v>
       </c>
@@ -24297,7 +24265,7 @@
         <v>Y($G$36="",$H$36="",J37=0)+</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>38</v>
       </c>
@@ -24324,7 +24292,7 @@
         <v>Y($G$38="",$H$38="",J39=0)+</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>40</v>
       </c>
@@ -24351,7 +24319,7 @@
         <v>Y($G$40="",$H$40="",J41=0)+</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>42</v>
       </c>
@@ -24378,7 +24346,7 @@
         <v>Y($G$42="",$H$42="",J43=0)+</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>44</v>
       </c>
@@ -24405,7 +24373,7 @@
         <v>Y($G$44="",$H$44="",J45=0)+</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>46</v>
       </c>
@@ -24432,7 +24400,7 @@
         <v>Y($G$46="",$H$46="",J47=0)+</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>48</v>
       </c>
@@ -24459,7 +24427,7 @@
         <v>Y($G$48="",$H$48="",J49=0)+</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>50</v>
       </c>
@@ -24486,7 +24454,7 @@
         <v>Y($G$50="",$H$50="",J51=0)+</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>52</v>
       </c>
@@ -24513,7 +24481,7 @@
         <v>Y($G$52="",$H$52="",J53=0)+</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>54</v>
       </c>
@@ -24540,7 +24508,7 @@
         <v>Y($G$54="",$H$54="",J55=0)+</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>56</v>
       </c>
@@ -24567,7 +24535,7 @@
         <v>Y($G$56="",$H$56="",J57=0)+</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>58</v>
       </c>
@@ -24594,7 +24562,7 @@
         <v>Y($G$58="",$H$58="",J59=0)+</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>60</v>
       </c>
@@ -24621,7 +24589,7 @@
         <v>Y($G$60="",$H$60="",J61=0)+</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>62</v>
       </c>
@@ -24648,7 +24616,7 @@
         <v>Y($G$62="",$H$62="",J63=0)+</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>64</v>
       </c>
@@ -24675,7 +24643,7 @@
         <v>Y($G$64="",$H$64="",J65=0)+</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>66</v>
       </c>
@@ -24702,7 +24670,7 @@
         <v>Y($G$66="",$H$66="",J67=0)+</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>68</v>
       </c>
@@ -24729,7 +24697,7 @@
         <v>Y($G$68="",$H$68="",J69=0)+</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>70</v>
       </c>
@@ -24756,7 +24724,7 @@
         <v>Y($G$70="",$H$70="",J71=0)+</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>72</v>
       </c>
@@ -24783,7 +24751,7 @@
         <v>Y($G$72="",$H$72="",J73=0)+</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>74</v>
       </c>
@@ -24810,7 +24778,7 @@
         <v>Y($G$74="",$H$74="",J75=0)+</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>76</v>
       </c>
@@ -24837,7 +24805,7 @@
         <v>Y($G$76="",$H$76="",J77=0)+</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>78</v>
       </c>
@@ -24864,7 +24832,7 @@
         <v>Y($G$78="",$H$78="",J79=0)+</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>80</v>
       </c>
@@ -24895,7 +24863,7 @@
         <v>SUMA(Y($G$80="",$H$80="",J81=0)+Y($G$82="",$H$82="",J83=0)+Y($G$84="",$H$84="",J85=0)+Y($G$86="",$H$86="",J87=0)+Y($G$88="",$H$88="",J89=0)+Y($G$90="",$H$90="",J91=0)+Y($G$92="",$H$92="",J93=0)+Y($G$94="",$H$94="",J95=0)+Y($G$96="",$H$96="",J97=0)+Y($G$98="",$H$98="",J99=0)+Y($G$100="",$H$100="",J101=0)+Y($G$102="",$H$102="",J103=0)+Y($G$104="",$H$104="",J105=0)+Y($G$106="",$H$106="",J107=0)+Y($G$108="",$H$108="",J109=0)+Y($G$110="",$H$110="",J111=0)+Y($G$112="",$H$112="",J113=0)+Y($G$114="",$H$114="",J115=0)+Y($G$116="",$H$116="",J117=0)+Y($G$118="",$H$118="",J119=0)+Y($G$120="",$H$120="",J121=0)+Y($G$122="",$H$122="",J123=0)+Y($G$124="",$H$124="",J125=0)+Y($G$126="",$H$126="",J127=0)+Y($G$128="",$H$128="",J129=0)+Y($G$130="",$H$130="",J131=0)+Y($G$132="",$H$132="",J133=0)+Y($G$134="",$H$134="",J135=0)+Y($G$136="",$H$136="",J137=0)+Y($G$138="",$H$138="",J139=0)+Y($G$140="",$H$140="",J141=0)+Y($G$142="",$H$142="",J143=0)+Y($G$144="",$H$144="",J145=0)+Y($G$146="",$H$146="",J147=0)+Y($G$148="",$H$148="",J149=0)+Y($G$150="",$H$150="",J151=0)+</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>82</v>
       </c>
@@ -24925,7 +24893,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>84</v>
       </c>
@@ -24952,7 +24920,7 @@
         <v>Y($G$84="",$H$84="",J85=0)+</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>86</v>
       </c>
@@ -24979,7 +24947,7 @@
         <v>Y($G$86="",$H$86="",J87=0)+</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>88</v>
       </c>
@@ -25006,7 +24974,7 @@
         <v>Y($G$88="",$H$88="",J89=0)+</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>90</v>
       </c>
@@ -25033,7 +25001,7 @@
         <v>Y($G$90="",$H$90="",J91=0)+</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>92</v>
       </c>
@@ -25060,7 +25028,7 @@
         <v>Y($G$92="",$H$92="",J93=0)+</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>94</v>
       </c>
@@ -25087,7 +25055,7 @@
         <v>Y($G$94="",$H$94="",J95=0)+</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>96</v>
       </c>
@@ -25114,7 +25082,7 @@
         <v>Y($G$96="",$H$96="",J97=0)+</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>98</v>
       </c>
@@ -25141,7 +25109,7 @@
         <v>Y($G$98="",$H$98="",J99=0)+</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>100</v>
       </c>
@@ -25168,7 +25136,7 @@
         <v>Y($G$100="",$H$100="",J101=0)+</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>102</v>
       </c>
@@ -25195,7 +25163,7 @@
         <v>Y($G$102="",$H$102="",J103=0)+</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>104</v>
       </c>
@@ -25222,7 +25190,7 @@
         <v>Y($G$104="",$H$104="",J105=0)+</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>106</v>
       </c>
@@ -25249,7 +25217,7 @@
         <v>Y($G$106="",$H$106="",J107=0)+</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>108</v>
       </c>
@@ -25276,7 +25244,7 @@
         <v>Y($G$108="",$H$108="",J109=0)+</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>110</v>
       </c>
@@ -25303,7 +25271,7 @@
         <v>Y($G$110="",$H$110="",J111=0)+</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>112</v>
       </c>
@@ -25330,7 +25298,7 @@
         <v>Y($G$112="",$H$112="",J113=0)+</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>114</v>
       </c>
@@ -25357,7 +25325,7 @@
         <v>Y($G$114="",$H$114="",J115=0)+</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>116</v>
       </c>
@@ -25384,7 +25352,7 @@
         <v>Y($G$116="",$H$116="",J117=0)+</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>118</v>
       </c>
@@ -25411,7 +25379,7 @@
         <v>Y($G$118="",$H$118="",J119=0)+</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>120</v>
       </c>
@@ -25438,7 +25406,7 @@
         <v>Y($G$120="",$H$120="",J121=0)+</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>122</v>
       </c>
@@ -25465,7 +25433,7 @@
         <v>Y($G$122="",$H$122="",J123=0)+</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>124</v>
       </c>
@@ -25492,7 +25460,7 @@
         <v>Y($G$124="",$H$124="",J125=0)+</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>126</v>
       </c>
@@ -25519,7 +25487,7 @@
         <v>Y($G$126="",$H$126="",J127=0)+</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>128</v>
       </c>
@@ -25546,7 +25514,7 @@
         <v>Y($G$128="",$H$128="",J129=0)+</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>130</v>
       </c>
@@ -25573,7 +25541,7 @@
         <v>Y($G$130="",$H$130="",J131=0)+</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>132</v>
       </c>
@@ -25600,7 +25568,7 @@
         <v>Y($G$132="",$H$132="",J133=0)+</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>134</v>
       </c>
@@ -25627,7 +25595,7 @@
         <v>Y($G$134="",$H$134="",J135=0)+</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>136</v>
       </c>
@@ -25654,7 +25622,7 @@
         <v>Y($G$136="",$H$136="",J137=0)+</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>138</v>
       </c>
@@ -25681,7 +25649,7 @@
         <v>Y($G$138="",$H$138="",J139=0)+</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>140</v>
       </c>
@@ -25708,7 +25676,7 @@
         <v>Y($G$140="",$H$140="",J141=0)+</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>142</v>
       </c>
@@ -25735,7 +25703,7 @@
         <v>Y($G$142="",$H$142="",J143=0)+</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>144</v>
       </c>
@@ -25762,7 +25730,7 @@
         <v>Y($G$144="",$H$144="",J145=0)+</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>146</v>
       </c>
@@ -25789,7 +25757,7 @@
         <v>Y($G$146="",$H$146="",J147=0)+</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>148</v>
       </c>
@@ -25816,7 +25784,7 @@
         <v>Y($G$148="",$H$148="",J149=0)+</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>150</v>
       </c>
@@ -25854,21 +25822,21 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:AF65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.88671875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="6.109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" style="3" customWidth="1"/>
-    <col min="9" max="24" width="5.33203125" style="3" customWidth="1"/>
-    <col min="25" max="30" width="11.44140625" style="3"/>
+    <col min="2" max="2" width="13.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.85546875" style="3" customWidth="1"/>
+    <col min="6" max="7" width="6.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" style="3" customWidth="1"/>
+    <col min="9" max="24" width="5.28515625" style="3" customWidth="1"/>
+    <col min="25" max="30" width="11.42578125" style="3"/>
     <col min="31" max="32" width="0" style="3" hidden="1" customWidth="1"/>
-    <col min="33" max="16384" width="11.44140625" style="3"/>
+    <col min="33" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="99" t="s">
         <v>28</v>
       </c>
@@ -25928,7 +25896,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -25954,7 +25922,7 @@
       <c r="W2" s="38"/>
       <c r="X2" s="39"/>
     </row>
-    <row r="3" spans="1:32" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -26045,7 +26013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="125" t="s">
         <v>77</v>
       </c>
@@ -26084,7 +26052,7 @@
       <c r="W4" s="17"/>
       <c r="X4" s="22"/>
     </row>
-    <row r="5" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="103"/>
       <c r="B5" s="133"/>
       <c r="C5" s="154"/>
@@ -26148,7 +26116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="103"/>
       <c r="B6" s="132">
         <v>46203</v>
@@ -26191,7 +26159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="103"/>
       <c r="B7" s="133"/>
       <c r="C7" s="154"/>
@@ -26255,7 +26223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="103"/>
       <c r="B8" s="132">
         <v>46201</v>
@@ -26296,7 +26264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="103"/>
       <c r="B9" s="133"/>
       <c r="C9" s="154"/>
@@ -26358,7 +26326,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="103"/>
       <c r="B10" s="132">
         <v>46202</v>
@@ -26399,7 +26367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="103"/>
       <c r="B11" s="133"/>
       <c r="C11" s="154"/>
@@ -26461,7 +26429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="103"/>
       <c r="B12" s="130">
         <v>46205</v>
@@ -26502,7 +26470,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="103"/>
       <c r="B13" s="131"/>
       <c r="C13" s="156"/>
@@ -26564,7 +26532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="103"/>
       <c r="B14" s="130">
         <v>46205</v>
@@ -26605,7 +26573,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="103"/>
       <c r="B15" s="131"/>
       <c r="C15" s="156"/>
@@ -26667,7 +26635,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="103"/>
       <c r="B16" s="130">
         <v>46204</v>
@@ -26708,7 +26676,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="103"/>
       <c r="B17" s="131"/>
       <c r="C17" s="156"/>
@@ -26770,7 +26738,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="103"/>
       <c r="B18" s="130">
         <v>46204</v>
@@ -26811,7 +26779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="103"/>
       <c r="B19" s="131"/>
       <c r="C19" s="156"/>
@@ -26873,7 +26841,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="125" t="s">
         <v>78</v>
       </c>
@@ -26912,7 +26880,7 @@
       <c r="W20" s="18"/>
       <c r="X20" s="24"/>
     </row>
-    <row r="21" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="103"/>
       <c r="B21" s="133"/>
       <c r="C21" s="154"/>
@@ -26970,7 +26938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="103"/>
       <c r="B22" s="132">
         <v>46203</v>
@@ -27007,7 +26975,7 @@
       <c r="W22" s="13"/>
       <c r="X22" s="25"/>
     </row>
-    <row r="23" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="103"/>
       <c r="B23" s="133"/>
       <c r="C23" s="154"/>
@@ -27065,7 +27033,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="103"/>
       <c r="B24" s="132">
         <v>46203</v>
@@ -27102,7 +27070,7 @@
       <c r="W24" s="18"/>
       <c r="X24" s="24"/>
     </row>
-    <row r="25" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="103"/>
       <c r="B25" s="133"/>
       <c r="C25" s="154"/>
@@ -27160,7 +27128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="103"/>
       <c r="B26" s="132">
         <v>46204</v>
@@ -27197,7 +27165,7 @@
       <c r="W26" s="13"/>
       <c r="X26" s="25"/>
     </row>
-    <row r="27" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="103"/>
       <c r="B27" s="133"/>
       <c r="C27" s="154"/>
@@ -27255,7 +27223,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="103"/>
       <c r="B28" s="130">
         <v>46206</v>
@@ -27292,7 +27260,7 @@
       <c r="W28" s="19"/>
       <c r="X28" s="28"/>
     </row>
-    <row r="29" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="103"/>
       <c r="B29" s="131"/>
       <c r="C29" s="156"/>
@@ -27350,7 +27318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="103"/>
       <c r="B30" s="130">
         <v>46206</v>
@@ -27387,7 +27355,7 @@
       <c r="W30" s="13"/>
       <c r="X30" s="25"/>
     </row>
-    <row r="31" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="103"/>
       <c r="B31" s="131"/>
       <c r="C31" s="156"/>
@@ -27445,7 +27413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="103"/>
       <c r="B32" s="130">
         <v>46205</v>
@@ -27482,7 +27450,7 @@
       <c r="W32" s="19"/>
       <c r="X32" s="28"/>
     </row>
-    <row r="33" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="103"/>
       <c r="B33" s="131"/>
       <c r="C33" s="156"/>
@@ -27540,7 +27508,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="103"/>
       <c r="B34" s="130">
         <v>46206</v>
@@ -27577,7 +27545,7 @@
       <c r="W34" s="13"/>
       <c r="X34" s="25"/>
     </row>
-    <row r="35" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="104"/>
       <c r="B35" s="131"/>
       <c r="C35" s="156"/>
@@ -27635,7 +27603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E36" s="151" t="s">
         <v>10</v>
       </c>
@@ -27710,7 +27678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:24" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E37" s="135" t="s">
         <v>14</v>
       </c>
@@ -27782,7 +27750,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="I38" s="4">
         <f>IF(I36=$H$36,100,IF($H$36-I36=1,99,IF($H$36-I36=-1,99,IF($H$36-I36=2,98,IF($H$36-I36=-2,98,IF($H$36-I36=3,97,IF($H$36-I36=-3,97,IF($H$36-I36=4,96,IF($H$36-I36=-4,96,IF($H$36-I36=5,95,IF($H$36-I36=-5,95,IF($H$36-I36=6,94,IF($H$36-I36=-6,94,IF($H$36-I36=7,93,IF($H$36-I36=-7,93,IF($H$36-I36=8,92,IF($H$36-I36=-8,92,IF($H$36-I36=9,91,IF($H$36-I36=-9,91,IF($H$36-I36=10,90,IF($H$36-I36=-10,90,IF($H$36-I36=11,89,IF($H$36-I36=-11,89,IF($H$36-I36=12,88,IF($H$36-I36=-12,88,IF($H$36-I36=13,87,IF($H$36-I36=-13,87,IF($H$36-I36=14,86,IF($H$36-I36=-14,86,IF($H$36-I36=15,85,IF($H$36-I36=-15,85,IF($H$36-I36=16,84,IF($H$36-I36=-16,84,IF($H$36-I36=17,83,IF($H$36-I36=-17,83,IF($H$36-I36=18,82,IF($H$36-I36=-18,82,IF($H$36-I36=19,81,IF($H$36-I36=-19,81,IF($H$36-I36=20,80,IF($H$36-I36=-20,80,IF($H$36-I36=21,79,IF($H$36-I36=-21,79,IF($H$36-I36=22,78,IF($H$36-I36=-22,78,IF($H$36-I36=23,77,IF($H$36-I36=-23,77,IF($H$36-I36=24,76,IF($H$36-I36=-24,76,IF($H$36-I36=25,75,IF($H$36-I36=-25,75,IF($H$36-I36=26,74,IF($H$36-I36=-26,74,IF($H$36-I36=27,73,IF($H$36-I36=-27,73,IF($H$36-I36=28,72,IF($H$36-I36=-28,72,IF($H$36-I36=29,71,IF($H$36-I36=-29,71,IF($H$36-I36=30,70,IF($H$36-I36=-30,70,IF($H$36-I36=31,69,IF($H$36-I36=-31,69,IF($H$36-I36=32,68,IF($H$36-I36=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>100</v>
@@ -27848,7 +27816,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="I39" s="4">
         <f>IF($H$36-I36=33,67,IF($H$36-I36=-33,67,IF($H$36-I36=34,66,IF($H$36-I36=-34,66,IF($H$36-I36=35,65,IF($H$36-I36=-35,65,IF($H$36-I36=36,64,IF($H$36-I36=-36,64,IF($H$36-I36=37,63,IF($H$36-I36=-37,63,IF($H$36-I36=38,62,IF($H$36-I36=-38,62,IF($H$36-I36=39,61,IF($H$36-I36=-39,61,IF($H$36-I36=40,60,IF($H$36-I36=-40,60,IF($H$36-I36=41,59,IF($H$36-I36=-41,59,IF($H$36-I36=42,58,IF($H$36-I36=-42,58,IF($H$36-I36=43,57,IF($H$36-I36=-43,57,IF($H$36-I36=44,56,IF($H$36-I36=-44,56,IF($H$36-I36=45,55,IF($H$36-I36=-45,55,IF($H$36-I36=46,54,IF($H$36-I36=-46,54,IF($H$36-I36=47,53,IF($H$36-I36=-47,53,IF($H$36-I36=48,52,IF($H$36-I36=-48,52,IF($H$36-I36=49,51,IF($H$36-I36=-49,51,IF($H$36-I36=50,50,IF($H$36-I36=-50,50,IF($H$36-I36=51,49,IF($H$36-I36=-51,49,IF($H$36-I36=52,48,IF($H$36-I36=-52,48,IF($H$36-I36=53,47,IF($H$36-I36=-53,47,IF($H$36-I36=54,46,IF($H$36-I36=-54,46,IF($H$36-I36=55,45,IF($H$36-I36=-55,45,IF($H$36-I36=56,44,IF($H$36-I36=-56,44,IF($H$36-I36=57,43,IF($H$36-I36=-57,43,IF($H$36-I36=58,42,IF($H$36-I36=-58,42,IF($H$36-I36=59,41,IF($H$36-I36=-59,41,IF($H$36-I36=60,40,IF($H$36-I36=-60,40,IF($H$36-I36=61,39,IF($H$36-I36=-61,39,IF($H$36-I36=62,38,IF($H$36-I36=-62,38,IF($H$36-I36=63,37,IF($H$36-I36=-63,37,IF($H$36-I36=64,36,IF($H$36-I36=-64,36,IF($H$36-I36=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -27914,7 +27882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="I40" s="4">
         <f>IF($H$36-I36=-65,35,IF($H$36-I36=66,34,IF($H$36-I36=-66,34,IF($H$36-I36=67,33,IF($H$36-I36=-67,33,IF($H$36-I36=68,32,IF($H$36-I36=-68,32,IF($H$36-I36=69,31,IF($H$36-I36=-69,31,IF($H$36-I36=70,30,IF($H$36-I36=-70,30,IF($H$36-I36=71,29,IF($H$36-I36=-71,29,IF($H$36-I36=72,28,IF($H$36-I36=-72,28,IF($H$36-I36=73,27,IF($H$36-I36=-73,27,IF($H$36-I36=74,26,IF($H$36-I36=-74,26,IF($H$36-I36=75,25,IF($H$36-I36=-75,25,IF($H$36-I36=76,24,IF($H$36-I36=-76,24,IF($H$36-I36=77,23,IF($H$36-I36=-77,23,IF($H$36-I36=78,22,IF($H$36-I36=-78,22,IF($H$36-I36=79,21,IF($H$36-I36=-79,21,IF($H$36-I36=80,20,IF($H$36-I36=-80,20,IF($H$36-I36=81,19,IF($H$36-I36=-81,19,IF($H$36-I36=82,18,IF($H$36-I36=-82,18,IF($H$36-I36=83,17,IF($H$36-I36=-83,17,IF($H$36-I36=84,16,IF($H$36-I36=-84,16,IF($H$36-I36=85,15,IF($H$36-I36=-85,15,IF($H$36-I36=86,14,IF($H$36-I36=-86,14,IF($H$36-I36=87,13,IF($H$36-I36=-87,13,IF($H$36-I36=88,12,IF($H$36-I36=-88,12,IF($H$36-I36=89,11,IF($H$36-I36=-89,11,IF($H$36-I36=90,10,IF($H$36-I36=-90,10,IF($H$36-I36=91,9,IF($H$36-I36=-91,9,IF($H$36-I36=92,8,IF($H$36-I36=-92,8,IF($H$36-I36=93,7,IF($H$36-I36=-93,7,IF($H$36-I36=94,6,IF($H$36-I36=-94,6,IF($H$36-I36=95,5,IF($H$36-I36=-95,5,IF($H$36-I36=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -27980,7 +27948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="I41" s="4">
         <f>IF($H$36-I36=-96,4,IF($H$36-I36=97,3,IF($H$36-I36=-97,3,IF($H$36-I36=98,2,IF($H$36-I36=-98,2,IF($H$36-I36=99,1,IF($H$36-I36=-99,1,IF($H$36-I36=100,0,IF($H$36-I36=-100,0,0)))))))))</f>
         <v>0</v>
@@ -28046,25 +28014,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="152"/>
       <c r="E42" s="152"/>
       <c r="F42" s="152"/>
       <c r="G42" s="152"/>
     </row>
-    <row r="43" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="152"/>
       <c r="E43" s="152"/>
       <c r="F43" s="152"/>
       <c r="G43" s="152"/>
     </row>
-    <row r="44" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="152"/>
       <c r="E44" s="152"/>
       <c r="F44" s="152"/>
       <c r="G44" s="152"/>
     </row>
-    <row r="65" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I65" s="3">
         <v>1</v>
       </c>
@@ -28215,21 +28183,21 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:Y49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.88671875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="6.109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" style="3" customWidth="1"/>
-    <col min="9" max="17" width="5.33203125" style="3" customWidth="1"/>
-    <col min="18" max="23" width="11.44140625" style="3"/>
+    <col min="2" max="2" width="13.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.85546875" style="3" customWidth="1"/>
+    <col min="6" max="7" width="6.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" style="3" customWidth="1"/>
+    <col min="9" max="17" width="5.28515625" style="3" customWidth="1"/>
+    <col min="18" max="23" width="11.42578125" style="3"/>
     <col min="24" max="25" width="0" style="3" hidden="1" customWidth="1"/>
-    <col min="26" max="16384" width="11.44140625" style="3"/>
+    <col min="26" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="99" t="s">
         <v>28</v>
       </c>
@@ -28268,7 +28236,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -28287,7 +28255,7 @@
       <c r="P2" s="38"/>
       <c r="Q2" s="39"/>
     </row>
-    <row r="3" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -28356,7 +28324,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="125" t="s">
         <v>77</v>
       </c>
@@ -28388,7 +28356,7 @@
       <c r="P4" s="17"/>
       <c r="Q4" s="22"/>
     </row>
-    <row r="5" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="103"/>
       <c r="B5" s="133"/>
       <c r="C5" s="154"/>
@@ -28431,7 +28399,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="103"/>
       <c r="B6" s="132">
         <v>46207</v>
@@ -28467,7 +28435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="103"/>
       <c r="B7" s="133"/>
       <c r="C7" s="154"/>
@@ -28510,7 +28478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="103"/>
       <c r="B8" s="132">
         <v>46209</v>
@@ -28544,7 +28512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="103"/>
       <c r="B9" s="133"/>
       <c r="C9" s="154"/>
@@ -28585,7 +28553,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="103"/>
       <c r="B10" s="132">
         <v>46209</v>
@@ -28619,7 +28587,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="103"/>
       <c r="B11" s="133"/>
       <c r="C11" s="154"/>
@@ -28660,7 +28628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="125" t="s">
         <v>78</v>
       </c>
@@ -28692,7 +28660,7 @@
       <c r="P12" s="19"/>
       <c r="Q12" s="28"/>
     </row>
-    <row r="13" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="103"/>
       <c r="B13" s="131"/>
       <c r="C13" s="156"/>
@@ -28729,7 +28697,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="103"/>
       <c r="B14" s="130">
         <v>46208</v>
@@ -28759,7 +28727,7 @@
       <c r="P14" s="13"/>
       <c r="Q14" s="25"/>
     </row>
-    <row r="15" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="103"/>
       <c r="B15" s="131"/>
       <c r="C15" s="156"/>
@@ -28796,7 +28764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="103"/>
       <c r="B16" s="130">
         <v>46210</v>
@@ -28826,7 +28794,7 @@
       <c r="P16" s="19"/>
       <c r="Q16" s="28"/>
     </row>
-    <row r="17" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="103"/>
       <c r="B17" s="131"/>
       <c r="C17" s="156"/>
@@ -28863,7 +28831,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="103"/>
       <c r="B18" s="130">
         <v>46210</v>
@@ -28893,7 +28861,7 @@
       <c r="P18" s="13"/>
       <c r="Q18" s="25"/>
     </row>
-    <row r="19" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="104"/>
       <c r="B19" s="131"/>
       <c r="C19" s="156"/>
@@ -28930,7 +28898,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E20" s="151" t="s">
         <v>10</v>
       </c>
@@ -28977,7 +28945,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E21" s="135" t="s">
         <v>14</v>
       </c>
@@ -29021,7 +28989,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="I22" s="4" t="e">
         <f>IF(I20=$H$20,100,IF($H$20-I20=1,99,IF($H$20-I20=-1,99,IF($H$20-I20=2,98,IF($H$20-I20=-2,98,IF($H$20-I20=3,97,IF($H$20-I20=-3,97,IF($H$20-I20=4,96,IF($H$20-I20=-4,96,IF($H$20-I20=5,95,IF($H$20-I20=-5,95,IF($H$20-I20=6,94,IF($H$20-I20=-6,94,IF($H$20-I20=7,93,IF($H$20-I20=-7,93,IF($H$20-I20=8,92,IF($H$20-I20=-8,92,IF($H$20-I20=9,91,IF($H$20-I20=-9,91,IF($H$20-I20=10,90,IF($H$20-I20=-10,90,IF($H$20-I20=11,89,IF($H$20-I20=-11,89,IF($H$20-I20=12,88,IF($H$20-I20=-12,88,IF($H$20-I20=13,87,IF($H$20-I20=-13,87,IF($H$20-I20=14,86,IF($H$20-I20=-14,86,IF($H$20-I20=15,85,IF($H$20-I20=-15,85,IF($H$20-I20=16,84,IF($H$20-I20=-16,84,IF($H$20-I20=17,83,IF($H$20-I20=-17,83,IF($H$20-I20=18,82,IF($H$20-I20=-18,82,IF($H$20-I20=19,81,IF($H$20-I20=-19,81,IF($H$20-I20=20,80,IF($H$20-I20=-20,80,IF($H$20-I20=21,79,IF($H$20-I20=-21,79,IF($H$20-I20=22,78,IF($H$20-I20=-22,78,IF($H$20-I20=23,77,IF($H$20-I20=-23,77,IF($H$20-I20=24,76,IF($H$20-I20=-24,76,IF($H$20-I20=25,75,IF($H$20-I20=-25,75,IF($H$20-I20=26,74,IF($H$20-I20=-26,74,IF($H$20-I20=27,73,IF($H$20-I20=-27,73,IF($H$20-I20=28,72,IF($H$20-I20=-28,72,IF($H$20-I20=29,71,IF($H$20-I20=-29,71,IF($H$20-I20=30,70,IF($H$20-I20=-30,70,IF($H$20-I20=31,69,IF($H$20-I20=-31,69,IF($H$20-I20=32,68,IF($H$20-I20=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>#REF!</v>
@@ -29059,7 +29027,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I23" s="4" t="e">
         <f>IF($H$20-I20=33,67,IF($H$20-I20=-33,67,IF($H$20-I20=34,66,IF($H$20-I20=-34,66,IF($H$20-I20=35,65,IF($H$20-I20=-35,65,IF($H$20-I20=36,64,IF($H$20-I20=-36,64,IF($H$20-I20=37,63,IF($H$20-I20=-37,63,IF($H$20-I20=38,62,IF($H$20-I20=-38,62,IF($H$20-I20=39,61,IF($H$20-I20=-39,61,IF($H$20-I20=40,60,IF($H$20-I20=-40,60,IF($H$20-I20=41,59,IF($H$20-I20=-41,59,IF($H$20-I20=42,58,IF($H$20-I20=-42,58,IF($H$20-I20=43,57,IF($H$20-I20=-43,57,IF($H$20-I20=44,56,IF($H$20-I20=-44,56,IF($H$20-I20=45,55,IF($H$20-I20=-45,55,IF($H$20-I20=46,54,IF($H$20-I20=-46,54,IF($H$20-I20=47,53,IF($H$20-I20=-47,53,IF($H$20-I20=48,52,IF($H$20-I20=-48,52,IF($H$20-I20=49,51,IF($H$20-I20=-49,51,IF($H$20-I20=50,50,IF($H$20-I20=-50,50,IF($H$20-I20=51,49,IF($H$20-I20=-51,49,IF($H$20-I20=52,48,IF($H$20-I20=-52,48,IF($H$20-I20=53,47,IF($H$20-I20=-53,47,IF($H$20-I20=54,46,IF($H$20-I20=-54,46,IF($H$20-I20=55,45,IF($H$20-I20=-55,45,IF($H$20-I20=56,44,IF($H$20-I20=-56,44,IF($H$20-I20=57,43,IF($H$20-I20=-57,43,IF($H$20-I20=58,42,IF($H$20-I20=-58,42,IF($H$20-I20=59,41,IF($H$20-I20=-59,41,IF($H$20-I20=60,40,IF($H$20-I20=-60,40,IF($H$20-I20=61,39,IF($H$20-I20=-61,39,IF($H$20-I20=62,38,IF($H$20-I20=-62,38,IF($H$20-I20=63,37,IF($H$20-I20=-63,37,IF($H$20-I20=64,36,IF($H$20-I20=-64,36,IF($H$20-I20=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>#REF!</v>
@@ -29097,7 +29065,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I24" s="4" t="e">
         <f>IF($H$20-I20=-65,35,IF($H$20-I20=66,34,IF($H$20-I20=-66,34,IF($H$20-I20=67,33,IF($H$20-I20=-67,33,IF($H$20-I20=68,32,IF($H$20-I20=-68,32,IF($H$20-I20=69,31,IF($H$20-I20=-69,31,IF($H$20-I20=70,30,IF($H$20-I20=-70,30,IF($H$20-I20=71,29,IF($H$20-I20=-71,29,IF($H$20-I20=72,28,IF($H$20-I20=-72,28,IF($H$20-I20=73,27,IF($H$20-I20=-73,27,IF($H$20-I20=74,26,IF($H$20-I20=-74,26,IF($H$20-I20=75,25,IF($H$20-I20=-75,25,IF($H$20-I20=76,24,IF($H$20-I20=-76,24,IF($H$20-I20=77,23,IF($H$20-I20=-77,23,IF($H$20-I20=78,22,IF($H$20-I20=-78,22,IF($H$20-I20=79,21,IF($H$20-I20=-79,21,IF($H$20-I20=80,20,IF($H$20-I20=-80,20,IF($H$20-I20=81,19,IF($H$20-I20=-81,19,IF($H$20-I20=82,18,IF($H$20-I20=-82,18,IF($H$20-I20=83,17,IF($H$20-I20=-83,17,IF($H$20-I20=84,16,IF($H$20-I20=-84,16,IF($H$20-I20=85,15,IF($H$20-I20=-85,15,IF($H$20-I20=86,14,IF($H$20-I20=-86,14,IF($H$20-I20=87,13,IF($H$20-I20=-87,13,IF($H$20-I20=88,12,IF($H$20-I20=-88,12,IF($H$20-I20=89,11,IF($H$20-I20=-89,11,IF($H$20-I20=90,10,IF($H$20-I20=-90,10,IF($H$20-I20=91,9,IF($H$20-I20=-91,9,IF($H$20-I20=92,8,IF($H$20-I20=-92,8,IF($H$20-I20=93,7,IF($H$20-I20=-93,7,IF($H$20-I20=94,6,IF($H$20-I20=-94,6,IF($H$20-I20=95,5,IF($H$20-I20=-95,5,IF($H$20-I20=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>#REF!</v>
@@ -29135,7 +29103,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I25" s="4" t="e">
         <f>IF($H$20-I20=-96,4,IF($H$20-I20=97,3,IF($H$20-I20=-97,3,IF($H$20-I20=98,2,IF($H$20-I20=-98,2,IF($H$20-I20=99,1,IF($H$20-I20=-99,1,IF($H$20-I20=100,0,IF($H$20-I20=-100,0,0)))))))))</f>
         <v>#REF!</v>
@@ -29173,25 +29141,25 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="152"/>
       <c r="E26" s="152"/>
       <c r="F26" s="152"/>
       <c r="G26" s="152"/>
     </row>
-    <row r="27" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="152"/>
       <c r="E27" s="152"/>
       <c r="F27" s="152"/>
       <c r="G27" s="152"/>
     </row>
-    <row r="28" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="152"/>
       <c r="E28" s="152"/>
       <c r="F28" s="152"/>
       <c r="G28" s="152"/>
     </row>
-    <row r="49" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I49" s="3">
         <v>1</v>
       </c>
@@ -29286,21 +29254,21 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:V41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.88671875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="6.109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" style="3" customWidth="1"/>
-    <col min="9" max="14" width="5.33203125" style="3" customWidth="1"/>
-    <col min="15" max="20" width="11.44140625" style="3"/>
+    <col min="2" max="2" width="13.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.85546875" style="3" customWidth="1"/>
+    <col min="6" max="7" width="6.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" style="3" customWidth="1"/>
+    <col min="9" max="14" width="5.28515625" style="3" customWidth="1"/>
+    <col min="15" max="20" width="11.42578125" style="3"/>
     <col min="21" max="22" width="0" style="3" hidden="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.44140625" style="3"/>
+    <col min="23" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="99" t="s">
         <v>28</v>
       </c>
@@ -29330,7 +29298,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -29346,7 +29314,7 @@
       <c r="M2" s="38"/>
       <c r="N2" s="39"/>
     </row>
-    <row r="3" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -29394,7 +29362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="125" t="s">
         <v>77</v>
       </c>
@@ -29423,7 +29391,7 @@
       <c r="M4" s="17"/>
       <c r="N4" s="22"/>
     </row>
-    <row r="5" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="103"/>
       <c r="B5" s="133"/>
       <c r="C5" s="154"/>
@@ -29457,7 +29425,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="103"/>
       <c r="B6" s="132">
         <v>46213</v>
@@ -29490,7 +29458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="103"/>
       <c r="B7" s="133"/>
       <c r="C7" s="154"/>
@@ -29524,7 +29492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="125" t="s">
         <v>78</v>
       </c>
@@ -29553,7 +29521,7 @@
       <c r="M8" s="19"/>
       <c r="N8" s="28"/>
     </row>
-    <row r="9" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="103"/>
       <c r="B9" s="131"/>
       <c r="C9" s="156"/>
@@ -29581,7 +29549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="103"/>
       <c r="B10" s="130">
         <v>46214</v>
@@ -29608,7 +29576,7 @@
       <c r="M10" s="13"/>
       <c r="N10" s="25"/>
     </row>
-    <row r="11" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="104"/>
       <c r="B11" s="131"/>
       <c r="C11" s="156"/>
@@ -29636,7 +29604,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E12" s="151" t="s">
         <v>10</v>
       </c>
@@ -29671,7 +29639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E13" s="135" t="s">
         <v>14</v>
       </c>
@@ -29703,7 +29671,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="I14" s="4">
         <f>IF(I12=$H$12,100,IF($H$12-I12=1,99,IF($H$12-I12=-1,99,IF($H$12-I12=2,98,IF($H$12-I12=-2,98,IF($H$12-I12=3,97,IF($H$12-I12=-3,97,IF($H$12-I12=4,96,IF($H$12-I12=-4,96,IF($H$12-I12=5,95,IF($H$12-I12=-5,95,IF($H$12-I12=6,94,IF($H$12-I12=-6,94,IF($H$12-I12=7,93,IF($H$12-I12=-7,93,IF($H$12-I12=8,92,IF($H$12-I12=-8,92,IF($H$12-I12=9,91,IF($H$12-I12=-9,91,IF($H$12-I12=10,90,IF($H$12-I12=-10,90,IF($H$12-I12=11,89,IF($H$12-I12=-11,89,IF($H$12-I12=12,88,IF($H$12-I12=-12,88,IF($H$12-I12=13,87,IF($H$12-I12=-13,87,IF($H$12-I12=14,86,IF($H$12-I12=-14,86,IF($H$12-I12=15,85,IF($H$12-I12=-15,85,IF($H$12-I12=16,84,IF($H$12-I12=-16,84,IF($H$12-I12=17,83,IF($H$12-I12=-17,83,IF($H$12-I12=18,82,IF($H$12-I12=-18,82,IF($H$12-I12=19,81,IF($H$12-I12=-19,81,IF($H$12-I12=20,80,IF($H$12-I12=-20,80,IF($H$12-I12=21,79,IF($H$12-I12=-21,79,IF($H$12-I12=22,78,IF($H$12-I12=-22,78,IF($H$12-I12=23,77,IF($H$12-I12=-23,77,IF($H$12-I12=24,76,IF($H$12-I12=-24,76,IF($H$12-I12=25,75,IF($H$12-I12=-25,75,IF($H$12-I12=26,74,IF($H$12-I12=-26,74,IF($H$12-I12=27,73,IF($H$12-I12=-27,73,IF($H$12-I12=28,72,IF($H$12-I12=-28,72,IF($H$12-I12=29,71,IF($H$12-I12=-29,71,IF($H$12-I12=30,70,IF($H$12-I12=-30,70,IF($H$12-I12=31,69,IF($H$12-I12=-31,69,IF($H$12-I12=32,68,IF($H$12-I12=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>100</v>
@@ -29729,7 +29697,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I15" s="4">
         <f>IF($H$12-I12=33,67,IF($H$12-I12=-33,67,IF($H$12-I12=34,66,IF($H$12-I12=-34,66,IF($H$12-I12=35,65,IF($H$12-I12=-35,65,IF($H$12-I12=36,64,IF($H$12-I12=-36,64,IF($H$12-I12=37,63,IF($H$12-I12=-37,63,IF($H$12-I12=38,62,IF($H$12-I12=-38,62,IF($H$12-I12=39,61,IF($H$12-I12=-39,61,IF($H$12-I12=40,60,IF($H$12-I12=-40,60,IF($H$12-I12=41,59,IF($H$12-I12=-41,59,IF($H$12-I12=42,58,IF($H$12-I12=-42,58,IF($H$12-I12=43,57,IF($H$12-I12=-43,57,IF($H$12-I12=44,56,IF($H$12-I12=-44,56,IF($H$12-I12=45,55,IF($H$12-I12=-45,55,IF($H$12-I12=46,54,IF($H$12-I12=-46,54,IF($H$12-I12=47,53,IF($H$12-I12=-47,53,IF($H$12-I12=48,52,IF($H$12-I12=-48,52,IF($H$12-I12=49,51,IF($H$12-I12=-49,51,IF($H$12-I12=50,50,IF($H$12-I12=-50,50,IF($H$12-I12=51,49,IF($H$12-I12=-51,49,IF($H$12-I12=52,48,IF($H$12-I12=-52,48,IF($H$12-I12=53,47,IF($H$12-I12=-53,47,IF($H$12-I12=54,46,IF($H$12-I12=-54,46,IF($H$12-I12=55,45,IF($H$12-I12=-55,45,IF($H$12-I12=56,44,IF($H$12-I12=-56,44,IF($H$12-I12=57,43,IF($H$12-I12=-57,43,IF($H$12-I12=58,42,IF($H$12-I12=-58,42,IF($H$12-I12=59,41,IF($H$12-I12=-59,41,IF($H$12-I12=60,40,IF($H$12-I12=-60,40,IF($H$12-I12=61,39,IF($H$12-I12=-61,39,IF($H$12-I12=62,38,IF($H$12-I12=-62,38,IF($H$12-I12=63,37,IF($H$12-I12=-63,37,IF($H$12-I12=64,36,IF($H$12-I12=-64,36,IF($H$12-I12=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -29755,7 +29723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I16" s="4">
         <f>IF($H$12-I12=-65,35,IF($H$12-I12=66,34,IF($H$12-I12=-66,34,IF($H$12-I12=67,33,IF($H$12-I12=-67,33,IF($H$12-I12=68,32,IF($H$12-I12=-68,32,IF($H$12-I12=69,31,IF($H$12-I12=-69,31,IF($H$12-I12=70,30,IF($H$12-I12=-70,30,IF($H$12-I12=71,29,IF($H$12-I12=-71,29,IF($H$12-I12=72,28,IF($H$12-I12=-72,28,IF($H$12-I12=73,27,IF($H$12-I12=-73,27,IF($H$12-I12=74,26,IF($H$12-I12=-74,26,IF($H$12-I12=75,25,IF($H$12-I12=-75,25,IF($H$12-I12=76,24,IF($H$12-I12=-76,24,IF($H$12-I12=77,23,IF($H$12-I12=-77,23,IF($H$12-I12=78,22,IF($H$12-I12=-78,22,IF($H$12-I12=79,21,IF($H$12-I12=-79,21,IF($H$12-I12=80,20,IF($H$12-I12=-80,20,IF($H$12-I12=81,19,IF($H$12-I12=-81,19,IF($H$12-I12=82,18,IF($H$12-I12=-82,18,IF($H$12-I12=83,17,IF($H$12-I12=-83,17,IF($H$12-I12=84,16,IF($H$12-I12=-84,16,IF($H$12-I12=85,15,IF($H$12-I12=-85,15,IF($H$12-I12=86,14,IF($H$12-I12=-86,14,IF($H$12-I12=87,13,IF($H$12-I12=-87,13,IF($H$12-I12=88,12,IF($H$12-I12=-88,12,IF($H$12-I12=89,11,IF($H$12-I12=-89,11,IF($H$12-I12=90,10,IF($H$12-I12=-90,10,IF($H$12-I12=91,9,IF($H$12-I12=-91,9,IF($H$12-I12=92,8,IF($H$12-I12=-92,8,IF($H$12-I12=93,7,IF($H$12-I12=-93,7,IF($H$12-I12=94,6,IF($H$12-I12=-94,6,IF($H$12-I12=95,5,IF($H$12-I12=-95,5,IF($H$12-I12=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -29781,7 +29749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:14" x14ac:dyDescent="0.25">
       <c r="I17" s="4">
         <f>IF($H$12-I12=-96,4,IF($H$12-I12=97,3,IF($H$12-I12=-97,3,IF($H$12-I12=98,2,IF($H$12-I12=-98,2,IF($H$12-I12=99,1,IF($H$12-I12=-99,1,IF($H$12-I12=100,0,IF($H$12-I12=-100,0,0)))))))))</f>
         <v>0</v>
@@ -29807,25 +29775,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="152"/>
       <c r="E18" s="152"/>
       <c r="F18" s="152"/>
       <c r="G18" s="152"/>
     </row>
-    <row r="19" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="152"/>
       <c r="E19" s="152"/>
       <c r="F19" s="152"/>
       <c r="G19" s="152"/>
     </row>
-    <row r="20" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="152"/>
       <c r="E20" s="152"/>
       <c r="F20" s="152"/>
       <c r="G20" s="152"/>
     </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I41" s="3">
         <v>1</v>
       </c>
@@ -29892,21 +29860,21 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:T41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.88671875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="6.109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" style="3" customWidth="1"/>
-    <col min="9" max="12" width="5.33203125" style="3" customWidth="1"/>
-    <col min="13" max="18" width="11.44140625" style="3"/>
+    <col min="2" max="2" width="13.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.85546875" style="3" customWidth="1"/>
+    <col min="6" max="7" width="6.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" style="3" customWidth="1"/>
+    <col min="9" max="12" width="5.28515625" style="3" customWidth="1"/>
+    <col min="13" max="18" width="11.42578125" style="3"/>
     <col min="19" max="20" width="0" style="3" hidden="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.44140625" style="3"/>
+    <col min="21" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="99" t="s">
         <v>28</v>
       </c>
@@ -29930,7 +29898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -29944,7 +29912,7 @@
       <c r="K2" s="38"/>
       <c r="L2" s="39"/>
     </row>
-    <row r="3" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -29984,7 +29952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="125" t="s">
         <v>127</v>
       </c>
@@ -30011,7 +29979,7 @@
       <c r="K4" s="17"/>
       <c r="L4" s="22"/>
     </row>
-    <row r="5" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="103"/>
       <c r="B5" s="133"/>
       <c r="C5" s="154"/>
@@ -30039,7 +30007,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="103"/>
       <c r="B6" s="132">
         <v>46218</v>
@@ -30070,7 +30038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="103"/>
       <c r="B7" s="133"/>
       <c r="C7" s="154"/>
@@ -30098,7 +30066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="163" t="s">
         <v>128</v>
       </c>
@@ -30125,7 +30093,7 @@
       <c r="K8" s="19"/>
       <c r="L8" s="28"/>
     </row>
-    <row r="9" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="163"/>
       <c r="B9" s="131"/>
       <c r="C9" s="156"/>
@@ -30147,7 +30115,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="163" t="s">
         <v>25</v>
       </c>
@@ -30174,7 +30142,7 @@
       <c r="K10" s="13"/>
       <c r="L10" s="25"/>
     </row>
-    <row r="11" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="163"/>
       <c r="B11" s="131"/>
       <c r="C11" s="156"/>
@@ -30196,7 +30164,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E12" s="151" t="s">
         <v>10</v>
       </c>
@@ -30223,7 +30191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E13" s="135" t="s">
         <v>14</v>
       </c>
@@ -30247,7 +30215,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="I14" s="4">
         <f>IF(I12=$H$12,100,IF($H$12-I12=1,99,IF($H$12-I12=-1,99,IF($H$12-I12=2,98,IF($H$12-I12=-2,98,IF($H$12-I12=3,97,IF($H$12-I12=-3,97,IF($H$12-I12=4,96,IF($H$12-I12=-4,96,IF($H$12-I12=5,95,IF($H$12-I12=-5,95,IF($H$12-I12=6,94,IF($H$12-I12=-6,94,IF($H$12-I12=7,93,IF($H$12-I12=-7,93,IF($H$12-I12=8,92,IF($H$12-I12=-8,92,IF($H$12-I12=9,91,IF($H$12-I12=-9,91,IF($H$12-I12=10,90,IF($H$12-I12=-10,90,IF($H$12-I12=11,89,IF($H$12-I12=-11,89,IF($H$12-I12=12,88,IF($H$12-I12=-12,88,IF($H$12-I12=13,87,IF($H$12-I12=-13,87,IF($H$12-I12=14,86,IF($H$12-I12=-14,86,IF($H$12-I12=15,85,IF($H$12-I12=-15,85,IF($H$12-I12=16,84,IF($H$12-I12=-16,84,IF($H$12-I12=17,83,IF($H$12-I12=-17,83,IF($H$12-I12=18,82,IF($H$12-I12=-18,82,IF($H$12-I12=19,81,IF($H$12-I12=-19,81,IF($H$12-I12=20,80,IF($H$12-I12=-20,80,IF($H$12-I12=21,79,IF($H$12-I12=-21,79,IF($H$12-I12=22,78,IF($H$12-I12=-22,78,IF($H$12-I12=23,77,IF($H$12-I12=-23,77,IF($H$12-I12=24,76,IF($H$12-I12=-24,76,IF($H$12-I12=25,75,IF($H$12-I12=-25,75,IF($H$12-I12=26,74,IF($H$12-I12=-26,74,IF($H$12-I12=27,73,IF($H$12-I12=-27,73,IF($H$12-I12=28,72,IF($H$12-I12=-28,72,IF($H$12-I12=29,71,IF($H$12-I12=-29,71,IF($H$12-I12=30,70,IF($H$12-I12=-30,70,IF($H$12-I12=31,69,IF($H$12-I12=-31,69,IF($H$12-I12=32,68,IF($H$12-I12=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>100</v>
@@ -30265,7 +30233,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="I15" s="4">
         <f>IF($H$12-I12=33,67,IF($H$12-I12=-33,67,IF($H$12-I12=34,66,IF($H$12-I12=-34,66,IF($H$12-I12=35,65,IF($H$12-I12=-35,65,IF($H$12-I12=36,64,IF($H$12-I12=-36,64,IF($H$12-I12=37,63,IF($H$12-I12=-37,63,IF($H$12-I12=38,62,IF($H$12-I12=-38,62,IF($H$12-I12=39,61,IF($H$12-I12=-39,61,IF($H$12-I12=40,60,IF($H$12-I12=-40,60,IF($H$12-I12=41,59,IF($H$12-I12=-41,59,IF($H$12-I12=42,58,IF($H$12-I12=-42,58,IF($H$12-I12=43,57,IF($H$12-I12=-43,57,IF($H$12-I12=44,56,IF($H$12-I12=-44,56,IF($H$12-I12=45,55,IF($H$12-I12=-45,55,IF($H$12-I12=46,54,IF($H$12-I12=-46,54,IF($H$12-I12=47,53,IF($H$12-I12=-47,53,IF($H$12-I12=48,52,IF($H$12-I12=-48,52,IF($H$12-I12=49,51,IF($H$12-I12=-49,51,IF($H$12-I12=50,50,IF($H$12-I12=-50,50,IF($H$12-I12=51,49,IF($H$12-I12=-51,49,IF($H$12-I12=52,48,IF($H$12-I12=-52,48,IF($H$12-I12=53,47,IF($H$12-I12=-53,47,IF($H$12-I12=54,46,IF($H$12-I12=-54,46,IF($H$12-I12=55,45,IF($H$12-I12=-55,45,IF($H$12-I12=56,44,IF($H$12-I12=-56,44,IF($H$12-I12=57,43,IF($H$12-I12=-57,43,IF($H$12-I12=58,42,IF($H$12-I12=-58,42,IF($H$12-I12=59,41,IF($H$12-I12=-59,41,IF($H$12-I12=60,40,IF($H$12-I12=-60,40,IF($H$12-I12=61,39,IF($H$12-I12=-61,39,IF($H$12-I12=62,38,IF($H$12-I12=-62,38,IF($H$12-I12=63,37,IF($H$12-I12=-63,37,IF($H$12-I12=64,36,IF($H$12-I12=-64,36,IF($H$12-I12=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -30283,7 +30251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="I16" s="4">
         <f>IF($H$12-I12=-65,35,IF($H$12-I12=66,34,IF($H$12-I12=-66,34,IF($H$12-I12=67,33,IF($H$12-I12=-67,33,IF($H$12-I12=68,32,IF($H$12-I12=-68,32,IF($H$12-I12=69,31,IF($H$12-I12=-69,31,IF($H$12-I12=70,30,IF($H$12-I12=-70,30,IF($H$12-I12=71,29,IF($H$12-I12=-71,29,IF($H$12-I12=72,28,IF($H$12-I12=-72,28,IF($H$12-I12=73,27,IF($H$12-I12=-73,27,IF($H$12-I12=74,26,IF($H$12-I12=-74,26,IF($H$12-I12=75,25,IF($H$12-I12=-75,25,IF($H$12-I12=76,24,IF($H$12-I12=-76,24,IF($H$12-I12=77,23,IF($H$12-I12=-77,23,IF($H$12-I12=78,22,IF($H$12-I12=-78,22,IF($H$12-I12=79,21,IF($H$12-I12=-79,21,IF($H$12-I12=80,20,IF($H$12-I12=-80,20,IF($H$12-I12=81,19,IF($H$12-I12=-81,19,IF($H$12-I12=82,18,IF($H$12-I12=-82,18,IF($H$12-I12=83,17,IF($H$12-I12=-83,17,IF($H$12-I12=84,16,IF($H$12-I12=-84,16,IF($H$12-I12=85,15,IF($H$12-I12=-85,15,IF($H$12-I12=86,14,IF($H$12-I12=-86,14,IF($H$12-I12=87,13,IF($H$12-I12=-87,13,IF($H$12-I12=88,12,IF($H$12-I12=-88,12,IF($H$12-I12=89,11,IF($H$12-I12=-89,11,IF($H$12-I12=90,10,IF($H$12-I12=-90,10,IF($H$12-I12=91,9,IF($H$12-I12=-91,9,IF($H$12-I12=92,8,IF($H$12-I12=-92,8,IF($H$12-I12=93,7,IF($H$12-I12=-93,7,IF($H$12-I12=94,6,IF($H$12-I12=-94,6,IF($H$12-I12=95,5,IF($H$12-I12=-95,5,IF($H$12-I12=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -30301,7 +30269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="4:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:12" x14ac:dyDescent="0.25">
       <c r="I17" s="4">
         <f>IF($H$12-I12=-96,4,IF($H$12-I12=97,3,IF($H$12-I12=-97,3,IF($H$12-I12=98,2,IF($H$12-I12=-98,2,IF($H$12-I12=99,1,IF($H$12-I12=-99,1,IF($H$12-I12=100,0,IF($H$12-I12=-100,0,0)))))))))</f>
         <v>0</v>
@@ -30319,25 +30287,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="152"/>
       <c r="E18" s="152"/>
       <c r="F18" s="152"/>
       <c r="G18" s="152"/>
     </row>
-    <row r="19" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="152"/>
       <c r="E19" s="152"/>
       <c r="F19" s="152"/>
       <c r="G19" s="152"/>
     </row>
-    <row r="20" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="152"/>
       <c r="E20" s="152"/>
       <c r="F20" s="152"/>
       <c r="G20" s="152"/>
     </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I41" s="3">
         <v>1</v>
       </c>
@@ -30402,14 +30370,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B1:O99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="11.44140625" style="1"/>
-    <col min="7" max="7" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.44140625" style="1"/>
+    <col min="1" max="6" width="11.42578125" style="1"/>
+    <col min="7" max="7" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
@@ -30455,7 +30423,7 @@
         <v>SI(G28-H28=-2;98;</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
@@ -30498,7 +30466,7 @@
         <v>SI(G28-H28=-3;97;</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
@@ -30541,7 +30509,7 @@
         <v>SI(G28-H28=-4;96;</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
@@ -30584,7 +30552,7 @@
         <v>SI(G28-H28=-5;95;</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
@@ -30627,7 +30595,7 @@
         <v>SI(G28-H28=-6;94;</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
@@ -30670,7 +30638,7 @@
         <v>SI(G28-H28=-7;93;</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
@@ -30713,7 +30681,7 @@
         <v>SI(G28-H28=-8;92;</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
@@ -30756,7 +30724,7 @@
         <v>SI(G28-H28=-9;91;</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
@@ -30799,7 +30767,7 @@
         <v>SI(G28-H28=-10;90;</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
@@ -30842,7 +30810,7 @@
         <v>SI(G28-H28=-11;89;</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
@@ -30885,7 +30853,7 @@
         <v>SI(G28-H28=-12;88;</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
@@ -30928,7 +30896,7 @@
         <v>SI(G28-H28=-13;87;</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
@@ -30971,7 +30939,7 @@
         <v>SI(G28-H28=-14;86;</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
@@ -31014,7 +30982,7 @@
         <v>SI(G28-H28=-15;85;</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>11</v>
       </c>
@@ -31057,7 +31025,7 @@
         <v>SI(G28-H28=-16;84;</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
@@ -31100,7 +31068,7 @@
         <v>SI(G28-H28=-17;83;</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>11</v>
       </c>
@@ -31143,7 +31111,7 @@
         <v>SI(G28-H28=-18;82;</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
@@ -31186,7 +31154,7 @@
         <v>SI(G28-H28=-19;81;</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
@@ -31229,7 +31197,7 @@
         <v>SI(G28-H28=-20;80;</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>11</v>
       </c>
@@ -31272,7 +31240,7 @@
         <v>SI(G28-H28=-21;79;</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>11</v>
       </c>
@@ -31315,7 +31283,7 @@
         <v>SI(G28-H28=-22;78;</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>11</v>
       </c>
@@ -31358,7 +31326,7 @@
         <v>SI(G28-H28=-23;77;</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>11</v>
       </c>
@@ -31401,7 +31369,7 @@
         <v>SI(G28-H28=-24;76;</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
@@ -31444,7 +31412,7 @@
         <v>SI(G28-H28=-25;75;</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>11</v>
       </c>
@@ -31487,7 +31455,7 @@
         <v>SI(G28-H28=-26;74;</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>11</v>
       </c>
@@ -31530,7 +31498,7 @@
         <v>SI(G28-H28=-27;73;</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>11</v>
       </c>
@@ -31573,7 +31541,7 @@
         <v>SI(G28-H28=-28;72;</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>11</v>
       </c>
@@ -31616,7 +31584,7 @@
         <v>SI(G28-H28=-29;71;</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>11</v>
       </c>
@@ -31659,7 +31627,7 @@
         <v>SI(G28-H28=-30;70;</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>11</v>
       </c>
@@ -31702,7 +31670,7 @@
         <v>SI(G28-H28=-31;69;</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>11</v>
       </c>
@@ -31745,7 +31713,7 @@
         <v>SI(G28-H28=-32;68;</v>
       </c>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
         <v>11</v>
       </c>
@@ -31788,7 +31756,7 @@
         <v>SI(G28-H28=-33;67;</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
         <v>11</v>
       </c>
@@ -31831,7 +31799,7 @@
         <v>SI(G28-H28=-34;66;</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
@@ -31874,7 +31842,7 @@
         <v>SI(G28-H28=-35;65;</v>
       </c>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>11</v>
       </c>
@@ -31917,7 +31885,7 @@
         <v>SI(G28-H28=-36;64;</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>11</v>
       </c>
@@ -31960,7 +31928,7 @@
         <v>SI(G28-H28=-37;63;</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>11</v>
       </c>
@@ -32003,7 +31971,7 @@
         <v>SI(G28-H28=-38;62;</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
         <v>11</v>
       </c>
@@ -32046,7 +32014,7 @@
         <v>SI(G28-H28=-39;61;</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
         <v>11</v>
       </c>
@@ -32089,7 +32057,7 @@
         <v>SI(G28-H28=-40;60;</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
         <v>11</v>
       </c>
@@ -32132,7 +32100,7 @@
         <v>SI(G28-H28=-41;59;</v>
       </c>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
         <v>11</v>
       </c>
@@ -32175,7 +32143,7 @@
         <v>SI(G28-H28=-42;58;</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>11</v>
       </c>
@@ -32218,7 +32186,7 @@
         <v>SI(G28-H28=-43;57;</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
         <v>11</v>
       </c>
@@ -32261,7 +32229,7 @@
         <v>SI(G28-H28=-44;56;</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>11</v>
       </c>
@@ -32304,7 +32272,7 @@
         <v>SI(G28-H28=-45;55;</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
         <v>11</v>
       </c>
@@ -32347,7 +32315,7 @@
         <v>SI(G28-H28=-46;54;</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>11</v>
       </c>
@@ -32390,7 +32358,7 @@
         <v>SI(G28-H28=-47;53;</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
         <v>11</v>
       </c>
@@ -32433,7 +32401,7 @@
         <v>SI(G28-H28=-48;52;</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
         <v>11</v>
       </c>
@@ -32476,7 +32444,7 @@
         <v>SI(G28-H28=-49;51;</v>
       </c>
     </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
@@ -32519,7 +32487,7 @@
         <v>SI(G28-H28=-50;50;</v>
       </c>
     </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>11</v>
       </c>
@@ -32562,7 +32530,7 @@
         <v>SI(G28-H28=-51;49;</v>
       </c>
     </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
         <v>11</v>
       </c>
@@ -32605,7 +32573,7 @@
         <v>SI(G28-H28=-52;48;</v>
       </c>
     </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
         <v>11</v>
       </c>
@@ -32648,7 +32616,7 @@
         <v>SI(G28-H28=-53;47;</v>
       </c>
     </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
         <v>11</v>
       </c>
@@ -32691,7 +32659,7 @@
         <v>SI(G28-H28=-54;46;</v>
       </c>
     </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
         <v>11</v>
       </c>
@@ -32734,7 +32702,7 @@
         <v>SI(G28-H28=-55;45;</v>
       </c>
     </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>11</v>
       </c>
@@ -32777,7 +32745,7 @@
         <v>SI(G28-H28=-56;44;</v>
       </c>
     </row>
-    <row r="56" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
         <v>11</v>
       </c>
@@ -32820,7 +32788,7 @@
         <v>SI(G28-H28=-57;43;</v>
       </c>
     </row>
-    <row r="57" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
         <v>11</v>
       </c>
@@ -32863,7 +32831,7 @@
         <v>SI(G28-H28=-58;42;</v>
       </c>
     </row>
-    <row r="58" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
         <v>11</v>
       </c>
@@ -32906,7 +32874,7 @@
         <v>SI(G28-H28=-59;41;</v>
       </c>
     </row>
-    <row r="59" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
         <v>11</v>
       </c>
@@ -32949,7 +32917,7 @@
         <v>SI(G28-H28=-60;40;</v>
       </c>
     </row>
-    <row r="60" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
         <v>11</v>
       </c>
@@ -32992,7 +32960,7 @@
         <v>SI(G28-H28=-61;39;</v>
       </c>
     </row>
-    <row r="61" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
         <v>11</v>
       </c>
@@ -33035,7 +33003,7 @@
         <v>SI(G28-H28=-62;38;</v>
       </c>
     </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
         <v>11</v>
       </c>
@@ -33078,7 +33046,7 @@
         <v>SI(G28-H28=-63;37;</v>
       </c>
     </row>
-    <row r="63" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
         <v>11</v>
       </c>
@@ -33121,7 +33089,7 @@
         <v>SI(G28-H28=-64;36;</v>
       </c>
     </row>
-    <row r="64" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
         <v>11</v>
       </c>
@@ -33164,7 +33132,7 @@
         <v>SI(G28-H28=-65;35;</v>
       </c>
     </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
         <v>11</v>
       </c>
@@ -33207,7 +33175,7 @@
         <v>SI(G28-H28=-66;34;</v>
       </c>
     </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
         <v>11</v>
       </c>
@@ -33250,7 +33218,7 @@
         <v>SI(G28-H28=-67;33;</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B67" s="1" t="s">
         <v>11</v>
       </c>
@@ -33293,7 +33261,7 @@
         <v>SI(G28-H28=-68;32;</v>
       </c>
     </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
         <v>11</v>
       </c>
@@ -33336,7 +33304,7 @@
         <v>SI(G28-H28=-69;31;</v>
       </c>
     </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
         <v>11</v>
       </c>
@@ -33379,7 +33347,7 @@
         <v>SI(G28-H28=-70;30;</v>
       </c>
     </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B70" s="1" t="s">
         <v>11</v>
       </c>
@@ -33422,7 +33390,7 @@
         <v>SI(G28-H28=-71;29;</v>
       </c>
     </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B71" s="1" t="s">
         <v>11</v>
       </c>
@@ -33465,7 +33433,7 @@
         <v>SI(G28-H28=-72;28;</v>
       </c>
     </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
         <v>11</v>
       </c>
@@ -33508,7 +33476,7 @@
         <v>SI(G28-H28=-73;27;</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B73" s="1" t="s">
         <v>11</v>
       </c>
@@ -33551,7 +33519,7 @@
         <v>SI(G28-H28=-74;26;</v>
       </c>
     </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
         <v>11</v>
       </c>
@@ -33594,7 +33562,7 @@
         <v>SI(G28-H28=-75;25;</v>
       </c>
     </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B75" s="1" t="s">
         <v>11</v>
       </c>
@@ -33637,7 +33605,7 @@
         <v>SI(G28-H28=-76;24;</v>
       </c>
     </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
         <v>11</v>
       </c>
@@ -33680,7 +33648,7 @@
         <v>SI(G28-H28=-77;23;</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
         <v>11</v>
       </c>
@@ -33723,7 +33691,7 @@
         <v>SI(G28-H28=-78;22;</v>
       </c>
     </row>
-    <row r="78" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B78" s="1" t="s">
         <v>11</v>
       </c>
@@ -33766,7 +33734,7 @@
         <v>SI(G28-H28=-79;21;</v>
       </c>
     </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
         <v>11</v>
       </c>
@@ -33809,7 +33777,7 @@
         <v>SI(G28-H28=-80;20;</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B80" s="1" t="s">
         <v>11</v>
       </c>
@@ -33852,7 +33820,7 @@
         <v>SI(G28-H28=-81;19;</v>
       </c>
     </row>
-    <row r="81" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
         <v>11</v>
       </c>
@@ -33895,7 +33863,7 @@
         <v>SI(G28-H28=-82;18;</v>
       </c>
     </row>
-    <row r="82" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
         <v>11</v>
       </c>
@@ -33938,7 +33906,7 @@
         <v>SI(G28-H28=-83;17;</v>
       </c>
     </row>
-    <row r="83" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B83" s="1" t="s">
         <v>11</v>
       </c>
@@ -33981,7 +33949,7 @@
         <v>SI(G28-H28=-84;16;</v>
       </c>
     </row>
-    <row r="84" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B84" s="1" t="s">
         <v>11</v>
       </c>
@@ -34024,7 +33992,7 @@
         <v>SI(G28-H28=-85;15;</v>
       </c>
     </row>
-    <row r="85" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B85" s="1" t="s">
         <v>11</v>
       </c>
@@ -34067,7 +34035,7 @@
         <v>SI(G28-H28=-86;14;</v>
       </c>
     </row>
-    <row r="86" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
         <v>11</v>
       </c>
@@ -34110,7 +34078,7 @@
         <v>SI(G28-H28=-87;13;</v>
       </c>
     </row>
-    <row r="87" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
         <v>11</v>
       </c>
@@ -34153,7 +34121,7 @@
         <v>SI(G28-H28=-88;12;</v>
       </c>
     </row>
-    <row r="88" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
         <v>11</v>
       </c>
@@ -34196,7 +34164,7 @@
         <v>SI(G28-H28=-89;11;</v>
       </c>
     </row>
-    <row r="89" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
         <v>11</v>
       </c>
@@ -34239,7 +34207,7 @@
         <v>SI(G28-H28=-90;10;</v>
       </c>
     </row>
-    <row r="90" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
         <v>11</v>
       </c>
@@ -34282,7 +34250,7 @@
         <v>SI(G28-H28=-91;9;</v>
       </c>
     </row>
-    <row r="91" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
         <v>11</v>
       </c>
@@ -34325,7 +34293,7 @@
         <v>SI(G28-H28=-92;8;</v>
       </c>
     </row>
-    <row r="92" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B92" s="1" t="s">
         <v>11</v>
       </c>
@@ -34368,7 +34336,7 @@
         <v>SI(G28-H28=-93;7;</v>
       </c>
     </row>
-    <row r="93" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B93" s="1" t="s">
         <v>11</v>
       </c>
@@ -34411,7 +34379,7 @@
         <v>SI(G28-H28=-94;6;</v>
       </c>
     </row>
-    <row r="94" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B94" s="1" t="s">
         <v>11</v>
       </c>
@@ -34454,7 +34422,7 @@
         <v>SI(G28-H28=-95;5;</v>
       </c>
     </row>
-    <row r="95" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B95" s="1" t="s">
         <v>11</v>
       </c>
@@ -34497,7 +34465,7 @@
         <v>SI(G28-H28=-96;4;</v>
       </c>
     </row>
-    <row r="96" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
         <v>11</v>
       </c>
@@ -34540,7 +34508,7 @@
         <v>SI(G28-H28=-97;3;</v>
       </c>
     </row>
-    <row r="97" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B97" s="1" t="s">
         <v>11</v>
       </c>
@@ -34583,7 +34551,7 @@
         <v>SI(G28-H28=-98;2;</v>
       </c>
     </row>
-    <row r="98" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B98" s="1" t="s">
         <v>11</v>
       </c>
@@ -34626,7 +34594,7 @@
         <v>SI(G28-H28=-99;1;</v>
       </c>
     </row>
-    <row r="99" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B99" s="1" t="s">
         <v>11</v>
       </c>

--- a/Copa del Mundo-2026 trabajo.xlsx
+++ b/Copa del Mundo-2026 trabajo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_corporativa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="8_{4B119FBF-818B-466F-B1F3-AB97609A7929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FABCC11-9755-484A-9385-434C6ABA617C}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{4B119FBF-818B-466F-B1F3-AB97609A7929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A991B22-D113-468D-9351-54AE578FFA20}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA 2026" sheetId="3" r:id="rId1"/>
@@ -2485,45 +2485,45 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:BB181"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="20.6640625" style="56" customWidth="1"/>
-    <col min="7" max="8" width="6.109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.44140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="4.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="7.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.33203125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.33203125" style="2" customWidth="1"/>
-    <col min="25" max="27" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.33203125" style="2" customWidth="1"/>
-    <col min="29" max="31" width="4.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="5.33203125" style="2" customWidth="1"/>
-    <col min="35" max="35" width="4.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="5.33203125" style="2" customWidth="1"/>
-    <col min="39" max="40" width="4.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="4.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="4.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="47" max="52" width="11.44140625" style="2"/>
-    <col min="53" max="54" width="11.44140625" style="2" customWidth="1"/>
-    <col min="55" max="16384" width="11.44140625" style="2"/>
+    <col min="1" max="1" width="8.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" style="56" customWidth="1"/>
+    <col min="7" max="8" width="6.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.28515625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.28515625" style="2" customWidth="1"/>
+    <col min="25" max="27" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.28515625" style="2" customWidth="1"/>
+    <col min="29" max="31" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="5.28515625" style="2" customWidth="1"/>
+    <col min="35" max="35" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="5.28515625" style="2" customWidth="1"/>
+    <col min="39" max="40" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="4.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="47" max="52" width="11.42578125" style="2"/>
+    <col min="53" max="54" width="11.42578125" style="2" customWidth="1"/>
+    <col min="55" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:54" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="99" t="s">
         <v>28</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:54" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -2690,10 +2690,10 @@
         <v>157</v>
       </c>
       <c r="T2" s="52" t="s">
+        <v>172</v>
+      </c>
+      <c r="U2" s="52" t="s">
         <v>169</v>
-      </c>
-      <c r="U2" s="52" t="s">
-        <v>172</v>
       </c>
       <c r="V2" s="52" t="s">
         <v>167</v>
@@ -2714,22 +2714,22 @@
         <v>143</v>
       </c>
       <c r="AB2" s="52" t="s">
+        <v>171</v>
+      </c>
+      <c r="AC2" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="AC2" s="52" t="s">
+      <c r="AD2" s="52" t="s">
         <v>145</v>
-      </c>
-      <c r="AD2" s="52" t="s">
-        <v>171</v>
       </c>
       <c r="AE2" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="AF2" s="52" t="s">
+      <c r="AF2" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG2" s="52" t="s">
         <v>131</v>
-      </c>
-      <c r="AG2" s="36" t="s">
-        <v>156</v>
       </c>
       <c r="AH2" s="36" t="s">
         <v>155</v>
@@ -2771,7 +2771,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:54" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
         <v>0</v>
       </c>
@@ -2799,154 +2799,154 @@
       </c>
       <c r="J3" s="67">
         <f>SUM(J4+J5)-SUM(J6+J7)</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K3" s="68">
         <f>SUM(K4+K5)-SUM(K6+K7)</f>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L3" s="68">
         <f>SUM(L4+L5)-SUM(L6+L7)</f>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M3" s="68">
         <f>SUM(M4+M5)-SUM(M6+M7)</f>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N3" s="68">
         <f>SUM(N4+N5)-SUM(N6+N7)</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O3" s="68">
         <f>SUM(O4+O5)-SUM(O6+O7)</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P3" s="68">
         <f>SUM(P4+P5)-SUM(P6+P7)</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q3" s="68">
         <f>SUM(Q4+Q5)-SUM(Q6+Q7)</f>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R3" s="68">
         <f>SUM(R4+R5)-SUM(R6+R7)</f>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S3" s="68">
         <f>SUM(S4+S5)-SUM(S6+S7)</f>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="T3" s="68">
         <f>SUM(T4+T5)-SUM(T6+T7)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="U3" s="68">
         <f>SUM(U4+U5)-SUM(U6+U7)</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="V3" s="68">
         <f>SUM(V4+V5)-SUM(V6+V7)</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="W3" s="68">
         <f>SUM(W4+W5)-SUM(W6+W7)</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="X3" s="68">
         <f>SUM(X4+X5)-SUM(X6+X7)</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="68">
         <f>SUM(Y4+Y5)-SUM(Y6+Y7)</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Z3" s="68">
         <f>SUM(Z4+Z5)-SUM(Z6+Z7)</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA3" s="68">
         <f>SUM(AA4+AA5)-SUM(AA6+AA7)</f>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AB3" s="68">
         <f>SUM(AB4+AB5)-SUM(AB6+AB7)</f>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AC3" s="68">
         <f>SUM(AC4+AC5)-SUM(AC6+AC7)</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AD3" s="68">
         <f>SUM(AD4+AD5)-SUM(AD6+AD7)</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE3" s="68">
         <f>SUM(AE4+AE5)-SUM(AE6+AE7)</f>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AF3" s="68">
         <f>SUM(AF4+AF5)-SUM(AF6+AF7)</f>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AG3" s="68">
         <f>SUM(AG4+AG5)-SUM(AG6+AG7)</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AH3" s="68">
         <f>SUM(AH4+AH5)-SUM(AH6+AH7)</f>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI3" s="68">
         <f>SUM(AI4+AI5)-SUM(AI6+AI7)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AJ3" s="68">
         <f>SUM(AJ4+AJ5)-SUM(AJ6+AJ7)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AK3" s="68">
         <f>SUM(AK4+AK5)-SUM(AK6+AK7)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AL3" s="68">
         <f>SUM(AL4+AL5)-SUM(AL6+AL7)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AM3" s="68">
         <f>SUM(AM4+AM5)-SUM(AM6+AM7)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AN3" s="68">
         <f>SUM(AN4+AN5)-SUM(AN6+AN7)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO3" s="68">
         <f>SUM(AO4+AO5)-SUM(AO6+AO7)</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AP3" s="68">
         <f>SUM(AP4+AP5)-SUM(AP6+AP7)</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AQ3" s="68">
         <f>SUM(AQ4+AQ5)-SUM(AQ6+AQ7)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AR3" s="68">
         <f>SUM(AR4+AR5)-SUM(AR6+AR7)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AS3" s="68">
         <f>SUM(AS4+AS5)-SUM(AS6+AS7)</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AT3" s="69">
         <f>SUM(AT4+AT5)-SUM(AT6+AT7)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:54" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:54" ht="15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="61"/>
       <c r="B4" s="61"/>
       <c r="C4" s="61"/>
@@ -3009,12 +3009,12 @@
       <c r="T4" s="73">
         <f>SUM(IF(T8=$I$8,3,0)+IF(T9=$G8+$H8,1,0)+IF(T10=$I$10,3,0)+IF(T11=$G10+$H10,1,0)+IF(T12=$I$12,3,0)+IF(T13=$G12+$H12,1,0)+IF(T14=$I$14,3,0)+IF(T15=$G14+$H14,1,0)
 +IF(T16=$I$16,3,0)+IF(T17=$G16+$H16,1,0)+IF(T18=$I$18,3,0)+IF(T19=$G18+$H18,1,0)+IF(T20=$I$20,3,0)+IF(T21=$G20+$H20,1,0)+IF(T22=$I$22,3,0)+IF(T23=$G22+$H22,1,0)+IF(T24=$I$24,3,0)+IF(T25=$G24+$H24,1,0)+IF(T26=$I$26,3,0)+IF(T27=$G26+$H26,1,0)+IF(T28=$I$28,3,0)+IF(T29=$G28+$H28,1,0)+IF(T30=$I$30,3,0)+IF(T31=$G30+$H30,1,0)+IF(T32=$I$32,3,0)+IF(T33=$G32+$H32,1,0)+IF(T34=$I$34,3,0)+IF(T35=$G34+$H34,1,0)+IF(T36=$I$36,3,0)+IF(T37=$G36+$H36,1,0)+IF(T38=$I$38,3,0)+IF(T39=$G38+$H38,1,0)+IF(T40=$I$40,3,0)+IF(T41=$G40+$H40,1,0)+IF(T42=$I$42,3,0)+IF(T43=$G42+$H42,1,0)+IF(T44=$I$44,3,0)+IF(T45=$G44+$H44,1,0)+IF(T46=$I$46,3,0)+IF(T47=$G46+$H46,1,0)+IF(T48=$I$48,3,0)+IF(T49=$G48+$H48,1,0)+IF(T50=$I$50,3,0)+IF(T51=$G50+$H50,1,0)+IF(T52=$I$52,3,0)+IF(T53=$G52+$H52,1,0)+IF(T54=$I$54,3,0)+IF(T55=$G54+$H54,1,0)+IF(T56=$I$56,3,0)+IF(T57=$G56+$H56,1,0)+IF(T58=$I$58,3,0)+IF(T59=$G58+$H58,1,0)+IF(T60=$I$60,3,0)+IF(T61=$G60+$H60,1,0)+IF(T62=$I$62,3,0)+IF(T63=$G62+$H62,1,0)+IF(T64=$I$64,3,0)+IF(T65=$G64+$H64,1,0)+IF(T66=$I$66,3,0)+IF(T67=$G66+$H66,1,0)+IF(T68=$I$68,3,0)+IF(T69=$G68+$H68,1,0)+IF(T70=$I$70,3,0)+IF(T71=$G70+$H70,1,0)+IF(T72=$I$72,3,0)+IF(T73=$G72+$H72,1,0)+IF(T74=$I$74,3,0)+IF(T75=$G74+$H74,1,0)+IF(T76=$I$76,3,0)+IF(T77=$G76+$H76,1,0)+IF(T78=$I$78,3,0)+IF(T79=$G78+$H78,1,0))</f>
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="U4" s="73">
         <f>SUM(IF(U8=$I$8,3,0)+IF(U9=$G8+$H8,1,0)+IF(U10=$I$10,3,0)+IF(U11=$G10+$H10,1,0)+IF(U12=$I$12,3,0)+IF(U13=$G12+$H12,1,0)+IF(U14=$I$14,3,0)+IF(U15=$G14+$H14,1,0)
 +IF(U16=$I$16,3,0)+IF(U17=$G16+$H16,1,0)+IF(U18=$I$18,3,0)+IF(U19=$G18+$H18,1,0)+IF(U20=$I$20,3,0)+IF(U21=$G20+$H20,1,0)+IF(U22=$I$22,3,0)+IF(U23=$G22+$H22,1,0)+IF(U24=$I$24,3,0)+IF(U25=$G24+$H24,1,0)+IF(U26=$I$26,3,0)+IF(U27=$G26+$H26,1,0)+IF(U28=$I$28,3,0)+IF(U29=$G28+$H28,1,0)+IF(U30=$I$30,3,0)+IF(U31=$G30+$H30,1,0)+IF(U32=$I$32,3,0)+IF(U33=$G32+$H32,1,0)+IF(U34=$I$34,3,0)+IF(U35=$G34+$H34,1,0)+IF(U36=$I$36,3,0)+IF(U37=$G36+$H36,1,0)+IF(U38=$I$38,3,0)+IF(U39=$G38+$H38,1,0)+IF(U40=$I$40,3,0)+IF(U41=$G40+$H40,1,0)+IF(U42=$I$42,3,0)+IF(U43=$G42+$H42,1,0)+IF(U44=$I$44,3,0)+IF(U45=$G44+$H44,1,0)+IF(U46=$I$46,3,0)+IF(U47=$G46+$H46,1,0)+IF(U48=$I$48,3,0)+IF(U49=$G48+$H48,1,0)+IF(U50=$I$50,3,0)+IF(U51=$G50+$H50,1,0)+IF(U52=$I$52,3,0)+IF(U53=$G52+$H52,1,0)+IF(U54=$I$54,3,0)+IF(U55=$G54+$H54,1,0)+IF(U56=$I$56,3,0)+IF(U57=$G56+$H56,1,0)+IF(U58=$I$58,3,0)+IF(U59=$G58+$H58,1,0)+IF(U60=$I$60,3,0)+IF(U61=$G60+$H60,1,0)+IF(U62=$I$62,3,0)+IF(U63=$G62+$H62,1,0)+IF(U64=$I$64,3,0)+IF(U65=$G64+$H64,1,0)+IF(U66=$I$66,3,0)+IF(U67=$G66+$H66,1,0)+IF(U68=$I$68,3,0)+IF(U69=$G68+$H68,1,0)+IF(U70=$I$70,3,0)+IF(U71=$G70+$H70,1,0)+IF(U72=$I$72,3,0)+IF(U73=$G72+$H72,1,0)+IF(U74=$I$74,3,0)+IF(U75=$G74+$H74,1,0)+IF(U76=$I$76,3,0)+IF(U77=$G76+$H76,1,0)+IF(U78=$I$78,3,0)+IF(U79=$G78+$H78,1,0))</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="V4" s="73">
         <f>SUM(IF(V8=$I$8,3,0)+IF(V9=$G8+$H8,1,0)+IF(V10=$I$10,3,0)+IF(V11=$G10+$H10,1,0)+IF(V12=$I$12,3,0)+IF(V13=$G12+$H12,1,0)+IF(V14=$I$14,3,0)+IF(V15=$G14+$H14,1,0)
@@ -3049,17 +3049,17 @@
       <c r="AB4" s="73">
         <f>SUM(IF(AB8=$I$8,3,0)+IF(AB9=$G8+$H8,1,0)+IF(AB10=$I$10,3,0)+IF(AB11=$G10+$H10,1,0)+IF(AB12=$I$12,3,0)+IF(AB13=$G12+$H12,1,0)+IF(AB14=$I$14,3,0)+IF(AB15=$G14+$H14,1,0)
 +IF(AB16=$I$16,3,0)+IF(AB17=$G16+$H16,1,0)+IF(AB18=$I$18,3,0)+IF(AB19=$G18+$H18,1,0)+IF(AB20=$I$20,3,0)+IF(AB21=$G20+$H20,1,0)+IF(AB22=$I$22,3,0)+IF(AB23=$G22+$H22,1,0)+IF(AB24=$I$24,3,0)+IF(AB25=$G24+$H24,1,0)+IF(AB26=$I$26,3,0)+IF(AB27=$G26+$H26,1,0)+IF(AB28=$I$28,3,0)+IF(AB29=$G28+$H28,1,0)+IF(AB30=$I$30,3,0)+IF(AB31=$G30+$H30,1,0)+IF(AB32=$I$32,3,0)+IF(AB33=$G32+$H32,1,0)+IF(AB34=$I$34,3,0)+IF(AB35=$G34+$H34,1,0)+IF(AB36=$I$36,3,0)+IF(AB37=$G36+$H36,1,0)+IF(AB38=$I$38,3,0)+IF(AB39=$G38+$H38,1,0)+IF(AB40=$I$40,3,0)+IF(AB41=$G40+$H40,1,0)+IF(AB42=$I$42,3,0)+IF(AB43=$G42+$H42,1,0)+IF(AB44=$I$44,3,0)+IF(AB45=$G44+$H44,1,0)+IF(AB46=$I$46,3,0)+IF(AB47=$G46+$H46,1,0)+IF(AB48=$I$48,3,0)+IF(AB49=$G48+$H48,1,0)+IF(AB50=$I$50,3,0)+IF(AB51=$G50+$H50,1,0)+IF(AB52=$I$52,3,0)+IF(AB53=$G52+$H52,1,0)+IF(AB54=$I$54,3,0)+IF(AB55=$G54+$H54,1,0)+IF(AB56=$I$56,3,0)+IF(AB57=$G56+$H56,1,0)+IF(AB58=$I$58,3,0)+IF(AB59=$G58+$H58,1,0)+IF(AB60=$I$60,3,0)+IF(AB61=$G60+$H60,1,0)+IF(AB62=$I$62,3,0)+IF(AB63=$G62+$H62,1,0)+IF(AB64=$I$64,3,0)+IF(AB65=$G64+$H64,1,0)+IF(AB66=$I$66,3,0)+IF(AB67=$G66+$H66,1,0)+IF(AB68=$I$68,3,0)+IF(AB69=$G68+$H68,1,0)+IF(AB70=$I$70,3,0)+IF(AB71=$G70+$H70,1,0)+IF(AB72=$I$72,3,0)+IF(AB73=$G72+$H72,1,0)+IF(AB74=$I$74,3,0)+IF(AB75=$G74+$H74,1,0)+IF(AB76=$I$76,3,0)+IF(AB77=$G76+$H76,1,0)+IF(AB78=$I$78,3,0)+IF(AB79=$G78+$H78,1,0))</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AC4" s="73">
         <f>SUM(IF(AC8=$I$8,3,0)+IF(AC9=$G8+$H8,1,0)+IF(AC10=$I$10,3,0)+IF(AC11=$G10+$H10,1,0)+IF(AC12=$I$12,3,0)+IF(AC13=$G12+$H12,1,0)+IF(AC14=$I$14,3,0)+IF(AC15=$G14+$H14,1,0)
 +IF(AC16=$I$16,3,0)+IF(AC17=$G16+$H16,1,0)+IF(AC18=$I$18,3,0)+IF(AC19=$G18+$H18,1,0)+IF(AC20=$I$20,3,0)+IF(AC21=$G20+$H20,1,0)+IF(AC22=$I$22,3,0)+IF(AC23=$G22+$H22,1,0)+IF(AC24=$I$24,3,0)+IF(AC25=$G24+$H24,1,0)+IF(AC26=$I$26,3,0)+IF(AC27=$G26+$H26,1,0)+IF(AC28=$I$28,3,0)+IF(AC29=$G28+$H28,1,0)+IF(AC30=$I$30,3,0)+IF(AC31=$G30+$H30,1,0)+IF(AC32=$I$32,3,0)+IF(AC33=$G32+$H32,1,0)+IF(AC34=$I$34,3,0)+IF(AC35=$G34+$H34,1,0)+IF(AC36=$I$36,3,0)+IF(AC37=$G36+$H36,1,0)+IF(AC38=$I$38,3,0)+IF(AC39=$G38+$H38,1,0)+IF(AC40=$I$40,3,0)+IF(AC41=$G40+$H40,1,0)+IF(AC42=$I$42,3,0)+IF(AC43=$G42+$H42,1,0)+IF(AC44=$I$44,3,0)+IF(AC45=$G44+$H44,1,0)+IF(AC46=$I$46,3,0)+IF(AC47=$G46+$H46,1,0)+IF(AC48=$I$48,3,0)+IF(AC49=$G48+$H48,1,0)+IF(AC50=$I$50,3,0)+IF(AC51=$G50+$H50,1,0)+IF(AC52=$I$52,3,0)+IF(AC53=$G52+$H52,1,0)+IF(AC54=$I$54,3,0)+IF(AC55=$G54+$H54,1,0)+IF(AC56=$I$56,3,0)+IF(AC57=$G56+$H56,1,0)+IF(AC58=$I$58,3,0)+IF(AC59=$G58+$H58,1,0)+IF(AC60=$I$60,3,0)+IF(AC61=$G60+$H60,1,0)+IF(AC62=$I$62,3,0)+IF(AC63=$G62+$H62,1,0)+IF(AC64=$I$64,3,0)+IF(AC65=$G64+$H64,1,0)+IF(AC66=$I$66,3,0)+IF(AC67=$G66+$H66,1,0)+IF(AC68=$I$68,3,0)+IF(AC69=$G68+$H68,1,0)+IF(AC70=$I$70,3,0)+IF(AC71=$G70+$H70,1,0)+IF(AC72=$I$72,3,0)+IF(AC73=$G72+$H72,1,0)+IF(AC74=$I$74,3,0)+IF(AC75=$G74+$H74,1,0)+IF(AC76=$I$76,3,0)+IF(AC77=$G76+$H76,1,0)+IF(AC78=$I$78,3,0)+IF(AC79=$G78+$H78,1,0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD4" s="73">
         <f>SUM(IF(AD8=$I$8,3,0)+IF(AD9=$G8+$H8,1,0)+IF(AD10=$I$10,3,0)+IF(AD11=$G10+$H10,1,0)+IF(AD12=$I$12,3,0)+IF(AD13=$G12+$H12,1,0)+IF(AD14=$I$14,3,0)+IF(AD15=$G14+$H14,1,0)
 +IF(AD16=$I$16,3,0)+IF(AD17=$G16+$H16,1,0)+IF(AD18=$I$18,3,0)+IF(AD19=$G18+$H18,1,0)+IF(AD20=$I$20,3,0)+IF(AD21=$G20+$H20,1,0)+IF(AD22=$I$22,3,0)+IF(AD23=$G22+$H22,1,0)+IF(AD24=$I$24,3,0)+IF(AD25=$G24+$H24,1,0)+IF(AD26=$I$26,3,0)+IF(AD27=$G26+$H26,1,0)+IF(AD28=$I$28,3,0)+IF(AD29=$G28+$H28,1,0)+IF(AD30=$I$30,3,0)+IF(AD31=$G30+$H30,1,0)+IF(AD32=$I$32,3,0)+IF(AD33=$G32+$H32,1,0)+IF(AD34=$I$34,3,0)+IF(AD35=$G34+$H34,1,0)+IF(AD36=$I$36,3,0)+IF(AD37=$G36+$H36,1,0)+IF(AD38=$I$38,3,0)+IF(AD39=$G38+$H38,1,0)+IF(AD40=$I$40,3,0)+IF(AD41=$G40+$H40,1,0)+IF(AD42=$I$42,3,0)+IF(AD43=$G42+$H42,1,0)+IF(AD44=$I$44,3,0)+IF(AD45=$G44+$H44,1,0)+IF(AD46=$I$46,3,0)+IF(AD47=$G46+$H46,1,0)+IF(AD48=$I$48,3,0)+IF(AD49=$G48+$H48,1,0)+IF(AD50=$I$50,3,0)+IF(AD51=$G50+$H50,1,0)+IF(AD52=$I$52,3,0)+IF(AD53=$G52+$H52,1,0)+IF(AD54=$I$54,3,0)+IF(AD55=$G54+$H54,1,0)+IF(AD56=$I$56,3,0)+IF(AD57=$G56+$H56,1,0)+IF(AD58=$I$58,3,0)+IF(AD59=$G58+$H58,1,0)+IF(AD60=$I$60,3,0)+IF(AD61=$G60+$H60,1,0)+IF(AD62=$I$62,3,0)+IF(AD63=$G62+$H62,1,0)+IF(AD64=$I$64,3,0)+IF(AD65=$G64+$H64,1,0)+IF(AD66=$I$66,3,0)+IF(AD67=$G66+$H66,1,0)+IF(AD68=$I$68,3,0)+IF(AD69=$G68+$H68,1,0)+IF(AD70=$I$70,3,0)+IF(AD71=$G70+$H70,1,0)+IF(AD72=$I$72,3,0)+IF(AD73=$G72+$H72,1,0)+IF(AD74=$I$74,3,0)+IF(AD75=$G74+$H74,1,0)+IF(AD76=$I$76,3,0)+IF(AD77=$G76+$H76,1,0)+IF(AD78=$I$78,3,0)+IF(AD79=$G78+$H78,1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE4" s="73">
         <f>SUM(IF(AE8=$I$8,3,0)+IF(AE9=$G8+$H8,1,0)+IF(AE10=$I$10,3,0)+IF(AE11=$G10+$H10,1,0)+IF(AE12=$I$12,3,0)+IF(AE13=$G12+$H12,1,0)+IF(AE14=$I$14,3,0)+IF(AE15=$G14+$H14,1,0)
@@ -3069,12 +3069,12 @@
       <c r="AF4" s="73">
         <f>SUM(IF(AF8=$I$8,3,0)+IF(AF9=$G8+$H8,1,0)+IF(AF10=$I$10,3,0)+IF(AF11=$G10+$H10,1,0)+IF(AF12=$I$12,3,0)+IF(AF13=$G12+$H12,1,0)+IF(AF14=$I$14,3,0)+IF(AF15=$G14+$H14,1,0)
 +IF(AF16=$I$16,3,0)+IF(AF17=$G16+$H16,1,0)+IF(AF18=$I$18,3,0)+IF(AF19=$G18+$H18,1,0)+IF(AF20=$I$20,3,0)+IF(AF21=$G20+$H20,1,0)+IF(AF22=$I$22,3,0)+IF(AF23=$G22+$H22,1,0)+IF(AF24=$I$24,3,0)+IF(AF25=$G24+$H24,1,0)+IF(AF26=$I$26,3,0)+IF(AF27=$G26+$H26,1,0)+IF(AF28=$I$28,3,0)+IF(AF29=$G28+$H28,1,0)+IF(AF30=$I$30,3,0)+IF(AF31=$G30+$H30,1,0)+IF(AF32=$I$32,3,0)+IF(AF33=$G32+$H32,1,0)+IF(AF34=$I$34,3,0)+IF(AF35=$G34+$H34,1,0)+IF(AF36=$I$36,3,0)+IF(AF37=$G36+$H36,1,0)+IF(AF38=$I$38,3,0)+IF(AF39=$G38+$H38,1,0)+IF(AF40=$I$40,3,0)+IF(AF41=$G40+$H40,1,0)+IF(AF42=$I$42,3,0)+IF(AF43=$G42+$H42,1,0)+IF(AF44=$I$44,3,0)+IF(AF45=$G44+$H44,1,0)+IF(AF46=$I$46,3,0)+IF(AF47=$G46+$H46,1,0)+IF(AF48=$I$48,3,0)+IF(AF49=$G48+$H48,1,0)+IF(AF50=$I$50,3,0)+IF(AF51=$G50+$H50,1,0)+IF(AF52=$I$52,3,0)+IF(AF53=$G52+$H52,1,0)+IF(AF54=$I$54,3,0)+IF(AF55=$G54+$H54,1,0)+IF(AF56=$I$56,3,0)+IF(AF57=$G56+$H56,1,0)+IF(AF58=$I$58,3,0)+IF(AF59=$G58+$H58,1,0)+IF(AF60=$I$60,3,0)+IF(AF61=$G60+$H60,1,0)+IF(AF62=$I$62,3,0)+IF(AF63=$G62+$H62,1,0)+IF(AF64=$I$64,3,0)+IF(AF65=$G64+$H64,1,0)+IF(AF66=$I$66,3,0)+IF(AF67=$G66+$H66,1,0)+IF(AF68=$I$68,3,0)+IF(AF69=$G68+$H68,1,0)+IF(AF70=$I$70,3,0)+IF(AF71=$G70+$H70,1,0)+IF(AF72=$I$72,3,0)+IF(AF73=$G72+$H72,1,0)+IF(AF74=$I$74,3,0)+IF(AF75=$G74+$H74,1,0)+IF(AF76=$I$76,3,0)+IF(AF77=$G76+$H76,1,0)+IF(AF78=$I$78,3,0)+IF(AF79=$G78+$H78,1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG4" s="73">
         <f>SUM(IF(AG8=$I$8,3,0)+IF(AG9=$G8+$H8,1,0)+IF(AG10=$I$10,3,0)+IF(AG11=$G10+$H10,1,0)+IF(AG12=$I$12,3,0)+IF(AG13=$G12+$H12,1,0)+IF(AG14=$I$14,3,0)+IF(AG15=$G14+$H14,1,0)
 +IF(AG16=$I$16,3,0)+IF(AG17=$G16+$H16,1,0)+IF(AG18=$I$18,3,0)+IF(AG19=$G18+$H18,1,0)+IF(AG20=$I$20,3,0)+IF(AG21=$G20+$H20,1,0)+IF(AG22=$I$22,3,0)+IF(AG23=$G22+$H22,1,0)+IF(AG24=$I$24,3,0)+IF(AG25=$G24+$H24,1,0)+IF(AG26=$I$26,3,0)+IF(AG27=$G26+$H26,1,0)+IF(AG28=$I$28,3,0)+IF(AG29=$G28+$H28,1,0)+IF(AG30=$I$30,3,0)+IF(AG31=$G30+$H30,1,0)+IF(AG32=$I$32,3,0)+IF(AG33=$G32+$H32,1,0)+IF(AG34=$I$34,3,0)+IF(AG35=$G34+$H34,1,0)+IF(AG36=$I$36,3,0)+IF(AG37=$G36+$H36,1,0)+IF(AG38=$I$38,3,0)+IF(AG39=$G38+$H38,1,0)+IF(AG40=$I$40,3,0)+IF(AG41=$G40+$H40,1,0)+IF(AG42=$I$42,3,0)+IF(AG43=$G42+$H42,1,0)+IF(AG44=$I$44,3,0)+IF(AG45=$G44+$H44,1,0)+IF(AG46=$I$46,3,0)+IF(AG47=$G46+$H46,1,0)+IF(AG48=$I$48,3,0)+IF(AG49=$G48+$H48,1,0)+IF(AG50=$I$50,3,0)+IF(AG51=$G50+$H50,1,0)+IF(AG52=$I$52,3,0)+IF(AG53=$G52+$H52,1,0)+IF(AG54=$I$54,3,0)+IF(AG55=$G54+$H54,1,0)+IF(AG56=$I$56,3,0)+IF(AG57=$G56+$H56,1,0)+IF(AG58=$I$58,3,0)+IF(AG59=$G58+$H58,1,0)+IF(AG60=$I$60,3,0)+IF(AG61=$G60+$H60,1,0)+IF(AG62=$I$62,3,0)+IF(AG63=$G62+$H62,1,0)+IF(AG64=$I$64,3,0)+IF(AG65=$G64+$H64,1,0)+IF(AG66=$I$66,3,0)+IF(AG67=$G66+$H66,1,0)+IF(AG68=$I$68,3,0)+IF(AG69=$G68+$H68,1,0)+IF(AG70=$I$70,3,0)+IF(AG71=$G70+$H70,1,0)+IF(AG72=$I$72,3,0)+IF(AG73=$G72+$H72,1,0)+IF(AG74=$I$74,3,0)+IF(AG75=$G74+$H74,1,0)+IF(AG76=$I$76,3,0)+IF(AG77=$G76+$H76,1,0)+IF(AG78=$I$78,3,0)+IF(AG79=$G78+$H78,1,0))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH4" s="73">
         <f>SUM(IF(AH8=$I$8,3,0)+IF(AH9=$G8+$H8,1,0)+IF(AH10=$I$10,3,0)+IF(AH11=$G10+$H10,1,0)+IF(AH12=$I$12,3,0)+IF(AH13=$G12+$H12,1,0)+IF(AH14=$I$14,3,0)+IF(AH15=$G14+$H14,1,0)
@@ -3142,7 +3142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:54" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" ht="15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="64"/>
       <c r="B5" s="64"/>
       <c r="C5" s="64"/>
@@ -3154,83 +3154,83 @@
       <c r="I5" s="66"/>
       <c r="J5" s="74">
         <f>SUM(IF(J80=$I$80,3,0)+IF(J81=$G80+$H80,1,0)+IF(J82=$I$82,3,0)+IF(J83=$G82+$H82,1,0)+IF(J84=$I$84,3,0)+IF(J85=$G84+$H84,1,0)+IF(J86=$I$86,3,0)+IF(J87=$G86+$H86,1,0)+IF(J88=$I$88,3,0)+IF(J89=$G88+$H88,1,0)+IF(J90=$I$90,3,0)+IF(J91=$G90+$H90,1,0)+IF(J92=$I$92,3,0)+IF(J93=$G92+$H92,1,0)+IF(J94=$I$94,3,0)+IF(J95=$G94+$H94,1,0)+IF(J96=$I$96,3,0)+IF(J97=$G96+$H96,1,0)+IF(J98=$I$98,3,0)+IF(J99=$G98+$H98,1,0)+IF(J100=$I$100,3,0)+IF(J101=$G100+$H100,1,0)+IF(J102=$I$102,3,0)+IF(J103=$G102+$H102,1,0)+IF(J104=$I$104,3,0)+IF(J105=$G104+$H104,1,0)+IF(J106=$I$106,3,0)+IF(J107=$G106+$H106,1,0)+IF(J108=$I$108,3,0)+IF(J109=$G108+$H108,1,0)+IF(J110=$I$110,3,0)+IF(J111=$G110+$H110,1,0)+IF(J112=$I$112,3,0)+IF(J113=$G112+$H112,1,0)+IF(J114=$I$114,3,0)+IF(J115=$G114+$H114,1,0)+IF(J116=$I$116,3,0)+IF(J117=$G116+$H116,1,0)+IF(J118=$I$118,3,0)+IF(J119=$G118+$H118,1,0)+IF(J120=$I$120,3,0)+IF(J121=$G120+$H120,1,0)+IF(J122=$I$122,3,0)+IF(J123=$G122+$H122,1,0)+IF(J124=$I$124,3,0)+IF(J125=$G124+$H124,1,0)+IF(J126=$I$126,3,0)+IF(J127=$G126+$H126,1,0)+IF(J128=$I$128,3,0)+IF(J129=$G128+$H128,1,0)+IF(J130=$I$130,3,0)+IF(J131=$G130+$H130,1,0)+IF(J132=$I$132,3,0)+IF(J133=$G132+$H132,1,0)+IF(J134=$I$134,3,0)+IF(J135=$G134+$H134,1,0)+IF(J136=$I$136,3,0)+IF(J137=$G136+$H136,1,0)+IF(J138=$I$138,3,0)+IF(J139=$G138+$H138,1,0)+IF(J140=$I$140,3,0)+IF(J141=$G140+$H140,1,0)+IF(J142=$I$142,3,0)+IF(J143=$G142+$H142,1,0)+IF(J144=$I$144,3,0)+IF(J145=$G144+$H144,1,0)+IF(J146=$I$146,3,0)+IF(J147=$G146+$H146,1,0)+IF(J148=$I$148,3,0)+IF(J149=$G148+$H148,1,0)+IF(J150=$I$150,3,0)+IF(J151=$G150+$H150,1,0))</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K5" s="75">
         <f>SUM(IF(K80=$I$80,3,0)+IF(K81=$G80+$H80,1,0)+IF(K82=$I$82,3,0)+IF(K83=$G82+$H82,1,0)+IF(K84=$I$84,3,0)+IF(K85=$G84+$H84,1,0)+IF(K86=$I$86,3,0)+IF(K87=$G86+$H86,1,0)+IF(K88=$I$88,3,0)+IF(K89=$G88+$H88,1,0)+IF(K90=$I$90,3,0)+IF(K91=$G90+$H90,1,0)+IF(K92=$I$92,3,0)+IF(K93=$G92+$H92,1,0)+IF(K94=$I$94,3,0)+IF(K95=$G94+$H94,1,0)+IF(K96=$I$96,3,0)+IF(K97=$G96+$H96,1,0)+IF(K98=$I$98,3,0)+IF(K99=$G98+$H98,1,0)+IF(K100=$I$100,3,0)+IF(K101=$G100+$H100,1,0)+IF(K102=$I$102,3,0)+IF(K103=$G102+$H102,1,0)+IF(K104=$I$104,3,0)+IF(K105=$G104+$H104,1,0)+IF(K106=$I$106,3,0)+IF(K107=$G106+$H106,1,0)+IF(K108=$I$108,3,0)+IF(K109=$G108+$H108,1,0)+IF(K110=$I$110,3,0)+IF(K111=$G110+$H110,1,0)+IF(K112=$I$112,3,0)+IF(K113=$G112+$H112,1,0)+IF(K114=$I$114,3,0)+IF(K115=$G114+$H114,1,0)+IF(K116=$I$116,3,0)+IF(K117=$G116+$H116,1,0)+IF(K118=$I$118,3,0)+IF(K119=$G118+$H118,1,0)+IF(K120=$I$120,3,0)+IF(K121=$G120+$H120,1,0)+IF(K122=$I$122,3,0)+IF(K123=$G122+$H122,1,0)+IF(K124=$I$124,3,0)+IF(K125=$G124+$H124,1,0)+IF(K126=$I$126,3,0)+IF(K127=$G126+$H126,1,0)+IF(K128=$I$128,3,0)+IF(K129=$G128+$H128,1,0)+IF(K130=$I$130,3,0)+IF(K131=$G130+$H130,1,0)+IF(K132=$I$132,3,0)+IF(K133=$G132+$H132,1,0)+IF(K134=$I$134,3,0)+IF(K135=$G134+$H134,1,0)+IF(K136=$I$136,3,0)+IF(K137=$G136+$H136,1,0)+IF(K138=$I$138,3,0)+IF(K139=$G138+$H138,1,0)+IF(K140=$I$140,3,0)+IF(K141=$G140+$H140,1,0)+IF(K142=$I$142,3,0)+IF(K143=$G142+$H142,1,0)+IF(K144=$I$144,3,0)+IF(K145=$G144+$H144,1,0)+IF(K146=$I$146,3,0)+IF(K147=$G146+$H146,1,0)+IF(K148=$I$148,3,0)+IF(K149=$G148+$H148,1,0)+IF(K150=$I$150,3,0)+IF(K151=$G150+$H150,1,0))</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L5" s="75">
         <f>SUM(IF(L80=$I$80,3,0)+IF(L81=$G80+$H80,1,0)+IF(L82=$I$82,3,0)+IF(L83=$G82+$H82,1,0)+IF(L84=$I$84,3,0)+IF(L85=$G84+$H84,1,0)+IF(L86=$I$86,3,0)+IF(L87=$G86+$H86,1,0)+IF(L88=$I$88,3,0)+IF(L89=$G88+$H88,1,0)+IF(L90=$I$90,3,0)+IF(L91=$G90+$H90,1,0)+IF(L92=$I$92,3,0)+IF(L93=$G92+$H92,1,0)+IF(L94=$I$94,3,0)+IF(L95=$G94+$H94,1,0)+IF(L96=$I$96,3,0)+IF(L97=$G96+$H96,1,0)+IF(L98=$I$98,3,0)+IF(L99=$G98+$H98,1,0)+IF(L100=$I$100,3,0)+IF(L101=$G100+$H100,1,0)+IF(L102=$I$102,3,0)+IF(L103=$G102+$H102,1,0)+IF(L104=$I$104,3,0)+IF(L105=$G104+$H104,1,0)+IF(L106=$I$106,3,0)+IF(L107=$G106+$H106,1,0)+IF(L108=$I$108,3,0)+IF(L109=$G108+$H108,1,0)+IF(L110=$I$110,3,0)+IF(L111=$G110+$H110,1,0)+IF(L112=$I$112,3,0)+IF(L113=$G112+$H112,1,0)+IF(L114=$I$114,3,0)+IF(L115=$G114+$H114,1,0)+IF(L116=$I$116,3,0)+IF(L117=$G116+$H116,1,0)+IF(L118=$I$118,3,0)+IF(L119=$G118+$H118,1,0)+IF(L120=$I$120,3,0)+IF(L121=$G120+$H120,1,0)+IF(L122=$I$122,3,0)+IF(L123=$G122+$H122,1,0)+IF(L124=$I$124,3,0)+IF(L125=$G124+$H124,1,0)+IF(L126=$I$126,3,0)+IF(L127=$G126+$H126,1,0)+IF(L128=$I$128,3,0)+IF(L129=$G128+$H128,1,0)+IF(L130=$I$130,3,0)+IF(L131=$G130+$H130,1,0)+IF(L132=$I$132,3,0)+IF(L133=$G132+$H132,1,0)+IF(L134=$I$134,3,0)+IF(L135=$G134+$H134,1,0)+IF(L136=$I$136,3,0)+IF(L137=$G136+$H136,1,0)+IF(L138=$I$138,3,0)+IF(L139=$G138+$H138,1,0)+IF(L140=$I$140,3,0)+IF(L141=$G140+$H140,1,0)+IF(L142=$I$142,3,0)+IF(L143=$G142+$H142,1,0)+IF(L144=$I$144,3,0)+IF(L145=$G144+$H144,1,0)+IF(L146=$I$146,3,0)+IF(L147=$G146+$H146,1,0)+IF(L148=$I$148,3,0)+IF(L149=$G148+$H148,1,0)+IF(L150=$I$150,3,0)+IF(L151=$G150+$H150,1,0))</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M5" s="75">
         <f>SUM(IF(M80=$I$80,3,0)+IF(M81=$G80+$H80,1,0)+IF(M82=$I$82,3,0)+IF(M83=$G82+$H82,1,0)+IF(M84=$I$84,3,0)+IF(M85=$G84+$H84,1,0)+IF(M86=$I$86,3,0)+IF(M87=$G86+$H86,1,0)+IF(M88=$I$88,3,0)+IF(M89=$G88+$H88,1,0)+IF(M90=$I$90,3,0)+IF(M91=$G90+$H90,1,0)+IF(M92=$I$92,3,0)+IF(M93=$G92+$H92,1,0)+IF(M94=$I$94,3,0)+IF(M95=$G94+$H94,1,0)+IF(M96=$I$96,3,0)+IF(M97=$G96+$H96,1,0)+IF(M98=$I$98,3,0)+IF(M99=$G98+$H98,1,0)+IF(M100=$I$100,3,0)+IF(M101=$G100+$H100,1,0)+IF(M102=$I$102,3,0)+IF(M103=$G102+$H102,1,0)+IF(M104=$I$104,3,0)+IF(M105=$G104+$H104,1,0)+IF(M106=$I$106,3,0)+IF(M107=$G106+$H106,1,0)+IF(M108=$I$108,3,0)+IF(M109=$G108+$H108,1,0)+IF(M110=$I$110,3,0)+IF(M111=$G110+$H110,1,0)+IF(M112=$I$112,3,0)+IF(M113=$G112+$H112,1,0)+IF(M114=$I$114,3,0)+IF(M115=$G114+$H114,1,0)+IF(M116=$I$116,3,0)+IF(M117=$G116+$H116,1,0)+IF(M118=$I$118,3,0)+IF(M119=$G118+$H118,1,0)+IF(M120=$I$120,3,0)+IF(M121=$G120+$H120,1,0)+IF(M122=$I$122,3,0)+IF(M123=$G122+$H122,1,0)+IF(M124=$I$124,3,0)+IF(M125=$G124+$H124,1,0)+IF(M126=$I$126,3,0)+IF(M127=$G126+$H126,1,0)+IF(M128=$I$128,3,0)+IF(M129=$G128+$H128,1,0)+IF(M130=$I$130,3,0)+IF(M131=$G130+$H130,1,0)+IF(M132=$I$132,3,0)+IF(M133=$G132+$H132,1,0)+IF(M134=$I$134,3,0)+IF(M135=$G134+$H134,1,0)+IF(M136=$I$136,3,0)+IF(M137=$G136+$H136,1,0)+IF(M138=$I$138,3,0)+IF(M139=$G138+$H138,1,0)+IF(M140=$I$140,3,0)+IF(M141=$G140+$H140,1,0)+IF(M142=$I$142,3,0)+IF(M143=$G142+$H142,1,0)+IF(M144=$I$144,3,0)+IF(M145=$G144+$H144,1,0)+IF(M146=$I$146,3,0)+IF(M147=$G146+$H146,1,0)+IF(M148=$I$148,3,0)+IF(M149=$G148+$H148,1,0)+IF(M150=$I$150,3,0)+IF(M151=$G150+$H150,1,0))</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N5" s="75">
         <f>SUM(IF(N80=$I$80,3,0)+IF(N81=$G80+$H80,1,0)+IF(N82=$I$82,3,0)+IF(N83=$G82+$H82,1,0)+IF(N84=$I$84,3,0)+IF(N85=$G84+$H84,1,0)+IF(N86=$I$86,3,0)+IF(N87=$G86+$H86,1,0)+IF(N88=$I$88,3,0)+IF(N89=$G88+$H88,1,0)+IF(N90=$I$90,3,0)+IF(N91=$G90+$H90,1,0)+IF(N92=$I$92,3,0)+IF(N93=$G92+$H92,1,0)+IF(N94=$I$94,3,0)+IF(N95=$G94+$H94,1,0)+IF(N96=$I$96,3,0)+IF(N97=$G96+$H96,1,0)+IF(N98=$I$98,3,0)+IF(N99=$G98+$H98,1,0)+IF(N100=$I$100,3,0)+IF(N101=$G100+$H100,1,0)+IF(N102=$I$102,3,0)+IF(N103=$G102+$H102,1,0)+IF(N104=$I$104,3,0)+IF(N105=$G104+$H104,1,0)+IF(N106=$I$106,3,0)+IF(N107=$G106+$H106,1,0)+IF(N108=$I$108,3,0)+IF(N109=$G108+$H108,1,0)+IF(N110=$I$110,3,0)+IF(N111=$G110+$H110,1,0)+IF(N112=$I$112,3,0)+IF(N113=$G112+$H112,1,0)+IF(N114=$I$114,3,0)+IF(N115=$G114+$H114,1,0)+IF(N116=$I$116,3,0)+IF(N117=$G116+$H116,1,0)+IF(N118=$I$118,3,0)+IF(N119=$G118+$H118,1,0)+IF(N120=$I$120,3,0)+IF(N121=$G120+$H120,1,0)+IF(N122=$I$122,3,0)+IF(N123=$G122+$H122,1,0)+IF(N124=$I$124,3,0)+IF(N125=$G124+$H124,1,0)+IF(N126=$I$126,3,0)+IF(N127=$G126+$H126,1,0)+IF(N128=$I$128,3,0)+IF(N129=$G128+$H128,1,0)+IF(N130=$I$130,3,0)+IF(N131=$G130+$H130,1,0)+IF(N132=$I$132,3,0)+IF(N133=$G132+$H132,1,0)+IF(N134=$I$134,3,0)+IF(N135=$G134+$H134,1,0)+IF(N136=$I$136,3,0)+IF(N137=$G136+$H136,1,0)+IF(N138=$I$138,3,0)+IF(N139=$G138+$H138,1,0)+IF(N140=$I$140,3,0)+IF(N141=$G140+$H140,1,0)+IF(N142=$I$142,3,0)+IF(N143=$G142+$H142,1,0)+IF(N144=$I$144,3,0)+IF(N145=$G144+$H144,1,0)+IF(N146=$I$146,3,0)+IF(N147=$G146+$H146,1,0)+IF(N148=$I$148,3,0)+IF(N149=$G148+$H148,1,0)+IF(N150=$I$150,3,0)+IF(N151=$G150+$H150,1,0))</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O5" s="75">
         <f>SUM(IF(O80=$I$80,3,0)+IF(O81=$G80+$H80,1,0)+IF(O82=$I$82,3,0)+IF(O83=$G82+$H82,1,0)+IF(O84=$I$84,3,0)+IF(O85=$G84+$H84,1,0)+IF(O86=$I$86,3,0)+IF(O87=$G86+$H86,1,0)+IF(O88=$I$88,3,0)+IF(O89=$G88+$H88,1,0)+IF(O90=$I$90,3,0)+IF(O91=$G90+$H90,1,0)+IF(O92=$I$92,3,0)+IF(O93=$G92+$H92,1,0)+IF(O94=$I$94,3,0)+IF(O95=$G94+$H94,1,0)+IF(O96=$I$96,3,0)+IF(O97=$G96+$H96,1,0)+IF(O98=$I$98,3,0)+IF(O99=$G98+$H98,1,0)+IF(O100=$I$100,3,0)+IF(O101=$G100+$H100,1,0)+IF(O102=$I$102,3,0)+IF(O103=$G102+$H102,1,0)+IF(O104=$I$104,3,0)+IF(O105=$G104+$H104,1,0)+IF(O106=$I$106,3,0)+IF(O107=$G106+$H106,1,0)+IF(O108=$I$108,3,0)+IF(O109=$G108+$H108,1,0)+IF(O110=$I$110,3,0)+IF(O111=$G110+$H110,1,0)+IF(O112=$I$112,3,0)+IF(O113=$G112+$H112,1,0)+IF(O114=$I$114,3,0)+IF(O115=$G114+$H114,1,0)+IF(O116=$I$116,3,0)+IF(O117=$G116+$H116,1,0)+IF(O118=$I$118,3,0)+IF(O119=$G118+$H118,1,0)+IF(O120=$I$120,3,0)+IF(O121=$G120+$H120,1,0)+IF(O122=$I$122,3,0)+IF(O123=$G122+$H122,1,0)+IF(O124=$I$124,3,0)+IF(O125=$G124+$H124,1,0)+IF(O126=$I$126,3,0)+IF(O127=$G126+$H126,1,0)+IF(O128=$I$128,3,0)+IF(O129=$G128+$H128,1,0)+IF(O130=$I$130,3,0)+IF(O131=$G130+$H130,1,0)+IF(O132=$I$132,3,0)+IF(O133=$G132+$H132,1,0)+IF(O134=$I$134,3,0)+IF(O135=$G134+$H134,1,0)+IF(O136=$I$136,3,0)+IF(O137=$G136+$H136,1,0)+IF(O138=$I$138,3,0)+IF(O139=$G138+$H138,1,0)+IF(O140=$I$140,3,0)+IF(O141=$G140+$H140,1,0)+IF(O142=$I$142,3,0)+IF(O143=$G142+$H142,1,0)+IF(O144=$I$144,3,0)+IF(O145=$G144+$H144,1,0)+IF(O146=$I$146,3,0)+IF(O147=$G146+$H146,1,0)+IF(O148=$I$148,3,0)+IF(O149=$G148+$H148,1,0)+IF(O150=$I$150,3,0)+IF(O151=$G150+$H150,1,0))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P5" s="75">
         <f>SUM(IF(P80=$I$80,3,0)+IF(P81=$G80+$H80,1,0)+IF(P82=$I$82,3,0)+IF(P83=$G82+$H82,1,0)+IF(P84=$I$84,3,0)+IF(P85=$G84+$H84,1,0)+IF(P86=$I$86,3,0)+IF(P87=$G86+$H86,1,0)+IF(P88=$I$88,3,0)+IF(P89=$G88+$H88,1,0)+IF(P90=$I$90,3,0)+IF(P91=$G90+$H90,1,0)+IF(P92=$I$92,3,0)+IF(P93=$G92+$H92,1,0)+IF(P94=$I$94,3,0)+IF(P95=$G94+$H94,1,0)+IF(P96=$I$96,3,0)+IF(P97=$G96+$H96,1,0)+IF(P98=$I$98,3,0)+IF(P99=$G98+$H98,1,0)+IF(P100=$I$100,3,0)+IF(P101=$G100+$H100,1,0)+IF(P102=$I$102,3,0)+IF(P103=$G102+$H102,1,0)+IF(P104=$I$104,3,0)+IF(P105=$G104+$H104,1,0)+IF(P106=$I$106,3,0)+IF(P107=$G106+$H106,1,0)+IF(P108=$I$108,3,0)+IF(P109=$G108+$H108,1,0)+IF(P110=$I$110,3,0)+IF(P111=$G110+$H110,1,0)+IF(P112=$I$112,3,0)+IF(P113=$G112+$H112,1,0)+IF(P114=$I$114,3,0)+IF(P115=$G114+$H114,1,0)+IF(P116=$I$116,3,0)+IF(P117=$G116+$H116,1,0)+IF(P118=$I$118,3,0)+IF(P119=$G118+$H118,1,0)+IF(P120=$I$120,3,0)+IF(P121=$G120+$H120,1,0)+IF(P122=$I$122,3,0)+IF(P123=$G122+$H122,1,0)+IF(P124=$I$124,3,0)+IF(P125=$G124+$H124,1,0)+IF(P126=$I$126,3,0)+IF(P127=$G126+$H126,1,0)+IF(P128=$I$128,3,0)+IF(P129=$G128+$H128,1,0)+IF(P130=$I$130,3,0)+IF(P131=$G130+$H130,1,0)+IF(P132=$I$132,3,0)+IF(P133=$G132+$H132,1,0)+IF(P134=$I$134,3,0)+IF(P135=$G134+$H134,1,0)+IF(P136=$I$136,3,0)+IF(P137=$G136+$H136,1,0)+IF(P138=$I$138,3,0)+IF(P139=$G138+$H138,1,0)+IF(P140=$I$140,3,0)+IF(P141=$G140+$H140,1,0)+IF(P142=$I$142,3,0)+IF(P143=$G142+$H142,1,0)+IF(P144=$I$144,3,0)+IF(P145=$G144+$H144,1,0)+IF(P146=$I$146,3,0)+IF(P147=$G146+$H146,1,0)+IF(P148=$I$148,3,0)+IF(P149=$G148+$H148,1,0)+IF(P150=$I$150,3,0)+IF(P151=$G150+$H150,1,0))</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q5" s="75">
         <f>SUM(IF(Q80=$I$80,3,0)+IF(Q81=$G80+$H80,1,0)+IF(Q82=$I$82,3,0)+IF(Q83=$G82+$H82,1,0)+IF(Q84=$I$84,3,0)+IF(Q85=$G84+$H84,1,0)+IF(Q86=$I$86,3,0)+IF(Q87=$G86+$H86,1,0)+IF(Q88=$I$88,3,0)+IF(Q89=$G88+$H88,1,0)+IF(Q90=$I$90,3,0)+IF(Q91=$G90+$H90,1,0)+IF(Q92=$I$92,3,0)+IF(Q93=$G92+$H92,1,0)+IF(Q94=$I$94,3,0)+IF(Q95=$G94+$H94,1,0)+IF(Q96=$I$96,3,0)+IF(Q97=$G96+$H96,1,0)+IF(Q98=$I$98,3,0)+IF(Q99=$G98+$H98,1,0)+IF(Q100=$I$100,3,0)+IF(Q101=$G100+$H100,1,0)+IF(Q102=$I$102,3,0)+IF(Q103=$G102+$H102,1,0)+IF(Q104=$I$104,3,0)+IF(Q105=$G104+$H104,1,0)+IF(Q106=$I$106,3,0)+IF(Q107=$G106+$H106,1,0)+IF(Q108=$I$108,3,0)+IF(Q109=$G108+$H108,1,0)+IF(Q110=$I$110,3,0)+IF(Q111=$G110+$H110,1,0)+IF(Q112=$I$112,3,0)+IF(Q113=$G112+$H112,1,0)+IF(Q114=$I$114,3,0)+IF(Q115=$G114+$H114,1,0)+IF(Q116=$I$116,3,0)+IF(Q117=$G116+$H116,1,0)+IF(Q118=$I$118,3,0)+IF(Q119=$G118+$H118,1,0)+IF(Q120=$I$120,3,0)+IF(Q121=$G120+$H120,1,0)+IF(Q122=$I$122,3,0)+IF(Q123=$G122+$H122,1,0)+IF(Q124=$I$124,3,0)+IF(Q125=$G124+$H124,1,0)+IF(Q126=$I$126,3,0)+IF(Q127=$G126+$H126,1,0)+IF(Q128=$I$128,3,0)+IF(Q129=$G128+$H128,1,0)+IF(Q130=$I$130,3,0)+IF(Q131=$G130+$H130,1,0)+IF(Q132=$I$132,3,0)+IF(Q133=$G132+$H132,1,0)+IF(Q134=$I$134,3,0)+IF(Q135=$G134+$H134,1,0)+IF(Q136=$I$136,3,0)+IF(Q137=$G136+$H136,1,0)+IF(Q138=$I$138,3,0)+IF(Q139=$G138+$H138,1,0)+IF(Q140=$I$140,3,0)+IF(Q141=$G140+$H140,1,0)+IF(Q142=$I$142,3,0)+IF(Q143=$G142+$H142,1,0)+IF(Q144=$I$144,3,0)+IF(Q145=$G144+$H144,1,0)+IF(Q146=$I$146,3,0)+IF(Q147=$G146+$H146,1,0)+IF(Q148=$I$148,3,0)+IF(Q149=$G148+$H148,1,0)+IF(Q150=$I$150,3,0)+IF(Q151=$G150+$H150,1,0))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R5" s="75">
         <f>SUM(IF(R80=$I$80,3,0)+IF(R81=$G80+$H80,1,0)+IF(R82=$I$82,3,0)+IF(R83=$G82+$H82,1,0)+IF(R84=$I$84,3,0)+IF(R85=$G84+$H84,1,0)+IF(R86=$I$86,3,0)+IF(R87=$G86+$H86,1,0)+IF(R88=$I$88,3,0)+IF(R89=$G88+$H88,1,0)+IF(R90=$I$90,3,0)+IF(R91=$G90+$H90,1,0)+IF(R92=$I$92,3,0)+IF(R93=$G92+$H92,1,0)+IF(R94=$I$94,3,0)+IF(R95=$G94+$H94,1,0)+IF(R96=$I$96,3,0)+IF(R97=$G96+$H96,1,0)+IF(R98=$I$98,3,0)+IF(R99=$G98+$H98,1,0)+IF(R100=$I$100,3,0)+IF(R101=$G100+$H100,1,0)+IF(R102=$I$102,3,0)+IF(R103=$G102+$H102,1,0)+IF(R104=$I$104,3,0)+IF(R105=$G104+$H104,1,0)+IF(R106=$I$106,3,0)+IF(R107=$G106+$H106,1,0)+IF(R108=$I$108,3,0)+IF(R109=$G108+$H108,1,0)+IF(R110=$I$110,3,0)+IF(R111=$G110+$H110,1,0)+IF(R112=$I$112,3,0)+IF(R113=$G112+$H112,1,0)+IF(R114=$I$114,3,0)+IF(R115=$G114+$H114,1,0)+IF(R116=$I$116,3,0)+IF(R117=$G116+$H116,1,0)+IF(R118=$I$118,3,0)+IF(R119=$G118+$H118,1,0)+IF(R120=$I$120,3,0)+IF(R121=$G120+$H120,1,0)+IF(R122=$I$122,3,0)+IF(R123=$G122+$H122,1,0)+IF(R124=$I$124,3,0)+IF(R125=$G124+$H124,1,0)+IF(R126=$I$126,3,0)+IF(R127=$G126+$H126,1,0)+IF(R128=$I$128,3,0)+IF(R129=$G128+$H128,1,0)+IF(R130=$I$130,3,0)+IF(R131=$G130+$H130,1,0)+IF(R132=$I$132,3,0)+IF(R133=$G132+$H132,1,0)+IF(R134=$I$134,3,0)+IF(R135=$G134+$H134,1,0)+IF(R136=$I$136,3,0)+IF(R137=$G136+$H136,1,0)+IF(R138=$I$138,3,0)+IF(R139=$G138+$H138,1,0)+IF(R140=$I$140,3,0)+IF(R141=$G140+$H140,1,0)+IF(R142=$I$142,3,0)+IF(R143=$G142+$H142,1,0)+IF(R144=$I$144,3,0)+IF(R145=$G144+$H144,1,0)+IF(R146=$I$146,3,0)+IF(R147=$G146+$H146,1,0)+IF(R148=$I$148,3,0)+IF(R149=$G148+$H148,1,0)+IF(R150=$I$150,3,0)+IF(R151=$G150+$H150,1,0))</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S5" s="75">
         <f>SUM(IF(S80=$I$80,3,0)+IF(S81=$G80+$H80,1,0)+IF(S82=$I$82,3,0)+IF(S83=$G82+$H82,1,0)+IF(S84=$I$84,3,0)+IF(S85=$G84+$H84,1,0)+IF(S86=$I$86,3,0)+IF(S87=$G86+$H86,1,0)+IF(S88=$I$88,3,0)+IF(S89=$G88+$H88,1,0)+IF(S90=$I$90,3,0)+IF(S91=$G90+$H90,1,0)+IF(S92=$I$92,3,0)+IF(S93=$G92+$H92,1,0)+IF(S94=$I$94,3,0)+IF(S95=$G94+$H94,1,0)+IF(S96=$I$96,3,0)+IF(S97=$G96+$H96,1,0)+IF(S98=$I$98,3,0)+IF(S99=$G98+$H98,1,0)+IF(S100=$I$100,3,0)+IF(S101=$G100+$H100,1,0)+IF(S102=$I$102,3,0)+IF(S103=$G102+$H102,1,0)+IF(S104=$I$104,3,0)+IF(S105=$G104+$H104,1,0)+IF(S106=$I$106,3,0)+IF(S107=$G106+$H106,1,0)+IF(S108=$I$108,3,0)+IF(S109=$G108+$H108,1,0)+IF(S110=$I$110,3,0)+IF(S111=$G110+$H110,1,0)+IF(S112=$I$112,3,0)+IF(S113=$G112+$H112,1,0)+IF(S114=$I$114,3,0)+IF(S115=$G114+$H114,1,0)+IF(S116=$I$116,3,0)+IF(S117=$G116+$H116,1,0)+IF(S118=$I$118,3,0)+IF(S119=$G118+$H118,1,0)+IF(S120=$I$120,3,0)+IF(S121=$G120+$H120,1,0)+IF(S122=$I$122,3,0)+IF(S123=$G122+$H122,1,0)+IF(S124=$I$124,3,0)+IF(S125=$G124+$H124,1,0)+IF(S126=$I$126,3,0)+IF(S127=$G126+$H126,1,0)+IF(S128=$I$128,3,0)+IF(S129=$G128+$H128,1,0)+IF(S130=$I$130,3,0)+IF(S131=$G130+$H130,1,0)+IF(S132=$I$132,3,0)+IF(S133=$G132+$H132,1,0)+IF(S134=$I$134,3,0)+IF(S135=$G134+$H134,1,0)+IF(S136=$I$136,3,0)+IF(S137=$G136+$H136,1,0)+IF(S138=$I$138,3,0)+IF(S139=$G138+$H138,1,0)+IF(S140=$I$140,3,0)+IF(S141=$G140+$H140,1,0)+IF(S142=$I$142,3,0)+IF(S143=$G142+$H142,1,0)+IF(S144=$I$144,3,0)+IF(S145=$G144+$H144,1,0)+IF(S146=$I$146,3,0)+IF(S147=$G146+$H146,1,0)+IF(S148=$I$148,3,0)+IF(S149=$G148+$H148,1,0)+IF(S150=$I$150,3,0)+IF(S151=$G150+$H150,1,0))</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T5" s="75">
         <f>SUM(IF(T80=$I$80,3,0)+IF(T81=$G80+$H80,1,0)+IF(T82=$I$82,3,0)+IF(T83=$G82+$H82,1,0)+IF(T84=$I$84,3,0)+IF(T85=$G84+$H84,1,0)+IF(T86=$I$86,3,0)+IF(T87=$G86+$H86,1,0)+IF(T88=$I$88,3,0)+IF(T89=$G88+$H88,1,0)+IF(T90=$I$90,3,0)+IF(T91=$G90+$H90,1,0)+IF(T92=$I$92,3,0)+IF(T93=$G92+$H92,1,0)+IF(T94=$I$94,3,0)+IF(T95=$G94+$H94,1,0)+IF(T96=$I$96,3,0)+IF(T97=$G96+$H96,1,0)+IF(T98=$I$98,3,0)+IF(T99=$G98+$H98,1,0)+IF(T100=$I$100,3,0)+IF(T101=$G100+$H100,1,0)+IF(T102=$I$102,3,0)+IF(T103=$G102+$H102,1,0)+IF(T104=$I$104,3,0)+IF(T105=$G104+$H104,1,0)+IF(T106=$I$106,3,0)+IF(T107=$G106+$H106,1,0)+IF(T108=$I$108,3,0)+IF(T109=$G108+$H108,1,0)+IF(T110=$I$110,3,0)+IF(T111=$G110+$H110,1,0)+IF(T112=$I$112,3,0)+IF(T113=$G112+$H112,1,0)+IF(T114=$I$114,3,0)+IF(T115=$G114+$H114,1,0)+IF(T116=$I$116,3,0)+IF(T117=$G116+$H116,1,0)+IF(T118=$I$118,3,0)+IF(T119=$G118+$H118,1,0)+IF(T120=$I$120,3,0)+IF(T121=$G120+$H120,1,0)+IF(T122=$I$122,3,0)+IF(T123=$G122+$H122,1,0)+IF(T124=$I$124,3,0)+IF(T125=$G124+$H124,1,0)+IF(T126=$I$126,3,0)+IF(T127=$G126+$H126,1,0)+IF(T128=$I$128,3,0)+IF(T129=$G128+$H128,1,0)+IF(T130=$I$130,3,0)+IF(T131=$G130+$H130,1,0)+IF(T132=$I$132,3,0)+IF(T133=$G132+$H132,1,0)+IF(T134=$I$134,3,0)+IF(T135=$G134+$H134,1,0)+IF(T136=$I$136,3,0)+IF(T137=$G136+$H136,1,0)+IF(T138=$I$138,3,0)+IF(T139=$G138+$H138,1,0)+IF(T140=$I$140,3,0)+IF(T141=$G140+$H140,1,0)+IF(T142=$I$142,3,0)+IF(T143=$G142+$H142,1,0)+IF(T144=$I$144,3,0)+IF(T145=$G144+$H144,1,0)+IF(T146=$I$146,3,0)+IF(T147=$G146+$H146,1,0)+IF(T148=$I$148,3,0)+IF(T149=$G148+$H148,1,0)+IF(T150=$I$150,3,0)+IF(T151=$G150+$H150,1,0))</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U5" s="75">
         <f>SUM(IF(U80=$I$80,3,0)+IF(U81=$G80+$H80,1,0)+IF(U82=$I$82,3,0)+IF(U83=$G82+$H82,1,0)+IF(U84=$I$84,3,0)+IF(U85=$G84+$H84,1,0)+IF(U86=$I$86,3,0)+IF(U87=$G86+$H86,1,0)+IF(U88=$I$88,3,0)+IF(U89=$G88+$H88,1,0)+IF(U90=$I$90,3,0)+IF(U91=$G90+$H90,1,0)+IF(U92=$I$92,3,0)+IF(U93=$G92+$H92,1,0)+IF(U94=$I$94,3,0)+IF(U95=$G94+$H94,1,0)+IF(U96=$I$96,3,0)+IF(U97=$G96+$H96,1,0)+IF(U98=$I$98,3,0)+IF(U99=$G98+$H98,1,0)+IF(U100=$I$100,3,0)+IF(U101=$G100+$H100,1,0)+IF(U102=$I$102,3,0)+IF(U103=$G102+$H102,1,0)+IF(U104=$I$104,3,0)+IF(U105=$G104+$H104,1,0)+IF(U106=$I$106,3,0)+IF(U107=$G106+$H106,1,0)+IF(U108=$I$108,3,0)+IF(U109=$G108+$H108,1,0)+IF(U110=$I$110,3,0)+IF(U111=$G110+$H110,1,0)+IF(U112=$I$112,3,0)+IF(U113=$G112+$H112,1,0)+IF(U114=$I$114,3,0)+IF(U115=$G114+$H114,1,0)+IF(U116=$I$116,3,0)+IF(U117=$G116+$H116,1,0)+IF(U118=$I$118,3,0)+IF(U119=$G118+$H118,1,0)+IF(U120=$I$120,3,0)+IF(U121=$G120+$H120,1,0)+IF(U122=$I$122,3,0)+IF(U123=$G122+$H122,1,0)+IF(U124=$I$124,3,0)+IF(U125=$G124+$H124,1,0)+IF(U126=$I$126,3,0)+IF(U127=$G126+$H126,1,0)+IF(U128=$I$128,3,0)+IF(U129=$G128+$H128,1,0)+IF(U130=$I$130,3,0)+IF(U131=$G130+$H130,1,0)+IF(U132=$I$132,3,0)+IF(U133=$G132+$H132,1,0)+IF(U134=$I$134,3,0)+IF(U135=$G134+$H134,1,0)+IF(U136=$I$136,3,0)+IF(U137=$G136+$H136,1,0)+IF(U138=$I$138,3,0)+IF(U139=$G138+$H138,1,0)+IF(U140=$I$140,3,0)+IF(U141=$G140+$H140,1,0)+IF(U142=$I$142,3,0)+IF(U143=$G142+$H142,1,0)+IF(U144=$I$144,3,0)+IF(U145=$G144+$H144,1,0)+IF(U146=$I$146,3,0)+IF(U147=$G146+$H146,1,0)+IF(U148=$I$148,3,0)+IF(U149=$G148+$H148,1,0)+IF(U150=$I$150,3,0)+IF(U151=$G150+$H150,1,0))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V5" s="75">
         <f>SUM(IF(V80=$I$80,3,0)+IF(V81=$G80+$H80,1,0)+IF(V82=$I$82,3,0)+IF(V83=$G82+$H82,1,0)+IF(V84=$I$84,3,0)+IF(V85=$G84+$H84,1,0)+IF(V86=$I$86,3,0)+IF(V87=$G86+$H86,1,0)+IF(V88=$I$88,3,0)+IF(V89=$G88+$H88,1,0)+IF(V90=$I$90,3,0)+IF(V91=$G90+$H90,1,0)+IF(V92=$I$92,3,0)+IF(V93=$G92+$H92,1,0)+IF(V94=$I$94,3,0)+IF(V95=$G94+$H94,1,0)+IF(V96=$I$96,3,0)+IF(V97=$G96+$H96,1,0)+IF(V98=$I$98,3,0)+IF(V99=$G98+$H98,1,0)+IF(V100=$I$100,3,0)+IF(V101=$G100+$H100,1,0)+IF(V102=$I$102,3,0)+IF(V103=$G102+$H102,1,0)+IF(V104=$I$104,3,0)+IF(V105=$G104+$H104,1,0)+IF(V106=$I$106,3,0)+IF(V107=$G106+$H106,1,0)+IF(V108=$I$108,3,0)+IF(V109=$G108+$H108,1,0)+IF(V110=$I$110,3,0)+IF(V111=$G110+$H110,1,0)+IF(V112=$I$112,3,0)+IF(V113=$G112+$H112,1,0)+IF(V114=$I$114,3,0)+IF(V115=$G114+$H114,1,0)+IF(V116=$I$116,3,0)+IF(V117=$G116+$H116,1,0)+IF(V118=$I$118,3,0)+IF(V119=$G118+$H118,1,0)+IF(V120=$I$120,3,0)+IF(V121=$G120+$H120,1,0)+IF(V122=$I$122,3,0)+IF(V123=$G122+$H122,1,0)+IF(V124=$I$124,3,0)+IF(V125=$G124+$H124,1,0)+IF(V126=$I$126,3,0)+IF(V127=$G126+$H126,1,0)+IF(V128=$I$128,3,0)+IF(V129=$G128+$H128,1,0)+IF(V130=$I$130,3,0)+IF(V131=$G130+$H130,1,0)+IF(V132=$I$132,3,0)+IF(V133=$G132+$H132,1,0)+IF(V134=$I$134,3,0)+IF(V135=$G134+$H134,1,0)+IF(V136=$I$136,3,0)+IF(V137=$G136+$H136,1,0)+IF(V138=$I$138,3,0)+IF(V139=$G138+$H138,1,0)+IF(V140=$I$140,3,0)+IF(V141=$G140+$H140,1,0)+IF(V142=$I$142,3,0)+IF(V143=$G142+$H142,1,0)+IF(V144=$I$144,3,0)+IF(V145=$G144+$H144,1,0)+IF(V146=$I$146,3,0)+IF(V147=$G146+$H146,1,0)+IF(V148=$I$148,3,0)+IF(V149=$G148+$H148,1,0)+IF(V150=$I$150,3,0)+IF(V151=$G150+$H150,1,0))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W5" s="75">
         <f>SUM(IF(W80=$I$80,3,0)+IF(W81=$G80+$H80,1,0)+IF(W82=$I$82,3,0)+IF(W83=$G82+$H82,1,0)+IF(W84=$I$84,3,0)+IF(W85=$G84+$H84,1,0)+IF(W86=$I$86,3,0)+IF(W87=$G86+$H86,1,0)+IF(W88=$I$88,3,0)+IF(W89=$G88+$H88,1,0)+IF(W90=$I$90,3,0)+IF(W91=$G90+$H90,1,0)+IF(W92=$I$92,3,0)+IF(W93=$G92+$H92,1,0)+IF(W94=$I$94,3,0)+IF(W95=$G94+$H94,1,0)+IF(W96=$I$96,3,0)+IF(W97=$G96+$H96,1,0)+IF(W98=$I$98,3,0)+IF(W99=$G98+$H98,1,0)+IF(W100=$I$100,3,0)+IF(W101=$G100+$H100,1,0)+IF(W102=$I$102,3,0)+IF(W103=$G102+$H102,1,0)+IF(W104=$I$104,3,0)+IF(W105=$G104+$H104,1,0)+IF(W106=$I$106,3,0)+IF(W107=$G106+$H106,1,0)+IF(W108=$I$108,3,0)+IF(W109=$G108+$H108,1,0)+IF(W110=$I$110,3,0)+IF(W111=$G110+$H110,1,0)+IF(W112=$I$112,3,0)+IF(W113=$G112+$H112,1,0)+IF(W114=$I$114,3,0)+IF(W115=$G114+$H114,1,0)+IF(W116=$I$116,3,0)+IF(W117=$G116+$H116,1,0)+IF(W118=$I$118,3,0)+IF(W119=$G118+$H118,1,0)+IF(W120=$I$120,3,0)+IF(W121=$G120+$H120,1,0)+IF(W122=$I$122,3,0)+IF(W123=$G122+$H122,1,0)+IF(W124=$I$124,3,0)+IF(W125=$G124+$H124,1,0)+IF(W126=$I$126,3,0)+IF(W127=$G126+$H126,1,0)+IF(W128=$I$128,3,0)+IF(W129=$G128+$H128,1,0)+IF(W130=$I$130,3,0)+IF(W131=$G130+$H130,1,0)+IF(W132=$I$132,3,0)+IF(W133=$G132+$H132,1,0)+IF(W134=$I$134,3,0)+IF(W135=$G134+$H134,1,0)+IF(W136=$I$136,3,0)+IF(W137=$G136+$H136,1,0)+IF(W138=$I$138,3,0)+IF(W139=$G138+$H138,1,0)+IF(W140=$I$140,3,0)+IF(W141=$G140+$H140,1,0)+IF(W142=$I$142,3,0)+IF(W143=$G142+$H142,1,0)+IF(W144=$I$144,3,0)+IF(W145=$G144+$H144,1,0)+IF(W146=$I$146,3,0)+IF(W147=$G146+$H146,1,0)+IF(W148=$I$148,3,0)+IF(W149=$G148+$H148,1,0)+IF(W150=$I$150,3,0)+IF(W151=$G150+$H150,1,0))</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X5" s="75">
         <f>SUM(IF(X80=$I$80,3,0)+IF(X81=$G80+$H80,1,0)+IF(X82=$I$82,3,0)+IF(X83=$G82+$H82,1,0)+IF(X84=$I$84,3,0)+IF(X85=$G84+$H84,1,0)+IF(X86=$I$86,3,0)+IF(X87=$G86+$H86,1,0)+IF(X88=$I$88,3,0)+IF(X89=$G88+$H88,1,0)+IF(X90=$I$90,3,0)+IF(X91=$G90+$H90,1,0)+IF(X92=$I$92,3,0)+IF(X93=$G92+$H92,1,0)+IF(X94=$I$94,3,0)+IF(X95=$G94+$H94,1,0)+IF(X96=$I$96,3,0)+IF(X97=$G96+$H96,1,0)+IF(X98=$I$98,3,0)+IF(X99=$G98+$H98,1,0)+IF(X100=$I$100,3,0)+IF(X101=$G100+$H100,1,0)+IF(X102=$I$102,3,0)+IF(X103=$G102+$H102,1,0)+IF(X104=$I$104,3,0)+IF(X105=$G104+$H104,1,0)+IF(X106=$I$106,3,0)+IF(X107=$G106+$H106,1,0)+IF(X108=$I$108,3,0)+IF(X109=$G108+$H108,1,0)+IF(X110=$I$110,3,0)+IF(X111=$G110+$H110,1,0)+IF(X112=$I$112,3,0)+IF(X113=$G112+$H112,1,0)+IF(X114=$I$114,3,0)+IF(X115=$G114+$H114,1,0)+IF(X116=$I$116,3,0)+IF(X117=$G116+$H116,1,0)+IF(X118=$I$118,3,0)+IF(X119=$G118+$H118,1,0)+IF(X120=$I$120,3,0)+IF(X121=$G120+$H120,1,0)+IF(X122=$I$122,3,0)+IF(X123=$G122+$H122,1,0)+IF(X124=$I$124,3,0)+IF(X125=$G124+$H124,1,0)+IF(X126=$I$126,3,0)+IF(X127=$G126+$H126,1,0)+IF(X128=$I$128,3,0)+IF(X129=$G128+$H128,1,0)+IF(X130=$I$130,3,0)+IF(X131=$G130+$H130,1,0)+IF(X132=$I$132,3,0)+IF(X133=$G132+$H132,1,0)+IF(X134=$I$134,3,0)+IF(X135=$G134+$H134,1,0)+IF(X136=$I$136,3,0)+IF(X137=$G136+$H136,1,0)+IF(X138=$I$138,3,0)+IF(X139=$G138+$H138,1,0)+IF(X140=$I$140,3,0)+IF(X141=$G140+$H140,1,0)+IF(X142=$I$142,3,0)+IF(X143=$G142+$H142,1,0)+IF(X144=$I$144,3,0)+IF(X145=$G144+$H144,1,0)+IF(X146=$I$146,3,0)+IF(X147=$G146+$H146,1,0)+IF(X148=$I$148,3,0)+IF(X149=$G148+$H148,1,0)+IF(X150=$I$150,3,0)+IF(X151=$G150+$H150,1,0))</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y5" s="75">
         <f>SUM(IF(Y80=$I$80,3,0)+IF(Y81=$G80+$H80,1,0)+IF(Y82=$I$82,3,0)+IF(Y83=$G82+$H82,1,0)+IF(Y84=$I$84,3,0)+IF(Y85=$G84+$H84,1,0)+IF(Y86=$I$86,3,0)+IF(Y87=$G86+$H86,1,0)+IF(Y88=$I$88,3,0)+IF(Y89=$G88+$H88,1,0)+IF(Y90=$I$90,3,0)+IF(Y91=$G90+$H90,1,0)+IF(Y92=$I$92,3,0)+IF(Y93=$G92+$H92,1,0)+IF(Y94=$I$94,3,0)+IF(Y95=$G94+$H94,1,0)+IF(Y96=$I$96,3,0)+IF(Y97=$G96+$H96,1,0)+IF(Y98=$I$98,3,0)+IF(Y99=$G98+$H98,1,0)+IF(Y100=$I$100,3,0)+IF(Y101=$G100+$H100,1,0)+IF(Y102=$I$102,3,0)+IF(Y103=$G102+$H102,1,0)+IF(Y104=$I$104,3,0)+IF(Y105=$G104+$H104,1,0)+IF(Y106=$I$106,3,0)+IF(Y107=$G106+$H106,1,0)+IF(Y108=$I$108,3,0)+IF(Y109=$G108+$H108,1,0)+IF(Y110=$I$110,3,0)+IF(Y111=$G110+$H110,1,0)+IF(Y112=$I$112,3,0)+IF(Y113=$G112+$H112,1,0)+IF(Y114=$I$114,3,0)+IF(Y115=$G114+$H114,1,0)+IF(Y116=$I$116,3,0)+IF(Y117=$G116+$H116,1,0)+IF(Y118=$I$118,3,0)+IF(Y119=$G118+$H118,1,0)+IF(Y120=$I$120,3,0)+IF(Y121=$G120+$H120,1,0)+IF(Y122=$I$122,3,0)+IF(Y123=$G122+$H122,1,0)+IF(Y124=$I$124,3,0)+IF(Y125=$G124+$H124,1,0)+IF(Y126=$I$126,3,0)+IF(Y127=$G126+$H126,1,0)+IF(Y128=$I$128,3,0)+IF(Y129=$G128+$H128,1,0)+IF(Y130=$I$130,3,0)+IF(Y131=$G130+$H130,1,0)+IF(Y132=$I$132,3,0)+IF(Y133=$G132+$H132,1,0)+IF(Y134=$I$134,3,0)+IF(Y135=$G134+$H134,1,0)+IF(Y136=$I$136,3,0)+IF(Y137=$G136+$H136,1,0)+IF(Y138=$I$138,3,0)+IF(Y139=$G138+$H138,1,0)+IF(Y140=$I$140,3,0)+IF(Y141=$G140+$H140,1,0)+IF(Y142=$I$142,3,0)+IF(Y143=$G142+$H142,1,0)+IF(Y144=$I$144,3,0)+IF(Y145=$G144+$H144,1,0)+IF(Y146=$I$146,3,0)+IF(Y147=$G146+$H146,1,0)+IF(Y148=$I$148,3,0)+IF(Y149=$G148+$H148,1,0)+IF(Y150=$I$150,3,0)+IF(Y151=$G150+$H150,1,0))</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z5" s="75">
         <f>SUM(IF(Z80=$I$80,3,0)+IF(Z81=$G80+$H80,1,0)+IF(Z82=$I$82,3,0)+IF(Z83=$G82+$H82,1,0)+IF(Z84=$I$84,3,0)+IF(Z85=$G84+$H84,1,0)+IF(Z86=$I$86,3,0)+IF(Z87=$G86+$H86,1,0)+IF(Z88=$I$88,3,0)+IF(Z89=$G88+$H88,1,0)+IF(Z90=$I$90,3,0)+IF(Z91=$G90+$H90,1,0)+IF(Z92=$I$92,3,0)+IF(Z93=$G92+$H92,1,0)+IF(Z94=$I$94,3,0)+IF(Z95=$G94+$H94,1,0)+IF(Z96=$I$96,3,0)+IF(Z97=$G96+$H96,1,0)+IF(Z98=$I$98,3,0)+IF(Z99=$G98+$H98,1,0)+IF(Z100=$I$100,3,0)+IF(Z101=$G100+$H100,1,0)+IF(Z102=$I$102,3,0)+IF(Z103=$G102+$H102,1,0)+IF(Z104=$I$104,3,0)+IF(Z105=$G104+$H104,1,0)+IF(Z106=$I$106,3,0)+IF(Z107=$G106+$H106,1,0)+IF(Z108=$I$108,3,0)+IF(Z109=$G108+$H108,1,0)+IF(Z110=$I$110,3,0)+IF(Z111=$G110+$H110,1,0)+IF(Z112=$I$112,3,0)+IF(Z113=$G112+$H112,1,0)+IF(Z114=$I$114,3,0)+IF(Z115=$G114+$H114,1,0)+IF(Z116=$I$116,3,0)+IF(Z117=$G116+$H116,1,0)+IF(Z118=$I$118,3,0)+IF(Z119=$G118+$H118,1,0)+IF(Z120=$I$120,3,0)+IF(Z121=$G120+$H120,1,0)+IF(Z122=$I$122,3,0)+IF(Z123=$G122+$H122,1,0)+IF(Z124=$I$124,3,0)+IF(Z125=$G124+$H124,1,0)+IF(Z126=$I$126,3,0)+IF(Z127=$G126+$H126,1,0)+IF(Z128=$I$128,3,0)+IF(Z129=$G128+$H128,1,0)+IF(Z130=$I$130,3,0)+IF(Z131=$G130+$H130,1,0)+IF(Z132=$I$132,3,0)+IF(Z133=$G132+$H132,1,0)+IF(Z134=$I$134,3,0)+IF(Z135=$G134+$H134,1,0)+IF(Z136=$I$136,3,0)+IF(Z137=$G136+$H136,1,0)+IF(Z138=$I$138,3,0)+IF(Z139=$G138+$H138,1,0)+IF(Z140=$I$140,3,0)+IF(Z141=$G140+$H140,1,0)+IF(Z142=$I$142,3,0)+IF(Z143=$G142+$H142,1,0)+IF(Z144=$I$144,3,0)+IF(Z145=$G144+$H144,1,0)+IF(Z146=$I$146,3,0)+IF(Z147=$G146+$H146,1,0)+IF(Z148=$I$148,3,0)+IF(Z149=$G148+$H148,1,0)+IF(Z150=$I$150,3,0)+IF(Z151=$G150+$H150,1,0))</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AA5" s="75">
         <f>SUM(IF(AA80=$I$80,3,0)+IF(AA81=$G80+$H80,1,0)+IF(AA82=$I$82,3,0)+IF(AA83=$G82+$H82,1,0)+IF(AA84=$I$84,3,0)+IF(AA85=$G84+$H84,1,0)+IF(AA86=$I$86,3,0)+IF(AA87=$G86+$H86,1,0)+IF(AA88=$I$88,3,0)+IF(AA89=$G88+$H88,1,0)+IF(AA90=$I$90,3,0)+IF(AA91=$G90+$H90,1,0)+IF(AA92=$I$92,3,0)+IF(AA93=$G92+$H92,1,0)+IF(AA94=$I$94,3,0)+IF(AA95=$G94+$H94,1,0)+IF(AA96=$I$96,3,0)+IF(AA97=$G96+$H96,1,0)+IF(AA98=$I$98,3,0)+IF(AA99=$G98+$H98,1,0)+IF(AA100=$I$100,3,0)+IF(AA101=$G100+$H100,1,0)+IF(AA102=$I$102,3,0)+IF(AA103=$G102+$H102,1,0)+IF(AA104=$I$104,3,0)+IF(AA105=$G104+$H104,1,0)+IF(AA106=$I$106,3,0)+IF(AA107=$G106+$H106,1,0)+IF(AA108=$I$108,3,0)+IF(AA109=$G108+$H108,1,0)+IF(AA110=$I$110,3,0)+IF(AA111=$G110+$H110,1,0)+IF(AA112=$I$112,3,0)+IF(AA113=$G112+$H112,1,0)+IF(AA114=$I$114,3,0)+IF(AA115=$G114+$H114,1,0)+IF(AA116=$I$116,3,0)+IF(AA117=$G116+$H116,1,0)+IF(AA118=$I$118,3,0)+IF(AA119=$G118+$H118,1,0)+IF(AA120=$I$120,3,0)+IF(AA121=$G120+$H120,1,0)+IF(AA122=$I$122,3,0)+IF(AA123=$G122+$H122,1,0)+IF(AA124=$I$124,3,0)+IF(AA125=$G124+$H124,1,0)+IF(AA126=$I$126,3,0)+IF(AA127=$G126+$H126,1,0)+IF(AA128=$I$128,3,0)+IF(AA129=$G128+$H128,1,0)+IF(AA130=$I$130,3,0)+IF(AA131=$G130+$H130,1,0)+IF(AA132=$I$132,3,0)+IF(AA133=$G132+$H132,1,0)+IF(AA134=$I$134,3,0)+IF(AA135=$G134+$H134,1,0)+IF(AA136=$I$136,3,0)+IF(AA137=$G136+$H136,1,0)+IF(AA138=$I$138,3,0)+IF(AA139=$G138+$H138,1,0)+IF(AA140=$I$140,3,0)+IF(AA141=$G140+$H140,1,0)+IF(AA142=$I$142,3,0)+IF(AA143=$G142+$H142,1,0)+IF(AA144=$I$144,3,0)+IF(AA145=$G144+$H144,1,0)+IF(AA146=$I$146,3,0)+IF(AA147=$G146+$H146,1,0)+IF(AA148=$I$148,3,0)+IF(AA149=$G148+$H148,1,0)+IF(AA150=$I$150,3,0)+IF(AA151=$G150+$H150,1,0))</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB5" s="75">
         <f>SUM(IF(AB80=$I$80,3,0)+IF(AB81=$G80+$H80,1,0)+IF(AB82=$I$82,3,0)+IF(AB83=$G82+$H82,1,0)+IF(AB84=$I$84,3,0)+IF(AB85=$G84+$H84,1,0)+IF(AB86=$I$86,3,0)+IF(AB87=$G86+$H86,1,0)+IF(AB88=$I$88,3,0)+IF(AB89=$G88+$H88,1,0)+IF(AB90=$I$90,3,0)+IF(AB91=$G90+$H90,1,0)+IF(AB92=$I$92,3,0)+IF(AB93=$G92+$H92,1,0)+IF(AB94=$I$94,3,0)+IF(AB95=$G94+$H94,1,0)+IF(AB96=$I$96,3,0)+IF(AB97=$G96+$H96,1,0)+IF(AB98=$I$98,3,0)+IF(AB99=$G98+$H98,1,0)+IF(AB100=$I$100,3,0)+IF(AB101=$G100+$H100,1,0)+IF(AB102=$I$102,3,0)+IF(AB103=$G102+$H102,1,0)+IF(AB104=$I$104,3,0)+IF(AB105=$G104+$H104,1,0)+IF(AB106=$I$106,3,0)+IF(AB107=$G106+$H106,1,0)+IF(AB108=$I$108,3,0)+IF(AB109=$G108+$H108,1,0)+IF(AB110=$I$110,3,0)+IF(AB111=$G110+$H110,1,0)+IF(AB112=$I$112,3,0)+IF(AB113=$G112+$H112,1,0)+IF(AB114=$I$114,3,0)+IF(AB115=$G114+$H114,1,0)+IF(AB116=$I$116,3,0)+IF(AB117=$G116+$H116,1,0)+IF(AB118=$I$118,3,0)+IF(AB119=$G118+$H118,1,0)+IF(AB120=$I$120,3,0)+IF(AB121=$G120+$H120,1,0)+IF(AB122=$I$122,3,0)+IF(AB123=$G122+$H122,1,0)+IF(AB124=$I$124,3,0)+IF(AB125=$G124+$H124,1,0)+IF(AB126=$I$126,3,0)+IF(AB127=$G126+$H126,1,0)+IF(AB128=$I$128,3,0)+IF(AB129=$G128+$H128,1,0)+IF(AB130=$I$130,3,0)+IF(AB131=$G130+$H130,1,0)+IF(AB132=$I$132,3,0)+IF(AB133=$G132+$H132,1,0)+IF(AB134=$I$134,3,0)+IF(AB135=$G134+$H134,1,0)+IF(AB136=$I$136,3,0)+IF(AB137=$G136+$H136,1,0)+IF(AB138=$I$138,3,0)+IF(AB139=$G138+$H138,1,0)+IF(AB140=$I$140,3,0)+IF(AB141=$G140+$H140,1,0)+IF(AB142=$I$142,3,0)+IF(AB143=$G142+$H142,1,0)+IF(AB144=$I$144,3,0)+IF(AB145=$G144+$H144,1,0)+IF(AB146=$I$146,3,0)+IF(AB147=$G146+$H146,1,0)+IF(AB148=$I$148,3,0)+IF(AB149=$G148+$H148,1,0)+IF(AB150=$I$150,3,0)+IF(AB151=$G150+$H150,1,0))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC5" s="75">
         <f>SUM(IF(AC80=$I$80,3,0)+IF(AC81=$G80+$H80,1,0)+IF(AC82=$I$82,3,0)+IF(AC83=$G82+$H82,1,0)+IF(AC84=$I$84,3,0)+IF(AC85=$G84+$H84,1,0)+IF(AC86=$I$86,3,0)+IF(AC87=$G86+$H86,1,0)+IF(AC88=$I$88,3,0)+IF(AC89=$G88+$H88,1,0)+IF(AC90=$I$90,3,0)+IF(AC91=$G90+$H90,1,0)+IF(AC92=$I$92,3,0)+IF(AC93=$G92+$H92,1,0)+IF(AC94=$I$94,3,0)+IF(AC95=$G94+$H94,1,0)+IF(AC96=$I$96,3,0)+IF(AC97=$G96+$H96,1,0)+IF(AC98=$I$98,3,0)+IF(AC99=$G98+$H98,1,0)+IF(AC100=$I$100,3,0)+IF(AC101=$G100+$H100,1,0)+IF(AC102=$I$102,3,0)+IF(AC103=$G102+$H102,1,0)+IF(AC104=$I$104,3,0)+IF(AC105=$G104+$H104,1,0)+IF(AC106=$I$106,3,0)+IF(AC107=$G106+$H106,1,0)+IF(AC108=$I$108,3,0)+IF(AC109=$G108+$H108,1,0)+IF(AC110=$I$110,3,0)+IF(AC111=$G110+$H110,1,0)+IF(AC112=$I$112,3,0)+IF(AC113=$G112+$H112,1,0)+IF(AC114=$I$114,3,0)+IF(AC115=$G114+$H114,1,0)+IF(AC116=$I$116,3,0)+IF(AC117=$G116+$H116,1,0)+IF(AC118=$I$118,3,0)+IF(AC119=$G118+$H118,1,0)+IF(AC120=$I$120,3,0)+IF(AC121=$G120+$H120,1,0)+IF(AC122=$I$122,3,0)+IF(AC123=$G122+$H122,1,0)+IF(AC124=$I$124,3,0)+IF(AC125=$G124+$H124,1,0)+IF(AC126=$I$126,3,0)+IF(AC127=$G126+$H126,1,0)+IF(AC128=$I$128,3,0)+IF(AC129=$G128+$H128,1,0)+IF(AC130=$I$130,3,0)+IF(AC131=$G130+$H130,1,0)+IF(AC132=$I$132,3,0)+IF(AC133=$G132+$H132,1,0)+IF(AC134=$I$134,3,0)+IF(AC135=$G134+$H134,1,0)+IF(AC136=$I$136,3,0)+IF(AC137=$G136+$H136,1,0)+IF(AC138=$I$138,3,0)+IF(AC139=$G138+$H138,1,0)+IF(AC140=$I$140,3,0)+IF(AC141=$G140+$H140,1,0)+IF(AC142=$I$142,3,0)+IF(AC143=$G142+$H142,1,0)+IF(AC144=$I$144,3,0)+IF(AC145=$G144+$H144,1,0)+IF(AC146=$I$146,3,0)+IF(AC147=$G146+$H146,1,0)+IF(AC148=$I$148,3,0)+IF(AC149=$G148+$H148,1,0)+IF(AC150=$I$150,3,0)+IF(AC151=$G150+$H150,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD5" s="75">
         <f>SUM(IF(AD80=$I$80,3,0)+IF(AD81=$G80+$H80,1,0)+IF(AD82=$I$82,3,0)+IF(AD83=$G82+$H82,1,0)+IF(AD84=$I$84,3,0)+IF(AD85=$G84+$H84,1,0)+IF(AD86=$I$86,3,0)+IF(AD87=$G86+$H86,1,0)+IF(AD88=$I$88,3,0)+IF(AD89=$G88+$H88,1,0)+IF(AD90=$I$90,3,0)+IF(AD91=$G90+$H90,1,0)+IF(AD92=$I$92,3,0)+IF(AD93=$G92+$H92,1,0)+IF(AD94=$I$94,3,0)+IF(AD95=$G94+$H94,1,0)+IF(AD96=$I$96,3,0)+IF(AD97=$G96+$H96,1,0)+IF(AD98=$I$98,3,0)+IF(AD99=$G98+$H98,1,0)+IF(AD100=$I$100,3,0)+IF(AD101=$G100+$H100,1,0)+IF(AD102=$I$102,3,0)+IF(AD103=$G102+$H102,1,0)+IF(AD104=$I$104,3,0)+IF(AD105=$G104+$H104,1,0)+IF(AD106=$I$106,3,0)+IF(AD107=$G106+$H106,1,0)+IF(AD108=$I$108,3,0)+IF(AD109=$G108+$H108,1,0)+IF(AD110=$I$110,3,0)+IF(AD111=$G110+$H110,1,0)+IF(AD112=$I$112,3,0)+IF(AD113=$G112+$H112,1,0)+IF(AD114=$I$114,3,0)+IF(AD115=$G114+$H114,1,0)+IF(AD116=$I$116,3,0)+IF(AD117=$G116+$H116,1,0)+IF(AD118=$I$118,3,0)+IF(AD119=$G118+$H118,1,0)+IF(AD120=$I$120,3,0)+IF(AD121=$G120+$H120,1,0)+IF(AD122=$I$122,3,0)+IF(AD123=$G122+$H122,1,0)+IF(AD124=$I$124,3,0)+IF(AD125=$G124+$H124,1,0)+IF(AD126=$I$126,3,0)+IF(AD127=$G126+$H126,1,0)+IF(AD128=$I$128,3,0)+IF(AD129=$G128+$H128,1,0)+IF(AD130=$I$130,3,0)+IF(AD131=$G130+$H130,1,0)+IF(AD132=$I$132,3,0)+IF(AD133=$G132+$H132,1,0)+IF(AD134=$I$134,3,0)+IF(AD135=$G134+$H134,1,0)+IF(AD136=$I$136,3,0)+IF(AD137=$G136+$H136,1,0)+IF(AD138=$I$138,3,0)+IF(AD139=$G138+$H138,1,0)+IF(AD140=$I$140,3,0)+IF(AD141=$G140+$H140,1,0)+IF(AD142=$I$142,3,0)+IF(AD143=$G142+$H142,1,0)+IF(AD144=$I$144,3,0)+IF(AD145=$G144+$H144,1,0)+IF(AD146=$I$146,3,0)+IF(AD147=$G146+$H146,1,0)+IF(AD148=$I$148,3,0)+IF(AD149=$G148+$H148,1,0)+IF(AD150=$I$150,3,0)+IF(AD151=$G150+$H150,1,0))</f>
@@ -3238,70 +3238,70 @@
       </c>
       <c r="AE5" s="75">
         <f>SUM(IF(AE80=$I$80,3,0)+IF(AE81=$G80+$H80,1,0)+IF(AE82=$I$82,3,0)+IF(AE83=$G82+$H82,1,0)+IF(AE84=$I$84,3,0)+IF(AE85=$G84+$H84,1,0)+IF(AE86=$I$86,3,0)+IF(AE87=$G86+$H86,1,0)+IF(AE88=$I$88,3,0)+IF(AE89=$G88+$H88,1,0)+IF(AE90=$I$90,3,0)+IF(AE91=$G90+$H90,1,0)+IF(AE92=$I$92,3,0)+IF(AE93=$G92+$H92,1,0)+IF(AE94=$I$94,3,0)+IF(AE95=$G94+$H94,1,0)+IF(AE96=$I$96,3,0)+IF(AE97=$G96+$H96,1,0)+IF(AE98=$I$98,3,0)+IF(AE99=$G98+$H98,1,0)+IF(AE100=$I$100,3,0)+IF(AE101=$G100+$H100,1,0)+IF(AE102=$I$102,3,0)+IF(AE103=$G102+$H102,1,0)+IF(AE104=$I$104,3,0)+IF(AE105=$G104+$H104,1,0)+IF(AE106=$I$106,3,0)+IF(AE107=$G106+$H106,1,0)+IF(AE108=$I$108,3,0)+IF(AE109=$G108+$H108,1,0)+IF(AE110=$I$110,3,0)+IF(AE111=$G110+$H110,1,0)+IF(AE112=$I$112,3,0)+IF(AE113=$G112+$H112,1,0)+IF(AE114=$I$114,3,0)+IF(AE115=$G114+$H114,1,0)+IF(AE116=$I$116,3,0)+IF(AE117=$G116+$H116,1,0)+IF(AE118=$I$118,3,0)+IF(AE119=$G118+$H118,1,0)+IF(AE120=$I$120,3,0)+IF(AE121=$G120+$H120,1,0)+IF(AE122=$I$122,3,0)+IF(AE123=$G122+$H122,1,0)+IF(AE124=$I$124,3,0)+IF(AE125=$G124+$H124,1,0)+IF(AE126=$I$126,3,0)+IF(AE127=$G126+$H126,1,0)+IF(AE128=$I$128,3,0)+IF(AE129=$G128+$H128,1,0)+IF(AE130=$I$130,3,0)+IF(AE131=$G130+$H130,1,0)+IF(AE132=$I$132,3,0)+IF(AE133=$G132+$H132,1,0)+IF(AE134=$I$134,3,0)+IF(AE135=$G134+$H134,1,0)+IF(AE136=$I$136,3,0)+IF(AE137=$G136+$H136,1,0)+IF(AE138=$I$138,3,0)+IF(AE139=$G138+$H138,1,0)+IF(AE140=$I$140,3,0)+IF(AE141=$G140+$H140,1,0)+IF(AE142=$I$142,3,0)+IF(AE143=$G142+$H142,1,0)+IF(AE144=$I$144,3,0)+IF(AE145=$G144+$H144,1,0)+IF(AE146=$I$146,3,0)+IF(AE147=$G146+$H146,1,0)+IF(AE148=$I$148,3,0)+IF(AE149=$G148+$H148,1,0)+IF(AE150=$I$150,3,0)+IF(AE151=$G150+$H150,1,0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF5" s="75">
         <f>SUM(IF(AF80=$I$80,3,0)+IF(AF81=$G80+$H80,1,0)+IF(AF82=$I$82,3,0)+IF(AF83=$G82+$H82,1,0)+IF(AF84=$I$84,3,0)+IF(AF85=$G84+$H84,1,0)+IF(AF86=$I$86,3,0)+IF(AF87=$G86+$H86,1,0)+IF(AF88=$I$88,3,0)+IF(AF89=$G88+$H88,1,0)+IF(AF90=$I$90,3,0)+IF(AF91=$G90+$H90,1,0)+IF(AF92=$I$92,3,0)+IF(AF93=$G92+$H92,1,0)+IF(AF94=$I$94,3,0)+IF(AF95=$G94+$H94,1,0)+IF(AF96=$I$96,3,0)+IF(AF97=$G96+$H96,1,0)+IF(AF98=$I$98,3,0)+IF(AF99=$G98+$H98,1,0)+IF(AF100=$I$100,3,0)+IF(AF101=$G100+$H100,1,0)+IF(AF102=$I$102,3,0)+IF(AF103=$G102+$H102,1,0)+IF(AF104=$I$104,3,0)+IF(AF105=$G104+$H104,1,0)+IF(AF106=$I$106,3,0)+IF(AF107=$G106+$H106,1,0)+IF(AF108=$I$108,3,0)+IF(AF109=$G108+$H108,1,0)+IF(AF110=$I$110,3,0)+IF(AF111=$G110+$H110,1,0)+IF(AF112=$I$112,3,0)+IF(AF113=$G112+$H112,1,0)+IF(AF114=$I$114,3,0)+IF(AF115=$G114+$H114,1,0)+IF(AF116=$I$116,3,0)+IF(AF117=$G116+$H116,1,0)+IF(AF118=$I$118,3,0)+IF(AF119=$G118+$H118,1,0)+IF(AF120=$I$120,3,0)+IF(AF121=$G120+$H120,1,0)+IF(AF122=$I$122,3,0)+IF(AF123=$G122+$H122,1,0)+IF(AF124=$I$124,3,0)+IF(AF125=$G124+$H124,1,0)+IF(AF126=$I$126,3,0)+IF(AF127=$G126+$H126,1,0)+IF(AF128=$I$128,3,0)+IF(AF129=$G128+$H128,1,0)+IF(AF130=$I$130,3,0)+IF(AF131=$G130+$H130,1,0)+IF(AF132=$I$132,3,0)+IF(AF133=$G132+$H132,1,0)+IF(AF134=$I$134,3,0)+IF(AF135=$G134+$H134,1,0)+IF(AF136=$I$136,3,0)+IF(AF137=$G136+$H136,1,0)+IF(AF138=$I$138,3,0)+IF(AF139=$G138+$H138,1,0)+IF(AF140=$I$140,3,0)+IF(AF141=$G140+$H140,1,0)+IF(AF142=$I$142,3,0)+IF(AF143=$G142+$H142,1,0)+IF(AF144=$I$144,3,0)+IF(AF145=$G144+$H144,1,0)+IF(AF146=$I$146,3,0)+IF(AF147=$G146+$H146,1,0)+IF(AF148=$I$148,3,0)+IF(AF149=$G148+$H148,1,0)+IF(AF150=$I$150,3,0)+IF(AF151=$G150+$H150,1,0))</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG5" s="75">
         <f>SUM(IF(AG80=$I$80,3,0)+IF(AG81=$G80+$H80,1,0)+IF(AG82=$I$82,3,0)+IF(AG83=$G82+$H82,1,0)+IF(AG84=$I$84,3,0)+IF(AG85=$G84+$H84,1,0)+IF(AG86=$I$86,3,0)+IF(AG87=$G86+$H86,1,0)+IF(AG88=$I$88,3,0)+IF(AG89=$G88+$H88,1,0)+IF(AG90=$I$90,3,0)+IF(AG91=$G90+$H90,1,0)+IF(AG92=$I$92,3,0)+IF(AG93=$G92+$H92,1,0)+IF(AG94=$I$94,3,0)+IF(AG95=$G94+$H94,1,0)+IF(AG96=$I$96,3,0)+IF(AG97=$G96+$H96,1,0)+IF(AG98=$I$98,3,0)+IF(AG99=$G98+$H98,1,0)+IF(AG100=$I$100,3,0)+IF(AG101=$G100+$H100,1,0)+IF(AG102=$I$102,3,0)+IF(AG103=$G102+$H102,1,0)+IF(AG104=$I$104,3,0)+IF(AG105=$G104+$H104,1,0)+IF(AG106=$I$106,3,0)+IF(AG107=$G106+$H106,1,0)+IF(AG108=$I$108,3,0)+IF(AG109=$G108+$H108,1,0)+IF(AG110=$I$110,3,0)+IF(AG111=$G110+$H110,1,0)+IF(AG112=$I$112,3,0)+IF(AG113=$G112+$H112,1,0)+IF(AG114=$I$114,3,0)+IF(AG115=$G114+$H114,1,0)+IF(AG116=$I$116,3,0)+IF(AG117=$G116+$H116,1,0)+IF(AG118=$I$118,3,0)+IF(AG119=$G118+$H118,1,0)+IF(AG120=$I$120,3,0)+IF(AG121=$G120+$H120,1,0)+IF(AG122=$I$122,3,0)+IF(AG123=$G122+$H122,1,0)+IF(AG124=$I$124,3,0)+IF(AG125=$G124+$H124,1,0)+IF(AG126=$I$126,3,0)+IF(AG127=$G126+$H126,1,0)+IF(AG128=$I$128,3,0)+IF(AG129=$G128+$H128,1,0)+IF(AG130=$I$130,3,0)+IF(AG131=$G130+$H130,1,0)+IF(AG132=$I$132,3,0)+IF(AG133=$G132+$H132,1,0)+IF(AG134=$I$134,3,0)+IF(AG135=$G134+$H134,1,0)+IF(AG136=$I$136,3,0)+IF(AG137=$G136+$H136,1,0)+IF(AG138=$I$138,3,0)+IF(AG139=$G138+$H138,1,0)+IF(AG140=$I$140,3,0)+IF(AG141=$G140+$H140,1,0)+IF(AG142=$I$142,3,0)+IF(AG143=$G142+$H142,1,0)+IF(AG144=$I$144,3,0)+IF(AG145=$G144+$H144,1,0)+IF(AG146=$I$146,3,0)+IF(AG147=$G146+$H146,1,0)+IF(AG148=$I$148,3,0)+IF(AG149=$G148+$H148,1,0)+IF(AG150=$I$150,3,0)+IF(AG151=$G150+$H150,1,0))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH5" s="75">
         <f>SUM(IF(AH80=$I$80,3,0)+IF(AH81=$G80+$H80,1,0)+IF(AH82=$I$82,3,0)+IF(AH83=$G82+$H82,1,0)+IF(AH84=$I$84,3,0)+IF(AH85=$G84+$H84,1,0)+IF(AH86=$I$86,3,0)+IF(AH87=$G86+$H86,1,0)+IF(AH88=$I$88,3,0)+IF(AH89=$G88+$H88,1,0)+IF(AH90=$I$90,3,0)+IF(AH91=$G90+$H90,1,0)+IF(AH92=$I$92,3,0)+IF(AH93=$G92+$H92,1,0)+IF(AH94=$I$94,3,0)+IF(AH95=$G94+$H94,1,0)+IF(AH96=$I$96,3,0)+IF(AH97=$G96+$H96,1,0)+IF(AH98=$I$98,3,0)+IF(AH99=$G98+$H98,1,0)+IF(AH100=$I$100,3,0)+IF(AH101=$G100+$H100,1,0)+IF(AH102=$I$102,3,0)+IF(AH103=$G102+$H102,1,0)+IF(AH104=$I$104,3,0)+IF(AH105=$G104+$H104,1,0)+IF(AH106=$I$106,3,0)+IF(AH107=$G106+$H106,1,0)+IF(AH108=$I$108,3,0)+IF(AH109=$G108+$H108,1,0)+IF(AH110=$I$110,3,0)+IF(AH111=$G110+$H110,1,0)+IF(AH112=$I$112,3,0)+IF(AH113=$G112+$H112,1,0)+IF(AH114=$I$114,3,0)+IF(AH115=$G114+$H114,1,0)+IF(AH116=$I$116,3,0)+IF(AH117=$G116+$H116,1,0)+IF(AH118=$I$118,3,0)+IF(AH119=$G118+$H118,1,0)+IF(AH120=$I$120,3,0)+IF(AH121=$G120+$H120,1,0)+IF(AH122=$I$122,3,0)+IF(AH123=$G122+$H122,1,0)+IF(AH124=$I$124,3,0)+IF(AH125=$G124+$H124,1,0)+IF(AH126=$I$126,3,0)+IF(AH127=$G126+$H126,1,0)+IF(AH128=$I$128,3,0)+IF(AH129=$G128+$H128,1,0)+IF(AH130=$I$130,3,0)+IF(AH131=$G130+$H130,1,0)+IF(AH132=$I$132,3,0)+IF(AH133=$G132+$H132,1,0)+IF(AH134=$I$134,3,0)+IF(AH135=$G134+$H134,1,0)+IF(AH136=$I$136,3,0)+IF(AH137=$G136+$H136,1,0)+IF(AH138=$I$138,3,0)+IF(AH139=$G138+$H138,1,0)+IF(AH140=$I$140,3,0)+IF(AH141=$G140+$H140,1,0)+IF(AH142=$I$142,3,0)+IF(AH143=$G142+$H142,1,0)+IF(AH144=$I$144,3,0)+IF(AH145=$G144+$H144,1,0)+IF(AH146=$I$146,3,0)+IF(AH147=$G146+$H146,1,0)+IF(AH148=$I$148,3,0)+IF(AH149=$G148+$H148,1,0)+IF(AH150=$I$150,3,0)+IF(AH151=$G150+$H150,1,0))</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AI5" s="75">
         <f>SUM(IF(AI80=$I$80,3,0)+IF(AI81=$G80+$H80,1,0)+IF(AI82=$I$82,3,0)+IF(AI83=$G82+$H82,1,0)+IF(AI84=$I$84,3,0)+IF(AI85=$G84+$H84,1,0)+IF(AI86=$I$86,3,0)+IF(AI87=$G86+$H86,1,0)+IF(AI88=$I$88,3,0)+IF(AI89=$G88+$H88,1,0)+IF(AI90=$I$90,3,0)+IF(AI91=$G90+$H90,1,0)+IF(AI92=$I$92,3,0)+IF(AI93=$G92+$H92,1,0)+IF(AI94=$I$94,3,0)+IF(AI95=$G94+$H94,1,0)+IF(AI96=$I$96,3,0)+IF(AI97=$G96+$H96,1,0)+IF(AI98=$I$98,3,0)+IF(AI99=$G98+$H98,1,0)+IF(AI100=$I$100,3,0)+IF(AI101=$G100+$H100,1,0)+IF(AI102=$I$102,3,0)+IF(AI103=$G102+$H102,1,0)+IF(AI104=$I$104,3,0)+IF(AI105=$G104+$H104,1,0)+IF(AI106=$I$106,3,0)+IF(AI107=$G106+$H106,1,0)+IF(AI108=$I$108,3,0)+IF(AI109=$G108+$H108,1,0)+IF(AI110=$I$110,3,0)+IF(AI111=$G110+$H110,1,0)+IF(AI112=$I$112,3,0)+IF(AI113=$G112+$H112,1,0)+IF(AI114=$I$114,3,0)+IF(AI115=$G114+$H114,1,0)+IF(AI116=$I$116,3,0)+IF(AI117=$G116+$H116,1,0)+IF(AI118=$I$118,3,0)+IF(AI119=$G118+$H118,1,0)+IF(AI120=$I$120,3,0)+IF(AI121=$G120+$H120,1,0)+IF(AI122=$I$122,3,0)+IF(AI123=$G122+$H122,1,0)+IF(AI124=$I$124,3,0)+IF(AI125=$G124+$H124,1,0)+IF(AI126=$I$126,3,0)+IF(AI127=$G126+$H126,1,0)+IF(AI128=$I$128,3,0)+IF(AI129=$G128+$H128,1,0)+IF(AI130=$I$130,3,0)+IF(AI131=$G130+$H130,1,0)+IF(AI132=$I$132,3,0)+IF(AI133=$G132+$H132,1,0)+IF(AI134=$I$134,3,0)+IF(AI135=$G134+$H134,1,0)+IF(AI136=$I$136,3,0)+IF(AI137=$G136+$H136,1,0)+IF(AI138=$I$138,3,0)+IF(AI139=$G138+$H138,1,0)+IF(AI140=$I$140,3,0)+IF(AI141=$G140+$H140,1,0)+IF(AI142=$I$142,3,0)+IF(AI143=$G142+$H142,1,0)+IF(AI144=$I$144,3,0)+IF(AI145=$G144+$H144,1,0)+IF(AI146=$I$146,3,0)+IF(AI147=$G146+$H146,1,0)+IF(AI148=$I$148,3,0)+IF(AI149=$G148+$H148,1,0)+IF(AI150=$I$150,3,0)+IF(AI151=$G150+$H150,1,0))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ5" s="75">
         <f>SUM(IF(AJ80=$I$80,3,0)+IF(AJ81=$G80+$H80,1,0)+IF(AJ82=$I$82,3,0)+IF(AJ83=$G82+$H82,1,0)+IF(AJ84=$I$84,3,0)+IF(AJ85=$G84+$H84,1,0)+IF(AJ86=$I$86,3,0)+IF(AJ87=$G86+$H86,1,0)+IF(AJ88=$I$88,3,0)+IF(AJ89=$G88+$H88,1,0)+IF(AJ90=$I$90,3,0)+IF(AJ91=$G90+$H90,1,0)+IF(AJ92=$I$92,3,0)+IF(AJ93=$G92+$H92,1,0)+IF(AJ94=$I$94,3,0)+IF(AJ95=$G94+$H94,1,0)+IF(AJ96=$I$96,3,0)+IF(AJ97=$G96+$H96,1,0)+IF(AJ98=$I$98,3,0)+IF(AJ99=$G98+$H98,1,0)+IF(AJ100=$I$100,3,0)+IF(AJ101=$G100+$H100,1,0)+IF(AJ102=$I$102,3,0)+IF(AJ103=$G102+$H102,1,0)+IF(AJ104=$I$104,3,0)+IF(AJ105=$G104+$H104,1,0)+IF(AJ106=$I$106,3,0)+IF(AJ107=$G106+$H106,1,0)+IF(AJ108=$I$108,3,0)+IF(AJ109=$G108+$H108,1,0)+IF(AJ110=$I$110,3,0)+IF(AJ111=$G110+$H110,1,0)+IF(AJ112=$I$112,3,0)+IF(AJ113=$G112+$H112,1,0)+IF(AJ114=$I$114,3,0)+IF(AJ115=$G114+$H114,1,0)+IF(AJ116=$I$116,3,0)+IF(AJ117=$G116+$H116,1,0)+IF(AJ118=$I$118,3,0)+IF(AJ119=$G118+$H118,1,0)+IF(AJ120=$I$120,3,0)+IF(AJ121=$G120+$H120,1,0)+IF(AJ122=$I$122,3,0)+IF(AJ123=$G122+$H122,1,0)+IF(AJ124=$I$124,3,0)+IF(AJ125=$G124+$H124,1,0)+IF(AJ126=$I$126,3,0)+IF(AJ127=$G126+$H126,1,0)+IF(AJ128=$I$128,3,0)+IF(AJ129=$G128+$H128,1,0)+IF(AJ130=$I$130,3,0)+IF(AJ131=$G130+$H130,1,0)+IF(AJ132=$I$132,3,0)+IF(AJ133=$G132+$H132,1,0)+IF(AJ134=$I$134,3,0)+IF(AJ135=$G134+$H134,1,0)+IF(AJ136=$I$136,3,0)+IF(AJ137=$G136+$H136,1,0)+IF(AJ138=$I$138,3,0)+IF(AJ139=$G138+$H138,1,0)+IF(AJ140=$I$140,3,0)+IF(AJ141=$G140+$H140,1,0)+IF(AJ142=$I$142,3,0)+IF(AJ143=$G142+$H142,1,0)+IF(AJ144=$I$144,3,0)+IF(AJ145=$G144+$H144,1,0)+IF(AJ146=$I$146,3,0)+IF(AJ147=$G146+$H146,1,0)+IF(AJ148=$I$148,3,0)+IF(AJ149=$G148+$H148,1,0)+IF(AJ150=$I$150,3,0)+IF(AJ151=$G150+$H150,1,0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK5" s="75">
         <f>SUM(IF(AK80=$I$80,3,0)+IF(AK81=$G80+$H80,1,0)+IF(AK82=$I$82,3,0)+IF(AK83=$G82+$H82,1,0)+IF(AK84=$I$84,3,0)+IF(AK85=$G84+$H84,1,0)+IF(AK86=$I$86,3,0)+IF(AK87=$G86+$H86,1,0)+IF(AK88=$I$88,3,0)+IF(AK89=$G88+$H88,1,0)+IF(AK90=$I$90,3,0)+IF(AK91=$G90+$H90,1,0)+IF(AK92=$I$92,3,0)+IF(AK93=$G92+$H92,1,0)+IF(AK94=$I$94,3,0)+IF(AK95=$G94+$H94,1,0)+IF(AK96=$I$96,3,0)+IF(AK97=$G96+$H96,1,0)+IF(AK98=$I$98,3,0)+IF(AK99=$G98+$H98,1,0)+IF(AK100=$I$100,3,0)+IF(AK101=$G100+$H100,1,0)+IF(AK102=$I$102,3,0)+IF(AK103=$G102+$H102,1,0)+IF(AK104=$I$104,3,0)+IF(AK105=$G104+$H104,1,0)+IF(AK106=$I$106,3,0)+IF(AK107=$G106+$H106,1,0)+IF(AK108=$I$108,3,0)+IF(AK109=$G108+$H108,1,0)+IF(AK110=$I$110,3,0)+IF(AK111=$G110+$H110,1,0)+IF(AK112=$I$112,3,0)+IF(AK113=$G112+$H112,1,0)+IF(AK114=$I$114,3,0)+IF(AK115=$G114+$H114,1,0)+IF(AK116=$I$116,3,0)+IF(AK117=$G116+$H116,1,0)+IF(AK118=$I$118,3,0)+IF(AK119=$G118+$H118,1,0)+IF(AK120=$I$120,3,0)+IF(AK121=$G120+$H120,1,0)+IF(AK122=$I$122,3,0)+IF(AK123=$G122+$H122,1,0)+IF(AK124=$I$124,3,0)+IF(AK125=$G124+$H124,1,0)+IF(AK126=$I$126,3,0)+IF(AK127=$G126+$H126,1,0)+IF(AK128=$I$128,3,0)+IF(AK129=$G128+$H128,1,0)+IF(AK130=$I$130,3,0)+IF(AK131=$G130+$H130,1,0)+IF(AK132=$I$132,3,0)+IF(AK133=$G132+$H132,1,0)+IF(AK134=$I$134,3,0)+IF(AK135=$G134+$H134,1,0)+IF(AK136=$I$136,3,0)+IF(AK137=$G136+$H136,1,0)+IF(AK138=$I$138,3,0)+IF(AK139=$G138+$H138,1,0)+IF(AK140=$I$140,3,0)+IF(AK141=$G140+$H140,1,0)+IF(AK142=$I$142,3,0)+IF(AK143=$G142+$H142,1,0)+IF(AK144=$I$144,3,0)+IF(AK145=$G144+$H144,1,0)+IF(AK146=$I$146,3,0)+IF(AK147=$G146+$H146,1,0)+IF(AK148=$I$148,3,0)+IF(AK149=$G148+$H148,1,0)+IF(AK150=$I$150,3,0)+IF(AK151=$G150+$H150,1,0))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL5" s="75">
         <f>SUM(IF(AL80=$I$80,3,0)+IF(AL81=$G80+$H80,1,0)+IF(AL82=$I$82,3,0)+IF(AL83=$G82+$H82,1,0)+IF(AL84=$I$84,3,0)+IF(AL85=$G84+$H84,1,0)+IF(AL86=$I$86,3,0)+IF(AL87=$G86+$H86,1,0)+IF(AL88=$I$88,3,0)+IF(AL89=$G88+$H88,1,0)+IF(AL90=$I$90,3,0)+IF(AL91=$G90+$H90,1,0)+IF(AL92=$I$92,3,0)+IF(AL93=$G92+$H92,1,0)+IF(AL94=$I$94,3,0)+IF(AL95=$G94+$H94,1,0)+IF(AL96=$I$96,3,0)+IF(AL97=$G96+$H96,1,0)+IF(AL98=$I$98,3,0)+IF(AL99=$G98+$H98,1,0)+IF(AL100=$I$100,3,0)+IF(AL101=$G100+$H100,1,0)+IF(AL102=$I$102,3,0)+IF(AL103=$G102+$H102,1,0)+IF(AL104=$I$104,3,0)+IF(AL105=$G104+$H104,1,0)+IF(AL106=$I$106,3,0)+IF(AL107=$G106+$H106,1,0)+IF(AL108=$I$108,3,0)+IF(AL109=$G108+$H108,1,0)+IF(AL110=$I$110,3,0)+IF(AL111=$G110+$H110,1,0)+IF(AL112=$I$112,3,0)+IF(AL113=$G112+$H112,1,0)+IF(AL114=$I$114,3,0)+IF(AL115=$G114+$H114,1,0)+IF(AL116=$I$116,3,0)+IF(AL117=$G116+$H116,1,0)+IF(AL118=$I$118,3,0)+IF(AL119=$G118+$H118,1,0)+IF(AL120=$I$120,3,0)+IF(AL121=$G120+$H120,1,0)+IF(AL122=$I$122,3,0)+IF(AL123=$G122+$H122,1,0)+IF(AL124=$I$124,3,0)+IF(AL125=$G124+$H124,1,0)+IF(AL126=$I$126,3,0)+IF(AL127=$G126+$H126,1,0)+IF(AL128=$I$128,3,0)+IF(AL129=$G128+$H128,1,0)+IF(AL130=$I$130,3,0)+IF(AL131=$G130+$H130,1,0)+IF(AL132=$I$132,3,0)+IF(AL133=$G132+$H132,1,0)+IF(AL134=$I$134,3,0)+IF(AL135=$G134+$H134,1,0)+IF(AL136=$I$136,3,0)+IF(AL137=$G136+$H136,1,0)+IF(AL138=$I$138,3,0)+IF(AL139=$G138+$H138,1,0)+IF(AL140=$I$140,3,0)+IF(AL141=$G140+$H140,1,0)+IF(AL142=$I$142,3,0)+IF(AL143=$G142+$H142,1,0)+IF(AL144=$I$144,3,0)+IF(AL145=$G144+$H144,1,0)+IF(AL146=$I$146,3,0)+IF(AL147=$G146+$H146,1,0)+IF(AL148=$I$148,3,0)+IF(AL149=$G148+$H148,1,0)+IF(AL150=$I$150,3,0)+IF(AL151=$G150+$H150,1,0))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AM5" s="75">
         <f>SUM(IF(AM80=$I$80,3,0)+IF(AM81=$G80+$H80,1,0)+IF(AM82=$I$82,3,0)+IF(AM83=$G82+$H82,1,0)+IF(AM84=$I$84,3,0)+IF(AM85=$G84+$H84,1,0)+IF(AM86=$I$86,3,0)+IF(AM87=$G86+$H86,1,0)+IF(AM88=$I$88,3,0)+IF(AM89=$G88+$H88,1,0)+IF(AM90=$I$90,3,0)+IF(AM91=$G90+$H90,1,0)+IF(AM92=$I$92,3,0)+IF(AM93=$G92+$H92,1,0)+IF(AM94=$I$94,3,0)+IF(AM95=$G94+$H94,1,0)+IF(AM96=$I$96,3,0)+IF(AM97=$G96+$H96,1,0)+IF(AM98=$I$98,3,0)+IF(AM99=$G98+$H98,1,0)+IF(AM100=$I$100,3,0)+IF(AM101=$G100+$H100,1,0)+IF(AM102=$I$102,3,0)+IF(AM103=$G102+$H102,1,0)+IF(AM104=$I$104,3,0)+IF(AM105=$G104+$H104,1,0)+IF(AM106=$I$106,3,0)+IF(AM107=$G106+$H106,1,0)+IF(AM108=$I$108,3,0)+IF(AM109=$G108+$H108,1,0)+IF(AM110=$I$110,3,0)+IF(AM111=$G110+$H110,1,0)+IF(AM112=$I$112,3,0)+IF(AM113=$G112+$H112,1,0)+IF(AM114=$I$114,3,0)+IF(AM115=$G114+$H114,1,0)+IF(AM116=$I$116,3,0)+IF(AM117=$G116+$H116,1,0)+IF(AM118=$I$118,3,0)+IF(AM119=$G118+$H118,1,0)+IF(AM120=$I$120,3,0)+IF(AM121=$G120+$H120,1,0)+IF(AM122=$I$122,3,0)+IF(AM123=$G122+$H122,1,0)+IF(AM124=$I$124,3,0)+IF(AM125=$G124+$H124,1,0)+IF(AM126=$I$126,3,0)+IF(AM127=$G126+$H126,1,0)+IF(AM128=$I$128,3,0)+IF(AM129=$G128+$H128,1,0)+IF(AM130=$I$130,3,0)+IF(AM131=$G130+$H130,1,0)+IF(AM132=$I$132,3,0)+IF(AM133=$G132+$H132,1,0)+IF(AM134=$I$134,3,0)+IF(AM135=$G134+$H134,1,0)+IF(AM136=$I$136,3,0)+IF(AM137=$G136+$H136,1,0)+IF(AM138=$I$138,3,0)+IF(AM139=$G138+$H138,1,0)+IF(AM140=$I$140,3,0)+IF(AM141=$G140+$H140,1,0)+IF(AM142=$I$142,3,0)+IF(AM143=$G142+$H142,1,0)+IF(AM144=$I$144,3,0)+IF(AM145=$G144+$H144,1,0)+IF(AM146=$I$146,3,0)+IF(AM147=$G146+$H146,1,0)+IF(AM148=$I$148,3,0)+IF(AM149=$G148+$H148,1,0)+IF(AM150=$I$150,3,0)+IF(AM151=$G150+$H150,1,0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN5" s="75">
         <f>SUM(IF(AN80=$I$80,3,0)+IF(AN81=$G80+$H80,1,0)+IF(AN82=$I$82,3,0)+IF(AN83=$G82+$H82,1,0)+IF(AN84=$I$84,3,0)+IF(AN85=$G84+$H84,1,0)+IF(AN86=$I$86,3,0)+IF(AN87=$G86+$H86,1,0)+IF(AN88=$I$88,3,0)+IF(AN89=$G88+$H88,1,0)+IF(AN90=$I$90,3,0)+IF(AN91=$G90+$H90,1,0)+IF(AN92=$I$92,3,0)+IF(AN93=$G92+$H92,1,0)+IF(AN94=$I$94,3,0)+IF(AN95=$G94+$H94,1,0)+IF(AN96=$I$96,3,0)+IF(AN97=$G96+$H96,1,0)+IF(AN98=$I$98,3,0)+IF(AN99=$G98+$H98,1,0)+IF(AN100=$I$100,3,0)+IF(AN101=$G100+$H100,1,0)+IF(AN102=$I$102,3,0)+IF(AN103=$G102+$H102,1,0)+IF(AN104=$I$104,3,0)+IF(AN105=$G104+$H104,1,0)+IF(AN106=$I$106,3,0)+IF(AN107=$G106+$H106,1,0)+IF(AN108=$I$108,3,0)+IF(AN109=$G108+$H108,1,0)+IF(AN110=$I$110,3,0)+IF(AN111=$G110+$H110,1,0)+IF(AN112=$I$112,3,0)+IF(AN113=$G112+$H112,1,0)+IF(AN114=$I$114,3,0)+IF(AN115=$G114+$H114,1,0)+IF(AN116=$I$116,3,0)+IF(AN117=$G116+$H116,1,0)+IF(AN118=$I$118,3,0)+IF(AN119=$G118+$H118,1,0)+IF(AN120=$I$120,3,0)+IF(AN121=$G120+$H120,1,0)+IF(AN122=$I$122,3,0)+IF(AN123=$G122+$H122,1,0)+IF(AN124=$I$124,3,0)+IF(AN125=$G124+$H124,1,0)+IF(AN126=$I$126,3,0)+IF(AN127=$G126+$H126,1,0)+IF(AN128=$I$128,3,0)+IF(AN129=$G128+$H128,1,0)+IF(AN130=$I$130,3,0)+IF(AN131=$G130+$H130,1,0)+IF(AN132=$I$132,3,0)+IF(AN133=$G132+$H132,1,0)+IF(AN134=$I$134,3,0)+IF(AN135=$G134+$H134,1,0)+IF(AN136=$I$136,3,0)+IF(AN137=$G136+$H136,1,0)+IF(AN138=$I$138,3,0)+IF(AN139=$G138+$H138,1,0)+IF(AN140=$I$140,3,0)+IF(AN141=$G140+$H140,1,0)+IF(AN142=$I$142,3,0)+IF(AN143=$G142+$H142,1,0)+IF(AN144=$I$144,3,0)+IF(AN145=$G144+$H144,1,0)+IF(AN146=$I$146,3,0)+IF(AN147=$G146+$H146,1,0)+IF(AN148=$I$148,3,0)+IF(AN149=$G148+$H148,1,0)+IF(AN150=$I$150,3,0)+IF(AN151=$G150+$H150,1,0))</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO5" s="75">
         <f>SUM(IF(AO80=$I$80,3,0)+IF(AO81=$G80+$H80,1,0)+IF(AO82=$I$82,3,0)+IF(AO83=$G82+$H82,1,0)+IF(AO84=$I$84,3,0)+IF(AO85=$G84+$H84,1,0)+IF(AO86=$I$86,3,0)+IF(AO87=$G86+$H86,1,0)+IF(AO88=$I$88,3,0)+IF(AO89=$G88+$H88,1,0)+IF(AO90=$I$90,3,0)+IF(AO91=$G90+$H90,1,0)+IF(AO92=$I$92,3,0)+IF(AO93=$G92+$H92,1,0)+IF(AO94=$I$94,3,0)+IF(AO95=$G94+$H94,1,0)+IF(AO96=$I$96,3,0)+IF(AO97=$G96+$H96,1,0)+IF(AO98=$I$98,3,0)+IF(AO99=$G98+$H98,1,0)+IF(AO100=$I$100,3,0)+IF(AO101=$G100+$H100,1,0)+IF(AO102=$I$102,3,0)+IF(AO103=$G102+$H102,1,0)+IF(AO104=$I$104,3,0)+IF(AO105=$G104+$H104,1,0)+IF(AO106=$I$106,3,0)+IF(AO107=$G106+$H106,1,0)+IF(AO108=$I$108,3,0)+IF(AO109=$G108+$H108,1,0)+IF(AO110=$I$110,3,0)+IF(AO111=$G110+$H110,1,0)+IF(AO112=$I$112,3,0)+IF(AO113=$G112+$H112,1,0)+IF(AO114=$I$114,3,0)+IF(AO115=$G114+$H114,1,0)+IF(AO116=$I$116,3,0)+IF(AO117=$G116+$H116,1,0)+IF(AO118=$I$118,3,0)+IF(AO119=$G118+$H118,1,0)+IF(AO120=$I$120,3,0)+IF(AO121=$G120+$H120,1,0)+IF(AO122=$I$122,3,0)+IF(AO123=$G122+$H122,1,0)+IF(AO124=$I$124,3,0)+IF(AO125=$G124+$H124,1,0)+IF(AO126=$I$126,3,0)+IF(AO127=$G126+$H126,1,0)+IF(AO128=$I$128,3,0)+IF(AO129=$G128+$H128,1,0)+IF(AO130=$I$130,3,0)+IF(AO131=$G130+$H130,1,0)+IF(AO132=$I$132,3,0)+IF(AO133=$G132+$H132,1,0)+IF(AO134=$I$134,3,0)+IF(AO135=$G134+$H134,1,0)+IF(AO136=$I$136,3,0)+IF(AO137=$G136+$H136,1,0)+IF(AO138=$I$138,3,0)+IF(AO139=$G138+$H138,1,0)+IF(AO140=$I$140,3,0)+IF(AO141=$G140+$H140,1,0)+IF(AO142=$I$142,3,0)+IF(AO143=$G142+$H142,1,0)+IF(AO144=$I$144,3,0)+IF(AO145=$G144+$H144,1,0)+IF(AO146=$I$146,3,0)+IF(AO147=$G146+$H146,1,0)+IF(AO148=$I$148,3,0)+IF(AO149=$G148+$H148,1,0)+IF(AO150=$I$150,3,0)+IF(AO151=$G150+$H150,1,0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AP5" s="75">
         <f>SUM(IF(AP80=$I$80,3,0)+IF(AP81=$G80+$H80,1,0)+IF(AP82=$I$82,3,0)+IF(AP83=$G82+$H82,1,0)+IF(AP84=$I$84,3,0)+IF(AP85=$G84+$H84,1,0)+IF(AP86=$I$86,3,0)+IF(AP87=$G86+$H86,1,0)+IF(AP88=$I$88,3,0)+IF(AP89=$G88+$H88,1,0)+IF(AP90=$I$90,3,0)+IF(AP91=$G90+$H90,1,0)+IF(AP92=$I$92,3,0)+IF(AP93=$G92+$H92,1,0)+IF(AP94=$I$94,3,0)+IF(AP95=$G94+$H94,1,0)+IF(AP96=$I$96,3,0)+IF(AP97=$G96+$H96,1,0)+IF(AP98=$I$98,3,0)+IF(AP99=$G98+$H98,1,0)+IF(AP100=$I$100,3,0)+IF(AP101=$G100+$H100,1,0)+IF(AP102=$I$102,3,0)+IF(AP103=$G102+$H102,1,0)+IF(AP104=$I$104,3,0)+IF(AP105=$G104+$H104,1,0)+IF(AP106=$I$106,3,0)+IF(AP107=$G106+$H106,1,0)+IF(AP108=$I$108,3,0)+IF(AP109=$G108+$H108,1,0)+IF(AP110=$I$110,3,0)+IF(AP111=$G110+$H110,1,0)+IF(AP112=$I$112,3,0)+IF(AP113=$G112+$H112,1,0)+IF(AP114=$I$114,3,0)+IF(AP115=$G114+$H114,1,0)+IF(AP116=$I$116,3,0)+IF(AP117=$G116+$H116,1,0)+IF(AP118=$I$118,3,0)+IF(AP119=$G118+$H118,1,0)+IF(AP120=$I$120,3,0)+IF(AP121=$G120+$H120,1,0)+IF(AP122=$I$122,3,0)+IF(AP123=$G122+$H122,1,0)+IF(AP124=$I$124,3,0)+IF(AP125=$G124+$H124,1,0)+IF(AP126=$I$126,3,0)+IF(AP127=$G126+$H126,1,0)+IF(AP128=$I$128,3,0)+IF(AP129=$G128+$H128,1,0)+IF(AP130=$I$130,3,0)+IF(AP131=$G130+$H130,1,0)+IF(AP132=$I$132,3,0)+IF(AP133=$G132+$H132,1,0)+IF(AP134=$I$134,3,0)+IF(AP135=$G134+$H134,1,0)+IF(AP136=$I$136,3,0)+IF(AP137=$G136+$H136,1,0)+IF(AP138=$I$138,3,0)+IF(AP139=$G138+$H138,1,0)+IF(AP140=$I$140,3,0)+IF(AP141=$G140+$H140,1,0)+IF(AP142=$I$142,3,0)+IF(AP143=$G142+$H142,1,0)+IF(AP144=$I$144,3,0)+IF(AP145=$G144+$H144,1,0)+IF(AP146=$I$146,3,0)+IF(AP147=$G146+$H146,1,0)+IF(AP148=$I$148,3,0)+IF(AP149=$G148+$H148,1,0)+IF(AP150=$I$150,3,0)+IF(AP151=$G150+$H150,1,0))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AQ5" s="75">
         <f>SUM(IF(AQ80=$I$80,3,0)+IF(AQ81=$G80+$H80,1,0)+IF(AQ82=$I$82,3,0)+IF(AQ83=$G82+$H82,1,0)+IF(AQ84=$I$84,3,0)+IF(AQ85=$G84+$H84,1,0)+IF(AQ86=$I$86,3,0)+IF(AQ87=$G86+$H86,1,0)+IF(AQ88=$I$88,3,0)+IF(AQ89=$G88+$H88,1,0)+IF(AQ90=$I$90,3,0)+IF(AQ91=$G90+$H90,1,0)+IF(AQ92=$I$92,3,0)+IF(AQ93=$G92+$H92,1,0)+IF(AQ94=$I$94,3,0)+IF(AQ95=$G94+$H94,1,0)+IF(AQ96=$I$96,3,0)+IF(AQ97=$G96+$H96,1,0)+IF(AQ98=$I$98,3,0)+IF(AQ99=$G98+$H98,1,0)+IF(AQ100=$I$100,3,0)+IF(AQ101=$G100+$H100,1,0)+IF(AQ102=$I$102,3,0)+IF(AQ103=$G102+$H102,1,0)+IF(AQ104=$I$104,3,0)+IF(AQ105=$G104+$H104,1,0)+IF(AQ106=$I$106,3,0)+IF(AQ107=$G106+$H106,1,0)+IF(AQ108=$I$108,3,0)+IF(AQ109=$G108+$H108,1,0)+IF(AQ110=$I$110,3,0)+IF(AQ111=$G110+$H110,1,0)+IF(AQ112=$I$112,3,0)+IF(AQ113=$G112+$H112,1,0)+IF(AQ114=$I$114,3,0)+IF(AQ115=$G114+$H114,1,0)+IF(AQ116=$I$116,3,0)+IF(AQ117=$G116+$H116,1,0)+IF(AQ118=$I$118,3,0)+IF(AQ119=$G118+$H118,1,0)+IF(AQ120=$I$120,3,0)+IF(AQ121=$G120+$H120,1,0)+IF(AQ122=$I$122,3,0)+IF(AQ123=$G122+$H122,1,0)+IF(AQ124=$I$124,3,0)+IF(AQ125=$G124+$H124,1,0)+IF(AQ126=$I$126,3,0)+IF(AQ127=$G126+$H126,1,0)+IF(AQ128=$I$128,3,0)+IF(AQ129=$G128+$H128,1,0)+IF(AQ130=$I$130,3,0)+IF(AQ131=$G130+$H130,1,0)+IF(AQ132=$I$132,3,0)+IF(AQ133=$G132+$H132,1,0)+IF(AQ134=$I$134,3,0)+IF(AQ135=$G134+$H134,1,0)+IF(AQ136=$I$136,3,0)+IF(AQ137=$G136+$H136,1,0)+IF(AQ138=$I$138,3,0)+IF(AQ139=$G138+$H138,1,0)+IF(AQ140=$I$140,3,0)+IF(AQ141=$G140+$H140,1,0)+IF(AQ142=$I$142,3,0)+IF(AQ143=$G142+$H142,1,0)+IF(AQ144=$I$144,3,0)+IF(AQ145=$G144+$H144,1,0)+IF(AQ146=$I$146,3,0)+IF(AQ147=$G146+$H146,1,0)+IF(AQ148=$I$148,3,0)+IF(AQ149=$G148+$H148,1,0)+IF(AQ150=$I$150,3,0)+IF(AQ151=$G150+$H150,1,0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AR5" s="75">
         <f>SUM(IF(AR80=$I$80,3,0)+IF(AR81=$G80+$H80,1,0)+IF(AR82=$I$82,3,0)+IF(AR83=$G82+$H82,1,0)+IF(AR84=$I$84,3,0)+IF(AR85=$G84+$H84,1,0)+IF(AR86=$I$86,3,0)+IF(AR87=$G86+$H86,1,0)+IF(AR88=$I$88,3,0)+IF(AR89=$G88+$H88,1,0)+IF(AR90=$I$90,3,0)+IF(AR91=$G90+$H90,1,0)+IF(AR92=$I$92,3,0)+IF(AR93=$G92+$H92,1,0)+IF(AR94=$I$94,3,0)+IF(AR95=$G94+$H94,1,0)+IF(AR96=$I$96,3,0)+IF(AR97=$G96+$H96,1,0)+IF(AR98=$I$98,3,0)+IF(AR99=$G98+$H98,1,0)+IF(AR100=$I$100,3,0)+IF(AR101=$G100+$H100,1,0)+IF(AR102=$I$102,3,0)+IF(AR103=$G102+$H102,1,0)+IF(AR104=$I$104,3,0)+IF(AR105=$G104+$H104,1,0)+IF(AR106=$I$106,3,0)+IF(AR107=$G106+$H106,1,0)+IF(AR108=$I$108,3,0)+IF(AR109=$G108+$H108,1,0)+IF(AR110=$I$110,3,0)+IF(AR111=$G110+$H110,1,0)+IF(AR112=$I$112,3,0)+IF(AR113=$G112+$H112,1,0)+IF(AR114=$I$114,3,0)+IF(AR115=$G114+$H114,1,0)+IF(AR116=$I$116,3,0)+IF(AR117=$G116+$H116,1,0)+IF(AR118=$I$118,3,0)+IF(AR119=$G118+$H118,1,0)+IF(AR120=$I$120,3,0)+IF(AR121=$G120+$H120,1,0)+IF(AR122=$I$122,3,0)+IF(AR123=$G122+$H122,1,0)+IF(AR124=$I$124,3,0)+IF(AR125=$G124+$H124,1,0)+IF(AR126=$I$126,3,0)+IF(AR127=$G126+$H126,1,0)+IF(AR128=$I$128,3,0)+IF(AR129=$G128+$H128,1,0)+IF(AR130=$I$130,3,0)+IF(AR131=$G130+$H130,1,0)+IF(AR132=$I$132,3,0)+IF(AR133=$G132+$H132,1,0)+IF(AR134=$I$134,3,0)+IF(AR135=$G134+$H134,1,0)+IF(AR136=$I$136,3,0)+IF(AR137=$G136+$H136,1,0)+IF(AR138=$I$138,3,0)+IF(AR139=$G138+$H138,1,0)+IF(AR140=$I$140,3,0)+IF(AR141=$G140+$H140,1,0)+IF(AR142=$I$142,3,0)+IF(AR143=$G142+$H142,1,0)+IF(AR144=$I$144,3,0)+IF(AR145=$G144+$H144,1,0)+IF(AR146=$I$146,3,0)+IF(AR147=$G146+$H146,1,0)+IF(AR148=$I$148,3,0)+IF(AR149=$G148+$H148,1,0)+IF(AR150=$I$150,3,0)+IF(AR151=$G150+$H150,1,0))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AS5" s="75">
         <f>SUM(IF(AS80=$I$80,3,0)+IF(AS81=$G80+$H80,1,0)+IF(AS82=$I$82,3,0)+IF(AS83=$G82+$H82,1,0)+IF(AS84=$I$84,3,0)+IF(AS85=$G84+$H84,1,0)+IF(AS86=$I$86,3,0)+IF(AS87=$G86+$H86,1,0)+IF(AS88=$I$88,3,0)+IF(AS89=$G88+$H88,1,0)+IF(AS90=$I$90,3,0)+IF(AS91=$G90+$H90,1,0)+IF(AS92=$I$92,3,0)+IF(AS93=$G92+$H92,1,0)+IF(AS94=$I$94,3,0)+IF(AS95=$G94+$H94,1,0)+IF(AS96=$I$96,3,0)+IF(AS97=$G96+$H96,1,0)+IF(AS98=$I$98,3,0)+IF(AS99=$G98+$H98,1,0)+IF(AS100=$I$100,3,0)+IF(AS101=$G100+$H100,1,0)+IF(AS102=$I$102,3,0)+IF(AS103=$G102+$H102,1,0)+IF(AS104=$I$104,3,0)+IF(AS105=$G104+$H104,1,0)+IF(AS106=$I$106,3,0)+IF(AS107=$G106+$H106,1,0)+IF(AS108=$I$108,3,0)+IF(AS109=$G108+$H108,1,0)+IF(AS110=$I$110,3,0)+IF(AS111=$G110+$H110,1,0)+IF(AS112=$I$112,3,0)+IF(AS113=$G112+$H112,1,0)+IF(AS114=$I$114,3,0)+IF(AS115=$G114+$H114,1,0)+IF(AS116=$I$116,3,0)+IF(AS117=$G116+$H116,1,0)+IF(AS118=$I$118,3,0)+IF(AS119=$G118+$H118,1,0)+IF(AS120=$I$120,3,0)+IF(AS121=$G120+$H120,1,0)+IF(AS122=$I$122,3,0)+IF(AS123=$G122+$H122,1,0)+IF(AS124=$I$124,3,0)+IF(AS125=$G124+$H124,1,0)+IF(AS126=$I$126,3,0)+IF(AS127=$G126+$H126,1,0)+IF(AS128=$I$128,3,0)+IF(AS129=$G128+$H128,1,0)+IF(AS130=$I$130,3,0)+IF(AS131=$G130+$H130,1,0)+IF(AS132=$I$132,3,0)+IF(AS133=$G132+$H132,1,0)+IF(AS134=$I$134,3,0)+IF(AS135=$G134+$H134,1,0)+IF(AS136=$I$136,3,0)+IF(AS137=$G136+$H136,1,0)+IF(AS138=$I$138,3,0)+IF(AS139=$G138+$H138,1,0)+IF(AS140=$I$140,3,0)+IF(AS141=$G140+$H140,1,0)+IF(AS142=$I$142,3,0)+IF(AS143=$G142+$H142,1,0)+IF(AS144=$I$144,3,0)+IF(AS145=$G144+$H144,1,0)+IF(AS146=$I$146,3,0)+IF(AS147=$G146+$H146,1,0)+IF(AS148=$I$148,3,0)+IF(AS149=$G148+$H148,1,0)+IF(AS150=$I$150,3,0)+IF(AS151=$G150+$H150,1,0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT5" s="79">
         <f>SUM(IF(AT80=$I$80,3,0)+IF(AT81=$G80+$H80,1,0)+IF(AT82=$I$82,3,0)+IF(AT83=$G82+$H82,1,0)+IF(AT84=$I$84,3,0)+IF(AT85=$G84+$H84,1,0)+IF(AT86=$I$86,3,0)+IF(AT87=$G86+$H86,1,0)+IF(AT88=$I$88,3,0)+IF(AT89=$G88+$H88,1,0)+IF(AT90=$I$90,3,0)+IF(AT91=$G90+$H90,1,0)+IF(AT92=$I$92,3,0)+IF(AT93=$G92+$H92,1,0)+IF(AT94=$I$94,3,0)+IF(AT95=$G94+$H94,1,0)+IF(AT96=$I$96,3,0)+IF(AT97=$G96+$H96,1,0)+IF(AT98=$I$98,3,0)+IF(AT99=$G98+$H98,1,0)+IF(AT100=$I$100,3,0)+IF(AT101=$G100+$H100,1,0)+IF(AT102=$I$102,3,0)+IF(AT103=$G102+$H102,1,0)+IF(AT104=$I$104,3,0)+IF(AT105=$G104+$H104,1,0)+IF(AT106=$I$106,3,0)+IF(AT107=$G106+$H106,1,0)+IF(AT108=$I$108,3,0)+IF(AT109=$G108+$H108,1,0)+IF(AT110=$I$110,3,0)+IF(AT111=$G110+$H110,1,0)+IF(AT112=$I$112,3,0)+IF(AT113=$G112+$H112,1,0)+IF(AT114=$I$114,3,0)+IF(AT115=$G114+$H114,1,0)+IF(AT116=$I$116,3,0)+IF(AT117=$G116+$H116,1,0)+IF(AT118=$I$118,3,0)+IF(AT119=$G118+$H118,1,0)+IF(AT120=$I$120,3,0)+IF(AT121=$G120+$H120,1,0)+IF(AT122=$I$122,3,0)+IF(AT123=$G122+$H122,1,0)+IF(AT124=$I$124,3,0)+IF(AT125=$G124+$H124,1,0)+IF(AT126=$I$126,3,0)+IF(AT127=$G126+$H126,1,0)+IF(AT128=$I$128,3,0)+IF(AT129=$G128+$H128,1,0)+IF(AT130=$I$130,3,0)+IF(AT131=$G130+$H130,1,0)+IF(AT132=$I$132,3,0)+IF(AT133=$G132+$H132,1,0)+IF(AT134=$I$134,3,0)+IF(AT135=$G134+$H134,1,0)+IF(AT136=$I$136,3,0)+IF(AT137=$G136+$H136,1,0)+IF(AT138=$I$138,3,0)+IF(AT139=$G138+$H138,1,0)+IF(AT140=$I$140,3,0)+IF(AT141=$G140+$H140,1,0)+IF(AT142=$I$142,3,0)+IF(AT143=$G142+$H142,1,0)+IF(AT144=$I$144,3,0)+IF(AT145=$G144+$H144,1,0)+IF(AT146=$I$146,3,0)+IF(AT147=$G146+$H146,1,0)+IF(AT148=$I$148,3,0)+IF(AT149=$G148+$H148,1,0)+IF(AT150=$I$150,3,0)+IF(AT151=$G150+$H150,1,0))</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:54" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:54" ht="15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="61"/>
       <c r="B6" s="61"/>
       <c r="C6" s="61"/>
@@ -3460,7 +3460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:54" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" ht="15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
       <c r="C7" s="61"/>
@@ -3512,11 +3512,11 @@
       </c>
       <c r="T7" s="77">
         <f>SUM(AND($G$80="",$H$80="",T81=0)+AND($G$82="",$H$82="",T83=0)+AND($G$84="",$H$84="",T85=0)+AND($G$86="",$H$86="",T87=0)+AND($G$88="",$H$88="",T89=0)+AND($G$90="",$H$90="",T91=0)+AND($G$92="",$H$92="",T93=0)+AND($G$94="",$H$94="",T95=0)+AND($G$96="",$H$96="",T97=0)+AND($G$98="",$H$98="",T99=0)+AND($G$100="",$H$100="",T101=0)+AND($G$102="",$H$102="",T103=0)+AND($G$104="",$H$104="",T105=0)+AND($G$106="",$H$106="",T107=0)+AND($G$108="",$H$108="",T109=0)+AND($G$110="",$H$110="",T111=0)+AND($G$112="",$H$112="",T113=0)+AND($G$114="",$H$114="",T115=0)+AND($G$116="",$H$116="",T117=0)+AND($G$118="",$H$118="",T119=0)+AND($G$120="",$H$120="",T121=0)+AND($G$122="",$H$122="",T123=0)+AND($G$124="",$H$124="",T125=0)+AND($G$126="",$H$126="",T127=0)+AND($G$128="",$H$128="",T129=0)+AND($G$130="",$H$130="",T131=0)+AND($G$132="",$H$132="",T133=0)+AND($G$134="",$H$134="",T135=0)+AND($G$136="",$H$136="",T137=0)+AND($G$138="",$H$138="",T139=0)+AND($G$140="",$H$140="",T141=0)+AND($G$142="",$H$142="",T143=0)+AND($G$144="",$H$144="",T145=0)+AND($G$146="",$H$146="",T147=0)+AND($G$148="",$H$148="",T149=0)+AND($G$150="",$H$150="",T151=0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U7" s="77">
         <f>SUM(AND($G$80="",$H$80="",U81=0)+AND($G$82="",$H$82="",U83=0)+AND($G$84="",$H$84="",U85=0)+AND($G$86="",$H$86="",U87=0)+AND($G$88="",$H$88="",U89=0)+AND($G$90="",$H$90="",U91=0)+AND($G$92="",$H$92="",U93=0)+AND($G$94="",$H$94="",U95=0)+AND($G$96="",$H$96="",U97=0)+AND($G$98="",$H$98="",U99=0)+AND($G$100="",$H$100="",U101=0)+AND($G$102="",$H$102="",U103=0)+AND($G$104="",$H$104="",U105=0)+AND($G$106="",$H$106="",U107=0)+AND($G$108="",$H$108="",U109=0)+AND($G$110="",$H$110="",U111=0)+AND($G$112="",$H$112="",U113=0)+AND($G$114="",$H$114="",U115=0)+AND($G$116="",$H$116="",U117=0)+AND($G$118="",$H$118="",U119=0)+AND($G$120="",$H$120="",U121=0)+AND($G$122="",$H$122="",U123=0)+AND($G$124="",$H$124="",U125=0)+AND($G$126="",$H$126="",U127=0)+AND($G$128="",$H$128="",U129=0)+AND($G$130="",$H$130="",U131=0)+AND($G$132="",$H$132="",U133=0)+AND($G$134="",$H$134="",U135=0)+AND($G$136="",$H$136="",U137=0)+AND($G$138="",$H$138="",U139=0)+AND($G$140="",$H$140="",U141=0)+AND($G$142="",$H$142="",U143=0)+AND($G$144="",$H$144="",U145=0)+AND($G$146="",$H$146="",U147=0)+AND($G$148="",$H$148="",U149=0)+AND($G$150="",$H$150="",U151=0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V7" s="77">
         <f>SUM(AND($G$80="",$H$80="",V81=0)+AND($G$82="",$H$82="",V83=0)+AND($G$84="",$H$84="",V85=0)+AND($G$86="",$H$86="",V87=0)+AND($G$88="",$H$88="",V89=0)+AND($G$90="",$H$90="",V91=0)+AND($G$92="",$H$92="",V93=0)+AND($G$94="",$H$94="",V95=0)+AND($G$96="",$H$96="",V97=0)+AND($G$98="",$H$98="",V99=0)+AND($G$100="",$H$100="",V101=0)+AND($G$102="",$H$102="",V103=0)+AND($G$104="",$H$104="",V105=0)+AND($G$106="",$H$106="",V107=0)+AND($G$108="",$H$108="",V109=0)+AND($G$110="",$H$110="",V111=0)+AND($G$112="",$H$112="",V113=0)+AND($G$114="",$H$114="",V115=0)+AND($G$116="",$H$116="",V117=0)+AND($G$118="",$H$118="",V119=0)+AND($G$120="",$H$120="",V121=0)+AND($G$122="",$H$122="",V123=0)+AND($G$124="",$H$124="",V125=0)+AND($G$126="",$H$126="",V127=0)+AND($G$128="",$H$128="",V129=0)+AND($G$130="",$H$130="",V131=0)+AND($G$132="",$H$132="",V133=0)+AND($G$134="",$H$134="",V135=0)+AND($G$136="",$H$136="",V137=0)+AND($G$138="",$H$138="",V139=0)+AND($G$140="",$H$140="",V141=0)+AND($G$142="",$H$142="",V143=0)+AND($G$144="",$H$144="",V145=0)+AND($G$146="",$H$146="",V147=0)+AND($G$148="",$H$148="",V149=0)+AND($G$150="",$H$150="",V151=0))</f>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="AB7" s="77">
         <f>SUM(AND($G$80="",$H$80="",AB81=0)+AND($G$82="",$H$82="",AB83=0)+AND($G$84="",$H$84="",AB85=0)+AND($G$86="",$H$86="",AB87=0)+AND($G$88="",$H$88="",AB89=0)+AND($G$90="",$H$90="",AB91=0)+AND($G$92="",$H$92="",AB93=0)+AND($G$94="",$H$94="",AB95=0)+AND($G$96="",$H$96="",AB97=0)+AND($G$98="",$H$98="",AB99=0)+AND($G$100="",$H$100="",AB101=0)+AND($G$102="",$H$102="",AB103=0)+AND($G$104="",$H$104="",AB105=0)+AND($G$106="",$H$106="",AB107=0)+AND($G$108="",$H$108="",AB109=0)+AND($G$110="",$H$110="",AB111=0)+AND($G$112="",$H$112="",AB113=0)+AND($G$114="",$H$114="",AB115=0)+AND($G$116="",$H$116="",AB117=0)+AND($G$118="",$H$118="",AB119=0)+AND($G$120="",$H$120="",AB121=0)+AND($G$122="",$H$122="",AB123=0)+AND($G$124="",$H$124="",AB125=0)+AND($G$126="",$H$126="",AB127=0)+AND($G$128="",$H$128="",AB129=0)+AND($G$130="",$H$130="",AB131=0)+AND($G$132="",$H$132="",AB133=0)+AND($G$134="",$H$134="",AB135=0)+AND($G$136="",$H$136="",AB137=0)+AND($G$138="",$H$138="",AB139=0)+AND($G$140="",$H$140="",AB141=0)+AND($G$142="",$H$142="",AB143=0)+AND($G$144="",$H$144="",AB145=0)+AND($G$146="",$H$146="",AB147=0)+AND($G$148="",$H$148="",AB149=0)+AND($G$150="",$H$150="",AB151=0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC7" s="77">
         <f>SUM(AND($G$80="",$H$80="",AC81=0)+AND($G$82="",$H$82="",AC83=0)+AND($G$84="",$H$84="",AC85=0)+AND($G$86="",$H$86="",AC87=0)+AND($G$88="",$H$88="",AC89=0)+AND($G$90="",$H$90="",AC91=0)+AND($G$92="",$H$92="",AC93=0)+AND($G$94="",$H$94="",AC95=0)+AND($G$96="",$H$96="",AC97=0)+AND($G$98="",$H$98="",AC99=0)+AND($G$100="",$H$100="",AC101=0)+AND($G$102="",$H$102="",AC103=0)+AND($G$104="",$H$104="",AC105=0)+AND($G$106="",$H$106="",AC107=0)+AND($G$108="",$H$108="",AC109=0)+AND($G$110="",$H$110="",AC111=0)+AND($G$112="",$H$112="",AC113=0)+AND($G$114="",$H$114="",AC115=0)+AND($G$116="",$H$116="",AC117=0)+AND($G$118="",$H$118="",AC119=0)+AND($G$120="",$H$120="",AC121=0)+AND($G$122="",$H$122="",AC123=0)+AND($G$124="",$H$124="",AC125=0)+AND($G$126="",$H$126="",AC127=0)+AND($G$128="",$H$128="",AC129=0)+AND($G$130="",$H$130="",AC131=0)+AND($G$132="",$H$132="",AC133=0)+AND($G$134="",$H$134="",AC135=0)+AND($G$136="",$H$136="",AC137=0)+AND($G$138="",$H$138="",AC139=0)+AND($G$140="",$H$140="",AC141=0)+AND($G$142="",$H$142="",AC143=0)+AND($G$144="",$H$144="",AC145=0)+AND($G$146="",$H$146="",AC147=0)+AND($G$148="",$H$148="",AC149=0)+AND($G$150="",$H$150="",AC151=0))</f>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="AD7" s="77">
         <f>SUM(AND($G$80="",$H$80="",AD81=0)+AND($G$82="",$H$82="",AD83=0)+AND($G$84="",$H$84="",AD85=0)+AND($G$86="",$H$86="",AD87=0)+AND($G$88="",$H$88="",AD89=0)+AND($G$90="",$H$90="",AD91=0)+AND($G$92="",$H$92="",AD93=0)+AND($G$94="",$H$94="",AD95=0)+AND($G$96="",$H$96="",AD97=0)+AND($G$98="",$H$98="",AD99=0)+AND($G$100="",$H$100="",AD101=0)+AND($G$102="",$H$102="",AD103=0)+AND($G$104="",$H$104="",AD105=0)+AND($G$106="",$H$106="",AD107=0)+AND($G$108="",$H$108="",AD109=0)+AND($G$110="",$H$110="",AD111=0)+AND($G$112="",$H$112="",AD113=0)+AND($G$114="",$H$114="",AD115=0)+AND($G$116="",$H$116="",AD117=0)+AND($G$118="",$H$118="",AD119=0)+AND($G$120="",$H$120="",AD121=0)+AND($G$122="",$H$122="",AD123=0)+AND($G$124="",$H$124="",AD125=0)+AND($G$126="",$H$126="",AD127=0)+AND($G$128="",$H$128="",AD129=0)+AND($G$130="",$H$130="",AD131=0)+AND($G$132="",$H$132="",AD133=0)+AND($G$134="",$H$134="",AD135=0)+AND($G$136="",$H$136="",AD137=0)+AND($G$138="",$H$138="",AD139=0)+AND($G$140="",$H$140="",AD141=0)+AND($G$142="",$H$142="",AD143=0)+AND($G$144="",$H$144="",AD145=0)+AND($G$146="",$H$146="",AD147=0)+AND($G$148="",$H$148="",AD149=0)+AND($G$150="",$H$150="",AD151=0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="77">
         <f>SUM(AND($G$80="",$H$80="",AE81=0)+AND($G$82="",$H$82="",AE83=0)+AND($G$84="",$H$84="",AE85=0)+AND($G$86="",$H$86="",AE87=0)+AND($G$88="",$H$88="",AE89=0)+AND($G$90="",$H$90="",AE91=0)+AND($G$92="",$H$92="",AE93=0)+AND($G$94="",$H$94="",AE95=0)+AND($G$96="",$H$96="",AE97=0)+AND($G$98="",$H$98="",AE99=0)+AND($G$100="",$H$100="",AE101=0)+AND($G$102="",$H$102="",AE103=0)+AND($G$104="",$H$104="",AE105=0)+AND($G$106="",$H$106="",AE107=0)+AND($G$108="",$H$108="",AE109=0)+AND($G$110="",$H$110="",AE111=0)+AND($G$112="",$H$112="",AE113=0)+AND($G$114="",$H$114="",AE115=0)+AND($G$116="",$H$116="",AE117=0)+AND($G$118="",$H$118="",AE119=0)+AND($G$120="",$H$120="",AE121=0)+AND($G$122="",$H$122="",AE123=0)+AND($G$124="",$H$124="",AE125=0)+AND($G$126="",$H$126="",AE127=0)+AND($G$128="",$H$128="",AE129=0)+AND($G$130="",$H$130="",AE131=0)+AND($G$132="",$H$132="",AE133=0)+AND($G$134="",$H$134="",AE135=0)+AND($G$136="",$H$136="",AE137=0)+AND($G$138="",$H$138="",AE139=0)+AND($G$140="",$H$140="",AE141=0)+AND($G$142="",$H$142="",AE143=0)+AND($G$144="",$H$144="",AE145=0)+AND($G$146="",$H$146="",AE147=0)+AND($G$148="",$H$148="",AE149=0)+AND($G$150="",$H$150="",AE151=0))</f>
@@ -3560,11 +3560,11 @@
       </c>
       <c r="AF7" s="77">
         <f>SUM(AND($G$80="",$H$80="",AF81=0)+AND($G$82="",$H$82="",AF83=0)+AND($G$84="",$H$84="",AF85=0)+AND($G$86="",$H$86="",AF87=0)+AND($G$88="",$H$88="",AF89=0)+AND($G$90="",$H$90="",AF91=0)+AND($G$92="",$H$92="",AF93=0)+AND($G$94="",$H$94="",AF95=0)+AND($G$96="",$H$96="",AF97=0)+AND($G$98="",$H$98="",AF99=0)+AND($G$100="",$H$100="",AF101=0)+AND($G$102="",$H$102="",AF103=0)+AND($G$104="",$H$104="",AF105=0)+AND($G$106="",$H$106="",AF107=0)+AND($G$108="",$H$108="",AF109=0)+AND($G$110="",$H$110="",AF111=0)+AND($G$112="",$H$112="",AF113=0)+AND($G$114="",$H$114="",AF115=0)+AND($G$116="",$H$116="",AF117=0)+AND($G$118="",$H$118="",AF119=0)+AND($G$120="",$H$120="",AF121=0)+AND($G$122="",$H$122="",AF123=0)+AND($G$124="",$H$124="",AF125=0)+AND($G$126="",$H$126="",AF127=0)+AND($G$128="",$H$128="",AF129=0)+AND($G$130="",$H$130="",AF131=0)+AND($G$132="",$H$132="",AF133=0)+AND($G$134="",$H$134="",AF135=0)+AND($G$136="",$H$136="",AF137=0)+AND($G$138="",$H$138="",AF139=0)+AND($G$140="",$H$140="",AF141=0)+AND($G$142="",$H$142="",AF143=0)+AND($G$144="",$H$144="",AF145=0)+AND($G$146="",$H$146="",AF147=0)+AND($G$148="",$H$148="",AF149=0)+AND($G$150="",$H$150="",AF151=0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" s="77">
         <f>SUM(AND($G$80="",$H$80="",AG81=0)+AND($G$82="",$H$82="",AG83=0)+AND($G$84="",$H$84="",AG85=0)+AND($G$86="",$H$86="",AG87=0)+AND($G$88="",$H$88="",AG89=0)+AND($G$90="",$H$90="",AG91=0)+AND($G$92="",$H$92="",AG93=0)+AND($G$94="",$H$94="",AG95=0)+AND($G$96="",$H$96="",AG97=0)+AND($G$98="",$H$98="",AG99=0)+AND($G$100="",$H$100="",AG101=0)+AND($G$102="",$H$102="",AG103=0)+AND($G$104="",$H$104="",AG105=0)+AND($G$106="",$H$106="",AG107=0)+AND($G$108="",$H$108="",AG109=0)+AND($G$110="",$H$110="",AG111=0)+AND($G$112="",$H$112="",AG113=0)+AND($G$114="",$H$114="",AG115=0)+AND($G$116="",$H$116="",AG117=0)+AND($G$118="",$H$118="",AG119=0)+AND($G$120="",$H$120="",AG121=0)+AND($G$122="",$H$122="",AG123=0)+AND($G$124="",$H$124="",AG125=0)+AND($G$126="",$H$126="",AG127=0)+AND($G$128="",$H$128="",AG129=0)+AND($G$130="",$H$130="",AG131=0)+AND($G$132="",$H$132="",AG133=0)+AND($G$134="",$H$134="",AG135=0)+AND($G$136="",$H$136="",AG137=0)+AND($G$138="",$H$138="",AG139=0)+AND($G$140="",$H$140="",AG141=0)+AND($G$142="",$H$142="",AG143=0)+AND($G$144="",$H$144="",AG145=0)+AND($G$146="",$H$146="",AG147=0)+AND($G$148="",$H$148="",AG149=0)+AND($G$150="",$H$150="",AG151=0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" s="77">
         <f>SUM(AND($G$80="",$H$80="",AH81=0)+AND($G$82="",$H$82="",AH83=0)+AND($G$84="",$H$84="",AH85=0)+AND($G$86="",$H$86="",AH87=0)+AND($G$88="",$H$88="",AH89=0)+AND($G$90="",$H$90="",AH91=0)+AND($G$92="",$H$92="",AH93=0)+AND($G$94="",$H$94="",AH95=0)+AND($G$96="",$H$96="",AH97=0)+AND($G$98="",$H$98="",AH99=0)+AND($G$100="",$H$100="",AH101=0)+AND($G$102="",$H$102="",AH103=0)+AND($G$104="",$H$104="",AH105=0)+AND($G$106="",$H$106="",AH107=0)+AND($G$108="",$H$108="",AH109=0)+AND($G$110="",$H$110="",AH111=0)+AND($G$112="",$H$112="",AH113=0)+AND($G$114="",$H$114="",AH115=0)+AND($G$116="",$H$116="",AH117=0)+AND($G$118="",$H$118="",AH119=0)+AND($G$120="",$H$120="",AH121=0)+AND($G$122="",$H$122="",AH123=0)+AND($G$124="",$H$124="",AH125=0)+AND($G$126="",$H$126="",AH127=0)+AND($G$128="",$H$128="",AH129=0)+AND($G$130="",$H$130="",AH131=0)+AND($G$132="",$H$132="",AH133=0)+AND($G$134="",$H$134="",AH135=0)+AND($G$136="",$H$136="",AH137=0)+AND($G$138="",$H$138="",AH139=0)+AND($G$140="",$H$140="",AH141=0)+AND($G$142="",$H$142="",AH143=0)+AND($G$144="",$H$144="",AH145=0)+AND($G$146="",$H$146="",AH147=0)+AND($G$148="",$H$148="",AH149=0)+AND($G$150="",$H$150="",AH151=0))</f>
@@ -3619,7 +3619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:54" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="103" t="s">
         <v>1</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:54" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="103"/>
       <c r="B9" s="133"/>
       <c r="C9" s="133"/>
@@ -3801,10 +3801,10 @@
         <v>3</v>
       </c>
       <c r="T9" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U9" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V9" s="18">
         <v>2</v>
@@ -3825,22 +3825,22 @@
         <v>3</v>
       </c>
       <c r="AB9" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC9" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD9" s="18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE9" s="18">
         <v>3</v>
       </c>
       <c r="AF9" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG9" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH9" s="18">
         <v>3</v>
@@ -3888,7 +3888,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="103"/>
       <c r="B10" s="132">
         <v>46184</v>
@@ -3970,22 +3970,22 @@
         <v>7</v>
       </c>
       <c r="AB10" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AC10" s="13" t="s">
         <v>16</v>
       </c>
       <c r="AD10" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE10" s="13" t="s">
         <v>7</v>
       </c>
       <c r="AF10" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AG10" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AH10" s="13" t="s">
         <v>7</v>
@@ -4033,7 +4033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="103"/>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -4074,10 +4074,10 @@
         <v>2</v>
       </c>
       <c r="T11" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U11" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V11" s="13">
         <v>2</v>
@@ -4110,10 +4110,10 @@
         <v>2</v>
       </c>
       <c r="AF11" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG11" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH11" s="13">
         <v>3</v>
@@ -4161,7 +4161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="103"/>
       <c r="B12" s="132">
         <v>46191</v>
@@ -4300,7 +4300,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="103"/>
       <c r="B13" s="133"/>
       <c r="C13" s="133"/>
@@ -4365,22 +4365,22 @@
         <v>2</v>
       </c>
       <c r="AB13" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC13" s="18">
         <v>3</v>
       </c>
       <c r="AD13" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE13" s="18">
         <v>3</v>
       </c>
       <c r="AF13" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG13" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH13" s="18">
         <v>2</v>
@@ -4426,7 +4426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="103"/>
       <c r="B14" s="132">
         <v>46191</v>
@@ -4504,22 +4504,22 @@
         <v>7</v>
       </c>
       <c r="AB14" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AC14" s="13" t="s">
         <v>7</v>
       </c>
       <c r="AD14" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE14" s="13" t="s">
         <v>7</v>
       </c>
       <c r="AF14" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AG14" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AH14" s="13" t="s">
         <v>16</v>
@@ -4565,7 +4565,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="103"/>
       <c r="B15" s="133"/>
       <c r="C15" s="133"/>
@@ -4606,10 +4606,10 @@
         <v>2</v>
       </c>
       <c r="T15" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V15" s="13">
         <v>1</v>
@@ -4630,22 +4630,22 @@
         <v>3</v>
       </c>
       <c r="AB15" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC15" s="13">
         <v>3</v>
       </c>
       <c r="AD15" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE15" s="13">
         <v>2</v>
       </c>
       <c r="AF15" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG15" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH15" s="13">
         <v>2</v>
@@ -4691,7 +4691,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="103"/>
       <c r="B16" s="132">
         <v>46197</v>
@@ -4781,10 +4781,10 @@
         <v>16</v>
       </c>
       <c r="AF16" s="18" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AG16" s="18" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AH16" s="18" t="s">
         <v>15</v>
@@ -4830,7 +4830,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="103"/>
       <c r="B17" s="133"/>
       <c r="C17" s="133"/>
@@ -4871,10 +4871,10 @@
         <v>2</v>
       </c>
       <c r="T17" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U17" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V17" s="18">
         <v>2</v>
@@ -4907,10 +4907,10 @@
         <v>4</v>
       </c>
       <c r="AF17" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG17" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH17" s="18">
         <v>3</v>
@@ -4956,7 +4956,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="103"/>
       <c r="B18" s="132">
         <v>46197</v>
@@ -5010,10 +5010,10 @@
         <v>15</v>
       </c>
       <c r="T18" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U18" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V18" s="13" t="s">
         <v>15</v>
@@ -5095,7 +5095,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="104"/>
       <c r="B19" s="133"/>
       <c r="C19" s="133"/>
@@ -5136,10 +5136,10 @@
         <v>3</v>
       </c>
       <c r="T19" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U19" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V19" s="13">
         <v>2</v>
@@ -5160,13 +5160,13 @@
         <v>2</v>
       </c>
       <c r="AB19" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC19" s="13">
+        <v>3</v>
+      </c>
+      <c r="AD19" s="13">
         <v>1</v>
-      </c>
-      <c r="AD19" s="13">
-        <v>2</v>
       </c>
       <c r="AE19" s="13">
         <v>2</v>
@@ -5221,7 +5221,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="114" t="s">
         <v>2</v>
       </c>
@@ -5305,10 +5305,10 @@
         <v>7</v>
       </c>
       <c r="AB20" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AC20" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AD20" s="19" t="s">
         <v>7</v>
@@ -5366,7 +5366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="115"/>
       <c r="B21" s="131"/>
       <c r="C21" s="131"/>
@@ -5407,10 +5407,10 @@
         <v>3</v>
       </c>
       <c r="T21" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U21" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V21" s="19">
         <v>2</v>
@@ -5431,22 +5431,22 @@
         <v>3</v>
       </c>
       <c r="AB21" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC21" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD21" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE21" s="19">
         <v>1</v>
       </c>
       <c r="AF21" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG21" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH21" s="19">
         <v>1</v>
@@ -5492,7 +5492,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="115"/>
       <c r="B22" s="130">
         <v>46186</v>
@@ -5635,7 +5635,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="115"/>
       <c r="B23" s="131"/>
       <c r="C23" s="131"/>
@@ -5676,10 +5676,10 @@
         <v>3</v>
       </c>
       <c r="T23" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U23" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V23" s="13">
         <v>2</v>
@@ -5712,10 +5712,10 @@
         <v>2</v>
       </c>
       <c r="AF23" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG23" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH23" s="13">
         <v>2</v>
@@ -5761,7 +5761,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="115"/>
       <c r="B24" s="130">
         <v>46191</v>
@@ -5839,22 +5839,22 @@
         <v>7</v>
       </c>
       <c r="AB24" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AC24" s="19" t="s">
         <v>7</v>
       </c>
       <c r="AD24" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE24" s="19" t="s">
         <v>7</v>
       </c>
       <c r="AF24" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AG24" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AH24" s="19" t="s">
         <v>7</v>
@@ -5900,7 +5900,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="115"/>
       <c r="B25" s="131"/>
       <c r="C25" s="131"/>
@@ -5965,22 +5965,22 @@
         <v>4</v>
       </c>
       <c r="AB25" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC25" s="19">
         <v>2</v>
       </c>
       <c r="AD25" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE25" s="19">
         <v>3</v>
       </c>
       <c r="AF25" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG25" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH25" s="19">
         <v>3</v>
@@ -6026,7 +6026,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="115"/>
       <c r="B26" s="130">
         <v>46191</v>
@@ -6165,7 +6165,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="115"/>
       <c r="B27" s="131"/>
       <c r="C27" s="131"/>
@@ -6206,10 +6206,10 @@
         <v>3</v>
       </c>
       <c r="T27" s="13">
+        <v>2</v>
+      </c>
+      <c r="U27" s="13">
         <v>1</v>
-      </c>
-      <c r="U27" s="13">
-        <v>2</v>
       </c>
       <c r="V27" s="13">
         <v>2</v>
@@ -6230,22 +6230,22 @@
         <v>1</v>
       </c>
       <c r="AB27" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC27" s="13">
         <v>2</v>
       </c>
       <c r="AD27" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE27" s="13">
         <v>2</v>
       </c>
       <c r="AF27" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG27" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH27" s="13">
         <v>3</v>
@@ -6291,7 +6291,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="115"/>
       <c r="B28" s="130">
         <v>46197</v>
@@ -6345,10 +6345,10 @@
         <v>15</v>
       </c>
       <c r="T28" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="U28" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="V28" s="19" t="s">
         <v>16</v>
@@ -6430,7 +6430,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="115"/>
       <c r="B29" s="131"/>
       <c r="C29" s="131"/>
@@ -6556,7 +6556,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="115"/>
       <c r="B30" s="130">
         <v>46197</v>
@@ -6610,10 +6610,10 @@
         <v>16</v>
       </c>
       <c r="T30" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="U30" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="V30" s="13" t="s">
         <v>16</v>
@@ -6695,7 +6695,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="116"/>
       <c r="B31" s="131"/>
       <c r="C31" s="131"/>
@@ -6736,10 +6736,10 @@
         <v>2</v>
       </c>
       <c r="T31" s="13">
+        <v>2</v>
+      </c>
+      <c r="U31" s="13">
         <v>1</v>
-      </c>
-      <c r="U31" s="13">
-        <v>2</v>
       </c>
       <c r="V31" s="13">
         <v>1</v>
@@ -6760,13 +6760,13 @@
         <v>2</v>
       </c>
       <c r="AB31" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC31" s="13">
         <v>3</v>
       </c>
       <c r="AD31" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE31" s="13">
         <v>2</v>
@@ -6817,7 +6817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="125" t="s">
         <v>3</v>
       </c>
@@ -6958,7 +6958,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="103"/>
       <c r="B33" s="133"/>
       <c r="C33" s="133"/>
@@ -7023,10 +7023,10 @@
         <v>3</v>
       </c>
       <c r="AB33" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC33" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD33" s="18">
         <v>2</v>
@@ -7035,10 +7035,10 @@
         <v>4</v>
       </c>
       <c r="AF33" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG33" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH33" s="18">
         <v>3</v>
@@ -7080,7 +7080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="103"/>
       <c r="B34" s="132">
         <v>46186</v>
@@ -7138,10 +7138,10 @@
         <v>16</v>
       </c>
       <c r="T34" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U34" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V34" s="13" t="s">
         <v>16</v>
@@ -7219,7 +7219,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="103"/>
       <c r="B35" s="133"/>
       <c r="C35" s="133"/>
@@ -7260,10 +7260,10 @@
         <v>2</v>
       </c>
       <c r="T35" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U35" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V35" s="13">
         <v>2</v>
@@ -7284,22 +7284,22 @@
         <v>1</v>
       </c>
       <c r="AB35" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC35" s="13">
         <v>3</v>
       </c>
       <c r="AD35" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE35" s="13">
         <v>3</v>
       </c>
       <c r="AF35" s="13">
+        <v>2</v>
+      </c>
+      <c r="AG35" s="13">
         <v>1</v>
-      </c>
-      <c r="AG35" s="13">
-        <v>2</v>
       </c>
       <c r="AH35" s="13">
         <v>3</v>
@@ -7341,7 +7341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="103"/>
       <c r="B36" s="132">
         <v>46192</v>
@@ -7476,7 +7476,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="103"/>
       <c r="B37" s="133"/>
       <c r="C37" s="133"/>
@@ -7541,13 +7541,13 @@
         <v>5</v>
       </c>
       <c r="AB37" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC37" s="18">
         <v>4</v>
       </c>
       <c r="AD37" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE37" s="18">
         <v>3</v>
@@ -7598,7 +7598,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="103"/>
       <c r="B38" s="132">
         <v>46192</v>
@@ -7652,10 +7652,10 @@
         <v>16</v>
       </c>
       <c r="T38" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="U38" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="V38" s="13" t="s">
         <v>15</v>
@@ -7676,13 +7676,13 @@
         <v>15</v>
       </c>
       <c r="AB38" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC38" s="13" t="s">
         <v>16</v>
       </c>
       <c r="AD38" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE38" s="13" t="s">
         <v>15</v>
@@ -7733,7 +7733,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="103"/>
       <c r="B39" s="133"/>
       <c r="C39" s="133"/>
@@ -7774,10 +7774,10 @@
         <v>2</v>
       </c>
       <c r="T39" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U39" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V39" s="13">
         <v>2</v>
@@ -7798,22 +7798,22 @@
         <v>3</v>
       </c>
       <c r="AB39" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC39" s="13">
         <v>2</v>
       </c>
       <c r="AD39" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE39" s="13">
         <v>2</v>
       </c>
       <c r="AF39" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG39" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH39" s="13">
         <v>3</v>
@@ -7855,7 +7855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="103"/>
       <c r="B40" s="139">
         <v>46197</v>
@@ -7909,10 +7909,10 @@
         <v>15</v>
       </c>
       <c r="T40" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U40" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V40" s="18" t="s">
         <v>15</v>
@@ -7990,7 +7990,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="103"/>
       <c r="B41" s="140"/>
       <c r="C41" s="140"/>
@@ -8031,10 +8031,10 @@
         <v>4</v>
       </c>
       <c r="T41" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U41" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V41" s="18">
         <v>2</v>
@@ -8055,22 +8055,22 @@
         <v>3</v>
       </c>
       <c r="AB41" s="18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC41" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD41" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE41" s="18">
         <v>3</v>
       </c>
       <c r="AF41" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG41" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH41" s="18">
         <v>3</v>
@@ -8112,7 +8112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="103"/>
       <c r="B42" s="132">
         <v>46197</v>
@@ -8247,7 +8247,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="104"/>
       <c r="B43" s="133"/>
       <c r="C43" s="133"/>
@@ -8288,10 +8288,10 @@
         <v>3</v>
       </c>
       <c r="T43" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U43" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V43" s="13">
         <v>3</v>
@@ -8369,7 +8369,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="114" t="s">
         <v>4</v>
       </c>
@@ -8453,22 +8453,22 @@
         <v>7</v>
       </c>
       <c r="AB44" s="19" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AC44" s="19" t="s">
         <v>7</v>
       </c>
       <c r="AD44" s="19" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AE44" s="19" t="s">
         <v>16</v>
       </c>
       <c r="AF44" s="19" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AG44" s="19" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AH44" s="19" t="s">
         <v>16</v>
@@ -8510,7 +8510,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="115"/>
       <c r="B45" s="131"/>
       <c r="C45" s="131"/>
@@ -8551,10 +8551,10 @@
         <v>4</v>
       </c>
       <c r="T45" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U45" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V45" s="19">
         <v>2</v>
@@ -8587,10 +8587,10 @@
         <v>2</v>
       </c>
       <c r="AF45" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG45" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH45" s="19">
         <v>4</v>
@@ -8632,7 +8632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="115"/>
       <c r="B46" s="130">
         <v>46186</v>
@@ -8714,10 +8714,10 @@
         <v>16</v>
       </c>
       <c r="AB46" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC46" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD46" s="13" t="s">
         <v>16</v>
@@ -8726,10 +8726,10 @@
         <v>16</v>
       </c>
       <c r="AF46" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG46" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH46" s="13" t="s">
         <v>15</v>
@@ -8771,7 +8771,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="115"/>
       <c r="B47" s="131"/>
       <c r="C47" s="131"/>
@@ -8812,10 +8812,10 @@
         <v>3</v>
       </c>
       <c r="T47" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U47" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V47" s="13">
         <v>2</v>
@@ -8836,10 +8836,10 @@
         <v>2</v>
       </c>
       <c r="AB47" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC47" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD47" s="13">
         <v>2</v>
@@ -8848,10 +8848,10 @@
         <v>4</v>
       </c>
       <c r="AF47" s="13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG47" s="13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH47" s="13">
         <v>3</v>
@@ -8893,7 +8893,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="115"/>
       <c r="B48" s="130">
         <v>46192</v>
@@ -8971,13 +8971,13 @@
         <v>16</v>
       </c>
       <c r="AB48" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AC48" s="19" t="s">
         <v>7</v>
       </c>
       <c r="AD48" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE48" s="19" t="s">
         <v>15</v>
@@ -9028,7 +9028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="115"/>
       <c r="B49" s="131"/>
       <c r="C49" s="131"/>
@@ -9069,10 +9069,10 @@
         <v>2</v>
       </c>
       <c r="T49" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U49" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V49" s="19">
         <v>2</v>
@@ -9093,22 +9093,22 @@
         <v>2</v>
       </c>
       <c r="AB49" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC49" s="19">
         <v>3</v>
       </c>
       <c r="AD49" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE49" s="19">
         <v>1</v>
       </c>
       <c r="AF49" s="19">
+        <v>2</v>
+      </c>
+      <c r="AG49" s="19">
         <v>1</v>
-      </c>
-      <c r="AG49" s="19">
-        <v>2</v>
       </c>
       <c r="AH49" s="19">
         <v>2</v>
@@ -9150,7 +9150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="115"/>
       <c r="B50" s="130">
         <v>46192</v>
@@ -9285,7 +9285,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="115"/>
       <c r="B51" s="131"/>
       <c r="C51" s="131"/>
@@ -9326,10 +9326,10 @@
         <v>3</v>
       </c>
       <c r="T51" s="13">
+        <v>2</v>
+      </c>
+      <c r="U51" s="13">
         <v>1</v>
-      </c>
-      <c r="U51" s="13">
-        <v>2</v>
       </c>
       <c r="V51" s="13">
         <v>2</v>
@@ -9407,7 +9407,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="115"/>
       <c r="B52" s="130">
         <v>46198</v>
@@ -9461,10 +9461,10 @@
         <v>15</v>
       </c>
       <c r="T52" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U52" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V52" s="19" t="s">
         <v>15</v>
@@ -9485,10 +9485,10 @@
         <v>15</v>
       </c>
       <c r="AB52" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC52" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD52" s="19" t="s">
         <v>15</v>
@@ -9497,10 +9497,10 @@
         <v>15</v>
       </c>
       <c r="AF52" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG52" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH52" s="19" t="s">
         <v>15</v>
@@ -9542,7 +9542,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="115"/>
       <c r="B53" s="131"/>
       <c r="C53" s="131"/>
@@ -9583,11 +9583,11 @@
         <v>3</v>
       </c>
       <c r="T53" s="19">
+        <v>2</v>
+      </c>
+      <c r="U53" s="19">
         <v>1</v>
       </c>
-      <c r="U53" s="19">
-        <v>2</v>
-      </c>
       <c r="V53" s="19">
         <v>2</v>
       </c>
@@ -9607,22 +9607,22 @@
         <v>2</v>
       </c>
       <c r="AB53" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC53" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD53" s="19">
+        <v>3</v>
+      </c>
+      <c r="AE53" s="19">
+        <v>2</v>
+      </c>
+      <c r="AF53" s="19">
         <v>1</v>
       </c>
-      <c r="AE53" s="19">
-        <v>2</v>
-      </c>
-      <c r="AF53" s="19">
-        <v>2</v>
-      </c>
       <c r="AG53" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH53" s="19">
         <v>2</v>
@@ -9664,7 +9664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="115"/>
       <c r="B54" s="128">
         <v>46198</v>
@@ -9718,10 +9718,10 @@
         <v>7</v>
       </c>
       <c r="T54" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="U54" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="V54" s="13" t="s">
         <v>7</v>
@@ -9742,10 +9742,10 @@
         <v>7</v>
       </c>
       <c r="AB54" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AC54" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AD54" s="13" t="s">
         <v>7</v>
@@ -9754,10 +9754,10 @@
         <v>7</v>
       </c>
       <c r="AF54" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AG54" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AH54" s="13" t="s">
         <v>7</v>
@@ -9799,7 +9799,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="116"/>
       <c r="B55" s="129"/>
       <c r="C55" s="129"/>
@@ -9840,10 +9840,10 @@
         <v>2</v>
       </c>
       <c r="T55" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U55" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V55" s="13">
         <v>2</v>
@@ -9876,10 +9876,10 @@
         <v>2</v>
       </c>
       <c r="AF55" s="13">
+        <v>2</v>
+      </c>
+      <c r="AG55" s="13">
         <v>1</v>
-      </c>
-      <c r="AG55" s="13">
-        <v>2</v>
       </c>
       <c r="AH55" s="13">
         <v>3</v>
@@ -9921,7 +9921,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="125" t="s">
         <v>16</v>
       </c>
@@ -10062,7 +10062,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="103"/>
       <c r="B57" s="133"/>
       <c r="C57" s="133"/>
@@ -10103,10 +10103,10 @@
         <v>4</v>
       </c>
       <c r="T57" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U57" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V57" s="18">
         <v>5</v>
@@ -10127,13 +10127,13 @@
         <v>3</v>
       </c>
       <c r="AB57" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC57" s="18">
         <v>4</v>
       </c>
       <c r="AD57" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE57" s="18">
         <v>5</v>
@@ -10184,7 +10184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="103"/>
       <c r="B58" s="132">
         <v>46187</v>
@@ -10242,10 +10242,10 @@
         <v>16</v>
       </c>
       <c r="T58" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U58" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V58" s="13" t="s">
         <v>16</v>
@@ -10266,22 +10266,22 @@
         <v>15</v>
       </c>
       <c r="AB58" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC58" s="13" t="s">
         <v>16</v>
       </c>
       <c r="AD58" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE58" s="13" t="s">
         <v>7</v>
       </c>
       <c r="AF58" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG58" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH58" s="13" t="s">
         <v>15</v>
@@ -10323,7 +10323,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="103"/>
       <c r="B59" s="133"/>
       <c r="C59" s="133"/>
@@ -10364,10 +10364,10 @@
         <v>2</v>
       </c>
       <c r="T59" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U59" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V59" s="13">
         <v>1</v>
@@ -10388,22 +10388,22 @@
         <v>3</v>
       </c>
       <c r="AB59" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC59" s="13">
         <v>2</v>
       </c>
       <c r="AD59" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE59" s="13">
         <v>3</v>
       </c>
       <c r="AF59" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG59" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH59" s="13">
         <v>3</v>
@@ -10445,7 +10445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="103"/>
       <c r="B60" s="132">
         <v>46193</v>
@@ -10580,7 +10580,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="103"/>
       <c r="B61" s="133"/>
       <c r="C61" s="133"/>
@@ -10621,10 +10621,10 @@
         <v>3</v>
       </c>
       <c r="T61" s="18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U61" s="18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V61" s="18">
         <v>3</v>
@@ -10645,10 +10645,10 @@
         <v>3</v>
       </c>
       <c r="AB61" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC61" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD61" s="18">
         <v>3</v>
@@ -10657,10 +10657,10 @@
         <v>4</v>
       </c>
       <c r="AF61" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG61" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH61" s="18">
         <v>3</v>
@@ -10702,7 +10702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="103"/>
       <c r="B62" s="132">
         <v>46193</v>
@@ -10837,7 +10837,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="103"/>
       <c r="B63" s="133"/>
       <c r="C63" s="133"/>
@@ -10878,10 +10878,10 @@
         <v>2</v>
       </c>
       <c r="T63" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U63" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V63" s="13">
         <v>2</v>
@@ -10905,19 +10905,19 @@
         <v>2</v>
       </c>
       <c r="AC63" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD63" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE63" s="13">
         <v>2</v>
       </c>
       <c r="AF63" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG63" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH63" s="13">
         <v>2</v>
@@ -10959,7 +10959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="103"/>
       <c r="B64" s="132">
         <v>46198</v>
@@ -11094,7 +11094,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="103"/>
       <c r="B65" s="133"/>
       <c r="C65" s="133"/>
@@ -11135,10 +11135,10 @@
         <v>4</v>
       </c>
       <c r="T65" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U65" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V65" s="18">
         <v>2</v>
@@ -11159,22 +11159,22 @@
         <v>2</v>
       </c>
       <c r="AB65" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC65" s="18">
         <v>3</v>
       </c>
       <c r="AD65" s="18">
+        <v>3</v>
+      </c>
+      <c r="AE65" s="18">
+        <v>4</v>
+      </c>
+      <c r="AF65" s="18">
         <v>1</v>
       </c>
-      <c r="AE65" s="18">
-        <v>4</v>
-      </c>
-      <c r="AF65" s="18">
-        <v>3</v>
-      </c>
       <c r="AG65" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH65" s="18">
         <v>3</v>
@@ -11216,7 +11216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="103"/>
       <c r="B66" s="132">
         <v>46198</v>
@@ -11270,10 +11270,10 @@
         <v>15</v>
       </c>
       <c r="T66" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U66" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V66" s="13" t="s">
         <v>15</v>
@@ -11294,22 +11294,22 @@
         <v>16</v>
       </c>
       <c r="AB66" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AC66" s="13" t="s">
         <v>15</v>
       </c>
       <c r="AD66" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AE66" s="13" t="s">
         <v>15</v>
       </c>
       <c r="AF66" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AG66" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AH66" s="13" t="s">
         <v>7</v>
@@ -11351,7 +11351,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="104"/>
       <c r="B67" s="133"/>
       <c r="C67" s="133"/>
@@ -11392,10 +11392,10 @@
         <v>3</v>
       </c>
       <c r="T67" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U67" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V67" s="13">
         <v>2</v>
@@ -11428,10 +11428,10 @@
         <v>3</v>
       </c>
       <c r="AF67" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG67" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH67" s="13">
         <v>2</v>
@@ -11473,7 +11473,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="114" t="s">
         <v>21</v>
       </c>
@@ -11533,10 +11533,10 @@
         <v>16</v>
       </c>
       <c r="T68" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U68" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V68" s="19" t="s">
         <v>7</v>
@@ -11614,7 +11614,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="115"/>
       <c r="B69" s="131"/>
       <c r="C69" s="131"/>
@@ -11655,10 +11655,10 @@
         <v>2</v>
       </c>
       <c r="T69" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U69" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V69" s="19">
         <v>2</v>
@@ -11679,13 +11679,13 @@
         <v>2</v>
       </c>
       <c r="AB69" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC69" s="19">
         <v>3</v>
       </c>
       <c r="AD69" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE69" s="19">
         <v>3</v>
@@ -11736,7 +11736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="115"/>
       <c r="B70" s="130">
         <v>46187</v>
@@ -11875,7 +11875,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="115"/>
       <c r="B71" s="131"/>
       <c r="C71" s="131"/>
@@ -11916,10 +11916,10 @@
         <v>2</v>
       </c>
       <c r="T71" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U71" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V71" s="13">
         <v>2</v>
@@ -11940,10 +11940,10 @@
         <v>2</v>
       </c>
       <c r="AB71" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC71" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD71" s="13">
         <v>2</v>
@@ -11952,10 +11952,10 @@
         <v>2</v>
       </c>
       <c r="AF71" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG71" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH71" s="13">
         <v>2</v>
@@ -11997,7 +11997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="115"/>
       <c r="B72" s="130">
         <v>46193</v>
@@ -12075,22 +12075,22 @@
         <v>7</v>
       </c>
       <c r="AB72" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AC72" s="19" t="s">
         <v>7</v>
       </c>
       <c r="AD72" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE72" s="19" t="s">
         <v>7</v>
       </c>
       <c r="AF72" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AG72" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AH72" s="19" t="s">
         <v>7</v>
@@ -12132,7 +12132,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="115"/>
       <c r="B73" s="131"/>
       <c r="C73" s="131"/>
@@ -12173,10 +12173,10 @@
         <v>3</v>
       </c>
       <c r="T73" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U73" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V73" s="19">
         <v>2</v>
@@ -12197,22 +12197,22 @@
         <v>3</v>
       </c>
       <c r="AB73" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC73" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD73" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE73" s="19">
         <v>3</v>
       </c>
       <c r="AF73" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG73" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH73" s="19">
         <v>3</v>
@@ -12254,7 +12254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="115"/>
       <c r="B74" s="130">
         <v>46193</v>
@@ -12344,10 +12344,10 @@
         <v>15</v>
       </c>
       <c r="AF74" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG74" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH74" s="13" t="s">
         <v>15</v>
@@ -12389,7 +12389,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="115"/>
       <c r="B75" s="131"/>
       <c r="C75" s="131"/>
@@ -12457,19 +12457,19 @@
         <v>2</v>
       </c>
       <c r="AC75" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD75" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE75" s="13">
         <v>3</v>
       </c>
       <c r="AF75" s="13">
+        <v>2</v>
+      </c>
+      <c r="AG75" s="13">
         <v>1</v>
-      </c>
-      <c r="AG75" s="13">
-        <v>2</v>
       </c>
       <c r="AH75" s="13">
         <v>3</v>
@@ -12511,7 +12511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="115"/>
       <c r="B76" s="130">
         <v>46198</v>
@@ -12589,10 +12589,10 @@
         <v>7</v>
       </c>
       <c r="AB76" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AC76" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AD76" s="19" t="s">
         <v>16</v>
@@ -12601,10 +12601,10 @@
         <v>7</v>
       </c>
       <c r="AF76" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG76" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH76" s="19" t="s">
         <v>16</v>
@@ -12646,7 +12646,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="115"/>
       <c r="B77" s="131"/>
       <c r="C77" s="131"/>
@@ -12687,10 +12687,10 @@
         <v>4</v>
       </c>
       <c r="T77" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U77" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V77" s="19">
         <v>1</v>
@@ -12711,10 +12711,10 @@
         <v>3</v>
       </c>
       <c r="AB77" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC77" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD77" s="19">
         <v>2</v>
@@ -12768,7 +12768,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="115"/>
       <c r="B78" s="130">
         <v>46198</v>
@@ -12903,7 +12903,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="116"/>
       <c r="B79" s="131"/>
       <c r="C79" s="131"/>
@@ -12944,10 +12944,10 @@
         <v>3</v>
       </c>
       <c r="T79" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U79" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V79" s="14">
         <v>2</v>
@@ -12968,22 +12968,22 @@
         <v>3</v>
       </c>
       <c r="AB79" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC79" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD79" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE79" s="14">
         <v>3</v>
       </c>
       <c r="AF79" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG79" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH79" s="14">
         <v>4</v>
@@ -13025,7 +13025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="125" t="s">
         <v>48</v>
       </c>
@@ -13085,10 +13085,10 @@
         <v>16</v>
       </c>
       <c r="T80" s="18" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="U80" s="18" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V80" s="18" t="s">
         <v>7</v>
@@ -13121,10 +13121,10 @@
         <v>15</v>
       </c>
       <c r="AF80" s="18" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AG80" s="18" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AH80" s="18" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="103"/>
       <c r="B81" s="133"/>
       <c r="C81" s="133"/>
@@ -13234,10 +13234,10 @@
         <v>1</v>
       </c>
       <c r="AC81" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD81" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE81" s="18">
         <v>3</v>
@@ -13288,7 +13288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="103"/>
       <c r="B82" s="132">
         <v>46188</v>
@@ -13346,10 +13346,10 @@
         <v>7</v>
       </c>
       <c r="T82" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="U82" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="V82" s="13" t="s">
         <v>7</v>
@@ -13427,7 +13427,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="103"/>
       <c r="B83" s="133"/>
       <c r="C83" s="133"/>
@@ -13492,22 +13492,22 @@
         <v>3</v>
       </c>
       <c r="AB83" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC83" s="13">
         <v>3</v>
       </c>
       <c r="AD83" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE83" s="13">
         <v>3</v>
       </c>
       <c r="AF83" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG83" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH83" s="13">
         <v>3</v>
@@ -13549,7 +13549,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="103"/>
       <c r="B84" s="132">
         <v>46194</v>
@@ -13603,10 +13603,10 @@
         <v>7</v>
       </c>
       <c r="T84" s="18" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="U84" s="18" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="V84" s="18" t="s">
         <v>7</v>
@@ -13684,7 +13684,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="85" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="103"/>
       <c r="B85" s="133"/>
       <c r="C85" s="133"/>
@@ -13749,22 +13749,22 @@
         <v>4</v>
       </c>
       <c r="AB85" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC85" s="18">
         <v>2</v>
       </c>
       <c r="AD85" s="18">
+        <v>2</v>
+      </c>
+      <c r="AE85" s="18">
+        <v>3</v>
+      </c>
+      <c r="AF85" s="18">
         <v>1</v>
       </c>
-      <c r="AE85" s="18">
-        <v>3</v>
-      </c>
-      <c r="AF85" s="18">
-        <v>3</v>
-      </c>
       <c r="AG85" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH85" s="18">
         <v>3</v>
@@ -13806,7 +13806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="103"/>
       <c r="B86" s="132">
         <v>46194</v>
@@ -13941,7 +13941,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="103"/>
       <c r="B87" s="133"/>
       <c r="C87" s="133"/>
@@ -13982,10 +13982,10 @@
         <v>2</v>
       </c>
       <c r="T87" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U87" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V87" s="13">
         <v>2</v>
@@ -14006,13 +14006,13 @@
         <v>1</v>
       </c>
       <c r="AB87" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC87" s="13">
         <v>2</v>
       </c>
       <c r="AD87" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE87" s="13">
         <v>2</v>
@@ -14063,7 +14063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="103"/>
       <c r="B88" s="132">
         <v>46199</v>
@@ -14117,10 +14117,10 @@
         <v>15</v>
       </c>
       <c r="T88" s="18" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="U88" s="18" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V88" s="18" t="s">
         <v>15</v>
@@ -14198,7 +14198,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="103"/>
       <c r="B89" s="133"/>
       <c r="C89" s="133"/>
@@ -14239,10 +14239,10 @@
         <v>3</v>
       </c>
       <c r="T89" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U89" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V89" s="18">
         <v>3</v>
@@ -14320,7 +14320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="103"/>
       <c r="B90" s="132">
         <v>46199</v>
@@ -14410,10 +14410,10 @@
         <v>16</v>
       </c>
       <c r="AF90" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AG90" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AH90" s="13" t="s">
         <v>16</v>
@@ -14455,7 +14455,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="91" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="104"/>
       <c r="B91" s="133"/>
       <c r="C91" s="133"/>
@@ -14520,13 +14520,13 @@
         <v>2</v>
       </c>
       <c r="AB91" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC91" s="13">
         <v>2</v>
       </c>
       <c r="AD91" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE91" s="13">
         <v>2</v>
@@ -14577,7 +14577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="114" t="s">
         <v>49</v>
       </c>
@@ -14718,7 +14718,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="115"/>
       <c r="B93" s="131"/>
       <c r="C93" s="131"/>
@@ -14759,10 +14759,10 @@
         <v>4</v>
       </c>
       <c r="T93" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U93" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V93" s="19">
         <v>3</v>
@@ -14783,22 +14783,22 @@
         <v>3</v>
       </c>
       <c r="AB93" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC93" s="19">
         <v>3</v>
       </c>
       <c r="AD93" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE93" s="19">
         <v>3</v>
       </c>
       <c r="AF93" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG93" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH93" s="19">
         <v>4</v>
@@ -14840,7 +14840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="115"/>
       <c r="B94" s="130">
         <v>46188</v>
@@ -14979,7 +14979,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="115"/>
       <c r="B95" s="131"/>
       <c r="C95" s="131"/>
@@ -15044,10 +15044,10 @@
         <v>2</v>
       </c>
       <c r="AB95" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC95" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD95" s="13">
         <v>2</v>
@@ -15056,10 +15056,10 @@
         <v>3</v>
       </c>
       <c r="AF95" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG95" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH95" s="13">
         <v>2</v>
@@ -15101,7 +15101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="115"/>
       <c r="B96" s="130">
         <v>46194</v>
@@ -15236,7 +15236,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="115"/>
       <c r="B97" s="131"/>
       <c r="C97" s="131"/>
@@ -15277,10 +15277,10 @@
         <v>4</v>
       </c>
       <c r="T97" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U97" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V97" s="19">
         <v>3</v>
@@ -15301,22 +15301,22 @@
         <v>4</v>
       </c>
       <c r="AB97" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC97" s="19">
         <v>3</v>
       </c>
       <c r="AD97" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE97" s="19">
         <v>3</v>
       </c>
       <c r="AF97" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG97" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH97" s="19">
         <v>4</v>
@@ -15358,7 +15358,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="115"/>
       <c r="B98" s="130">
         <v>46194</v>
@@ -15493,7 +15493,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="115"/>
       <c r="B99" s="131"/>
       <c r="C99" s="131"/>
@@ -15534,10 +15534,10 @@
         <v>3</v>
       </c>
       <c r="T99" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U99" s="13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V99" s="13">
         <v>3</v>
@@ -15558,22 +15558,22 @@
         <v>3</v>
       </c>
       <c r="AB99" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC99" s="13">
         <v>2</v>
       </c>
       <c r="AD99" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE99" s="13">
         <v>2</v>
       </c>
       <c r="AF99" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG99" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH99" s="13">
         <v>4</v>
@@ -15615,7 +15615,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="115"/>
       <c r="B100" s="130">
         <v>46199</v>
@@ -15693,10 +15693,10 @@
         <v>16</v>
       </c>
       <c r="AB100" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AC100" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AD100" s="19" t="s">
         <v>16</v>
@@ -15705,10 +15705,10 @@
         <v>15</v>
       </c>
       <c r="AF100" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG100" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH100" s="19" t="s">
         <v>15</v>
@@ -15750,7 +15750,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="115"/>
       <c r="B101" s="131"/>
       <c r="C101" s="131"/>
@@ -15815,10 +15815,10 @@
         <v>4</v>
       </c>
       <c r="AB101" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC101" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD101" s="19">
         <v>2</v>
@@ -15872,7 +15872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="115"/>
       <c r="B102" s="130">
         <v>46199</v>
@@ -15962,10 +15962,10 @@
         <v>15</v>
       </c>
       <c r="AF102" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AG102" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AH102" s="13" t="s">
         <v>16</v>
@@ -16007,7 +16007,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="103" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="116"/>
       <c r="B103" s="131"/>
       <c r="C103" s="131"/>
@@ -16048,10 +16048,10 @@
         <v>3</v>
       </c>
       <c r="T103" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U103" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V103" s="14">
         <v>2</v>
@@ -16072,22 +16072,22 @@
         <v>3</v>
       </c>
       <c r="AB103" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC103" s="14">
         <v>2</v>
       </c>
       <c r="AD103" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE103" s="14">
         <v>2</v>
       </c>
       <c r="AF103" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG103" s="14">
         <v>1</v>
-      </c>
-      <c r="AG103" s="14">
-        <v>0</v>
       </c>
       <c r="AH103" s="14">
         <v>2</v>
@@ -16129,7 +16129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="125" t="s">
         <v>50</v>
       </c>
@@ -16148,11 +16148,15 @@
       <c r="F104" s="111" t="s">
         <v>65</v>
       </c>
-      <c r="G104" s="113"/>
-      <c r="H104" s="113"/>
+      <c r="G104" s="113">
+        <v>3</v>
+      </c>
+      <c r="H104" s="113">
+        <v>1</v>
+      </c>
       <c r="I104" s="112" t="str">
         <f>IF(G104="","-",IF(G104&gt;H104,"L",IF(G104=H104,"E",IF(G104&lt;H104,"V"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="J104" s="23" t="s">
         <v>7</v>
@@ -16266,7 +16270,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="103"/>
       <c r="B105" s="133"/>
       <c r="C105" s="133"/>
@@ -16307,10 +16311,10 @@
         <v>4</v>
       </c>
       <c r="T105" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U105" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V105" s="18">
         <v>3</v>
@@ -16331,22 +16335,22 @@
         <v>3</v>
       </c>
       <c r="AB105" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC105" s="18">
         <v>3</v>
       </c>
       <c r="AD105" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE105" s="18">
         <v>4</v>
       </c>
       <c r="AF105" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG105" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH105" s="18">
         <v>4</v>
@@ -16388,7 +16392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="103"/>
       <c r="B106" s="132">
         <v>46189</v>
@@ -16523,7 +16527,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="103"/>
       <c r="B107" s="133"/>
       <c r="C107" s="133"/>
@@ -16564,10 +16568,10 @@
         <v>2</v>
       </c>
       <c r="T107" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U107" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V107" s="13">
         <v>2</v>
@@ -16588,22 +16592,22 @@
         <v>3</v>
       </c>
       <c r="AB107" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC107" s="13">
         <v>2</v>
       </c>
       <c r="AD107" s="13">
+        <v>2</v>
+      </c>
+      <c r="AE107" s="13">
+        <v>4</v>
+      </c>
+      <c r="AF107" s="13">
         <v>1</v>
       </c>
-      <c r="AE107" s="13">
-        <v>4</v>
-      </c>
-      <c r="AF107" s="13">
-        <v>3</v>
-      </c>
       <c r="AG107" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH107" s="13">
         <v>2</v>
@@ -16645,7 +16649,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="103"/>
       <c r="B108" s="132">
         <v>46195</v>
@@ -16780,7 +16784,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="103"/>
       <c r="B109" s="133"/>
       <c r="C109" s="133"/>
@@ -16821,10 +16825,10 @@
         <v>5</v>
       </c>
       <c r="T109" s="18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U109" s="18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V109" s="18">
         <v>3</v>
@@ -16848,19 +16852,19 @@
         <v>3</v>
       </c>
       <c r="AC109" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD109" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE109" s="18">
         <v>3</v>
       </c>
       <c r="AF109" s="18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG109" s="18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH109" s="18">
         <v>3</v>
@@ -16902,7 +16906,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="103"/>
       <c r="B110" s="132">
         <v>46195</v>
@@ -16980,22 +16984,22 @@
         <v>7</v>
       </c>
       <c r="AB110" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AC110" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AD110" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE110" s="13" t="s">
         <v>7</v>
       </c>
       <c r="AF110" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG110" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH110" s="13" t="s">
         <v>15</v>
@@ -17037,7 +17041,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="111" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="103"/>
       <c r="B111" s="133"/>
       <c r="C111" s="133"/>
@@ -17102,22 +17106,22 @@
         <v>3</v>
       </c>
       <c r="AB111" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC111" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD111" s="13">
+        <v>2</v>
+      </c>
+      <c r="AE111" s="13">
+        <v>4</v>
+      </c>
+      <c r="AF111" s="13">
         <v>1</v>
       </c>
-      <c r="AE111" s="13">
-        <v>4</v>
-      </c>
-      <c r="AF111" s="13">
-        <v>2</v>
-      </c>
       <c r="AG111" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH111" s="13">
         <v>2</v>
@@ -17159,7 +17163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="103"/>
       <c r="B112" s="132">
         <v>46199</v>
@@ -17294,7 +17298,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="113" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="103"/>
       <c r="B113" s="133"/>
       <c r="C113" s="133"/>
@@ -17359,22 +17363,22 @@
         <v>3</v>
       </c>
       <c r="AB113" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC113" s="18">
         <v>3</v>
       </c>
       <c r="AD113" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE113" s="18">
         <v>3</v>
       </c>
       <c r="AF113" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG113" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH113" s="18">
         <v>3</v>
@@ -17416,7 +17420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="103"/>
       <c r="B114" s="132">
         <v>46199</v>
@@ -17470,10 +17474,10 @@
         <v>16</v>
       </c>
       <c r="T114" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="U114" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="V114" s="13" t="s">
         <v>7</v>
@@ -17494,22 +17498,22 @@
         <v>16</v>
       </c>
       <c r="AB114" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AC114" s="13" t="s">
         <v>7</v>
       </c>
       <c r="AD114" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE114" s="13" t="s">
         <v>7</v>
       </c>
       <c r="AF114" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AG114" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AH114" s="13" t="s">
         <v>16</v>
@@ -17551,7 +17555,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="104"/>
       <c r="B115" s="133"/>
       <c r="C115" s="133"/>
@@ -17592,11 +17596,11 @@
         <v>4</v>
       </c>
       <c r="T115" s="13">
+        <v>4</v>
+      </c>
+      <c r="U115" s="13">
         <v>1</v>
       </c>
-      <c r="U115" s="13">
-        <v>4</v>
-      </c>
       <c r="V115" s="13">
         <v>2</v>
       </c>
@@ -17616,23 +17620,23 @@
         <v>2</v>
       </c>
       <c r="AB115" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC115" s="13">
         <v>2</v>
       </c>
       <c r="AD115" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE115" s="13">
         <v>3</v>
       </c>
       <c r="AF115" s="13">
+        <v>4</v>
+      </c>
+      <c r="AG115" s="13">
         <v>1</v>
       </c>
-      <c r="AG115" s="13">
-        <v>4</v>
-      </c>
       <c r="AH115" s="13">
         <v>4</v>
       </c>
@@ -17673,7 +17677,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="114" t="s">
         <v>51</v>
       </c>
@@ -17810,7 +17814,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="115"/>
       <c r="B117" s="131"/>
       <c r="C117" s="131"/>
@@ -17875,10 +17879,10 @@
         <v>1</v>
       </c>
       <c r="AB117" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC117" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD117" s="19">
         <v>3</v>
@@ -17932,7 +17936,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="115"/>
       <c r="B118" s="130">
         <v>46189</v>
@@ -18010,13 +18014,13 @@
         <v>15</v>
       </c>
       <c r="AB118" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AC118" s="13" t="s">
         <v>7</v>
       </c>
       <c r="AD118" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE118" s="13" t="s">
         <v>7</v>
@@ -18067,7 +18071,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="115"/>
       <c r="B119" s="131"/>
       <c r="C119" s="131"/>
@@ -18108,11 +18112,11 @@
         <v>4</v>
       </c>
       <c r="T119" s="13">
+        <v>2</v>
+      </c>
+      <c r="U119" s="13">
         <v>1</v>
       </c>
-      <c r="U119" s="13">
-        <v>2</v>
-      </c>
       <c r="V119" s="13">
         <v>2</v>
       </c>
@@ -18135,19 +18139,19 @@
         <v>2</v>
       </c>
       <c r="AC119" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD119" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE119" s="13">
         <v>3</v>
       </c>
       <c r="AF119" s="13">
+        <v>2</v>
+      </c>
+      <c r="AG119" s="13">
         <v>1</v>
-      </c>
-      <c r="AG119" s="13">
-        <v>2</v>
       </c>
       <c r="AH119" s="13">
         <v>3</v>
@@ -18189,7 +18193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="115"/>
       <c r="B120" s="130">
         <v>46195</v>
@@ -18324,7 +18328,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="115"/>
       <c r="B121" s="131"/>
       <c r="C121" s="131"/>
@@ -18365,10 +18369,10 @@
         <v>4</v>
       </c>
       <c r="T121" s="19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U121" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V121" s="19">
         <v>2</v>
@@ -18389,22 +18393,22 @@
         <v>2</v>
       </c>
       <c r="AB121" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC121" s="19">
         <v>3</v>
       </c>
       <c r="AD121" s="19">
+        <v>3</v>
+      </c>
+      <c r="AE121" s="19">
+        <v>2</v>
+      </c>
+      <c r="AF121" s="19">
         <v>1</v>
       </c>
-      <c r="AE121" s="19">
-        <v>2</v>
-      </c>
-      <c r="AF121" s="19">
-        <v>4</v>
-      </c>
       <c r="AG121" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH121" s="19">
         <v>3</v>
@@ -18446,7 +18450,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="115"/>
       <c r="B122" s="130">
         <v>46195</v>
@@ -18500,10 +18504,10 @@
         <v>16</v>
       </c>
       <c r="T122" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U122" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V122" s="13" t="s">
         <v>16</v>
@@ -18536,10 +18540,10 @@
         <v>16</v>
       </c>
       <c r="AF122" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG122" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH122" s="13" t="s">
         <v>16</v>
@@ -18581,7 +18585,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="115"/>
       <c r="B123" s="131"/>
       <c r="C123" s="131"/>
@@ -18622,10 +18626,10 @@
         <v>4</v>
       </c>
       <c r="T123" s="13">
+        <v>2</v>
+      </c>
+      <c r="U123" s="13">
         <v>1</v>
-      </c>
-      <c r="U123" s="13">
-        <v>2</v>
       </c>
       <c r="V123" s="13">
         <v>1</v>
@@ -18646,22 +18650,22 @@
         <v>2</v>
       </c>
       <c r="AB123" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC123" s="13">
         <v>2</v>
       </c>
       <c r="AD123" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE123" s="13">
         <v>2</v>
       </c>
       <c r="AF123" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG123" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH123" s="13">
         <v>2</v>
@@ -18703,7 +18707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="115"/>
       <c r="B124" s="130">
         <v>46200</v>
@@ -18838,7 +18842,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="125" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="115"/>
       <c r="B125" s="131"/>
       <c r="C125" s="131"/>
@@ -18879,10 +18883,10 @@
         <v>3</v>
       </c>
       <c r="T125" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U125" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V125" s="19">
         <v>3</v>
@@ -18960,7 +18964,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="115"/>
       <c r="B126" s="130">
         <v>46200</v>
@@ -19014,10 +19018,10 @@
         <v>15</v>
       </c>
       <c r="T126" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U126" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V126" s="13" t="s">
         <v>16</v>
@@ -19041,19 +19045,19 @@
         <v>16</v>
       </c>
       <c r="AC126" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD126" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE126" s="13" t="s">
         <v>15</v>
       </c>
       <c r="AF126" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG126" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH126" s="13" t="s">
         <v>15</v>
@@ -19095,7 +19099,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="127" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="116"/>
       <c r="B127" s="131"/>
       <c r="C127" s="131"/>
@@ -19136,10 +19140,10 @@
         <v>3</v>
       </c>
       <c r="T127" s="14">
+        <v>2</v>
+      </c>
+      <c r="U127" s="14">
         <v>1</v>
-      </c>
-      <c r="U127" s="14">
-        <v>2</v>
       </c>
       <c r="V127" s="14">
         <v>2</v>
@@ -19172,10 +19176,10 @@
         <v>2</v>
       </c>
       <c r="AF127" s="14">
+        <v>2</v>
+      </c>
+      <c r="AG127" s="14">
         <v>1</v>
-      </c>
-      <c r="AG127" s="14">
-        <v>2</v>
       </c>
       <c r="AH127" s="14">
         <v>3</v>
@@ -19217,7 +19221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="125" t="s">
         <v>52</v>
       </c>
@@ -19354,7 +19358,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="103"/>
       <c r="B129" s="133"/>
       <c r="C129" s="133"/>
@@ -19395,10 +19399,10 @@
         <v>3</v>
       </c>
       <c r="T129" s="18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U129" s="18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V129" s="18">
         <v>3</v>
@@ -19476,7 +19480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="103"/>
       <c r="B130" s="132">
         <v>46190</v>
@@ -19611,7 +19615,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="103"/>
       <c r="B131" s="133"/>
       <c r="C131" s="133"/>
@@ -19652,10 +19656,10 @@
         <v>4</v>
       </c>
       <c r="T131" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U131" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V131" s="13">
         <v>3</v>
@@ -19676,22 +19680,22 @@
         <v>3</v>
       </c>
       <c r="AB131" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC131" s="13">
         <v>2</v>
       </c>
       <c r="AD131" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE131" s="13">
         <v>2</v>
       </c>
       <c r="AF131" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG131" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH131" s="13">
         <v>4</v>
@@ -19733,7 +19737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="103"/>
       <c r="B132" s="132">
         <v>46196</v>
@@ -19868,7 +19872,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="133" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="103"/>
       <c r="B133" s="133"/>
       <c r="C133" s="133"/>
@@ -19909,10 +19913,10 @@
         <v>4</v>
       </c>
       <c r="T133" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U133" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V133" s="18">
         <v>2</v>
@@ -19936,19 +19940,19 @@
         <v>2</v>
       </c>
       <c r="AC133" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD133" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE133" s="18">
         <v>3</v>
       </c>
       <c r="AF133" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG133" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH133" s="18">
         <v>2</v>
@@ -19990,7 +19994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="103"/>
       <c r="B134" s="132">
         <v>46196</v>
@@ -20071,10 +20075,10 @@
         <v>7</v>
       </c>
       <c r="AC134" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AD134" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AE134" s="13" t="s">
         <v>7</v>
@@ -20125,7 +20129,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="135" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="103"/>
       <c r="B135" s="133"/>
       <c r="C135" s="133"/>
@@ -20166,10 +20170,10 @@
         <v>3</v>
       </c>
       <c r="T135" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U135" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V135" s="13">
         <v>2</v>
@@ -20190,22 +20194,22 @@
         <v>3</v>
       </c>
       <c r="AB135" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC135" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD135" s="13">
+        <v>3</v>
+      </c>
+      <c r="AE135" s="13">
+        <v>3</v>
+      </c>
+      <c r="AF135" s="13">
         <v>1</v>
       </c>
-      <c r="AE135" s="13">
-        <v>3</v>
-      </c>
-      <c r="AF135" s="13">
-        <v>2</v>
-      </c>
       <c r="AG135" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH135" s="13">
         <v>2</v>
@@ -20247,7 +20251,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="103"/>
       <c r="B136" s="132">
         <v>46200</v>
@@ -20301,10 +20305,10 @@
         <v>16</v>
       </c>
       <c r="T136" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U136" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V136" s="18" t="s">
         <v>15</v>
@@ -20325,22 +20329,22 @@
         <v>16</v>
       </c>
       <c r="AB136" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC136" s="18" t="s">
         <v>15</v>
       </c>
       <c r="AD136" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE136" s="18" t="s">
         <v>15</v>
       </c>
       <c r="AF136" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG136" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH136" s="18" t="s">
         <v>16</v>
@@ -20382,7 +20386,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="137" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="103"/>
       <c r="B137" s="133"/>
       <c r="C137" s="133"/>
@@ -20423,10 +20427,10 @@
         <v>4</v>
       </c>
       <c r="T137" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U137" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V137" s="18">
         <v>2</v>
@@ -20447,13 +20451,13 @@
         <v>4</v>
       </c>
       <c r="AB137" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC137" s="18">
         <v>3</v>
       </c>
       <c r="AD137" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE137" s="18">
         <v>3</v>
@@ -20504,7 +20508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="103"/>
       <c r="B138" s="132">
         <v>46200</v>
@@ -20585,19 +20589,19 @@
         <v>16</v>
       </c>
       <c r="AC138" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AD138" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE138" s="13" t="s">
         <v>16</v>
       </c>
       <c r="AF138" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG138" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH138" s="13" t="s">
         <v>16</v>
@@ -20639,7 +20643,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="139" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="104"/>
       <c r="B139" s="133"/>
       <c r="C139" s="133"/>
@@ -20680,11 +20684,11 @@
         <v>3</v>
       </c>
       <c r="T139" s="13">
+        <v>3</v>
+      </c>
+      <c r="U139" s="13">
         <v>1</v>
       </c>
-      <c r="U139" s="13">
-        <v>3</v>
-      </c>
       <c r="V139" s="13">
         <v>2</v>
       </c>
@@ -20716,10 +20720,10 @@
         <v>2</v>
       </c>
       <c r="AF139" s="13">
+        <v>2</v>
+      </c>
+      <c r="AG139" s="13">
         <v>1</v>
-      </c>
-      <c r="AG139" s="13">
-        <v>2</v>
       </c>
       <c r="AH139" s="13">
         <v>2</v>
@@ -20761,7 +20765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="114" t="s">
         <v>7</v>
       </c>
@@ -20817,10 +20821,10 @@
         <v>16</v>
       </c>
       <c r="T140" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="U140" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="V140" s="19" t="s">
         <v>7</v>
@@ -20841,10 +20845,10 @@
         <v>15</v>
       </c>
       <c r="AB140" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AC140" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AD140" s="19" t="s">
         <v>7</v>
@@ -20853,10 +20857,10 @@
         <v>16</v>
       </c>
       <c r="AF140" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AG140" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AH140" s="19" t="s">
         <v>7</v>
@@ -20898,7 +20902,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="141" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="115"/>
       <c r="B141" s="131"/>
       <c r="C141" s="131"/>
@@ -20939,10 +20943,10 @@
         <v>4</v>
       </c>
       <c r="T141" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U141" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V141" s="19">
         <v>2</v>
@@ -20963,22 +20967,22 @@
         <v>3</v>
       </c>
       <c r="AB141" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC141" s="19">
         <v>2</v>
       </c>
       <c r="AD141" s="19">
+        <v>2</v>
+      </c>
+      <c r="AE141" s="19">
+        <v>4</v>
+      </c>
+      <c r="AF141" s="19">
         <v>1</v>
       </c>
-      <c r="AE141" s="19">
-        <v>4</v>
-      </c>
-      <c r="AF141" s="19">
-        <v>2</v>
-      </c>
       <c r="AG141" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH141" s="19">
         <v>3</v>
@@ -21020,7 +21024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="115"/>
       <c r="B142" s="130">
         <v>46190</v>
@@ -21155,7 +21159,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="143" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="115"/>
       <c r="B143" s="131"/>
       <c r="C143" s="131"/>
@@ -21196,10 +21200,10 @@
         <v>3</v>
       </c>
       <c r="T143" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U143" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V143" s="13">
         <v>2</v>
@@ -21223,19 +21227,19 @@
         <v>1</v>
       </c>
       <c r="AC143" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD143" s="13">
+        <v>3</v>
+      </c>
+      <c r="AE143" s="13">
+        <v>3</v>
+      </c>
+      <c r="AF143" s="13">
         <v>1</v>
       </c>
-      <c r="AE143" s="13">
-        <v>3</v>
-      </c>
-      <c r="AF143" s="13">
-        <v>2</v>
-      </c>
       <c r="AG143" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH143" s="13">
         <v>1</v>
@@ -21277,7 +21281,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="115"/>
       <c r="B144" s="130">
         <v>46196</v>
@@ -21412,7 +21416,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="145" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="115"/>
       <c r="B145" s="131"/>
       <c r="C145" s="131"/>
@@ -21477,10 +21481,10 @@
         <v>1</v>
       </c>
       <c r="AB145" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC145" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD145" s="19">
         <v>3</v>
@@ -21534,7 +21538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="115"/>
       <c r="B146" s="130">
         <v>46196</v>
@@ -21588,10 +21592,10 @@
         <v>15</v>
       </c>
       <c r="T146" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U146" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V146" s="13" t="s">
         <v>16</v>
@@ -21669,7 +21673,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="115"/>
       <c r="B147" s="131"/>
       <c r="C147" s="131"/>
@@ -21734,22 +21738,22 @@
         <v>3</v>
       </c>
       <c r="AB147" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC147" s="13">
         <v>2</v>
       </c>
       <c r="AD147" s="13">
+        <v>2</v>
+      </c>
+      <c r="AE147" s="13">
+        <v>4</v>
+      </c>
+      <c r="AF147" s="13">
         <v>1</v>
       </c>
-      <c r="AE147" s="13">
-        <v>4</v>
-      </c>
-      <c r="AF147" s="13">
-        <v>2</v>
-      </c>
       <c r="AG147" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH147" s="13">
         <v>2</v>
@@ -21791,7 +21795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="115"/>
       <c r="B148" s="130">
         <v>46200</v>
@@ -21926,7 +21930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="115"/>
       <c r="B149" s="131"/>
       <c r="C149" s="131"/>
@@ -21967,10 +21971,10 @@
         <v>3</v>
       </c>
       <c r="T149" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U149" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V149" s="19">
         <v>2</v>
@@ -22048,7 +22052,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="115"/>
       <c r="B150" s="130">
         <v>46200</v>
@@ -22183,7 +22187,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="151" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="116"/>
       <c r="B151" s="131"/>
       <c r="C151" s="131"/>
@@ -22224,10 +22228,10 @@
         <v>3</v>
       </c>
       <c r="T151" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U151" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V151" s="14">
         <v>2</v>
@@ -22248,10 +22252,10 @@
         <v>3</v>
       </c>
       <c r="AB151" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC151" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD151" s="14">
         <v>2</v>
@@ -22305,7 +22309,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F152" s="134" t="s">
         <v>10</v>
       </c>
@@ -22357,11 +22361,11 @@
       </c>
       <c r="T152" s="15">
         <f>SUM(T79,T77,T75,T73,T71,T69,T67,T65,T63,T61,T59,T57,T55,T53,T51,T49,T47,T45,T43,T41,T39,T37,T35,T33,T31,T29,T27,T25,T23,T21,T19,T17,T15,T13,T11,T9,T81,T83,T85,T87,T89,T91,T93,T95,T97,T99,T101,T103,T105,T107,T109,T111,T113,T115,T117,T119,T121,T123,T125,T127,T129,T131,T133,T135,T137,T139,T141,T143,T145,T147,T149,T151)</f>
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="U152" s="15">
         <f>SUM(U79,U77,U75,U73,U71,U69,U67,U65,U63,U61,U59,U57,U55,U53,U51,U49,U47,U45,U43,U41,U39,U37,U35,U33,U31,U29,U27,U25,U23,U21,U19,U17,U15,U13,U11,U9,U81,U83,U85,U87,U89,U91,U93,U95,U97,U99,U101,U103,U105,U107,U109,U111,U113,U115,U117,U119,U121,U123,U125,U127,U129,U131,U133,U135,U137,U139,U141,U143,U145,U147,U149,U151)</f>
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="V152" s="15">
         <f>SUM(V79,V77,V75,V73,V71,V69,V67,V65,V63,V61,V59,V57,V55,V53,V51,V49,V47,V45,V43,V41,V39,V37,V35,V33,V31,V29,V27,V25,V23,V21,V19,V17,V15,V13,V11,V9,V81,V83,V85,V87,V89,V91,V93,V95,V97,V99,V101,V103,V105,V107,V109,V111,V113,V115,V117,V119,V121,V123,V125,V127,V129,V131,V133,V135,V137,V139,V141,V143,V145,V147,V149,V151)</f>
@@ -22389,7 +22393,7 @@
       </c>
       <c r="AB152" s="15">
         <f>SUM(AB79,AB77,AB75,AB73,AB71,AB69,AB67,AB65,AB63,AB61,AB59,AB57,AB55,AB53,AB51,AB49,AB47,AB45,AB43,AB41,AB39,AB37,AB35,AB33,AB31,AB29,AB27,AB25,AB23,AB21,AB19,AB17,AB15,AB13,AB11,AB9,AB81,AB83,AB85,AB87,AB89,AB91,AB93,AB95,AB97,AB99,AB101,AB103,AB105,AB107,AB109,AB111,AB113,AB115,AB117,AB119,AB121,AB123,AB125,AB127,AB129,AB131,AB133,AB135,AB137,AB139,AB141,AB143,AB145,AB147,AB149,AB151)</f>
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="AC152" s="15">
         <f>SUM(AC79,AC77,AC75,AC73,AC71,AC69,AC67,AC65,AC63,AC61,AC59,AC57,AC55,AC53,AC51,AC49,AC47,AC45,AC43,AC41,AC39,AC37,AC35,AC33,AC31,AC29,AC27,AC25,AC23,AC21,AC19,AC17,AC15,AC13,AC11,AC9,AC81,AC83,AC85,AC87,AC89,AC91,AC93,AC95,AC97,AC99,AC101,AC103,AC105,AC107,AC109,AC111,AC113,AC115,AC117,AC119,AC121,AC123,AC125,AC127,AC129,AC131,AC133,AC135,AC137,AC139,AC141,AC143,AC145,AC147,AC149,AC151)</f>
@@ -22397,7 +22401,7 @@
       </c>
       <c r="AD152" s="15">
         <f>SUM(AD79,AD77,AD75,AD73,AD71,AD69,AD67,AD65,AD63,AD61,AD59,AD57,AD55,AD53,AD51,AD49,AD47,AD45,AD43,AD41,AD39,AD37,AD35,AD33,AD31,AD29,AD27,AD25,AD23,AD21,AD19,AD17,AD15,AD13,AD11,AD9,AD81,AD83,AD85,AD87,AD89,AD91,AD93,AD95,AD97,AD99,AD101,AD103,AD105,AD107,AD109,AD111,AD113,AD115,AD117,AD119,AD121,AD123,AD125,AD127,AD129,AD131,AD133,AD135,AD137,AD139,AD141,AD143,AD145,AD147,AD149,AD151)</f>
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="AE152" s="15">
         <f>SUM(AE79,AE77,AE75,AE73,AE71,AE69,AE67,AE65,AE63,AE61,AE59,AE57,AE55,AE53,AE51,AE49,AE47,AE45,AE43,AE41,AE39,AE37,AE35,AE33,AE31,AE29,AE27,AE25,AE23,AE21,AE19,AE17,AE15,AE13,AE11,AE9,AE81,AE83,AE85,AE87,AE89,AE91,AE93,AE95,AE97,AE99,AE101,AE103,AE105,AE107,AE109,AE111,AE113,AE115,AE117,AE119,AE121,AE123,AE125,AE127,AE129,AE131,AE133,AE135,AE137,AE139,AE141,AE143,AE145,AE147,AE149,AE151)</f>
@@ -22405,11 +22409,11 @@
       </c>
       <c r="AF152" s="15">
         <f>SUM(AF79,AF77,AF75,AF73,AF71,AF69,AF67,AF65,AF63,AF61,AF59,AF57,AF55,AF53,AF51,AF49,AF47,AF45,AF43,AF41,AF39,AF37,AF35,AF33,AF31,AF29,AF27,AF25,AF23,AF21,AF19,AF17,AF15,AF13,AF11,AF9,AF81,AF83,AF85,AF87,AF89,AF91,AF93,AF95,AF97,AF99,AF101,AF103,AF105,AF107,AF109,AF111,AF113,AF115,AF117,AF119,AF121,AF123,AF125,AF127,AF129,AF131,AF133,AF135,AF137,AF139,AF141,AF143,AF145,AF147,AF149,AF151)</f>
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="AG152" s="15">
         <f>SUM(AG79,AG77,AG75,AG73,AG71,AG69,AG67,AG65,AG63,AG61,AG59,AG57,AG55,AG53,AG51,AG49,AG47,AG45,AG43,AG41,AG39,AG37,AG35,AG33,AG31,AG29,AG27,AG25,AG23,AG21,AG19,AG17,AG15,AG13,AG11,AG9,AG81,AG83,AG85,AG87,AG89,AG91,AG93,AG95,AG97,AG99,AG101,AG103,AG105,AG107,AG109,AG111,AG113,AG115,AG117,AG119,AG121,AG123,AG125,AG127,AG129,AG131,AG133,AG135,AG137,AG139,AG141,AG143,AG145,AG147,AG149,AG151)</f>
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="AH152" s="15">
         <f>SUM(AH79,AH77,AH75,AH73,AH71,AH69,AH67,AH65,AH63,AH61,AH59,AH57,AH55,AH53,AH51,AH49,AH47,AH45,AH43,AH41,AH39,AH37,AH35,AH33,AH31,AH29,AH27,AH25,AH23,AH21,AH19,AH17,AH15,AH13,AH11,AH9,AH81,AH83,AH85,AH87,AH89,AH91,AH93,AH95,AH97,AH99,AH101,AH103,AH105,AH107,AH109,AH111,AH113,AH115,AH117,AH119,AH121,AH123,AH125,AH127,AH129,AH131,AH133,AH135,AH137,AH139,AH141,AH143,AH145,AH147,AH149,AH151)</f>
@@ -22464,7 +22468,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="153" spans="1:46" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:46" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F153" s="135" t="s">
         <v>14</v>
       </c>
@@ -22620,7 +22624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:46" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:46" ht="19.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="F154" s="57"/>
       <c r="G154" s="3"/>
       <c r="H154" s="3"/>
@@ -22774,7 +22778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:46" x14ac:dyDescent="0.25">
       <c r="F155" s="57"/>
       <c r="G155" s="3"/>
       <c r="H155" s="3"/>
@@ -22928,7 +22932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:46" x14ac:dyDescent="0.25">
       <c r="F156" s="57"/>
       <c r="G156" s="3"/>
       <c r="H156" s="3"/>
@@ -23082,7 +23086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:46" x14ac:dyDescent="0.25">
       <c r="F157" s="57"/>
       <c r="G157" s="3"/>
       <c r="H157" s="3"/>
@@ -23236,28 +23240,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E158" s="136"/>
       <c r="F158" s="136"/>
       <c r="G158" s="136"/>
       <c r="H158" s="136"/>
       <c r="I158" s="3"/>
     </row>
-    <row r="159" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E159" s="136"/>
       <c r="F159" s="136"/>
       <c r="G159" s="136"/>
       <c r="H159" s="136"/>
       <c r="I159" s="3"/>
     </row>
-    <row r="160" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E160" s="136"/>
       <c r="F160" s="136"/>
       <c r="G160" s="136"/>
       <c r="H160" s="136"/>
       <c r="I160" s="3"/>
     </row>
-    <row r="181" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="181" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J181" s="2">
         <v>1</v>
       </c>
@@ -23891,17 +23895,17 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A2:K76"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>8</v>
       </c>
@@ -23932,7 +23936,7 @@
         <v>SUMA(Y($G$8="",$H$8="",J9=0)+Y($G$10="",$H$10="",J11=0)+Y($G$12="",$H$12="",J13=0)+Y($G$14="",$H$14="",J15=0)+Y($G$16="",$H$16="",J17=0)+Y($G$18="",$H$18="",J19=0)+Y($G$20="",$H$20="",J21=0)+Y($G$22="",$H$22="",J23=0)+Y($G$24="",$H$24="",J25=0)+Y($G$26="",$H$26="",J27=0)+Y($G$28="",$H$28="",J29=0)+Y($G$30="",$H$30="",J31=0)+Y($G$32="",$H$32="",J33=0)+Y($G$34="",$H$34="",J35=0)+Y($G$36="",$H$36="",J37=0)+Y($G$38="",$H$38="",J39=0)+Y($G$40="",$H$40="",J41=0)+Y($G$42="",$H$42="",J43=0)+Y($G$44="",$H$44="",J45=0)+Y($G$46="",$H$46="",J47=0)+Y($G$48="",$H$48="",J49=0)+Y($G$50="",$H$50="",J51=0)+Y($G$52="",$H$52="",J53=0)+Y($G$54="",$H$54="",J55=0)+Y($G$56="",$H$56="",J57=0)+Y($G$58="",$H$58="",J59=0)+Y($G$60="",$H$60="",J61=0)+Y($G$62="",$H$62="",J63=0)+Y($G$64="",$H$64="",J65=0)+Y($G$66="",$H$66="",J67=0)+Y($G$68="",$H$68="",J69=0)+Y($G$70="",$H$70="",J71=0)+Y($G$72="",$H$72="",J73=0)+Y($G$74="",$H$74="",J75=0)+Y($G$76="",$H$76="",J77=0)+Y($G$78="",$H$78="",J79=0)+</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>10</v>
       </c>
@@ -23962,7 +23966,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>12</v>
       </c>
@@ -23989,7 +23993,7 @@
         <v>Y($G$12="",$H$12="",J13=0)+</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>14</v>
       </c>
@@ -24016,7 +24020,7 @@
         <v>Y($G$14="",$H$14="",J15=0)+</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>16</v>
       </c>
@@ -24043,7 +24047,7 @@
         <v>Y($G$16="",$H$16="",J17=0)+</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>18</v>
       </c>
@@ -24070,7 +24074,7 @@
         <v>Y($G$18="",$H$18="",J19=0)+</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>20</v>
       </c>
@@ -24097,7 +24101,7 @@
         <v>Y($G$20="",$H$20="",J21=0)+</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>22</v>
       </c>
@@ -24124,7 +24128,7 @@
         <v>Y($G$22="",$H$22="",J23=0)+</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>24</v>
       </c>
@@ -24151,7 +24155,7 @@
         <v>Y($G$24="",$H$24="",J25=0)+</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26</v>
       </c>
@@ -24178,7 +24182,7 @@
         <v>Y($G$26="",$H$26="",J27=0)+</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>28</v>
       </c>
@@ -24205,7 +24209,7 @@
         <v>Y($G$28="",$H$28="",J29=0)+</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>30</v>
       </c>
@@ -24232,7 +24236,7 @@
         <v>Y($G$30="",$H$30="",J31=0)+</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>32</v>
       </c>
@@ -24259,7 +24263,7 @@
         <v>Y($G$32="",$H$32="",J33=0)+</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>34</v>
       </c>
@@ -24286,7 +24290,7 @@
         <v>Y($G$34="",$H$34="",J35=0)+</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>36</v>
       </c>
@@ -24313,7 +24317,7 @@
         <v>Y($G$36="",$H$36="",J37=0)+</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>38</v>
       </c>
@@ -24340,7 +24344,7 @@
         <v>Y($G$38="",$H$38="",J39=0)+</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>40</v>
       </c>
@@ -24367,7 +24371,7 @@
         <v>Y($G$40="",$H$40="",J41=0)+</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>42</v>
       </c>
@@ -24394,7 +24398,7 @@
         <v>Y($G$42="",$H$42="",J43=0)+</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>44</v>
       </c>
@@ -24421,7 +24425,7 @@
         <v>Y($G$44="",$H$44="",J45=0)+</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>46</v>
       </c>
@@ -24448,7 +24452,7 @@
         <v>Y($G$46="",$H$46="",J47=0)+</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>48</v>
       </c>
@@ -24475,7 +24479,7 @@
         <v>Y($G$48="",$H$48="",J49=0)+</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>50</v>
       </c>
@@ -24502,7 +24506,7 @@
         <v>Y($G$50="",$H$50="",J51=0)+</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>52</v>
       </c>
@@ -24529,7 +24533,7 @@
         <v>Y($G$52="",$H$52="",J53=0)+</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>54</v>
       </c>
@@ -24556,7 +24560,7 @@
         <v>Y($G$54="",$H$54="",J55=0)+</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>56</v>
       </c>
@@ -24583,7 +24587,7 @@
         <v>Y($G$56="",$H$56="",J57=0)+</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>58</v>
       </c>
@@ -24610,7 +24614,7 @@
         <v>Y($G$58="",$H$58="",J59=0)+</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>60</v>
       </c>
@@ -24637,7 +24641,7 @@
         <v>Y($G$60="",$H$60="",J61=0)+</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>62</v>
       </c>
@@ -24664,7 +24668,7 @@
         <v>Y($G$62="",$H$62="",J63=0)+</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>64</v>
       </c>
@@ -24691,7 +24695,7 @@
         <v>Y($G$64="",$H$64="",J65=0)+</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>66</v>
       </c>
@@ -24718,7 +24722,7 @@
         <v>Y($G$66="",$H$66="",J67=0)+</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>68</v>
       </c>
@@ -24745,7 +24749,7 @@
         <v>Y($G$68="",$H$68="",J69=0)+</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>70</v>
       </c>
@@ -24772,7 +24776,7 @@
         <v>Y($G$70="",$H$70="",J71=0)+</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>72</v>
       </c>
@@ -24799,7 +24803,7 @@
         <v>Y($G$72="",$H$72="",J73=0)+</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>74</v>
       </c>
@@ -24826,7 +24830,7 @@
         <v>Y($G$74="",$H$74="",J75=0)+</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>76</v>
       </c>
@@ -24853,7 +24857,7 @@
         <v>Y($G$76="",$H$76="",J77=0)+</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>78</v>
       </c>
@@ -24880,7 +24884,7 @@
         <v>Y($G$78="",$H$78="",J79=0)+</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>80</v>
       </c>
@@ -24911,7 +24915,7 @@
         <v>SUMA(Y($G$80="",$H$80="",J81=0)+Y($G$82="",$H$82="",J83=0)+Y($G$84="",$H$84="",J85=0)+Y($G$86="",$H$86="",J87=0)+Y($G$88="",$H$88="",J89=0)+Y($G$90="",$H$90="",J91=0)+Y($G$92="",$H$92="",J93=0)+Y($G$94="",$H$94="",J95=0)+Y($G$96="",$H$96="",J97=0)+Y($G$98="",$H$98="",J99=0)+Y($G$100="",$H$100="",J101=0)+Y($G$102="",$H$102="",J103=0)+Y($G$104="",$H$104="",J105=0)+Y($G$106="",$H$106="",J107=0)+Y($G$108="",$H$108="",J109=0)+Y($G$110="",$H$110="",J111=0)+Y($G$112="",$H$112="",J113=0)+Y($G$114="",$H$114="",J115=0)+Y($G$116="",$H$116="",J117=0)+Y($G$118="",$H$118="",J119=0)+Y($G$120="",$H$120="",J121=0)+Y($G$122="",$H$122="",J123=0)+Y($G$124="",$H$124="",J125=0)+Y($G$126="",$H$126="",J127=0)+Y($G$128="",$H$128="",J129=0)+Y($G$130="",$H$130="",J131=0)+Y($G$132="",$H$132="",J133=0)+Y($G$134="",$H$134="",J135=0)+Y($G$136="",$H$136="",J137=0)+Y($G$138="",$H$138="",J139=0)+Y($G$140="",$H$140="",J141=0)+Y($G$142="",$H$142="",J143=0)+Y($G$144="",$H$144="",J145=0)+Y($G$146="",$H$146="",J147=0)+Y($G$148="",$H$148="",J149=0)+Y($G$150="",$H$150="",J151=0)+</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>82</v>
       </c>
@@ -24941,7 +24945,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>84</v>
       </c>
@@ -24968,7 +24972,7 @@
         <v>Y($G$84="",$H$84="",J85=0)+</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>86</v>
       </c>
@@ -24995,7 +24999,7 @@
         <v>Y($G$86="",$H$86="",J87=0)+</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>88</v>
       </c>
@@ -25022,7 +25026,7 @@
         <v>Y($G$88="",$H$88="",J89=0)+</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>90</v>
       </c>
@@ -25049,7 +25053,7 @@
         <v>Y($G$90="",$H$90="",J91=0)+</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>92</v>
       </c>
@@ -25076,7 +25080,7 @@
         <v>Y($G$92="",$H$92="",J93=0)+</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>94</v>
       </c>
@@ -25103,7 +25107,7 @@
         <v>Y($G$94="",$H$94="",J95=0)+</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>96</v>
       </c>
@@ -25130,7 +25134,7 @@
         <v>Y($G$96="",$H$96="",J97=0)+</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>98</v>
       </c>
@@ -25157,7 +25161,7 @@
         <v>Y($G$98="",$H$98="",J99=0)+</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>100</v>
       </c>
@@ -25184,7 +25188,7 @@
         <v>Y($G$100="",$H$100="",J101=0)+</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>102</v>
       </c>
@@ -25211,7 +25215,7 @@
         <v>Y($G$102="",$H$102="",J103=0)+</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>104</v>
       </c>
@@ -25238,7 +25242,7 @@
         <v>Y($G$104="",$H$104="",J105=0)+</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>106</v>
       </c>
@@ -25265,7 +25269,7 @@
         <v>Y($G$106="",$H$106="",J107=0)+</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>108</v>
       </c>
@@ -25292,7 +25296,7 @@
         <v>Y($G$108="",$H$108="",J109=0)+</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>110</v>
       </c>
@@ -25319,7 +25323,7 @@
         <v>Y($G$110="",$H$110="",J111=0)+</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>112</v>
       </c>
@@ -25346,7 +25350,7 @@
         <v>Y($G$112="",$H$112="",J113=0)+</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>114</v>
       </c>
@@ -25373,7 +25377,7 @@
         <v>Y($G$114="",$H$114="",J115=0)+</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>116</v>
       </c>
@@ -25400,7 +25404,7 @@
         <v>Y($G$116="",$H$116="",J117=0)+</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>118</v>
       </c>
@@ -25427,7 +25431,7 @@
         <v>Y($G$118="",$H$118="",J119=0)+</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>120</v>
       </c>
@@ -25454,7 +25458,7 @@
         <v>Y($G$120="",$H$120="",J121=0)+</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>122</v>
       </c>
@@ -25481,7 +25485,7 @@
         <v>Y($G$122="",$H$122="",J123=0)+</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>124</v>
       </c>
@@ -25508,7 +25512,7 @@
         <v>Y($G$124="",$H$124="",J125=0)+</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>126</v>
       </c>
@@ -25535,7 +25539,7 @@
         <v>Y($G$126="",$H$126="",J127=0)+</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>128</v>
       </c>
@@ -25562,7 +25566,7 @@
         <v>Y($G$128="",$H$128="",J129=0)+</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>130</v>
       </c>
@@ -25589,7 +25593,7 @@
         <v>Y($G$130="",$H$130="",J131=0)+</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>132</v>
       </c>
@@ -25616,7 +25620,7 @@
         <v>Y($G$132="",$H$132="",J133=0)+</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>134</v>
       </c>
@@ -25643,7 +25647,7 @@
         <v>Y($G$134="",$H$134="",J135=0)+</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>136</v>
       </c>
@@ -25670,7 +25674,7 @@
         <v>Y($G$136="",$H$136="",J137=0)+</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>138</v>
       </c>
@@ -25697,7 +25701,7 @@
         <v>Y($G$138="",$H$138="",J139=0)+</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>140</v>
       </c>
@@ -25724,7 +25728,7 @@
         <v>Y($G$140="",$H$140="",J141=0)+</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>142</v>
       </c>
@@ -25751,7 +25755,7 @@
         <v>Y($G$142="",$H$142="",J143=0)+</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>144</v>
       </c>
@@ -25778,7 +25782,7 @@
         <v>Y($G$144="",$H$144="",J145=0)+</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>146</v>
       </c>
@@ -25805,7 +25809,7 @@
         <v>Y($G$146="",$H$146="",J147=0)+</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>148</v>
       </c>
@@ -25832,7 +25836,7 @@
         <v>Y($G$148="",$H$148="",J149=0)+</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>150</v>
       </c>
@@ -25870,21 +25874,21 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:AF65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.88671875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="6.109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" style="3" customWidth="1"/>
-    <col min="9" max="24" width="5.33203125" style="3" customWidth="1"/>
-    <col min="25" max="30" width="11.44140625" style="3"/>
+    <col min="2" max="2" width="13.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.85546875" style="3" customWidth="1"/>
+    <col min="6" max="7" width="6.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" style="3" customWidth="1"/>
+    <col min="9" max="24" width="5.28515625" style="3" customWidth="1"/>
+    <col min="25" max="30" width="11.42578125" style="3"/>
     <col min="31" max="32" width="0" style="3" hidden="1" customWidth="1"/>
-    <col min="33" max="16384" width="11.44140625" style="3"/>
+    <col min="33" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="99" t="s">
         <v>28</v>
       </c>
@@ -25944,7 +25948,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -25970,7 +25974,7 @@
       <c r="W2" s="38"/>
       <c r="X2" s="39"/>
     </row>
-    <row r="3" spans="1:32" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -26061,7 +26065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="125" t="s">
         <v>77</v>
       </c>
@@ -26100,7 +26104,7 @@
       <c r="W4" s="17"/>
       <c r="X4" s="22"/>
     </row>
-    <row r="5" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="103"/>
       <c r="B5" s="133"/>
       <c r="C5" s="154"/>
@@ -26164,7 +26168,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="103"/>
       <c r="B6" s="132">
         <v>46203</v>
@@ -26207,7 +26211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="103"/>
       <c r="B7" s="133"/>
       <c r="C7" s="154"/>
@@ -26271,7 +26275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="103"/>
       <c r="B8" s="132">
         <v>46201</v>
@@ -26312,7 +26316,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="103"/>
       <c r="B9" s="133"/>
       <c r="C9" s="154"/>
@@ -26374,7 +26378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="103"/>
       <c r="B10" s="132">
         <v>46202</v>
@@ -26415,7 +26419,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="103"/>
       <c r="B11" s="133"/>
       <c r="C11" s="154"/>
@@ -26477,7 +26481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="103"/>
       <c r="B12" s="130">
         <v>46205</v>
@@ -26518,7 +26522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="103"/>
       <c r="B13" s="131"/>
       <c r="C13" s="156"/>
@@ -26580,7 +26584,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="103"/>
       <c r="B14" s="130">
         <v>46205</v>
@@ -26621,7 +26625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="103"/>
       <c r="B15" s="131"/>
       <c r="C15" s="156"/>
@@ -26683,7 +26687,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="103"/>
       <c r="B16" s="130">
         <v>46204</v>
@@ -26724,7 +26728,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="103"/>
       <c r="B17" s="131"/>
       <c r="C17" s="156"/>
@@ -26786,7 +26790,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="103"/>
       <c r="B18" s="130">
         <v>46204</v>
@@ -26827,7 +26831,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="103"/>
       <c r="B19" s="131"/>
       <c r="C19" s="156"/>
@@ -26889,7 +26893,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="125" t="s">
         <v>78</v>
       </c>
@@ -26928,7 +26932,7 @@
       <c r="W20" s="18"/>
       <c r="X20" s="24"/>
     </row>
-    <row r="21" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="103"/>
       <c r="B21" s="133"/>
       <c r="C21" s="154"/>
@@ -26986,7 +26990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="103"/>
       <c r="B22" s="132">
         <v>46203</v>
@@ -27023,7 +27027,7 @@
       <c r="W22" s="13"/>
       <c r="X22" s="25"/>
     </row>
-    <row r="23" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="103"/>
       <c r="B23" s="133"/>
       <c r="C23" s="154"/>
@@ -27081,7 +27085,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="103"/>
       <c r="B24" s="132">
         <v>46203</v>
@@ -27118,7 +27122,7 @@
       <c r="W24" s="18"/>
       <c r="X24" s="24"/>
     </row>
-    <row r="25" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="103"/>
       <c r="B25" s="133"/>
       <c r="C25" s="154"/>
@@ -27176,7 +27180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="103"/>
       <c r="B26" s="132">
         <v>46204</v>
@@ -27213,7 +27217,7 @@
       <c r="W26" s="13"/>
       <c r="X26" s="25"/>
     </row>
-    <row r="27" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="103"/>
       <c r="B27" s="133"/>
       <c r="C27" s="154"/>
@@ -27271,7 +27275,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="103"/>
       <c r="B28" s="130">
         <v>46206</v>
@@ -27308,7 +27312,7 @@
       <c r="W28" s="19"/>
       <c r="X28" s="28"/>
     </row>
-    <row r="29" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="103"/>
       <c r="B29" s="131"/>
       <c r="C29" s="156"/>
@@ -27366,7 +27370,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="103"/>
       <c r="B30" s="130">
         <v>46206</v>
@@ -27403,7 +27407,7 @@
       <c r="W30" s="13"/>
       <c r="X30" s="25"/>
     </row>
-    <row r="31" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="103"/>
       <c r="B31" s="131"/>
       <c r="C31" s="156"/>
@@ -27461,7 +27465,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="103"/>
       <c r="B32" s="130">
         <v>46205</v>
@@ -27498,7 +27502,7 @@
       <c r="W32" s="19"/>
       <c r="X32" s="28"/>
     </row>
-    <row r="33" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="103"/>
       <c r="B33" s="131"/>
       <c r="C33" s="156"/>
@@ -27556,7 +27560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="103"/>
       <c r="B34" s="130">
         <v>46206</v>
@@ -27593,7 +27597,7 @@
       <c r="W34" s="13"/>
       <c r="X34" s="25"/>
     </row>
-    <row r="35" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="104"/>
       <c r="B35" s="131"/>
       <c r="C35" s="156"/>
@@ -27651,7 +27655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E36" s="151" t="s">
         <v>10</v>
       </c>
@@ -27726,7 +27730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:24" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E37" s="135" t="s">
         <v>14</v>
       </c>
@@ -27798,7 +27802,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="I38" s="4">
         <f>IF(I36=$H$36,100,IF($H$36-I36=1,99,IF($H$36-I36=-1,99,IF($H$36-I36=2,98,IF($H$36-I36=-2,98,IF($H$36-I36=3,97,IF($H$36-I36=-3,97,IF($H$36-I36=4,96,IF($H$36-I36=-4,96,IF($H$36-I36=5,95,IF($H$36-I36=-5,95,IF($H$36-I36=6,94,IF($H$36-I36=-6,94,IF($H$36-I36=7,93,IF($H$36-I36=-7,93,IF($H$36-I36=8,92,IF($H$36-I36=-8,92,IF($H$36-I36=9,91,IF($H$36-I36=-9,91,IF($H$36-I36=10,90,IF($H$36-I36=-10,90,IF($H$36-I36=11,89,IF($H$36-I36=-11,89,IF($H$36-I36=12,88,IF($H$36-I36=-12,88,IF($H$36-I36=13,87,IF($H$36-I36=-13,87,IF($H$36-I36=14,86,IF($H$36-I36=-14,86,IF($H$36-I36=15,85,IF($H$36-I36=-15,85,IF($H$36-I36=16,84,IF($H$36-I36=-16,84,IF($H$36-I36=17,83,IF($H$36-I36=-17,83,IF($H$36-I36=18,82,IF($H$36-I36=-18,82,IF($H$36-I36=19,81,IF($H$36-I36=-19,81,IF($H$36-I36=20,80,IF($H$36-I36=-20,80,IF($H$36-I36=21,79,IF($H$36-I36=-21,79,IF($H$36-I36=22,78,IF($H$36-I36=-22,78,IF($H$36-I36=23,77,IF($H$36-I36=-23,77,IF($H$36-I36=24,76,IF($H$36-I36=-24,76,IF($H$36-I36=25,75,IF($H$36-I36=-25,75,IF($H$36-I36=26,74,IF($H$36-I36=-26,74,IF($H$36-I36=27,73,IF($H$36-I36=-27,73,IF($H$36-I36=28,72,IF($H$36-I36=-28,72,IF($H$36-I36=29,71,IF($H$36-I36=-29,71,IF($H$36-I36=30,70,IF($H$36-I36=-30,70,IF($H$36-I36=31,69,IF($H$36-I36=-31,69,IF($H$36-I36=32,68,IF($H$36-I36=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>100</v>
@@ -27864,7 +27868,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="I39" s="4">
         <f>IF($H$36-I36=33,67,IF($H$36-I36=-33,67,IF($H$36-I36=34,66,IF($H$36-I36=-34,66,IF($H$36-I36=35,65,IF($H$36-I36=-35,65,IF($H$36-I36=36,64,IF($H$36-I36=-36,64,IF($H$36-I36=37,63,IF($H$36-I36=-37,63,IF($H$36-I36=38,62,IF($H$36-I36=-38,62,IF($H$36-I36=39,61,IF($H$36-I36=-39,61,IF($H$36-I36=40,60,IF($H$36-I36=-40,60,IF($H$36-I36=41,59,IF($H$36-I36=-41,59,IF($H$36-I36=42,58,IF($H$36-I36=-42,58,IF($H$36-I36=43,57,IF($H$36-I36=-43,57,IF($H$36-I36=44,56,IF($H$36-I36=-44,56,IF($H$36-I36=45,55,IF($H$36-I36=-45,55,IF($H$36-I36=46,54,IF($H$36-I36=-46,54,IF($H$36-I36=47,53,IF($H$36-I36=-47,53,IF($H$36-I36=48,52,IF($H$36-I36=-48,52,IF($H$36-I36=49,51,IF($H$36-I36=-49,51,IF($H$36-I36=50,50,IF($H$36-I36=-50,50,IF($H$36-I36=51,49,IF($H$36-I36=-51,49,IF($H$36-I36=52,48,IF($H$36-I36=-52,48,IF($H$36-I36=53,47,IF($H$36-I36=-53,47,IF($H$36-I36=54,46,IF($H$36-I36=-54,46,IF($H$36-I36=55,45,IF($H$36-I36=-55,45,IF($H$36-I36=56,44,IF($H$36-I36=-56,44,IF($H$36-I36=57,43,IF($H$36-I36=-57,43,IF($H$36-I36=58,42,IF($H$36-I36=-58,42,IF($H$36-I36=59,41,IF($H$36-I36=-59,41,IF($H$36-I36=60,40,IF($H$36-I36=-60,40,IF($H$36-I36=61,39,IF($H$36-I36=-61,39,IF($H$36-I36=62,38,IF($H$36-I36=-62,38,IF($H$36-I36=63,37,IF($H$36-I36=-63,37,IF($H$36-I36=64,36,IF($H$36-I36=-64,36,IF($H$36-I36=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -27930,7 +27934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="I40" s="4">
         <f>IF($H$36-I36=-65,35,IF($H$36-I36=66,34,IF($H$36-I36=-66,34,IF($H$36-I36=67,33,IF($H$36-I36=-67,33,IF($H$36-I36=68,32,IF($H$36-I36=-68,32,IF($H$36-I36=69,31,IF($H$36-I36=-69,31,IF($H$36-I36=70,30,IF($H$36-I36=-70,30,IF($H$36-I36=71,29,IF($H$36-I36=-71,29,IF($H$36-I36=72,28,IF($H$36-I36=-72,28,IF($H$36-I36=73,27,IF($H$36-I36=-73,27,IF($H$36-I36=74,26,IF($H$36-I36=-74,26,IF($H$36-I36=75,25,IF($H$36-I36=-75,25,IF($H$36-I36=76,24,IF($H$36-I36=-76,24,IF($H$36-I36=77,23,IF($H$36-I36=-77,23,IF($H$36-I36=78,22,IF($H$36-I36=-78,22,IF($H$36-I36=79,21,IF($H$36-I36=-79,21,IF($H$36-I36=80,20,IF($H$36-I36=-80,20,IF($H$36-I36=81,19,IF($H$36-I36=-81,19,IF($H$36-I36=82,18,IF($H$36-I36=-82,18,IF($H$36-I36=83,17,IF($H$36-I36=-83,17,IF($H$36-I36=84,16,IF($H$36-I36=-84,16,IF($H$36-I36=85,15,IF($H$36-I36=-85,15,IF($H$36-I36=86,14,IF($H$36-I36=-86,14,IF($H$36-I36=87,13,IF($H$36-I36=-87,13,IF($H$36-I36=88,12,IF($H$36-I36=-88,12,IF($H$36-I36=89,11,IF($H$36-I36=-89,11,IF($H$36-I36=90,10,IF($H$36-I36=-90,10,IF($H$36-I36=91,9,IF($H$36-I36=-91,9,IF($H$36-I36=92,8,IF($H$36-I36=-92,8,IF($H$36-I36=93,7,IF($H$36-I36=-93,7,IF($H$36-I36=94,6,IF($H$36-I36=-94,6,IF($H$36-I36=95,5,IF($H$36-I36=-95,5,IF($H$36-I36=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -27996,7 +28000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="I41" s="4">
         <f>IF($H$36-I36=-96,4,IF($H$36-I36=97,3,IF($H$36-I36=-97,3,IF($H$36-I36=98,2,IF($H$36-I36=-98,2,IF($H$36-I36=99,1,IF($H$36-I36=-99,1,IF($H$36-I36=100,0,IF($H$36-I36=-100,0,0)))))))))</f>
         <v>0</v>
@@ -28062,25 +28066,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="152"/>
       <c r="E42" s="152"/>
       <c r="F42" s="152"/>
       <c r="G42" s="152"/>
     </row>
-    <row r="43" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="152"/>
       <c r="E43" s="152"/>
       <c r="F43" s="152"/>
       <c r="G43" s="152"/>
     </row>
-    <row r="44" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="152"/>
       <c r="E44" s="152"/>
       <c r="F44" s="152"/>
       <c r="G44" s="152"/>
     </row>
-    <row r="65" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I65" s="3">
         <v>1</v>
       </c>
@@ -28231,21 +28235,21 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:Y49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.88671875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="6.109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" style="3" customWidth="1"/>
-    <col min="9" max="17" width="5.33203125" style="3" customWidth="1"/>
-    <col min="18" max="23" width="11.44140625" style="3"/>
+    <col min="2" max="2" width="13.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.85546875" style="3" customWidth="1"/>
+    <col min="6" max="7" width="6.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" style="3" customWidth="1"/>
+    <col min="9" max="17" width="5.28515625" style="3" customWidth="1"/>
+    <col min="18" max="23" width="11.42578125" style="3"/>
     <col min="24" max="25" width="0" style="3" hidden="1" customWidth="1"/>
-    <col min="26" max="16384" width="11.44140625" style="3"/>
+    <col min="26" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="99" t="s">
         <v>28</v>
       </c>
@@ -28284,7 +28288,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -28303,7 +28307,7 @@
       <c r="P2" s="38"/>
       <c r="Q2" s="39"/>
     </row>
-    <row r="3" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -28372,7 +28376,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="125" t="s">
         <v>77</v>
       </c>
@@ -28404,7 +28408,7 @@
       <c r="P4" s="17"/>
       <c r="Q4" s="22"/>
     </row>
-    <row r="5" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="103"/>
       <c r="B5" s="133"/>
       <c r="C5" s="154"/>
@@ -28447,7 +28451,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="103"/>
       <c r="B6" s="132">
         <v>46207</v>
@@ -28483,7 +28487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="103"/>
       <c r="B7" s="133"/>
       <c r="C7" s="154"/>
@@ -28526,7 +28530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="103"/>
       <c r="B8" s="132">
         <v>46209</v>
@@ -28560,7 +28564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="103"/>
       <c r="B9" s="133"/>
       <c r="C9" s="154"/>
@@ -28601,7 +28605,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="103"/>
       <c r="B10" s="132">
         <v>46209</v>
@@ -28635,7 +28639,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="103"/>
       <c r="B11" s="133"/>
       <c r="C11" s="154"/>
@@ -28676,7 +28680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="125" t="s">
         <v>78</v>
       </c>
@@ -28708,7 +28712,7 @@
       <c r="P12" s="19"/>
       <c r="Q12" s="28"/>
     </row>
-    <row r="13" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="103"/>
       <c r="B13" s="131"/>
       <c r="C13" s="156"/>
@@ -28745,7 +28749,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="103"/>
       <c r="B14" s="130">
         <v>46208</v>
@@ -28775,7 +28779,7 @@
       <c r="P14" s="13"/>
       <c r="Q14" s="25"/>
     </row>
-    <row r="15" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="103"/>
       <c r="B15" s="131"/>
       <c r="C15" s="156"/>
@@ -28812,7 +28816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="103"/>
       <c r="B16" s="130">
         <v>46210</v>
@@ -28842,7 +28846,7 @@
       <c r="P16" s="19"/>
       <c r="Q16" s="28"/>
     </row>
-    <row r="17" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="103"/>
       <c r="B17" s="131"/>
       <c r="C17" s="156"/>
@@ -28879,7 +28883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="103"/>
       <c r="B18" s="130">
         <v>46210</v>
@@ -28909,7 +28913,7 @@
       <c r="P18" s="13"/>
       <c r="Q18" s="25"/>
     </row>
-    <row r="19" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="104"/>
       <c r="B19" s="131"/>
       <c r="C19" s="156"/>
@@ -28946,7 +28950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E20" s="151" t="s">
         <v>10</v>
       </c>
@@ -28993,7 +28997,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E21" s="135" t="s">
         <v>14</v>
       </c>
@@ -29037,7 +29041,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="I22" s="4" t="e">
         <f>IF(I20=$H$20,100,IF($H$20-I20=1,99,IF($H$20-I20=-1,99,IF($H$20-I20=2,98,IF($H$20-I20=-2,98,IF($H$20-I20=3,97,IF($H$20-I20=-3,97,IF($H$20-I20=4,96,IF($H$20-I20=-4,96,IF($H$20-I20=5,95,IF($H$20-I20=-5,95,IF($H$20-I20=6,94,IF($H$20-I20=-6,94,IF($H$20-I20=7,93,IF($H$20-I20=-7,93,IF($H$20-I20=8,92,IF($H$20-I20=-8,92,IF($H$20-I20=9,91,IF($H$20-I20=-9,91,IF($H$20-I20=10,90,IF($H$20-I20=-10,90,IF($H$20-I20=11,89,IF($H$20-I20=-11,89,IF($H$20-I20=12,88,IF($H$20-I20=-12,88,IF($H$20-I20=13,87,IF($H$20-I20=-13,87,IF($H$20-I20=14,86,IF($H$20-I20=-14,86,IF($H$20-I20=15,85,IF($H$20-I20=-15,85,IF($H$20-I20=16,84,IF($H$20-I20=-16,84,IF($H$20-I20=17,83,IF($H$20-I20=-17,83,IF($H$20-I20=18,82,IF($H$20-I20=-18,82,IF($H$20-I20=19,81,IF($H$20-I20=-19,81,IF($H$20-I20=20,80,IF($H$20-I20=-20,80,IF($H$20-I20=21,79,IF($H$20-I20=-21,79,IF($H$20-I20=22,78,IF($H$20-I20=-22,78,IF($H$20-I20=23,77,IF($H$20-I20=-23,77,IF($H$20-I20=24,76,IF($H$20-I20=-24,76,IF($H$20-I20=25,75,IF($H$20-I20=-25,75,IF($H$20-I20=26,74,IF($H$20-I20=-26,74,IF($H$20-I20=27,73,IF($H$20-I20=-27,73,IF($H$20-I20=28,72,IF($H$20-I20=-28,72,IF($H$20-I20=29,71,IF($H$20-I20=-29,71,IF($H$20-I20=30,70,IF($H$20-I20=-30,70,IF($H$20-I20=31,69,IF($H$20-I20=-31,69,IF($H$20-I20=32,68,IF($H$20-I20=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>#REF!</v>
@@ -29075,7 +29079,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I23" s="4" t="e">
         <f>IF($H$20-I20=33,67,IF($H$20-I20=-33,67,IF($H$20-I20=34,66,IF($H$20-I20=-34,66,IF($H$20-I20=35,65,IF($H$20-I20=-35,65,IF($H$20-I20=36,64,IF($H$20-I20=-36,64,IF($H$20-I20=37,63,IF($H$20-I20=-37,63,IF($H$20-I20=38,62,IF($H$20-I20=-38,62,IF($H$20-I20=39,61,IF($H$20-I20=-39,61,IF($H$20-I20=40,60,IF($H$20-I20=-40,60,IF($H$20-I20=41,59,IF($H$20-I20=-41,59,IF($H$20-I20=42,58,IF($H$20-I20=-42,58,IF($H$20-I20=43,57,IF($H$20-I20=-43,57,IF($H$20-I20=44,56,IF($H$20-I20=-44,56,IF($H$20-I20=45,55,IF($H$20-I20=-45,55,IF($H$20-I20=46,54,IF($H$20-I20=-46,54,IF($H$20-I20=47,53,IF($H$20-I20=-47,53,IF($H$20-I20=48,52,IF($H$20-I20=-48,52,IF($H$20-I20=49,51,IF($H$20-I20=-49,51,IF($H$20-I20=50,50,IF($H$20-I20=-50,50,IF($H$20-I20=51,49,IF($H$20-I20=-51,49,IF($H$20-I20=52,48,IF($H$20-I20=-52,48,IF($H$20-I20=53,47,IF($H$20-I20=-53,47,IF($H$20-I20=54,46,IF($H$20-I20=-54,46,IF($H$20-I20=55,45,IF($H$20-I20=-55,45,IF($H$20-I20=56,44,IF($H$20-I20=-56,44,IF($H$20-I20=57,43,IF($H$20-I20=-57,43,IF($H$20-I20=58,42,IF($H$20-I20=-58,42,IF($H$20-I20=59,41,IF($H$20-I20=-59,41,IF($H$20-I20=60,40,IF($H$20-I20=-60,40,IF($H$20-I20=61,39,IF($H$20-I20=-61,39,IF($H$20-I20=62,38,IF($H$20-I20=-62,38,IF($H$20-I20=63,37,IF($H$20-I20=-63,37,IF($H$20-I20=64,36,IF($H$20-I20=-64,36,IF($H$20-I20=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>#REF!</v>
@@ -29113,7 +29117,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I24" s="4" t="e">
         <f>IF($H$20-I20=-65,35,IF($H$20-I20=66,34,IF($H$20-I20=-66,34,IF($H$20-I20=67,33,IF($H$20-I20=-67,33,IF($H$20-I20=68,32,IF($H$20-I20=-68,32,IF($H$20-I20=69,31,IF($H$20-I20=-69,31,IF($H$20-I20=70,30,IF($H$20-I20=-70,30,IF($H$20-I20=71,29,IF($H$20-I20=-71,29,IF($H$20-I20=72,28,IF($H$20-I20=-72,28,IF($H$20-I20=73,27,IF($H$20-I20=-73,27,IF($H$20-I20=74,26,IF($H$20-I20=-74,26,IF($H$20-I20=75,25,IF($H$20-I20=-75,25,IF($H$20-I20=76,24,IF($H$20-I20=-76,24,IF($H$20-I20=77,23,IF($H$20-I20=-77,23,IF($H$20-I20=78,22,IF($H$20-I20=-78,22,IF($H$20-I20=79,21,IF($H$20-I20=-79,21,IF($H$20-I20=80,20,IF($H$20-I20=-80,20,IF($H$20-I20=81,19,IF($H$20-I20=-81,19,IF($H$20-I20=82,18,IF($H$20-I20=-82,18,IF($H$20-I20=83,17,IF($H$20-I20=-83,17,IF($H$20-I20=84,16,IF($H$20-I20=-84,16,IF($H$20-I20=85,15,IF($H$20-I20=-85,15,IF($H$20-I20=86,14,IF($H$20-I20=-86,14,IF($H$20-I20=87,13,IF($H$20-I20=-87,13,IF($H$20-I20=88,12,IF($H$20-I20=-88,12,IF($H$20-I20=89,11,IF($H$20-I20=-89,11,IF($H$20-I20=90,10,IF($H$20-I20=-90,10,IF($H$20-I20=91,9,IF($H$20-I20=-91,9,IF($H$20-I20=92,8,IF($H$20-I20=-92,8,IF($H$20-I20=93,7,IF($H$20-I20=-93,7,IF($H$20-I20=94,6,IF($H$20-I20=-94,6,IF($H$20-I20=95,5,IF($H$20-I20=-95,5,IF($H$20-I20=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>#REF!</v>
@@ -29151,7 +29155,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I25" s="4" t="e">
         <f>IF($H$20-I20=-96,4,IF($H$20-I20=97,3,IF($H$20-I20=-97,3,IF($H$20-I20=98,2,IF($H$20-I20=-98,2,IF($H$20-I20=99,1,IF($H$20-I20=-99,1,IF($H$20-I20=100,0,IF($H$20-I20=-100,0,0)))))))))</f>
         <v>#REF!</v>
@@ -29189,25 +29193,25 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="152"/>
       <c r="E26" s="152"/>
       <c r="F26" s="152"/>
       <c r="G26" s="152"/>
     </row>
-    <row r="27" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="152"/>
       <c r="E27" s="152"/>
       <c r="F27" s="152"/>
       <c r="G27" s="152"/>
     </row>
-    <row r="28" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="152"/>
       <c r="E28" s="152"/>
       <c r="F28" s="152"/>
       <c r="G28" s="152"/>
     </row>
-    <row r="49" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I49" s="3">
         <v>1</v>
       </c>
@@ -29302,21 +29306,21 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:V41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.88671875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="6.109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" style="3" customWidth="1"/>
-    <col min="9" max="14" width="5.33203125" style="3" customWidth="1"/>
-    <col min="15" max="20" width="11.44140625" style="3"/>
+    <col min="2" max="2" width="13.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.85546875" style="3" customWidth="1"/>
+    <col min="6" max="7" width="6.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" style="3" customWidth="1"/>
+    <col min="9" max="14" width="5.28515625" style="3" customWidth="1"/>
+    <col min="15" max="20" width="11.42578125" style="3"/>
     <col min="21" max="22" width="0" style="3" hidden="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.44140625" style="3"/>
+    <col min="23" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="99" t="s">
         <v>28</v>
       </c>
@@ -29346,7 +29350,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -29362,7 +29366,7 @@
       <c r="M2" s="38"/>
       <c r="N2" s="39"/>
     </row>
-    <row r="3" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -29410,7 +29414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="125" t="s">
         <v>77</v>
       </c>
@@ -29439,7 +29443,7 @@
       <c r="M4" s="17"/>
       <c r="N4" s="22"/>
     </row>
-    <row r="5" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="103"/>
       <c r="B5" s="133"/>
       <c r="C5" s="154"/>
@@ -29473,7 +29477,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="103"/>
       <c r="B6" s="132">
         <v>46213</v>
@@ -29506,7 +29510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="103"/>
       <c r="B7" s="133"/>
       <c r="C7" s="154"/>
@@ -29540,7 +29544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="125" t="s">
         <v>78</v>
       </c>
@@ -29569,7 +29573,7 @@
       <c r="M8" s="19"/>
       <c r="N8" s="28"/>
     </row>
-    <row r="9" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="103"/>
       <c r="B9" s="131"/>
       <c r="C9" s="156"/>
@@ -29597,7 +29601,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="103"/>
       <c r="B10" s="130">
         <v>46214</v>
@@ -29624,7 +29628,7 @@
       <c r="M10" s="13"/>
       <c r="N10" s="25"/>
     </row>
-    <row r="11" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="104"/>
       <c r="B11" s="131"/>
       <c r="C11" s="156"/>
@@ -29652,7 +29656,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E12" s="151" t="s">
         <v>10</v>
       </c>
@@ -29687,7 +29691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E13" s="135" t="s">
         <v>14</v>
       </c>
@@ -29719,7 +29723,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="I14" s="4">
         <f>IF(I12=$H$12,100,IF($H$12-I12=1,99,IF($H$12-I12=-1,99,IF($H$12-I12=2,98,IF($H$12-I12=-2,98,IF($H$12-I12=3,97,IF($H$12-I12=-3,97,IF($H$12-I12=4,96,IF($H$12-I12=-4,96,IF($H$12-I12=5,95,IF($H$12-I12=-5,95,IF($H$12-I12=6,94,IF($H$12-I12=-6,94,IF($H$12-I12=7,93,IF($H$12-I12=-7,93,IF($H$12-I12=8,92,IF($H$12-I12=-8,92,IF($H$12-I12=9,91,IF($H$12-I12=-9,91,IF($H$12-I12=10,90,IF($H$12-I12=-10,90,IF($H$12-I12=11,89,IF($H$12-I12=-11,89,IF($H$12-I12=12,88,IF($H$12-I12=-12,88,IF($H$12-I12=13,87,IF($H$12-I12=-13,87,IF($H$12-I12=14,86,IF($H$12-I12=-14,86,IF($H$12-I12=15,85,IF($H$12-I12=-15,85,IF($H$12-I12=16,84,IF($H$12-I12=-16,84,IF($H$12-I12=17,83,IF($H$12-I12=-17,83,IF($H$12-I12=18,82,IF($H$12-I12=-18,82,IF($H$12-I12=19,81,IF($H$12-I12=-19,81,IF($H$12-I12=20,80,IF($H$12-I12=-20,80,IF($H$12-I12=21,79,IF($H$12-I12=-21,79,IF($H$12-I12=22,78,IF($H$12-I12=-22,78,IF($H$12-I12=23,77,IF($H$12-I12=-23,77,IF($H$12-I12=24,76,IF($H$12-I12=-24,76,IF($H$12-I12=25,75,IF($H$12-I12=-25,75,IF($H$12-I12=26,74,IF($H$12-I12=-26,74,IF($H$12-I12=27,73,IF($H$12-I12=-27,73,IF($H$12-I12=28,72,IF($H$12-I12=-28,72,IF($H$12-I12=29,71,IF($H$12-I12=-29,71,IF($H$12-I12=30,70,IF($H$12-I12=-30,70,IF($H$12-I12=31,69,IF($H$12-I12=-31,69,IF($H$12-I12=32,68,IF($H$12-I12=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>100</v>
@@ -29745,7 +29749,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I15" s="4">
         <f>IF($H$12-I12=33,67,IF($H$12-I12=-33,67,IF($H$12-I12=34,66,IF($H$12-I12=-34,66,IF($H$12-I12=35,65,IF($H$12-I12=-35,65,IF($H$12-I12=36,64,IF($H$12-I12=-36,64,IF($H$12-I12=37,63,IF($H$12-I12=-37,63,IF($H$12-I12=38,62,IF($H$12-I12=-38,62,IF($H$12-I12=39,61,IF($H$12-I12=-39,61,IF($H$12-I12=40,60,IF($H$12-I12=-40,60,IF($H$12-I12=41,59,IF($H$12-I12=-41,59,IF($H$12-I12=42,58,IF($H$12-I12=-42,58,IF($H$12-I12=43,57,IF($H$12-I12=-43,57,IF($H$12-I12=44,56,IF($H$12-I12=-44,56,IF($H$12-I12=45,55,IF($H$12-I12=-45,55,IF($H$12-I12=46,54,IF($H$12-I12=-46,54,IF($H$12-I12=47,53,IF($H$12-I12=-47,53,IF($H$12-I12=48,52,IF($H$12-I12=-48,52,IF($H$12-I12=49,51,IF($H$12-I12=-49,51,IF($H$12-I12=50,50,IF($H$12-I12=-50,50,IF($H$12-I12=51,49,IF($H$12-I12=-51,49,IF($H$12-I12=52,48,IF($H$12-I12=-52,48,IF($H$12-I12=53,47,IF($H$12-I12=-53,47,IF($H$12-I12=54,46,IF($H$12-I12=-54,46,IF($H$12-I12=55,45,IF($H$12-I12=-55,45,IF($H$12-I12=56,44,IF($H$12-I12=-56,44,IF($H$12-I12=57,43,IF($H$12-I12=-57,43,IF($H$12-I12=58,42,IF($H$12-I12=-58,42,IF($H$12-I12=59,41,IF($H$12-I12=-59,41,IF($H$12-I12=60,40,IF($H$12-I12=-60,40,IF($H$12-I12=61,39,IF($H$12-I12=-61,39,IF($H$12-I12=62,38,IF($H$12-I12=-62,38,IF($H$12-I12=63,37,IF($H$12-I12=-63,37,IF($H$12-I12=64,36,IF($H$12-I12=-64,36,IF($H$12-I12=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -29771,7 +29775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I16" s="4">
         <f>IF($H$12-I12=-65,35,IF($H$12-I12=66,34,IF($H$12-I12=-66,34,IF($H$12-I12=67,33,IF($H$12-I12=-67,33,IF($H$12-I12=68,32,IF($H$12-I12=-68,32,IF($H$12-I12=69,31,IF($H$12-I12=-69,31,IF($H$12-I12=70,30,IF($H$12-I12=-70,30,IF($H$12-I12=71,29,IF($H$12-I12=-71,29,IF($H$12-I12=72,28,IF($H$12-I12=-72,28,IF($H$12-I12=73,27,IF($H$12-I12=-73,27,IF($H$12-I12=74,26,IF($H$12-I12=-74,26,IF($H$12-I12=75,25,IF($H$12-I12=-75,25,IF($H$12-I12=76,24,IF($H$12-I12=-76,24,IF($H$12-I12=77,23,IF($H$12-I12=-77,23,IF($H$12-I12=78,22,IF($H$12-I12=-78,22,IF($H$12-I12=79,21,IF($H$12-I12=-79,21,IF($H$12-I12=80,20,IF($H$12-I12=-80,20,IF($H$12-I12=81,19,IF($H$12-I12=-81,19,IF($H$12-I12=82,18,IF($H$12-I12=-82,18,IF($H$12-I12=83,17,IF($H$12-I12=-83,17,IF($H$12-I12=84,16,IF($H$12-I12=-84,16,IF($H$12-I12=85,15,IF($H$12-I12=-85,15,IF($H$12-I12=86,14,IF($H$12-I12=-86,14,IF($H$12-I12=87,13,IF($H$12-I12=-87,13,IF($H$12-I12=88,12,IF($H$12-I12=-88,12,IF($H$12-I12=89,11,IF($H$12-I12=-89,11,IF($H$12-I12=90,10,IF($H$12-I12=-90,10,IF($H$12-I12=91,9,IF($H$12-I12=-91,9,IF($H$12-I12=92,8,IF($H$12-I12=-92,8,IF($H$12-I12=93,7,IF($H$12-I12=-93,7,IF($H$12-I12=94,6,IF($H$12-I12=-94,6,IF($H$12-I12=95,5,IF($H$12-I12=-95,5,IF($H$12-I12=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -29797,7 +29801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:14" x14ac:dyDescent="0.25">
       <c r="I17" s="4">
         <f>IF($H$12-I12=-96,4,IF($H$12-I12=97,3,IF($H$12-I12=-97,3,IF($H$12-I12=98,2,IF($H$12-I12=-98,2,IF($H$12-I12=99,1,IF($H$12-I12=-99,1,IF($H$12-I12=100,0,IF($H$12-I12=-100,0,0)))))))))</f>
         <v>0</v>
@@ -29823,25 +29827,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="152"/>
       <c r="E18" s="152"/>
       <c r="F18" s="152"/>
       <c r="G18" s="152"/>
     </row>
-    <row r="19" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="152"/>
       <c r="E19" s="152"/>
       <c r="F19" s="152"/>
       <c r="G19" s="152"/>
     </row>
-    <row r="20" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="152"/>
       <c r="E20" s="152"/>
       <c r="F20" s="152"/>
       <c r="G20" s="152"/>
     </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I41" s="3">
         <v>1</v>
       </c>
@@ -29908,21 +29912,21 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:T41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.88671875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="6.109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" style="3" customWidth="1"/>
-    <col min="9" max="12" width="5.33203125" style="3" customWidth="1"/>
-    <col min="13" max="18" width="11.44140625" style="3"/>
+    <col min="2" max="2" width="13.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.85546875" style="3" customWidth="1"/>
+    <col min="6" max="7" width="6.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" style="3" customWidth="1"/>
+    <col min="9" max="12" width="5.28515625" style="3" customWidth="1"/>
+    <col min="13" max="18" width="11.42578125" style="3"/>
     <col min="19" max="20" width="0" style="3" hidden="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.44140625" style="3"/>
+    <col min="21" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="99" t="s">
         <v>28</v>
       </c>
@@ -29946,7 +29950,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -29960,7 +29964,7 @@
       <c r="K2" s="38"/>
       <c r="L2" s="39"/>
     </row>
-    <row r="3" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -30000,7 +30004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="125" t="s">
         <v>127</v>
       </c>
@@ -30027,7 +30031,7 @@
       <c r="K4" s="17"/>
       <c r="L4" s="22"/>
     </row>
-    <row r="5" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="103"/>
       <c r="B5" s="133"/>
       <c r="C5" s="154"/>
@@ -30055,7 +30059,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="103"/>
       <c r="B6" s="132">
         <v>46218</v>
@@ -30086,7 +30090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="103"/>
       <c r="B7" s="133"/>
       <c r="C7" s="154"/>
@@ -30114,7 +30118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="163" t="s">
         <v>128</v>
       </c>
@@ -30141,7 +30145,7 @@
       <c r="K8" s="19"/>
       <c r="L8" s="28"/>
     </row>
-    <row r="9" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="163"/>
       <c r="B9" s="131"/>
       <c r="C9" s="156"/>
@@ -30163,7 +30167,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="163" t="s">
         <v>25</v>
       </c>
@@ -30190,7 +30194,7 @@
       <c r="K10" s="13"/>
       <c r="L10" s="25"/>
     </row>
-    <row r="11" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="163"/>
       <c r="B11" s="131"/>
       <c r="C11" s="156"/>
@@ -30212,7 +30216,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E12" s="151" t="s">
         <v>10</v>
       </c>
@@ -30239,7 +30243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E13" s="135" t="s">
         <v>14</v>
       </c>
@@ -30263,7 +30267,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="I14" s="4">
         <f>IF(I12=$H$12,100,IF($H$12-I12=1,99,IF($H$12-I12=-1,99,IF($H$12-I12=2,98,IF($H$12-I12=-2,98,IF($H$12-I12=3,97,IF($H$12-I12=-3,97,IF($H$12-I12=4,96,IF($H$12-I12=-4,96,IF($H$12-I12=5,95,IF($H$12-I12=-5,95,IF($H$12-I12=6,94,IF($H$12-I12=-6,94,IF($H$12-I12=7,93,IF($H$12-I12=-7,93,IF($H$12-I12=8,92,IF($H$12-I12=-8,92,IF($H$12-I12=9,91,IF($H$12-I12=-9,91,IF($H$12-I12=10,90,IF($H$12-I12=-10,90,IF($H$12-I12=11,89,IF($H$12-I12=-11,89,IF($H$12-I12=12,88,IF($H$12-I12=-12,88,IF($H$12-I12=13,87,IF($H$12-I12=-13,87,IF($H$12-I12=14,86,IF($H$12-I12=-14,86,IF($H$12-I12=15,85,IF($H$12-I12=-15,85,IF($H$12-I12=16,84,IF($H$12-I12=-16,84,IF($H$12-I12=17,83,IF($H$12-I12=-17,83,IF($H$12-I12=18,82,IF($H$12-I12=-18,82,IF($H$12-I12=19,81,IF($H$12-I12=-19,81,IF($H$12-I12=20,80,IF($H$12-I12=-20,80,IF($H$12-I12=21,79,IF($H$12-I12=-21,79,IF($H$12-I12=22,78,IF($H$12-I12=-22,78,IF($H$12-I12=23,77,IF($H$12-I12=-23,77,IF($H$12-I12=24,76,IF($H$12-I12=-24,76,IF($H$12-I12=25,75,IF($H$12-I12=-25,75,IF($H$12-I12=26,74,IF($H$12-I12=-26,74,IF($H$12-I12=27,73,IF($H$12-I12=-27,73,IF($H$12-I12=28,72,IF($H$12-I12=-28,72,IF($H$12-I12=29,71,IF($H$12-I12=-29,71,IF($H$12-I12=30,70,IF($H$12-I12=-30,70,IF($H$12-I12=31,69,IF($H$12-I12=-31,69,IF($H$12-I12=32,68,IF($H$12-I12=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>100</v>
@@ -30281,7 +30285,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="I15" s="4">
         <f>IF($H$12-I12=33,67,IF($H$12-I12=-33,67,IF($H$12-I12=34,66,IF($H$12-I12=-34,66,IF($H$12-I12=35,65,IF($H$12-I12=-35,65,IF($H$12-I12=36,64,IF($H$12-I12=-36,64,IF($H$12-I12=37,63,IF($H$12-I12=-37,63,IF($H$12-I12=38,62,IF($H$12-I12=-38,62,IF($H$12-I12=39,61,IF($H$12-I12=-39,61,IF($H$12-I12=40,60,IF($H$12-I12=-40,60,IF($H$12-I12=41,59,IF($H$12-I12=-41,59,IF($H$12-I12=42,58,IF($H$12-I12=-42,58,IF($H$12-I12=43,57,IF($H$12-I12=-43,57,IF($H$12-I12=44,56,IF($H$12-I12=-44,56,IF($H$12-I12=45,55,IF($H$12-I12=-45,55,IF($H$12-I12=46,54,IF($H$12-I12=-46,54,IF($H$12-I12=47,53,IF($H$12-I12=-47,53,IF($H$12-I12=48,52,IF($H$12-I12=-48,52,IF($H$12-I12=49,51,IF($H$12-I12=-49,51,IF($H$12-I12=50,50,IF($H$12-I12=-50,50,IF($H$12-I12=51,49,IF($H$12-I12=-51,49,IF($H$12-I12=52,48,IF($H$12-I12=-52,48,IF($H$12-I12=53,47,IF($H$12-I12=-53,47,IF($H$12-I12=54,46,IF($H$12-I12=-54,46,IF($H$12-I12=55,45,IF($H$12-I12=-55,45,IF($H$12-I12=56,44,IF($H$12-I12=-56,44,IF($H$12-I12=57,43,IF($H$12-I12=-57,43,IF($H$12-I12=58,42,IF($H$12-I12=-58,42,IF($H$12-I12=59,41,IF($H$12-I12=-59,41,IF($H$12-I12=60,40,IF($H$12-I12=-60,40,IF($H$12-I12=61,39,IF($H$12-I12=-61,39,IF($H$12-I12=62,38,IF($H$12-I12=-62,38,IF($H$12-I12=63,37,IF($H$12-I12=-63,37,IF($H$12-I12=64,36,IF($H$12-I12=-64,36,IF($H$12-I12=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -30299,7 +30303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="I16" s="4">
         <f>IF($H$12-I12=-65,35,IF($H$12-I12=66,34,IF($H$12-I12=-66,34,IF($H$12-I12=67,33,IF($H$12-I12=-67,33,IF($H$12-I12=68,32,IF($H$12-I12=-68,32,IF($H$12-I12=69,31,IF($H$12-I12=-69,31,IF($H$12-I12=70,30,IF($H$12-I12=-70,30,IF($H$12-I12=71,29,IF($H$12-I12=-71,29,IF($H$12-I12=72,28,IF($H$12-I12=-72,28,IF($H$12-I12=73,27,IF($H$12-I12=-73,27,IF($H$12-I12=74,26,IF($H$12-I12=-74,26,IF($H$12-I12=75,25,IF($H$12-I12=-75,25,IF($H$12-I12=76,24,IF($H$12-I12=-76,24,IF($H$12-I12=77,23,IF($H$12-I12=-77,23,IF($H$12-I12=78,22,IF($H$12-I12=-78,22,IF($H$12-I12=79,21,IF($H$12-I12=-79,21,IF($H$12-I12=80,20,IF($H$12-I12=-80,20,IF($H$12-I12=81,19,IF($H$12-I12=-81,19,IF($H$12-I12=82,18,IF($H$12-I12=-82,18,IF($H$12-I12=83,17,IF($H$12-I12=-83,17,IF($H$12-I12=84,16,IF($H$12-I12=-84,16,IF($H$12-I12=85,15,IF($H$12-I12=-85,15,IF($H$12-I12=86,14,IF($H$12-I12=-86,14,IF($H$12-I12=87,13,IF($H$12-I12=-87,13,IF($H$12-I12=88,12,IF($H$12-I12=-88,12,IF($H$12-I12=89,11,IF($H$12-I12=-89,11,IF($H$12-I12=90,10,IF($H$12-I12=-90,10,IF($H$12-I12=91,9,IF($H$12-I12=-91,9,IF($H$12-I12=92,8,IF($H$12-I12=-92,8,IF($H$12-I12=93,7,IF($H$12-I12=-93,7,IF($H$12-I12=94,6,IF($H$12-I12=-94,6,IF($H$12-I12=95,5,IF($H$12-I12=-95,5,IF($H$12-I12=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -30317,7 +30321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="4:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:12" x14ac:dyDescent="0.25">
       <c r="I17" s="4">
         <f>IF($H$12-I12=-96,4,IF($H$12-I12=97,3,IF($H$12-I12=-97,3,IF($H$12-I12=98,2,IF($H$12-I12=-98,2,IF($H$12-I12=99,1,IF($H$12-I12=-99,1,IF($H$12-I12=100,0,IF($H$12-I12=-100,0,0)))))))))</f>
         <v>0</v>
@@ -30335,25 +30339,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="152"/>
       <c r="E18" s="152"/>
       <c r="F18" s="152"/>
       <c r="G18" s="152"/>
     </row>
-    <row r="19" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="152"/>
       <c r="E19" s="152"/>
       <c r="F19" s="152"/>
       <c r="G19" s="152"/>
     </row>
-    <row r="20" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="152"/>
       <c r="E20" s="152"/>
       <c r="F20" s="152"/>
       <c r="G20" s="152"/>
     </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I41" s="3">
         <v>1</v>
       </c>
@@ -30418,14 +30422,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B1:O99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="11.44140625" style="1"/>
-    <col min="7" max="7" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.44140625" style="1"/>
+    <col min="1" max="6" width="11.42578125" style="1"/>
+    <col min="7" max="7" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
@@ -30471,7 +30475,7 @@
         <v>SI(G28-H28=-2;98;</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
@@ -30514,7 +30518,7 @@
         <v>SI(G28-H28=-3;97;</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
@@ -30557,7 +30561,7 @@
         <v>SI(G28-H28=-4;96;</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
@@ -30600,7 +30604,7 @@
         <v>SI(G28-H28=-5;95;</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
@@ -30643,7 +30647,7 @@
         <v>SI(G28-H28=-6;94;</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
@@ -30686,7 +30690,7 @@
         <v>SI(G28-H28=-7;93;</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
@@ -30729,7 +30733,7 @@
         <v>SI(G28-H28=-8;92;</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
@@ -30772,7 +30776,7 @@
         <v>SI(G28-H28=-9;91;</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
@@ -30815,7 +30819,7 @@
         <v>SI(G28-H28=-10;90;</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
@@ -30858,7 +30862,7 @@
         <v>SI(G28-H28=-11;89;</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
@@ -30901,7 +30905,7 @@
         <v>SI(G28-H28=-12;88;</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
@@ -30944,7 +30948,7 @@
         <v>SI(G28-H28=-13;87;</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
@@ -30987,7 +30991,7 @@
         <v>SI(G28-H28=-14;86;</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
@@ -31030,7 +31034,7 @@
         <v>SI(G28-H28=-15;85;</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>11</v>
       </c>
@@ -31073,7 +31077,7 @@
         <v>SI(G28-H28=-16;84;</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
@@ -31116,7 +31120,7 @@
         <v>SI(G28-H28=-17;83;</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>11</v>
       </c>
@@ -31159,7 +31163,7 @@
         <v>SI(G28-H28=-18;82;</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
@@ -31202,7 +31206,7 @@
         <v>SI(G28-H28=-19;81;</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
@@ -31245,7 +31249,7 @@
         <v>SI(G28-H28=-20;80;</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>11</v>
       </c>
@@ -31288,7 +31292,7 @@
         <v>SI(G28-H28=-21;79;</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>11</v>
       </c>
@@ -31331,7 +31335,7 @@
         <v>SI(G28-H28=-22;78;</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>11</v>
       </c>
@@ -31374,7 +31378,7 @@
         <v>SI(G28-H28=-23;77;</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>11</v>
       </c>
@@ -31417,7 +31421,7 @@
         <v>SI(G28-H28=-24;76;</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
@@ -31460,7 +31464,7 @@
         <v>SI(G28-H28=-25;75;</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>11</v>
       </c>
@@ -31503,7 +31507,7 @@
         <v>SI(G28-H28=-26;74;</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>11</v>
       </c>
@@ -31546,7 +31550,7 @@
         <v>SI(G28-H28=-27;73;</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>11</v>
       </c>
@@ -31589,7 +31593,7 @@
         <v>SI(G28-H28=-28;72;</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>11</v>
       </c>
@@ -31632,7 +31636,7 @@
         <v>SI(G28-H28=-29;71;</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>11</v>
       </c>
@@ -31675,7 +31679,7 @@
         <v>SI(G28-H28=-30;70;</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>11</v>
       </c>
@@ -31718,7 +31722,7 @@
         <v>SI(G28-H28=-31;69;</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>11</v>
       </c>
@@ -31761,7 +31765,7 @@
         <v>SI(G28-H28=-32;68;</v>
       </c>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
         <v>11</v>
       </c>
@@ -31804,7 +31808,7 @@
         <v>SI(G28-H28=-33;67;</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
         <v>11</v>
       </c>
@@ -31847,7 +31851,7 @@
         <v>SI(G28-H28=-34;66;</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
@@ -31890,7 +31894,7 @@
         <v>SI(G28-H28=-35;65;</v>
       </c>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>11</v>
       </c>
@@ -31933,7 +31937,7 @@
         <v>SI(G28-H28=-36;64;</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>11</v>
       </c>
@@ -31976,7 +31980,7 @@
         <v>SI(G28-H28=-37;63;</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>11</v>
       </c>
@@ -32019,7 +32023,7 @@
         <v>SI(G28-H28=-38;62;</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
         <v>11</v>
       </c>
@@ -32062,7 +32066,7 @@
         <v>SI(G28-H28=-39;61;</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
         <v>11</v>
       </c>
@@ -32105,7 +32109,7 @@
         <v>SI(G28-H28=-40;60;</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
         <v>11</v>
       </c>
@@ -32148,7 +32152,7 @@
         <v>SI(G28-H28=-41;59;</v>
       </c>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
         <v>11</v>
       </c>
@@ -32191,7 +32195,7 @@
         <v>SI(G28-H28=-42;58;</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>11</v>
       </c>
@@ -32234,7 +32238,7 @@
         <v>SI(G28-H28=-43;57;</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
         <v>11</v>
       </c>
@@ -32277,7 +32281,7 @@
         <v>SI(G28-H28=-44;56;</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>11</v>
       </c>
@@ -32320,7 +32324,7 @@
         <v>SI(G28-H28=-45;55;</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
         <v>11</v>
       </c>
@@ -32363,7 +32367,7 @@
         <v>SI(G28-H28=-46;54;</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>11</v>
       </c>
@@ -32406,7 +32410,7 @@
         <v>SI(G28-H28=-47;53;</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
         <v>11</v>
       </c>
@@ -32449,7 +32453,7 @@
         <v>SI(G28-H28=-48;52;</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
         <v>11</v>
       </c>
@@ -32492,7 +32496,7 @@
         <v>SI(G28-H28=-49;51;</v>
       </c>
     </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
@@ -32535,7 +32539,7 @@
         <v>SI(G28-H28=-50;50;</v>
       </c>
     </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>11</v>
       </c>
@@ -32578,7 +32582,7 @@
         <v>SI(G28-H28=-51;49;</v>
       </c>
     </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
         <v>11</v>
       </c>
@@ -32621,7 +32625,7 @@
         <v>SI(G28-H28=-52;48;</v>
       </c>
     </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
         <v>11</v>
       </c>
@@ -32664,7 +32668,7 @@
         <v>SI(G28-H28=-53;47;</v>
       </c>
     </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
         <v>11</v>
       </c>
@@ -32707,7 +32711,7 @@
         <v>SI(G28-H28=-54;46;</v>
       </c>
     </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
         <v>11</v>
       </c>
@@ -32750,7 +32754,7 @@
         <v>SI(G28-H28=-55;45;</v>
       </c>
     </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>11</v>
       </c>
@@ -32793,7 +32797,7 @@
         <v>SI(G28-H28=-56;44;</v>
       </c>
     </row>
-    <row r="56" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
         <v>11</v>
       </c>
@@ -32836,7 +32840,7 @@
         <v>SI(G28-H28=-57;43;</v>
       </c>
     </row>
-    <row r="57" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
         <v>11</v>
       </c>
@@ -32879,7 +32883,7 @@
         <v>SI(G28-H28=-58;42;</v>
       </c>
     </row>
-    <row r="58" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
         <v>11</v>
       </c>
@@ -32922,7 +32926,7 @@
         <v>SI(G28-H28=-59;41;</v>
       </c>
     </row>
-    <row r="59" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
         <v>11</v>
       </c>
@@ -32965,7 +32969,7 @@
         <v>SI(G28-H28=-60;40;</v>
       </c>
     </row>
-    <row r="60" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
         <v>11</v>
       </c>
@@ -33008,7 +33012,7 @@
         <v>SI(G28-H28=-61;39;</v>
       </c>
     </row>
-    <row r="61" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
         <v>11</v>
       </c>
@@ -33051,7 +33055,7 @@
         <v>SI(G28-H28=-62;38;</v>
       </c>
     </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
         <v>11</v>
       </c>
@@ -33094,7 +33098,7 @@
         <v>SI(G28-H28=-63;37;</v>
       </c>
     </row>
-    <row r="63" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
         <v>11</v>
       </c>
@@ -33137,7 +33141,7 @@
         <v>SI(G28-H28=-64;36;</v>
       </c>
     </row>
-    <row r="64" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
         <v>11</v>
       </c>
@@ -33180,7 +33184,7 @@
         <v>SI(G28-H28=-65;35;</v>
       </c>
     </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
         <v>11</v>
       </c>
@@ -33223,7 +33227,7 @@
         <v>SI(G28-H28=-66;34;</v>
       </c>
     </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
         <v>11</v>
       </c>
@@ -33266,7 +33270,7 @@
         <v>SI(G28-H28=-67;33;</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B67" s="1" t="s">
         <v>11</v>
       </c>
@@ -33309,7 +33313,7 @@
         <v>SI(G28-H28=-68;32;</v>
       </c>
     </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
         <v>11</v>
       </c>
@@ -33352,7 +33356,7 @@
         <v>SI(G28-H28=-69;31;</v>
       </c>
     </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
         <v>11</v>
       </c>
@@ -33395,7 +33399,7 @@
         <v>SI(G28-H28=-70;30;</v>
       </c>
     </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B70" s="1" t="s">
         <v>11</v>
       </c>
@@ -33438,7 +33442,7 @@
         <v>SI(G28-H28=-71;29;</v>
       </c>
     </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B71" s="1" t="s">
         <v>11</v>
       </c>
@@ -33481,7 +33485,7 @@
         <v>SI(G28-H28=-72;28;</v>
       </c>
     </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
         <v>11</v>
       </c>
@@ -33524,7 +33528,7 @@
         <v>SI(G28-H28=-73;27;</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B73" s="1" t="s">
         <v>11</v>
       </c>
@@ -33567,7 +33571,7 @@
         <v>SI(G28-H28=-74;26;</v>
       </c>
     </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
         <v>11</v>
       </c>
@@ -33610,7 +33614,7 @@
         <v>SI(G28-H28=-75;25;</v>
       </c>
     </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B75" s="1" t="s">
         <v>11</v>
       </c>
@@ -33653,7 +33657,7 @@
         <v>SI(G28-H28=-76;24;</v>
       </c>
     </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
         <v>11</v>
       </c>
@@ -33696,7 +33700,7 @@
         <v>SI(G28-H28=-77;23;</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
         <v>11</v>
       </c>
@@ -33739,7 +33743,7 @@
         <v>SI(G28-H28=-78;22;</v>
       </c>
     </row>
-    <row r="78" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B78" s="1" t="s">
         <v>11</v>
       </c>
@@ -33782,7 +33786,7 @@
         <v>SI(G28-H28=-79;21;</v>
       </c>
     </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
         <v>11</v>
       </c>
@@ -33825,7 +33829,7 @@
         <v>SI(G28-H28=-80;20;</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B80" s="1" t="s">
         <v>11</v>
       </c>
@@ -33868,7 +33872,7 @@
         <v>SI(G28-H28=-81;19;</v>
       </c>
     </row>
-    <row r="81" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
         <v>11</v>
       </c>
@@ -33911,7 +33915,7 @@
         <v>SI(G28-H28=-82;18;</v>
       </c>
     </row>
-    <row r="82" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
         <v>11</v>
       </c>
@@ -33954,7 +33958,7 @@
         <v>SI(G28-H28=-83;17;</v>
       </c>
     </row>
-    <row r="83" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B83" s="1" t="s">
         <v>11</v>
       </c>
@@ -33997,7 +34001,7 @@
         <v>SI(G28-H28=-84;16;</v>
       </c>
     </row>
-    <row r="84" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B84" s="1" t="s">
         <v>11</v>
       </c>
@@ -34040,7 +34044,7 @@
         <v>SI(G28-H28=-85;15;</v>
       </c>
     </row>
-    <row r="85" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B85" s="1" t="s">
         <v>11</v>
       </c>
@@ -34083,7 +34087,7 @@
         <v>SI(G28-H28=-86;14;</v>
       </c>
     </row>
-    <row r="86" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
         <v>11</v>
       </c>
@@ -34126,7 +34130,7 @@
         <v>SI(G28-H28=-87;13;</v>
       </c>
     </row>
-    <row r="87" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
         <v>11</v>
       </c>
@@ -34169,7 +34173,7 @@
         <v>SI(G28-H28=-88;12;</v>
       </c>
     </row>
-    <row r="88" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
         <v>11</v>
       </c>
@@ -34212,7 +34216,7 @@
         <v>SI(G28-H28=-89;11;</v>
       </c>
     </row>
-    <row r="89" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
         <v>11</v>
       </c>
@@ -34255,7 +34259,7 @@
         <v>SI(G28-H28=-90;10;</v>
       </c>
     </row>
-    <row r="90" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
         <v>11</v>
       </c>
@@ -34298,7 +34302,7 @@
         <v>SI(G28-H28=-91;9;</v>
       </c>
     </row>
-    <row r="91" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
         <v>11</v>
       </c>
@@ -34341,7 +34345,7 @@
         <v>SI(G28-H28=-92;8;</v>
       </c>
     </row>
-    <row r="92" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B92" s="1" t="s">
         <v>11</v>
       </c>
@@ -34384,7 +34388,7 @@
         <v>SI(G28-H28=-93;7;</v>
       </c>
     </row>
-    <row r="93" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B93" s="1" t="s">
         <v>11</v>
       </c>
@@ -34427,7 +34431,7 @@
         <v>SI(G28-H28=-94;6;</v>
       </c>
     </row>
-    <row r="94" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B94" s="1" t="s">
         <v>11</v>
       </c>
@@ -34470,7 +34474,7 @@
         <v>SI(G28-H28=-95;5;</v>
       </c>
     </row>
-    <row r="95" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B95" s="1" t="s">
         <v>11</v>
       </c>
@@ -34513,7 +34517,7 @@
         <v>SI(G28-H28=-96;4;</v>
       </c>
     </row>
-    <row r="96" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
         <v>11</v>
       </c>
@@ -34556,7 +34560,7 @@
         <v>SI(G28-H28=-97;3;</v>
       </c>
     </row>
-    <row r="97" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B97" s="1" t="s">
         <v>11</v>
       </c>
@@ -34599,7 +34603,7 @@
         <v>SI(G28-H28=-98;2;</v>
       </c>
     </row>
-    <row r="98" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B98" s="1" t="s">
         <v>11</v>
       </c>
@@ -34642,7 +34646,7 @@
         <v>SI(G28-H28=-99;1;</v>
       </c>
     </row>
-    <row r="99" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B99" s="1" t="s">
         <v>11</v>
       </c>

--- a/Copa del Mundo-2026 trabajo.xlsx
+++ b/Copa del Mundo-2026 trabajo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_corporativa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="8_{4B119FBF-818B-466F-B1F3-AB97609A7929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64931F7B-5CD0-42CE-B0D4-BE1E28845573}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="8_{4B119FBF-818B-466F-B1F3-AB97609A7929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04361354-ABD1-475A-A781-97BF814D5C0D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2679,14 +2679,14 @@
       <c r="O2" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="P2" s="52" t="s">
+      <c r="P2" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q2" s="52" t="s">
+        <v>173</v>
+      </c>
+      <c r="R2" s="52" t="s">
         <v>167</v>
-      </c>
-      <c r="Q2" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="R2" s="52" t="s">
-        <v>173</v>
       </c>
       <c r="S2" s="36" t="s">
         <v>142</v>
@@ -2698,13 +2698,13 @@
         <v>138</v>
       </c>
       <c r="V2" s="52" t="s">
+        <v>171</v>
+      </c>
+      <c r="W2" s="52" t="s">
         <v>169</v>
       </c>
-      <c r="W2" s="52" t="s">
+      <c r="X2" s="52" t="s">
         <v>158</v>
-      </c>
-      <c r="X2" s="52" t="s">
-        <v>171</v>
       </c>
       <c r="Y2" s="52" t="s">
         <v>145</v>
@@ -2725,13 +2725,13 @@
         <v>134</v>
       </c>
       <c r="AE2" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="AF2" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="AF2" s="52" t="s">
+      <c r="AG2" s="52" t="s">
         <v>148</v>
-      </c>
-      <c r="AG2" s="36" t="s">
-        <v>156</v>
       </c>
       <c r="AH2" s="36" t="s">
         <v>130</v>
@@ -2745,11 +2745,11 @@
       <c r="AK2" s="52" t="s">
         <v>152</v>
       </c>
-      <c r="AL2" s="52" t="s">
+      <c r="AL2" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="AM2" s="58" t="s">
         <v>150</v>
-      </c>
-      <c r="AM2" s="53" t="s">
-        <v>175</v>
       </c>
       <c r="AN2" s="58" t="s">
         <v>151</v>
@@ -2801,151 +2801,151 @@
       </c>
       <c r="J3" s="67">
         <f>SUM(J4+J5)-SUM(J6+J7)</f>
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K3" s="68">
         <f>SUM(K4+K5)-SUM(K6+K7)</f>
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L3" s="68">
         <f>SUM(L4+L5)-SUM(L6+L7)</f>
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="M3" s="68">
         <f>SUM(M4+M5)-SUM(M6+M7)</f>
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="N3" s="68">
         <f>SUM(N4+N5)-SUM(N6+N7)</f>
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="O3" s="68">
         <f>SUM(O4+O5)-SUM(O6+O7)</f>
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="P3" s="68">
         <f>SUM(P4+P5)-SUM(P6+P7)</f>
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="Q3" s="68">
         <f>SUM(Q4+Q5)-SUM(Q6+Q7)</f>
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="R3" s="68">
         <f>SUM(R4+R5)-SUM(R6+R7)</f>
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="S3" s="68">
         <f>SUM(S4+S5)-SUM(S6+S7)</f>
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="T3" s="68">
         <f>SUM(T4+T5)-SUM(T6+T7)</f>
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="U3" s="68">
         <f>SUM(U4+U5)-SUM(U6+U7)</f>
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="V3" s="68">
         <f>SUM(V4+V5)-SUM(V6+V7)</f>
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="W3" s="68">
         <f>SUM(W4+W5)-SUM(W6+W7)</f>
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="X3" s="68">
         <f>SUM(X4+X5)-SUM(X6+X7)</f>
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="Y3" s="68">
         <f>SUM(Y4+Y5)-SUM(Y6+Y7)</f>
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="Z3" s="68">
         <f>SUM(Z4+Z5)-SUM(Z6+Z7)</f>
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="AA3" s="68">
         <f>SUM(AA4+AA5)-SUM(AA6+AA7)</f>
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="AB3" s="68">
         <f>SUM(AB4+AB5)-SUM(AB6+AB7)</f>
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="AC3" s="68">
         <f>SUM(AC4+AC5)-SUM(AC6+AC7)</f>
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="AD3" s="68">
         <f>SUM(AD4+AD5)-SUM(AD6+AD7)</f>
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AE3" s="68">
         <f>SUM(AE4+AE5)-SUM(AE6+AE7)</f>
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AF3" s="68">
         <f>SUM(AF4+AF5)-SUM(AF6+AF7)</f>
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AG3" s="68">
         <f>SUM(AG4+AG5)-SUM(AG6+AG7)</f>
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AH3" s="68">
         <f>SUM(AH4+AH5)-SUM(AH6+AH7)</f>
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI3" s="68">
         <f>SUM(AI4+AI5)-SUM(AI6+AI7)</f>
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AJ3" s="68">
         <f>SUM(AJ4+AJ5)-SUM(AJ6+AJ7)</f>
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AK3" s="68">
         <f>SUM(AK4+AK5)-SUM(AK6+AK7)</f>
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AL3" s="68">
         <f>SUM(AL4+AL5)-SUM(AL6+AL7)</f>
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AM3" s="68">
         <f>SUM(AM4+AM5)-SUM(AM6+AM7)</f>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AN3" s="68">
         <f>SUM(AN4+AN5)-SUM(AN6+AN7)</f>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AO3" s="68">
         <f>SUM(AO4+AO5)-SUM(AO6+AO7)</f>
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AP3" s="68">
         <f>SUM(AP4+AP5)-SUM(AP6+AP7)</f>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AQ3" s="68">
         <f>SUM(AQ4+AQ5)-SUM(AQ6+AQ7)</f>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AR3" s="68">
         <f>SUM(AR4+AR5)-SUM(AR6+AR7)</f>
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="AS3" s="68">
         <f>SUM(AS4+AS5)-SUM(AS6+AS7)</f>
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="AT3" s="69">
         <f>SUM(AT4+AT5)-SUM(AT6+AT7)</f>
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:54" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -2991,7 +2991,7 @@
       <c r="P4" s="73">
         <f>SUM(IF(P8=$I$8,3,0)+IF(P9=$G8+$H8,1,0)+IF(P10=$I$10,3,0)+IF(P11=$G10+$H10,1,0)+IF(P12=$I$12,3,0)+IF(P13=$G12+$H12,1,0)+IF(P14=$I$14,3,0)+IF(P15=$G14+$H14,1,0)
 +IF(P16=$I$16,3,0)+IF(P17=$G16+$H16,1,0)+IF(P18=$I$18,3,0)+IF(P19=$G18+$H18,1,0)+IF(P20=$I$20,3,0)+IF(P21=$G20+$H20,1,0)+IF(P22=$I$22,3,0)+IF(P23=$G22+$H22,1,0)+IF(P24=$I$24,3,0)+IF(P25=$G24+$H24,1,0)+IF(P26=$I$26,3,0)+IF(P27=$G26+$H26,1,0)+IF(P28=$I$28,3,0)+IF(P29=$G28+$H28,1,0)+IF(P30=$I$30,3,0)+IF(P31=$G30+$H30,1,0)+IF(P32=$I$32,3,0)+IF(P33=$G32+$H32,1,0)+IF(P34=$I$34,3,0)+IF(P35=$G34+$H34,1,0)+IF(P36=$I$36,3,0)+IF(P37=$G36+$H36,1,0)+IF(P38=$I$38,3,0)+IF(P39=$G38+$H38,1,0)+IF(P40=$I$40,3,0)+IF(P41=$G40+$H40,1,0)+IF(P42=$I$42,3,0)+IF(P43=$G42+$H42,1,0)+IF(P44=$I$44,3,0)+IF(P45=$G44+$H44,1,0)+IF(P46=$I$46,3,0)+IF(P47=$G46+$H46,1,0)+IF(P48=$I$48,3,0)+IF(P49=$G48+$H48,1,0)+IF(P50=$I$50,3,0)+IF(P51=$G50+$H50,1,0)+IF(P52=$I$52,3,0)+IF(P53=$G52+$H52,1,0)+IF(P54=$I$54,3,0)+IF(P55=$G54+$H54,1,0)+IF(P56=$I$56,3,0)+IF(P57=$G56+$H56,1,0)+IF(P58=$I$58,3,0)+IF(P59=$G58+$H58,1,0)+IF(P60=$I$60,3,0)+IF(P61=$G60+$H60,1,0)+IF(P62=$I$62,3,0)+IF(P63=$G62+$H62,1,0)+IF(P64=$I$64,3,0)+IF(P65=$G64+$H64,1,0)+IF(P66=$I$66,3,0)+IF(P67=$G66+$H66,1,0)+IF(P68=$I$68,3,0)+IF(P69=$G68+$H68,1,0)+IF(P70=$I$70,3,0)+IF(P71=$G70+$H70,1,0)+IF(P72=$I$72,3,0)+IF(P73=$G72+$H72,1,0)+IF(P74=$I$74,3,0)+IF(P75=$G74+$H74,1,0)+IF(P76=$I$76,3,0)+IF(P77=$G76+$H76,1,0)+IF(P78=$I$78,3,0)+IF(P79=$G78+$H78,1,0))</f>
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="Q4" s="73">
         <f>SUM(IF(Q8=$I$8,3,0)+IF(Q9=$G8+$H8,1,0)+IF(Q10=$I$10,3,0)+IF(Q11=$G10+$H10,1,0)+IF(Q12=$I$12,3,0)+IF(Q13=$G12+$H12,1,0)+IF(Q14=$I$14,3,0)+IF(Q15=$G14+$H14,1,0)
@@ -3001,7 +3001,7 @@
       <c r="R4" s="73">
         <f>SUM(IF(R8=$I$8,3,0)+IF(R9=$G8+$H8,1,0)+IF(R10=$I$10,3,0)+IF(R11=$G10+$H10,1,0)+IF(R12=$I$12,3,0)+IF(R13=$G12+$H12,1,0)+IF(R14=$I$14,3,0)+IF(R15=$G14+$H14,1,0)
 +IF(R16=$I$16,3,0)+IF(R17=$G16+$H16,1,0)+IF(R18=$I$18,3,0)+IF(R19=$G18+$H18,1,0)+IF(R20=$I$20,3,0)+IF(R21=$G20+$H20,1,0)+IF(R22=$I$22,3,0)+IF(R23=$G22+$H22,1,0)+IF(R24=$I$24,3,0)+IF(R25=$G24+$H24,1,0)+IF(R26=$I$26,3,0)+IF(R27=$G26+$H26,1,0)+IF(R28=$I$28,3,0)+IF(R29=$G28+$H28,1,0)+IF(R30=$I$30,3,0)+IF(R31=$G30+$H30,1,0)+IF(R32=$I$32,3,0)+IF(R33=$G32+$H32,1,0)+IF(R34=$I$34,3,0)+IF(R35=$G34+$H34,1,0)+IF(R36=$I$36,3,0)+IF(R37=$G36+$H36,1,0)+IF(R38=$I$38,3,0)+IF(R39=$G38+$H38,1,0)+IF(R40=$I$40,3,0)+IF(R41=$G40+$H40,1,0)+IF(R42=$I$42,3,0)+IF(R43=$G42+$H42,1,0)+IF(R44=$I$44,3,0)+IF(R45=$G44+$H44,1,0)+IF(R46=$I$46,3,0)+IF(R47=$G46+$H46,1,0)+IF(R48=$I$48,3,0)+IF(R49=$G48+$H48,1,0)+IF(R50=$I$50,3,0)+IF(R51=$G50+$H50,1,0)+IF(R52=$I$52,3,0)+IF(R53=$G52+$H52,1,0)+IF(R54=$I$54,3,0)+IF(R55=$G54+$H54,1,0)+IF(R56=$I$56,3,0)+IF(R57=$G56+$H56,1,0)+IF(R58=$I$58,3,0)+IF(R59=$G58+$H58,1,0)+IF(R60=$I$60,3,0)+IF(R61=$G60+$H60,1,0)+IF(R62=$I$62,3,0)+IF(R63=$G62+$H62,1,0)+IF(R64=$I$64,3,0)+IF(R65=$G64+$H64,1,0)+IF(R66=$I$66,3,0)+IF(R67=$G66+$H66,1,0)+IF(R68=$I$68,3,0)+IF(R69=$G68+$H68,1,0)+IF(R70=$I$70,3,0)+IF(R71=$G70+$H70,1,0)+IF(R72=$I$72,3,0)+IF(R73=$G72+$H72,1,0)+IF(R74=$I$74,3,0)+IF(R75=$G74+$H74,1,0)+IF(R76=$I$76,3,0)+IF(R77=$G76+$H76,1,0)+IF(R78=$I$78,3,0)+IF(R79=$G78+$H78,1,0))</f>
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="S4" s="73">
         <f>SUM(IF(S8=$I$8,3,0)+IF(S9=$G8+$H8,1,0)+IF(S10=$I$10,3,0)+IF(S11=$G10+$H10,1,0)+IF(S12=$I$12,3,0)+IF(S13=$G12+$H12,1,0)+IF(S14=$I$14,3,0)+IF(S15=$G14+$H14,1,0)
@@ -3021,17 +3021,17 @@
       <c r="V4" s="73">
         <f>SUM(IF(V8=$I$8,3,0)+IF(V9=$G8+$H8,1,0)+IF(V10=$I$10,3,0)+IF(V11=$G10+$H10,1,0)+IF(V12=$I$12,3,0)+IF(V13=$G12+$H12,1,0)+IF(V14=$I$14,3,0)+IF(V15=$G14+$H14,1,0)
 +IF(V16=$I$16,3,0)+IF(V17=$G16+$H16,1,0)+IF(V18=$I$18,3,0)+IF(V19=$G18+$H18,1,0)+IF(V20=$I$20,3,0)+IF(V21=$G20+$H20,1,0)+IF(V22=$I$22,3,0)+IF(V23=$G22+$H22,1,0)+IF(V24=$I$24,3,0)+IF(V25=$G24+$H24,1,0)+IF(V26=$I$26,3,0)+IF(V27=$G26+$H26,1,0)+IF(V28=$I$28,3,0)+IF(V29=$G28+$H28,1,0)+IF(V30=$I$30,3,0)+IF(V31=$G30+$H30,1,0)+IF(V32=$I$32,3,0)+IF(V33=$G32+$H32,1,0)+IF(V34=$I$34,3,0)+IF(V35=$G34+$H34,1,0)+IF(V36=$I$36,3,0)+IF(V37=$G36+$H36,1,0)+IF(V38=$I$38,3,0)+IF(V39=$G38+$H38,1,0)+IF(V40=$I$40,3,0)+IF(V41=$G40+$H40,1,0)+IF(V42=$I$42,3,0)+IF(V43=$G42+$H42,1,0)+IF(V44=$I$44,3,0)+IF(V45=$G44+$H44,1,0)+IF(V46=$I$46,3,0)+IF(V47=$G46+$H46,1,0)+IF(V48=$I$48,3,0)+IF(V49=$G48+$H48,1,0)+IF(V50=$I$50,3,0)+IF(V51=$G50+$H50,1,0)+IF(V52=$I$52,3,0)+IF(V53=$G52+$H52,1,0)+IF(V54=$I$54,3,0)+IF(V55=$G54+$H54,1,0)+IF(V56=$I$56,3,0)+IF(V57=$G56+$H56,1,0)+IF(V58=$I$58,3,0)+IF(V59=$G58+$H58,1,0)+IF(V60=$I$60,3,0)+IF(V61=$G60+$H60,1,0)+IF(V62=$I$62,3,0)+IF(V63=$G62+$H62,1,0)+IF(V64=$I$64,3,0)+IF(V65=$G64+$H64,1,0)+IF(V66=$I$66,3,0)+IF(V67=$G66+$H66,1,0)+IF(V68=$I$68,3,0)+IF(V69=$G68+$H68,1,0)+IF(V70=$I$70,3,0)+IF(V71=$G70+$H70,1,0)+IF(V72=$I$72,3,0)+IF(V73=$G72+$H72,1,0)+IF(V74=$I$74,3,0)+IF(V75=$G74+$H74,1,0)+IF(V76=$I$76,3,0)+IF(V77=$G76+$H76,1,0)+IF(V78=$I$78,3,0)+IF(V79=$G78+$H78,1,0))</f>
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="W4" s="73">
         <f>SUM(IF(W8=$I$8,3,0)+IF(W9=$G8+$H8,1,0)+IF(W10=$I$10,3,0)+IF(W11=$G10+$H10,1,0)+IF(W12=$I$12,3,0)+IF(W13=$G12+$H12,1,0)+IF(W14=$I$14,3,0)+IF(W15=$G14+$H14,1,0)
 +IF(W16=$I$16,3,0)+IF(W17=$G16+$H16,1,0)+IF(W18=$I$18,3,0)+IF(W19=$G18+$H18,1,0)+IF(W20=$I$20,3,0)+IF(W21=$G20+$H20,1,0)+IF(W22=$I$22,3,0)+IF(W23=$G22+$H22,1,0)+IF(W24=$I$24,3,0)+IF(W25=$G24+$H24,1,0)+IF(W26=$I$26,3,0)+IF(W27=$G26+$H26,1,0)+IF(W28=$I$28,3,0)+IF(W29=$G28+$H28,1,0)+IF(W30=$I$30,3,0)+IF(W31=$G30+$H30,1,0)+IF(W32=$I$32,3,0)+IF(W33=$G32+$H32,1,0)+IF(W34=$I$34,3,0)+IF(W35=$G34+$H34,1,0)+IF(W36=$I$36,3,0)+IF(W37=$G36+$H36,1,0)+IF(W38=$I$38,3,0)+IF(W39=$G38+$H38,1,0)+IF(W40=$I$40,3,0)+IF(W41=$G40+$H40,1,0)+IF(W42=$I$42,3,0)+IF(W43=$G42+$H42,1,0)+IF(W44=$I$44,3,0)+IF(W45=$G44+$H44,1,0)+IF(W46=$I$46,3,0)+IF(W47=$G46+$H46,1,0)+IF(W48=$I$48,3,0)+IF(W49=$G48+$H48,1,0)+IF(W50=$I$50,3,0)+IF(W51=$G50+$H50,1,0)+IF(W52=$I$52,3,0)+IF(W53=$G52+$H52,1,0)+IF(W54=$I$54,3,0)+IF(W55=$G54+$H54,1,0)+IF(W56=$I$56,3,0)+IF(W57=$G56+$H56,1,0)+IF(W58=$I$58,3,0)+IF(W59=$G58+$H58,1,0)+IF(W60=$I$60,3,0)+IF(W61=$G60+$H60,1,0)+IF(W62=$I$62,3,0)+IF(W63=$G62+$H62,1,0)+IF(W64=$I$64,3,0)+IF(W65=$G64+$H64,1,0)+IF(W66=$I$66,3,0)+IF(W67=$G66+$H66,1,0)+IF(W68=$I$68,3,0)+IF(W69=$G68+$H68,1,0)+IF(W70=$I$70,3,0)+IF(W71=$G70+$H70,1,0)+IF(W72=$I$72,3,0)+IF(W73=$G72+$H72,1,0)+IF(W74=$I$74,3,0)+IF(W75=$G74+$H74,1,0)+IF(W76=$I$76,3,0)+IF(W77=$G76+$H76,1,0)+IF(W78=$I$78,3,0)+IF(W79=$G78+$H78,1,0))</f>
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="X4" s="73">
         <f>SUM(IF(X8=$I$8,3,0)+IF(X9=$G8+$H8,1,0)+IF(X10=$I$10,3,0)+IF(X11=$G10+$H10,1,0)+IF(X12=$I$12,3,0)+IF(X13=$G12+$H12,1,0)+IF(X14=$I$14,3,0)+IF(X15=$G14+$H14,1,0)
 +IF(X16=$I$16,3,0)+IF(X17=$G16+$H16,1,0)+IF(X18=$I$18,3,0)+IF(X19=$G18+$H18,1,0)+IF(X20=$I$20,3,0)+IF(X21=$G20+$H20,1,0)+IF(X22=$I$22,3,0)+IF(X23=$G22+$H22,1,0)+IF(X24=$I$24,3,0)+IF(X25=$G24+$H24,1,0)+IF(X26=$I$26,3,0)+IF(X27=$G26+$H26,1,0)+IF(X28=$I$28,3,0)+IF(X29=$G28+$H28,1,0)+IF(X30=$I$30,3,0)+IF(X31=$G30+$H30,1,0)+IF(X32=$I$32,3,0)+IF(X33=$G32+$H32,1,0)+IF(X34=$I$34,3,0)+IF(X35=$G34+$H34,1,0)+IF(X36=$I$36,3,0)+IF(X37=$G36+$H36,1,0)+IF(X38=$I$38,3,0)+IF(X39=$G38+$H38,1,0)+IF(X40=$I$40,3,0)+IF(X41=$G40+$H40,1,0)+IF(X42=$I$42,3,0)+IF(X43=$G42+$H42,1,0)+IF(X44=$I$44,3,0)+IF(X45=$G44+$H44,1,0)+IF(X46=$I$46,3,0)+IF(X47=$G46+$H46,1,0)+IF(X48=$I$48,3,0)+IF(X49=$G48+$H48,1,0)+IF(X50=$I$50,3,0)+IF(X51=$G50+$H50,1,0)+IF(X52=$I$52,3,0)+IF(X53=$G52+$H52,1,0)+IF(X54=$I$54,3,0)+IF(X55=$G54+$H54,1,0)+IF(X56=$I$56,3,0)+IF(X57=$G56+$H56,1,0)+IF(X58=$I$58,3,0)+IF(X59=$G58+$H58,1,0)+IF(X60=$I$60,3,0)+IF(X61=$G60+$H60,1,0)+IF(X62=$I$62,3,0)+IF(X63=$G62+$H62,1,0)+IF(X64=$I$64,3,0)+IF(X65=$G64+$H64,1,0)+IF(X66=$I$66,3,0)+IF(X67=$G66+$H66,1,0)+IF(X68=$I$68,3,0)+IF(X69=$G68+$H68,1,0)+IF(X70=$I$70,3,0)+IF(X71=$G70+$H70,1,0)+IF(X72=$I$72,3,0)+IF(X73=$G72+$H72,1,0)+IF(X74=$I$74,3,0)+IF(X75=$G74+$H74,1,0)+IF(X76=$I$76,3,0)+IF(X77=$G76+$H76,1,0)+IF(X78=$I$78,3,0)+IF(X79=$G78+$H78,1,0))</f>
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="Y4" s="73">
         <f>SUM(IF(Y8=$I$8,3,0)+IF(Y9=$G8+$H8,1,0)+IF(Y10=$I$10,3,0)+IF(Y11=$G10+$H10,1,0)+IF(Y12=$I$12,3,0)+IF(Y13=$G12+$H12,1,0)+IF(Y14=$I$14,3,0)+IF(Y15=$G14+$H14,1,0)
@@ -3066,17 +3066,17 @@
       <c r="AE4" s="73">
         <f>SUM(IF(AE8=$I$8,3,0)+IF(AE9=$G8+$H8,1,0)+IF(AE10=$I$10,3,0)+IF(AE11=$G10+$H10,1,0)+IF(AE12=$I$12,3,0)+IF(AE13=$G12+$H12,1,0)+IF(AE14=$I$14,3,0)+IF(AE15=$G14+$H14,1,0)
 +IF(AE16=$I$16,3,0)+IF(AE17=$G16+$H16,1,0)+IF(AE18=$I$18,3,0)+IF(AE19=$G18+$H18,1,0)+IF(AE20=$I$20,3,0)+IF(AE21=$G20+$H20,1,0)+IF(AE22=$I$22,3,0)+IF(AE23=$G22+$H22,1,0)+IF(AE24=$I$24,3,0)+IF(AE25=$G24+$H24,1,0)+IF(AE26=$I$26,3,0)+IF(AE27=$G26+$H26,1,0)+IF(AE28=$I$28,3,0)+IF(AE29=$G28+$H28,1,0)+IF(AE30=$I$30,3,0)+IF(AE31=$G30+$H30,1,0)+IF(AE32=$I$32,3,0)+IF(AE33=$G32+$H32,1,0)+IF(AE34=$I$34,3,0)+IF(AE35=$G34+$H34,1,0)+IF(AE36=$I$36,3,0)+IF(AE37=$G36+$H36,1,0)+IF(AE38=$I$38,3,0)+IF(AE39=$G38+$H38,1,0)+IF(AE40=$I$40,3,0)+IF(AE41=$G40+$H40,1,0)+IF(AE42=$I$42,3,0)+IF(AE43=$G42+$H42,1,0)+IF(AE44=$I$44,3,0)+IF(AE45=$G44+$H44,1,0)+IF(AE46=$I$46,3,0)+IF(AE47=$G46+$H46,1,0)+IF(AE48=$I$48,3,0)+IF(AE49=$G48+$H48,1,0)+IF(AE50=$I$50,3,0)+IF(AE51=$G50+$H50,1,0)+IF(AE52=$I$52,3,0)+IF(AE53=$G52+$H52,1,0)+IF(AE54=$I$54,3,0)+IF(AE55=$G54+$H54,1,0)+IF(AE56=$I$56,3,0)+IF(AE57=$G56+$H56,1,0)+IF(AE58=$I$58,3,0)+IF(AE59=$G58+$H58,1,0)+IF(AE60=$I$60,3,0)+IF(AE61=$G60+$H60,1,0)+IF(AE62=$I$62,3,0)+IF(AE63=$G62+$H62,1,0)+IF(AE64=$I$64,3,0)+IF(AE65=$G64+$H64,1,0)+IF(AE66=$I$66,3,0)+IF(AE67=$G66+$H66,1,0)+IF(AE68=$I$68,3,0)+IF(AE69=$G68+$H68,1,0)+IF(AE70=$I$70,3,0)+IF(AE71=$G70+$H70,1,0)+IF(AE72=$I$72,3,0)+IF(AE73=$G72+$H72,1,0)+IF(AE74=$I$74,3,0)+IF(AE75=$G74+$H74,1,0)+IF(AE76=$I$76,3,0)+IF(AE77=$G76+$H76,1,0)+IF(AE78=$I$78,3,0)+IF(AE79=$G78+$H78,1,0))</f>
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AF4" s="73">
         <f>SUM(IF(AF8=$I$8,3,0)+IF(AF9=$G8+$H8,1,0)+IF(AF10=$I$10,3,0)+IF(AF11=$G10+$H10,1,0)+IF(AF12=$I$12,3,0)+IF(AF13=$G12+$H12,1,0)+IF(AF14=$I$14,3,0)+IF(AF15=$G14+$H14,1,0)
 +IF(AF16=$I$16,3,0)+IF(AF17=$G16+$H16,1,0)+IF(AF18=$I$18,3,0)+IF(AF19=$G18+$H18,1,0)+IF(AF20=$I$20,3,0)+IF(AF21=$G20+$H20,1,0)+IF(AF22=$I$22,3,0)+IF(AF23=$G22+$H22,1,0)+IF(AF24=$I$24,3,0)+IF(AF25=$G24+$H24,1,0)+IF(AF26=$I$26,3,0)+IF(AF27=$G26+$H26,1,0)+IF(AF28=$I$28,3,0)+IF(AF29=$G28+$H28,1,0)+IF(AF30=$I$30,3,0)+IF(AF31=$G30+$H30,1,0)+IF(AF32=$I$32,3,0)+IF(AF33=$G32+$H32,1,0)+IF(AF34=$I$34,3,0)+IF(AF35=$G34+$H34,1,0)+IF(AF36=$I$36,3,0)+IF(AF37=$G36+$H36,1,0)+IF(AF38=$I$38,3,0)+IF(AF39=$G38+$H38,1,0)+IF(AF40=$I$40,3,0)+IF(AF41=$G40+$H40,1,0)+IF(AF42=$I$42,3,0)+IF(AF43=$G42+$H42,1,0)+IF(AF44=$I$44,3,0)+IF(AF45=$G44+$H44,1,0)+IF(AF46=$I$46,3,0)+IF(AF47=$G46+$H46,1,0)+IF(AF48=$I$48,3,0)+IF(AF49=$G48+$H48,1,0)+IF(AF50=$I$50,3,0)+IF(AF51=$G50+$H50,1,0)+IF(AF52=$I$52,3,0)+IF(AF53=$G52+$H52,1,0)+IF(AF54=$I$54,3,0)+IF(AF55=$G54+$H54,1,0)+IF(AF56=$I$56,3,0)+IF(AF57=$G56+$H56,1,0)+IF(AF58=$I$58,3,0)+IF(AF59=$G58+$H58,1,0)+IF(AF60=$I$60,3,0)+IF(AF61=$G60+$H60,1,0)+IF(AF62=$I$62,3,0)+IF(AF63=$G62+$H62,1,0)+IF(AF64=$I$64,3,0)+IF(AF65=$G64+$H64,1,0)+IF(AF66=$I$66,3,0)+IF(AF67=$G66+$H66,1,0)+IF(AF68=$I$68,3,0)+IF(AF69=$G68+$H68,1,0)+IF(AF70=$I$70,3,0)+IF(AF71=$G70+$H70,1,0)+IF(AF72=$I$72,3,0)+IF(AF73=$G72+$H72,1,0)+IF(AF74=$I$74,3,0)+IF(AF75=$G74+$H74,1,0)+IF(AF76=$I$76,3,0)+IF(AF77=$G76+$H76,1,0)+IF(AF78=$I$78,3,0)+IF(AF79=$G78+$H78,1,0))</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AG4" s="73">
         <f>SUM(IF(AG8=$I$8,3,0)+IF(AG9=$G8+$H8,1,0)+IF(AG10=$I$10,3,0)+IF(AG11=$G10+$H10,1,0)+IF(AG12=$I$12,3,0)+IF(AG13=$G12+$H12,1,0)+IF(AG14=$I$14,3,0)+IF(AG15=$G14+$H14,1,0)
 +IF(AG16=$I$16,3,0)+IF(AG17=$G16+$H16,1,0)+IF(AG18=$I$18,3,0)+IF(AG19=$G18+$H18,1,0)+IF(AG20=$I$20,3,0)+IF(AG21=$G20+$H20,1,0)+IF(AG22=$I$22,3,0)+IF(AG23=$G22+$H22,1,0)+IF(AG24=$I$24,3,0)+IF(AG25=$G24+$H24,1,0)+IF(AG26=$I$26,3,0)+IF(AG27=$G26+$H26,1,0)+IF(AG28=$I$28,3,0)+IF(AG29=$G28+$H28,1,0)+IF(AG30=$I$30,3,0)+IF(AG31=$G30+$H30,1,0)+IF(AG32=$I$32,3,0)+IF(AG33=$G32+$H32,1,0)+IF(AG34=$I$34,3,0)+IF(AG35=$G34+$H34,1,0)+IF(AG36=$I$36,3,0)+IF(AG37=$G36+$H36,1,0)+IF(AG38=$I$38,3,0)+IF(AG39=$G38+$H38,1,0)+IF(AG40=$I$40,3,0)+IF(AG41=$G40+$H40,1,0)+IF(AG42=$I$42,3,0)+IF(AG43=$G42+$H42,1,0)+IF(AG44=$I$44,3,0)+IF(AG45=$G44+$H44,1,0)+IF(AG46=$I$46,3,0)+IF(AG47=$G46+$H46,1,0)+IF(AG48=$I$48,3,0)+IF(AG49=$G48+$H48,1,0)+IF(AG50=$I$50,3,0)+IF(AG51=$G50+$H50,1,0)+IF(AG52=$I$52,3,0)+IF(AG53=$G52+$H52,1,0)+IF(AG54=$I$54,3,0)+IF(AG55=$G54+$H54,1,0)+IF(AG56=$I$56,3,0)+IF(AG57=$G56+$H56,1,0)+IF(AG58=$I$58,3,0)+IF(AG59=$G58+$H58,1,0)+IF(AG60=$I$60,3,0)+IF(AG61=$G60+$H60,1,0)+IF(AG62=$I$62,3,0)+IF(AG63=$G62+$H62,1,0)+IF(AG64=$I$64,3,0)+IF(AG65=$G64+$H64,1,0)+IF(AG66=$I$66,3,0)+IF(AG67=$G66+$H66,1,0)+IF(AG68=$I$68,3,0)+IF(AG69=$G68+$H68,1,0)+IF(AG70=$I$70,3,0)+IF(AG71=$G70+$H70,1,0)+IF(AG72=$I$72,3,0)+IF(AG73=$G72+$H72,1,0)+IF(AG74=$I$74,3,0)+IF(AG75=$G74+$H74,1,0)+IF(AG76=$I$76,3,0)+IF(AG77=$G76+$H76,1,0)+IF(AG78=$I$78,3,0)+IF(AG79=$G78+$H78,1,0))</f>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="AH4" s="73">
         <f>SUM(IF(AH8=$I$8,3,0)+IF(AH9=$G8+$H8,1,0)+IF(AH10=$I$10,3,0)+IF(AH11=$G10+$H10,1,0)+IF(AH12=$I$12,3,0)+IF(AH13=$G12+$H12,1,0)+IF(AH14=$I$14,3,0)+IF(AH15=$G14+$H14,1,0)
@@ -3101,12 +3101,12 @@
       <c r="AL4" s="73">
         <f>SUM(IF(AL8=$I$8,3,0)+IF(AL9=$G8+$H8,1,0)+IF(AL10=$I$10,3,0)+IF(AL11=$G10+$H10,1,0)+IF(AL12=$I$12,3,0)+IF(AL13=$G12+$H12,1,0)+IF(AL14=$I$14,3,0)+IF(AL15=$G14+$H14,1,0)
 +IF(AL16=$I$16,3,0)+IF(AL17=$G16+$H16,1,0)+IF(AL18=$I$18,3,0)+IF(AL19=$G18+$H18,1,0)+IF(AL20=$I$20,3,0)+IF(AL21=$G20+$H20,1,0)+IF(AL22=$I$22,3,0)+IF(AL23=$G22+$H22,1,0)+IF(AL24=$I$24,3,0)+IF(AL25=$G24+$H24,1,0)+IF(AL26=$I$26,3,0)+IF(AL27=$G26+$H26,1,0)+IF(AL28=$I$28,3,0)+IF(AL29=$G28+$H28,1,0)+IF(AL30=$I$30,3,0)+IF(AL31=$G30+$H30,1,0)+IF(AL32=$I$32,3,0)+IF(AL33=$G32+$H32,1,0)+IF(AL34=$I$34,3,0)+IF(AL35=$G34+$H34,1,0)+IF(AL36=$I$36,3,0)+IF(AL37=$G36+$H36,1,0)+IF(AL38=$I$38,3,0)+IF(AL39=$G38+$H38,1,0)+IF(AL40=$I$40,3,0)+IF(AL41=$G40+$H40,1,0)+IF(AL42=$I$42,3,0)+IF(AL43=$G42+$H42,1,0)+IF(AL44=$I$44,3,0)+IF(AL45=$G44+$H44,1,0)+IF(AL46=$I$46,3,0)+IF(AL47=$G46+$H46,1,0)+IF(AL48=$I$48,3,0)+IF(AL49=$G48+$H48,1,0)+IF(AL50=$I$50,3,0)+IF(AL51=$G50+$H50,1,0)+IF(AL52=$I$52,3,0)+IF(AL53=$G52+$H52,1,0)+IF(AL54=$I$54,3,0)+IF(AL55=$G54+$H54,1,0)+IF(AL56=$I$56,3,0)+IF(AL57=$G56+$H56,1,0)+IF(AL58=$I$58,3,0)+IF(AL59=$G58+$H58,1,0)+IF(AL60=$I$60,3,0)+IF(AL61=$G60+$H60,1,0)+IF(AL62=$I$62,3,0)+IF(AL63=$G62+$H62,1,0)+IF(AL64=$I$64,3,0)+IF(AL65=$G64+$H64,1,0)+IF(AL66=$I$66,3,0)+IF(AL67=$G66+$H66,1,0)+IF(AL68=$I$68,3,0)+IF(AL69=$G68+$H68,1,0)+IF(AL70=$I$70,3,0)+IF(AL71=$G70+$H70,1,0)+IF(AL72=$I$72,3,0)+IF(AL73=$G72+$H72,1,0)+IF(AL74=$I$74,3,0)+IF(AL75=$G74+$H74,1,0)+IF(AL76=$I$76,3,0)+IF(AL77=$G76+$H76,1,0)+IF(AL78=$I$78,3,0)+IF(AL79=$G78+$H78,1,0))</f>
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AM4" s="73">
         <f>SUM(IF(AM8=$I$8,3,0)+IF(AM9=$G8+$H8,1,0)+IF(AM10=$I$10,3,0)+IF(AM11=$G10+$H10,1,0)+IF(AM12=$I$12,3,0)+IF(AM13=$G12+$H12,1,0)+IF(AM14=$I$14,3,0)+IF(AM15=$G14+$H14,1,0)
 +IF(AM16=$I$16,3,0)+IF(AM17=$G16+$H16,1,0)+IF(AM18=$I$18,3,0)+IF(AM19=$G18+$H18,1,0)+IF(AM20=$I$20,3,0)+IF(AM21=$G20+$H20,1,0)+IF(AM22=$I$22,3,0)+IF(AM23=$G22+$H22,1,0)+IF(AM24=$I$24,3,0)+IF(AM25=$G24+$H24,1,0)+IF(AM26=$I$26,3,0)+IF(AM27=$G26+$H26,1,0)+IF(AM28=$I$28,3,0)+IF(AM29=$G28+$H28,1,0)+IF(AM30=$I$30,3,0)+IF(AM31=$G30+$H30,1,0)+IF(AM32=$I$32,3,0)+IF(AM33=$G32+$H32,1,0)+IF(AM34=$I$34,3,0)+IF(AM35=$G34+$H34,1,0)+IF(AM36=$I$36,3,0)+IF(AM37=$G36+$H36,1,0)+IF(AM38=$I$38,3,0)+IF(AM39=$G38+$H38,1,0)+IF(AM40=$I$40,3,0)+IF(AM41=$G40+$H40,1,0)+IF(AM42=$I$42,3,0)+IF(AM43=$G42+$H42,1,0)+IF(AM44=$I$44,3,0)+IF(AM45=$G44+$H44,1,0)+IF(AM46=$I$46,3,0)+IF(AM47=$G46+$H46,1,0)+IF(AM48=$I$48,3,0)+IF(AM49=$G48+$H48,1,0)+IF(AM50=$I$50,3,0)+IF(AM51=$G50+$H50,1,0)+IF(AM52=$I$52,3,0)+IF(AM53=$G52+$H52,1,0)+IF(AM54=$I$54,3,0)+IF(AM55=$G54+$H54,1,0)+IF(AM56=$I$56,3,0)+IF(AM57=$G56+$H56,1,0)+IF(AM58=$I$58,3,0)+IF(AM59=$G58+$H58,1,0)+IF(AM60=$I$60,3,0)+IF(AM61=$G60+$H60,1,0)+IF(AM62=$I$62,3,0)+IF(AM63=$G62+$H62,1,0)+IF(AM64=$I$64,3,0)+IF(AM65=$G64+$H64,1,0)+IF(AM66=$I$66,3,0)+IF(AM67=$G66+$H66,1,0)+IF(AM68=$I$68,3,0)+IF(AM69=$G68+$H68,1,0)+IF(AM70=$I$70,3,0)+IF(AM71=$G70+$H70,1,0)+IF(AM72=$I$72,3,0)+IF(AM73=$G72+$H72,1,0)+IF(AM74=$I$74,3,0)+IF(AM75=$G74+$H74,1,0)+IF(AM76=$I$76,3,0)+IF(AM77=$G76+$H76,1,0)+IF(AM78=$I$78,3,0)+IF(AM79=$G78+$H78,1,0))</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AN4" s="73">
         <f>SUM(IF(AN8=$I$8,3,0)+IF(AN9=$G8+$H8,1,0)+IF(AN10=$I$10,3,0)+IF(AN11=$G10+$H10,1,0)+IF(AN12=$I$12,3,0)+IF(AN13=$G12+$H12,1,0)+IF(AN14=$I$14,3,0)+IF(AN15=$G14+$H14,1,0)
@@ -3156,151 +3156,151 @@
       <c r="I5" s="66"/>
       <c r="J5" s="74">
         <f>SUM(IF(J80=$I$80,3,0)+IF(J81=$G80+$H80,1,0)+IF(J82=$I$82,3,0)+IF(J83=$G82+$H82,1,0)+IF(J84=$I$84,3,0)+IF(J85=$G84+$H84,1,0)+IF(J86=$I$86,3,0)+IF(J87=$G86+$H86,1,0)+IF(J88=$I$88,3,0)+IF(J89=$G88+$H88,1,0)+IF(J90=$I$90,3,0)+IF(J91=$G90+$H90,1,0)+IF(J92=$I$92,3,0)+IF(J93=$G92+$H92,1,0)+IF(J94=$I$94,3,0)+IF(J95=$G94+$H94,1,0)+IF(J96=$I$96,3,0)+IF(J97=$G96+$H96,1,0)+IF(J98=$I$98,3,0)+IF(J99=$G98+$H98,1,0)+IF(J100=$I$100,3,0)+IF(J101=$G100+$H100,1,0)+IF(J102=$I$102,3,0)+IF(J103=$G102+$H102,1,0)+IF(J104=$I$104,3,0)+IF(J105=$G104+$H104,1,0)+IF(J106=$I$106,3,0)+IF(J107=$G106+$H106,1,0)+IF(J108=$I$108,3,0)+IF(J109=$G108+$H108,1,0)+IF(J110=$I$110,3,0)+IF(J111=$G110+$H110,1,0)+IF(J112=$I$112,3,0)+IF(J113=$G112+$H112,1,0)+IF(J114=$I$114,3,0)+IF(J115=$G114+$H114,1,0)+IF(J116=$I$116,3,0)+IF(J117=$G116+$H116,1,0)+IF(J118=$I$118,3,0)+IF(J119=$G118+$H118,1,0)+IF(J120=$I$120,3,0)+IF(J121=$G120+$H120,1,0)+IF(J122=$I$122,3,0)+IF(J123=$G122+$H122,1,0)+IF(J124=$I$124,3,0)+IF(J125=$G124+$H124,1,0)+IF(J126=$I$126,3,0)+IF(J127=$G126+$H126,1,0)+IF(J128=$I$128,3,0)+IF(J129=$G128+$H128,1,0)+IF(J130=$I$130,3,0)+IF(J131=$G130+$H130,1,0)+IF(J132=$I$132,3,0)+IF(J133=$G132+$H132,1,0)+IF(J134=$I$134,3,0)+IF(J135=$G134+$H134,1,0)+IF(J136=$I$136,3,0)+IF(J137=$G136+$H136,1,0)+IF(J138=$I$138,3,0)+IF(J139=$G138+$H138,1,0)+IF(J140=$I$140,3,0)+IF(J141=$G140+$H140,1,0)+IF(J142=$I$142,3,0)+IF(J143=$G142+$H142,1,0)+IF(J144=$I$144,3,0)+IF(J145=$G144+$H144,1,0)+IF(J146=$I$146,3,0)+IF(J147=$G146+$H146,1,0)+IF(J148=$I$148,3,0)+IF(J149=$G148+$H148,1,0)+IF(J150=$I$150,3,0)+IF(J151=$G150+$H150,1,0))</f>
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K5" s="75">
         <f>SUM(IF(K80=$I$80,3,0)+IF(K81=$G80+$H80,1,0)+IF(K82=$I$82,3,0)+IF(K83=$G82+$H82,1,0)+IF(K84=$I$84,3,0)+IF(K85=$G84+$H84,1,0)+IF(K86=$I$86,3,0)+IF(K87=$G86+$H86,1,0)+IF(K88=$I$88,3,0)+IF(K89=$G88+$H88,1,0)+IF(K90=$I$90,3,0)+IF(K91=$G90+$H90,1,0)+IF(K92=$I$92,3,0)+IF(K93=$G92+$H92,1,0)+IF(K94=$I$94,3,0)+IF(K95=$G94+$H94,1,0)+IF(K96=$I$96,3,0)+IF(K97=$G96+$H96,1,0)+IF(K98=$I$98,3,0)+IF(K99=$G98+$H98,1,0)+IF(K100=$I$100,3,0)+IF(K101=$G100+$H100,1,0)+IF(K102=$I$102,3,0)+IF(K103=$G102+$H102,1,0)+IF(K104=$I$104,3,0)+IF(K105=$G104+$H104,1,0)+IF(K106=$I$106,3,0)+IF(K107=$G106+$H106,1,0)+IF(K108=$I$108,3,0)+IF(K109=$G108+$H108,1,0)+IF(K110=$I$110,3,0)+IF(K111=$G110+$H110,1,0)+IF(K112=$I$112,3,0)+IF(K113=$G112+$H112,1,0)+IF(K114=$I$114,3,0)+IF(K115=$G114+$H114,1,0)+IF(K116=$I$116,3,0)+IF(K117=$G116+$H116,1,0)+IF(K118=$I$118,3,0)+IF(K119=$G118+$H118,1,0)+IF(K120=$I$120,3,0)+IF(K121=$G120+$H120,1,0)+IF(K122=$I$122,3,0)+IF(K123=$G122+$H122,1,0)+IF(K124=$I$124,3,0)+IF(K125=$G124+$H124,1,0)+IF(K126=$I$126,3,0)+IF(K127=$G126+$H126,1,0)+IF(K128=$I$128,3,0)+IF(K129=$G128+$H128,1,0)+IF(K130=$I$130,3,0)+IF(K131=$G130+$H130,1,0)+IF(K132=$I$132,3,0)+IF(K133=$G132+$H132,1,0)+IF(K134=$I$134,3,0)+IF(K135=$G134+$H134,1,0)+IF(K136=$I$136,3,0)+IF(K137=$G136+$H136,1,0)+IF(K138=$I$138,3,0)+IF(K139=$G138+$H138,1,0)+IF(K140=$I$140,3,0)+IF(K141=$G140+$H140,1,0)+IF(K142=$I$142,3,0)+IF(K143=$G142+$H142,1,0)+IF(K144=$I$144,3,0)+IF(K145=$G144+$H144,1,0)+IF(K146=$I$146,3,0)+IF(K147=$G146+$H146,1,0)+IF(K148=$I$148,3,0)+IF(K149=$G148+$H148,1,0)+IF(K150=$I$150,3,0)+IF(K151=$G150+$H150,1,0))</f>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L5" s="75">
         <f>SUM(IF(L80=$I$80,3,0)+IF(L81=$G80+$H80,1,0)+IF(L82=$I$82,3,0)+IF(L83=$G82+$H82,1,0)+IF(L84=$I$84,3,0)+IF(L85=$G84+$H84,1,0)+IF(L86=$I$86,3,0)+IF(L87=$G86+$H86,1,0)+IF(L88=$I$88,3,0)+IF(L89=$G88+$H88,1,0)+IF(L90=$I$90,3,0)+IF(L91=$G90+$H90,1,0)+IF(L92=$I$92,3,0)+IF(L93=$G92+$H92,1,0)+IF(L94=$I$94,3,0)+IF(L95=$G94+$H94,1,0)+IF(L96=$I$96,3,0)+IF(L97=$G96+$H96,1,0)+IF(L98=$I$98,3,0)+IF(L99=$G98+$H98,1,0)+IF(L100=$I$100,3,0)+IF(L101=$G100+$H100,1,0)+IF(L102=$I$102,3,0)+IF(L103=$G102+$H102,1,0)+IF(L104=$I$104,3,0)+IF(L105=$G104+$H104,1,0)+IF(L106=$I$106,3,0)+IF(L107=$G106+$H106,1,0)+IF(L108=$I$108,3,0)+IF(L109=$G108+$H108,1,0)+IF(L110=$I$110,3,0)+IF(L111=$G110+$H110,1,0)+IF(L112=$I$112,3,0)+IF(L113=$G112+$H112,1,0)+IF(L114=$I$114,3,0)+IF(L115=$G114+$H114,1,0)+IF(L116=$I$116,3,0)+IF(L117=$G116+$H116,1,0)+IF(L118=$I$118,3,0)+IF(L119=$G118+$H118,1,0)+IF(L120=$I$120,3,0)+IF(L121=$G120+$H120,1,0)+IF(L122=$I$122,3,0)+IF(L123=$G122+$H122,1,0)+IF(L124=$I$124,3,0)+IF(L125=$G124+$H124,1,0)+IF(L126=$I$126,3,0)+IF(L127=$G126+$H126,1,0)+IF(L128=$I$128,3,0)+IF(L129=$G128+$H128,1,0)+IF(L130=$I$130,3,0)+IF(L131=$G130+$H130,1,0)+IF(L132=$I$132,3,0)+IF(L133=$G132+$H132,1,0)+IF(L134=$I$134,3,0)+IF(L135=$G134+$H134,1,0)+IF(L136=$I$136,3,0)+IF(L137=$G136+$H136,1,0)+IF(L138=$I$138,3,0)+IF(L139=$G138+$H138,1,0)+IF(L140=$I$140,3,0)+IF(L141=$G140+$H140,1,0)+IF(L142=$I$142,3,0)+IF(L143=$G142+$H142,1,0)+IF(L144=$I$144,3,0)+IF(L145=$G144+$H144,1,0)+IF(L146=$I$146,3,0)+IF(L147=$G146+$H146,1,0)+IF(L148=$I$148,3,0)+IF(L149=$G148+$H148,1,0)+IF(L150=$I$150,3,0)+IF(L151=$G150+$H150,1,0))</f>
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="M5" s="75">
         <f>SUM(IF(M80=$I$80,3,0)+IF(M81=$G80+$H80,1,0)+IF(M82=$I$82,3,0)+IF(M83=$G82+$H82,1,0)+IF(M84=$I$84,3,0)+IF(M85=$G84+$H84,1,0)+IF(M86=$I$86,3,0)+IF(M87=$G86+$H86,1,0)+IF(M88=$I$88,3,0)+IF(M89=$G88+$H88,1,0)+IF(M90=$I$90,3,0)+IF(M91=$G90+$H90,1,0)+IF(M92=$I$92,3,0)+IF(M93=$G92+$H92,1,0)+IF(M94=$I$94,3,0)+IF(M95=$G94+$H94,1,0)+IF(M96=$I$96,3,0)+IF(M97=$G96+$H96,1,0)+IF(M98=$I$98,3,0)+IF(M99=$G98+$H98,1,0)+IF(M100=$I$100,3,0)+IF(M101=$G100+$H100,1,0)+IF(M102=$I$102,3,0)+IF(M103=$G102+$H102,1,0)+IF(M104=$I$104,3,0)+IF(M105=$G104+$H104,1,0)+IF(M106=$I$106,3,0)+IF(M107=$G106+$H106,1,0)+IF(M108=$I$108,3,0)+IF(M109=$G108+$H108,1,0)+IF(M110=$I$110,3,0)+IF(M111=$G110+$H110,1,0)+IF(M112=$I$112,3,0)+IF(M113=$G112+$H112,1,0)+IF(M114=$I$114,3,0)+IF(M115=$G114+$H114,1,0)+IF(M116=$I$116,3,0)+IF(M117=$G116+$H116,1,0)+IF(M118=$I$118,3,0)+IF(M119=$G118+$H118,1,0)+IF(M120=$I$120,3,0)+IF(M121=$G120+$H120,1,0)+IF(M122=$I$122,3,0)+IF(M123=$G122+$H122,1,0)+IF(M124=$I$124,3,0)+IF(M125=$G124+$H124,1,0)+IF(M126=$I$126,3,0)+IF(M127=$G126+$H126,1,0)+IF(M128=$I$128,3,0)+IF(M129=$G128+$H128,1,0)+IF(M130=$I$130,3,0)+IF(M131=$G130+$H130,1,0)+IF(M132=$I$132,3,0)+IF(M133=$G132+$H132,1,0)+IF(M134=$I$134,3,0)+IF(M135=$G134+$H134,1,0)+IF(M136=$I$136,3,0)+IF(M137=$G136+$H136,1,0)+IF(M138=$I$138,3,0)+IF(M139=$G138+$H138,1,0)+IF(M140=$I$140,3,0)+IF(M141=$G140+$H140,1,0)+IF(M142=$I$142,3,0)+IF(M143=$G142+$H142,1,0)+IF(M144=$I$144,3,0)+IF(M145=$G144+$H144,1,0)+IF(M146=$I$146,3,0)+IF(M147=$G146+$H146,1,0)+IF(M148=$I$148,3,0)+IF(M149=$G148+$H148,1,0)+IF(M150=$I$150,3,0)+IF(M151=$G150+$H150,1,0))</f>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="N5" s="75">
         <f>SUM(IF(N80=$I$80,3,0)+IF(N81=$G80+$H80,1,0)+IF(N82=$I$82,3,0)+IF(N83=$G82+$H82,1,0)+IF(N84=$I$84,3,0)+IF(N85=$G84+$H84,1,0)+IF(N86=$I$86,3,0)+IF(N87=$G86+$H86,1,0)+IF(N88=$I$88,3,0)+IF(N89=$G88+$H88,1,0)+IF(N90=$I$90,3,0)+IF(N91=$G90+$H90,1,0)+IF(N92=$I$92,3,0)+IF(N93=$G92+$H92,1,0)+IF(N94=$I$94,3,0)+IF(N95=$G94+$H94,1,0)+IF(N96=$I$96,3,0)+IF(N97=$G96+$H96,1,0)+IF(N98=$I$98,3,0)+IF(N99=$G98+$H98,1,0)+IF(N100=$I$100,3,0)+IF(N101=$G100+$H100,1,0)+IF(N102=$I$102,3,0)+IF(N103=$G102+$H102,1,0)+IF(N104=$I$104,3,0)+IF(N105=$G104+$H104,1,0)+IF(N106=$I$106,3,0)+IF(N107=$G106+$H106,1,0)+IF(N108=$I$108,3,0)+IF(N109=$G108+$H108,1,0)+IF(N110=$I$110,3,0)+IF(N111=$G110+$H110,1,0)+IF(N112=$I$112,3,0)+IF(N113=$G112+$H112,1,0)+IF(N114=$I$114,3,0)+IF(N115=$G114+$H114,1,0)+IF(N116=$I$116,3,0)+IF(N117=$G116+$H116,1,0)+IF(N118=$I$118,3,0)+IF(N119=$G118+$H118,1,0)+IF(N120=$I$120,3,0)+IF(N121=$G120+$H120,1,0)+IF(N122=$I$122,3,0)+IF(N123=$G122+$H122,1,0)+IF(N124=$I$124,3,0)+IF(N125=$G124+$H124,1,0)+IF(N126=$I$126,3,0)+IF(N127=$G126+$H126,1,0)+IF(N128=$I$128,3,0)+IF(N129=$G128+$H128,1,0)+IF(N130=$I$130,3,0)+IF(N131=$G130+$H130,1,0)+IF(N132=$I$132,3,0)+IF(N133=$G132+$H132,1,0)+IF(N134=$I$134,3,0)+IF(N135=$G134+$H134,1,0)+IF(N136=$I$136,3,0)+IF(N137=$G136+$H136,1,0)+IF(N138=$I$138,3,0)+IF(N139=$G138+$H138,1,0)+IF(N140=$I$140,3,0)+IF(N141=$G140+$H140,1,0)+IF(N142=$I$142,3,0)+IF(N143=$G142+$H142,1,0)+IF(N144=$I$144,3,0)+IF(N145=$G144+$H144,1,0)+IF(N146=$I$146,3,0)+IF(N147=$G146+$H146,1,0)+IF(N148=$I$148,3,0)+IF(N149=$G148+$H148,1,0)+IF(N150=$I$150,3,0)+IF(N151=$G150+$H150,1,0))</f>
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O5" s="75">
         <f>SUM(IF(O80=$I$80,3,0)+IF(O81=$G80+$H80,1,0)+IF(O82=$I$82,3,0)+IF(O83=$G82+$H82,1,0)+IF(O84=$I$84,3,0)+IF(O85=$G84+$H84,1,0)+IF(O86=$I$86,3,0)+IF(O87=$G86+$H86,1,0)+IF(O88=$I$88,3,0)+IF(O89=$G88+$H88,1,0)+IF(O90=$I$90,3,0)+IF(O91=$G90+$H90,1,0)+IF(O92=$I$92,3,0)+IF(O93=$G92+$H92,1,0)+IF(O94=$I$94,3,0)+IF(O95=$G94+$H94,1,0)+IF(O96=$I$96,3,0)+IF(O97=$G96+$H96,1,0)+IF(O98=$I$98,3,0)+IF(O99=$G98+$H98,1,0)+IF(O100=$I$100,3,0)+IF(O101=$G100+$H100,1,0)+IF(O102=$I$102,3,0)+IF(O103=$G102+$H102,1,0)+IF(O104=$I$104,3,0)+IF(O105=$G104+$H104,1,0)+IF(O106=$I$106,3,0)+IF(O107=$G106+$H106,1,0)+IF(O108=$I$108,3,0)+IF(O109=$G108+$H108,1,0)+IF(O110=$I$110,3,0)+IF(O111=$G110+$H110,1,0)+IF(O112=$I$112,3,0)+IF(O113=$G112+$H112,1,0)+IF(O114=$I$114,3,0)+IF(O115=$G114+$H114,1,0)+IF(O116=$I$116,3,0)+IF(O117=$G116+$H116,1,0)+IF(O118=$I$118,3,0)+IF(O119=$G118+$H118,1,0)+IF(O120=$I$120,3,0)+IF(O121=$G120+$H120,1,0)+IF(O122=$I$122,3,0)+IF(O123=$G122+$H122,1,0)+IF(O124=$I$124,3,0)+IF(O125=$G124+$H124,1,0)+IF(O126=$I$126,3,0)+IF(O127=$G126+$H126,1,0)+IF(O128=$I$128,3,0)+IF(O129=$G128+$H128,1,0)+IF(O130=$I$130,3,0)+IF(O131=$G130+$H130,1,0)+IF(O132=$I$132,3,0)+IF(O133=$G132+$H132,1,0)+IF(O134=$I$134,3,0)+IF(O135=$G134+$H134,1,0)+IF(O136=$I$136,3,0)+IF(O137=$G136+$H136,1,0)+IF(O138=$I$138,3,0)+IF(O139=$G138+$H138,1,0)+IF(O140=$I$140,3,0)+IF(O141=$G140+$H140,1,0)+IF(O142=$I$142,3,0)+IF(O143=$G142+$H142,1,0)+IF(O144=$I$144,3,0)+IF(O145=$G144+$H144,1,0)+IF(O146=$I$146,3,0)+IF(O147=$G146+$H146,1,0)+IF(O148=$I$148,3,0)+IF(O149=$G148+$H148,1,0)+IF(O150=$I$150,3,0)+IF(O151=$G150+$H150,1,0))</f>
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="P5" s="75">
         <f>SUM(IF(P80=$I$80,3,0)+IF(P81=$G80+$H80,1,0)+IF(P82=$I$82,3,0)+IF(P83=$G82+$H82,1,0)+IF(P84=$I$84,3,0)+IF(P85=$G84+$H84,1,0)+IF(P86=$I$86,3,0)+IF(P87=$G86+$H86,1,0)+IF(P88=$I$88,3,0)+IF(P89=$G88+$H88,1,0)+IF(P90=$I$90,3,0)+IF(P91=$G90+$H90,1,0)+IF(P92=$I$92,3,0)+IF(P93=$G92+$H92,1,0)+IF(P94=$I$94,3,0)+IF(P95=$G94+$H94,1,0)+IF(P96=$I$96,3,0)+IF(P97=$G96+$H96,1,0)+IF(P98=$I$98,3,0)+IF(P99=$G98+$H98,1,0)+IF(P100=$I$100,3,0)+IF(P101=$G100+$H100,1,0)+IF(P102=$I$102,3,0)+IF(P103=$G102+$H102,1,0)+IF(P104=$I$104,3,0)+IF(P105=$G104+$H104,1,0)+IF(P106=$I$106,3,0)+IF(P107=$G106+$H106,1,0)+IF(P108=$I$108,3,0)+IF(P109=$G108+$H108,1,0)+IF(P110=$I$110,3,0)+IF(P111=$G110+$H110,1,0)+IF(P112=$I$112,3,0)+IF(P113=$G112+$H112,1,0)+IF(P114=$I$114,3,0)+IF(P115=$G114+$H114,1,0)+IF(P116=$I$116,3,0)+IF(P117=$G116+$H116,1,0)+IF(P118=$I$118,3,0)+IF(P119=$G118+$H118,1,0)+IF(P120=$I$120,3,0)+IF(P121=$G120+$H120,1,0)+IF(P122=$I$122,3,0)+IF(P123=$G122+$H122,1,0)+IF(P124=$I$124,3,0)+IF(P125=$G124+$H124,1,0)+IF(P126=$I$126,3,0)+IF(P127=$G126+$H126,1,0)+IF(P128=$I$128,3,0)+IF(P129=$G128+$H128,1,0)+IF(P130=$I$130,3,0)+IF(P131=$G130+$H130,1,0)+IF(P132=$I$132,3,0)+IF(P133=$G132+$H132,1,0)+IF(P134=$I$134,3,0)+IF(P135=$G134+$H134,1,0)+IF(P136=$I$136,3,0)+IF(P137=$G136+$H136,1,0)+IF(P138=$I$138,3,0)+IF(P139=$G138+$H138,1,0)+IF(P140=$I$140,3,0)+IF(P141=$G140+$H140,1,0)+IF(P142=$I$142,3,0)+IF(P143=$G142+$H142,1,0)+IF(P144=$I$144,3,0)+IF(P145=$G144+$H144,1,0)+IF(P146=$I$146,3,0)+IF(P147=$G146+$H146,1,0)+IF(P148=$I$148,3,0)+IF(P149=$G148+$H148,1,0)+IF(P150=$I$150,3,0)+IF(P151=$G150+$H150,1,0))</f>
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="Q5" s="75">
         <f>SUM(IF(Q80=$I$80,3,0)+IF(Q81=$G80+$H80,1,0)+IF(Q82=$I$82,3,0)+IF(Q83=$G82+$H82,1,0)+IF(Q84=$I$84,3,0)+IF(Q85=$G84+$H84,1,0)+IF(Q86=$I$86,3,0)+IF(Q87=$G86+$H86,1,0)+IF(Q88=$I$88,3,0)+IF(Q89=$G88+$H88,1,0)+IF(Q90=$I$90,3,0)+IF(Q91=$G90+$H90,1,0)+IF(Q92=$I$92,3,0)+IF(Q93=$G92+$H92,1,0)+IF(Q94=$I$94,3,0)+IF(Q95=$G94+$H94,1,0)+IF(Q96=$I$96,3,0)+IF(Q97=$G96+$H96,1,0)+IF(Q98=$I$98,3,0)+IF(Q99=$G98+$H98,1,0)+IF(Q100=$I$100,3,0)+IF(Q101=$G100+$H100,1,0)+IF(Q102=$I$102,3,0)+IF(Q103=$G102+$H102,1,0)+IF(Q104=$I$104,3,0)+IF(Q105=$G104+$H104,1,0)+IF(Q106=$I$106,3,0)+IF(Q107=$G106+$H106,1,0)+IF(Q108=$I$108,3,0)+IF(Q109=$G108+$H108,1,0)+IF(Q110=$I$110,3,0)+IF(Q111=$G110+$H110,1,0)+IF(Q112=$I$112,3,0)+IF(Q113=$G112+$H112,1,0)+IF(Q114=$I$114,3,0)+IF(Q115=$G114+$H114,1,0)+IF(Q116=$I$116,3,0)+IF(Q117=$G116+$H116,1,0)+IF(Q118=$I$118,3,0)+IF(Q119=$G118+$H118,1,0)+IF(Q120=$I$120,3,0)+IF(Q121=$G120+$H120,1,0)+IF(Q122=$I$122,3,0)+IF(Q123=$G122+$H122,1,0)+IF(Q124=$I$124,3,0)+IF(Q125=$G124+$H124,1,0)+IF(Q126=$I$126,3,0)+IF(Q127=$G126+$H126,1,0)+IF(Q128=$I$128,3,0)+IF(Q129=$G128+$H128,1,0)+IF(Q130=$I$130,3,0)+IF(Q131=$G130+$H130,1,0)+IF(Q132=$I$132,3,0)+IF(Q133=$G132+$H132,1,0)+IF(Q134=$I$134,3,0)+IF(Q135=$G134+$H134,1,0)+IF(Q136=$I$136,3,0)+IF(Q137=$G136+$H136,1,0)+IF(Q138=$I$138,3,0)+IF(Q139=$G138+$H138,1,0)+IF(Q140=$I$140,3,0)+IF(Q141=$G140+$H140,1,0)+IF(Q142=$I$142,3,0)+IF(Q143=$G142+$H142,1,0)+IF(Q144=$I$144,3,0)+IF(Q145=$G144+$H144,1,0)+IF(Q146=$I$146,3,0)+IF(Q147=$G146+$H146,1,0)+IF(Q148=$I$148,3,0)+IF(Q149=$G148+$H148,1,0)+IF(Q150=$I$150,3,0)+IF(Q151=$G150+$H150,1,0))</f>
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="R5" s="75">
         <f>SUM(IF(R80=$I$80,3,0)+IF(R81=$G80+$H80,1,0)+IF(R82=$I$82,3,0)+IF(R83=$G82+$H82,1,0)+IF(R84=$I$84,3,0)+IF(R85=$G84+$H84,1,0)+IF(R86=$I$86,3,0)+IF(R87=$G86+$H86,1,0)+IF(R88=$I$88,3,0)+IF(R89=$G88+$H88,1,0)+IF(R90=$I$90,3,0)+IF(R91=$G90+$H90,1,0)+IF(R92=$I$92,3,0)+IF(R93=$G92+$H92,1,0)+IF(R94=$I$94,3,0)+IF(R95=$G94+$H94,1,0)+IF(R96=$I$96,3,0)+IF(R97=$G96+$H96,1,0)+IF(R98=$I$98,3,0)+IF(R99=$G98+$H98,1,0)+IF(R100=$I$100,3,0)+IF(R101=$G100+$H100,1,0)+IF(R102=$I$102,3,0)+IF(R103=$G102+$H102,1,0)+IF(R104=$I$104,3,0)+IF(R105=$G104+$H104,1,0)+IF(R106=$I$106,3,0)+IF(R107=$G106+$H106,1,0)+IF(R108=$I$108,3,0)+IF(R109=$G108+$H108,1,0)+IF(R110=$I$110,3,0)+IF(R111=$G110+$H110,1,0)+IF(R112=$I$112,3,0)+IF(R113=$G112+$H112,1,0)+IF(R114=$I$114,3,0)+IF(R115=$G114+$H114,1,0)+IF(R116=$I$116,3,0)+IF(R117=$G116+$H116,1,0)+IF(R118=$I$118,3,0)+IF(R119=$G118+$H118,1,0)+IF(R120=$I$120,3,0)+IF(R121=$G120+$H120,1,0)+IF(R122=$I$122,3,0)+IF(R123=$G122+$H122,1,0)+IF(R124=$I$124,3,0)+IF(R125=$G124+$H124,1,0)+IF(R126=$I$126,3,0)+IF(R127=$G126+$H126,1,0)+IF(R128=$I$128,3,0)+IF(R129=$G128+$H128,1,0)+IF(R130=$I$130,3,0)+IF(R131=$G130+$H130,1,0)+IF(R132=$I$132,3,0)+IF(R133=$G132+$H132,1,0)+IF(R134=$I$134,3,0)+IF(R135=$G134+$H134,1,0)+IF(R136=$I$136,3,0)+IF(R137=$G136+$H136,1,0)+IF(R138=$I$138,3,0)+IF(R139=$G138+$H138,1,0)+IF(R140=$I$140,3,0)+IF(R141=$G140+$H140,1,0)+IF(R142=$I$142,3,0)+IF(R143=$G142+$H142,1,0)+IF(R144=$I$144,3,0)+IF(R145=$G144+$H144,1,0)+IF(R146=$I$146,3,0)+IF(R147=$G146+$H146,1,0)+IF(R148=$I$148,3,0)+IF(R149=$G148+$H148,1,0)+IF(R150=$I$150,3,0)+IF(R151=$G150+$H150,1,0))</f>
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="S5" s="75">
         <f>SUM(IF(S80=$I$80,3,0)+IF(S81=$G80+$H80,1,0)+IF(S82=$I$82,3,0)+IF(S83=$G82+$H82,1,0)+IF(S84=$I$84,3,0)+IF(S85=$G84+$H84,1,0)+IF(S86=$I$86,3,0)+IF(S87=$G86+$H86,1,0)+IF(S88=$I$88,3,0)+IF(S89=$G88+$H88,1,0)+IF(S90=$I$90,3,0)+IF(S91=$G90+$H90,1,0)+IF(S92=$I$92,3,0)+IF(S93=$G92+$H92,1,0)+IF(S94=$I$94,3,0)+IF(S95=$G94+$H94,1,0)+IF(S96=$I$96,3,0)+IF(S97=$G96+$H96,1,0)+IF(S98=$I$98,3,0)+IF(S99=$G98+$H98,1,0)+IF(S100=$I$100,3,0)+IF(S101=$G100+$H100,1,0)+IF(S102=$I$102,3,0)+IF(S103=$G102+$H102,1,0)+IF(S104=$I$104,3,0)+IF(S105=$G104+$H104,1,0)+IF(S106=$I$106,3,0)+IF(S107=$G106+$H106,1,0)+IF(S108=$I$108,3,0)+IF(S109=$G108+$H108,1,0)+IF(S110=$I$110,3,0)+IF(S111=$G110+$H110,1,0)+IF(S112=$I$112,3,0)+IF(S113=$G112+$H112,1,0)+IF(S114=$I$114,3,0)+IF(S115=$G114+$H114,1,0)+IF(S116=$I$116,3,0)+IF(S117=$G116+$H116,1,0)+IF(S118=$I$118,3,0)+IF(S119=$G118+$H118,1,0)+IF(S120=$I$120,3,0)+IF(S121=$G120+$H120,1,0)+IF(S122=$I$122,3,0)+IF(S123=$G122+$H122,1,0)+IF(S124=$I$124,3,0)+IF(S125=$G124+$H124,1,0)+IF(S126=$I$126,3,0)+IF(S127=$G126+$H126,1,0)+IF(S128=$I$128,3,0)+IF(S129=$G128+$H128,1,0)+IF(S130=$I$130,3,0)+IF(S131=$G130+$H130,1,0)+IF(S132=$I$132,3,0)+IF(S133=$G132+$H132,1,0)+IF(S134=$I$134,3,0)+IF(S135=$G134+$H134,1,0)+IF(S136=$I$136,3,0)+IF(S137=$G136+$H136,1,0)+IF(S138=$I$138,3,0)+IF(S139=$G138+$H138,1,0)+IF(S140=$I$140,3,0)+IF(S141=$G140+$H140,1,0)+IF(S142=$I$142,3,0)+IF(S143=$G142+$H142,1,0)+IF(S144=$I$144,3,0)+IF(S145=$G144+$H144,1,0)+IF(S146=$I$146,3,0)+IF(S147=$G146+$H146,1,0)+IF(S148=$I$148,3,0)+IF(S149=$G148+$H148,1,0)+IF(S150=$I$150,3,0)+IF(S151=$G150+$H150,1,0))</f>
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="T5" s="75">
         <f>SUM(IF(T80=$I$80,3,0)+IF(T81=$G80+$H80,1,0)+IF(T82=$I$82,3,0)+IF(T83=$G82+$H82,1,0)+IF(T84=$I$84,3,0)+IF(T85=$G84+$H84,1,0)+IF(T86=$I$86,3,0)+IF(T87=$G86+$H86,1,0)+IF(T88=$I$88,3,0)+IF(T89=$G88+$H88,1,0)+IF(T90=$I$90,3,0)+IF(T91=$G90+$H90,1,0)+IF(T92=$I$92,3,0)+IF(T93=$G92+$H92,1,0)+IF(T94=$I$94,3,0)+IF(T95=$G94+$H94,1,0)+IF(T96=$I$96,3,0)+IF(T97=$G96+$H96,1,0)+IF(T98=$I$98,3,0)+IF(T99=$G98+$H98,1,0)+IF(T100=$I$100,3,0)+IF(T101=$G100+$H100,1,0)+IF(T102=$I$102,3,0)+IF(T103=$G102+$H102,1,0)+IF(T104=$I$104,3,0)+IF(T105=$G104+$H104,1,0)+IF(T106=$I$106,3,0)+IF(T107=$G106+$H106,1,0)+IF(T108=$I$108,3,0)+IF(T109=$G108+$H108,1,0)+IF(T110=$I$110,3,0)+IF(T111=$G110+$H110,1,0)+IF(T112=$I$112,3,0)+IF(T113=$G112+$H112,1,0)+IF(T114=$I$114,3,0)+IF(T115=$G114+$H114,1,0)+IF(T116=$I$116,3,0)+IF(T117=$G116+$H116,1,0)+IF(T118=$I$118,3,0)+IF(T119=$G118+$H118,1,0)+IF(T120=$I$120,3,0)+IF(T121=$G120+$H120,1,0)+IF(T122=$I$122,3,0)+IF(T123=$G122+$H122,1,0)+IF(T124=$I$124,3,0)+IF(T125=$G124+$H124,1,0)+IF(T126=$I$126,3,0)+IF(T127=$G126+$H126,1,0)+IF(T128=$I$128,3,0)+IF(T129=$G128+$H128,1,0)+IF(T130=$I$130,3,0)+IF(T131=$G130+$H130,1,0)+IF(T132=$I$132,3,0)+IF(T133=$G132+$H132,1,0)+IF(T134=$I$134,3,0)+IF(T135=$G134+$H134,1,0)+IF(T136=$I$136,3,0)+IF(T137=$G136+$H136,1,0)+IF(T138=$I$138,3,0)+IF(T139=$G138+$H138,1,0)+IF(T140=$I$140,3,0)+IF(T141=$G140+$H140,1,0)+IF(T142=$I$142,3,0)+IF(T143=$G142+$H142,1,0)+IF(T144=$I$144,3,0)+IF(T145=$G144+$H144,1,0)+IF(T146=$I$146,3,0)+IF(T147=$G146+$H146,1,0)+IF(T148=$I$148,3,0)+IF(T149=$G148+$H148,1,0)+IF(T150=$I$150,3,0)+IF(T151=$G150+$H150,1,0))</f>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="U5" s="75">
         <f>SUM(IF(U80=$I$80,3,0)+IF(U81=$G80+$H80,1,0)+IF(U82=$I$82,3,0)+IF(U83=$G82+$H82,1,0)+IF(U84=$I$84,3,0)+IF(U85=$G84+$H84,1,0)+IF(U86=$I$86,3,0)+IF(U87=$G86+$H86,1,0)+IF(U88=$I$88,3,0)+IF(U89=$G88+$H88,1,0)+IF(U90=$I$90,3,0)+IF(U91=$G90+$H90,1,0)+IF(U92=$I$92,3,0)+IF(U93=$G92+$H92,1,0)+IF(U94=$I$94,3,0)+IF(U95=$G94+$H94,1,0)+IF(U96=$I$96,3,0)+IF(U97=$G96+$H96,1,0)+IF(U98=$I$98,3,0)+IF(U99=$G98+$H98,1,0)+IF(U100=$I$100,3,0)+IF(U101=$G100+$H100,1,0)+IF(U102=$I$102,3,0)+IF(U103=$G102+$H102,1,0)+IF(U104=$I$104,3,0)+IF(U105=$G104+$H104,1,0)+IF(U106=$I$106,3,0)+IF(U107=$G106+$H106,1,0)+IF(U108=$I$108,3,0)+IF(U109=$G108+$H108,1,0)+IF(U110=$I$110,3,0)+IF(U111=$G110+$H110,1,0)+IF(U112=$I$112,3,0)+IF(U113=$G112+$H112,1,0)+IF(U114=$I$114,3,0)+IF(U115=$G114+$H114,1,0)+IF(U116=$I$116,3,0)+IF(U117=$G116+$H116,1,0)+IF(U118=$I$118,3,0)+IF(U119=$G118+$H118,1,0)+IF(U120=$I$120,3,0)+IF(U121=$G120+$H120,1,0)+IF(U122=$I$122,3,0)+IF(U123=$G122+$H122,1,0)+IF(U124=$I$124,3,0)+IF(U125=$G124+$H124,1,0)+IF(U126=$I$126,3,0)+IF(U127=$G126+$H126,1,0)+IF(U128=$I$128,3,0)+IF(U129=$G128+$H128,1,0)+IF(U130=$I$130,3,0)+IF(U131=$G130+$H130,1,0)+IF(U132=$I$132,3,0)+IF(U133=$G132+$H132,1,0)+IF(U134=$I$134,3,0)+IF(U135=$G134+$H134,1,0)+IF(U136=$I$136,3,0)+IF(U137=$G136+$H136,1,0)+IF(U138=$I$138,3,0)+IF(U139=$G138+$H138,1,0)+IF(U140=$I$140,3,0)+IF(U141=$G140+$H140,1,0)+IF(U142=$I$142,3,0)+IF(U143=$G142+$H142,1,0)+IF(U144=$I$144,3,0)+IF(U145=$G144+$H144,1,0)+IF(U146=$I$146,3,0)+IF(U147=$G146+$H146,1,0)+IF(U148=$I$148,3,0)+IF(U149=$G148+$H148,1,0)+IF(U150=$I$150,3,0)+IF(U151=$G150+$H150,1,0))</f>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="V5" s="75">
         <f>SUM(IF(V80=$I$80,3,0)+IF(V81=$G80+$H80,1,0)+IF(V82=$I$82,3,0)+IF(V83=$G82+$H82,1,0)+IF(V84=$I$84,3,0)+IF(V85=$G84+$H84,1,0)+IF(V86=$I$86,3,0)+IF(V87=$G86+$H86,1,0)+IF(V88=$I$88,3,0)+IF(V89=$G88+$H88,1,0)+IF(V90=$I$90,3,0)+IF(V91=$G90+$H90,1,0)+IF(V92=$I$92,3,0)+IF(V93=$G92+$H92,1,0)+IF(V94=$I$94,3,0)+IF(V95=$G94+$H94,1,0)+IF(V96=$I$96,3,0)+IF(V97=$G96+$H96,1,0)+IF(V98=$I$98,3,0)+IF(V99=$G98+$H98,1,0)+IF(V100=$I$100,3,0)+IF(V101=$G100+$H100,1,0)+IF(V102=$I$102,3,0)+IF(V103=$G102+$H102,1,0)+IF(V104=$I$104,3,0)+IF(V105=$G104+$H104,1,0)+IF(V106=$I$106,3,0)+IF(V107=$G106+$H106,1,0)+IF(V108=$I$108,3,0)+IF(V109=$G108+$H108,1,0)+IF(V110=$I$110,3,0)+IF(V111=$G110+$H110,1,0)+IF(V112=$I$112,3,0)+IF(V113=$G112+$H112,1,0)+IF(V114=$I$114,3,0)+IF(V115=$G114+$H114,1,0)+IF(V116=$I$116,3,0)+IF(V117=$G116+$H116,1,0)+IF(V118=$I$118,3,0)+IF(V119=$G118+$H118,1,0)+IF(V120=$I$120,3,0)+IF(V121=$G120+$H120,1,0)+IF(V122=$I$122,3,0)+IF(V123=$G122+$H122,1,0)+IF(V124=$I$124,3,0)+IF(V125=$G124+$H124,1,0)+IF(V126=$I$126,3,0)+IF(V127=$G126+$H126,1,0)+IF(V128=$I$128,3,0)+IF(V129=$G128+$H128,1,0)+IF(V130=$I$130,3,0)+IF(V131=$G130+$H130,1,0)+IF(V132=$I$132,3,0)+IF(V133=$G132+$H132,1,0)+IF(V134=$I$134,3,0)+IF(V135=$G134+$H134,1,0)+IF(V136=$I$136,3,0)+IF(V137=$G136+$H136,1,0)+IF(V138=$I$138,3,0)+IF(V139=$G138+$H138,1,0)+IF(V140=$I$140,3,0)+IF(V141=$G140+$H140,1,0)+IF(V142=$I$142,3,0)+IF(V143=$G142+$H142,1,0)+IF(V144=$I$144,3,0)+IF(V145=$G144+$H144,1,0)+IF(V146=$I$146,3,0)+IF(V147=$G146+$H146,1,0)+IF(V148=$I$148,3,0)+IF(V149=$G148+$H148,1,0)+IF(V150=$I$150,3,0)+IF(V151=$G150+$H150,1,0))</f>
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W5" s="75">
         <f>SUM(IF(W80=$I$80,3,0)+IF(W81=$G80+$H80,1,0)+IF(W82=$I$82,3,0)+IF(W83=$G82+$H82,1,0)+IF(W84=$I$84,3,0)+IF(W85=$G84+$H84,1,0)+IF(W86=$I$86,3,0)+IF(W87=$G86+$H86,1,0)+IF(W88=$I$88,3,0)+IF(W89=$G88+$H88,1,0)+IF(W90=$I$90,3,0)+IF(W91=$G90+$H90,1,0)+IF(W92=$I$92,3,0)+IF(W93=$G92+$H92,1,0)+IF(W94=$I$94,3,0)+IF(W95=$G94+$H94,1,0)+IF(W96=$I$96,3,0)+IF(W97=$G96+$H96,1,0)+IF(W98=$I$98,3,0)+IF(W99=$G98+$H98,1,0)+IF(W100=$I$100,3,0)+IF(W101=$G100+$H100,1,0)+IF(W102=$I$102,3,0)+IF(W103=$G102+$H102,1,0)+IF(W104=$I$104,3,0)+IF(W105=$G104+$H104,1,0)+IF(W106=$I$106,3,0)+IF(W107=$G106+$H106,1,0)+IF(W108=$I$108,3,0)+IF(W109=$G108+$H108,1,0)+IF(W110=$I$110,3,0)+IF(W111=$G110+$H110,1,0)+IF(W112=$I$112,3,0)+IF(W113=$G112+$H112,1,0)+IF(W114=$I$114,3,0)+IF(W115=$G114+$H114,1,0)+IF(W116=$I$116,3,0)+IF(W117=$G116+$H116,1,0)+IF(W118=$I$118,3,0)+IF(W119=$G118+$H118,1,0)+IF(W120=$I$120,3,0)+IF(W121=$G120+$H120,1,0)+IF(W122=$I$122,3,0)+IF(W123=$G122+$H122,1,0)+IF(W124=$I$124,3,0)+IF(W125=$G124+$H124,1,0)+IF(W126=$I$126,3,0)+IF(W127=$G126+$H126,1,0)+IF(W128=$I$128,3,0)+IF(W129=$G128+$H128,1,0)+IF(W130=$I$130,3,0)+IF(W131=$G130+$H130,1,0)+IF(W132=$I$132,3,0)+IF(W133=$G132+$H132,1,0)+IF(W134=$I$134,3,0)+IF(W135=$G134+$H134,1,0)+IF(W136=$I$136,3,0)+IF(W137=$G136+$H136,1,0)+IF(W138=$I$138,3,0)+IF(W139=$G138+$H138,1,0)+IF(W140=$I$140,3,0)+IF(W141=$G140+$H140,1,0)+IF(W142=$I$142,3,0)+IF(W143=$G142+$H142,1,0)+IF(W144=$I$144,3,0)+IF(W145=$G144+$H144,1,0)+IF(W146=$I$146,3,0)+IF(W147=$G146+$H146,1,0)+IF(W148=$I$148,3,0)+IF(W149=$G148+$H148,1,0)+IF(W150=$I$150,3,0)+IF(W151=$G150+$H150,1,0))</f>
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="X5" s="75">
         <f>SUM(IF(X80=$I$80,3,0)+IF(X81=$G80+$H80,1,0)+IF(X82=$I$82,3,0)+IF(X83=$G82+$H82,1,0)+IF(X84=$I$84,3,0)+IF(X85=$G84+$H84,1,0)+IF(X86=$I$86,3,0)+IF(X87=$G86+$H86,1,0)+IF(X88=$I$88,3,0)+IF(X89=$G88+$H88,1,0)+IF(X90=$I$90,3,0)+IF(X91=$G90+$H90,1,0)+IF(X92=$I$92,3,0)+IF(X93=$G92+$H92,1,0)+IF(X94=$I$94,3,0)+IF(X95=$G94+$H94,1,0)+IF(X96=$I$96,3,0)+IF(X97=$G96+$H96,1,0)+IF(X98=$I$98,3,0)+IF(X99=$G98+$H98,1,0)+IF(X100=$I$100,3,0)+IF(X101=$G100+$H100,1,0)+IF(X102=$I$102,3,0)+IF(X103=$G102+$H102,1,0)+IF(X104=$I$104,3,0)+IF(X105=$G104+$H104,1,0)+IF(X106=$I$106,3,0)+IF(X107=$G106+$H106,1,0)+IF(X108=$I$108,3,0)+IF(X109=$G108+$H108,1,0)+IF(X110=$I$110,3,0)+IF(X111=$G110+$H110,1,0)+IF(X112=$I$112,3,0)+IF(X113=$G112+$H112,1,0)+IF(X114=$I$114,3,0)+IF(X115=$G114+$H114,1,0)+IF(X116=$I$116,3,0)+IF(X117=$G116+$H116,1,0)+IF(X118=$I$118,3,0)+IF(X119=$G118+$H118,1,0)+IF(X120=$I$120,3,0)+IF(X121=$G120+$H120,1,0)+IF(X122=$I$122,3,0)+IF(X123=$G122+$H122,1,0)+IF(X124=$I$124,3,0)+IF(X125=$G124+$H124,1,0)+IF(X126=$I$126,3,0)+IF(X127=$G126+$H126,1,0)+IF(X128=$I$128,3,0)+IF(X129=$G128+$H128,1,0)+IF(X130=$I$130,3,0)+IF(X131=$G130+$H130,1,0)+IF(X132=$I$132,3,0)+IF(X133=$G132+$H132,1,0)+IF(X134=$I$134,3,0)+IF(X135=$G134+$H134,1,0)+IF(X136=$I$136,3,0)+IF(X137=$G136+$H136,1,0)+IF(X138=$I$138,3,0)+IF(X139=$G138+$H138,1,0)+IF(X140=$I$140,3,0)+IF(X141=$G140+$H140,1,0)+IF(X142=$I$142,3,0)+IF(X143=$G142+$H142,1,0)+IF(X144=$I$144,3,0)+IF(X145=$G144+$H144,1,0)+IF(X146=$I$146,3,0)+IF(X147=$G146+$H146,1,0)+IF(X148=$I$148,3,0)+IF(X149=$G148+$H148,1,0)+IF(X150=$I$150,3,0)+IF(X151=$G150+$H150,1,0))</f>
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Y5" s="75">
         <f>SUM(IF(Y80=$I$80,3,0)+IF(Y81=$G80+$H80,1,0)+IF(Y82=$I$82,3,0)+IF(Y83=$G82+$H82,1,0)+IF(Y84=$I$84,3,0)+IF(Y85=$G84+$H84,1,0)+IF(Y86=$I$86,3,0)+IF(Y87=$G86+$H86,1,0)+IF(Y88=$I$88,3,0)+IF(Y89=$G88+$H88,1,0)+IF(Y90=$I$90,3,0)+IF(Y91=$G90+$H90,1,0)+IF(Y92=$I$92,3,0)+IF(Y93=$G92+$H92,1,0)+IF(Y94=$I$94,3,0)+IF(Y95=$G94+$H94,1,0)+IF(Y96=$I$96,3,0)+IF(Y97=$G96+$H96,1,0)+IF(Y98=$I$98,3,0)+IF(Y99=$G98+$H98,1,0)+IF(Y100=$I$100,3,0)+IF(Y101=$G100+$H100,1,0)+IF(Y102=$I$102,3,0)+IF(Y103=$G102+$H102,1,0)+IF(Y104=$I$104,3,0)+IF(Y105=$G104+$H104,1,0)+IF(Y106=$I$106,3,0)+IF(Y107=$G106+$H106,1,0)+IF(Y108=$I$108,3,0)+IF(Y109=$G108+$H108,1,0)+IF(Y110=$I$110,3,0)+IF(Y111=$G110+$H110,1,0)+IF(Y112=$I$112,3,0)+IF(Y113=$G112+$H112,1,0)+IF(Y114=$I$114,3,0)+IF(Y115=$G114+$H114,1,0)+IF(Y116=$I$116,3,0)+IF(Y117=$G116+$H116,1,0)+IF(Y118=$I$118,3,0)+IF(Y119=$G118+$H118,1,0)+IF(Y120=$I$120,3,0)+IF(Y121=$G120+$H120,1,0)+IF(Y122=$I$122,3,0)+IF(Y123=$G122+$H122,1,0)+IF(Y124=$I$124,3,0)+IF(Y125=$G124+$H124,1,0)+IF(Y126=$I$126,3,0)+IF(Y127=$G126+$H126,1,0)+IF(Y128=$I$128,3,0)+IF(Y129=$G128+$H128,1,0)+IF(Y130=$I$130,3,0)+IF(Y131=$G130+$H130,1,0)+IF(Y132=$I$132,3,0)+IF(Y133=$G132+$H132,1,0)+IF(Y134=$I$134,3,0)+IF(Y135=$G134+$H134,1,0)+IF(Y136=$I$136,3,0)+IF(Y137=$G136+$H136,1,0)+IF(Y138=$I$138,3,0)+IF(Y139=$G138+$H138,1,0)+IF(Y140=$I$140,3,0)+IF(Y141=$G140+$H140,1,0)+IF(Y142=$I$142,3,0)+IF(Y143=$G142+$H142,1,0)+IF(Y144=$I$144,3,0)+IF(Y145=$G144+$H144,1,0)+IF(Y146=$I$146,3,0)+IF(Y147=$G146+$H146,1,0)+IF(Y148=$I$148,3,0)+IF(Y149=$G148+$H148,1,0)+IF(Y150=$I$150,3,0)+IF(Y151=$G150+$H150,1,0))</f>
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Z5" s="75">
         <f>SUM(IF(Z80=$I$80,3,0)+IF(Z81=$G80+$H80,1,0)+IF(Z82=$I$82,3,0)+IF(Z83=$G82+$H82,1,0)+IF(Z84=$I$84,3,0)+IF(Z85=$G84+$H84,1,0)+IF(Z86=$I$86,3,0)+IF(Z87=$G86+$H86,1,0)+IF(Z88=$I$88,3,0)+IF(Z89=$G88+$H88,1,0)+IF(Z90=$I$90,3,0)+IF(Z91=$G90+$H90,1,0)+IF(Z92=$I$92,3,0)+IF(Z93=$G92+$H92,1,0)+IF(Z94=$I$94,3,0)+IF(Z95=$G94+$H94,1,0)+IF(Z96=$I$96,3,0)+IF(Z97=$G96+$H96,1,0)+IF(Z98=$I$98,3,0)+IF(Z99=$G98+$H98,1,0)+IF(Z100=$I$100,3,0)+IF(Z101=$G100+$H100,1,0)+IF(Z102=$I$102,3,0)+IF(Z103=$G102+$H102,1,0)+IF(Z104=$I$104,3,0)+IF(Z105=$G104+$H104,1,0)+IF(Z106=$I$106,3,0)+IF(Z107=$G106+$H106,1,0)+IF(Z108=$I$108,3,0)+IF(Z109=$G108+$H108,1,0)+IF(Z110=$I$110,3,0)+IF(Z111=$G110+$H110,1,0)+IF(Z112=$I$112,3,0)+IF(Z113=$G112+$H112,1,0)+IF(Z114=$I$114,3,0)+IF(Z115=$G114+$H114,1,0)+IF(Z116=$I$116,3,0)+IF(Z117=$G116+$H116,1,0)+IF(Z118=$I$118,3,0)+IF(Z119=$G118+$H118,1,0)+IF(Z120=$I$120,3,0)+IF(Z121=$G120+$H120,1,0)+IF(Z122=$I$122,3,0)+IF(Z123=$G122+$H122,1,0)+IF(Z124=$I$124,3,0)+IF(Z125=$G124+$H124,1,0)+IF(Z126=$I$126,3,0)+IF(Z127=$G126+$H126,1,0)+IF(Z128=$I$128,3,0)+IF(Z129=$G128+$H128,1,0)+IF(Z130=$I$130,3,0)+IF(Z131=$G130+$H130,1,0)+IF(Z132=$I$132,3,0)+IF(Z133=$G132+$H132,1,0)+IF(Z134=$I$134,3,0)+IF(Z135=$G134+$H134,1,0)+IF(Z136=$I$136,3,0)+IF(Z137=$G136+$H136,1,0)+IF(Z138=$I$138,3,0)+IF(Z139=$G138+$H138,1,0)+IF(Z140=$I$140,3,0)+IF(Z141=$G140+$H140,1,0)+IF(Z142=$I$142,3,0)+IF(Z143=$G142+$H142,1,0)+IF(Z144=$I$144,3,0)+IF(Z145=$G144+$H144,1,0)+IF(Z146=$I$146,3,0)+IF(Z147=$G146+$H146,1,0)+IF(Z148=$I$148,3,0)+IF(Z149=$G148+$H148,1,0)+IF(Z150=$I$150,3,0)+IF(Z151=$G150+$H150,1,0))</f>
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AA5" s="75">
         <f>SUM(IF(AA80=$I$80,3,0)+IF(AA81=$G80+$H80,1,0)+IF(AA82=$I$82,3,0)+IF(AA83=$G82+$H82,1,0)+IF(AA84=$I$84,3,0)+IF(AA85=$G84+$H84,1,0)+IF(AA86=$I$86,3,0)+IF(AA87=$G86+$H86,1,0)+IF(AA88=$I$88,3,0)+IF(AA89=$G88+$H88,1,0)+IF(AA90=$I$90,3,0)+IF(AA91=$G90+$H90,1,0)+IF(AA92=$I$92,3,0)+IF(AA93=$G92+$H92,1,0)+IF(AA94=$I$94,3,0)+IF(AA95=$G94+$H94,1,0)+IF(AA96=$I$96,3,0)+IF(AA97=$G96+$H96,1,0)+IF(AA98=$I$98,3,0)+IF(AA99=$G98+$H98,1,0)+IF(AA100=$I$100,3,0)+IF(AA101=$G100+$H100,1,0)+IF(AA102=$I$102,3,0)+IF(AA103=$G102+$H102,1,0)+IF(AA104=$I$104,3,0)+IF(AA105=$G104+$H104,1,0)+IF(AA106=$I$106,3,0)+IF(AA107=$G106+$H106,1,0)+IF(AA108=$I$108,3,0)+IF(AA109=$G108+$H108,1,0)+IF(AA110=$I$110,3,0)+IF(AA111=$G110+$H110,1,0)+IF(AA112=$I$112,3,0)+IF(AA113=$G112+$H112,1,0)+IF(AA114=$I$114,3,0)+IF(AA115=$G114+$H114,1,0)+IF(AA116=$I$116,3,0)+IF(AA117=$G116+$H116,1,0)+IF(AA118=$I$118,3,0)+IF(AA119=$G118+$H118,1,0)+IF(AA120=$I$120,3,0)+IF(AA121=$G120+$H120,1,0)+IF(AA122=$I$122,3,0)+IF(AA123=$G122+$H122,1,0)+IF(AA124=$I$124,3,0)+IF(AA125=$G124+$H124,1,0)+IF(AA126=$I$126,3,0)+IF(AA127=$G126+$H126,1,0)+IF(AA128=$I$128,3,0)+IF(AA129=$G128+$H128,1,0)+IF(AA130=$I$130,3,0)+IF(AA131=$G130+$H130,1,0)+IF(AA132=$I$132,3,0)+IF(AA133=$G132+$H132,1,0)+IF(AA134=$I$134,3,0)+IF(AA135=$G134+$H134,1,0)+IF(AA136=$I$136,3,0)+IF(AA137=$G136+$H136,1,0)+IF(AA138=$I$138,3,0)+IF(AA139=$G138+$H138,1,0)+IF(AA140=$I$140,3,0)+IF(AA141=$G140+$H140,1,0)+IF(AA142=$I$142,3,0)+IF(AA143=$G142+$H142,1,0)+IF(AA144=$I$144,3,0)+IF(AA145=$G144+$H144,1,0)+IF(AA146=$I$146,3,0)+IF(AA147=$G146+$H146,1,0)+IF(AA148=$I$148,3,0)+IF(AA149=$G148+$H148,1,0)+IF(AA150=$I$150,3,0)+IF(AA151=$G150+$H150,1,0))</f>
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="AB5" s="75">
         <f>SUM(IF(AB80=$I$80,3,0)+IF(AB81=$G80+$H80,1,0)+IF(AB82=$I$82,3,0)+IF(AB83=$G82+$H82,1,0)+IF(AB84=$I$84,3,0)+IF(AB85=$G84+$H84,1,0)+IF(AB86=$I$86,3,0)+IF(AB87=$G86+$H86,1,0)+IF(AB88=$I$88,3,0)+IF(AB89=$G88+$H88,1,0)+IF(AB90=$I$90,3,0)+IF(AB91=$G90+$H90,1,0)+IF(AB92=$I$92,3,0)+IF(AB93=$G92+$H92,1,0)+IF(AB94=$I$94,3,0)+IF(AB95=$G94+$H94,1,0)+IF(AB96=$I$96,3,0)+IF(AB97=$G96+$H96,1,0)+IF(AB98=$I$98,3,0)+IF(AB99=$G98+$H98,1,0)+IF(AB100=$I$100,3,0)+IF(AB101=$G100+$H100,1,0)+IF(AB102=$I$102,3,0)+IF(AB103=$G102+$H102,1,0)+IF(AB104=$I$104,3,0)+IF(AB105=$G104+$H104,1,0)+IF(AB106=$I$106,3,0)+IF(AB107=$G106+$H106,1,0)+IF(AB108=$I$108,3,0)+IF(AB109=$G108+$H108,1,0)+IF(AB110=$I$110,3,0)+IF(AB111=$G110+$H110,1,0)+IF(AB112=$I$112,3,0)+IF(AB113=$G112+$H112,1,0)+IF(AB114=$I$114,3,0)+IF(AB115=$G114+$H114,1,0)+IF(AB116=$I$116,3,0)+IF(AB117=$G116+$H116,1,0)+IF(AB118=$I$118,3,0)+IF(AB119=$G118+$H118,1,0)+IF(AB120=$I$120,3,0)+IF(AB121=$G120+$H120,1,0)+IF(AB122=$I$122,3,0)+IF(AB123=$G122+$H122,1,0)+IF(AB124=$I$124,3,0)+IF(AB125=$G124+$H124,1,0)+IF(AB126=$I$126,3,0)+IF(AB127=$G126+$H126,1,0)+IF(AB128=$I$128,3,0)+IF(AB129=$G128+$H128,1,0)+IF(AB130=$I$130,3,0)+IF(AB131=$G130+$H130,1,0)+IF(AB132=$I$132,3,0)+IF(AB133=$G132+$H132,1,0)+IF(AB134=$I$134,3,0)+IF(AB135=$G134+$H134,1,0)+IF(AB136=$I$136,3,0)+IF(AB137=$G136+$H136,1,0)+IF(AB138=$I$138,3,0)+IF(AB139=$G138+$H138,1,0)+IF(AB140=$I$140,3,0)+IF(AB141=$G140+$H140,1,0)+IF(AB142=$I$142,3,0)+IF(AB143=$G142+$H142,1,0)+IF(AB144=$I$144,3,0)+IF(AB145=$G144+$H144,1,0)+IF(AB146=$I$146,3,0)+IF(AB147=$G146+$H146,1,0)+IF(AB148=$I$148,3,0)+IF(AB149=$G148+$H148,1,0)+IF(AB150=$I$150,3,0)+IF(AB151=$G150+$H150,1,0))</f>
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AC5" s="75">
         <f>SUM(IF(AC80=$I$80,3,0)+IF(AC81=$G80+$H80,1,0)+IF(AC82=$I$82,3,0)+IF(AC83=$G82+$H82,1,0)+IF(AC84=$I$84,3,0)+IF(AC85=$G84+$H84,1,0)+IF(AC86=$I$86,3,0)+IF(AC87=$G86+$H86,1,0)+IF(AC88=$I$88,3,0)+IF(AC89=$G88+$H88,1,0)+IF(AC90=$I$90,3,0)+IF(AC91=$G90+$H90,1,0)+IF(AC92=$I$92,3,0)+IF(AC93=$G92+$H92,1,0)+IF(AC94=$I$94,3,0)+IF(AC95=$G94+$H94,1,0)+IF(AC96=$I$96,3,0)+IF(AC97=$G96+$H96,1,0)+IF(AC98=$I$98,3,0)+IF(AC99=$G98+$H98,1,0)+IF(AC100=$I$100,3,0)+IF(AC101=$G100+$H100,1,0)+IF(AC102=$I$102,3,0)+IF(AC103=$G102+$H102,1,0)+IF(AC104=$I$104,3,0)+IF(AC105=$G104+$H104,1,0)+IF(AC106=$I$106,3,0)+IF(AC107=$G106+$H106,1,0)+IF(AC108=$I$108,3,0)+IF(AC109=$G108+$H108,1,0)+IF(AC110=$I$110,3,0)+IF(AC111=$G110+$H110,1,0)+IF(AC112=$I$112,3,0)+IF(AC113=$G112+$H112,1,0)+IF(AC114=$I$114,3,0)+IF(AC115=$G114+$H114,1,0)+IF(AC116=$I$116,3,0)+IF(AC117=$G116+$H116,1,0)+IF(AC118=$I$118,3,0)+IF(AC119=$G118+$H118,1,0)+IF(AC120=$I$120,3,0)+IF(AC121=$G120+$H120,1,0)+IF(AC122=$I$122,3,0)+IF(AC123=$G122+$H122,1,0)+IF(AC124=$I$124,3,0)+IF(AC125=$G124+$H124,1,0)+IF(AC126=$I$126,3,0)+IF(AC127=$G126+$H126,1,0)+IF(AC128=$I$128,3,0)+IF(AC129=$G128+$H128,1,0)+IF(AC130=$I$130,3,0)+IF(AC131=$G130+$H130,1,0)+IF(AC132=$I$132,3,0)+IF(AC133=$G132+$H132,1,0)+IF(AC134=$I$134,3,0)+IF(AC135=$G134+$H134,1,0)+IF(AC136=$I$136,3,0)+IF(AC137=$G136+$H136,1,0)+IF(AC138=$I$138,3,0)+IF(AC139=$G138+$H138,1,0)+IF(AC140=$I$140,3,0)+IF(AC141=$G140+$H140,1,0)+IF(AC142=$I$142,3,0)+IF(AC143=$G142+$H142,1,0)+IF(AC144=$I$144,3,0)+IF(AC145=$G144+$H144,1,0)+IF(AC146=$I$146,3,0)+IF(AC147=$G146+$H146,1,0)+IF(AC148=$I$148,3,0)+IF(AC149=$G148+$H148,1,0)+IF(AC150=$I$150,3,0)+IF(AC151=$G150+$H150,1,0))</f>
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD5" s="75">
         <f>SUM(IF(AD80=$I$80,3,0)+IF(AD81=$G80+$H80,1,0)+IF(AD82=$I$82,3,0)+IF(AD83=$G82+$H82,1,0)+IF(AD84=$I$84,3,0)+IF(AD85=$G84+$H84,1,0)+IF(AD86=$I$86,3,0)+IF(AD87=$G86+$H86,1,0)+IF(AD88=$I$88,3,0)+IF(AD89=$G88+$H88,1,0)+IF(AD90=$I$90,3,0)+IF(AD91=$G90+$H90,1,0)+IF(AD92=$I$92,3,0)+IF(AD93=$G92+$H92,1,0)+IF(AD94=$I$94,3,0)+IF(AD95=$G94+$H94,1,0)+IF(AD96=$I$96,3,0)+IF(AD97=$G96+$H96,1,0)+IF(AD98=$I$98,3,0)+IF(AD99=$G98+$H98,1,0)+IF(AD100=$I$100,3,0)+IF(AD101=$G100+$H100,1,0)+IF(AD102=$I$102,3,0)+IF(AD103=$G102+$H102,1,0)+IF(AD104=$I$104,3,0)+IF(AD105=$G104+$H104,1,0)+IF(AD106=$I$106,3,0)+IF(AD107=$G106+$H106,1,0)+IF(AD108=$I$108,3,0)+IF(AD109=$G108+$H108,1,0)+IF(AD110=$I$110,3,0)+IF(AD111=$G110+$H110,1,0)+IF(AD112=$I$112,3,0)+IF(AD113=$G112+$H112,1,0)+IF(AD114=$I$114,3,0)+IF(AD115=$G114+$H114,1,0)+IF(AD116=$I$116,3,0)+IF(AD117=$G116+$H116,1,0)+IF(AD118=$I$118,3,0)+IF(AD119=$G118+$H118,1,0)+IF(AD120=$I$120,3,0)+IF(AD121=$G120+$H120,1,0)+IF(AD122=$I$122,3,0)+IF(AD123=$G122+$H122,1,0)+IF(AD124=$I$124,3,0)+IF(AD125=$G124+$H124,1,0)+IF(AD126=$I$126,3,0)+IF(AD127=$G126+$H126,1,0)+IF(AD128=$I$128,3,0)+IF(AD129=$G128+$H128,1,0)+IF(AD130=$I$130,3,0)+IF(AD131=$G130+$H130,1,0)+IF(AD132=$I$132,3,0)+IF(AD133=$G132+$H132,1,0)+IF(AD134=$I$134,3,0)+IF(AD135=$G134+$H134,1,0)+IF(AD136=$I$136,3,0)+IF(AD137=$G136+$H136,1,0)+IF(AD138=$I$138,3,0)+IF(AD139=$G138+$H138,1,0)+IF(AD140=$I$140,3,0)+IF(AD141=$G140+$H140,1,0)+IF(AD142=$I$142,3,0)+IF(AD143=$G142+$H142,1,0)+IF(AD144=$I$144,3,0)+IF(AD145=$G144+$H144,1,0)+IF(AD146=$I$146,3,0)+IF(AD147=$G146+$H146,1,0)+IF(AD148=$I$148,3,0)+IF(AD149=$G148+$H148,1,0)+IF(AD150=$I$150,3,0)+IF(AD151=$G150+$H150,1,0))</f>
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="AE5" s="75">
         <f>SUM(IF(AE80=$I$80,3,0)+IF(AE81=$G80+$H80,1,0)+IF(AE82=$I$82,3,0)+IF(AE83=$G82+$H82,1,0)+IF(AE84=$I$84,3,0)+IF(AE85=$G84+$H84,1,0)+IF(AE86=$I$86,3,0)+IF(AE87=$G86+$H86,1,0)+IF(AE88=$I$88,3,0)+IF(AE89=$G88+$H88,1,0)+IF(AE90=$I$90,3,0)+IF(AE91=$G90+$H90,1,0)+IF(AE92=$I$92,3,0)+IF(AE93=$G92+$H92,1,0)+IF(AE94=$I$94,3,0)+IF(AE95=$G94+$H94,1,0)+IF(AE96=$I$96,3,0)+IF(AE97=$G96+$H96,1,0)+IF(AE98=$I$98,3,0)+IF(AE99=$G98+$H98,1,0)+IF(AE100=$I$100,3,0)+IF(AE101=$G100+$H100,1,0)+IF(AE102=$I$102,3,0)+IF(AE103=$G102+$H102,1,0)+IF(AE104=$I$104,3,0)+IF(AE105=$G104+$H104,1,0)+IF(AE106=$I$106,3,0)+IF(AE107=$G106+$H106,1,0)+IF(AE108=$I$108,3,0)+IF(AE109=$G108+$H108,1,0)+IF(AE110=$I$110,3,0)+IF(AE111=$G110+$H110,1,0)+IF(AE112=$I$112,3,0)+IF(AE113=$G112+$H112,1,0)+IF(AE114=$I$114,3,0)+IF(AE115=$G114+$H114,1,0)+IF(AE116=$I$116,3,0)+IF(AE117=$G116+$H116,1,0)+IF(AE118=$I$118,3,0)+IF(AE119=$G118+$H118,1,0)+IF(AE120=$I$120,3,0)+IF(AE121=$G120+$H120,1,0)+IF(AE122=$I$122,3,0)+IF(AE123=$G122+$H122,1,0)+IF(AE124=$I$124,3,0)+IF(AE125=$G124+$H124,1,0)+IF(AE126=$I$126,3,0)+IF(AE127=$G126+$H126,1,0)+IF(AE128=$I$128,3,0)+IF(AE129=$G128+$H128,1,0)+IF(AE130=$I$130,3,0)+IF(AE131=$G130+$H130,1,0)+IF(AE132=$I$132,3,0)+IF(AE133=$G132+$H132,1,0)+IF(AE134=$I$134,3,0)+IF(AE135=$G134+$H134,1,0)+IF(AE136=$I$136,3,0)+IF(AE137=$G136+$H136,1,0)+IF(AE138=$I$138,3,0)+IF(AE139=$G138+$H138,1,0)+IF(AE140=$I$140,3,0)+IF(AE141=$G140+$H140,1,0)+IF(AE142=$I$142,3,0)+IF(AE143=$G142+$H142,1,0)+IF(AE144=$I$144,3,0)+IF(AE145=$G144+$H144,1,0)+IF(AE146=$I$146,3,0)+IF(AE147=$G146+$H146,1,0)+IF(AE148=$I$148,3,0)+IF(AE149=$G148+$H148,1,0)+IF(AE150=$I$150,3,0)+IF(AE151=$G150+$H150,1,0))</f>
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AF5" s="75">
         <f>SUM(IF(AF80=$I$80,3,0)+IF(AF81=$G80+$H80,1,0)+IF(AF82=$I$82,3,0)+IF(AF83=$G82+$H82,1,0)+IF(AF84=$I$84,3,0)+IF(AF85=$G84+$H84,1,0)+IF(AF86=$I$86,3,0)+IF(AF87=$G86+$H86,1,0)+IF(AF88=$I$88,3,0)+IF(AF89=$G88+$H88,1,0)+IF(AF90=$I$90,3,0)+IF(AF91=$G90+$H90,1,0)+IF(AF92=$I$92,3,0)+IF(AF93=$G92+$H92,1,0)+IF(AF94=$I$94,3,0)+IF(AF95=$G94+$H94,1,0)+IF(AF96=$I$96,3,0)+IF(AF97=$G96+$H96,1,0)+IF(AF98=$I$98,3,0)+IF(AF99=$G98+$H98,1,0)+IF(AF100=$I$100,3,0)+IF(AF101=$G100+$H100,1,0)+IF(AF102=$I$102,3,0)+IF(AF103=$G102+$H102,1,0)+IF(AF104=$I$104,3,0)+IF(AF105=$G104+$H104,1,0)+IF(AF106=$I$106,3,0)+IF(AF107=$G106+$H106,1,0)+IF(AF108=$I$108,3,0)+IF(AF109=$G108+$H108,1,0)+IF(AF110=$I$110,3,0)+IF(AF111=$G110+$H110,1,0)+IF(AF112=$I$112,3,0)+IF(AF113=$G112+$H112,1,0)+IF(AF114=$I$114,3,0)+IF(AF115=$G114+$H114,1,0)+IF(AF116=$I$116,3,0)+IF(AF117=$G116+$H116,1,0)+IF(AF118=$I$118,3,0)+IF(AF119=$G118+$H118,1,0)+IF(AF120=$I$120,3,0)+IF(AF121=$G120+$H120,1,0)+IF(AF122=$I$122,3,0)+IF(AF123=$G122+$H122,1,0)+IF(AF124=$I$124,3,0)+IF(AF125=$G124+$H124,1,0)+IF(AF126=$I$126,3,0)+IF(AF127=$G126+$H126,1,0)+IF(AF128=$I$128,3,0)+IF(AF129=$G128+$H128,1,0)+IF(AF130=$I$130,3,0)+IF(AF131=$G130+$H130,1,0)+IF(AF132=$I$132,3,0)+IF(AF133=$G132+$H132,1,0)+IF(AF134=$I$134,3,0)+IF(AF135=$G134+$H134,1,0)+IF(AF136=$I$136,3,0)+IF(AF137=$G136+$H136,1,0)+IF(AF138=$I$138,3,0)+IF(AF139=$G138+$H138,1,0)+IF(AF140=$I$140,3,0)+IF(AF141=$G140+$H140,1,0)+IF(AF142=$I$142,3,0)+IF(AF143=$G142+$H142,1,0)+IF(AF144=$I$144,3,0)+IF(AF145=$G144+$H144,1,0)+IF(AF146=$I$146,3,0)+IF(AF147=$G146+$H146,1,0)+IF(AF148=$I$148,3,0)+IF(AF149=$G148+$H148,1,0)+IF(AF150=$I$150,3,0)+IF(AF151=$G150+$H150,1,0))</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AG5" s="75">
         <f>SUM(IF(AG80=$I$80,3,0)+IF(AG81=$G80+$H80,1,0)+IF(AG82=$I$82,3,0)+IF(AG83=$G82+$H82,1,0)+IF(AG84=$I$84,3,0)+IF(AG85=$G84+$H84,1,0)+IF(AG86=$I$86,3,0)+IF(AG87=$G86+$H86,1,0)+IF(AG88=$I$88,3,0)+IF(AG89=$G88+$H88,1,0)+IF(AG90=$I$90,3,0)+IF(AG91=$G90+$H90,1,0)+IF(AG92=$I$92,3,0)+IF(AG93=$G92+$H92,1,0)+IF(AG94=$I$94,3,0)+IF(AG95=$G94+$H94,1,0)+IF(AG96=$I$96,3,0)+IF(AG97=$G96+$H96,1,0)+IF(AG98=$I$98,3,0)+IF(AG99=$G98+$H98,1,0)+IF(AG100=$I$100,3,0)+IF(AG101=$G100+$H100,1,0)+IF(AG102=$I$102,3,0)+IF(AG103=$G102+$H102,1,0)+IF(AG104=$I$104,3,0)+IF(AG105=$G104+$H104,1,0)+IF(AG106=$I$106,3,0)+IF(AG107=$G106+$H106,1,0)+IF(AG108=$I$108,3,0)+IF(AG109=$G108+$H108,1,0)+IF(AG110=$I$110,3,0)+IF(AG111=$G110+$H110,1,0)+IF(AG112=$I$112,3,0)+IF(AG113=$G112+$H112,1,0)+IF(AG114=$I$114,3,0)+IF(AG115=$G114+$H114,1,0)+IF(AG116=$I$116,3,0)+IF(AG117=$G116+$H116,1,0)+IF(AG118=$I$118,3,0)+IF(AG119=$G118+$H118,1,0)+IF(AG120=$I$120,3,0)+IF(AG121=$G120+$H120,1,0)+IF(AG122=$I$122,3,0)+IF(AG123=$G122+$H122,1,0)+IF(AG124=$I$124,3,0)+IF(AG125=$G124+$H124,1,0)+IF(AG126=$I$126,3,0)+IF(AG127=$G126+$H126,1,0)+IF(AG128=$I$128,3,0)+IF(AG129=$G128+$H128,1,0)+IF(AG130=$I$130,3,0)+IF(AG131=$G130+$H130,1,0)+IF(AG132=$I$132,3,0)+IF(AG133=$G132+$H132,1,0)+IF(AG134=$I$134,3,0)+IF(AG135=$G134+$H134,1,0)+IF(AG136=$I$136,3,0)+IF(AG137=$G136+$H136,1,0)+IF(AG138=$I$138,3,0)+IF(AG139=$G138+$H138,1,0)+IF(AG140=$I$140,3,0)+IF(AG141=$G140+$H140,1,0)+IF(AG142=$I$142,3,0)+IF(AG143=$G142+$H142,1,0)+IF(AG144=$I$144,3,0)+IF(AG145=$G144+$H144,1,0)+IF(AG146=$I$146,3,0)+IF(AG147=$G146+$H146,1,0)+IF(AG148=$I$148,3,0)+IF(AG149=$G148+$H148,1,0)+IF(AG150=$I$150,3,0)+IF(AG151=$G150+$H150,1,0))</f>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AH5" s="75">
         <f>SUM(IF(AH80=$I$80,3,0)+IF(AH81=$G80+$H80,1,0)+IF(AH82=$I$82,3,0)+IF(AH83=$G82+$H82,1,0)+IF(AH84=$I$84,3,0)+IF(AH85=$G84+$H84,1,0)+IF(AH86=$I$86,3,0)+IF(AH87=$G86+$H86,1,0)+IF(AH88=$I$88,3,0)+IF(AH89=$G88+$H88,1,0)+IF(AH90=$I$90,3,0)+IF(AH91=$G90+$H90,1,0)+IF(AH92=$I$92,3,0)+IF(AH93=$G92+$H92,1,0)+IF(AH94=$I$94,3,0)+IF(AH95=$G94+$H94,1,0)+IF(AH96=$I$96,3,0)+IF(AH97=$G96+$H96,1,0)+IF(AH98=$I$98,3,0)+IF(AH99=$G98+$H98,1,0)+IF(AH100=$I$100,3,0)+IF(AH101=$G100+$H100,1,0)+IF(AH102=$I$102,3,0)+IF(AH103=$G102+$H102,1,0)+IF(AH104=$I$104,3,0)+IF(AH105=$G104+$H104,1,0)+IF(AH106=$I$106,3,0)+IF(AH107=$G106+$H106,1,0)+IF(AH108=$I$108,3,0)+IF(AH109=$G108+$H108,1,0)+IF(AH110=$I$110,3,0)+IF(AH111=$G110+$H110,1,0)+IF(AH112=$I$112,3,0)+IF(AH113=$G112+$H112,1,0)+IF(AH114=$I$114,3,0)+IF(AH115=$G114+$H114,1,0)+IF(AH116=$I$116,3,0)+IF(AH117=$G116+$H116,1,0)+IF(AH118=$I$118,3,0)+IF(AH119=$G118+$H118,1,0)+IF(AH120=$I$120,3,0)+IF(AH121=$G120+$H120,1,0)+IF(AH122=$I$122,3,0)+IF(AH123=$G122+$H122,1,0)+IF(AH124=$I$124,3,0)+IF(AH125=$G124+$H124,1,0)+IF(AH126=$I$126,3,0)+IF(AH127=$G126+$H126,1,0)+IF(AH128=$I$128,3,0)+IF(AH129=$G128+$H128,1,0)+IF(AH130=$I$130,3,0)+IF(AH131=$G130+$H130,1,0)+IF(AH132=$I$132,3,0)+IF(AH133=$G132+$H132,1,0)+IF(AH134=$I$134,3,0)+IF(AH135=$G134+$H134,1,0)+IF(AH136=$I$136,3,0)+IF(AH137=$G136+$H136,1,0)+IF(AH138=$I$138,3,0)+IF(AH139=$G138+$H138,1,0)+IF(AH140=$I$140,3,0)+IF(AH141=$G140+$H140,1,0)+IF(AH142=$I$142,3,0)+IF(AH143=$G142+$H142,1,0)+IF(AH144=$I$144,3,0)+IF(AH145=$G144+$H144,1,0)+IF(AH146=$I$146,3,0)+IF(AH147=$G146+$H146,1,0)+IF(AH148=$I$148,3,0)+IF(AH149=$G148+$H148,1,0)+IF(AH150=$I$150,3,0)+IF(AH151=$G150+$H150,1,0))</f>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AI5" s="75">
         <f>SUM(IF(AI80=$I$80,3,0)+IF(AI81=$G80+$H80,1,0)+IF(AI82=$I$82,3,0)+IF(AI83=$G82+$H82,1,0)+IF(AI84=$I$84,3,0)+IF(AI85=$G84+$H84,1,0)+IF(AI86=$I$86,3,0)+IF(AI87=$G86+$H86,1,0)+IF(AI88=$I$88,3,0)+IF(AI89=$G88+$H88,1,0)+IF(AI90=$I$90,3,0)+IF(AI91=$G90+$H90,1,0)+IF(AI92=$I$92,3,0)+IF(AI93=$G92+$H92,1,0)+IF(AI94=$I$94,3,0)+IF(AI95=$G94+$H94,1,0)+IF(AI96=$I$96,3,0)+IF(AI97=$G96+$H96,1,0)+IF(AI98=$I$98,3,0)+IF(AI99=$G98+$H98,1,0)+IF(AI100=$I$100,3,0)+IF(AI101=$G100+$H100,1,0)+IF(AI102=$I$102,3,0)+IF(AI103=$G102+$H102,1,0)+IF(AI104=$I$104,3,0)+IF(AI105=$G104+$H104,1,0)+IF(AI106=$I$106,3,0)+IF(AI107=$G106+$H106,1,0)+IF(AI108=$I$108,3,0)+IF(AI109=$G108+$H108,1,0)+IF(AI110=$I$110,3,0)+IF(AI111=$G110+$H110,1,0)+IF(AI112=$I$112,3,0)+IF(AI113=$G112+$H112,1,0)+IF(AI114=$I$114,3,0)+IF(AI115=$G114+$H114,1,0)+IF(AI116=$I$116,3,0)+IF(AI117=$G116+$H116,1,0)+IF(AI118=$I$118,3,0)+IF(AI119=$G118+$H118,1,0)+IF(AI120=$I$120,3,0)+IF(AI121=$G120+$H120,1,0)+IF(AI122=$I$122,3,0)+IF(AI123=$G122+$H122,1,0)+IF(AI124=$I$124,3,0)+IF(AI125=$G124+$H124,1,0)+IF(AI126=$I$126,3,0)+IF(AI127=$G126+$H126,1,0)+IF(AI128=$I$128,3,0)+IF(AI129=$G128+$H128,1,0)+IF(AI130=$I$130,3,0)+IF(AI131=$G130+$H130,1,0)+IF(AI132=$I$132,3,0)+IF(AI133=$G132+$H132,1,0)+IF(AI134=$I$134,3,0)+IF(AI135=$G134+$H134,1,0)+IF(AI136=$I$136,3,0)+IF(AI137=$G136+$H136,1,0)+IF(AI138=$I$138,3,0)+IF(AI139=$G138+$H138,1,0)+IF(AI140=$I$140,3,0)+IF(AI141=$G140+$H140,1,0)+IF(AI142=$I$142,3,0)+IF(AI143=$G142+$H142,1,0)+IF(AI144=$I$144,3,0)+IF(AI145=$G144+$H144,1,0)+IF(AI146=$I$146,3,0)+IF(AI147=$G146+$H146,1,0)+IF(AI148=$I$148,3,0)+IF(AI149=$G148+$H148,1,0)+IF(AI150=$I$150,3,0)+IF(AI151=$G150+$H150,1,0))</f>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AJ5" s="75">
         <f>SUM(IF(AJ80=$I$80,3,0)+IF(AJ81=$G80+$H80,1,0)+IF(AJ82=$I$82,3,0)+IF(AJ83=$G82+$H82,1,0)+IF(AJ84=$I$84,3,0)+IF(AJ85=$G84+$H84,1,0)+IF(AJ86=$I$86,3,0)+IF(AJ87=$G86+$H86,1,0)+IF(AJ88=$I$88,3,0)+IF(AJ89=$G88+$H88,1,0)+IF(AJ90=$I$90,3,0)+IF(AJ91=$G90+$H90,1,0)+IF(AJ92=$I$92,3,0)+IF(AJ93=$G92+$H92,1,0)+IF(AJ94=$I$94,3,0)+IF(AJ95=$G94+$H94,1,0)+IF(AJ96=$I$96,3,0)+IF(AJ97=$G96+$H96,1,0)+IF(AJ98=$I$98,3,0)+IF(AJ99=$G98+$H98,1,0)+IF(AJ100=$I$100,3,0)+IF(AJ101=$G100+$H100,1,0)+IF(AJ102=$I$102,3,0)+IF(AJ103=$G102+$H102,1,0)+IF(AJ104=$I$104,3,0)+IF(AJ105=$G104+$H104,1,0)+IF(AJ106=$I$106,3,0)+IF(AJ107=$G106+$H106,1,0)+IF(AJ108=$I$108,3,0)+IF(AJ109=$G108+$H108,1,0)+IF(AJ110=$I$110,3,0)+IF(AJ111=$G110+$H110,1,0)+IF(AJ112=$I$112,3,0)+IF(AJ113=$G112+$H112,1,0)+IF(AJ114=$I$114,3,0)+IF(AJ115=$G114+$H114,1,0)+IF(AJ116=$I$116,3,0)+IF(AJ117=$G116+$H116,1,0)+IF(AJ118=$I$118,3,0)+IF(AJ119=$G118+$H118,1,0)+IF(AJ120=$I$120,3,0)+IF(AJ121=$G120+$H120,1,0)+IF(AJ122=$I$122,3,0)+IF(AJ123=$G122+$H122,1,0)+IF(AJ124=$I$124,3,0)+IF(AJ125=$G124+$H124,1,0)+IF(AJ126=$I$126,3,0)+IF(AJ127=$G126+$H126,1,0)+IF(AJ128=$I$128,3,0)+IF(AJ129=$G128+$H128,1,0)+IF(AJ130=$I$130,3,0)+IF(AJ131=$G130+$H130,1,0)+IF(AJ132=$I$132,3,0)+IF(AJ133=$G132+$H132,1,0)+IF(AJ134=$I$134,3,0)+IF(AJ135=$G134+$H134,1,0)+IF(AJ136=$I$136,3,0)+IF(AJ137=$G136+$H136,1,0)+IF(AJ138=$I$138,3,0)+IF(AJ139=$G138+$H138,1,0)+IF(AJ140=$I$140,3,0)+IF(AJ141=$G140+$H140,1,0)+IF(AJ142=$I$142,3,0)+IF(AJ143=$G142+$H142,1,0)+IF(AJ144=$I$144,3,0)+IF(AJ145=$G144+$H144,1,0)+IF(AJ146=$I$146,3,0)+IF(AJ147=$G146+$H146,1,0)+IF(AJ148=$I$148,3,0)+IF(AJ149=$G148+$H148,1,0)+IF(AJ150=$I$150,3,0)+IF(AJ151=$G150+$H150,1,0))</f>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AK5" s="75">
         <f>SUM(IF(AK80=$I$80,3,0)+IF(AK81=$G80+$H80,1,0)+IF(AK82=$I$82,3,0)+IF(AK83=$G82+$H82,1,0)+IF(AK84=$I$84,3,0)+IF(AK85=$G84+$H84,1,0)+IF(AK86=$I$86,3,0)+IF(AK87=$G86+$H86,1,0)+IF(AK88=$I$88,3,0)+IF(AK89=$G88+$H88,1,0)+IF(AK90=$I$90,3,0)+IF(AK91=$G90+$H90,1,0)+IF(AK92=$I$92,3,0)+IF(AK93=$G92+$H92,1,0)+IF(AK94=$I$94,3,0)+IF(AK95=$G94+$H94,1,0)+IF(AK96=$I$96,3,0)+IF(AK97=$G96+$H96,1,0)+IF(AK98=$I$98,3,0)+IF(AK99=$G98+$H98,1,0)+IF(AK100=$I$100,3,0)+IF(AK101=$G100+$H100,1,0)+IF(AK102=$I$102,3,0)+IF(AK103=$G102+$H102,1,0)+IF(AK104=$I$104,3,0)+IF(AK105=$G104+$H104,1,0)+IF(AK106=$I$106,3,0)+IF(AK107=$G106+$H106,1,0)+IF(AK108=$I$108,3,0)+IF(AK109=$G108+$H108,1,0)+IF(AK110=$I$110,3,0)+IF(AK111=$G110+$H110,1,0)+IF(AK112=$I$112,3,0)+IF(AK113=$G112+$H112,1,0)+IF(AK114=$I$114,3,0)+IF(AK115=$G114+$H114,1,0)+IF(AK116=$I$116,3,0)+IF(AK117=$G116+$H116,1,0)+IF(AK118=$I$118,3,0)+IF(AK119=$G118+$H118,1,0)+IF(AK120=$I$120,3,0)+IF(AK121=$G120+$H120,1,0)+IF(AK122=$I$122,3,0)+IF(AK123=$G122+$H122,1,0)+IF(AK124=$I$124,3,0)+IF(AK125=$G124+$H124,1,0)+IF(AK126=$I$126,3,0)+IF(AK127=$G126+$H126,1,0)+IF(AK128=$I$128,3,0)+IF(AK129=$G128+$H128,1,0)+IF(AK130=$I$130,3,0)+IF(AK131=$G130+$H130,1,0)+IF(AK132=$I$132,3,0)+IF(AK133=$G132+$H132,1,0)+IF(AK134=$I$134,3,0)+IF(AK135=$G134+$H134,1,0)+IF(AK136=$I$136,3,0)+IF(AK137=$G136+$H136,1,0)+IF(AK138=$I$138,3,0)+IF(AK139=$G138+$H138,1,0)+IF(AK140=$I$140,3,0)+IF(AK141=$G140+$H140,1,0)+IF(AK142=$I$142,3,0)+IF(AK143=$G142+$H142,1,0)+IF(AK144=$I$144,3,0)+IF(AK145=$G144+$H144,1,0)+IF(AK146=$I$146,3,0)+IF(AK147=$G146+$H146,1,0)+IF(AK148=$I$148,3,0)+IF(AK149=$G148+$H148,1,0)+IF(AK150=$I$150,3,0)+IF(AK151=$G150+$H150,1,0))</f>
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AL5" s="75">
         <f>SUM(IF(AL80=$I$80,3,0)+IF(AL81=$G80+$H80,1,0)+IF(AL82=$I$82,3,0)+IF(AL83=$G82+$H82,1,0)+IF(AL84=$I$84,3,0)+IF(AL85=$G84+$H84,1,0)+IF(AL86=$I$86,3,0)+IF(AL87=$G86+$H86,1,0)+IF(AL88=$I$88,3,0)+IF(AL89=$G88+$H88,1,0)+IF(AL90=$I$90,3,0)+IF(AL91=$G90+$H90,1,0)+IF(AL92=$I$92,3,0)+IF(AL93=$G92+$H92,1,0)+IF(AL94=$I$94,3,0)+IF(AL95=$G94+$H94,1,0)+IF(AL96=$I$96,3,0)+IF(AL97=$G96+$H96,1,0)+IF(AL98=$I$98,3,0)+IF(AL99=$G98+$H98,1,0)+IF(AL100=$I$100,3,0)+IF(AL101=$G100+$H100,1,0)+IF(AL102=$I$102,3,0)+IF(AL103=$G102+$H102,1,0)+IF(AL104=$I$104,3,0)+IF(AL105=$G104+$H104,1,0)+IF(AL106=$I$106,3,0)+IF(AL107=$G106+$H106,1,0)+IF(AL108=$I$108,3,0)+IF(AL109=$G108+$H108,1,0)+IF(AL110=$I$110,3,0)+IF(AL111=$G110+$H110,1,0)+IF(AL112=$I$112,3,0)+IF(AL113=$G112+$H112,1,0)+IF(AL114=$I$114,3,0)+IF(AL115=$G114+$H114,1,0)+IF(AL116=$I$116,3,0)+IF(AL117=$G116+$H116,1,0)+IF(AL118=$I$118,3,0)+IF(AL119=$G118+$H118,1,0)+IF(AL120=$I$120,3,0)+IF(AL121=$G120+$H120,1,0)+IF(AL122=$I$122,3,0)+IF(AL123=$G122+$H122,1,0)+IF(AL124=$I$124,3,0)+IF(AL125=$G124+$H124,1,0)+IF(AL126=$I$126,3,0)+IF(AL127=$G126+$H126,1,0)+IF(AL128=$I$128,3,0)+IF(AL129=$G128+$H128,1,0)+IF(AL130=$I$130,3,0)+IF(AL131=$G130+$H130,1,0)+IF(AL132=$I$132,3,0)+IF(AL133=$G132+$H132,1,0)+IF(AL134=$I$134,3,0)+IF(AL135=$G134+$H134,1,0)+IF(AL136=$I$136,3,0)+IF(AL137=$G136+$H136,1,0)+IF(AL138=$I$138,3,0)+IF(AL139=$G138+$H138,1,0)+IF(AL140=$I$140,3,0)+IF(AL141=$G140+$H140,1,0)+IF(AL142=$I$142,3,0)+IF(AL143=$G142+$H142,1,0)+IF(AL144=$I$144,3,0)+IF(AL145=$G144+$H144,1,0)+IF(AL146=$I$146,3,0)+IF(AL147=$G146+$H146,1,0)+IF(AL148=$I$148,3,0)+IF(AL149=$G148+$H148,1,0)+IF(AL150=$I$150,3,0)+IF(AL151=$G150+$H150,1,0))</f>
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM5" s="75">
         <f>SUM(IF(AM80=$I$80,3,0)+IF(AM81=$G80+$H80,1,0)+IF(AM82=$I$82,3,0)+IF(AM83=$G82+$H82,1,0)+IF(AM84=$I$84,3,0)+IF(AM85=$G84+$H84,1,0)+IF(AM86=$I$86,3,0)+IF(AM87=$G86+$H86,1,0)+IF(AM88=$I$88,3,0)+IF(AM89=$G88+$H88,1,0)+IF(AM90=$I$90,3,0)+IF(AM91=$G90+$H90,1,0)+IF(AM92=$I$92,3,0)+IF(AM93=$G92+$H92,1,0)+IF(AM94=$I$94,3,0)+IF(AM95=$G94+$H94,1,0)+IF(AM96=$I$96,3,0)+IF(AM97=$G96+$H96,1,0)+IF(AM98=$I$98,3,0)+IF(AM99=$G98+$H98,1,0)+IF(AM100=$I$100,3,0)+IF(AM101=$G100+$H100,1,0)+IF(AM102=$I$102,3,0)+IF(AM103=$G102+$H102,1,0)+IF(AM104=$I$104,3,0)+IF(AM105=$G104+$H104,1,0)+IF(AM106=$I$106,3,0)+IF(AM107=$G106+$H106,1,0)+IF(AM108=$I$108,3,0)+IF(AM109=$G108+$H108,1,0)+IF(AM110=$I$110,3,0)+IF(AM111=$G110+$H110,1,0)+IF(AM112=$I$112,3,0)+IF(AM113=$G112+$H112,1,0)+IF(AM114=$I$114,3,0)+IF(AM115=$G114+$H114,1,0)+IF(AM116=$I$116,3,0)+IF(AM117=$G116+$H116,1,0)+IF(AM118=$I$118,3,0)+IF(AM119=$G118+$H118,1,0)+IF(AM120=$I$120,3,0)+IF(AM121=$G120+$H120,1,0)+IF(AM122=$I$122,3,0)+IF(AM123=$G122+$H122,1,0)+IF(AM124=$I$124,3,0)+IF(AM125=$G124+$H124,1,0)+IF(AM126=$I$126,3,0)+IF(AM127=$G126+$H126,1,0)+IF(AM128=$I$128,3,0)+IF(AM129=$G128+$H128,1,0)+IF(AM130=$I$130,3,0)+IF(AM131=$G130+$H130,1,0)+IF(AM132=$I$132,3,0)+IF(AM133=$G132+$H132,1,0)+IF(AM134=$I$134,3,0)+IF(AM135=$G134+$H134,1,0)+IF(AM136=$I$136,3,0)+IF(AM137=$G136+$H136,1,0)+IF(AM138=$I$138,3,0)+IF(AM139=$G138+$H138,1,0)+IF(AM140=$I$140,3,0)+IF(AM141=$G140+$H140,1,0)+IF(AM142=$I$142,3,0)+IF(AM143=$G142+$H142,1,0)+IF(AM144=$I$144,3,0)+IF(AM145=$G144+$H144,1,0)+IF(AM146=$I$146,3,0)+IF(AM147=$G146+$H146,1,0)+IF(AM148=$I$148,3,0)+IF(AM149=$G148+$H148,1,0)+IF(AM150=$I$150,3,0)+IF(AM151=$G150+$H150,1,0))</f>
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AN5" s="75">
         <f>SUM(IF(AN80=$I$80,3,0)+IF(AN81=$G80+$H80,1,0)+IF(AN82=$I$82,3,0)+IF(AN83=$G82+$H82,1,0)+IF(AN84=$I$84,3,0)+IF(AN85=$G84+$H84,1,0)+IF(AN86=$I$86,3,0)+IF(AN87=$G86+$H86,1,0)+IF(AN88=$I$88,3,0)+IF(AN89=$G88+$H88,1,0)+IF(AN90=$I$90,3,0)+IF(AN91=$G90+$H90,1,0)+IF(AN92=$I$92,3,0)+IF(AN93=$G92+$H92,1,0)+IF(AN94=$I$94,3,0)+IF(AN95=$G94+$H94,1,0)+IF(AN96=$I$96,3,0)+IF(AN97=$G96+$H96,1,0)+IF(AN98=$I$98,3,0)+IF(AN99=$G98+$H98,1,0)+IF(AN100=$I$100,3,0)+IF(AN101=$G100+$H100,1,0)+IF(AN102=$I$102,3,0)+IF(AN103=$G102+$H102,1,0)+IF(AN104=$I$104,3,0)+IF(AN105=$G104+$H104,1,0)+IF(AN106=$I$106,3,0)+IF(AN107=$G106+$H106,1,0)+IF(AN108=$I$108,3,0)+IF(AN109=$G108+$H108,1,0)+IF(AN110=$I$110,3,0)+IF(AN111=$G110+$H110,1,0)+IF(AN112=$I$112,3,0)+IF(AN113=$G112+$H112,1,0)+IF(AN114=$I$114,3,0)+IF(AN115=$G114+$H114,1,0)+IF(AN116=$I$116,3,0)+IF(AN117=$G116+$H116,1,0)+IF(AN118=$I$118,3,0)+IF(AN119=$G118+$H118,1,0)+IF(AN120=$I$120,3,0)+IF(AN121=$G120+$H120,1,0)+IF(AN122=$I$122,3,0)+IF(AN123=$G122+$H122,1,0)+IF(AN124=$I$124,3,0)+IF(AN125=$G124+$H124,1,0)+IF(AN126=$I$126,3,0)+IF(AN127=$G126+$H126,1,0)+IF(AN128=$I$128,3,0)+IF(AN129=$G128+$H128,1,0)+IF(AN130=$I$130,3,0)+IF(AN131=$G130+$H130,1,0)+IF(AN132=$I$132,3,0)+IF(AN133=$G132+$H132,1,0)+IF(AN134=$I$134,3,0)+IF(AN135=$G134+$H134,1,0)+IF(AN136=$I$136,3,0)+IF(AN137=$G136+$H136,1,0)+IF(AN138=$I$138,3,0)+IF(AN139=$G138+$H138,1,0)+IF(AN140=$I$140,3,0)+IF(AN141=$G140+$H140,1,0)+IF(AN142=$I$142,3,0)+IF(AN143=$G142+$H142,1,0)+IF(AN144=$I$144,3,0)+IF(AN145=$G144+$H144,1,0)+IF(AN146=$I$146,3,0)+IF(AN147=$G146+$H146,1,0)+IF(AN148=$I$148,3,0)+IF(AN149=$G148+$H148,1,0)+IF(AN150=$I$150,3,0)+IF(AN151=$G150+$H150,1,0))</f>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AO5" s="75">
         <f>SUM(IF(AO80=$I$80,3,0)+IF(AO81=$G80+$H80,1,0)+IF(AO82=$I$82,3,0)+IF(AO83=$G82+$H82,1,0)+IF(AO84=$I$84,3,0)+IF(AO85=$G84+$H84,1,0)+IF(AO86=$I$86,3,0)+IF(AO87=$G86+$H86,1,0)+IF(AO88=$I$88,3,0)+IF(AO89=$G88+$H88,1,0)+IF(AO90=$I$90,3,0)+IF(AO91=$G90+$H90,1,0)+IF(AO92=$I$92,3,0)+IF(AO93=$G92+$H92,1,0)+IF(AO94=$I$94,3,0)+IF(AO95=$G94+$H94,1,0)+IF(AO96=$I$96,3,0)+IF(AO97=$G96+$H96,1,0)+IF(AO98=$I$98,3,0)+IF(AO99=$G98+$H98,1,0)+IF(AO100=$I$100,3,0)+IF(AO101=$G100+$H100,1,0)+IF(AO102=$I$102,3,0)+IF(AO103=$G102+$H102,1,0)+IF(AO104=$I$104,3,0)+IF(AO105=$G104+$H104,1,0)+IF(AO106=$I$106,3,0)+IF(AO107=$G106+$H106,1,0)+IF(AO108=$I$108,3,0)+IF(AO109=$G108+$H108,1,0)+IF(AO110=$I$110,3,0)+IF(AO111=$G110+$H110,1,0)+IF(AO112=$I$112,3,0)+IF(AO113=$G112+$H112,1,0)+IF(AO114=$I$114,3,0)+IF(AO115=$G114+$H114,1,0)+IF(AO116=$I$116,3,0)+IF(AO117=$G116+$H116,1,0)+IF(AO118=$I$118,3,0)+IF(AO119=$G118+$H118,1,0)+IF(AO120=$I$120,3,0)+IF(AO121=$G120+$H120,1,0)+IF(AO122=$I$122,3,0)+IF(AO123=$G122+$H122,1,0)+IF(AO124=$I$124,3,0)+IF(AO125=$G124+$H124,1,0)+IF(AO126=$I$126,3,0)+IF(AO127=$G126+$H126,1,0)+IF(AO128=$I$128,3,0)+IF(AO129=$G128+$H128,1,0)+IF(AO130=$I$130,3,0)+IF(AO131=$G130+$H130,1,0)+IF(AO132=$I$132,3,0)+IF(AO133=$G132+$H132,1,0)+IF(AO134=$I$134,3,0)+IF(AO135=$G134+$H134,1,0)+IF(AO136=$I$136,3,0)+IF(AO137=$G136+$H136,1,0)+IF(AO138=$I$138,3,0)+IF(AO139=$G138+$H138,1,0)+IF(AO140=$I$140,3,0)+IF(AO141=$G140+$H140,1,0)+IF(AO142=$I$142,3,0)+IF(AO143=$G142+$H142,1,0)+IF(AO144=$I$144,3,0)+IF(AO145=$G144+$H144,1,0)+IF(AO146=$I$146,3,0)+IF(AO147=$G146+$H146,1,0)+IF(AO148=$I$148,3,0)+IF(AO149=$G148+$H148,1,0)+IF(AO150=$I$150,3,0)+IF(AO151=$G150+$H150,1,0))</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="AP5" s="75">
         <f>SUM(IF(AP80=$I$80,3,0)+IF(AP81=$G80+$H80,1,0)+IF(AP82=$I$82,3,0)+IF(AP83=$G82+$H82,1,0)+IF(AP84=$I$84,3,0)+IF(AP85=$G84+$H84,1,0)+IF(AP86=$I$86,3,0)+IF(AP87=$G86+$H86,1,0)+IF(AP88=$I$88,3,0)+IF(AP89=$G88+$H88,1,0)+IF(AP90=$I$90,3,0)+IF(AP91=$G90+$H90,1,0)+IF(AP92=$I$92,3,0)+IF(AP93=$G92+$H92,1,0)+IF(AP94=$I$94,3,0)+IF(AP95=$G94+$H94,1,0)+IF(AP96=$I$96,3,0)+IF(AP97=$G96+$H96,1,0)+IF(AP98=$I$98,3,0)+IF(AP99=$G98+$H98,1,0)+IF(AP100=$I$100,3,0)+IF(AP101=$G100+$H100,1,0)+IF(AP102=$I$102,3,0)+IF(AP103=$G102+$H102,1,0)+IF(AP104=$I$104,3,0)+IF(AP105=$G104+$H104,1,0)+IF(AP106=$I$106,3,0)+IF(AP107=$G106+$H106,1,0)+IF(AP108=$I$108,3,0)+IF(AP109=$G108+$H108,1,0)+IF(AP110=$I$110,3,0)+IF(AP111=$G110+$H110,1,0)+IF(AP112=$I$112,3,0)+IF(AP113=$G112+$H112,1,0)+IF(AP114=$I$114,3,0)+IF(AP115=$G114+$H114,1,0)+IF(AP116=$I$116,3,0)+IF(AP117=$G116+$H116,1,0)+IF(AP118=$I$118,3,0)+IF(AP119=$G118+$H118,1,0)+IF(AP120=$I$120,3,0)+IF(AP121=$G120+$H120,1,0)+IF(AP122=$I$122,3,0)+IF(AP123=$G122+$H122,1,0)+IF(AP124=$I$124,3,0)+IF(AP125=$G124+$H124,1,0)+IF(AP126=$I$126,3,0)+IF(AP127=$G126+$H126,1,0)+IF(AP128=$I$128,3,0)+IF(AP129=$G128+$H128,1,0)+IF(AP130=$I$130,3,0)+IF(AP131=$G130+$H130,1,0)+IF(AP132=$I$132,3,0)+IF(AP133=$G132+$H132,1,0)+IF(AP134=$I$134,3,0)+IF(AP135=$G134+$H134,1,0)+IF(AP136=$I$136,3,0)+IF(AP137=$G136+$H136,1,0)+IF(AP138=$I$138,3,0)+IF(AP139=$G138+$H138,1,0)+IF(AP140=$I$140,3,0)+IF(AP141=$G140+$H140,1,0)+IF(AP142=$I$142,3,0)+IF(AP143=$G142+$H142,1,0)+IF(AP144=$I$144,3,0)+IF(AP145=$G144+$H144,1,0)+IF(AP146=$I$146,3,0)+IF(AP147=$G146+$H146,1,0)+IF(AP148=$I$148,3,0)+IF(AP149=$G148+$H148,1,0)+IF(AP150=$I$150,3,0)+IF(AP151=$G150+$H150,1,0))</f>
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="AQ5" s="75">
         <f>SUM(IF(AQ80=$I$80,3,0)+IF(AQ81=$G80+$H80,1,0)+IF(AQ82=$I$82,3,0)+IF(AQ83=$G82+$H82,1,0)+IF(AQ84=$I$84,3,0)+IF(AQ85=$G84+$H84,1,0)+IF(AQ86=$I$86,3,0)+IF(AQ87=$G86+$H86,1,0)+IF(AQ88=$I$88,3,0)+IF(AQ89=$G88+$H88,1,0)+IF(AQ90=$I$90,3,0)+IF(AQ91=$G90+$H90,1,0)+IF(AQ92=$I$92,3,0)+IF(AQ93=$G92+$H92,1,0)+IF(AQ94=$I$94,3,0)+IF(AQ95=$G94+$H94,1,0)+IF(AQ96=$I$96,3,0)+IF(AQ97=$G96+$H96,1,0)+IF(AQ98=$I$98,3,0)+IF(AQ99=$G98+$H98,1,0)+IF(AQ100=$I$100,3,0)+IF(AQ101=$G100+$H100,1,0)+IF(AQ102=$I$102,3,0)+IF(AQ103=$G102+$H102,1,0)+IF(AQ104=$I$104,3,0)+IF(AQ105=$G104+$H104,1,0)+IF(AQ106=$I$106,3,0)+IF(AQ107=$G106+$H106,1,0)+IF(AQ108=$I$108,3,0)+IF(AQ109=$G108+$H108,1,0)+IF(AQ110=$I$110,3,0)+IF(AQ111=$G110+$H110,1,0)+IF(AQ112=$I$112,3,0)+IF(AQ113=$G112+$H112,1,0)+IF(AQ114=$I$114,3,0)+IF(AQ115=$G114+$H114,1,0)+IF(AQ116=$I$116,3,0)+IF(AQ117=$G116+$H116,1,0)+IF(AQ118=$I$118,3,0)+IF(AQ119=$G118+$H118,1,0)+IF(AQ120=$I$120,3,0)+IF(AQ121=$G120+$H120,1,0)+IF(AQ122=$I$122,3,0)+IF(AQ123=$G122+$H122,1,0)+IF(AQ124=$I$124,3,0)+IF(AQ125=$G124+$H124,1,0)+IF(AQ126=$I$126,3,0)+IF(AQ127=$G126+$H126,1,0)+IF(AQ128=$I$128,3,0)+IF(AQ129=$G128+$H128,1,0)+IF(AQ130=$I$130,3,0)+IF(AQ131=$G130+$H130,1,0)+IF(AQ132=$I$132,3,0)+IF(AQ133=$G132+$H132,1,0)+IF(AQ134=$I$134,3,0)+IF(AQ135=$G134+$H134,1,0)+IF(AQ136=$I$136,3,0)+IF(AQ137=$G136+$H136,1,0)+IF(AQ138=$I$138,3,0)+IF(AQ139=$G138+$H138,1,0)+IF(AQ140=$I$140,3,0)+IF(AQ141=$G140+$H140,1,0)+IF(AQ142=$I$142,3,0)+IF(AQ143=$G142+$H142,1,0)+IF(AQ144=$I$144,3,0)+IF(AQ145=$G144+$H144,1,0)+IF(AQ146=$I$146,3,0)+IF(AQ147=$G146+$H146,1,0)+IF(AQ148=$I$148,3,0)+IF(AQ149=$G148+$H148,1,0)+IF(AQ150=$I$150,3,0)+IF(AQ151=$G150+$H150,1,0))</f>
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AR5" s="75">
         <f>SUM(IF(AR80=$I$80,3,0)+IF(AR81=$G80+$H80,1,0)+IF(AR82=$I$82,3,0)+IF(AR83=$G82+$H82,1,0)+IF(AR84=$I$84,3,0)+IF(AR85=$G84+$H84,1,0)+IF(AR86=$I$86,3,0)+IF(AR87=$G86+$H86,1,0)+IF(AR88=$I$88,3,0)+IF(AR89=$G88+$H88,1,0)+IF(AR90=$I$90,3,0)+IF(AR91=$G90+$H90,1,0)+IF(AR92=$I$92,3,0)+IF(AR93=$G92+$H92,1,0)+IF(AR94=$I$94,3,0)+IF(AR95=$G94+$H94,1,0)+IF(AR96=$I$96,3,0)+IF(AR97=$G96+$H96,1,0)+IF(AR98=$I$98,3,0)+IF(AR99=$G98+$H98,1,0)+IF(AR100=$I$100,3,0)+IF(AR101=$G100+$H100,1,0)+IF(AR102=$I$102,3,0)+IF(AR103=$G102+$H102,1,0)+IF(AR104=$I$104,3,0)+IF(AR105=$G104+$H104,1,0)+IF(AR106=$I$106,3,0)+IF(AR107=$G106+$H106,1,0)+IF(AR108=$I$108,3,0)+IF(AR109=$G108+$H108,1,0)+IF(AR110=$I$110,3,0)+IF(AR111=$G110+$H110,1,0)+IF(AR112=$I$112,3,0)+IF(AR113=$G112+$H112,1,0)+IF(AR114=$I$114,3,0)+IF(AR115=$G114+$H114,1,0)+IF(AR116=$I$116,3,0)+IF(AR117=$G116+$H116,1,0)+IF(AR118=$I$118,3,0)+IF(AR119=$G118+$H118,1,0)+IF(AR120=$I$120,3,0)+IF(AR121=$G120+$H120,1,0)+IF(AR122=$I$122,3,0)+IF(AR123=$G122+$H122,1,0)+IF(AR124=$I$124,3,0)+IF(AR125=$G124+$H124,1,0)+IF(AR126=$I$126,3,0)+IF(AR127=$G126+$H126,1,0)+IF(AR128=$I$128,3,0)+IF(AR129=$G128+$H128,1,0)+IF(AR130=$I$130,3,0)+IF(AR131=$G130+$H130,1,0)+IF(AR132=$I$132,3,0)+IF(AR133=$G132+$H132,1,0)+IF(AR134=$I$134,3,0)+IF(AR135=$G134+$H134,1,0)+IF(AR136=$I$136,3,0)+IF(AR137=$G136+$H136,1,0)+IF(AR138=$I$138,3,0)+IF(AR139=$G138+$H138,1,0)+IF(AR140=$I$140,3,0)+IF(AR141=$G140+$H140,1,0)+IF(AR142=$I$142,3,0)+IF(AR143=$G142+$H142,1,0)+IF(AR144=$I$144,3,0)+IF(AR145=$G144+$H144,1,0)+IF(AR146=$I$146,3,0)+IF(AR147=$G146+$H146,1,0)+IF(AR148=$I$148,3,0)+IF(AR149=$G148+$H148,1,0)+IF(AR150=$I$150,3,0)+IF(AR151=$G150+$H150,1,0))</f>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AS5" s="75">
         <f>SUM(IF(AS80=$I$80,3,0)+IF(AS81=$G80+$H80,1,0)+IF(AS82=$I$82,3,0)+IF(AS83=$G82+$H82,1,0)+IF(AS84=$I$84,3,0)+IF(AS85=$G84+$H84,1,0)+IF(AS86=$I$86,3,0)+IF(AS87=$G86+$H86,1,0)+IF(AS88=$I$88,3,0)+IF(AS89=$G88+$H88,1,0)+IF(AS90=$I$90,3,0)+IF(AS91=$G90+$H90,1,0)+IF(AS92=$I$92,3,0)+IF(AS93=$G92+$H92,1,0)+IF(AS94=$I$94,3,0)+IF(AS95=$G94+$H94,1,0)+IF(AS96=$I$96,3,0)+IF(AS97=$G96+$H96,1,0)+IF(AS98=$I$98,3,0)+IF(AS99=$G98+$H98,1,0)+IF(AS100=$I$100,3,0)+IF(AS101=$G100+$H100,1,0)+IF(AS102=$I$102,3,0)+IF(AS103=$G102+$H102,1,0)+IF(AS104=$I$104,3,0)+IF(AS105=$G104+$H104,1,0)+IF(AS106=$I$106,3,0)+IF(AS107=$G106+$H106,1,0)+IF(AS108=$I$108,3,0)+IF(AS109=$G108+$H108,1,0)+IF(AS110=$I$110,3,0)+IF(AS111=$G110+$H110,1,0)+IF(AS112=$I$112,3,0)+IF(AS113=$G112+$H112,1,0)+IF(AS114=$I$114,3,0)+IF(AS115=$G114+$H114,1,0)+IF(AS116=$I$116,3,0)+IF(AS117=$G116+$H116,1,0)+IF(AS118=$I$118,3,0)+IF(AS119=$G118+$H118,1,0)+IF(AS120=$I$120,3,0)+IF(AS121=$G120+$H120,1,0)+IF(AS122=$I$122,3,0)+IF(AS123=$G122+$H122,1,0)+IF(AS124=$I$124,3,0)+IF(AS125=$G124+$H124,1,0)+IF(AS126=$I$126,3,0)+IF(AS127=$G126+$H126,1,0)+IF(AS128=$I$128,3,0)+IF(AS129=$G128+$H128,1,0)+IF(AS130=$I$130,3,0)+IF(AS131=$G130+$H130,1,0)+IF(AS132=$I$132,3,0)+IF(AS133=$G132+$H132,1,0)+IF(AS134=$I$134,3,0)+IF(AS135=$G134+$H134,1,0)+IF(AS136=$I$136,3,0)+IF(AS137=$G136+$H136,1,0)+IF(AS138=$I$138,3,0)+IF(AS139=$G138+$H138,1,0)+IF(AS140=$I$140,3,0)+IF(AS141=$G140+$H140,1,0)+IF(AS142=$I$142,3,0)+IF(AS143=$G142+$H142,1,0)+IF(AS144=$I$144,3,0)+IF(AS145=$G144+$H144,1,0)+IF(AS146=$I$146,3,0)+IF(AS147=$G146+$H146,1,0)+IF(AS148=$I$148,3,0)+IF(AS149=$G148+$H148,1,0)+IF(AS150=$I$150,3,0)+IF(AS151=$G150+$H150,1,0))</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AT5" s="79">
         <f>SUM(IF(AT80=$I$80,3,0)+IF(AT81=$G80+$H80,1,0)+IF(AT82=$I$82,3,0)+IF(AT83=$G82+$H82,1,0)+IF(AT84=$I$84,3,0)+IF(AT85=$G84+$H84,1,0)+IF(AT86=$I$86,3,0)+IF(AT87=$G86+$H86,1,0)+IF(AT88=$I$88,3,0)+IF(AT89=$G88+$H88,1,0)+IF(AT90=$I$90,3,0)+IF(AT91=$G90+$H90,1,0)+IF(AT92=$I$92,3,0)+IF(AT93=$G92+$H92,1,0)+IF(AT94=$I$94,3,0)+IF(AT95=$G94+$H94,1,0)+IF(AT96=$I$96,3,0)+IF(AT97=$G96+$H96,1,0)+IF(AT98=$I$98,3,0)+IF(AT99=$G98+$H98,1,0)+IF(AT100=$I$100,3,0)+IF(AT101=$G100+$H100,1,0)+IF(AT102=$I$102,3,0)+IF(AT103=$G102+$H102,1,0)+IF(AT104=$I$104,3,0)+IF(AT105=$G104+$H104,1,0)+IF(AT106=$I$106,3,0)+IF(AT107=$G106+$H106,1,0)+IF(AT108=$I$108,3,0)+IF(AT109=$G108+$H108,1,0)+IF(AT110=$I$110,3,0)+IF(AT111=$G110+$H110,1,0)+IF(AT112=$I$112,3,0)+IF(AT113=$G112+$H112,1,0)+IF(AT114=$I$114,3,0)+IF(AT115=$G114+$H114,1,0)+IF(AT116=$I$116,3,0)+IF(AT117=$G116+$H116,1,0)+IF(AT118=$I$118,3,0)+IF(AT119=$G118+$H118,1,0)+IF(AT120=$I$120,3,0)+IF(AT121=$G120+$H120,1,0)+IF(AT122=$I$122,3,0)+IF(AT123=$G122+$H122,1,0)+IF(AT124=$I$124,3,0)+IF(AT125=$G124+$H124,1,0)+IF(AT126=$I$126,3,0)+IF(AT127=$G126+$H126,1,0)+IF(AT128=$I$128,3,0)+IF(AT129=$G128+$H128,1,0)+IF(AT130=$I$130,3,0)+IF(AT131=$G130+$H130,1,0)+IF(AT132=$I$132,3,0)+IF(AT133=$G132+$H132,1,0)+IF(AT134=$I$134,3,0)+IF(AT135=$G134+$H134,1,0)+IF(AT136=$I$136,3,0)+IF(AT137=$G136+$H136,1,0)+IF(AT138=$I$138,3,0)+IF(AT139=$G138+$H138,1,0)+IF(AT140=$I$140,3,0)+IF(AT141=$G140+$H140,1,0)+IF(AT142=$I$142,3,0)+IF(AT143=$G142+$H142,1,0)+IF(AT144=$I$144,3,0)+IF(AT145=$G144+$H144,1,0)+IF(AT146=$I$146,3,0)+IF(AT147=$G146+$H146,1,0)+IF(AT148=$I$148,3,0)+IF(AT149=$G148+$H148,1,0)+IF(AT150=$I$150,3,0)+IF(AT151=$G150+$H150,1,0))</f>
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:54" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3403,11 +3403,11 @@
       </c>
       <c r="AF6" s="75">
         <f>SUM(AND($G$8="",$H$8="",AF9=0)+AND($G$10="",$H$10="",AF11=0)+AND($G$12="",$H$12="",AF13=0)+AND($G$14="",$H$14="",AF15=0)+AND($G$16="",$H$16="",AF17=0)+AND($G$18="",$H$18="",AF19=0)+AND($G$20="",$H$20="",AF21=0)+AND($G$22="",$H$22="",AF23=0)+AND($G$24="",$H$24="",AF25=0)+AND($G$26="",$H$26="",AF27=0)+AND($G$28="",$H$28="",AF29=0)+AND($G$30="",$H$30="",AF31=0)+AND($G$32="",$H$32="",AF33=0)+AND($G$34="",$H$34="",AF35=0)+AND($G$36="",$H$36="",AF37=0)+AND($G$38="",$H$38="",AF39=0)+AND($G$40="",$H$40="",AF41=0)+AND($G$42="",$H$42="",AF43=0)+AND($G$44="",$H$44="",AF45=0)+AND($G$46="",$H$46="",AF47=0)+AND($G$48="",$H$48="",AF49=0)+AND($G$50="",$H$50="",AF51=0)+AND($G$52="",$H$52="",AF53=0)+AND($G$54="",$H$54="",AF55=0)+AND($G$56="",$H$56="",AF57=0)+AND($G$58="",$H$58="",AF59=0)+AND($G$60="",$H$60="",AF61=0)+AND($G$62="",$H$62="",AF63=0)+AND($G$64="",$H$64="",AF65=0)+AND($G$66="",$H$66="",AF67=0)+AND($G$68="",$H$68="",AF69=0)+AND($G$70="",$H$70="",AF71=0)+AND($G$72="",$H$72="",AF73=0)+AND($G$74="",$H$74="",AF75=0)+AND($G$76="",$H$76="",AF77=0)+AND($G$78="",$H$78="",AF79=0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="75">
         <f>SUM(AND($G$8="",$H$8="",AG9=0)+AND($G$10="",$H$10="",AG11=0)+AND($G$12="",$H$12="",AG13=0)+AND($G$14="",$H$14="",AG15=0)+AND($G$16="",$H$16="",AG17=0)+AND($G$18="",$H$18="",AG19=0)+AND($G$20="",$H$20="",AG21=0)+AND($G$22="",$H$22="",AG23=0)+AND($G$24="",$H$24="",AG25=0)+AND($G$26="",$H$26="",AG27=0)+AND($G$28="",$H$28="",AG29=0)+AND($G$30="",$H$30="",AG31=0)+AND($G$32="",$H$32="",AG33=0)+AND($G$34="",$H$34="",AG35=0)+AND($G$36="",$H$36="",AG37=0)+AND($G$38="",$H$38="",AG39=0)+AND($G$40="",$H$40="",AG41=0)+AND($G$42="",$H$42="",AG43=0)+AND($G$44="",$H$44="",AG45=0)+AND($G$46="",$H$46="",AG47=0)+AND($G$48="",$H$48="",AG49=0)+AND($G$50="",$H$50="",AG51=0)+AND($G$52="",$H$52="",AG53=0)+AND($G$54="",$H$54="",AG55=0)+AND($G$56="",$H$56="",AG57=0)+AND($G$58="",$H$58="",AG59=0)+AND($G$60="",$H$60="",AG61=0)+AND($G$62="",$H$62="",AG63=0)+AND($G$64="",$H$64="",AG65=0)+AND($G$66="",$H$66="",AG67=0)+AND($G$68="",$H$68="",AG69=0)+AND($G$70="",$H$70="",AG71=0)+AND($G$72="",$H$72="",AG73=0)+AND($G$74="",$H$74="",AG75=0)+AND($G$76="",$H$76="",AG77=0)+AND($G$78="",$H$78="",AG79=0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH6" s="75">
         <f>SUM(AND($G$8="",$H$8="",AH9=0)+AND($G$10="",$H$10="",AH11=0)+AND($G$12="",$H$12="",AH13=0)+AND($G$14="",$H$14="",AH15=0)+AND($G$16="",$H$16="",AH17=0)+AND($G$18="",$H$18="",AH19=0)+AND($G$20="",$H$20="",AH21=0)+AND($G$22="",$H$22="",AH23=0)+AND($G$24="",$H$24="",AH25=0)+AND($G$26="",$H$26="",AH27=0)+AND($G$28="",$H$28="",AH29=0)+AND($G$30="",$H$30="",AH31=0)+AND($G$32="",$H$32="",AH33=0)+AND($G$34="",$H$34="",AH35=0)+AND($G$36="",$H$36="",AH37=0)+AND($G$38="",$H$38="",AH39=0)+AND($G$40="",$H$40="",AH41=0)+AND($G$42="",$H$42="",AH43=0)+AND($G$44="",$H$44="",AH45=0)+AND($G$46="",$H$46="",AH47=0)+AND($G$48="",$H$48="",AH49=0)+AND($G$50="",$H$50="",AH51=0)+AND($G$52="",$H$52="",AH53=0)+AND($G$54="",$H$54="",AH55=0)+AND($G$56="",$H$56="",AH57=0)+AND($G$58="",$H$58="",AH59=0)+AND($G$60="",$H$60="",AH61=0)+AND($G$62="",$H$62="",AH63=0)+AND($G$64="",$H$64="",AH65=0)+AND($G$66="",$H$66="",AH67=0)+AND($G$68="",$H$68="",AH69=0)+AND($G$70="",$H$70="",AH71=0)+AND($G$72="",$H$72="",AH73=0)+AND($G$74="",$H$74="",AH75=0)+AND($G$76="",$H$76="",AH77=0)+AND($G$78="",$H$78="",AH79=0))</f>
@@ -3427,11 +3427,11 @@
       </c>
       <c r="AL6" s="75">
         <f>SUM(AND($G$8="",$H$8="",AL9=0)+AND($G$10="",$H$10="",AL11=0)+AND($G$12="",$H$12="",AL13=0)+AND($G$14="",$H$14="",AL15=0)+AND($G$16="",$H$16="",AL17=0)+AND($G$18="",$H$18="",AL19=0)+AND($G$20="",$H$20="",AL21=0)+AND($G$22="",$H$22="",AL23=0)+AND($G$24="",$H$24="",AL25=0)+AND($G$26="",$H$26="",AL27=0)+AND($G$28="",$H$28="",AL29=0)+AND($G$30="",$H$30="",AL31=0)+AND($G$32="",$H$32="",AL33=0)+AND($G$34="",$H$34="",AL35=0)+AND($G$36="",$H$36="",AL37=0)+AND($G$38="",$H$38="",AL39=0)+AND($G$40="",$H$40="",AL41=0)+AND($G$42="",$H$42="",AL43=0)+AND($G$44="",$H$44="",AL45=0)+AND($G$46="",$H$46="",AL47=0)+AND($G$48="",$H$48="",AL49=0)+AND($G$50="",$H$50="",AL51=0)+AND($G$52="",$H$52="",AL53=0)+AND($G$54="",$H$54="",AL55=0)+AND($G$56="",$H$56="",AL57=0)+AND($G$58="",$H$58="",AL59=0)+AND($G$60="",$H$60="",AL61=0)+AND($G$62="",$H$62="",AL63=0)+AND($G$64="",$H$64="",AL65=0)+AND($G$66="",$H$66="",AL67=0)+AND($G$68="",$H$68="",AL69=0)+AND($G$70="",$H$70="",AL71=0)+AND($G$72="",$H$72="",AL73=0)+AND($G$74="",$H$74="",AL75=0)+AND($G$76="",$H$76="",AL77=0)+AND($G$78="",$H$78="",AL79=0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM6" s="75">
         <f>SUM(AND($G$8="",$H$8="",AM9=0)+AND($G$10="",$H$10="",AM11=0)+AND($G$12="",$H$12="",AM13=0)+AND($G$14="",$H$14="",AM15=0)+AND($G$16="",$H$16="",AM17=0)+AND($G$18="",$H$18="",AM19=0)+AND($G$20="",$H$20="",AM21=0)+AND($G$22="",$H$22="",AM23=0)+AND($G$24="",$H$24="",AM25=0)+AND($G$26="",$H$26="",AM27=0)+AND($G$28="",$H$28="",AM29=0)+AND($G$30="",$H$30="",AM31=0)+AND($G$32="",$H$32="",AM33=0)+AND($G$34="",$H$34="",AM35=0)+AND($G$36="",$H$36="",AM37=0)+AND($G$38="",$H$38="",AM39=0)+AND($G$40="",$H$40="",AM41=0)+AND($G$42="",$H$42="",AM43=0)+AND($G$44="",$H$44="",AM45=0)+AND($G$46="",$H$46="",AM47=0)+AND($G$48="",$H$48="",AM49=0)+AND($G$50="",$H$50="",AM51=0)+AND($G$52="",$H$52="",AM53=0)+AND($G$54="",$H$54="",AM55=0)+AND($G$56="",$H$56="",AM57=0)+AND($G$58="",$H$58="",AM59=0)+AND($G$60="",$H$60="",AM61=0)+AND($G$62="",$H$62="",AM63=0)+AND($G$64="",$H$64="",AM65=0)+AND($G$66="",$H$66="",AM67=0)+AND($G$68="",$H$68="",AM69=0)+AND($G$70="",$H$70="",AM71=0)+AND($G$72="",$H$72="",AM73=0)+AND($G$74="",$H$74="",AM75=0)+AND($G$76="",$H$76="",AM77=0)+AND($G$78="",$H$78="",AM79=0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN6" s="75">
         <f>SUM(AND($G$8="",$H$8="",AN9=0)+AND($G$10="",$H$10="",AN11=0)+AND($G$12="",$H$12="",AN13=0)+AND($G$14="",$H$14="",AN15=0)+AND($G$16="",$H$16="",AN17=0)+AND($G$18="",$H$18="",AN19=0)+AND($G$20="",$H$20="",AN21=0)+AND($G$22="",$H$22="",AN23=0)+AND($G$24="",$H$24="",AN25=0)+AND($G$26="",$H$26="",AN27=0)+AND($G$28="",$H$28="",AN29=0)+AND($G$30="",$H$30="",AN31=0)+AND($G$32="",$H$32="",AN33=0)+AND($G$34="",$H$34="",AN35=0)+AND($G$36="",$H$36="",AN37=0)+AND($G$38="",$H$38="",AN39=0)+AND($G$40="",$H$40="",AN41=0)+AND($G$42="",$H$42="",AN43=0)+AND($G$44="",$H$44="",AN45=0)+AND($G$46="",$H$46="",AN47=0)+AND($G$48="",$H$48="",AN49=0)+AND($G$50="",$H$50="",AN51=0)+AND($G$52="",$H$52="",AN53=0)+AND($G$54="",$H$54="",AN55=0)+AND($G$56="",$H$56="",AN57=0)+AND($G$58="",$H$58="",AN59=0)+AND($G$60="",$H$60="",AN61=0)+AND($G$62="",$H$62="",AN63=0)+AND($G$64="",$H$64="",AN65=0)+AND($G$66="",$H$66="",AN67=0)+AND($G$68="",$H$68="",AN69=0)+AND($G$70="",$H$70="",AN71=0)+AND($G$72="",$H$72="",AN73=0)+AND($G$74="",$H$74="",AN75=0)+AND($G$76="",$H$76="",AN77=0)+AND($G$78="",$H$78="",AN79=0))</f>
@@ -3522,15 +3522,15 @@
       </c>
       <c r="V7" s="77">
         <f>SUM(AND($G$80="",$H$80="",V81=0)+AND($G$82="",$H$82="",V83=0)+AND($G$84="",$H$84="",V85=0)+AND($G$86="",$H$86="",V87=0)+AND($G$88="",$H$88="",V89=0)+AND($G$90="",$H$90="",V91=0)+AND($G$92="",$H$92="",V93=0)+AND($G$94="",$H$94="",V95=0)+AND($G$96="",$H$96="",V97=0)+AND($G$98="",$H$98="",V99=0)+AND($G$100="",$H$100="",V101=0)+AND($G$102="",$H$102="",V103=0)+AND($G$104="",$H$104="",V105=0)+AND($G$106="",$H$106="",V107=0)+AND($G$108="",$H$108="",V109=0)+AND($G$110="",$H$110="",V111=0)+AND($G$112="",$H$112="",V113=0)+AND($G$114="",$H$114="",V115=0)+AND($G$116="",$H$116="",V117=0)+AND($G$118="",$H$118="",V119=0)+AND($G$120="",$H$120="",V121=0)+AND($G$122="",$H$122="",V123=0)+AND($G$124="",$H$124="",V125=0)+AND($G$126="",$H$126="",V127=0)+AND($G$128="",$H$128="",V129=0)+AND($G$130="",$H$130="",V131=0)+AND($G$132="",$H$132="",V133=0)+AND($G$134="",$H$134="",V135=0)+AND($G$136="",$H$136="",V137=0)+AND($G$138="",$H$138="",V139=0)+AND($G$140="",$H$140="",V141=0)+AND($G$142="",$H$142="",V143=0)+AND($G$144="",$H$144="",V145=0)+AND($G$146="",$H$146="",V147=0)+AND($G$148="",$H$148="",V149=0)+AND($G$150="",$H$150="",V151=0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W7" s="77">
         <f>SUM(AND($G$80="",$H$80="",W81=0)+AND($G$82="",$H$82="",W83=0)+AND($G$84="",$H$84="",W85=0)+AND($G$86="",$H$86="",W87=0)+AND($G$88="",$H$88="",W89=0)+AND($G$90="",$H$90="",W91=0)+AND($G$92="",$H$92="",W93=0)+AND($G$94="",$H$94="",W95=0)+AND($G$96="",$H$96="",W97=0)+AND($G$98="",$H$98="",W99=0)+AND($G$100="",$H$100="",W101=0)+AND($G$102="",$H$102="",W103=0)+AND($G$104="",$H$104="",W105=0)+AND($G$106="",$H$106="",W107=0)+AND($G$108="",$H$108="",W109=0)+AND($G$110="",$H$110="",W111=0)+AND($G$112="",$H$112="",W113=0)+AND($G$114="",$H$114="",W115=0)+AND($G$116="",$H$116="",W117=0)+AND($G$118="",$H$118="",W119=0)+AND($G$120="",$H$120="",W121=0)+AND($G$122="",$H$122="",W123=0)+AND($G$124="",$H$124="",W125=0)+AND($G$126="",$H$126="",W127=0)+AND($G$128="",$H$128="",W129=0)+AND($G$130="",$H$130="",W131=0)+AND($G$132="",$H$132="",W133=0)+AND($G$134="",$H$134="",W135=0)+AND($G$136="",$H$136="",W137=0)+AND($G$138="",$H$138="",W139=0)+AND($G$140="",$H$140="",W141=0)+AND($G$142="",$H$142="",W143=0)+AND($G$144="",$H$144="",W145=0)+AND($G$146="",$H$146="",W147=0)+AND($G$148="",$H$148="",W149=0)+AND($G$150="",$H$150="",W151=0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" s="77">
         <f>SUM(AND($G$80="",$H$80="",X81=0)+AND($G$82="",$H$82="",X83=0)+AND($G$84="",$H$84="",X85=0)+AND($G$86="",$H$86="",X87=0)+AND($G$88="",$H$88="",X89=0)+AND($G$90="",$H$90="",X91=0)+AND($G$92="",$H$92="",X93=0)+AND($G$94="",$H$94="",X95=0)+AND($G$96="",$H$96="",X97=0)+AND($G$98="",$H$98="",X99=0)+AND($G$100="",$H$100="",X101=0)+AND($G$102="",$H$102="",X103=0)+AND($G$104="",$H$104="",X105=0)+AND($G$106="",$H$106="",X107=0)+AND($G$108="",$H$108="",X109=0)+AND($G$110="",$H$110="",X111=0)+AND($G$112="",$H$112="",X113=0)+AND($G$114="",$H$114="",X115=0)+AND($G$116="",$H$116="",X117=0)+AND($G$118="",$H$118="",X119=0)+AND($G$120="",$H$120="",X121=0)+AND($G$122="",$H$122="",X123=0)+AND($G$124="",$H$124="",X125=0)+AND($G$126="",$H$126="",X127=0)+AND($G$128="",$H$128="",X129=0)+AND($G$130="",$H$130="",X131=0)+AND($G$132="",$H$132="",X133=0)+AND($G$134="",$H$134="",X135=0)+AND($G$136="",$H$136="",X137=0)+AND($G$138="",$H$138="",X139=0)+AND($G$140="",$H$140="",X141=0)+AND($G$142="",$H$142="",X143=0)+AND($G$144="",$H$144="",X145=0)+AND($G$146="",$H$146="",X147=0)+AND($G$148="",$H$148="",X149=0)+AND($G$150="",$H$150="",X151=0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="77">
         <f>SUM(AND($G$80="",$H$80="",Y81=0)+AND($G$82="",$H$82="",Y83=0)+AND($G$84="",$H$84="",Y85=0)+AND($G$86="",$H$86="",Y87=0)+AND($G$88="",$H$88="",Y89=0)+AND($G$90="",$H$90="",Y91=0)+AND($G$92="",$H$92="",Y93=0)+AND($G$94="",$H$94="",Y95=0)+AND($G$96="",$H$96="",Y97=0)+AND($G$98="",$H$98="",Y99=0)+AND($G$100="",$H$100="",Y101=0)+AND($G$102="",$H$102="",Y103=0)+AND($G$104="",$H$104="",Y105=0)+AND($G$106="",$H$106="",Y107=0)+AND($G$108="",$H$108="",Y109=0)+AND($G$110="",$H$110="",Y111=0)+AND($G$112="",$H$112="",Y113=0)+AND($G$114="",$H$114="",Y115=0)+AND($G$116="",$H$116="",Y117=0)+AND($G$118="",$H$118="",Y119=0)+AND($G$120="",$H$120="",Y121=0)+AND($G$122="",$H$122="",Y123=0)+AND($G$124="",$H$124="",Y125=0)+AND($G$126="",$H$126="",Y127=0)+AND($G$128="",$H$128="",Y129=0)+AND($G$130="",$H$130="",Y131=0)+AND($G$132="",$H$132="",Y133=0)+AND($G$134="",$H$134="",Y135=0)+AND($G$136="",$H$136="",Y137=0)+AND($G$138="",$H$138="",Y139=0)+AND($G$140="",$H$140="",Y141=0)+AND($G$142="",$H$142="",Y143=0)+AND($G$144="",$H$144="",Y145=0)+AND($G$146="",$H$146="",Y147=0)+AND($G$148="",$H$148="",Y149=0)+AND($G$150="",$H$150="",Y151=0))</f>
@@ -3558,11 +3558,11 @@
       </c>
       <c r="AE7" s="77">
         <f>SUM(AND($G$80="",$H$80="",AE81=0)+AND($G$82="",$H$82="",AE83=0)+AND($G$84="",$H$84="",AE85=0)+AND($G$86="",$H$86="",AE87=0)+AND($G$88="",$H$88="",AE89=0)+AND($G$90="",$H$90="",AE91=0)+AND($G$92="",$H$92="",AE93=0)+AND($G$94="",$H$94="",AE95=0)+AND($G$96="",$H$96="",AE97=0)+AND($G$98="",$H$98="",AE99=0)+AND($G$100="",$H$100="",AE101=0)+AND($G$102="",$H$102="",AE103=0)+AND($G$104="",$H$104="",AE105=0)+AND($G$106="",$H$106="",AE107=0)+AND($G$108="",$H$108="",AE109=0)+AND($G$110="",$H$110="",AE111=0)+AND($G$112="",$H$112="",AE113=0)+AND($G$114="",$H$114="",AE115=0)+AND($G$116="",$H$116="",AE117=0)+AND($G$118="",$H$118="",AE119=0)+AND($G$120="",$H$120="",AE121=0)+AND($G$122="",$H$122="",AE123=0)+AND($G$124="",$H$124="",AE125=0)+AND($G$126="",$H$126="",AE127=0)+AND($G$128="",$H$128="",AE129=0)+AND($G$130="",$H$130="",AE131=0)+AND($G$132="",$H$132="",AE133=0)+AND($G$134="",$H$134="",AE135=0)+AND($G$136="",$H$136="",AE137=0)+AND($G$138="",$H$138="",AE139=0)+AND($G$140="",$H$140="",AE141=0)+AND($G$142="",$H$142="",AE143=0)+AND($G$144="",$H$144="",AE145=0)+AND($G$146="",$H$146="",AE147=0)+AND($G$148="",$H$148="",AE149=0)+AND($G$150="",$H$150="",AE151=0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" s="77">
         <f>SUM(AND($G$80="",$H$80="",AF81=0)+AND($G$82="",$H$82="",AF83=0)+AND($G$84="",$H$84="",AF85=0)+AND($G$86="",$H$86="",AF87=0)+AND($G$88="",$H$88="",AF89=0)+AND($G$90="",$H$90="",AF91=0)+AND($G$92="",$H$92="",AF93=0)+AND($G$94="",$H$94="",AF95=0)+AND($G$96="",$H$96="",AF97=0)+AND($G$98="",$H$98="",AF99=0)+AND($G$100="",$H$100="",AF101=0)+AND($G$102="",$H$102="",AF103=0)+AND($G$104="",$H$104="",AF105=0)+AND($G$106="",$H$106="",AF107=0)+AND($G$108="",$H$108="",AF109=0)+AND($G$110="",$H$110="",AF111=0)+AND($G$112="",$H$112="",AF113=0)+AND($G$114="",$H$114="",AF115=0)+AND($G$116="",$H$116="",AF117=0)+AND($G$118="",$H$118="",AF119=0)+AND($G$120="",$H$120="",AF121=0)+AND($G$122="",$H$122="",AF123=0)+AND($G$124="",$H$124="",AF125=0)+AND($G$126="",$H$126="",AF127=0)+AND($G$128="",$H$128="",AF129=0)+AND($G$130="",$H$130="",AF131=0)+AND($G$132="",$H$132="",AF133=0)+AND($G$134="",$H$134="",AF135=0)+AND($G$136="",$H$136="",AF137=0)+AND($G$138="",$H$138="",AF139=0)+AND($G$140="",$H$140="",AF141=0)+AND($G$142="",$H$142="",AF143=0)+AND($G$144="",$H$144="",AF145=0)+AND($G$146="",$H$146="",AF147=0)+AND($G$148="",$H$148="",AF149=0)+AND($G$150="",$H$150="",AF151=0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="77">
         <f>SUM(AND($G$80="",$H$80="",AG81=0)+AND($G$82="",$H$82="",AG83=0)+AND($G$84="",$H$84="",AG85=0)+AND($G$86="",$H$86="",AG87=0)+AND($G$88="",$H$88="",AG89=0)+AND($G$90="",$H$90="",AG91=0)+AND($G$92="",$H$92="",AG93=0)+AND($G$94="",$H$94="",AG95=0)+AND($G$96="",$H$96="",AG97=0)+AND($G$98="",$H$98="",AG99=0)+AND($G$100="",$H$100="",AG101=0)+AND($G$102="",$H$102="",AG103=0)+AND($G$104="",$H$104="",AG105=0)+AND($G$106="",$H$106="",AG107=0)+AND($G$108="",$H$108="",AG109=0)+AND($G$110="",$H$110="",AG111=0)+AND($G$112="",$H$112="",AG113=0)+AND($G$114="",$H$114="",AG115=0)+AND($G$116="",$H$116="",AG117=0)+AND($G$118="",$H$118="",AG119=0)+AND($G$120="",$H$120="",AG121=0)+AND($G$122="",$H$122="",AG123=0)+AND($G$124="",$H$124="",AG125=0)+AND($G$126="",$H$126="",AG127=0)+AND($G$128="",$H$128="",AG129=0)+AND($G$130="",$H$130="",AG131=0)+AND($G$132="",$H$132="",AG133=0)+AND($G$134="",$H$134="",AG135=0)+AND($G$136="",$H$136="",AG137=0)+AND($G$138="",$H$138="",AG139=0)+AND($G$140="",$H$140="",AG141=0)+AND($G$142="",$H$142="",AG143=0)+AND($G$144="",$H$144="",AG145=0)+AND($G$146="",$H$146="",AG147=0)+AND($G$148="",$H$148="",AG149=0)+AND($G$150="",$H$150="",AG151=0))</f>
@@ -3586,11 +3586,11 @@
       </c>
       <c r="AL7" s="77">
         <f>SUM(AND($G$80="",$H$80="",AL81=0)+AND($G$82="",$H$82="",AL83=0)+AND($G$84="",$H$84="",AL85=0)+AND($G$86="",$H$86="",AL87=0)+AND($G$88="",$H$88="",AL89=0)+AND($G$90="",$H$90="",AL91=0)+AND($G$92="",$H$92="",AL93=0)+AND($G$94="",$H$94="",AL95=0)+AND($G$96="",$H$96="",AL97=0)+AND($G$98="",$H$98="",AL99=0)+AND($G$100="",$H$100="",AL101=0)+AND($G$102="",$H$102="",AL103=0)+AND($G$104="",$H$104="",AL105=0)+AND($G$106="",$H$106="",AL107=0)+AND($G$108="",$H$108="",AL109=0)+AND($G$110="",$H$110="",AL111=0)+AND($G$112="",$H$112="",AL113=0)+AND($G$114="",$H$114="",AL115=0)+AND($G$116="",$H$116="",AL117=0)+AND($G$118="",$H$118="",AL119=0)+AND($G$120="",$H$120="",AL121=0)+AND($G$122="",$H$122="",AL123=0)+AND($G$124="",$H$124="",AL125=0)+AND($G$126="",$H$126="",AL127=0)+AND($G$128="",$H$128="",AL129=0)+AND($G$130="",$H$130="",AL131=0)+AND($G$132="",$H$132="",AL133=0)+AND($G$134="",$H$134="",AL135=0)+AND($G$136="",$H$136="",AL137=0)+AND($G$138="",$H$138="",AL139=0)+AND($G$140="",$H$140="",AL141=0)+AND($G$142="",$H$142="",AL143=0)+AND($G$144="",$H$144="",AL145=0)+AND($G$146="",$H$146="",AL147=0)+AND($G$148="",$H$148="",AL149=0)+AND($G$150="",$H$150="",AL151=0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM7" s="77">
         <f>SUM(AND($G$80="",$H$80="",AM81=0)+AND($G$82="",$H$82="",AM83=0)+AND($G$84="",$H$84="",AM85=0)+AND($G$86="",$H$86="",AM87=0)+AND($G$88="",$H$88="",AM89=0)+AND($G$90="",$H$90="",AM91=0)+AND($G$92="",$H$92="",AM93=0)+AND($G$94="",$H$94="",AM95=0)+AND($G$96="",$H$96="",AM97=0)+AND($G$98="",$H$98="",AM99=0)+AND($G$100="",$H$100="",AM101=0)+AND($G$102="",$H$102="",AM103=0)+AND($G$104="",$H$104="",AM105=0)+AND($G$106="",$H$106="",AM107=0)+AND($G$108="",$H$108="",AM109=0)+AND($G$110="",$H$110="",AM111=0)+AND($G$112="",$H$112="",AM113=0)+AND($G$114="",$H$114="",AM115=0)+AND($G$116="",$H$116="",AM117=0)+AND($G$118="",$H$118="",AM119=0)+AND($G$120="",$H$120="",AM121=0)+AND($G$122="",$H$122="",AM123=0)+AND($G$124="",$H$124="",AM125=0)+AND($G$126="",$H$126="",AM127=0)+AND($G$128="",$H$128="",AM129=0)+AND($G$130="",$H$130="",AM131=0)+AND($G$132="",$H$132="",AM133=0)+AND($G$134="",$H$134="",AM135=0)+AND($G$136="",$H$136="",AM137=0)+AND($G$138="",$H$138="",AM139=0)+AND($G$140="",$H$140="",AM141=0)+AND($G$142="",$H$142="",AM143=0)+AND($G$144="",$H$144="",AM145=0)+AND($G$146="",$H$146="",AM147=0)+AND($G$148="",$H$148="",AM149=0)+AND($G$150="",$H$150="",AM151=0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN7" s="77">
         <f>SUM(AND($G$80="",$H$80="",AN81=0)+AND($G$82="",$H$82="",AN83=0)+AND($G$84="",$H$84="",AN85=0)+AND($G$86="",$H$86="",AN87=0)+AND($G$88="",$H$88="",AN89=0)+AND($G$90="",$H$90="",AN91=0)+AND($G$92="",$H$92="",AN93=0)+AND($G$94="",$H$94="",AN95=0)+AND($G$96="",$H$96="",AN97=0)+AND($G$98="",$H$98="",AN99=0)+AND($G$100="",$H$100="",AN101=0)+AND($G$102="",$H$102="",AN103=0)+AND($G$104="",$H$104="",AN105=0)+AND($G$106="",$H$106="",AN107=0)+AND($G$108="",$H$108="",AN109=0)+AND($G$110="",$H$110="",AN111=0)+AND($G$112="",$H$112="",AN113=0)+AND($G$114="",$H$114="",AN115=0)+AND($G$116="",$H$116="",AN117=0)+AND($G$118="",$H$118="",AN119=0)+AND($G$120="",$H$120="",AN121=0)+AND($G$122="",$H$122="",AN123=0)+AND($G$124="",$H$124="",AN125=0)+AND($G$126="",$H$126="",AN127=0)+AND($G$128="",$H$128="",AN129=0)+AND($G$130="",$H$130="",AN131=0)+AND($G$132="",$H$132="",AN133=0)+AND($G$134="",$H$134="",AN135=0)+AND($G$136="",$H$136="",AN137=0)+AND($G$138="",$H$138="",AN139=0)+AND($G$140="",$H$140="",AN141=0)+AND($G$142="",$H$142="",AN143=0)+AND($G$144="",$H$144="",AN145=0)+AND($G$146="",$H$146="",AN147=0)+AND($G$148="",$H$148="",AN149=0)+AND($G$150="",$H$150="",AN151=0))</f>
@@ -3794,10 +3794,10 @@
         <v>2</v>
       </c>
       <c r="Q9" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S9" s="18">
         <v>2</v>
@@ -3809,13 +3809,13 @@
         <v>3</v>
       </c>
       <c r="V9" s="18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W9" s="18">
         <v>2</v>
       </c>
       <c r="X9" s="18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y9" s="18">
         <v>2</v>
@@ -3836,13 +3836,13 @@
         <v>3</v>
       </c>
       <c r="AE9" s="18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF9" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG9" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH9" s="18">
         <v>2</v>
@@ -3857,10 +3857,10 @@
         <v>3</v>
       </c>
       <c r="AL9" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM9" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN9" s="18">
         <v>2</v>
@@ -3936,10 +3936,10 @@
         <v>7</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q10" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R10" s="13" t="s">
         <v>7</v>
@@ -3981,13 +3981,13 @@
         <v>16</v>
       </c>
       <c r="AE10" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AF10" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG10" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AH10" s="13" t="s">
         <v>16</v>
@@ -4002,10 +4002,10 @@
         <v>16</v>
       </c>
       <c r="AL10" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM10" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN10" s="13" t="s">
         <v>16</v>
@@ -4067,10 +4067,10 @@
         <v>2</v>
       </c>
       <c r="Q11" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R11" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S11" s="13">
         <v>3</v>
@@ -4082,10 +4082,10 @@
         <v>2</v>
       </c>
       <c r="V11" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W11" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X11" s="13">
         <v>2</v>
@@ -4109,13 +4109,13 @@
         <v>4</v>
       </c>
       <c r="AE11" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF11" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG11" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH11" s="13">
         <v>2</v>
@@ -4130,10 +4130,10 @@
         <v>4</v>
       </c>
       <c r="AL11" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM11" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN11" s="13">
         <v>4</v>
@@ -4209,13 +4209,13 @@
         <v>16</v>
       </c>
       <c r="P12" s="18" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q12" s="18" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="R12" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S12" s="18" t="s">
         <v>7</v>
@@ -4257,10 +4257,10 @@
         <v>7</v>
       </c>
       <c r="AF12" s="18" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AG12" s="18" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AH12" s="18" t="s">
         <v>7</v>
@@ -4338,10 +4338,10 @@
         <v>2</v>
       </c>
       <c r="Q13" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R13" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S13" s="18">
         <v>3</v>
@@ -4356,10 +4356,10 @@
         <v>2</v>
       </c>
       <c r="W13" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X13" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y13" s="18">
         <v>3</v>
@@ -4380,13 +4380,13 @@
         <v>4</v>
       </c>
       <c r="AE13" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF13" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG13" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH13" s="18">
         <v>3</v>
@@ -4496,13 +4496,13 @@
         <v>7</v>
       </c>
       <c r="V14" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="W14" s="13" t="s">
         <v>7</v>
       </c>
       <c r="X14" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y14" s="13" t="s">
         <v>7</v>
@@ -4523,13 +4523,13 @@
         <v>7</v>
       </c>
       <c r="AE14" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AF14" s="13" t="s">
         <v>7</v>
       </c>
       <c r="AG14" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AH14" s="13" t="s">
         <v>16</v>
@@ -4604,14 +4604,14 @@
         <v>2</v>
       </c>
       <c r="P15" s="13">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="13">
+        <v>3</v>
+      </c>
+      <c r="R15" s="13">
         <v>1</v>
       </c>
-      <c r="Q15" s="13">
-        <v>3</v>
-      </c>
-      <c r="R15" s="13">
-        <v>3</v>
-      </c>
       <c r="S15" s="13">
         <v>3</v>
       </c>
@@ -4625,10 +4625,10 @@
         <v>2</v>
       </c>
       <c r="W15" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X15" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y15" s="13">
         <v>3</v>
@@ -4649,13 +4649,13 @@
         <v>5</v>
       </c>
       <c r="AE15" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF15" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG15" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH15" s="13">
         <v>2</v>
@@ -4670,10 +4670,10 @@
         <v>2</v>
       </c>
       <c r="AL15" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM15" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN15" s="13">
         <v>4</v>
@@ -4743,10 +4743,10 @@
         <v>15</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q16" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R16" s="18" t="s">
         <v>15</v>
@@ -4764,10 +4764,10 @@
         <v>15</v>
       </c>
       <c r="W16" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X16" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y16" s="18" t="s">
         <v>15</v>
@@ -4791,10 +4791,10 @@
         <v>15</v>
       </c>
       <c r="AF16" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG16" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH16" s="18" t="s">
         <v>16</v>
@@ -4887,13 +4887,13 @@
         <v>4</v>
       </c>
       <c r="V17" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W17" s="18">
         <v>2</v>
       </c>
       <c r="X17" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y17" s="18">
         <v>3</v>
@@ -4917,10 +4917,10 @@
         <v>3</v>
       </c>
       <c r="AF17" s="18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG17" s="18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH17" s="18">
         <v>2</v>
@@ -5053,10 +5053,10 @@
         <v>15</v>
       </c>
       <c r="AE18" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF18" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG18" s="13" t="s">
         <v>15</v>
@@ -5074,10 +5074,10 @@
         <v>15</v>
       </c>
       <c r="AL18" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM18" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN18" s="13" t="s">
         <v>15</v>
@@ -5152,10 +5152,10 @@
         <v>3</v>
       </c>
       <c r="V19" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W19" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X19" s="13">
         <v>2</v>
@@ -5182,10 +5182,10 @@
         <v>2</v>
       </c>
       <c r="AF19" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG19" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH19" s="13">
         <v>1</v>
@@ -5324,10 +5324,10 @@
         <v>7</v>
       </c>
       <c r="AE20" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AF20" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AG20" s="19" t="s">
         <v>7</v>
@@ -5405,10 +5405,10 @@
         <v>1</v>
       </c>
       <c r="P21" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21" s="19">
         <v>2</v>
@@ -5423,13 +5423,13 @@
         <v>2</v>
       </c>
       <c r="V21" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W21" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X21" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y21" s="19">
         <v>3</v>
@@ -5450,13 +5450,13 @@
         <v>1</v>
       </c>
       <c r="AE21" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF21" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG21" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH21" s="19">
         <v>3</v>
@@ -5677,10 +5677,10 @@
         <v>2</v>
       </c>
       <c r="Q23" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R23" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S23" s="13">
         <v>3</v>
@@ -5692,13 +5692,13 @@
         <v>3</v>
       </c>
       <c r="V23" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W23" s="13">
         <v>3</v>
       </c>
       <c r="X23" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y23" s="13">
         <v>2</v>
@@ -5722,10 +5722,10 @@
         <v>2</v>
       </c>
       <c r="AF23" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG23" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH23" s="13">
         <v>2</v>
@@ -5817,10 +5817,10 @@
         <v>7</v>
       </c>
       <c r="P24" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q24" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R24" s="19" t="s">
         <v>7</v>
@@ -5835,13 +5835,13 @@
         <v>7</v>
       </c>
       <c r="V24" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="W24" s="19" t="s">
         <v>7</v>
       </c>
       <c r="X24" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y24" s="19" t="s">
         <v>7</v>
@@ -5862,10 +5862,10 @@
         <v>7</v>
       </c>
       <c r="AE24" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AF24" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AG24" s="19" t="s">
         <v>16</v>
@@ -5883,10 +5883,10 @@
         <v>7</v>
       </c>
       <c r="AL24" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AM24" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AN24" s="19" t="s">
         <v>16</v>
@@ -5961,13 +5961,13 @@
         <v>3</v>
       </c>
       <c r="V25" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W25" s="19">
         <v>3</v>
       </c>
       <c r="X25" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y25" s="19">
         <v>2</v>
@@ -5988,10 +5988,10 @@
         <v>1</v>
       </c>
       <c r="AE25" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF25" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG25" s="19">
         <v>4</v>
@@ -6009,10 +6009,10 @@
         <v>2</v>
       </c>
       <c r="AL25" s="19">
+        <v>2</v>
+      </c>
+      <c r="AM25" s="19">
         <v>1</v>
-      </c>
-      <c r="AM25" s="19">
-        <v>2</v>
       </c>
       <c r="AN25" s="19">
         <v>2</v>
@@ -6230,13 +6230,13 @@
         <v>4</v>
       </c>
       <c r="V27" s="13">
+        <v>3</v>
+      </c>
+      <c r="W27" s="13">
         <v>1</v>
       </c>
-      <c r="W27" s="13">
-        <v>2</v>
-      </c>
       <c r="X27" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y27" s="13">
         <v>2</v>
@@ -6257,10 +6257,10 @@
         <v>2</v>
       </c>
       <c r="AE27" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF27" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG27" s="13">
         <v>3</v>
@@ -6278,10 +6278,10 @@
         <v>3</v>
       </c>
       <c r="AL27" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM27" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN27" s="13">
         <v>2</v>
@@ -6354,10 +6354,10 @@
         <v>16</v>
       </c>
       <c r="Q28" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R28" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S28" s="19" t="s">
         <v>7</v>
@@ -6369,13 +6369,13 @@
         <v>16</v>
       </c>
       <c r="V28" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="W28" s="19" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="X28" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y28" s="19" t="s">
         <v>16</v>
@@ -6399,10 +6399,10 @@
         <v>16</v>
       </c>
       <c r="AF28" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AG28" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AH28" s="19" t="s">
         <v>7</v>
@@ -6417,10 +6417,10 @@
         <v>16</v>
       </c>
       <c r="AL28" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AM28" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AN28" s="19" t="s">
         <v>16</v>
@@ -6477,14 +6477,14 @@
         <v>3</v>
       </c>
       <c r="P29" s="19">
+        <v>2</v>
+      </c>
+      <c r="Q29" s="19">
+        <v>2</v>
+      </c>
+      <c r="R29" s="19">
         <v>1</v>
       </c>
-      <c r="Q29" s="19">
-        <v>2</v>
-      </c>
-      <c r="R29" s="19">
-        <v>2</v>
-      </c>
       <c r="S29" s="19">
         <v>3</v>
       </c>
@@ -6498,10 +6498,10 @@
         <v>2</v>
       </c>
       <c r="W29" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X29" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y29" s="19">
         <v>2</v>
@@ -6525,10 +6525,10 @@
         <v>2</v>
       </c>
       <c r="AF29" s="19">
+        <v>2</v>
+      </c>
+      <c r="AG29" s="19">
         <v>5</v>
-      </c>
-      <c r="AG29" s="19">
-        <v>2</v>
       </c>
       <c r="AH29" s="19">
         <v>3</v>
@@ -6616,13 +6616,13 @@
         <v>16</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q30" s="13" t="s">
         <v>7</v>
       </c>
       <c r="R30" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="S30" s="13" t="s">
         <v>7</v>
@@ -6637,10 +6637,10 @@
         <v>7</v>
       </c>
       <c r="W30" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="X30" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Y30" s="13" t="s">
         <v>7</v>
@@ -6742,13 +6742,13 @@
         <v>2</v>
       </c>
       <c r="P31" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="13">
+        <v>2</v>
+      </c>
+      <c r="R31" s="13">
         <v>1</v>
-      </c>
-      <c r="Q31" s="13">
-        <v>2</v>
-      </c>
-      <c r="R31" s="13">
-        <v>2</v>
       </c>
       <c r="S31" s="13">
         <v>2</v>
@@ -6763,10 +6763,10 @@
         <v>1</v>
       </c>
       <c r="W31" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X31" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y31" s="13">
         <v>3</v>
@@ -6787,13 +6787,13 @@
         <v>1</v>
       </c>
       <c r="AE31" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF31" s="13">
         <v>3</v>
       </c>
       <c r="AG31" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH31" s="13">
         <v>1</v>
@@ -6949,10 +6949,10 @@
         <v>15</v>
       </c>
       <c r="AL32" s="18" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AM32" s="18" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AN32" s="18" t="s">
         <v>16</v>
@@ -7008,10 +7008,10 @@
         <v>2</v>
       </c>
       <c r="Q33" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R33" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S33" s="18">
         <v>4</v>
@@ -7023,13 +7023,13 @@
         <v>3</v>
       </c>
       <c r="V33" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W33" s="18">
         <v>3</v>
       </c>
       <c r="X33" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y33" s="18">
         <v>2</v>
@@ -7050,13 +7050,13 @@
         <v>3</v>
       </c>
       <c r="AE33" s="18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AF33" s="18">
+        <v>4</v>
+      </c>
+      <c r="AG33" s="18">
         <v>5</v>
-      </c>
-      <c r="AG33" s="18">
-        <v>1</v>
       </c>
       <c r="AH33" s="18">
         <v>3</v>
@@ -7071,10 +7071,10 @@
         <v>3</v>
       </c>
       <c r="AL33" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM33" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN33" s="18">
         <v>4</v>
@@ -7144,13 +7144,13 @@
         <v>15</v>
       </c>
       <c r="P34" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q34" s="13" t="s">
         <v>15</v>
       </c>
       <c r="R34" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S34" s="13" t="s">
         <v>15</v>
@@ -7284,13 +7284,13 @@
         <v>3</v>
       </c>
       <c r="V35" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W35" s="13">
         <v>3</v>
       </c>
       <c r="X35" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y35" s="13">
         <v>3</v>
@@ -7314,10 +7314,10 @@
         <v>2</v>
       </c>
       <c r="AF35" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG35" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH35" s="13">
         <v>2</v>
@@ -7332,10 +7332,10 @@
         <v>4</v>
       </c>
       <c r="AL35" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM35" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN35" s="13">
         <v>3</v>
@@ -7530,10 +7530,10 @@
         <v>3</v>
       </c>
       <c r="Q37" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R37" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S37" s="18">
         <v>5</v>
@@ -7545,13 +7545,13 @@
         <v>4</v>
       </c>
       <c r="V37" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W37" s="18">
         <v>4</v>
       </c>
       <c r="X37" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y37" s="18">
         <v>4</v>
@@ -7572,13 +7572,13 @@
         <v>3</v>
       </c>
       <c r="AE37" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF37" s="18">
         <v>4</v>
       </c>
       <c r="AG37" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH37" s="18">
         <v>4</v>
@@ -7593,10 +7593,10 @@
         <v>5</v>
       </c>
       <c r="AL37" s="18">
+        <v>4</v>
+      </c>
+      <c r="AM37" s="18">
         <v>5</v>
-      </c>
-      <c r="AM37" s="18">
-        <v>4</v>
       </c>
       <c r="AN37" s="18">
         <v>5</v>
@@ -7684,10 +7684,10 @@
         <v>15</v>
       </c>
       <c r="V38" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="W38" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="X38" s="13" t="s">
         <v>15</v>
@@ -7711,10 +7711,10 @@
         <v>15</v>
       </c>
       <c r="AE38" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF38" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG38" s="13" t="s">
         <v>15</v>
@@ -7732,10 +7732,10 @@
         <v>15</v>
       </c>
       <c r="AL38" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM38" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN38" s="13" t="s">
         <v>15</v>
@@ -7791,10 +7791,10 @@
         <v>2</v>
       </c>
       <c r="Q39" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R39" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S39" s="13">
         <v>3</v>
@@ -7806,10 +7806,10 @@
         <v>3</v>
       </c>
       <c r="V39" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W39" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X39" s="13">
         <v>3</v>
@@ -7833,13 +7833,13 @@
         <v>2</v>
       </c>
       <c r="AE39" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF39" s="13">
         <v>2</v>
       </c>
       <c r="AG39" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH39" s="13">
         <v>3</v>
@@ -7854,10 +7854,10 @@
         <v>3</v>
       </c>
       <c r="AL39" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AM39" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN39" s="13">
         <v>3</v>
@@ -8048,10 +8048,10 @@
         <v>2</v>
       </c>
       <c r="Q41" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R41" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S41" s="18">
         <v>3</v>
@@ -8063,13 +8063,13 @@
         <v>2</v>
       </c>
       <c r="V41" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W41" s="18">
         <v>3</v>
       </c>
       <c r="X41" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y41" s="18">
         <v>3</v>
@@ -8090,10 +8090,10 @@
         <v>3</v>
       </c>
       <c r="AE41" s="18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF41" s="18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG41" s="18">
         <v>2</v>
@@ -8111,10 +8111,10 @@
         <v>3</v>
       </c>
       <c r="AL41" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM41" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN41" s="18">
         <v>3</v>
@@ -8305,10 +8305,10 @@
         <v>3</v>
       </c>
       <c r="Q43" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R43" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S43" s="13">
         <v>3</v>
@@ -8320,13 +8320,13 @@
         <v>3</v>
       </c>
       <c r="V43" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W43" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X43" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y43" s="13">
         <v>3</v>
@@ -8347,13 +8347,13 @@
         <v>3</v>
       </c>
       <c r="AE43" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF43" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG43" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH43" s="13">
         <v>3</v>
@@ -8368,10 +8368,10 @@
         <v>4</v>
       </c>
       <c r="AL43" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM43" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN43" s="13">
         <v>3</v>
@@ -8443,13 +8443,13 @@
         <v>16</v>
       </c>
       <c r="P44" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q44" s="19" t="s">
         <v>7</v>
       </c>
       <c r="R44" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="S44" s="19" t="s">
         <v>7</v>
@@ -8461,13 +8461,13 @@
         <v>16</v>
       </c>
       <c r="V44" s="19" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="W44" s="19" t="s">
         <v>7</v>
       </c>
       <c r="X44" s="19" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Y44" s="19" t="s">
         <v>7</v>
@@ -8488,10 +8488,10 @@
         <v>15</v>
       </c>
       <c r="AE44" s="19" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AF44" s="19" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AG44" s="19" t="s">
         <v>15</v>
@@ -8509,10 +8509,10 @@
         <v>7</v>
       </c>
       <c r="AL44" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AM44" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AN44" s="19" t="s">
         <v>7</v>
@@ -8568,10 +8568,10 @@
         <v>2</v>
       </c>
       <c r="Q45" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R45" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S45" s="19">
         <v>2</v>
@@ -8583,10 +8583,10 @@
         <v>2</v>
       </c>
       <c r="V45" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W45" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X45" s="19">
         <v>3</v>
@@ -8704,13 +8704,13 @@
         <v>15</v>
       </c>
       <c r="P46" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q46" s="13" t="s">
         <v>15</v>
       </c>
       <c r="R46" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="S46" s="13" t="s">
         <v>15</v>
@@ -8722,10 +8722,10 @@
         <v>15</v>
       </c>
       <c r="V46" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W46" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X46" s="13" t="s">
         <v>16</v>
@@ -8752,10 +8752,10 @@
         <v>16</v>
       </c>
       <c r="AF46" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG46" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH46" s="13" t="s">
         <v>15</v>
@@ -8770,10 +8770,10 @@
         <v>15</v>
       </c>
       <c r="AL46" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM46" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN46" s="13" t="s">
         <v>15</v>
@@ -8826,13 +8826,13 @@
         <v>3</v>
       </c>
       <c r="P47" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R47" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S47" s="13">
         <v>1</v>
@@ -8871,13 +8871,13 @@
         <v>3</v>
       </c>
       <c r="AE47" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF47" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG47" s="13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH47" s="13">
         <v>3</v>
@@ -8892,10 +8892,10 @@
         <v>3</v>
       </c>
       <c r="AL47" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM47" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN47" s="13">
         <v>3</v>
@@ -8968,10 +8968,10 @@
         <v>15</v>
       </c>
       <c r="Q48" s="19" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="R48" s="19" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="S48" s="19" t="s">
         <v>16</v>
@@ -8983,10 +8983,10 @@
         <v>15</v>
       </c>
       <c r="V48" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="W48" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="X48" s="19" t="s">
         <v>16</v>
@@ -9010,10 +9010,10 @@
         <v>7</v>
       </c>
       <c r="AE48" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AF48" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AG48" s="19" t="s">
         <v>16</v>
@@ -9031,10 +9031,10 @@
         <v>7</v>
       </c>
       <c r="AL48" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AM48" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AN48" s="19" t="s">
         <v>7</v>
@@ -9108,10 +9108,10 @@
         <v>2</v>
       </c>
       <c r="W49" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X49" s="19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y49" s="19">
         <v>3</v>
@@ -9132,10 +9132,10 @@
         <v>2</v>
       </c>
       <c r="AE49" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF49" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG49" s="19">
         <v>2</v>
@@ -9153,10 +9153,10 @@
         <v>3</v>
       </c>
       <c r="AL49" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM49" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN49" s="19">
         <v>3</v>
@@ -9351,10 +9351,10 @@
         <v>2</v>
       </c>
       <c r="Q51" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R51" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S51" s="13">
         <v>2</v>
@@ -9366,11 +9366,11 @@
         <v>3</v>
       </c>
       <c r="V51" s="13">
+        <v>2</v>
+      </c>
+      <c r="W51" s="13">
         <v>1</v>
       </c>
-      <c r="W51" s="13">
-        <v>2</v>
-      </c>
       <c r="X51" s="13">
         <v>2</v>
       </c>
@@ -9393,13 +9393,13 @@
         <v>3</v>
       </c>
       <c r="AE51" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF51" s="13">
         <v>3</v>
       </c>
       <c r="AG51" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH51" s="13">
         <v>2</v>
@@ -9414,10 +9414,10 @@
         <v>3</v>
       </c>
       <c r="AL51" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM51" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN51" s="13">
         <v>3</v>
@@ -9486,10 +9486,10 @@
         <v>15</v>
       </c>
       <c r="Q52" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R52" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S52" s="19" t="s">
         <v>16</v>
@@ -9531,10 +9531,10 @@
         <v>15</v>
       </c>
       <c r="AF52" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG52" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH52" s="19" t="s">
         <v>16</v>
@@ -9549,10 +9549,10 @@
         <v>16</v>
       </c>
       <c r="AL52" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM52" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN52" s="19" t="s">
         <v>16</v>
@@ -9608,10 +9608,10 @@
         <v>2</v>
       </c>
       <c r="Q53" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R53" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S53" s="19">
         <v>2</v>
@@ -9626,37 +9626,37 @@
         <v>1</v>
       </c>
       <c r="W53" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X53" s="19">
+        <v>3</v>
+      </c>
+      <c r="Y53" s="19">
+        <v>3</v>
+      </c>
+      <c r="Z53" s="19">
+        <v>2</v>
+      </c>
+      <c r="AA53" s="19">
+        <v>2</v>
+      </c>
+      <c r="AB53" s="19">
+        <v>3</v>
+      </c>
+      <c r="AC53" s="19">
+        <v>2</v>
+      </c>
+      <c r="AD53" s="19">
+        <v>2</v>
+      </c>
+      <c r="AE53" s="19">
         <v>1</v>
       </c>
-      <c r="Y53" s="19">
-        <v>3</v>
-      </c>
-      <c r="Z53" s="19">
-        <v>2</v>
-      </c>
-      <c r="AA53" s="19">
-        <v>2</v>
-      </c>
-      <c r="AB53" s="19">
-        <v>3</v>
-      </c>
-      <c r="AC53" s="19">
-        <v>2</v>
-      </c>
-      <c r="AD53" s="19">
-        <v>2</v>
-      </c>
-      <c r="AE53" s="19">
-        <v>3</v>
-      </c>
       <c r="AF53" s="19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG53" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH53" s="19">
         <v>2</v>
@@ -9671,10 +9671,10 @@
         <v>6</v>
       </c>
       <c r="AL53" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM53" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN53" s="19">
         <v>4</v>
@@ -9761,10 +9761,10 @@
         <v>7</v>
       </c>
       <c r="W54" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="X54" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Y54" s="13" t="s">
         <v>7</v>
@@ -9785,10 +9785,10 @@
         <v>16</v>
       </c>
       <c r="AE54" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AF54" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AG54" s="13" t="s">
         <v>7</v>
@@ -9880,10 +9880,10 @@
         <v>1</v>
       </c>
       <c r="V55" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W55" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X55" s="13">
         <v>2</v>
@@ -10125,13 +10125,13 @@
         <v>3</v>
       </c>
       <c r="P57" s="18">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="18">
+        <v>4</v>
+      </c>
+      <c r="R57" s="18">
         <v>5</v>
-      </c>
-      <c r="Q57" s="18">
-        <v>4</v>
-      </c>
-      <c r="R57" s="18">
-        <v>4</v>
       </c>
       <c r="S57" s="18">
         <v>4</v>
@@ -10143,13 +10143,13 @@
         <v>4</v>
       </c>
       <c r="V57" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W57" s="18">
         <v>4</v>
       </c>
       <c r="X57" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y57" s="18">
         <v>4</v>
@@ -10173,10 +10173,10 @@
         <v>3</v>
       </c>
       <c r="AF57" s="18">
+        <v>3</v>
+      </c>
+      <c r="AG57" s="18">
         <v>6</v>
-      </c>
-      <c r="AG57" s="18">
-        <v>3</v>
       </c>
       <c r="AH57" s="18">
         <v>6</v>
@@ -10267,10 +10267,10 @@
         <v>16</v>
       </c>
       <c r="Q58" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R58" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="S58" s="13" t="s">
         <v>16</v>
@@ -10285,10 +10285,10 @@
         <v>15</v>
       </c>
       <c r="W58" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X58" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y58" s="13" t="s">
         <v>16</v>
@@ -10309,10 +10309,10 @@
         <v>16</v>
       </c>
       <c r="AE58" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF58" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG58" s="13" t="s">
         <v>15</v>
@@ -10386,14 +10386,14 @@
         <v>3</v>
       </c>
       <c r="P59" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q59" s="13">
+        <v>3</v>
+      </c>
+      <c r="R59" s="13">
         <v>1</v>
       </c>
-      <c r="Q59" s="13">
-        <v>2</v>
-      </c>
-      <c r="R59" s="13">
-        <v>3</v>
-      </c>
       <c r="S59" s="13">
         <v>2</v>
       </c>
@@ -10407,10 +10407,10 @@
         <v>3</v>
       </c>
       <c r="W59" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X59" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y59" s="13">
         <v>2</v>
@@ -10431,10 +10431,10 @@
         <v>0</v>
       </c>
       <c r="AE59" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF59" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG59" s="13">
         <v>3</v>
@@ -10573,10 +10573,10 @@
         <v>7</v>
       </c>
       <c r="AF60" s="18" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AG60" s="18" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AH60" s="18" t="s">
         <v>7</v>
@@ -10665,10 +10665,10 @@
         <v>3</v>
       </c>
       <c r="V61" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W61" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X61" s="18">
         <v>3</v>
@@ -10692,13 +10692,13 @@
         <v>3</v>
       </c>
       <c r="AE61" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF61" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG61" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH61" s="18">
         <v>3</v>
@@ -10713,10 +10713,10 @@
         <v>3</v>
       </c>
       <c r="AL61" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM61" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN61" s="18">
         <v>4</v>
@@ -10926,10 +10926,10 @@
         <v>3</v>
       </c>
       <c r="V63" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W63" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X63" s="13">
         <v>2</v>
@@ -10956,10 +10956,10 @@
         <v>2</v>
       </c>
       <c r="AF63" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG63" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH63" s="13">
         <v>3</v>
@@ -10974,10 +10974,10 @@
         <v>3</v>
       </c>
       <c r="AL63" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM63" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN63" s="13">
         <v>3</v>
@@ -11091,10 +11091,10 @@
         <v>15</v>
       </c>
       <c r="AF64" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG64" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH64" s="18" t="s">
         <v>15</v>
@@ -11109,10 +11109,10 @@
         <v>15</v>
       </c>
       <c r="AL64" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM64" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN64" s="18" t="s">
         <v>16</v>
@@ -11183,40 +11183,40 @@
         <v>3</v>
       </c>
       <c r="V65" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W65" s="18">
         <v>3</v>
       </c>
       <c r="X65" s="18">
+        <v>3</v>
+      </c>
+      <c r="Y65" s="18">
+        <v>3</v>
+      </c>
+      <c r="Z65" s="18">
+        <v>3</v>
+      </c>
+      <c r="AA65" s="18">
+        <v>2</v>
+      </c>
+      <c r="AB65" s="18">
+        <v>4</v>
+      </c>
+      <c r="AC65" s="18">
+        <v>2</v>
+      </c>
+      <c r="AD65" s="18">
+        <v>3</v>
+      </c>
+      <c r="AE65" s="18">
         <v>1</v>
       </c>
-      <c r="Y65" s="18">
-        <v>3</v>
-      </c>
-      <c r="Z65" s="18">
-        <v>3</v>
-      </c>
-      <c r="AA65" s="18">
-        <v>2</v>
-      </c>
-      <c r="AB65" s="18">
-        <v>4</v>
-      </c>
-      <c r="AC65" s="18">
-        <v>2</v>
-      </c>
-      <c r="AD65" s="18">
-        <v>3</v>
-      </c>
-      <c r="AE65" s="18">
-        <v>3</v>
-      </c>
       <c r="AF65" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG65" s="18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH65" s="18">
         <v>3</v>
@@ -11231,10 +11231,10 @@
         <v>7</v>
       </c>
       <c r="AL65" s="18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AM65" s="18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN65" s="18">
         <v>2</v>
@@ -11300,10 +11300,10 @@
         <v>7</v>
       </c>
       <c r="P66" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q66" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R66" s="13" t="s">
         <v>15</v>
@@ -11318,13 +11318,13 @@
         <v>15</v>
       </c>
       <c r="V66" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="W66" s="13" t="s">
         <v>15</v>
       </c>
       <c r="X66" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Y66" s="13" t="s">
         <v>15</v>
@@ -11345,13 +11345,13 @@
         <v>15</v>
       </c>
       <c r="AE66" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AF66" s="13" t="s">
         <v>15</v>
       </c>
       <c r="AG66" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AH66" s="13" t="s">
         <v>15</v>
@@ -11366,10 +11366,10 @@
         <v>16</v>
       </c>
       <c r="AL66" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM66" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN66" s="13" t="s">
         <v>15</v>
@@ -11425,10 +11425,10 @@
         <v>2</v>
       </c>
       <c r="Q67" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R67" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S67" s="13">
         <v>3</v>
@@ -11440,10 +11440,10 @@
         <v>2</v>
       </c>
       <c r="V67" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W67" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X67" s="13">
         <v>2</v>
@@ -11470,10 +11470,10 @@
         <v>2</v>
       </c>
       <c r="AF67" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG67" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH67" s="13">
         <v>2</v>
@@ -11488,10 +11488,10 @@
         <v>4</v>
       </c>
       <c r="AL67" s="13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM67" s="13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN67" s="13">
         <v>3</v>
@@ -11563,10 +11563,10 @@
         <v>7</v>
       </c>
       <c r="P68" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q68" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R68" s="19" t="s">
         <v>7</v>
@@ -11581,13 +11581,13 @@
         <v>7</v>
       </c>
       <c r="V68" s="19" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="W68" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X68" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Y68" s="19" t="s">
         <v>7</v>
@@ -11611,10 +11611,10 @@
         <v>7</v>
       </c>
       <c r="AF68" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AG68" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AH68" s="19" t="s">
         <v>7</v>
@@ -11629,10 +11629,10 @@
         <v>7</v>
       </c>
       <c r="AL68" s="19" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AM68" s="19" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AN68" s="19" t="s">
         <v>7</v>
@@ -11688,10 +11688,10 @@
         <v>2</v>
       </c>
       <c r="Q69" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R69" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S69" s="19">
         <v>4</v>
@@ -11703,10 +11703,10 @@
         <v>3</v>
       </c>
       <c r="V69" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W69" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X69" s="19">
         <v>2</v>
@@ -11733,10 +11733,10 @@
         <v>3</v>
       </c>
       <c r="AF69" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG69" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH69" s="19">
         <v>3</v>
@@ -11751,10 +11751,10 @@
         <v>3</v>
       </c>
       <c r="AL69" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM69" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN69" s="19">
         <v>5</v>
@@ -11827,10 +11827,10 @@
         <v>7</v>
       </c>
       <c r="Q70" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="R70" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="S70" s="13" t="s">
         <v>7</v>
@@ -11890,10 +11890,10 @@
         <v>16</v>
       </c>
       <c r="AL70" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AM70" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AN70" s="13" t="s">
         <v>15</v>
@@ -11964,14 +11964,14 @@
         <v>1</v>
       </c>
       <c r="V71" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W71" s="13">
+        <v>3</v>
+      </c>
+      <c r="X71" s="13">
         <v>1</v>
       </c>
-      <c r="X71" s="13">
-        <v>2</v>
-      </c>
       <c r="Y71" s="13">
         <v>2</v>
       </c>
@@ -11994,10 +11994,10 @@
         <v>2</v>
       </c>
       <c r="AF71" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG71" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH71" s="13">
         <v>1</v>
@@ -12012,10 +12012,10 @@
         <v>4</v>
       </c>
       <c r="AL71" s="13">
+        <v>2</v>
+      </c>
+      <c r="AM71" s="13">
         <v>1</v>
-      </c>
-      <c r="AM71" s="13">
-        <v>2</v>
       </c>
       <c r="AN71" s="13">
         <v>2</v>
@@ -12088,10 +12088,10 @@
         <v>16</v>
       </c>
       <c r="Q72" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R72" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="S72" s="19" t="s">
         <v>7</v>
@@ -12103,10 +12103,10 @@
         <v>16</v>
       </c>
       <c r="V72" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="W72" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="X72" s="19" t="s">
         <v>16</v>
@@ -12133,10 +12133,10 @@
         <v>16</v>
       </c>
       <c r="AF72" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AG72" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AH72" s="19" t="s">
         <v>7</v>
@@ -12151,10 +12151,10 @@
         <v>7</v>
       </c>
       <c r="AL72" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AM72" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AN72" s="19" t="s">
         <v>7</v>
@@ -12210,10 +12210,10 @@
         <v>2</v>
       </c>
       <c r="Q73" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R73" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S73" s="19">
         <v>2</v>
@@ -12225,13 +12225,13 @@
         <v>4</v>
       </c>
       <c r="V73" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W73" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X73" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y73" s="19">
         <v>2</v>
@@ -12252,13 +12252,13 @@
         <v>2</v>
       </c>
       <c r="AE73" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF73" s="19">
         <v>2</v>
       </c>
       <c r="AG73" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH73" s="19">
         <v>2</v>
@@ -12273,10 +12273,10 @@
         <v>5</v>
       </c>
       <c r="AL73" s="19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM73" s="19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN73" s="19">
         <v>3</v>
@@ -12471,10 +12471,10 @@
         <v>2</v>
       </c>
       <c r="Q75" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R75" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S75" s="13">
         <v>2</v>
@@ -12486,13 +12486,13 @@
         <v>3</v>
       </c>
       <c r="V75" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W75" s="13">
+        <v>3</v>
+      </c>
+      <c r="X75" s="13">
         <v>1</v>
-      </c>
-      <c r="X75" s="13">
-        <v>2</v>
       </c>
       <c r="Y75" s="13">
         <v>3</v>
@@ -12516,10 +12516,10 @@
         <v>2</v>
       </c>
       <c r="AF75" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG75" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH75" s="13">
         <v>1</v>
@@ -12534,10 +12534,10 @@
         <v>3</v>
       </c>
       <c r="AL75" s="13">
+        <v>3</v>
+      </c>
+      <c r="AM75" s="13">
         <v>1</v>
-      </c>
-      <c r="AM75" s="13">
-        <v>3</v>
       </c>
       <c r="AN75" s="13">
         <v>4</v>
@@ -12603,13 +12603,13 @@
         <v>16</v>
       </c>
       <c r="P76" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q76" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R76" s="19" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="S76" s="19" t="s">
         <v>16</v>
@@ -12621,13 +12621,13 @@
         <v>16</v>
       </c>
       <c r="V76" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="W76" s="19" t="s">
         <v>7</v>
       </c>
       <c r="X76" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y76" s="19" t="s">
         <v>16</v>
@@ -12651,10 +12651,10 @@
         <v>16</v>
       </c>
       <c r="AF76" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG76" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH76" s="19" t="s">
         <v>7</v>
@@ -12725,14 +12725,14 @@
         <v>2</v>
       </c>
       <c r="P77" s="19">
+        <v>2</v>
+      </c>
+      <c r="Q77" s="19">
+        <v>2</v>
+      </c>
+      <c r="R77" s="19">
         <v>1</v>
       </c>
-      <c r="Q77" s="19">
-        <v>2</v>
-      </c>
-      <c r="R77" s="19">
-        <v>2</v>
-      </c>
       <c r="S77" s="19">
         <v>2</v>
       </c>
@@ -12743,10 +12743,10 @@
         <v>2</v>
       </c>
       <c r="V77" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W77" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X77" s="19">
         <v>2</v>
@@ -12773,10 +12773,10 @@
         <v>2</v>
       </c>
       <c r="AF77" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG77" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH77" s="19">
         <v>3</v>
@@ -12985,10 +12985,10 @@
         <v>2</v>
       </c>
       <c r="Q79" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R79" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S79" s="14">
         <v>2</v>
@@ -13000,13 +13000,13 @@
         <v>2</v>
       </c>
       <c r="V79" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W79" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X79" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y79" s="14">
         <v>3</v>
@@ -13027,14 +13027,14 @@
         <v>3</v>
       </c>
       <c r="AE79" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF79" s="14">
+        <v>3</v>
+      </c>
+      <c r="AG79" s="14">
         <v>5</v>
       </c>
-      <c r="AG79" s="14">
-        <v>4</v>
-      </c>
       <c r="AH79" s="14">
         <v>2</v>
       </c>
@@ -13048,10 +13048,10 @@
         <v>2</v>
       </c>
       <c r="AL79" s="14">
+        <v>3</v>
+      </c>
+      <c r="AM79" s="14">
         <v>1</v>
-      </c>
-      <c r="AM79" s="14">
-        <v>3</v>
       </c>
       <c r="AN79" s="14">
         <v>3</v>
@@ -13123,13 +13123,13 @@
         <v>7</v>
       </c>
       <c r="P80" s="18" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q80" s="18" t="s">
         <v>16</v>
       </c>
       <c r="R80" s="18" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="S80" s="18" t="s">
         <v>16</v>
@@ -13141,13 +13141,13 @@
         <v>7</v>
       </c>
       <c r="V80" s="18" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="W80" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X80" s="18" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Y80" s="18" t="s">
         <v>7</v>
@@ -13168,10 +13168,10 @@
         <v>7</v>
       </c>
       <c r="AE80" s="18" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AF80" s="18" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AG80" s="18" t="s">
         <v>7</v>
@@ -13189,10 +13189,10 @@
         <v>7</v>
       </c>
       <c r="AL80" s="18" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AM80" s="18" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AN80" s="18" t="s">
         <v>7</v>
@@ -13248,10 +13248,10 @@
         <v>2</v>
       </c>
       <c r="Q81" s="18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R81" s="18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S81" s="18">
         <v>2</v>
@@ -13266,10 +13266,10 @@
         <v>1</v>
       </c>
       <c r="W81" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X81" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="18">
         <v>2</v>
@@ -13290,13 +13290,13 @@
         <v>2</v>
       </c>
       <c r="AE81" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF81" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG81" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH81" s="18">
         <v>2</v>
@@ -13311,10 +13311,10 @@
         <v>3</v>
       </c>
       <c r="AL81" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM81" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN81" s="18">
         <v>3</v>
@@ -13506,13 +13506,13 @@
         <v>3</v>
       </c>
       <c r="P83" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q83" s="13">
         <v>2</v>
       </c>
       <c r="R83" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S83" s="13">
         <v>3</v>
@@ -13527,10 +13527,10 @@
         <v>2</v>
       </c>
       <c r="W83" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X83" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y83" s="13">
         <v>3</v>
@@ -13551,13 +13551,13 @@
         <v>3</v>
       </c>
       <c r="AE83" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF83" s="13">
+        <v>3</v>
+      </c>
+      <c r="AG83" s="13">
         <v>1</v>
-      </c>
-      <c r="AG83" s="13">
-        <v>2</v>
       </c>
       <c r="AH83" s="13">
         <v>3</v>
@@ -13572,10 +13572,10 @@
         <v>5</v>
       </c>
       <c r="AL83" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM83" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN83" s="13">
         <v>2</v>
@@ -13770,10 +13770,10 @@
         <v>2</v>
       </c>
       <c r="Q85" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R85" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S85" s="18">
         <v>3</v>
@@ -13785,40 +13785,40 @@
         <v>2</v>
       </c>
       <c r="V85" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W85" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X85" s="18">
+        <v>3</v>
+      </c>
+      <c r="Y85" s="18">
+        <v>2</v>
+      </c>
+      <c r="Z85" s="18">
+        <v>2</v>
+      </c>
+      <c r="AA85" s="18">
+        <v>4</v>
+      </c>
+      <c r="AB85" s="18">
+        <v>3</v>
+      </c>
+      <c r="AC85" s="18">
+        <v>2</v>
+      </c>
+      <c r="AD85" s="18">
+        <v>4</v>
+      </c>
+      <c r="AE85" s="18">
         <v>1</v>
       </c>
-      <c r="Y85" s="18">
-        <v>2</v>
-      </c>
-      <c r="Z85" s="18">
-        <v>2</v>
-      </c>
-      <c r="AA85" s="18">
-        <v>4</v>
-      </c>
-      <c r="AB85" s="18">
-        <v>3</v>
-      </c>
-      <c r="AC85" s="18">
-        <v>2</v>
-      </c>
-      <c r="AD85" s="18">
-        <v>4</v>
-      </c>
-      <c r="AE85" s="18">
-        <v>2</v>
-      </c>
       <c r="AF85" s="18">
         <v>2</v>
       </c>
       <c r="AG85" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH85" s="18">
         <v>2</v>
@@ -13951,10 +13951,10 @@
         <v>15</v>
       </c>
       <c r="AE86" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF86" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG86" s="13" t="s">
         <v>15</v>
@@ -14028,13 +14028,13 @@
         <v>1</v>
       </c>
       <c r="P87" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q87" s="13">
         <v>3</v>
       </c>
       <c r="R87" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S87" s="13">
         <v>2</v>
@@ -14046,13 +14046,13 @@
         <v>3</v>
       </c>
       <c r="V87" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W87" s="13">
         <v>2</v>
       </c>
       <c r="X87" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y87" s="13">
         <v>2</v>
@@ -14073,10 +14073,10 @@
         <v>1</v>
       </c>
       <c r="AE87" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF87" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG87" s="13">
         <v>1</v>
@@ -14285,13 +14285,13 @@
         <v>3</v>
       </c>
       <c r="P89" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q89" s="18">
         <v>2</v>
       </c>
       <c r="R89" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S89" s="18">
         <v>3</v>
@@ -14303,10 +14303,10 @@
         <v>2</v>
       </c>
       <c r="V89" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W89" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X89" s="18">
         <v>3</v>
@@ -14330,10 +14330,10 @@
         <v>4</v>
       </c>
       <c r="AE89" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF89" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG89" s="18">
         <v>3</v>
@@ -14420,13 +14420,13 @@
         <v>16</v>
       </c>
       <c r="P90" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q90" s="13" t="s">
         <v>7</v>
       </c>
       <c r="R90" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="S90" s="13" t="s">
         <v>7</v>
@@ -14438,13 +14438,13 @@
         <v>16</v>
       </c>
       <c r="V90" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="W90" s="13" t="s">
         <v>7</v>
       </c>
       <c r="X90" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y90" s="13" t="s">
         <v>16</v>
@@ -14542,14 +14542,14 @@
         <v>2</v>
       </c>
       <c r="P91" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q91" s="13">
+        <v>3</v>
+      </c>
+      <c r="R91" s="13">
         <v>1</v>
       </c>
-      <c r="Q91" s="13">
-        <v>2</v>
-      </c>
-      <c r="R91" s="13">
-        <v>3</v>
-      </c>
       <c r="S91" s="13">
         <v>3</v>
       </c>
@@ -14560,13 +14560,13 @@
         <v>2</v>
       </c>
       <c r="V91" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W91" s="13">
         <v>2</v>
       </c>
       <c r="X91" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y91" s="13">
         <v>2</v>
@@ -14590,10 +14590,10 @@
         <v>2</v>
       </c>
       <c r="AF91" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG91" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH91" s="13">
         <v>2</v>
@@ -14608,10 +14608,10 @@
         <v>4</v>
       </c>
       <c r="AL91" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM91" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN91" s="13">
         <v>4</v>
@@ -14805,13 +14805,13 @@
         <v>4</v>
       </c>
       <c r="P93" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q93" s="19">
         <v>4</v>
       </c>
       <c r="R93" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S93" s="19">
         <v>4</v>
@@ -14850,13 +14850,13 @@
         <v>4</v>
       </c>
       <c r="AE93" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF93" s="19">
+        <v>3</v>
+      </c>
+      <c r="AG93" s="19">
         <v>6</v>
-      </c>
-      <c r="AG93" s="19">
-        <v>4</v>
       </c>
       <c r="AH93" s="19">
         <v>3</v>
@@ -14871,10 +14871,10 @@
         <v>3</v>
       </c>
       <c r="AL93" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM93" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN93" s="19">
         <v>4</v>
@@ -15010,10 +15010,10 @@
         <v>15</v>
       </c>
       <c r="AL94" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM94" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN94" s="13" t="s">
         <v>15</v>
@@ -15069,10 +15069,10 @@
         <v>2</v>
       </c>
       <c r="Q95" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R95" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S95" s="13">
         <v>2</v>
@@ -15084,13 +15084,13 @@
         <v>3</v>
       </c>
       <c r="V95" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W95" s="13">
         <v>3</v>
       </c>
       <c r="X95" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y95" s="13">
         <v>2</v>
@@ -15111,13 +15111,13 @@
         <v>3</v>
       </c>
       <c r="AE95" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF95" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG95" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH95" s="13">
         <v>2</v>
@@ -15132,10 +15132,10 @@
         <v>5</v>
       </c>
       <c r="AL95" s="13">
+        <v>2</v>
+      </c>
+      <c r="AM95" s="13">
         <v>1</v>
-      </c>
-      <c r="AM95" s="13">
-        <v>2</v>
       </c>
       <c r="AN95" s="13">
         <v>2</v>
@@ -15345,13 +15345,13 @@
         <v>2</v>
       </c>
       <c r="V97" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W97" s="19">
         <v>3</v>
       </c>
       <c r="X97" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y97" s="19">
         <v>3</v>
@@ -15375,11 +15375,11 @@
         <v>4</v>
       </c>
       <c r="AF97" s="19">
+        <v>4</v>
+      </c>
+      <c r="AG97" s="19">
         <v>5</v>
       </c>
-      <c r="AG97" s="19">
-        <v>4</v>
-      </c>
       <c r="AH97" s="19">
         <v>3</v>
       </c>
@@ -15393,10 +15393,10 @@
         <v>2</v>
       </c>
       <c r="AL97" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM97" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN97" s="19">
         <v>3</v>
@@ -15591,10 +15591,10 @@
         <v>3</v>
       </c>
       <c r="Q99" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R99" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S99" s="13">
         <v>3</v>
@@ -15606,13 +15606,13 @@
         <v>4</v>
       </c>
       <c r="V99" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W99" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X99" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y99" s="13">
         <v>2</v>
@@ -15633,10 +15633,10 @@
         <v>4</v>
       </c>
       <c r="AE99" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF99" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG99" s="13">
         <v>4</v>
@@ -15741,13 +15741,13 @@
         <v>15</v>
       </c>
       <c r="V100" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W100" s="19" t="s">
         <v>15</v>
       </c>
       <c r="X100" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y100" s="19" t="s">
         <v>16</v>
@@ -15768,10 +15768,10 @@
         <v>15</v>
       </c>
       <c r="AE100" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF100" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG100" s="19" t="s">
         <v>16</v>
@@ -15848,10 +15848,10 @@
         <v>2</v>
       </c>
       <c r="Q101" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R101" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S101" s="19">
         <v>2</v>
@@ -15863,13 +15863,13 @@
         <v>3</v>
       </c>
       <c r="V101" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W101" s="19">
         <v>3</v>
       </c>
       <c r="X101" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y101" s="19">
         <v>2</v>
@@ -15890,13 +15890,13 @@
         <v>3</v>
       </c>
       <c r="AE101" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF101" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG101" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH101" s="19">
         <v>3</v>
@@ -15980,10 +15980,10 @@
         <v>16</v>
       </c>
       <c r="P102" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q102" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R102" s="13" t="s">
         <v>15</v>
@@ -16028,10 +16028,10 @@
         <v>16</v>
       </c>
       <c r="AF102" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG102" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH102" s="13" t="s">
         <v>16</v>
@@ -16046,10 +16046,10 @@
         <v>15</v>
       </c>
       <c r="AL102" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AM102" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AN102" s="13" t="s">
         <v>16</v>
@@ -16102,10 +16102,10 @@
         <v>2</v>
       </c>
       <c r="P103" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q103" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R103" s="14">
         <v>2</v>
@@ -16123,10 +16123,10 @@
         <v>0</v>
       </c>
       <c r="W103" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X103" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y103" s="14">
         <v>2</v>
@@ -16147,13 +16147,13 @@
         <v>2</v>
       </c>
       <c r="AE103" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF103" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG103" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH103" s="14">
         <v>2</v>
@@ -16168,10 +16168,10 @@
         <v>3</v>
       </c>
       <c r="AL103" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM103" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN103" s="14">
         <v>4</v>
@@ -16383,10 +16383,10 @@
         <v>3</v>
       </c>
       <c r="V105" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W105" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X105" s="18">
         <v>4</v>
@@ -16410,13 +16410,13 @@
         <v>3</v>
       </c>
       <c r="AE105" s="18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF105" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG105" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH105" s="18">
         <v>3</v>
@@ -16525,10 +16525,10 @@
         <v>15</v>
       </c>
       <c r="W106" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X106" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y106" s="13" t="s">
         <v>15</v>
@@ -16570,10 +16570,10 @@
         <v>16</v>
       </c>
       <c r="AL106" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM106" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN106" s="13" t="s">
         <v>15</v>
@@ -16626,13 +16626,13 @@
         <v>2</v>
       </c>
       <c r="P107" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q107" s="13">
         <v>3</v>
       </c>
       <c r="R107" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S107" s="13">
         <v>3</v>
@@ -16644,41 +16644,41 @@
         <v>2</v>
       </c>
       <c r="V107" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W107" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X107" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="13">
+        <v>2</v>
+      </c>
+      <c r="Z107" s="13">
+        <v>2</v>
+      </c>
+      <c r="AA107" s="13">
+        <v>3</v>
+      </c>
+      <c r="AB107" s="13">
+        <v>2</v>
+      </c>
+      <c r="AC107" s="13">
+        <v>3</v>
+      </c>
+      <c r="AD107" s="13">
+        <v>4</v>
+      </c>
+      <c r="AE107" s="13">
         <v>1</v>
       </c>
-      <c r="Y107" s="13">
-        <v>2</v>
-      </c>
-      <c r="Z107" s="13">
-        <v>2</v>
-      </c>
-      <c r="AA107" s="13">
-        <v>3</v>
-      </c>
-      <c r="AB107" s="13">
-        <v>2</v>
-      </c>
-      <c r="AC107" s="13">
-        <v>3</v>
-      </c>
-      <c r="AD107" s="13">
-        <v>4</v>
-      </c>
-      <c r="AE107" s="13">
-        <v>3</v>
-      </c>
       <c r="AF107" s="13">
+        <v>3</v>
+      </c>
+      <c r="AG107" s="13">
         <v>5</v>
       </c>
-      <c r="AG107" s="13">
-        <v>1</v>
-      </c>
       <c r="AH107" s="13">
         <v>2</v>
       </c>
@@ -16692,10 +16692,10 @@
         <v>4</v>
       </c>
       <c r="AL107" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM107" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN107" s="13">
         <v>3</v>
@@ -16890,10 +16890,10 @@
         <v>3</v>
       </c>
       <c r="Q109" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R109" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S109" s="18">
         <v>4</v>
@@ -16932,13 +16932,13 @@
         <v>5</v>
       </c>
       <c r="AE109" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF109" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG109" s="18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH109" s="18">
         <v>3</v>
@@ -17026,13 +17026,13 @@
         <v>15</v>
       </c>
       <c r="P110" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q110" s="13" t="s">
         <v>7</v>
       </c>
       <c r="R110" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="S110" s="13" t="s">
         <v>16</v>
@@ -17044,10 +17044,10 @@
         <v>7</v>
       </c>
       <c r="V110" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="W110" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="X110" s="13" t="s">
         <v>15</v>
@@ -17071,13 +17071,13 @@
         <v>16</v>
       </c>
       <c r="AE110" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF110" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AG110" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AH110" s="13" t="s">
         <v>16</v>
@@ -17092,10 +17092,10 @@
         <v>15</v>
       </c>
       <c r="AL110" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AM110" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AN110" s="13" t="s">
         <v>16</v>
@@ -17151,10 +17151,10 @@
         <v>2</v>
       </c>
       <c r="Q111" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R111" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S111" s="13">
         <v>2</v>
@@ -17166,40 +17166,40 @@
         <v>3</v>
       </c>
       <c r="V111" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W111" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X111" s="13">
+        <v>3</v>
+      </c>
+      <c r="Y111" s="13">
+        <v>2</v>
+      </c>
+      <c r="Z111" s="13">
+        <v>3</v>
+      </c>
+      <c r="AA111" s="13">
+        <v>3</v>
+      </c>
+      <c r="AB111" s="13">
+        <v>4</v>
+      </c>
+      <c r="AC111" s="13">
+        <v>3</v>
+      </c>
+      <c r="AD111" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="13">
         <v>1</v>
       </c>
-      <c r="Y111" s="13">
-        <v>2</v>
-      </c>
-      <c r="Z111" s="13">
-        <v>3</v>
-      </c>
-      <c r="AA111" s="13">
-        <v>3</v>
-      </c>
-      <c r="AB111" s="13">
-        <v>4</v>
-      </c>
-      <c r="AC111" s="13">
-        <v>3</v>
-      </c>
-      <c r="AD111" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE111" s="13">
-        <v>2</v>
-      </c>
       <c r="AF111" s="13">
         <v>2</v>
       </c>
       <c r="AG111" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH111" s="13">
         <v>2</v>
@@ -17214,10 +17214,10 @@
         <v>5</v>
       </c>
       <c r="AL111" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM111" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN111" s="13">
         <v>4</v>
@@ -17349,10 +17349,10 @@
         <v>15</v>
       </c>
       <c r="AL112" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM112" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN112" s="18" t="s">
         <v>15</v>
@@ -17405,10 +17405,10 @@
         <v>3</v>
       </c>
       <c r="P113" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q113" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R113" s="18">
         <v>3</v>
@@ -17426,10 +17426,10 @@
         <v>2</v>
       </c>
       <c r="W113" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X113" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y113" s="18">
         <v>3</v>
@@ -17450,13 +17450,13 @@
         <v>4</v>
       </c>
       <c r="AE113" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF113" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG113" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH113" s="18">
         <v>3</v>
@@ -17471,10 +17471,10 @@
         <v>4</v>
       </c>
       <c r="AL113" s="18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AM113" s="18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN113" s="18">
         <v>3</v>
@@ -17558,10 +17558,10 @@
         <v>7</v>
       </c>
       <c r="V114" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="W114" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="X114" s="13" t="s">
         <v>16</v>
@@ -17585,13 +17585,13 @@
         <v>7</v>
       </c>
       <c r="AE114" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AF114" s="13" t="s">
         <v>7</v>
       </c>
       <c r="AG114" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AH114" s="13" t="s">
         <v>7</v>
@@ -17606,10 +17606,10 @@
         <v>16</v>
       </c>
       <c r="AL114" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AM114" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AN114" s="13" t="s">
         <v>7</v>
@@ -17665,10 +17665,10 @@
         <v>2</v>
       </c>
       <c r="Q115" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R115" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S115" s="13">
         <v>2</v>
@@ -17680,13 +17680,13 @@
         <v>2</v>
       </c>
       <c r="V115" s="13">
+        <v>4</v>
+      </c>
+      <c r="W115" s="13">
         <v>1</v>
       </c>
-      <c r="W115" s="13">
-        <v>2</v>
-      </c>
       <c r="X115" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y115" s="13">
         <v>2</v>
@@ -17707,13 +17707,13 @@
         <v>4</v>
       </c>
       <c r="AE115" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF115" s="13">
         <v>3</v>
       </c>
       <c r="AG115" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH115" s="13">
         <v>2</v>
@@ -17728,10 +17728,10 @@
         <v>4</v>
       </c>
       <c r="AL115" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM115" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN115" s="13">
         <v>3</v>
@@ -17928,10 +17928,10 @@
         <v>3</v>
       </c>
       <c r="Q117" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R117" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S117" s="19">
         <v>2</v>
@@ -17973,10 +17973,10 @@
         <v>3</v>
       </c>
       <c r="AF117" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG117" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH117" s="19">
         <v>3</v>
@@ -17991,10 +17991,10 @@
         <v>3</v>
       </c>
       <c r="AL117" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM117" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN117" s="19">
         <v>2</v>
@@ -18082,13 +18082,13 @@
         <v>7</v>
       </c>
       <c r="V118" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="W118" s="13" t="s">
         <v>7</v>
       </c>
       <c r="X118" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y118" s="13" t="s">
         <v>7</v>
@@ -18109,13 +18109,13 @@
         <v>7</v>
       </c>
       <c r="AE118" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AF118" s="13" t="s">
         <v>7</v>
       </c>
       <c r="AG118" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AH118" s="13" t="s">
         <v>7</v>
@@ -18130,10 +18130,10 @@
         <v>7</v>
       </c>
       <c r="AL118" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AM118" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AN118" s="13" t="s">
         <v>7</v>
@@ -18204,11 +18204,11 @@
         <v>2</v>
       </c>
       <c r="V119" s="13">
+        <v>2</v>
+      </c>
+      <c r="W119" s="13">
         <v>1</v>
       </c>
-      <c r="W119" s="13">
-        <v>2</v>
-      </c>
       <c r="X119" s="13">
         <v>2</v>
       </c>
@@ -18234,10 +18234,10 @@
         <v>2</v>
       </c>
       <c r="AF119" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG119" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH119" s="13">
         <v>2</v>
@@ -18252,10 +18252,10 @@
         <v>1</v>
       </c>
       <c r="AL119" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM119" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN119" s="13">
         <v>2</v>
@@ -18450,10 +18450,10 @@
         <v>2</v>
       </c>
       <c r="Q121" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R121" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S121" s="19">
         <v>2</v>
@@ -18465,40 +18465,40 @@
         <v>3</v>
       </c>
       <c r="V121" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W121" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X121" s="19">
+        <v>3</v>
+      </c>
+      <c r="Y121" s="19">
+        <v>3</v>
+      </c>
+      <c r="Z121" s="19">
+        <v>3</v>
+      </c>
+      <c r="AA121" s="19">
+        <v>2</v>
+      </c>
+      <c r="AB121" s="19">
+        <v>4</v>
+      </c>
+      <c r="AC121" s="19">
+        <v>3</v>
+      </c>
+      <c r="AD121" s="19">
+        <v>3</v>
+      </c>
+      <c r="AE121" s="19">
         <v>1</v>
       </c>
-      <c r="Y121" s="19">
-        <v>3</v>
-      </c>
-      <c r="Z121" s="19">
-        <v>3</v>
-      </c>
-      <c r="AA121" s="19">
-        <v>2</v>
-      </c>
-      <c r="AB121" s="19">
-        <v>4</v>
-      </c>
-      <c r="AC121" s="19">
-        <v>3</v>
-      </c>
-      <c r="AD121" s="19">
-        <v>3</v>
-      </c>
-      <c r="AE121" s="19">
-        <v>3</v>
-      </c>
       <c r="AF121" s="19">
         <v>3</v>
       </c>
       <c r="AG121" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH121" s="19">
         <v>3</v>
@@ -18586,13 +18586,13 @@
         <v>16</v>
       </c>
       <c r="P122" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q122" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="R122" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="S122" s="13" t="s">
         <v>15</v>
@@ -18607,10 +18607,10 @@
         <v>15</v>
       </c>
       <c r="W122" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X122" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y122" s="13" t="s">
         <v>15</v>
@@ -18631,13 +18631,13 @@
         <v>15</v>
       </c>
       <c r="AE122" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF122" s="13" t="s">
         <v>16</v>
       </c>
       <c r="AG122" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH122" s="13" t="s">
         <v>15</v>
@@ -18708,13 +18708,13 @@
         <v>2</v>
       </c>
       <c r="P123" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q123" s="13">
+        <v>2</v>
+      </c>
+      <c r="R123" s="13">
         <v>1</v>
-      </c>
-      <c r="Q123" s="13">
-        <v>2</v>
-      </c>
-      <c r="R123" s="13">
-        <v>2</v>
       </c>
       <c r="S123" s="13">
         <v>1</v>
@@ -18726,13 +18726,13 @@
         <v>2</v>
       </c>
       <c r="V123" s="13">
+        <v>3</v>
+      </c>
+      <c r="W123" s="13">
         <v>1</v>
       </c>
-      <c r="W123" s="13">
-        <v>2</v>
-      </c>
       <c r="X123" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y123" s="13">
         <v>2</v>
@@ -18753,13 +18753,13 @@
         <v>3</v>
       </c>
       <c r="AE123" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF123" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG123" s="13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH123" s="13">
         <v>1</v>
@@ -18774,10 +18774,10 @@
         <v>2</v>
       </c>
       <c r="AL123" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM123" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN123" s="13">
         <v>3</v>
@@ -18986,10 +18986,10 @@
         <v>3</v>
       </c>
       <c r="W125" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X125" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y125" s="19">
         <v>3</v>
@@ -19010,13 +19010,13 @@
         <v>4</v>
       </c>
       <c r="AE125" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF125" s="19">
         <v>2</v>
       </c>
       <c r="AG125" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH125" s="19">
         <v>3</v>
@@ -19031,10 +19031,10 @@
         <v>3</v>
       </c>
       <c r="AL125" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM125" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN125" s="19">
         <v>4</v>
@@ -19103,10 +19103,10 @@
         <v>16</v>
       </c>
       <c r="Q126" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R126" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="S126" s="13" t="s">
         <v>16</v>
@@ -19118,13 +19118,13 @@
         <v>16</v>
       </c>
       <c r="V126" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W126" s="13" t="s">
         <v>15</v>
       </c>
       <c r="X126" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y126" s="13" t="s">
         <v>15</v>
@@ -19148,10 +19148,10 @@
         <v>16</v>
       </c>
       <c r="AF126" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG126" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH126" s="13" t="s">
         <v>16</v>
@@ -19225,10 +19225,10 @@
         <v>2</v>
       </c>
       <c r="Q127" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R127" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S127" s="14">
         <v>2</v>
@@ -19240,13 +19240,13 @@
         <v>2</v>
       </c>
       <c r="V127" s="14">
+        <v>2</v>
+      </c>
+      <c r="W127" s="14">
         <v>1</v>
       </c>
-      <c r="W127" s="14">
-        <v>3</v>
-      </c>
       <c r="X127" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y127" s="14">
         <v>2</v>
@@ -19270,10 +19270,10 @@
         <v>2</v>
       </c>
       <c r="AF127" s="14">
+        <v>2</v>
+      </c>
+      <c r="AG127" s="14">
         <v>1</v>
-      </c>
-      <c r="AG127" s="14">
-        <v>2</v>
       </c>
       <c r="AH127" s="14">
         <v>2</v>
@@ -19488,10 +19488,10 @@
         <v>3</v>
       </c>
       <c r="Q129" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R129" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S129" s="18">
         <v>3</v>
@@ -19503,10 +19503,10 @@
         <v>3</v>
       </c>
       <c r="V129" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W129" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X129" s="18">
         <v>3</v>
@@ -19533,11 +19533,11 @@
         <v>3</v>
       </c>
       <c r="AF129" s="18">
+        <v>3</v>
+      </c>
+      <c r="AG129" s="18">
         <v>5</v>
       </c>
-      <c r="AG129" s="18">
-        <v>3</v>
-      </c>
       <c r="AH129" s="18">
         <v>3</v>
       </c>
@@ -19551,10 +19551,10 @@
         <v>2</v>
       </c>
       <c r="AL129" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM129" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN129" s="18">
         <v>4</v>
@@ -19746,13 +19746,13 @@
         <v>4</v>
       </c>
       <c r="P131" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q131" s="13">
         <v>2</v>
       </c>
       <c r="R131" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S131" s="13">
         <v>3</v>
@@ -19764,10 +19764,10 @@
         <v>3</v>
       </c>
       <c r="V131" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W131" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X131" s="13">
         <v>4</v>
@@ -19791,10 +19791,10 @@
         <v>3</v>
       </c>
       <c r="AE131" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF131" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG131" s="13">
         <v>4</v>
@@ -19856,11 +19856,15 @@
       <c r="F132" s="132" t="s">
         <v>69</v>
       </c>
-      <c r="G132" s="130"/>
-      <c r="H132" s="130"/>
+      <c r="G132" s="130">
+        <v>5</v>
+      </c>
+      <c r="H132" s="130">
+        <v>0</v>
+      </c>
       <c r="I132" s="136" t="str">
         <f t="shared" ref="I132" si="35">IF(G132="","-",IF(G132&gt;H132,"L",IF(G132=H132,"E",IF(G132&lt;H132,"V"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="J132" s="23" t="s">
         <v>7</v>
@@ -20003,13 +20007,13 @@
         <v>2</v>
       </c>
       <c r="P133" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q133" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R133" s="18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S133" s="18">
         <v>4</v>
@@ -20021,13 +20025,13 @@
         <v>3</v>
       </c>
       <c r="V133" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W133" s="18">
         <v>3</v>
       </c>
       <c r="X133" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y133" s="18">
         <v>3</v>
@@ -20051,10 +20055,10 @@
         <v>2</v>
       </c>
       <c r="AF133" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG133" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH133" s="18">
         <v>4</v>
@@ -20204,10 +20208,10 @@
         <v>7</v>
       </c>
       <c r="AL134" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AM134" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AN134" s="13" t="s">
         <v>7</v>
@@ -20263,10 +20267,10 @@
         <v>2</v>
       </c>
       <c r="Q135" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R135" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S135" s="13">
         <v>3</v>
@@ -20278,13 +20282,13 @@
         <v>3</v>
       </c>
       <c r="V135" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W135" s="13">
         <v>3</v>
       </c>
       <c r="X135" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y135" s="13">
         <v>3</v>
@@ -20305,31 +20309,31 @@
         <v>3</v>
       </c>
       <c r="AE135" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF135" s="13">
         <v>2</v>
       </c>
       <c r="AG135" s="13">
+        <v>2</v>
+      </c>
+      <c r="AH135" s="13">
+        <v>2</v>
+      </c>
+      <c r="AI135" s="13">
+        <v>4</v>
+      </c>
+      <c r="AJ135" s="13">
+        <v>2</v>
+      </c>
+      <c r="AK135" s="13">
+        <v>4</v>
+      </c>
+      <c r="AL135" s="13">
         <v>1</v>
       </c>
-      <c r="AH135" s="13">
-        <v>2</v>
-      </c>
-      <c r="AI135" s="13">
-        <v>4</v>
-      </c>
-      <c r="AJ135" s="13">
-        <v>2</v>
-      </c>
-      <c r="AK135" s="13">
-        <v>4</v>
-      </c>
-      <c r="AL135" s="13">
-        <v>2</v>
-      </c>
       <c r="AM135" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN135" s="13">
         <v>3</v>
@@ -20395,10 +20399,10 @@
         <v>16</v>
       </c>
       <c r="P136" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q136" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R136" s="18" t="s">
         <v>15</v>
@@ -20413,10 +20417,10 @@
         <v>16</v>
       </c>
       <c r="V136" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W136" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X136" s="18" t="s">
         <v>16</v>
@@ -20520,10 +20524,10 @@
         <v>2</v>
       </c>
       <c r="Q137" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R137" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S137" s="18">
         <v>4</v>
@@ -20535,13 +20539,13 @@
         <v>4</v>
       </c>
       <c r="V137" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W137" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X137" s="18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y137" s="18">
         <v>3</v>
@@ -20565,10 +20569,10 @@
         <v>2</v>
       </c>
       <c r="AF137" s="18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG137" s="18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH137" s="18">
         <v>3</v>
@@ -20583,10 +20587,10 @@
         <v>4</v>
       </c>
       <c r="AL137" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM137" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN137" s="18">
         <v>3</v>
@@ -20652,13 +20656,13 @@
         <v>16</v>
       </c>
       <c r="P138" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q138" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R138" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="S138" s="13" t="s">
         <v>7</v>
@@ -20670,13 +20674,13 @@
         <v>15</v>
       </c>
       <c r="V138" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="W138" s="13" t="s">
         <v>7</v>
       </c>
       <c r="X138" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y138" s="13" t="s">
         <v>7</v>
@@ -20697,13 +20701,13 @@
         <v>15</v>
       </c>
       <c r="AE138" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF138" s="13" t="s">
         <v>15</v>
       </c>
       <c r="AG138" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH138" s="13" t="s">
         <v>16</v>
@@ -20718,10 +20722,10 @@
         <v>15</v>
       </c>
       <c r="AL138" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AM138" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AN138" s="13" t="s">
         <v>16</v>
@@ -20792,13 +20796,13 @@
         <v>1</v>
       </c>
       <c r="V139" s="13">
+        <v>2</v>
+      </c>
+      <c r="W139" s="13">
         <v>1</v>
       </c>
-      <c r="W139" s="13">
-        <v>3</v>
-      </c>
       <c r="X139" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y139" s="13">
         <v>2</v>
@@ -20822,10 +20826,10 @@
         <v>2</v>
       </c>
       <c r="AF139" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG139" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH139" s="13">
         <v>2</v>
@@ -20915,10 +20919,10 @@
         <v>7</v>
       </c>
       <c r="P140" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q140" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R140" s="19" t="s">
         <v>7</v>
@@ -20933,10 +20937,10 @@
         <v>7</v>
       </c>
       <c r="V140" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="W140" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="X140" s="19" t="s">
         <v>7</v>
@@ -21040,10 +21044,10 @@
         <v>2</v>
       </c>
       <c r="Q141" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R141" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S141" s="19">
         <v>2</v>
@@ -21055,40 +21059,40 @@
         <v>3</v>
       </c>
       <c r="V141" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W141" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X141" s="19">
+        <v>3</v>
+      </c>
+      <c r="Y141" s="19">
+        <v>2</v>
+      </c>
+      <c r="Z141" s="19">
+        <v>2</v>
+      </c>
+      <c r="AA141" s="19">
+        <v>3</v>
+      </c>
+      <c r="AB141" s="19">
+        <v>4</v>
+      </c>
+      <c r="AC141" s="19">
+        <v>3</v>
+      </c>
+      <c r="AD141" s="19">
+        <v>3</v>
+      </c>
+      <c r="AE141" s="19">
         <v>1</v>
       </c>
-      <c r="Y141" s="19">
-        <v>2</v>
-      </c>
-      <c r="Z141" s="19">
-        <v>2</v>
-      </c>
-      <c r="AA141" s="19">
-        <v>3</v>
-      </c>
-      <c r="AB141" s="19">
-        <v>4</v>
-      </c>
-      <c r="AC141" s="19">
-        <v>3</v>
-      </c>
-      <c r="AD141" s="19">
-        <v>3</v>
-      </c>
-      <c r="AE141" s="19">
-        <v>3</v>
-      </c>
       <c r="AF141" s="19">
         <v>3</v>
       </c>
       <c r="AG141" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH141" s="19">
         <v>3</v>
@@ -21103,10 +21107,10 @@
         <v>5</v>
       </c>
       <c r="AL141" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM141" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN141" s="19">
         <v>2</v>
@@ -21179,10 +21183,10 @@
         <v>16</v>
       </c>
       <c r="Q142" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R142" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="S142" s="13" t="s">
         <v>7</v>
@@ -21194,13 +21198,13 @@
         <v>7</v>
       </c>
       <c r="V142" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="W142" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X142" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Y142" s="13" t="s">
         <v>7</v>
@@ -21242,10 +21246,10 @@
         <v>7</v>
       </c>
       <c r="AL142" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AM142" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AN142" s="13" t="s">
         <v>7</v>
@@ -21301,10 +21305,10 @@
         <v>2</v>
       </c>
       <c r="Q143" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R143" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S143" s="13">
         <v>2</v>
@@ -21316,10 +21320,10 @@
         <v>3</v>
       </c>
       <c r="V143" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W143" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X143" s="13">
         <v>1</v>
@@ -21343,13 +21347,13 @@
         <v>3</v>
       </c>
       <c r="AE143" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF143" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG143" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH143" s="13">
         <v>2</v>
@@ -21364,10 +21368,10 @@
         <v>3</v>
       </c>
       <c r="AL143" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM143" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN143" s="13">
         <v>3</v>
@@ -21408,11 +21412,15 @@
       <c r="F144" s="127" t="s">
         <v>72</v>
       </c>
-      <c r="G144" s="128"/>
-      <c r="H144" s="128"/>
+      <c r="G144" s="128">
+        <v>0</v>
+      </c>
+      <c r="H144" s="128">
+        <v>0</v>
+      </c>
       <c r="I144" s="125" t="str">
         <f t="shared" ref="I144" si="41">IF(G144="","-",IF(G144&gt;H144,"L",IF(G144=H144,"E",IF(G144&lt;H144,"V"))))</f>
-        <v>-</v>
+        <v>E</v>
       </c>
       <c r="J144" s="27" t="s">
         <v>7</v>
@@ -21499,10 +21507,10 @@
         <v>7</v>
       </c>
       <c r="AL144" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AM144" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AN144" s="19" t="s">
         <v>7</v>
@@ -21558,10 +21566,10 @@
         <v>2</v>
       </c>
       <c r="Q145" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R145" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S145" s="19">
         <v>2</v>
@@ -21600,13 +21608,13 @@
         <v>4</v>
       </c>
       <c r="AE145" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF145" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG145" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH145" s="19">
         <v>3</v>
@@ -21621,10 +21629,10 @@
         <v>4</v>
       </c>
       <c r="AL145" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM145" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN145" s="19">
         <v>3</v>
@@ -21665,11 +21673,15 @@
       <c r="F146" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="G146" s="128"/>
-      <c r="H146" s="128"/>
+      <c r="G146" s="128">
+        <v>0</v>
+      </c>
+      <c r="H146" s="128">
+        <v>1</v>
+      </c>
       <c r="I146" s="125" t="str">
         <f t="shared" ref="I146" si="42">IF(G146="","-",IF(G146&gt;H146,"L",IF(G146=H146,"E",IF(G146&lt;H146,"V"))))</f>
-        <v>-</v>
+        <v>V</v>
       </c>
       <c r="J146" s="26" t="s">
         <v>15</v>
@@ -21690,13 +21702,13 @@
         <v>15</v>
       </c>
       <c r="P146" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q146" s="13" t="s">
         <v>15</v>
       </c>
       <c r="R146" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S146" s="13" t="s">
         <v>15</v>
@@ -21756,10 +21768,10 @@
         <v>15</v>
       </c>
       <c r="AL146" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM146" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN146" s="13" t="s">
         <v>15</v>
@@ -21812,14 +21824,14 @@
         <v>2</v>
       </c>
       <c r="P147" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q147" s="13">
+        <v>3</v>
+      </c>
+      <c r="R147" s="13">
         <v>1</v>
       </c>
-      <c r="Q147" s="13">
-        <v>2</v>
-      </c>
-      <c r="R147" s="13">
-        <v>3</v>
-      </c>
       <c r="S147" s="13">
         <v>2</v>
       </c>
@@ -21830,58 +21842,58 @@
         <v>3</v>
       </c>
       <c r="V147" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W147" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X147" s="13">
+        <v>3</v>
+      </c>
+      <c r="Y147" s="13">
+        <v>2</v>
+      </c>
+      <c r="Z147" s="13">
+        <v>2</v>
+      </c>
+      <c r="AA147" s="13">
+        <v>3</v>
+      </c>
+      <c r="AB147" s="13">
+        <v>3</v>
+      </c>
+      <c r="AC147" s="13">
+        <v>3</v>
+      </c>
+      <c r="AD147" s="13">
+        <v>3</v>
+      </c>
+      <c r="AE147" s="13">
         <v>1</v>
       </c>
-      <c r="Y147" s="13">
-        <v>2</v>
-      </c>
-      <c r="Z147" s="13">
-        <v>2</v>
-      </c>
-      <c r="AA147" s="13">
-        <v>3</v>
-      </c>
-      <c r="AB147" s="13">
-        <v>3</v>
-      </c>
-      <c r="AC147" s="13">
-        <v>3</v>
-      </c>
-      <c r="AD147" s="13">
-        <v>3</v>
-      </c>
-      <c r="AE147" s="13">
-        <v>3</v>
-      </c>
       <c r="AF147" s="13">
         <v>3</v>
       </c>
       <c r="AG147" s="13">
+        <v>3</v>
+      </c>
+      <c r="AH147" s="13">
+        <v>2</v>
+      </c>
+      <c r="AI147" s="13">
+        <v>3</v>
+      </c>
+      <c r="AJ147" s="13">
+        <v>2</v>
+      </c>
+      <c r="AK147" s="13">
+        <v>4</v>
+      </c>
+      <c r="AL147" s="13">
         <v>1</v>
       </c>
-      <c r="AH147" s="13">
-        <v>2</v>
-      </c>
-      <c r="AI147" s="13">
-        <v>3</v>
-      </c>
-      <c r="AJ147" s="13">
-        <v>2</v>
-      </c>
-      <c r="AK147" s="13">
-        <v>4</v>
-      </c>
-      <c r="AL147" s="13">
-        <v>2</v>
-      </c>
       <c r="AM147" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN147" s="13">
         <v>4</v>
@@ -22072,10 +22084,10 @@
         <v>2</v>
       </c>
       <c r="Q149" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R149" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S149" s="19">
         <v>3</v>
@@ -22117,10 +22129,10 @@
         <v>3</v>
       </c>
       <c r="AF149" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG149" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH149" s="19">
         <v>3</v>
@@ -22135,10 +22147,10 @@
         <v>3</v>
       </c>
       <c r="AL149" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM149" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN149" s="19">
         <v>4</v>
@@ -22252,10 +22264,10 @@
         <v>7</v>
       </c>
       <c r="AF150" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AG150" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AH150" s="13" t="s">
         <v>7</v>
@@ -22347,10 +22359,10 @@
         <v>2</v>
       </c>
       <c r="W151" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X151" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y151" s="14">
         <v>2</v>
@@ -22371,13 +22383,13 @@
         <v>3</v>
       </c>
       <c r="AE151" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF151" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG151" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH151" s="14">
         <v>3</v>
@@ -22392,10 +22404,10 @@
         <v>2</v>
       </c>
       <c r="AL151" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM151" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN151" s="14">
         <v>4</v>
@@ -22427,7 +22439,7 @@
       <c r="H152" s="138"/>
       <c r="I152" s="5">
         <f>SUM(G8:H151)</f>
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="J152" s="51">
         <f>SUM(J79,J77,J75,J73,J71,J69,J67,J65,J63,J61,J59,J57,J55,J53,J51,J49,J47,J45,J43,J41,J39,J37,J35,J33,J31,J29,J27,J25,J23,J21,J19,J17,J15,J13,J11,J9,J81,J83,J85,J87,J89,J91,J93,J95,J97,J99,J101,J103,J105,J107,J109,J111,J113,J115,J117,J119,J121,J123,J125,J127,J129,J131,J133,J135,J137,J139,J141,J143,J145,J147,J149,J151)</f>
@@ -22455,15 +22467,15 @@
       </c>
       <c r="P152" s="15">
         <f>SUM(P79,P77,P75,P73,P71,P69,P67,P65,P63,P61,P59,P57,P55,P53,P51,P49,P47,P45,P43,P41,P39,P37,P35,P33,P31,P29,P27,P25,P23,P21,P19,P17,P15,P13,P11,P9,P81,P83,P85,P87,P89,P91,P93,P95,P97,P99,P101,P103,P105,P107,P109,P111,P113,P115,P117,P119,P121,P123,P125,P127,P129,P131,P133,P135,P137,P139,P141,P143,P145,P147,P149,P151)</f>
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="Q152" s="15">
         <f>SUM(Q79,Q77,Q75,Q73,Q71,Q69,Q67,Q65,Q63,Q61,Q59,Q57,Q55,Q53,Q51,Q49,Q47,Q45,Q43,Q41,Q39,Q37,Q35,Q33,Q31,Q29,Q27,Q25,Q23,Q21,Q19,Q17,Q15,Q13,Q11,Q9,Q81,Q83,Q85,Q87,Q89,Q91,Q93,Q95,Q97,Q99,Q101,Q103,Q105,Q107,Q109,Q111,Q113,Q115,Q117,Q119,Q121,Q123,Q125,Q127,Q129,Q131,Q133,Q135,Q137,Q139,Q141,Q143,Q145,Q147,Q149,Q151)</f>
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="R152" s="15">
         <f>SUM(R79,R77,R75,R73,R71,R69,R67,R65,R63,R61,R59,R57,R55,R53,R51,R49,R47,R45,R43,R41,R39,R37,R35,R33,R31,R29,R27,R25,R23,R21,R19,R17,R15,R13,R11,R9,R81,R83,R85,R87,R89,R91,R93,R95,R97,R99,R101,R103,R105,R107,R109,R111,R113,R115,R117,R119,R121,R123,R125,R127,R129,R131,R133,R135,R137,R139,R141,R143,R145,R147,R149,R151)</f>
-        <v>201</v>
+        <v>154</v>
       </c>
       <c r="S152" s="15">
         <f>SUM(S79,S77,S75,S73,S71,S69,S67,S65,S63,S61,S59,S57,S55,S53,S51,S49,S47,S45,S43,S41,S39,S37,S35,S33,S31,S29,S27,S25,S23,S21,S19,S17,S15,S13,S11,S9,S81,S83,S85,S87,S89,S91,S93,S95,S97,S99,S101,S103,S105,S107,S109,S111,S113,S115,S117,S119,S121,S123,S125,S127,S129,S131,S133,S135,S137,S139,S141,S143,S145,S147,S149,S151)</f>
@@ -22479,15 +22491,15 @@
       </c>
       <c r="V152" s="15">
         <f>SUM(V79,V77,V75,V73,V71,V69,V67,V65,V63,V61,V59,V57,V55,V53,V51,V49,V47,V45,V43,V41,V39,V37,V35,V33,V31,V29,V27,V25,V23,V21,V19,V17,V15,V13,V11,V9,V81,V83,V85,V87,V89,V91,V93,V95,V97,V99,V101,V103,V105,V107,V109,V111,V113,V115,V117,V119,V121,V123,V125,V127,V129,V131,V133,V135,V137,V139,V141,V143,V145,V147,V149,V151)</f>
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="W152" s="15">
         <f>SUM(W79,W77,W75,W73,W71,W69,W67,W65,W63,W61,W59,W57,W55,W53,W51,W49,W47,W45,W43,W41,W39,W37,W35,W33,W31,W29,W27,W25,W23,W21,W19,W17,W15,W13,W11,W9,W81,W83,W85,W87,W89,W91,W93,W95,W97,W99,W101,W103,W105,W107,W109,W111,W113,W115,W117,W119,W121,W123,W125,W127,W129,W131,W133,W135,W137,W139,W141,W143,W145,W147,W149,W151)</f>
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="X152" s="15">
         <f>SUM(X79,X77,X75,X73,X71,X69,X67,X65,X63,X61,X59,X57,X55,X53,X51,X49,X47,X45,X43,X41,X39,X37,X35,X33,X31,X29,X27,X25,X23,X21,X19,X17,X15,X13,X11,X9,X81,X83,X85,X87,X89,X91,X93,X95,X97,X99,X101,X103,X105,X107,X109,X111,X113,X115,X117,X119,X121,X123,X125,X127,X129,X131,X133,X135,X137,X139,X141,X143,X145,X147,X149,X151)</f>
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="Y152" s="15">
         <f>SUM(Y79,Y77,Y75,Y73,Y71,Y69,Y67,Y65,Y63,Y61,Y59,Y57,Y55,Y53,Y51,Y49,Y47,Y45,Y43,Y41,Y39,Y37,Y35,Y33,Y31,Y29,Y27,Y25,Y23,Y21,Y19,Y17,Y15,Y13,Y11,Y9,Y81,Y83,Y85,Y87,Y89,Y91,Y93,Y95,Y97,Y99,Y101,Y103,Y105,Y107,Y109,Y111,Y113,Y115,Y117,Y119,Y121,Y123,Y125,Y127,Y129,Y131,Y133,Y135,Y137,Y139,Y141,Y143,Y145,Y147,Y149,Y151)</f>
@@ -22515,15 +22527,15 @@
       </c>
       <c r="AE152" s="15">
         <f>SUM(AE79,AE77,AE75,AE73,AE71,AE69,AE67,AE65,AE63,AE61,AE59,AE57,AE55,AE53,AE51,AE49,AE47,AE45,AE43,AE41,AE39,AE37,AE35,AE33,AE31,AE29,AE27,AE25,AE23,AE21,AE19,AE17,AE15,AE13,AE11,AE9,AE81,AE83,AE85,AE87,AE89,AE91,AE93,AE95,AE97,AE99,AE101,AE103,AE105,AE107,AE109,AE111,AE113,AE115,AE117,AE119,AE121,AE123,AE125,AE127,AE129,AE131,AE133,AE135,AE137,AE139,AE141,AE143,AE145,AE147,AE149,AE151)</f>
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="AF152" s="15">
         <f>SUM(AF79,AF77,AF75,AF73,AF71,AF69,AF67,AF65,AF63,AF61,AF59,AF57,AF55,AF53,AF51,AF49,AF47,AF45,AF43,AF41,AF39,AF37,AF35,AF33,AF31,AF29,AF27,AF25,AF23,AF21,AF19,AF17,AF15,AF13,AF11,AF9,AF81,AF83,AF85,AF87,AF89,AF91,AF93,AF95,AF97,AF99,AF101,AF103,AF105,AF107,AF109,AF111,AF113,AF115,AF117,AF119,AF121,AF123,AF125,AF127,AF129,AF131,AF133,AF135,AF137,AF139,AF141,AF143,AF145,AF147,AF149,AF151)</f>
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="AG152" s="15">
         <f>SUM(AG79,AG77,AG75,AG73,AG71,AG69,AG67,AG65,AG63,AG61,AG59,AG57,AG55,AG53,AG51,AG49,AG47,AG45,AG43,AG41,AG39,AG37,AG35,AG33,AG31,AG29,AG27,AG25,AG23,AG21,AG19,AG17,AG15,AG13,AG11,AG9,AG81,AG83,AG85,AG87,AG89,AG91,AG93,AG95,AG97,AG99,AG101,AG103,AG105,AG107,AG109,AG111,AG113,AG115,AG117,AG119,AG121,AG123,AG125,AG127,AG129,AG131,AG133,AG135,AG137,AG139,AG141,AG143,AG145,AG147,AG149,AG151)</f>
-        <v>159</v>
+        <v>222</v>
       </c>
       <c r="AH152" s="15">
         <f>SUM(AH79,AH77,AH75,AH73,AH71,AH69,AH67,AH65,AH63,AH61,AH59,AH57,AH55,AH53,AH51,AH49,AH47,AH45,AH43,AH41,AH39,AH37,AH35,AH33,AH31,AH29,AH27,AH25,AH23,AH21,AH19,AH17,AH15,AH13,AH11,AH9,AH81,AH83,AH85,AH87,AH89,AH91,AH93,AH95,AH97,AH99,AH101,AH103,AH105,AH107,AH109,AH111,AH113,AH115,AH117,AH119,AH121,AH123,AH125,AH127,AH129,AH131,AH133,AH135,AH137,AH139,AH141,AH143,AH145,AH147,AH149,AH151)</f>
@@ -22587,151 +22599,151 @@
       <c r="I153" s="139"/>
       <c r="J153" s="31">
         <f>SUM(J154:J157)</f>
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="K153" s="32">
         <f>SUM(K154:K157)</f>
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L153" s="32">
         <f>SUM(L154:L157)</f>
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="M153" s="32">
         <f>SUM(M154:M157)</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N153" s="32">
         <f>SUM(N154:N157)</f>
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="O153" s="32">
         <f>SUM(O154:O157)</f>
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="P153" s="32">
         <f>SUM(P154:P157)</f>
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Q153" s="32">
         <f>SUM(Q154:Q157)</f>
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="R153" s="32">
         <f>SUM(R154:R157)</f>
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="S153" s="32">
         <f>SUM(S154:S157)</f>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="T153" s="32">
         <f>SUM(T154:T157)</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="U153" s="32">
         <f>SUM(U154:U157)</f>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="V153" s="32">
         <f>SUM(V154:V157)</f>
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="W153" s="32">
         <f>SUM(W154:W157)</f>
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="X153" s="32">
         <f>SUM(X154:X157)</f>
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="Y153" s="32">
         <f>SUM(Y154:Y157)</f>
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="Z153" s="32">
         <f>SUM(Z154:Z157)</f>
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AA153" s="32">
         <f>SUM(AA154:AA157)</f>
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AB153" s="32">
         <f>SUM(AB154:AB157)</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AC153" s="32">
         <f>SUM(AC154:AC157)</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AD153" s="32">
         <f>SUM(AD154:AD157)</f>
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AE153" s="32">
         <f>SUM(AE154:AE157)</f>
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="AF153" s="32">
         <f>SUM(AF154:AF157)</f>
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="AG153" s="32">
         <f>SUM(AG154:AG157)</f>
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="AH153" s="32">
         <f>SUM(AH154:AH157)</f>
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="AI153" s="32">
         <f>SUM(AI154:AI157)</f>
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="AJ153" s="32">
         <f>SUM(AJ154:AJ157)</f>
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="AK153" s="32">
         <f>SUM(AK154:AK157)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL153" s="32">
         <f>SUM(AL154:AL157)</f>
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="AM153" s="32">
         <f>SUM(AM154:AM157)</f>
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="AN153" s="32">
         <f>SUM(AN154:AN157)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AO153" s="32">
         <f>SUM(AO154:AO157)</f>
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="AP153" s="32">
         <f>SUM(AP154:AP157)</f>
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="AQ153" s="32">
         <f>SUM(AQ154:AQ157)</f>
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AR153" s="32">
         <f>SUM(AR154:AR157)</f>
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="AS153" s="32">
         <f>SUM(AS154:AS157)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AT153" s="33">
         <f>SUM(AT154:AT157)</f>
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154" spans="1:46" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.3">
@@ -22741,7 +22753,7 @@
       <c r="I154" s="3"/>
       <c r="J154" s="4">
         <f>IF(J152=$I$152,100,IF($I$152-J152=1,99,IF($I$152-J152=-1,99,IF($I$152-J152=2,98,IF($I$152-J152=-2,98,IF($I$152-J152=3,97,IF($I$152-J152=-3,97,IF($I$152-J152=4,96,IF($I$152-J152=-4,96,IF($I$152-J152=5,95,IF($I$152-J152=-5,95,IF($I$152-J152=6,94,IF($I$152-J152=-6,94,IF($I$152-J152=7,93,IF($I$152-J152=-7,93,IF($I$152-J152=8,92,IF($I$152-J152=-8,92,IF($I$152-J152=9,91,IF($I$152-J152=-9,91,IF($I$152-J152=10,90,IF($I$152-J152=-10,90,IF($I$152-J152=11,89,IF($I$152-J152=-11,89,IF($I$152-J152=12,88,IF($I$152-J152=-12,88,IF($I$152-J152=13,87,IF($I$152-J152=-13,87,IF($I$152-J152=14,86,IF($I$152-J152=-14,86,IF($I$152-J152=15,85,IF($I$152-J152=-15,85,IF($I$152-J152=16,84,IF($I$152-J152=-16,84,IF($I$152-J152=17,83,IF($I$152-J152=-17,83,IF($I$152-J152=18,82,IF($I$152-J152=-18,82,IF($I$152-J152=19,81,IF($I$152-J152=-19,81,IF($I$152-J152=20,80,IF($I$152-J152=-20,80,IF($I$152-J152=21,79,IF($I$152-J152=-21,79,IF($I$152-J152=22,78,IF($I$152-J152=-22,78,IF($I$152-J152=23,77,IF($I$152-J152=-23,77,IF($I$152-J152=24,76,IF($I$152-J152=-24,76,IF($I$152-J152=25,75,IF($I$152-J152=-25,75,IF($I$152-J152=26,74,IF($I$152-J152=-26,74,IF($I$152-J152=27,73,IF($I$152-J152=-27,73,IF($I$152-J152=28,72,IF($I$152-J152=-28,72,IF($I$152-J152=29,71,IF($I$152-J152=-29,71,IF($I$152-J152=30,70,IF($I$152-J152=-30,70,IF($I$152-J152=31,69,IF($I$152-J152=-31,69,IF($I$152-J152=32,68,IF($I$152-J152=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="K154" s="4">
         <f t="shared" ref="K154:AL154" si="45">IF(K152=$I$152,100,IF($I$152-K152=1,99,IF($I$152-K152=-1,99,IF($I$152-K152=2,98,IF($I$152-K152=-2,98,IF($I$152-K152=3,97,IF($I$152-K152=-3,97,IF($I$152-K152=4,96,IF($I$152-K152=-4,96,IF($I$152-K152=5,95,IF($I$152-K152=-5,95,IF($I$152-K152=6,94,IF($I$152-K152=-6,94,IF($I$152-K152=7,93,IF($I$152-K152=-7,93,IF($I$152-K152=8,92,IF($I$152-K152=-8,92,IF($I$152-K152=9,91,IF($I$152-K152=-9,91,IF($I$152-K152=10,90,IF($I$152-K152=-10,90,IF($I$152-K152=11,89,IF($I$152-K152=-11,89,IF($I$152-K152=12,88,IF($I$152-K152=-12,88,IF($I$152-K152=13,87,IF($I$152-K152=-13,87,IF($I$152-K152=14,86,IF($I$152-K152=-14,86,IF($I$152-K152=15,85,IF($I$152-K152=-15,85,IF($I$152-K152=16,84,IF($I$152-K152=-16,84,IF($I$152-K152=17,83,IF($I$152-K152=-17,83,IF($I$152-K152=18,82,IF($I$152-K152=-18,82,IF($I$152-K152=19,81,IF($I$152-K152=-19,81,IF($I$152-K152=20,80,IF($I$152-K152=-20,80,IF($I$152-K152=21,79,IF($I$152-K152=-21,79,IF($I$152-K152=22,78,IF($I$152-K152=-22,78,IF($I$152-K152=23,77,IF($I$152-K152=-23,77,IF($I$152-K152=24,76,IF($I$152-K152=-24,76,IF($I$152-K152=25,75,IF($I$152-K152=-25,75,IF($I$152-K152=26,74,IF($I$152-K152=-26,74,IF($I$152-K152=27,73,IF($I$152-K152=-27,73,IF($I$152-K152=28,72,IF($I$152-K152=-28,72,IF($I$152-K152=29,71,IF($I$152-K152=-29,71,IF($I$152-K152=30,70,IF($I$152-K152=-30,70,IF($I$152-K152=31,69,IF($I$152-K152=-31,69,IF($I$152-K152=32,68,IF($I$152-K152=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
@@ -22765,15 +22777,15 @@
       </c>
       <c r="P154" s="4">
         <f t="shared" si="45"/>
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Q154" s="4">
         <f t="shared" si="45"/>
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="R154" s="4">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="S154" s="4">
         <f t="shared" si="45"/>
@@ -22789,15 +22801,15 @@
       </c>
       <c r="V154" s="4">
         <f t="shared" ref="V154:X154" si="46">IF(V152=$I$152,100,IF($I$152-V152=1,99,IF($I$152-V152=-1,99,IF($I$152-V152=2,98,IF($I$152-V152=-2,98,IF($I$152-V152=3,97,IF($I$152-V152=-3,97,IF($I$152-V152=4,96,IF($I$152-V152=-4,96,IF($I$152-V152=5,95,IF($I$152-V152=-5,95,IF($I$152-V152=6,94,IF($I$152-V152=-6,94,IF($I$152-V152=7,93,IF($I$152-V152=-7,93,IF($I$152-V152=8,92,IF($I$152-V152=-8,92,IF($I$152-V152=9,91,IF($I$152-V152=-9,91,IF($I$152-V152=10,90,IF($I$152-V152=-10,90,IF($I$152-V152=11,89,IF($I$152-V152=-11,89,IF($I$152-V152=12,88,IF($I$152-V152=-12,88,IF($I$152-V152=13,87,IF($I$152-V152=-13,87,IF($I$152-V152=14,86,IF($I$152-V152=-14,86,IF($I$152-V152=15,85,IF($I$152-V152=-15,85,IF($I$152-V152=16,84,IF($I$152-V152=-16,84,IF($I$152-V152=17,83,IF($I$152-V152=-17,83,IF($I$152-V152=18,82,IF($I$152-V152=-18,82,IF($I$152-V152=19,81,IF($I$152-V152=-19,81,IF($I$152-V152=20,80,IF($I$152-V152=-20,80,IF($I$152-V152=21,79,IF($I$152-V152=-21,79,IF($I$152-V152=22,78,IF($I$152-V152=-22,78,IF($I$152-V152=23,77,IF($I$152-V152=-23,77,IF($I$152-V152=24,76,IF($I$152-V152=-24,76,IF($I$152-V152=25,75,IF($I$152-V152=-25,75,IF($I$152-V152=26,74,IF($I$152-V152=-26,74,IF($I$152-V152=27,73,IF($I$152-V152=-27,73,IF($I$152-V152=28,72,IF($I$152-V152=-28,72,IF($I$152-V152=29,71,IF($I$152-V152=-29,71,IF($I$152-V152=30,70,IF($I$152-V152=-30,70,IF($I$152-V152=31,69,IF($I$152-V152=-31,69,IF($I$152-V152=32,68,IF($I$152-V152=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="W154" s="4">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X154" s="4">
         <f t="shared" si="46"/>
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="Y154" s="4">
         <f t="shared" si="45"/>
@@ -22825,7 +22837,7 @@
       </c>
       <c r="AE154" s="4">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AF154" s="4">
         <f t="shared" si="45"/>
@@ -22833,7 +22845,7 @@
       </c>
       <c r="AG154" s="4">
         <f t="shared" si="45"/>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AH154" s="4">
         <f t="shared" si="45"/>
@@ -22841,7 +22853,7 @@
       </c>
       <c r="AI154" s="4">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AJ154" s="4">
         <f t="shared" si="45"/>
@@ -22853,11 +22865,11 @@
       </c>
       <c r="AL154" s="4">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AM154" s="4">
         <f t="shared" ref="AM154:AP154" si="47">IF(AM152=$I$152,100,IF($I$152-AM152=1,99,IF($I$152-AM152=-1,99,IF($I$152-AM152=2,98,IF($I$152-AM152=-2,98,IF($I$152-AM152=3,97,IF($I$152-AM152=-3,97,IF($I$152-AM152=4,96,IF($I$152-AM152=-4,96,IF($I$152-AM152=5,95,IF($I$152-AM152=-5,95,IF($I$152-AM152=6,94,IF($I$152-AM152=-6,94,IF($I$152-AM152=7,93,IF($I$152-AM152=-7,93,IF($I$152-AM152=8,92,IF($I$152-AM152=-8,92,IF($I$152-AM152=9,91,IF($I$152-AM152=-9,91,IF($I$152-AM152=10,90,IF($I$152-AM152=-10,90,IF($I$152-AM152=11,89,IF($I$152-AM152=-11,89,IF($I$152-AM152=12,88,IF($I$152-AM152=-12,88,IF($I$152-AM152=13,87,IF($I$152-AM152=-13,87,IF($I$152-AM152=14,86,IF($I$152-AM152=-14,86,IF($I$152-AM152=15,85,IF($I$152-AM152=-15,85,IF($I$152-AM152=16,84,IF($I$152-AM152=-16,84,IF($I$152-AM152=17,83,IF($I$152-AM152=-17,83,IF($I$152-AM152=18,82,IF($I$152-AM152=-18,82,IF($I$152-AM152=19,81,IF($I$152-AM152=-19,81,IF($I$152-AM152=20,80,IF($I$152-AM152=-20,80,IF($I$152-AM152=21,79,IF($I$152-AM152=-21,79,IF($I$152-AM152=22,78,IF($I$152-AM152=-22,78,IF($I$152-AM152=23,77,IF($I$152-AM152=-23,77,IF($I$152-AM152=24,76,IF($I$152-AM152=-24,76,IF($I$152-AM152=25,75,IF($I$152-AM152=-25,75,IF($I$152-AM152=26,74,IF($I$152-AM152=-26,74,IF($I$152-AM152=27,73,IF($I$152-AM152=-27,73,IF($I$152-AM152=28,72,IF($I$152-AM152=-28,72,IF($I$152-AM152=29,71,IF($I$152-AM152=-29,71,IF($I$152-AM152=30,70,IF($I$152-AM152=-30,70,IF($I$152-AM152=31,69,IF($I$152-AM152=-31,69,IF($I$152-AM152=32,68,IF($I$152-AM152=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AN154" s="4">
         <f t="shared" si="47"/>
@@ -22865,11 +22877,11 @@
       </c>
       <c r="AO154" s="4">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AP154" s="4">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AQ154" s="4">
         <f t="shared" ref="AQ154:AT154" si="48">IF(AQ152=$I$152,100,IF($I$152-AQ152=1,99,IF($I$152-AQ152=-1,99,IF($I$152-AQ152=2,98,IF($I$152-AQ152=-2,98,IF($I$152-AQ152=3,97,IF($I$152-AQ152=-3,97,IF($I$152-AQ152=4,96,IF($I$152-AQ152=-4,96,IF($I$152-AQ152=5,95,IF($I$152-AQ152=-5,95,IF($I$152-AQ152=6,94,IF($I$152-AQ152=-6,94,IF($I$152-AQ152=7,93,IF($I$152-AQ152=-7,93,IF($I$152-AQ152=8,92,IF($I$152-AQ152=-8,92,IF($I$152-AQ152=9,91,IF($I$152-AQ152=-9,91,IF($I$152-AQ152=10,90,IF($I$152-AQ152=-10,90,IF($I$152-AQ152=11,89,IF($I$152-AQ152=-11,89,IF($I$152-AQ152=12,88,IF($I$152-AQ152=-12,88,IF($I$152-AQ152=13,87,IF($I$152-AQ152=-13,87,IF($I$152-AQ152=14,86,IF($I$152-AQ152=-14,86,IF($I$152-AQ152=15,85,IF($I$152-AQ152=-15,85,IF($I$152-AQ152=16,84,IF($I$152-AQ152=-16,84,IF($I$152-AQ152=17,83,IF($I$152-AQ152=-17,83,IF($I$152-AQ152=18,82,IF($I$152-AQ152=-18,82,IF($I$152-AQ152=19,81,IF($I$152-AQ152=-19,81,IF($I$152-AQ152=20,80,IF($I$152-AQ152=-20,80,IF($I$152-AQ152=21,79,IF($I$152-AQ152=-21,79,IF($I$152-AQ152=22,78,IF($I$152-AQ152=-22,78,IF($I$152-AQ152=23,77,IF($I$152-AQ152=-23,77,IF($I$152-AQ152=24,76,IF($I$152-AQ152=-24,76,IF($I$152-AQ152=25,75,IF($I$152-AQ152=-25,75,IF($I$152-AQ152=26,74,IF($I$152-AQ152=-26,74,IF($I$152-AQ152=27,73,IF($I$152-AQ152=-27,73,IF($I$152-AQ152=28,72,IF($I$152-AQ152=-28,72,IF($I$152-AQ152=29,71,IF($I$152-AQ152=-29,71,IF($I$152-AQ152=30,70,IF($I$152-AQ152=-30,70,IF($I$152-AQ152=31,69,IF($I$152-AQ152=-31,69,IF($I$152-AQ152=32,68,IF($I$152-AQ152=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
@@ -22877,7 +22889,7 @@
       </c>
       <c r="AR154" s="4">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AS154" s="4">
         <f t="shared" si="48"/>
@@ -22895,27 +22907,27 @@
       <c r="I155" s="3"/>
       <c r="J155" s="4">
         <f>IF($I$152-J152=33,67,IF($I$152-J152=-33,67,IF($I$152-J152=34,66,IF($I$152-J152=-34,66,IF($I$152-J152=35,65,IF($I$152-J152=-35,65,IF($I$152-J152=36,64,IF($I$152-J152=-36,64,IF($I$152-J152=37,63,IF($I$152-J152=-37,63,IF($I$152-J152=38,62,IF($I$152-J152=-38,62,IF($I$152-J152=39,61,IF($I$152-J152=-39,61,IF($I$152-J152=40,60,IF($I$152-J152=-40,60,IF($I$152-J152=41,59,IF($I$152-J152=-41,59,IF($I$152-J152=42,58,IF($I$152-J152=-42,58,IF($I$152-J152=43,57,IF($I$152-J152=-43,57,IF($I$152-J152=44,56,IF($I$152-J152=-44,56,IF($I$152-J152=45,55,IF($I$152-J152=-45,55,IF($I$152-J152=46,54,IF($I$152-J152=-46,54,IF($I$152-J152=47,53,IF($I$152-J152=-47,53,IF($I$152-J152=48,52,IF($I$152-J152=-48,52,IF($I$152-J152=49,51,IF($I$152-J152=-49,51,IF($I$152-J152=50,50,IF($I$152-J152=-50,50,IF($I$152-J152=51,49,IF($I$152-J152=-51,49,IF($I$152-J152=52,48,IF($I$152-J152=-52,48,IF($I$152-J152=53,47,IF($I$152-J152=-53,47,IF($I$152-J152=54,46,IF($I$152-J152=-54,46,IF($I$152-J152=55,45,IF($I$152-J152=-55,45,IF($I$152-J152=56,44,IF($I$152-J152=-56,44,IF($I$152-J152=57,43,IF($I$152-J152=-57,43,IF($I$152-J152=58,42,IF($I$152-J152=-58,42,IF($I$152-J152=59,41,IF($I$152-J152=-59,41,IF($I$152-J152=60,40,IF($I$152-J152=-60,40,IF($I$152-J152=61,39,IF($I$152-J152=-61,39,IF($I$152-J152=62,38,IF($I$152-J152=-62,38,IF($I$152-J152=63,37,IF($I$152-J152=-63,37,IF($I$152-J152=64,36,IF($I$152-J152=-64,36,IF($I$152-J152=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="K155" s="4">
         <f t="shared" ref="K155:AL155" si="49">IF($I$152-K152=33,67,IF($I$152-K152=-33,67,IF($I$152-K152=34,66,IF($I$152-K152=-34,66,IF($I$152-K152=35,65,IF($I$152-K152=-35,65,IF($I$152-K152=36,64,IF($I$152-K152=-36,64,IF($I$152-K152=37,63,IF($I$152-K152=-37,63,IF($I$152-K152=38,62,IF($I$152-K152=-38,62,IF($I$152-K152=39,61,IF($I$152-K152=-39,61,IF($I$152-K152=40,60,IF($I$152-K152=-40,60,IF($I$152-K152=41,59,IF($I$152-K152=-41,59,IF($I$152-K152=42,58,IF($I$152-K152=-42,58,IF($I$152-K152=43,57,IF($I$152-K152=-43,57,IF($I$152-K152=44,56,IF($I$152-K152=-44,56,IF($I$152-K152=45,55,IF($I$152-K152=-45,55,IF($I$152-K152=46,54,IF($I$152-K152=-46,54,IF($I$152-K152=47,53,IF($I$152-K152=-47,53,IF($I$152-K152=48,52,IF($I$152-K152=-48,52,IF($I$152-K152=49,51,IF($I$152-K152=-49,51,IF($I$152-K152=50,50,IF($I$152-K152=-50,50,IF($I$152-K152=51,49,IF($I$152-K152=-51,49,IF($I$152-K152=52,48,IF($I$152-K152=-52,48,IF($I$152-K152=53,47,IF($I$152-K152=-53,47,IF($I$152-K152=54,46,IF($I$152-K152=-54,46,IF($I$152-K152=55,45,IF($I$152-K152=-55,45,IF($I$152-K152=56,44,IF($I$152-K152=-56,44,IF($I$152-K152=57,43,IF($I$152-K152=-57,43,IF($I$152-K152=58,42,IF($I$152-K152=-58,42,IF($I$152-K152=59,41,IF($I$152-K152=-59,41,IF($I$152-K152=60,40,IF($I$152-K152=-60,40,IF($I$152-K152=61,39,IF($I$152-K152=-61,39,IF($I$152-K152=62,38,IF($I$152-K152=-62,38,IF($I$152-K152=63,37,IF($I$152-K152=-63,37,IF($I$152-K152=64,36,IF($I$152-K152=-64,36,IF($I$152-K152=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L155" s="4">
         <f t="shared" si="49"/>
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="M155" s="4">
         <f t="shared" si="49"/>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N155" s="4">
         <f t="shared" si="49"/>
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="O155" s="4">
         <f t="shared" si="49"/>
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="P155" s="4">
         <f t="shared" si="49"/>
@@ -22923,7 +22935,7 @@
       </c>
       <c r="Q155" s="4">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="R155" s="4">
         <f t="shared" si="49"/>
@@ -22931,39 +22943,39 @@
       </c>
       <c r="S155" s="4">
         <f t="shared" si="49"/>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="T155" s="4">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="U155" s="4">
         <f t="shared" si="49"/>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="V155" s="4">
         <f t="shared" ref="V155:X155" si="50">IF($I$152-V152=33,67,IF($I$152-V152=-33,67,IF($I$152-V152=34,66,IF($I$152-V152=-34,66,IF($I$152-V152=35,65,IF($I$152-V152=-35,65,IF($I$152-V152=36,64,IF($I$152-V152=-36,64,IF($I$152-V152=37,63,IF($I$152-V152=-37,63,IF($I$152-V152=38,62,IF($I$152-V152=-38,62,IF($I$152-V152=39,61,IF($I$152-V152=-39,61,IF($I$152-V152=40,60,IF($I$152-V152=-40,60,IF($I$152-V152=41,59,IF($I$152-V152=-41,59,IF($I$152-V152=42,58,IF($I$152-V152=-42,58,IF($I$152-V152=43,57,IF($I$152-V152=-43,57,IF($I$152-V152=44,56,IF($I$152-V152=-44,56,IF($I$152-V152=45,55,IF($I$152-V152=-45,55,IF($I$152-V152=46,54,IF($I$152-V152=-46,54,IF($I$152-V152=47,53,IF($I$152-V152=-47,53,IF($I$152-V152=48,52,IF($I$152-V152=-48,52,IF($I$152-V152=49,51,IF($I$152-V152=-49,51,IF($I$152-V152=50,50,IF($I$152-V152=-50,50,IF($I$152-V152=51,49,IF($I$152-V152=-51,49,IF($I$152-V152=52,48,IF($I$152-V152=-52,48,IF($I$152-V152=53,47,IF($I$152-V152=-53,47,IF($I$152-V152=54,46,IF($I$152-V152=-54,46,IF($I$152-V152=55,45,IF($I$152-V152=-55,45,IF($I$152-V152=56,44,IF($I$152-V152=-56,44,IF($I$152-V152=57,43,IF($I$152-V152=-57,43,IF($I$152-V152=58,42,IF($I$152-V152=-58,42,IF($I$152-V152=59,41,IF($I$152-V152=-59,41,IF($I$152-V152=60,40,IF($I$152-V152=-60,40,IF($I$152-V152=61,39,IF($I$152-V152=-61,39,IF($I$152-V152=62,38,IF($I$152-V152=-62,38,IF($I$152-V152=63,37,IF($I$152-V152=-63,37,IF($I$152-V152=64,36,IF($I$152-V152=-64,36,IF($I$152-V152=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="W155" s="4">
         <f t="shared" si="50"/>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="X155" s="4">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="Y155" s="4">
         <f t="shared" si="49"/>
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="Z155" s="4">
         <f t="shared" si="49"/>
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AA155" s="4">
         <f t="shared" si="49"/>
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AB155" s="4">
         <f t="shared" si="49"/>
@@ -22971,7 +22983,7 @@
       </c>
       <c r="AC155" s="4">
         <f t="shared" si="49"/>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AD155" s="4">
         <f t="shared" si="49"/>
@@ -22979,11 +22991,11 @@
       </c>
       <c r="AE155" s="4">
         <f t="shared" si="49"/>
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="AF155" s="4">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AG155" s="4">
         <f t="shared" si="49"/>
@@ -22991,15 +23003,15 @@
       </c>
       <c r="AH155" s="4">
         <f t="shared" si="49"/>
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="AI155" s="4">
         <f t="shared" si="49"/>
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="AJ155" s="4">
         <f t="shared" si="49"/>
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="AK155" s="4">
         <f t="shared" si="49"/>
@@ -23007,11 +23019,11 @@
       </c>
       <c r="AL155" s="4">
         <f t="shared" si="49"/>
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM155" s="4">
         <f t="shared" ref="AM155:AP155" si="51">IF($I$152-AM152=33,67,IF($I$152-AM152=-33,67,IF($I$152-AM152=34,66,IF($I$152-AM152=-34,66,IF($I$152-AM152=35,65,IF($I$152-AM152=-35,65,IF($I$152-AM152=36,64,IF($I$152-AM152=-36,64,IF($I$152-AM152=37,63,IF($I$152-AM152=-37,63,IF($I$152-AM152=38,62,IF($I$152-AM152=-38,62,IF($I$152-AM152=39,61,IF($I$152-AM152=-39,61,IF($I$152-AM152=40,60,IF($I$152-AM152=-40,60,IF($I$152-AM152=41,59,IF($I$152-AM152=-41,59,IF($I$152-AM152=42,58,IF($I$152-AM152=-42,58,IF($I$152-AM152=43,57,IF($I$152-AM152=-43,57,IF($I$152-AM152=44,56,IF($I$152-AM152=-44,56,IF($I$152-AM152=45,55,IF($I$152-AM152=-45,55,IF($I$152-AM152=46,54,IF($I$152-AM152=-46,54,IF($I$152-AM152=47,53,IF($I$152-AM152=-47,53,IF($I$152-AM152=48,52,IF($I$152-AM152=-48,52,IF($I$152-AM152=49,51,IF($I$152-AM152=-49,51,IF($I$152-AM152=50,50,IF($I$152-AM152=-50,50,IF($I$152-AM152=51,49,IF($I$152-AM152=-51,49,IF($I$152-AM152=52,48,IF($I$152-AM152=-52,48,IF($I$152-AM152=53,47,IF($I$152-AM152=-53,47,IF($I$152-AM152=54,46,IF($I$152-AM152=-54,46,IF($I$152-AM152=55,45,IF($I$152-AM152=-55,45,IF($I$152-AM152=56,44,IF($I$152-AM152=-56,44,IF($I$152-AM152=57,43,IF($I$152-AM152=-57,43,IF($I$152-AM152=58,42,IF($I$152-AM152=-58,42,IF($I$152-AM152=59,41,IF($I$152-AM152=-59,41,IF($I$152-AM152=60,40,IF($I$152-AM152=-60,40,IF($I$152-AM152=61,39,IF($I$152-AM152=-61,39,IF($I$152-AM152=62,38,IF($I$152-AM152=-62,38,IF($I$152-AM152=63,37,IF($I$152-AM152=-63,37,IF($I$152-AM152=64,36,IF($I$152-AM152=-64,36,IF($I$152-AM152=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AN155" s="4">
         <f t="shared" si="51"/>
@@ -23019,19 +23031,19 @@
       </c>
       <c r="AO155" s="4">
         <f t="shared" si="51"/>
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="AP155" s="4">
         <f t="shared" si="51"/>
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="AQ155" s="4">
         <f t="shared" ref="AQ155:AT155" si="52">IF($I$152-AQ152=33,67,IF($I$152-AQ152=-33,67,IF($I$152-AQ152=34,66,IF($I$152-AQ152=-34,66,IF($I$152-AQ152=35,65,IF($I$152-AQ152=-35,65,IF($I$152-AQ152=36,64,IF($I$152-AQ152=-36,64,IF($I$152-AQ152=37,63,IF($I$152-AQ152=-37,63,IF($I$152-AQ152=38,62,IF($I$152-AQ152=-38,62,IF($I$152-AQ152=39,61,IF($I$152-AQ152=-39,61,IF($I$152-AQ152=40,60,IF($I$152-AQ152=-40,60,IF($I$152-AQ152=41,59,IF($I$152-AQ152=-41,59,IF($I$152-AQ152=42,58,IF($I$152-AQ152=-42,58,IF($I$152-AQ152=43,57,IF($I$152-AQ152=-43,57,IF($I$152-AQ152=44,56,IF($I$152-AQ152=-44,56,IF($I$152-AQ152=45,55,IF($I$152-AQ152=-45,55,IF($I$152-AQ152=46,54,IF($I$152-AQ152=-46,54,IF($I$152-AQ152=47,53,IF($I$152-AQ152=-47,53,IF($I$152-AQ152=48,52,IF($I$152-AQ152=-48,52,IF($I$152-AQ152=49,51,IF($I$152-AQ152=-49,51,IF($I$152-AQ152=50,50,IF($I$152-AQ152=-50,50,IF($I$152-AQ152=51,49,IF($I$152-AQ152=-51,49,IF($I$152-AQ152=52,48,IF($I$152-AQ152=-52,48,IF($I$152-AQ152=53,47,IF($I$152-AQ152=-53,47,IF($I$152-AQ152=54,46,IF($I$152-AQ152=-54,46,IF($I$152-AQ152=55,45,IF($I$152-AQ152=-55,45,IF($I$152-AQ152=56,44,IF($I$152-AQ152=-56,44,IF($I$152-AQ152=57,43,IF($I$152-AQ152=-57,43,IF($I$152-AQ152=58,42,IF($I$152-AQ152=-58,42,IF($I$152-AQ152=59,41,IF($I$152-AQ152=-59,41,IF($I$152-AQ152=60,40,IF($I$152-AQ152=-60,40,IF($I$152-AQ152=61,39,IF($I$152-AQ152=-61,39,IF($I$152-AQ152=62,38,IF($I$152-AQ152=-62,38,IF($I$152-AQ152=63,37,IF($I$152-AQ152=-63,37,IF($I$152-AQ152=64,36,IF($I$152-AQ152=-64,36,IF($I$152-AQ152=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AR155" s="4">
         <f t="shared" si="52"/>
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="AS155" s="4">
         <f t="shared" si="52"/>
@@ -23081,7 +23093,7 @@
       </c>
       <c r="R156" s="4">
         <f t="shared" si="53"/>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="S156" s="4">
         <f t="shared" si="53"/>
@@ -23089,7 +23101,7 @@
       </c>
       <c r="T156" s="4">
         <f t="shared" si="53"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="U156" s="4">
         <f t="shared" si="53"/>
@@ -23121,7 +23133,7 @@
       </c>
       <c r="AB156" s="4">
         <f t="shared" si="53"/>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AC156" s="4">
         <f t="shared" si="53"/>
@@ -23129,7 +23141,7 @@
       </c>
       <c r="AD156" s="4">
         <f t="shared" si="53"/>
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AE156" s="4">
         <f t="shared" si="53"/>
@@ -23137,11 +23149,11 @@
       </c>
       <c r="AF156" s="4">
         <f t="shared" si="53"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG156" s="4">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH156" s="4">
         <f t="shared" si="53"/>
@@ -23169,7 +23181,7 @@
       </c>
       <c r="AN156" s="4">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AO156" s="4">
         <f t="shared" si="55"/>
@@ -23189,11 +23201,11 @@
       </c>
       <c r="AS156" s="4">
         <f t="shared" si="56"/>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AT156" s="4">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157" spans="1:46" x14ac:dyDescent="0.3">
@@ -23311,7 +23323,7 @@
       </c>
       <c r="AK157" s="4">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL157" s="4">
         <f t="shared" si="57"/>
@@ -23323,7 +23335,7 @@
       </c>
       <c r="AN157" s="4">
         <f t="shared" si="59"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO157" s="4">
         <f t="shared" si="59"/>
@@ -23347,7 +23359,7 @@
       </c>
       <c r="AT157" s="4">
         <f t="shared" si="60"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.3">

--- a/Copa del Mundo-2026 trabajo.xlsx
+++ b/Copa del Mundo-2026 trabajo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_corporativa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B96018D8-DE5F-4E85-AA31-98D2E2DE2118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{B96018D8-DE5F-4E85-AA31-98D2E2DE2118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C931DD41-88D8-429E-877A-96437234049F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA 2026" sheetId="3" r:id="rId1"/>
@@ -2155,6 +2155,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -2446,22 +2450,22 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:BB181"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" style="56" customWidth="1"/>
-    <col min="7" max="8" width="6.140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" style="2" customWidth="1"/>
-    <col min="10" max="46" width="5.28515625" style="2" customWidth="1"/>
-    <col min="47" max="52" width="11.42578125" style="2"/>
-    <col min="53" max="54" width="11.42578125" style="2" customWidth="1"/>
-    <col min="55" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="8.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" style="56" customWidth="1"/>
+    <col min="7" max="8" width="6.109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" style="2" customWidth="1"/>
+    <col min="10" max="46" width="5.33203125" style="2" customWidth="1"/>
+    <col min="47" max="52" width="11.44140625" style="2"/>
+    <col min="53" max="54" width="11.44140625" style="2" customWidth="1"/>
+    <col min="55" max="16384" width="11.44140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="109" t="s">
         <v>28</v>
       </c>
@@ -2585,7 +2589,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:54" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:54" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -2709,7 +2713,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="1:54" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:54" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="58" t="s">
         <v>0</v>
       </c>
@@ -2884,7 +2888,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:54" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:54" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="60"/>
       <c r="B4" s="60"/>
       <c r="C4" s="60"/>
@@ -3044,7 +3048,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:54" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:54" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="63"/>
       <c r="B5" s="63"/>
       <c r="C5" s="63"/>
@@ -3203,7 +3207,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:54" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:54" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="60"/>
       <c r="B6" s="60"/>
       <c r="C6" s="60"/>
@@ -3362,7 +3366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:54" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:54" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="60"/>
       <c r="B7" s="60"/>
       <c r="C7" s="60"/>
@@ -3521,7 +3525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="134" t="s">
         <v>1</v>
       </c>
@@ -3662,7 +3666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="134"/>
       <c r="B9" s="102"/>
       <c r="C9" s="102"/>
@@ -3790,7 +3794,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="134"/>
       <c r="B10" s="101">
         <v>46184</v>
@@ -3935,7 +3939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="134"/>
       <c r="B11" s="102"/>
       <c r="C11" s="102"/>
@@ -4063,7 +4067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="134"/>
       <c r="B12" s="101">
         <v>46191</v>
@@ -4206,7 +4210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="134"/>
       <c r="B13" s="102"/>
       <c r="C13" s="102"/>
@@ -4332,7 +4336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="134"/>
       <c r="B14" s="101">
         <v>46191</v>
@@ -4475,7 +4479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="134"/>
       <c r="B15" s="102"/>
       <c r="C15" s="102"/>
@@ -4601,7 +4605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="134"/>
       <c r="B16" s="101">
         <v>46197</v>
@@ -4744,7 +4748,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="134"/>
       <c r="B17" s="102"/>
       <c r="C17" s="102"/>
@@ -4870,7 +4874,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="134"/>
       <c r="B18" s="101">
         <v>46197</v>
@@ -5013,7 +5017,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="135"/>
       <c r="B19" s="102"/>
       <c r="C19" s="102"/>
@@ -5139,7 +5143,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="157" t="s">
         <v>2</v>
       </c>
@@ -5284,7 +5288,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="158"/>
       <c r="B21" s="118"/>
       <c r="C21" s="118"/>
@@ -5410,7 +5414,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="158"/>
       <c r="B22" s="117">
         <v>46186</v>
@@ -5553,7 +5557,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="158"/>
       <c r="B23" s="118"/>
       <c r="C23" s="118"/>
@@ -5679,7 +5683,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="158"/>
       <c r="B24" s="117">
         <v>46191</v>
@@ -5822,7 +5826,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="158"/>
       <c r="B25" s="118"/>
       <c r="C25" s="118"/>
@@ -5948,7 +5952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="158"/>
       <c r="B26" s="117">
         <v>46191</v>
@@ -6091,7 +6095,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="158"/>
       <c r="B27" s="118"/>
       <c r="C27" s="118"/>
@@ -6217,7 +6221,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="158"/>
       <c r="B28" s="117">
         <v>46197</v>
@@ -6360,7 +6364,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="158"/>
       <c r="B29" s="118"/>
       <c r="C29" s="118"/>
@@ -6486,7 +6490,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="158"/>
       <c r="B30" s="117">
         <v>46197</v>
@@ -6629,7 +6633,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="159"/>
       <c r="B31" s="118"/>
       <c r="C31" s="118"/>
@@ -6751,7 +6755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:54" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="133" t="s">
         <v>3</v>
       </c>
@@ -6892,7 +6896,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="134"/>
       <c r="B33" s="102"/>
       <c r="C33" s="102"/>
@@ -7014,7 +7018,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="134"/>
       <c r="B34" s="101">
         <v>46186</v>
@@ -7153,7 +7157,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="134"/>
       <c r="B35" s="102"/>
       <c r="C35" s="102"/>
@@ -7275,7 +7279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="134"/>
       <c r="B36" s="101">
         <v>46192</v>
@@ -7414,7 +7418,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="134"/>
       <c r="B37" s="102"/>
       <c r="C37" s="102"/>
@@ -7536,7 +7540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="134"/>
       <c r="B38" s="101">
         <v>46192</v>
@@ -7675,7 +7679,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="134"/>
       <c r="B39" s="102"/>
       <c r="C39" s="102"/>
@@ -7797,7 +7801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="134"/>
       <c r="B40" s="152">
         <v>46197</v>
@@ -7936,7 +7940,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="134"/>
       <c r="B41" s="149"/>
       <c r="C41" s="149"/>
@@ -8058,7 +8062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="134"/>
       <c r="B42" s="101">
         <v>46197</v>
@@ -8197,7 +8201,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="135"/>
       <c r="B43" s="102"/>
       <c r="C43" s="102"/>
@@ -8319,7 +8323,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="157" t="s">
         <v>4</v>
       </c>
@@ -8460,7 +8464,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="158"/>
       <c r="B45" s="118"/>
       <c r="C45" s="118"/>
@@ -8582,7 +8586,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="158"/>
       <c r="B46" s="117">
         <v>46186</v>
@@ -8721,7 +8725,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="158"/>
       <c r="B47" s="118"/>
       <c r="C47" s="118"/>
@@ -8843,7 +8847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="158"/>
       <c r="B48" s="117">
         <v>46192</v>
@@ -8982,7 +8986,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="158"/>
       <c r="B49" s="118"/>
       <c r="C49" s="118"/>
@@ -9104,7 +9108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="158"/>
       <c r="B50" s="117">
         <v>46192</v>
@@ -9243,7 +9247,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="158"/>
       <c r="B51" s="118"/>
       <c r="C51" s="118"/>
@@ -9365,7 +9369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="158"/>
       <c r="B52" s="117">
         <v>46198</v>
@@ -9504,7 +9508,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="158"/>
       <c r="B53" s="118"/>
       <c r="C53" s="118"/>
@@ -9626,7 +9630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="158"/>
       <c r="B54" s="164">
         <v>46198</v>
@@ -9765,7 +9769,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="159"/>
       <c r="B55" s="147"/>
       <c r="C55" s="147"/>
@@ -9887,7 +9891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="133" t="s">
         <v>16</v>
       </c>
@@ -10028,7 +10032,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="134"/>
       <c r="B57" s="102"/>
       <c r="C57" s="102"/>
@@ -10150,7 +10154,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="134"/>
       <c r="B58" s="101">
         <v>46187</v>
@@ -10289,7 +10293,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="134"/>
       <c r="B59" s="102"/>
       <c r="C59" s="102"/>
@@ -10411,7 +10415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="134"/>
       <c r="B60" s="101">
         <v>46193</v>
@@ -10550,7 +10554,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="134"/>
       <c r="B61" s="102"/>
       <c r="C61" s="102"/>
@@ -10672,7 +10676,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="134"/>
       <c r="B62" s="101">
         <v>46193</v>
@@ -10811,7 +10815,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="134"/>
       <c r="B63" s="102"/>
       <c r="C63" s="102"/>
@@ -10933,7 +10937,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="134"/>
       <c r="B64" s="101">
         <v>46198</v>
@@ -11072,7 +11076,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="134"/>
       <c r="B65" s="102"/>
       <c r="C65" s="102"/>
@@ -11194,7 +11198,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="134"/>
       <c r="B66" s="101">
         <v>46198</v>
@@ -11333,7 +11337,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="135"/>
       <c r="B67" s="102"/>
       <c r="C67" s="102"/>
@@ -11455,7 +11459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="157" t="s">
         <v>21</v>
       </c>
@@ -11596,7 +11600,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="158"/>
       <c r="B69" s="118"/>
       <c r="C69" s="118"/>
@@ -11718,7 +11722,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="158"/>
       <c r="B70" s="117">
         <v>46187</v>
@@ -11857,7 +11861,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="158"/>
       <c r="B71" s="118"/>
       <c r="C71" s="118"/>
@@ -11979,7 +11983,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="158"/>
       <c r="B72" s="117">
         <v>46193</v>
@@ -12118,7 +12122,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="158"/>
       <c r="B73" s="118"/>
       <c r="C73" s="118"/>
@@ -12240,7 +12244,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="158"/>
       <c r="B74" s="117">
         <v>46193</v>
@@ -12379,7 +12383,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="158"/>
       <c r="B75" s="118"/>
       <c r="C75" s="118"/>
@@ -12501,7 +12505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="158"/>
       <c r="B76" s="117">
         <v>46198</v>
@@ -12640,7 +12644,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="158"/>
       <c r="B77" s="118"/>
       <c r="C77" s="118"/>
@@ -12762,7 +12766,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="158"/>
       <c r="B78" s="117">
         <v>46198</v>
@@ -12901,7 +12905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="159"/>
       <c r="B79" s="118"/>
       <c r="C79" s="118"/>
@@ -13023,7 +13027,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="133" t="s">
         <v>47</v>
       </c>
@@ -13164,7 +13168,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="134"/>
       <c r="B81" s="102"/>
       <c r="C81" s="102"/>
@@ -13286,7 +13290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="134"/>
       <c r="B82" s="101">
         <v>46188</v>
@@ -13425,7 +13429,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="134"/>
       <c r="B83" s="102"/>
       <c r="C83" s="102"/>
@@ -13547,7 +13551,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="134"/>
       <c r="B84" s="101">
         <v>46194</v>
@@ -13686,7 +13690,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="134"/>
       <c r="B85" s="102"/>
       <c r="C85" s="102"/>
@@ -13808,7 +13812,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="134"/>
       <c r="B86" s="101">
         <v>46194</v>
@@ -13947,7 +13951,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="134"/>
       <c r="B87" s="102"/>
       <c r="C87" s="102"/>
@@ -14069,7 +14073,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="134"/>
       <c r="B88" s="101">
         <v>46199</v>
@@ -14208,7 +14212,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="89" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="134"/>
       <c r="B89" s="102"/>
       <c r="C89" s="102"/>
@@ -14330,7 +14334,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="134"/>
       <c r="B90" s="101">
         <v>46199</v>
@@ -14469,7 +14473,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="135"/>
       <c r="B91" s="102"/>
       <c r="C91" s="102"/>
@@ -14591,7 +14595,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="157" t="s">
         <v>48</v>
       </c>
@@ -14732,7 +14736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="158"/>
       <c r="B93" s="118"/>
       <c r="C93" s="118"/>
@@ -14854,7 +14858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="158"/>
       <c r="B94" s="117">
         <v>46188</v>
@@ -14993,7 +14997,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="158"/>
       <c r="B95" s="118"/>
       <c r="C95" s="118"/>
@@ -15115,7 +15119,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="158"/>
       <c r="B96" s="117">
         <v>46194</v>
@@ -15254,7 +15258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="158"/>
       <c r="B97" s="118"/>
       <c r="C97" s="118"/>
@@ -15376,7 +15380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="158"/>
       <c r="B98" s="117">
         <v>46194</v>
@@ -15515,7 +15519,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="158"/>
       <c r="B99" s="118"/>
       <c r="C99" s="118"/>
@@ -15637,7 +15641,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="158"/>
       <c r="B100" s="117">
         <v>46199</v>
@@ -15776,7 +15780,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="158"/>
       <c r="B101" s="118"/>
       <c r="C101" s="118"/>
@@ -15898,7 +15902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="158"/>
       <c r="B102" s="117">
         <v>46199</v>
@@ -16037,7 +16041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="159"/>
       <c r="B103" s="118"/>
       <c r="C103" s="118"/>
@@ -16159,7 +16163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="133" t="s">
         <v>49</v>
       </c>
@@ -16300,7 +16304,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="134"/>
       <c r="B105" s="102"/>
       <c r="C105" s="102"/>
@@ -16422,7 +16426,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="134"/>
       <c r="B106" s="101">
         <v>46189</v>
@@ -16561,7 +16565,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="134"/>
       <c r="B107" s="102"/>
       <c r="C107" s="102"/>
@@ -16683,7 +16687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="134"/>
       <c r="B108" s="101">
         <v>46195</v>
@@ -16822,7 +16826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="134"/>
       <c r="B109" s="102"/>
       <c r="C109" s="102"/>
@@ -16944,7 +16948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="134"/>
       <c r="B110" s="101">
         <v>46195</v>
@@ -17083,7 +17087,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:46" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="134"/>
       <c r="B111" s="102"/>
       <c r="C111" s="102"/>
@@ -17205,7 +17209,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="134"/>
       <c r="B112" s="101">
         <v>46199</v>
@@ -17344,7 +17348,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="134"/>
       <c r="B113" s="102"/>
       <c r="C113" s="102"/>
@@ -17466,7 +17470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="134"/>
       <c r="B114" s="101">
         <v>46199</v>
@@ -17605,7 +17609,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="135"/>
       <c r="B115" s="102"/>
       <c r="C115" s="102"/>
@@ -17727,7 +17731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="157" t="s">
         <v>50</v>
       </c>
@@ -17868,7 +17872,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="158"/>
       <c r="B117" s="118"/>
       <c r="C117" s="118"/>
@@ -17990,7 +17994,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="158"/>
       <c r="B118" s="117">
         <v>46189</v>
@@ -18129,7 +18133,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="158"/>
       <c r="B119" s="118"/>
       <c r="C119" s="118"/>
@@ -18251,7 +18255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="158"/>
       <c r="B120" s="117">
         <v>46195</v>
@@ -18390,7 +18394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="121" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="158"/>
       <c r="B121" s="118"/>
       <c r="C121" s="118"/>
@@ -18512,7 +18516,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="158"/>
       <c r="B122" s="117">
         <v>46195</v>
@@ -18651,7 +18655,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="158"/>
       <c r="B123" s="118"/>
       <c r="C123" s="118"/>
@@ -18773,7 +18777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="158"/>
       <c r="B124" s="117">
         <v>46200</v>
@@ -18912,7 +18916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="125" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="158"/>
       <c r="B125" s="118"/>
       <c r="C125" s="118"/>
@@ -19034,7 +19038,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="158"/>
       <c r="B126" s="117">
         <v>46200</v>
@@ -19173,7 +19177,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="159"/>
       <c r="B127" s="118"/>
       <c r="C127" s="118"/>
@@ -19295,7 +19299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="133" t="s">
         <v>51</v>
       </c>
@@ -19436,7 +19440,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="134"/>
       <c r="B129" s="102"/>
       <c r="C129" s="102"/>
@@ -19558,7 +19562,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="134"/>
       <c r="B130" s="101">
         <v>46190</v>
@@ -19697,7 +19701,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="134"/>
       <c r="B131" s="102"/>
       <c r="C131" s="102"/>
@@ -19819,7 +19823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="134"/>
       <c r="B132" s="101">
         <v>46196</v>
@@ -19958,7 +19962,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="133" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="134"/>
       <c r="B133" s="102"/>
       <c r="C133" s="102"/>
@@ -20080,7 +20084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="134"/>
       <c r="B134" s="101">
         <v>46196</v>
@@ -20219,7 +20223,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="135" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="134"/>
       <c r="B135" s="102"/>
       <c r="C135" s="102"/>
@@ -20341,7 +20345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="134"/>
       <c r="B136" s="101">
         <v>46200</v>
@@ -20480,7 +20484,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="137" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="134"/>
       <c r="B137" s="102"/>
       <c r="C137" s="102"/>
@@ -20602,7 +20606,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="134"/>
       <c r="B138" s="101">
         <v>46200</v>
@@ -20741,7 +20745,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="135"/>
       <c r="B139" s="102"/>
       <c r="C139" s="102"/>
@@ -20863,7 +20867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="157" t="s">
         <v>7</v>
       </c>
@@ -21004,7 +21008,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="141" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="158"/>
       <c r="B141" s="118"/>
       <c r="C141" s="118"/>
@@ -21126,7 +21130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="158"/>
       <c r="B142" s="117">
         <v>46190</v>
@@ -21265,7 +21269,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="143" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="158"/>
       <c r="B143" s="118"/>
       <c r="C143" s="118"/>
@@ -21387,7 +21391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="158"/>
       <c r="B144" s="117">
         <v>46196</v>
@@ -21526,7 +21530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="145" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="158"/>
       <c r="B145" s="118"/>
       <c r="C145" s="118"/>
@@ -21648,7 +21652,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="158"/>
       <c r="B146" s="117">
         <v>46196</v>
@@ -21787,7 +21791,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="158"/>
       <c r="B147" s="118"/>
       <c r="C147" s="118"/>
@@ -21909,7 +21913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="158"/>
       <c r="B148" s="117">
         <v>46200</v>
@@ -22048,7 +22052,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="149" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="158"/>
       <c r="B149" s="118"/>
       <c r="C149" s="118"/>
@@ -22170,7 +22174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="158"/>
       <c r="B150" s="117">
         <v>46200</v>
@@ -22309,7 +22313,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="151" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="159"/>
       <c r="B151" s="118"/>
       <c r="C151" s="118"/>
@@ -22431,7 +22435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:46" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F152" s="160" t="s">
         <v>10</v>
       </c>
@@ -22590,7 +22594,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="153" spans="1:46" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:46" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F153" s="131" t="s">
         <v>14</v>
       </c>
@@ -22746,7 +22750,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="154" spans="1:46" ht="19.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:46" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.3">
       <c r="F154" s="57"/>
       <c r="G154" s="3"/>
       <c r="H154" s="3"/>
@@ -22900,7 +22904,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="155" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:46" x14ac:dyDescent="0.3">
       <c r="F155" s="57"/>
       <c r="G155" s="3"/>
       <c r="H155" s="3"/>
@@ -23054,7 +23058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:46" x14ac:dyDescent="0.3">
       <c r="F156" s="57"/>
       <c r="G156" s="3"/>
       <c r="H156" s="3"/>
@@ -23208,7 +23212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:46" x14ac:dyDescent="0.3">
       <c r="F157" s="57"/>
       <c r="G157" s="3"/>
       <c r="H157" s="3"/>
@@ -23362,28 +23366,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E158" s="161"/>
       <c r="F158" s="161"/>
       <c r="G158" s="161"/>
       <c r="H158" s="161"/>
       <c r="I158" s="3"/>
     </row>
-    <row r="159" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E159" s="161"/>
       <c r="F159" s="161"/>
       <c r="G159" s="161"/>
       <c r="H159" s="161"/>
       <c r="I159" s="3"/>
     </row>
-    <row r="160" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:46" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E160" s="161"/>
       <c r="F160" s="161"/>
       <c r="G160" s="161"/>
       <c r="H160" s="161"/>
       <c r="I160" s="3"/>
     </row>
-    <row r="181" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J181" s="2">
         <v>1</v>
       </c>
@@ -24017,17 +24021,17 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A2:K76"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>8</v>
       </c>
@@ -24058,7 +24062,7 @@
         <v>SUMA(Y($G$8="",$H$8="",J9=0)+Y($G$10="",$H$10="",J11=0)+Y($G$12="",$H$12="",J13=0)+Y($G$14="",$H$14="",J15=0)+Y($G$16="",$H$16="",J17=0)+Y($G$18="",$H$18="",J19=0)+Y($G$20="",$H$20="",J21=0)+Y($G$22="",$H$22="",J23=0)+Y($G$24="",$H$24="",J25=0)+Y($G$26="",$H$26="",J27=0)+Y($G$28="",$H$28="",J29=0)+Y($G$30="",$H$30="",J31=0)+Y($G$32="",$H$32="",J33=0)+Y($G$34="",$H$34="",J35=0)+Y($G$36="",$H$36="",J37=0)+Y($G$38="",$H$38="",J39=0)+Y($G$40="",$H$40="",J41=0)+Y($G$42="",$H$42="",J43=0)+Y($G$44="",$H$44="",J45=0)+Y($G$46="",$H$46="",J47=0)+Y($G$48="",$H$48="",J49=0)+Y($G$50="",$H$50="",J51=0)+Y($G$52="",$H$52="",J53=0)+Y($G$54="",$H$54="",J55=0)+Y($G$56="",$H$56="",J57=0)+Y($G$58="",$H$58="",J59=0)+Y($G$60="",$H$60="",J61=0)+Y($G$62="",$H$62="",J63=0)+Y($G$64="",$H$64="",J65=0)+Y($G$66="",$H$66="",J67=0)+Y($G$68="",$H$68="",J69=0)+Y($G$70="",$H$70="",J71=0)+Y($G$72="",$H$72="",J73=0)+Y($G$74="",$H$74="",J75=0)+Y($G$76="",$H$76="",J77=0)+Y($G$78="",$H$78="",J79=0)+</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>10</v>
       </c>
@@ -24088,7 +24092,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>12</v>
       </c>
@@ -24115,7 +24119,7 @@
         <v>Y($G$12="",$H$12="",J13=0)+</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>14</v>
       </c>
@@ -24142,7 +24146,7 @@
         <v>Y($G$14="",$H$14="",J15=0)+</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>16</v>
       </c>
@@ -24169,7 +24173,7 @@
         <v>Y($G$16="",$H$16="",J17=0)+</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>18</v>
       </c>
@@ -24196,7 +24200,7 @@
         <v>Y($G$18="",$H$18="",J19=0)+</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>20</v>
       </c>
@@ -24223,7 +24227,7 @@
         <v>Y($G$20="",$H$20="",J21=0)+</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>22</v>
       </c>
@@ -24250,7 +24254,7 @@
         <v>Y($G$22="",$H$22="",J23=0)+</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>24</v>
       </c>
@@ -24277,7 +24281,7 @@
         <v>Y($G$24="",$H$24="",J25=0)+</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26</v>
       </c>
@@ -24304,7 +24308,7 @@
         <v>Y($G$26="",$H$26="",J27=0)+</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>28</v>
       </c>
@@ -24331,7 +24335,7 @@
         <v>Y($G$28="",$H$28="",J29=0)+</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>30</v>
       </c>
@@ -24358,7 +24362,7 @@
         <v>Y($G$30="",$H$30="",J31=0)+</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>32</v>
       </c>
@@ -24385,7 +24389,7 @@
         <v>Y($G$32="",$H$32="",J33=0)+</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>34</v>
       </c>
@@ -24412,7 +24416,7 @@
         <v>Y($G$34="",$H$34="",J35=0)+</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>36</v>
       </c>
@@ -24439,7 +24443,7 @@
         <v>Y($G$36="",$H$36="",J37=0)+</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>38</v>
       </c>
@@ -24466,7 +24470,7 @@
         <v>Y($G$38="",$H$38="",J39=0)+</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>40</v>
       </c>
@@ -24493,7 +24497,7 @@
         <v>Y($G$40="",$H$40="",J41=0)+</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>42</v>
       </c>
@@ -24520,7 +24524,7 @@
         <v>Y($G$42="",$H$42="",J43=0)+</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>44</v>
       </c>
@@ -24547,7 +24551,7 @@
         <v>Y($G$44="",$H$44="",J45=0)+</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>46</v>
       </c>
@@ -24574,7 +24578,7 @@
         <v>Y($G$46="",$H$46="",J47=0)+</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>48</v>
       </c>
@@ -24601,7 +24605,7 @@
         <v>Y($G$48="",$H$48="",J49=0)+</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>50</v>
       </c>
@@ -24628,7 +24632,7 @@
         <v>Y($G$50="",$H$50="",J51=0)+</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>52</v>
       </c>
@@ -24655,7 +24659,7 @@
         <v>Y($G$52="",$H$52="",J53=0)+</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>54</v>
       </c>
@@ -24682,7 +24686,7 @@
         <v>Y($G$54="",$H$54="",J55=0)+</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>56</v>
       </c>
@@ -24709,7 +24713,7 @@
         <v>Y($G$56="",$H$56="",J57=0)+</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>58</v>
       </c>
@@ -24736,7 +24740,7 @@
         <v>Y($G$58="",$H$58="",J59=0)+</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>60</v>
       </c>
@@ -24763,7 +24767,7 @@
         <v>Y($G$60="",$H$60="",J61=0)+</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>62</v>
       </c>
@@ -24790,7 +24794,7 @@
         <v>Y($G$62="",$H$62="",J63=0)+</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>64</v>
       </c>
@@ -24817,7 +24821,7 @@
         <v>Y($G$64="",$H$64="",J65=0)+</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>66</v>
       </c>
@@ -24844,7 +24848,7 @@
         <v>Y($G$66="",$H$66="",J67=0)+</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>68</v>
       </c>
@@ -24871,7 +24875,7 @@
         <v>Y($G$68="",$H$68="",J69=0)+</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>70</v>
       </c>
@@ -24898,7 +24902,7 @@
         <v>Y($G$70="",$H$70="",J71=0)+</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>72</v>
       </c>
@@ -24925,7 +24929,7 @@
         <v>Y($G$72="",$H$72="",J73=0)+</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>74</v>
       </c>
@@ -24952,7 +24956,7 @@
         <v>Y($G$74="",$H$74="",J75=0)+</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>76</v>
       </c>
@@ -24979,7 +24983,7 @@
         <v>Y($G$76="",$H$76="",J77=0)+</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>78</v>
       </c>
@@ -25006,7 +25010,7 @@
         <v>Y($G$78="",$H$78="",J79=0)+</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>80</v>
       </c>
@@ -25037,7 +25041,7 @@
         <v>SUMA(Y($G$80="",$H$80="",J81=0)+Y($G$82="",$H$82="",J83=0)+Y($G$84="",$H$84="",J85=0)+Y($G$86="",$H$86="",J87=0)+Y($G$88="",$H$88="",J89=0)+Y($G$90="",$H$90="",J91=0)+Y($G$92="",$H$92="",J93=0)+Y($G$94="",$H$94="",J95=0)+Y($G$96="",$H$96="",J97=0)+Y($G$98="",$H$98="",J99=0)+Y($G$100="",$H$100="",J101=0)+Y($G$102="",$H$102="",J103=0)+Y($G$104="",$H$104="",J105=0)+Y($G$106="",$H$106="",J107=0)+Y($G$108="",$H$108="",J109=0)+Y($G$110="",$H$110="",J111=0)+Y($G$112="",$H$112="",J113=0)+Y($G$114="",$H$114="",J115=0)+Y($G$116="",$H$116="",J117=0)+Y($G$118="",$H$118="",J119=0)+Y($G$120="",$H$120="",J121=0)+Y($G$122="",$H$122="",J123=0)+Y($G$124="",$H$124="",J125=0)+Y($G$126="",$H$126="",J127=0)+Y($G$128="",$H$128="",J129=0)+Y($G$130="",$H$130="",J131=0)+Y($G$132="",$H$132="",J133=0)+Y($G$134="",$H$134="",J135=0)+Y($G$136="",$H$136="",J137=0)+Y($G$138="",$H$138="",J139=0)+Y($G$140="",$H$140="",J141=0)+Y($G$142="",$H$142="",J143=0)+Y($G$144="",$H$144="",J145=0)+Y($G$146="",$H$146="",J147=0)+Y($G$148="",$H$148="",J149=0)+Y($G$150="",$H$150="",J151=0)+</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>82</v>
       </c>
@@ -25067,7 +25071,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>84</v>
       </c>
@@ -25094,7 +25098,7 @@
         <v>Y($G$84="",$H$84="",J85=0)+</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>86</v>
       </c>
@@ -25121,7 +25125,7 @@
         <v>Y($G$86="",$H$86="",J87=0)+</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>88</v>
       </c>
@@ -25148,7 +25152,7 @@
         <v>Y($G$88="",$H$88="",J89=0)+</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>90</v>
       </c>
@@ -25175,7 +25179,7 @@
         <v>Y($G$90="",$H$90="",J91=0)+</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>92</v>
       </c>
@@ -25202,7 +25206,7 @@
         <v>Y($G$92="",$H$92="",J93=0)+</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>94</v>
       </c>
@@ -25229,7 +25233,7 @@
         <v>Y($G$94="",$H$94="",J95=0)+</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>96</v>
       </c>
@@ -25256,7 +25260,7 @@
         <v>Y($G$96="",$H$96="",J97=0)+</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>98</v>
       </c>
@@ -25283,7 +25287,7 @@
         <v>Y($G$98="",$H$98="",J99=0)+</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>100</v>
       </c>
@@ -25310,7 +25314,7 @@
         <v>Y($G$100="",$H$100="",J101=0)+</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>102</v>
       </c>
@@ -25337,7 +25341,7 @@
         <v>Y($G$102="",$H$102="",J103=0)+</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>104</v>
       </c>
@@ -25364,7 +25368,7 @@
         <v>Y($G$104="",$H$104="",J105=0)+</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>106</v>
       </c>
@@ -25391,7 +25395,7 @@
         <v>Y($G$106="",$H$106="",J107=0)+</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>108</v>
       </c>
@@ -25418,7 +25422,7 @@
         <v>Y($G$108="",$H$108="",J109=0)+</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>110</v>
       </c>
@@ -25445,7 +25449,7 @@
         <v>Y($G$110="",$H$110="",J111=0)+</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>112</v>
       </c>
@@ -25472,7 +25476,7 @@
         <v>Y($G$112="",$H$112="",J113=0)+</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>114</v>
       </c>
@@ -25499,7 +25503,7 @@
         <v>Y($G$114="",$H$114="",J115=0)+</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>116</v>
       </c>
@@ -25526,7 +25530,7 @@
         <v>Y($G$116="",$H$116="",J117=0)+</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>118</v>
       </c>
@@ -25553,7 +25557,7 @@
         <v>Y($G$118="",$H$118="",J119=0)+</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>120</v>
       </c>
@@ -25580,7 +25584,7 @@
         <v>Y($G$120="",$H$120="",J121=0)+</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>122</v>
       </c>
@@ -25607,7 +25611,7 @@
         <v>Y($G$122="",$H$122="",J123=0)+</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>124</v>
       </c>
@@ -25634,7 +25638,7 @@
         <v>Y($G$124="",$H$124="",J125=0)+</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>126</v>
       </c>
@@ -25661,7 +25665,7 @@
         <v>Y($G$126="",$H$126="",J127=0)+</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>128</v>
       </c>
@@ -25688,7 +25692,7 @@
         <v>Y($G$128="",$H$128="",J129=0)+</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>130</v>
       </c>
@@ -25715,7 +25719,7 @@
         <v>Y($G$130="",$H$130="",J131=0)+</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>132</v>
       </c>
@@ -25742,7 +25746,7 @@
         <v>Y($G$132="",$H$132="",J133=0)+</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>134</v>
       </c>
@@ -25769,7 +25773,7 @@
         <v>Y($G$134="",$H$134="",J135=0)+</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>136</v>
       </c>
@@ -25796,7 +25800,7 @@
         <v>Y($G$136="",$H$136="",J137=0)+</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>138</v>
       </c>
@@ -25823,7 +25827,7 @@
         <v>Y($G$138="",$H$138="",J139=0)+</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>140</v>
       </c>
@@ -25850,7 +25854,7 @@
         <v>Y($G$140="",$H$140="",J141=0)+</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>142</v>
       </c>
@@ -25877,7 +25881,7 @@
         <v>Y($G$142="",$H$142="",J143=0)+</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>144</v>
       </c>
@@ -25904,7 +25908,7 @@
         <v>Y($G$144="",$H$144="",J145=0)+</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>146</v>
       </c>
@@ -25931,7 +25935,7 @@
         <v>Y($G$146="",$H$146="",J147=0)+</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>148</v>
       </c>
@@ -25958,7 +25962,7 @@
         <v>Y($G$148="",$H$148="",J149=0)+</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>150</v>
       </c>
@@ -25996,21 +26000,36 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:AJ65"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" style="3" customWidth="1"/>
-    <col min="6" max="7" width="6.140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" style="3" customWidth="1"/>
-    <col min="9" max="28" width="5.28515625" style="3" customWidth="1"/>
-    <col min="29" max="34" width="11.42578125" style="3"/>
-    <col min="35" max="36" width="11.42578125" style="3" hidden="1" customWidth="1"/>
-    <col min="37" max="16384" width="11.42578125" style="3"/>
+    <col min="2" max="2" width="13.88671875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="20.6640625" style="3" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="3.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="5.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="5.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="7.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="29" max="34" width="11.44140625" style="3"/>
+    <col min="35" max="36" width="11.44140625" style="3" hidden="1" customWidth="1"/>
+    <col min="37" max="16384" width="11.44140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="109" t="s">
         <v>28</v>
       </c>
@@ -26082,7 +26101,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:36" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -26096,83 +26115,83 @@
         <v>NISH G</v>
       </c>
       <c r="J2" s="35" t="str">
+        <f>'FIFA 2026'!M2</f>
+        <v>Mario Barona</v>
+      </c>
+      <c r="K2" s="36" t="str">
+        <f>'FIFA 2026'!X2</f>
+        <v>EDER R. GARCIA COVARRUBIAS</v>
+      </c>
+      <c r="L2" s="36" t="str">
         <f>'FIFA 2026'!U2</f>
         <v>Jesús Lauder</v>
-      </c>
-      <c r="K2" s="36" t="str">
-        <f>'FIFA 2026'!Z2</f>
-        <v>Geovanni Pinto</v>
-      </c>
-      <c r="L2" s="36" t="str">
-        <f>'FIFA 2026'!N2</f>
-        <v>Mario  Valdés</v>
       </c>
       <c r="M2" s="36" t="str">
         <f>'FIFA 2026'!AA2</f>
         <v>Alex Spartan</v>
       </c>
       <c r="N2" s="36" t="str">
+        <f>'FIFA 2026'!K2</f>
+        <v>JUAN DE SAN. RODRIGUEZ</v>
+      </c>
+      <c r="O2" s="36" t="str">
+        <f>'FIFA 2026'!P2</f>
+        <v>Alex Valdés</v>
+      </c>
+      <c r="P2" s="36" t="str">
+        <f>'FIFA 2026'!Z2</f>
+        <v>Geovanni Pinto</v>
+      </c>
+      <c r="Q2" s="36" t="str">
+        <f>'FIFA 2026'!O2</f>
+        <v>Raúl Santillán</v>
+      </c>
+      <c r="R2" s="36" t="str">
+        <f>'FIFA 2026'!Y2</f>
+        <v>REYNA TELLEZ</v>
+      </c>
+      <c r="S2" s="36" t="str">
+        <f>'FIFA 2026'!V2</f>
+        <v>LIMON</v>
+      </c>
+      <c r="T2" s="36" t="str">
+        <f>'FIFA 2026'!T2</f>
+        <v>Pedro Ocio</v>
+      </c>
+      <c r="U2" s="36" t="str">
+        <f>'FIFA 2026'!R2</f>
+        <v>Manuel Guillén</v>
+      </c>
+      <c r="V2" s="36" t="str">
+        <f>'FIFA 2026'!J2</f>
+        <v>Mario Alberto Pérez</v>
+      </c>
+      <c r="W2" s="36" t="str">
+        <f>'FIFA 2026'!AC2</f>
+        <v>JUAN DE SAN. VAZQUEZ</v>
+      </c>
+      <c r="X2" s="36" t="str">
+        <f>'FIFA 2026'!N2</f>
+        <v>Mario  Valdés</v>
+      </c>
+      <c r="Y2" s="36" t="str">
+        <f>'FIFA 2026'!Q2</f>
+        <v>Silvia</v>
+      </c>
+      <c r="Z2" s="36" t="str">
         <f>'FIFA 2026'!L2</f>
         <v>MYRIAM LUGO</v>
       </c>
-      <c r="O2" s="36" t="str">
-        <f>'FIFA 2026'!M2</f>
-        <v>Mario Barona</v>
-      </c>
-      <c r="P2" s="36" t="str">
-        <f>'FIFA 2026'!X2</f>
-        <v>EDER R. GARCIA COVARRUBIAS</v>
-      </c>
-      <c r="Q2" s="36" t="str">
-        <f>'FIFA 2026'!K2</f>
-        <v>JUAN DE SAN. RODRIGUEZ</v>
-      </c>
-      <c r="R2" s="36" t="str">
-        <f>'FIFA 2026'!P2</f>
-        <v>Alex Valdés</v>
-      </c>
-      <c r="S2" s="36" t="str">
-        <f>'FIFA 2026'!O2</f>
-        <v>Raúl Santillán</v>
-      </c>
-      <c r="T2" s="36" t="str">
-        <f>'FIFA 2026'!V2</f>
-        <v>LIMON</v>
-      </c>
-      <c r="U2" s="36" t="str">
-        <f>'FIFA 2026'!J2</f>
-        <v>Mario Alberto Pérez</v>
-      </c>
-      <c r="V2" s="36" t="str">
-        <f>'FIFA 2026'!AC2</f>
-        <v>JUAN DE SAN. VAZQUEZ</v>
-      </c>
-      <c r="W2" s="36" t="str">
-        <f>'FIFA 2026'!T2</f>
-        <v>Pedro Ocio</v>
-      </c>
-      <c r="X2" s="36" t="str">
-        <f>'FIFA 2026'!Y2</f>
-        <v>REYNA TELLEZ</v>
-      </c>
-      <c r="Y2" s="36" t="str">
+      <c r="AA2" s="36" t="str">
+        <f>'FIFA 2026'!S2</f>
+        <v>LUIS SALVADOR</v>
+      </c>
+      <c r="AB2" s="95" t="str">
         <f>'FIFA 2026'!W2</f>
         <v>JOANNA LARA</v>
       </c>
-      <c r="Z2" s="36" t="str">
-        <f>'FIFA 2026'!R2</f>
-        <v>Manuel Guillén</v>
-      </c>
-      <c r="AA2" s="36" t="str">
-        <f>'FIFA 2026'!Q2</f>
-        <v>Silvia</v>
-      </c>
-      <c r="AB2" s="95" t="str">
-        <f>'FIFA 2026'!S2</f>
-        <v>LUIS SALVADOR</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:36" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -26198,105 +26217,105 @@
       <c r="I3" s="20">
         <f>SUM(IF(I4=$H$4,3,0)+IF(I5=$F4+$G4,1,0)+IF(I6=$H$6,3,0)+IF(I7=$F6+$G6,1,0)+IF(I8=$H$8,3,0)+IF(I9=$F8+$G8,1,0)+IF(I10=$H$10,3,0)+IF(I11=$F10+$G10,1,0)
 +IF(I12=$H$12,3,0)+IF(I13=$F12+$G12,1,0)+IF(I14=$H$14,3,0)+IF(I15=$F14+$G14,1,0)+IF(I16=$H$16,3,0)+IF(I17=$F16+$G16,1,0)+IF(I18=$H$18,3,0)+IF(I19=$F18+$G18,1,0)+IF(I20=$H$20,3,0)+IF(I21=$F20+$G20,1,0)+IF(I22=$H$22,3,0)+IF(I23=$F22+$G22,1,0)+IF(I24=$H$24,3,0)+IF(I25=$F24+$G24,1,0)+IF(I26=$H$26,3,0)+IF(I27=$F26+$G26,1,0)+IF(I28=$H$28,3,0)+IF(I29=$F28+$G28,1,0)+IF(I30=$H$30,3,0)+IF(I31=$F30+$G30,1,0)+IF(I32=$H$32,3,0)+IF(I33=$F32+$G32,1,0)+IF(I34=$H$34,3,0)+IF(I35=$F34+$G34,1,0))</f>
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="J3" s="6">
         <f>SUM(IF(J4=$H$4,3,0)+IF(J5=$F4+$G4,1,0)+IF(J6=$H$6,3,0)+IF(J7=$F6+$G6,1,0)+IF(J8=$H$8,3,0)+IF(J9=$F8+$G8,1,0)+IF(J10=$H$10,3,0)+IF(J11=$F10+$G10,1,0)
 +IF(J12=$H$12,3,0)+IF(J13=$F12+$G12,1,0)+IF(J14=$H$14,3,0)+IF(J15=$F14+$G14,1,0)+IF(J16=$H$16,3,0)+IF(J17=$F16+$G16,1,0)+IF(J18=$H$18,3,0)+IF(J19=$F18+$G18,1,0)+IF(J20=$H$20,3,0)+IF(J21=$F20+$G20,1,0)+IF(J22=$H$22,3,0)+IF(J23=$F22+$G22,1,0)+IF(J24=$H$24,3,0)+IF(J25=$F24+$G24,1,0)+IF(J26=$H$26,3,0)+IF(J27=$F26+$G26,1,0)+IF(J28=$H$28,3,0)+IF(J29=$F28+$G28,1,0)+IF(J30=$H$30,3,0)+IF(J31=$F30+$G30,1,0)+IF(J32=$H$32,3,0)+IF(J33=$F32+$G32,1,0)+IF(J34=$H$34,3,0)+IF(J35=$F34+$G34,1,0))</f>
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K3" s="6">
         <f>SUM(IF(K4=$H$4,3,0)+IF(K5=$F4+$G4,1,0)+IF(K6=$H$6,3,0)+IF(K7=$F6+$G6,1,0)+IF(K8=$H$8,3,0)+IF(K9=$F8+$G8,1,0)+IF(K10=$H$10,3,0)+IF(K11=$F10+$G10,1,0)
 +IF(K12=$H$12,3,0)+IF(K13=$F12+$G12,1,0)+IF(K14=$H$14,3,0)+IF(K15=$F14+$G14,1,0)+IF(K16=$H$16,3,0)+IF(K17=$F16+$G16,1,0)+IF(K18=$H$18,3,0)+IF(K19=$F18+$G18,1,0)+IF(K20=$H$20,3,0)+IF(K21=$F20+$G20,1,0)+IF(K22=$H$22,3,0)+IF(K23=$F22+$G22,1,0)+IF(K24=$H$24,3,0)+IF(K25=$F24+$G24,1,0)+IF(K26=$H$26,3,0)+IF(K27=$F26+$G26,1,0)+IF(K28=$H$28,3,0)+IF(K29=$F28+$G28,1,0)+IF(K30=$H$30,3,0)+IF(K31=$F30+$G30,1,0)+IF(K32=$H$32,3,0)+IF(K33=$F32+$G32,1,0)+IF(K34=$H$34,3,0)+IF(K35=$F34+$G34,1,0))</f>
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="L3" s="6">
         <f>SUM(IF(L4=$H$4,3,0)+IF(L5=$F4+$G4,1,0)+IF(L6=$H$6,3,0)+IF(L7=$F6+$G6,1,0)+IF(L8=$H$8,3,0)+IF(L9=$F8+$G8,1,0)+IF(L10=$H$10,3,0)+IF(L11=$F10+$G10,1,0)
 +IF(L12=$H$12,3,0)+IF(L13=$F12+$G12,1,0)+IF(L14=$H$14,3,0)+IF(L15=$F14+$G14,1,0)+IF(L16=$H$16,3,0)+IF(L17=$F16+$G16,1,0)+IF(L18=$H$18,3,0)+IF(L19=$F18+$G18,1,0)+IF(L20=$H$20,3,0)+IF(L21=$F20+$G20,1,0)+IF(L22=$H$22,3,0)+IF(L23=$F22+$G22,1,0)+IF(L24=$H$24,3,0)+IF(L25=$F24+$G24,1,0)+IF(L26=$H$26,3,0)+IF(L27=$F26+$G26,1,0)+IF(L28=$H$28,3,0)+IF(L29=$F28+$G28,1,0)+IF(L30=$H$30,3,0)+IF(L31=$F30+$G30,1,0)+IF(L32=$H$32,3,0)+IF(L33=$F32+$G32,1,0)+IF(L34=$H$34,3,0)+IF(L35=$F34+$G34,1,0))</f>
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="M3" s="6">
         <f>SUM(IF(M4=$H$4,3,0)+IF(M5=$F4+$G4,1,0)+IF(M6=$H$6,3,0)+IF(M7=$F6+$G6,1,0)+IF(M8=$H$8,3,0)+IF(M9=$F8+$G8,1,0)+IF(M10=$H$10,3,0)+IF(M11=$F10+$G10,1,0)
 +IF(M12=$H$12,3,0)+IF(M13=$F12+$G12,1,0)+IF(M14=$H$14,3,0)+IF(M15=$F14+$G14,1,0)+IF(M16=$H$16,3,0)+IF(M17=$F16+$G16,1,0)+IF(M18=$H$18,3,0)+IF(M19=$F18+$G18,1,0)+IF(M20=$H$20,3,0)+IF(M21=$F20+$G20,1,0)+IF(M22=$H$22,3,0)+IF(M23=$F22+$G22,1,0)+IF(M24=$H$24,3,0)+IF(M25=$F24+$G24,1,0)+IF(M26=$H$26,3,0)+IF(M27=$F26+$G26,1,0)+IF(M28=$H$28,3,0)+IF(M29=$F28+$G28,1,0)+IF(M30=$H$30,3,0)+IF(M31=$F30+$G30,1,0)+IF(M32=$H$32,3,0)+IF(M33=$F32+$G32,1,0)+IF(M34=$H$34,3,0)+IF(M35=$F34+$G34,1,0))</f>
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="N3" s="6">
         <f>SUM(IF(N4=$H$4,3,0)+IF(N5=$F4+$G4,1,0)+IF(N6=$H$6,3,0)+IF(N7=$F6+$G6,1,0)+IF(N8=$H$8,3,0)+IF(N9=$F8+$G8,1,0)+IF(N10=$H$10,3,0)+IF(N11=$F10+$G10,1,0)
 +IF(N12=$H$12,3,0)+IF(N13=$F12+$G12,1,0)+IF(N14=$H$14,3,0)+IF(N15=$F14+$G14,1,0)+IF(N16=$H$16,3,0)+IF(N17=$F16+$G16,1,0)+IF(N18=$H$18,3,0)+IF(N19=$F18+$G18,1,0)+IF(N20=$H$20,3,0)+IF(N21=$F20+$G20,1,0)+IF(N22=$H$22,3,0)+IF(N23=$F22+$G22,1,0)+IF(N24=$H$24,3,0)+IF(N25=$F24+$G24,1,0)+IF(N26=$H$26,3,0)+IF(N27=$F26+$G26,1,0)+IF(N28=$H$28,3,0)+IF(N29=$F28+$G28,1,0)+IF(N30=$H$30,3,0)+IF(N31=$F30+$G30,1,0)+IF(N32=$H$32,3,0)+IF(N33=$F32+$G32,1,0)+IF(N34=$H$34,3,0)+IF(N35=$F34+$G34,1,0))</f>
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="O3" s="6">
         <f>SUM(IF(O4=$H$4,3,0)+IF(O5=$F4+$G4,1,0)+IF(O6=$H$6,3,0)+IF(O7=$F6+$G6,1,0)+IF(O8=$H$8,3,0)+IF(O9=$F8+$G8,1,0)+IF(O10=$H$10,3,0)+IF(O11=$F10+$G10,1,0)
 +IF(O12=$H$12,3,0)+IF(O13=$F12+$G12,1,0)+IF(O14=$H$14,3,0)+IF(O15=$F14+$G14,1,0)+IF(O16=$H$16,3,0)+IF(O17=$F16+$G16,1,0)+IF(O18=$H$18,3,0)+IF(O19=$F18+$G18,1,0)+IF(O20=$H$20,3,0)+IF(O21=$F20+$G20,1,0)+IF(O22=$H$22,3,0)+IF(O23=$F22+$G22,1,0)+IF(O24=$H$24,3,0)+IF(O25=$F24+$G24,1,0)+IF(O26=$H$26,3,0)+IF(O27=$F26+$G26,1,0)+IF(O28=$H$28,3,0)+IF(O29=$F28+$G28,1,0)+IF(O30=$H$30,3,0)+IF(O31=$F30+$G30,1,0)+IF(O32=$H$32,3,0)+IF(O33=$F32+$G32,1,0)+IF(O34=$H$34,3,0)+IF(O35=$F34+$G34,1,0))</f>
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="P3" s="6">
         <f>SUM(IF(P4=$H$4,3,0)+IF(P5=$F4+$G4,1,0)+IF(P6=$H$6,3,0)+IF(P7=$F6+$G6,1,0)+IF(P8=$H$8,3,0)+IF(P9=$F8+$G8,1,0)+IF(P10=$H$10,3,0)+IF(P11=$F10+$G10,1,0)
 +IF(P12=$H$12,3,0)+IF(P13=$F12+$G12,1,0)+IF(P14=$H$14,3,0)+IF(P15=$F14+$G14,1,0)+IF(P16=$H$16,3,0)+IF(P17=$F16+$G16,1,0)+IF(P18=$H$18,3,0)+IF(P19=$F18+$G18,1,0)+IF(P20=$H$20,3,0)+IF(P21=$F20+$G20,1,0)+IF(P22=$H$22,3,0)+IF(P23=$F22+$G22,1,0)+IF(P24=$H$24,3,0)+IF(P25=$F24+$G24,1,0)+IF(P26=$H$26,3,0)+IF(P27=$F26+$G26,1,0)+IF(P28=$H$28,3,0)+IF(P29=$F28+$G28,1,0)+IF(P30=$H$30,3,0)+IF(P31=$F30+$G30,1,0)+IF(P32=$H$32,3,0)+IF(P33=$F32+$G32,1,0)+IF(P34=$H$34,3,0)+IF(P35=$F34+$G34,1,0))</f>
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="6">
         <f>SUM(IF(Q4=$H$4,3,0)+IF(Q5=$F4+$G4,1,0)+IF(Q6=$H$6,3,0)+IF(Q7=$F6+$G6,1,0)+IF(Q8=$H$8,3,0)+IF(Q9=$F8+$G8,1,0)+IF(Q10=$H$10,3,0)+IF(Q11=$F10+$G10,1,0)
 +IF(Q12=$H$12,3,0)+IF(Q13=$F12+$G12,1,0)+IF(Q14=$H$14,3,0)+IF(Q15=$F14+$G14,1,0)+IF(Q16=$H$16,3,0)+IF(Q17=$F16+$G16,1,0)+IF(Q18=$H$18,3,0)+IF(Q19=$F18+$G18,1,0)+IF(Q20=$H$20,3,0)+IF(Q21=$F20+$G20,1,0)+IF(Q22=$H$22,3,0)+IF(Q23=$F22+$G22,1,0)+IF(Q24=$H$24,3,0)+IF(Q25=$F24+$G24,1,0)+IF(Q26=$H$26,3,0)+IF(Q27=$F26+$G26,1,0)+IF(Q28=$H$28,3,0)+IF(Q29=$F28+$G28,1,0)+IF(Q30=$H$30,3,0)+IF(Q31=$F30+$G30,1,0)+IF(Q32=$H$32,3,0)+IF(Q33=$F32+$G32,1,0)+IF(Q34=$H$34,3,0)+IF(Q35=$F34+$G34,1,0))</f>
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="R3" s="6">
         <f>SUM(IF(R4=$H$4,3,0)+IF(R5=$F4+$G4,1,0)+IF(R6=$H$6,3,0)+IF(R7=$F6+$G6,1,0)+IF(R8=$H$8,3,0)+IF(R9=$F8+$G8,1,0)+IF(R10=$H$10,3,0)+IF(R11=$F10+$G10,1,0)
 +IF(R12=$H$12,3,0)+IF(R13=$F12+$G12,1,0)+IF(R14=$H$14,3,0)+IF(R15=$F14+$G14,1,0)+IF(R16=$H$16,3,0)+IF(R17=$F16+$G16,1,0)+IF(R18=$H$18,3,0)+IF(R19=$F18+$G18,1,0)+IF(R20=$H$20,3,0)+IF(R21=$F20+$G20,1,0)+IF(R22=$H$22,3,0)+IF(R23=$F22+$G22,1,0)+IF(R24=$H$24,3,0)+IF(R25=$F24+$G24,1,0)+IF(R26=$H$26,3,0)+IF(R27=$F26+$G26,1,0)+IF(R28=$H$28,3,0)+IF(R29=$F28+$G28,1,0)+IF(R30=$H$30,3,0)+IF(R31=$F30+$G30,1,0)+IF(R32=$H$32,3,0)+IF(R33=$F32+$G32,1,0)+IF(R34=$H$34,3,0)+IF(R35=$F34+$G34,1,0))</f>
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="S3" s="6">
         <f>SUM(IF(S4=$H$4,3,0)+IF(S5=$F4+$G4,1,0)+IF(S6=$H$6,3,0)+IF(S7=$F6+$G6,1,0)+IF(S8=$H$8,3,0)+IF(S9=$F8+$G8,1,0)+IF(S10=$H$10,3,0)+IF(S11=$F10+$G10,1,0)
 +IF(S12=$H$12,3,0)+IF(S13=$F12+$G12,1,0)+IF(S14=$H$14,3,0)+IF(S15=$F14+$G14,1,0)+IF(S16=$H$16,3,0)+IF(S17=$F16+$G16,1,0)+IF(S18=$H$18,3,0)+IF(S19=$F18+$G18,1,0)+IF(S20=$H$20,3,0)+IF(S21=$F20+$G20,1,0)+IF(S22=$H$22,3,0)+IF(S23=$F22+$G22,1,0)+IF(S24=$H$24,3,0)+IF(S25=$F24+$G24,1,0)+IF(S26=$H$26,3,0)+IF(S27=$F26+$G26,1,0)+IF(S28=$H$28,3,0)+IF(S29=$F28+$G28,1,0)+IF(S30=$H$30,3,0)+IF(S31=$F30+$G30,1,0)+IF(S32=$H$32,3,0)+IF(S33=$F32+$G32,1,0)+IF(S34=$H$34,3,0)+IF(S35=$F34+$G34,1,0))</f>
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="T3" s="6">
         <f>SUM(IF(T4=$H$4,3,0)+IF(T5=$F4+$G4,1,0)+IF(T6=$H$6,3,0)+IF(T7=$F6+$G6,1,0)+IF(T8=$H$8,3,0)+IF(T9=$F8+$G8,1,0)+IF(T10=$H$10,3,0)+IF(T11=$F10+$G10,1,0)
 +IF(T12=$H$12,3,0)+IF(T13=$F12+$G12,1,0)+IF(T14=$H$14,3,0)+IF(T15=$F14+$G14,1,0)+IF(T16=$H$16,3,0)+IF(T17=$F16+$G16,1,0)+IF(T18=$H$18,3,0)+IF(T19=$F18+$G18,1,0)+IF(T20=$H$20,3,0)+IF(T21=$F20+$G20,1,0)+IF(T22=$H$22,3,0)+IF(T23=$F22+$G22,1,0)+IF(T24=$H$24,3,0)+IF(T25=$F24+$G24,1,0)+IF(T26=$H$26,3,0)+IF(T27=$F26+$G26,1,0)+IF(T28=$H$28,3,0)+IF(T29=$F28+$G28,1,0)+IF(T30=$H$30,3,0)+IF(T31=$F30+$G30,1,0)+IF(T32=$H$32,3,0)+IF(T33=$F32+$G32,1,0)+IF(T34=$H$34,3,0)+IF(T35=$F34+$G34,1,0))</f>
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="U3" s="6">
         <f>SUM(IF(U4=$H$4,3,0)+IF(U5=$F4+$G4,1,0)+IF(U6=$H$6,3,0)+IF(U7=$F6+$G6,1,0)+IF(U8=$H$8,3,0)+IF(U9=$F8+$G8,1,0)+IF(U10=$H$10,3,0)+IF(U11=$F10+$G10,1,0)
 +IF(U12=$H$12,3,0)+IF(U13=$F12+$G12,1,0)+IF(U14=$H$14,3,0)+IF(U15=$F14+$G14,1,0)+IF(U16=$H$16,3,0)+IF(U17=$F16+$G16,1,0)+IF(U18=$H$18,3,0)+IF(U19=$F18+$G18,1,0)+IF(U20=$H$20,3,0)+IF(U21=$F20+$G20,1,0)+IF(U22=$H$22,3,0)+IF(U23=$F22+$G22,1,0)+IF(U24=$H$24,3,0)+IF(U25=$F24+$G24,1,0)+IF(U26=$H$26,3,0)+IF(U27=$F26+$G26,1,0)+IF(U28=$H$28,3,0)+IF(U29=$F28+$G28,1,0)+IF(U30=$H$30,3,0)+IF(U31=$F30+$G30,1,0)+IF(U32=$H$32,3,0)+IF(U33=$F32+$G32,1,0)+IF(U34=$H$34,3,0)+IF(U35=$F34+$G34,1,0))</f>
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="V3" s="6">
         <f>SUM(IF(V4=$H$4,3,0)+IF(V5=$F4+$G4,1,0)+IF(V6=$H$6,3,0)+IF(V7=$F6+$G6,1,0)+IF(V8=$H$8,3,0)+IF(V9=$F8+$G8,1,0)+IF(V10=$H$10,3,0)+IF(V11=$F10+$G10,1,0)
 +IF(V12=$H$12,3,0)+IF(V13=$F12+$G12,1,0)+IF(V14=$H$14,3,0)+IF(V15=$F14+$G14,1,0)+IF(V16=$H$16,3,0)+IF(V17=$F16+$G16,1,0)+IF(V18=$H$18,3,0)+IF(V19=$F18+$G18,1,0)+IF(V20=$H$20,3,0)+IF(V21=$F20+$G20,1,0)+IF(V22=$H$22,3,0)+IF(V23=$F22+$G22,1,0)+IF(V24=$H$24,3,0)+IF(V25=$F24+$G24,1,0)+IF(V26=$H$26,3,0)+IF(V27=$F26+$G26,1,0)+IF(V28=$H$28,3,0)+IF(V29=$F28+$G28,1,0)+IF(V30=$H$30,3,0)+IF(V31=$F30+$G30,1,0)+IF(V32=$H$32,3,0)+IF(V33=$F32+$G32,1,0)+IF(V34=$H$34,3,0)+IF(V35=$F34+$G34,1,0))</f>
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="W3" s="6">
         <f>SUM(IF(W4=$H$4,3,0)+IF(W5=$F4+$G4,1,0)+IF(W6=$H$6,3,0)+IF(W7=$F6+$G6,1,0)+IF(W8=$H$8,3,0)+IF(W9=$F8+$G8,1,0)+IF(W10=$H$10,3,0)+IF(W11=$F10+$G10,1,0)
 +IF(W12=$H$12,3,0)+IF(W13=$F12+$G12,1,0)+IF(W14=$H$14,3,0)+IF(W15=$F14+$G14,1,0)+IF(W16=$H$16,3,0)+IF(W17=$F16+$G16,1,0)+IF(W18=$H$18,3,0)+IF(W19=$F18+$G18,1,0)+IF(W20=$H$20,3,0)+IF(W21=$F20+$G20,1,0)+IF(W22=$H$22,3,0)+IF(W23=$F22+$G22,1,0)+IF(W24=$H$24,3,0)+IF(W25=$F24+$G24,1,0)+IF(W26=$H$26,3,0)+IF(W27=$F26+$G26,1,0)+IF(W28=$H$28,3,0)+IF(W29=$F28+$G28,1,0)+IF(W30=$H$30,3,0)+IF(W31=$F30+$G30,1,0)+IF(W32=$H$32,3,0)+IF(W33=$F32+$G32,1,0)+IF(W34=$H$34,3,0)+IF(W35=$F34+$G34,1,0))</f>
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="X3" s="6">
         <f>SUM(IF(X4=$H$4,3,0)+IF(X5=$F4+$G4,1,0)+IF(X6=$H$6,3,0)+IF(X7=$F6+$G6,1,0)+IF(X8=$H$8,3,0)+IF(X9=$F8+$G8,1,0)+IF(X10=$H$10,3,0)+IF(X11=$F10+$G10,1,0)
 +IF(X12=$H$12,3,0)+IF(X13=$F12+$G12,1,0)+IF(X14=$H$14,3,0)+IF(X15=$F14+$G14,1,0)+IF(X16=$H$16,3,0)+IF(X17=$F16+$G16,1,0)+IF(X18=$H$18,3,0)+IF(X19=$F18+$G18,1,0)+IF(X20=$H$20,3,0)+IF(X21=$F20+$G20,1,0)+IF(X22=$H$22,3,0)+IF(X23=$F22+$G22,1,0)+IF(X24=$H$24,3,0)+IF(X25=$F24+$G24,1,0)+IF(X26=$H$26,3,0)+IF(X27=$F26+$G26,1,0)+IF(X28=$H$28,3,0)+IF(X29=$F28+$G28,1,0)+IF(X30=$H$30,3,0)+IF(X31=$F30+$G30,1,0)+IF(X32=$H$32,3,0)+IF(X33=$F32+$G32,1,0)+IF(X34=$H$34,3,0)+IF(X35=$F34+$G34,1,0))</f>
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="Y3" s="6">
         <f>SUM(IF(Y4=$H$4,3,0)+IF(Y5=$F4+$G4,1,0)+IF(Y6=$H$6,3,0)+IF(Y7=$F6+$G6,1,0)+IF(Y8=$H$8,3,0)+IF(Y9=$F8+$G8,1,0)+IF(Y10=$H$10,3,0)+IF(Y11=$F10+$G10,1,0)
 +IF(Y12=$H$12,3,0)+IF(Y13=$F12+$G12,1,0)+IF(Y14=$H$14,3,0)+IF(Y15=$F14+$G14,1,0)+IF(Y16=$H$16,3,0)+IF(Y17=$F16+$G16,1,0)+IF(Y18=$H$18,3,0)+IF(Y19=$F18+$G18,1,0)+IF(Y20=$H$20,3,0)+IF(Y21=$F20+$G20,1,0)+IF(Y22=$H$22,3,0)+IF(Y23=$F22+$G22,1,0)+IF(Y24=$H$24,3,0)+IF(Y25=$F24+$G24,1,0)+IF(Y26=$H$26,3,0)+IF(Y27=$F26+$G26,1,0)+IF(Y28=$H$28,3,0)+IF(Y29=$F28+$G28,1,0)+IF(Y30=$H$30,3,0)+IF(Y31=$F30+$G30,1,0)+IF(Y32=$H$32,3,0)+IF(Y33=$F32+$G32,1,0)+IF(Y34=$H$34,3,0)+IF(Y35=$F34+$G34,1,0))</f>
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="Z3" s="6">
         <f>SUM(IF(Z4=$H$4,3,0)+IF(Z5=$F4+$G4,1,0)+IF(Z6=$H$6,3,0)+IF(Z7=$F6+$G6,1,0)+IF(Z8=$H$8,3,0)+IF(Z9=$F8+$G8,1,0)+IF(Z10=$H$10,3,0)+IF(Z11=$F10+$G10,1,0)
 +IF(Z12=$H$12,3,0)+IF(Z13=$F12+$G12,1,0)+IF(Z14=$H$14,3,0)+IF(Z15=$F14+$G14,1,0)+IF(Z16=$H$16,3,0)+IF(Z17=$F16+$G16,1,0)+IF(Z18=$H$18,3,0)+IF(Z19=$F18+$G18,1,0)+IF(Z20=$H$20,3,0)+IF(Z21=$F20+$G20,1,0)+IF(Z22=$H$22,3,0)+IF(Z23=$F22+$G22,1,0)+IF(Z24=$H$24,3,0)+IF(Z25=$F24+$G24,1,0)+IF(Z26=$H$26,3,0)+IF(Z27=$F26+$G26,1,0)+IF(Z28=$H$28,3,0)+IF(Z29=$F28+$G28,1,0)+IF(Z30=$H$30,3,0)+IF(Z31=$F30+$G30,1,0)+IF(Z32=$H$32,3,0)+IF(Z33=$F32+$G32,1,0)+IF(Z34=$H$34,3,0)+IF(Z35=$F34+$G34,1,0))</f>
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AA3" s="6">
         <f>SUM(IF(AA4=$H$4,3,0)+IF(AA5=$F4+$G4,1,0)+IF(AA6=$H$6,3,0)+IF(AA7=$F6+$G6,1,0)+IF(AA8=$H$8,3,0)+IF(AA9=$F8+$G8,1,0)+IF(AA10=$H$10,3,0)+IF(AA11=$F10+$G10,1,0)
 +IF(AA12=$H$12,3,0)+IF(AA13=$F12+$G12,1,0)+IF(AA14=$H$14,3,0)+IF(AA15=$F14+$G14,1,0)+IF(AA16=$H$16,3,0)+IF(AA17=$F16+$G16,1,0)+IF(AA18=$H$18,3,0)+IF(AA19=$F18+$G18,1,0)+IF(AA20=$H$20,3,0)+IF(AA21=$F20+$G20,1,0)+IF(AA22=$H$22,3,0)+IF(AA23=$F22+$G22,1,0)+IF(AA24=$H$24,3,0)+IF(AA25=$F24+$G24,1,0)+IF(AA26=$H$26,3,0)+IF(AA27=$F26+$G26,1,0)+IF(AA28=$H$28,3,0)+IF(AA29=$F28+$G28,1,0)+IF(AA30=$H$30,3,0)+IF(AA31=$F30+$G30,1,0)+IF(AA32=$H$32,3,0)+IF(AA33=$F32+$G32,1,0)+IF(AA34=$H$34,3,0)+IF(AA35=$F34+$G34,1,0))</f>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AB3" s="21">
         <f>SUM(IF(AB4=$H$4,3,0)+IF(AB5=$F4+$G4,1,0)+IF(AB6=$H$6,3,0)+IF(AB7=$F6+$G6,1,0)+IF(AB8=$H$8,3,0)+IF(AB9=$F8+$G8,1,0)+IF(AB10=$H$10,3,0)+IF(AB11=$F10+$G10,1,0)
 +IF(AB12=$H$12,3,0)+IF(AB13=$F12+$G12,1,0)+IF(AB14=$H$14,3,0)+IF(AB15=$F14+$G14,1,0)+IF(AB16=$H$16,3,0)+IF(AB17=$F16+$G16,1,0)+IF(AB18=$H$18,3,0)+IF(AB19=$F18+$G18,1,0)+IF(AB20=$H$20,3,0)+IF(AB21=$F20+$G20,1,0)+IF(AB22=$H$22,3,0)+IF(AB23=$F22+$G22,1,0)+IF(AB24=$H$24,3,0)+IF(AB25=$F24+$G24,1,0)+IF(AB26=$H$26,3,0)+IF(AB27=$F26+$G26,1,0)+IF(AB28=$H$28,3,0)+IF(AB29=$F28+$G28,1,0)+IF(AB30=$H$30,3,0)+IF(AB31=$F30+$G30,1,0)+IF(AB32=$H$32,3,0)+IF(AB33=$F32+$G32,1,0)+IF(AB34=$H$34,3,0)+IF(AB35=$F34+$G34,1,0))</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="133" t="s">
         <v>76</v>
       </c>
@@ -26383,7 +26402,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="134"/>
       <c r="B5" s="102"/>
       <c r="C5" s="114"/>
@@ -26396,10 +26415,10 @@
         <v>2</v>
       </c>
       <c r="J5" s="18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K5" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5" s="18">
         <v>4</v>
@@ -26408,28 +26427,28 @@
         <v>3</v>
       </c>
       <c r="N5" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P5" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="18">
         <v>3</v>
       </c>
       <c r="R5" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5" s="18">
         <v>3</v>
       </c>
       <c r="T5" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U5" s="18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V5" s="18">
         <v>4</v>
@@ -26441,7 +26460,7 @@
         <v>4</v>
       </c>
       <c r="Y5" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z5" s="18">
         <v>2</v>
@@ -26450,7 +26469,7 @@
         <v>2</v>
       </c>
       <c r="AB5" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI5" s="47" t="s">
         <v>7</v>
@@ -26459,7 +26478,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="134"/>
       <c r="B6" s="101">
         <v>46203</v>
@@ -26473,11 +26492,15 @@
       <c r="E6" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="105"/>
-      <c r="G6" s="105"/>
+      <c r="F6" s="105">
+        <v>3</v>
+      </c>
+      <c r="G6" s="105">
+        <v>0</v>
+      </c>
       <c r="H6" s="107" t="str">
         <f t="shared" ref="H6:H34" si="0">IF(F6="","-",IF(F6&gt;G6,"L",IF(F6=G6,"E",IF(F6&lt;G6,"V"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="I6" s="26" t="s">
         <v>7</v>
@@ -26546,7 +26569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="134"/>
       <c r="B7" s="102"/>
       <c r="C7" s="114"/>
@@ -26559,25 +26582,25 @@
         <v>3</v>
       </c>
       <c r="J7" s="13">
+        <v>4</v>
+      </c>
+      <c r="K7" s="13">
+        <v>3</v>
+      </c>
+      <c r="L7" s="13">
         <v>5</v>
-      </c>
-      <c r="K7" s="13">
-        <v>4</v>
-      </c>
-      <c r="L7" s="13">
-        <v>2</v>
       </c>
       <c r="M7" s="13">
         <v>5</v>
       </c>
       <c r="N7" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P7" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="13">
         <v>4</v>
@@ -26586,10 +26609,10 @@
         <v>3</v>
       </c>
       <c r="S7" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T7" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U7" s="13">
         <v>3</v>
@@ -26598,22 +26621,22 @@
         <v>3</v>
       </c>
       <c r="W7" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X7" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y7" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z7" s="13">
         <v>3</v>
       </c>
       <c r="AA7" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB7" s="25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI7" s="49" t="s">
         <v>15</v>
@@ -26622,7 +26645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="134"/>
       <c r="B8" s="101">
         <v>46201</v>
@@ -26683,7 +26706,7 @@
         <v>15</v>
       </c>
       <c r="U8" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V8" s="18" t="s">
         <v>15</v>
@@ -26695,23 +26718,23 @@
         <v>15</v>
       </c>
       <c r="Y8" s="18" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z8" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA8" s="18" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AB8" s="24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI8" s="49"/>
       <c r="AJ8" s="50">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="134"/>
       <c r="B9" s="102"/>
       <c r="C9" s="114"/>
@@ -26724,7 +26747,7 @@
         <v>3</v>
       </c>
       <c r="J9" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9" s="18">
         <v>3</v>
@@ -26739,7 +26762,7 @@
         <v>3</v>
       </c>
       <c r="O9" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P9" s="18">
         <v>3</v>
@@ -26760,7 +26783,7 @@
         <v>4</v>
       </c>
       <c r="V9" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W9" s="18">
         <v>3</v>
@@ -26772,20 +26795,20 @@
         <v>3</v>
       </c>
       <c r="Z9" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA9" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB9" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI9" s="49"/>
       <c r="AJ9" s="50">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="134"/>
       <c r="B10" s="101">
         <v>46202</v>
@@ -26816,7 +26839,7 @@
         <v>16</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>16</v>
@@ -26828,10 +26851,10 @@
         <v>7</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q10" s="13" t="s">
         <v>7</v>
@@ -26855,7 +26878,7 @@
         <v>7</v>
       </c>
       <c r="X10" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Y10" s="13" t="s">
         <v>7</v>
@@ -26864,17 +26887,17 @@
         <v>7</v>
       </c>
       <c r="AA10" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AB10" s="25" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AI10" s="49"/>
       <c r="AJ10" s="50">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="134"/>
       <c r="B11" s="102"/>
       <c r="C11" s="114"/>
@@ -26893,62 +26916,62 @@
         <v>2</v>
       </c>
       <c r="L11" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M11" s="13">
         <v>2</v>
       </c>
       <c r="N11" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O11" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P11" s="13">
         <v>2</v>
       </c>
       <c r="Q11" s="13">
+        <v>3</v>
+      </c>
+      <c r="R11" s="13">
+        <v>3</v>
+      </c>
+      <c r="S11" s="13">
+        <v>1</v>
+      </c>
+      <c r="T11" s="13">
+        <v>3</v>
+      </c>
+      <c r="U11" s="13">
+        <v>4</v>
+      </c>
+      <c r="V11" s="13">
+        <v>6</v>
+      </c>
+      <c r="W11" s="13">
         <v>5</v>
       </c>
-      <c r="R11" s="13">
-        <v>3</v>
-      </c>
-      <c r="S11" s="13">
-        <v>3</v>
-      </c>
-      <c r="T11" s="13">
-        <v>1</v>
-      </c>
-      <c r="U11" s="13">
-        <v>6</v>
-      </c>
-      <c r="V11" s="13">
-        <v>5</v>
-      </c>
-      <c r="W11" s="13">
-        <v>3</v>
-      </c>
       <c r="X11" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y11" s="13">
         <v>3</v>
       </c>
       <c r="Z11" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA11" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB11" s="25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI11" s="49"/>
       <c r="AJ11" s="50">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="134"/>
       <c r="B12" s="117">
         <v>46205</v>
@@ -26975,10 +26998,10 @@
         <v>7</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L12" s="19" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M12" s="19" t="s">
         <v>15</v>
@@ -26987,16 +27010,16 @@
         <v>7</v>
       </c>
       <c r="O12" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="P12" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q12" s="19" t="s">
         <v>7</v>
       </c>
       <c r="R12" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S12" s="19" t="s">
         <v>7</v>
@@ -27005,13 +27028,13 @@
         <v>7</v>
       </c>
       <c r="U12" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="V12" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="W12" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="X12" s="19" t="s">
         <v>15</v>
@@ -27020,20 +27043,20 @@
         <v>7</v>
       </c>
       <c r="Z12" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AA12" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AB12" s="28" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AI12" s="49"/>
       <c r="AJ12" s="50">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="134"/>
       <c r="B13" s="118"/>
       <c r="C13" s="125"/>
@@ -27046,7 +27069,7 @@
         <v>3</v>
       </c>
       <c r="J13" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" s="19">
         <v>2</v>
@@ -27061,53 +27084,53 @@
         <v>3</v>
       </c>
       <c r="O13" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P13" s="19">
         <v>2</v>
       </c>
       <c r="Q13" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R13" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S13" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T13" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U13" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V13" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W13" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X13" s="19">
         <v>3</v>
       </c>
       <c r="Y13" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z13" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA13" s="19">
         <v>2</v>
       </c>
       <c r="AB13" s="28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI13" s="49"/>
       <c r="AJ13" s="50">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="134"/>
       <c r="B14" s="117">
         <v>46205</v>
@@ -27158,10 +27181,10 @@
         <v>7</v>
       </c>
       <c r="S14" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="T14" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="U14" s="13" t="s">
         <v>7</v>
@@ -27192,7 +27215,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="134"/>
       <c r="B15" s="118"/>
       <c r="C15" s="125"/>
@@ -27208,10 +27231,10 @@
         <v>3</v>
       </c>
       <c r="K15" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L15" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M15" s="13">
         <v>2</v>
@@ -27223,7 +27246,7 @@
         <v>3</v>
       </c>
       <c r="P15" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="13">
         <v>3</v>
@@ -27232,41 +27255,41 @@
         <v>3</v>
       </c>
       <c r="S15" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T15" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U15" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V15" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W15" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X15" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y15" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z15" s="13">
         <v>3</v>
       </c>
       <c r="AA15" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB15" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI15" s="49"/>
       <c r="AJ15" s="50">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="134"/>
       <c r="B16" s="117">
         <v>46204</v>
@@ -27280,11 +27303,15 @@
       <c r="E16" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
+      <c r="F16" s="122">
+        <v>2</v>
+      </c>
+      <c r="G16" s="122">
+        <v>0</v>
+      </c>
       <c r="H16" s="115" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="I16" s="27" t="s">
         <v>7</v>
@@ -27351,7 +27378,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="134"/>
       <c r="B17" s="118"/>
       <c r="C17" s="125"/>
@@ -27367,10 +27394,10 @@
         <v>2</v>
       </c>
       <c r="K17" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M17" s="19">
         <v>2</v>
@@ -27379,13 +27406,13 @@
         <v>3</v>
       </c>
       <c r="O17" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P17" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R17" s="19">
         <v>3</v>
@@ -27394,13 +27421,13 @@
         <v>2</v>
       </c>
       <c r="T17" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U17" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V17" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W17" s="19">
         <v>3</v>
@@ -27409,13 +27436,13 @@
         <v>3</v>
       </c>
       <c r="Y17" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z17" s="19">
         <v>3</v>
       </c>
       <c r="AA17" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB17" s="28">
         <v>4</v>
@@ -27425,7 +27452,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="134"/>
       <c r="B18" s="117">
         <v>46204</v>
@@ -27439,29 +27466,33 @@
       <c r="E18" s="121" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
+      <c r="F18" s="122">
+        <v>2</v>
+      </c>
+      <c r="G18" s="122">
+        <v>2</v>
+      </c>
       <c r="H18" s="115" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>E</v>
       </c>
       <c r="I18" s="26" t="s">
         <v>16</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" s="13" t="s">
         <v>16</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>16</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O18" s="13" t="s">
         <v>16</v>
@@ -27470,19 +27501,19 @@
         <v>16</v>
       </c>
       <c r="Q18" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R18" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S18" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T18" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="U18" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V18" s="13" t="s">
         <v>7</v>
@@ -27491,13 +27522,13 @@
         <v>7</v>
       </c>
       <c r="X18" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Y18" s="13" t="s">
         <v>7</v>
       </c>
       <c r="Z18" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AA18" s="13" t="s">
         <v>7</v>
@@ -27510,7 +27541,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="134"/>
       <c r="B19" s="118"/>
       <c r="C19" s="125"/>
@@ -27523,7 +27554,7 @@
         <v>2</v>
       </c>
       <c r="J19" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19" s="13">
         <v>2</v>
@@ -27535,7 +27566,7 @@
         <v>4</v>
       </c>
       <c r="N19" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O19" s="13">
         <v>2</v>
@@ -27544,37 +27575,37 @@
         <v>2</v>
       </c>
       <c r="Q19" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S19" s="13">
+        <v>3</v>
+      </c>
+      <c r="T19" s="13">
+        <v>3</v>
+      </c>
+      <c r="U19" s="13">
+        <v>2</v>
+      </c>
+      <c r="V19" s="13">
+        <v>3</v>
+      </c>
+      <c r="W19" s="13">
         <v>1</v>
       </c>
-      <c r="T19" s="13">
-        <v>3</v>
-      </c>
-      <c r="U19" s="13">
-        <v>3</v>
-      </c>
-      <c r="V19" s="13">
-        <v>1</v>
-      </c>
-      <c r="W19" s="13">
-        <v>3</v>
-      </c>
       <c r="X19" s="13">
         <v>3</v>
       </c>
       <c r="Y19" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z19" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA19" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB19" s="25">
         <v>3</v>
@@ -27584,7 +27615,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="133" t="s">
         <v>77</v>
       </c>
@@ -27614,7 +27645,7 @@
         <v>7</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K20" s="18" t="s">
         <v>7</v>
@@ -27629,7 +27660,7 @@
         <v>7</v>
       </c>
       <c r="O20" s="18" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="P20" s="18" t="s">
         <v>7</v>
@@ -27665,16 +27696,16 @@
         <v>7</v>
       </c>
       <c r="AA20" s="18" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AB20" s="24" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AJ20" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="134"/>
       <c r="B21" s="102"/>
       <c r="C21" s="114"/>
@@ -27687,13 +27718,13 @@
         <v>3</v>
       </c>
       <c r="J21" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K21" s="18">
         <v>3</v>
       </c>
       <c r="L21" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M21" s="18">
         <v>3</v>
@@ -27702,7 +27733,7 @@
         <v>3</v>
       </c>
       <c r="O21" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P21" s="18">
         <v>3</v>
@@ -27711,20 +27742,20 @@
         <v>3</v>
       </c>
       <c r="R21" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S21" s="18">
         <v>3</v>
       </c>
       <c r="T21" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U21" s="18">
+        <v>3</v>
+      </c>
+      <c r="V21" s="18">
         <v>5</v>
       </c>
-      <c r="V21" s="18">
-        <v>4</v>
-      </c>
       <c r="W21" s="18">
         <v>4</v>
       </c>
@@ -27732,19 +27763,19 @@
         <v>4</v>
       </c>
       <c r="Y21" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z21" s="18">
         <v>3</v>
       </c>
       <c r="AA21" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB21" s="24">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="134"/>
       <c r="B22" s="101">
         <v>46203</v>
@@ -27758,11 +27789,15 @@
       <c r="E22" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="105"/>
-      <c r="G22" s="105"/>
+      <c r="F22" s="105">
+        <v>1</v>
+      </c>
+      <c r="G22" s="105">
+        <v>2</v>
+      </c>
       <c r="H22" s="107" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>V</v>
       </c>
       <c r="I22" s="26" t="s">
         <v>15</v>
@@ -27771,22 +27806,22 @@
         <v>15</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>15</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O22" s="13" t="s">
         <v>15</v>
       </c>
       <c r="P22" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q22" s="13" t="s">
         <v>15</v>
@@ -27810,22 +27845,22 @@
         <v>15</v>
       </c>
       <c r="X22" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Y22" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Z22" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA22" s="13" t="s">
         <v>15</v>
       </c>
       <c r="AB22" s="25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="134"/>
       <c r="B23" s="102"/>
       <c r="C23" s="114"/>
@@ -27838,25 +27873,25 @@
         <v>2</v>
       </c>
       <c r="J23" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M23" s="13">
         <v>2</v>
       </c>
       <c r="N23" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O23" s="13">
         <v>3</v>
       </c>
       <c r="P23" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="13">
         <v>3</v>
@@ -27865,25 +27900,25 @@
         <v>3</v>
       </c>
       <c r="S23" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T23" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U23" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V23" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W23" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X23" s="13">
         <v>3</v>
       </c>
       <c r="Y23" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z23" s="13">
         <v>2</v>
@@ -27892,10 +27927,10 @@
         <v>4</v>
       </c>
       <c r="AB23" s="25">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="134"/>
       <c r="B24" s="101">
         <v>46203</v>
@@ -27909,11 +27944,15 @@
       <c r="E24" s="126" t="s">
         <v>45</v>
       </c>
-      <c r="F24" s="105"/>
-      <c r="G24" s="105"/>
+      <c r="F24" s="105">
+        <v>2</v>
+      </c>
+      <c r="G24" s="105">
+        <v>0</v>
+      </c>
       <c r="H24" s="107" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="I24" s="23" t="s">
         <v>7</v>
@@ -27976,7 +28015,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="134"/>
       <c r="B25" s="102"/>
       <c r="C25" s="114"/>
@@ -27992,10 +28031,10 @@
         <v>2</v>
       </c>
       <c r="K25" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L25" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M25" s="18">
         <v>3</v>
@@ -28004,25 +28043,25 @@
         <v>3</v>
       </c>
       <c r="O25" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P25" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q25" s="18">
+        <v>2</v>
+      </c>
+      <c r="R25" s="18">
+        <v>2</v>
+      </c>
+      <c r="S25" s="18">
         <v>1</v>
       </c>
-      <c r="Q25" s="18">
-        <v>3</v>
-      </c>
-      <c r="R25" s="18">
-        <v>1</v>
-      </c>
-      <c r="S25" s="18">
-        <v>2</v>
-      </c>
       <c r="T25" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U25" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V25" s="18">
         <v>3</v>
@@ -28031,22 +28070,22 @@
         <v>3</v>
       </c>
       <c r="X25" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y25" s="18">
         <v>3</v>
       </c>
       <c r="Z25" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA25" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB25" s="24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="134"/>
       <c r="B26" s="101">
         <v>46204</v>
@@ -28060,11 +28099,15 @@
       <c r="E26" s="103" t="s">
         <v>147</v>
       </c>
-      <c r="F26" s="105"/>
-      <c r="G26" s="105"/>
+      <c r="F26" s="105">
+        <v>2</v>
+      </c>
+      <c r="G26" s="105">
+        <v>1</v>
+      </c>
       <c r="H26" s="107" t="str">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="I26" s="26" t="s">
         <v>7</v>
@@ -28127,7 +28170,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="134"/>
       <c r="B27" s="102"/>
       <c r="C27" s="114"/>
@@ -28140,10 +28183,10 @@
         <v>2</v>
       </c>
       <c r="J27" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K27" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L27" s="13">
         <v>4</v>
@@ -28152,52 +28195,52 @@
         <v>2</v>
       </c>
       <c r="N27" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O27" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P27" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q27" s="13">
         <v>3</v>
       </c>
       <c r="R27" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S27" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T27" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U27" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V27" s="13">
         <v>4</v>
       </c>
       <c r="W27" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X27" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y27" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z27" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA27" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB27" s="25">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="134"/>
       <c r="B28" s="117">
         <v>46206</v>
@@ -28278,7 +28321,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="134"/>
       <c r="B29" s="118"/>
       <c r="C29" s="125"/>
@@ -28294,31 +28337,31 @@
         <v>3</v>
       </c>
       <c r="K29" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L29" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M29" s="19">
         <v>4</v>
       </c>
       <c r="N29" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O29" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P29" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q29" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R29" s="19">
         <v>4</v>
       </c>
       <c r="S29" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T29" s="19">
         <v>3</v>
@@ -28327,28 +28370,28 @@
         <v>3</v>
       </c>
       <c r="V29" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W29" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X29" s="19">
         <v>4</v>
       </c>
       <c r="Y29" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z29" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA29" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB29" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="134"/>
       <c r="B30" s="117">
         <v>46206</v>
@@ -28372,10 +28415,10 @@
         <v>16</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>15</v>
@@ -28384,19 +28427,19 @@
         <v>15</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="O30" s="13" t="s">
         <v>16</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q30" s="13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="R30" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S30" s="13" t="s">
         <v>15</v>
@@ -28405,13 +28448,13 @@
         <v>15</v>
       </c>
       <c r="U30" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V30" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W30" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X30" s="13" t="s">
         <v>15</v>
@@ -28429,7 +28472,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="134"/>
       <c r="B31" s="118"/>
       <c r="C31" s="125"/>
@@ -28442,10 +28485,10 @@
         <v>2</v>
       </c>
       <c r="J31" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K31" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" s="13">
         <v>3</v>
@@ -28454,34 +28497,34 @@
         <v>1</v>
       </c>
       <c r="N31" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O31" s="13">
         <v>2</v>
       </c>
       <c r="P31" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q31" s="13">
         <v>1</v>
       </c>
       <c r="R31" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S31" s="13">
         <v>1</v>
       </c>
       <c r="T31" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U31" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V31" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W31" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X31" s="13">
         <v>3</v>
@@ -28493,13 +28536,13 @@
         <v>2</v>
       </c>
       <c r="AA31" s="13">
+        <v>3</v>
+      </c>
+      <c r="AB31" s="25">
         <v>1</v>
       </c>
-      <c r="AB31" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="134"/>
       <c r="B32" s="117">
         <v>46205</v>
@@ -28535,7 +28578,7 @@
         <v>16</v>
       </c>
       <c r="N32" s="19" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O32" s="19" t="s">
         <v>7</v>
@@ -28544,7 +28587,7 @@
         <v>7</v>
       </c>
       <c r="Q32" s="19" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R32" s="19" t="s">
         <v>7</v>
@@ -28580,7 +28623,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="134"/>
       <c r="B33" s="118"/>
       <c r="C33" s="125"/>
@@ -28596,7 +28639,7 @@
         <v>3</v>
       </c>
       <c r="K33" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L33" s="19">
         <v>3</v>
@@ -28605,52 +28648,52 @@
         <v>2</v>
       </c>
       <c r="N33" s="19">
+        <v>4</v>
+      </c>
+      <c r="O33" s="19">
+        <v>3</v>
+      </c>
+      <c r="P33" s="19">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="19">
+        <v>3</v>
+      </c>
+      <c r="R33" s="19">
+        <v>2</v>
+      </c>
+      <c r="S33" s="19">
+        <v>4</v>
+      </c>
+      <c r="T33" s="19">
+        <v>3</v>
+      </c>
+      <c r="U33" s="19">
+        <v>3</v>
+      </c>
+      <c r="V33" s="19">
+        <v>2</v>
+      </c>
+      <c r="W33" s="19">
+        <v>3</v>
+      </c>
+      <c r="X33" s="19">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="19">
         <v>1</v>
       </c>
-      <c r="O33" s="19">
-        <v>3</v>
-      </c>
-      <c r="P33" s="19">
-        <v>2</v>
-      </c>
-      <c r="Q33" s="19">
-        <v>4</v>
-      </c>
-      <c r="R33" s="19">
-        <v>3</v>
-      </c>
-      <c r="S33" s="19">
-        <v>3</v>
-      </c>
-      <c r="T33" s="19">
-        <v>4</v>
-      </c>
-      <c r="U33" s="19">
-        <v>2</v>
-      </c>
-      <c r="V33" s="19">
-        <v>3</v>
-      </c>
-      <c r="W33" s="19">
-        <v>3</v>
-      </c>
-      <c r="X33" s="19">
-        <v>2</v>
-      </c>
-      <c r="Y33" s="19">
-        <v>2</v>
-      </c>
       <c r="Z33" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA33" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB33" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="134"/>
       <c r="B34" s="117">
         <v>46206</v>
@@ -28674,10 +28717,10 @@
         <v>7</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="L34" s="13" t="s">
         <v>7</v>
@@ -28689,10 +28732,10 @@
         <v>7</v>
       </c>
       <c r="O34" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="P34" s="13" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q34" s="13" t="s">
         <v>7</v>
@@ -28731,7 +28774,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="135"/>
       <c r="B35" s="118"/>
       <c r="C35" s="125"/>
@@ -28747,7 +28790,7 @@
         <v>2</v>
       </c>
       <c r="K35" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L35" s="13">
         <v>2</v>
@@ -28759,49 +28802,49 @@
         <v>3</v>
       </c>
       <c r="O35" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P35" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q35" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R35" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S35" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T35" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U35" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V35" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W35" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X35" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y35" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z35" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA35" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB35" s="25">
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E36" s="130" t="s">
         <v>10</v>
       </c>
@@ -28809,7 +28852,7 @@
       <c r="G36" s="130"/>
       <c r="H36" s="5">
         <f>SUM(F4:G35)</f>
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="I36" s="51">
         <f>SUM(I35,I33,I31,I29,I27,I25,I23,I21,I19,I17,I15,I13,I11,I9,I7,I5)</f>
@@ -28817,15 +28860,15 @@
       </c>
       <c r="J36" s="15">
         <f>SUM(J35,J33,J31,J29,J27,J25,J23,J21,J19,J17,J15,J13,J11,J9,J7,J5)</f>
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="K36" s="15">
         <f>SUM(K35,K33,K31,K29,K27,K25,K23,K21,K19,K17,K15,K13,K11,K9,K7,K5)</f>
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="L36" s="15">
         <f>SUM(L35,L33,L31,L29,L27,L25,L23,L21,L19,L17,L15,L13,L11,L9,L7,L5)</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M36" s="15">
         <f>SUM(M35,M33,M31,M29,M27,M25,M23,M21,M19,M17,M15,M13,M11,M9,M7,M5)</f>
@@ -28833,23 +28876,23 @@
       </c>
       <c r="N36" s="15">
         <f>SUM(N35,N33,N31,N29,N27,N25,N23,N21,N19,N17,N15,N13,N11,N9,N7,N5)</f>
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="O36" s="15">
         <f>SUM(O35,O33,O31,O29,O27,O25,O23,O21,O19,O17,O15,O13,O11,O9,O7,O5)</f>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="P36" s="15">
         <f>SUM(P35,P33,P31,P29,P27,P25,P23,P21,P19,P17,P15,P13,P11,P9,P7,P5)</f>
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Q36" s="15">
         <f>SUM(Q35,Q33,Q31,Q29,Q27,Q25,Q23,Q21,Q19,Q17,Q15,Q13,Q11,Q9,Q7,Q5)</f>
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="R36" s="15">
         <f>SUM(R35,R33,R31,R29,R27,R25,R23,R21,R19,R17,R15,R13,R11,R9,R7,R5)</f>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S36" s="15">
         <f>SUM(S35,S33,S31,S29,S27,S25,S23,S21,S19,S17,S15,S13,S11,S9,S7,S5)</f>
@@ -28857,42 +28900,42 @@
       </c>
       <c r="T36" s="15">
         <f>SUM(T35,T33,T31,T29,T27,T25,T23,T21,T19,T17,T15,T13,T11,T9,T7,T5)</f>
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="U36" s="15">
         <f>SUM(U35,U33,U31,U29,U27,U25,U23,U21,U19,U17,U15,U13,U11,U9,U7,U5)</f>
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="V36" s="15">
         <f>SUM(V35,V33,V31,V29,V27,V25,V23,V21,V19,V17,V15,V13,V11,V9,V7,V5)</f>
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="W36" s="15">
         <f>SUM(W35,W33,W31,W29,W27,W25,W23,W21,W19,W17,W15,W13,W11,W9,W7,W5)</f>
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="X36" s="15">
         <f>SUM(X35,X33,X31,X29,X27,X25,X23,X21,X19,X17,X15,X13,X11,X9,X7,X5)</f>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Y36" s="15">
         <f>SUM(Y35,Y33,Y31,Y29,Y27,Y25,Y23,Y21,Y19,Y17,Y15,Y13,Y11,Y9,Y7,Y5)</f>
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Z36" s="15">
         <f>SUM(Z35,Z33,Z31,Z29,Z27,Z25,Z23,Z21,Z19,Z17,Z15,Z13,Z11,Z9,Z7,Z5)</f>
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="AA36" s="15">
         <f>SUM(AA35,AA33,AA31,AA29,AA27,AA25,AA23,AA21,AA19,AA17,AA15,AA13,AA11,AA9,AA7,AA5)</f>
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="AB36" s="30">
         <f>SUM(AB35,AB33,AB31,AB29,AB27,AB25,AB23,AB21,AB19,AB17,AB15,AB13,AB11,AB9,AB7,AB5)</f>
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:28" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:28" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E37" s="131" t="s">
         <v>14</v>
       </c>
@@ -28901,191 +28944,191 @@
       <c r="H37" s="131"/>
       <c r="I37" s="31">
         <f>SUM(I38:I41)</f>
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="J37" s="32">
         <f>SUM(J38:J41)</f>
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="K37" s="32">
         <f>SUM(K38:K41)</f>
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="L37" s="32">
         <f>SUM(L38:L41)</f>
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="M37" s="32">
         <f>SUM(M38:M41)</f>
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="N37" s="32">
         <f>SUM(N38:N41)</f>
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="O37" s="32">
         <f>SUM(O38:O41)</f>
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="P37" s="32">
         <f>SUM(P38:P41)</f>
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="Q37" s="32">
         <f>SUM(Q38:Q41)</f>
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="R37" s="32">
         <f>SUM(R38:R41)</f>
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="S37" s="32">
         <f>SUM(S38:S41)</f>
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="T37" s="32">
         <f>SUM(T38:T41)</f>
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="U37" s="32">
         <f>SUM(U38:U41)</f>
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="V37" s="32">
         <f>SUM(V38:V41)</f>
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="W37" s="32">
         <f>SUM(W38:W41)</f>
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="X37" s="32">
         <f>SUM(X38:X41)</f>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Y37" s="32">
         <f>SUM(Y38:Y41)</f>
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="Z37" s="32">
         <f>SUM(Z38:Z41)</f>
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="AA37" s="32">
         <f>SUM(AA38:AA41)</f>
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="AB37" s="33">
         <f>SUM(AB38:AB41)</f>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:28" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="I38" s="4">
         <f>IF(I36=$H$36,100,IF($H$36-I36=1,99,IF($H$36-I36=-1,99,IF($H$36-I36=2,98,IF($H$36-I36=-2,98,IF($H$36-I36=3,97,IF($H$36-I36=-3,97,IF($H$36-I36=4,96,IF($H$36-I36=-4,96,IF($H$36-I36=5,95,IF($H$36-I36=-5,95,IF($H$36-I36=6,94,IF($H$36-I36=-6,94,IF($H$36-I36=7,93,IF($H$36-I36=-7,93,IF($H$36-I36=8,92,IF($H$36-I36=-8,92,IF($H$36-I36=9,91,IF($H$36-I36=-9,91,IF($H$36-I36=10,90,IF($H$36-I36=-10,90,IF($H$36-I36=11,89,IF($H$36-I36=-11,89,IF($H$36-I36=12,88,IF($H$36-I36=-12,88,IF($H$36-I36=13,87,IF($H$36-I36=-13,87,IF($H$36-I36=14,86,IF($H$36-I36=-14,86,IF($H$36-I36=15,85,IF($H$36-I36=-15,85,IF($H$36-I36=16,84,IF($H$36-I36=-16,84,IF($H$36-I36=17,83,IF($H$36-I36=-17,83,IF($H$36-I36=18,82,IF($H$36-I36=-18,82,IF($H$36-I36=19,81,IF($H$36-I36=-19,81,IF($H$36-I36=20,80,IF($H$36-I36=-20,80,IF($H$36-I36=21,79,IF($H$36-I36=-21,79,IF($H$36-I36=22,78,IF($H$36-I36=-22,78,IF($H$36-I36=23,77,IF($H$36-I36=-23,77,IF($H$36-I36=24,76,IF($H$36-I36=-24,76,IF($H$36-I36=25,75,IF($H$36-I36=-25,75,IF($H$36-I36=26,74,IF($H$36-I36=-26,74,IF($H$36-I36=27,73,IF($H$36-I36=-27,73,IF($H$36-I36=28,72,IF($H$36-I36=-28,72,IF($H$36-I36=29,71,IF($H$36-I36=-29,71,IF($H$36-I36=30,70,IF($H$36-I36=-30,70,IF($H$36-I36=31,69,IF($H$36-I36=-31,69,IF($H$36-I36=32,68,IF($H$36-I36=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" ref="J38:Q38" si="1">IF(J36=$H$36,100,IF($H$36-J36=1,99,IF($H$36-J36=-1,99,IF($H$36-J36=2,98,IF($H$36-J36=-2,98,IF($H$36-J36=3,97,IF($H$36-J36=-3,97,IF($H$36-J36=4,96,IF($H$36-J36=-4,96,IF($H$36-J36=5,95,IF($H$36-J36=-5,95,IF($H$36-J36=6,94,IF($H$36-J36=-6,94,IF($H$36-J36=7,93,IF($H$36-J36=-7,93,IF($H$36-J36=8,92,IF($H$36-J36=-8,92,IF($H$36-J36=9,91,IF($H$36-J36=-9,91,IF($H$36-J36=10,90,IF($H$36-J36=-10,90,IF($H$36-J36=11,89,IF($H$36-J36=-11,89,IF($H$36-J36=12,88,IF($H$36-J36=-12,88,IF($H$36-J36=13,87,IF($H$36-J36=-13,87,IF($H$36-J36=14,86,IF($H$36-J36=-14,86,IF($H$36-J36=15,85,IF($H$36-J36=-15,85,IF($H$36-J36=16,84,IF($H$36-J36=-16,84,IF($H$36-J36=17,83,IF($H$36-J36=-17,83,IF($H$36-J36=18,82,IF($H$36-J36=-18,82,IF($H$36-J36=19,81,IF($H$36-J36=-19,81,IF($H$36-J36=20,80,IF($H$36-J36=-20,80,IF($H$36-J36=21,79,IF($H$36-J36=-21,79,IF($H$36-J36=22,78,IF($H$36-J36=-22,78,IF($H$36-J36=23,77,IF($H$36-J36=-23,77,IF($H$36-J36=24,76,IF($H$36-J36=-24,76,IF($H$36-J36=25,75,IF($H$36-J36=-25,75,IF($H$36-J36=26,74,IF($H$36-J36=-26,74,IF($H$36-J36=27,73,IF($H$36-J36=-27,73,IF($H$36-J36=28,72,IF($H$36-J36=-28,72,IF($H$36-J36=29,71,IF($H$36-J36=-29,71,IF($H$36-J36=30,70,IF($H$36-J36=-30,70,IF($H$36-J36=31,69,IF($H$36-J36=-31,69,IF($H$36-J36=32,68,IF($H$36-J36=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="L38" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M38" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N38" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O38" s="4">
         <f t="shared" si="1"/>
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="P38" s="4">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="Q38" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="R38" s="4">
         <f t="shared" ref="R38:AB38" si="2">IF(R36=$H$36,100,IF($H$36-R36=1,99,IF($H$36-R36=-1,99,IF($H$36-R36=2,98,IF($H$36-R36=-2,98,IF($H$36-R36=3,97,IF($H$36-R36=-3,97,IF($H$36-R36=4,96,IF($H$36-R36=-4,96,IF($H$36-R36=5,95,IF($H$36-R36=-5,95,IF($H$36-R36=6,94,IF($H$36-R36=-6,94,IF($H$36-R36=7,93,IF($H$36-R36=-7,93,IF($H$36-R36=8,92,IF($H$36-R36=-8,92,IF($H$36-R36=9,91,IF($H$36-R36=-9,91,IF($H$36-R36=10,90,IF($H$36-R36=-10,90,IF($H$36-R36=11,89,IF($H$36-R36=-11,89,IF($H$36-R36=12,88,IF($H$36-R36=-12,88,IF($H$36-R36=13,87,IF($H$36-R36=-13,87,IF($H$36-R36=14,86,IF($H$36-R36=-14,86,IF($H$36-R36=15,85,IF($H$36-R36=-15,85,IF($H$36-R36=16,84,IF($H$36-R36=-16,84,IF($H$36-R36=17,83,IF($H$36-R36=-17,83,IF($H$36-R36=18,82,IF($H$36-R36=-18,82,IF($H$36-R36=19,81,IF($H$36-R36=-19,81,IF($H$36-R36=20,80,IF($H$36-R36=-20,80,IF($H$36-R36=21,79,IF($H$36-R36=-21,79,IF($H$36-R36=22,78,IF($H$36-R36=-22,78,IF($H$36-R36=23,77,IF($H$36-R36=-23,77,IF($H$36-R36=24,76,IF($H$36-R36=-24,76,IF($H$36-R36=25,75,IF($H$36-R36=-25,75,IF($H$36-R36=26,74,IF($H$36-R36=-26,74,IF($H$36-R36=27,73,IF($H$36-R36=-27,73,IF($H$36-R36=28,72,IF($H$36-R36=-28,72,IF($H$36-R36=29,71,IF($H$36-R36=-29,71,IF($H$36-R36=30,70,IF($H$36-R36=-30,70,IF($H$36-R36=31,69,IF($H$36-R36=-31,69,IF($H$36-R36=32,68,IF($H$36-R36=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="S38" s="4">
         <f t="shared" si="2"/>
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="T38" s="4">
         <f t="shared" si="2"/>
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="U38" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="W38" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="X38" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Y38" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="Z38" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AA38" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB38" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
       <c r="I39" s="4">
         <f>IF($H$36-I36=33,67,IF($H$36-I36=-33,67,IF($H$36-I36=34,66,IF($H$36-I36=-34,66,IF($H$36-I36=35,65,IF($H$36-I36=-35,65,IF($H$36-I36=36,64,IF($H$36-I36=-36,64,IF($H$36-I36=37,63,IF($H$36-I36=-37,63,IF($H$36-I36=38,62,IF($H$36-I36=-38,62,IF($H$36-I36=39,61,IF($H$36-I36=-39,61,IF($H$36-I36=40,60,IF($H$36-I36=-40,60,IF($H$36-I36=41,59,IF($H$36-I36=-41,59,IF($H$36-I36=42,58,IF($H$36-I36=-42,58,IF($H$36-I36=43,57,IF($H$36-I36=-43,57,IF($H$36-I36=44,56,IF($H$36-I36=-44,56,IF($H$36-I36=45,55,IF($H$36-I36=-45,55,IF($H$36-I36=46,54,IF($H$36-I36=-46,54,IF($H$36-I36=47,53,IF($H$36-I36=-47,53,IF($H$36-I36=48,52,IF($H$36-I36=-48,52,IF($H$36-I36=49,51,IF($H$36-I36=-49,51,IF($H$36-I36=50,50,IF($H$36-I36=-50,50,IF($H$36-I36=51,49,IF($H$36-I36=-51,49,IF($H$36-I36=52,48,IF($H$36-I36=-52,48,IF($H$36-I36=53,47,IF($H$36-I36=-53,47,IF($H$36-I36=54,46,IF($H$36-I36=-54,46,IF($H$36-I36=55,45,IF($H$36-I36=-55,45,IF($H$36-I36=56,44,IF($H$36-I36=-56,44,IF($H$36-I36=57,43,IF($H$36-I36=-57,43,IF($H$36-I36=58,42,IF($H$36-I36=-58,42,IF($H$36-I36=59,41,IF($H$36-I36=-59,41,IF($H$36-I36=60,40,IF($H$36-I36=-60,40,IF($H$36-I36=61,39,IF($H$36-I36=-61,39,IF($H$36-I36=62,38,IF($H$36-I36=-62,38,IF($H$36-I36=63,37,IF($H$36-I36=-63,37,IF($H$36-I36=64,36,IF($H$36-I36=-64,36,IF($H$36-I36=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="J39" s="4">
         <f t="shared" ref="J39:Q39" si="3">IF($H$36-J36=33,67,IF($H$36-J36=-33,67,IF($H$36-J36=34,66,IF($H$36-J36=-34,66,IF($H$36-J36=35,65,IF($H$36-J36=-35,65,IF($H$36-J36=36,64,IF($H$36-J36=-36,64,IF($H$36-J36=37,63,IF($H$36-J36=-37,63,IF($H$36-J36=38,62,IF($H$36-J36=-38,62,IF($H$36-J36=39,61,IF($H$36-J36=-39,61,IF($H$36-J36=40,60,IF($H$36-J36=-40,60,IF($H$36-J36=41,59,IF($H$36-J36=-41,59,IF($H$36-J36=42,58,IF($H$36-J36=-42,58,IF($H$36-J36=43,57,IF($H$36-J36=-43,57,IF($H$36-J36=44,56,IF($H$36-J36=-44,56,IF($H$36-J36=45,55,IF($H$36-J36=-45,55,IF($H$36-J36=46,54,IF($H$36-J36=-46,54,IF($H$36-J36=47,53,IF($H$36-J36=-47,53,IF($H$36-J36=48,52,IF($H$36-J36=-48,52,IF($H$36-J36=49,51,IF($H$36-J36=-49,51,IF($H$36-J36=50,50,IF($H$36-J36=-50,50,IF($H$36-J36=51,49,IF($H$36-J36=-51,49,IF($H$36-J36=52,48,IF($H$36-J36=-52,48,IF($H$36-J36=53,47,IF($H$36-J36=-53,47,IF($H$36-J36=54,46,IF($H$36-J36=-54,46,IF($H$36-J36=55,45,IF($H$36-J36=-55,45,IF($H$36-J36=56,44,IF($H$36-J36=-56,44,IF($H$36-J36=57,43,IF($H$36-J36=-57,43,IF($H$36-J36=58,42,IF($H$36-J36=-58,42,IF($H$36-J36=59,41,IF($H$36-J36=-59,41,IF($H$36-J36=60,40,IF($H$36-J36=-60,40,IF($H$36-J36=61,39,IF($H$36-J36=-61,39,IF($H$36-J36=62,38,IF($H$36-J36=-62,38,IF($H$36-J36=63,37,IF($H$36-J36=-63,37,IF($H$36-J36=64,36,IF($H$36-J36=-64,36,IF($H$36-J36=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="K39" s="4">
         <f t="shared" si="3"/>
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L39" s="4">
         <f t="shared" si="3"/>
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M39" s="4">
         <f t="shared" si="3"/>
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="N39" s="4">
         <f t="shared" si="3"/>
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="O39" s="4">
         <f t="shared" si="3"/>
@@ -29097,11 +29140,11 @@
       </c>
       <c r="Q39" s="4">
         <f t="shared" si="3"/>
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R39" s="4">
         <f t="shared" ref="R39:AB39" si="4">IF($H$36-R36=33,67,IF($H$36-R36=-33,67,IF($H$36-R36=34,66,IF($H$36-R36=-34,66,IF($H$36-R36=35,65,IF($H$36-R36=-35,65,IF($H$36-R36=36,64,IF($H$36-R36=-36,64,IF($H$36-R36=37,63,IF($H$36-R36=-37,63,IF($H$36-R36=38,62,IF($H$36-R36=-38,62,IF($H$36-R36=39,61,IF($H$36-R36=-39,61,IF($H$36-R36=40,60,IF($H$36-R36=-40,60,IF($H$36-R36=41,59,IF($H$36-R36=-41,59,IF($H$36-R36=42,58,IF($H$36-R36=-42,58,IF($H$36-R36=43,57,IF($H$36-R36=-43,57,IF($H$36-R36=44,56,IF($H$36-R36=-44,56,IF($H$36-R36=45,55,IF($H$36-R36=-45,55,IF($H$36-R36=46,54,IF($H$36-R36=-46,54,IF($H$36-R36=47,53,IF($H$36-R36=-47,53,IF($H$36-R36=48,52,IF($H$36-R36=-48,52,IF($H$36-R36=49,51,IF($H$36-R36=-49,51,IF($H$36-R36=50,50,IF($H$36-R36=-50,50,IF($H$36-R36=51,49,IF($H$36-R36=-51,49,IF($H$36-R36=52,48,IF($H$36-R36=-52,48,IF($H$36-R36=53,47,IF($H$36-R36=-53,47,IF($H$36-R36=54,46,IF($H$36-R36=-54,46,IF($H$36-R36=55,45,IF($H$36-R36=-55,45,IF($H$36-R36=56,44,IF($H$36-R36=-56,44,IF($H$36-R36=57,43,IF($H$36-R36=-57,43,IF($H$36-R36=58,42,IF($H$36-R36=-58,42,IF($H$36-R36=59,41,IF($H$36-R36=-59,41,IF($H$36-R36=60,40,IF($H$36-R36=-60,40,IF($H$36-R36=61,39,IF($H$36-R36=-61,39,IF($H$36-R36=62,38,IF($H$36-R36=-62,38,IF($H$36-R36=63,37,IF($H$36-R36=-63,37,IF($H$36-R36=64,36,IF($H$36-R36=-64,36,IF($H$36-R36=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="S39" s="4">
         <f t="shared" si="4"/>
@@ -29113,38 +29156,38 @@
       </c>
       <c r="U39" s="4">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="V39" s="4">
         <f t="shared" si="4"/>
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="W39" s="4">
         <f t="shared" si="4"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="X39" s="4">
         <f t="shared" si="4"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Y39" s="4">
         <f t="shared" si="4"/>
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="Z39" s="4">
         <f t="shared" si="4"/>
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="AA39" s="4">
         <f t="shared" si="4"/>
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="AB39" s="4">
         <f t="shared" si="4"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
       <c r="I40" s="4">
         <f>IF($H$36-I36=-65,35,IF($H$36-I36=66,34,IF($H$36-I36=-66,34,IF($H$36-I36=67,33,IF($H$36-I36=-67,33,IF($H$36-I36=68,32,IF($H$36-I36=-68,32,IF($H$36-I36=69,31,IF($H$36-I36=-69,31,IF($H$36-I36=70,30,IF($H$36-I36=-70,30,IF($H$36-I36=71,29,IF($H$36-I36=-71,29,IF($H$36-I36=72,28,IF($H$36-I36=-72,28,IF($H$36-I36=73,27,IF($H$36-I36=-73,27,IF($H$36-I36=74,26,IF($H$36-I36=-74,26,IF($H$36-I36=75,25,IF($H$36-I36=-75,25,IF($H$36-I36=76,24,IF($H$36-I36=-76,24,IF($H$36-I36=77,23,IF($H$36-I36=-77,23,IF($H$36-I36=78,22,IF($H$36-I36=-78,22,IF($H$36-I36=79,21,IF($H$36-I36=-79,21,IF($H$36-I36=80,20,IF($H$36-I36=-80,20,IF($H$36-I36=81,19,IF($H$36-I36=-81,19,IF($H$36-I36=82,18,IF($H$36-I36=-82,18,IF($H$36-I36=83,17,IF($H$36-I36=-83,17,IF($H$36-I36=84,16,IF($H$36-I36=-84,16,IF($H$36-I36=85,15,IF($H$36-I36=-85,15,IF($H$36-I36=86,14,IF($H$36-I36=-86,14,IF($H$36-I36=87,13,IF($H$36-I36=-87,13,IF($H$36-I36=88,12,IF($H$36-I36=-88,12,IF($H$36-I36=89,11,IF($H$36-I36=-89,11,IF($H$36-I36=90,10,IF($H$36-I36=-90,10,IF($H$36-I36=91,9,IF($H$36-I36=-91,9,IF($H$36-I36=92,8,IF($H$36-I36=-92,8,IF($H$36-I36=93,7,IF($H$36-I36=-93,7,IF($H$36-I36=94,6,IF($H$36-I36=-94,6,IF($H$36-I36=95,5,IF($H$36-I36=-95,5,IF($H$36-I36=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -29226,7 +29269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
       <c r="I41" s="4">
         <f>IF($H$36-I36=-96,4,IF($H$36-I36=97,3,IF($H$36-I36=-97,3,IF($H$36-I36=98,2,IF($H$36-I36=-98,2,IF($H$36-I36=99,1,IF($H$36-I36=-99,1,IF($H$36-I36=100,0,IF($H$36-I36=-100,0,0)))))))))</f>
         <v>0</v>
@@ -29308,25 +29351,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D42" s="132"/>
       <c r="E42" s="132"/>
       <c r="F42" s="132"/>
       <c r="G42" s="132"/>
     </row>
-    <row r="43" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D43" s="132"/>
       <c r="E43" s="132"/>
       <c r="F43" s="132"/>
       <c r="G43" s="132"/>
     </row>
-    <row r="44" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D44" s="132"/>
       <c r="E44" s="132"/>
       <c r="F44" s="132"/>
       <c r="G44" s="132"/>
     </row>
-    <row r="65" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I65" s="3">
         <v>1</v>
       </c>
@@ -29483,21 +29526,21 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:Y49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.85546875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="6.140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" style="3" customWidth="1"/>
-    <col min="9" max="17" width="5.28515625" style="3" customWidth="1"/>
-    <col min="18" max="23" width="11.42578125" style="3"/>
+    <col min="2" max="2" width="13.88671875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.88671875" style="3" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" style="3" customWidth="1"/>
+    <col min="9" max="17" width="5.33203125" style="3" customWidth="1"/>
+    <col min="18" max="23" width="11.44140625" style="3"/>
     <col min="24" max="25" width="0" style="3" hidden="1" customWidth="1"/>
-    <col min="26" max="16384" width="11.42578125" style="3"/>
+    <col min="26" max="16384" width="11.44140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="109" t="s">
         <v>28</v>
       </c>
@@ -29536,7 +29579,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -29555,7 +29598,7 @@
       <c r="P2" s="38"/>
       <c r="Q2" s="39"/>
     </row>
-    <row r="3" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -29624,7 +29667,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="133" t="s">
         <v>76</v>
       </c>
@@ -29656,7 +29699,7 @@
       <c r="P4" s="17"/>
       <c r="Q4" s="22"/>
     </row>
-    <row r="5" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="134"/>
       <c r="B5" s="102"/>
       <c r="C5" s="114"/>
@@ -29699,7 +29742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="134"/>
       <c r="B6" s="101">
         <v>46207</v>
@@ -29735,7 +29778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="134"/>
       <c r="B7" s="102"/>
       <c r="C7" s="114"/>
@@ -29778,7 +29821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="134"/>
       <c r="B8" s="101">
         <v>46209</v>
@@ -29812,7 +29855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="134"/>
       <c r="B9" s="102"/>
       <c r="C9" s="114"/>
@@ -29853,7 +29896,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="134"/>
       <c r="B10" s="101">
         <v>46209</v>
@@ -29887,7 +29930,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="134"/>
       <c r="B11" s="102"/>
       <c r="C11" s="114"/>
@@ -29928,7 +29971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="133" t="s">
         <v>77</v>
       </c>
@@ -29960,7 +30003,7 @@
       <c r="P12" s="19"/>
       <c r="Q12" s="28"/>
     </row>
-    <row r="13" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="134"/>
       <c r="B13" s="118"/>
       <c r="C13" s="125"/>
@@ -29997,7 +30040,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="134"/>
       <c r="B14" s="117">
         <v>46208</v>
@@ -30027,7 +30070,7 @@
       <c r="P14" s="13"/>
       <c r="Q14" s="25"/>
     </row>
-    <row r="15" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="134"/>
       <c r="B15" s="118"/>
       <c r="C15" s="125"/>
@@ -30064,7 +30107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="134"/>
       <c r="B16" s="117">
         <v>46210</v>
@@ -30094,7 +30137,7 @@
       <c r="P16" s="19"/>
       <c r="Q16" s="28"/>
     </row>
-    <row r="17" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="134"/>
       <c r="B17" s="118"/>
       <c r="C17" s="125"/>
@@ -30131,7 +30174,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="134"/>
       <c r="B18" s="117">
         <v>46210</v>
@@ -30161,7 +30204,7 @@
       <c r="P18" s="13"/>
       <c r="Q18" s="25"/>
     </row>
-    <row r="19" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="135"/>
       <c r="B19" s="118"/>
       <c r="C19" s="125"/>
@@ -30198,7 +30241,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E20" s="130" t="s">
         <v>10</v>
       </c>
@@ -30245,7 +30288,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E21" s="131" t="s">
         <v>14</v>
       </c>
@@ -30289,7 +30332,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="I22" s="4" t="e">
         <f>IF(I20=$H$20,100,IF($H$20-I20=1,99,IF($H$20-I20=-1,99,IF($H$20-I20=2,98,IF($H$20-I20=-2,98,IF($H$20-I20=3,97,IF($H$20-I20=-3,97,IF($H$20-I20=4,96,IF($H$20-I20=-4,96,IF($H$20-I20=5,95,IF($H$20-I20=-5,95,IF($H$20-I20=6,94,IF($H$20-I20=-6,94,IF($H$20-I20=7,93,IF($H$20-I20=-7,93,IF($H$20-I20=8,92,IF($H$20-I20=-8,92,IF($H$20-I20=9,91,IF($H$20-I20=-9,91,IF($H$20-I20=10,90,IF($H$20-I20=-10,90,IF($H$20-I20=11,89,IF($H$20-I20=-11,89,IF($H$20-I20=12,88,IF($H$20-I20=-12,88,IF($H$20-I20=13,87,IF($H$20-I20=-13,87,IF($H$20-I20=14,86,IF($H$20-I20=-14,86,IF($H$20-I20=15,85,IF($H$20-I20=-15,85,IF($H$20-I20=16,84,IF($H$20-I20=-16,84,IF($H$20-I20=17,83,IF($H$20-I20=-17,83,IF($H$20-I20=18,82,IF($H$20-I20=-18,82,IF($H$20-I20=19,81,IF($H$20-I20=-19,81,IF($H$20-I20=20,80,IF($H$20-I20=-20,80,IF($H$20-I20=21,79,IF($H$20-I20=-21,79,IF($H$20-I20=22,78,IF($H$20-I20=-22,78,IF($H$20-I20=23,77,IF($H$20-I20=-23,77,IF($H$20-I20=24,76,IF($H$20-I20=-24,76,IF($H$20-I20=25,75,IF($H$20-I20=-25,75,IF($H$20-I20=26,74,IF($H$20-I20=-26,74,IF($H$20-I20=27,73,IF($H$20-I20=-27,73,IF($H$20-I20=28,72,IF($H$20-I20=-28,72,IF($H$20-I20=29,71,IF($H$20-I20=-29,71,IF($H$20-I20=30,70,IF($H$20-I20=-30,70,IF($H$20-I20=31,69,IF($H$20-I20=-31,69,IF($H$20-I20=32,68,IF($H$20-I20=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>#REF!</v>
@@ -30327,7 +30370,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="I23" s="4" t="e">
         <f>IF($H$20-I20=33,67,IF($H$20-I20=-33,67,IF($H$20-I20=34,66,IF($H$20-I20=-34,66,IF($H$20-I20=35,65,IF($H$20-I20=-35,65,IF($H$20-I20=36,64,IF($H$20-I20=-36,64,IF($H$20-I20=37,63,IF($H$20-I20=-37,63,IF($H$20-I20=38,62,IF($H$20-I20=-38,62,IF($H$20-I20=39,61,IF($H$20-I20=-39,61,IF($H$20-I20=40,60,IF($H$20-I20=-40,60,IF($H$20-I20=41,59,IF($H$20-I20=-41,59,IF($H$20-I20=42,58,IF($H$20-I20=-42,58,IF($H$20-I20=43,57,IF($H$20-I20=-43,57,IF($H$20-I20=44,56,IF($H$20-I20=-44,56,IF($H$20-I20=45,55,IF($H$20-I20=-45,55,IF($H$20-I20=46,54,IF($H$20-I20=-46,54,IF($H$20-I20=47,53,IF($H$20-I20=-47,53,IF($H$20-I20=48,52,IF($H$20-I20=-48,52,IF($H$20-I20=49,51,IF($H$20-I20=-49,51,IF($H$20-I20=50,50,IF($H$20-I20=-50,50,IF($H$20-I20=51,49,IF($H$20-I20=-51,49,IF($H$20-I20=52,48,IF($H$20-I20=-52,48,IF($H$20-I20=53,47,IF($H$20-I20=-53,47,IF($H$20-I20=54,46,IF($H$20-I20=-54,46,IF($H$20-I20=55,45,IF($H$20-I20=-55,45,IF($H$20-I20=56,44,IF($H$20-I20=-56,44,IF($H$20-I20=57,43,IF($H$20-I20=-57,43,IF($H$20-I20=58,42,IF($H$20-I20=-58,42,IF($H$20-I20=59,41,IF($H$20-I20=-59,41,IF($H$20-I20=60,40,IF($H$20-I20=-60,40,IF($H$20-I20=61,39,IF($H$20-I20=-61,39,IF($H$20-I20=62,38,IF($H$20-I20=-62,38,IF($H$20-I20=63,37,IF($H$20-I20=-63,37,IF($H$20-I20=64,36,IF($H$20-I20=-64,36,IF($H$20-I20=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>#REF!</v>
@@ -30365,7 +30408,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="I24" s="4" t="e">
         <f>IF($H$20-I20=-65,35,IF($H$20-I20=66,34,IF($H$20-I20=-66,34,IF($H$20-I20=67,33,IF($H$20-I20=-67,33,IF($H$20-I20=68,32,IF($H$20-I20=-68,32,IF($H$20-I20=69,31,IF($H$20-I20=-69,31,IF($H$20-I20=70,30,IF($H$20-I20=-70,30,IF($H$20-I20=71,29,IF($H$20-I20=-71,29,IF($H$20-I20=72,28,IF($H$20-I20=-72,28,IF($H$20-I20=73,27,IF($H$20-I20=-73,27,IF($H$20-I20=74,26,IF($H$20-I20=-74,26,IF($H$20-I20=75,25,IF($H$20-I20=-75,25,IF($H$20-I20=76,24,IF($H$20-I20=-76,24,IF($H$20-I20=77,23,IF($H$20-I20=-77,23,IF($H$20-I20=78,22,IF($H$20-I20=-78,22,IF($H$20-I20=79,21,IF($H$20-I20=-79,21,IF($H$20-I20=80,20,IF($H$20-I20=-80,20,IF($H$20-I20=81,19,IF($H$20-I20=-81,19,IF($H$20-I20=82,18,IF($H$20-I20=-82,18,IF($H$20-I20=83,17,IF($H$20-I20=-83,17,IF($H$20-I20=84,16,IF($H$20-I20=-84,16,IF($H$20-I20=85,15,IF($H$20-I20=-85,15,IF($H$20-I20=86,14,IF($H$20-I20=-86,14,IF($H$20-I20=87,13,IF($H$20-I20=-87,13,IF($H$20-I20=88,12,IF($H$20-I20=-88,12,IF($H$20-I20=89,11,IF($H$20-I20=-89,11,IF($H$20-I20=90,10,IF($H$20-I20=-90,10,IF($H$20-I20=91,9,IF($H$20-I20=-91,9,IF($H$20-I20=92,8,IF($H$20-I20=-92,8,IF($H$20-I20=93,7,IF($H$20-I20=-93,7,IF($H$20-I20=94,6,IF($H$20-I20=-94,6,IF($H$20-I20=95,5,IF($H$20-I20=-95,5,IF($H$20-I20=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>#REF!</v>
@@ -30403,7 +30446,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="I25" s="4" t="e">
         <f>IF($H$20-I20=-96,4,IF($H$20-I20=97,3,IF($H$20-I20=-97,3,IF($H$20-I20=98,2,IF($H$20-I20=-98,2,IF($H$20-I20=99,1,IF($H$20-I20=-99,1,IF($H$20-I20=100,0,IF($H$20-I20=-100,0,0)))))))))</f>
         <v>#REF!</v>
@@ -30441,25 +30484,25 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D26" s="132"/>
       <c r="E26" s="132"/>
       <c r="F26" s="132"/>
       <c r="G26" s="132"/>
     </row>
-    <row r="27" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D27" s="132"/>
       <c r="E27" s="132"/>
       <c r="F27" s="132"/>
       <c r="G27" s="132"/>
     </row>
-    <row r="28" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D28" s="132"/>
       <c r="E28" s="132"/>
       <c r="F28" s="132"/>
       <c r="G28" s="132"/>
     </row>
-    <row r="49" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I49" s="3">
         <v>1</v>
       </c>
@@ -30554,21 +30597,21 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:V41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.85546875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="6.140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" style="3" customWidth="1"/>
-    <col min="9" max="14" width="5.28515625" style="3" customWidth="1"/>
-    <col min="15" max="20" width="11.42578125" style="3"/>
+    <col min="2" max="2" width="13.88671875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.88671875" style="3" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" style="3" customWidth="1"/>
+    <col min="9" max="14" width="5.33203125" style="3" customWidth="1"/>
+    <col min="15" max="20" width="11.44140625" style="3"/>
     <col min="21" max="22" width="0" style="3" hidden="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.42578125" style="3"/>
+    <col min="23" max="16384" width="11.44140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="109" t="s">
         <v>28</v>
       </c>
@@ -30598,7 +30641,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -30614,7 +30657,7 @@
       <c r="M2" s="38"/>
       <c r="N2" s="39"/>
     </row>
-    <row r="3" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -30662,7 +30705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="133" t="s">
         <v>76</v>
       </c>
@@ -30691,7 +30734,7 @@
       <c r="M4" s="17"/>
       <c r="N4" s="22"/>
     </row>
-    <row r="5" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="134"/>
       <c r="B5" s="102"/>
       <c r="C5" s="114"/>
@@ -30725,7 +30768,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="134"/>
       <c r="B6" s="101">
         <v>46213</v>
@@ -30758,7 +30801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="134"/>
       <c r="B7" s="102"/>
       <c r="C7" s="114"/>
@@ -30792,7 +30835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="133" t="s">
         <v>77</v>
       </c>
@@ -30821,7 +30864,7 @@
       <c r="M8" s="19"/>
       <c r="N8" s="28"/>
     </row>
-    <row r="9" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="134"/>
       <c r="B9" s="118"/>
       <c r="C9" s="125"/>
@@ -30849,7 +30892,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="134"/>
       <c r="B10" s="117">
         <v>46214</v>
@@ -30876,7 +30919,7 @@
       <c r="M10" s="13"/>
       <c r="N10" s="25"/>
     </row>
-    <row r="11" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="135"/>
       <c r="B11" s="118"/>
       <c r="C11" s="125"/>
@@ -30904,7 +30947,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E12" s="130" t="s">
         <v>10</v>
       </c>
@@ -30939,7 +30982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E13" s="131" t="s">
         <v>14</v>
       </c>
@@ -30971,7 +31014,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="I14" s="4">
         <f>IF(I12=$H$12,100,IF($H$12-I12=1,99,IF($H$12-I12=-1,99,IF($H$12-I12=2,98,IF($H$12-I12=-2,98,IF($H$12-I12=3,97,IF($H$12-I12=-3,97,IF($H$12-I12=4,96,IF($H$12-I12=-4,96,IF($H$12-I12=5,95,IF($H$12-I12=-5,95,IF($H$12-I12=6,94,IF($H$12-I12=-6,94,IF($H$12-I12=7,93,IF($H$12-I12=-7,93,IF($H$12-I12=8,92,IF($H$12-I12=-8,92,IF($H$12-I12=9,91,IF($H$12-I12=-9,91,IF($H$12-I12=10,90,IF($H$12-I12=-10,90,IF($H$12-I12=11,89,IF($H$12-I12=-11,89,IF($H$12-I12=12,88,IF($H$12-I12=-12,88,IF($H$12-I12=13,87,IF($H$12-I12=-13,87,IF($H$12-I12=14,86,IF($H$12-I12=-14,86,IF($H$12-I12=15,85,IF($H$12-I12=-15,85,IF($H$12-I12=16,84,IF($H$12-I12=-16,84,IF($H$12-I12=17,83,IF($H$12-I12=-17,83,IF($H$12-I12=18,82,IF($H$12-I12=-18,82,IF($H$12-I12=19,81,IF($H$12-I12=-19,81,IF($H$12-I12=20,80,IF($H$12-I12=-20,80,IF($H$12-I12=21,79,IF($H$12-I12=-21,79,IF($H$12-I12=22,78,IF($H$12-I12=-22,78,IF($H$12-I12=23,77,IF($H$12-I12=-23,77,IF($H$12-I12=24,76,IF($H$12-I12=-24,76,IF($H$12-I12=25,75,IF($H$12-I12=-25,75,IF($H$12-I12=26,74,IF($H$12-I12=-26,74,IF($H$12-I12=27,73,IF($H$12-I12=-27,73,IF($H$12-I12=28,72,IF($H$12-I12=-28,72,IF($H$12-I12=29,71,IF($H$12-I12=-29,71,IF($H$12-I12=30,70,IF($H$12-I12=-30,70,IF($H$12-I12=31,69,IF($H$12-I12=-31,69,IF($H$12-I12=32,68,IF($H$12-I12=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>100</v>
@@ -30997,7 +31040,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="I15" s="4">
         <f>IF($H$12-I12=33,67,IF($H$12-I12=-33,67,IF($H$12-I12=34,66,IF($H$12-I12=-34,66,IF($H$12-I12=35,65,IF($H$12-I12=-35,65,IF($H$12-I12=36,64,IF($H$12-I12=-36,64,IF($H$12-I12=37,63,IF($H$12-I12=-37,63,IF($H$12-I12=38,62,IF($H$12-I12=-38,62,IF($H$12-I12=39,61,IF($H$12-I12=-39,61,IF($H$12-I12=40,60,IF($H$12-I12=-40,60,IF($H$12-I12=41,59,IF($H$12-I12=-41,59,IF($H$12-I12=42,58,IF($H$12-I12=-42,58,IF($H$12-I12=43,57,IF($H$12-I12=-43,57,IF($H$12-I12=44,56,IF($H$12-I12=-44,56,IF($H$12-I12=45,55,IF($H$12-I12=-45,55,IF($H$12-I12=46,54,IF($H$12-I12=-46,54,IF($H$12-I12=47,53,IF($H$12-I12=-47,53,IF($H$12-I12=48,52,IF($H$12-I12=-48,52,IF($H$12-I12=49,51,IF($H$12-I12=-49,51,IF($H$12-I12=50,50,IF($H$12-I12=-50,50,IF($H$12-I12=51,49,IF($H$12-I12=-51,49,IF($H$12-I12=52,48,IF($H$12-I12=-52,48,IF($H$12-I12=53,47,IF($H$12-I12=-53,47,IF($H$12-I12=54,46,IF($H$12-I12=-54,46,IF($H$12-I12=55,45,IF($H$12-I12=-55,45,IF($H$12-I12=56,44,IF($H$12-I12=-56,44,IF($H$12-I12=57,43,IF($H$12-I12=-57,43,IF($H$12-I12=58,42,IF($H$12-I12=-58,42,IF($H$12-I12=59,41,IF($H$12-I12=-59,41,IF($H$12-I12=60,40,IF($H$12-I12=-60,40,IF($H$12-I12=61,39,IF($H$12-I12=-61,39,IF($H$12-I12=62,38,IF($H$12-I12=-62,38,IF($H$12-I12=63,37,IF($H$12-I12=-63,37,IF($H$12-I12=64,36,IF($H$12-I12=-64,36,IF($H$12-I12=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -31023,7 +31066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="I16" s="4">
         <f>IF($H$12-I12=-65,35,IF($H$12-I12=66,34,IF($H$12-I12=-66,34,IF($H$12-I12=67,33,IF($H$12-I12=-67,33,IF($H$12-I12=68,32,IF($H$12-I12=-68,32,IF($H$12-I12=69,31,IF($H$12-I12=-69,31,IF($H$12-I12=70,30,IF($H$12-I12=-70,30,IF($H$12-I12=71,29,IF($H$12-I12=-71,29,IF($H$12-I12=72,28,IF($H$12-I12=-72,28,IF($H$12-I12=73,27,IF($H$12-I12=-73,27,IF($H$12-I12=74,26,IF($H$12-I12=-74,26,IF($H$12-I12=75,25,IF($H$12-I12=-75,25,IF($H$12-I12=76,24,IF($H$12-I12=-76,24,IF($H$12-I12=77,23,IF($H$12-I12=-77,23,IF($H$12-I12=78,22,IF($H$12-I12=-78,22,IF($H$12-I12=79,21,IF($H$12-I12=-79,21,IF($H$12-I12=80,20,IF($H$12-I12=-80,20,IF($H$12-I12=81,19,IF($H$12-I12=-81,19,IF($H$12-I12=82,18,IF($H$12-I12=-82,18,IF($H$12-I12=83,17,IF($H$12-I12=-83,17,IF($H$12-I12=84,16,IF($H$12-I12=-84,16,IF($H$12-I12=85,15,IF($H$12-I12=-85,15,IF($H$12-I12=86,14,IF($H$12-I12=-86,14,IF($H$12-I12=87,13,IF($H$12-I12=-87,13,IF($H$12-I12=88,12,IF($H$12-I12=-88,12,IF($H$12-I12=89,11,IF($H$12-I12=-89,11,IF($H$12-I12=90,10,IF($H$12-I12=-90,10,IF($H$12-I12=91,9,IF($H$12-I12=-91,9,IF($H$12-I12=92,8,IF($H$12-I12=-92,8,IF($H$12-I12=93,7,IF($H$12-I12=-93,7,IF($H$12-I12=94,6,IF($H$12-I12=-94,6,IF($H$12-I12=95,5,IF($H$12-I12=-95,5,IF($H$12-I12=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -31049,7 +31092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="4:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:14" x14ac:dyDescent="0.3">
       <c r="I17" s="4">
         <f>IF($H$12-I12=-96,4,IF($H$12-I12=97,3,IF($H$12-I12=-97,3,IF($H$12-I12=98,2,IF($H$12-I12=-98,2,IF($H$12-I12=99,1,IF($H$12-I12=-99,1,IF($H$12-I12=100,0,IF($H$12-I12=-100,0,0)))))))))</f>
         <v>0</v>
@@ -31075,25 +31118,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D18" s="132"/>
       <c r="E18" s="132"/>
       <c r="F18" s="132"/>
       <c r="G18" s="132"/>
     </row>
-    <row r="19" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D19" s="132"/>
       <c r="E19" s="132"/>
       <c r="F19" s="132"/>
       <c r="G19" s="132"/>
     </row>
-    <row r="20" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D20" s="132"/>
       <c r="E20" s="132"/>
       <c r="F20" s="132"/>
       <c r="G20" s="132"/>
     </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I41" s="3">
         <v>1</v>
       </c>
@@ -31160,21 +31203,21 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:T41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.85546875" style="3" customWidth="1"/>
-    <col min="6" max="7" width="6.140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" style="3" customWidth="1"/>
-    <col min="9" max="12" width="5.28515625" style="3" customWidth="1"/>
-    <col min="13" max="18" width="11.42578125" style="3"/>
+    <col min="2" max="2" width="13.88671875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.88671875" style="3" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" style="3" customWidth="1"/>
+    <col min="9" max="12" width="5.33203125" style="3" customWidth="1"/>
+    <col min="13" max="18" width="11.44140625" style="3"/>
     <col min="19" max="20" width="0" style="3" hidden="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.42578125" style="3"/>
+    <col min="21" max="16384" width="11.44140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="109" t="s">
         <v>28</v>
       </c>
@@ -31198,7 +31241,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="132.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -31212,7 +31255,7 @@
       <c r="K2" s="38"/>
       <c r="L2" s="39"/>
     </row>
-    <row r="3" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -31252,7 +31295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="133" t="s">
         <v>94</v>
       </c>
@@ -31279,7 +31322,7 @@
       <c r="K4" s="17"/>
       <c r="L4" s="22"/>
     </row>
-    <row r="5" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="134"/>
       <c r="B5" s="102"/>
       <c r="C5" s="114"/>
@@ -31307,7 +31350,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="134"/>
       <c r="B6" s="101">
         <v>46218</v>
@@ -31338,7 +31381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="134"/>
       <c r="B7" s="102"/>
       <c r="C7" s="114"/>
@@ -31366,7 +31409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="171" t="s">
         <v>95</v>
       </c>
@@ -31393,7 +31436,7 @@
       <c r="K8" s="19"/>
       <c r="L8" s="28"/>
     </row>
-    <row r="9" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="171"/>
       <c r="B9" s="118"/>
       <c r="C9" s="125"/>
@@ -31415,7 +31458,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="171" t="s">
         <v>25</v>
       </c>
@@ -31442,7 +31485,7 @@
       <c r="K10" s="13"/>
       <c r="L10" s="25"/>
     </row>
-    <row r="11" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="171"/>
       <c r="B11" s="118"/>
       <c r="C11" s="125"/>
@@ -31464,7 +31507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E12" s="130" t="s">
         <v>10</v>
       </c>
@@ -31491,7 +31534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E13" s="131" t="s">
         <v>14</v>
       </c>
@@ -31515,7 +31558,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="I14" s="4">
         <f>IF(I12=$H$12,100,IF($H$12-I12=1,99,IF($H$12-I12=-1,99,IF($H$12-I12=2,98,IF($H$12-I12=-2,98,IF($H$12-I12=3,97,IF($H$12-I12=-3,97,IF($H$12-I12=4,96,IF($H$12-I12=-4,96,IF($H$12-I12=5,95,IF($H$12-I12=-5,95,IF($H$12-I12=6,94,IF($H$12-I12=-6,94,IF($H$12-I12=7,93,IF($H$12-I12=-7,93,IF($H$12-I12=8,92,IF($H$12-I12=-8,92,IF($H$12-I12=9,91,IF($H$12-I12=-9,91,IF($H$12-I12=10,90,IF($H$12-I12=-10,90,IF($H$12-I12=11,89,IF($H$12-I12=-11,89,IF($H$12-I12=12,88,IF($H$12-I12=-12,88,IF($H$12-I12=13,87,IF($H$12-I12=-13,87,IF($H$12-I12=14,86,IF($H$12-I12=-14,86,IF($H$12-I12=15,85,IF($H$12-I12=-15,85,IF($H$12-I12=16,84,IF($H$12-I12=-16,84,IF($H$12-I12=17,83,IF($H$12-I12=-17,83,IF($H$12-I12=18,82,IF($H$12-I12=-18,82,IF($H$12-I12=19,81,IF($H$12-I12=-19,81,IF($H$12-I12=20,80,IF($H$12-I12=-20,80,IF($H$12-I12=21,79,IF($H$12-I12=-21,79,IF($H$12-I12=22,78,IF($H$12-I12=-22,78,IF($H$12-I12=23,77,IF($H$12-I12=-23,77,IF($H$12-I12=24,76,IF($H$12-I12=-24,76,IF($H$12-I12=25,75,IF($H$12-I12=-25,75,IF($H$12-I12=26,74,IF($H$12-I12=-26,74,IF($H$12-I12=27,73,IF($H$12-I12=-27,73,IF($H$12-I12=28,72,IF($H$12-I12=-28,72,IF($H$12-I12=29,71,IF($H$12-I12=-29,71,IF($H$12-I12=30,70,IF($H$12-I12=-30,70,IF($H$12-I12=31,69,IF($H$12-I12=-31,69,IF($H$12-I12=32,68,IF($H$12-I12=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>100</v>
@@ -31533,7 +31576,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="I15" s="4">
         <f>IF($H$12-I12=33,67,IF($H$12-I12=-33,67,IF($H$12-I12=34,66,IF($H$12-I12=-34,66,IF($H$12-I12=35,65,IF($H$12-I12=-35,65,IF($H$12-I12=36,64,IF($H$12-I12=-36,64,IF($H$12-I12=37,63,IF($H$12-I12=-37,63,IF($H$12-I12=38,62,IF($H$12-I12=-38,62,IF($H$12-I12=39,61,IF($H$12-I12=-39,61,IF($H$12-I12=40,60,IF($H$12-I12=-40,60,IF($H$12-I12=41,59,IF($H$12-I12=-41,59,IF($H$12-I12=42,58,IF($H$12-I12=-42,58,IF($H$12-I12=43,57,IF($H$12-I12=-43,57,IF($H$12-I12=44,56,IF($H$12-I12=-44,56,IF($H$12-I12=45,55,IF($H$12-I12=-45,55,IF($H$12-I12=46,54,IF($H$12-I12=-46,54,IF($H$12-I12=47,53,IF($H$12-I12=-47,53,IF($H$12-I12=48,52,IF($H$12-I12=-48,52,IF($H$12-I12=49,51,IF($H$12-I12=-49,51,IF($H$12-I12=50,50,IF($H$12-I12=-50,50,IF($H$12-I12=51,49,IF($H$12-I12=-51,49,IF($H$12-I12=52,48,IF($H$12-I12=-52,48,IF($H$12-I12=53,47,IF($H$12-I12=-53,47,IF($H$12-I12=54,46,IF($H$12-I12=-54,46,IF($H$12-I12=55,45,IF($H$12-I12=-55,45,IF($H$12-I12=56,44,IF($H$12-I12=-56,44,IF($H$12-I12=57,43,IF($H$12-I12=-57,43,IF($H$12-I12=58,42,IF($H$12-I12=-58,42,IF($H$12-I12=59,41,IF($H$12-I12=-59,41,IF($H$12-I12=60,40,IF($H$12-I12=-60,40,IF($H$12-I12=61,39,IF($H$12-I12=-61,39,IF($H$12-I12=62,38,IF($H$12-I12=-62,38,IF($H$12-I12=63,37,IF($H$12-I12=-63,37,IF($H$12-I12=64,36,IF($H$12-I12=-64,36,IF($H$12-I12=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -31551,7 +31594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="I16" s="4">
         <f>IF($H$12-I12=-65,35,IF($H$12-I12=66,34,IF($H$12-I12=-66,34,IF($H$12-I12=67,33,IF($H$12-I12=-67,33,IF($H$12-I12=68,32,IF($H$12-I12=-68,32,IF($H$12-I12=69,31,IF($H$12-I12=-69,31,IF($H$12-I12=70,30,IF($H$12-I12=-70,30,IF($H$12-I12=71,29,IF($H$12-I12=-71,29,IF($H$12-I12=72,28,IF($H$12-I12=-72,28,IF($H$12-I12=73,27,IF($H$12-I12=-73,27,IF($H$12-I12=74,26,IF($H$12-I12=-74,26,IF($H$12-I12=75,25,IF($H$12-I12=-75,25,IF($H$12-I12=76,24,IF($H$12-I12=-76,24,IF($H$12-I12=77,23,IF($H$12-I12=-77,23,IF($H$12-I12=78,22,IF($H$12-I12=-78,22,IF($H$12-I12=79,21,IF($H$12-I12=-79,21,IF($H$12-I12=80,20,IF($H$12-I12=-80,20,IF($H$12-I12=81,19,IF($H$12-I12=-81,19,IF($H$12-I12=82,18,IF($H$12-I12=-82,18,IF($H$12-I12=83,17,IF($H$12-I12=-83,17,IF($H$12-I12=84,16,IF($H$12-I12=-84,16,IF($H$12-I12=85,15,IF($H$12-I12=-85,15,IF($H$12-I12=86,14,IF($H$12-I12=-86,14,IF($H$12-I12=87,13,IF($H$12-I12=-87,13,IF($H$12-I12=88,12,IF($H$12-I12=-88,12,IF($H$12-I12=89,11,IF($H$12-I12=-89,11,IF($H$12-I12=90,10,IF($H$12-I12=-90,10,IF($H$12-I12=91,9,IF($H$12-I12=-91,9,IF($H$12-I12=92,8,IF($H$12-I12=-92,8,IF($H$12-I12=93,7,IF($H$12-I12=-93,7,IF($H$12-I12=94,6,IF($H$12-I12=-94,6,IF($H$12-I12=95,5,IF($H$12-I12=-95,5,IF($H$12-I12=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
@@ -31569,7 +31612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:12" x14ac:dyDescent="0.3">
       <c r="I17" s="4">
         <f>IF($H$12-I12=-96,4,IF($H$12-I12=97,3,IF($H$12-I12=-97,3,IF($H$12-I12=98,2,IF($H$12-I12=-98,2,IF($H$12-I12=99,1,IF($H$12-I12=-99,1,IF($H$12-I12=100,0,IF($H$12-I12=-100,0,0)))))))))</f>
         <v>0</v>
@@ -31587,25 +31630,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D18" s="132"/>
       <c r="E18" s="132"/>
       <c r="F18" s="132"/>
       <c r="G18" s="132"/>
     </row>
-    <row r="19" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D19" s="132"/>
       <c r="E19" s="132"/>
       <c r="F19" s="132"/>
       <c r="G19" s="132"/>
     </row>
-    <row r="20" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D20" s="132"/>
       <c r="E20" s="132"/>
       <c r="F20" s="132"/>
       <c r="G20" s="132"/>
     </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I41" s="3">
         <v>1</v>
       </c>
@@ -31670,14 +31713,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B1:O99"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="11.42578125" style="1"/>
-    <col min="7" max="7" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="6" width="11.44140625" style="1"/>
+    <col min="7" max="7" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
@@ -31723,7 +31766,7 @@
         <v>SI(G28-H28=-2;98;</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
@@ -31766,7 +31809,7 @@
         <v>SI(G28-H28=-3;97;</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
@@ -31809,7 +31852,7 @@
         <v>SI(G28-H28=-4;96;</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
@@ -31852,7 +31895,7 @@
         <v>SI(G28-H28=-5;95;</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
@@ -31895,7 +31938,7 @@
         <v>SI(G28-H28=-6;94;</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
@@ -31938,7 +31981,7 @@
         <v>SI(G28-H28=-7;93;</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
@@ -31981,7 +32024,7 @@
         <v>SI(G28-H28=-8;92;</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
@@ -32024,7 +32067,7 @@
         <v>SI(G28-H28=-9;91;</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
@@ -32067,7 +32110,7 @@
         <v>SI(G28-H28=-10;90;</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
@@ -32110,7 +32153,7 @@
         <v>SI(G28-H28=-11;89;</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
@@ -32153,7 +32196,7 @@
         <v>SI(G28-H28=-12;88;</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
@@ -32196,7 +32239,7 @@
         <v>SI(G28-H28=-13;87;</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
@@ -32239,7 +32282,7 @@
         <v>SI(G28-H28=-14;86;</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
@@ -32282,7 +32325,7 @@
         <v>SI(G28-H28=-15;85;</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>11</v>
       </c>
@@ -32325,7 +32368,7 @@
         <v>SI(G28-H28=-16;84;</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
@@ -32368,7 +32411,7 @@
         <v>SI(G28-H28=-17;83;</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>11</v>
       </c>
@@ -32411,7 +32454,7 @@
         <v>SI(G28-H28=-18;82;</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
@@ -32454,7 +32497,7 @@
         <v>SI(G28-H28=-19;81;</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
@@ -32497,7 +32540,7 @@
         <v>SI(G28-H28=-20;80;</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>11</v>
       </c>
@@ -32540,7 +32583,7 @@
         <v>SI(G28-H28=-21;79;</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>11</v>
       </c>
@@ -32583,7 +32626,7 @@
         <v>SI(G28-H28=-22;78;</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>11</v>
       </c>
@@ -32626,7 +32669,7 @@
         <v>SI(G28-H28=-23;77;</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>11</v>
       </c>
@@ -32669,7 +32712,7 @@
         <v>SI(G28-H28=-24;76;</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
@@ -32712,7 +32755,7 @@
         <v>SI(G28-H28=-25;75;</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>11</v>
       </c>
@@ -32755,7 +32798,7 @@
         <v>SI(G28-H28=-26;74;</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>11</v>
       </c>
@@ -32798,7 +32841,7 @@
         <v>SI(G28-H28=-27;73;</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>11</v>
       </c>
@@ -32841,7 +32884,7 @@
         <v>SI(G28-H28=-28;72;</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>11</v>
       </c>
@@ -32884,7 +32927,7 @@
         <v>SI(G28-H28=-29;71;</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>11</v>
       </c>
@@ -32927,7 +32970,7 @@
         <v>SI(G28-H28=-30;70;</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>11</v>
       </c>
@@ -32970,7 +33013,7 @@
         <v>SI(G28-H28=-31;69;</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>11</v>
       </c>
@@ -33013,7 +33056,7 @@
         <v>SI(G28-H28=-32;68;</v>
       </c>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>11</v>
       </c>
@@ -33056,7 +33099,7 @@
         <v>SI(G28-H28=-33;67;</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>11</v>
       </c>
@@ -33099,7 +33142,7 @@
         <v>SI(G28-H28=-34;66;</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
@@ -33142,7 +33185,7 @@
         <v>SI(G28-H28=-35;65;</v>
       </c>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>11</v>
       </c>
@@ -33185,7 +33228,7 @@
         <v>SI(G28-H28=-36;64;</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
         <v>11</v>
       </c>
@@ -33228,7 +33271,7 @@
         <v>SI(G28-H28=-37;63;</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
         <v>11</v>
       </c>
@@ -33271,7 +33314,7 @@
         <v>SI(G28-H28=-38;62;</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
         <v>11</v>
       </c>
@@ -33314,7 +33357,7 @@
         <v>SI(G28-H28=-39;61;</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
         <v>11</v>
       </c>
@@ -33357,7 +33400,7 @@
         <v>SI(G28-H28=-40;60;</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
         <v>11</v>
       </c>
@@ -33400,7 +33443,7 @@
         <v>SI(G28-H28=-41;59;</v>
       </c>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
         <v>11</v>
       </c>
@@ -33443,7 +33486,7 @@
         <v>SI(G28-H28=-42;58;</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
         <v>11</v>
       </c>
@@ -33486,7 +33529,7 @@
         <v>SI(G28-H28=-43;57;</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
         <v>11</v>
       </c>
@@ -33529,7 +33572,7 @@
         <v>SI(G28-H28=-44;56;</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
         <v>11</v>
       </c>
@@ -33572,7 +33615,7 @@
         <v>SI(G28-H28=-45;55;</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
         <v>11</v>
       </c>
@@ -33615,7 +33658,7 @@
         <v>SI(G28-H28=-46;54;</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
         <v>11</v>
       </c>
@@ -33658,7 +33701,7 @@
         <v>SI(G28-H28=-47;53;</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
         <v>11</v>
       </c>
@@ -33701,7 +33744,7 @@
         <v>SI(G28-H28=-48;52;</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
         <v>11</v>
       </c>
@@ -33744,7 +33787,7 @@
         <v>SI(G28-H28=-49;51;</v>
       </c>
     </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
@@ -33787,7 +33830,7 @@
         <v>SI(G28-H28=-50;50;</v>
       </c>
     </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
         <v>11</v>
       </c>
@@ -33830,7 +33873,7 @@
         <v>SI(G28-H28=-51;49;</v>
       </c>
     </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
         <v>11</v>
       </c>
@@ -33873,7 +33916,7 @@
         <v>SI(G28-H28=-52;48;</v>
       </c>
     </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
         <v>11</v>
       </c>
@@ -33916,7 +33959,7 @@
         <v>SI(G28-H28=-53;47;</v>
       </c>
     </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
         <v>11</v>
       </c>
@@ -33959,7 +34002,7 @@
         <v>SI(G28-H28=-54;46;</v>
       </c>
     </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
         <v>11</v>
       </c>
@@ -34002,7 +34045,7 @@
         <v>SI(G28-H28=-55;45;</v>
       </c>
     </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
         <v>11</v>
       </c>
@@ -34045,7 +34088,7 @@
         <v>SI(G28-H28=-56;44;</v>
       </c>
     </row>
-    <row r="56" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
         <v>11</v>
       </c>
@@ -34088,7 +34131,7 @@
         <v>SI(G28-H28=-57;43;</v>
       </c>
     </row>
-    <row r="57" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
         <v>11</v>
       </c>
@@ -34131,7 +34174,7 @@
         <v>SI(G28-H28=-58;42;</v>
       </c>
     </row>
-    <row r="58" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
         <v>11</v>
       </c>
@@ -34174,7 +34217,7 @@
         <v>SI(G28-H28=-59;41;</v>
       </c>
     </row>
-    <row r="59" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
         <v>11</v>
       </c>
@@ -34217,7 +34260,7 @@
         <v>SI(G28-H28=-60;40;</v>
       </c>
     </row>
-    <row r="60" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
         <v>11</v>
       </c>
@@ -34260,7 +34303,7 @@
         <v>SI(G28-H28=-61;39;</v>
       </c>
     </row>
-    <row r="61" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
         <v>11</v>
       </c>
@@ -34303,7 +34346,7 @@
         <v>SI(G28-H28=-62;38;</v>
       </c>
     </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
         <v>11</v>
       </c>
@@ -34346,7 +34389,7 @@
         <v>SI(G28-H28=-63;37;</v>
       </c>
     </row>
-    <row r="63" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
         <v>11</v>
       </c>
@@ -34389,7 +34432,7 @@
         <v>SI(G28-H28=-64;36;</v>
       </c>
     </row>
-    <row r="64" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
         <v>11</v>
       </c>
@@ -34432,7 +34475,7 @@
         <v>SI(G28-H28=-65;35;</v>
       </c>
     </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
         <v>11</v>
       </c>
@@ -34475,7 +34518,7 @@
         <v>SI(G28-H28=-66;34;</v>
       </c>
     </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
         <v>11</v>
       </c>
@@ -34518,7 +34561,7 @@
         <v>SI(G28-H28=-67;33;</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
         <v>11</v>
       </c>
@@ -34561,7 +34604,7 @@
         <v>SI(G28-H28=-68;32;</v>
       </c>
     </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
         <v>11</v>
       </c>
@@ -34604,7 +34647,7 @@
         <v>SI(G28-H28=-69;31;</v>
       </c>
     </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
         <v>11</v>
       </c>
@@ -34647,7 +34690,7 @@
         <v>SI(G28-H28=-70;30;</v>
       </c>
     </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
         <v>11</v>
       </c>
@@ -34690,7 +34733,7 @@
         <v>SI(G28-H28=-71;29;</v>
       </c>
     </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
         <v>11</v>
       </c>
@@ -34733,7 +34776,7 @@
         <v>SI(G28-H28=-72;28;</v>
       </c>
     </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
         <v>11</v>
       </c>
@@ -34776,7 +34819,7 @@
         <v>SI(G28-H28=-73;27;</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
         <v>11</v>
       </c>
@@ -34819,7 +34862,7 @@
         <v>SI(G28-H28=-74;26;</v>
       </c>
     </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
         <v>11</v>
       </c>
@@ -34862,7 +34905,7 @@
         <v>SI(G28-H28=-75;25;</v>
       </c>
     </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
         <v>11</v>
       </c>
@@ -34905,7 +34948,7 @@
         <v>SI(G28-H28=-76;24;</v>
       </c>
     </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
         <v>11</v>
       </c>
@@ -34948,7 +34991,7 @@
         <v>SI(G28-H28=-77;23;</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
         <v>11</v>
       </c>
@@ -34991,7 +35034,7 @@
         <v>SI(G28-H28=-78;22;</v>
       </c>
     </row>
-    <row r="78" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
         <v>11</v>
       </c>
@@ -35034,7 +35077,7 @@
         <v>SI(G28-H28=-79;21;</v>
       </c>
     </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
         <v>11</v>
       </c>
@@ -35077,7 +35120,7 @@
         <v>SI(G28-H28=-80;20;</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
         <v>11</v>
       </c>
@@ -35120,7 +35163,7 @@
         <v>SI(G28-H28=-81;19;</v>
       </c>
     </row>
-    <row r="81" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
         <v>11</v>
       </c>
@@ -35163,7 +35206,7 @@
         <v>SI(G28-H28=-82;18;</v>
       </c>
     </row>
-    <row r="82" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
         <v>11</v>
       </c>
@@ -35206,7 +35249,7 @@
         <v>SI(G28-H28=-83;17;</v>
       </c>
     </row>
-    <row r="83" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
         <v>11</v>
       </c>
@@ -35249,7 +35292,7 @@
         <v>SI(G28-H28=-84;16;</v>
       </c>
     </row>
-    <row r="84" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
         <v>11</v>
       </c>
@@ -35292,7 +35335,7 @@
         <v>SI(G28-H28=-85;15;</v>
       </c>
     </row>
-    <row r="85" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
         <v>11</v>
       </c>
@@ -35335,7 +35378,7 @@
         <v>SI(G28-H28=-86;14;</v>
       </c>
     </row>
-    <row r="86" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
         <v>11</v>
       </c>
@@ -35378,7 +35421,7 @@
         <v>SI(G28-H28=-87;13;</v>
       </c>
     </row>
-    <row r="87" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
         <v>11</v>
       </c>
@@ -35421,7 +35464,7 @@
         <v>SI(G28-H28=-88;12;</v>
       </c>
     </row>
-    <row r="88" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
         <v>11</v>
       </c>
@@ -35464,7 +35507,7 @@
         <v>SI(G28-H28=-89;11;</v>
       </c>
     </row>
-    <row r="89" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
         <v>11</v>
       </c>
@@ -35507,7 +35550,7 @@
         <v>SI(G28-H28=-90;10;</v>
       </c>
     </row>
-    <row r="90" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
         <v>11</v>
       </c>
@@ -35550,7 +35593,7 @@
         <v>SI(G28-H28=-91;9;</v>
       </c>
     </row>
-    <row r="91" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
         <v>11</v>
       </c>
@@ -35593,7 +35636,7 @@
         <v>SI(G28-H28=-92;8;</v>
       </c>
     </row>
-    <row r="92" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
         <v>11</v>
       </c>
@@ -35636,7 +35679,7 @@
         <v>SI(G28-H28=-93;7;</v>
       </c>
     </row>
-    <row r="93" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
         <v>11</v>
       </c>
@@ -35679,7 +35722,7 @@
         <v>SI(G28-H28=-94;6;</v>
       </c>
     </row>
-    <row r="94" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
         <v>11</v>
       </c>
@@ -35722,7 +35765,7 @@
         <v>SI(G28-H28=-95;5;</v>
       </c>
     </row>
-    <row r="95" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
         <v>11</v>
       </c>
@@ -35765,7 +35808,7 @@
         <v>SI(G28-H28=-96;4;</v>
       </c>
     </row>
-    <row r="96" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
         <v>11</v>
       </c>
@@ -35808,7 +35851,7 @@
         <v>SI(G28-H28=-97;3;</v>
       </c>
     </row>
-    <row r="97" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
         <v>11</v>
       </c>
@@ -35851,7 +35894,7 @@
         <v>SI(G28-H28=-98;2;</v>
       </c>
     </row>
-    <row r="98" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
         <v>11</v>
       </c>
@@ -35894,7 +35937,7 @@
         <v>SI(G28-H28=-99;1;</v>
       </c>
     </row>
-    <row r="99" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
         <v>11</v>
       </c>
